--- a/api/xlsx/en/SectorGroup.xlsx
+++ b/api/xlsx/en/SectorGroup.xlsx
@@ -28,15 +28,15 @@
     <t>codeforiati:sector-name</t>
   </si>
   <si>
+    <t>codeforiati:category-name</t>
+  </si>
+  <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
     <t>codeforiati:sector-code</t>
   </si>
   <si>
-    <t>codeforiati:category-name</t>
-  </si>
-  <si>
     <t>110</t>
   </si>
   <si>
@@ -49,15 +49,15 @@
     <t>Advanced technical and managerial training</t>
   </si>
   <si>
+    <t>Post-Secondary Education</t>
+  </si>
+  <si>
     <t>114</t>
   </si>
   <si>
     <t>11430</t>
   </si>
   <si>
-    <t>Post-Secondary Education</t>
-  </si>
-  <si>
     <t>120</t>
   </si>
   <si>
@@ -67,15 +67,15 @@
     <t>Research for prevention and control of NCDs</t>
   </si>
   <si>
+    <t>Non-communicable diseases (NCDs)</t>
+  </si>
+  <si>
     <t>123</t>
   </si>
   <si>
     <t>12382</t>
   </si>
   <si>
-    <t>Non-communicable diseases (NCDs)</t>
-  </si>
-  <si>
     <t>130</t>
   </si>
   <si>
@@ -109,15 +109,15 @@
     <t>Child soldiers (prevention and demobilisation)</t>
   </si>
   <si>
+    <t>Conflict, Peace &amp; Security</t>
+  </si>
+  <si>
     <t>152</t>
   </si>
   <si>
     <t>15261</t>
   </si>
   <si>
-    <t>Conflict, Peace &amp; Security</t>
-  </si>
-  <si>
     <t>160</t>
   </si>
   <si>
@@ -163,15 +163,15 @@
     <t>Electric mobility infrastructures</t>
   </si>
   <si>
+    <t>Energy distribution</t>
+  </si>
+  <si>
     <t>236</t>
   </si>
   <si>
     <t>23642</t>
   </si>
   <si>
-    <t>Energy distribution</t>
-  </si>
-  <si>
     <t>240</t>
   </si>
   <si>
@@ -205,15 +205,15 @@
     <t>Fishery services</t>
   </si>
   <si>
+    <t>Fishing</t>
+  </si>
+  <si>
     <t>313</t>
   </si>
   <si>
     <t>31391</t>
   </si>
   <si>
-    <t>Fishing</t>
-  </si>
-  <si>
     <t>320</t>
   </si>
   <si>
@@ -223,13 +223,13 @@
     <t>Construction policy and administrative management</t>
   </si>
   <si>
+    <t>Construction</t>
+  </si>
+  <si>
     <t>323</t>
   </si>
   <si>
     <t>32310</t>
-  </si>
-  <si>
-    <t>Construction</t>
   </si>
   <si>
     <t>331</t>
@@ -815,13 +815,13 @@
         <v>22</v>
       </c>
       <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
         <v>20</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>23</v>
-      </c>
-      <c r="G4" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -838,13 +838,13 @@
         <v>26</v>
       </c>
       <c r="E5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" t="s">
         <v>24</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>27</v>
-      </c>
-      <c r="G5" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -884,13 +884,13 @@
         <v>36</v>
       </c>
       <c r="E7" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" t="s">
         <v>34</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>37</v>
-      </c>
-      <c r="G7" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -907,13 +907,13 @@
         <v>40</v>
       </c>
       <c r="E8" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" t="s">
         <v>38</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>41</v>
-      </c>
-      <c r="G8" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -930,13 +930,13 @@
         <v>44</v>
       </c>
       <c r="E9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F9" t="s">
         <v>42</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>45</v>
-      </c>
-      <c r="G9" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -976,13 +976,13 @@
         <v>54</v>
       </c>
       <c r="E11" t="s">
+        <v>53</v>
+      </c>
+      <c r="F11" t="s">
         <v>52</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>55</v>
-      </c>
-      <c r="G11" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -999,13 +999,13 @@
         <v>58</v>
       </c>
       <c r="E12" t="s">
+        <v>57</v>
+      </c>
+      <c r="F12" t="s">
         <v>56</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>59</v>
-      </c>
-      <c r="G12" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1068,13 +1068,13 @@
         <v>74</v>
       </c>
       <c r="E15" t="s">
+        <v>73</v>
+      </c>
+      <c r="F15" t="s">
         <v>72</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>75</v>
-      </c>
-      <c r="G15" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1091,13 +1091,13 @@
         <v>78</v>
       </c>
       <c r="E16" t="s">
+        <v>77</v>
+      </c>
+      <c r="F16" t="s">
         <v>76</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>79</v>
-      </c>
-      <c r="G16" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1114,13 +1114,13 @@
         <v>82</v>
       </c>
       <c r="E17" t="s">
+        <v>81</v>
+      </c>
+      <c r="F17" t="s">
         <v>80</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>83</v>
-      </c>
-      <c r="G17" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1137,13 +1137,13 @@
         <v>86</v>
       </c>
       <c r="E18" t="s">
+        <v>85</v>
+      </c>
+      <c r="F18" t="s">
         <v>84</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>87</v>
-      </c>
-      <c r="G18" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1160,13 +1160,13 @@
         <v>90</v>
       </c>
       <c r="E19" t="s">
+        <v>89</v>
+      </c>
+      <c r="F19" t="s">
         <v>88</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>91</v>
-      </c>
-      <c r="G19" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1183,13 +1183,13 @@
         <v>94</v>
       </c>
       <c r="E20" t="s">
+        <v>93</v>
+      </c>
+      <c r="F20" t="s">
         <v>92</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
         <v>95</v>
-      </c>
-      <c r="G20" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1206,13 +1206,13 @@
         <v>98</v>
       </c>
       <c r="E21" t="s">
+        <v>97</v>
+      </c>
+      <c r="F21" t="s">
         <v>96</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>99</v>
-      </c>
-      <c r="G21" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1229,13 +1229,13 @@
         <v>102</v>
       </c>
       <c r="E22" t="s">
+        <v>101</v>
+      </c>
+      <c r="F22" t="s">
         <v>100</v>
       </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>103</v>
-      </c>
-      <c r="G22" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1252,13 +1252,13 @@
         <v>106</v>
       </c>
       <c r="E23" t="s">
+        <v>105</v>
+      </c>
+      <c r="F23" t="s">
         <v>104</v>
       </c>
-      <c r="F23" t="s">
+      <c r="G23" t="s">
         <v>107</v>
-      </c>
-      <c r="G23" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1275,13 +1275,13 @@
         <v>110</v>
       </c>
       <c r="E24" t="s">
+        <v>109</v>
+      </c>
+      <c r="F24" t="s">
         <v>108</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
         <v>111</v>
-      </c>
-      <c r="G24" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1298,13 +1298,13 @@
         <v>114</v>
       </c>
       <c r="E25" t="s">
+        <v>113</v>
+      </c>
+      <c r="F25" t="s">
         <v>112</v>
       </c>
-      <c r="F25" t="s">
+      <c r="G25" t="s">
         <v>115</v>
-      </c>
-      <c r="G25" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1321,13 +1321,13 @@
         <v>118</v>
       </c>
       <c r="E26" t="s">
+        <v>117</v>
+      </c>
+      <c r="F26" t="s">
         <v>116</v>
       </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
         <v>119</v>
-      </c>
-      <c r="G26" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1344,13 +1344,13 @@
         <v>122</v>
       </c>
       <c r="E27" t="s">
+        <v>121</v>
+      </c>
+      <c r="F27" t="s">
         <v>120</v>
       </c>
-      <c r="F27" t="s">
+      <c r="G27" t="s">
         <v>123</v>
-      </c>
-      <c r="G27" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1367,13 +1367,13 @@
         <v>126</v>
       </c>
       <c r="E28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F28" t="s">
         <v>124</v>
       </c>
-      <c r="F28" t="s">
+      <c r="G28" t="s">
         <v>127</v>
-      </c>
-      <c r="G28" t="s">
-        <v>125</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/en/SectorGroup.xlsx
+++ b/api/xlsx/en/SectorGroup.xlsx
@@ -28,15 +28,15 @@
     <t>codeforiati:sector-name</t>
   </si>
   <si>
+    <t>codeforiati:sector-code</t>
+  </si>
+  <si>
     <t>codeforiati:category-name</t>
   </si>
   <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
-    <t>codeforiati:sector-code</t>
-  </si>
-  <si>
     <t>110</t>
   </si>
   <si>
@@ -49,15 +49,15 @@
     <t>Advanced technical and managerial training</t>
   </si>
   <si>
+    <t>11430</t>
+  </si>
+  <si>
     <t>Post-Secondary Education</t>
   </si>
   <si>
     <t>114</t>
   </si>
   <si>
-    <t>11430</t>
-  </si>
-  <si>
     <t>120</t>
   </si>
   <si>
@@ -67,15 +67,15 @@
     <t>Research for prevention and control of NCDs</t>
   </si>
   <si>
+    <t>12382</t>
+  </si>
+  <si>
     <t>Non-communicable diseases (NCDs)</t>
   </si>
   <si>
     <t>123</t>
   </si>
   <si>
-    <t>12382</t>
-  </si>
-  <si>
     <t>130</t>
   </si>
   <si>
@@ -109,15 +109,15 @@
     <t>Child soldiers (prevention and demobilisation)</t>
   </si>
   <si>
+    <t>15261</t>
+  </si>
+  <si>
     <t>Conflict, Peace &amp; Security</t>
   </si>
   <si>
     <t>152</t>
   </si>
   <si>
-    <t>15261</t>
-  </si>
-  <si>
     <t>160</t>
   </si>
   <si>
@@ -163,15 +163,15 @@
     <t>Electric mobility infrastructures</t>
   </si>
   <si>
+    <t>23642</t>
+  </si>
+  <si>
     <t>Energy distribution</t>
   </si>
   <si>
     <t>236</t>
   </si>
   <si>
-    <t>23642</t>
-  </si>
-  <si>
     <t>240</t>
   </si>
   <si>
@@ -205,15 +205,15 @@
     <t>Fishery services</t>
   </si>
   <si>
+    <t>31391</t>
+  </si>
+  <si>
     <t>Fishing</t>
   </si>
   <si>
     <t>313</t>
   </si>
   <si>
-    <t>31391</t>
-  </si>
-  <si>
     <t>320</t>
   </si>
   <si>
@@ -223,13 +223,13 @@
     <t>Construction policy and administrative management</t>
   </si>
   <si>
+    <t>32310</t>
+  </si>
+  <si>
     <t>Construction</t>
   </si>
   <si>
     <t>323</t>
-  </si>
-  <si>
-    <t>32310</t>
   </si>
   <si>
     <t>331</t>
@@ -815,13 +815,13 @@
         <v>22</v>
       </c>
       <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" t="s">
         <v>21</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>20</v>
-      </c>
-      <c r="G4" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -838,13 +838,13 @@
         <v>26</v>
       </c>
       <c r="E5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" t="s">
         <v>25</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>24</v>
-      </c>
-      <c r="G5" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -884,13 +884,13 @@
         <v>36</v>
       </c>
       <c r="E7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" t="s">
         <v>35</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>34</v>
-      </c>
-      <c r="G7" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -907,13 +907,13 @@
         <v>40</v>
       </c>
       <c r="E8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F8" t="s">
         <v>39</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>38</v>
-      </c>
-      <c r="G8" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -930,13 +930,13 @@
         <v>44</v>
       </c>
       <c r="E9" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" t="s">
         <v>43</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>42</v>
-      </c>
-      <c r="G9" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -976,13 +976,13 @@
         <v>54</v>
       </c>
       <c r="E11" t="s">
+        <v>55</v>
+      </c>
+      <c r="F11" t="s">
         <v>53</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>52</v>
-      </c>
-      <c r="G11" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -999,13 +999,13 @@
         <v>58</v>
       </c>
       <c r="E12" t="s">
+        <v>59</v>
+      </c>
+      <c r="F12" t="s">
         <v>57</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>56</v>
-      </c>
-      <c r="G12" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1068,13 +1068,13 @@
         <v>74</v>
       </c>
       <c r="E15" t="s">
+        <v>75</v>
+      </c>
+      <c r="F15" t="s">
         <v>73</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>72</v>
-      </c>
-      <c r="G15" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1091,13 +1091,13 @@
         <v>78</v>
       </c>
       <c r="E16" t="s">
+        <v>79</v>
+      </c>
+      <c r="F16" t="s">
         <v>77</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>76</v>
-      </c>
-      <c r="G16" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1114,13 +1114,13 @@
         <v>82</v>
       </c>
       <c r="E17" t="s">
+        <v>83</v>
+      </c>
+      <c r="F17" t="s">
         <v>81</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>80</v>
-      </c>
-      <c r="G17" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1137,13 +1137,13 @@
         <v>86</v>
       </c>
       <c r="E18" t="s">
+        <v>87</v>
+      </c>
+      <c r="F18" t="s">
         <v>85</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>84</v>
-      </c>
-      <c r="G18" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1160,13 +1160,13 @@
         <v>90</v>
       </c>
       <c r="E19" t="s">
+        <v>91</v>
+      </c>
+      <c r="F19" t="s">
         <v>89</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>88</v>
-      </c>
-      <c r="G19" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1183,13 +1183,13 @@
         <v>94</v>
       </c>
       <c r="E20" t="s">
+        <v>95</v>
+      </c>
+      <c r="F20" t="s">
         <v>93</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
         <v>92</v>
-      </c>
-      <c r="G20" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1206,13 +1206,13 @@
         <v>98</v>
       </c>
       <c r="E21" t="s">
+        <v>99</v>
+      </c>
+      <c r="F21" t="s">
         <v>97</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>96</v>
-      </c>
-      <c r="G21" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1229,13 +1229,13 @@
         <v>102</v>
       </c>
       <c r="E22" t="s">
+        <v>103</v>
+      </c>
+      <c r="F22" t="s">
         <v>101</v>
       </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>100</v>
-      </c>
-      <c r="G22" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1252,13 +1252,13 @@
         <v>106</v>
       </c>
       <c r="E23" t="s">
+        <v>107</v>
+      </c>
+      <c r="F23" t="s">
         <v>105</v>
       </c>
-      <c r="F23" t="s">
+      <c r="G23" t="s">
         <v>104</v>
-      </c>
-      <c r="G23" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1275,13 +1275,13 @@
         <v>110</v>
       </c>
       <c r="E24" t="s">
+        <v>111</v>
+      </c>
+      <c r="F24" t="s">
         <v>109</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
         <v>108</v>
-      </c>
-      <c r="G24" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1298,13 +1298,13 @@
         <v>114</v>
       </c>
       <c r="E25" t="s">
+        <v>115</v>
+      </c>
+      <c r="F25" t="s">
         <v>113</v>
       </c>
-      <c r="F25" t="s">
+      <c r="G25" t="s">
         <v>112</v>
-      </c>
-      <c r="G25" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1321,13 +1321,13 @@
         <v>118</v>
       </c>
       <c r="E26" t="s">
+        <v>119</v>
+      </c>
+      <c r="F26" t="s">
         <v>117</v>
       </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
         <v>116</v>
-      </c>
-      <c r="G26" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1344,13 +1344,13 @@
         <v>122</v>
       </c>
       <c r="E27" t="s">
+        <v>123</v>
+      </c>
+      <c r="F27" t="s">
         <v>121</v>
       </c>
-      <c r="F27" t="s">
+      <c r="G27" t="s">
         <v>120</v>
-      </c>
-      <c r="G27" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1367,13 +1367,13 @@
         <v>126</v>
       </c>
       <c r="E28" t="s">
+        <v>127</v>
+      </c>
+      <c r="F28" t="s">
         <v>125</v>
       </c>
-      <c r="F28" t="s">
+      <c r="G28" t="s">
         <v>124</v>
-      </c>
-      <c r="G28" t="s">
-        <v>127</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/en/SectorGroup.xlsx
+++ b/api/xlsx/en/SectorGroup.xlsx
@@ -25,15 +25,15 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:category-name</t>
+  </si>
+  <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
-    <t>codeforiati:category-name</t>
-  </si>
-  <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
@@ -46,15 +46,15 @@
     <t>active</t>
   </si>
   <si>
+    <t>Education, Level Unspecified</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
     <t>111</t>
   </si>
   <si>
-    <t>Education</t>
-  </si>
-  <si>
-    <t>Education, Level Unspecified</t>
-  </si>
-  <si>
     <t>110</t>
   </si>
   <si>
@@ -82,12 +82,12 @@
     <t>Primary education</t>
   </si>
   <si>
+    <t>Basic Education</t>
+  </si>
+  <si>
     <t>112</t>
   </si>
   <si>
-    <t>Basic Education</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -112,12 +112,12 @@
     <t>Secondary education</t>
   </si>
   <si>
+    <t>Secondary Education</t>
+  </si>
+  <si>
     <t>113</t>
   </si>
   <si>
-    <t>Secondary Education</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
@@ -130,12 +130,12 @@
     <t>Higher education</t>
   </si>
   <si>
+    <t>Post-Secondary Education</t>
+  </si>
+  <si>
     <t>114</t>
   </si>
   <si>
-    <t>Post-Secondary Education</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -148,15 +148,15 @@
     <t>Health policy and administrative management</t>
   </si>
   <si>
+    <t>Health, General</t>
+  </si>
+  <si>
+    <t>Health</t>
+  </si>
+  <si>
     <t>121</t>
   </si>
   <si>
-    <t>Health</t>
-  </si>
-  <si>
-    <t>Health, General</t>
-  </si>
-  <si>
     <t>120</t>
   </si>
   <si>
@@ -184,12 +184,12 @@
     <t>Basic health care</t>
   </si>
   <si>
+    <t>Basic Health</t>
+  </si>
+  <si>
     <t>122</t>
   </si>
   <si>
-    <t>Basic Health</t>
-  </si>
-  <si>
     <t>12230</t>
   </si>
   <si>
@@ -238,12 +238,12 @@
     <t>NCDs control, general</t>
   </si>
   <si>
+    <t>Non-communicable diseases (NCDs)</t>
+  </si>
+  <si>
     <t>123</t>
   </si>
   <si>
-    <t>Non-communicable diseases (NCDs)</t>
-  </si>
-  <si>
     <t>12320</t>
   </si>
   <si>
@@ -280,12 +280,12 @@
     <t>Population policy and administrative management</t>
   </si>
   <si>
+    <t>Population Policies/Programmes &amp; Reproductive Health</t>
+  </si>
+  <si>
     <t>130</t>
   </si>
   <si>
-    <t>Population Policies/Programmes &amp; Reproductive Health</t>
-  </si>
-  <si>
     <t>13020</t>
   </si>
   <si>
@@ -316,12 +316,12 @@
     <t>Water sector policy and administrative management</t>
   </si>
   <si>
+    <t>Water Supply &amp; Sanitation</t>
+  </si>
+  <si>
     <t>140</t>
   </si>
   <si>
-    <t>Water Supply &amp; Sanitation</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -388,15 +388,15 @@
     <t>Public sector policy and administrative management</t>
   </si>
   <si>
+    <t>Government &amp; Civil Society-general</t>
+  </si>
+  <si>
+    <t>Government &amp; Civil Society</t>
+  </si>
+  <si>
     <t>151</t>
   </si>
   <si>
-    <t>Government &amp; Civil Society</t>
-  </si>
-  <si>
-    <t>Government &amp; Civil Society-general</t>
-  </si>
-  <si>
     <t>150</t>
   </si>
   <si>
@@ -496,12 +496,12 @@
     <t>Security system management and reform</t>
   </si>
   <si>
+    <t>Conflict, Peace &amp; Security</t>
+  </si>
+  <si>
     <t>152</t>
   </si>
   <si>
-    <t>Conflict, Peace &amp; Security</t>
-  </si>
-  <si>
     <t>15220</t>
   </si>
   <si>
@@ -538,12 +538,12 @@
     <t>Social Protection</t>
   </si>
   <si>
+    <t>Other Social Infrastructure &amp; Services</t>
+  </si>
+  <si>
     <t>160</t>
   </si>
   <si>
-    <t>Other Social Infrastructure &amp; Services</t>
-  </si>
-  <si>
     <t>16020</t>
   </si>
   <si>
@@ -610,12 +610,12 @@
     <t>Transport policy and administrative management</t>
   </si>
   <si>
+    <t>Transport &amp; Storage</t>
+  </si>
+  <si>
     <t>210</t>
   </si>
   <si>
-    <t>Transport &amp; Storage</t>
-  </si>
-  <si>
     <t>21020</t>
   </si>
   <si>
@@ -658,12 +658,12 @@
     <t>Communications policy and administrative management</t>
   </si>
   <si>
+    <t>Communications</t>
+  </si>
+  <si>
     <t>220</t>
   </si>
   <si>
-    <t>Communications</t>
-  </si>
-  <si>
     <t>22020</t>
   </si>
   <si>
@@ -688,15 +688,15 @@
     <t>Energy policy and administrative management</t>
   </si>
   <si>
+    <t>Energy Policy</t>
+  </si>
+  <si>
+    <t>Energy</t>
+  </si>
+  <si>
     <t>231</t>
   </si>
   <si>
-    <t>Energy</t>
-  </si>
-  <si>
-    <t>Energy Policy</t>
-  </si>
-  <si>
     <t>230</t>
   </si>
   <si>
@@ -724,12 +724,12 @@
     <t>Energy generation, renewable sources - multiple technologies</t>
   </si>
   <si>
+    <t>Energy generation, renewable sources</t>
+  </si>
+  <si>
     <t>232</t>
   </si>
   <si>
-    <t>Energy generation, renewable sources</t>
-  </si>
-  <si>
     <t>23220</t>
   </si>
   <si>
@@ -784,12 +784,12 @@
     <t>Energy generation, non-renewable sources, unspecified</t>
   </si>
   <si>
+    <t>Energy generation, non-renewable sources</t>
+  </si>
+  <si>
     <t>233</t>
   </si>
   <si>
-    <t>Energy generation, non-renewable sources</t>
-  </si>
-  <si>
     <t>23320</t>
   </si>
   <si>
@@ -826,36 +826,36 @@
     <t>Hybrid energy electric power plants</t>
   </si>
   <si>
+    <t>Hybrid energy plants</t>
+  </si>
+  <si>
     <t>234</t>
   </si>
   <si>
-    <t>Hybrid energy plants</t>
-  </si>
-  <si>
     <t>23510</t>
   </si>
   <si>
     <t>Nuclear energy electric power plants and nuclear safety</t>
   </si>
   <si>
+    <t>Nuclear energy plants</t>
+  </si>
+  <si>
     <t>235</t>
   </si>
   <si>
-    <t>Nuclear energy plants</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
     <t>Heat plants</t>
   </si>
   <si>
+    <t>Energy distribution</t>
+  </si>
+  <si>
     <t>236</t>
   </si>
   <si>
-    <t>Energy distribution</t>
-  </si>
-  <si>
     <t>23620</t>
   </si>
   <si>
@@ -898,12 +898,12 @@
     <t>Financial policy and administrative management</t>
   </si>
   <si>
+    <t>Banking &amp; Financial Services</t>
+  </si>
+  <si>
     <t>240</t>
   </si>
   <si>
-    <t>Banking &amp; Financial Services</t>
-  </si>
-  <si>
     <t>24020</t>
   </si>
   <si>
@@ -940,12 +940,12 @@
     <t>Business policy and administration</t>
   </si>
   <si>
+    <t>Business &amp; Other Services</t>
+  </si>
+  <si>
     <t>250</t>
   </si>
   <si>
-    <t>Business &amp; Other Services</t>
-  </si>
-  <si>
     <t>25020</t>
   </si>
   <si>
@@ -970,15 +970,15 @@
     <t>Agricultural policy and administrative management</t>
   </si>
   <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
+    <t>Agriculture, Forestry, Fishing</t>
+  </si>
+  <si>
     <t>311</t>
   </si>
   <si>
-    <t>Agriculture, Forestry, Fishing</t>
-  </si>
-  <si>
-    <t>Agriculture</t>
-  </si>
-  <si>
     <t>310</t>
   </si>
   <si>
@@ -1090,12 +1090,12 @@
     <t>Forestry policy and administrative management</t>
   </si>
   <si>
+    <t>Forestry</t>
+  </si>
+  <si>
     <t>312</t>
   </si>
   <si>
-    <t>Forestry</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -1132,12 +1132,12 @@
     <t>Fishing policy and administrative management</t>
   </si>
   <si>
+    <t>Fishing</t>
+  </si>
+  <si>
     <t>313</t>
   </si>
   <si>
-    <t>Fishing</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -1168,15 +1168,15 @@
     <t>Industrial policy and administrative management</t>
   </si>
   <si>
+    <t>Industry</t>
+  </si>
+  <si>
+    <t>Industry, Mining, Construction</t>
+  </si>
+  <si>
     <t>321</t>
   </si>
   <si>
-    <t>Industry, Mining, Construction</t>
-  </si>
-  <si>
-    <t>Industry</t>
-  </si>
-  <si>
     <t>320</t>
   </si>
   <si>
@@ -1294,12 +1294,12 @@
     <t>Mineral/mining policy and administrative management</t>
   </si>
   <si>
+    <t>Mineral Resources &amp; Mining</t>
+  </si>
+  <si>
     <t>322</t>
   </si>
   <si>
-    <t>Mineral Resources &amp; Mining</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -1360,24 +1360,24 @@
     <t>Construction policy and administrative management</t>
   </si>
   <si>
+    <t>Construction</t>
+  </si>
+  <si>
     <t>323</t>
   </si>
   <si>
-    <t>Construction</t>
-  </si>
-  <si>
     <t>33110</t>
   </si>
   <si>
     <t>Trade policy and administrative management</t>
   </si>
   <si>
+    <t>Trade Policies &amp; Regulations</t>
+  </si>
+  <si>
     <t>331</t>
   </si>
   <si>
-    <t>Trade Policies &amp; Regulations</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1414,24 +1414,24 @@
     <t>Tourism policy and administrative management</t>
   </si>
   <si>
+    <t>Tourism</t>
+  </si>
+  <si>
     <t>332</t>
   </si>
   <si>
-    <t>Tourism</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
     <t>Environmental policy and administrative management</t>
   </si>
   <si>
+    <t>General Environment Protection</t>
+  </si>
+  <si>
     <t>410</t>
   </si>
   <si>
-    <t>General Environment Protection</t>
-  </si>
-  <si>
     <t>41020</t>
   </si>
   <si>
@@ -1468,12 +1468,12 @@
     <t>Multisector aid</t>
   </si>
   <si>
+    <t>Other Multisector</t>
+  </si>
+  <si>
     <t>430</t>
   </si>
   <si>
-    <t>Other Multisector</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -1534,36 +1534,36 @@
     <t>General budget support-related aid</t>
   </si>
   <si>
+    <t>General Budget Support</t>
+  </si>
+  <si>
     <t>510</t>
   </si>
   <si>
-    <t>General Budget Support</t>
-  </si>
-  <si>
     <t>52010</t>
   </si>
   <si>
     <t>Food assistance</t>
   </si>
   <si>
+    <t>Development Food Assistance</t>
+  </si>
+  <si>
     <t>520</t>
   </si>
   <si>
-    <t>Development Food Assistance</t>
-  </si>
-  <si>
     <t>53030</t>
   </si>
   <si>
     <t>Import support (capital goods)</t>
   </si>
   <si>
+    <t>Other Commodity Assistance</t>
+  </si>
+  <si>
     <t>530</t>
   </si>
   <si>
-    <t>Other Commodity Assistance</t>
-  </si>
-  <si>
     <t>53040</t>
   </si>
   <si>
@@ -1576,12 +1576,12 @@
     <t>Action relating to debt</t>
   </si>
   <si>
+    <t>Action Relating to Debt</t>
+  </si>
+  <si>
     <t>600</t>
   </si>
   <si>
-    <t>Action Relating to Debt</t>
-  </si>
-  <si>
     <t>60020</t>
   </si>
   <si>
@@ -1624,12 +1624,12 @@
     <t>Material relief assistance and services</t>
   </si>
   <si>
+    <t>Emergency Response</t>
+  </si>
+  <si>
     <t>720</t>
   </si>
   <si>
-    <t>Emergency Response</t>
-  </si>
-  <si>
     <t>72040</t>
   </si>
   <si>
@@ -1648,58 +1648,58 @@
     <t>Immediate post-emergency reconstruction and rehabilitation</t>
   </si>
   <si>
+    <t>Reconstruction Relief &amp; Rehabilitation</t>
+  </si>
+  <si>
     <t>730</t>
   </si>
   <si>
-    <t>Reconstruction Relief &amp; Rehabilitation</t>
-  </si>
-  <si>
     <t>74020</t>
   </si>
   <si>
     <t>Multi-hazard response preparedness</t>
   </si>
   <si>
+    <t>Disaster Prevention &amp; Preparedness</t>
+  </si>
+  <si>
     <t>740</t>
   </si>
   <si>
-    <t>Disaster Prevention &amp; Preparedness</t>
-  </si>
-  <si>
     <t>91010</t>
   </si>
   <si>
     <t>Administrative costs (non-sector allocable)</t>
   </si>
   <si>
+    <t>Administrative Costs of Donors</t>
+  </si>
+  <si>
     <t>910</t>
   </si>
   <si>
-    <t>Administrative Costs of Donors</t>
-  </si>
-  <si>
     <t>93010</t>
   </si>
   <si>
     <t>Refugees/asylum seekers in donor countries (non-sector allocable)</t>
   </si>
   <si>
+    <t>Refugees in Donor Countries</t>
+  </si>
+  <si>
     <t>930</t>
   </si>
   <si>
-    <t>Refugees in Donor Countries</t>
-  </si>
-  <si>
     <t>99810</t>
   </si>
   <si>
     <t>Sectors not specified</t>
   </si>
   <si>
+    <t>Unallocated / Unspecified</t>
+  </si>
+  <si>
     <t>998</t>
-  </si>
-  <si>
-    <t>Unallocated / Unspecified</t>
   </si>
   <si>
     <t>99820</t>
@@ -2767,13 +2767,13 @@
         <v>88</v>
       </c>
       <c r="E32" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F32" t="s">
         <v>89</v>
       </c>
       <c r="G32" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2790,13 +2790,13 @@
         <v>88</v>
       </c>
       <c r="E33" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F33" t="s">
         <v>89</v>
       </c>
       <c r="G33" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2813,13 +2813,13 @@
         <v>88</v>
       </c>
       <c r="E34" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F34" t="s">
         <v>89</v>
       </c>
       <c r="G34" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2836,13 +2836,13 @@
         <v>88</v>
       </c>
       <c r="E35" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F35" t="s">
         <v>89</v>
       </c>
       <c r="G35" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2859,13 +2859,13 @@
         <v>88</v>
       </c>
       <c r="E36" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F36" t="s">
         <v>89</v>
       </c>
       <c r="G36" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2882,13 +2882,13 @@
         <v>100</v>
       </c>
       <c r="E37" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F37" t="s">
         <v>101</v>
       </c>
       <c r="G37" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2905,13 +2905,13 @@
         <v>100</v>
       </c>
       <c r="E38" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F38" t="s">
         <v>101</v>
       </c>
       <c r="G38" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2928,13 +2928,13 @@
         <v>100</v>
       </c>
       <c r="E39" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F39" t="s">
         <v>101</v>
       </c>
       <c r="G39" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2951,13 +2951,13 @@
         <v>100</v>
       </c>
       <c r="E40" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F40" t="s">
         <v>101</v>
       </c>
       <c r="G40" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2974,13 +2974,13 @@
         <v>100</v>
       </c>
       <c r="E41" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F41" t="s">
         <v>101</v>
       </c>
       <c r="G41" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2997,13 +2997,13 @@
         <v>100</v>
       </c>
       <c r="E42" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F42" t="s">
         <v>101</v>
       </c>
       <c r="G42" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3020,13 +3020,13 @@
         <v>100</v>
       </c>
       <c r="E43" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F43" t="s">
         <v>101</v>
       </c>
       <c r="G43" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3043,13 +3043,13 @@
         <v>100</v>
       </c>
       <c r="E44" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F44" t="s">
         <v>101</v>
       </c>
       <c r="G44" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3066,13 +3066,13 @@
         <v>100</v>
       </c>
       <c r="E45" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F45" t="s">
         <v>101</v>
       </c>
       <c r="G45" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3089,13 +3089,13 @@
         <v>100</v>
       </c>
       <c r="E46" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F46" t="s">
         <v>101</v>
       </c>
       <c r="G46" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3112,13 +3112,13 @@
         <v>100</v>
       </c>
       <c r="E47" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F47" t="s">
         <v>101</v>
       </c>
       <c r="G47" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3641,13 +3641,13 @@
         <v>174</v>
       </c>
       <c r="E70" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F70" t="s">
         <v>175</v>
       </c>
       <c r="G70" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3664,13 +3664,13 @@
         <v>174</v>
       </c>
       <c r="E71" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F71" t="s">
         <v>175</v>
       </c>
       <c r="G71" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3687,13 +3687,13 @@
         <v>174</v>
       </c>
       <c r="E72" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F72" t="s">
         <v>175</v>
       </c>
       <c r="G72" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3710,13 +3710,13 @@
         <v>174</v>
       </c>
       <c r="E73" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F73" t="s">
         <v>175</v>
       </c>
       <c r="G73" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3733,13 +3733,13 @@
         <v>174</v>
       </c>
       <c r="E74" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F74" t="s">
         <v>175</v>
       </c>
       <c r="G74" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3756,13 +3756,13 @@
         <v>174</v>
       </c>
       <c r="E75" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F75" t="s">
         <v>175</v>
       </c>
       <c r="G75" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3779,13 +3779,13 @@
         <v>174</v>
       </c>
       <c r="E76" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F76" t="s">
         <v>175</v>
       </c>
       <c r="G76" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3802,13 +3802,13 @@
         <v>174</v>
       </c>
       <c r="E77" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F77" t="s">
         <v>175</v>
       </c>
       <c r="G77" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3825,13 +3825,13 @@
         <v>174</v>
       </c>
       <c r="E78" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F78" t="s">
         <v>175</v>
       </c>
       <c r="G78" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3848,13 +3848,13 @@
         <v>174</v>
       </c>
       <c r="E79" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F79" t="s">
         <v>175</v>
       </c>
       <c r="G79" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3871,13 +3871,13 @@
         <v>174</v>
       </c>
       <c r="E80" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F80" t="s">
         <v>175</v>
       </c>
       <c r="G80" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3894,13 +3894,13 @@
         <v>198</v>
       </c>
       <c r="E81" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F81" t="s">
         <v>199</v>
       </c>
       <c r="G81" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3917,13 +3917,13 @@
         <v>198</v>
       </c>
       <c r="E82" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F82" t="s">
         <v>199</v>
       </c>
       <c r="G82" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3940,13 +3940,13 @@
         <v>198</v>
       </c>
       <c r="E83" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F83" t="s">
         <v>199</v>
       </c>
       <c r="G83" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3963,13 +3963,13 @@
         <v>198</v>
       </c>
       <c r="E84" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F84" t="s">
         <v>199</v>
       </c>
       <c r="G84" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3986,13 +3986,13 @@
         <v>198</v>
       </c>
       <c r="E85" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F85" t="s">
         <v>199</v>
       </c>
       <c r="G85" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4009,13 +4009,13 @@
         <v>198</v>
       </c>
       <c r="E86" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F86" t="s">
         <v>199</v>
       </c>
       <c r="G86" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4032,13 +4032,13 @@
         <v>198</v>
       </c>
       <c r="E87" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F87" t="s">
         <v>199</v>
       </c>
       <c r="G87" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4055,13 +4055,13 @@
         <v>214</v>
       </c>
       <c r="E88" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F88" t="s">
         <v>215</v>
       </c>
       <c r="G88" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4078,13 +4078,13 @@
         <v>214</v>
       </c>
       <c r="E89" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F89" t="s">
         <v>215</v>
       </c>
       <c r="G89" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4101,13 +4101,13 @@
         <v>214</v>
       </c>
       <c r="E90" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F90" t="s">
         <v>215</v>
       </c>
       <c r="G90" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4124,13 +4124,13 @@
         <v>214</v>
       </c>
       <c r="E91" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F91" t="s">
         <v>215</v>
       </c>
       <c r="G91" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4791,13 +4791,13 @@
         <v>294</v>
       </c>
       <c r="E120" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F120" t="s">
         <v>295</v>
       </c>
       <c r="G120" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4814,13 +4814,13 @@
         <v>294</v>
       </c>
       <c r="E121" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F121" t="s">
         <v>295</v>
       </c>
       <c r="G121" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4837,13 +4837,13 @@
         <v>294</v>
       </c>
       <c r="E122" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F122" t="s">
         <v>295</v>
       </c>
       <c r="G122" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4860,13 +4860,13 @@
         <v>294</v>
       </c>
       <c r="E123" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F123" t="s">
         <v>295</v>
       </c>
       <c r="G123" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4883,13 +4883,13 @@
         <v>294</v>
       </c>
       <c r="E124" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F124" t="s">
         <v>295</v>
       </c>
       <c r="G124" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4906,13 +4906,13 @@
         <v>294</v>
       </c>
       <c r="E125" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F125" t="s">
         <v>295</v>
       </c>
       <c r="G125" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4929,13 +4929,13 @@
         <v>308</v>
       </c>
       <c r="E126" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F126" t="s">
         <v>309</v>
       </c>
       <c r="G126" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4952,13 +4952,13 @@
         <v>308</v>
       </c>
       <c r="E127" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F127" t="s">
         <v>309</v>
       </c>
       <c r="G127" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4975,13 +4975,13 @@
         <v>308</v>
       </c>
       <c r="E128" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F128" t="s">
         <v>309</v>
       </c>
       <c r="G128" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4998,13 +4998,13 @@
         <v>308</v>
       </c>
       <c r="E129" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F129" t="s">
         <v>309</v>
       </c>
       <c r="G129" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -6378,13 +6378,13 @@
         <v>452</v>
       </c>
       <c r="E189" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F189" t="s">
         <v>453</v>
       </c>
       <c r="G189" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6401,13 +6401,13 @@
         <v>452</v>
       </c>
       <c r="E190" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F190" t="s">
         <v>453</v>
       </c>
       <c r="G190" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6424,13 +6424,13 @@
         <v>452</v>
       </c>
       <c r="E191" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F191" t="s">
         <v>453</v>
       </c>
       <c r="G191" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6447,13 +6447,13 @@
         <v>452</v>
       </c>
       <c r="E192" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F192" t="s">
         <v>453</v>
       </c>
       <c r="G192" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6470,13 +6470,13 @@
         <v>452</v>
       </c>
       <c r="E193" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F193" t="s">
         <v>453</v>
       </c>
       <c r="G193" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6493,13 +6493,13 @@
         <v>452</v>
       </c>
       <c r="E194" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F194" t="s">
         <v>453</v>
       </c>
       <c r="G194" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6516,13 +6516,13 @@
         <v>466</v>
       </c>
       <c r="E195" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F195" t="s">
         <v>467</v>
       </c>
       <c r="G195" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6539,13 +6539,13 @@
         <v>470</v>
       </c>
       <c r="E196" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F196" t="s">
         <v>471</v>
       </c>
       <c r="G196" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6562,13 +6562,13 @@
         <v>470</v>
       </c>
       <c r="E197" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F197" t="s">
         <v>471</v>
       </c>
       <c r="G197" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6585,13 +6585,13 @@
         <v>470</v>
       </c>
       <c r="E198" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F198" t="s">
         <v>471</v>
       </c>
       <c r="G198" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6608,13 +6608,13 @@
         <v>470</v>
       </c>
       <c r="E199" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F199" t="s">
         <v>471</v>
       </c>
       <c r="G199" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6631,13 +6631,13 @@
         <v>470</v>
       </c>
       <c r="E200" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F200" t="s">
         <v>471</v>
       </c>
       <c r="G200" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6654,13 +6654,13 @@
         <v>470</v>
       </c>
       <c r="E201" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F201" t="s">
         <v>471</v>
       </c>
       <c r="G201" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6677,13 +6677,13 @@
         <v>484</v>
       </c>
       <c r="E202" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F202" t="s">
         <v>485</v>
       </c>
       <c r="G202" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6700,13 +6700,13 @@
         <v>484</v>
       </c>
       <c r="E203" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F203" t="s">
         <v>485</v>
       </c>
       <c r="G203" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6723,13 +6723,13 @@
         <v>484</v>
       </c>
       <c r="E204" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F204" t="s">
         <v>485</v>
       </c>
       <c r="G204" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6746,13 +6746,13 @@
         <v>484</v>
       </c>
       <c r="E205" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F205" t="s">
         <v>485</v>
       </c>
       <c r="G205" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6769,13 +6769,13 @@
         <v>484</v>
       </c>
       <c r="E206" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F206" t="s">
         <v>485</v>
       </c>
       <c r="G206" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6792,13 +6792,13 @@
         <v>484</v>
       </c>
       <c r="E207" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F207" t="s">
         <v>485</v>
       </c>
       <c r="G207" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6815,13 +6815,13 @@
         <v>484</v>
       </c>
       <c r="E208" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F208" t="s">
         <v>485</v>
       </c>
       <c r="G208" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6838,13 +6838,13 @@
         <v>484</v>
       </c>
       <c r="E209" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F209" t="s">
         <v>485</v>
       </c>
       <c r="G209" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6861,13 +6861,13 @@
         <v>484</v>
       </c>
       <c r="E210" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F210" t="s">
         <v>485</v>
       </c>
       <c r="G210" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6884,13 +6884,13 @@
         <v>484</v>
       </c>
       <c r="E211" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F211" t="s">
         <v>485</v>
       </c>
       <c r="G211" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6907,13 +6907,13 @@
         <v>506</v>
       </c>
       <c r="E212" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="F212" t="s">
         <v>507</v>
       </c>
       <c r="G212" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6930,13 +6930,13 @@
         <v>510</v>
       </c>
       <c r="E213" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F213" t="s">
         <v>511</v>
       </c>
       <c r="G213" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6953,13 +6953,13 @@
         <v>514</v>
       </c>
       <c r="E214" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F214" t="s">
         <v>515</v>
       </c>
       <c r="G214" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6976,13 +6976,13 @@
         <v>514</v>
       </c>
       <c r="E215" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F215" t="s">
         <v>515</v>
       </c>
       <c r="G215" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6999,13 +6999,13 @@
         <v>520</v>
       </c>
       <c r="E216" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F216" t="s">
         <v>521</v>
       </c>
       <c r="G216" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -7022,13 +7022,13 @@
         <v>520</v>
       </c>
       <c r="E217" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F217" t="s">
         <v>521</v>
       </c>
       <c r="G217" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -7045,13 +7045,13 @@
         <v>520</v>
       </c>
       <c r="E218" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F218" t="s">
         <v>521</v>
       </c>
       <c r="G218" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -7068,13 +7068,13 @@
         <v>520</v>
       </c>
       <c r="E219" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F219" t="s">
         <v>521</v>
       </c>
       <c r="G219" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -7091,13 +7091,13 @@
         <v>520</v>
       </c>
       <c r="E220" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F220" t="s">
         <v>521</v>
       </c>
       <c r="G220" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -7114,13 +7114,13 @@
         <v>520</v>
       </c>
       <c r="E221" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F221" t="s">
         <v>521</v>
       </c>
       <c r="G221" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -7137,13 +7137,13 @@
         <v>520</v>
       </c>
       <c r="E222" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F222" t="s">
         <v>521</v>
       </c>
       <c r="G222" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -7160,13 +7160,13 @@
         <v>536</v>
       </c>
       <c r="E223" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F223" t="s">
         <v>537</v>
       </c>
       <c r="G223" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -7183,13 +7183,13 @@
         <v>536</v>
       </c>
       <c r="E224" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F224" t="s">
         <v>537</v>
       </c>
       <c r="G224" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -7206,13 +7206,13 @@
         <v>536</v>
       </c>
       <c r="E225" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F225" t="s">
         <v>537</v>
       </c>
       <c r="G225" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -7229,13 +7229,13 @@
         <v>544</v>
       </c>
       <c r="E226" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F226" t="s">
         <v>545</v>
       </c>
       <c r="G226" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -7252,13 +7252,13 @@
         <v>548</v>
       </c>
       <c r="E227" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="F227" t="s">
         <v>549</v>
       </c>
       <c r="G227" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -7275,13 +7275,13 @@
         <v>552</v>
       </c>
       <c r="E228" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="F228" t="s">
         <v>553</v>
       </c>
       <c r="G228" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -7298,13 +7298,13 @@
         <v>556</v>
       </c>
       <c r="E229" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="F229" t="s">
         <v>557</v>
       </c>
       <c r="G229" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -7321,13 +7321,13 @@
         <v>560</v>
       </c>
       <c r="E230" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="F230" t="s">
         <v>561</v>
       </c>
       <c r="G230" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -7344,13 +7344,13 @@
         <v>560</v>
       </c>
       <c r="E231" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="F231" t="s">
         <v>561</v>
       </c>
       <c r="G231" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/en/SectorGroup.xlsx
+++ b/api/xlsx/en/SectorGroup.xlsx
@@ -25,18 +25,18 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
     <t>codeforiati:category-name</t>
   </si>
   <si>
     <t>codeforiati:group-name</t>
   </si>
   <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -46,18 +46,18 @@
     <t>active</t>
   </si>
   <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
     <t>Education, Level Unspecified</t>
   </si>
   <si>
     <t>Education</t>
   </si>
   <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -82,12 +82,12 @@
     <t>Primary education</t>
   </si>
   <si>
+    <t>112</t>
+  </si>
+  <si>
     <t>Basic Education</t>
   </si>
   <si>
-    <t>112</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -112,12 +112,12 @@
     <t>Secondary education</t>
   </si>
   <si>
+    <t>113</t>
+  </si>
+  <si>
     <t>Secondary Education</t>
   </si>
   <si>
-    <t>113</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
@@ -130,12 +130,12 @@
     <t>Higher education</t>
   </si>
   <si>
+    <t>114</t>
+  </si>
+  <si>
     <t>Post-Secondary Education</t>
   </si>
   <si>
-    <t>114</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -148,18 +148,18 @@
     <t>Health policy and administrative management</t>
   </si>
   <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
     <t>Health, General</t>
   </si>
   <si>
     <t>Health</t>
   </si>
   <si>
-    <t>121</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -184,12 +184,12 @@
     <t>Basic health care</t>
   </si>
   <si>
+    <t>122</t>
+  </si>
+  <si>
     <t>Basic Health</t>
   </si>
   <si>
-    <t>122</t>
-  </si>
-  <si>
     <t>12230</t>
   </si>
   <si>
@@ -238,12 +238,12 @@
     <t>NCDs control, general</t>
   </si>
   <si>
+    <t>123</t>
+  </si>
+  <si>
     <t>Non-communicable diseases (NCDs)</t>
   </si>
   <si>
-    <t>123</t>
-  </si>
-  <si>
     <t>12320</t>
   </si>
   <si>
@@ -280,12 +280,12 @@
     <t>Population policy and administrative management</t>
   </si>
   <si>
+    <t>130</t>
+  </si>
+  <si>
     <t>Population Policies/Programmes &amp; Reproductive Health</t>
   </si>
   <si>
-    <t>130</t>
-  </si>
-  <si>
     <t>13020</t>
   </si>
   <si>
@@ -316,12 +316,12 @@
     <t>Water sector policy and administrative management</t>
   </si>
   <si>
+    <t>140</t>
+  </si>
+  <si>
     <t>Water Supply &amp; Sanitation</t>
   </si>
   <si>
-    <t>140</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -388,18 +388,18 @@
     <t>Public sector policy and administrative management</t>
   </si>
   <si>
+    <t>151</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
     <t>Government &amp; Civil Society-general</t>
   </si>
   <si>
     <t>Government &amp; Civil Society</t>
   </si>
   <si>
-    <t>151</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -496,12 +496,12 @@
     <t>Security system management and reform</t>
   </si>
   <si>
+    <t>152</t>
+  </si>
+  <si>
     <t>Conflict, Peace &amp; Security</t>
   </si>
   <si>
-    <t>152</t>
-  </si>
-  <si>
     <t>15220</t>
   </si>
   <si>
@@ -538,12 +538,12 @@
     <t>Social Protection</t>
   </si>
   <si>
+    <t>160</t>
+  </si>
+  <si>
     <t>Other Social Infrastructure &amp; Services</t>
   </si>
   <si>
-    <t>160</t>
-  </si>
-  <si>
     <t>16020</t>
   </si>
   <si>
@@ -610,12 +610,12 @@
     <t>Transport policy and administrative management</t>
   </si>
   <si>
+    <t>210</t>
+  </si>
+  <si>
     <t>Transport &amp; Storage</t>
   </si>
   <si>
-    <t>210</t>
-  </si>
-  <si>
     <t>21020</t>
   </si>
   <si>
@@ -658,12 +658,12 @@
     <t>Communications policy and administrative management</t>
   </si>
   <si>
+    <t>220</t>
+  </si>
+  <si>
     <t>Communications</t>
   </si>
   <si>
-    <t>220</t>
-  </si>
-  <si>
     <t>22020</t>
   </si>
   <si>
@@ -688,18 +688,18 @@
     <t>Energy policy and administrative management</t>
   </si>
   <si>
+    <t>231</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
     <t>Energy Policy</t>
   </si>
   <si>
     <t>Energy</t>
   </si>
   <si>
-    <t>231</t>
-  </si>
-  <si>
-    <t>230</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -724,12 +724,12 @@
     <t>Energy generation, renewable sources - multiple technologies</t>
   </si>
   <si>
+    <t>232</t>
+  </si>
+  <si>
     <t>Energy generation, renewable sources</t>
   </si>
   <si>
-    <t>232</t>
-  </si>
-  <si>
     <t>23220</t>
   </si>
   <si>
@@ -784,12 +784,12 @@
     <t>Energy generation, non-renewable sources, unspecified</t>
   </si>
   <si>
+    <t>233</t>
+  </si>
+  <si>
     <t>Energy generation, non-renewable sources</t>
   </si>
   <si>
-    <t>233</t>
-  </si>
-  <si>
     <t>23320</t>
   </si>
   <si>
@@ -826,36 +826,36 @@
     <t>Hybrid energy electric power plants</t>
   </si>
   <si>
+    <t>234</t>
+  </si>
+  <si>
     <t>Hybrid energy plants</t>
   </si>
   <si>
-    <t>234</t>
-  </si>
-  <si>
     <t>23510</t>
   </si>
   <si>
     <t>Nuclear energy electric power plants and nuclear safety</t>
   </si>
   <si>
+    <t>235</t>
+  </si>
+  <si>
     <t>Nuclear energy plants</t>
   </si>
   <si>
-    <t>235</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
     <t>Heat plants</t>
   </si>
   <si>
+    <t>236</t>
+  </si>
+  <si>
     <t>Energy distribution</t>
   </si>
   <si>
-    <t>236</t>
-  </si>
-  <si>
     <t>23620</t>
   </si>
   <si>
@@ -898,12 +898,12 @@
     <t>Financial policy and administrative management</t>
   </si>
   <si>
+    <t>240</t>
+  </si>
+  <si>
     <t>Banking &amp; Financial Services</t>
   </si>
   <si>
-    <t>240</t>
-  </si>
-  <si>
     <t>24020</t>
   </si>
   <si>
@@ -940,12 +940,12 @@
     <t>Business policy and administration</t>
   </si>
   <si>
+    <t>250</t>
+  </si>
+  <si>
     <t>Business &amp; Other Services</t>
   </si>
   <si>
-    <t>250</t>
-  </si>
-  <si>
     <t>25020</t>
   </si>
   <si>
@@ -970,18 +970,18 @@
     <t>Agricultural policy and administrative management</t>
   </si>
   <si>
+    <t>311</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
     <t>Agriculture</t>
   </si>
   <si>
     <t>Agriculture, Forestry, Fishing</t>
   </si>
   <si>
-    <t>311</t>
-  </si>
-  <si>
-    <t>310</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1090,12 +1090,12 @@
     <t>Forestry policy and administrative management</t>
   </si>
   <si>
+    <t>312</t>
+  </si>
+  <si>
     <t>Forestry</t>
   </si>
   <si>
-    <t>312</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -1132,12 +1132,12 @@
     <t>Fishing policy and administrative management</t>
   </si>
   <si>
+    <t>313</t>
+  </si>
+  <si>
     <t>Fishing</t>
   </si>
   <si>
-    <t>313</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -1168,18 +1168,18 @@
     <t>Industrial policy and administrative management</t>
   </si>
   <si>
+    <t>321</t>
+  </si>
+  <si>
+    <t>320</t>
+  </si>
+  <si>
     <t>Industry</t>
   </si>
   <si>
     <t>Industry, Mining, Construction</t>
   </si>
   <si>
-    <t>321</t>
-  </si>
-  <si>
-    <t>320</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1294,12 +1294,12 @@
     <t>Mineral/mining policy and administrative management</t>
   </si>
   <si>
+    <t>322</t>
+  </si>
+  <si>
     <t>Mineral Resources &amp; Mining</t>
   </si>
   <si>
-    <t>322</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -1360,24 +1360,24 @@
     <t>Construction policy and administrative management</t>
   </si>
   <si>
+    <t>323</t>
+  </si>
+  <si>
     <t>Construction</t>
   </si>
   <si>
-    <t>323</t>
-  </si>
-  <si>
     <t>33110</t>
   </si>
   <si>
     <t>Trade policy and administrative management</t>
   </si>
   <si>
+    <t>331</t>
+  </si>
+  <si>
     <t>Trade Policies &amp; Regulations</t>
   </si>
   <si>
-    <t>331</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1414,24 +1414,24 @@
     <t>Tourism policy and administrative management</t>
   </si>
   <si>
+    <t>332</t>
+  </si>
+  <si>
     <t>Tourism</t>
   </si>
   <si>
-    <t>332</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
     <t>Environmental policy and administrative management</t>
   </si>
   <si>
+    <t>410</t>
+  </si>
+  <si>
     <t>General Environment Protection</t>
   </si>
   <si>
-    <t>410</t>
-  </si>
-  <si>
     <t>41020</t>
   </si>
   <si>
@@ -1468,12 +1468,12 @@
     <t>Multisector aid</t>
   </si>
   <si>
+    <t>430</t>
+  </si>
+  <si>
     <t>Other Multisector</t>
   </si>
   <si>
-    <t>430</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -1534,36 +1534,36 @@
     <t>General budget support-related aid</t>
   </si>
   <si>
+    <t>510</t>
+  </si>
+  <si>
     <t>General Budget Support</t>
   </si>
   <si>
-    <t>510</t>
-  </si>
-  <si>
     <t>52010</t>
   </si>
   <si>
     <t>Food assistance</t>
   </si>
   <si>
+    <t>520</t>
+  </si>
+  <si>
     <t>Development Food Assistance</t>
   </si>
   <si>
-    <t>520</t>
-  </si>
-  <si>
     <t>53030</t>
   </si>
   <si>
     <t>Import support (capital goods)</t>
   </si>
   <si>
+    <t>530</t>
+  </si>
+  <si>
     <t>Other Commodity Assistance</t>
   </si>
   <si>
-    <t>530</t>
-  </si>
-  <si>
     <t>53040</t>
   </si>
   <si>
@@ -1576,12 +1576,12 @@
     <t>Action relating to debt</t>
   </si>
   <si>
+    <t>600</t>
+  </si>
+  <si>
     <t>Action Relating to Debt</t>
   </si>
   <si>
-    <t>600</t>
-  </si>
-  <si>
     <t>60020</t>
   </si>
   <si>
@@ -1624,12 +1624,12 @@
     <t>Material relief assistance and services</t>
   </si>
   <si>
+    <t>720</t>
+  </si>
+  <si>
     <t>Emergency Response</t>
   </si>
   <si>
-    <t>720</t>
-  </si>
-  <si>
     <t>72040</t>
   </si>
   <si>
@@ -1648,58 +1648,58 @@
     <t>Immediate post-emergency reconstruction and rehabilitation</t>
   </si>
   <si>
+    <t>730</t>
+  </si>
+  <si>
     <t>Reconstruction Relief &amp; Rehabilitation</t>
   </si>
   <si>
-    <t>730</t>
-  </si>
-  <si>
     <t>74020</t>
   </si>
   <si>
     <t>Multi-hazard response preparedness</t>
   </si>
   <si>
+    <t>740</t>
+  </si>
+  <si>
     <t>Disaster Prevention &amp; Preparedness</t>
   </si>
   <si>
-    <t>740</t>
-  </si>
-  <si>
     <t>91010</t>
   </si>
   <si>
     <t>Administrative costs (non-sector allocable)</t>
   </si>
   <si>
+    <t>910</t>
+  </si>
+  <si>
     <t>Administrative Costs of Donors</t>
   </si>
   <si>
-    <t>910</t>
-  </si>
-  <si>
     <t>93010</t>
   </si>
   <si>
     <t>Refugees/asylum seekers in donor countries (non-sector allocable)</t>
   </si>
   <si>
+    <t>930</t>
+  </si>
+  <si>
     <t>Refugees in Donor Countries</t>
   </si>
   <si>
-    <t>930</t>
-  </si>
-  <si>
     <t>99810</t>
   </si>
   <si>
     <t>Sectors not specified</t>
   </si>
   <si>
+    <t>998</t>
+  </si>
+  <si>
     <t>Unallocated / Unspecified</t>
-  </si>
-  <si>
-    <t>998</t>
   </si>
   <si>
     <t>99820</t>

--- a/api/xlsx/en/SectorGroup.xlsx
+++ b/api/xlsx/en/SectorGroup.xlsx
@@ -28,12 +28,12 @@
     <t>codeforiati:category-code</t>
   </si>
   <si>
+    <t>codeforiati:category-name</t>
+  </si>
+  <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
-    <t>codeforiati:category-name</t>
-  </si>
-  <si>
     <t>codeforiati:group-name</t>
   </si>
   <si>
@@ -49,12 +49,12 @@
     <t>111</t>
   </si>
   <si>
+    <t>Education, Level Unspecified</t>
+  </si>
+  <si>
     <t>110</t>
   </si>
   <si>
-    <t>Education, Level Unspecified</t>
-  </si>
-  <si>
     <t>Education</t>
   </si>
   <si>
@@ -151,12 +151,12 @@
     <t>121</t>
   </si>
   <si>
+    <t>Health, General</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
-    <t>Health, General</t>
-  </si>
-  <si>
     <t>Health</t>
   </si>
   <si>
@@ -391,12 +391,12 @@
     <t>151</t>
   </si>
   <si>
+    <t>Government &amp; Civil Society-general</t>
+  </si>
+  <si>
     <t>150</t>
   </si>
   <si>
-    <t>Government &amp; Civil Society-general</t>
-  </si>
-  <si>
     <t>Government &amp; Civil Society</t>
   </si>
   <si>
@@ -691,12 +691,12 @@
     <t>231</t>
   </si>
   <si>
+    <t>Energy Policy</t>
+  </si>
+  <si>
     <t>230</t>
   </si>
   <si>
-    <t>Energy Policy</t>
-  </si>
-  <si>
     <t>Energy</t>
   </si>
   <si>
@@ -973,12 +973,12 @@
     <t>311</t>
   </si>
   <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
     <t>310</t>
   </si>
   <si>
-    <t>Agriculture</t>
-  </si>
-  <si>
     <t>Agriculture, Forestry, Fishing</t>
   </si>
   <si>
@@ -1171,10 +1171,10 @@
     <t>321</t>
   </si>
   <si>
+    <t>Industry</t>
+  </si>
+  <si>
     <t>320</t>
-  </si>
-  <si>
-    <t>Industry</t>
   </si>
   <si>
     <t>Industry, Mining, Construction</t>
@@ -2169,10 +2169,10 @@
         <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F6" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G6" t="s">
         <v>13</v>
@@ -2192,10 +2192,10 @@
         <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F7" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G7" t="s">
         <v>13</v>
@@ -2215,10 +2215,10 @@
         <v>22</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F8" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G8" t="s">
         <v>13</v>
@@ -2238,10 +2238,10 @@
         <v>22</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F9" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G9" t="s">
         <v>13</v>
@@ -2261,10 +2261,10 @@
         <v>32</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="F10" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="G10" t="s">
         <v>13</v>
@@ -2284,10 +2284,10 @@
         <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="F11" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="G11" t="s">
         <v>13</v>
@@ -2307,10 +2307,10 @@
         <v>38</v>
       </c>
       <c r="E12" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="F12" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="G12" t="s">
         <v>13</v>
@@ -2330,10 +2330,10 @@
         <v>38</v>
       </c>
       <c r="E13" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="F13" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="G13" t="s">
         <v>13</v>
@@ -2445,10 +2445,10 @@
         <v>56</v>
       </c>
       <c r="E18" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F18" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G18" t="s">
         <v>47</v>
@@ -2468,10 +2468,10 @@
         <v>56</v>
       </c>
       <c r="E19" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F19" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G19" t="s">
         <v>47</v>
@@ -2491,10 +2491,10 @@
         <v>56</v>
       </c>
       <c r="E20" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F20" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G20" t="s">
         <v>47</v>
@@ -2514,10 +2514,10 @@
         <v>56</v>
       </c>
       <c r="E21" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F21" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G21" t="s">
         <v>47</v>
@@ -2537,10 +2537,10 @@
         <v>56</v>
       </c>
       <c r="E22" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F22" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G22" t="s">
         <v>47</v>
@@ -2560,10 +2560,10 @@
         <v>56</v>
       </c>
       <c r="E23" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F23" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G23" t="s">
         <v>47</v>
@@ -2583,10 +2583,10 @@
         <v>56</v>
       </c>
       <c r="E24" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F24" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G24" t="s">
         <v>47</v>
@@ -2606,10 +2606,10 @@
         <v>56</v>
       </c>
       <c r="E25" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F25" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G25" t="s">
         <v>47</v>
@@ -2629,10 +2629,10 @@
         <v>74</v>
       </c>
       <c r="E26" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="F26" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="G26" t="s">
         <v>47</v>
@@ -2652,10 +2652,10 @@
         <v>74</v>
       </c>
       <c r="E27" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="F27" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="G27" t="s">
         <v>47</v>
@@ -2675,10 +2675,10 @@
         <v>74</v>
       </c>
       <c r="E28" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="F28" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="G28" t="s">
         <v>47</v>
@@ -2698,10 +2698,10 @@
         <v>74</v>
       </c>
       <c r="E29" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="F29" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="G29" t="s">
         <v>47</v>
@@ -2721,10 +2721,10 @@
         <v>74</v>
       </c>
       <c r="E30" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="F30" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="G30" t="s">
         <v>47</v>
@@ -2744,10 +2744,10 @@
         <v>74</v>
       </c>
       <c r="E31" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="F31" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="G31" t="s">
         <v>47</v>
@@ -2767,10 +2767,10 @@
         <v>88</v>
       </c>
       <c r="E32" t="s">
+        <v>89</v>
+      </c>
+      <c r="F32" t="s">
         <v>88</v>
-      </c>
-      <c r="F32" t="s">
-        <v>89</v>
       </c>
       <c r="G32" t="s">
         <v>89</v>
@@ -2790,10 +2790,10 @@
         <v>88</v>
       </c>
       <c r="E33" t="s">
+        <v>89</v>
+      </c>
+      <c r="F33" t="s">
         <v>88</v>
-      </c>
-      <c r="F33" t="s">
-        <v>89</v>
       </c>
       <c r="G33" t="s">
         <v>89</v>
@@ -2813,10 +2813,10 @@
         <v>88</v>
       </c>
       <c r="E34" t="s">
+        <v>89</v>
+      </c>
+      <c r="F34" t="s">
         <v>88</v>
-      </c>
-      <c r="F34" t="s">
-        <v>89</v>
       </c>
       <c r="G34" t="s">
         <v>89</v>
@@ -2836,10 +2836,10 @@
         <v>88</v>
       </c>
       <c r="E35" t="s">
+        <v>89</v>
+      </c>
+      <c r="F35" t="s">
         <v>88</v>
-      </c>
-      <c r="F35" t="s">
-        <v>89</v>
       </c>
       <c r="G35" t="s">
         <v>89</v>
@@ -2859,10 +2859,10 @@
         <v>88</v>
       </c>
       <c r="E36" t="s">
+        <v>89</v>
+      </c>
+      <c r="F36" t="s">
         <v>88</v>
-      </c>
-      <c r="F36" t="s">
-        <v>89</v>
       </c>
       <c r="G36" t="s">
         <v>89</v>
@@ -2882,10 +2882,10 @@
         <v>100</v>
       </c>
       <c r="E37" t="s">
+        <v>101</v>
+      </c>
+      <c r="F37" t="s">
         <v>100</v>
-      </c>
-      <c r="F37" t="s">
-        <v>101</v>
       </c>
       <c r="G37" t="s">
         <v>101</v>
@@ -2905,10 +2905,10 @@
         <v>100</v>
       </c>
       <c r="E38" t="s">
+        <v>101</v>
+      </c>
+      <c r="F38" t="s">
         <v>100</v>
-      </c>
-      <c r="F38" t="s">
-        <v>101</v>
       </c>
       <c r="G38" t="s">
         <v>101</v>
@@ -2928,10 +2928,10 @@
         <v>100</v>
       </c>
       <c r="E39" t="s">
+        <v>101</v>
+      </c>
+      <c r="F39" t="s">
         <v>100</v>
-      </c>
-      <c r="F39" t="s">
-        <v>101</v>
       </c>
       <c r="G39" t="s">
         <v>101</v>
@@ -2951,10 +2951,10 @@
         <v>100</v>
       </c>
       <c r="E40" t="s">
+        <v>101</v>
+      </c>
+      <c r="F40" t="s">
         <v>100</v>
-      </c>
-      <c r="F40" t="s">
-        <v>101</v>
       </c>
       <c r="G40" t="s">
         <v>101</v>
@@ -2974,10 +2974,10 @@
         <v>100</v>
       </c>
       <c r="E41" t="s">
+        <v>101</v>
+      </c>
+      <c r="F41" t="s">
         <v>100</v>
-      </c>
-      <c r="F41" t="s">
-        <v>101</v>
       </c>
       <c r="G41" t="s">
         <v>101</v>
@@ -2997,10 +2997,10 @@
         <v>100</v>
       </c>
       <c r="E42" t="s">
+        <v>101</v>
+      </c>
+      <c r="F42" t="s">
         <v>100</v>
-      </c>
-      <c r="F42" t="s">
-        <v>101</v>
       </c>
       <c r="G42" t="s">
         <v>101</v>
@@ -3020,10 +3020,10 @@
         <v>100</v>
       </c>
       <c r="E43" t="s">
+        <v>101</v>
+      </c>
+      <c r="F43" t="s">
         <v>100</v>
-      </c>
-      <c r="F43" t="s">
-        <v>101</v>
       </c>
       <c r="G43" t="s">
         <v>101</v>
@@ -3043,10 +3043,10 @@
         <v>100</v>
       </c>
       <c r="E44" t="s">
+        <v>101</v>
+      </c>
+      <c r="F44" t="s">
         <v>100</v>
-      </c>
-      <c r="F44" t="s">
-        <v>101</v>
       </c>
       <c r="G44" t="s">
         <v>101</v>
@@ -3066,10 +3066,10 @@
         <v>100</v>
       </c>
       <c r="E45" t="s">
+        <v>101</v>
+      </c>
+      <c r="F45" t="s">
         <v>100</v>
-      </c>
-      <c r="F45" t="s">
-        <v>101</v>
       </c>
       <c r="G45" t="s">
         <v>101</v>
@@ -3089,10 +3089,10 @@
         <v>100</v>
       </c>
       <c r="E46" t="s">
+        <v>101</v>
+      </c>
+      <c r="F46" t="s">
         <v>100</v>
-      </c>
-      <c r="F46" t="s">
-        <v>101</v>
       </c>
       <c r="G46" t="s">
         <v>101</v>
@@ -3112,10 +3112,10 @@
         <v>100</v>
       </c>
       <c r="E47" t="s">
+        <v>101</v>
+      </c>
+      <c r="F47" t="s">
         <v>100</v>
-      </c>
-      <c r="F47" t="s">
-        <v>101</v>
       </c>
       <c r="G47" t="s">
         <v>101</v>
@@ -3503,10 +3503,10 @@
         <v>160</v>
       </c>
       <c r="E64" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="F64" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="G64" t="s">
         <v>127</v>
@@ -3526,10 +3526,10 @@
         <v>160</v>
       </c>
       <c r="E65" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="F65" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="G65" t="s">
         <v>127</v>
@@ -3549,10 +3549,10 @@
         <v>160</v>
       </c>
       <c r="E66" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="F66" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="G66" t="s">
         <v>127</v>
@@ -3572,10 +3572,10 @@
         <v>160</v>
       </c>
       <c r="E67" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="F67" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="G67" t="s">
         <v>127</v>
@@ -3595,10 +3595,10 @@
         <v>160</v>
       </c>
       <c r="E68" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="F68" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="G68" t="s">
         <v>127</v>
@@ -3618,10 +3618,10 @@
         <v>160</v>
       </c>
       <c r="E69" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="F69" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="G69" t="s">
         <v>127</v>
@@ -3641,10 +3641,10 @@
         <v>174</v>
       </c>
       <c r="E70" t="s">
+        <v>175</v>
+      </c>
+      <c r="F70" t="s">
         <v>174</v>
-      </c>
-      <c r="F70" t="s">
-        <v>175</v>
       </c>
       <c r="G70" t="s">
         <v>175</v>
@@ -3664,10 +3664,10 @@
         <v>174</v>
       </c>
       <c r="E71" t="s">
+        <v>175</v>
+      </c>
+      <c r="F71" t="s">
         <v>174</v>
-      </c>
-      <c r="F71" t="s">
-        <v>175</v>
       </c>
       <c r="G71" t="s">
         <v>175</v>
@@ -3687,10 +3687,10 @@
         <v>174</v>
       </c>
       <c r="E72" t="s">
+        <v>175</v>
+      </c>
+      <c r="F72" t="s">
         <v>174</v>
-      </c>
-      <c r="F72" t="s">
-        <v>175</v>
       </c>
       <c r="G72" t="s">
         <v>175</v>
@@ -3710,10 +3710,10 @@
         <v>174</v>
       </c>
       <c r="E73" t="s">
+        <v>175</v>
+      </c>
+      <c r="F73" t="s">
         <v>174</v>
-      </c>
-      <c r="F73" t="s">
-        <v>175</v>
       </c>
       <c r="G73" t="s">
         <v>175</v>
@@ -3733,10 +3733,10 @@
         <v>174</v>
       </c>
       <c r="E74" t="s">
+        <v>175</v>
+      </c>
+      <c r="F74" t="s">
         <v>174</v>
-      </c>
-      <c r="F74" t="s">
-        <v>175</v>
       </c>
       <c r="G74" t="s">
         <v>175</v>
@@ -3756,10 +3756,10 @@
         <v>174</v>
       </c>
       <c r="E75" t="s">
+        <v>175</v>
+      </c>
+      <c r="F75" t="s">
         <v>174</v>
-      </c>
-      <c r="F75" t="s">
-        <v>175</v>
       </c>
       <c r="G75" t="s">
         <v>175</v>
@@ -3779,10 +3779,10 @@
         <v>174</v>
       </c>
       <c r="E76" t="s">
+        <v>175</v>
+      </c>
+      <c r="F76" t="s">
         <v>174</v>
-      </c>
-      <c r="F76" t="s">
-        <v>175</v>
       </c>
       <c r="G76" t="s">
         <v>175</v>
@@ -3802,10 +3802,10 @@
         <v>174</v>
       </c>
       <c r="E77" t="s">
+        <v>175</v>
+      </c>
+      <c r="F77" t="s">
         <v>174</v>
-      </c>
-      <c r="F77" t="s">
-        <v>175</v>
       </c>
       <c r="G77" t="s">
         <v>175</v>
@@ -3825,10 +3825,10 @@
         <v>174</v>
       </c>
       <c r="E78" t="s">
+        <v>175</v>
+      </c>
+      <c r="F78" t="s">
         <v>174</v>
-      </c>
-      <c r="F78" t="s">
-        <v>175</v>
       </c>
       <c r="G78" t="s">
         <v>175</v>
@@ -3848,10 +3848,10 @@
         <v>174</v>
       </c>
       <c r="E79" t="s">
+        <v>175</v>
+      </c>
+      <c r="F79" t="s">
         <v>174</v>
-      </c>
-      <c r="F79" t="s">
-        <v>175</v>
       </c>
       <c r="G79" t="s">
         <v>175</v>
@@ -3871,10 +3871,10 @@
         <v>174</v>
       </c>
       <c r="E80" t="s">
+        <v>175</v>
+      </c>
+      <c r="F80" t="s">
         <v>174</v>
-      </c>
-      <c r="F80" t="s">
-        <v>175</v>
       </c>
       <c r="G80" t="s">
         <v>175</v>
@@ -3894,10 +3894,10 @@
         <v>198</v>
       </c>
       <c r="E81" t="s">
+        <v>199</v>
+      </c>
+      <c r="F81" t="s">
         <v>198</v>
-      </c>
-      <c r="F81" t="s">
-        <v>199</v>
       </c>
       <c r="G81" t="s">
         <v>199</v>
@@ -3917,10 +3917,10 @@
         <v>198</v>
       </c>
       <c r="E82" t="s">
+        <v>199</v>
+      </c>
+      <c r="F82" t="s">
         <v>198</v>
-      </c>
-      <c r="F82" t="s">
-        <v>199</v>
       </c>
       <c r="G82" t="s">
         <v>199</v>
@@ -3940,10 +3940,10 @@
         <v>198</v>
       </c>
       <c r="E83" t="s">
+        <v>199</v>
+      </c>
+      <c r="F83" t="s">
         <v>198</v>
-      </c>
-      <c r="F83" t="s">
-        <v>199</v>
       </c>
       <c r="G83" t="s">
         <v>199</v>
@@ -3963,10 +3963,10 @@
         <v>198</v>
       </c>
       <c r="E84" t="s">
+        <v>199</v>
+      </c>
+      <c r="F84" t="s">
         <v>198</v>
-      </c>
-      <c r="F84" t="s">
-        <v>199</v>
       </c>
       <c r="G84" t="s">
         <v>199</v>
@@ -3986,10 +3986,10 @@
         <v>198</v>
       </c>
       <c r="E85" t="s">
+        <v>199</v>
+      </c>
+      <c r="F85" t="s">
         <v>198</v>
-      </c>
-      <c r="F85" t="s">
-        <v>199</v>
       </c>
       <c r="G85" t="s">
         <v>199</v>
@@ -4009,10 +4009,10 @@
         <v>198</v>
       </c>
       <c r="E86" t="s">
+        <v>199</v>
+      </c>
+      <c r="F86" t="s">
         <v>198</v>
-      </c>
-      <c r="F86" t="s">
-        <v>199</v>
       </c>
       <c r="G86" t="s">
         <v>199</v>
@@ -4032,10 +4032,10 @@
         <v>198</v>
       </c>
       <c r="E87" t="s">
+        <v>199</v>
+      </c>
+      <c r="F87" t="s">
         <v>198</v>
-      </c>
-      <c r="F87" t="s">
-        <v>199</v>
       </c>
       <c r="G87" t="s">
         <v>199</v>
@@ -4055,10 +4055,10 @@
         <v>214</v>
       </c>
       <c r="E88" t="s">
+        <v>215</v>
+      </c>
+      <c r="F88" t="s">
         <v>214</v>
-      </c>
-      <c r="F88" t="s">
-        <v>215</v>
       </c>
       <c r="G88" t="s">
         <v>215</v>
@@ -4078,10 +4078,10 @@
         <v>214</v>
       </c>
       <c r="E89" t="s">
+        <v>215</v>
+      </c>
+      <c r="F89" t="s">
         <v>214</v>
-      </c>
-      <c r="F89" t="s">
-        <v>215</v>
       </c>
       <c r="G89" t="s">
         <v>215</v>
@@ -4101,10 +4101,10 @@
         <v>214</v>
       </c>
       <c r="E90" t="s">
+        <v>215</v>
+      </c>
+      <c r="F90" t="s">
         <v>214</v>
-      </c>
-      <c r="F90" t="s">
-        <v>215</v>
       </c>
       <c r="G90" t="s">
         <v>215</v>
@@ -4124,10 +4124,10 @@
         <v>214</v>
       </c>
       <c r="E91" t="s">
+        <v>215</v>
+      </c>
+      <c r="F91" t="s">
         <v>214</v>
-      </c>
-      <c r="F91" t="s">
-        <v>215</v>
       </c>
       <c r="G91" t="s">
         <v>215</v>
@@ -4239,10 +4239,10 @@
         <v>236</v>
       </c>
       <c r="E96" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F96" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G96" t="s">
         <v>227</v>
@@ -4262,10 +4262,10 @@
         <v>236</v>
       </c>
       <c r="E97" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F97" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G97" t="s">
         <v>227</v>
@@ -4285,10 +4285,10 @@
         <v>236</v>
       </c>
       <c r="E98" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F98" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G98" t="s">
         <v>227</v>
@@ -4308,10 +4308,10 @@
         <v>236</v>
       </c>
       <c r="E99" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F99" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G99" t="s">
         <v>227</v>
@@ -4331,10 +4331,10 @@
         <v>236</v>
       </c>
       <c r="E100" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F100" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G100" t="s">
         <v>227</v>
@@ -4354,10 +4354,10 @@
         <v>236</v>
       </c>
       <c r="E101" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F101" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G101" t="s">
         <v>227</v>
@@ -4377,10 +4377,10 @@
         <v>236</v>
       </c>
       <c r="E102" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F102" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G102" t="s">
         <v>227</v>
@@ -4400,10 +4400,10 @@
         <v>236</v>
       </c>
       <c r="E103" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F103" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G103" t="s">
         <v>227</v>
@@ -4423,10 +4423,10 @@
         <v>236</v>
       </c>
       <c r="E104" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F104" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G104" t="s">
         <v>227</v>
@@ -4446,10 +4446,10 @@
         <v>256</v>
       </c>
       <c r="E105" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="F105" t="s">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="G105" t="s">
         <v>227</v>
@@ -4469,10 +4469,10 @@
         <v>256</v>
       </c>
       <c r="E106" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="F106" t="s">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="G106" t="s">
         <v>227</v>
@@ -4492,10 +4492,10 @@
         <v>256</v>
       </c>
       <c r="E107" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="F107" t="s">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="G107" t="s">
         <v>227</v>
@@ -4515,10 +4515,10 @@
         <v>256</v>
       </c>
       <c r="E108" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="F108" t="s">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="G108" t="s">
         <v>227</v>
@@ -4538,10 +4538,10 @@
         <v>256</v>
       </c>
       <c r="E109" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="F109" t="s">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="G109" t="s">
         <v>227</v>
@@ -4561,10 +4561,10 @@
         <v>256</v>
       </c>
       <c r="E110" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="F110" t="s">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="G110" t="s">
         <v>227</v>
@@ -4584,10 +4584,10 @@
         <v>270</v>
       </c>
       <c r="E111" t="s">
-        <v>225</v>
+        <v>271</v>
       </c>
       <c r="F111" t="s">
-        <v>271</v>
+        <v>226</v>
       </c>
       <c r="G111" t="s">
         <v>227</v>
@@ -4607,10 +4607,10 @@
         <v>274</v>
       </c>
       <c r="E112" t="s">
-        <v>225</v>
+        <v>275</v>
       </c>
       <c r="F112" t="s">
-        <v>275</v>
+        <v>226</v>
       </c>
       <c r="G112" t="s">
         <v>227</v>
@@ -4630,10 +4630,10 @@
         <v>278</v>
       </c>
       <c r="E113" t="s">
-        <v>225</v>
+        <v>279</v>
       </c>
       <c r="F113" t="s">
-        <v>279</v>
+        <v>226</v>
       </c>
       <c r="G113" t="s">
         <v>227</v>
@@ -4653,10 +4653,10 @@
         <v>278</v>
       </c>
       <c r="E114" t="s">
-        <v>225</v>
+        <v>279</v>
       </c>
       <c r="F114" t="s">
-        <v>279</v>
+        <v>226</v>
       </c>
       <c r="G114" t="s">
         <v>227</v>
@@ -4676,10 +4676,10 @@
         <v>278</v>
       </c>
       <c r="E115" t="s">
-        <v>225</v>
+        <v>279</v>
       </c>
       <c r="F115" t="s">
-        <v>279</v>
+        <v>226</v>
       </c>
       <c r="G115" t="s">
         <v>227</v>
@@ -4699,10 +4699,10 @@
         <v>278</v>
       </c>
       <c r="E116" t="s">
-        <v>225</v>
+        <v>279</v>
       </c>
       <c r="F116" t="s">
-        <v>279</v>
+        <v>226</v>
       </c>
       <c r="G116" t="s">
         <v>227</v>
@@ -4722,10 +4722,10 @@
         <v>278</v>
       </c>
       <c r="E117" t="s">
-        <v>225</v>
+        <v>279</v>
       </c>
       <c r="F117" t="s">
-        <v>279</v>
+        <v>226</v>
       </c>
       <c r="G117" t="s">
         <v>227</v>
@@ -4745,10 +4745,10 @@
         <v>278</v>
       </c>
       <c r="E118" t="s">
-        <v>225</v>
+        <v>279</v>
       </c>
       <c r="F118" t="s">
-        <v>279</v>
+        <v>226</v>
       </c>
       <c r="G118" t="s">
         <v>227</v>
@@ -4768,10 +4768,10 @@
         <v>278</v>
       </c>
       <c r="E119" t="s">
-        <v>225</v>
+        <v>279</v>
       </c>
       <c r="F119" t="s">
-        <v>279</v>
+        <v>226</v>
       </c>
       <c r="G119" t="s">
         <v>227</v>
@@ -4791,10 +4791,10 @@
         <v>294</v>
       </c>
       <c r="E120" t="s">
+        <v>295</v>
+      </c>
+      <c r="F120" t="s">
         <v>294</v>
-      </c>
-      <c r="F120" t="s">
-        <v>295</v>
       </c>
       <c r="G120" t="s">
         <v>295</v>
@@ -4814,10 +4814,10 @@
         <v>294</v>
       </c>
       <c r="E121" t="s">
+        <v>295</v>
+      </c>
+      <c r="F121" t="s">
         <v>294</v>
-      </c>
-      <c r="F121" t="s">
-        <v>295</v>
       </c>
       <c r="G121" t="s">
         <v>295</v>
@@ -4837,10 +4837,10 @@
         <v>294</v>
       </c>
       <c r="E122" t="s">
+        <v>295</v>
+      </c>
+      <c r="F122" t="s">
         <v>294</v>
-      </c>
-      <c r="F122" t="s">
-        <v>295</v>
       </c>
       <c r="G122" t="s">
         <v>295</v>
@@ -4860,10 +4860,10 @@
         <v>294</v>
       </c>
       <c r="E123" t="s">
+        <v>295</v>
+      </c>
+      <c r="F123" t="s">
         <v>294</v>
-      </c>
-      <c r="F123" t="s">
-        <v>295</v>
       </c>
       <c r="G123" t="s">
         <v>295</v>
@@ -4883,10 +4883,10 @@
         <v>294</v>
       </c>
       <c r="E124" t="s">
+        <v>295</v>
+      </c>
+      <c r="F124" t="s">
         <v>294</v>
-      </c>
-      <c r="F124" t="s">
-        <v>295</v>
       </c>
       <c r="G124" t="s">
         <v>295</v>
@@ -4906,10 +4906,10 @@
         <v>294</v>
       </c>
       <c r="E125" t="s">
+        <v>295</v>
+      </c>
+      <c r="F125" t="s">
         <v>294</v>
-      </c>
-      <c r="F125" t="s">
-        <v>295</v>
       </c>
       <c r="G125" t="s">
         <v>295</v>
@@ -4929,10 +4929,10 @@
         <v>308</v>
       </c>
       <c r="E126" t="s">
+        <v>309</v>
+      </c>
+      <c r="F126" t="s">
         <v>308</v>
-      </c>
-      <c r="F126" t="s">
-        <v>309</v>
       </c>
       <c r="G126" t="s">
         <v>309</v>
@@ -4952,10 +4952,10 @@
         <v>308</v>
       </c>
       <c r="E127" t="s">
+        <v>309</v>
+      </c>
+      <c r="F127" t="s">
         <v>308</v>
-      </c>
-      <c r="F127" t="s">
-        <v>309</v>
       </c>
       <c r="G127" t="s">
         <v>309</v>
@@ -4975,10 +4975,10 @@
         <v>308</v>
       </c>
       <c r="E128" t="s">
+        <v>309</v>
+      </c>
+      <c r="F128" t="s">
         <v>308</v>
-      </c>
-      <c r="F128" t="s">
-        <v>309</v>
       </c>
       <c r="G128" t="s">
         <v>309</v>
@@ -4998,10 +4998,10 @@
         <v>308</v>
       </c>
       <c r="E129" t="s">
+        <v>309</v>
+      </c>
+      <c r="F129" t="s">
         <v>308</v>
-      </c>
-      <c r="F129" t="s">
-        <v>309</v>
       </c>
       <c r="G129" t="s">
         <v>309</v>
@@ -5435,10 +5435,10 @@
         <v>358</v>
       </c>
       <c r="E148" t="s">
-        <v>319</v>
+        <v>359</v>
       </c>
       <c r="F148" t="s">
-        <v>359</v>
+        <v>320</v>
       </c>
       <c r="G148" t="s">
         <v>321</v>
@@ -5458,10 +5458,10 @@
         <v>358</v>
       </c>
       <c r="E149" t="s">
-        <v>319</v>
+        <v>359</v>
       </c>
       <c r="F149" t="s">
-        <v>359</v>
+        <v>320</v>
       </c>
       <c r="G149" t="s">
         <v>321</v>
@@ -5481,10 +5481,10 @@
         <v>358</v>
       </c>
       <c r="E150" t="s">
-        <v>319</v>
+        <v>359</v>
       </c>
       <c r="F150" t="s">
-        <v>359</v>
+        <v>320</v>
       </c>
       <c r="G150" t="s">
         <v>321</v>
@@ -5504,10 +5504,10 @@
         <v>358</v>
       </c>
       <c r="E151" t="s">
-        <v>319</v>
+        <v>359</v>
       </c>
       <c r="F151" t="s">
-        <v>359</v>
+        <v>320</v>
       </c>
       <c r="G151" t="s">
         <v>321</v>
@@ -5527,10 +5527,10 @@
         <v>358</v>
       </c>
       <c r="E152" t="s">
-        <v>319</v>
+        <v>359</v>
       </c>
       <c r="F152" t="s">
-        <v>359</v>
+        <v>320</v>
       </c>
       <c r="G152" t="s">
         <v>321</v>
@@ -5550,10 +5550,10 @@
         <v>358</v>
       </c>
       <c r="E153" t="s">
-        <v>319</v>
+        <v>359</v>
       </c>
       <c r="F153" t="s">
-        <v>359</v>
+        <v>320</v>
       </c>
       <c r="G153" t="s">
         <v>321</v>
@@ -5573,10 +5573,10 @@
         <v>372</v>
       </c>
       <c r="E154" t="s">
-        <v>319</v>
+        <v>373</v>
       </c>
       <c r="F154" t="s">
-        <v>373</v>
+        <v>320</v>
       </c>
       <c r="G154" t="s">
         <v>321</v>
@@ -5596,10 +5596,10 @@
         <v>372</v>
       </c>
       <c r="E155" t="s">
-        <v>319</v>
+        <v>373</v>
       </c>
       <c r="F155" t="s">
-        <v>373</v>
+        <v>320</v>
       </c>
       <c r="G155" t="s">
         <v>321</v>
@@ -5619,10 +5619,10 @@
         <v>372</v>
       </c>
       <c r="E156" t="s">
-        <v>319</v>
+        <v>373</v>
       </c>
       <c r="F156" t="s">
-        <v>373</v>
+        <v>320</v>
       </c>
       <c r="G156" t="s">
         <v>321</v>
@@ -5642,10 +5642,10 @@
         <v>372</v>
       </c>
       <c r="E157" t="s">
-        <v>319</v>
+        <v>373</v>
       </c>
       <c r="F157" t="s">
-        <v>373</v>
+        <v>320</v>
       </c>
       <c r="G157" t="s">
         <v>321</v>
@@ -5665,10 +5665,10 @@
         <v>372</v>
       </c>
       <c r="E158" t="s">
-        <v>319</v>
+        <v>373</v>
       </c>
       <c r="F158" t="s">
-        <v>373</v>
+        <v>320</v>
       </c>
       <c r="G158" t="s">
         <v>321</v>
@@ -6125,10 +6125,10 @@
         <v>426</v>
       </c>
       <c r="E178" t="s">
-        <v>385</v>
+        <v>427</v>
       </c>
       <c r="F178" t="s">
-        <v>427</v>
+        <v>386</v>
       </c>
       <c r="G178" t="s">
         <v>387</v>
@@ -6148,10 +6148,10 @@
         <v>426</v>
       </c>
       <c r="E179" t="s">
-        <v>385</v>
+        <v>427</v>
       </c>
       <c r="F179" t="s">
-        <v>427</v>
+        <v>386</v>
       </c>
       <c r="G179" t="s">
         <v>387</v>
@@ -6171,10 +6171,10 @@
         <v>426</v>
       </c>
       <c r="E180" t="s">
-        <v>385</v>
+        <v>427</v>
       </c>
       <c r="F180" t="s">
-        <v>427</v>
+        <v>386</v>
       </c>
       <c r="G180" t="s">
         <v>387</v>
@@ -6194,10 +6194,10 @@
         <v>426</v>
       </c>
       <c r="E181" t="s">
-        <v>385</v>
+        <v>427</v>
       </c>
       <c r="F181" t="s">
-        <v>427</v>
+        <v>386</v>
       </c>
       <c r="G181" t="s">
         <v>387</v>
@@ -6217,10 +6217,10 @@
         <v>426</v>
       </c>
       <c r="E182" t="s">
-        <v>385</v>
+        <v>427</v>
       </c>
       <c r="F182" t="s">
-        <v>427</v>
+        <v>386</v>
       </c>
       <c r="G182" t="s">
         <v>387</v>
@@ -6240,10 +6240,10 @@
         <v>426</v>
       </c>
       <c r="E183" t="s">
-        <v>385</v>
+        <v>427</v>
       </c>
       <c r="F183" t="s">
-        <v>427</v>
+        <v>386</v>
       </c>
       <c r="G183" t="s">
         <v>387</v>
@@ -6263,10 +6263,10 @@
         <v>426</v>
       </c>
       <c r="E184" t="s">
-        <v>385</v>
+        <v>427</v>
       </c>
       <c r="F184" t="s">
-        <v>427</v>
+        <v>386</v>
       </c>
       <c r="G184" t="s">
         <v>387</v>
@@ -6286,10 +6286,10 @@
         <v>426</v>
       </c>
       <c r="E185" t="s">
-        <v>385</v>
+        <v>427</v>
       </c>
       <c r="F185" t="s">
-        <v>427</v>
+        <v>386</v>
       </c>
       <c r="G185" t="s">
         <v>387</v>
@@ -6309,10 +6309,10 @@
         <v>426</v>
       </c>
       <c r="E186" t="s">
-        <v>385</v>
+        <v>427</v>
       </c>
       <c r="F186" t="s">
-        <v>427</v>
+        <v>386</v>
       </c>
       <c r="G186" t="s">
         <v>387</v>
@@ -6332,10 +6332,10 @@
         <v>426</v>
       </c>
       <c r="E187" t="s">
-        <v>385</v>
+        <v>427</v>
       </c>
       <c r="F187" t="s">
-        <v>427</v>
+        <v>386</v>
       </c>
       <c r="G187" t="s">
         <v>387</v>
@@ -6355,10 +6355,10 @@
         <v>448</v>
       </c>
       <c r="E188" t="s">
-        <v>385</v>
+        <v>449</v>
       </c>
       <c r="F188" t="s">
-        <v>449</v>
+        <v>386</v>
       </c>
       <c r="G188" t="s">
         <v>387</v>
@@ -6378,10 +6378,10 @@
         <v>452</v>
       </c>
       <c r="E189" t="s">
+        <v>453</v>
+      </c>
+      <c r="F189" t="s">
         <v>452</v>
-      </c>
-      <c r="F189" t="s">
-        <v>453</v>
       </c>
       <c r="G189" t="s">
         <v>453</v>
@@ -6401,10 +6401,10 @@
         <v>452</v>
       </c>
       <c r="E190" t="s">
+        <v>453</v>
+      </c>
+      <c r="F190" t="s">
         <v>452</v>
-      </c>
-      <c r="F190" t="s">
-        <v>453</v>
       </c>
       <c r="G190" t="s">
         <v>453</v>
@@ -6424,10 +6424,10 @@
         <v>452</v>
       </c>
       <c r="E191" t="s">
+        <v>453</v>
+      </c>
+      <c r="F191" t="s">
         <v>452</v>
-      </c>
-      <c r="F191" t="s">
-        <v>453</v>
       </c>
       <c r="G191" t="s">
         <v>453</v>
@@ -6447,10 +6447,10 @@
         <v>452</v>
       </c>
       <c r="E192" t="s">
+        <v>453</v>
+      </c>
+      <c r="F192" t="s">
         <v>452</v>
-      </c>
-      <c r="F192" t="s">
-        <v>453</v>
       </c>
       <c r="G192" t="s">
         <v>453</v>
@@ -6470,10 +6470,10 @@
         <v>452</v>
       </c>
       <c r="E193" t="s">
+        <v>453</v>
+      </c>
+      <c r="F193" t="s">
         <v>452</v>
-      </c>
-      <c r="F193" t="s">
-        <v>453</v>
       </c>
       <c r="G193" t="s">
         <v>453</v>
@@ -6493,10 +6493,10 @@
         <v>452</v>
       </c>
       <c r="E194" t="s">
+        <v>453</v>
+      </c>
+      <c r="F194" t="s">
         <v>452</v>
-      </c>
-      <c r="F194" t="s">
-        <v>453</v>
       </c>
       <c r="G194" t="s">
         <v>453</v>
@@ -6516,10 +6516,10 @@
         <v>466</v>
       </c>
       <c r="E195" t="s">
+        <v>467</v>
+      </c>
+      <c r="F195" t="s">
         <v>466</v>
-      </c>
-      <c r="F195" t="s">
-        <v>467</v>
       </c>
       <c r="G195" t="s">
         <v>467</v>
@@ -6539,10 +6539,10 @@
         <v>470</v>
       </c>
       <c r="E196" t="s">
+        <v>471</v>
+      </c>
+      <c r="F196" t="s">
         <v>470</v>
-      </c>
-      <c r="F196" t="s">
-        <v>471</v>
       </c>
       <c r="G196" t="s">
         <v>471</v>
@@ -6562,10 +6562,10 @@
         <v>470</v>
       </c>
       <c r="E197" t="s">
+        <v>471</v>
+      </c>
+      <c r="F197" t="s">
         <v>470</v>
-      </c>
-      <c r="F197" t="s">
-        <v>471</v>
       </c>
       <c r="G197" t="s">
         <v>471</v>
@@ -6585,10 +6585,10 @@
         <v>470</v>
       </c>
       <c r="E198" t="s">
+        <v>471</v>
+      </c>
+      <c r="F198" t="s">
         <v>470</v>
-      </c>
-      <c r="F198" t="s">
-        <v>471</v>
       </c>
       <c r="G198" t="s">
         <v>471</v>
@@ -6608,10 +6608,10 @@
         <v>470</v>
       </c>
       <c r="E199" t="s">
+        <v>471</v>
+      </c>
+      <c r="F199" t="s">
         <v>470</v>
-      </c>
-      <c r="F199" t="s">
-        <v>471</v>
       </c>
       <c r="G199" t="s">
         <v>471</v>
@@ -6631,10 +6631,10 @@
         <v>470</v>
       </c>
       <c r="E200" t="s">
+        <v>471</v>
+      </c>
+      <c r="F200" t="s">
         <v>470</v>
-      </c>
-      <c r="F200" t="s">
-        <v>471</v>
       </c>
       <c r="G200" t="s">
         <v>471</v>
@@ -6654,10 +6654,10 @@
         <v>470</v>
       </c>
       <c r="E201" t="s">
+        <v>471</v>
+      </c>
+      <c r="F201" t="s">
         <v>470</v>
-      </c>
-      <c r="F201" t="s">
-        <v>471</v>
       </c>
       <c r="G201" t="s">
         <v>471</v>
@@ -6677,10 +6677,10 @@
         <v>484</v>
       </c>
       <c r="E202" t="s">
+        <v>485</v>
+      </c>
+      <c r="F202" t="s">
         <v>484</v>
-      </c>
-      <c r="F202" t="s">
-        <v>485</v>
       </c>
       <c r="G202" t="s">
         <v>485</v>
@@ -6700,10 +6700,10 @@
         <v>484</v>
       </c>
       <c r="E203" t="s">
+        <v>485</v>
+      </c>
+      <c r="F203" t="s">
         <v>484</v>
-      </c>
-      <c r="F203" t="s">
-        <v>485</v>
       </c>
       <c r="G203" t="s">
         <v>485</v>
@@ -6723,10 +6723,10 @@
         <v>484</v>
       </c>
       <c r="E204" t="s">
+        <v>485</v>
+      </c>
+      <c r="F204" t="s">
         <v>484</v>
-      </c>
-      <c r="F204" t="s">
-        <v>485</v>
       </c>
       <c r="G204" t="s">
         <v>485</v>
@@ -6746,10 +6746,10 @@
         <v>484</v>
       </c>
       <c r="E205" t="s">
+        <v>485</v>
+      </c>
+      <c r="F205" t="s">
         <v>484</v>
-      </c>
-      <c r="F205" t="s">
-        <v>485</v>
       </c>
       <c r="G205" t="s">
         <v>485</v>
@@ -6769,10 +6769,10 @@
         <v>484</v>
       </c>
       <c r="E206" t="s">
+        <v>485</v>
+      </c>
+      <c r="F206" t="s">
         <v>484</v>
-      </c>
-      <c r="F206" t="s">
-        <v>485</v>
       </c>
       <c r="G206" t="s">
         <v>485</v>
@@ -6792,10 +6792,10 @@
         <v>484</v>
       </c>
       <c r="E207" t="s">
+        <v>485</v>
+      </c>
+      <c r="F207" t="s">
         <v>484</v>
-      </c>
-      <c r="F207" t="s">
-        <v>485</v>
       </c>
       <c r="G207" t="s">
         <v>485</v>
@@ -6815,10 +6815,10 @@
         <v>484</v>
       </c>
       <c r="E208" t="s">
+        <v>485</v>
+      </c>
+      <c r="F208" t="s">
         <v>484</v>
-      </c>
-      <c r="F208" t="s">
-        <v>485</v>
       </c>
       <c r="G208" t="s">
         <v>485</v>
@@ -6838,10 +6838,10 @@
         <v>484</v>
       </c>
       <c r="E209" t="s">
+        <v>485</v>
+      </c>
+      <c r="F209" t="s">
         <v>484</v>
-      </c>
-      <c r="F209" t="s">
-        <v>485</v>
       </c>
       <c r="G209" t="s">
         <v>485</v>
@@ -6861,10 +6861,10 @@
         <v>484</v>
       </c>
       <c r="E210" t="s">
+        <v>485</v>
+      </c>
+      <c r="F210" t="s">
         <v>484</v>
-      </c>
-      <c r="F210" t="s">
-        <v>485</v>
       </c>
       <c r="G210" t="s">
         <v>485</v>
@@ -6884,10 +6884,10 @@
         <v>484</v>
       </c>
       <c r="E211" t="s">
+        <v>485</v>
+      </c>
+      <c r="F211" t="s">
         <v>484</v>
-      </c>
-      <c r="F211" t="s">
-        <v>485</v>
       </c>
       <c r="G211" t="s">
         <v>485</v>
@@ -6907,10 +6907,10 @@
         <v>506</v>
       </c>
       <c r="E212" t="s">
+        <v>507</v>
+      </c>
+      <c r="F212" t="s">
         <v>506</v>
-      </c>
-      <c r="F212" t="s">
-        <v>507</v>
       </c>
       <c r="G212" t="s">
         <v>507</v>
@@ -6930,10 +6930,10 @@
         <v>510</v>
       </c>
       <c r="E213" t="s">
+        <v>511</v>
+      </c>
+      <c r="F213" t="s">
         <v>510</v>
-      </c>
-      <c r="F213" t="s">
-        <v>511</v>
       </c>
       <c r="G213" t="s">
         <v>511</v>
@@ -6953,10 +6953,10 @@
         <v>514</v>
       </c>
       <c r="E214" t="s">
+        <v>515</v>
+      </c>
+      <c r="F214" t="s">
         <v>514</v>
-      </c>
-      <c r="F214" t="s">
-        <v>515</v>
       </c>
       <c r="G214" t="s">
         <v>515</v>
@@ -6976,10 +6976,10 @@
         <v>514</v>
       </c>
       <c r="E215" t="s">
+        <v>515</v>
+      </c>
+      <c r="F215" t="s">
         <v>514</v>
-      </c>
-      <c r="F215" t="s">
-        <v>515</v>
       </c>
       <c r="G215" t="s">
         <v>515</v>
@@ -6999,10 +6999,10 @@
         <v>520</v>
       </c>
       <c r="E216" t="s">
+        <v>521</v>
+      </c>
+      <c r="F216" t="s">
         <v>520</v>
-      </c>
-      <c r="F216" t="s">
-        <v>521</v>
       </c>
       <c r="G216" t="s">
         <v>521</v>
@@ -7022,10 +7022,10 @@
         <v>520</v>
       </c>
       <c r="E217" t="s">
+        <v>521</v>
+      </c>
+      <c r="F217" t="s">
         <v>520</v>
-      </c>
-      <c r="F217" t="s">
-        <v>521</v>
       </c>
       <c r="G217" t="s">
         <v>521</v>
@@ -7045,10 +7045,10 @@
         <v>520</v>
       </c>
       <c r="E218" t="s">
+        <v>521</v>
+      </c>
+      <c r="F218" t="s">
         <v>520</v>
-      </c>
-      <c r="F218" t="s">
-        <v>521</v>
       </c>
       <c r="G218" t="s">
         <v>521</v>
@@ -7068,10 +7068,10 @@
         <v>520</v>
       </c>
       <c r="E219" t="s">
+        <v>521</v>
+      </c>
+      <c r="F219" t="s">
         <v>520</v>
-      </c>
-      <c r="F219" t="s">
-        <v>521</v>
       </c>
       <c r="G219" t="s">
         <v>521</v>
@@ -7091,10 +7091,10 @@
         <v>520</v>
       </c>
       <c r="E220" t="s">
+        <v>521</v>
+      </c>
+      <c r="F220" t="s">
         <v>520</v>
-      </c>
-      <c r="F220" t="s">
-        <v>521</v>
       </c>
       <c r="G220" t="s">
         <v>521</v>
@@ -7114,10 +7114,10 @@
         <v>520</v>
       </c>
       <c r="E221" t="s">
+        <v>521</v>
+      </c>
+      <c r="F221" t="s">
         <v>520</v>
-      </c>
-      <c r="F221" t="s">
-        <v>521</v>
       </c>
       <c r="G221" t="s">
         <v>521</v>
@@ -7137,10 +7137,10 @@
         <v>520</v>
       </c>
       <c r="E222" t="s">
+        <v>521</v>
+      </c>
+      <c r="F222" t="s">
         <v>520</v>
-      </c>
-      <c r="F222" t="s">
-        <v>521</v>
       </c>
       <c r="G222" t="s">
         <v>521</v>
@@ -7160,10 +7160,10 @@
         <v>536</v>
       </c>
       <c r="E223" t="s">
+        <v>537</v>
+      </c>
+      <c r="F223" t="s">
         <v>536</v>
-      </c>
-      <c r="F223" t="s">
-        <v>537</v>
       </c>
       <c r="G223" t="s">
         <v>537</v>
@@ -7183,10 +7183,10 @@
         <v>536</v>
       </c>
       <c r="E224" t="s">
+        <v>537</v>
+      </c>
+      <c r="F224" t="s">
         <v>536</v>
-      </c>
-      <c r="F224" t="s">
-        <v>537</v>
       </c>
       <c r="G224" t="s">
         <v>537</v>
@@ -7206,10 +7206,10 @@
         <v>536</v>
       </c>
       <c r="E225" t="s">
+        <v>537</v>
+      </c>
+      <c r="F225" t="s">
         <v>536</v>
-      </c>
-      <c r="F225" t="s">
-        <v>537</v>
       </c>
       <c r="G225" t="s">
         <v>537</v>
@@ -7229,10 +7229,10 @@
         <v>544</v>
       </c>
       <c r="E226" t="s">
+        <v>545</v>
+      </c>
+      <c r="F226" t="s">
         <v>544</v>
-      </c>
-      <c r="F226" t="s">
-        <v>545</v>
       </c>
       <c r="G226" t="s">
         <v>545</v>
@@ -7252,10 +7252,10 @@
         <v>548</v>
       </c>
       <c r="E227" t="s">
+        <v>549</v>
+      </c>
+      <c r="F227" t="s">
         <v>548</v>
-      </c>
-      <c r="F227" t="s">
-        <v>549</v>
       </c>
       <c r="G227" t="s">
         <v>549</v>
@@ -7275,10 +7275,10 @@
         <v>552</v>
       </c>
       <c r="E228" t="s">
+        <v>553</v>
+      </c>
+      <c r="F228" t="s">
         <v>552</v>
-      </c>
-      <c r="F228" t="s">
-        <v>553</v>
       </c>
       <c r="G228" t="s">
         <v>553</v>
@@ -7298,10 +7298,10 @@
         <v>556</v>
       </c>
       <c r="E229" t="s">
+        <v>557</v>
+      </c>
+      <c r="F229" t="s">
         <v>556</v>
-      </c>
-      <c r="F229" t="s">
-        <v>557</v>
       </c>
       <c r="G229" t="s">
         <v>557</v>
@@ -7321,10 +7321,10 @@
         <v>560</v>
       </c>
       <c r="E230" t="s">
+        <v>561</v>
+      </c>
+      <c r="F230" t="s">
         <v>560</v>
-      </c>
-      <c r="F230" t="s">
-        <v>561</v>
       </c>
       <c r="G230" t="s">
         <v>561</v>
@@ -7344,10 +7344,10 @@
         <v>560</v>
       </c>
       <c r="E231" t="s">
+        <v>561</v>
+      </c>
+      <c r="F231" t="s">
         <v>560</v>
-      </c>
-      <c r="F231" t="s">
-        <v>561</v>
       </c>
       <c r="G231" t="s">
         <v>561</v>

--- a/api/xlsx/en/SectorGroup.xlsx
+++ b/api/xlsx/en/SectorGroup.xlsx
@@ -31,12 +31,12 @@
     <t>codeforiati:category-name</t>
   </si>
   <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -52,12 +52,12 @@
     <t>Education, Level Unspecified</t>
   </si>
   <si>
+    <t>Education</t>
+  </si>
+  <si>
     <t>110</t>
   </si>
   <si>
-    <t>Education</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -154,12 +154,12 @@
     <t>Health, General</t>
   </si>
   <si>
+    <t>Health</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
-    <t>Health</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -394,12 +394,12 @@
     <t>Government &amp; Civil Society-general</t>
   </si>
   <si>
+    <t>Government &amp; Civil Society</t>
+  </si>
+  <si>
     <t>150</t>
   </si>
   <si>
-    <t>Government &amp; Civil Society</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -694,12 +694,12 @@
     <t>Energy Policy</t>
   </si>
   <si>
+    <t>Energy</t>
+  </si>
+  <si>
     <t>230</t>
   </si>
   <si>
-    <t>Energy</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -976,12 +976,12 @@
     <t>Agriculture</t>
   </si>
   <si>
+    <t>Agriculture, Forestry, Fishing</t>
+  </si>
+  <si>
     <t>310</t>
   </si>
   <si>
-    <t>Agriculture, Forestry, Fishing</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1174,10 +1174,10 @@
     <t>Industry</t>
   </si>
   <si>
+    <t>Industry, Mining, Construction</t>
+  </si>
+  <si>
     <t>320</t>
-  </si>
-  <si>
-    <t>Industry, Mining, Construction</t>
   </si>
   <si>
     <t>32120</t>
@@ -2770,10 +2770,10 @@
         <v>89</v>
       </c>
       <c r="F32" t="s">
+        <v>89</v>
+      </c>
+      <c r="G32" t="s">
         <v>88</v>
-      </c>
-      <c r="G32" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2793,10 +2793,10 @@
         <v>89</v>
       </c>
       <c r="F33" t="s">
+        <v>89</v>
+      </c>
+      <c r="G33" t="s">
         <v>88</v>
-      </c>
-      <c r="G33" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2816,10 +2816,10 @@
         <v>89</v>
       </c>
       <c r="F34" t="s">
+        <v>89</v>
+      </c>
+      <c r="G34" t="s">
         <v>88</v>
-      </c>
-      <c r="G34" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2839,10 +2839,10 @@
         <v>89</v>
       </c>
       <c r="F35" t="s">
+        <v>89</v>
+      </c>
+      <c r="G35" t="s">
         <v>88</v>
-      </c>
-      <c r="G35" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2862,10 +2862,10 @@
         <v>89</v>
       </c>
       <c r="F36" t="s">
+        <v>89</v>
+      </c>
+      <c r="G36" t="s">
         <v>88</v>
-      </c>
-      <c r="G36" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2885,10 +2885,10 @@
         <v>101</v>
       </c>
       <c r="F37" t="s">
+        <v>101</v>
+      </c>
+      <c r="G37" t="s">
         <v>100</v>
-      </c>
-      <c r="G37" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2908,10 +2908,10 @@
         <v>101</v>
       </c>
       <c r="F38" t="s">
+        <v>101</v>
+      </c>
+      <c r="G38" t="s">
         <v>100</v>
-      </c>
-      <c r="G38" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2931,10 +2931,10 @@
         <v>101</v>
       </c>
       <c r="F39" t="s">
+        <v>101</v>
+      </c>
+      <c r="G39" t="s">
         <v>100</v>
-      </c>
-      <c r="G39" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2954,10 +2954,10 @@
         <v>101</v>
       </c>
       <c r="F40" t="s">
+        <v>101</v>
+      </c>
+      <c r="G40" t="s">
         <v>100</v>
-      </c>
-      <c r="G40" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2977,10 +2977,10 @@
         <v>101</v>
       </c>
       <c r="F41" t="s">
+        <v>101</v>
+      </c>
+      <c r="G41" t="s">
         <v>100</v>
-      </c>
-      <c r="G41" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -3000,10 +3000,10 @@
         <v>101</v>
       </c>
       <c r="F42" t="s">
+        <v>101</v>
+      </c>
+      <c r="G42" t="s">
         <v>100</v>
-      </c>
-      <c r="G42" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3023,10 +3023,10 @@
         <v>101</v>
       </c>
       <c r="F43" t="s">
+        <v>101</v>
+      </c>
+      <c r="G43" t="s">
         <v>100</v>
-      </c>
-      <c r="G43" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3046,10 +3046,10 @@
         <v>101</v>
       </c>
       <c r="F44" t="s">
+        <v>101</v>
+      </c>
+      <c r="G44" t="s">
         <v>100</v>
-      </c>
-      <c r="G44" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3069,10 +3069,10 @@
         <v>101</v>
       </c>
       <c r="F45" t="s">
+        <v>101</v>
+      </c>
+      <c r="G45" t="s">
         <v>100</v>
-      </c>
-      <c r="G45" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3092,10 +3092,10 @@
         <v>101</v>
       </c>
       <c r="F46" t="s">
+        <v>101</v>
+      </c>
+      <c r="G46" t="s">
         <v>100</v>
-      </c>
-      <c r="G46" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3115,10 +3115,10 @@
         <v>101</v>
       </c>
       <c r="F47" t="s">
+        <v>101</v>
+      </c>
+      <c r="G47" t="s">
         <v>100</v>
-      </c>
-      <c r="G47" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3644,10 +3644,10 @@
         <v>175</v>
       </c>
       <c r="F70" t="s">
+        <v>175</v>
+      </c>
+      <c r="G70" t="s">
         <v>174</v>
-      </c>
-      <c r="G70" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3667,10 +3667,10 @@
         <v>175</v>
       </c>
       <c r="F71" t="s">
+        <v>175</v>
+      </c>
+      <c r="G71" t="s">
         <v>174</v>
-      </c>
-      <c r="G71" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3690,10 +3690,10 @@
         <v>175</v>
       </c>
       <c r="F72" t="s">
+        <v>175</v>
+      </c>
+      <c r="G72" t="s">
         <v>174</v>
-      </c>
-      <c r="G72" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3713,10 +3713,10 @@
         <v>175</v>
       </c>
       <c r="F73" t="s">
+        <v>175</v>
+      </c>
+      <c r="G73" t="s">
         <v>174</v>
-      </c>
-      <c r="G73" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3736,10 +3736,10 @@
         <v>175</v>
       </c>
       <c r="F74" t="s">
+        <v>175</v>
+      </c>
+      <c r="G74" t="s">
         <v>174</v>
-      </c>
-      <c r="G74" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3759,10 +3759,10 @@
         <v>175</v>
       </c>
       <c r="F75" t="s">
+        <v>175</v>
+      </c>
+      <c r="G75" t="s">
         <v>174</v>
-      </c>
-      <c r="G75" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3782,10 +3782,10 @@
         <v>175</v>
       </c>
       <c r="F76" t="s">
+        <v>175</v>
+      </c>
+      <c r="G76" t="s">
         <v>174</v>
-      </c>
-      <c r="G76" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3805,10 +3805,10 @@
         <v>175</v>
       </c>
       <c r="F77" t="s">
+        <v>175</v>
+      </c>
+      <c r="G77" t="s">
         <v>174</v>
-      </c>
-      <c r="G77" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3828,10 +3828,10 @@
         <v>175</v>
       </c>
       <c r="F78" t="s">
+        <v>175</v>
+      </c>
+      <c r="G78" t="s">
         <v>174</v>
-      </c>
-      <c r="G78" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3851,10 +3851,10 @@
         <v>175</v>
       </c>
       <c r="F79" t="s">
+        <v>175</v>
+      </c>
+      <c r="G79" t="s">
         <v>174</v>
-      </c>
-      <c r="G79" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3874,10 +3874,10 @@
         <v>175</v>
       </c>
       <c r="F80" t="s">
+        <v>175</v>
+      </c>
+      <c r="G80" t="s">
         <v>174</v>
-      </c>
-      <c r="G80" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3897,10 +3897,10 @@
         <v>199</v>
       </c>
       <c r="F81" t="s">
+        <v>199</v>
+      </c>
+      <c r="G81" t="s">
         <v>198</v>
-      </c>
-      <c r="G81" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3920,10 +3920,10 @@
         <v>199</v>
       </c>
       <c r="F82" t="s">
+        <v>199</v>
+      </c>
+      <c r="G82" t="s">
         <v>198</v>
-      </c>
-      <c r="G82" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3943,10 +3943,10 @@
         <v>199</v>
       </c>
       <c r="F83" t="s">
+        <v>199</v>
+      </c>
+      <c r="G83" t="s">
         <v>198</v>
-      </c>
-      <c r="G83" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3966,10 +3966,10 @@
         <v>199</v>
       </c>
       <c r="F84" t="s">
+        <v>199</v>
+      </c>
+      <c r="G84" t="s">
         <v>198</v>
-      </c>
-      <c r="G84" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3989,10 +3989,10 @@
         <v>199</v>
       </c>
       <c r="F85" t="s">
+        <v>199</v>
+      </c>
+      <c r="G85" t="s">
         <v>198</v>
-      </c>
-      <c r="G85" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4012,10 +4012,10 @@
         <v>199</v>
       </c>
       <c r="F86" t="s">
+        <v>199</v>
+      </c>
+      <c r="G86" t="s">
         <v>198</v>
-      </c>
-      <c r="G86" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4035,10 +4035,10 @@
         <v>199</v>
       </c>
       <c r="F87" t="s">
+        <v>199</v>
+      </c>
+      <c r="G87" t="s">
         <v>198</v>
-      </c>
-      <c r="G87" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4058,10 +4058,10 @@
         <v>215</v>
       </c>
       <c r="F88" t="s">
+        <v>215</v>
+      </c>
+      <c r="G88" t="s">
         <v>214</v>
-      </c>
-      <c r="G88" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4081,10 +4081,10 @@
         <v>215</v>
       </c>
       <c r="F89" t="s">
+        <v>215</v>
+      </c>
+      <c r="G89" t="s">
         <v>214</v>
-      </c>
-      <c r="G89" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4104,10 +4104,10 @@
         <v>215</v>
       </c>
       <c r="F90" t="s">
+        <v>215</v>
+      </c>
+      <c r="G90" t="s">
         <v>214</v>
-      </c>
-      <c r="G90" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4127,10 +4127,10 @@
         <v>215</v>
       </c>
       <c r="F91" t="s">
+        <v>215</v>
+      </c>
+      <c r="G91" t="s">
         <v>214</v>
-      </c>
-      <c r="G91" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4794,10 +4794,10 @@
         <v>295</v>
       </c>
       <c r="F120" t="s">
+        <v>295</v>
+      </c>
+      <c r="G120" t="s">
         <v>294</v>
-      </c>
-      <c r="G120" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4817,10 +4817,10 @@
         <v>295</v>
       </c>
       <c r="F121" t="s">
+        <v>295</v>
+      </c>
+      <c r="G121" t="s">
         <v>294</v>
-      </c>
-      <c r="G121" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4840,10 +4840,10 @@
         <v>295</v>
       </c>
       <c r="F122" t="s">
+        <v>295</v>
+      </c>
+      <c r="G122" t="s">
         <v>294</v>
-      </c>
-      <c r="G122" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4863,10 +4863,10 @@
         <v>295</v>
       </c>
       <c r="F123" t="s">
+        <v>295</v>
+      </c>
+      <c r="G123" t="s">
         <v>294</v>
-      </c>
-      <c r="G123" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4886,10 +4886,10 @@
         <v>295</v>
       </c>
       <c r="F124" t="s">
+        <v>295</v>
+      </c>
+      <c r="G124" t="s">
         <v>294</v>
-      </c>
-      <c r="G124" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4909,10 +4909,10 @@
         <v>295</v>
       </c>
       <c r="F125" t="s">
+        <v>295</v>
+      </c>
+      <c r="G125" t="s">
         <v>294</v>
-      </c>
-      <c r="G125" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4932,10 +4932,10 @@
         <v>309</v>
       </c>
       <c r="F126" t="s">
+        <v>309</v>
+      </c>
+      <c r="G126" t="s">
         <v>308</v>
-      </c>
-      <c r="G126" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4955,10 +4955,10 @@
         <v>309</v>
       </c>
       <c r="F127" t="s">
+        <v>309</v>
+      </c>
+      <c r="G127" t="s">
         <v>308</v>
-      </c>
-      <c r="G127" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4978,10 +4978,10 @@
         <v>309</v>
       </c>
       <c r="F128" t="s">
+        <v>309</v>
+      </c>
+      <c r="G128" t="s">
         <v>308</v>
-      </c>
-      <c r="G128" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -5001,10 +5001,10 @@
         <v>309</v>
       </c>
       <c r="F129" t="s">
+        <v>309</v>
+      </c>
+      <c r="G129" t="s">
         <v>308</v>
-      </c>
-      <c r="G129" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -6381,10 +6381,10 @@
         <v>453</v>
       </c>
       <c r="F189" t="s">
+        <v>453</v>
+      </c>
+      <c r="G189" t="s">
         <v>452</v>
-      </c>
-      <c r="G189" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6404,10 +6404,10 @@
         <v>453</v>
       </c>
       <c r="F190" t="s">
+        <v>453</v>
+      </c>
+      <c r="G190" t="s">
         <v>452</v>
-      </c>
-      <c r="G190" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6427,10 +6427,10 @@
         <v>453</v>
       </c>
       <c r="F191" t="s">
+        <v>453</v>
+      </c>
+      <c r="G191" t="s">
         <v>452</v>
-      </c>
-      <c r="G191" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6450,10 +6450,10 @@
         <v>453</v>
       </c>
       <c r="F192" t="s">
+        <v>453</v>
+      </c>
+      <c r="G192" t="s">
         <v>452</v>
-      </c>
-      <c r="G192" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6473,10 +6473,10 @@
         <v>453</v>
       </c>
       <c r="F193" t="s">
+        <v>453</v>
+      </c>
+      <c r="G193" t="s">
         <v>452</v>
-      </c>
-      <c r="G193" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6496,10 +6496,10 @@
         <v>453</v>
       </c>
       <c r="F194" t="s">
+        <v>453</v>
+      </c>
+      <c r="G194" t="s">
         <v>452</v>
-      </c>
-      <c r="G194" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6519,10 +6519,10 @@
         <v>467</v>
       </c>
       <c r="F195" t="s">
+        <v>467</v>
+      </c>
+      <c r="G195" t="s">
         <v>466</v>
-      </c>
-      <c r="G195" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6542,10 +6542,10 @@
         <v>471</v>
       </c>
       <c r="F196" t="s">
+        <v>471</v>
+      </c>
+      <c r="G196" t="s">
         <v>470</v>
-      </c>
-      <c r="G196" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6565,10 +6565,10 @@
         <v>471</v>
       </c>
       <c r="F197" t="s">
+        <v>471</v>
+      </c>
+      <c r="G197" t="s">
         <v>470</v>
-      </c>
-      <c r="G197" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6588,10 +6588,10 @@
         <v>471</v>
       </c>
       <c r="F198" t="s">
+        <v>471</v>
+      </c>
+      <c r="G198" t="s">
         <v>470</v>
-      </c>
-      <c r="G198" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6611,10 +6611,10 @@
         <v>471</v>
       </c>
       <c r="F199" t="s">
+        <v>471</v>
+      </c>
+      <c r="G199" t="s">
         <v>470</v>
-      </c>
-      <c r="G199" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6634,10 +6634,10 @@
         <v>471</v>
       </c>
       <c r="F200" t="s">
+        <v>471</v>
+      </c>
+      <c r="G200" t="s">
         <v>470</v>
-      </c>
-      <c r="G200" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6657,10 +6657,10 @@
         <v>471</v>
       </c>
       <c r="F201" t="s">
+        <v>471</v>
+      </c>
+      <c r="G201" t="s">
         <v>470</v>
-      </c>
-      <c r="G201" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6680,10 +6680,10 @@
         <v>485</v>
       </c>
       <c r="F202" t="s">
+        <v>485</v>
+      </c>
+      <c r="G202" t="s">
         <v>484</v>
-      </c>
-      <c r="G202" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6703,10 +6703,10 @@
         <v>485</v>
       </c>
       <c r="F203" t="s">
+        <v>485</v>
+      </c>
+      <c r="G203" t="s">
         <v>484</v>
-      </c>
-      <c r="G203" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6726,10 +6726,10 @@
         <v>485</v>
       </c>
       <c r="F204" t="s">
+        <v>485</v>
+      </c>
+      <c r="G204" t="s">
         <v>484</v>
-      </c>
-      <c r="G204" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6749,10 +6749,10 @@
         <v>485</v>
       </c>
       <c r="F205" t="s">
+        <v>485</v>
+      </c>
+      <c r="G205" t="s">
         <v>484</v>
-      </c>
-      <c r="G205" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6772,10 +6772,10 @@
         <v>485</v>
       </c>
       <c r="F206" t="s">
+        <v>485</v>
+      </c>
+      <c r="G206" t="s">
         <v>484</v>
-      </c>
-      <c r="G206" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6795,10 +6795,10 @@
         <v>485</v>
       </c>
       <c r="F207" t="s">
+        <v>485</v>
+      </c>
+      <c r="G207" t="s">
         <v>484</v>
-      </c>
-      <c r="G207" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6818,10 +6818,10 @@
         <v>485</v>
       </c>
       <c r="F208" t="s">
+        <v>485</v>
+      </c>
+      <c r="G208" t="s">
         <v>484</v>
-      </c>
-      <c r="G208" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6841,10 +6841,10 @@
         <v>485</v>
       </c>
       <c r="F209" t="s">
+        <v>485</v>
+      </c>
+      <c r="G209" t="s">
         <v>484</v>
-      </c>
-      <c r="G209" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6864,10 +6864,10 @@
         <v>485</v>
       </c>
       <c r="F210" t="s">
+        <v>485</v>
+      </c>
+      <c r="G210" t="s">
         <v>484</v>
-      </c>
-      <c r="G210" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6887,10 +6887,10 @@
         <v>485</v>
       </c>
       <c r="F211" t="s">
+        <v>485</v>
+      </c>
+      <c r="G211" t="s">
         <v>484</v>
-      </c>
-      <c r="G211" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6910,10 +6910,10 @@
         <v>507</v>
       </c>
       <c r="F212" t="s">
+        <v>507</v>
+      </c>
+      <c r="G212" t="s">
         <v>506</v>
-      </c>
-      <c r="G212" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6933,10 +6933,10 @@
         <v>511</v>
       </c>
       <c r="F213" t="s">
+        <v>511</v>
+      </c>
+      <c r="G213" t="s">
         <v>510</v>
-      </c>
-      <c r="G213" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6956,10 +6956,10 @@
         <v>515</v>
       </c>
       <c r="F214" t="s">
+        <v>515</v>
+      </c>
+      <c r="G214" t="s">
         <v>514</v>
-      </c>
-      <c r="G214" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6979,10 +6979,10 @@
         <v>515</v>
       </c>
       <c r="F215" t="s">
+        <v>515</v>
+      </c>
+      <c r="G215" t="s">
         <v>514</v>
-      </c>
-      <c r="G215" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -7002,10 +7002,10 @@
         <v>521</v>
       </c>
       <c r="F216" t="s">
+        <v>521</v>
+      </c>
+      <c r="G216" t="s">
         <v>520</v>
-      </c>
-      <c r="G216" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -7025,10 +7025,10 @@
         <v>521</v>
       </c>
       <c r="F217" t="s">
+        <v>521</v>
+      </c>
+      <c r="G217" t="s">
         <v>520</v>
-      </c>
-      <c r="G217" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -7048,10 +7048,10 @@
         <v>521</v>
       </c>
       <c r="F218" t="s">
+        <v>521</v>
+      </c>
+      <c r="G218" t="s">
         <v>520</v>
-      </c>
-      <c r="G218" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -7071,10 +7071,10 @@
         <v>521</v>
       </c>
       <c r="F219" t="s">
+        <v>521</v>
+      </c>
+      <c r="G219" t="s">
         <v>520</v>
-      </c>
-      <c r="G219" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -7094,10 +7094,10 @@
         <v>521</v>
       </c>
       <c r="F220" t="s">
+        <v>521</v>
+      </c>
+      <c r="G220" t="s">
         <v>520</v>
-      </c>
-      <c r="G220" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -7117,10 +7117,10 @@
         <v>521</v>
       </c>
       <c r="F221" t="s">
+        <v>521</v>
+      </c>
+      <c r="G221" t="s">
         <v>520</v>
-      </c>
-      <c r="G221" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -7140,10 +7140,10 @@
         <v>521</v>
       </c>
       <c r="F222" t="s">
+        <v>521</v>
+      </c>
+      <c r="G222" t="s">
         <v>520</v>
-      </c>
-      <c r="G222" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -7163,10 +7163,10 @@
         <v>537</v>
       </c>
       <c r="F223" t="s">
+        <v>537</v>
+      </c>
+      <c r="G223" t="s">
         <v>536</v>
-      </c>
-      <c r="G223" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -7186,10 +7186,10 @@
         <v>537</v>
       </c>
       <c r="F224" t="s">
+        <v>537</v>
+      </c>
+      <c r="G224" t="s">
         <v>536</v>
-      </c>
-      <c r="G224" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -7209,10 +7209,10 @@
         <v>537</v>
       </c>
       <c r="F225" t="s">
+        <v>537</v>
+      </c>
+      <c r="G225" t="s">
         <v>536</v>
-      </c>
-      <c r="G225" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -7232,10 +7232,10 @@
         <v>545</v>
       </c>
       <c r="F226" t="s">
+        <v>545</v>
+      </c>
+      <c r="G226" t="s">
         <v>544</v>
-      </c>
-      <c r="G226" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -7255,10 +7255,10 @@
         <v>549</v>
       </c>
       <c r="F227" t="s">
+        <v>549</v>
+      </c>
+      <c r="G227" t="s">
         <v>548</v>
-      </c>
-      <c r="G227" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -7278,10 +7278,10 @@
         <v>553</v>
       </c>
       <c r="F228" t="s">
+        <v>553</v>
+      </c>
+      <c r="G228" t="s">
         <v>552</v>
-      </c>
-      <c r="G228" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -7301,10 +7301,10 @@
         <v>557</v>
       </c>
       <c r="F229" t="s">
+        <v>557</v>
+      </c>
+      <c r="G229" t="s">
         <v>556</v>
-      </c>
-      <c r="G229" t="s">
-        <v>557</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -7324,10 +7324,10 @@
         <v>561</v>
       </c>
       <c r="F230" t="s">
+        <v>561</v>
+      </c>
+      <c r="G230" t="s">
         <v>560</v>
-      </c>
-      <c r="G230" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -7347,10 +7347,10 @@
         <v>561</v>
       </c>
       <c r="F231" t="s">
+        <v>561</v>
+      </c>
+      <c r="G231" t="s">
         <v>560</v>
-      </c>
-      <c r="G231" t="s">
-        <v>561</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/en/SectorGroup.xlsx
+++ b/api/xlsx/en/SectorGroup.xlsx
@@ -25,18 +25,18 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
+    <t>codeforiati:category-name</t>
+  </si>
+  <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
-    <t>codeforiati:category-name</t>
-  </si>
-  <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -46,18 +46,18 @@
     <t>active</t>
   </si>
   <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>Education, Level Unspecified</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
     <t>111</t>
   </si>
   <si>
-    <t>Education, Level Unspecified</t>
-  </si>
-  <si>
-    <t>Education</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -82,12 +82,12 @@
     <t>Primary education</t>
   </si>
   <si>
+    <t>Basic Education</t>
+  </si>
+  <si>
     <t>112</t>
   </si>
   <si>
-    <t>Basic Education</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -112,12 +112,12 @@
     <t>Secondary education</t>
   </si>
   <si>
+    <t>Secondary Education</t>
+  </si>
+  <si>
     <t>113</t>
   </si>
   <si>
-    <t>Secondary Education</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
@@ -130,12 +130,12 @@
     <t>Higher education</t>
   </si>
   <si>
+    <t>Post-Secondary Education</t>
+  </si>
+  <si>
     <t>114</t>
   </si>
   <si>
-    <t>Post-Secondary Education</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -148,18 +148,18 @@
     <t>Health policy and administrative management</t>
   </si>
   <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>Health, General</t>
+  </si>
+  <si>
+    <t>Health</t>
+  </si>
+  <si>
     <t>121</t>
   </si>
   <si>
-    <t>Health, General</t>
-  </si>
-  <si>
-    <t>Health</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -184,12 +184,12 @@
     <t>Basic health care</t>
   </si>
   <si>
+    <t>Basic Health</t>
+  </si>
+  <si>
     <t>122</t>
   </si>
   <si>
-    <t>Basic Health</t>
-  </si>
-  <si>
     <t>12230</t>
   </si>
   <si>
@@ -238,12 +238,12 @@
     <t>NCDs control, general</t>
   </si>
   <si>
+    <t>Non-communicable diseases (NCDs)</t>
+  </si>
+  <si>
     <t>123</t>
   </si>
   <si>
-    <t>Non-communicable diseases (NCDs)</t>
-  </si>
-  <si>
     <t>12320</t>
   </si>
   <si>
@@ -388,18 +388,18 @@
     <t>Public sector policy and administrative management</t>
   </si>
   <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>Government &amp; Civil Society-general</t>
+  </si>
+  <si>
+    <t>Government &amp; Civil Society</t>
+  </si>
+  <si>
     <t>151</t>
   </si>
   <si>
-    <t>Government &amp; Civil Society-general</t>
-  </si>
-  <si>
-    <t>Government &amp; Civil Society</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -496,12 +496,12 @@
     <t>Security system management and reform</t>
   </si>
   <si>
+    <t>Conflict, Peace &amp; Security</t>
+  </si>
+  <si>
     <t>152</t>
   </si>
   <si>
-    <t>Conflict, Peace &amp; Security</t>
-  </si>
-  <si>
     <t>15220</t>
   </si>
   <si>
@@ -688,18 +688,18 @@
     <t>Energy policy and administrative management</t>
   </si>
   <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>Energy Policy</t>
+  </si>
+  <si>
+    <t>Energy</t>
+  </si>
+  <si>
     <t>231</t>
   </si>
   <si>
-    <t>Energy Policy</t>
-  </si>
-  <si>
-    <t>Energy</t>
-  </si>
-  <si>
-    <t>230</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -724,12 +724,12 @@
     <t>Energy generation, renewable sources - multiple technologies</t>
   </si>
   <si>
+    <t>Energy generation, renewable sources</t>
+  </si>
+  <si>
     <t>232</t>
   </si>
   <si>
-    <t>Energy generation, renewable sources</t>
-  </si>
-  <si>
     <t>23220</t>
   </si>
   <si>
@@ -784,12 +784,12 @@
     <t>Energy generation, non-renewable sources, unspecified</t>
   </si>
   <si>
+    <t>Energy generation, non-renewable sources</t>
+  </si>
+  <si>
     <t>233</t>
   </si>
   <si>
-    <t>Energy generation, non-renewable sources</t>
-  </si>
-  <si>
     <t>23320</t>
   </si>
   <si>
@@ -826,36 +826,36 @@
     <t>Hybrid energy electric power plants</t>
   </si>
   <si>
+    <t>Hybrid energy plants</t>
+  </si>
+  <si>
     <t>234</t>
   </si>
   <si>
-    <t>Hybrid energy plants</t>
-  </si>
-  <si>
     <t>23510</t>
   </si>
   <si>
     <t>Nuclear energy electric power plants and nuclear safety</t>
   </si>
   <si>
+    <t>Nuclear energy plants</t>
+  </si>
+  <si>
     <t>235</t>
   </si>
   <si>
-    <t>Nuclear energy plants</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
     <t>Heat plants</t>
   </si>
   <si>
+    <t>Energy distribution</t>
+  </si>
+  <si>
     <t>236</t>
   </si>
   <si>
-    <t>Energy distribution</t>
-  </si>
-  <si>
     <t>23620</t>
   </si>
   <si>
@@ -970,18 +970,18 @@
     <t>Agricultural policy and administrative management</t>
   </si>
   <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
+    <t>Agriculture, Forestry, Fishing</t>
+  </si>
+  <si>
     <t>311</t>
   </si>
   <si>
-    <t>Agriculture</t>
-  </si>
-  <si>
-    <t>Agriculture, Forestry, Fishing</t>
-  </si>
-  <si>
-    <t>310</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1090,12 +1090,12 @@
     <t>Forestry policy and administrative management</t>
   </si>
   <si>
+    <t>Forestry</t>
+  </si>
+  <si>
     <t>312</t>
   </si>
   <si>
-    <t>Forestry</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -1132,12 +1132,12 @@
     <t>Fishing policy and administrative management</t>
   </si>
   <si>
+    <t>Fishing</t>
+  </si>
+  <si>
     <t>313</t>
   </si>
   <si>
-    <t>Fishing</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -1168,18 +1168,18 @@
     <t>Industrial policy and administrative management</t>
   </si>
   <si>
+    <t>320</t>
+  </si>
+  <si>
+    <t>Industry</t>
+  </si>
+  <si>
+    <t>Industry, Mining, Construction</t>
+  </si>
+  <si>
     <t>321</t>
   </si>
   <si>
-    <t>Industry</t>
-  </si>
-  <si>
-    <t>Industry, Mining, Construction</t>
-  </si>
-  <si>
-    <t>320</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1294,12 +1294,12 @@
     <t>Mineral/mining policy and administrative management</t>
   </si>
   <si>
+    <t>Mineral Resources &amp; Mining</t>
+  </si>
+  <si>
     <t>322</t>
   </si>
   <si>
-    <t>Mineral Resources &amp; Mining</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -1360,10 +1360,10 @@
     <t>Construction policy and administrative management</t>
   </si>
   <si>
+    <t>Construction</t>
+  </si>
+  <si>
     <t>323</t>
-  </si>
-  <si>
-    <t>Construction</t>
   </si>
   <si>
     <t>33110</t>
@@ -2166,16 +2166,16 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
         <v>22</v>
-      </c>
-      <c r="E6" t="s">
-        <v>23</v>
       </c>
       <c r="F6" t="s">
         <v>12</v>
       </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2189,16 +2189,16 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" t="s">
         <v>22</v>
-      </c>
-      <c r="E7" t="s">
-        <v>23</v>
       </c>
       <c r="F7" t="s">
         <v>12</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2212,16 +2212,16 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" t="s">
         <v>22</v>
-      </c>
-      <c r="E8" t="s">
-        <v>23</v>
       </c>
       <c r="F8" t="s">
         <v>12</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2235,16 +2235,16 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" t="s">
         <v>22</v>
-      </c>
-      <c r="E9" t="s">
-        <v>23</v>
       </c>
       <c r="F9" t="s">
         <v>12</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2258,16 +2258,16 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" t="s">
         <v>32</v>
-      </c>
-      <c r="E10" t="s">
-        <v>33</v>
       </c>
       <c r="F10" t="s">
         <v>12</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2281,16 +2281,16 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" t="s">
         <v>32</v>
-      </c>
-      <c r="E11" t="s">
-        <v>33</v>
       </c>
       <c r="F11" t="s">
         <v>12</v>
       </c>
       <c r="G11" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2304,16 +2304,16 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" t="s">
         <v>38</v>
-      </c>
-      <c r="E12" t="s">
-        <v>39</v>
       </c>
       <c r="F12" t="s">
         <v>12</v>
       </c>
       <c r="G12" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2327,16 +2327,16 @@
         <v>9</v>
       </c>
       <c r="D13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" t="s">
         <v>38</v>
-      </c>
-      <c r="E13" t="s">
-        <v>39</v>
       </c>
       <c r="F13" t="s">
         <v>12</v>
       </c>
       <c r="G13" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2442,16 +2442,16 @@
         <v>9</v>
       </c>
       <c r="D18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18" t="s">
         <v>56</v>
-      </c>
-      <c r="E18" t="s">
-        <v>57</v>
       </c>
       <c r="F18" t="s">
         <v>46</v>
       </c>
       <c r="G18" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2465,16 +2465,16 @@
         <v>9</v>
       </c>
       <c r="D19" t="s">
+        <v>44</v>
+      </c>
+      <c r="E19" t="s">
         <v>56</v>
-      </c>
-      <c r="E19" t="s">
-        <v>57</v>
       </c>
       <c r="F19" t="s">
         <v>46</v>
       </c>
       <c r="G19" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2488,16 +2488,16 @@
         <v>9</v>
       </c>
       <c r="D20" t="s">
+        <v>44</v>
+      </c>
+      <c r="E20" t="s">
         <v>56</v>
-      </c>
-      <c r="E20" t="s">
-        <v>57</v>
       </c>
       <c r="F20" t="s">
         <v>46</v>
       </c>
       <c r="G20" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2511,16 +2511,16 @@
         <v>9</v>
       </c>
       <c r="D21" t="s">
+        <v>44</v>
+      </c>
+      <c r="E21" t="s">
         <v>56</v>
-      </c>
-      <c r="E21" t="s">
-        <v>57</v>
       </c>
       <c r="F21" t="s">
         <v>46</v>
       </c>
       <c r="G21" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2534,16 +2534,16 @@
         <v>9</v>
       </c>
       <c r="D22" t="s">
+        <v>44</v>
+      </c>
+      <c r="E22" t="s">
         <v>56</v>
-      </c>
-      <c r="E22" t="s">
-        <v>57</v>
       </c>
       <c r="F22" t="s">
         <v>46</v>
       </c>
       <c r="G22" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2557,16 +2557,16 @@
         <v>9</v>
       </c>
       <c r="D23" t="s">
+        <v>44</v>
+      </c>
+      <c r="E23" t="s">
         <v>56</v>
-      </c>
-      <c r="E23" t="s">
-        <v>57</v>
       </c>
       <c r="F23" t="s">
         <v>46</v>
       </c>
       <c r="G23" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2580,16 +2580,16 @@
         <v>9</v>
       </c>
       <c r="D24" t="s">
+        <v>44</v>
+      </c>
+      <c r="E24" t="s">
         <v>56</v>
-      </c>
-      <c r="E24" t="s">
-        <v>57</v>
       </c>
       <c r="F24" t="s">
         <v>46</v>
       </c>
       <c r="G24" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2603,16 +2603,16 @@
         <v>9</v>
       </c>
       <c r="D25" t="s">
+        <v>44</v>
+      </c>
+      <c r="E25" t="s">
         <v>56</v>
-      </c>
-      <c r="E25" t="s">
-        <v>57</v>
       </c>
       <c r="F25" t="s">
         <v>46</v>
       </c>
       <c r="G25" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2626,16 +2626,16 @@
         <v>9</v>
       </c>
       <c r="D26" t="s">
+        <v>44</v>
+      </c>
+      <c r="E26" t="s">
         <v>74</v>
-      </c>
-      <c r="E26" t="s">
-        <v>75</v>
       </c>
       <c r="F26" t="s">
         <v>46</v>
       </c>
       <c r="G26" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2649,16 +2649,16 @@
         <v>9</v>
       </c>
       <c r="D27" t="s">
+        <v>44</v>
+      </c>
+      <c r="E27" t="s">
         <v>74</v>
-      </c>
-      <c r="E27" t="s">
-        <v>75</v>
       </c>
       <c r="F27" t="s">
         <v>46</v>
       </c>
       <c r="G27" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2672,16 +2672,16 @@
         <v>9</v>
       </c>
       <c r="D28" t="s">
+        <v>44</v>
+      </c>
+      <c r="E28" t="s">
         <v>74</v>
-      </c>
-      <c r="E28" t="s">
-        <v>75</v>
       </c>
       <c r="F28" t="s">
         <v>46</v>
       </c>
       <c r="G28" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2695,16 +2695,16 @@
         <v>9</v>
       </c>
       <c r="D29" t="s">
+        <v>44</v>
+      </c>
+      <c r="E29" t="s">
         <v>74</v>
-      </c>
-      <c r="E29" t="s">
-        <v>75</v>
       </c>
       <c r="F29" t="s">
         <v>46</v>
       </c>
       <c r="G29" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2718,16 +2718,16 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
+        <v>44</v>
+      </c>
+      <c r="E30" t="s">
         <v>74</v>
-      </c>
-      <c r="E30" t="s">
-        <v>75</v>
       </c>
       <c r="F30" t="s">
         <v>46</v>
       </c>
       <c r="G30" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2741,16 +2741,16 @@
         <v>9</v>
       </c>
       <c r="D31" t="s">
+        <v>44</v>
+      </c>
+      <c r="E31" t="s">
         <v>74</v>
-      </c>
-      <c r="E31" t="s">
-        <v>75</v>
       </c>
       <c r="F31" t="s">
         <v>46</v>
       </c>
       <c r="G31" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -3500,16 +3500,16 @@
         <v>9</v>
       </c>
       <c r="D64" t="s">
+        <v>124</v>
+      </c>
+      <c r="E64" t="s">
         <v>160</v>
-      </c>
-      <c r="E64" t="s">
-        <v>161</v>
       </c>
       <c r="F64" t="s">
         <v>126</v>
       </c>
       <c r="G64" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3523,16 +3523,16 @@
         <v>9</v>
       </c>
       <c r="D65" t="s">
+        <v>124</v>
+      </c>
+      <c r="E65" t="s">
         <v>160</v>
-      </c>
-      <c r="E65" t="s">
-        <v>161</v>
       </c>
       <c r="F65" t="s">
         <v>126</v>
       </c>
       <c r="G65" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3546,16 +3546,16 @@
         <v>9</v>
       </c>
       <c r="D66" t="s">
+        <v>124</v>
+      </c>
+      <c r="E66" t="s">
         <v>160</v>
-      </c>
-      <c r="E66" t="s">
-        <v>161</v>
       </c>
       <c r="F66" t="s">
         <v>126</v>
       </c>
       <c r="G66" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3569,16 +3569,16 @@
         <v>9</v>
       </c>
       <c r="D67" t="s">
+        <v>124</v>
+      </c>
+      <c r="E67" t="s">
         <v>160</v>
-      </c>
-      <c r="E67" t="s">
-        <v>161</v>
       </c>
       <c r="F67" t="s">
         <v>126</v>
       </c>
       <c r="G67" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3592,16 +3592,16 @@
         <v>9</v>
       </c>
       <c r="D68" t="s">
+        <v>124</v>
+      </c>
+      <c r="E68" t="s">
         <v>160</v>
-      </c>
-      <c r="E68" t="s">
-        <v>161</v>
       </c>
       <c r="F68" t="s">
         <v>126</v>
       </c>
       <c r="G68" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3615,16 +3615,16 @@
         <v>9</v>
       </c>
       <c r="D69" t="s">
+        <v>124</v>
+      </c>
+      <c r="E69" t="s">
         <v>160</v>
-      </c>
-      <c r="E69" t="s">
-        <v>161</v>
       </c>
       <c r="F69" t="s">
         <v>126</v>
       </c>
       <c r="G69" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -4236,16 +4236,16 @@
         <v>9</v>
       </c>
       <c r="D96" t="s">
+        <v>224</v>
+      </c>
+      <c r="E96" t="s">
         <v>236</v>
-      </c>
-      <c r="E96" t="s">
-        <v>237</v>
       </c>
       <c r="F96" t="s">
         <v>226</v>
       </c>
       <c r="G96" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -4259,16 +4259,16 @@
         <v>9</v>
       </c>
       <c r="D97" t="s">
+        <v>224</v>
+      </c>
+      <c r="E97" t="s">
         <v>236</v>
-      </c>
-      <c r="E97" t="s">
-        <v>237</v>
       </c>
       <c r="F97" t="s">
         <v>226</v>
       </c>
       <c r="G97" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4282,16 +4282,16 @@
         <v>9</v>
       </c>
       <c r="D98" t="s">
+        <v>224</v>
+      </c>
+      <c r="E98" t="s">
         <v>236</v>
-      </c>
-      <c r="E98" t="s">
-        <v>237</v>
       </c>
       <c r="F98" t="s">
         <v>226</v>
       </c>
       <c r="G98" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4305,16 +4305,16 @@
         <v>9</v>
       </c>
       <c r="D99" t="s">
+        <v>224</v>
+      </c>
+      <c r="E99" t="s">
         <v>236</v>
-      </c>
-      <c r="E99" t="s">
-        <v>237</v>
       </c>
       <c r="F99" t="s">
         <v>226</v>
       </c>
       <c r="G99" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4328,16 +4328,16 @@
         <v>9</v>
       </c>
       <c r="D100" t="s">
+        <v>224</v>
+      </c>
+      <c r="E100" t="s">
         <v>236</v>
-      </c>
-      <c r="E100" t="s">
-        <v>237</v>
       </c>
       <c r="F100" t="s">
         <v>226</v>
       </c>
       <c r="G100" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4351,16 +4351,16 @@
         <v>9</v>
       </c>
       <c r="D101" t="s">
+        <v>224</v>
+      </c>
+      <c r="E101" t="s">
         <v>236</v>
-      </c>
-      <c r="E101" t="s">
-        <v>237</v>
       </c>
       <c r="F101" t="s">
         <v>226</v>
       </c>
       <c r="G101" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4374,16 +4374,16 @@
         <v>9</v>
       </c>
       <c r="D102" t="s">
+        <v>224</v>
+      </c>
+      <c r="E102" t="s">
         <v>236</v>
-      </c>
-      <c r="E102" t="s">
-        <v>237</v>
       </c>
       <c r="F102" t="s">
         <v>226</v>
       </c>
       <c r="G102" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4397,16 +4397,16 @@
         <v>9</v>
       </c>
       <c r="D103" t="s">
+        <v>224</v>
+      </c>
+      <c r="E103" t="s">
         <v>236</v>
-      </c>
-      <c r="E103" t="s">
-        <v>237</v>
       </c>
       <c r="F103" t="s">
         <v>226</v>
       </c>
       <c r="G103" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4420,16 +4420,16 @@
         <v>9</v>
       </c>
       <c r="D104" t="s">
+        <v>224</v>
+      </c>
+      <c r="E104" t="s">
         <v>236</v>
-      </c>
-      <c r="E104" t="s">
-        <v>237</v>
       </c>
       <c r="F104" t="s">
         <v>226</v>
       </c>
       <c r="G104" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4443,16 +4443,16 @@
         <v>9</v>
       </c>
       <c r="D105" t="s">
+        <v>224</v>
+      </c>
+      <c r="E105" t="s">
         <v>256</v>
-      </c>
-      <c r="E105" t="s">
-        <v>257</v>
       </c>
       <c r="F105" t="s">
         <v>226</v>
       </c>
       <c r="G105" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4466,16 +4466,16 @@
         <v>9</v>
       </c>
       <c r="D106" t="s">
+        <v>224</v>
+      </c>
+      <c r="E106" t="s">
         <v>256</v>
-      </c>
-      <c r="E106" t="s">
-        <v>257</v>
       </c>
       <c r="F106" t="s">
         <v>226</v>
       </c>
       <c r="G106" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4489,16 +4489,16 @@
         <v>9</v>
       </c>
       <c r="D107" t="s">
+        <v>224</v>
+      </c>
+      <c r="E107" t="s">
         <v>256</v>
-      </c>
-      <c r="E107" t="s">
-        <v>257</v>
       </c>
       <c r="F107" t="s">
         <v>226</v>
       </c>
       <c r="G107" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4512,16 +4512,16 @@
         <v>9</v>
       </c>
       <c r="D108" t="s">
+        <v>224</v>
+      </c>
+      <c r="E108" t="s">
         <v>256</v>
-      </c>
-      <c r="E108" t="s">
-        <v>257</v>
       </c>
       <c r="F108" t="s">
         <v>226</v>
       </c>
       <c r="G108" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4535,16 +4535,16 @@
         <v>9</v>
       </c>
       <c r="D109" t="s">
+        <v>224</v>
+      </c>
+      <c r="E109" t="s">
         <v>256</v>
-      </c>
-      <c r="E109" t="s">
-        <v>257</v>
       </c>
       <c r="F109" t="s">
         <v>226</v>
       </c>
       <c r="G109" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4558,16 +4558,16 @@
         <v>9</v>
       </c>
       <c r="D110" t="s">
+        <v>224</v>
+      </c>
+      <c r="E110" t="s">
         <v>256</v>
-      </c>
-      <c r="E110" t="s">
-        <v>257</v>
       </c>
       <c r="F110" t="s">
         <v>226</v>
       </c>
       <c r="G110" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4581,16 +4581,16 @@
         <v>9</v>
       </c>
       <c r="D111" t="s">
+        <v>224</v>
+      </c>
+      <c r="E111" t="s">
         <v>270</v>
-      </c>
-      <c r="E111" t="s">
-        <v>271</v>
       </c>
       <c r="F111" t="s">
         <v>226</v>
       </c>
       <c r="G111" t="s">
-        <v>227</v>
+        <v>271</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4604,16 +4604,16 @@
         <v>9</v>
       </c>
       <c r="D112" t="s">
+        <v>224</v>
+      </c>
+      <c r="E112" t="s">
         <v>274</v>
-      </c>
-      <c r="E112" t="s">
-        <v>275</v>
       </c>
       <c r="F112" t="s">
         <v>226</v>
       </c>
       <c r="G112" t="s">
-        <v>227</v>
+        <v>275</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4627,16 +4627,16 @@
         <v>9</v>
       </c>
       <c r="D113" t="s">
+        <v>224</v>
+      </c>
+      <c r="E113" t="s">
         <v>278</v>
-      </c>
-      <c r="E113" t="s">
-        <v>279</v>
       </c>
       <c r="F113" t="s">
         <v>226</v>
       </c>
       <c r="G113" t="s">
-        <v>227</v>
+        <v>279</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4650,16 +4650,16 @@
         <v>9</v>
       </c>
       <c r="D114" t="s">
+        <v>224</v>
+      </c>
+      <c r="E114" t="s">
         <v>278</v>
-      </c>
-      <c r="E114" t="s">
-        <v>279</v>
       </c>
       <c r="F114" t="s">
         <v>226</v>
       </c>
       <c r="G114" t="s">
-        <v>227</v>
+        <v>279</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4673,16 +4673,16 @@
         <v>9</v>
       </c>
       <c r="D115" t="s">
+        <v>224</v>
+      </c>
+      <c r="E115" t="s">
         <v>278</v>
-      </c>
-      <c r="E115" t="s">
-        <v>279</v>
       </c>
       <c r="F115" t="s">
         <v>226</v>
       </c>
       <c r="G115" t="s">
-        <v>227</v>
+        <v>279</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4696,16 +4696,16 @@
         <v>9</v>
       </c>
       <c r="D116" t="s">
+        <v>224</v>
+      </c>
+      <c r="E116" t="s">
         <v>278</v>
-      </c>
-      <c r="E116" t="s">
-        <v>279</v>
       </c>
       <c r="F116" t="s">
         <v>226</v>
       </c>
       <c r="G116" t="s">
-        <v>227</v>
+        <v>279</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4719,16 +4719,16 @@
         <v>9</v>
       </c>
       <c r="D117" t="s">
+        <v>224</v>
+      </c>
+      <c r="E117" t="s">
         <v>278</v>
-      </c>
-      <c r="E117" t="s">
-        <v>279</v>
       </c>
       <c r="F117" t="s">
         <v>226</v>
       </c>
       <c r="G117" t="s">
-        <v>227</v>
+        <v>279</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4742,16 +4742,16 @@
         <v>9</v>
       </c>
       <c r="D118" t="s">
+        <v>224</v>
+      </c>
+      <c r="E118" t="s">
         <v>278</v>
-      </c>
-      <c r="E118" t="s">
-        <v>279</v>
       </c>
       <c r="F118" t="s">
         <v>226</v>
       </c>
       <c r="G118" t="s">
-        <v>227</v>
+        <v>279</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4765,16 +4765,16 @@
         <v>9</v>
       </c>
       <c r="D119" t="s">
+        <v>224</v>
+      </c>
+      <c r="E119" t="s">
         <v>278</v>
-      </c>
-      <c r="E119" t="s">
-        <v>279</v>
       </c>
       <c r="F119" t="s">
         <v>226</v>
       </c>
       <c r="G119" t="s">
-        <v>227</v>
+        <v>279</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -5432,16 +5432,16 @@
         <v>9</v>
       </c>
       <c r="D148" t="s">
+        <v>318</v>
+      </c>
+      <c r="E148" t="s">
         <v>358</v>
-      </c>
-      <c r="E148" t="s">
-        <v>359</v>
       </c>
       <c r="F148" t="s">
         <v>320</v>
       </c>
       <c r="G148" t="s">
-        <v>321</v>
+        <v>359</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5455,16 +5455,16 @@
         <v>9</v>
       </c>
       <c r="D149" t="s">
+        <v>318</v>
+      </c>
+      <c r="E149" t="s">
         <v>358</v>
-      </c>
-      <c r="E149" t="s">
-        <v>359</v>
       </c>
       <c r="F149" t="s">
         <v>320</v>
       </c>
       <c r="G149" t="s">
-        <v>321</v>
+        <v>359</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5478,16 +5478,16 @@
         <v>9</v>
       </c>
       <c r="D150" t="s">
+        <v>318</v>
+      </c>
+      <c r="E150" t="s">
         <v>358</v>
-      </c>
-      <c r="E150" t="s">
-        <v>359</v>
       </c>
       <c r="F150" t="s">
         <v>320</v>
       </c>
       <c r="G150" t="s">
-        <v>321</v>
+        <v>359</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5501,16 +5501,16 @@
         <v>9</v>
       </c>
       <c r="D151" t="s">
+        <v>318</v>
+      </c>
+      <c r="E151" t="s">
         <v>358</v>
-      </c>
-      <c r="E151" t="s">
-        <v>359</v>
       </c>
       <c r="F151" t="s">
         <v>320</v>
       </c>
       <c r="G151" t="s">
-        <v>321</v>
+        <v>359</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5524,16 +5524,16 @@
         <v>9</v>
       </c>
       <c r="D152" t="s">
+        <v>318</v>
+      </c>
+      <c r="E152" t="s">
         <v>358</v>
-      </c>
-      <c r="E152" t="s">
-        <v>359</v>
       </c>
       <c r="F152" t="s">
         <v>320</v>
       </c>
       <c r="G152" t="s">
-        <v>321</v>
+        <v>359</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5547,16 +5547,16 @@
         <v>9</v>
       </c>
       <c r="D153" t="s">
+        <v>318</v>
+      </c>
+      <c r="E153" t="s">
         <v>358</v>
-      </c>
-      <c r="E153" t="s">
-        <v>359</v>
       </c>
       <c r="F153" t="s">
         <v>320</v>
       </c>
       <c r="G153" t="s">
-        <v>321</v>
+        <v>359</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5570,16 +5570,16 @@
         <v>9</v>
       </c>
       <c r="D154" t="s">
+        <v>318</v>
+      </c>
+      <c r="E154" t="s">
         <v>372</v>
-      </c>
-      <c r="E154" t="s">
-        <v>373</v>
       </c>
       <c r="F154" t="s">
         <v>320</v>
       </c>
       <c r="G154" t="s">
-        <v>321</v>
+        <v>373</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5593,16 +5593,16 @@
         <v>9</v>
       </c>
       <c r="D155" t="s">
+        <v>318</v>
+      </c>
+      <c r="E155" t="s">
         <v>372</v>
-      </c>
-      <c r="E155" t="s">
-        <v>373</v>
       </c>
       <c r="F155" t="s">
         <v>320</v>
       </c>
       <c r="G155" t="s">
-        <v>321</v>
+        <v>373</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5616,16 +5616,16 @@
         <v>9</v>
       </c>
       <c r="D156" t="s">
+        <v>318</v>
+      </c>
+      <c r="E156" t="s">
         <v>372</v>
-      </c>
-      <c r="E156" t="s">
-        <v>373</v>
       </c>
       <c r="F156" t="s">
         <v>320</v>
       </c>
       <c r="G156" t="s">
-        <v>321</v>
+        <v>373</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5639,16 +5639,16 @@
         <v>9</v>
       </c>
       <c r="D157" t="s">
+        <v>318</v>
+      </c>
+      <c r="E157" t="s">
         <v>372</v>
-      </c>
-      <c r="E157" t="s">
-        <v>373</v>
       </c>
       <c r="F157" t="s">
         <v>320</v>
       </c>
       <c r="G157" t="s">
-        <v>321</v>
+        <v>373</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5662,16 +5662,16 @@
         <v>9</v>
       </c>
       <c r="D158" t="s">
+        <v>318</v>
+      </c>
+      <c r="E158" t="s">
         <v>372</v>
-      </c>
-      <c r="E158" t="s">
-        <v>373</v>
       </c>
       <c r="F158" t="s">
         <v>320</v>
       </c>
       <c r="G158" t="s">
-        <v>321</v>
+        <v>373</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -6122,16 +6122,16 @@
         <v>9</v>
       </c>
       <c r="D178" t="s">
+        <v>384</v>
+      </c>
+      <c r="E178" t="s">
         <v>426</v>
-      </c>
-      <c r="E178" t="s">
-        <v>427</v>
       </c>
       <c r="F178" t="s">
         <v>386</v>
       </c>
       <c r="G178" t="s">
-        <v>387</v>
+        <v>427</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -6145,16 +6145,16 @@
         <v>9</v>
       </c>
       <c r="D179" t="s">
+        <v>384</v>
+      </c>
+      <c r="E179" t="s">
         <v>426</v>
-      </c>
-      <c r="E179" t="s">
-        <v>427</v>
       </c>
       <c r="F179" t="s">
         <v>386</v>
       </c>
       <c r="G179" t="s">
-        <v>387</v>
+        <v>427</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -6168,16 +6168,16 @@
         <v>9</v>
       </c>
       <c r="D180" t="s">
+        <v>384</v>
+      </c>
+      <c r="E180" t="s">
         <v>426</v>
-      </c>
-      <c r="E180" t="s">
-        <v>427</v>
       </c>
       <c r="F180" t="s">
         <v>386</v>
       </c>
       <c r="G180" t="s">
-        <v>387</v>
+        <v>427</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -6191,16 +6191,16 @@
         <v>9</v>
       </c>
       <c r="D181" t="s">
+        <v>384</v>
+      </c>
+      <c r="E181" t="s">
         <v>426</v>
-      </c>
-      <c r="E181" t="s">
-        <v>427</v>
       </c>
       <c r="F181" t="s">
         <v>386</v>
       </c>
       <c r="G181" t="s">
-        <v>387</v>
+        <v>427</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -6214,16 +6214,16 @@
         <v>9</v>
       </c>
       <c r="D182" t="s">
+        <v>384</v>
+      </c>
+      <c r="E182" t="s">
         <v>426</v>
-      </c>
-      <c r="E182" t="s">
-        <v>427</v>
       </c>
       <c r="F182" t="s">
         <v>386</v>
       </c>
       <c r="G182" t="s">
-        <v>387</v>
+        <v>427</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -6237,16 +6237,16 @@
         <v>9</v>
       </c>
       <c r="D183" t="s">
+        <v>384</v>
+      </c>
+      <c r="E183" t="s">
         <v>426</v>
-      </c>
-      <c r="E183" t="s">
-        <v>427</v>
       </c>
       <c r="F183" t="s">
         <v>386</v>
       </c>
       <c r="G183" t="s">
-        <v>387</v>
+        <v>427</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -6260,16 +6260,16 @@
         <v>9</v>
       </c>
       <c r="D184" t="s">
+        <v>384</v>
+      </c>
+      <c r="E184" t="s">
         <v>426</v>
-      </c>
-      <c r="E184" t="s">
-        <v>427</v>
       </c>
       <c r="F184" t="s">
         <v>386</v>
       </c>
       <c r="G184" t="s">
-        <v>387</v>
+        <v>427</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -6283,16 +6283,16 @@
         <v>9</v>
       </c>
       <c r="D185" t="s">
+        <v>384</v>
+      </c>
+      <c r="E185" t="s">
         <v>426</v>
-      </c>
-      <c r="E185" t="s">
-        <v>427</v>
       </c>
       <c r="F185" t="s">
         <v>386</v>
       </c>
       <c r="G185" t="s">
-        <v>387</v>
+        <v>427</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -6306,16 +6306,16 @@
         <v>9</v>
       </c>
       <c r="D186" t="s">
+        <v>384</v>
+      </c>
+      <c r="E186" t="s">
         <v>426</v>
-      </c>
-      <c r="E186" t="s">
-        <v>427</v>
       </c>
       <c r="F186" t="s">
         <v>386</v>
       </c>
       <c r="G186" t="s">
-        <v>387</v>
+        <v>427</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -6329,16 +6329,16 @@
         <v>9</v>
       </c>
       <c r="D187" t="s">
+        <v>384</v>
+      </c>
+      <c r="E187" t="s">
         <v>426</v>
-      </c>
-      <c r="E187" t="s">
-        <v>427</v>
       </c>
       <c r="F187" t="s">
         <v>386</v>
       </c>
       <c r="G187" t="s">
-        <v>387</v>
+        <v>427</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -6352,16 +6352,16 @@
         <v>9</v>
       </c>
       <c r="D188" t="s">
+        <v>384</v>
+      </c>
+      <c r="E188" t="s">
         <v>448</v>
-      </c>
-      <c r="E188" t="s">
-        <v>449</v>
       </c>
       <c r="F188" t="s">
         <v>386</v>
       </c>
       <c r="G188" t="s">
-        <v>387</v>
+        <v>449</v>
       </c>
     </row>
     <row r="189" spans="1:7">

--- a/api/xlsx/en/SectorGroup.xlsx
+++ b/api/xlsx/en/SectorGroup.xlsx
@@ -25,15 +25,15 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:category-name</t>
+  </si>
+  <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
-    <t>codeforiati:category-name</t>
-  </si>
-  <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
@@ -46,15 +46,15 @@
     <t>active</t>
   </si>
   <si>
+    <t>Education, Level Unspecified</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
     <t>110</t>
   </si>
   <si>
-    <t>Education, Level Unspecified</t>
-  </si>
-  <si>
-    <t>Education</t>
-  </si>
-  <si>
     <t>111</t>
   </si>
   <si>
@@ -148,15 +148,15 @@
     <t>Health policy and administrative management</t>
   </si>
   <si>
+    <t>Health, General</t>
+  </si>
+  <si>
+    <t>Health</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
-    <t>Health, General</t>
-  </si>
-  <si>
-    <t>Health</t>
-  </si>
-  <si>
     <t>121</t>
   </si>
   <si>
@@ -280,12 +280,12 @@
     <t>Population policy and administrative management</t>
   </si>
   <si>
+    <t>Population Policies/Programmes &amp; Reproductive Health</t>
+  </si>
+  <si>
     <t>130</t>
   </si>
   <si>
-    <t>Population Policies/Programmes &amp; Reproductive Health</t>
-  </si>
-  <si>
     <t>13020</t>
   </si>
   <si>
@@ -316,12 +316,12 @@
     <t>Water sector policy and administrative management</t>
   </si>
   <si>
+    <t>Water Supply &amp; Sanitation</t>
+  </si>
+  <si>
     <t>140</t>
   </si>
   <si>
-    <t>Water Supply &amp; Sanitation</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -388,15 +388,15 @@
     <t>Public sector policy and administrative management</t>
   </si>
   <si>
+    <t>Government &amp; Civil Society-general</t>
+  </si>
+  <si>
+    <t>Government &amp; Civil Society</t>
+  </si>
+  <si>
     <t>150</t>
   </si>
   <si>
-    <t>Government &amp; Civil Society-general</t>
-  </si>
-  <si>
-    <t>Government &amp; Civil Society</t>
-  </si>
-  <si>
     <t>151</t>
   </si>
   <si>
@@ -538,12 +538,12 @@
     <t>Social Protection</t>
   </si>
   <si>
+    <t>Other Social Infrastructure &amp; Services</t>
+  </si>
+  <si>
     <t>160</t>
   </si>
   <si>
-    <t>Other Social Infrastructure &amp; Services</t>
-  </si>
-  <si>
     <t>16020</t>
   </si>
   <si>
@@ -610,12 +610,12 @@
     <t>Transport policy and administrative management</t>
   </si>
   <si>
+    <t>Transport &amp; Storage</t>
+  </si>
+  <si>
     <t>210</t>
   </si>
   <si>
-    <t>Transport &amp; Storage</t>
-  </si>
-  <si>
     <t>21020</t>
   </si>
   <si>
@@ -658,12 +658,12 @@
     <t>Communications policy and administrative management</t>
   </si>
   <si>
+    <t>Communications</t>
+  </si>
+  <si>
     <t>220</t>
   </si>
   <si>
-    <t>Communications</t>
-  </si>
-  <si>
     <t>22020</t>
   </si>
   <si>
@@ -688,15 +688,15 @@
     <t>Energy policy and administrative management</t>
   </si>
   <si>
+    <t>Energy Policy</t>
+  </si>
+  <si>
+    <t>Energy</t>
+  </si>
+  <si>
     <t>230</t>
   </si>
   <si>
-    <t>Energy Policy</t>
-  </si>
-  <si>
-    <t>Energy</t>
-  </si>
-  <si>
     <t>231</t>
   </si>
   <si>
@@ -898,12 +898,12 @@
     <t>Financial policy and administrative management</t>
   </si>
   <si>
+    <t>Banking &amp; Financial Services</t>
+  </si>
+  <si>
     <t>240</t>
   </si>
   <si>
-    <t>Banking &amp; Financial Services</t>
-  </si>
-  <si>
     <t>24020</t>
   </si>
   <si>
@@ -940,12 +940,12 @@
     <t>Business policy and administration</t>
   </si>
   <si>
+    <t>Business &amp; Other Services</t>
+  </si>
+  <si>
     <t>250</t>
   </si>
   <si>
-    <t>Business &amp; Other Services</t>
-  </si>
-  <si>
     <t>25020</t>
   </si>
   <si>
@@ -970,15 +970,15 @@
     <t>Agricultural policy and administrative management</t>
   </si>
   <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
+    <t>Agriculture, Forestry, Fishing</t>
+  </si>
+  <si>
     <t>310</t>
   </si>
   <si>
-    <t>Agriculture</t>
-  </si>
-  <si>
-    <t>Agriculture, Forestry, Fishing</t>
-  </si>
-  <si>
     <t>311</t>
   </si>
   <si>
@@ -1168,15 +1168,15 @@
     <t>Industrial policy and administrative management</t>
   </si>
   <si>
+    <t>Industry</t>
+  </si>
+  <si>
+    <t>Industry, Mining, Construction</t>
+  </si>
+  <si>
     <t>320</t>
   </si>
   <si>
-    <t>Industry</t>
-  </si>
-  <si>
-    <t>Industry, Mining, Construction</t>
-  </si>
-  <si>
     <t>321</t>
   </si>
   <si>
@@ -1372,12 +1372,12 @@
     <t>Trade policy and administrative management</t>
   </si>
   <si>
+    <t>Trade Policies &amp; Regulations</t>
+  </si>
+  <si>
     <t>331</t>
   </si>
   <si>
-    <t>Trade Policies &amp; Regulations</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1414,24 +1414,24 @@
     <t>Tourism policy and administrative management</t>
   </si>
   <si>
+    <t>Tourism</t>
+  </si>
+  <si>
     <t>332</t>
   </si>
   <si>
-    <t>Tourism</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
     <t>Environmental policy and administrative management</t>
   </si>
   <si>
+    <t>General Environment Protection</t>
+  </si>
+  <si>
     <t>410</t>
   </si>
   <si>
-    <t>General Environment Protection</t>
-  </si>
-  <si>
     <t>41020</t>
   </si>
   <si>
@@ -1468,12 +1468,12 @@
     <t>Multisector aid</t>
   </si>
   <si>
+    <t>Other Multisector</t>
+  </si>
+  <si>
     <t>430</t>
   </si>
   <si>
-    <t>Other Multisector</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -1534,36 +1534,36 @@
     <t>General budget support-related aid</t>
   </si>
   <si>
+    <t>General Budget Support</t>
+  </si>
+  <si>
     <t>510</t>
   </si>
   <si>
-    <t>General Budget Support</t>
-  </si>
-  <si>
     <t>52010</t>
   </si>
   <si>
     <t>Food assistance</t>
   </si>
   <si>
+    <t>Development Food Assistance</t>
+  </si>
+  <si>
     <t>520</t>
   </si>
   <si>
-    <t>Development Food Assistance</t>
-  </si>
-  <si>
     <t>53030</t>
   </si>
   <si>
     <t>Import support (capital goods)</t>
   </si>
   <si>
+    <t>Other Commodity Assistance</t>
+  </si>
+  <si>
     <t>530</t>
   </si>
   <si>
-    <t>Other Commodity Assistance</t>
-  </si>
-  <si>
     <t>53040</t>
   </si>
   <si>
@@ -1576,12 +1576,12 @@
     <t>Action relating to debt</t>
   </si>
   <si>
+    <t>Action Relating to Debt</t>
+  </si>
+  <si>
     <t>600</t>
   </si>
   <si>
-    <t>Action Relating to Debt</t>
-  </si>
-  <si>
     <t>60020</t>
   </si>
   <si>
@@ -1624,12 +1624,12 @@
     <t>Material relief assistance and services</t>
   </si>
   <si>
+    <t>Emergency Response</t>
+  </si>
+  <si>
     <t>720</t>
   </si>
   <si>
-    <t>Emergency Response</t>
-  </si>
-  <si>
     <t>72040</t>
   </si>
   <si>
@@ -1648,58 +1648,58 @@
     <t>Immediate post-emergency reconstruction and rehabilitation</t>
   </si>
   <si>
+    <t>Reconstruction Relief &amp; Rehabilitation</t>
+  </si>
+  <si>
     <t>730</t>
   </si>
   <si>
-    <t>Reconstruction Relief &amp; Rehabilitation</t>
-  </si>
-  <si>
     <t>74020</t>
   </si>
   <si>
     <t>Multi-hazard response preparedness</t>
   </si>
   <si>
+    <t>Disaster Prevention &amp; Preparedness</t>
+  </si>
+  <si>
     <t>740</t>
   </si>
   <si>
-    <t>Disaster Prevention &amp; Preparedness</t>
-  </si>
-  <si>
     <t>91010</t>
   </si>
   <si>
     <t>Administrative costs (non-sector allocable)</t>
   </si>
   <si>
+    <t>Administrative Costs of Donors</t>
+  </si>
+  <si>
     <t>910</t>
   </si>
   <si>
-    <t>Administrative Costs of Donors</t>
-  </si>
-  <si>
     <t>93010</t>
   </si>
   <si>
     <t>Refugees/asylum seekers in donor countries (non-sector allocable)</t>
   </si>
   <si>
+    <t>Refugees in Donor Countries</t>
+  </si>
+  <si>
     <t>930</t>
   </si>
   <si>
-    <t>Refugees in Donor Countries</t>
-  </si>
-  <si>
     <t>99810</t>
   </si>
   <si>
     <t>Sectors not specified</t>
   </si>
   <si>
+    <t>Unallocated / Unspecified</t>
+  </si>
+  <si>
     <t>998</t>
-  </si>
-  <si>
-    <t>Unallocated / Unspecified</t>
   </si>
   <si>
     <t>99820</t>
@@ -2166,10 +2166,10 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
         <v>12</v>
@@ -2189,10 +2189,10 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
         <v>12</v>
@@ -2212,10 +2212,10 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s">
         <v>12</v>
@@ -2235,10 +2235,10 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E9" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
         <v>12</v>
@@ -2258,10 +2258,10 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E10" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F10" t="s">
         <v>12</v>
@@ -2281,10 +2281,10 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F11" t="s">
         <v>12</v>
@@ -2304,10 +2304,10 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F12" t="s">
         <v>12</v>
@@ -2327,10 +2327,10 @@
         <v>9</v>
       </c>
       <c r="D13" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E13" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F13" t="s">
         <v>12</v>
@@ -2442,10 +2442,10 @@
         <v>9</v>
       </c>
       <c r="D18" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E18" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F18" t="s">
         <v>46</v>
@@ -2465,10 +2465,10 @@
         <v>9</v>
       </c>
       <c r="D19" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E19" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F19" t="s">
         <v>46</v>
@@ -2488,10 +2488,10 @@
         <v>9</v>
       </c>
       <c r="D20" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E20" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F20" t="s">
         <v>46</v>
@@ -2511,10 +2511,10 @@
         <v>9</v>
       </c>
       <c r="D21" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E21" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F21" t="s">
         <v>46</v>
@@ -2534,10 +2534,10 @@
         <v>9</v>
       </c>
       <c r="D22" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E22" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F22" t="s">
         <v>46</v>
@@ -2557,10 +2557,10 @@
         <v>9</v>
       </c>
       <c r="D23" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E23" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F23" t="s">
         <v>46</v>
@@ -2580,10 +2580,10 @@
         <v>9</v>
       </c>
       <c r="D24" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E24" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F24" t="s">
         <v>46</v>
@@ -2603,10 +2603,10 @@
         <v>9</v>
       </c>
       <c r="D25" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E25" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F25" t="s">
         <v>46</v>
@@ -2626,10 +2626,10 @@
         <v>9</v>
       </c>
       <c r="D26" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E26" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="F26" t="s">
         <v>46</v>
@@ -2649,10 +2649,10 @@
         <v>9</v>
       </c>
       <c r="D27" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E27" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="F27" t="s">
         <v>46</v>
@@ -2672,10 +2672,10 @@
         <v>9</v>
       </c>
       <c r="D28" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E28" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="F28" t="s">
         <v>46</v>
@@ -2695,10 +2695,10 @@
         <v>9</v>
       </c>
       <c r="D29" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E29" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="F29" t="s">
         <v>46</v>
@@ -2718,10 +2718,10 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E30" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="F30" t="s">
         <v>46</v>
@@ -2741,10 +2741,10 @@
         <v>9</v>
       </c>
       <c r="D31" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E31" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="F31" t="s">
         <v>46</v>
@@ -2767,13 +2767,13 @@
         <v>88</v>
       </c>
       <c r="E32" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F32" t="s">
         <v>89</v>
       </c>
       <c r="G32" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2790,13 +2790,13 @@
         <v>88</v>
       </c>
       <c r="E33" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F33" t="s">
         <v>89</v>
       </c>
       <c r="G33" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2813,13 +2813,13 @@
         <v>88</v>
       </c>
       <c r="E34" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F34" t="s">
         <v>89</v>
       </c>
       <c r="G34" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2836,13 +2836,13 @@
         <v>88</v>
       </c>
       <c r="E35" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F35" t="s">
         <v>89</v>
       </c>
       <c r="G35" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2859,13 +2859,13 @@
         <v>88</v>
       </c>
       <c r="E36" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F36" t="s">
         <v>89</v>
       </c>
       <c r="G36" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2882,13 +2882,13 @@
         <v>100</v>
       </c>
       <c r="E37" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F37" t="s">
         <v>101</v>
       </c>
       <c r="G37" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2905,13 +2905,13 @@
         <v>100</v>
       </c>
       <c r="E38" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F38" t="s">
         <v>101</v>
       </c>
       <c r="G38" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2928,13 +2928,13 @@
         <v>100</v>
       </c>
       <c r="E39" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F39" t="s">
         <v>101</v>
       </c>
       <c r="G39" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2951,13 +2951,13 @@
         <v>100</v>
       </c>
       <c r="E40" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F40" t="s">
         <v>101</v>
       </c>
       <c r="G40" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2974,13 +2974,13 @@
         <v>100</v>
       </c>
       <c r="E41" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F41" t="s">
         <v>101</v>
       </c>
       <c r="G41" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2997,13 +2997,13 @@
         <v>100</v>
       </c>
       <c r="E42" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F42" t="s">
         <v>101</v>
       </c>
       <c r="G42" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3020,13 +3020,13 @@
         <v>100</v>
       </c>
       <c r="E43" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F43" t="s">
         <v>101</v>
       </c>
       <c r="G43" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3043,13 +3043,13 @@
         <v>100</v>
       </c>
       <c r="E44" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F44" t="s">
         <v>101</v>
       </c>
       <c r="G44" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3066,13 +3066,13 @@
         <v>100</v>
       </c>
       <c r="E45" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F45" t="s">
         <v>101</v>
       </c>
       <c r="G45" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3089,13 +3089,13 @@
         <v>100</v>
       </c>
       <c r="E46" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F46" t="s">
         <v>101</v>
       </c>
       <c r="G46" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3112,13 +3112,13 @@
         <v>100</v>
       </c>
       <c r="E47" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F47" t="s">
         <v>101</v>
       </c>
       <c r="G47" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3500,10 +3500,10 @@
         <v>9</v>
       </c>
       <c r="D64" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E64" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="F64" t="s">
         <v>126</v>
@@ -3523,10 +3523,10 @@
         <v>9</v>
       </c>
       <c r="D65" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E65" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="F65" t="s">
         <v>126</v>
@@ -3546,10 +3546,10 @@
         <v>9</v>
       </c>
       <c r="D66" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E66" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="F66" t="s">
         <v>126</v>
@@ -3569,10 +3569,10 @@
         <v>9</v>
       </c>
       <c r="D67" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E67" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="F67" t="s">
         <v>126</v>
@@ -3592,10 +3592,10 @@
         <v>9</v>
       </c>
       <c r="D68" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E68" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="F68" t="s">
         <v>126</v>
@@ -3615,10 +3615,10 @@
         <v>9</v>
       </c>
       <c r="D69" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E69" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="F69" t="s">
         <v>126</v>
@@ -3641,13 +3641,13 @@
         <v>174</v>
       </c>
       <c r="E70" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F70" t="s">
         <v>175</v>
       </c>
       <c r="G70" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3664,13 +3664,13 @@
         <v>174</v>
       </c>
       <c r="E71" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F71" t="s">
         <v>175</v>
       </c>
       <c r="G71" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3687,13 +3687,13 @@
         <v>174</v>
       </c>
       <c r="E72" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F72" t="s">
         <v>175</v>
       </c>
       <c r="G72" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3710,13 +3710,13 @@
         <v>174</v>
       </c>
       <c r="E73" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F73" t="s">
         <v>175</v>
       </c>
       <c r="G73" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3733,13 +3733,13 @@
         <v>174</v>
       </c>
       <c r="E74" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F74" t="s">
         <v>175</v>
       </c>
       <c r="G74" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3756,13 +3756,13 @@
         <v>174</v>
       </c>
       <c r="E75" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F75" t="s">
         <v>175</v>
       </c>
       <c r="G75" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3779,13 +3779,13 @@
         <v>174</v>
       </c>
       <c r="E76" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F76" t="s">
         <v>175</v>
       </c>
       <c r="G76" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3802,13 +3802,13 @@
         <v>174</v>
       </c>
       <c r="E77" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F77" t="s">
         <v>175</v>
       </c>
       <c r="G77" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3825,13 +3825,13 @@
         <v>174</v>
       </c>
       <c r="E78" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F78" t="s">
         <v>175</v>
       </c>
       <c r="G78" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3848,13 +3848,13 @@
         <v>174</v>
       </c>
       <c r="E79" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F79" t="s">
         <v>175</v>
       </c>
       <c r="G79" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3871,13 +3871,13 @@
         <v>174</v>
       </c>
       <c r="E80" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F80" t="s">
         <v>175</v>
       </c>
       <c r="G80" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3894,13 +3894,13 @@
         <v>198</v>
       </c>
       <c r="E81" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F81" t="s">
         <v>199</v>
       </c>
       <c r="G81" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3917,13 +3917,13 @@
         <v>198</v>
       </c>
       <c r="E82" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F82" t="s">
         <v>199</v>
       </c>
       <c r="G82" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3940,13 +3940,13 @@
         <v>198</v>
       </c>
       <c r="E83" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F83" t="s">
         <v>199</v>
       </c>
       <c r="G83" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3963,13 +3963,13 @@
         <v>198</v>
       </c>
       <c r="E84" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F84" t="s">
         <v>199</v>
       </c>
       <c r="G84" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3986,13 +3986,13 @@
         <v>198</v>
       </c>
       <c r="E85" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F85" t="s">
         <v>199</v>
       </c>
       <c r="G85" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4009,13 +4009,13 @@
         <v>198</v>
       </c>
       <c r="E86" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F86" t="s">
         <v>199</v>
       </c>
       <c r="G86" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4032,13 +4032,13 @@
         <v>198</v>
       </c>
       <c r="E87" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F87" t="s">
         <v>199</v>
       </c>
       <c r="G87" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4055,13 +4055,13 @@
         <v>214</v>
       </c>
       <c r="E88" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F88" t="s">
         <v>215</v>
       </c>
       <c r="G88" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4078,13 +4078,13 @@
         <v>214</v>
       </c>
       <c r="E89" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F89" t="s">
         <v>215</v>
       </c>
       <c r="G89" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4101,13 +4101,13 @@
         <v>214</v>
       </c>
       <c r="E90" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F90" t="s">
         <v>215</v>
       </c>
       <c r="G90" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4124,13 +4124,13 @@
         <v>214</v>
       </c>
       <c r="E91" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F91" t="s">
         <v>215</v>
       </c>
       <c r="G91" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4236,10 +4236,10 @@
         <v>9</v>
       </c>
       <c r="D96" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E96" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F96" t="s">
         <v>226</v>
@@ -4259,10 +4259,10 @@
         <v>9</v>
       </c>
       <c r="D97" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E97" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F97" t="s">
         <v>226</v>
@@ -4282,10 +4282,10 @@
         <v>9</v>
       </c>
       <c r="D98" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E98" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F98" t="s">
         <v>226</v>
@@ -4305,10 +4305,10 @@
         <v>9</v>
       </c>
       <c r="D99" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E99" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F99" t="s">
         <v>226</v>
@@ -4328,10 +4328,10 @@
         <v>9</v>
       </c>
       <c r="D100" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E100" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F100" t="s">
         <v>226</v>
@@ -4351,10 +4351,10 @@
         <v>9</v>
       </c>
       <c r="D101" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E101" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F101" t="s">
         <v>226</v>
@@ -4374,10 +4374,10 @@
         <v>9</v>
       </c>
       <c r="D102" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E102" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F102" t="s">
         <v>226</v>
@@ -4397,10 +4397,10 @@
         <v>9</v>
       </c>
       <c r="D103" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E103" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F103" t="s">
         <v>226</v>
@@ -4420,10 +4420,10 @@
         <v>9</v>
       </c>
       <c r="D104" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E104" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F104" t="s">
         <v>226</v>
@@ -4443,10 +4443,10 @@
         <v>9</v>
       </c>
       <c r="D105" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E105" t="s">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="F105" t="s">
         <v>226</v>
@@ -4466,10 +4466,10 @@
         <v>9</v>
       </c>
       <c r="D106" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E106" t="s">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="F106" t="s">
         <v>226</v>
@@ -4489,10 +4489,10 @@
         <v>9</v>
       </c>
       <c r="D107" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E107" t="s">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="F107" t="s">
         <v>226</v>
@@ -4512,10 +4512,10 @@
         <v>9</v>
       </c>
       <c r="D108" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E108" t="s">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="F108" t="s">
         <v>226</v>
@@ -4535,10 +4535,10 @@
         <v>9</v>
       </c>
       <c r="D109" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E109" t="s">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="F109" t="s">
         <v>226</v>
@@ -4558,10 +4558,10 @@
         <v>9</v>
       </c>
       <c r="D110" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E110" t="s">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="F110" t="s">
         <v>226</v>
@@ -4581,10 +4581,10 @@
         <v>9</v>
       </c>
       <c r="D111" t="s">
-        <v>224</v>
+        <v>270</v>
       </c>
       <c r="E111" t="s">
-        <v>270</v>
+        <v>225</v>
       </c>
       <c r="F111" t="s">
         <v>226</v>
@@ -4604,10 +4604,10 @@
         <v>9</v>
       </c>
       <c r="D112" t="s">
-        <v>224</v>
+        <v>274</v>
       </c>
       <c r="E112" t="s">
-        <v>274</v>
+        <v>225</v>
       </c>
       <c r="F112" t="s">
         <v>226</v>
@@ -4627,10 +4627,10 @@
         <v>9</v>
       </c>
       <c r="D113" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E113" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="F113" t="s">
         <v>226</v>
@@ -4650,10 +4650,10 @@
         <v>9</v>
       </c>
       <c r="D114" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E114" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="F114" t="s">
         <v>226</v>
@@ -4673,10 +4673,10 @@
         <v>9</v>
       </c>
       <c r="D115" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E115" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="F115" t="s">
         <v>226</v>
@@ -4696,10 +4696,10 @@
         <v>9</v>
       </c>
       <c r="D116" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E116" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="F116" t="s">
         <v>226</v>
@@ -4719,10 +4719,10 @@
         <v>9</v>
       </c>
       <c r="D117" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E117" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="F117" t="s">
         <v>226</v>
@@ -4742,10 +4742,10 @@
         <v>9</v>
       </c>
       <c r="D118" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E118" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="F118" t="s">
         <v>226</v>
@@ -4765,10 +4765,10 @@
         <v>9</v>
       </c>
       <c r="D119" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E119" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="F119" t="s">
         <v>226</v>
@@ -4791,13 +4791,13 @@
         <v>294</v>
       </c>
       <c r="E120" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F120" t="s">
         <v>295</v>
       </c>
       <c r="G120" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4814,13 +4814,13 @@
         <v>294</v>
       </c>
       <c r="E121" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F121" t="s">
         <v>295</v>
       </c>
       <c r="G121" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4837,13 +4837,13 @@
         <v>294</v>
       </c>
       <c r="E122" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F122" t="s">
         <v>295</v>
       </c>
       <c r="G122" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4860,13 +4860,13 @@
         <v>294</v>
       </c>
       <c r="E123" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F123" t="s">
         <v>295</v>
       </c>
       <c r="G123" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4883,13 +4883,13 @@
         <v>294</v>
       </c>
       <c r="E124" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F124" t="s">
         <v>295</v>
       </c>
       <c r="G124" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4906,13 +4906,13 @@
         <v>294</v>
       </c>
       <c r="E125" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F125" t="s">
         <v>295</v>
       </c>
       <c r="G125" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4929,13 +4929,13 @@
         <v>308</v>
       </c>
       <c r="E126" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F126" t="s">
         <v>309</v>
       </c>
       <c r="G126" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4952,13 +4952,13 @@
         <v>308</v>
       </c>
       <c r="E127" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F127" t="s">
         <v>309</v>
       </c>
       <c r="G127" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4975,13 +4975,13 @@
         <v>308</v>
       </c>
       <c r="E128" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F128" t="s">
         <v>309</v>
       </c>
       <c r="G128" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4998,13 +4998,13 @@
         <v>308</v>
       </c>
       <c r="E129" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F129" t="s">
         <v>309</v>
       </c>
       <c r="G129" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -5432,10 +5432,10 @@
         <v>9</v>
       </c>
       <c r="D148" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E148" t="s">
-        <v>358</v>
+        <v>319</v>
       </c>
       <c r="F148" t="s">
         <v>320</v>
@@ -5455,10 +5455,10 @@
         <v>9</v>
       </c>
       <c r="D149" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E149" t="s">
-        <v>358</v>
+        <v>319</v>
       </c>
       <c r="F149" t="s">
         <v>320</v>
@@ -5478,10 +5478,10 @@
         <v>9</v>
       </c>
       <c r="D150" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E150" t="s">
-        <v>358</v>
+        <v>319</v>
       </c>
       <c r="F150" t="s">
         <v>320</v>
@@ -5501,10 +5501,10 @@
         <v>9</v>
       </c>
       <c r="D151" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E151" t="s">
-        <v>358</v>
+        <v>319</v>
       </c>
       <c r="F151" t="s">
         <v>320</v>
@@ -5524,10 +5524,10 @@
         <v>9</v>
       </c>
       <c r="D152" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E152" t="s">
-        <v>358</v>
+        <v>319</v>
       </c>
       <c r="F152" t="s">
         <v>320</v>
@@ -5547,10 +5547,10 @@
         <v>9</v>
       </c>
       <c r="D153" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E153" t="s">
-        <v>358</v>
+        <v>319</v>
       </c>
       <c r="F153" t="s">
         <v>320</v>
@@ -5570,10 +5570,10 @@
         <v>9</v>
       </c>
       <c r="D154" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="E154" t="s">
-        <v>372</v>
+        <v>319</v>
       </c>
       <c r="F154" t="s">
         <v>320</v>
@@ -5593,10 +5593,10 @@
         <v>9</v>
       </c>
       <c r="D155" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="E155" t="s">
-        <v>372</v>
+        <v>319</v>
       </c>
       <c r="F155" t="s">
         <v>320</v>
@@ -5616,10 +5616,10 @@
         <v>9</v>
       </c>
       <c r="D156" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="E156" t="s">
-        <v>372</v>
+        <v>319</v>
       </c>
       <c r="F156" t="s">
         <v>320</v>
@@ -5639,10 +5639,10 @@
         <v>9</v>
       </c>
       <c r="D157" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="E157" t="s">
-        <v>372</v>
+        <v>319</v>
       </c>
       <c r="F157" t="s">
         <v>320</v>
@@ -5662,10 +5662,10 @@
         <v>9</v>
       </c>
       <c r="D158" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="E158" t="s">
-        <v>372</v>
+        <v>319</v>
       </c>
       <c r="F158" t="s">
         <v>320</v>
@@ -6122,10 +6122,10 @@
         <v>9</v>
       </c>
       <c r="D178" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E178" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="F178" t="s">
         <v>386</v>
@@ -6145,10 +6145,10 @@
         <v>9</v>
       </c>
       <c r="D179" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E179" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="F179" t="s">
         <v>386</v>
@@ -6168,10 +6168,10 @@
         <v>9</v>
       </c>
       <c r="D180" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E180" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="F180" t="s">
         <v>386</v>
@@ -6191,10 +6191,10 @@
         <v>9</v>
       </c>
       <c r="D181" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E181" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="F181" t="s">
         <v>386</v>
@@ -6214,10 +6214,10 @@
         <v>9</v>
       </c>
       <c r="D182" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E182" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="F182" t="s">
         <v>386</v>
@@ -6237,10 +6237,10 @@
         <v>9</v>
       </c>
       <c r="D183" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E183" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="F183" t="s">
         <v>386</v>
@@ -6260,10 +6260,10 @@
         <v>9</v>
       </c>
       <c r="D184" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E184" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="F184" t="s">
         <v>386</v>
@@ -6283,10 +6283,10 @@
         <v>9</v>
       </c>
       <c r="D185" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E185" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="F185" t="s">
         <v>386</v>
@@ -6306,10 +6306,10 @@
         <v>9</v>
       </c>
       <c r="D186" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E186" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="F186" t="s">
         <v>386</v>
@@ -6329,10 +6329,10 @@
         <v>9</v>
       </c>
       <c r="D187" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E187" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="F187" t="s">
         <v>386</v>
@@ -6352,10 +6352,10 @@
         <v>9</v>
       </c>
       <c r="D188" t="s">
-        <v>384</v>
+        <v>448</v>
       </c>
       <c r="E188" t="s">
-        <v>448</v>
+        <v>385</v>
       </c>
       <c r="F188" t="s">
         <v>386</v>
@@ -6378,13 +6378,13 @@
         <v>452</v>
       </c>
       <c r="E189" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F189" t="s">
         <v>453</v>
       </c>
       <c r="G189" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6401,13 +6401,13 @@
         <v>452</v>
       </c>
       <c r="E190" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F190" t="s">
         <v>453</v>
       </c>
       <c r="G190" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6424,13 +6424,13 @@
         <v>452</v>
       </c>
       <c r="E191" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F191" t="s">
         <v>453</v>
       </c>
       <c r="G191" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6447,13 +6447,13 @@
         <v>452</v>
       </c>
       <c r="E192" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F192" t="s">
         <v>453</v>
       </c>
       <c r="G192" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6470,13 +6470,13 @@
         <v>452</v>
       </c>
       <c r="E193" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F193" t="s">
         <v>453</v>
       </c>
       <c r="G193" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6493,13 +6493,13 @@
         <v>452</v>
       </c>
       <c r="E194" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F194" t="s">
         <v>453</v>
       </c>
       <c r="G194" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6516,13 +6516,13 @@
         <v>466</v>
       </c>
       <c r="E195" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F195" t="s">
         <v>467</v>
       </c>
       <c r="G195" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6539,13 +6539,13 @@
         <v>470</v>
       </c>
       <c r="E196" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F196" t="s">
         <v>471</v>
       </c>
       <c r="G196" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6562,13 +6562,13 @@
         <v>470</v>
       </c>
       <c r="E197" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F197" t="s">
         <v>471</v>
       </c>
       <c r="G197" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6585,13 +6585,13 @@
         <v>470</v>
       </c>
       <c r="E198" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F198" t="s">
         <v>471</v>
       </c>
       <c r="G198" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6608,13 +6608,13 @@
         <v>470</v>
       </c>
       <c r="E199" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F199" t="s">
         <v>471</v>
       </c>
       <c r="G199" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6631,13 +6631,13 @@
         <v>470</v>
       </c>
       <c r="E200" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F200" t="s">
         <v>471</v>
       </c>
       <c r="G200" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6654,13 +6654,13 @@
         <v>470</v>
       </c>
       <c r="E201" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F201" t="s">
         <v>471</v>
       </c>
       <c r="G201" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6677,13 +6677,13 @@
         <v>484</v>
       </c>
       <c r="E202" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F202" t="s">
         <v>485</v>
       </c>
       <c r="G202" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6700,13 +6700,13 @@
         <v>484</v>
       </c>
       <c r="E203" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F203" t="s">
         <v>485</v>
       </c>
       <c r="G203" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6723,13 +6723,13 @@
         <v>484</v>
       </c>
       <c r="E204" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F204" t="s">
         <v>485</v>
       </c>
       <c r="G204" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6746,13 +6746,13 @@
         <v>484</v>
       </c>
       <c r="E205" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F205" t="s">
         <v>485</v>
       </c>
       <c r="G205" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6769,13 +6769,13 @@
         <v>484</v>
       </c>
       <c r="E206" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F206" t="s">
         <v>485</v>
       </c>
       <c r="G206" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6792,13 +6792,13 @@
         <v>484</v>
       </c>
       <c r="E207" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F207" t="s">
         <v>485</v>
       </c>
       <c r="G207" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6815,13 +6815,13 @@
         <v>484</v>
       </c>
       <c r="E208" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F208" t="s">
         <v>485</v>
       </c>
       <c r="G208" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6838,13 +6838,13 @@
         <v>484</v>
       </c>
       <c r="E209" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F209" t="s">
         <v>485</v>
       </c>
       <c r="G209" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6861,13 +6861,13 @@
         <v>484</v>
       </c>
       <c r="E210" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F210" t="s">
         <v>485</v>
       </c>
       <c r="G210" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6884,13 +6884,13 @@
         <v>484</v>
       </c>
       <c r="E211" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F211" t="s">
         <v>485</v>
       </c>
       <c r="G211" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6907,13 +6907,13 @@
         <v>506</v>
       </c>
       <c r="E212" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="F212" t="s">
         <v>507</v>
       </c>
       <c r="G212" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6930,13 +6930,13 @@
         <v>510</v>
       </c>
       <c r="E213" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F213" t="s">
         <v>511</v>
       </c>
       <c r="G213" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6953,13 +6953,13 @@
         <v>514</v>
       </c>
       <c r="E214" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F214" t="s">
         <v>515</v>
       </c>
       <c r="G214" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6976,13 +6976,13 @@
         <v>514</v>
       </c>
       <c r="E215" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F215" t="s">
         <v>515</v>
       </c>
       <c r="G215" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6999,13 +6999,13 @@
         <v>520</v>
       </c>
       <c r="E216" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F216" t="s">
         <v>521</v>
       </c>
       <c r="G216" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -7022,13 +7022,13 @@
         <v>520</v>
       </c>
       <c r="E217" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F217" t="s">
         <v>521</v>
       </c>
       <c r="G217" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -7045,13 +7045,13 @@
         <v>520</v>
       </c>
       <c r="E218" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F218" t="s">
         <v>521</v>
       </c>
       <c r="G218" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -7068,13 +7068,13 @@
         <v>520</v>
       </c>
       <c r="E219" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F219" t="s">
         <v>521</v>
       </c>
       <c r="G219" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -7091,13 +7091,13 @@
         <v>520</v>
       </c>
       <c r="E220" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F220" t="s">
         <v>521</v>
       </c>
       <c r="G220" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -7114,13 +7114,13 @@
         <v>520</v>
       </c>
       <c r="E221" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F221" t="s">
         <v>521</v>
       </c>
       <c r="G221" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -7137,13 +7137,13 @@
         <v>520</v>
       </c>
       <c r="E222" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F222" t="s">
         <v>521</v>
       </c>
       <c r="G222" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -7160,13 +7160,13 @@
         <v>536</v>
       </c>
       <c r="E223" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F223" t="s">
         <v>537</v>
       </c>
       <c r="G223" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -7183,13 +7183,13 @@
         <v>536</v>
       </c>
       <c r="E224" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F224" t="s">
         <v>537</v>
       </c>
       <c r="G224" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -7206,13 +7206,13 @@
         <v>536</v>
       </c>
       <c r="E225" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F225" t="s">
         <v>537</v>
       </c>
       <c r="G225" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -7229,13 +7229,13 @@
         <v>544</v>
       </c>
       <c r="E226" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F226" t="s">
         <v>545</v>
       </c>
       <c r="G226" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -7252,13 +7252,13 @@
         <v>548</v>
       </c>
       <c r="E227" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="F227" t="s">
         <v>549</v>
       </c>
       <c r="G227" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -7275,13 +7275,13 @@
         <v>552</v>
       </c>
       <c r="E228" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="F228" t="s">
         <v>553</v>
       </c>
       <c r="G228" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -7298,13 +7298,13 @@
         <v>556</v>
       </c>
       <c r="E229" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="F229" t="s">
         <v>557</v>
       </c>
       <c r="G229" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -7321,13 +7321,13 @@
         <v>560</v>
       </c>
       <c r="E230" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="F230" t="s">
         <v>561</v>
       </c>
       <c r="G230" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -7344,13 +7344,13 @@
         <v>560</v>
       </c>
       <c r="E231" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="F231" t="s">
         <v>561</v>
       </c>
       <c r="G231" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/en/SectorGroup.xlsx
+++ b/api/xlsx/en/SectorGroup.xlsx
@@ -25,18 +25,18 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
     <t>codeforiati:category-name</t>
   </si>
   <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -46,18 +46,18 @@
     <t>active</t>
   </si>
   <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
     <t>Education, Level Unspecified</t>
   </si>
   <si>
-    <t>Education</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -82,12 +82,12 @@
     <t>Primary education</t>
   </si>
   <si>
+    <t>112</t>
+  </si>
+  <si>
     <t>Basic Education</t>
   </si>
   <si>
-    <t>112</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -112,12 +112,12 @@
     <t>Secondary education</t>
   </si>
   <si>
+    <t>113</t>
+  </si>
+  <si>
     <t>Secondary Education</t>
   </si>
   <si>
-    <t>113</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
@@ -130,12 +130,12 @@
     <t>Higher education</t>
   </si>
   <si>
+    <t>114</t>
+  </si>
+  <si>
     <t>Post-Secondary Education</t>
   </si>
   <si>
-    <t>114</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -148,18 +148,18 @@
     <t>Health policy and administrative management</t>
   </si>
   <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>Health</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
     <t>Health, General</t>
   </si>
   <si>
-    <t>Health</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -184,12 +184,12 @@
     <t>Basic health care</t>
   </si>
   <si>
+    <t>122</t>
+  </si>
+  <si>
     <t>Basic Health</t>
   </si>
   <si>
-    <t>122</t>
-  </si>
-  <si>
     <t>12230</t>
   </si>
   <si>
@@ -238,12 +238,12 @@
     <t>NCDs control, general</t>
   </si>
   <si>
+    <t>123</t>
+  </si>
+  <si>
     <t>Non-communicable diseases (NCDs)</t>
   </si>
   <si>
-    <t>123</t>
-  </si>
-  <si>
     <t>12320</t>
   </si>
   <si>
@@ -280,12 +280,12 @@
     <t>Population policy and administrative management</t>
   </si>
   <si>
+    <t>130</t>
+  </si>
+  <si>
     <t>Population Policies/Programmes &amp; Reproductive Health</t>
   </si>
   <si>
-    <t>130</t>
-  </si>
-  <si>
     <t>13020</t>
   </si>
   <si>
@@ -316,12 +316,12 @@
     <t>Water sector policy and administrative management</t>
   </si>
   <si>
+    <t>140</t>
+  </si>
+  <si>
     <t>Water Supply &amp; Sanitation</t>
   </si>
   <si>
-    <t>140</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -388,18 +388,18 @@
     <t>Public sector policy and administrative management</t>
   </si>
   <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>Government &amp; Civil Society</t>
+  </si>
+  <si>
+    <t>151</t>
+  </si>
+  <si>
     <t>Government &amp; Civil Society-general</t>
   </si>
   <si>
-    <t>Government &amp; Civil Society</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>151</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -496,12 +496,12 @@
     <t>Security system management and reform</t>
   </si>
   <si>
+    <t>152</t>
+  </si>
+  <si>
     <t>Conflict, Peace &amp; Security</t>
   </si>
   <si>
-    <t>152</t>
-  </si>
-  <si>
     <t>15220</t>
   </si>
   <si>
@@ -538,12 +538,12 @@
     <t>Social Protection</t>
   </si>
   <si>
+    <t>160</t>
+  </si>
+  <si>
     <t>Other Social Infrastructure &amp; Services</t>
   </si>
   <si>
-    <t>160</t>
-  </si>
-  <si>
     <t>16020</t>
   </si>
   <si>
@@ -610,12 +610,12 @@
     <t>Transport policy and administrative management</t>
   </si>
   <si>
+    <t>210</t>
+  </si>
+  <si>
     <t>Transport &amp; Storage</t>
   </si>
   <si>
-    <t>210</t>
-  </si>
-  <si>
     <t>21020</t>
   </si>
   <si>
@@ -658,12 +658,12 @@
     <t>Communications policy and administrative management</t>
   </si>
   <si>
+    <t>220</t>
+  </si>
+  <si>
     <t>Communications</t>
   </si>
   <si>
-    <t>220</t>
-  </si>
-  <si>
     <t>22020</t>
   </si>
   <si>
@@ -688,18 +688,18 @@
     <t>Energy policy and administrative management</t>
   </si>
   <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>Energy</t>
+  </si>
+  <si>
+    <t>231</t>
+  </si>
+  <si>
     <t>Energy Policy</t>
   </si>
   <si>
-    <t>Energy</t>
-  </si>
-  <si>
-    <t>230</t>
-  </si>
-  <si>
-    <t>231</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -724,12 +724,12 @@
     <t>Energy generation, renewable sources - multiple technologies</t>
   </si>
   <si>
+    <t>232</t>
+  </si>
+  <si>
     <t>Energy generation, renewable sources</t>
   </si>
   <si>
-    <t>232</t>
-  </si>
-  <si>
     <t>23220</t>
   </si>
   <si>
@@ -784,12 +784,12 @@
     <t>Energy generation, non-renewable sources, unspecified</t>
   </si>
   <si>
+    <t>233</t>
+  </si>
+  <si>
     <t>Energy generation, non-renewable sources</t>
   </si>
   <si>
-    <t>233</t>
-  </si>
-  <si>
     <t>23320</t>
   </si>
   <si>
@@ -826,36 +826,36 @@
     <t>Hybrid energy electric power plants</t>
   </si>
   <si>
+    <t>234</t>
+  </si>
+  <si>
     <t>Hybrid energy plants</t>
   </si>
   <si>
-    <t>234</t>
-  </si>
-  <si>
     <t>23510</t>
   </si>
   <si>
     <t>Nuclear energy electric power plants and nuclear safety</t>
   </si>
   <si>
+    <t>235</t>
+  </si>
+  <si>
     <t>Nuclear energy plants</t>
   </si>
   <si>
-    <t>235</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
     <t>Heat plants</t>
   </si>
   <si>
+    <t>236</t>
+  </si>
+  <si>
     <t>Energy distribution</t>
   </si>
   <si>
-    <t>236</t>
-  </si>
-  <si>
     <t>23620</t>
   </si>
   <si>
@@ -898,12 +898,12 @@
     <t>Financial policy and administrative management</t>
   </si>
   <si>
+    <t>240</t>
+  </si>
+  <si>
     <t>Banking &amp; Financial Services</t>
   </si>
   <si>
-    <t>240</t>
-  </si>
-  <si>
     <t>24020</t>
   </si>
   <si>
@@ -940,12 +940,12 @@
     <t>Business policy and administration</t>
   </si>
   <si>
+    <t>250</t>
+  </si>
+  <si>
     <t>Business &amp; Other Services</t>
   </si>
   <si>
-    <t>250</t>
-  </si>
-  <si>
     <t>25020</t>
   </si>
   <si>
@@ -970,18 +970,18 @@
     <t>Agricultural policy and administrative management</t>
   </si>
   <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>Agriculture, Forestry, Fishing</t>
+  </si>
+  <si>
+    <t>311</t>
+  </si>
+  <si>
     <t>Agriculture</t>
   </si>
   <si>
-    <t>Agriculture, Forestry, Fishing</t>
-  </si>
-  <si>
-    <t>310</t>
-  </si>
-  <si>
-    <t>311</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1090,12 +1090,12 @@
     <t>Forestry policy and administrative management</t>
   </si>
   <si>
+    <t>312</t>
+  </si>
+  <si>
     <t>Forestry</t>
   </si>
   <si>
-    <t>312</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -1132,12 +1132,12 @@
     <t>Fishing policy and administrative management</t>
   </si>
   <si>
+    <t>313</t>
+  </si>
+  <si>
     <t>Fishing</t>
   </si>
   <si>
-    <t>313</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -1168,18 +1168,18 @@
     <t>Industrial policy and administrative management</t>
   </si>
   <si>
+    <t>320</t>
+  </si>
+  <si>
+    <t>Industry, Mining, Construction</t>
+  </si>
+  <si>
+    <t>321</t>
+  </si>
+  <si>
     <t>Industry</t>
   </si>
   <si>
-    <t>Industry, Mining, Construction</t>
-  </si>
-  <si>
-    <t>320</t>
-  </si>
-  <si>
-    <t>321</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1294,12 +1294,12 @@
     <t>Mineral/mining policy and administrative management</t>
   </si>
   <si>
+    <t>322</t>
+  </si>
+  <si>
     <t>Mineral Resources &amp; Mining</t>
   </si>
   <si>
-    <t>322</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -1360,24 +1360,24 @@
     <t>Construction policy and administrative management</t>
   </si>
   <si>
+    <t>323</t>
+  </si>
+  <si>
     <t>Construction</t>
   </si>
   <si>
-    <t>323</t>
-  </si>
-  <si>
     <t>33110</t>
   </si>
   <si>
     <t>Trade policy and administrative management</t>
   </si>
   <si>
+    <t>331</t>
+  </si>
+  <si>
     <t>Trade Policies &amp; Regulations</t>
   </si>
   <si>
-    <t>331</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1414,24 +1414,24 @@
     <t>Tourism policy and administrative management</t>
   </si>
   <si>
+    <t>332</t>
+  </si>
+  <si>
     <t>Tourism</t>
   </si>
   <si>
-    <t>332</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
     <t>Environmental policy and administrative management</t>
   </si>
   <si>
+    <t>410</t>
+  </si>
+  <si>
     <t>General Environment Protection</t>
   </si>
   <si>
-    <t>410</t>
-  </si>
-  <si>
     <t>41020</t>
   </si>
   <si>
@@ -1468,12 +1468,12 @@
     <t>Multisector aid</t>
   </si>
   <si>
+    <t>430</t>
+  </si>
+  <si>
     <t>Other Multisector</t>
   </si>
   <si>
-    <t>430</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -1534,36 +1534,36 @@
     <t>General budget support-related aid</t>
   </si>
   <si>
+    <t>510</t>
+  </si>
+  <si>
     <t>General Budget Support</t>
   </si>
   <si>
-    <t>510</t>
-  </si>
-  <si>
     <t>52010</t>
   </si>
   <si>
     <t>Food assistance</t>
   </si>
   <si>
+    <t>520</t>
+  </si>
+  <si>
     <t>Development Food Assistance</t>
   </si>
   <si>
-    <t>520</t>
-  </si>
-  <si>
     <t>53030</t>
   </si>
   <si>
     <t>Import support (capital goods)</t>
   </si>
   <si>
+    <t>530</t>
+  </si>
+  <si>
     <t>Other Commodity Assistance</t>
   </si>
   <si>
-    <t>530</t>
-  </si>
-  <si>
     <t>53040</t>
   </si>
   <si>
@@ -1576,12 +1576,12 @@
     <t>Action relating to debt</t>
   </si>
   <si>
+    <t>600</t>
+  </si>
+  <si>
     <t>Action Relating to Debt</t>
   </si>
   <si>
-    <t>600</t>
-  </si>
-  <si>
     <t>60020</t>
   </si>
   <si>
@@ -1624,12 +1624,12 @@
     <t>Material relief assistance and services</t>
   </si>
   <si>
+    <t>720</t>
+  </si>
+  <si>
     <t>Emergency Response</t>
   </si>
   <si>
-    <t>720</t>
-  </si>
-  <si>
     <t>72040</t>
   </si>
   <si>
@@ -1648,58 +1648,58 @@
     <t>Immediate post-emergency reconstruction and rehabilitation</t>
   </si>
   <si>
+    <t>730</t>
+  </si>
+  <si>
     <t>Reconstruction Relief &amp; Rehabilitation</t>
   </si>
   <si>
-    <t>730</t>
-  </si>
-  <si>
     <t>74020</t>
   </si>
   <si>
     <t>Multi-hazard response preparedness</t>
   </si>
   <si>
+    <t>740</t>
+  </si>
+  <si>
     <t>Disaster Prevention &amp; Preparedness</t>
   </si>
   <si>
-    <t>740</t>
-  </si>
-  <si>
     <t>91010</t>
   </si>
   <si>
     <t>Administrative costs (non-sector allocable)</t>
   </si>
   <si>
+    <t>910</t>
+  </si>
+  <si>
     <t>Administrative Costs of Donors</t>
   </si>
   <si>
-    <t>910</t>
-  </si>
-  <si>
     <t>93010</t>
   </si>
   <si>
     <t>Refugees/asylum seekers in donor countries (non-sector allocable)</t>
   </si>
   <si>
+    <t>930</t>
+  </si>
+  <si>
     <t>Refugees in Donor Countries</t>
   </si>
   <si>
-    <t>930</t>
-  </si>
-  <si>
     <t>99810</t>
   </si>
   <si>
     <t>Sectors not specified</t>
   </si>
   <si>
+    <t>998</t>
+  </si>
+  <si>
     <t>Unallocated / Unspecified</t>
-  </si>
-  <si>
-    <t>998</t>
   </si>
   <si>
     <t>99820</t>
@@ -2166,13 +2166,13 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E6" t="s">
         <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G6" t="s">
         <v>23</v>
@@ -2189,13 +2189,13 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G7" t="s">
         <v>23</v>
@@ -2212,13 +2212,13 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E8" t="s">
         <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G8" t="s">
         <v>23</v>
@@ -2235,13 +2235,13 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G9" t="s">
         <v>23</v>
@@ -2258,13 +2258,13 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="E10" t="s">
         <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="G10" t="s">
         <v>33</v>
@@ -2281,13 +2281,13 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="E11" t="s">
         <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="G11" t="s">
         <v>33</v>
@@ -2304,13 +2304,13 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="E12" t="s">
         <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="G12" t="s">
         <v>39</v>
@@ -2327,13 +2327,13 @@
         <v>9</v>
       </c>
       <c r="D13" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="E13" t="s">
         <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="G13" t="s">
         <v>39</v>
@@ -2442,13 +2442,13 @@
         <v>9</v>
       </c>
       <c r="D18" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E18" t="s">
         <v>45</v>
       </c>
       <c r="F18" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="G18" t="s">
         <v>57</v>
@@ -2465,13 +2465,13 @@
         <v>9</v>
       </c>
       <c r="D19" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E19" t="s">
         <v>45</v>
       </c>
       <c r="F19" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="G19" t="s">
         <v>57</v>
@@ -2488,13 +2488,13 @@
         <v>9</v>
       </c>
       <c r="D20" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E20" t="s">
         <v>45</v>
       </c>
       <c r="F20" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="G20" t="s">
         <v>57</v>
@@ -2511,13 +2511,13 @@
         <v>9</v>
       </c>
       <c r="D21" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E21" t="s">
         <v>45</v>
       </c>
       <c r="F21" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="G21" t="s">
         <v>57</v>
@@ -2534,13 +2534,13 @@
         <v>9</v>
       </c>
       <c r="D22" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E22" t="s">
         <v>45</v>
       </c>
       <c r="F22" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="G22" t="s">
         <v>57</v>
@@ -2557,13 +2557,13 @@
         <v>9</v>
       </c>
       <c r="D23" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E23" t="s">
         <v>45</v>
       </c>
       <c r="F23" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="G23" t="s">
         <v>57</v>
@@ -2580,13 +2580,13 @@
         <v>9</v>
       </c>
       <c r="D24" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E24" t="s">
         <v>45</v>
       </c>
       <c r="F24" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="G24" t="s">
         <v>57</v>
@@ -2603,13 +2603,13 @@
         <v>9</v>
       </c>
       <c r="D25" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E25" t="s">
         <v>45</v>
       </c>
       <c r="F25" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="G25" t="s">
         <v>57</v>
@@ -2626,13 +2626,13 @@
         <v>9</v>
       </c>
       <c r="D26" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="E26" t="s">
         <v>45</v>
       </c>
       <c r="F26" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="G26" t="s">
         <v>75</v>
@@ -2649,13 +2649,13 @@
         <v>9</v>
       </c>
       <c r="D27" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="E27" t="s">
         <v>45</v>
       </c>
       <c r="F27" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="G27" t="s">
         <v>75</v>
@@ -2672,13 +2672,13 @@
         <v>9</v>
       </c>
       <c r="D28" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="E28" t="s">
         <v>45</v>
       </c>
       <c r="F28" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="G28" t="s">
         <v>75</v>
@@ -2695,13 +2695,13 @@
         <v>9</v>
       </c>
       <c r="D29" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="E29" t="s">
         <v>45</v>
       </c>
       <c r="F29" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="G29" t="s">
         <v>75</v>
@@ -2718,13 +2718,13 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="E30" t="s">
         <v>45</v>
       </c>
       <c r="F30" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="G30" t="s">
         <v>75</v>
@@ -2741,13 +2741,13 @@
         <v>9</v>
       </c>
       <c r="D31" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="E31" t="s">
         <v>45</v>
       </c>
       <c r="F31" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="G31" t="s">
         <v>75</v>
@@ -2767,10 +2767,10 @@
         <v>88</v>
       </c>
       <c r="E32" t="s">
+        <v>89</v>
+      </c>
+      <c r="F32" t="s">
         <v>88</v>
-      </c>
-      <c r="F32" t="s">
-        <v>89</v>
       </c>
       <c r="G32" t="s">
         <v>89</v>
@@ -2790,10 +2790,10 @@
         <v>88</v>
       </c>
       <c r="E33" t="s">
+        <v>89</v>
+      </c>
+      <c r="F33" t="s">
         <v>88</v>
-      </c>
-      <c r="F33" t="s">
-        <v>89</v>
       </c>
       <c r="G33" t="s">
         <v>89</v>
@@ -2813,10 +2813,10 @@
         <v>88</v>
       </c>
       <c r="E34" t="s">
+        <v>89</v>
+      </c>
+      <c r="F34" t="s">
         <v>88</v>
-      </c>
-      <c r="F34" t="s">
-        <v>89</v>
       </c>
       <c r="G34" t="s">
         <v>89</v>
@@ -2836,10 +2836,10 @@
         <v>88</v>
       </c>
       <c r="E35" t="s">
+        <v>89</v>
+      </c>
+      <c r="F35" t="s">
         <v>88</v>
-      </c>
-      <c r="F35" t="s">
-        <v>89</v>
       </c>
       <c r="G35" t="s">
         <v>89</v>
@@ -2859,10 +2859,10 @@
         <v>88</v>
       </c>
       <c r="E36" t="s">
+        <v>89</v>
+      </c>
+      <c r="F36" t="s">
         <v>88</v>
-      </c>
-      <c r="F36" t="s">
-        <v>89</v>
       </c>
       <c r="G36" t="s">
         <v>89</v>
@@ -2882,10 +2882,10 @@
         <v>100</v>
       </c>
       <c r="E37" t="s">
+        <v>101</v>
+      </c>
+      <c r="F37" t="s">
         <v>100</v>
-      </c>
-      <c r="F37" t="s">
-        <v>101</v>
       </c>
       <c r="G37" t="s">
         <v>101</v>
@@ -2905,10 +2905,10 @@
         <v>100</v>
       </c>
       <c r="E38" t="s">
+        <v>101</v>
+      </c>
+      <c r="F38" t="s">
         <v>100</v>
-      </c>
-      <c r="F38" t="s">
-        <v>101</v>
       </c>
       <c r="G38" t="s">
         <v>101</v>
@@ -2928,10 +2928,10 @@
         <v>100</v>
       </c>
       <c r="E39" t="s">
+        <v>101</v>
+      </c>
+      <c r="F39" t="s">
         <v>100</v>
-      </c>
-      <c r="F39" t="s">
-        <v>101</v>
       </c>
       <c r="G39" t="s">
         <v>101</v>
@@ -2951,10 +2951,10 @@
         <v>100</v>
       </c>
       <c r="E40" t="s">
+        <v>101</v>
+      </c>
+      <c r="F40" t="s">
         <v>100</v>
-      </c>
-      <c r="F40" t="s">
-        <v>101</v>
       </c>
       <c r="G40" t="s">
         <v>101</v>
@@ -2974,10 +2974,10 @@
         <v>100</v>
       </c>
       <c r="E41" t="s">
+        <v>101</v>
+      </c>
+      <c r="F41" t="s">
         <v>100</v>
-      </c>
-      <c r="F41" t="s">
-        <v>101</v>
       </c>
       <c r="G41" t="s">
         <v>101</v>
@@ -2997,10 +2997,10 @@
         <v>100</v>
       </c>
       <c r="E42" t="s">
+        <v>101</v>
+      </c>
+      <c r="F42" t="s">
         <v>100</v>
-      </c>
-      <c r="F42" t="s">
-        <v>101</v>
       </c>
       <c r="G42" t="s">
         <v>101</v>
@@ -3020,10 +3020,10 @@
         <v>100</v>
       </c>
       <c r="E43" t="s">
+        <v>101</v>
+      </c>
+      <c r="F43" t="s">
         <v>100</v>
-      </c>
-      <c r="F43" t="s">
-        <v>101</v>
       </c>
       <c r="G43" t="s">
         <v>101</v>
@@ -3043,10 +3043,10 @@
         <v>100</v>
       </c>
       <c r="E44" t="s">
+        <v>101</v>
+      </c>
+      <c r="F44" t="s">
         <v>100</v>
-      </c>
-      <c r="F44" t="s">
-        <v>101</v>
       </c>
       <c r="G44" t="s">
         <v>101</v>
@@ -3066,10 +3066,10 @@
         <v>100</v>
       </c>
       <c r="E45" t="s">
+        <v>101</v>
+      </c>
+      <c r="F45" t="s">
         <v>100</v>
-      </c>
-      <c r="F45" t="s">
-        <v>101</v>
       </c>
       <c r="G45" t="s">
         <v>101</v>
@@ -3089,10 +3089,10 @@
         <v>100</v>
       </c>
       <c r="E46" t="s">
+        <v>101</v>
+      </c>
+      <c r="F46" t="s">
         <v>100</v>
-      </c>
-      <c r="F46" t="s">
-        <v>101</v>
       </c>
       <c r="G46" t="s">
         <v>101</v>
@@ -3112,10 +3112,10 @@
         <v>100</v>
       </c>
       <c r="E47" t="s">
+        <v>101</v>
+      </c>
+      <c r="F47" t="s">
         <v>100</v>
-      </c>
-      <c r="F47" t="s">
-        <v>101</v>
       </c>
       <c r="G47" t="s">
         <v>101</v>
@@ -3500,13 +3500,13 @@
         <v>9</v>
       </c>
       <c r="D64" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="E64" t="s">
         <v>125</v>
       </c>
       <c r="F64" t="s">
-        <v>126</v>
+        <v>160</v>
       </c>
       <c r="G64" t="s">
         <v>161</v>
@@ -3523,13 +3523,13 @@
         <v>9</v>
       </c>
       <c r="D65" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="E65" t="s">
         <v>125</v>
       </c>
       <c r="F65" t="s">
-        <v>126</v>
+        <v>160</v>
       </c>
       <c r="G65" t="s">
         <v>161</v>
@@ -3546,13 +3546,13 @@
         <v>9</v>
       </c>
       <c r="D66" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="E66" t="s">
         <v>125</v>
       </c>
       <c r="F66" t="s">
-        <v>126</v>
+        <v>160</v>
       </c>
       <c r="G66" t="s">
         <v>161</v>
@@ -3569,13 +3569,13 @@
         <v>9</v>
       </c>
       <c r="D67" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="E67" t="s">
         <v>125</v>
       </c>
       <c r="F67" t="s">
-        <v>126</v>
+        <v>160</v>
       </c>
       <c r="G67" t="s">
         <v>161</v>
@@ -3592,13 +3592,13 @@
         <v>9</v>
       </c>
       <c r="D68" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="E68" t="s">
         <v>125</v>
       </c>
       <c r="F68" t="s">
-        <v>126</v>
+        <v>160</v>
       </c>
       <c r="G68" t="s">
         <v>161</v>
@@ -3615,13 +3615,13 @@
         <v>9</v>
       </c>
       <c r="D69" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="E69" t="s">
         <v>125</v>
       </c>
       <c r="F69" t="s">
-        <v>126</v>
+        <v>160</v>
       </c>
       <c r="G69" t="s">
         <v>161</v>
@@ -3641,10 +3641,10 @@
         <v>174</v>
       </c>
       <c r="E70" t="s">
+        <v>175</v>
+      </c>
+      <c r="F70" t="s">
         <v>174</v>
-      </c>
-      <c r="F70" t="s">
-        <v>175</v>
       </c>
       <c r="G70" t="s">
         <v>175</v>
@@ -3664,10 +3664,10 @@
         <v>174</v>
       </c>
       <c r="E71" t="s">
+        <v>175</v>
+      </c>
+      <c r="F71" t="s">
         <v>174</v>
-      </c>
-      <c r="F71" t="s">
-        <v>175</v>
       </c>
       <c r="G71" t="s">
         <v>175</v>
@@ -3687,10 +3687,10 @@
         <v>174</v>
       </c>
       <c r="E72" t="s">
+        <v>175</v>
+      </c>
+      <c r="F72" t="s">
         <v>174</v>
-      </c>
-      <c r="F72" t="s">
-        <v>175</v>
       </c>
       <c r="G72" t="s">
         <v>175</v>
@@ -3710,10 +3710,10 @@
         <v>174</v>
       </c>
       <c r="E73" t="s">
+        <v>175</v>
+      </c>
+      <c r="F73" t="s">
         <v>174</v>
-      </c>
-      <c r="F73" t="s">
-        <v>175</v>
       </c>
       <c r="G73" t="s">
         <v>175</v>
@@ -3733,10 +3733,10 @@
         <v>174</v>
       </c>
       <c r="E74" t="s">
+        <v>175</v>
+      </c>
+      <c r="F74" t="s">
         <v>174</v>
-      </c>
-      <c r="F74" t="s">
-        <v>175</v>
       </c>
       <c r="G74" t="s">
         <v>175</v>
@@ -3756,10 +3756,10 @@
         <v>174</v>
       </c>
       <c r="E75" t="s">
+        <v>175</v>
+      </c>
+      <c r="F75" t="s">
         <v>174</v>
-      </c>
-      <c r="F75" t="s">
-        <v>175</v>
       </c>
       <c r="G75" t="s">
         <v>175</v>
@@ -3779,10 +3779,10 @@
         <v>174</v>
       </c>
       <c r="E76" t="s">
+        <v>175</v>
+      </c>
+      <c r="F76" t="s">
         <v>174</v>
-      </c>
-      <c r="F76" t="s">
-        <v>175</v>
       </c>
       <c r="G76" t="s">
         <v>175</v>
@@ -3802,10 +3802,10 @@
         <v>174</v>
       </c>
       <c r="E77" t="s">
+        <v>175</v>
+      </c>
+      <c r="F77" t="s">
         <v>174</v>
-      </c>
-      <c r="F77" t="s">
-        <v>175</v>
       </c>
       <c r="G77" t="s">
         <v>175</v>
@@ -3825,10 +3825,10 @@
         <v>174</v>
       </c>
       <c r="E78" t="s">
+        <v>175</v>
+      </c>
+      <c r="F78" t="s">
         <v>174</v>
-      </c>
-      <c r="F78" t="s">
-        <v>175</v>
       </c>
       <c r="G78" t="s">
         <v>175</v>
@@ -3848,10 +3848,10 @@
         <v>174</v>
       </c>
       <c r="E79" t="s">
+        <v>175</v>
+      </c>
+      <c r="F79" t="s">
         <v>174</v>
-      </c>
-      <c r="F79" t="s">
-        <v>175</v>
       </c>
       <c r="G79" t="s">
         <v>175</v>
@@ -3871,10 +3871,10 @@
         <v>174</v>
       </c>
       <c r="E80" t="s">
+        <v>175</v>
+      </c>
+      <c r="F80" t="s">
         <v>174</v>
-      </c>
-      <c r="F80" t="s">
-        <v>175</v>
       </c>
       <c r="G80" t="s">
         <v>175</v>
@@ -3894,10 +3894,10 @@
         <v>198</v>
       </c>
       <c r="E81" t="s">
+        <v>199</v>
+      </c>
+      <c r="F81" t="s">
         <v>198</v>
-      </c>
-      <c r="F81" t="s">
-        <v>199</v>
       </c>
       <c r="G81" t="s">
         <v>199</v>
@@ -3917,10 +3917,10 @@
         <v>198</v>
       </c>
       <c r="E82" t="s">
+        <v>199</v>
+      </c>
+      <c r="F82" t="s">
         <v>198</v>
-      </c>
-      <c r="F82" t="s">
-        <v>199</v>
       </c>
       <c r="G82" t="s">
         <v>199</v>
@@ -3940,10 +3940,10 @@
         <v>198</v>
       </c>
       <c r="E83" t="s">
+        <v>199</v>
+      </c>
+      <c r="F83" t="s">
         <v>198</v>
-      </c>
-      <c r="F83" t="s">
-        <v>199</v>
       </c>
       <c r="G83" t="s">
         <v>199</v>
@@ -3963,10 +3963,10 @@
         <v>198</v>
       </c>
       <c r="E84" t="s">
+        <v>199</v>
+      </c>
+      <c r="F84" t="s">
         <v>198</v>
-      </c>
-      <c r="F84" t="s">
-        <v>199</v>
       </c>
       <c r="G84" t="s">
         <v>199</v>
@@ -3986,10 +3986,10 @@
         <v>198</v>
       </c>
       <c r="E85" t="s">
+        <v>199</v>
+      </c>
+      <c r="F85" t="s">
         <v>198</v>
-      </c>
-      <c r="F85" t="s">
-        <v>199</v>
       </c>
       <c r="G85" t="s">
         <v>199</v>
@@ -4009,10 +4009,10 @@
         <v>198</v>
       </c>
       <c r="E86" t="s">
+        <v>199</v>
+      </c>
+      <c r="F86" t="s">
         <v>198</v>
-      </c>
-      <c r="F86" t="s">
-        <v>199</v>
       </c>
       <c r="G86" t="s">
         <v>199</v>
@@ -4032,10 +4032,10 @@
         <v>198</v>
       </c>
       <c r="E87" t="s">
+        <v>199</v>
+      </c>
+      <c r="F87" t="s">
         <v>198</v>
-      </c>
-      <c r="F87" t="s">
-        <v>199</v>
       </c>
       <c r="G87" t="s">
         <v>199</v>
@@ -4055,10 +4055,10 @@
         <v>214</v>
       </c>
       <c r="E88" t="s">
+        <v>215</v>
+      </c>
+      <c r="F88" t="s">
         <v>214</v>
-      </c>
-      <c r="F88" t="s">
-        <v>215</v>
       </c>
       <c r="G88" t="s">
         <v>215</v>
@@ -4078,10 +4078,10 @@
         <v>214</v>
       </c>
       <c r="E89" t="s">
+        <v>215</v>
+      </c>
+      <c r="F89" t="s">
         <v>214</v>
-      </c>
-      <c r="F89" t="s">
-        <v>215</v>
       </c>
       <c r="G89" t="s">
         <v>215</v>
@@ -4101,10 +4101,10 @@
         <v>214</v>
       </c>
       <c r="E90" t="s">
+        <v>215</v>
+      </c>
+      <c r="F90" t="s">
         <v>214</v>
-      </c>
-      <c r="F90" t="s">
-        <v>215</v>
       </c>
       <c r="G90" t="s">
         <v>215</v>
@@ -4124,10 +4124,10 @@
         <v>214</v>
       </c>
       <c r="E91" t="s">
+        <v>215</v>
+      </c>
+      <c r="F91" t="s">
         <v>214</v>
-      </c>
-      <c r="F91" t="s">
-        <v>215</v>
       </c>
       <c r="G91" t="s">
         <v>215</v>
@@ -4236,13 +4236,13 @@
         <v>9</v>
       </c>
       <c r="D96" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E96" t="s">
         <v>225</v>
       </c>
       <c r="F96" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="G96" t="s">
         <v>237</v>
@@ -4259,13 +4259,13 @@
         <v>9</v>
       </c>
       <c r="D97" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E97" t="s">
         <v>225</v>
       </c>
       <c r="F97" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="G97" t="s">
         <v>237</v>
@@ -4282,13 +4282,13 @@
         <v>9</v>
       </c>
       <c r="D98" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E98" t="s">
         <v>225</v>
       </c>
       <c r="F98" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="G98" t="s">
         <v>237</v>
@@ -4305,13 +4305,13 @@
         <v>9</v>
       </c>
       <c r="D99" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E99" t="s">
         <v>225</v>
       </c>
       <c r="F99" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="G99" t="s">
         <v>237</v>
@@ -4328,13 +4328,13 @@
         <v>9</v>
       </c>
       <c r="D100" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E100" t="s">
         <v>225</v>
       </c>
       <c r="F100" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="G100" t="s">
         <v>237</v>
@@ -4351,13 +4351,13 @@
         <v>9</v>
       </c>
       <c r="D101" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E101" t="s">
         <v>225</v>
       </c>
       <c r="F101" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="G101" t="s">
         <v>237</v>
@@ -4374,13 +4374,13 @@
         <v>9</v>
       </c>
       <c r="D102" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E102" t="s">
         <v>225</v>
       </c>
       <c r="F102" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="G102" t="s">
         <v>237</v>
@@ -4397,13 +4397,13 @@
         <v>9</v>
       </c>
       <c r="D103" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E103" t="s">
         <v>225</v>
       </c>
       <c r="F103" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="G103" t="s">
         <v>237</v>
@@ -4420,13 +4420,13 @@
         <v>9</v>
       </c>
       <c r="D104" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E104" t="s">
         <v>225</v>
       </c>
       <c r="F104" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="G104" t="s">
         <v>237</v>
@@ -4443,13 +4443,13 @@
         <v>9</v>
       </c>
       <c r="D105" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="E105" t="s">
         <v>225</v>
       </c>
       <c r="F105" t="s">
-        <v>226</v>
+        <v>256</v>
       </c>
       <c r="G105" t="s">
         <v>257</v>
@@ -4466,13 +4466,13 @@
         <v>9</v>
       </c>
       <c r="D106" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="E106" t="s">
         <v>225</v>
       </c>
       <c r="F106" t="s">
-        <v>226</v>
+        <v>256</v>
       </c>
       <c r="G106" t="s">
         <v>257</v>
@@ -4489,13 +4489,13 @@
         <v>9</v>
       </c>
       <c r="D107" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="E107" t="s">
         <v>225</v>
       </c>
       <c r="F107" t="s">
-        <v>226</v>
+        <v>256</v>
       </c>
       <c r="G107" t="s">
         <v>257</v>
@@ -4512,13 +4512,13 @@
         <v>9</v>
       </c>
       <c r="D108" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="E108" t="s">
         <v>225</v>
       </c>
       <c r="F108" t="s">
-        <v>226</v>
+        <v>256</v>
       </c>
       <c r="G108" t="s">
         <v>257</v>
@@ -4535,13 +4535,13 @@
         <v>9</v>
       </c>
       <c r="D109" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="E109" t="s">
         <v>225</v>
       </c>
       <c r="F109" t="s">
-        <v>226</v>
+        <v>256</v>
       </c>
       <c r="G109" t="s">
         <v>257</v>
@@ -4558,13 +4558,13 @@
         <v>9</v>
       </c>
       <c r="D110" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="E110" t="s">
         <v>225</v>
       </c>
       <c r="F110" t="s">
-        <v>226</v>
+        <v>256</v>
       </c>
       <c r="G110" t="s">
         <v>257</v>
@@ -4581,13 +4581,13 @@
         <v>9</v>
       </c>
       <c r="D111" t="s">
-        <v>270</v>
+        <v>224</v>
       </c>
       <c r="E111" t="s">
         <v>225</v>
       </c>
       <c r="F111" t="s">
-        <v>226</v>
+        <v>270</v>
       </c>
       <c r="G111" t="s">
         <v>271</v>
@@ -4604,13 +4604,13 @@
         <v>9</v>
       </c>
       <c r="D112" t="s">
-        <v>274</v>
+        <v>224</v>
       </c>
       <c r="E112" t="s">
         <v>225</v>
       </c>
       <c r="F112" t="s">
-        <v>226</v>
+        <v>274</v>
       </c>
       <c r="G112" t="s">
         <v>275</v>
@@ -4627,13 +4627,13 @@
         <v>9</v>
       </c>
       <c r="D113" t="s">
-        <v>278</v>
+        <v>224</v>
       </c>
       <c r="E113" t="s">
         <v>225</v>
       </c>
       <c r="F113" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="G113" t="s">
         <v>279</v>
@@ -4650,13 +4650,13 @@
         <v>9</v>
       </c>
       <c r="D114" t="s">
-        <v>278</v>
+        <v>224</v>
       </c>
       <c r="E114" t="s">
         <v>225</v>
       </c>
       <c r="F114" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="G114" t="s">
         <v>279</v>
@@ -4673,13 +4673,13 @@
         <v>9</v>
       </c>
       <c r="D115" t="s">
-        <v>278</v>
+        <v>224</v>
       </c>
       <c r="E115" t="s">
         <v>225</v>
       </c>
       <c r="F115" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="G115" t="s">
         <v>279</v>
@@ -4696,13 +4696,13 @@
         <v>9</v>
       </c>
       <c r="D116" t="s">
-        <v>278</v>
+        <v>224</v>
       </c>
       <c r="E116" t="s">
         <v>225</v>
       </c>
       <c r="F116" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="G116" t="s">
         <v>279</v>
@@ -4719,13 +4719,13 @@
         <v>9</v>
       </c>
       <c r="D117" t="s">
-        <v>278</v>
+        <v>224</v>
       </c>
       <c r="E117" t="s">
         <v>225</v>
       </c>
       <c r="F117" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="G117" t="s">
         <v>279</v>
@@ -4742,13 +4742,13 @@
         <v>9</v>
       </c>
       <c r="D118" t="s">
-        <v>278</v>
+        <v>224</v>
       </c>
       <c r="E118" t="s">
         <v>225</v>
       </c>
       <c r="F118" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="G118" t="s">
         <v>279</v>
@@ -4765,13 +4765,13 @@
         <v>9</v>
       </c>
       <c r="D119" t="s">
-        <v>278</v>
+        <v>224</v>
       </c>
       <c r="E119" t="s">
         <v>225</v>
       </c>
       <c r="F119" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="G119" t="s">
         <v>279</v>
@@ -4791,10 +4791,10 @@
         <v>294</v>
       </c>
       <c r="E120" t="s">
+        <v>295</v>
+      </c>
+      <c r="F120" t="s">
         <v>294</v>
-      </c>
-      <c r="F120" t="s">
-        <v>295</v>
       </c>
       <c r="G120" t="s">
         <v>295</v>
@@ -4814,10 +4814,10 @@
         <v>294</v>
       </c>
       <c r="E121" t="s">
+        <v>295</v>
+      </c>
+      <c r="F121" t="s">
         <v>294</v>
-      </c>
-      <c r="F121" t="s">
-        <v>295</v>
       </c>
       <c r="G121" t="s">
         <v>295</v>
@@ -4837,10 +4837,10 @@
         <v>294</v>
       </c>
       <c r="E122" t="s">
+        <v>295</v>
+      </c>
+      <c r="F122" t="s">
         <v>294</v>
-      </c>
-      <c r="F122" t="s">
-        <v>295</v>
       </c>
       <c r="G122" t="s">
         <v>295</v>
@@ -4860,10 +4860,10 @@
         <v>294</v>
       </c>
       <c r="E123" t="s">
+        <v>295</v>
+      </c>
+      <c r="F123" t="s">
         <v>294</v>
-      </c>
-      <c r="F123" t="s">
-        <v>295</v>
       </c>
       <c r="G123" t="s">
         <v>295</v>
@@ -4883,10 +4883,10 @@
         <v>294</v>
       </c>
       <c r="E124" t="s">
+        <v>295</v>
+      </c>
+      <c r="F124" t="s">
         <v>294</v>
-      </c>
-      <c r="F124" t="s">
-        <v>295</v>
       </c>
       <c r="G124" t="s">
         <v>295</v>
@@ -4906,10 +4906,10 @@
         <v>294</v>
       </c>
       <c r="E125" t="s">
+        <v>295</v>
+      </c>
+      <c r="F125" t="s">
         <v>294</v>
-      </c>
-      <c r="F125" t="s">
-        <v>295</v>
       </c>
       <c r="G125" t="s">
         <v>295</v>
@@ -4929,10 +4929,10 @@
         <v>308</v>
       </c>
       <c r="E126" t="s">
+        <v>309</v>
+      </c>
+      <c r="F126" t="s">
         <v>308</v>
-      </c>
-      <c r="F126" t="s">
-        <v>309</v>
       </c>
       <c r="G126" t="s">
         <v>309</v>
@@ -4952,10 +4952,10 @@
         <v>308</v>
       </c>
       <c r="E127" t="s">
+        <v>309</v>
+      </c>
+      <c r="F127" t="s">
         <v>308</v>
-      </c>
-      <c r="F127" t="s">
-        <v>309</v>
       </c>
       <c r="G127" t="s">
         <v>309</v>
@@ -4975,10 +4975,10 @@
         <v>308</v>
       </c>
       <c r="E128" t="s">
+        <v>309</v>
+      </c>
+      <c r="F128" t="s">
         <v>308</v>
-      </c>
-      <c r="F128" t="s">
-        <v>309</v>
       </c>
       <c r="G128" t="s">
         <v>309</v>
@@ -4998,10 +4998,10 @@
         <v>308</v>
       </c>
       <c r="E129" t="s">
+        <v>309</v>
+      </c>
+      <c r="F129" t="s">
         <v>308</v>
-      </c>
-      <c r="F129" t="s">
-        <v>309</v>
       </c>
       <c r="G129" t="s">
         <v>309</v>
@@ -5432,13 +5432,13 @@
         <v>9</v>
       </c>
       <c r="D148" t="s">
-        <v>358</v>
+        <v>318</v>
       </c>
       <c r="E148" t="s">
         <v>319</v>
       </c>
       <c r="F148" t="s">
-        <v>320</v>
+        <v>358</v>
       </c>
       <c r="G148" t="s">
         <v>359</v>
@@ -5455,13 +5455,13 @@
         <v>9</v>
       </c>
       <c r="D149" t="s">
-        <v>358</v>
+        <v>318</v>
       </c>
       <c r="E149" t="s">
         <v>319</v>
       </c>
       <c r="F149" t="s">
-        <v>320</v>
+        <v>358</v>
       </c>
       <c r="G149" t="s">
         <v>359</v>
@@ -5478,13 +5478,13 @@
         <v>9</v>
       </c>
       <c r="D150" t="s">
-        <v>358</v>
+        <v>318</v>
       </c>
       <c r="E150" t="s">
         <v>319</v>
       </c>
       <c r="F150" t="s">
-        <v>320</v>
+        <v>358</v>
       </c>
       <c r="G150" t="s">
         <v>359</v>
@@ -5501,13 +5501,13 @@
         <v>9</v>
       </c>
       <c r="D151" t="s">
-        <v>358</v>
+        <v>318</v>
       </c>
       <c r="E151" t="s">
         <v>319</v>
       </c>
       <c r="F151" t="s">
-        <v>320</v>
+        <v>358</v>
       </c>
       <c r="G151" t="s">
         <v>359</v>
@@ -5524,13 +5524,13 @@
         <v>9</v>
       </c>
       <c r="D152" t="s">
-        <v>358</v>
+        <v>318</v>
       </c>
       <c r="E152" t="s">
         <v>319</v>
       </c>
       <c r="F152" t="s">
-        <v>320</v>
+        <v>358</v>
       </c>
       <c r="G152" t="s">
         <v>359</v>
@@ -5547,13 +5547,13 @@
         <v>9</v>
       </c>
       <c r="D153" t="s">
-        <v>358</v>
+        <v>318</v>
       </c>
       <c r="E153" t="s">
         <v>319</v>
       </c>
       <c r="F153" t="s">
-        <v>320</v>
+        <v>358</v>
       </c>
       <c r="G153" t="s">
         <v>359</v>
@@ -5570,13 +5570,13 @@
         <v>9</v>
       </c>
       <c r="D154" t="s">
-        <v>372</v>
+        <v>318</v>
       </c>
       <c r="E154" t="s">
         <v>319</v>
       </c>
       <c r="F154" t="s">
-        <v>320</v>
+        <v>372</v>
       </c>
       <c r="G154" t="s">
         <v>373</v>
@@ -5593,13 +5593,13 @@
         <v>9</v>
       </c>
       <c r="D155" t="s">
-        <v>372</v>
+        <v>318</v>
       </c>
       <c r="E155" t="s">
         <v>319</v>
       </c>
       <c r="F155" t="s">
-        <v>320</v>
+        <v>372</v>
       </c>
       <c r="G155" t="s">
         <v>373</v>
@@ -5616,13 +5616,13 @@
         <v>9</v>
       </c>
       <c r="D156" t="s">
-        <v>372</v>
+        <v>318</v>
       </c>
       <c r="E156" t="s">
         <v>319</v>
       </c>
       <c r="F156" t="s">
-        <v>320</v>
+        <v>372</v>
       </c>
       <c r="G156" t="s">
         <v>373</v>
@@ -5639,13 +5639,13 @@
         <v>9</v>
       </c>
       <c r="D157" t="s">
-        <v>372</v>
+        <v>318</v>
       </c>
       <c r="E157" t="s">
         <v>319</v>
       </c>
       <c r="F157" t="s">
-        <v>320</v>
+        <v>372</v>
       </c>
       <c r="G157" t="s">
         <v>373</v>
@@ -5662,13 +5662,13 @@
         <v>9</v>
       </c>
       <c r="D158" t="s">
-        <v>372</v>
+        <v>318</v>
       </c>
       <c r="E158" t="s">
         <v>319</v>
       </c>
       <c r="F158" t="s">
-        <v>320</v>
+        <v>372</v>
       </c>
       <c r="G158" t="s">
         <v>373</v>
@@ -6122,13 +6122,13 @@
         <v>9</v>
       </c>
       <c r="D178" t="s">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="E178" t="s">
         <v>385</v>
       </c>
       <c r="F178" t="s">
-        <v>386</v>
+        <v>426</v>
       </c>
       <c r="G178" t="s">
         <v>427</v>
@@ -6145,13 +6145,13 @@
         <v>9</v>
       </c>
       <c r="D179" t="s">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="E179" t="s">
         <v>385</v>
       </c>
       <c r="F179" t="s">
-        <v>386</v>
+        <v>426</v>
       </c>
       <c r="G179" t="s">
         <v>427</v>
@@ -6168,13 +6168,13 @@
         <v>9</v>
       </c>
       <c r="D180" t="s">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="E180" t="s">
         <v>385</v>
       </c>
       <c r="F180" t="s">
-        <v>386</v>
+        <v>426</v>
       </c>
       <c r="G180" t="s">
         <v>427</v>
@@ -6191,13 +6191,13 @@
         <v>9</v>
       </c>
       <c r="D181" t="s">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="E181" t="s">
         <v>385</v>
       </c>
       <c r="F181" t="s">
-        <v>386</v>
+        <v>426</v>
       </c>
       <c r="G181" t="s">
         <v>427</v>
@@ -6214,13 +6214,13 @@
         <v>9</v>
       </c>
       <c r="D182" t="s">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="E182" t="s">
         <v>385</v>
       </c>
       <c r="F182" t="s">
-        <v>386</v>
+        <v>426</v>
       </c>
       <c r="G182" t="s">
         <v>427</v>
@@ -6237,13 +6237,13 @@
         <v>9</v>
       </c>
       <c r="D183" t="s">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="E183" t="s">
         <v>385</v>
       </c>
       <c r="F183" t="s">
-        <v>386</v>
+        <v>426</v>
       </c>
       <c r="G183" t="s">
         <v>427</v>
@@ -6260,13 +6260,13 @@
         <v>9</v>
       </c>
       <c r="D184" t="s">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="E184" t="s">
         <v>385</v>
       </c>
       <c r="F184" t="s">
-        <v>386</v>
+        <v>426</v>
       </c>
       <c r="G184" t="s">
         <v>427</v>
@@ -6283,13 +6283,13 @@
         <v>9</v>
       </c>
       <c r="D185" t="s">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="E185" t="s">
         <v>385</v>
       </c>
       <c r="F185" t="s">
-        <v>386</v>
+        <v>426</v>
       </c>
       <c r="G185" t="s">
         <v>427</v>
@@ -6306,13 +6306,13 @@
         <v>9</v>
       </c>
       <c r="D186" t="s">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="E186" t="s">
         <v>385</v>
       </c>
       <c r="F186" t="s">
-        <v>386</v>
+        <v>426</v>
       </c>
       <c r="G186" t="s">
         <v>427</v>
@@ -6329,13 +6329,13 @@
         <v>9</v>
       </c>
       <c r="D187" t="s">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="E187" t="s">
         <v>385</v>
       </c>
       <c r="F187" t="s">
-        <v>386</v>
+        <v>426</v>
       </c>
       <c r="G187" t="s">
         <v>427</v>
@@ -6352,13 +6352,13 @@
         <v>9</v>
       </c>
       <c r="D188" t="s">
-        <v>448</v>
+        <v>384</v>
       </c>
       <c r="E188" t="s">
         <v>385</v>
       </c>
       <c r="F188" t="s">
-        <v>386</v>
+        <v>448</v>
       </c>
       <c r="G188" t="s">
         <v>449</v>
@@ -6378,10 +6378,10 @@
         <v>452</v>
       </c>
       <c r="E189" t="s">
+        <v>453</v>
+      </c>
+      <c r="F189" t="s">
         <v>452</v>
-      </c>
-      <c r="F189" t="s">
-        <v>453</v>
       </c>
       <c r="G189" t="s">
         <v>453</v>
@@ -6401,10 +6401,10 @@
         <v>452</v>
       </c>
       <c r="E190" t="s">
+        <v>453</v>
+      </c>
+      <c r="F190" t="s">
         <v>452</v>
-      </c>
-      <c r="F190" t="s">
-        <v>453</v>
       </c>
       <c r="G190" t="s">
         <v>453</v>
@@ -6424,10 +6424,10 @@
         <v>452</v>
       </c>
       <c r="E191" t="s">
+        <v>453</v>
+      </c>
+      <c r="F191" t="s">
         <v>452</v>
-      </c>
-      <c r="F191" t="s">
-        <v>453</v>
       </c>
       <c r="G191" t="s">
         <v>453</v>
@@ -6447,10 +6447,10 @@
         <v>452</v>
       </c>
       <c r="E192" t="s">
+        <v>453</v>
+      </c>
+      <c r="F192" t="s">
         <v>452</v>
-      </c>
-      <c r="F192" t="s">
-        <v>453</v>
       </c>
       <c r="G192" t="s">
         <v>453</v>
@@ -6470,10 +6470,10 @@
         <v>452</v>
       </c>
       <c r="E193" t="s">
+        <v>453</v>
+      </c>
+      <c r="F193" t="s">
         <v>452</v>
-      </c>
-      <c r="F193" t="s">
-        <v>453</v>
       </c>
       <c r="G193" t="s">
         <v>453</v>
@@ -6493,10 +6493,10 @@
         <v>452</v>
       </c>
       <c r="E194" t="s">
+        <v>453</v>
+      </c>
+      <c r="F194" t="s">
         <v>452</v>
-      </c>
-      <c r="F194" t="s">
-        <v>453</v>
       </c>
       <c r="G194" t="s">
         <v>453</v>
@@ -6516,10 +6516,10 @@
         <v>466</v>
       </c>
       <c r="E195" t="s">
+        <v>467</v>
+      </c>
+      <c r="F195" t="s">
         <v>466</v>
-      </c>
-      <c r="F195" t="s">
-        <v>467</v>
       </c>
       <c r="G195" t="s">
         <v>467</v>
@@ -6539,10 +6539,10 @@
         <v>470</v>
       </c>
       <c r="E196" t="s">
+        <v>471</v>
+      </c>
+      <c r="F196" t="s">
         <v>470</v>
-      </c>
-      <c r="F196" t="s">
-        <v>471</v>
       </c>
       <c r="G196" t="s">
         <v>471</v>
@@ -6562,10 +6562,10 @@
         <v>470</v>
       </c>
       <c r="E197" t="s">
+        <v>471</v>
+      </c>
+      <c r="F197" t="s">
         <v>470</v>
-      </c>
-      <c r="F197" t="s">
-        <v>471</v>
       </c>
       <c r="G197" t="s">
         <v>471</v>
@@ -6585,10 +6585,10 @@
         <v>470</v>
       </c>
       <c r="E198" t="s">
+        <v>471</v>
+      </c>
+      <c r="F198" t="s">
         <v>470</v>
-      </c>
-      <c r="F198" t="s">
-        <v>471</v>
       </c>
       <c r="G198" t="s">
         <v>471</v>
@@ -6608,10 +6608,10 @@
         <v>470</v>
       </c>
       <c r="E199" t="s">
+        <v>471</v>
+      </c>
+      <c r="F199" t="s">
         <v>470</v>
-      </c>
-      <c r="F199" t="s">
-        <v>471</v>
       </c>
       <c r="G199" t="s">
         <v>471</v>
@@ -6631,10 +6631,10 @@
         <v>470</v>
       </c>
       <c r="E200" t="s">
+        <v>471</v>
+      </c>
+      <c r="F200" t="s">
         <v>470</v>
-      </c>
-      <c r="F200" t="s">
-        <v>471</v>
       </c>
       <c r="G200" t="s">
         <v>471</v>
@@ -6654,10 +6654,10 @@
         <v>470</v>
       </c>
       <c r="E201" t="s">
+        <v>471</v>
+      </c>
+      <c r="F201" t="s">
         <v>470</v>
-      </c>
-      <c r="F201" t="s">
-        <v>471</v>
       </c>
       <c r="G201" t="s">
         <v>471</v>
@@ -6677,10 +6677,10 @@
         <v>484</v>
       </c>
       <c r="E202" t="s">
+        <v>485</v>
+      </c>
+      <c r="F202" t="s">
         <v>484</v>
-      </c>
-      <c r="F202" t="s">
-        <v>485</v>
       </c>
       <c r="G202" t="s">
         <v>485</v>
@@ -6700,10 +6700,10 @@
         <v>484</v>
       </c>
       <c r="E203" t="s">
+        <v>485</v>
+      </c>
+      <c r="F203" t="s">
         <v>484</v>
-      </c>
-      <c r="F203" t="s">
-        <v>485</v>
       </c>
       <c r="G203" t="s">
         <v>485</v>
@@ -6723,10 +6723,10 @@
         <v>484</v>
       </c>
       <c r="E204" t="s">
+        <v>485</v>
+      </c>
+      <c r="F204" t="s">
         <v>484</v>
-      </c>
-      <c r="F204" t="s">
-        <v>485</v>
       </c>
       <c r="G204" t="s">
         <v>485</v>
@@ -6746,10 +6746,10 @@
         <v>484</v>
       </c>
       <c r="E205" t="s">
+        <v>485</v>
+      </c>
+      <c r="F205" t="s">
         <v>484</v>
-      </c>
-      <c r="F205" t="s">
-        <v>485</v>
       </c>
       <c r="G205" t="s">
         <v>485</v>
@@ -6769,10 +6769,10 @@
         <v>484</v>
       </c>
       <c r="E206" t="s">
+        <v>485</v>
+      </c>
+      <c r="F206" t="s">
         <v>484</v>
-      </c>
-      <c r="F206" t="s">
-        <v>485</v>
       </c>
       <c r="G206" t="s">
         <v>485</v>
@@ -6792,10 +6792,10 @@
         <v>484</v>
       </c>
       <c r="E207" t="s">
+        <v>485</v>
+      </c>
+      <c r="F207" t="s">
         <v>484</v>
-      </c>
-      <c r="F207" t="s">
-        <v>485</v>
       </c>
       <c r="G207" t="s">
         <v>485</v>
@@ -6815,10 +6815,10 @@
         <v>484</v>
       </c>
       <c r="E208" t="s">
+        <v>485</v>
+      </c>
+      <c r="F208" t="s">
         <v>484</v>
-      </c>
-      <c r="F208" t="s">
-        <v>485</v>
       </c>
       <c r="G208" t="s">
         <v>485</v>
@@ -6838,10 +6838,10 @@
         <v>484</v>
       </c>
       <c r="E209" t="s">
+        <v>485</v>
+      </c>
+      <c r="F209" t="s">
         <v>484</v>
-      </c>
-      <c r="F209" t="s">
-        <v>485</v>
       </c>
       <c r="G209" t="s">
         <v>485</v>
@@ -6861,10 +6861,10 @@
         <v>484</v>
       </c>
       <c r="E210" t="s">
+        <v>485</v>
+      </c>
+      <c r="F210" t="s">
         <v>484</v>
-      </c>
-      <c r="F210" t="s">
-        <v>485</v>
       </c>
       <c r="G210" t="s">
         <v>485</v>
@@ -6884,10 +6884,10 @@
         <v>484</v>
       </c>
       <c r="E211" t="s">
+        <v>485</v>
+      </c>
+      <c r="F211" t="s">
         <v>484</v>
-      </c>
-      <c r="F211" t="s">
-        <v>485</v>
       </c>
       <c r="G211" t="s">
         <v>485</v>
@@ -6907,10 +6907,10 @@
         <v>506</v>
       </c>
       <c r="E212" t="s">
+        <v>507</v>
+      </c>
+      <c r="F212" t="s">
         <v>506</v>
-      </c>
-      <c r="F212" t="s">
-        <v>507</v>
       </c>
       <c r="G212" t="s">
         <v>507</v>
@@ -6930,10 +6930,10 @@
         <v>510</v>
       </c>
       <c r="E213" t="s">
+        <v>511</v>
+      </c>
+      <c r="F213" t="s">
         <v>510</v>
-      </c>
-      <c r="F213" t="s">
-        <v>511</v>
       </c>
       <c r="G213" t="s">
         <v>511</v>
@@ -6953,10 +6953,10 @@
         <v>514</v>
       </c>
       <c r="E214" t="s">
+        <v>515</v>
+      </c>
+      <c r="F214" t="s">
         <v>514</v>
-      </c>
-      <c r="F214" t="s">
-        <v>515</v>
       </c>
       <c r="G214" t="s">
         <v>515</v>
@@ -6976,10 +6976,10 @@
         <v>514</v>
       </c>
       <c r="E215" t="s">
+        <v>515</v>
+      </c>
+      <c r="F215" t="s">
         <v>514</v>
-      </c>
-      <c r="F215" t="s">
-        <v>515</v>
       </c>
       <c r="G215" t="s">
         <v>515</v>
@@ -6999,10 +6999,10 @@
         <v>520</v>
       </c>
       <c r="E216" t="s">
+        <v>521</v>
+      </c>
+      <c r="F216" t="s">
         <v>520</v>
-      </c>
-      <c r="F216" t="s">
-        <v>521</v>
       </c>
       <c r="G216" t="s">
         <v>521</v>
@@ -7022,10 +7022,10 @@
         <v>520</v>
       </c>
       <c r="E217" t="s">
+        <v>521</v>
+      </c>
+      <c r="F217" t="s">
         <v>520</v>
-      </c>
-      <c r="F217" t="s">
-        <v>521</v>
       </c>
       <c r="G217" t="s">
         <v>521</v>
@@ -7045,10 +7045,10 @@
         <v>520</v>
       </c>
       <c r="E218" t="s">
+        <v>521</v>
+      </c>
+      <c r="F218" t="s">
         <v>520</v>
-      </c>
-      <c r="F218" t="s">
-        <v>521</v>
       </c>
       <c r="G218" t="s">
         <v>521</v>
@@ -7068,10 +7068,10 @@
         <v>520</v>
       </c>
       <c r="E219" t="s">
+        <v>521</v>
+      </c>
+      <c r="F219" t="s">
         <v>520</v>
-      </c>
-      <c r="F219" t="s">
-        <v>521</v>
       </c>
       <c r="G219" t="s">
         <v>521</v>
@@ -7091,10 +7091,10 @@
         <v>520</v>
       </c>
       <c r="E220" t="s">
+        <v>521</v>
+      </c>
+      <c r="F220" t="s">
         <v>520</v>
-      </c>
-      <c r="F220" t="s">
-        <v>521</v>
       </c>
       <c r="G220" t="s">
         <v>521</v>
@@ -7114,10 +7114,10 @@
         <v>520</v>
       </c>
       <c r="E221" t="s">
+        <v>521</v>
+      </c>
+      <c r="F221" t="s">
         <v>520</v>
-      </c>
-      <c r="F221" t="s">
-        <v>521</v>
       </c>
       <c r="G221" t="s">
         <v>521</v>
@@ -7137,10 +7137,10 @@
         <v>520</v>
       </c>
       <c r="E222" t="s">
+        <v>521</v>
+      </c>
+      <c r="F222" t="s">
         <v>520</v>
-      </c>
-      <c r="F222" t="s">
-        <v>521</v>
       </c>
       <c r="G222" t="s">
         <v>521</v>
@@ -7160,10 +7160,10 @@
         <v>536</v>
       </c>
       <c r="E223" t="s">
+        <v>537</v>
+      </c>
+      <c r="F223" t="s">
         <v>536</v>
-      </c>
-      <c r="F223" t="s">
-        <v>537</v>
       </c>
       <c r="G223" t="s">
         <v>537</v>
@@ -7183,10 +7183,10 @@
         <v>536</v>
       </c>
       <c r="E224" t="s">
+        <v>537</v>
+      </c>
+      <c r="F224" t="s">
         <v>536</v>
-      </c>
-      <c r="F224" t="s">
-        <v>537</v>
       </c>
       <c r="G224" t="s">
         <v>537</v>
@@ -7206,10 +7206,10 @@
         <v>536</v>
       </c>
       <c r="E225" t="s">
+        <v>537</v>
+      </c>
+      <c r="F225" t="s">
         <v>536</v>
-      </c>
-      <c r="F225" t="s">
-        <v>537</v>
       </c>
       <c r="G225" t="s">
         <v>537</v>
@@ -7229,10 +7229,10 @@
         <v>544</v>
       </c>
       <c r="E226" t="s">
+        <v>545</v>
+      </c>
+      <c r="F226" t="s">
         <v>544</v>
-      </c>
-      <c r="F226" t="s">
-        <v>545</v>
       </c>
       <c r="G226" t="s">
         <v>545</v>
@@ -7252,10 +7252,10 @@
         <v>548</v>
       </c>
       <c r="E227" t="s">
+        <v>549</v>
+      </c>
+      <c r="F227" t="s">
         <v>548</v>
-      </c>
-      <c r="F227" t="s">
-        <v>549</v>
       </c>
       <c r="G227" t="s">
         <v>549</v>
@@ -7275,10 +7275,10 @@
         <v>552</v>
       </c>
       <c r="E228" t="s">
+        <v>553</v>
+      </c>
+      <c r="F228" t="s">
         <v>552</v>
-      </c>
-      <c r="F228" t="s">
-        <v>553</v>
       </c>
       <c r="G228" t="s">
         <v>553</v>
@@ -7298,10 +7298,10 @@
         <v>556</v>
       </c>
       <c r="E229" t="s">
+        <v>557</v>
+      </c>
+      <c r="F229" t="s">
         <v>556</v>
-      </c>
-      <c r="F229" t="s">
-        <v>557</v>
       </c>
       <c r="G229" t="s">
         <v>557</v>
@@ -7321,10 +7321,10 @@
         <v>560</v>
       </c>
       <c r="E230" t="s">
+        <v>561</v>
+      </c>
+      <c r="F230" t="s">
         <v>560</v>
-      </c>
-      <c r="F230" t="s">
-        <v>561</v>
       </c>
       <c r="G230" t="s">
         <v>561</v>
@@ -7344,10 +7344,10 @@
         <v>560</v>
       </c>
       <c r="E231" t="s">
+        <v>561</v>
+      </c>
+      <c r="F231" t="s">
         <v>560</v>
-      </c>
-      <c r="F231" t="s">
-        <v>561</v>
       </c>
       <c r="G231" t="s">
         <v>561</v>

--- a/api/xlsx/en/SectorGroup.xlsx
+++ b/api/xlsx/en/SectorGroup.xlsx
@@ -28,15 +28,15 @@
     <t>codeforiati:group-code</t>
   </si>
   <si>
+    <t>codeforiati:category-name</t>
+  </si>
+  <si>
     <t>codeforiati:group-name</t>
   </si>
   <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
-    <t>codeforiati:category-name</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -49,15 +49,15 @@
     <t>110</t>
   </si>
   <si>
+    <t>Education, Level Unspecified</t>
+  </si>
+  <si>
     <t>Education</t>
   </si>
   <si>
     <t>111</t>
   </si>
   <si>
-    <t>Education, Level Unspecified</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -82,12 +82,12 @@
     <t>Primary education</t>
   </si>
   <si>
+    <t>Basic Education</t>
+  </si>
+  <si>
     <t>112</t>
   </si>
   <si>
-    <t>Basic Education</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -112,12 +112,12 @@
     <t>Secondary education</t>
   </si>
   <si>
+    <t>Secondary Education</t>
+  </si>
+  <si>
     <t>113</t>
   </si>
   <si>
-    <t>Secondary Education</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
@@ -130,12 +130,12 @@
     <t>Higher education</t>
   </si>
   <si>
+    <t>Post-Secondary Education</t>
+  </si>
+  <si>
     <t>114</t>
   </si>
   <si>
-    <t>Post-Secondary Education</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -151,15 +151,15 @@
     <t>120</t>
   </si>
   <si>
+    <t>Health, General</t>
+  </si>
+  <si>
     <t>Health</t>
   </si>
   <si>
     <t>121</t>
   </si>
   <si>
-    <t>Health, General</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -184,12 +184,12 @@
     <t>Basic health care</t>
   </si>
   <si>
+    <t>Basic Health</t>
+  </si>
+  <si>
     <t>122</t>
   </si>
   <si>
-    <t>Basic Health</t>
-  </si>
-  <si>
     <t>12230</t>
   </si>
   <si>
@@ -238,12 +238,12 @@
     <t>NCDs control, general</t>
   </si>
   <si>
+    <t>Non-communicable diseases (NCDs)</t>
+  </si>
+  <si>
     <t>123</t>
   </si>
   <si>
-    <t>Non-communicable diseases (NCDs)</t>
-  </si>
-  <si>
     <t>12320</t>
   </si>
   <si>
@@ -391,15 +391,15 @@
     <t>150</t>
   </si>
   <si>
+    <t>Government &amp; Civil Society-general</t>
+  </si>
+  <si>
     <t>Government &amp; Civil Society</t>
   </si>
   <si>
     <t>151</t>
   </si>
   <si>
-    <t>Government &amp; Civil Society-general</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -496,12 +496,12 @@
     <t>Security system management and reform</t>
   </si>
   <si>
+    <t>Conflict, Peace &amp; Security</t>
+  </si>
+  <si>
     <t>152</t>
   </si>
   <si>
-    <t>Conflict, Peace &amp; Security</t>
-  </si>
-  <si>
     <t>15220</t>
   </si>
   <si>
@@ -691,15 +691,15 @@
     <t>230</t>
   </si>
   <si>
+    <t>Energy Policy</t>
+  </si>
+  <si>
     <t>Energy</t>
   </si>
   <si>
     <t>231</t>
   </si>
   <si>
-    <t>Energy Policy</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -724,12 +724,12 @@
     <t>Energy generation, renewable sources - multiple technologies</t>
   </si>
   <si>
+    <t>Energy generation, renewable sources</t>
+  </si>
+  <si>
     <t>232</t>
   </si>
   <si>
-    <t>Energy generation, renewable sources</t>
-  </si>
-  <si>
     <t>23220</t>
   </si>
   <si>
@@ -784,12 +784,12 @@
     <t>Energy generation, non-renewable sources, unspecified</t>
   </si>
   <si>
+    <t>Energy generation, non-renewable sources</t>
+  </si>
+  <si>
     <t>233</t>
   </si>
   <si>
-    <t>Energy generation, non-renewable sources</t>
-  </si>
-  <si>
     <t>23320</t>
   </si>
   <si>
@@ -826,36 +826,36 @@
     <t>Hybrid energy electric power plants</t>
   </si>
   <si>
+    <t>Hybrid energy plants</t>
+  </si>
+  <si>
     <t>234</t>
   </si>
   <si>
-    <t>Hybrid energy plants</t>
-  </si>
-  <si>
     <t>23510</t>
   </si>
   <si>
     <t>Nuclear energy electric power plants and nuclear safety</t>
   </si>
   <si>
+    <t>Nuclear energy plants</t>
+  </si>
+  <si>
     <t>235</t>
   </si>
   <si>
-    <t>Nuclear energy plants</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
     <t>Heat plants</t>
   </si>
   <si>
+    <t>Energy distribution</t>
+  </si>
+  <si>
     <t>236</t>
   </si>
   <si>
-    <t>Energy distribution</t>
-  </si>
-  <si>
     <t>23620</t>
   </si>
   <si>
@@ -973,15 +973,15 @@
     <t>310</t>
   </si>
   <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
     <t>Agriculture, Forestry, Fishing</t>
   </si>
   <si>
     <t>311</t>
   </si>
   <si>
-    <t>Agriculture</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1090,12 +1090,12 @@
     <t>Forestry policy and administrative management</t>
   </si>
   <si>
+    <t>Forestry</t>
+  </si>
+  <si>
     <t>312</t>
   </si>
   <si>
-    <t>Forestry</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -1132,12 +1132,12 @@
     <t>Fishing policy and administrative management</t>
   </si>
   <si>
+    <t>Fishing</t>
+  </si>
+  <si>
     <t>313</t>
   </si>
   <si>
-    <t>Fishing</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -1171,15 +1171,15 @@
     <t>320</t>
   </si>
   <si>
+    <t>Industry</t>
+  </si>
+  <si>
     <t>Industry, Mining, Construction</t>
   </si>
   <si>
     <t>321</t>
   </si>
   <si>
-    <t>Industry</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1294,12 +1294,12 @@
     <t>Mineral/mining policy and administrative management</t>
   </si>
   <si>
+    <t>Mineral Resources &amp; Mining</t>
+  </si>
+  <si>
     <t>322</t>
   </si>
   <si>
-    <t>Mineral Resources &amp; Mining</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -1360,10 +1360,10 @@
     <t>Construction policy and administrative management</t>
   </si>
   <si>
+    <t>Construction</t>
+  </si>
+  <si>
     <t>323</t>
-  </si>
-  <si>
-    <t>Construction</t>
   </si>
   <si>
     <t>33110</t>
@@ -2169,10 +2169,10 @@
         <v>10</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F6" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G6" t="s">
         <v>23</v>
@@ -2192,10 +2192,10 @@
         <v>10</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F7" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G7" t="s">
         <v>23</v>
@@ -2215,10 +2215,10 @@
         <v>10</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F8" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G8" t="s">
         <v>23</v>
@@ -2238,10 +2238,10 @@
         <v>10</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F9" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G9" t="s">
         <v>23</v>
@@ -2261,10 +2261,10 @@
         <v>10</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F10" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="G10" t="s">
         <v>33</v>
@@ -2284,10 +2284,10 @@
         <v>10</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F11" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="G11" t="s">
         <v>33</v>
@@ -2307,10 +2307,10 @@
         <v>10</v>
       </c>
       <c r="E12" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="F12" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="G12" t="s">
         <v>39</v>
@@ -2330,10 +2330,10 @@
         <v>10</v>
       </c>
       <c r="E13" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="F13" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="G13" t="s">
         <v>39</v>
@@ -2445,10 +2445,10 @@
         <v>44</v>
       </c>
       <c r="E18" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="F18" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G18" t="s">
         <v>57</v>
@@ -2468,10 +2468,10 @@
         <v>44</v>
       </c>
       <c r="E19" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="F19" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G19" t="s">
         <v>57</v>
@@ -2491,10 +2491,10 @@
         <v>44</v>
       </c>
       <c r="E20" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="F20" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G20" t="s">
         <v>57</v>
@@ -2514,10 +2514,10 @@
         <v>44</v>
       </c>
       <c r="E21" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="F21" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G21" t="s">
         <v>57</v>
@@ -2537,10 +2537,10 @@
         <v>44</v>
       </c>
       <c r="E22" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="F22" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G22" t="s">
         <v>57</v>
@@ -2560,10 +2560,10 @@
         <v>44</v>
       </c>
       <c r="E23" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="F23" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G23" t="s">
         <v>57</v>
@@ -2583,10 +2583,10 @@
         <v>44</v>
       </c>
       <c r="E24" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="F24" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G24" t="s">
         <v>57</v>
@@ -2606,10 +2606,10 @@
         <v>44</v>
       </c>
       <c r="E25" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="F25" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G25" t="s">
         <v>57</v>
@@ -2629,10 +2629,10 @@
         <v>44</v>
       </c>
       <c r="E26" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="F26" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G26" t="s">
         <v>75</v>
@@ -2652,10 +2652,10 @@
         <v>44</v>
       </c>
       <c r="E27" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="F27" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G27" t="s">
         <v>75</v>
@@ -2675,10 +2675,10 @@
         <v>44</v>
       </c>
       <c r="E28" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="F28" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G28" t="s">
         <v>75</v>
@@ -2698,10 +2698,10 @@
         <v>44</v>
       </c>
       <c r="E29" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="F29" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G29" t="s">
         <v>75</v>
@@ -2721,10 +2721,10 @@
         <v>44</v>
       </c>
       <c r="E30" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="F30" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G30" t="s">
         <v>75</v>
@@ -2744,10 +2744,10 @@
         <v>44</v>
       </c>
       <c r="E31" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="F31" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G31" t="s">
         <v>75</v>
@@ -2770,10 +2770,10 @@
         <v>89</v>
       </c>
       <c r="F32" t="s">
+        <v>89</v>
+      </c>
+      <c r="G32" t="s">
         <v>88</v>
-      </c>
-      <c r="G32" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2793,10 +2793,10 @@
         <v>89</v>
       </c>
       <c r="F33" t="s">
+        <v>89</v>
+      </c>
+      <c r="G33" t="s">
         <v>88</v>
-      </c>
-      <c r="G33" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2816,10 +2816,10 @@
         <v>89</v>
       </c>
       <c r="F34" t="s">
+        <v>89</v>
+      </c>
+      <c r="G34" t="s">
         <v>88</v>
-      </c>
-      <c r="G34" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2839,10 +2839,10 @@
         <v>89</v>
       </c>
       <c r="F35" t="s">
+        <v>89</v>
+      </c>
+      <c r="G35" t="s">
         <v>88</v>
-      </c>
-      <c r="G35" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2862,10 +2862,10 @@
         <v>89</v>
       </c>
       <c r="F36" t="s">
+        <v>89</v>
+      </c>
+      <c r="G36" t="s">
         <v>88</v>
-      </c>
-      <c r="G36" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2885,10 +2885,10 @@
         <v>101</v>
       </c>
       <c r="F37" t="s">
+        <v>101</v>
+      </c>
+      <c r="G37" t="s">
         <v>100</v>
-      </c>
-      <c r="G37" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2908,10 +2908,10 @@
         <v>101</v>
       </c>
       <c r="F38" t="s">
+        <v>101</v>
+      </c>
+      <c r="G38" t="s">
         <v>100</v>
-      </c>
-      <c r="G38" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2931,10 +2931,10 @@
         <v>101</v>
       </c>
       <c r="F39" t="s">
+        <v>101</v>
+      </c>
+      <c r="G39" t="s">
         <v>100</v>
-      </c>
-      <c r="G39" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2954,10 +2954,10 @@
         <v>101</v>
       </c>
       <c r="F40" t="s">
+        <v>101</v>
+      </c>
+      <c r="G40" t="s">
         <v>100</v>
-      </c>
-      <c r="G40" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2977,10 +2977,10 @@
         <v>101</v>
       </c>
       <c r="F41" t="s">
+        <v>101</v>
+      </c>
+      <c r="G41" t="s">
         <v>100</v>
-      </c>
-      <c r="G41" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -3000,10 +3000,10 @@
         <v>101</v>
       </c>
       <c r="F42" t="s">
+        <v>101</v>
+      </c>
+      <c r="G42" t="s">
         <v>100</v>
-      </c>
-      <c r="G42" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3023,10 +3023,10 @@
         <v>101</v>
       </c>
       <c r="F43" t="s">
+        <v>101</v>
+      </c>
+      <c r="G43" t="s">
         <v>100</v>
-      </c>
-      <c r="G43" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3046,10 +3046,10 @@
         <v>101</v>
       </c>
       <c r="F44" t="s">
+        <v>101</v>
+      </c>
+      <c r="G44" t="s">
         <v>100</v>
-      </c>
-      <c r="G44" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3069,10 +3069,10 @@
         <v>101</v>
       </c>
       <c r="F45" t="s">
+        <v>101</v>
+      </c>
+      <c r="G45" t="s">
         <v>100</v>
-      </c>
-      <c r="G45" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3092,10 +3092,10 @@
         <v>101</v>
       </c>
       <c r="F46" t="s">
+        <v>101</v>
+      </c>
+      <c r="G46" t="s">
         <v>100</v>
-      </c>
-      <c r="G46" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3115,10 +3115,10 @@
         <v>101</v>
       </c>
       <c r="F47" t="s">
+        <v>101</v>
+      </c>
+      <c r="G47" t="s">
         <v>100</v>
-      </c>
-      <c r="G47" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3503,10 +3503,10 @@
         <v>124</v>
       </c>
       <c r="E64" t="s">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="F64" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="G64" t="s">
         <v>161</v>
@@ -3526,10 +3526,10 @@
         <v>124</v>
       </c>
       <c r="E65" t="s">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="F65" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="G65" t="s">
         <v>161</v>
@@ -3549,10 +3549,10 @@
         <v>124</v>
       </c>
       <c r="E66" t="s">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="F66" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="G66" t="s">
         <v>161</v>
@@ -3572,10 +3572,10 @@
         <v>124</v>
       </c>
       <c r="E67" t="s">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="F67" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="G67" t="s">
         <v>161</v>
@@ -3595,10 +3595,10 @@
         <v>124</v>
       </c>
       <c r="E68" t="s">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="F68" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="G68" t="s">
         <v>161</v>
@@ -3618,10 +3618,10 @@
         <v>124</v>
       </c>
       <c r="E69" t="s">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="F69" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="G69" t="s">
         <v>161</v>
@@ -3644,10 +3644,10 @@
         <v>175</v>
       </c>
       <c r="F70" t="s">
+        <v>175</v>
+      </c>
+      <c r="G70" t="s">
         <v>174</v>
-      </c>
-      <c r="G70" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3667,10 +3667,10 @@
         <v>175</v>
       </c>
       <c r="F71" t="s">
+        <v>175</v>
+      </c>
+      <c r="G71" t="s">
         <v>174</v>
-      </c>
-      <c r="G71" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3690,10 +3690,10 @@
         <v>175</v>
       </c>
       <c r="F72" t="s">
+        <v>175</v>
+      </c>
+      <c r="G72" t="s">
         <v>174</v>
-      </c>
-      <c r="G72" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3713,10 +3713,10 @@
         <v>175</v>
       </c>
       <c r="F73" t="s">
+        <v>175</v>
+      </c>
+      <c r="G73" t="s">
         <v>174</v>
-      </c>
-      <c r="G73" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3736,10 +3736,10 @@
         <v>175</v>
       </c>
       <c r="F74" t="s">
+        <v>175</v>
+      </c>
+      <c r="G74" t="s">
         <v>174</v>
-      </c>
-      <c r="G74" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3759,10 +3759,10 @@
         <v>175</v>
       </c>
       <c r="F75" t="s">
+        <v>175</v>
+      </c>
+      <c r="G75" t="s">
         <v>174</v>
-      </c>
-      <c r="G75" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3782,10 +3782,10 @@
         <v>175</v>
       </c>
       <c r="F76" t="s">
+        <v>175</v>
+      </c>
+      <c r="G76" t="s">
         <v>174</v>
-      </c>
-      <c r="G76" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3805,10 +3805,10 @@
         <v>175</v>
       </c>
       <c r="F77" t="s">
+        <v>175</v>
+      </c>
+      <c r="G77" t="s">
         <v>174</v>
-      </c>
-      <c r="G77" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3828,10 +3828,10 @@
         <v>175</v>
       </c>
       <c r="F78" t="s">
+        <v>175</v>
+      </c>
+      <c r="G78" t="s">
         <v>174</v>
-      </c>
-      <c r="G78" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3851,10 +3851,10 @@
         <v>175</v>
       </c>
       <c r="F79" t="s">
+        <v>175</v>
+      </c>
+      <c r="G79" t="s">
         <v>174</v>
-      </c>
-      <c r="G79" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3874,10 +3874,10 @@
         <v>175</v>
       </c>
       <c r="F80" t="s">
+        <v>175</v>
+      </c>
+      <c r="G80" t="s">
         <v>174</v>
-      </c>
-      <c r="G80" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3897,10 +3897,10 @@
         <v>199</v>
       </c>
       <c r="F81" t="s">
+        <v>199</v>
+      </c>
+      <c r="G81" t="s">
         <v>198</v>
-      </c>
-      <c r="G81" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3920,10 +3920,10 @@
         <v>199</v>
       </c>
       <c r="F82" t="s">
+        <v>199</v>
+      </c>
+      <c r="G82" t="s">
         <v>198</v>
-      </c>
-      <c r="G82" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3943,10 +3943,10 @@
         <v>199</v>
       </c>
       <c r="F83" t="s">
+        <v>199</v>
+      </c>
+      <c r="G83" t="s">
         <v>198</v>
-      </c>
-      <c r="G83" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3966,10 +3966,10 @@
         <v>199</v>
       </c>
       <c r="F84" t="s">
+        <v>199</v>
+      </c>
+      <c r="G84" t="s">
         <v>198</v>
-      </c>
-      <c r="G84" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3989,10 +3989,10 @@
         <v>199</v>
       </c>
       <c r="F85" t="s">
+        <v>199</v>
+      </c>
+      <c r="G85" t="s">
         <v>198</v>
-      </c>
-      <c r="G85" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4012,10 +4012,10 @@
         <v>199</v>
       </c>
       <c r="F86" t="s">
+        <v>199</v>
+      </c>
+      <c r="G86" t="s">
         <v>198</v>
-      </c>
-      <c r="G86" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4035,10 +4035,10 @@
         <v>199</v>
       </c>
       <c r="F87" t="s">
+        <v>199</v>
+      </c>
+      <c r="G87" t="s">
         <v>198</v>
-      </c>
-      <c r="G87" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4058,10 +4058,10 @@
         <v>215</v>
       </c>
       <c r="F88" t="s">
+        <v>215</v>
+      </c>
+      <c r="G88" t="s">
         <v>214</v>
-      </c>
-      <c r="G88" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4081,10 +4081,10 @@
         <v>215</v>
       </c>
       <c r="F89" t="s">
+        <v>215</v>
+      </c>
+      <c r="G89" t="s">
         <v>214</v>
-      </c>
-      <c r="G89" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4104,10 +4104,10 @@
         <v>215</v>
       </c>
       <c r="F90" t="s">
+        <v>215</v>
+      </c>
+      <c r="G90" t="s">
         <v>214</v>
-      </c>
-      <c r="G90" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4127,10 +4127,10 @@
         <v>215</v>
       </c>
       <c r="F91" t="s">
+        <v>215</v>
+      </c>
+      <c r="G91" t="s">
         <v>214</v>
-      </c>
-      <c r="G91" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4239,10 +4239,10 @@
         <v>224</v>
       </c>
       <c r="E96" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="F96" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G96" t="s">
         <v>237</v>
@@ -4262,10 +4262,10 @@
         <v>224</v>
       </c>
       <c r="E97" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="F97" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G97" t="s">
         <v>237</v>
@@ -4285,10 +4285,10 @@
         <v>224</v>
       </c>
       <c r="E98" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="F98" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G98" t="s">
         <v>237</v>
@@ -4308,10 +4308,10 @@
         <v>224</v>
       </c>
       <c r="E99" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="F99" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G99" t="s">
         <v>237</v>
@@ -4331,10 +4331,10 @@
         <v>224</v>
       </c>
       <c r="E100" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="F100" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G100" t="s">
         <v>237</v>
@@ -4354,10 +4354,10 @@
         <v>224</v>
       </c>
       <c r="E101" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="F101" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G101" t="s">
         <v>237</v>
@@ -4377,10 +4377,10 @@
         <v>224</v>
       </c>
       <c r="E102" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="F102" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G102" t="s">
         <v>237</v>
@@ -4400,10 +4400,10 @@
         <v>224</v>
       </c>
       <c r="E103" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="F103" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G103" t="s">
         <v>237</v>
@@ -4423,10 +4423,10 @@
         <v>224</v>
       </c>
       <c r="E104" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="F104" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G104" t="s">
         <v>237</v>
@@ -4446,10 +4446,10 @@
         <v>224</v>
       </c>
       <c r="E105" t="s">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="F105" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="G105" t="s">
         <v>257</v>
@@ -4469,10 +4469,10 @@
         <v>224</v>
       </c>
       <c r="E106" t="s">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="F106" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="G106" t="s">
         <v>257</v>
@@ -4492,10 +4492,10 @@
         <v>224</v>
       </c>
       <c r="E107" t="s">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="F107" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="G107" t="s">
         <v>257</v>
@@ -4515,10 +4515,10 @@
         <v>224</v>
       </c>
       <c r="E108" t="s">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="F108" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="G108" t="s">
         <v>257</v>
@@ -4538,10 +4538,10 @@
         <v>224</v>
       </c>
       <c r="E109" t="s">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="F109" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="G109" t="s">
         <v>257</v>
@@ -4561,10 +4561,10 @@
         <v>224</v>
       </c>
       <c r="E110" t="s">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="F110" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="G110" t="s">
         <v>257</v>
@@ -4584,10 +4584,10 @@
         <v>224</v>
       </c>
       <c r="E111" t="s">
-        <v>225</v>
+        <v>270</v>
       </c>
       <c r="F111" t="s">
-        <v>270</v>
+        <v>226</v>
       </c>
       <c r="G111" t="s">
         <v>271</v>
@@ -4607,10 +4607,10 @@
         <v>224</v>
       </c>
       <c r="E112" t="s">
-        <v>225</v>
+        <v>274</v>
       </c>
       <c r="F112" t="s">
-        <v>274</v>
+        <v>226</v>
       </c>
       <c r="G112" t="s">
         <v>275</v>
@@ -4630,10 +4630,10 @@
         <v>224</v>
       </c>
       <c r="E113" t="s">
-        <v>225</v>
+        <v>278</v>
       </c>
       <c r="F113" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="G113" t="s">
         <v>279</v>
@@ -4653,10 +4653,10 @@
         <v>224</v>
       </c>
       <c r="E114" t="s">
-        <v>225</v>
+        <v>278</v>
       </c>
       <c r="F114" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="G114" t="s">
         <v>279</v>
@@ -4676,10 +4676,10 @@
         <v>224</v>
       </c>
       <c r="E115" t="s">
-        <v>225</v>
+        <v>278</v>
       </c>
       <c r="F115" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="G115" t="s">
         <v>279</v>
@@ -4699,10 +4699,10 @@
         <v>224</v>
       </c>
       <c r="E116" t="s">
-        <v>225</v>
+        <v>278</v>
       </c>
       <c r="F116" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="G116" t="s">
         <v>279</v>
@@ -4722,10 +4722,10 @@
         <v>224</v>
       </c>
       <c r="E117" t="s">
-        <v>225</v>
+        <v>278</v>
       </c>
       <c r="F117" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="G117" t="s">
         <v>279</v>
@@ -4745,10 +4745,10 @@
         <v>224</v>
       </c>
       <c r="E118" t="s">
-        <v>225</v>
+        <v>278</v>
       </c>
       <c r="F118" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="G118" t="s">
         <v>279</v>
@@ -4768,10 +4768,10 @@
         <v>224</v>
       </c>
       <c r="E119" t="s">
-        <v>225</v>
+        <v>278</v>
       </c>
       <c r="F119" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="G119" t="s">
         <v>279</v>
@@ -4794,10 +4794,10 @@
         <v>295</v>
       </c>
       <c r="F120" t="s">
+        <v>295</v>
+      </c>
+      <c r="G120" t="s">
         <v>294</v>
-      </c>
-      <c r="G120" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4817,10 +4817,10 @@
         <v>295</v>
       </c>
       <c r="F121" t="s">
+        <v>295</v>
+      </c>
+      <c r="G121" t="s">
         <v>294</v>
-      </c>
-      <c r="G121" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4840,10 +4840,10 @@
         <v>295</v>
       </c>
       <c r="F122" t="s">
+        <v>295</v>
+      </c>
+      <c r="G122" t="s">
         <v>294</v>
-      </c>
-      <c r="G122" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4863,10 +4863,10 @@
         <v>295</v>
       </c>
       <c r="F123" t="s">
+        <v>295</v>
+      </c>
+      <c r="G123" t="s">
         <v>294</v>
-      </c>
-      <c r="G123" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4886,10 +4886,10 @@
         <v>295</v>
       </c>
       <c r="F124" t="s">
+        <v>295</v>
+      </c>
+      <c r="G124" t="s">
         <v>294</v>
-      </c>
-      <c r="G124" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4909,10 +4909,10 @@
         <v>295</v>
       </c>
       <c r="F125" t="s">
+        <v>295</v>
+      </c>
+      <c r="G125" t="s">
         <v>294</v>
-      </c>
-      <c r="G125" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4932,10 +4932,10 @@
         <v>309</v>
       </c>
       <c r="F126" t="s">
+        <v>309</v>
+      </c>
+      <c r="G126" t="s">
         <v>308</v>
-      </c>
-      <c r="G126" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4955,10 +4955,10 @@
         <v>309</v>
       </c>
       <c r="F127" t="s">
+        <v>309</v>
+      </c>
+      <c r="G127" t="s">
         <v>308</v>
-      </c>
-      <c r="G127" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4978,10 +4978,10 @@
         <v>309</v>
       </c>
       <c r="F128" t="s">
+        <v>309</v>
+      </c>
+      <c r="G128" t="s">
         <v>308</v>
-      </c>
-      <c r="G128" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -5001,10 +5001,10 @@
         <v>309</v>
       </c>
       <c r="F129" t="s">
+        <v>309</v>
+      </c>
+      <c r="G129" t="s">
         <v>308</v>
-      </c>
-      <c r="G129" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -5435,10 +5435,10 @@
         <v>318</v>
       </c>
       <c r="E148" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="F148" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
       <c r="G148" t="s">
         <v>359</v>
@@ -5458,10 +5458,10 @@
         <v>318</v>
       </c>
       <c r="E149" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="F149" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
       <c r="G149" t="s">
         <v>359</v>
@@ -5481,10 +5481,10 @@
         <v>318</v>
       </c>
       <c r="E150" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="F150" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
       <c r="G150" t="s">
         <v>359</v>
@@ -5504,10 +5504,10 @@
         <v>318</v>
       </c>
       <c r="E151" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="F151" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
       <c r="G151" t="s">
         <v>359</v>
@@ -5527,10 +5527,10 @@
         <v>318</v>
       </c>
       <c r="E152" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="F152" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
       <c r="G152" t="s">
         <v>359</v>
@@ -5550,10 +5550,10 @@
         <v>318</v>
       </c>
       <c r="E153" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="F153" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
       <c r="G153" t="s">
         <v>359</v>
@@ -5573,10 +5573,10 @@
         <v>318</v>
       </c>
       <c r="E154" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="F154" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
       <c r="G154" t="s">
         <v>373</v>
@@ -5596,10 +5596,10 @@
         <v>318</v>
       </c>
       <c r="E155" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="F155" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
       <c r="G155" t="s">
         <v>373</v>
@@ -5619,10 +5619,10 @@
         <v>318</v>
       </c>
       <c r="E156" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="F156" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
       <c r="G156" t="s">
         <v>373</v>
@@ -5642,10 +5642,10 @@
         <v>318</v>
       </c>
       <c r="E157" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="F157" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
       <c r="G157" t="s">
         <v>373</v>
@@ -5665,10 +5665,10 @@
         <v>318</v>
       </c>
       <c r="E158" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="F158" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
       <c r="G158" t="s">
         <v>373</v>
@@ -6125,10 +6125,10 @@
         <v>384</v>
       </c>
       <c r="E178" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="F178" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
       <c r="G178" t="s">
         <v>427</v>
@@ -6148,10 +6148,10 @@
         <v>384</v>
       </c>
       <c r="E179" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="F179" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
       <c r="G179" t="s">
         <v>427</v>
@@ -6171,10 +6171,10 @@
         <v>384</v>
       </c>
       <c r="E180" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="F180" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
       <c r="G180" t="s">
         <v>427</v>
@@ -6194,10 +6194,10 @@
         <v>384</v>
       </c>
       <c r="E181" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="F181" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
       <c r="G181" t="s">
         <v>427</v>
@@ -6217,10 +6217,10 @@
         <v>384</v>
       </c>
       <c r="E182" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="F182" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
       <c r="G182" t="s">
         <v>427</v>
@@ -6240,10 +6240,10 @@
         <v>384</v>
       </c>
       <c r="E183" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="F183" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
       <c r="G183" t="s">
         <v>427</v>
@@ -6263,10 +6263,10 @@
         <v>384</v>
       </c>
       <c r="E184" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="F184" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
       <c r="G184" t="s">
         <v>427</v>
@@ -6286,10 +6286,10 @@
         <v>384</v>
       </c>
       <c r="E185" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="F185" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
       <c r="G185" t="s">
         <v>427</v>
@@ -6309,10 +6309,10 @@
         <v>384</v>
       </c>
       <c r="E186" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="F186" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
       <c r="G186" t="s">
         <v>427</v>
@@ -6332,10 +6332,10 @@
         <v>384</v>
       </c>
       <c r="E187" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="F187" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
       <c r="G187" t="s">
         <v>427</v>
@@ -6355,10 +6355,10 @@
         <v>384</v>
       </c>
       <c r="E188" t="s">
-        <v>385</v>
+        <v>448</v>
       </c>
       <c r="F188" t="s">
-        <v>448</v>
+        <v>386</v>
       </c>
       <c r="G188" t="s">
         <v>449</v>
@@ -6381,10 +6381,10 @@
         <v>453</v>
       </c>
       <c r="F189" t="s">
+        <v>453</v>
+      </c>
+      <c r="G189" t="s">
         <v>452</v>
-      </c>
-      <c r="G189" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6404,10 +6404,10 @@
         <v>453</v>
       </c>
       <c r="F190" t="s">
+        <v>453</v>
+      </c>
+      <c r="G190" t="s">
         <v>452</v>
-      </c>
-      <c r="G190" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6427,10 +6427,10 @@
         <v>453</v>
       </c>
       <c r="F191" t="s">
+        <v>453</v>
+      </c>
+      <c r="G191" t="s">
         <v>452</v>
-      </c>
-      <c r="G191" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6450,10 +6450,10 @@
         <v>453</v>
       </c>
       <c r="F192" t="s">
+        <v>453</v>
+      </c>
+      <c r="G192" t="s">
         <v>452</v>
-      </c>
-      <c r="G192" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6473,10 +6473,10 @@
         <v>453</v>
       </c>
       <c r="F193" t="s">
+        <v>453</v>
+      </c>
+      <c r="G193" t="s">
         <v>452</v>
-      </c>
-      <c r="G193" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6496,10 +6496,10 @@
         <v>453</v>
       </c>
       <c r="F194" t="s">
+        <v>453</v>
+      </c>
+      <c r="G194" t="s">
         <v>452</v>
-      </c>
-      <c r="G194" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6519,10 +6519,10 @@
         <v>467</v>
       </c>
       <c r="F195" t="s">
+        <v>467</v>
+      </c>
+      <c r="G195" t="s">
         <v>466</v>
-      </c>
-      <c r="G195" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6542,10 +6542,10 @@
         <v>471</v>
       </c>
       <c r="F196" t="s">
+        <v>471</v>
+      </c>
+      <c r="G196" t="s">
         <v>470</v>
-      </c>
-      <c r="G196" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6565,10 +6565,10 @@
         <v>471</v>
       </c>
       <c r="F197" t="s">
+        <v>471</v>
+      </c>
+      <c r="G197" t="s">
         <v>470</v>
-      </c>
-      <c r="G197" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6588,10 +6588,10 @@
         <v>471</v>
       </c>
       <c r="F198" t="s">
+        <v>471</v>
+      </c>
+      <c r="G198" t="s">
         <v>470</v>
-      </c>
-      <c r="G198" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6611,10 +6611,10 @@
         <v>471</v>
       </c>
       <c r="F199" t="s">
+        <v>471</v>
+      </c>
+      <c r="G199" t="s">
         <v>470</v>
-      </c>
-      <c r="G199" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6634,10 +6634,10 @@
         <v>471</v>
       </c>
       <c r="F200" t="s">
+        <v>471</v>
+      </c>
+      <c r="G200" t="s">
         <v>470</v>
-      </c>
-      <c r="G200" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6657,10 +6657,10 @@
         <v>471</v>
       </c>
       <c r="F201" t="s">
+        <v>471</v>
+      </c>
+      <c r="G201" t="s">
         <v>470</v>
-      </c>
-      <c r="G201" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6680,10 +6680,10 @@
         <v>485</v>
       </c>
       <c r="F202" t="s">
+        <v>485</v>
+      </c>
+      <c r="G202" t="s">
         <v>484</v>
-      </c>
-      <c r="G202" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6703,10 +6703,10 @@
         <v>485</v>
       </c>
       <c r="F203" t="s">
+        <v>485</v>
+      </c>
+      <c r="G203" t="s">
         <v>484</v>
-      </c>
-      <c r="G203" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6726,10 +6726,10 @@
         <v>485</v>
       </c>
       <c r="F204" t="s">
+        <v>485</v>
+      </c>
+      <c r="G204" t="s">
         <v>484</v>
-      </c>
-      <c r="G204" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6749,10 +6749,10 @@
         <v>485</v>
       </c>
       <c r="F205" t="s">
+        <v>485</v>
+      </c>
+      <c r="G205" t="s">
         <v>484</v>
-      </c>
-      <c r="G205" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6772,10 +6772,10 @@
         <v>485</v>
       </c>
       <c r="F206" t="s">
+        <v>485</v>
+      </c>
+      <c r="G206" t="s">
         <v>484</v>
-      </c>
-      <c r="G206" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6795,10 +6795,10 @@
         <v>485</v>
       </c>
       <c r="F207" t="s">
+        <v>485</v>
+      </c>
+      <c r="G207" t="s">
         <v>484</v>
-      </c>
-      <c r="G207" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6818,10 +6818,10 @@
         <v>485</v>
       </c>
       <c r="F208" t="s">
+        <v>485</v>
+      </c>
+      <c r="G208" t="s">
         <v>484</v>
-      </c>
-      <c r="G208" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6841,10 +6841,10 @@
         <v>485</v>
       </c>
       <c r="F209" t="s">
+        <v>485</v>
+      </c>
+      <c r="G209" t="s">
         <v>484</v>
-      </c>
-      <c r="G209" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6864,10 +6864,10 @@
         <v>485</v>
       </c>
       <c r="F210" t="s">
+        <v>485</v>
+      </c>
+      <c r="G210" t="s">
         <v>484</v>
-      </c>
-      <c r="G210" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6887,10 +6887,10 @@
         <v>485</v>
       </c>
       <c r="F211" t="s">
+        <v>485</v>
+      </c>
+      <c r="G211" t="s">
         <v>484</v>
-      </c>
-      <c r="G211" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6910,10 +6910,10 @@
         <v>507</v>
       </c>
       <c r="F212" t="s">
+        <v>507</v>
+      </c>
+      <c r="G212" t="s">
         <v>506</v>
-      </c>
-      <c r="G212" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6933,10 +6933,10 @@
         <v>511</v>
       </c>
       <c r="F213" t="s">
+        <v>511</v>
+      </c>
+      <c r="G213" t="s">
         <v>510</v>
-      </c>
-      <c r="G213" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6956,10 +6956,10 @@
         <v>515</v>
       </c>
       <c r="F214" t="s">
+        <v>515</v>
+      </c>
+      <c r="G214" t="s">
         <v>514</v>
-      </c>
-      <c r="G214" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6979,10 +6979,10 @@
         <v>515</v>
       </c>
       <c r="F215" t="s">
+        <v>515</v>
+      </c>
+      <c r="G215" t="s">
         <v>514</v>
-      </c>
-      <c r="G215" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -7002,10 +7002,10 @@
         <v>521</v>
       </c>
       <c r="F216" t="s">
+        <v>521</v>
+      </c>
+      <c r="G216" t="s">
         <v>520</v>
-      </c>
-      <c r="G216" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -7025,10 +7025,10 @@
         <v>521</v>
       </c>
       <c r="F217" t="s">
+        <v>521</v>
+      </c>
+      <c r="G217" t="s">
         <v>520</v>
-      </c>
-      <c r="G217" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -7048,10 +7048,10 @@
         <v>521</v>
       </c>
       <c r="F218" t="s">
+        <v>521</v>
+      </c>
+      <c r="G218" t="s">
         <v>520</v>
-      </c>
-      <c r="G218" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -7071,10 +7071,10 @@
         <v>521</v>
       </c>
       <c r="F219" t="s">
+        <v>521</v>
+      </c>
+      <c r="G219" t="s">
         <v>520</v>
-      </c>
-      <c r="G219" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -7094,10 +7094,10 @@
         <v>521</v>
       </c>
       <c r="F220" t="s">
+        <v>521</v>
+      </c>
+      <c r="G220" t="s">
         <v>520</v>
-      </c>
-      <c r="G220" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -7117,10 +7117,10 @@
         <v>521</v>
       </c>
       <c r="F221" t="s">
+        <v>521</v>
+      </c>
+      <c r="G221" t="s">
         <v>520</v>
-      </c>
-      <c r="G221" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -7140,10 +7140,10 @@
         <v>521</v>
       </c>
       <c r="F222" t="s">
+        <v>521</v>
+      </c>
+      <c r="G222" t="s">
         <v>520</v>
-      </c>
-      <c r="G222" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -7163,10 +7163,10 @@
         <v>537</v>
       </c>
       <c r="F223" t="s">
+        <v>537</v>
+      </c>
+      <c r="G223" t="s">
         <v>536</v>
-      </c>
-      <c r="G223" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -7186,10 +7186,10 @@
         <v>537</v>
       </c>
       <c r="F224" t="s">
+        <v>537</v>
+      </c>
+      <c r="G224" t="s">
         <v>536</v>
-      </c>
-      <c r="G224" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -7209,10 +7209,10 @@
         <v>537</v>
       </c>
       <c r="F225" t="s">
+        <v>537</v>
+      </c>
+      <c r="G225" t="s">
         <v>536</v>
-      </c>
-      <c r="G225" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -7232,10 +7232,10 @@
         <v>545</v>
       </c>
       <c r="F226" t="s">
+        <v>545</v>
+      </c>
+      <c r="G226" t="s">
         <v>544</v>
-      </c>
-      <c r="G226" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -7255,10 +7255,10 @@
         <v>549</v>
       </c>
       <c r="F227" t="s">
+        <v>549</v>
+      </c>
+      <c r="G227" t="s">
         <v>548</v>
-      </c>
-      <c r="G227" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -7278,10 +7278,10 @@
         <v>553</v>
       </c>
       <c r="F228" t="s">
+        <v>553</v>
+      </c>
+      <c r="G228" t="s">
         <v>552</v>
-      </c>
-      <c r="G228" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -7301,10 +7301,10 @@
         <v>557</v>
       </c>
       <c r="F229" t="s">
+        <v>557</v>
+      </c>
+      <c r="G229" t="s">
         <v>556</v>
-      </c>
-      <c r="G229" t="s">
-        <v>557</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -7324,10 +7324,10 @@
         <v>561</v>
       </c>
       <c r="F230" t="s">
+        <v>561</v>
+      </c>
+      <c r="G230" t="s">
         <v>560</v>
-      </c>
-      <c r="G230" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -7347,10 +7347,10 @@
         <v>561</v>
       </c>
       <c r="F231" t="s">
+        <v>561</v>
+      </c>
+      <c r="G231" t="s">
         <v>560</v>
-      </c>
-      <c r="G231" t="s">
-        <v>561</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/en/SectorGroup.xlsx
+++ b/api/xlsx/en/SectorGroup.xlsx
@@ -31,12 +31,12 @@
     <t>codeforiati:category-name</t>
   </si>
   <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
     <t>codeforiati:group-name</t>
   </si>
   <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -52,12 +52,12 @@
     <t>Education, Level Unspecified</t>
   </si>
   <si>
+    <t>111</t>
+  </si>
+  <si>
     <t>Education</t>
   </si>
   <si>
-    <t>111</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -154,12 +154,12 @@
     <t>Health, General</t>
   </si>
   <si>
+    <t>121</t>
+  </si>
+  <si>
     <t>Health</t>
   </si>
   <si>
-    <t>121</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -394,12 +394,12 @@
     <t>Government &amp; Civil Society-general</t>
   </si>
   <si>
+    <t>151</t>
+  </si>
+  <si>
     <t>Government &amp; Civil Society</t>
   </si>
   <si>
-    <t>151</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -694,12 +694,12 @@
     <t>Energy Policy</t>
   </si>
   <si>
+    <t>231</t>
+  </si>
+  <si>
     <t>Energy</t>
   </si>
   <si>
-    <t>231</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -976,12 +976,12 @@
     <t>Agriculture</t>
   </si>
   <si>
+    <t>311</t>
+  </si>
+  <si>
     <t>Agriculture, Forestry, Fishing</t>
   </si>
   <si>
-    <t>311</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1174,10 +1174,10 @@
     <t>Industry</t>
   </si>
   <si>
+    <t>321</t>
+  </si>
+  <si>
     <t>Industry, Mining, Construction</t>
-  </si>
-  <si>
-    <t>321</t>
   </si>
   <si>
     <t>32120</t>
@@ -2172,10 +2172,10 @@
         <v>22</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2195,10 +2195,10 @@
         <v>22</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G7" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2218,10 +2218,10 @@
         <v>22</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G8" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2241,10 +2241,10 @@
         <v>22</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G9" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2264,10 +2264,10 @@
         <v>32</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="G10" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2287,10 +2287,10 @@
         <v>32</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="G11" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2310,10 +2310,10 @@
         <v>38</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="G12" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2333,10 +2333,10 @@
         <v>38</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="G13" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2448,10 +2448,10 @@
         <v>56</v>
       </c>
       <c r="F18" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G18" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2471,10 +2471,10 @@
         <v>56</v>
       </c>
       <c r="F19" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G19" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2494,10 +2494,10 @@
         <v>56</v>
       </c>
       <c r="F20" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G20" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2517,10 +2517,10 @@
         <v>56</v>
       </c>
       <c r="F21" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G21" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2540,10 +2540,10 @@
         <v>56</v>
       </c>
       <c r="F22" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G22" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2563,10 +2563,10 @@
         <v>56</v>
       </c>
       <c r="F23" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G23" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2586,10 +2586,10 @@
         <v>56</v>
       </c>
       <c r="F24" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G24" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2609,10 +2609,10 @@
         <v>56</v>
       </c>
       <c r="F25" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G25" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2632,10 +2632,10 @@
         <v>74</v>
       </c>
       <c r="F26" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G26" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2655,10 +2655,10 @@
         <v>74</v>
       </c>
       <c r="F27" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G27" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2678,10 +2678,10 @@
         <v>74</v>
       </c>
       <c r="F28" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G28" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2701,10 +2701,10 @@
         <v>74</v>
       </c>
       <c r="F29" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G29" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2724,10 +2724,10 @@
         <v>74</v>
       </c>
       <c r="F30" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G30" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2747,10 +2747,10 @@
         <v>74</v>
       </c>
       <c r="F31" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G31" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2770,10 +2770,10 @@
         <v>89</v>
       </c>
       <c r="F32" t="s">
+        <v>88</v>
+      </c>
+      <c r="G32" t="s">
         <v>89</v>
-      </c>
-      <c r="G32" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2793,10 +2793,10 @@
         <v>89</v>
       </c>
       <c r="F33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G33" t="s">
         <v>89</v>
-      </c>
-      <c r="G33" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2816,10 +2816,10 @@
         <v>89</v>
       </c>
       <c r="F34" t="s">
+        <v>88</v>
+      </c>
+      <c r="G34" t="s">
         <v>89</v>
-      </c>
-      <c r="G34" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2839,10 +2839,10 @@
         <v>89</v>
       </c>
       <c r="F35" t="s">
+        <v>88</v>
+      </c>
+      <c r="G35" t="s">
         <v>89</v>
-      </c>
-      <c r="G35" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2862,10 +2862,10 @@
         <v>89</v>
       </c>
       <c r="F36" t="s">
+        <v>88</v>
+      </c>
+      <c r="G36" t="s">
         <v>89</v>
-      </c>
-      <c r="G36" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2885,10 +2885,10 @@
         <v>101</v>
       </c>
       <c r="F37" t="s">
+        <v>100</v>
+      </c>
+      <c r="G37" t="s">
         <v>101</v>
-      </c>
-      <c r="G37" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2908,10 +2908,10 @@
         <v>101</v>
       </c>
       <c r="F38" t="s">
+        <v>100</v>
+      </c>
+      <c r="G38" t="s">
         <v>101</v>
-      </c>
-      <c r="G38" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2931,10 +2931,10 @@
         <v>101</v>
       </c>
       <c r="F39" t="s">
+        <v>100</v>
+      </c>
+      <c r="G39" t="s">
         <v>101</v>
-      </c>
-      <c r="G39" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2954,10 +2954,10 @@
         <v>101</v>
       </c>
       <c r="F40" t="s">
+        <v>100</v>
+      </c>
+      <c r="G40" t="s">
         <v>101</v>
-      </c>
-      <c r="G40" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2977,10 +2977,10 @@
         <v>101</v>
       </c>
       <c r="F41" t="s">
+        <v>100</v>
+      </c>
+      <c r="G41" t="s">
         <v>101</v>
-      </c>
-      <c r="G41" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -3000,10 +3000,10 @@
         <v>101</v>
       </c>
       <c r="F42" t="s">
+        <v>100</v>
+      </c>
+      <c r="G42" t="s">
         <v>101</v>
-      </c>
-      <c r="G42" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3023,10 +3023,10 @@
         <v>101</v>
       </c>
       <c r="F43" t="s">
+        <v>100</v>
+      </c>
+      <c r="G43" t="s">
         <v>101</v>
-      </c>
-      <c r="G43" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3046,10 +3046,10 @@
         <v>101</v>
       </c>
       <c r="F44" t="s">
+        <v>100</v>
+      </c>
+      <c r="G44" t="s">
         <v>101</v>
-      </c>
-      <c r="G44" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3069,10 +3069,10 @@
         <v>101</v>
       </c>
       <c r="F45" t="s">
+        <v>100</v>
+      </c>
+      <c r="G45" t="s">
         <v>101</v>
-      </c>
-      <c r="G45" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3092,10 +3092,10 @@
         <v>101</v>
       </c>
       <c r="F46" t="s">
+        <v>100</v>
+      </c>
+      <c r="G46" t="s">
         <v>101</v>
-      </c>
-      <c r="G46" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3115,10 +3115,10 @@
         <v>101</v>
       </c>
       <c r="F47" t="s">
+        <v>100</v>
+      </c>
+      <c r="G47" t="s">
         <v>101</v>
-      </c>
-      <c r="G47" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3506,10 +3506,10 @@
         <v>160</v>
       </c>
       <c r="F64" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G64" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3529,10 +3529,10 @@
         <v>160</v>
       </c>
       <c r="F65" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G65" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3552,10 +3552,10 @@
         <v>160</v>
       </c>
       <c r="F66" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G66" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3575,10 +3575,10 @@
         <v>160</v>
       </c>
       <c r="F67" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G67" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3598,10 +3598,10 @@
         <v>160</v>
       </c>
       <c r="F68" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G68" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3621,10 +3621,10 @@
         <v>160</v>
       </c>
       <c r="F69" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G69" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3644,10 +3644,10 @@
         <v>175</v>
       </c>
       <c r="F70" t="s">
+        <v>174</v>
+      </c>
+      <c r="G70" t="s">
         <v>175</v>
-      </c>
-      <c r="G70" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3667,10 +3667,10 @@
         <v>175</v>
       </c>
       <c r="F71" t="s">
+        <v>174</v>
+      </c>
+      <c r="G71" t="s">
         <v>175</v>
-      </c>
-      <c r="G71" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3690,10 +3690,10 @@
         <v>175</v>
       </c>
       <c r="F72" t="s">
+        <v>174</v>
+      </c>
+      <c r="G72" t="s">
         <v>175</v>
-      </c>
-      <c r="G72" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3713,10 +3713,10 @@
         <v>175</v>
       </c>
       <c r="F73" t="s">
+        <v>174</v>
+      </c>
+      <c r="G73" t="s">
         <v>175</v>
-      </c>
-      <c r="G73" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3736,10 +3736,10 @@
         <v>175</v>
       </c>
       <c r="F74" t="s">
+        <v>174</v>
+      </c>
+      <c r="G74" t="s">
         <v>175</v>
-      </c>
-      <c r="G74" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3759,10 +3759,10 @@
         <v>175</v>
       </c>
       <c r="F75" t="s">
+        <v>174</v>
+      </c>
+      <c r="G75" t="s">
         <v>175</v>
-      </c>
-      <c r="G75" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3782,10 +3782,10 @@
         <v>175</v>
       </c>
       <c r="F76" t="s">
+        <v>174</v>
+      </c>
+      <c r="G76" t="s">
         <v>175</v>
-      </c>
-      <c r="G76" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3805,10 +3805,10 @@
         <v>175</v>
       </c>
       <c r="F77" t="s">
+        <v>174</v>
+      </c>
+      <c r="G77" t="s">
         <v>175</v>
-      </c>
-      <c r="G77" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3828,10 +3828,10 @@
         <v>175</v>
       </c>
       <c r="F78" t="s">
+        <v>174</v>
+      </c>
+      <c r="G78" t="s">
         <v>175</v>
-      </c>
-      <c r="G78" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3851,10 +3851,10 @@
         <v>175</v>
       </c>
       <c r="F79" t="s">
+        <v>174</v>
+      </c>
+      <c r="G79" t="s">
         <v>175</v>
-      </c>
-      <c r="G79" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3874,10 +3874,10 @@
         <v>175</v>
       </c>
       <c r="F80" t="s">
+        <v>174</v>
+      </c>
+      <c r="G80" t="s">
         <v>175</v>
-      </c>
-      <c r="G80" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3897,10 +3897,10 @@
         <v>199</v>
       </c>
       <c r="F81" t="s">
+        <v>198</v>
+      </c>
+      <c r="G81" t="s">
         <v>199</v>
-      </c>
-      <c r="G81" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3920,10 +3920,10 @@
         <v>199</v>
       </c>
       <c r="F82" t="s">
+        <v>198</v>
+      </c>
+      <c r="G82" t="s">
         <v>199</v>
-      </c>
-      <c r="G82" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3943,10 +3943,10 @@
         <v>199</v>
       </c>
       <c r="F83" t="s">
+        <v>198</v>
+      </c>
+      <c r="G83" t="s">
         <v>199</v>
-      </c>
-      <c r="G83" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3966,10 +3966,10 @@
         <v>199</v>
       </c>
       <c r="F84" t="s">
+        <v>198</v>
+      </c>
+      <c r="G84" t="s">
         <v>199</v>
-      </c>
-      <c r="G84" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3989,10 +3989,10 @@
         <v>199</v>
       </c>
       <c r="F85" t="s">
+        <v>198</v>
+      </c>
+      <c r="G85" t="s">
         <v>199</v>
-      </c>
-      <c r="G85" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4012,10 +4012,10 @@
         <v>199</v>
       </c>
       <c r="F86" t="s">
+        <v>198</v>
+      </c>
+      <c r="G86" t="s">
         <v>199</v>
-      </c>
-      <c r="G86" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4035,10 +4035,10 @@
         <v>199</v>
       </c>
       <c r="F87" t="s">
+        <v>198</v>
+      </c>
+      <c r="G87" t="s">
         <v>199</v>
-      </c>
-      <c r="G87" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4058,10 +4058,10 @@
         <v>215</v>
       </c>
       <c r="F88" t="s">
+        <v>214</v>
+      </c>
+      <c r="G88" t="s">
         <v>215</v>
-      </c>
-      <c r="G88" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4081,10 +4081,10 @@
         <v>215</v>
       </c>
       <c r="F89" t="s">
+        <v>214</v>
+      </c>
+      <c r="G89" t="s">
         <v>215</v>
-      </c>
-      <c r="G89" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4104,10 +4104,10 @@
         <v>215</v>
       </c>
       <c r="F90" t="s">
+        <v>214</v>
+      </c>
+      <c r="G90" t="s">
         <v>215</v>
-      </c>
-      <c r="G90" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4127,10 +4127,10 @@
         <v>215</v>
       </c>
       <c r="F91" t="s">
+        <v>214</v>
+      </c>
+      <c r="G91" t="s">
         <v>215</v>
-      </c>
-      <c r="G91" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4242,10 +4242,10 @@
         <v>236</v>
       </c>
       <c r="F96" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G96" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -4265,10 +4265,10 @@
         <v>236</v>
       </c>
       <c r="F97" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G97" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4288,10 +4288,10 @@
         <v>236</v>
       </c>
       <c r="F98" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G98" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4311,10 +4311,10 @@
         <v>236</v>
       </c>
       <c r="F99" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G99" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4334,10 +4334,10 @@
         <v>236</v>
       </c>
       <c r="F100" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G100" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4357,10 +4357,10 @@
         <v>236</v>
       </c>
       <c r="F101" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G101" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4380,10 +4380,10 @@
         <v>236</v>
       </c>
       <c r="F102" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G102" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4403,10 +4403,10 @@
         <v>236</v>
       </c>
       <c r="F103" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G103" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4426,10 +4426,10 @@
         <v>236</v>
       </c>
       <c r="F104" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G104" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4449,10 +4449,10 @@
         <v>256</v>
       </c>
       <c r="F105" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G105" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4472,10 +4472,10 @@
         <v>256</v>
       </c>
       <c r="F106" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G106" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4495,10 +4495,10 @@
         <v>256</v>
       </c>
       <c r="F107" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G107" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4518,10 +4518,10 @@
         <v>256</v>
       </c>
       <c r="F108" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G108" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4541,10 +4541,10 @@
         <v>256</v>
       </c>
       <c r="F109" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G109" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4564,10 +4564,10 @@
         <v>256</v>
       </c>
       <c r="F110" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G110" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4587,10 +4587,10 @@
         <v>270</v>
       </c>
       <c r="F111" t="s">
-        <v>226</v>
+        <v>271</v>
       </c>
       <c r="G111" t="s">
-        <v>271</v>
+        <v>227</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4610,10 +4610,10 @@
         <v>274</v>
       </c>
       <c r="F112" t="s">
-        <v>226</v>
+        <v>275</v>
       </c>
       <c r="G112" t="s">
-        <v>275</v>
+        <v>227</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4633,10 +4633,10 @@
         <v>278</v>
       </c>
       <c r="F113" t="s">
-        <v>226</v>
+        <v>279</v>
       </c>
       <c r="G113" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4656,10 +4656,10 @@
         <v>278</v>
       </c>
       <c r="F114" t="s">
-        <v>226</v>
+        <v>279</v>
       </c>
       <c r="G114" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4679,10 +4679,10 @@
         <v>278</v>
       </c>
       <c r="F115" t="s">
-        <v>226</v>
+        <v>279</v>
       </c>
       <c r="G115" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4702,10 +4702,10 @@
         <v>278</v>
       </c>
       <c r="F116" t="s">
-        <v>226</v>
+        <v>279</v>
       </c>
       <c r="G116" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4725,10 +4725,10 @@
         <v>278</v>
       </c>
       <c r="F117" t="s">
-        <v>226</v>
+        <v>279</v>
       </c>
       <c r="G117" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4748,10 +4748,10 @@
         <v>278</v>
       </c>
       <c r="F118" t="s">
-        <v>226</v>
+        <v>279</v>
       </c>
       <c r="G118" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4771,10 +4771,10 @@
         <v>278</v>
       </c>
       <c r="F119" t="s">
-        <v>226</v>
+        <v>279</v>
       </c>
       <c r="G119" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4794,10 +4794,10 @@
         <v>295</v>
       </c>
       <c r="F120" t="s">
+        <v>294</v>
+      </c>
+      <c r="G120" t="s">
         <v>295</v>
-      </c>
-      <c r="G120" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4817,10 +4817,10 @@
         <v>295</v>
       </c>
       <c r="F121" t="s">
+        <v>294</v>
+      </c>
+      <c r="G121" t="s">
         <v>295</v>
-      </c>
-      <c r="G121" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4840,10 +4840,10 @@
         <v>295</v>
       </c>
       <c r="F122" t="s">
+        <v>294</v>
+      </c>
+      <c r="G122" t="s">
         <v>295</v>
-      </c>
-      <c r="G122" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4863,10 +4863,10 @@
         <v>295</v>
       </c>
       <c r="F123" t="s">
+        <v>294</v>
+      </c>
+      <c r="G123" t="s">
         <v>295</v>
-      </c>
-      <c r="G123" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4886,10 +4886,10 @@
         <v>295</v>
       </c>
       <c r="F124" t="s">
+        <v>294</v>
+      </c>
+      <c r="G124" t="s">
         <v>295</v>
-      </c>
-      <c r="G124" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4909,10 +4909,10 @@
         <v>295</v>
       </c>
       <c r="F125" t="s">
+        <v>294</v>
+      </c>
+      <c r="G125" t="s">
         <v>295</v>
-      </c>
-      <c r="G125" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4932,10 +4932,10 @@
         <v>309</v>
       </c>
       <c r="F126" t="s">
+        <v>308</v>
+      </c>
+      <c r="G126" t="s">
         <v>309</v>
-      </c>
-      <c r="G126" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4955,10 +4955,10 @@
         <v>309</v>
       </c>
       <c r="F127" t="s">
+        <v>308</v>
+      </c>
+      <c r="G127" t="s">
         <v>309</v>
-      </c>
-      <c r="G127" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4978,10 +4978,10 @@
         <v>309</v>
       </c>
       <c r="F128" t="s">
+        <v>308</v>
+      </c>
+      <c r="G128" t="s">
         <v>309</v>
-      </c>
-      <c r="G128" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -5001,10 +5001,10 @@
         <v>309</v>
       </c>
       <c r="F129" t="s">
+        <v>308</v>
+      </c>
+      <c r="G129" t="s">
         <v>309</v>
-      </c>
-      <c r="G129" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -5438,10 +5438,10 @@
         <v>358</v>
       </c>
       <c r="F148" t="s">
-        <v>320</v>
+        <v>359</v>
       </c>
       <c r="G148" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5461,10 +5461,10 @@
         <v>358</v>
       </c>
       <c r="F149" t="s">
-        <v>320</v>
+        <v>359</v>
       </c>
       <c r="G149" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5484,10 +5484,10 @@
         <v>358</v>
       </c>
       <c r="F150" t="s">
-        <v>320</v>
+        <v>359</v>
       </c>
       <c r="G150" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5507,10 +5507,10 @@
         <v>358</v>
       </c>
       <c r="F151" t="s">
-        <v>320</v>
+        <v>359</v>
       </c>
       <c r="G151" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5530,10 +5530,10 @@
         <v>358</v>
       </c>
       <c r="F152" t="s">
-        <v>320</v>
+        <v>359</v>
       </c>
       <c r="G152" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5553,10 +5553,10 @@
         <v>358</v>
       </c>
       <c r="F153" t="s">
-        <v>320</v>
+        <v>359</v>
       </c>
       <c r="G153" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5576,10 +5576,10 @@
         <v>372</v>
       </c>
       <c r="F154" t="s">
-        <v>320</v>
+        <v>373</v>
       </c>
       <c r="G154" t="s">
-        <v>373</v>
+        <v>321</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5599,10 +5599,10 @@
         <v>372</v>
       </c>
       <c r="F155" t="s">
-        <v>320</v>
+        <v>373</v>
       </c>
       <c r="G155" t="s">
-        <v>373</v>
+        <v>321</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5622,10 +5622,10 @@
         <v>372</v>
       </c>
       <c r="F156" t="s">
-        <v>320</v>
+        <v>373</v>
       </c>
       <c r="G156" t="s">
-        <v>373</v>
+        <v>321</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5645,10 +5645,10 @@
         <v>372</v>
       </c>
       <c r="F157" t="s">
-        <v>320</v>
+        <v>373</v>
       </c>
       <c r="G157" t="s">
-        <v>373</v>
+        <v>321</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5668,10 +5668,10 @@
         <v>372</v>
       </c>
       <c r="F158" t="s">
-        <v>320</v>
+        <v>373</v>
       </c>
       <c r="G158" t="s">
-        <v>373</v>
+        <v>321</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -6128,10 +6128,10 @@
         <v>426</v>
       </c>
       <c r="F178" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G178" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -6151,10 +6151,10 @@
         <v>426</v>
       </c>
       <c r="F179" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G179" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -6174,10 +6174,10 @@
         <v>426</v>
       </c>
       <c r="F180" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G180" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -6197,10 +6197,10 @@
         <v>426</v>
       </c>
       <c r="F181" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G181" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -6220,10 +6220,10 @@
         <v>426</v>
       </c>
       <c r="F182" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G182" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -6243,10 +6243,10 @@
         <v>426</v>
       </c>
       <c r="F183" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G183" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -6266,10 +6266,10 @@
         <v>426</v>
       </c>
       <c r="F184" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G184" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -6289,10 +6289,10 @@
         <v>426</v>
       </c>
       <c r="F185" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G185" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -6312,10 +6312,10 @@
         <v>426</v>
       </c>
       <c r="F186" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G186" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -6335,10 +6335,10 @@
         <v>426</v>
       </c>
       <c r="F187" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G187" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -6358,10 +6358,10 @@
         <v>448</v>
       </c>
       <c r="F188" t="s">
-        <v>386</v>
+        <v>449</v>
       </c>
       <c r="G188" t="s">
-        <v>449</v>
+        <v>387</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -6381,10 +6381,10 @@
         <v>453</v>
       </c>
       <c r="F189" t="s">
+        <v>452</v>
+      </c>
+      <c r="G189" t="s">
         <v>453</v>
-      </c>
-      <c r="G189" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6404,10 +6404,10 @@
         <v>453</v>
       </c>
       <c r="F190" t="s">
+        <v>452</v>
+      </c>
+      <c r="G190" t="s">
         <v>453</v>
-      </c>
-      <c r="G190" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6427,10 +6427,10 @@
         <v>453</v>
       </c>
       <c r="F191" t="s">
+        <v>452</v>
+      </c>
+      <c r="G191" t="s">
         <v>453</v>
-      </c>
-      <c r="G191" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6450,10 +6450,10 @@
         <v>453</v>
       </c>
       <c r="F192" t="s">
+        <v>452</v>
+      </c>
+      <c r="G192" t="s">
         <v>453</v>
-      </c>
-      <c r="G192" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6473,10 +6473,10 @@
         <v>453</v>
       </c>
       <c r="F193" t="s">
+        <v>452</v>
+      </c>
+      <c r="G193" t="s">
         <v>453</v>
-      </c>
-      <c r="G193" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6496,10 +6496,10 @@
         <v>453</v>
       </c>
       <c r="F194" t="s">
+        <v>452</v>
+      </c>
+      <c r="G194" t="s">
         <v>453</v>
-      </c>
-      <c r="G194" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6519,10 +6519,10 @@
         <v>467</v>
       </c>
       <c r="F195" t="s">
+        <v>466</v>
+      </c>
+      <c r="G195" t="s">
         <v>467</v>
-      </c>
-      <c r="G195" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6542,10 +6542,10 @@
         <v>471</v>
       </c>
       <c r="F196" t="s">
+        <v>470</v>
+      </c>
+      <c r="G196" t="s">
         <v>471</v>
-      </c>
-      <c r="G196" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6565,10 +6565,10 @@
         <v>471</v>
       </c>
       <c r="F197" t="s">
+        <v>470</v>
+      </c>
+      <c r="G197" t="s">
         <v>471</v>
-      </c>
-      <c r="G197" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6588,10 +6588,10 @@
         <v>471</v>
       </c>
       <c r="F198" t="s">
+        <v>470</v>
+      </c>
+      <c r="G198" t="s">
         <v>471</v>
-      </c>
-      <c r="G198" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6611,10 +6611,10 @@
         <v>471</v>
       </c>
       <c r="F199" t="s">
+        <v>470</v>
+      </c>
+      <c r="G199" t="s">
         <v>471</v>
-      </c>
-      <c r="G199" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6634,10 +6634,10 @@
         <v>471</v>
       </c>
       <c r="F200" t="s">
+        <v>470</v>
+      </c>
+      <c r="G200" t="s">
         <v>471</v>
-      </c>
-      <c r="G200" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6657,10 +6657,10 @@
         <v>471</v>
       </c>
       <c r="F201" t="s">
+        <v>470</v>
+      </c>
+      <c r="G201" t="s">
         <v>471</v>
-      </c>
-      <c r="G201" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6680,10 +6680,10 @@
         <v>485</v>
       </c>
       <c r="F202" t="s">
+        <v>484</v>
+      </c>
+      <c r="G202" t="s">
         <v>485</v>
-      </c>
-      <c r="G202" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6703,10 +6703,10 @@
         <v>485</v>
       </c>
       <c r="F203" t="s">
+        <v>484</v>
+      </c>
+      <c r="G203" t="s">
         <v>485</v>
-      </c>
-      <c r="G203" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6726,10 +6726,10 @@
         <v>485</v>
       </c>
       <c r="F204" t="s">
+        <v>484</v>
+      </c>
+      <c r="G204" t="s">
         <v>485</v>
-      </c>
-      <c r="G204" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6749,10 +6749,10 @@
         <v>485</v>
       </c>
       <c r="F205" t="s">
+        <v>484</v>
+      </c>
+      <c r="G205" t="s">
         <v>485</v>
-      </c>
-      <c r="G205" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6772,10 +6772,10 @@
         <v>485</v>
       </c>
       <c r="F206" t="s">
+        <v>484</v>
+      </c>
+      <c r="G206" t="s">
         <v>485</v>
-      </c>
-      <c r="G206" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6795,10 +6795,10 @@
         <v>485</v>
       </c>
       <c r="F207" t="s">
+        <v>484</v>
+      </c>
+      <c r="G207" t="s">
         <v>485</v>
-      </c>
-      <c r="G207" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6818,10 +6818,10 @@
         <v>485</v>
       </c>
       <c r="F208" t="s">
+        <v>484</v>
+      </c>
+      <c r="G208" t="s">
         <v>485</v>
-      </c>
-      <c r="G208" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6841,10 +6841,10 @@
         <v>485</v>
       </c>
       <c r="F209" t="s">
+        <v>484</v>
+      </c>
+      <c r="G209" t="s">
         <v>485</v>
-      </c>
-      <c r="G209" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6864,10 +6864,10 @@
         <v>485</v>
       </c>
       <c r="F210" t="s">
+        <v>484</v>
+      </c>
+      <c r="G210" t="s">
         <v>485</v>
-      </c>
-      <c r="G210" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6887,10 +6887,10 @@
         <v>485</v>
       </c>
       <c r="F211" t="s">
+        <v>484</v>
+      </c>
+      <c r="G211" t="s">
         <v>485</v>
-      </c>
-      <c r="G211" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6910,10 +6910,10 @@
         <v>507</v>
       </c>
       <c r="F212" t="s">
+        <v>506</v>
+      </c>
+      <c r="G212" t="s">
         <v>507</v>
-      </c>
-      <c r="G212" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6933,10 +6933,10 @@
         <v>511</v>
       </c>
       <c r="F213" t="s">
+        <v>510</v>
+      </c>
+      <c r="G213" t="s">
         <v>511</v>
-      </c>
-      <c r="G213" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6956,10 +6956,10 @@
         <v>515</v>
       </c>
       <c r="F214" t="s">
+        <v>514</v>
+      </c>
+      <c r="G214" t="s">
         <v>515</v>
-      </c>
-      <c r="G214" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6979,10 +6979,10 @@
         <v>515</v>
       </c>
       <c r="F215" t="s">
+        <v>514</v>
+      </c>
+      <c r="G215" t="s">
         <v>515</v>
-      </c>
-      <c r="G215" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -7002,10 +7002,10 @@
         <v>521</v>
       </c>
       <c r="F216" t="s">
+        <v>520</v>
+      </c>
+      <c r="G216" t="s">
         <v>521</v>
-      </c>
-      <c r="G216" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -7025,10 +7025,10 @@
         <v>521</v>
       </c>
       <c r="F217" t="s">
+        <v>520</v>
+      </c>
+      <c r="G217" t="s">
         <v>521</v>
-      </c>
-      <c r="G217" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -7048,10 +7048,10 @@
         <v>521</v>
       </c>
       <c r="F218" t="s">
+        <v>520</v>
+      </c>
+      <c r="G218" t="s">
         <v>521</v>
-      </c>
-      <c r="G218" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -7071,10 +7071,10 @@
         <v>521</v>
       </c>
       <c r="F219" t="s">
+        <v>520</v>
+      </c>
+      <c r="G219" t="s">
         <v>521</v>
-      </c>
-      <c r="G219" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -7094,10 +7094,10 @@
         <v>521</v>
       </c>
       <c r="F220" t="s">
+        <v>520</v>
+      </c>
+      <c r="G220" t="s">
         <v>521</v>
-      </c>
-      <c r="G220" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -7117,10 +7117,10 @@
         <v>521</v>
       </c>
       <c r="F221" t="s">
+        <v>520</v>
+      </c>
+      <c r="G221" t="s">
         <v>521</v>
-      </c>
-      <c r="G221" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -7140,10 +7140,10 @@
         <v>521</v>
       </c>
       <c r="F222" t="s">
+        <v>520</v>
+      </c>
+      <c r="G222" t="s">
         <v>521</v>
-      </c>
-      <c r="G222" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -7163,10 +7163,10 @@
         <v>537</v>
       </c>
       <c r="F223" t="s">
+        <v>536</v>
+      </c>
+      <c r="G223" t="s">
         <v>537</v>
-      </c>
-      <c r="G223" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -7186,10 +7186,10 @@
         <v>537</v>
       </c>
       <c r="F224" t="s">
+        <v>536</v>
+      </c>
+      <c r="G224" t="s">
         <v>537</v>
-      </c>
-      <c r="G224" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -7209,10 +7209,10 @@
         <v>537</v>
       </c>
       <c r="F225" t="s">
+        <v>536</v>
+      </c>
+      <c r="G225" t="s">
         <v>537</v>
-      </c>
-      <c r="G225" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -7232,10 +7232,10 @@
         <v>545</v>
       </c>
       <c r="F226" t="s">
+        <v>544</v>
+      </c>
+      <c r="G226" t="s">
         <v>545</v>
-      </c>
-      <c r="G226" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -7255,10 +7255,10 @@
         <v>549</v>
       </c>
       <c r="F227" t="s">
+        <v>548</v>
+      </c>
+      <c r="G227" t="s">
         <v>549</v>
-      </c>
-      <c r="G227" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -7278,10 +7278,10 @@
         <v>553</v>
       </c>
       <c r="F228" t="s">
+        <v>552</v>
+      </c>
+      <c r="G228" t="s">
         <v>553</v>
-      </c>
-      <c r="G228" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -7301,10 +7301,10 @@
         <v>557</v>
       </c>
       <c r="F229" t="s">
+        <v>556</v>
+      </c>
+      <c r="G229" t="s">
         <v>557</v>
-      </c>
-      <c r="G229" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -7324,10 +7324,10 @@
         <v>561</v>
       </c>
       <c r="F230" t="s">
+        <v>560</v>
+      </c>
+      <c r="G230" t="s">
         <v>561</v>
-      </c>
-      <c r="G230" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -7347,10 +7347,10 @@
         <v>561</v>
       </c>
       <c r="F231" t="s">
+        <v>560</v>
+      </c>
+      <c r="G231" t="s">
         <v>561</v>
-      </c>
-      <c r="G231" t="s">
-        <v>560</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/en/SectorGroup.xlsx
+++ b/api/xlsx/en/SectorGroup.xlsx
@@ -28,12 +28,12 @@
     <t>codeforiati:group-code</t>
   </si>
   <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
     <t>codeforiati:category-name</t>
   </si>
   <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
     <t>codeforiati:group-name</t>
   </si>
   <si>
@@ -49,12 +49,12 @@
     <t>110</t>
   </si>
   <si>
+    <t>111</t>
+  </si>
+  <si>
     <t>Education, Level Unspecified</t>
   </si>
   <si>
-    <t>111</t>
-  </si>
-  <si>
     <t>Education</t>
   </si>
   <si>
@@ -82,12 +82,12 @@
     <t>Primary education</t>
   </si>
   <si>
+    <t>112</t>
+  </si>
+  <si>
     <t>Basic Education</t>
   </si>
   <si>
-    <t>112</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -112,12 +112,12 @@
     <t>Secondary education</t>
   </si>
   <si>
+    <t>113</t>
+  </si>
+  <si>
     <t>Secondary Education</t>
   </si>
   <si>
-    <t>113</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
@@ -130,12 +130,12 @@
     <t>Higher education</t>
   </si>
   <si>
+    <t>114</t>
+  </si>
+  <si>
     <t>Post-Secondary Education</t>
   </si>
   <si>
-    <t>114</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -151,12 +151,12 @@
     <t>120</t>
   </si>
   <si>
+    <t>121</t>
+  </si>
+  <si>
     <t>Health, General</t>
   </si>
   <si>
-    <t>121</t>
-  </si>
-  <si>
     <t>Health</t>
   </si>
   <si>
@@ -184,12 +184,12 @@
     <t>Basic health care</t>
   </si>
   <si>
+    <t>122</t>
+  </si>
+  <si>
     <t>Basic Health</t>
   </si>
   <si>
-    <t>122</t>
-  </si>
-  <si>
     <t>12230</t>
   </si>
   <si>
@@ -238,12 +238,12 @@
     <t>NCDs control, general</t>
   </si>
   <si>
+    <t>123</t>
+  </si>
+  <si>
     <t>Non-communicable diseases (NCDs)</t>
   </si>
   <si>
-    <t>123</t>
-  </si>
-  <si>
     <t>12320</t>
   </si>
   <si>
@@ -391,12 +391,12 @@
     <t>150</t>
   </si>
   <si>
+    <t>151</t>
+  </si>
+  <si>
     <t>Government &amp; Civil Society-general</t>
   </si>
   <si>
-    <t>151</t>
-  </si>
-  <si>
     <t>Government &amp; Civil Society</t>
   </si>
   <si>
@@ -496,12 +496,12 @@
     <t>Security system management and reform</t>
   </si>
   <si>
+    <t>152</t>
+  </si>
+  <si>
     <t>Conflict, Peace &amp; Security</t>
   </si>
   <si>
-    <t>152</t>
-  </si>
-  <si>
     <t>15220</t>
   </si>
   <si>
@@ -691,12 +691,12 @@
     <t>230</t>
   </si>
   <si>
+    <t>231</t>
+  </si>
+  <si>
     <t>Energy Policy</t>
   </si>
   <si>
-    <t>231</t>
-  </si>
-  <si>
     <t>Energy</t>
   </si>
   <si>
@@ -724,12 +724,12 @@
     <t>Energy generation, renewable sources - multiple technologies</t>
   </si>
   <si>
+    <t>232</t>
+  </si>
+  <si>
     <t>Energy generation, renewable sources</t>
   </si>
   <si>
-    <t>232</t>
-  </si>
-  <si>
     <t>23220</t>
   </si>
   <si>
@@ -784,12 +784,12 @@
     <t>Energy generation, non-renewable sources, unspecified</t>
   </si>
   <si>
+    <t>233</t>
+  </si>
+  <si>
     <t>Energy generation, non-renewable sources</t>
   </si>
   <si>
-    <t>233</t>
-  </si>
-  <si>
     <t>23320</t>
   </si>
   <si>
@@ -826,36 +826,36 @@
     <t>Hybrid energy electric power plants</t>
   </si>
   <si>
+    <t>234</t>
+  </si>
+  <si>
     <t>Hybrid energy plants</t>
   </si>
   <si>
-    <t>234</t>
-  </si>
-  <si>
     <t>23510</t>
   </si>
   <si>
     <t>Nuclear energy electric power plants and nuclear safety</t>
   </si>
   <si>
+    <t>235</t>
+  </si>
+  <si>
     <t>Nuclear energy plants</t>
   </si>
   <si>
-    <t>235</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
     <t>Heat plants</t>
   </si>
   <si>
+    <t>236</t>
+  </si>
+  <si>
     <t>Energy distribution</t>
   </si>
   <si>
-    <t>236</t>
-  </si>
-  <si>
     <t>23620</t>
   </si>
   <si>
@@ -973,12 +973,12 @@
     <t>310</t>
   </si>
   <si>
+    <t>311</t>
+  </si>
+  <si>
     <t>Agriculture</t>
   </si>
   <si>
-    <t>311</t>
-  </si>
-  <si>
     <t>Agriculture, Forestry, Fishing</t>
   </si>
   <si>
@@ -1090,12 +1090,12 @@
     <t>Forestry policy and administrative management</t>
   </si>
   <si>
+    <t>312</t>
+  </si>
+  <si>
     <t>Forestry</t>
   </si>
   <si>
-    <t>312</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -1132,12 +1132,12 @@
     <t>Fishing policy and administrative management</t>
   </si>
   <si>
+    <t>313</t>
+  </si>
+  <si>
     <t>Fishing</t>
   </si>
   <si>
-    <t>313</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -1171,12 +1171,12 @@
     <t>320</t>
   </si>
   <si>
+    <t>321</t>
+  </si>
+  <si>
     <t>Industry</t>
   </si>
   <si>
-    <t>321</t>
-  </si>
-  <si>
     <t>Industry, Mining, Construction</t>
   </si>
   <si>
@@ -1294,12 +1294,12 @@
     <t>Mineral/mining policy and administrative management</t>
   </si>
   <si>
+    <t>322</t>
+  </si>
+  <si>
     <t>Mineral Resources &amp; Mining</t>
   </si>
   <si>
-    <t>322</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -1360,10 +1360,10 @@
     <t>Construction policy and administrative management</t>
   </si>
   <si>
+    <t>323</t>
+  </si>
+  <si>
     <t>Construction</t>
-  </si>
-  <si>
-    <t>323</t>
   </si>
   <si>
     <t>33110</t>
@@ -2767,10 +2767,10 @@
         <v>88</v>
       </c>
       <c r="E32" t="s">
+        <v>88</v>
+      </c>
+      <c r="F32" t="s">
         <v>89</v>
-      </c>
-      <c r="F32" t="s">
-        <v>88</v>
       </c>
       <c r="G32" t="s">
         <v>89</v>
@@ -2790,10 +2790,10 @@
         <v>88</v>
       </c>
       <c r="E33" t="s">
+        <v>88</v>
+      </c>
+      <c r="F33" t="s">
         <v>89</v>
-      </c>
-      <c r="F33" t="s">
-        <v>88</v>
       </c>
       <c r="G33" t="s">
         <v>89</v>
@@ -2813,10 +2813,10 @@
         <v>88</v>
       </c>
       <c r="E34" t="s">
+        <v>88</v>
+      </c>
+      <c r="F34" t="s">
         <v>89</v>
-      </c>
-      <c r="F34" t="s">
-        <v>88</v>
       </c>
       <c r="G34" t="s">
         <v>89</v>
@@ -2836,10 +2836,10 @@
         <v>88</v>
       </c>
       <c r="E35" t="s">
+        <v>88</v>
+      </c>
+      <c r="F35" t="s">
         <v>89</v>
-      </c>
-      <c r="F35" t="s">
-        <v>88</v>
       </c>
       <c r="G35" t="s">
         <v>89</v>
@@ -2859,10 +2859,10 @@
         <v>88</v>
       </c>
       <c r="E36" t="s">
+        <v>88</v>
+      </c>
+      <c r="F36" t="s">
         <v>89</v>
-      </c>
-      <c r="F36" t="s">
-        <v>88</v>
       </c>
       <c r="G36" t="s">
         <v>89</v>
@@ -2882,10 +2882,10 @@
         <v>100</v>
       </c>
       <c r="E37" t="s">
+        <v>100</v>
+      </c>
+      <c r="F37" t="s">
         <v>101</v>
-      </c>
-      <c r="F37" t="s">
-        <v>100</v>
       </c>
       <c r="G37" t="s">
         <v>101</v>
@@ -2905,10 +2905,10 @@
         <v>100</v>
       </c>
       <c r="E38" t="s">
+        <v>100</v>
+      </c>
+      <c r="F38" t="s">
         <v>101</v>
-      </c>
-      <c r="F38" t="s">
-        <v>100</v>
       </c>
       <c r="G38" t="s">
         <v>101</v>
@@ -2928,10 +2928,10 @@
         <v>100</v>
       </c>
       <c r="E39" t="s">
+        <v>100</v>
+      </c>
+      <c r="F39" t="s">
         <v>101</v>
-      </c>
-      <c r="F39" t="s">
-        <v>100</v>
       </c>
       <c r="G39" t="s">
         <v>101</v>
@@ -2951,10 +2951,10 @@
         <v>100</v>
       </c>
       <c r="E40" t="s">
+        <v>100</v>
+      </c>
+      <c r="F40" t="s">
         <v>101</v>
-      </c>
-      <c r="F40" t="s">
-        <v>100</v>
       </c>
       <c r="G40" t="s">
         <v>101</v>
@@ -2974,10 +2974,10 @@
         <v>100</v>
       </c>
       <c r="E41" t="s">
+        <v>100</v>
+      </c>
+      <c r="F41" t="s">
         <v>101</v>
-      </c>
-      <c r="F41" t="s">
-        <v>100</v>
       </c>
       <c r="G41" t="s">
         <v>101</v>
@@ -2997,10 +2997,10 @@
         <v>100</v>
       </c>
       <c r="E42" t="s">
+        <v>100</v>
+      </c>
+      <c r="F42" t="s">
         <v>101</v>
-      </c>
-      <c r="F42" t="s">
-        <v>100</v>
       </c>
       <c r="G42" t="s">
         <v>101</v>
@@ -3020,10 +3020,10 @@
         <v>100</v>
       </c>
       <c r="E43" t="s">
+        <v>100</v>
+      </c>
+      <c r="F43" t="s">
         <v>101</v>
-      </c>
-      <c r="F43" t="s">
-        <v>100</v>
       </c>
       <c r="G43" t="s">
         <v>101</v>
@@ -3043,10 +3043,10 @@
         <v>100</v>
       </c>
       <c r="E44" t="s">
+        <v>100</v>
+      </c>
+      <c r="F44" t="s">
         <v>101</v>
-      </c>
-      <c r="F44" t="s">
-        <v>100</v>
       </c>
       <c r="G44" t="s">
         <v>101</v>
@@ -3066,10 +3066,10 @@
         <v>100</v>
       </c>
       <c r="E45" t="s">
+        <v>100</v>
+      </c>
+      <c r="F45" t="s">
         <v>101</v>
-      </c>
-      <c r="F45" t="s">
-        <v>100</v>
       </c>
       <c r="G45" t="s">
         <v>101</v>
@@ -3089,10 +3089,10 @@
         <v>100</v>
       </c>
       <c r="E46" t="s">
+        <v>100</v>
+      </c>
+      <c r="F46" t="s">
         <v>101</v>
-      </c>
-      <c r="F46" t="s">
-        <v>100</v>
       </c>
       <c r="G46" t="s">
         <v>101</v>
@@ -3112,10 +3112,10 @@
         <v>100</v>
       </c>
       <c r="E47" t="s">
+        <v>100</v>
+      </c>
+      <c r="F47" t="s">
         <v>101</v>
-      </c>
-      <c r="F47" t="s">
-        <v>100</v>
       </c>
       <c r="G47" t="s">
         <v>101</v>
@@ -3641,10 +3641,10 @@
         <v>174</v>
       </c>
       <c r="E70" t="s">
+        <v>174</v>
+      </c>
+      <c r="F70" t="s">
         <v>175</v>
-      </c>
-      <c r="F70" t="s">
-        <v>174</v>
       </c>
       <c r="G70" t="s">
         <v>175</v>
@@ -3664,10 +3664,10 @@
         <v>174</v>
       </c>
       <c r="E71" t="s">
+        <v>174</v>
+      </c>
+      <c r="F71" t="s">
         <v>175</v>
-      </c>
-      <c r="F71" t="s">
-        <v>174</v>
       </c>
       <c r="G71" t="s">
         <v>175</v>
@@ -3687,10 +3687,10 @@
         <v>174</v>
       </c>
       <c r="E72" t="s">
+        <v>174</v>
+      </c>
+      <c r="F72" t="s">
         <v>175</v>
-      </c>
-      <c r="F72" t="s">
-        <v>174</v>
       </c>
       <c r="G72" t="s">
         <v>175</v>
@@ -3710,10 +3710,10 @@
         <v>174</v>
       </c>
       <c r="E73" t="s">
+        <v>174</v>
+      </c>
+      <c r="F73" t="s">
         <v>175</v>
-      </c>
-      <c r="F73" t="s">
-        <v>174</v>
       </c>
       <c r="G73" t="s">
         <v>175</v>
@@ -3733,10 +3733,10 @@
         <v>174</v>
       </c>
       <c r="E74" t="s">
+        <v>174</v>
+      </c>
+      <c r="F74" t="s">
         <v>175</v>
-      </c>
-      <c r="F74" t="s">
-        <v>174</v>
       </c>
       <c r="G74" t="s">
         <v>175</v>
@@ -3756,10 +3756,10 @@
         <v>174</v>
       </c>
       <c r="E75" t="s">
+        <v>174</v>
+      </c>
+      <c r="F75" t="s">
         <v>175</v>
-      </c>
-      <c r="F75" t="s">
-        <v>174</v>
       </c>
       <c r="G75" t="s">
         <v>175</v>
@@ -3779,10 +3779,10 @@
         <v>174</v>
       </c>
       <c r="E76" t="s">
+        <v>174</v>
+      </c>
+      <c r="F76" t="s">
         <v>175</v>
-      </c>
-      <c r="F76" t="s">
-        <v>174</v>
       </c>
       <c r="G76" t="s">
         <v>175</v>
@@ -3802,10 +3802,10 @@
         <v>174</v>
       </c>
       <c r="E77" t="s">
+        <v>174</v>
+      </c>
+      <c r="F77" t="s">
         <v>175</v>
-      </c>
-      <c r="F77" t="s">
-        <v>174</v>
       </c>
       <c r="G77" t="s">
         <v>175</v>
@@ -3825,10 +3825,10 @@
         <v>174</v>
       </c>
       <c r="E78" t="s">
+        <v>174</v>
+      </c>
+      <c r="F78" t="s">
         <v>175</v>
-      </c>
-      <c r="F78" t="s">
-        <v>174</v>
       </c>
       <c r="G78" t="s">
         <v>175</v>
@@ -3848,10 +3848,10 @@
         <v>174</v>
       </c>
       <c r="E79" t="s">
+        <v>174</v>
+      </c>
+      <c r="F79" t="s">
         <v>175</v>
-      </c>
-      <c r="F79" t="s">
-        <v>174</v>
       </c>
       <c r="G79" t="s">
         <v>175</v>
@@ -3871,10 +3871,10 @@
         <v>174</v>
       </c>
       <c r="E80" t="s">
+        <v>174</v>
+      </c>
+      <c r="F80" t="s">
         <v>175</v>
-      </c>
-      <c r="F80" t="s">
-        <v>174</v>
       </c>
       <c r="G80" t="s">
         <v>175</v>
@@ -3894,10 +3894,10 @@
         <v>198</v>
       </c>
       <c r="E81" t="s">
+        <v>198</v>
+      </c>
+      <c r="F81" t="s">
         <v>199</v>
-      </c>
-      <c r="F81" t="s">
-        <v>198</v>
       </c>
       <c r="G81" t="s">
         <v>199</v>
@@ -3917,10 +3917,10 @@
         <v>198</v>
       </c>
       <c r="E82" t="s">
+        <v>198</v>
+      </c>
+      <c r="F82" t="s">
         <v>199</v>
-      </c>
-      <c r="F82" t="s">
-        <v>198</v>
       </c>
       <c r="G82" t="s">
         <v>199</v>
@@ -3940,10 +3940,10 @@
         <v>198</v>
       </c>
       <c r="E83" t="s">
+        <v>198</v>
+      </c>
+      <c r="F83" t="s">
         <v>199</v>
-      </c>
-      <c r="F83" t="s">
-        <v>198</v>
       </c>
       <c r="G83" t="s">
         <v>199</v>
@@ -3963,10 +3963,10 @@
         <v>198</v>
       </c>
       <c r="E84" t="s">
+        <v>198</v>
+      </c>
+      <c r="F84" t="s">
         <v>199</v>
-      </c>
-      <c r="F84" t="s">
-        <v>198</v>
       </c>
       <c r="G84" t="s">
         <v>199</v>
@@ -3986,10 +3986,10 @@
         <v>198</v>
       </c>
       <c r="E85" t="s">
+        <v>198</v>
+      </c>
+      <c r="F85" t="s">
         <v>199</v>
-      </c>
-      <c r="F85" t="s">
-        <v>198</v>
       </c>
       <c r="G85" t="s">
         <v>199</v>
@@ -4009,10 +4009,10 @@
         <v>198</v>
       </c>
       <c r="E86" t="s">
+        <v>198</v>
+      </c>
+      <c r="F86" t="s">
         <v>199</v>
-      </c>
-      <c r="F86" t="s">
-        <v>198</v>
       </c>
       <c r="G86" t="s">
         <v>199</v>
@@ -4032,10 +4032,10 @@
         <v>198</v>
       </c>
       <c r="E87" t="s">
+        <v>198</v>
+      </c>
+      <c r="F87" t="s">
         <v>199</v>
-      </c>
-      <c r="F87" t="s">
-        <v>198</v>
       </c>
       <c r="G87" t="s">
         <v>199</v>
@@ -4055,10 +4055,10 @@
         <v>214</v>
       </c>
       <c r="E88" t="s">
+        <v>214</v>
+      </c>
+      <c r="F88" t="s">
         <v>215</v>
-      </c>
-      <c r="F88" t="s">
-        <v>214</v>
       </c>
       <c r="G88" t="s">
         <v>215</v>
@@ -4078,10 +4078,10 @@
         <v>214</v>
       </c>
       <c r="E89" t="s">
+        <v>214</v>
+      </c>
+      <c r="F89" t="s">
         <v>215</v>
-      </c>
-      <c r="F89" t="s">
-        <v>214</v>
       </c>
       <c r="G89" t="s">
         <v>215</v>
@@ -4101,10 +4101,10 @@
         <v>214</v>
       </c>
       <c r="E90" t="s">
+        <v>214</v>
+      </c>
+      <c r="F90" t="s">
         <v>215</v>
-      </c>
-      <c r="F90" t="s">
-        <v>214</v>
       </c>
       <c r="G90" t="s">
         <v>215</v>
@@ -4124,10 +4124,10 @@
         <v>214</v>
       </c>
       <c r="E91" t="s">
+        <v>214</v>
+      </c>
+      <c r="F91" t="s">
         <v>215</v>
-      </c>
-      <c r="F91" t="s">
-        <v>214</v>
       </c>
       <c r="G91" t="s">
         <v>215</v>
@@ -4791,10 +4791,10 @@
         <v>294</v>
       </c>
       <c r="E120" t="s">
+        <v>294</v>
+      </c>
+      <c r="F120" t="s">
         <v>295</v>
-      </c>
-      <c r="F120" t="s">
-        <v>294</v>
       </c>
       <c r="G120" t="s">
         <v>295</v>
@@ -4814,10 +4814,10 @@
         <v>294</v>
       </c>
       <c r="E121" t="s">
+        <v>294</v>
+      </c>
+      <c r="F121" t="s">
         <v>295</v>
-      </c>
-      <c r="F121" t="s">
-        <v>294</v>
       </c>
       <c r="G121" t="s">
         <v>295</v>
@@ -4837,10 +4837,10 @@
         <v>294</v>
       </c>
       <c r="E122" t="s">
+        <v>294</v>
+      </c>
+      <c r="F122" t="s">
         <v>295</v>
-      </c>
-      <c r="F122" t="s">
-        <v>294</v>
       </c>
       <c r="G122" t="s">
         <v>295</v>
@@ -4860,10 +4860,10 @@
         <v>294</v>
       </c>
       <c r="E123" t="s">
+        <v>294</v>
+      </c>
+      <c r="F123" t="s">
         <v>295</v>
-      </c>
-      <c r="F123" t="s">
-        <v>294</v>
       </c>
       <c r="G123" t="s">
         <v>295</v>
@@ -4883,10 +4883,10 @@
         <v>294</v>
       </c>
       <c r="E124" t="s">
+        <v>294</v>
+      </c>
+      <c r="F124" t="s">
         <v>295</v>
-      </c>
-      <c r="F124" t="s">
-        <v>294</v>
       </c>
       <c r="G124" t="s">
         <v>295</v>
@@ -4906,10 +4906,10 @@
         <v>294</v>
       </c>
       <c r="E125" t="s">
+        <v>294</v>
+      </c>
+      <c r="F125" t="s">
         <v>295</v>
-      </c>
-      <c r="F125" t="s">
-        <v>294</v>
       </c>
       <c r="G125" t="s">
         <v>295</v>
@@ -4929,10 +4929,10 @@
         <v>308</v>
       </c>
       <c r="E126" t="s">
+        <v>308</v>
+      </c>
+      <c r="F126" t="s">
         <v>309</v>
-      </c>
-      <c r="F126" t="s">
-        <v>308</v>
       </c>
       <c r="G126" t="s">
         <v>309</v>
@@ -4952,10 +4952,10 @@
         <v>308</v>
       </c>
       <c r="E127" t="s">
+        <v>308</v>
+      </c>
+      <c r="F127" t="s">
         <v>309</v>
-      </c>
-      <c r="F127" t="s">
-        <v>308</v>
       </c>
       <c r="G127" t="s">
         <v>309</v>
@@ -4975,10 +4975,10 @@
         <v>308</v>
       </c>
       <c r="E128" t="s">
+        <v>308</v>
+      </c>
+      <c r="F128" t="s">
         <v>309</v>
-      </c>
-      <c r="F128" t="s">
-        <v>308</v>
       </c>
       <c r="G128" t="s">
         <v>309</v>
@@ -4998,10 +4998,10 @@
         <v>308</v>
       </c>
       <c r="E129" t="s">
+        <v>308</v>
+      </c>
+      <c r="F129" t="s">
         <v>309</v>
-      </c>
-      <c r="F129" t="s">
-        <v>308</v>
       </c>
       <c r="G129" t="s">
         <v>309</v>
@@ -6378,10 +6378,10 @@
         <v>452</v>
       </c>
       <c r="E189" t="s">
+        <v>452</v>
+      </c>
+      <c r="F189" t="s">
         <v>453</v>
-      </c>
-      <c r="F189" t="s">
-        <v>452</v>
       </c>
       <c r="G189" t="s">
         <v>453</v>
@@ -6401,10 +6401,10 @@
         <v>452</v>
       </c>
       <c r="E190" t="s">
+        <v>452</v>
+      </c>
+      <c r="F190" t="s">
         <v>453</v>
-      </c>
-      <c r="F190" t="s">
-        <v>452</v>
       </c>
       <c r="G190" t="s">
         <v>453</v>
@@ -6424,10 +6424,10 @@
         <v>452</v>
       </c>
       <c r="E191" t="s">
+        <v>452</v>
+      </c>
+      <c r="F191" t="s">
         <v>453</v>
-      </c>
-      <c r="F191" t="s">
-        <v>452</v>
       </c>
       <c r="G191" t="s">
         <v>453</v>
@@ -6447,10 +6447,10 @@
         <v>452</v>
       </c>
       <c r="E192" t="s">
+        <v>452</v>
+      </c>
+      <c r="F192" t="s">
         <v>453</v>
-      </c>
-      <c r="F192" t="s">
-        <v>452</v>
       </c>
       <c r="G192" t="s">
         <v>453</v>
@@ -6470,10 +6470,10 @@
         <v>452</v>
       </c>
       <c r="E193" t="s">
+        <v>452</v>
+      </c>
+      <c r="F193" t="s">
         <v>453</v>
-      </c>
-      <c r="F193" t="s">
-        <v>452</v>
       </c>
       <c r="G193" t="s">
         <v>453</v>
@@ -6493,10 +6493,10 @@
         <v>452</v>
       </c>
       <c r="E194" t="s">
+        <v>452</v>
+      </c>
+      <c r="F194" t="s">
         <v>453</v>
-      </c>
-      <c r="F194" t="s">
-        <v>452</v>
       </c>
       <c r="G194" t="s">
         <v>453</v>
@@ -6516,10 +6516,10 @@
         <v>466</v>
       </c>
       <c r="E195" t="s">
+        <v>466</v>
+      </c>
+      <c r="F195" t="s">
         <v>467</v>
-      </c>
-      <c r="F195" t="s">
-        <v>466</v>
       </c>
       <c r="G195" t="s">
         <v>467</v>
@@ -6539,10 +6539,10 @@
         <v>470</v>
       </c>
       <c r="E196" t="s">
+        <v>470</v>
+      </c>
+      <c r="F196" t="s">
         <v>471</v>
-      </c>
-      <c r="F196" t="s">
-        <v>470</v>
       </c>
       <c r="G196" t="s">
         <v>471</v>
@@ -6562,10 +6562,10 @@
         <v>470</v>
       </c>
       <c r="E197" t="s">
+        <v>470</v>
+      </c>
+      <c r="F197" t="s">
         <v>471</v>
-      </c>
-      <c r="F197" t="s">
-        <v>470</v>
       </c>
       <c r="G197" t="s">
         <v>471</v>
@@ -6585,10 +6585,10 @@
         <v>470</v>
       </c>
       <c r="E198" t="s">
+        <v>470</v>
+      </c>
+      <c r="F198" t="s">
         <v>471</v>
-      </c>
-      <c r="F198" t="s">
-        <v>470</v>
       </c>
       <c r="G198" t="s">
         <v>471</v>
@@ -6608,10 +6608,10 @@
         <v>470</v>
       </c>
       <c r="E199" t="s">
+        <v>470</v>
+      </c>
+      <c r="F199" t="s">
         <v>471</v>
-      </c>
-      <c r="F199" t="s">
-        <v>470</v>
       </c>
       <c r="G199" t="s">
         <v>471</v>
@@ -6631,10 +6631,10 @@
         <v>470</v>
       </c>
       <c r="E200" t="s">
+        <v>470</v>
+      </c>
+      <c r="F200" t="s">
         <v>471</v>
-      </c>
-      <c r="F200" t="s">
-        <v>470</v>
       </c>
       <c r="G200" t="s">
         <v>471</v>
@@ -6654,10 +6654,10 @@
         <v>470</v>
       </c>
       <c r="E201" t="s">
+        <v>470</v>
+      </c>
+      <c r="F201" t="s">
         <v>471</v>
-      </c>
-      <c r="F201" t="s">
-        <v>470</v>
       </c>
       <c r="G201" t="s">
         <v>471</v>
@@ -6677,10 +6677,10 @@
         <v>484</v>
       </c>
       <c r="E202" t="s">
+        <v>484</v>
+      </c>
+      <c r="F202" t="s">
         <v>485</v>
-      </c>
-      <c r="F202" t="s">
-        <v>484</v>
       </c>
       <c r="G202" t="s">
         <v>485</v>
@@ -6700,10 +6700,10 @@
         <v>484</v>
       </c>
       <c r="E203" t="s">
+        <v>484</v>
+      </c>
+      <c r="F203" t="s">
         <v>485</v>
-      </c>
-      <c r="F203" t="s">
-        <v>484</v>
       </c>
       <c r="G203" t="s">
         <v>485</v>
@@ -6723,10 +6723,10 @@
         <v>484</v>
       </c>
       <c r="E204" t="s">
+        <v>484</v>
+      </c>
+      <c r="F204" t="s">
         <v>485</v>
-      </c>
-      <c r="F204" t="s">
-        <v>484</v>
       </c>
       <c r="G204" t="s">
         <v>485</v>
@@ -6746,10 +6746,10 @@
         <v>484</v>
       </c>
       <c r="E205" t="s">
+        <v>484</v>
+      </c>
+      <c r="F205" t="s">
         <v>485</v>
-      </c>
-      <c r="F205" t="s">
-        <v>484</v>
       </c>
       <c r="G205" t="s">
         <v>485</v>
@@ -6769,10 +6769,10 @@
         <v>484</v>
       </c>
       <c r="E206" t="s">
+        <v>484</v>
+      </c>
+      <c r="F206" t="s">
         <v>485</v>
-      </c>
-      <c r="F206" t="s">
-        <v>484</v>
       </c>
       <c r="G206" t="s">
         <v>485</v>
@@ -6792,10 +6792,10 @@
         <v>484</v>
       </c>
       <c r="E207" t="s">
+        <v>484</v>
+      </c>
+      <c r="F207" t="s">
         <v>485</v>
-      </c>
-      <c r="F207" t="s">
-        <v>484</v>
       </c>
       <c r="G207" t="s">
         <v>485</v>
@@ -6815,10 +6815,10 @@
         <v>484</v>
       </c>
       <c r="E208" t="s">
+        <v>484</v>
+      </c>
+      <c r="F208" t="s">
         <v>485</v>
-      </c>
-      <c r="F208" t="s">
-        <v>484</v>
       </c>
       <c r="G208" t="s">
         <v>485</v>
@@ -6838,10 +6838,10 @@
         <v>484</v>
       </c>
       <c r="E209" t="s">
+        <v>484</v>
+      </c>
+      <c r="F209" t="s">
         <v>485</v>
-      </c>
-      <c r="F209" t="s">
-        <v>484</v>
       </c>
       <c r="G209" t="s">
         <v>485</v>
@@ -6861,10 +6861,10 @@
         <v>484</v>
       </c>
       <c r="E210" t="s">
+        <v>484</v>
+      </c>
+      <c r="F210" t="s">
         <v>485</v>
-      </c>
-      <c r="F210" t="s">
-        <v>484</v>
       </c>
       <c r="G210" t="s">
         <v>485</v>
@@ -6884,10 +6884,10 @@
         <v>484</v>
       </c>
       <c r="E211" t="s">
+        <v>484</v>
+      </c>
+      <c r="F211" t="s">
         <v>485</v>
-      </c>
-      <c r="F211" t="s">
-        <v>484</v>
       </c>
       <c r="G211" t="s">
         <v>485</v>
@@ -6907,10 +6907,10 @@
         <v>506</v>
       </c>
       <c r="E212" t="s">
+        <v>506</v>
+      </c>
+      <c r="F212" t="s">
         <v>507</v>
-      </c>
-      <c r="F212" t="s">
-        <v>506</v>
       </c>
       <c r="G212" t="s">
         <v>507</v>
@@ -6930,10 +6930,10 @@
         <v>510</v>
       </c>
       <c r="E213" t="s">
+        <v>510</v>
+      </c>
+      <c r="F213" t="s">
         <v>511</v>
-      </c>
-      <c r="F213" t="s">
-        <v>510</v>
       </c>
       <c r="G213" t="s">
         <v>511</v>
@@ -6953,10 +6953,10 @@
         <v>514</v>
       </c>
       <c r="E214" t="s">
+        <v>514</v>
+      </c>
+      <c r="F214" t="s">
         <v>515</v>
-      </c>
-      <c r="F214" t="s">
-        <v>514</v>
       </c>
       <c r="G214" t="s">
         <v>515</v>
@@ -6976,10 +6976,10 @@
         <v>514</v>
       </c>
       <c r="E215" t="s">
+        <v>514</v>
+      </c>
+      <c r="F215" t="s">
         <v>515</v>
-      </c>
-      <c r="F215" t="s">
-        <v>514</v>
       </c>
       <c r="G215" t="s">
         <v>515</v>
@@ -6999,10 +6999,10 @@
         <v>520</v>
       </c>
       <c r="E216" t="s">
+        <v>520</v>
+      </c>
+      <c r="F216" t="s">
         <v>521</v>
-      </c>
-      <c r="F216" t="s">
-        <v>520</v>
       </c>
       <c r="G216" t="s">
         <v>521</v>
@@ -7022,10 +7022,10 @@
         <v>520</v>
       </c>
       <c r="E217" t="s">
+        <v>520</v>
+      </c>
+      <c r="F217" t="s">
         <v>521</v>
-      </c>
-      <c r="F217" t="s">
-        <v>520</v>
       </c>
       <c r="G217" t="s">
         <v>521</v>
@@ -7045,10 +7045,10 @@
         <v>520</v>
       </c>
       <c r="E218" t="s">
+        <v>520</v>
+      </c>
+      <c r="F218" t="s">
         <v>521</v>
-      </c>
-      <c r="F218" t="s">
-        <v>520</v>
       </c>
       <c r="G218" t="s">
         <v>521</v>
@@ -7068,10 +7068,10 @@
         <v>520</v>
       </c>
       <c r="E219" t="s">
+        <v>520</v>
+      </c>
+      <c r="F219" t="s">
         <v>521</v>
-      </c>
-      <c r="F219" t="s">
-        <v>520</v>
       </c>
       <c r="G219" t="s">
         <v>521</v>
@@ -7091,10 +7091,10 @@
         <v>520</v>
       </c>
       <c r="E220" t="s">
+        <v>520</v>
+      </c>
+      <c r="F220" t="s">
         <v>521</v>
-      </c>
-      <c r="F220" t="s">
-        <v>520</v>
       </c>
       <c r="G220" t="s">
         <v>521</v>
@@ -7114,10 +7114,10 @@
         <v>520</v>
       </c>
       <c r="E221" t="s">
+        <v>520</v>
+      </c>
+      <c r="F221" t="s">
         <v>521</v>
-      </c>
-      <c r="F221" t="s">
-        <v>520</v>
       </c>
       <c r="G221" t="s">
         <v>521</v>
@@ -7137,10 +7137,10 @@
         <v>520</v>
       </c>
       <c r="E222" t="s">
+        <v>520</v>
+      </c>
+      <c r="F222" t="s">
         <v>521</v>
-      </c>
-      <c r="F222" t="s">
-        <v>520</v>
       </c>
       <c r="G222" t="s">
         <v>521</v>
@@ -7160,10 +7160,10 @@
         <v>536</v>
       </c>
       <c r="E223" t="s">
+        <v>536</v>
+      </c>
+      <c r="F223" t="s">
         <v>537</v>
-      </c>
-      <c r="F223" t="s">
-        <v>536</v>
       </c>
       <c r="G223" t="s">
         <v>537</v>
@@ -7183,10 +7183,10 @@
         <v>536</v>
       </c>
       <c r="E224" t="s">
+        <v>536</v>
+      </c>
+      <c r="F224" t="s">
         <v>537</v>
-      </c>
-      <c r="F224" t="s">
-        <v>536</v>
       </c>
       <c r="G224" t="s">
         <v>537</v>
@@ -7206,10 +7206,10 @@
         <v>536</v>
       </c>
       <c r="E225" t="s">
+        <v>536</v>
+      </c>
+      <c r="F225" t="s">
         <v>537</v>
-      </c>
-      <c r="F225" t="s">
-        <v>536</v>
       </c>
       <c r="G225" t="s">
         <v>537</v>
@@ -7229,10 +7229,10 @@
         <v>544</v>
       </c>
       <c r="E226" t="s">
+        <v>544</v>
+      </c>
+      <c r="F226" t="s">
         <v>545</v>
-      </c>
-      <c r="F226" t="s">
-        <v>544</v>
       </c>
       <c r="G226" t="s">
         <v>545</v>
@@ -7252,10 +7252,10 @@
         <v>548</v>
       </c>
       <c r="E227" t="s">
+        <v>548</v>
+      </c>
+      <c r="F227" t="s">
         <v>549</v>
-      </c>
-      <c r="F227" t="s">
-        <v>548</v>
       </c>
       <c r="G227" t="s">
         <v>549</v>
@@ -7275,10 +7275,10 @@
         <v>552</v>
       </c>
       <c r="E228" t="s">
+        <v>552</v>
+      </c>
+      <c r="F228" t="s">
         <v>553</v>
-      </c>
-      <c r="F228" t="s">
-        <v>552</v>
       </c>
       <c r="G228" t="s">
         <v>553</v>
@@ -7298,10 +7298,10 @@
         <v>556</v>
       </c>
       <c r="E229" t="s">
+        <v>556</v>
+      </c>
+      <c r="F229" t="s">
         <v>557</v>
-      </c>
-      <c r="F229" t="s">
-        <v>556</v>
       </c>
       <c r="G229" t="s">
         <v>557</v>
@@ -7321,10 +7321,10 @@
         <v>560</v>
       </c>
       <c r="E230" t="s">
+        <v>560</v>
+      </c>
+      <c r="F230" t="s">
         <v>561</v>
-      </c>
-      <c r="F230" t="s">
-        <v>560</v>
       </c>
       <c r="G230" t="s">
         <v>561</v>
@@ -7344,10 +7344,10 @@
         <v>560</v>
       </c>
       <c r="E231" t="s">
+        <v>560</v>
+      </c>
+      <c r="F231" t="s">
         <v>561</v>
-      </c>
-      <c r="F231" t="s">
-        <v>560</v>
       </c>
       <c r="G231" t="s">
         <v>561</v>

--- a/api/xlsx/en/SectorGroup.xlsx
+++ b/api/xlsx/en/SectorGroup.xlsx
@@ -25,12 +25,12 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
     <t>codeforiati:category-name</t>
   </si>
   <si>
@@ -46,12 +46,12 @@
     <t>active</t>
   </si>
   <si>
+    <t>111</t>
+  </si>
+  <si>
     <t>110</t>
   </si>
   <si>
-    <t>111</t>
-  </si>
-  <si>
     <t>Education, Level Unspecified</t>
   </si>
   <si>
@@ -148,12 +148,12 @@
     <t>Health policy and administrative management</t>
   </si>
   <si>
+    <t>121</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
-    <t>121</t>
-  </si>
-  <si>
     <t>Health, General</t>
   </si>
   <si>
@@ -388,12 +388,12 @@
     <t>Public sector policy and administrative management</t>
   </si>
   <si>
+    <t>151</t>
+  </si>
+  <si>
     <t>150</t>
   </si>
   <si>
-    <t>151</t>
-  </si>
-  <si>
     <t>Government &amp; Civil Society-general</t>
   </si>
   <si>
@@ -688,12 +688,12 @@
     <t>Energy policy and administrative management</t>
   </si>
   <si>
+    <t>231</t>
+  </si>
+  <si>
     <t>230</t>
   </si>
   <si>
-    <t>231</t>
-  </si>
-  <si>
     <t>Energy Policy</t>
   </si>
   <si>
@@ -970,12 +970,12 @@
     <t>Agricultural policy and administrative management</t>
   </si>
   <si>
+    <t>311</t>
+  </si>
+  <si>
     <t>310</t>
   </si>
   <si>
-    <t>311</t>
-  </si>
-  <si>
     <t>Agriculture</t>
   </si>
   <si>
@@ -1168,10 +1168,10 @@
     <t>Industrial policy and administrative management</t>
   </si>
   <si>
+    <t>321</t>
+  </si>
+  <si>
     <t>320</t>
-  </si>
-  <si>
-    <t>321</t>
   </si>
   <si>
     <t>Industry</t>
@@ -2166,10 +2166,10 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
         <v>23</v>
@@ -2189,10 +2189,10 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
         <v>23</v>
@@ -2212,10 +2212,10 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s">
         <v>23</v>
@@ -2235,10 +2235,10 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E9" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
         <v>23</v>
@@ -2258,10 +2258,10 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E10" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F10" t="s">
         <v>33</v>
@@ -2281,10 +2281,10 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F11" t="s">
         <v>33</v>
@@ -2304,10 +2304,10 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F12" t="s">
         <v>39</v>
@@ -2327,10 +2327,10 @@
         <v>9</v>
       </c>
       <c r="D13" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E13" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F13" t="s">
         <v>39</v>
@@ -2442,10 +2442,10 @@
         <v>9</v>
       </c>
       <c r="D18" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E18" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F18" t="s">
         <v>57</v>
@@ -2465,10 +2465,10 @@
         <v>9</v>
       </c>
       <c r="D19" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E19" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F19" t="s">
         <v>57</v>
@@ -2488,10 +2488,10 @@
         <v>9</v>
       </c>
       <c r="D20" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E20" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F20" t="s">
         <v>57</v>
@@ -2511,10 +2511,10 @@
         <v>9</v>
       </c>
       <c r="D21" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E21" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F21" t="s">
         <v>57</v>
@@ -2534,10 +2534,10 @@
         <v>9</v>
       </c>
       <c r="D22" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E22" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F22" t="s">
         <v>57</v>
@@ -2557,10 +2557,10 @@
         <v>9</v>
       </c>
       <c r="D23" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E23" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F23" t="s">
         <v>57</v>
@@ -2580,10 +2580,10 @@
         <v>9</v>
       </c>
       <c r="D24" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E24" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F24" t="s">
         <v>57</v>
@@ -2603,10 +2603,10 @@
         <v>9</v>
       </c>
       <c r="D25" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E25" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F25" t="s">
         <v>57</v>
@@ -2626,10 +2626,10 @@
         <v>9</v>
       </c>
       <c r="D26" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E26" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="F26" t="s">
         <v>75</v>
@@ -2649,10 +2649,10 @@
         <v>9</v>
       </c>
       <c r="D27" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E27" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="F27" t="s">
         <v>75</v>
@@ -2672,10 +2672,10 @@
         <v>9</v>
       </c>
       <c r="D28" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E28" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="F28" t="s">
         <v>75</v>
@@ -2695,10 +2695,10 @@
         <v>9</v>
       </c>
       <c r="D29" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E29" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="F29" t="s">
         <v>75</v>
@@ -2718,10 +2718,10 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E30" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="F30" t="s">
         <v>75</v>
@@ -2741,10 +2741,10 @@
         <v>9</v>
       </c>
       <c r="D31" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E31" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="F31" t="s">
         <v>75</v>
@@ -3500,10 +3500,10 @@
         <v>9</v>
       </c>
       <c r="D64" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E64" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="F64" t="s">
         <v>161</v>
@@ -3523,10 +3523,10 @@
         <v>9</v>
       </c>
       <c r="D65" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E65" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="F65" t="s">
         <v>161</v>
@@ -3546,10 +3546,10 @@
         <v>9</v>
       </c>
       <c r="D66" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E66" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="F66" t="s">
         <v>161</v>
@@ -3569,10 +3569,10 @@
         <v>9</v>
       </c>
       <c r="D67" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E67" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="F67" t="s">
         <v>161</v>
@@ -3592,10 +3592,10 @@
         <v>9</v>
       </c>
       <c r="D68" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E68" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="F68" t="s">
         <v>161</v>
@@ -3615,10 +3615,10 @@
         <v>9</v>
       </c>
       <c r="D69" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E69" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="F69" t="s">
         <v>161</v>
@@ -4236,10 +4236,10 @@
         <v>9</v>
       </c>
       <c r="D96" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E96" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F96" t="s">
         <v>237</v>
@@ -4259,10 +4259,10 @@
         <v>9</v>
       </c>
       <c r="D97" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E97" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F97" t="s">
         <v>237</v>
@@ -4282,10 +4282,10 @@
         <v>9</v>
       </c>
       <c r="D98" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E98" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F98" t="s">
         <v>237</v>
@@ -4305,10 +4305,10 @@
         <v>9</v>
       </c>
       <c r="D99" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E99" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F99" t="s">
         <v>237</v>
@@ -4328,10 +4328,10 @@
         <v>9</v>
       </c>
       <c r="D100" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E100" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F100" t="s">
         <v>237</v>
@@ -4351,10 +4351,10 @@
         <v>9</v>
       </c>
       <c r="D101" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E101" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F101" t="s">
         <v>237</v>
@@ -4374,10 +4374,10 @@
         <v>9</v>
       </c>
       <c r="D102" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E102" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F102" t="s">
         <v>237</v>
@@ -4397,10 +4397,10 @@
         <v>9</v>
       </c>
       <c r="D103" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E103" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F103" t="s">
         <v>237</v>
@@ -4420,10 +4420,10 @@
         <v>9</v>
       </c>
       <c r="D104" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E104" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F104" t="s">
         <v>237</v>
@@ -4443,10 +4443,10 @@
         <v>9</v>
       </c>
       <c r="D105" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E105" t="s">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="F105" t="s">
         <v>257</v>
@@ -4466,10 +4466,10 @@
         <v>9</v>
       </c>
       <c r="D106" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E106" t="s">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="F106" t="s">
         <v>257</v>
@@ -4489,10 +4489,10 @@
         <v>9</v>
       </c>
       <c r="D107" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E107" t="s">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="F107" t="s">
         <v>257</v>
@@ -4512,10 +4512,10 @@
         <v>9</v>
       </c>
       <c r="D108" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E108" t="s">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="F108" t="s">
         <v>257</v>
@@ -4535,10 +4535,10 @@
         <v>9</v>
       </c>
       <c r="D109" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E109" t="s">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="F109" t="s">
         <v>257</v>
@@ -4558,10 +4558,10 @@
         <v>9</v>
       </c>
       <c r="D110" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E110" t="s">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="F110" t="s">
         <v>257</v>
@@ -4581,10 +4581,10 @@
         <v>9</v>
       </c>
       <c r="D111" t="s">
-        <v>224</v>
+        <v>270</v>
       </c>
       <c r="E111" t="s">
-        <v>270</v>
+        <v>225</v>
       </c>
       <c r="F111" t="s">
         <v>271</v>
@@ -4604,10 +4604,10 @@
         <v>9</v>
       </c>
       <c r="D112" t="s">
-        <v>224</v>
+        <v>274</v>
       </c>
       <c r="E112" t="s">
-        <v>274</v>
+        <v>225</v>
       </c>
       <c r="F112" t="s">
         <v>275</v>
@@ -4627,10 +4627,10 @@
         <v>9</v>
       </c>
       <c r="D113" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E113" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="F113" t="s">
         <v>279</v>
@@ -4650,10 +4650,10 @@
         <v>9</v>
       </c>
       <c r="D114" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E114" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="F114" t="s">
         <v>279</v>
@@ -4673,10 +4673,10 @@
         <v>9</v>
       </c>
       <c r="D115" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E115" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="F115" t="s">
         <v>279</v>
@@ -4696,10 +4696,10 @@
         <v>9</v>
       </c>
       <c r="D116" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E116" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="F116" t="s">
         <v>279</v>
@@ -4719,10 +4719,10 @@
         <v>9</v>
       </c>
       <c r="D117" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E117" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="F117" t="s">
         <v>279</v>
@@ -4742,10 +4742,10 @@
         <v>9</v>
       </c>
       <c r="D118" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E118" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="F118" t="s">
         <v>279</v>
@@ -4765,10 +4765,10 @@
         <v>9</v>
       </c>
       <c r="D119" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E119" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="F119" t="s">
         <v>279</v>
@@ -5432,10 +5432,10 @@
         <v>9</v>
       </c>
       <c r="D148" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E148" t="s">
-        <v>358</v>
+        <v>319</v>
       </c>
       <c r="F148" t="s">
         <v>359</v>
@@ -5455,10 +5455,10 @@
         <v>9</v>
       </c>
       <c r="D149" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E149" t="s">
-        <v>358</v>
+        <v>319</v>
       </c>
       <c r="F149" t="s">
         <v>359</v>
@@ -5478,10 +5478,10 @@
         <v>9</v>
       </c>
       <c r="D150" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E150" t="s">
-        <v>358</v>
+        <v>319</v>
       </c>
       <c r="F150" t="s">
         <v>359</v>
@@ -5501,10 +5501,10 @@
         <v>9</v>
       </c>
       <c r="D151" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E151" t="s">
-        <v>358</v>
+        <v>319</v>
       </c>
       <c r="F151" t="s">
         <v>359</v>
@@ -5524,10 +5524,10 @@
         <v>9</v>
       </c>
       <c r="D152" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E152" t="s">
-        <v>358</v>
+        <v>319</v>
       </c>
       <c r="F152" t="s">
         <v>359</v>
@@ -5547,10 +5547,10 @@
         <v>9</v>
       </c>
       <c r="D153" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E153" t="s">
-        <v>358</v>
+        <v>319</v>
       </c>
       <c r="F153" t="s">
         <v>359</v>
@@ -5570,10 +5570,10 @@
         <v>9</v>
       </c>
       <c r="D154" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="E154" t="s">
-        <v>372</v>
+        <v>319</v>
       </c>
       <c r="F154" t="s">
         <v>373</v>
@@ -5593,10 +5593,10 @@
         <v>9</v>
       </c>
       <c r="D155" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="E155" t="s">
-        <v>372</v>
+        <v>319</v>
       </c>
       <c r="F155" t="s">
         <v>373</v>
@@ -5616,10 +5616,10 @@
         <v>9</v>
       </c>
       <c r="D156" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="E156" t="s">
-        <v>372</v>
+        <v>319</v>
       </c>
       <c r="F156" t="s">
         <v>373</v>
@@ -5639,10 +5639,10 @@
         <v>9</v>
       </c>
       <c r="D157" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="E157" t="s">
-        <v>372</v>
+        <v>319</v>
       </c>
       <c r="F157" t="s">
         <v>373</v>
@@ -5662,10 +5662,10 @@
         <v>9</v>
       </c>
       <c r="D158" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="E158" t="s">
-        <v>372</v>
+        <v>319</v>
       </c>
       <c r="F158" t="s">
         <v>373</v>
@@ -6122,10 +6122,10 @@
         <v>9</v>
       </c>
       <c r="D178" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E178" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="F178" t="s">
         <v>427</v>
@@ -6145,10 +6145,10 @@
         <v>9</v>
       </c>
       <c r="D179" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E179" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="F179" t="s">
         <v>427</v>
@@ -6168,10 +6168,10 @@
         <v>9</v>
       </c>
       <c r="D180" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E180" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="F180" t="s">
         <v>427</v>
@@ -6191,10 +6191,10 @@
         <v>9</v>
       </c>
       <c r="D181" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E181" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="F181" t="s">
         <v>427</v>
@@ -6214,10 +6214,10 @@
         <v>9</v>
       </c>
       <c r="D182" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E182" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="F182" t="s">
         <v>427</v>
@@ -6237,10 +6237,10 @@
         <v>9</v>
       </c>
       <c r="D183" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E183" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="F183" t="s">
         <v>427</v>
@@ -6260,10 +6260,10 @@
         <v>9</v>
       </c>
       <c r="D184" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E184" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="F184" t="s">
         <v>427</v>
@@ -6283,10 +6283,10 @@
         <v>9</v>
       </c>
       <c r="D185" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E185" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="F185" t="s">
         <v>427</v>
@@ -6306,10 +6306,10 @@
         <v>9</v>
       </c>
       <c r="D186" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E186" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="F186" t="s">
         <v>427</v>
@@ -6329,10 +6329,10 @@
         <v>9</v>
       </c>
       <c r="D187" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E187" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="F187" t="s">
         <v>427</v>
@@ -6352,10 +6352,10 @@
         <v>9</v>
       </c>
       <c r="D188" t="s">
-        <v>384</v>
+        <v>448</v>
       </c>
       <c r="E188" t="s">
-        <v>448</v>
+        <v>385</v>
       </c>
       <c r="F188" t="s">
         <v>449</v>

--- a/api/xlsx/en/SectorGroup.xlsx
+++ b/api/xlsx/en/SectorGroup.xlsx
@@ -25,18 +25,18 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
+    <t>codeforiati:category-name</t>
+  </si>
+  <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
-    <t>codeforiati:category-name</t>
-  </si>
-  <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -46,18 +46,18 @@
     <t>active</t>
   </si>
   <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>Education, Level Unspecified</t>
+  </si>
+  <si>
     <t>111</t>
   </si>
   <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>Education, Level Unspecified</t>
-  </si>
-  <si>
-    <t>Education</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -82,12 +82,12 @@
     <t>Primary education</t>
   </si>
   <si>
+    <t>Basic Education</t>
+  </si>
+  <si>
     <t>112</t>
   </si>
   <si>
-    <t>Basic Education</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -112,12 +112,12 @@
     <t>Secondary education</t>
   </si>
   <si>
+    <t>Secondary Education</t>
+  </si>
+  <si>
     <t>113</t>
   </si>
   <si>
-    <t>Secondary Education</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
@@ -130,12 +130,12 @@
     <t>Higher education</t>
   </si>
   <si>
+    <t>Post-Secondary Education</t>
+  </si>
+  <si>
     <t>114</t>
   </si>
   <si>
-    <t>Post-Secondary Education</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -148,18 +148,18 @@
     <t>Health policy and administrative management</t>
   </si>
   <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>Health</t>
+  </si>
+  <si>
+    <t>Health, General</t>
+  </si>
+  <si>
     <t>121</t>
   </si>
   <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>Health, General</t>
-  </si>
-  <si>
-    <t>Health</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -184,12 +184,12 @@
     <t>Basic health care</t>
   </si>
   <si>
+    <t>Basic Health</t>
+  </si>
+  <si>
     <t>122</t>
   </si>
   <si>
-    <t>Basic Health</t>
-  </si>
-  <si>
     <t>12230</t>
   </si>
   <si>
@@ -238,12 +238,12 @@
     <t>NCDs control, general</t>
   </si>
   <si>
+    <t>Non-communicable diseases (NCDs)</t>
+  </si>
+  <si>
     <t>123</t>
   </si>
   <si>
-    <t>Non-communicable diseases (NCDs)</t>
-  </si>
-  <si>
     <t>12320</t>
   </si>
   <si>
@@ -388,18 +388,18 @@
     <t>Public sector policy and administrative management</t>
   </si>
   <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>Government &amp; Civil Society</t>
+  </si>
+  <si>
+    <t>Government &amp; Civil Society-general</t>
+  </si>
+  <si>
     <t>151</t>
   </si>
   <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>Government &amp; Civil Society-general</t>
-  </si>
-  <si>
-    <t>Government &amp; Civil Society</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -496,12 +496,12 @@
     <t>Security system management and reform</t>
   </si>
   <si>
+    <t>Conflict, Peace &amp; Security</t>
+  </si>
+  <si>
     <t>152</t>
   </si>
   <si>
-    <t>Conflict, Peace &amp; Security</t>
-  </si>
-  <si>
     <t>15220</t>
   </si>
   <si>
@@ -688,18 +688,18 @@
     <t>Energy policy and administrative management</t>
   </si>
   <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>Energy</t>
+  </si>
+  <si>
+    <t>Energy Policy</t>
+  </si>
+  <si>
     <t>231</t>
   </si>
   <si>
-    <t>230</t>
-  </si>
-  <si>
-    <t>Energy Policy</t>
-  </si>
-  <si>
-    <t>Energy</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -724,12 +724,12 @@
     <t>Energy generation, renewable sources - multiple technologies</t>
   </si>
   <si>
+    <t>Energy generation, renewable sources</t>
+  </si>
+  <si>
     <t>232</t>
   </si>
   <si>
-    <t>Energy generation, renewable sources</t>
-  </si>
-  <si>
     <t>23220</t>
   </si>
   <si>
@@ -784,12 +784,12 @@
     <t>Energy generation, non-renewable sources, unspecified</t>
   </si>
   <si>
+    <t>Energy generation, non-renewable sources</t>
+  </si>
+  <si>
     <t>233</t>
   </si>
   <si>
-    <t>Energy generation, non-renewable sources</t>
-  </si>
-  <si>
     <t>23320</t>
   </si>
   <si>
@@ -826,36 +826,36 @@
     <t>Hybrid energy electric power plants</t>
   </si>
   <si>
+    <t>Hybrid energy plants</t>
+  </si>
+  <si>
     <t>234</t>
   </si>
   <si>
-    <t>Hybrid energy plants</t>
-  </si>
-  <si>
     <t>23510</t>
   </si>
   <si>
     <t>Nuclear energy electric power plants and nuclear safety</t>
   </si>
   <si>
+    <t>Nuclear energy plants</t>
+  </si>
+  <si>
     <t>235</t>
   </si>
   <si>
-    <t>Nuclear energy plants</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
     <t>Heat plants</t>
   </si>
   <si>
+    <t>Energy distribution</t>
+  </si>
+  <si>
     <t>236</t>
   </si>
   <si>
-    <t>Energy distribution</t>
-  </si>
-  <si>
     <t>23620</t>
   </si>
   <si>
@@ -970,18 +970,18 @@
     <t>Agricultural policy and administrative management</t>
   </si>
   <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>Agriculture, Forestry, Fishing</t>
+  </si>
+  <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
     <t>311</t>
   </si>
   <si>
-    <t>310</t>
-  </si>
-  <si>
-    <t>Agriculture</t>
-  </si>
-  <si>
-    <t>Agriculture, Forestry, Fishing</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1090,12 +1090,12 @@
     <t>Forestry policy and administrative management</t>
   </si>
   <si>
+    <t>Forestry</t>
+  </si>
+  <si>
     <t>312</t>
   </si>
   <si>
-    <t>Forestry</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -1132,12 +1132,12 @@
     <t>Fishing policy and administrative management</t>
   </si>
   <si>
+    <t>Fishing</t>
+  </si>
+  <si>
     <t>313</t>
   </si>
   <si>
-    <t>Fishing</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -1168,18 +1168,18 @@
     <t>Industrial policy and administrative management</t>
   </si>
   <si>
+    <t>320</t>
+  </si>
+  <si>
+    <t>Industry, Mining, Construction</t>
+  </si>
+  <si>
+    <t>Industry</t>
+  </si>
+  <si>
     <t>321</t>
   </si>
   <si>
-    <t>320</t>
-  </si>
-  <si>
-    <t>Industry</t>
-  </si>
-  <si>
-    <t>Industry, Mining, Construction</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1294,12 +1294,12 @@
     <t>Mineral/mining policy and administrative management</t>
   </si>
   <si>
+    <t>Mineral Resources &amp; Mining</t>
+  </si>
+  <si>
     <t>322</t>
   </si>
   <si>
-    <t>Mineral Resources &amp; Mining</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -1360,10 +1360,10 @@
     <t>Construction policy and administrative management</t>
   </si>
   <si>
+    <t>Construction</t>
+  </si>
+  <si>
     <t>323</t>
-  </si>
-  <si>
-    <t>Construction</t>
   </si>
   <si>
     <t>33110</t>
@@ -2166,16 +2166,16 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E6" t="s">
         <v>11</v>
       </c>
       <c r="F6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" t="s">
         <v>23</v>
-      </c>
-      <c r="G6" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2189,16 +2189,16 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
       </c>
       <c r="F7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" t="s">
         <v>23</v>
-      </c>
-      <c r="G7" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2212,16 +2212,16 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E8" t="s">
         <v>11</v>
       </c>
       <c r="F8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" t="s">
         <v>23</v>
-      </c>
-      <c r="G8" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2235,16 +2235,16 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
       </c>
       <c r="F9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" t="s">
         <v>23</v>
-      </c>
-      <c r="G9" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2258,16 +2258,16 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="E10" t="s">
         <v>11</v>
       </c>
       <c r="F10" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" t="s">
         <v>33</v>
-      </c>
-      <c r="G10" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2281,16 +2281,16 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="E11" t="s">
         <v>11</v>
       </c>
       <c r="F11" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" t="s">
         <v>33</v>
-      </c>
-      <c r="G11" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2304,16 +2304,16 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="E12" t="s">
         <v>11</v>
       </c>
       <c r="F12" t="s">
+        <v>38</v>
+      </c>
+      <c r="G12" t="s">
         <v>39</v>
-      </c>
-      <c r="G12" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2327,16 +2327,16 @@
         <v>9</v>
       </c>
       <c r="D13" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="E13" t="s">
         <v>11</v>
       </c>
       <c r="F13" t="s">
+        <v>38</v>
+      </c>
+      <c r="G13" t="s">
         <v>39</v>
-      </c>
-      <c r="G13" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2442,16 +2442,16 @@
         <v>9</v>
       </c>
       <c r="D18" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E18" t="s">
         <v>45</v>
       </c>
       <c r="F18" t="s">
+        <v>56</v>
+      </c>
+      <c r="G18" t="s">
         <v>57</v>
-      </c>
-      <c r="G18" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2465,16 +2465,16 @@
         <v>9</v>
       </c>
       <c r="D19" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E19" t="s">
         <v>45</v>
       </c>
       <c r="F19" t="s">
+        <v>56</v>
+      </c>
+      <c r="G19" t="s">
         <v>57</v>
-      </c>
-      <c r="G19" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2488,16 +2488,16 @@
         <v>9</v>
       </c>
       <c r="D20" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E20" t="s">
         <v>45</v>
       </c>
       <c r="F20" t="s">
+        <v>56</v>
+      </c>
+      <c r="G20" t="s">
         <v>57</v>
-      </c>
-      <c r="G20" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2511,16 +2511,16 @@
         <v>9</v>
       </c>
       <c r="D21" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E21" t="s">
         <v>45</v>
       </c>
       <c r="F21" t="s">
+        <v>56</v>
+      </c>
+      <c r="G21" t="s">
         <v>57</v>
-      </c>
-      <c r="G21" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2534,16 +2534,16 @@
         <v>9</v>
       </c>
       <c r="D22" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E22" t="s">
         <v>45</v>
       </c>
       <c r="F22" t="s">
+        <v>56</v>
+      </c>
+      <c r="G22" t="s">
         <v>57</v>
-      </c>
-      <c r="G22" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2557,16 +2557,16 @@
         <v>9</v>
       </c>
       <c r="D23" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E23" t="s">
         <v>45</v>
       </c>
       <c r="F23" t="s">
+        <v>56</v>
+      </c>
+      <c r="G23" t="s">
         <v>57</v>
-      </c>
-      <c r="G23" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2580,16 +2580,16 @@
         <v>9</v>
       </c>
       <c r="D24" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E24" t="s">
         <v>45</v>
       </c>
       <c r="F24" t="s">
+        <v>56</v>
+      </c>
+      <c r="G24" t="s">
         <v>57</v>
-      </c>
-      <c r="G24" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2603,16 +2603,16 @@
         <v>9</v>
       </c>
       <c r="D25" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E25" t="s">
         <v>45</v>
       </c>
       <c r="F25" t="s">
+        <v>56</v>
+      </c>
+      <c r="G25" t="s">
         <v>57</v>
-      </c>
-      <c r="G25" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2626,16 +2626,16 @@
         <v>9</v>
       </c>
       <c r="D26" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="E26" t="s">
         <v>45</v>
       </c>
       <c r="F26" t="s">
+        <v>74</v>
+      </c>
+      <c r="G26" t="s">
         <v>75</v>
-      </c>
-      <c r="G26" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2649,16 +2649,16 @@
         <v>9</v>
       </c>
       <c r="D27" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="E27" t="s">
         <v>45</v>
       </c>
       <c r="F27" t="s">
+        <v>74</v>
+      </c>
+      <c r="G27" t="s">
         <v>75</v>
-      </c>
-      <c r="G27" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2672,16 +2672,16 @@
         <v>9</v>
       </c>
       <c r="D28" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="E28" t="s">
         <v>45</v>
       </c>
       <c r="F28" t="s">
+        <v>74</v>
+      </c>
+      <c r="G28" t="s">
         <v>75</v>
-      </c>
-      <c r="G28" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2695,16 +2695,16 @@
         <v>9</v>
       </c>
       <c r="D29" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="E29" t="s">
         <v>45</v>
       </c>
       <c r="F29" t="s">
+        <v>74</v>
+      </c>
+      <c r="G29" t="s">
         <v>75</v>
-      </c>
-      <c r="G29" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2718,16 +2718,16 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="E30" t="s">
         <v>45</v>
       </c>
       <c r="F30" t="s">
+        <v>74</v>
+      </c>
+      <c r="G30" t="s">
         <v>75</v>
-      </c>
-      <c r="G30" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2741,16 +2741,16 @@
         <v>9</v>
       </c>
       <c r="D31" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="E31" t="s">
         <v>45</v>
       </c>
       <c r="F31" t="s">
+        <v>74</v>
+      </c>
+      <c r="G31" t="s">
         <v>75</v>
-      </c>
-      <c r="G31" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2767,13 +2767,13 @@
         <v>88</v>
       </c>
       <c r="E32" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F32" t="s">
         <v>89</v>
       </c>
       <c r="G32" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2790,13 +2790,13 @@
         <v>88</v>
       </c>
       <c r="E33" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F33" t="s">
         <v>89</v>
       </c>
       <c r="G33" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2813,13 +2813,13 @@
         <v>88</v>
       </c>
       <c r="E34" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F34" t="s">
         <v>89</v>
       </c>
       <c r="G34" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2836,13 +2836,13 @@
         <v>88</v>
       </c>
       <c r="E35" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F35" t="s">
         <v>89</v>
       </c>
       <c r="G35" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2859,13 +2859,13 @@
         <v>88</v>
       </c>
       <c r="E36" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F36" t="s">
         <v>89</v>
       </c>
       <c r="G36" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2882,13 +2882,13 @@
         <v>100</v>
       </c>
       <c r="E37" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F37" t="s">
         <v>101</v>
       </c>
       <c r="G37" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2905,13 +2905,13 @@
         <v>100</v>
       </c>
       <c r="E38" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F38" t="s">
         <v>101</v>
       </c>
       <c r="G38" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2928,13 +2928,13 @@
         <v>100</v>
       </c>
       <c r="E39" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F39" t="s">
         <v>101</v>
       </c>
       <c r="G39" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2951,13 +2951,13 @@
         <v>100</v>
       </c>
       <c r="E40" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F40" t="s">
         <v>101</v>
       </c>
       <c r="G40" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2974,13 +2974,13 @@
         <v>100</v>
       </c>
       <c r="E41" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F41" t="s">
         <v>101</v>
       </c>
       <c r="G41" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2997,13 +2997,13 @@
         <v>100</v>
       </c>
       <c r="E42" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F42" t="s">
         <v>101</v>
       </c>
       <c r="G42" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3020,13 +3020,13 @@
         <v>100</v>
       </c>
       <c r="E43" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F43" t="s">
         <v>101</v>
       </c>
       <c r="G43" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3043,13 +3043,13 @@
         <v>100</v>
       </c>
       <c r="E44" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F44" t="s">
         <v>101</v>
       </c>
       <c r="G44" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3066,13 +3066,13 @@
         <v>100</v>
       </c>
       <c r="E45" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F45" t="s">
         <v>101</v>
       </c>
       <c r="G45" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3089,13 +3089,13 @@
         <v>100</v>
       </c>
       <c r="E46" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F46" t="s">
         <v>101</v>
       </c>
       <c r="G46" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3112,13 +3112,13 @@
         <v>100</v>
       </c>
       <c r="E47" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F47" t="s">
         <v>101</v>
       </c>
       <c r="G47" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3500,16 +3500,16 @@
         <v>9</v>
       </c>
       <c r="D64" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="E64" t="s">
         <v>125</v>
       </c>
       <c r="F64" t="s">
+        <v>160</v>
+      </c>
+      <c r="G64" t="s">
         <v>161</v>
-      </c>
-      <c r="G64" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3523,16 +3523,16 @@
         <v>9</v>
       </c>
       <c r="D65" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="E65" t="s">
         <v>125</v>
       </c>
       <c r="F65" t="s">
+        <v>160</v>
+      </c>
+      <c r="G65" t="s">
         <v>161</v>
-      </c>
-      <c r="G65" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3546,16 +3546,16 @@
         <v>9</v>
       </c>
       <c r="D66" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="E66" t="s">
         <v>125</v>
       </c>
       <c r="F66" t="s">
+        <v>160</v>
+      </c>
+      <c r="G66" t="s">
         <v>161</v>
-      </c>
-      <c r="G66" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3569,16 +3569,16 @@
         <v>9</v>
       </c>
       <c r="D67" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="E67" t="s">
         <v>125</v>
       </c>
       <c r="F67" t="s">
+        <v>160</v>
+      </c>
+      <c r="G67" t="s">
         <v>161</v>
-      </c>
-      <c r="G67" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3592,16 +3592,16 @@
         <v>9</v>
       </c>
       <c r="D68" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="E68" t="s">
         <v>125</v>
       </c>
       <c r="F68" t="s">
+        <v>160</v>
+      </c>
+      <c r="G68" t="s">
         <v>161</v>
-      </c>
-      <c r="G68" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3615,16 +3615,16 @@
         <v>9</v>
       </c>
       <c r="D69" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="E69" t="s">
         <v>125</v>
       </c>
       <c r="F69" t="s">
+        <v>160</v>
+      </c>
+      <c r="G69" t="s">
         <v>161</v>
-      </c>
-      <c r="G69" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3641,13 +3641,13 @@
         <v>174</v>
       </c>
       <c r="E70" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F70" t="s">
         <v>175</v>
       </c>
       <c r="G70" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3664,13 +3664,13 @@
         <v>174</v>
       </c>
       <c r="E71" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F71" t="s">
         <v>175</v>
       </c>
       <c r="G71" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3687,13 +3687,13 @@
         <v>174</v>
       </c>
       <c r="E72" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F72" t="s">
         <v>175</v>
       </c>
       <c r="G72" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3710,13 +3710,13 @@
         <v>174</v>
       </c>
       <c r="E73" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F73" t="s">
         <v>175</v>
       </c>
       <c r="G73" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3733,13 +3733,13 @@
         <v>174</v>
       </c>
       <c r="E74" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F74" t="s">
         <v>175</v>
       </c>
       <c r="G74" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3756,13 +3756,13 @@
         <v>174</v>
       </c>
       <c r="E75" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F75" t="s">
         <v>175</v>
       </c>
       <c r="G75" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3779,13 +3779,13 @@
         <v>174</v>
       </c>
       <c r="E76" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F76" t="s">
         <v>175</v>
       </c>
       <c r="G76" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3802,13 +3802,13 @@
         <v>174</v>
       </c>
       <c r="E77" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F77" t="s">
         <v>175</v>
       </c>
       <c r="G77" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3825,13 +3825,13 @@
         <v>174</v>
       </c>
       <c r="E78" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F78" t="s">
         <v>175</v>
       </c>
       <c r="G78" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3848,13 +3848,13 @@
         <v>174</v>
       </c>
       <c r="E79" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F79" t="s">
         <v>175</v>
       </c>
       <c r="G79" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3871,13 +3871,13 @@
         <v>174</v>
       </c>
       <c r="E80" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F80" t="s">
         <v>175</v>
       </c>
       <c r="G80" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3894,13 +3894,13 @@
         <v>198</v>
       </c>
       <c r="E81" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F81" t="s">
         <v>199</v>
       </c>
       <c r="G81" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3917,13 +3917,13 @@
         <v>198</v>
       </c>
       <c r="E82" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F82" t="s">
         <v>199</v>
       </c>
       <c r="G82" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3940,13 +3940,13 @@
         <v>198</v>
       </c>
       <c r="E83" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F83" t="s">
         <v>199</v>
       </c>
       <c r="G83" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3963,13 +3963,13 @@
         <v>198</v>
       </c>
       <c r="E84" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F84" t="s">
         <v>199</v>
       </c>
       <c r="G84" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3986,13 +3986,13 @@
         <v>198</v>
       </c>
       <c r="E85" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F85" t="s">
         <v>199</v>
       </c>
       <c r="G85" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4009,13 +4009,13 @@
         <v>198</v>
       </c>
       <c r="E86" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F86" t="s">
         <v>199</v>
       </c>
       <c r="G86" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4032,13 +4032,13 @@
         <v>198</v>
       </c>
       <c r="E87" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F87" t="s">
         <v>199</v>
       </c>
       <c r="G87" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4055,13 +4055,13 @@
         <v>214</v>
       </c>
       <c r="E88" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F88" t="s">
         <v>215</v>
       </c>
       <c r="G88" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4078,13 +4078,13 @@
         <v>214</v>
       </c>
       <c r="E89" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F89" t="s">
         <v>215</v>
       </c>
       <c r="G89" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4101,13 +4101,13 @@
         <v>214</v>
       </c>
       <c r="E90" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F90" t="s">
         <v>215</v>
       </c>
       <c r="G90" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4124,13 +4124,13 @@
         <v>214</v>
       </c>
       <c r="E91" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F91" t="s">
         <v>215</v>
       </c>
       <c r="G91" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4236,16 +4236,16 @@
         <v>9</v>
       </c>
       <c r="D96" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E96" t="s">
         <v>225</v>
       </c>
       <c r="F96" t="s">
+        <v>236</v>
+      </c>
+      <c r="G96" t="s">
         <v>237</v>
-      </c>
-      <c r="G96" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -4259,16 +4259,16 @@
         <v>9</v>
       </c>
       <c r="D97" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E97" t="s">
         <v>225</v>
       </c>
       <c r="F97" t="s">
+        <v>236</v>
+      </c>
+      <c r="G97" t="s">
         <v>237</v>
-      </c>
-      <c r="G97" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4282,16 +4282,16 @@
         <v>9</v>
       </c>
       <c r="D98" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E98" t="s">
         <v>225</v>
       </c>
       <c r="F98" t="s">
+        <v>236</v>
+      </c>
+      <c r="G98" t="s">
         <v>237</v>
-      </c>
-      <c r="G98" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4305,16 +4305,16 @@
         <v>9</v>
       </c>
       <c r="D99" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E99" t="s">
         <v>225</v>
       </c>
       <c r="F99" t="s">
+        <v>236</v>
+      </c>
+      <c r="G99" t="s">
         <v>237</v>
-      </c>
-      <c r="G99" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4328,16 +4328,16 @@
         <v>9</v>
       </c>
       <c r="D100" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E100" t="s">
         <v>225</v>
       </c>
       <c r="F100" t="s">
+        <v>236</v>
+      </c>
+      <c r="G100" t="s">
         <v>237</v>
-      </c>
-      <c r="G100" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4351,16 +4351,16 @@
         <v>9</v>
       </c>
       <c r="D101" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E101" t="s">
         <v>225</v>
       </c>
       <c r="F101" t="s">
+        <v>236</v>
+      </c>
+      <c r="G101" t="s">
         <v>237</v>
-      </c>
-      <c r="G101" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4374,16 +4374,16 @@
         <v>9</v>
       </c>
       <c r="D102" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E102" t="s">
         <v>225</v>
       </c>
       <c r="F102" t="s">
+        <v>236</v>
+      </c>
+      <c r="G102" t="s">
         <v>237</v>
-      </c>
-      <c r="G102" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4397,16 +4397,16 @@
         <v>9</v>
       </c>
       <c r="D103" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E103" t="s">
         <v>225</v>
       </c>
       <c r="F103" t="s">
+        <v>236</v>
+      </c>
+      <c r="G103" t="s">
         <v>237</v>
-      </c>
-      <c r="G103" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4420,16 +4420,16 @@
         <v>9</v>
       </c>
       <c r="D104" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E104" t="s">
         <v>225</v>
       </c>
       <c r="F104" t="s">
+        <v>236</v>
+      </c>
+      <c r="G104" t="s">
         <v>237</v>
-      </c>
-      <c r="G104" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4443,16 +4443,16 @@
         <v>9</v>
       </c>
       <c r="D105" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="E105" t="s">
         <v>225</v>
       </c>
       <c r="F105" t="s">
+        <v>256</v>
+      </c>
+      <c r="G105" t="s">
         <v>257</v>
-      </c>
-      <c r="G105" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4466,16 +4466,16 @@
         <v>9</v>
       </c>
       <c r="D106" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="E106" t="s">
         <v>225</v>
       </c>
       <c r="F106" t="s">
+        <v>256</v>
+      </c>
+      <c r="G106" t="s">
         <v>257</v>
-      </c>
-      <c r="G106" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4489,16 +4489,16 @@
         <v>9</v>
       </c>
       <c r="D107" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="E107" t="s">
         <v>225</v>
       </c>
       <c r="F107" t="s">
+        <v>256</v>
+      </c>
+      <c r="G107" t="s">
         <v>257</v>
-      </c>
-      <c r="G107" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4512,16 +4512,16 @@
         <v>9</v>
       </c>
       <c r="D108" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="E108" t="s">
         <v>225</v>
       </c>
       <c r="F108" t="s">
+        <v>256</v>
+      </c>
+      <c r="G108" t="s">
         <v>257</v>
-      </c>
-      <c r="G108" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4535,16 +4535,16 @@
         <v>9</v>
       </c>
       <c r="D109" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="E109" t="s">
         <v>225</v>
       </c>
       <c r="F109" t="s">
+        <v>256</v>
+      </c>
+      <c r="G109" t="s">
         <v>257</v>
-      </c>
-      <c r="G109" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4558,16 +4558,16 @@
         <v>9</v>
       </c>
       <c r="D110" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="E110" t="s">
         <v>225</v>
       </c>
       <c r="F110" t="s">
+        <v>256</v>
+      </c>
+      <c r="G110" t="s">
         <v>257</v>
-      </c>
-      <c r="G110" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4581,16 +4581,16 @@
         <v>9</v>
       </c>
       <c r="D111" t="s">
-        <v>270</v>
+        <v>224</v>
       </c>
       <c r="E111" t="s">
         <v>225</v>
       </c>
       <c r="F111" t="s">
+        <v>270</v>
+      </c>
+      <c r="G111" t="s">
         <v>271</v>
-      </c>
-      <c r="G111" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4604,16 +4604,16 @@
         <v>9</v>
       </c>
       <c r="D112" t="s">
-        <v>274</v>
+        <v>224</v>
       </c>
       <c r="E112" t="s">
         <v>225</v>
       </c>
       <c r="F112" t="s">
+        <v>274</v>
+      </c>
+      <c r="G112" t="s">
         <v>275</v>
-      </c>
-      <c r="G112" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4627,16 +4627,16 @@
         <v>9</v>
       </c>
       <c r="D113" t="s">
-        <v>278</v>
+        <v>224</v>
       </c>
       <c r="E113" t="s">
         <v>225</v>
       </c>
       <c r="F113" t="s">
+        <v>278</v>
+      </c>
+      <c r="G113" t="s">
         <v>279</v>
-      </c>
-      <c r="G113" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4650,16 +4650,16 @@
         <v>9</v>
       </c>
       <c r="D114" t="s">
-        <v>278</v>
+        <v>224</v>
       </c>
       <c r="E114" t="s">
         <v>225</v>
       </c>
       <c r="F114" t="s">
+        <v>278</v>
+      </c>
+      <c r="G114" t="s">
         <v>279</v>
-      </c>
-      <c r="G114" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4673,16 +4673,16 @@
         <v>9</v>
       </c>
       <c r="D115" t="s">
-        <v>278</v>
+        <v>224</v>
       </c>
       <c r="E115" t="s">
         <v>225</v>
       </c>
       <c r="F115" t="s">
+        <v>278</v>
+      </c>
+      <c r="G115" t="s">
         <v>279</v>
-      </c>
-      <c r="G115" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4696,16 +4696,16 @@
         <v>9</v>
       </c>
       <c r="D116" t="s">
-        <v>278</v>
+        <v>224</v>
       </c>
       <c r="E116" t="s">
         <v>225</v>
       </c>
       <c r="F116" t="s">
+        <v>278</v>
+      </c>
+      <c r="G116" t="s">
         <v>279</v>
-      </c>
-      <c r="G116" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4719,16 +4719,16 @@
         <v>9</v>
       </c>
       <c r="D117" t="s">
-        <v>278</v>
+        <v>224</v>
       </c>
       <c r="E117" t="s">
         <v>225</v>
       </c>
       <c r="F117" t="s">
+        <v>278</v>
+      </c>
+      <c r="G117" t="s">
         <v>279</v>
-      </c>
-      <c r="G117" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4742,16 +4742,16 @@
         <v>9</v>
       </c>
       <c r="D118" t="s">
-        <v>278</v>
+        <v>224</v>
       </c>
       <c r="E118" t="s">
         <v>225</v>
       </c>
       <c r="F118" t="s">
+        <v>278</v>
+      </c>
+      <c r="G118" t="s">
         <v>279</v>
-      </c>
-      <c r="G118" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4765,16 +4765,16 @@
         <v>9</v>
       </c>
       <c r="D119" t="s">
-        <v>278</v>
+        <v>224</v>
       </c>
       <c r="E119" t="s">
         <v>225</v>
       </c>
       <c r="F119" t="s">
+        <v>278</v>
+      </c>
+      <c r="G119" t="s">
         <v>279</v>
-      </c>
-      <c r="G119" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4791,13 +4791,13 @@
         <v>294</v>
       </c>
       <c r="E120" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F120" t="s">
         <v>295</v>
       </c>
       <c r="G120" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4814,13 +4814,13 @@
         <v>294</v>
       </c>
       <c r="E121" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F121" t="s">
         <v>295</v>
       </c>
       <c r="G121" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4837,13 +4837,13 @@
         <v>294</v>
       </c>
       <c r="E122" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F122" t="s">
         <v>295</v>
       </c>
       <c r="G122" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4860,13 +4860,13 @@
         <v>294</v>
       </c>
       <c r="E123" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F123" t="s">
         <v>295</v>
       </c>
       <c r="G123" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4883,13 +4883,13 @@
         <v>294</v>
       </c>
       <c r="E124" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F124" t="s">
         <v>295</v>
       </c>
       <c r="G124" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4906,13 +4906,13 @@
         <v>294</v>
       </c>
       <c r="E125" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F125" t="s">
         <v>295</v>
       </c>
       <c r="G125" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4929,13 +4929,13 @@
         <v>308</v>
       </c>
       <c r="E126" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F126" t="s">
         <v>309</v>
       </c>
       <c r="G126" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4952,13 +4952,13 @@
         <v>308</v>
       </c>
       <c r="E127" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F127" t="s">
         <v>309</v>
       </c>
       <c r="G127" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4975,13 +4975,13 @@
         <v>308</v>
       </c>
       <c r="E128" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F128" t="s">
         <v>309</v>
       </c>
       <c r="G128" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4998,13 +4998,13 @@
         <v>308</v>
       </c>
       <c r="E129" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F129" t="s">
         <v>309</v>
       </c>
       <c r="G129" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -5432,16 +5432,16 @@
         <v>9</v>
       </c>
       <c r="D148" t="s">
-        <v>358</v>
+        <v>318</v>
       </c>
       <c r="E148" t="s">
         <v>319</v>
       </c>
       <c r="F148" t="s">
+        <v>358</v>
+      </c>
+      <c r="G148" t="s">
         <v>359</v>
-      </c>
-      <c r="G148" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5455,16 +5455,16 @@
         <v>9</v>
       </c>
       <c r="D149" t="s">
-        <v>358</v>
+        <v>318</v>
       </c>
       <c r="E149" t="s">
         <v>319</v>
       </c>
       <c r="F149" t="s">
+        <v>358</v>
+      </c>
+      <c r="G149" t="s">
         <v>359</v>
-      </c>
-      <c r="G149" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5478,16 +5478,16 @@
         <v>9</v>
       </c>
       <c r="D150" t="s">
-        <v>358</v>
+        <v>318</v>
       </c>
       <c r="E150" t="s">
         <v>319</v>
       </c>
       <c r="F150" t="s">
+        <v>358</v>
+      </c>
+      <c r="G150" t="s">
         <v>359</v>
-      </c>
-      <c r="G150" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5501,16 +5501,16 @@
         <v>9</v>
       </c>
       <c r="D151" t="s">
-        <v>358</v>
+        <v>318</v>
       </c>
       <c r="E151" t="s">
         <v>319</v>
       </c>
       <c r="F151" t="s">
+        <v>358</v>
+      </c>
+      <c r="G151" t="s">
         <v>359</v>
-      </c>
-      <c r="G151" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5524,16 +5524,16 @@
         <v>9</v>
       </c>
       <c r="D152" t="s">
-        <v>358</v>
+        <v>318</v>
       </c>
       <c r="E152" t="s">
         <v>319</v>
       </c>
       <c r="F152" t="s">
+        <v>358</v>
+      </c>
+      <c r="G152" t="s">
         <v>359</v>
-      </c>
-      <c r="G152" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5547,16 +5547,16 @@
         <v>9</v>
       </c>
       <c r="D153" t="s">
-        <v>358</v>
+        <v>318</v>
       </c>
       <c r="E153" t="s">
         <v>319</v>
       </c>
       <c r="F153" t="s">
+        <v>358</v>
+      </c>
+      <c r="G153" t="s">
         <v>359</v>
-      </c>
-      <c r="G153" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5570,16 +5570,16 @@
         <v>9</v>
       </c>
       <c r="D154" t="s">
-        <v>372</v>
+        <v>318</v>
       </c>
       <c r="E154" t="s">
         <v>319</v>
       </c>
       <c r="F154" t="s">
+        <v>372</v>
+      </c>
+      <c r="G154" t="s">
         <v>373</v>
-      </c>
-      <c r="G154" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5593,16 +5593,16 @@
         <v>9</v>
       </c>
       <c r="D155" t="s">
-        <v>372</v>
+        <v>318</v>
       </c>
       <c r="E155" t="s">
         <v>319</v>
       </c>
       <c r="F155" t="s">
+        <v>372</v>
+      </c>
+      <c r="G155" t="s">
         <v>373</v>
-      </c>
-      <c r="G155" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5616,16 +5616,16 @@
         <v>9</v>
       </c>
       <c r="D156" t="s">
-        <v>372</v>
+        <v>318</v>
       </c>
       <c r="E156" t="s">
         <v>319</v>
       </c>
       <c r="F156" t="s">
+        <v>372</v>
+      </c>
+      <c r="G156" t="s">
         <v>373</v>
-      </c>
-      <c r="G156" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5639,16 +5639,16 @@
         <v>9</v>
       </c>
       <c r="D157" t="s">
-        <v>372</v>
+        <v>318</v>
       </c>
       <c r="E157" t="s">
         <v>319</v>
       </c>
       <c r="F157" t="s">
+        <v>372</v>
+      </c>
+      <c r="G157" t="s">
         <v>373</v>
-      </c>
-      <c r="G157" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5662,16 +5662,16 @@
         <v>9</v>
       </c>
       <c r="D158" t="s">
-        <v>372</v>
+        <v>318</v>
       </c>
       <c r="E158" t="s">
         <v>319</v>
       </c>
       <c r="F158" t="s">
+        <v>372</v>
+      </c>
+      <c r="G158" t="s">
         <v>373</v>
-      </c>
-      <c r="G158" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -6122,16 +6122,16 @@
         <v>9</v>
       </c>
       <c r="D178" t="s">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="E178" t="s">
         <v>385</v>
       </c>
       <c r="F178" t="s">
+        <v>426</v>
+      </c>
+      <c r="G178" t="s">
         <v>427</v>
-      </c>
-      <c r="G178" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -6145,16 +6145,16 @@
         <v>9</v>
       </c>
       <c r="D179" t="s">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="E179" t="s">
         <v>385</v>
       </c>
       <c r="F179" t="s">
+        <v>426</v>
+      </c>
+      <c r="G179" t="s">
         <v>427</v>
-      </c>
-      <c r="G179" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -6168,16 +6168,16 @@
         <v>9</v>
       </c>
       <c r="D180" t="s">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="E180" t="s">
         <v>385</v>
       </c>
       <c r="F180" t="s">
+        <v>426</v>
+      </c>
+      <c r="G180" t="s">
         <v>427</v>
-      </c>
-      <c r="G180" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -6191,16 +6191,16 @@
         <v>9</v>
       </c>
       <c r="D181" t="s">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="E181" t="s">
         <v>385</v>
       </c>
       <c r="F181" t="s">
+        <v>426</v>
+      </c>
+      <c r="G181" t="s">
         <v>427</v>
-      </c>
-      <c r="G181" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -6214,16 +6214,16 @@
         <v>9</v>
       </c>
       <c r="D182" t="s">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="E182" t="s">
         <v>385</v>
       </c>
       <c r="F182" t="s">
+        <v>426</v>
+      </c>
+      <c r="G182" t="s">
         <v>427</v>
-      </c>
-      <c r="G182" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -6237,16 +6237,16 @@
         <v>9</v>
       </c>
       <c r="D183" t="s">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="E183" t="s">
         <v>385</v>
       </c>
       <c r="F183" t="s">
+        <v>426</v>
+      </c>
+      <c r="G183" t="s">
         <v>427</v>
-      </c>
-      <c r="G183" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -6260,16 +6260,16 @@
         <v>9</v>
       </c>
       <c r="D184" t="s">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="E184" t="s">
         <v>385</v>
       </c>
       <c r="F184" t="s">
+        <v>426</v>
+      </c>
+      <c r="G184" t="s">
         <v>427</v>
-      </c>
-      <c r="G184" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -6283,16 +6283,16 @@
         <v>9</v>
       </c>
       <c r="D185" t="s">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="E185" t="s">
         <v>385</v>
       </c>
       <c r="F185" t="s">
+        <v>426</v>
+      </c>
+      <c r="G185" t="s">
         <v>427</v>
-      </c>
-      <c r="G185" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -6306,16 +6306,16 @@
         <v>9</v>
       </c>
       <c r="D186" t="s">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="E186" t="s">
         <v>385</v>
       </c>
       <c r="F186" t="s">
+        <v>426</v>
+      </c>
+      <c r="G186" t="s">
         <v>427</v>
-      </c>
-      <c r="G186" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -6329,16 +6329,16 @@
         <v>9</v>
       </c>
       <c r="D187" t="s">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="E187" t="s">
         <v>385</v>
       </c>
       <c r="F187" t="s">
+        <v>426</v>
+      </c>
+      <c r="G187" t="s">
         <v>427</v>
-      </c>
-      <c r="G187" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -6352,16 +6352,16 @@
         <v>9</v>
       </c>
       <c r="D188" t="s">
-        <v>448</v>
+        <v>384</v>
       </c>
       <c r="E188" t="s">
         <v>385</v>
       </c>
       <c r="F188" t="s">
+        <v>448</v>
+      </c>
+      <c r="G188" t="s">
         <v>449</v>
-      </c>
-      <c r="G188" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -6378,13 +6378,13 @@
         <v>452</v>
       </c>
       <c r="E189" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F189" t="s">
         <v>453</v>
       </c>
       <c r="G189" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6401,13 +6401,13 @@
         <v>452</v>
       </c>
       <c r="E190" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F190" t="s">
         <v>453</v>
       </c>
       <c r="G190" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6424,13 +6424,13 @@
         <v>452</v>
       </c>
       <c r="E191" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F191" t="s">
         <v>453</v>
       </c>
       <c r="G191" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6447,13 +6447,13 @@
         <v>452</v>
       </c>
       <c r="E192" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F192" t="s">
         <v>453</v>
       </c>
       <c r="G192" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6470,13 +6470,13 @@
         <v>452</v>
       </c>
       <c r="E193" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F193" t="s">
         <v>453</v>
       </c>
       <c r="G193" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6493,13 +6493,13 @@
         <v>452</v>
       </c>
       <c r="E194" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F194" t="s">
         <v>453</v>
       </c>
       <c r="G194" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6516,13 +6516,13 @@
         <v>466</v>
       </c>
       <c r="E195" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="F195" t="s">
         <v>467</v>
       </c>
       <c r="G195" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6539,13 +6539,13 @@
         <v>470</v>
       </c>
       <c r="E196" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F196" t="s">
         <v>471</v>
       </c>
       <c r="G196" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6562,13 +6562,13 @@
         <v>470</v>
       </c>
       <c r="E197" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F197" t="s">
         <v>471</v>
       </c>
       <c r="G197" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6585,13 +6585,13 @@
         <v>470</v>
       </c>
       <c r="E198" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F198" t="s">
         <v>471</v>
       </c>
       <c r="G198" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6608,13 +6608,13 @@
         <v>470</v>
       </c>
       <c r="E199" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F199" t="s">
         <v>471</v>
       </c>
       <c r="G199" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6631,13 +6631,13 @@
         <v>470</v>
       </c>
       <c r="E200" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F200" t="s">
         <v>471</v>
       </c>
       <c r="G200" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6654,13 +6654,13 @@
         <v>470</v>
       </c>
       <c r="E201" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F201" t="s">
         <v>471</v>
       </c>
       <c r="G201" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6677,13 +6677,13 @@
         <v>484</v>
       </c>
       <c r="E202" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F202" t="s">
         <v>485</v>
       </c>
       <c r="G202" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6700,13 +6700,13 @@
         <v>484</v>
       </c>
       <c r="E203" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F203" t="s">
         <v>485</v>
       </c>
       <c r="G203" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6723,13 +6723,13 @@
         <v>484</v>
       </c>
       <c r="E204" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F204" t="s">
         <v>485</v>
       </c>
       <c r="G204" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6746,13 +6746,13 @@
         <v>484</v>
       </c>
       <c r="E205" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F205" t="s">
         <v>485</v>
       </c>
       <c r="G205" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6769,13 +6769,13 @@
         <v>484</v>
       </c>
       <c r="E206" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F206" t="s">
         <v>485</v>
       </c>
       <c r="G206" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6792,13 +6792,13 @@
         <v>484</v>
       </c>
       <c r="E207" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F207" t="s">
         <v>485</v>
       </c>
       <c r="G207" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6815,13 +6815,13 @@
         <v>484</v>
       </c>
       <c r="E208" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F208" t="s">
         <v>485</v>
       </c>
       <c r="G208" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6838,13 +6838,13 @@
         <v>484</v>
       </c>
       <c r="E209" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F209" t="s">
         <v>485</v>
       </c>
       <c r="G209" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6861,13 +6861,13 @@
         <v>484</v>
       </c>
       <c r="E210" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F210" t="s">
         <v>485</v>
       </c>
       <c r="G210" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6884,13 +6884,13 @@
         <v>484</v>
       </c>
       <c r="E211" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F211" t="s">
         <v>485</v>
       </c>
       <c r="G211" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6907,13 +6907,13 @@
         <v>506</v>
       </c>
       <c r="E212" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F212" t="s">
         <v>507</v>
       </c>
       <c r="G212" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6930,13 +6930,13 @@
         <v>510</v>
       </c>
       <c r="E213" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F213" t="s">
         <v>511</v>
       </c>
       <c r="G213" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6953,13 +6953,13 @@
         <v>514</v>
       </c>
       <c r="E214" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="F214" t="s">
         <v>515</v>
       </c>
       <c r="G214" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6976,13 +6976,13 @@
         <v>514</v>
       </c>
       <c r="E215" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="F215" t="s">
         <v>515</v>
       </c>
       <c r="G215" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6999,13 +6999,13 @@
         <v>520</v>
       </c>
       <c r="E216" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F216" t="s">
         <v>521</v>
       </c>
       <c r="G216" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -7022,13 +7022,13 @@
         <v>520</v>
       </c>
       <c r="E217" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F217" t="s">
         <v>521</v>
       </c>
       <c r="G217" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -7045,13 +7045,13 @@
         <v>520</v>
       </c>
       <c r="E218" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F218" t="s">
         <v>521</v>
       </c>
       <c r="G218" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -7068,13 +7068,13 @@
         <v>520</v>
       </c>
       <c r="E219" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F219" t="s">
         <v>521</v>
       </c>
       <c r="G219" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -7091,13 +7091,13 @@
         <v>520</v>
       </c>
       <c r="E220" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F220" t="s">
         <v>521</v>
       </c>
       <c r="G220" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -7114,13 +7114,13 @@
         <v>520</v>
       </c>
       <c r="E221" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F221" t="s">
         <v>521</v>
       </c>
       <c r="G221" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -7137,13 +7137,13 @@
         <v>520</v>
       </c>
       <c r="E222" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F222" t="s">
         <v>521</v>
       </c>
       <c r="G222" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -7160,13 +7160,13 @@
         <v>536</v>
       </c>
       <c r="E223" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F223" t="s">
         <v>537</v>
       </c>
       <c r="G223" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -7183,13 +7183,13 @@
         <v>536</v>
       </c>
       <c r="E224" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F224" t="s">
         <v>537</v>
       </c>
       <c r="G224" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -7206,13 +7206,13 @@
         <v>536</v>
       </c>
       <c r="E225" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F225" t="s">
         <v>537</v>
       </c>
       <c r="G225" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -7229,13 +7229,13 @@
         <v>544</v>
       </c>
       <c r="E226" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="F226" t="s">
         <v>545</v>
       </c>
       <c r="G226" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -7252,13 +7252,13 @@
         <v>548</v>
       </c>
       <c r="E227" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="F227" t="s">
         <v>549</v>
       </c>
       <c r="G227" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -7275,13 +7275,13 @@
         <v>552</v>
       </c>
       <c r="E228" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="F228" t="s">
         <v>553</v>
       </c>
       <c r="G228" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -7298,13 +7298,13 @@
         <v>556</v>
       </c>
       <c r="E229" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="F229" t="s">
         <v>557</v>
       </c>
       <c r="G229" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -7321,13 +7321,13 @@
         <v>560</v>
       </c>
       <c r="E230" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F230" t="s">
         <v>561</v>
       </c>
       <c r="G230" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -7344,13 +7344,13 @@
         <v>560</v>
       </c>
       <c r="E231" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F231" t="s">
         <v>561</v>
       </c>
       <c r="G231" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/en/SectorGroup.xlsx
+++ b/api/xlsx/en/SectorGroup.xlsx
@@ -25,18 +25,18 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
     <t>codeforiati:category-name</t>
   </si>
   <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -46,18 +46,18 @@
     <t>active</t>
   </si>
   <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
     <t>110</t>
   </si>
   <si>
-    <t>Education</t>
-  </si>
-  <si>
     <t>Education, Level Unspecified</t>
   </si>
   <si>
-    <t>111</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -82,12 +82,12 @@
     <t>Primary education</t>
   </si>
   <si>
+    <t>112</t>
+  </si>
+  <si>
     <t>Basic Education</t>
   </si>
   <si>
-    <t>112</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -112,12 +112,12 @@
     <t>Secondary education</t>
   </si>
   <si>
+    <t>113</t>
+  </si>
+  <si>
     <t>Secondary Education</t>
   </si>
   <si>
-    <t>113</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
@@ -130,12 +130,12 @@
     <t>Higher education</t>
   </si>
   <si>
+    <t>114</t>
+  </si>
+  <si>
     <t>Post-Secondary Education</t>
   </si>
   <si>
-    <t>114</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -148,18 +148,18 @@
     <t>Health policy and administrative management</t>
   </si>
   <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>Health</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
-    <t>Health</t>
-  </si>
-  <si>
     <t>Health, General</t>
   </si>
   <si>
-    <t>121</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -184,12 +184,12 @@
     <t>Basic health care</t>
   </si>
   <si>
+    <t>122</t>
+  </si>
+  <si>
     <t>Basic Health</t>
   </si>
   <si>
-    <t>122</t>
-  </si>
-  <si>
     <t>12230</t>
   </si>
   <si>
@@ -238,12 +238,12 @@
     <t>NCDs control, general</t>
   </si>
   <si>
+    <t>123</t>
+  </si>
+  <si>
     <t>Non-communicable diseases (NCDs)</t>
   </si>
   <si>
-    <t>123</t>
-  </si>
-  <si>
     <t>12320</t>
   </si>
   <si>
@@ -388,18 +388,18 @@
     <t>Public sector policy and administrative management</t>
   </si>
   <si>
+    <t>151</t>
+  </si>
+  <si>
+    <t>Government &amp; Civil Society</t>
+  </si>
+  <si>
     <t>150</t>
   </si>
   <si>
-    <t>Government &amp; Civil Society</t>
-  </si>
-  <si>
     <t>Government &amp; Civil Society-general</t>
   </si>
   <si>
-    <t>151</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -496,12 +496,12 @@
     <t>Security system management and reform</t>
   </si>
   <si>
+    <t>152</t>
+  </si>
+  <si>
     <t>Conflict, Peace &amp; Security</t>
   </si>
   <si>
-    <t>152</t>
-  </si>
-  <si>
     <t>15220</t>
   </si>
   <si>
@@ -688,18 +688,18 @@
     <t>Energy policy and administrative management</t>
   </si>
   <si>
+    <t>231</t>
+  </si>
+  <si>
+    <t>Energy</t>
+  </si>
+  <si>
     <t>230</t>
   </si>
   <si>
-    <t>Energy</t>
-  </si>
-  <si>
     <t>Energy Policy</t>
   </si>
   <si>
-    <t>231</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -724,12 +724,12 @@
     <t>Energy generation, renewable sources - multiple technologies</t>
   </si>
   <si>
+    <t>232</t>
+  </si>
+  <si>
     <t>Energy generation, renewable sources</t>
   </si>
   <si>
-    <t>232</t>
-  </si>
-  <si>
     <t>23220</t>
   </si>
   <si>
@@ -784,12 +784,12 @@
     <t>Energy generation, non-renewable sources, unspecified</t>
   </si>
   <si>
+    <t>233</t>
+  </si>
+  <si>
     <t>Energy generation, non-renewable sources</t>
   </si>
   <si>
-    <t>233</t>
-  </si>
-  <si>
     <t>23320</t>
   </si>
   <si>
@@ -826,36 +826,36 @@
     <t>Hybrid energy electric power plants</t>
   </si>
   <si>
+    <t>234</t>
+  </si>
+  <si>
     <t>Hybrid energy plants</t>
   </si>
   <si>
-    <t>234</t>
-  </si>
-  <si>
     <t>23510</t>
   </si>
   <si>
     <t>Nuclear energy electric power plants and nuclear safety</t>
   </si>
   <si>
+    <t>235</t>
+  </si>
+  <si>
     <t>Nuclear energy plants</t>
   </si>
   <si>
-    <t>235</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
     <t>Heat plants</t>
   </si>
   <si>
+    <t>236</t>
+  </si>
+  <si>
     <t>Energy distribution</t>
   </si>
   <si>
-    <t>236</t>
-  </si>
-  <si>
     <t>23620</t>
   </si>
   <si>
@@ -970,18 +970,18 @@
     <t>Agricultural policy and administrative management</t>
   </si>
   <si>
+    <t>311</t>
+  </si>
+  <si>
+    <t>Agriculture, Forestry, Fishing</t>
+  </si>
+  <si>
     <t>310</t>
   </si>
   <si>
-    <t>Agriculture, Forestry, Fishing</t>
-  </si>
-  <si>
     <t>Agriculture</t>
   </si>
   <si>
-    <t>311</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1090,12 +1090,12 @@
     <t>Forestry policy and administrative management</t>
   </si>
   <si>
+    <t>312</t>
+  </si>
+  <si>
     <t>Forestry</t>
   </si>
   <si>
-    <t>312</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -1132,12 +1132,12 @@
     <t>Fishing policy and administrative management</t>
   </si>
   <si>
+    <t>313</t>
+  </si>
+  <si>
     <t>Fishing</t>
   </si>
   <si>
-    <t>313</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -1168,18 +1168,18 @@
     <t>Industrial policy and administrative management</t>
   </si>
   <si>
+    <t>321</t>
+  </si>
+  <si>
+    <t>Industry, Mining, Construction</t>
+  </si>
+  <si>
     <t>320</t>
   </si>
   <si>
-    <t>Industry, Mining, Construction</t>
-  </si>
-  <si>
     <t>Industry</t>
   </si>
   <si>
-    <t>321</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1294,12 +1294,12 @@
     <t>Mineral/mining policy and administrative management</t>
   </si>
   <si>
+    <t>322</t>
+  </si>
+  <si>
     <t>Mineral Resources &amp; Mining</t>
   </si>
   <si>
-    <t>322</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -1360,10 +1360,10 @@
     <t>Construction policy and administrative management</t>
   </si>
   <si>
+    <t>323</t>
+  </si>
+  <si>
     <t>Construction</t>
-  </si>
-  <si>
-    <t>323</t>
   </si>
   <si>
     <t>33110</t>
@@ -2166,13 +2166,13 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
         <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G6" t="s">
         <v>23</v>
@@ -2189,13 +2189,13 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G7" t="s">
         <v>23</v>
@@ -2212,13 +2212,13 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E8" t="s">
         <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G8" t="s">
         <v>23</v>
@@ -2235,13 +2235,13 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G9" t="s">
         <v>23</v>
@@ -2258,13 +2258,13 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E10" t="s">
         <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="G10" t="s">
         <v>33</v>
@@ -2281,13 +2281,13 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
         <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="G11" t="s">
         <v>33</v>
@@ -2304,13 +2304,13 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E12" t="s">
         <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="G12" t="s">
         <v>39</v>
@@ -2327,13 +2327,13 @@
         <v>9</v>
       </c>
       <c r="D13" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E13" t="s">
         <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="G13" t="s">
         <v>39</v>
@@ -2442,13 +2442,13 @@
         <v>9</v>
       </c>
       <c r="D18" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E18" t="s">
         <v>45</v>
       </c>
       <c r="F18" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G18" t="s">
         <v>57</v>
@@ -2465,13 +2465,13 @@
         <v>9</v>
       </c>
       <c r="D19" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E19" t="s">
         <v>45</v>
       </c>
       <c r="F19" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G19" t="s">
         <v>57</v>
@@ -2488,13 +2488,13 @@
         <v>9</v>
       </c>
       <c r="D20" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E20" t="s">
         <v>45</v>
       </c>
       <c r="F20" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G20" t="s">
         <v>57</v>
@@ -2511,13 +2511,13 @@
         <v>9</v>
       </c>
       <c r="D21" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E21" t="s">
         <v>45</v>
       </c>
       <c r="F21" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G21" t="s">
         <v>57</v>
@@ -2534,13 +2534,13 @@
         <v>9</v>
       </c>
       <c r="D22" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E22" t="s">
         <v>45</v>
       </c>
       <c r="F22" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G22" t="s">
         <v>57</v>
@@ -2557,13 +2557,13 @@
         <v>9</v>
       </c>
       <c r="D23" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E23" t="s">
         <v>45</v>
       </c>
       <c r="F23" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G23" t="s">
         <v>57</v>
@@ -2580,13 +2580,13 @@
         <v>9</v>
       </c>
       <c r="D24" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E24" t="s">
         <v>45</v>
       </c>
       <c r="F24" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G24" t="s">
         <v>57</v>
@@ -2603,13 +2603,13 @@
         <v>9</v>
       </c>
       <c r="D25" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E25" t="s">
         <v>45</v>
       </c>
       <c r="F25" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G25" t="s">
         <v>57</v>
@@ -2626,13 +2626,13 @@
         <v>9</v>
       </c>
       <c r="D26" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E26" t="s">
         <v>45</v>
       </c>
       <c r="F26" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G26" t="s">
         <v>75</v>
@@ -2649,13 +2649,13 @@
         <v>9</v>
       </c>
       <c r="D27" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E27" t="s">
         <v>45</v>
       </c>
       <c r="F27" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G27" t="s">
         <v>75</v>
@@ -2672,13 +2672,13 @@
         <v>9</v>
       </c>
       <c r="D28" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E28" t="s">
         <v>45</v>
       </c>
       <c r="F28" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G28" t="s">
         <v>75</v>
@@ -2695,13 +2695,13 @@
         <v>9</v>
       </c>
       <c r="D29" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E29" t="s">
         <v>45</v>
       </c>
       <c r="F29" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G29" t="s">
         <v>75</v>
@@ -2718,13 +2718,13 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E30" t="s">
         <v>45</v>
       </c>
       <c r="F30" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G30" t="s">
         <v>75</v>
@@ -2741,13 +2741,13 @@
         <v>9</v>
       </c>
       <c r="D31" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E31" t="s">
         <v>45</v>
       </c>
       <c r="F31" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G31" t="s">
         <v>75</v>
@@ -2770,10 +2770,10 @@
         <v>89</v>
       </c>
       <c r="F32" t="s">
+        <v>88</v>
+      </c>
+      <c r="G32" t="s">
         <v>89</v>
-      </c>
-      <c r="G32" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2793,10 +2793,10 @@
         <v>89</v>
       </c>
       <c r="F33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G33" t="s">
         <v>89</v>
-      </c>
-      <c r="G33" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2816,10 +2816,10 @@
         <v>89</v>
       </c>
       <c r="F34" t="s">
+        <v>88</v>
+      </c>
+      <c r="G34" t="s">
         <v>89</v>
-      </c>
-      <c r="G34" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2839,10 +2839,10 @@
         <v>89</v>
       </c>
       <c r="F35" t="s">
+        <v>88</v>
+      </c>
+      <c r="G35" t="s">
         <v>89</v>
-      </c>
-      <c r="G35" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2862,10 +2862,10 @@
         <v>89</v>
       </c>
       <c r="F36" t="s">
+        <v>88</v>
+      </c>
+      <c r="G36" t="s">
         <v>89</v>
-      </c>
-      <c r="G36" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2885,10 +2885,10 @@
         <v>101</v>
       </c>
       <c r="F37" t="s">
+        <v>100</v>
+      </c>
+      <c r="G37" t="s">
         <v>101</v>
-      </c>
-      <c r="G37" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2908,10 +2908,10 @@
         <v>101</v>
       </c>
       <c r="F38" t="s">
+        <v>100</v>
+      </c>
+      <c r="G38" t="s">
         <v>101</v>
-      </c>
-      <c r="G38" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2931,10 +2931,10 @@
         <v>101</v>
       </c>
       <c r="F39" t="s">
+        <v>100</v>
+      </c>
+      <c r="G39" t="s">
         <v>101</v>
-      </c>
-      <c r="G39" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2954,10 +2954,10 @@
         <v>101</v>
       </c>
       <c r="F40" t="s">
+        <v>100</v>
+      </c>
+      <c r="G40" t="s">
         <v>101</v>
-      </c>
-      <c r="G40" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2977,10 +2977,10 @@
         <v>101</v>
       </c>
       <c r="F41" t="s">
+        <v>100</v>
+      </c>
+      <c r="G41" t="s">
         <v>101</v>
-      </c>
-      <c r="G41" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -3000,10 +3000,10 @@
         <v>101</v>
       </c>
       <c r="F42" t="s">
+        <v>100</v>
+      </c>
+      <c r="G42" t="s">
         <v>101</v>
-      </c>
-      <c r="G42" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3023,10 +3023,10 @@
         <v>101</v>
       </c>
       <c r="F43" t="s">
+        <v>100</v>
+      </c>
+      <c r="G43" t="s">
         <v>101</v>
-      </c>
-      <c r="G43" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3046,10 +3046,10 @@
         <v>101</v>
       </c>
       <c r="F44" t="s">
+        <v>100</v>
+      </c>
+      <c r="G44" t="s">
         <v>101</v>
-      </c>
-      <c r="G44" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3069,10 +3069,10 @@
         <v>101</v>
       </c>
       <c r="F45" t="s">
+        <v>100</v>
+      </c>
+      <c r="G45" t="s">
         <v>101</v>
-      </c>
-      <c r="G45" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3092,10 +3092,10 @@
         <v>101</v>
       </c>
       <c r="F46" t="s">
+        <v>100</v>
+      </c>
+      <c r="G46" t="s">
         <v>101</v>
-      </c>
-      <c r="G46" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3115,10 +3115,10 @@
         <v>101</v>
       </c>
       <c r="F47" t="s">
+        <v>100</v>
+      </c>
+      <c r="G47" t="s">
         <v>101</v>
-      </c>
-      <c r="G47" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3500,13 +3500,13 @@
         <v>9</v>
       </c>
       <c r="D64" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E64" t="s">
         <v>125</v>
       </c>
       <c r="F64" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="G64" t="s">
         <v>161</v>
@@ -3523,13 +3523,13 @@
         <v>9</v>
       </c>
       <c r="D65" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E65" t="s">
         <v>125</v>
       </c>
       <c r="F65" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="G65" t="s">
         <v>161</v>
@@ -3546,13 +3546,13 @@
         <v>9</v>
       </c>
       <c r="D66" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E66" t="s">
         <v>125</v>
       </c>
       <c r="F66" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="G66" t="s">
         <v>161</v>
@@ -3569,13 +3569,13 @@
         <v>9</v>
       </c>
       <c r="D67" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E67" t="s">
         <v>125</v>
       </c>
       <c r="F67" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="G67" t="s">
         <v>161</v>
@@ -3592,13 +3592,13 @@
         <v>9</v>
       </c>
       <c r="D68" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E68" t="s">
         <v>125</v>
       </c>
       <c r="F68" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="G68" t="s">
         <v>161</v>
@@ -3615,13 +3615,13 @@
         <v>9</v>
       </c>
       <c r="D69" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E69" t="s">
         <v>125</v>
       </c>
       <c r="F69" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="G69" t="s">
         <v>161</v>
@@ -3644,10 +3644,10 @@
         <v>175</v>
       </c>
       <c r="F70" t="s">
+        <v>174</v>
+      </c>
+      <c r="G70" t="s">
         <v>175</v>
-      </c>
-      <c r="G70" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3667,10 +3667,10 @@
         <v>175</v>
       </c>
       <c r="F71" t="s">
+        <v>174</v>
+      </c>
+      <c r="G71" t="s">
         <v>175</v>
-      </c>
-      <c r="G71" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3690,10 +3690,10 @@
         <v>175</v>
       </c>
       <c r="F72" t="s">
+        <v>174</v>
+      </c>
+      <c r="G72" t="s">
         <v>175</v>
-      </c>
-      <c r="G72" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3713,10 +3713,10 @@
         <v>175</v>
       </c>
       <c r="F73" t="s">
+        <v>174</v>
+      </c>
+      <c r="G73" t="s">
         <v>175</v>
-      </c>
-      <c r="G73" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3736,10 +3736,10 @@
         <v>175</v>
       </c>
       <c r="F74" t="s">
+        <v>174</v>
+      </c>
+      <c r="G74" t="s">
         <v>175</v>
-      </c>
-      <c r="G74" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3759,10 +3759,10 @@
         <v>175</v>
       </c>
       <c r="F75" t="s">
+        <v>174</v>
+      </c>
+      <c r="G75" t="s">
         <v>175</v>
-      </c>
-      <c r="G75" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3782,10 +3782,10 @@
         <v>175</v>
       </c>
       <c r="F76" t="s">
+        <v>174</v>
+      </c>
+      <c r="G76" t="s">
         <v>175</v>
-      </c>
-      <c r="G76" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3805,10 +3805,10 @@
         <v>175</v>
       </c>
       <c r="F77" t="s">
+        <v>174</v>
+      </c>
+      <c r="G77" t="s">
         <v>175</v>
-      </c>
-      <c r="G77" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3828,10 +3828,10 @@
         <v>175</v>
       </c>
       <c r="F78" t="s">
+        <v>174</v>
+      </c>
+      <c r="G78" t="s">
         <v>175</v>
-      </c>
-      <c r="G78" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3851,10 +3851,10 @@
         <v>175</v>
       </c>
       <c r="F79" t="s">
+        <v>174</v>
+      </c>
+      <c r="G79" t="s">
         <v>175</v>
-      </c>
-      <c r="G79" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3874,10 +3874,10 @@
         <v>175</v>
       </c>
       <c r="F80" t="s">
+        <v>174</v>
+      </c>
+      <c r="G80" t="s">
         <v>175</v>
-      </c>
-      <c r="G80" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3897,10 +3897,10 @@
         <v>199</v>
       </c>
       <c r="F81" t="s">
+        <v>198</v>
+      </c>
+      <c r="G81" t="s">
         <v>199</v>
-      </c>
-      <c r="G81" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3920,10 +3920,10 @@
         <v>199</v>
       </c>
       <c r="F82" t="s">
+        <v>198</v>
+      </c>
+      <c r="G82" t="s">
         <v>199</v>
-      </c>
-      <c r="G82" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3943,10 +3943,10 @@
         <v>199</v>
       </c>
       <c r="F83" t="s">
+        <v>198</v>
+      </c>
+      <c r="G83" t="s">
         <v>199</v>
-      </c>
-      <c r="G83" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3966,10 +3966,10 @@
         <v>199</v>
       </c>
       <c r="F84" t="s">
+        <v>198</v>
+      </c>
+      <c r="G84" t="s">
         <v>199</v>
-      </c>
-      <c r="G84" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3989,10 +3989,10 @@
         <v>199</v>
       </c>
       <c r="F85" t="s">
+        <v>198</v>
+      </c>
+      <c r="G85" t="s">
         <v>199</v>
-      </c>
-      <c r="G85" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4012,10 +4012,10 @@
         <v>199</v>
       </c>
       <c r="F86" t="s">
+        <v>198</v>
+      </c>
+      <c r="G86" t="s">
         <v>199</v>
-      </c>
-      <c r="G86" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4035,10 +4035,10 @@
         <v>199</v>
       </c>
       <c r="F87" t="s">
+        <v>198</v>
+      </c>
+      <c r="G87" t="s">
         <v>199</v>
-      </c>
-      <c r="G87" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4058,10 +4058,10 @@
         <v>215</v>
       </c>
       <c r="F88" t="s">
+        <v>214</v>
+      </c>
+      <c r="G88" t="s">
         <v>215</v>
-      </c>
-      <c r="G88" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4081,10 +4081,10 @@
         <v>215</v>
       </c>
       <c r="F89" t="s">
+        <v>214</v>
+      </c>
+      <c r="G89" t="s">
         <v>215</v>
-      </c>
-      <c r="G89" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4104,10 +4104,10 @@
         <v>215</v>
       </c>
       <c r="F90" t="s">
+        <v>214</v>
+      </c>
+      <c r="G90" t="s">
         <v>215</v>
-      </c>
-      <c r="G90" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4127,10 +4127,10 @@
         <v>215</v>
       </c>
       <c r="F91" t="s">
+        <v>214</v>
+      </c>
+      <c r="G91" t="s">
         <v>215</v>
-      </c>
-      <c r="G91" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4236,13 +4236,13 @@
         <v>9</v>
       </c>
       <c r="D96" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E96" t="s">
         <v>225</v>
       </c>
       <c r="F96" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G96" t="s">
         <v>237</v>
@@ -4259,13 +4259,13 @@
         <v>9</v>
       </c>
       <c r="D97" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E97" t="s">
         <v>225</v>
       </c>
       <c r="F97" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G97" t="s">
         <v>237</v>
@@ -4282,13 +4282,13 @@
         <v>9</v>
       </c>
       <c r="D98" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E98" t="s">
         <v>225</v>
       </c>
       <c r="F98" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G98" t="s">
         <v>237</v>
@@ -4305,13 +4305,13 @@
         <v>9</v>
       </c>
       <c r="D99" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E99" t="s">
         <v>225</v>
       </c>
       <c r="F99" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G99" t="s">
         <v>237</v>
@@ -4328,13 +4328,13 @@
         <v>9</v>
       </c>
       <c r="D100" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E100" t="s">
         <v>225</v>
       </c>
       <c r="F100" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G100" t="s">
         <v>237</v>
@@ -4351,13 +4351,13 @@
         <v>9</v>
       </c>
       <c r="D101" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E101" t="s">
         <v>225</v>
       </c>
       <c r="F101" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G101" t="s">
         <v>237</v>
@@ -4374,13 +4374,13 @@
         <v>9</v>
       </c>
       <c r="D102" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E102" t="s">
         <v>225</v>
       </c>
       <c r="F102" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G102" t="s">
         <v>237</v>
@@ -4397,13 +4397,13 @@
         <v>9</v>
       </c>
       <c r="D103" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E103" t="s">
         <v>225</v>
       </c>
       <c r="F103" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G103" t="s">
         <v>237</v>
@@ -4420,13 +4420,13 @@
         <v>9</v>
       </c>
       <c r="D104" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E104" t="s">
         <v>225</v>
       </c>
       <c r="F104" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G104" t="s">
         <v>237</v>
@@ -4443,13 +4443,13 @@
         <v>9</v>
       </c>
       <c r="D105" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E105" t="s">
         <v>225</v>
       </c>
       <c r="F105" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="G105" t="s">
         <v>257</v>
@@ -4466,13 +4466,13 @@
         <v>9</v>
       </c>
       <c r="D106" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E106" t="s">
         <v>225</v>
       </c>
       <c r="F106" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="G106" t="s">
         <v>257</v>
@@ -4489,13 +4489,13 @@
         <v>9</v>
       </c>
       <c r="D107" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E107" t="s">
         <v>225</v>
       </c>
       <c r="F107" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="G107" t="s">
         <v>257</v>
@@ -4512,13 +4512,13 @@
         <v>9</v>
       </c>
       <c r="D108" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E108" t="s">
         <v>225</v>
       </c>
       <c r="F108" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="G108" t="s">
         <v>257</v>
@@ -4535,13 +4535,13 @@
         <v>9</v>
       </c>
       <c r="D109" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E109" t="s">
         <v>225</v>
       </c>
       <c r="F109" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="G109" t="s">
         <v>257</v>
@@ -4558,13 +4558,13 @@
         <v>9</v>
       </c>
       <c r="D110" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E110" t="s">
         <v>225</v>
       </c>
       <c r="F110" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="G110" t="s">
         <v>257</v>
@@ -4581,13 +4581,13 @@
         <v>9</v>
       </c>
       <c r="D111" t="s">
-        <v>224</v>
+        <v>270</v>
       </c>
       <c r="E111" t="s">
         <v>225</v>
       </c>
       <c r="F111" t="s">
-        <v>270</v>
+        <v>226</v>
       </c>
       <c r="G111" t="s">
         <v>271</v>
@@ -4604,13 +4604,13 @@
         <v>9</v>
       </c>
       <c r="D112" t="s">
-        <v>224</v>
+        <v>274</v>
       </c>
       <c r="E112" t="s">
         <v>225</v>
       </c>
       <c r="F112" t="s">
-        <v>274</v>
+        <v>226</v>
       </c>
       <c r="G112" t="s">
         <v>275</v>
@@ -4627,13 +4627,13 @@
         <v>9</v>
       </c>
       <c r="D113" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E113" t="s">
         <v>225</v>
       </c>
       <c r="F113" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="G113" t="s">
         <v>279</v>
@@ -4650,13 +4650,13 @@
         <v>9</v>
       </c>
       <c r="D114" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E114" t="s">
         <v>225</v>
       </c>
       <c r="F114" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="G114" t="s">
         <v>279</v>
@@ -4673,13 +4673,13 @@
         <v>9</v>
       </c>
       <c r="D115" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E115" t="s">
         <v>225</v>
       </c>
       <c r="F115" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="G115" t="s">
         <v>279</v>
@@ -4696,13 +4696,13 @@
         <v>9</v>
       </c>
       <c r="D116" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E116" t="s">
         <v>225</v>
       </c>
       <c r="F116" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="G116" t="s">
         <v>279</v>
@@ -4719,13 +4719,13 @@
         <v>9</v>
       </c>
       <c r="D117" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E117" t="s">
         <v>225</v>
       </c>
       <c r="F117" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="G117" t="s">
         <v>279</v>
@@ -4742,13 +4742,13 @@
         <v>9</v>
       </c>
       <c r="D118" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E118" t="s">
         <v>225</v>
       </c>
       <c r="F118" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="G118" t="s">
         <v>279</v>
@@ -4765,13 +4765,13 @@
         <v>9</v>
       </c>
       <c r="D119" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E119" t="s">
         <v>225</v>
       </c>
       <c r="F119" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="G119" t="s">
         <v>279</v>
@@ -4794,10 +4794,10 @@
         <v>295</v>
       </c>
       <c r="F120" t="s">
+        <v>294</v>
+      </c>
+      <c r="G120" t="s">
         <v>295</v>
-      </c>
-      <c r="G120" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4817,10 +4817,10 @@
         <v>295</v>
       </c>
       <c r="F121" t="s">
+        <v>294</v>
+      </c>
+      <c r="G121" t="s">
         <v>295</v>
-      </c>
-      <c r="G121" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4840,10 +4840,10 @@
         <v>295</v>
       </c>
       <c r="F122" t="s">
+        <v>294</v>
+      </c>
+      <c r="G122" t="s">
         <v>295</v>
-      </c>
-      <c r="G122" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4863,10 +4863,10 @@
         <v>295</v>
       </c>
       <c r="F123" t="s">
+        <v>294</v>
+      </c>
+      <c r="G123" t="s">
         <v>295</v>
-      </c>
-      <c r="G123" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4886,10 +4886,10 @@
         <v>295</v>
       </c>
       <c r="F124" t="s">
+        <v>294</v>
+      </c>
+      <c r="G124" t="s">
         <v>295</v>
-      </c>
-      <c r="G124" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4909,10 +4909,10 @@
         <v>295</v>
       </c>
       <c r="F125" t="s">
+        <v>294</v>
+      </c>
+      <c r="G125" t="s">
         <v>295</v>
-      </c>
-      <c r="G125" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4932,10 +4932,10 @@
         <v>309</v>
       </c>
       <c r="F126" t="s">
+        <v>308</v>
+      </c>
+      <c r="G126" t="s">
         <v>309</v>
-      </c>
-      <c r="G126" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4955,10 +4955,10 @@
         <v>309</v>
       </c>
       <c r="F127" t="s">
+        <v>308</v>
+      </c>
+      <c r="G127" t="s">
         <v>309</v>
-      </c>
-      <c r="G127" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4978,10 +4978,10 @@
         <v>309</v>
       </c>
       <c r="F128" t="s">
+        <v>308</v>
+      </c>
+      <c r="G128" t="s">
         <v>309</v>
-      </c>
-      <c r="G128" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -5001,10 +5001,10 @@
         <v>309</v>
       </c>
       <c r="F129" t="s">
+        <v>308</v>
+      </c>
+      <c r="G129" t="s">
         <v>309</v>
-      </c>
-      <c r="G129" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -5432,13 +5432,13 @@
         <v>9</v>
       </c>
       <c r="D148" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E148" t="s">
         <v>319</v>
       </c>
       <c r="F148" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
       <c r="G148" t="s">
         <v>359</v>
@@ -5455,13 +5455,13 @@
         <v>9</v>
       </c>
       <c r="D149" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E149" t="s">
         <v>319</v>
       </c>
       <c r="F149" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
       <c r="G149" t="s">
         <v>359</v>
@@ -5478,13 +5478,13 @@
         <v>9</v>
       </c>
       <c r="D150" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E150" t="s">
         <v>319</v>
       </c>
       <c r="F150" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
       <c r="G150" t="s">
         <v>359</v>
@@ -5501,13 +5501,13 @@
         <v>9</v>
       </c>
       <c r="D151" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E151" t="s">
         <v>319</v>
       </c>
       <c r="F151" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
       <c r="G151" t="s">
         <v>359</v>
@@ -5524,13 +5524,13 @@
         <v>9</v>
       </c>
       <c r="D152" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E152" t="s">
         <v>319</v>
       </c>
       <c r="F152" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
       <c r="G152" t="s">
         <v>359</v>
@@ -5547,13 +5547,13 @@
         <v>9</v>
       </c>
       <c r="D153" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E153" t="s">
         <v>319</v>
       </c>
       <c r="F153" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
       <c r="G153" t="s">
         <v>359</v>
@@ -5570,13 +5570,13 @@
         <v>9</v>
       </c>
       <c r="D154" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="E154" t="s">
         <v>319</v>
       </c>
       <c r="F154" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
       <c r="G154" t="s">
         <v>373</v>
@@ -5593,13 +5593,13 @@
         <v>9</v>
       </c>
       <c r="D155" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="E155" t="s">
         <v>319</v>
       </c>
       <c r="F155" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
       <c r="G155" t="s">
         <v>373</v>
@@ -5616,13 +5616,13 @@
         <v>9</v>
       </c>
       <c r="D156" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="E156" t="s">
         <v>319</v>
       </c>
       <c r="F156" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
       <c r="G156" t="s">
         <v>373</v>
@@ -5639,13 +5639,13 @@
         <v>9</v>
       </c>
       <c r="D157" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="E157" t="s">
         <v>319</v>
       </c>
       <c r="F157" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
       <c r="G157" t="s">
         <v>373</v>
@@ -5662,13 +5662,13 @@
         <v>9</v>
       </c>
       <c r="D158" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="E158" t="s">
         <v>319</v>
       </c>
       <c r="F158" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
       <c r="G158" t="s">
         <v>373</v>
@@ -6122,13 +6122,13 @@
         <v>9</v>
       </c>
       <c r="D178" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E178" t="s">
         <v>385</v>
       </c>
       <c r="F178" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
       <c r="G178" t="s">
         <v>427</v>
@@ -6145,13 +6145,13 @@
         <v>9</v>
       </c>
       <c r="D179" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E179" t="s">
         <v>385</v>
       </c>
       <c r="F179" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
       <c r="G179" t="s">
         <v>427</v>
@@ -6168,13 +6168,13 @@
         <v>9</v>
       </c>
       <c r="D180" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E180" t="s">
         <v>385</v>
       </c>
       <c r="F180" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
       <c r="G180" t="s">
         <v>427</v>
@@ -6191,13 +6191,13 @@
         <v>9</v>
       </c>
       <c r="D181" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E181" t="s">
         <v>385</v>
       </c>
       <c r="F181" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
       <c r="G181" t="s">
         <v>427</v>
@@ -6214,13 +6214,13 @@
         <v>9</v>
       </c>
       <c r="D182" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E182" t="s">
         <v>385</v>
       </c>
       <c r="F182" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
       <c r="G182" t="s">
         <v>427</v>
@@ -6237,13 +6237,13 @@
         <v>9</v>
       </c>
       <c r="D183" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E183" t="s">
         <v>385</v>
       </c>
       <c r="F183" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
       <c r="G183" t="s">
         <v>427</v>
@@ -6260,13 +6260,13 @@
         <v>9</v>
       </c>
       <c r="D184" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E184" t="s">
         <v>385</v>
       </c>
       <c r="F184" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
       <c r="G184" t="s">
         <v>427</v>
@@ -6283,13 +6283,13 @@
         <v>9</v>
       </c>
       <c r="D185" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E185" t="s">
         <v>385</v>
       </c>
       <c r="F185" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
       <c r="G185" t="s">
         <v>427</v>
@@ -6306,13 +6306,13 @@
         <v>9</v>
       </c>
       <c r="D186" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E186" t="s">
         <v>385</v>
       </c>
       <c r="F186" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
       <c r="G186" t="s">
         <v>427</v>
@@ -6329,13 +6329,13 @@
         <v>9</v>
       </c>
       <c r="D187" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E187" t="s">
         <v>385</v>
       </c>
       <c r="F187" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
       <c r="G187" t="s">
         <v>427</v>
@@ -6352,13 +6352,13 @@
         <v>9</v>
       </c>
       <c r="D188" t="s">
-        <v>384</v>
+        <v>448</v>
       </c>
       <c r="E188" t="s">
         <v>385</v>
       </c>
       <c r="F188" t="s">
-        <v>448</v>
+        <v>386</v>
       </c>
       <c r="G188" t="s">
         <v>449</v>
@@ -6381,10 +6381,10 @@
         <v>453</v>
       </c>
       <c r="F189" t="s">
+        <v>452</v>
+      </c>
+      <c r="G189" t="s">
         <v>453</v>
-      </c>
-      <c r="G189" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6404,10 +6404,10 @@
         <v>453</v>
       </c>
       <c r="F190" t="s">
+        <v>452</v>
+      </c>
+      <c r="G190" t="s">
         <v>453</v>
-      </c>
-      <c r="G190" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6427,10 +6427,10 @@
         <v>453</v>
       </c>
       <c r="F191" t="s">
+        <v>452</v>
+      </c>
+      <c r="G191" t="s">
         <v>453</v>
-      </c>
-      <c r="G191" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6450,10 +6450,10 @@
         <v>453</v>
       </c>
       <c r="F192" t="s">
+        <v>452</v>
+      </c>
+      <c r="G192" t="s">
         <v>453</v>
-      </c>
-      <c r="G192" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6473,10 +6473,10 @@
         <v>453</v>
       </c>
       <c r="F193" t="s">
+        <v>452</v>
+      </c>
+      <c r="G193" t="s">
         <v>453</v>
-      </c>
-      <c r="G193" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6496,10 +6496,10 @@
         <v>453</v>
       </c>
       <c r="F194" t="s">
+        <v>452</v>
+      </c>
+      <c r="G194" t="s">
         <v>453</v>
-      </c>
-      <c r="G194" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6519,10 +6519,10 @@
         <v>467</v>
       </c>
       <c r="F195" t="s">
+        <v>466</v>
+      </c>
+      <c r="G195" t="s">
         <v>467</v>
-      </c>
-      <c r="G195" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6542,10 +6542,10 @@
         <v>471</v>
       </c>
       <c r="F196" t="s">
+        <v>470</v>
+      </c>
+      <c r="G196" t="s">
         <v>471</v>
-      </c>
-      <c r="G196" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6565,10 +6565,10 @@
         <v>471</v>
       </c>
       <c r="F197" t="s">
+        <v>470</v>
+      </c>
+      <c r="G197" t="s">
         <v>471</v>
-      </c>
-      <c r="G197" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6588,10 +6588,10 @@
         <v>471</v>
       </c>
       <c r="F198" t="s">
+        <v>470</v>
+      </c>
+      <c r="G198" t="s">
         <v>471</v>
-      </c>
-      <c r="G198" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6611,10 +6611,10 @@
         <v>471</v>
       </c>
       <c r="F199" t="s">
+        <v>470</v>
+      </c>
+      <c r="G199" t="s">
         <v>471</v>
-      </c>
-      <c r="G199" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6634,10 +6634,10 @@
         <v>471</v>
       </c>
       <c r="F200" t="s">
+        <v>470</v>
+      </c>
+      <c r="G200" t="s">
         <v>471</v>
-      </c>
-      <c r="G200" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6657,10 +6657,10 @@
         <v>471</v>
       </c>
       <c r="F201" t="s">
+        <v>470</v>
+      </c>
+      <c r="G201" t="s">
         <v>471</v>
-      </c>
-      <c r="G201" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6680,10 +6680,10 @@
         <v>485</v>
       </c>
       <c r="F202" t="s">
+        <v>484</v>
+      </c>
+      <c r="G202" t="s">
         <v>485</v>
-      </c>
-      <c r="G202" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6703,10 +6703,10 @@
         <v>485</v>
       </c>
       <c r="F203" t="s">
+        <v>484</v>
+      </c>
+      <c r="G203" t="s">
         <v>485</v>
-      </c>
-      <c r="G203" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6726,10 +6726,10 @@
         <v>485</v>
       </c>
       <c r="F204" t="s">
+        <v>484</v>
+      </c>
+      <c r="G204" t="s">
         <v>485</v>
-      </c>
-      <c r="G204" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6749,10 +6749,10 @@
         <v>485</v>
       </c>
       <c r="F205" t="s">
+        <v>484</v>
+      </c>
+      <c r="G205" t="s">
         <v>485</v>
-      </c>
-      <c r="G205" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6772,10 +6772,10 @@
         <v>485</v>
       </c>
       <c r="F206" t="s">
+        <v>484</v>
+      </c>
+      <c r="G206" t="s">
         <v>485</v>
-      </c>
-      <c r="G206" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6795,10 +6795,10 @@
         <v>485</v>
       </c>
       <c r="F207" t="s">
+        <v>484</v>
+      </c>
+      <c r="G207" t="s">
         <v>485</v>
-      </c>
-      <c r="G207" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6818,10 +6818,10 @@
         <v>485</v>
       </c>
       <c r="F208" t="s">
+        <v>484</v>
+      </c>
+      <c r="G208" t="s">
         <v>485</v>
-      </c>
-      <c r="G208" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6841,10 +6841,10 @@
         <v>485</v>
       </c>
       <c r="F209" t="s">
+        <v>484</v>
+      </c>
+      <c r="G209" t="s">
         <v>485</v>
-      </c>
-      <c r="G209" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6864,10 +6864,10 @@
         <v>485</v>
       </c>
       <c r="F210" t="s">
+        <v>484</v>
+      </c>
+      <c r="G210" t="s">
         <v>485</v>
-      </c>
-      <c r="G210" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6887,10 +6887,10 @@
         <v>485</v>
       </c>
       <c r="F211" t="s">
+        <v>484</v>
+      </c>
+      <c r="G211" t="s">
         <v>485</v>
-      </c>
-      <c r="G211" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6910,10 +6910,10 @@
         <v>507</v>
       </c>
       <c r="F212" t="s">
+        <v>506</v>
+      </c>
+      <c r="G212" t="s">
         <v>507</v>
-      </c>
-      <c r="G212" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6933,10 +6933,10 @@
         <v>511</v>
       </c>
       <c r="F213" t="s">
+        <v>510</v>
+      </c>
+      <c r="G213" t="s">
         <v>511</v>
-      </c>
-      <c r="G213" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6956,10 +6956,10 @@
         <v>515</v>
       </c>
       <c r="F214" t="s">
+        <v>514</v>
+      </c>
+      <c r="G214" t="s">
         <v>515</v>
-      </c>
-      <c r="G214" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6979,10 +6979,10 @@
         <v>515</v>
       </c>
       <c r="F215" t="s">
+        <v>514</v>
+      </c>
+      <c r="G215" t="s">
         <v>515</v>
-      </c>
-      <c r="G215" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -7002,10 +7002,10 @@
         <v>521</v>
       </c>
       <c r="F216" t="s">
+        <v>520</v>
+      </c>
+      <c r="G216" t="s">
         <v>521</v>
-      </c>
-      <c r="G216" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -7025,10 +7025,10 @@
         <v>521</v>
       </c>
       <c r="F217" t="s">
+        <v>520</v>
+      </c>
+      <c r="G217" t="s">
         <v>521</v>
-      </c>
-      <c r="G217" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -7048,10 +7048,10 @@
         <v>521</v>
       </c>
       <c r="F218" t="s">
+        <v>520</v>
+      </c>
+      <c r="G218" t="s">
         <v>521</v>
-      </c>
-      <c r="G218" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -7071,10 +7071,10 @@
         <v>521</v>
       </c>
       <c r="F219" t="s">
+        <v>520</v>
+      </c>
+      <c r="G219" t="s">
         <v>521</v>
-      </c>
-      <c r="G219" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -7094,10 +7094,10 @@
         <v>521</v>
       </c>
       <c r="F220" t="s">
+        <v>520</v>
+      </c>
+      <c r="G220" t="s">
         <v>521</v>
-      </c>
-      <c r="G220" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -7117,10 +7117,10 @@
         <v>521</v>
       </c>
       <c r="F221" t="s">
+        <v>520</v>
+      </c>
+      <c r="G221" t="s">
         <v>521</v>
-      </c>
-      <c r="G221" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -7140,10 +7140,10 @@
         <v>521</v>
       </c>
       <c r="F222" t="s">
+        <v>520</v>
+      </c>
+      <c r="G222" t="s">
         <v>521</v>
-      </c>
-      <c r="G222" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -7163,10 +7163,10 @@
         <v>537</v>
       </c>
       <c r="F223" t="s">
+        <v>536</v>
+      </c>
+      <c r="G223" t="s">
         <v>537</v>
-      </c>
-      <c r="G223" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -7186,10 +7186,10 @@
         <v>537</v>
       </c>
       <c r="F224" t="s">
+        <v>536</v>
+      </c>
+      <c r="G224" t="s">
         <v>537</v>
-      </c>
-      <c r="G224" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -7209,10 +7209,10 @@
         <v>537</v>
       </c>
       <c r="F225" t="s">
+        <v>536</v>
+      </c>
+      <c r="G225" t="s">
         <v>537</v>
-      </c>
-      <c r="G225" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -7232,10 +7232,10 @@
         <v>545</v>
       </c>
       <c r="F226" t="s">
+        <v>544</v>
+      </c>
+      <c r="G226" t="s">
         <v>545</v>
-      </c>
-      <c r="G226" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -7255,10 +7255,10 @@
         <v>549</v>
       </c>
       <c r="F227" t="s">
+        <v>548</v>
+      </c>
+      <c r="G227" t="s">
         <v>549</v>
-      </c>
-      <c r="G227" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -7278,10 +7278,10 @@
         <v>553</v>
       </c>
       <c r="F228" t="s">
+        <v>552</v>
+      </c>
+      <c r="G228" t="s">
         <v>553</v>
-      </c>
-      <c r="G228" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -7301,10 +7301,10 @@
         <v>557</v>
       </c>
       <c r="F229" t="s">
+        <v>556</v>
+      </c>
+      <c r="G229" t="s">
         <v>557</v>
-      </c>
-      <c r="G229" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -7324,10 +7324,10 @@
         <v>561</v>
       </c>
       <c r="F230" t="s">
+        <v>560</v>
+      </c>
+      <c r="G230" t="s">
         <v>561</v>
-      </c>
-      <c r="G230" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -7347,10 +7347,10 @@
         <v>561</v>
       </c>
       <c r="F231" t="s">
+        <v>560</v>
+      </c>
+      <c r="G231" t="s">
         <v>561</v>
-      </c>
-      <c r="G231" t="s">
-        <v>560</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/en/SectorGroup.xlsx
+++ b/api/xlsx/en/SectorGroup.xlsx
@@ -25,15 +25,15 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
     <t>codeforiati:category-name</t>
   </si>
   <si>
@@ -46,15 +46,15 @@
     <t>active</t>
   </si>
   <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
     <t>111</t>
   </si>
   <si>
-    <t>Education</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
     <t>Education, Level Unspecified</t>
   </si>
   <si>
@@ -148,15 +148,15 @@
     <t>Health policy and administrative management</t>
   </si>
   <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>Health</t>
+  </si>
+  <si>
     <t>121</t>
   </si>
   <si>
-    <t>Health</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
     <t>Health, General</t>
   </si>
   <si>
@@ -388,15 +388,15 @@
     <t>Public sector policy and administrative management</t>
   </si>
   <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>Government &amp; Civil Society</t>
+  </si>
+  <si>
     <t>151</t>
   </si>
   <si>
-    <t>Government &amp; Civil Society</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
     <t>Government &amp; Civil Society-general</t>
   </si>
   <si>
@@ -688,15 +688,15 @@
     <t>Energy policy and administrative management</t>
   </si>
   <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>Energy</t>
+  </si>
+  <si>
     <t>231</t>
   </si>
   <si>
-    <t>Energy</t>
-  </si>
-  <si>
-    <t>230</t>
-  </si>
-  <si>
     <t>Energy Policy</t>
   </si>
   <si>
@@ -970,15 +970,15 @@
     <t>Agricultural policy and administrative management</t>
   </si>
   <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>Agriculture, Forestry, Fishing</t>
+  </si>
+  <si>
     <t>311</t>
   </si>
   <si>
-    <t>Agriculture, Forestry, Fishing</t>
-  </si>
-  <si>
-    <t>310</t>
-  </si>
-  <si>
     <t>Agriculture</t>
   </si>
   <si>
@@ -1168,13 +1168,13 @@
     <t>Industrial policy and administrative management</t>
   </si>
   <si>
+    <t>320</t>
+  </si>
+  <si>
+    <t>Industry, Mining, Construction</t>
+  </si>
+  <si>
     <t>321</t>
-  </si>
-  <si>
-    <t>Industry, Mining, Construction</t>
-  </si>
-  <si>
-    <t>320</t>
   </si>
   <si>
     <t>Industry</t>
@@ -2166,13 +2166,13 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E6" t="s">
         <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G6" t="s">
         <v>23</v>
@@ -2189,13 +2189,13 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G7" t="s">
         <v>23</v>
@@ -2212,13 +2212,13 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E8" t="s">
         <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G8" t="s">
         <v>23</v>
@@ -2235,13 +2235,13 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G9" t="s">
         <v>23</v>
@@ -2258,13 +2258,13 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="E10" t="s">
         <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="G10" t="s">
         <v>33</v>
@@ -2281,13 +2281,13 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="E11" t="s">
         <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="G11" t="s">
         <v>33</v>
@@ -2304,13 +2304,13 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="E12" t="s">
         <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="G12" t="s">
         <v>39</v>
@@ -2327,13 +2327,13 @@
         <v>9</v>
       </c>
       <c r="D13" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="E13" t="s">
         <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="G13" t="s">
         <v>39</v>
@@ -2442,13 +2442,13 @@
         <v>9</v>
       </c>
       <c r="D18" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E18" t="s">
         <v>45</v>
       </c>
       <c r="F18" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="G18" t="s">
         <v>57</v>
@@ -2465,13 +2465,13 @@
         <v>9</v>
       </c>
       <c r="D19" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E19" t="s">
         <v>45</v>
       </c>
       <c r="F19" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="G19" t="s">
         <v>57</v>
@@ -2488,13 +2488,13 @@
         <v>9</v>
       </c>
       <c r="D20" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E20" t="s">
         <v>45</v>
       </c>
       <c r="F20" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="G20" t="s">
         <v>57</v>
@@ -2511,13 +2511,13 @@
         <v>9</v>
       </c>
       <c r="D21" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E21" t="s">
         <v>45</v>
       </c>
       <c r="F21" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="G21" t="s">
         <v>57</v>
@@ -2534,13 +2534,13 @@
         <v>9</v>
       </c>
       <c r="D22" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E22" t="s">
         <v>45</v>
       </c>
       <c r="F22" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="G22" t="s">
         <v>57</v>
@@ -2557,13 +2557,13 @@
         <v>9</v>
       </c>
       <c r="D23" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E23" t="s">
         <v>45</v>
       </c>
       <c r="F23" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="G23" t="s">
         <v>57</v>
@@ -2580,13 +2580,13 @@
         <v>9</v>
       </c>
       <c r="D24" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E24" t="s">
         <v>45</v>
       </c>
       <c r="F24" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="G24" t="s">
         <v>57</v>
@@ -2603,13 +2603,13 @@
         <v>9</v>
       </c>
       <c r="D25" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E25" t="s">
         <v>45</v>
       </c>
       <c r="F25" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="G25" t="s">
         <v>57</v>
@@ -2626,13 +2626,13 @@
         <v>9</v>
       </c>
       <c r="D26" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="E26" t="s">
         <v>45</v>
       </c>
       <c r="F26" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="G26" t="s">
         <v>75</v>
@@ -2649,13 +2649,13 @@
         <v>9</v>
       </c>
       <c r="D27" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="E27" t="s">
         <v>45</v>
       </c>
       <c r="F27" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="G27" t="s">
         <v>75</v>
@@ -2672,13 +2672,13 @@
         <v>9</v>
       </c>
       <c r="D28" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="E28" t="s">
         <v>45</v>
       </c>
       <c r="F28" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="G28" t="s">
         <v>75</v>
@@ -2695,13 +2695,13 @@
         <v>9</v>
       </c>
       <c r="D29" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="E29" t="s">
         <v>45</v>
       </c>
       <c r="F29" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="G29" t="s">
         <v>75</v>
@@ -2718,13 +2718,13 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="E30" t="s">
         <v>45</v>
       </c>
       <c r="F30" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="G30" t="s">
         <v>75</v>
@@ -2741,13 +2741,13 @@
         <v>9</v>
       </c>
       <c r="D31" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="E31" t="s">
         <v>45</v>
       </c>
       <c r="F31" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="G31" t="s">
         <v>75</v>
@@ -3500,13 +3500,13 @@
         <v>9</v>
       </c>
       <c r="D64" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="E64" t="s">
         <v>125</v>
       </c>
       <c r="F64" t="s">
-        <v>126</v>
+        <v>160</v>
       </c>
       <c r="G64" t="s">
         <v>161</v>
@@ -3523,13 +3523,13 @@
         <v>9</v>
       </c>
       <c r="D65" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="E65" t="s">
         <v>125</v>
       </c>
       <c r="F65" t="s">
-        <v>126</v>
+        <v>160</v>
       </c>
       <c r="G65" t="s">
         <v>161</v>
@@ -3546,13 +3546,13 @@
         <v>9</v>
       </c>
       <c r="D66" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="E66" t="s">
         <v>125</v>
       </c>
       <c r="F66" t="s">
-        <v>126</v>
+        <v>160</v>
       </c>
       <c r="G66" t="s">
         <v>161</v>
@@ -3569,13 +3569,13 @@
         <v>9</v>
       </c>
       <c r="D67" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="E67" t="s">
         <v>125</v>
       </c>
       <c r="F67" t="s">
-        <v>126</v>
+        <v>160</v>
       </c>
       <c r="G67" t="s">
         <v>161</v>
@@ -3592,13 +3592,13 @@
         <v>9</v>
       </c>
       <c r="D68" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="E68" t="s">
         <v>125</v>
       </c>
       <c r="F68" t="s">
-        <v>126</v>
+        <v>160</v>
       </c>
       <c r="G68" t="s">
         <v>161</v>
@@ -3615,13 +3615,13 @@
         <v>9</v>
       </c>
       <c r="D69" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="E69" t="s">
         <v>125</v>
       </c>
       <c r="F69" t="s">
-        <v>126</v>
+        <v>160</v>
       </c>
       <c r="G69" t="s">
         <v>161</v>
@@ -4236,13 +4236,13 @@
         <v>9</v>
       </c>
       <c r="D96" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E96" t="s">
         <v>225</v>
       </c>
       <c r="F96" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="G96" t="s">
         <v>237</v>
@@ -4259,13 +4259,13 @@
         <v>9</v>
       </c>
       <c r="D97" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E97" t="s">
         <v>225</v>
       </c>
       <c r="F97" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="G97" t="s">
         <v>237</v>
@@ -4282,13 +4282,13 @@
         <v>9</v>
       </c>
       <c r="D98" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E98" t="s">
         <v>225</v>
       </c>
       <c r="F98" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="G98" t="s">
         <v>237</v>
@@ -4305,13 +4305,13 @@
         <v>9</v>
       </c>
       <c r="D99" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E99" t="s">
         <v>225</v>
       </c>
       <c r="F99" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="G99" t="s">
         <v>237</v>
@@ -4328,13 +4328,13 @@
         <v>9</v>
       </c>
       <c r="D100" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E100" t="s">
         <v>225</v>
       </c>
       <c r="F100" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="G100" t="s">
         <v>237</v>
@@ -4351,13 +4351,13 @@
         <v>9</v>
       </c>
       <c r="D101" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E101" t="s">
         <v>225</v>
       </c>
       <c r="F101" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="G101" t="s">
         <v>237</v>
@@ -4374,13 +4374,13 @@
         <v>9</v>
       </c>
       <c r="D102" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E102" t="s">
         <v>225</v>
       </c>
       <c r="F102" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="G102" t="s">
         <v>237</v>
@@ -4397,13 +4397,13 @@
         <v>9</v>
       </c>
       <c r="D103" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E103" t="s">
         <v>225</v>
       </c>
       <c r="F103" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="G103" t="s">
         <v>237</v>
@@ -4420,13 +4420,13 @@
         <v>9</v>
       </c>
       <c r="D104" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E104" t="s">
         <v>225</v>
       </c>
       <c r="F104" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="G104" t="s">
         <v>237</v>
@@ -4443,13 +4443,13 @@
         <v>9</v>
       </c>
       <c r="D105" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="E105" t="s">
         <v>225</v>
       </c>
       <c r="F105" t="s">
-        <v>226</v>
+        <v>256</v>
       </c>
       <c r="G105" t="s">
         <v>257</v>
@@ -4466,13 +4466,13 @@
         <v>9</v>
       </c>
       <c r="D106" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="E106" t="s">
         <v>225</v>
       </c>
       <c r="F106" t="s">
-        <v>226</v>
+        <v>256</v>
       </c>
       <c r="G106" t="s">
         <v>257</v>
@@ -4489,13 +4489,13 @@
         <v>9</v>
       </c>
       <c r="D107" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="E107" t="s">
         <v>225</v>
       </c>
       <c r="F107" t="s">
-        <v>226</v>
+        <v>256</v>
       </c>
       <c r="G107" t="s">
         <v>257</v>
@@ -4512,13 +4512,13 @@
         <v>9</v>
       </c>
       <c r="D108" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="E108" t="s">
         <v>225</v>
       </c>
       <c r="F108" t="s">
-        <v>226</v>
+        <v>256</v>
       </c>
       <c r="G108" t="s">
         <v>257</v>
@@ -4535,13 +4535,13 @@
         <v>9</v>
       </c>
       <c r="D109" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="E109" t="s">
         <v>225</v>
       </c>
       <c r="F109" t="s">
-        <v>226</v>
+        <v>256</v>
       </c>
       <c r="G109" t="s">
         <v>257</v>
@@ -4558,13 +4558,13 @@
         <v>9</v>
       </c>
       <c r="D110" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="E110" t="s">
         <v>225</v>
       </c>
       <c r="F110" t="s">
-        <v>226</v>
+        <v>256</v>
       </c>
       <c r="G110" t="s">
         <v>257</v>
@@ -4581,13 +4581,13 @@
         <v>9</v>
       </c>
       <c r="D111" t="s">
-        <v>270</v>
+        <v>224</v>
       </c>
       <c r="E111" t="s">
         <v>225</v>
       </c>
       <c r="F111" t="s">
-        <v>226</v>
+        <v>270</v>
       </c>
       <c r="G111" t="s">
         <v>271</v>
@@ -4604,13 +4604,13 @@
         <v>9</v>
       </c>
       <c r="D112" t="s">
-        <v>274</v>
+        <v>224</v>
       </c>
       <c r="E112" t="s">
         <v>225</v>
       </c>
       <c r="F112" t="s">
-        <v>226</v>
+        <v>274</v>
       </c>
       <c r="G112" t="s">
         <v>275</v>
@@ -4627,13 +4627,13 @@
         <v>9</v>
       </c>
       <c r="D113" t="s">
-        <v>278</v>
+        <v>224</v>
       </c>
       <c r="E113" t="s">
         <v>225</v>
       </c>
       <c r="F113" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="G113" t="s">
         <v>279</v>
@@ -4650,13 +4650,13 @@
         <v>9</v>
       </c>
       <c r="D114" t="s">
-        <v>278</v>
+        <v>224</v>
       </c>
       <c r="E114" t="s">
         <v>225</v>
       </c>
       <c r="F114" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="G114" t="s">
         <v>279</v>
@@ -4673,13 +4673,13 @@
         <v>9</v>
       </c>
       <c r="D115" t="s">
-        <v>278</v>
+        <v>224</v>
       </c>
       <c r="E115" t="s">
         <v>225</v>
       </c>
       <c r="F115" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="G115" t="s">
         <v>279</v>
@@ -4696,13 +4696,13 @@
         <v>9</v>
       </c>
       <c r="D116" t="s">
-        <v>278</v>
+        <v>224</v>
       </c>
       <c r="E116" t="s">
         <v>225</v>
       </c>
       <c r="F116" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="G116" t="s">
         <v>279</v>
@@ -4719,13 +4719,13 @@
         <v>9</v>
       </c>
       <c r="D117" t="s">
-        <v>278</v>
+        <v>224</v>
       </c>
       <c r="E117" t="s">
         <v>225</v>
       </c>
       <c r="F117" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="G117" t="s">
         <v>279</v>
@@ -4742,13 +4742,13 @@
         <v>9</v>
       </c>
       <c r="D118" t="s">
-        <v>278</v>
+        <v>224</v>
       </c>
       <c r="E118" t="s">
         <v>225</v>
       </c>
       <c r="F118" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="G118" t="s">
         <v>279</v>
@@ -4765,13 +4765,13 @@
         <v>9</v>
       </c>
       <c r="D119" t="s">
-        <v>278</v>
+        <v>224</v>
       </c>
       <c r="E119" t="s">
         <v>225</v>
       </c>
       <c r="F119" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="G119" t="s">
         <v>279</v>
@@ -5432,13 +5432,13 @@
         <v>9</v>
       </c>
       <c r="D148" t="s">
-        <v>358</v>
+        <v>318</v>
       </c>
       <c r="E148" t="s">
         <v>319</v>
       </c>
       <c r="F148" t="s">
-        <v>320</v>
+        <v>358</v>
       </c>
       <c r="G148" t="s">
         <v>359</v>
@@ -5455,13 +5455,13 @@
         <v>9</v>
       </c>
       <c r="D149" t="s">
-        <v>358</v>
+        <v>318</v>
       </c>
       <c r="E149" t="s">
         <v>319</v>
       </c>
       <c r="F149" t="s">
-        <v>320</v>
+        <v>358</v>
       </c>
       <c r="G149" t="s">
         <v>359</v>
@@ -5478,13 +5478,13 @@
         <v>9</v>
       </c>
       <c r="D150" t="s">
-        <v>358</v>
+        <v>318</v>
       </c>
       <c r="E150" t="s">
         <v>319</v>
       </c>
       <c r="F150" t="s">
-        <v>320</v>
+        <v>358</v>
       </c>
       <c r="G150" t="s">
         <v>359</v>
@@ -5501,13 +5501,13 @@
         <v>9</v>
       </c>
       <c r="D151" t="s">
-        <v>358</v>
+        <v>318</v>
       </c>
       <c r="E151" t="s">
         <v>319</v>
       </c>
       <c r="F151" t="s">
-        <v>320</v>
+        <v>358</v>
       </c>
       <c r="G151" t="s">
         <v>359</v>
@@ -5524,13 +5524,13 @@
         <v>9</v>
       </c>
       <c r="D152" t="s">
-        <v>358</v>
+        <v>318</v>
       </c>
       <c r="E152" t="s">
         <v>319</v>
       </c>
       <c r="F152" t="s">
-        <v>320</v>
+        <v>358</v>
       </c>
       <c r="G152" t="s">
         <v>359</v>
@@ -5547,13 +5547,13 @@
         <v>9</v>
       </c>
       <c r="D153" t="s">
-        <v>358</v>
+        <v>318</v>
       </c>
       <c r="E153" t="s">
         <v>319</v>
       </c>
       <c r="F153" t="s">
-        <v>320</v>
+        <v>358</v>
       </c>
       <c r="G153" t="s">
         <v>359</v>
@@ -5570,13 +5570,13 @@
         <v>9</v>
       </c>
       <c r="D154" t="s">
-        <v>372</v>
+        <v>318</v>
       </c>
       <c r="E154" t="s">
         <v>319</v>
       </c>
       <c r="F154" t="s">
-        <v>320</v>
+        <v>372</v>
       </c>
       <c r="G154" t="s">
         <v>373</v>
@@ -5593,13 +5593,13 @@
         <v>9</v>
       </c>
       <c r="D155" t="s">
-        <v>372</v>
+        <v>318</v>
       </c>
       <c r="E155" t="s">
         <v>319</v>
       </c>
       <c r="F155" t="s">
-        <v>320</v>
+        <v>372</v>
       </c>
       <c r="G155" t="s">
         <v>373</v>
@@ -5616,13 +5616,13 @@
         <v>9</v>
       </c>
       <c r="D156" t="s">
-        <v>372</v>
+        <v>318</v>
       </c>
       <c r="E156" t="s">
         <v>319</v>
       </c>
       <c r="F156" t="s">
-        <v>320</v>
+        <v>372</v>
       </c>
       <c r="G156" t="s">
         <v>373</v>
@@ -5639,13 +5639,13 @@
         <v>9</v>
       </c>
       <c r="D157" t="s">
-        <v>372</v>
+        <v>318</v>
       </c>
       <c r="E157" t="s">
         <v>319</v>
       </c>
       <c r="F157" t="s">
-        <v>320</v>
+        <v>372</v>
       </c>
       <c r="G157" t="s">
         <v>373</v>
@@ -5662,13 +5662,13 @@
         <v>9</v>
       </c>
       <c r="D158" t="s">
-        <v>372</v>
+        <v>318</v>
       </c>
       <c r="E158" t="s">
         <v>319</v>
       </c>
       <c r="F158" t="s">
-        <v>320</v>
+        <v>372</v>
       </c>
       <c r="G158" t="s">
         <v>373</v>
@@ -6122,13 +6122,13 @@
         <v>9</v>
       </c>
       <c r="D178" t="s">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="E178" t="s">
         <v>385</v>
       </c>
       <c r="F178" t="s">
-        <v>386</v>
+        <v>426</v>
       </c>
       <c r="G178" t="s">
         <v>427</v>
@@ -6145,13 +6145,13 @@
         <v>9</v>
       </c>
       <c r="D179" t="s">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="E179" t="s">
         <v>385</v>
       </c>
       <c r="F179" t="s">
-        <v>386</v>
+        <v>426</v>
       </c>
       <c r="G179" t="s">
         <v>427</v>
@@ -6168,13 +6168,13 @@
         <v>9</v>
       </c>
       <c r="D180" t="s">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="E180" t="s">
         <v>385</v>
       </c>
       <c r="F180" t="s">
-        <v>386</v>
+        <v>426</v>
       </c>
       <c r="G180" t="s">
         <v>427</v>
@@ -6191,13 +6191,13 @@
         <v>9</v>
       </c>
       <c r="D181" t="s">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="E181" t="s">
         <v>385</v>
       </c>
       <c r="F181" t="s">
-        <v>386</v>
+        <v>426</v>
       </c>
       <c r="G181" t="s">
         <v>427</v>
@@ -6214,13 +6214,13 @@
         <v>9</v>
       </c>
       <c r="D182" t="s">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="E182" t="s">
         <v>385</v>
       </c>
       <c r="F182" t="s">
-        <v>386</v>
+        <v>426</v>
       </c>
       <c r="G182" t="s">
         <v>427</v>
@@ -6237,13 +6237,13 @@
         <v>9</v>
       </c>
       <c r="D183" t="s">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="E183" t="s">
         <v>385</v>
       </c>
       <c r="F183" t="s">
-        <v>386</v>
+        <v>426</v>
       </c>
       <c r="G183" t="s">
         <v>427</v>
@@ -6260,13 +6260,13 @@
         <v>9</v>
       </c>
       <c r="D184" t="s">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="E184" t="s">
         <v>385</v>
       </c>
       <c r="F184" t="s">
-        <v>386</v>
+        <v>426</v>
       </c>
       <c r="G184" t="s">
         <v>427</v>
@@ -6283,13 +6283,13 @@
         <v>9</v>
       </c>
       <c r="D185" t="s">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="E185" t="s">
         <v>385</v>
       </c>
       <c r="F185" t="s">
-        <v>386</v>
+        <v>426</v>
       </c>
       <c r="G185" t="s">
         <v>427</v>
@@ -6306,13 +6306,13 @@
         <v>9</v>
       </c>
       <c r="D186" t="s">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="E186" t="s">
         <v>385</v>
       </c>
       <c r="F186" t="s">
-        <v>386</v>
+        <v>426</v>
       </c>
       <c r="G186" t="s">
         <v>427</v>
@@ -6329,13 +6329,13 @@
         <v>9</v>
       </c>
       <c r="D187" t="s">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="E187" t="s">
         <v>385</v>
       </c>
       <c r="F187" t="s">
-        <v>386</v>
+        <v>426</v>
       </c>
       <c r="G187" t="s">
         <v>427</v>
@@ -6352,13 +6352,13 @@
         <v>9</v>
       </c>
       <c r="D188" t="s">
-        <v>448</v>
+        <v>384</v>
       </c>
       <c r="E188" t="s">
         <v>385</v>
       </c>
       <c r="F188" t="s">
-        <v>386</v>
+        <v>448</v>
       </c>
       <c r="G188" t="s">
         <v>449</v>

--- a/api/xlsx/en/SectorGroup.xlsx
+++ b/api/xlsx/en/SectorGroup.xlsx
@@ -25,12 +25,12 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
@@ -46,12 +46,12 @@
     <t>active</t>
   </si>
   <si>
+    <t>Education</t>
+  </si>
+  <si>
     <t>110</t>
   </si>
   <si>
-    <t>Education</t>
-  </si>
-  <si>
     <t>111</t>
   </si>
   <si>
@@ -148,12 +148,12 @@
     <t>Health policy and administrative management</t>
   </si>
   <si>
+    <t>Health</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
-    <t>Health</t>
-  </si>
-  <si>
     <t>121</t>
   </si>
   <si>
@@ -280,12 +280,12 @@
     <t>Population policy and administrative management</t>
   </si>
   <si>
+    <t>Population Policies/Programmes &amp; Reproductive Health</t>
+  </si>
+  <si>
     <t>130</t>
   </si>
   <si>
-    <t>Population Policies/Programmes &amp; Reproductive Health</t>
-  </si>
-  <si>
     <t>13020</t>
   </si>
   <si>
@@ -316,12 +316,12 @@
     <t>Water sector policy and administrative management</t>
   </si>
   <si>
+    <t>Water Supply &amp; Sanitation</t>
+  </si>
+  <si>
     <t>140</t>
   </si>
   <si>
-    <t>Water Supply &amp; Sanitation</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -388,12 +388,12 @@
     <t>Public sector policy and administrative management</t>
   </si>
   <si>
+    <t>Government &amp; Civil Society</t>
+  </si>
+  <si>
     <t>150</t>
   </si>
   <si>
-    <t>Government &amp; Civil Society</t>
-  </si>
-  <si>
     <t>151</t>
   </si>
   <si>
@@ -538,12 +538,12 @@
     <t>Social Protection</t>
   </si>
   <si>
+    <t>Other Social Infrastructure &amp; Services</t>
+  </si>
+  <si>
     <t>160</t>
   </si>
   <si>
-    <t>Other Social Infrastructure &amp; Services</t>
-  </si>
-  <si>
     <t>16020</t>
   </si>
   <si>
@@ -610,12 +610,12 @@
     <t>Transport policy and administrative management</t>
   </si>
   <si>
+    <t>Transport &amp; Storage</t>
+  </si>
+  <si>
     <t>210</t>
   </si>
   <si>
-    <t>Transport &amp; Storage</t>
-  </si>
-  <si>
     <t>21020</t>
   </si>
   <si>
@@ -658,12 +658,12 @@
     <t>Communications policy and administrative management</t>
   </si>
   <si>
+    <t>Communications</t>
+  </si>
+  <si>
     <t>220</t>
   </si>
   <si>
-    <t>Communications</t>
-  </si>
-  <si>
     <t>22020</t>
   </si>
   <si>
@@ -688,12 +688,12 @@
     <t>Energy policy and administrative management</t>
   </si>
   <si>
+    <t>Energy</t>
+  </si>
+  <si>
     <t>230</t>
   </si>
   <si>
-    <t>Energy</t>
-  </si>
-  <si>
     <t>231</t>
   </si>
   <si>
@@ -898,12 +898,12 @@
     <t>Financial policy and administrative management</t>
   </si>
   <si>
+    <t>Banking &amp; Financial Services</t>
+  </si>
+  <si>
     <t>240</t>
   </si>
   <si>
-    <t>Banking &amp; Financial Services</t>
-  </si>
-  <si>
     <t>24020</t>
   </si>
   <si>
@@ -940,12 +940,12 @@
     <t>Business policy and administration</t>
   </si>
   <si>
+    <t>Business &amp; Other Services</t>
+  </si>
+  <si>
     <t>250</t>
   </si>
   <si>
-    <t>Business &amp; Other Services</t>
-  </si>
-  <si>
     <t>25020</t>
   </si>
   <si>
@@ -970,12 +970,12 @@
     <t>Agricultural policy and administrative management</t>
   </si>
   <si>
+    <t>Agriculture, Forestry, Fishing</t>
+  </si>
+  <si>
     <t>310</t>
   </si>
   <si>
-    <t>Agriculture, Forestry, Fishing</t>
-  </si>
-  <si>
     <t>311</t>
   </si>
   <si>
@@ -1168,12 +1168,12 @@
     <t>Industrial policy and administrative management</t>
   </si>
   <si>
+    <t>Industry, Mining, Construction</t>
+  </si>
+  <si>
     <t>320</t>
   </si>
   <si>
-    <t>Industry, Mining, Construction</t>
-  </si>
-  <si>
     <t>321</t>
   </si>
   <si>
@@ -1372,12 +1372,12 @@
     <t>Trade policy and administrative management</t>
   </si>
   <si>
+    <t>Trade Policies &amp; Regulations</t>
+  </si>
+  <si>
     <t>331</t>
   </si>
   <si>
-    <t>Trade Policies &amp; Regulations</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1414,24 +1414,24 @@
     <t>Tourism policy and administrative management</t>
   </si>
   <si>
+    <t>Tourism</t>
+  </si>
+  <si>
     <t>332</t>
   </si>
   <si>
-    <t>Tourism</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
     <t>Environmental policy and administrative management</t>
   </si>
   <si>
+    <t>General Environment Protection</t>
+  </si>
+  <si>
     <t>410</t>
   </si>
   <si>
-    <t>General Environment Protection</t>
-  </si>
-  <si>
     <t>41020</t>
   </si>
   <si>
@@ -1468,12 +1468,12 @@
     <t>Multisector aid</t>
   </si>
   <si>
+    <t>Other Multisector</t>
+  </si>
+  <si>
     <t>430</t>
   </si>
   <si>
-    <t>Other Multisector</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -1534,36 +1534,36 @@
     <t>General budget support-related aid</t>
   </si>
   <si>
+    <t>General Budget Support</t>
+  </si>
+  <si>
     <t>510</t>
   </si>
   <si>
-    <t>General Budget Support</t>
-  </si>
-  <si>
     <t>52010</t>
   </si>
   <si>
     <t>Food assistance</t>
   </si>
   <si>
+    <t>Development Food Assistance</t>
+  </si>
+  <si>
     <t>520</t>
   </si>
   <si>
-    <t>Development Food Assistance</t>
-  </si>
-  <si>
     <t>53030</t>
   </si>
   <si>
     <t>Import support (capital goods)</t>
   </si>
   <si>
+    <t>Other Commodity Assistance</t>
+  </si>
+  <si>
     <t>530</t>
   </si>
   <si>
-    <t>Other Commodity Assistance</t>
-  </si>
-  <si>
     <t>53040</t>
   </si>
   <si>
@@ -1576,12 +1576,12 @@
     <t>Action relating to debt</t>
   </si>
   <si>
+    <t>Action Relating to Debt</t>
+  </si>
+  <si>
     <t>600</t>
   </si>
   <si>
-    <t>Action Relating to Debt</t>
-  </si>
-  <si>
     <t>60020</t>
   </si>
   <si>
@@ -1624,12 +1624,12 @@
     <t>Material relief assistance and services</t>
   </si>
   <si>
+    <t>Emergency Response</t>
+  </si>
+  <si>
     <t>720</t>
   </si>
   <si>
-    <t>Emergency Response</t>
-  </si>
-  <si>
     <t>72040</t>
   </si>
   <si>
@@ -1648,58 +1648,58 @@
     <t>Immediate post-emergency reconstruction and rehabilitation</t>
   </si>
   <si>
+    <t>Reconstruction Relief &amp; Rehabilitation</t>
+  </si>
+  <si>
     <t>730</t>
   </si>
   <si>
-    <t>Reconstruction Relief &amp; Rehabilitation</t>
-  </si>
-  <si>
     <t>74020</t>
   </si>
   <si>
     <t>Multi-hazard response preparedness</t>
   </si>
   <si>
+    <t>Disaster Prevention &amp; Preparedness</t>
+  </si>
+  <si>
     <t>740</t>
   </si>
   <si>
-    <t>Disaster Prevention &amp; Preparedness</t>
-  </si>
-  <si>
     <t>91010</t>
   </si>
   <si>
     <t>Administrative costs (non-sector allocable)</t>
   </si>
   <si>
+    <t>Administrative Costs of Donors</t>
+  </si>
+  <si>
     <t>910</t>
   </si>
   <si>
-    <t>Administrative Costs of Donors</t>
-  </si>
-  <si>
     <t>93010</t>
   </si>
   <si>
     <t>Refugees/asylum seekers in donor countries (non-sector allocable)</t>
   </si>
   <si>
+    <t>Refugees in Donor Countries</t>
+  </si>
+  <si>
     <t>930</t>
   </si>
   <si>
-    <t>Refugees in Donor Countries</t>
-  </si>
-  <si>
     <t>99810</t>
   </si>
   <si>
     <t>Sectors not specified</t>
   </si>
   <si>
+    <t>Unallocated / Unspecified</t>
+  </si>
+  <si>
     <t>998</t>
-  </si>
-  <si>
-    <t>Unallocated / Unspecified</t>
   </si>
   <si>
     <t>99820</t>
@@ -2770,10 +2770,10 @@
         <v>89</v>
       </c>
       <c r="F32" t="s">
+        <v>89</v>
+      </c>
+      <c r="G32" t="s">
         <v>88</v>
-      </c>
-      <c r="G32" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2793,10 +2793,10 @@
         <v>89</v>
       </c>
       <c r="F33" t="s">
+        <v>89</v>
+      </c>
+      <c r="G33" t="s">
         <v>88</v>
-      </c>
-      <c r="G33" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2816,10 +2816,10 @@
         <v>89</v>
       </c>
       <c r="F34" t="s">
+        <v>89</v>
+      </c>
+      <c r="G34" t="s">
         <v>88</v>
-      </c>
-      <c r="G34" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2839,10 +2839,10 @@
         <v>89</v>
       </c>
       <c r="F35" t="s">
+        <v>89</v>
+      </c>
+      <c r="G35" t="s">
         <v>88</v>
-      </c>
-      <c r="G35" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2862,10 +2862,10 @@
         <v>89</v>
       </c>
       <c r="F36" t="s">
+        <v>89</v>
+      </c>
+      <c r="G36" t="s">
         <v>88</v>
-      </c>
-      <c r="G36" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2885,10 +2885,10 @@
         <v>101</v>
       </c>
       <c r="F37" t="s">
+        <v>101</v>
+      </c>
+      <c r="G37" t="s">
         <v>100</v>
-      </c>
-      <c r="G37" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2908,10 +2908,10 @@
         <v>101</v>
       </c>
       <c r="F38" t="s">
+        <v>101</v>
+      </c>
+      <c r="G38" t="s">
         <v>100</v>
-      </c>
-      <c r="G38" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2931,10 +2931,10 @@
         <v>101</v>
       </c>
       <c r="F39" t="s">
+        <v>101</v>
+      </c>
+      <c r="G39" t="s">
         <v>100</v>
-      </c>
-      <c r="G39" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2954,10 +2954,10 @@
         <v>101</v>
       </c>
       <c r="F40" t="s">
+        <v>101</v>
+      </c>
+      <c r="G40" t="s">
         <v>100</v>
-      </c>
-      <c r="G40" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2977,10 +2977,10 @@
         <v>101</v>
       </c>
       <c r="F41" t="s">
+        <v>101</v>
+      </c>
+      <c r="G41" t="s">
         <v>100</v>
-      </c>
-      <c r="G41" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -3000,10 +3000,10 @@
         <v>101</v>
       </c>
       <c r="F42" t="s">
+        <v>101</v>
+      </c>
+      <c r="G42" t="s">
         <v>100</v>
-      </c>
-      <c r="G42" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3023,10 +3023,10 @@
         <v>101</v>
       </c>
       <c r="F43" t="s">
+        <v>101</v>
+      </c>
+      <c r="G43" t="s">
         <v>100</v>
-      </c>
-      <c r="G43" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3046,10 +3046,10 @@
         <v>101</v>
       </c>
       <c r="F44" t="s">
+        <v>101</v>
+      </c>
+      <c r="G44" t="s">
         <v>100</v>
-      </c>
-      <c r="G44" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3069,10 +3069,10 @@
         <v>101</v>
       </c>
       <c r="F45" t="s">
+        <v>101</v>
+      </c>
+      <c r="G45" t="s">
         <v>100</v>
-      </c>
-      <c r="G45" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3092,10 +3092,10 @@
         <v>101</v>
       </c>
       <c r="F46" t="s">
+        <v>101</v>
+      </c>
+      <c r="G46" t="s">
         <v>100</v>
-      </c>
-      <c r="G46" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3115,10 +3115,10 @@
         <v>101</v>
       </c>
       <c r="F47" t="s">
+        <v>101</v>
+      </c>
+      <c r="G47" t="s">
         <v>100</v>
-      </c>
-      <c r="G47" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3644,10 +3644,10 @@
         <v>175</v>
       </c>
       <c r="F70" t="s">
+        <v>175</v>
+      </c>
+      <c r="G70" t="s">
         <v>174</v>
-      </c>
-      <c r="G70" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3667,10 +3667,10 @@
         <v>175</v>
       </c>
       <c r="F71" t="s">
+        <v>175</v>
+      </c>
+      <c r="G71" t="s">
         <v>174</v>
-      </c>
-      <c r="G71" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3690,10 +3690,10 @@
         <v>175</v>
       </c>
       <c r="F72" t="s">
+        <v>175</v>
+      </c>
+      <c r="G72" t="s">
         <v>174</v>
-      </c>
-      <c r="G72" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3713,10 +3713,10 @@
         <v>175</v>
       </c>
       <c r="F73" t="s">
+        <v>175</v>
+      </c>
+      <c r="G73" t="s">
         <v>174</v>
-      </c>
-      <c r="G73" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3736,10 +3736,10 @@
         <v>175</v>
       </c>
       <c r="F74" t="s">
+        <v>175</v>
+      </c>
+      <c r="G74" t="s">
         <v>174</v>
-      </c>
-      <c r="G74" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3759,10 +3759,10 @@
         <v>175</v>
       </c>
       <c r="F75" t="s">
+        <v>175</v>
+      </c>
+      <c r="G75" t="s">
         <v>174</v>
-      </c>
-      <c r="G75" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3782,10 +3782,10 @@
         <v>175</v>
       </c>
       <c r="F76" t="s">
+        <v>175</v>
+      </c>
+      <c r="G76" t="s">
         <v>174</v>
-      </c>
-      <c r="G76" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3805,10 +3805,10 @@
         <v>175</v>
       </c>
       <c r="F77" t="s">
+        <v>175</v>
+      </c>
+      <c r="G77" t="s">
         <v>174</v>
-      </c>
-      <c r="G77" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3828,10 +3828,10 @@
         <v>175</v>
       </c>
       <c r="F78" t="s">
+        <v>175</v>
+      </c>
+      <c r="G78" t="s">
         <v>174</v>
-      </c>
-      <c r="G78" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3851,10 +3851,10 @@
         <v>175</v>
       </c>
       <c r="F79" t="s">
+        <v>175</v>
+      </c>
+      <c r="G79" t="s">
         <v>174</v>
-      </c>
-      <c r="G79" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3874,10 +3874,10 @@
         <v>175</v>
       </c>
       <c r="F80" t="s">
+        <v>175</v>
+      </c>
+      <c r="G80" t="s">
         <v>174</v>
-      </c>
-      <c r="G80" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3897,10 +3897,10 @@
         <v>199</v>
       </c>
       <c r="F81" t="s">
+        <v>199</v>
+      </c>
+      <c r="G81" t="s">
         <v>198</v>
-      </c>
-      <c r="G81" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3920,10 +3920,10 @@
         <v>199</v>
       </c>
       <c r="F82" t="s">
+        <v>199</v>
+      </c>
+      <c r="G82" t="s">
         <v>198</v>
-      </c>
-      <c r="G82" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3943,10 +3943,10 @@
         <v>199</v>
       </c>
       <c r="F83" t="s">
+        <v>199</v>
+      </c>
+      <c r="G83" t="s">
         <v>198</v>
-      </c>
-      <c r="G83" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3966,10 +3966,10 @@
         <v>199</v>
       </c>
       <c r="F84" t="s">
+        <v>199</v>
+      </c>
+      <c r="G84" t="s">
         <v>198</v>
-      </c>
-      <c r="G84" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3989,10 +3989,10 @@
         <v>199</v>
       </c>
       <c r="F85" t="s">
+        <v>199</v>
+      </c>
+      <c r="G85" t="s">
         <v>198</v>
-      </c>
-      <c r="G85" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4012,10 +4012,10 @@
         <v>199</v>
       </c>
       <c r="F86" t="s">
+        <v>199</v>
+      </c>
+      <c r="G86" t="s">
         <v>198</v>
-      </c>
-      <c r="G86" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4035,10 +4035,10 @@
         <v>199</v>
       </c>
       <c r="F87" t="s">
+        <v>199</v>
+      </c>
+      <c r="G87" t="s">
         <v>198</v>
-      </c>
-      <c r="G87" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4058,10 +4058,10 @@
         <v>215</v>
       </c>
       <c r="F88" t="s">
+        <v>215</v>
+      </c>
+      <c r="G88" t="s">
         <v>214</v>
-      </c>
-      <c r="G88" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4081,10 +4081,10 @@
         <v>215</v>
       </c>
       <c r="F89" t="s">
+        <v>215</v>
+      </c>
+      <c r="G89" t="s">
         <v>214</v>
-      </c>
-      <c r="G89" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4104,10 +4104,10 @@
         <v>215</v>
       </c>
       <c r="F90" t="s">
+        <v>215</v>
+      </c>
+      <c r="G90" t="s">
         <v>214</v>
-      </c>
-      <c r="G90" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4127,10 +4127,10 @@
         <v>215</v>
       </c>
       <c r="F91" t="s">
+        <v>215</v>
+      </c>
+      <c r="G91" t="s">
         <v>214</v>
-      </c>
-      <c r="G91" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4794,10 +4794,10 @@
         <v>295</v>
       </c>
       <c r="F120" t="s">
+        <v>295</v>
+      </c>
+      <c r="G120" t="s">
         <v>294</v>
-      </c>
-      <c r="G120" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4817,10 +4817,10 @@
         <v>295</v>
       </c>
       <c r="F121" t="s">
+        <v>295</v>
+      </c>
+      <c r="G121" t="s">
         <v>294</v>
-      </c>
-      <c r="G121" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4840,10 +4840,10 @@
         <v>295</v>
       </c>
       <c r="F122" t="s">
+        <v>295</v>
+      </c>
+      <c r="G122" t="s">
         <v>294</v>
-      </c>
-      <c r="G122" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4863,10 +4863,10 @@
         <v>295</v>
       </c>
       <c r="F123" t="s">
+        <v>295</v>
+      </c>
+      <c r="G123" t="s">
         <v>294</v>
-      </c>
-      <c r="G123" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4886,10 +4886,10 @@
         <v>295</v>
       </c>
       <c r="F124" t="s">
+        <v>295</v>
+      </c>
+      <c r="G124" t="s">
         <v>294</v>
-      </c>
-      <c r="G124" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4909,10 +4909,10 @@
         <v>295</v>
       </c>
       <c r="F125" t="s">
+        <v>295</v>
+      </c>
+      <c r="G125" t="s">
         <v>294</v>
-      </c>
-      <c r="G125" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4932,10 +4932,10 @@
         <v>309</v>
       </c>
       <c r="F126" t="s">
+        <v>309</v>
+      </c>
+      <c r="G126" t="s">
         <v>308</v>
-      </c>
-      <c r="G126" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4955,10 +4955,10 @@
         <v>309</v>
       </c>
       <c r="F127" t="s">
+        <v>309</v>
+      </c>
+      <c r="G127" t="s">
         <v>308</v>
-      </c>
-      <c r="G127" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4978,10 +4978,10 @@
         <v>309</v>
       </c>
       <c r="F128" t="s">
+        <v>309</v>
+      </c>
+      <c r="G128" t="s">
         <v>308</v>
-      </c>
-      <c r="G128" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -5001,10 +5001,10 @@
         <v>309</v>
       </c>
       <c r="F129" t="s">
+        <v>309</v>
+      </c>
+      <c r="G129" t="s">
         <v>308</v>
-      </c>
-      <c r="G129" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -6381,10 +6381,10 @@
         <v>453</v>
       </c>
       <c r="F189" t="s">
+        <v>453</v>
+      </c>
+      <c r="G189" t="s">
         <v>452</v>
-      </c>
-      <c r="G189" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6404,10 +6404,10 @@
         <v>453</v>
       </c>
       <c r="F190" t="s">
+        <v>453</v>
+      </c>
+      <c r="G190" t="s">
         <v>452</v>
-      </c>
-      <c r="G190" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6427,10 +6427,10 @@
         <v>453</v>
       </c>
       <c r="F191" t="s">
+        <v>453</v>
+      </c>
+      <c r="G191" t="s">
         <v>452</v>
-      </c>
-      <c r="G191" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6450,10 +6450,10 @@
         <v>453</v>
       </c>
       <c r="F192" t="s">
+        <v>453</v>
+      </c>
+      <c r="G192" t="s">
         <v>452</v>
-      </c>
-      <c r="G192" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6473,10 +6473,10 @@
         <v>453</v>
       </c>
       <c r="F193" t="s">
+        <v>453</v>
+      </c>
+      <c r="G193" t="s">
         <v>452</v>
-      </c>
-      <c r="G193" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6496,10 +6496,10 @@
         <v>453</v>
       </c>
       <c r="F194" t="s">
+        <v>453</v>
+      </c>
+      <c r="G194" t="s">
         <v>452</v>
-      </c>
-      <c r="G194" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6519,10 +6519,10 @@
         <v>467</v>
       </c>
       <c r="F195" t="s">
+        <v>467</v>
+      </c>
+      <c r="G195" t="s">
         <v>466</v>
-      </c>
-      <c r="G195" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6542,10 +6542,10 @@
         <v>471</v>
       </c>
       <c r="F196" t="s">
+        <v>471</v>
+      </c>
+      <c r="G196" t="s">
         <v>470</v>
-      </c>
-      <c r="G196" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6565,10 +6565,10 @@
         <v>471</v>
       </c>
       <c r="F197" t="s">
+        <v>471</v>
+      </c>
+      <c r="G197" t="s">
         <v>470</v>
-      </c>
-      <c r="G197" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6588,10 +6588,10 @@
         <v>471</v>
       </c>
       <c r="F198" t="s">
+        <v>471</v>
+      </c>
+      <c r="G198" t="s">
         <v>470</v>
-      </c>
-      <c r="G198" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6611,10 +6611,10 @@
         <v>471</v>
       </c>
       <c r="F199" t="s">
+        <v>471</v>
+      </c>
+      <c r="G199" t="s">
         <v>470</v>
-      </c>
-      <c r="G199" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6634,10 +6634,10 @@
         <v>471</v>
       </c>
       <c r="F200" t="s">
+        <v>471</v>
+      </c>
+      <c r="G200" t="s">
         <v>470</v>
-      </c>
-      <c r="G200" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6657,10 +6657,10 @@
         <v>471</v>
       </c>
       <c r="F201" t="s">
+        <v>471</v>
+      </c>
+      <c r="G201" t="s">
         <v>470</v>
-      </c>
-      <c r="G201" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6680,10 +6680,10 @@
         <v>485</v>
       </c>
       <c r="F202" t="s">
+        <v>485</v>
+      </c>
+      <c r="G202" t="s">
         <v>484</v>
-      </c>
-      <c r="G202" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6703,10 +6703,10 @@
         <v>485</v>
       </c>
       <c r="F203" t="s">
+        <v>485</v>
+      </c>
+      <c r="G203" t="s">
         <v>484</v>
-      </c>
-      <c r="G203" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6726,10 +6726,10 @@
         <v>485</v>
       </c>
       <c r="F204" t="s">
+        <v>485</v>
+      </c>
+      <c r="G204" t="s">
         <v>484</v>
-      </c>
-      <c r="G204" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6749,10 +6749,10 @@
         <v>485</v>
       </c>
       <c r="F205" t="s">
+        <v>485</v>
+      </c>
+      <c r="G205" t="s">
         <v>484</v>
-      </c>
-      <c r="G205" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6772,10 +6772,10 @@
         <v>485</v>
       </c>
       <c r="F206" t="s">
+        <v>485</v>
+      </c>
+      <c r="G206" t="s">
         <v>484</v>
-      </c>
-      <c r="G206" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6795,10 +6795,10 @@
         <v>485</v>
       </c>
       <c r="F207" t="s">
+        <v>485</v>
+      </c>
+      <c r="G207" t="s">
         <v>484</v>
-      </c>
-      <c r="G207" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6818,10 +6818,10 @@
         <v>485</v>
       </c>
       <c r="F208" t="s">
+        <v>485</v>
+      </c>
+      <c r="G208" t="s">
         <v>484</v>
-      </c>
-      <c r="G208" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6841,10 +6841,10 @@
         <v>485</v>
       </c>
       <c r="F209" t="s">
+        <v>485</v>
+      </c>
+      <c r="G209" t="s">
         <v>484</v>
-      </c>
-      <c r="G209" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6864,10 +6864,10 @@
         <v>485</v>
       </c>
       <c r="F210" t="s">
+        <v>485</v>
+      </c>
+      <c r="G210" t="s">
         <v>484</v>
-      </c>
-      <c r="G210" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6887,10 +6887,10 @@
         <v>485</v>
       </c>
       <c r="F211" t="s">
+        <v>485</v>
+      </c>
+      <c r="G211" t="s">
         <v>484</v>
-      </c>
-      <c r="G211" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6910,10 +6910,10 @@
         <v>507</v>
       </c>
       <c r="F212" t="s">
+        <v>507</v>
+      </c>
+      <c r="G212" t="s">
         <v>506</v>
-      </c>
-      <c r="G212" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6933,10 +6933,10 @@
         <v>511</v>
       </c>
       <c r="F213" t="s">
+        <v>511</v>
+      </c>
+      <c r="G213" t="s">
         <v>510</v>
-      </c>
-      <c r="G213" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6956,10 +6956,10 @@
         <v>515</v>
       </c>
       <c r="F214" t="s">
+        <v>515</v>
+      </c>
+      <c r="G214" t="s">
         <v>514</v>
-      </c>
-      <c r="G214" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6979,10 +6979,10 @@
         <v>515</v>
       </c>
       <c r="F215" t="s">
+        <v>515</v>
+      </c>
+      <c r="G215" t="s">
         <v>514</v>
-      </c>
-      <c r="G215" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -7002,10 +7002,10 @@
         <v>521</v>
       </c>
       <c r="F216" t="s">
+        <v>521</v>
+      </c>
+      <c r="G216" t="s">
         <v>520</v>
-      </c>
-      <c r="G216" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -7025,10 +7025,10 @@
         <v>521</v>
       </c>
       <c r="F217" t="s">
+        <v>521</v>
+      </c>
+      <c r="G217" t="s">
         <v>520</v>
-      </c>
-      <c r="G217" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -7048,10 +7048,10 @@
         <v>521</v>
       </c>
       <c r="F218" t="s">
+        <v>521</v>
+      </c>
+      <c r="G218" t="s">
         <v>520</v>
-      </c>
-      <c r="G218" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -7071,10 +7071,10 @@
         <v>521</v>
       </c>
       <c r="F219" t="s">
+        <v>521</v>
+      </c>
+      <c r="G219" t="s">
         <v>520</v>
-      </c>
-      <c r="G219" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -7094,10 +7094,10 @@
         <v>521</v>
       </c>
       <c r="F220" t="s">
+        <v>521</v>
+      </c>
+      <c r="G220" t="s">
         <v>520</v>
-      </c>
-      <c r="G220" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -7117,10 +7117,10 @@
         <v>521</v>
       </c>
       <c r="F221" t="s">
+        <v>521</v>
+      </c>
+      <c r="G221" t="s">
         <v>520</v>
-      </c>
-      <c r="G221" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -7140,10 +7140,10 @@
         <v>521</v>
       </c>
       <c r="F222" t="s">
+        <v>521</v>
+      </c>
+      <c r="G222" t="s">
         <v>520</v>
-      </c>
-      <c r="G222" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -7163,10 +7163,10 @@
         <v>537</v>
       </c>
       <c r="F223" t="s">
+        <v>537</v>
+      </c>
+      <c r="G223" t="s">
         <v>536</v>
-      </c>
-      <c r="G223" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -7186,10 +7186,10 @@
         <v>537</v>
       </c>
       <c r="F224" t="s">
+        <v>537</v>
+      </c>
+      <c r="G224" t="s">
         <v>536</v>
-      </c>
-      <c r="G224" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -7209,10 +7209,10 @@
         <v>537</v>
       </c>
       <c r="F225" t="s">
+        <v>537</v>
+      </c>
+      <c r="G225" t="s">
         <v>536</v>
-      </c>
-      <c r="G225" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -7232,10 +7232,10 @@
         <v>545</v>
       </c>
       <c r="F226" t="s">
+        <v>545</v>
+      </c>
+      <c r="G226" t="s">
         <v>544</v>
-      </c>
-      <c r="G226" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -7255,10 +7255,10 @@
         <v>549</v>
       </c>
       <c r="F227" t="s">
+        <v>549</v>
+      </c>
+      <c r="G227" t="s">
         <v>548</v>
-      </c>
-      <c r="G227" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -7278,10 +7278,10 @@
         <v>553</v>
       </c>
       <c r="F228" t="s">
+        <v>553</v>
+      </c>
+      <c r="G228" t="s">
         <v>552</v>
-      </c>
-      <c r="G228" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -7301,10 +7301,10 @@
         <v>557</v>
       </c>
       <c r="F229" t="s">
+        <v>557</v>
+      </c>
+      <c r="G229" t="s">
         <v>556</v>
-      </c>
-      <c r="G229" t="s">
-        <v>557</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -7324,10 +7324,10 @@
         <v>561</v>
       </c>
       <c r="F230" t="s">
+        <v>561</v>
+      </c>
+      <c r="G230" t="s">
         <v>560</v>
-      </c>
-      <c r="G230" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -7347,10 +7347,10 @@
         <v>561</v>
       </c>
       <c r="F231" t="s">
+        <v>561</v>
+      </c>
+      <c r="G231" t="s">
         <v>560</v>
-      </c>
-      <c r="G231" t="s">
-        <v>561</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/en/SectorGroup.xlsx
+++ b/api/xlsx/en/SectorGroup.xlsx
@@ -28,15 +28,15 @@
     <t>codeforiati:group-name</t>
   </si>
   <si>
+    <t>codeforiati:category-name</t>
+  </si>
+  <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
-    <t>codeforiati:category-name</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -49,15 +49,15 @@
     <t>Education</t>
   </si>
   <si>
+    <t>Education, Level Unspecified</t>
+  </si>
+  <si>
     <t>110</t>
   </si>
   <si>
     <t>111</t>
   </si>
   <si>
-    <t>Education, Level Unspecified</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -82,12 +82,12 @@
     <t>Primary education</t>
   </si>
   <si>
+    <t>Basic Education</t>
+  </si>
+  <si>
     <t>112</t>
   </si>
   <si>
-    <t>Basic Education</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -112,12 +112,12 @@
     <t>Secondary education</t>
   </si>
   <si>
+    <t>Secondary Education</t>
+  </si>
+  <si>
     <t>113</t>
   </si>
   <si>
-    <t>Secondary Education</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
@@ -130,12 +130,12 @@
     <t>Higher education</t>
   </si>
   <si>
+    <t>Post-Secondary Education</t>
+  </si>
+  <si>
     <t>114</t>
   </si>
   <si>
-    <t>Post-Secondary Education</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -151,15 +151,15 @@
     <t>Health</t>
   </si>
   <si>
+    <t>Health, General</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
     <t>121</t>
   </si>
   <si>
-    <t>Health, General</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -184,12 +184,12 @@
     <t>Basic health care</t>
   </si>
   <si>
+    <t>Basic Health</t>
+  </si>
+  <si>
     <t>122</t>
   </si>
   <si>
-    <t>Basic Health</t>
-  </si>
-  <si>
     <t>12230</t>
   </si>
   <si>
@@ -238,12 +238,12 @@
     <t>NCDs control, general</t>
   </si>
   <si>
+    <t>Non-communicable diseases (NCDs)</t>
+  </si>
+  <si>
     <t>123</t>
   </si>
   <si>
-    <t>Non-communicable diseases (NCDs)</t>
-  </si>
-  <si>
     <t>12320</t>
   </si>
   <si>
@@ -391,15 +391,15 @@
     <t>Government &amp; Civil Society</t>
   </si>
   <si>
+    <t>Government &amp; Civil Society-general</t>
+  </si>
+  <si>
     <t>150</t>
   </si>
   <si>
     <t>151</t>
   </si>
   <si>
-    <t>Government &amp; Civil Society-general</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -496,12 +496,12 @@
     <t>Security system management and reform</t>
   </si>
   <si>
+    <t>Conflict, Peace &amp; Security</t>
+  </si>
+  <si>
     <t>152</t>
   </si>
   <si>
-    <t>Conflict, Peace &amp; Security</t>
-  </si>
-  <si>
     <t>15220</t>
   </si>
   <si>
@@ -691,15 +691,15 @@
     <t>Energy</t>
   </si>
   <si>
+    <t>Energy Policy</t>
+  </si>
+  <si>
     <t>230</t>
   </si>
   <si>
     <t>231</t>
   </si>
   <si>
-    <t>Energy Policy</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -724,12 +724,12 @@
     <t>Energy generation, renewable sources - multiple technologies</t>
   </si>
   <si>
+    <t>Energy generation, renewable sources</t>
+  </si>
+  <si>
     <t>232</t>
   </si>
   <si>
-    <t>Energy generation, renewable sources</t>
-  </si>
-  <si>
     <t>23220</t>
   </si>
   <si>
@@ -784,12 +784,12 @@
     <t>Energy generation, non-renewable sources, unspecified</t>
   </si>
   <si>
+    <t>Energy generation, non-renewable sources</t>
+  </si>
+  <si>
     <t>233</t>
   </si>
   <si>
-    <t>Energy generation, non-renewable sources</t>
-  </si>
-  <si>
     <t>23320</t>
   </si>
   <si>
@@ -826,36 +826,36 @@
     <t>Hybrid energy electric power plants</t>
   </si>
   <si>
+    <t>Hybrid energy plants</t>
+  </si>
+  <si>
     <t>234</t>
   </si>
   <si>
-    <t>Hybrid energy plants</t>
-  </si>
-  <si>
     <t>23510</t>
   </si>
   <si>
     <t>Nuclear energy electric power plants and nuclear safety</t>
   </si>
   <si>
+    <t>Nuclear energy plants</t>
+  </si>
+  <si>
     <t>235</t>
   </si>
   <si>
-    <t>Nuclear energy plants</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
     <t>Heat plants</t>
   </si>
   <si>
+    <t>Energy distribution</t>
+  </si>
+  <si>
     <t>236</t>
   </si>
   <si>
-    <t>Energy distribution</t>
-  </si>
-  <si>
     <t>23620</t>
   </si>
   <si>
@@ -973,15 +973,15 @@
     <t>Agriculture, Forestry, Fishing</t>
   </si>
   <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
     <t>310</t>
   </si>
   <si>
     <t>311</t>
   </si>
   <si>
-    <t>Agriculture</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1090,12 +1090,12 @@
     <t>Forestry policy and administrative management</t>
   </si>
   <si>
+    <t>Forestry</t>
+  </si>
+  <si>
     <t>312</t>
   </si>
   <si>
-    <t>Forestry</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -1132,12 +1132,12 @@
     <t>Fishing policy and administrative management</t>
   </si>
   <si>
+    <t>Fishing</t>
+  </si>
+  <si>
     <t>313</t>
   </si>
   <si>
-    <t>Fishing</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -1171,15 +1171,15 @@
     <t>Industry, Mining, Construction</t>
   </si>
   <si>
+    <t>Industry</t>
+  </si>
+  <si>
     <t>320</t>
   </si>
   <si>
     <t>321</t>
   </si>
   <si>
-    <t>Industry</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1294,12 +1294,12 @@
     <t>Mineral/mining policy and administrative management</t>
   </si>
   <si>
+    <t>Mineral Resources &amp; Mining</t>
+  </si>
+  <si>
     <t>322</t>
   </si>
   <si>
-    <t>Mineral Resources &amp; Mining</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -1360,10 +1360,10 @@
     <t>Construction policy and administrative management</t>
   </si>
   <si>
+    <t>Construction</t>
+  </si>
+  <si>
     <t>323</t>
-  </si>
-  <si>
-    <t>Construction</t>
   </si>
   <si>
     <t>33110</t>
@@ -2169,10 +2169,10 @@
         <v>10</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F6" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G6" t="s">
         <v>23</v>
@@ -2192,10 +2192,10 @@
         <v>10</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F7" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G7" t="s">
         <v>23</v>
@@ -2215,10 +2215,10 @@
         <v>10</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F8" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G8" t="s">
         <v>23</v>
@@ -2238,10 +2238,10 @@
         <v>10</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F9" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G9" t="s">
         <v>23</v>
@@ -2261,10 +2261,10 @@
         <v>10</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F10" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="G10" t="s">
         <v>33</v>
@@ -2284,10 +2284,10 @@
         <v>10</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F11" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="G11" t="s">
         <v>33</v>
@@ -2307,10 +2307,10 @@
         <v>10</v>
       </c>
       <c r="E12" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="F12" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="G12" t="s">
         <v>39</v>
@@ -2330,10 +2330,10 @@
         <v>10</v>
       </c>
       <c r="E13" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="F13" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="G13" t="s">
         <v>39</v>
@@ -2445,10 +2445,10 @@
         <v>44</v>
       </c>
       <c r="E18" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="F18" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G18" t="s">
         <v>57</v>
@@ -2468,10 +2468,10 @@
         <v>44</v>
       </c>
       <c r="E19" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="F19" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G19" t="s">
         <v>57</v>
@@ -2491,10 +2491,10 @@
         <v>44</v>
       </c>
       <c r="E20" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="F20" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G20" t="s">
         <v>57</v>
@@ -2514,10 +2514,10 @@
         <v>44</v>
       </c>
       <c r="E21" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="F21" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G21" t="s">
         <v>57</v>
@@ -2537,10 +2537,10 @@
         <v>44</v>
       </c>
       <c r="E22" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="F22" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G22" t="s">
         <v>57</v>
@@ -2560,10 +2560,10 @@
         <v>44</v>
       </c>
       <c r="E23" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="F23" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G23" t="s">
         <v>57</v>
@@ -2583,10 +2583,10 @@
         <v>44</v>
       </c>
       <c r="E24" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="F24" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G24" t="s">
         <v>57</v>
@@ -2606,10 +2606,10 @@
         <v>44</v>
       </c>
       <c r="E25" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="F25" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G25" t="s">
         <v>57</v>
@@ -2629,10 +2629,10 @@
         <v>44</v>
       </c>
       <c r="E26" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="F26" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G26" t="s">
         <v>75</v>
@@ -2652,10 +2652,10 @@
         <v>44</v>
       </c>
       <c r="E27" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="F27" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G27" t="s">
         <v>75</v>
@@ -2675,10 +2675,10 @@
         <v>44</v>
       </c>
       <c r="E28" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="F28" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G28" t="s">
         <v>75</v>
@@ -2698,10 +2698,10 @@
         <v>44</v>
       </c>
       <c r="E29" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="F29" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G29" t="s">
         <v>75</v>
@@ -2721,10 +2721,10 @@
         <v>44</v>
       </c>
       <c r="E30" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="F30" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G30" t="s">
         <v>75</v>
@@ -2744,10 +2744,10 @@
         <v>44</v>
       </c>
       <c r="E31" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="F31" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G31" t="s">
         <v>75</v>
@@ -2767,13 +2767,13 @@
         <v>88</v>
       </c>
       <c r="E32" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F32" t="s">
         <v>89</v>
       </c>
       <c r="G32" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2790,13 +2790,13 @@
         <v>88</v>
       </c>
       <c r="E33" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F33" t="s">
         <v>89</v>
       </c>
       <c r="G33" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2813,13 +2813,13 @@
         <v>88</v>
       </c>
       <c r="E34" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F34" t="s">
         <v>89</v>
       </c>
       <c r="G34" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2836,13 +2836,13 @@
         <v>88</v>
       </c>
       <c r="E35" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F35" t="s">
         <v>89</v>
       </c>
       <c r="G35" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2859,13 +2859,13 @@
         <v>88</v>
       </c>
       <c r="E36" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F36" t="s">
         <v>89</v>
       </c>
       <c r="G36" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2882,13 +2882,13 @@
         <v>100</v>
       </c>
       <c r="E37" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F37" t="s">
         <v>101</v>
       </c>
       <c r="G37" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2905,13 +2905,13 @@
         <v>100</v>
       </c>
       <c r="E38" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F38" t="s">
         <v>101</v>
       </c>
       <c r="G38" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2928,13 +2928,13 @@
         <v>100</v>
       </c>
       <c r="E39" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F39" t="s">
         <v>101</v>
       </c>
       <c r="G39" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2951,13 +2951,13 @@
         <v>100</v>
       </c>
       <c r="E40" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F40" t="s">
         <v>101</v>
       </c>
       <c r="G40" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2974,13 +2974,13 @@
         <v>100</v>
       </c>
       <c r="E41" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F41" t="s">
         <v>101</v>
       </c>
       <c r="G41" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2997,13 +2997,13 @@
         <v>100</v>
       </c>
       <c r="E42" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F42" t="s">
         <v>101</v>
       </c>
       <c r="G42" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3020,13 +3020,13 @@
         <v>100</v>
       </c>
       <c r="E43" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F43" t="s">
         <v>101</v>
       </c>
       <c r="G43" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3043,13 +3043,13 @@
         <v>100</v>
       </c>
       <c r="E44" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F44" t="s">
         <v>101</v>
       </c>
       <c r="G44" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3066,13 +3066,13 @@
         <v>100</v>
       </c>
       <c r="E45" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F45" t="s">
         <v>101</v>
       </c>
       <c r="G45" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3089,13 +3089,13 @@
         <v>100</v>
       </c>
       <c r="E46" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F46" t="s">
         <v>101</v>
       </c>
       <c r="G46" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3112,13 +3112,13 @@
         <v>100</v>
       </c>
       <c r="E47" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F47" t="s">
         <v>101</v>
       </c>
       <c r="G47" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3503,10 +3503,10 @@
         <v>124</v>
       </c>
       <c r="E64" t="s">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="F64" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="G64" t="s">
         <v>161</v>
@@ -3526,10 +3526,10 @@
         <v>124</v>
       </c>
       <c r="E65" t="s">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="F65" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="G65" t="s">
         <v>161</v>
@@ -3549,10 +3549,10 @@
         <v>124</v>
       </c>
       <c r="E66" t="s">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="F66" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="G66" t="s">
         <v>161</v>
@@ -3572,10 +3572,10 @@
         <v>124</v>
       </c>
       <c r="E67" t="s">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="F67" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="G67" t="s">
         <v>161</v>
@@ -3595,10 +3595,10 @@
         <v>124</v>
       </c>
       <c r="E68" t="s">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="F68" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="G68" t="s">
         <v>161</v>
@@ -3618,10 +3618,10 @@
         <v>124</v>
       </c>
       <c r="E69" t="s">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="F69" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="G69" t="s">
         <v>161</v>
@@ -3641,13 +3641,13 @@
         <v>174</v>
       </c>
       <c r="E70" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F70" t="s">
         <v>175</v>
       </c>
       <c r="G70" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3664,13 +3664,13 @@
         <v>174</v>
       </c>
       <c r="E71" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F71" t="s">
         <v>175</v>
       </c>
       <c r="G71" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3687,13 +3687,13 @@
         <v>174</v>
       </c>
       <c r="E72" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F72" t="s">
         <v>175</v>
       </c>
       <c r="G72" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3710,13 +3710,13 @@
         <v>174</v>
       </c>
       <c r="E73" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F73" t="s">
         <v>175</v>
       </c>
       <c r="G73" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3733,13 +3733,13 @@
         <v>174</v>
       </c>
       <c r="E74" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F74" t="s">
         <v>175</v>
       </c>
       <c r="G74" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3756,13 +3756,13 @@
         <v>174</v>
       </c>
       <c r="E75" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F75" t="s">
         <v>175</v>
       </c>
       <c r="G75" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3779,13 +3779,13 @@
         <v>174</v>
       </c>
       <c r="E76" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F76" t="s">
         <v>175</v>
       </c>
       <c r="G76" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3802,13 +3802,13 @@
         <v>174</v>
       </c>
       <c r="E77" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F77" t="s">
         <v>175</v>
       </c>
       <c r="G77" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3825,13 +3825,13 @@
         <v>174</v>
       </c>
       <c r="E78" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F78" t="s">
         <v>175</v>
       </c>
       <c r="G78" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3848,13 +3848,13 @@
         <v>174</v>
       </c>
       <c r="E79" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F79" t="s">
         <v>175</v>
       </c>
       <c r="G79" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3871,13 +3871,13 @@
         <v>174</v>
       </c>
       <c r="E80" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F80" t="s">
         <v>175</v>
       </c>
       <c r="G80" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3894,13 +3894,13 @@
         <v>198</v>
       </c>
       <c r="E81" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F81" t="s">
         <v>199</v>
       </c>
       <c r="G81" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3917,13 +3917,13 @@
         <v>198</v>
       </c>
       <c r="E82" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F82" t="s">
         <v>199</v>
       </c>
       <c r="G82" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3940,13 +3940,13 @@
         <v>198</v>
       </c>
       <c r="E83" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F83" t="s">
         <v>199</v>
       </c>
       <c r="G83" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3963,13 +3963,13 @@
         <v>198</v>
       </c>
       <c r="E84" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F84" t="s">
         <v>199</v>
       </c>
       <c r="G84" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3986,13 +3986,13 @@
         <v>198</v>
       </c>
       <c r="E85" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F85" t="s">
         <v>199</v>
       </c>
       <c r="G85" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4009,13 +4009,13 @@
         <v>198</v>
       </c>
       <c r="E86" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F86" t="s">
         <v>199</v>
       </c>
       <c r="G86" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4032,13 +4032,13 @@
         <v>198</v>
       </c>
       <c r="E87" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F87" t="s">
         <v>199</v>
       </c>
       <c r="G87" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4055,13 +4055,13 @@
         <v>214</v>
       </c>
       <c r="E88" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F88" t="s">
         <v>215</v>
       </c>
       <c r="G88" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4078,13 +4078,13 @@
         <v>214</v>
       </c>
       <c r="E89" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F89" t="s">
         <v>215</v>
       </c>
       <c r="G89" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4101,13 +4101,13 @@
         <v>214</v>
       </c>
       <c r="E90" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F90" t="s">
         <v>215</v>
       </c>
       <c r="G90" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4124,13 +4124,13 @@
         <v>214</v>
       </c>
       <c r="E91" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F91" t="s">
         <v>215</v>
       </c>
       <c r="G91" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4239,10 +4239,10 @@
         <v>224</v>
       </c>
       <c r="E96" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="F96" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G96" t="s">
         <v>237</v>
@@ -4262,10 +4262,10 @@
         <v>224</v>
       </c>
       <c r="E97" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="F97" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G97" t="s">
         <v>237</v>
@@ -4285,10 +4285,10 @@
         <v>224</v>
       </c>
       <c r="E98" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="F98" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G98" t="s">
         <v>237</v>
@@ -4308,10 +4308,10 @@
         <v>224</v>
       </c>
       <c r="E99" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="F99" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G99" t="s">
         <v>237</v>
@@ -4331,10 +4331,10 @@
         <v>224</v>
       </c>
       <c r="E100" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="F100" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G100" t="s">
         <v>237</v>
@@ -4354,10 +4354,10 @@
         <v>224</v>
       </c>
       <c r="E101" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="F101" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G101" t="s">
         <v>237</v>
@@ -4377,10 +4377,10 @@
         <v>224</v>
       </c>
       <c r="E102" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="F102" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G102" t="s">
         <v>237</v>
@@ -4400,10 +4400,10 @@
         <v>224</v>
       </c>
       <c r="E103" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="F103" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G103" t="s">
         <v>237</v>
@@ -4423,10 +4423,10 @@
         <v>224</v>
       </c>
       <c r="E104" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="F104" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G104" t="s">
         <v>237</v>
@@ -4446,10 +4446,10 @@
         <v>224</v>
       </c>
       <c r="E105" t="s">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="F105" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="G105" t="s">
         <v>257</v>
@@ -4469,10 +4469,10 @@
         <v>224</v>
       </c>
       <c r="E106" t="s">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="F106" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="G106" t="s">
         <v>257</v>
@@ -4492,10 +4492,10 @@
         <v>224</v>
       </c>
       <c r="E107" t="s">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="F107" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="G107" t="s">
         <v>257</v>
@@ -4515,10 +4515,10 @@
         <v>224</v>
       </c>
       <c r="E108" t="s">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="F108" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="G108" t="s">
         <v>257</v>
@@ -4538,10 +4538,10 @@
         <v>224</v>
       </c>
       <c r="E109" t="s">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="F109" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="G109" t="s">
         <v>257</v>
@@ -4561,10 +4561,10 @@
         <v>224</v>
       </c>
       <c r="E110" t="s">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="F110" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="G110" t="s">
         <v>257</v>
@@ -4584,10 +4584,10 @@
         <v>224</v>
       </c>
       <c r="E111" t="s">
-        <v>225</v>
+        <v>270</v>
       </c>
       <c r="F111" t="s">
-        <v>270</v>
+        <v>226</v>
       </c>
       <c r="G111" t="s">
         <v>271</v>
@@ -4607,10 +4607,10 @@
         <v>224</v>
       </c>
       <c r="E112" t="s">
-        <v>225</v>
+        <v>274</v>
       </c>
       <c r="F112" t="s">
-        <v>274</v>
+        <v>226</v>
       </c>
       <c r="G112" t="s">
         <v>275</v>
@@ -4630,10 +4630,10 @@
         <v>224</v>
       </c>
       <c r="E113" t="s">
-        <v>225</v>
+        <v>278</v>
       </c>
       <c r="F113" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="G113" t="s">
         <v>279</v>
@@ -4653,10 +4653,10 @@
         <v>224</v>
       </c>
       <c r="E114" t="s">
-        <v>225</v>
+        <v>278</v>
       </c>
       <c r="F114" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="G114" t="s">
         <v>279</v>
@@ -4676,10 +4676,10 @@
         <v>224</v>
       </c>
       <c r="E115" t="s">
-        <v>225</v>
+        <v>278</v>
       </c>
       <c r="F115" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="G115" t="s">
         <v>279</v>
@@ -4699,10 +4699,10 @@
         <v>224</v>
       </c>
       <c r="E116" t="s">
-        <v>225</v>
+        <v>278</v>
       </c>
       <c r="F116" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="G116" t="s">
         <v>279</v>
@@ -4722,10 +4722,10 @@
         <v>224</v>
       </c>
       <c r="E117" t="s">
-        <v>225</v>
+        <v>278</v>
       </c>
       <c r="F117" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="G117" t="s">
         <v>279</v>
@@ -4745,10 +4745,10 @@
         <v>224</v>
       </c>
       <c r="E118" t="s">
-        <v>225</v>
+        <v>278</v>
       </c>
       <c r="F118" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="G118" t="s">
         <v>279</v>
@@ -4768,10 +4768,10 @@
         <v>224</v>
       </c>
       <c r="E119" t="s">
-        <v>225</v>
+        <v>278</v>
       </c>
       <c r="F119" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="G119" t="s">
         <v>279</v>
@@ -4791,13 +4791,13 @@
         <v>294</v>
       </c>
       <c r="E120" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F120" t="s">
         <v>295</v>
       </c>
       <c r="G120" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4814,13 +4814,13 @@
         <v>294</v>
       </c>
       <c r="E121" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F121" t="s">
         <v>295</v>
       </c>
       <c r="G121" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4837,13 +4837,13 @@
         <v>294</v>
       </c>
       <c r="E122" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F122" t="s">
         <v>295</v>
       </c>
       <c r="G122" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4860,13 +4860,13 @@
         <v>294</v>
       </c>
       <c r="E123" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F123" t="s">
         <v>295</v>
       </c>
       <c r="G123" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4883,13 +4883,13 @@
         <v>294</v>
       </c>
       <c r="E124" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F124" t="s">
         <v>295</v>
       </c>
       <c r="G124" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4906,13 +4906,13 @@
         <v>294</v>
       </c>
       <c r="E125" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F125" t="s">
         <v>295</v>
       </c>
       <c r="G125" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4929,13 +4929,13 @@
         <v>308</v>
       </c>
       <c r="E126" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F126" t="s">
         <v>309</v>
       </c>
       <c r="G126" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4952,13 +4952,13 @@
         <v>308</v>
       </c>
       <c r="E127" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F127" t="s">
         <v>309</v>
       </c>
       <c r="G127" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4975,13 +4975,13 @@
         <v>308</v>
       </c>
       <c r="E128" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F128" t="s">
         <v>309</v>
       </c>
       <c r="G128" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4998,13 +4998,13 @@
         <v>308</v>
       </c>
       <c r="E129" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F129" t="s">
         <v>309</v>
       </c>
       <c r="G129" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -5435,10 +5435,10 @@
         <v>318</v>
       </c>
       <c r="E148" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="F148" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
       <c r="G148" t="s">
         <v>359</v>
@@ -5458,10 +5458,10 @@
         <v>318</v>
       </c>
       <c r="E149" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="F149" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
       <c r="G149" t="s">
         <v>359</v>
@@ -5481,10 +5481,10 @@
         <v>318</v>
       </c>
       <c r="E150" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="F150" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
       <c r="G150" t="s">
         <v>359</v>
@@ -5504,10 +5504,10 @@
         <v>318</v>
       </c>
       <c r="E151" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="F151" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
       <c r="G151" t="s">
         <v>359</v>
@@ -5527,10 +5527,10 @@
         <v>318</v>
       </c>
       <c r="E152" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="F152" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
       <c r="G152" t="s">
         <v>359</v>
@@ -5550,10 +5550,10 @@
         <v>318</v>
       </c>
       <c r="E153" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="F153" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
       <c r="G153" t="s">
         <v>359</v>
@@ -5573,10 +5573,10 @@
         <v>318</v>
       </c>
       <c r="E154" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="F154" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
       <c r="G154" t="s">
         <v>373</v>
@@ -5596,10 +5596,10 @@
         <v>318</v>
       </c>
       <c r="E155" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="F155" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
       <c r="G155" t="s">
         <v>373</v>
@@ -5619,10 +5619,10 @@
         <v>318</v>
       </c>
       <c r="E156" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="F156" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
       <c r="G156" t="s">
         <v>373</v>
@@ -5642,10 +5642,10 @@
         <v>318</v>
       </c>
       <c r="E157" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="F157" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
       <c r="G157" t="s">
         <v>373</v>
@@ -5665,10 +5665,10 @@
         <v>318</v>
       </c>
       <c r="E158" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="F158" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
       <c r="G158" t="s">
         <v>373</v>
@@ -6125,10 +6125,10 @@
         <v>384</v>
       </c>
       <c r="E178" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="F178" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
       <c r="G178" t="s">
         <v>427</v>
@@ -6148,10 +6148,10 @@
         <v>384</v>
       </c>
       <c r="E179" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="F179" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
       <c r="G179" t="s">
         <v>427</v>
@@ -6171,10 +6171,10 @@
         <v>384</v>
       </c>
       <c r="E180" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="F180" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
       <c r="G180" t="s">
         <v>427</v>
@@ -6194,10 +6194,10 @@
         <v>384</v>
       </c>
       <c r="E181" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="F181" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
       <c r="G181" t="s">
         <v>427</v>
@@ -6217,10 +6217,10 @@
         <v>384</v>
       </c>
       <c r="E182" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="F182" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
       <c r="G182" t="s">
         <v>427</v>
@@ -6240,10 +6240,10 @@
         <v>384</v>
       </c>
       <c r="E183" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="F183" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
       <c r="G183" t="s">
         <v>427</v>
@@ -6263,10 +6263,10 @@
         <v>384</v>
       </c>
       <c r="E184" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="F184" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
       <c r="G184" t="s">
         <v>427</v>
@@ -6286,10 +6286,10 @@
         <v>384</v>
       </c>
       <c r="E185" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="F185" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
       <c r="G185" t="s">
         <v>427</v>
@@ -6309,10 +6309,10 @@
         <v>384</v>
       </c>
       <c r="E186" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="F186" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
       <c r="G186" t="s">
         <v>427</v>
@@ -6332,10 +6332,10 @@
         <v>384</v>
       </c>
       <c r="E187" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="F187" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
       <c r="G187" t="s">
         <v>427</v>
@@ -6355,10 +6355,10 @@
         <v>384</v>
       </c>
       <c r="E188" t="s">
-        <v>385</v>
+        <v>448</v>
       </c>
       <c r="F188" t="s">
-        <v>448</v>
+        <v>386</v>
       </c>
       <c r="G188" t="s">
         <v>449</v>
@@ -6378,13 +6378,13 @@
         <v>452</v>
       </c>
       <c r="E189" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F189" t="s">
         <v>453</v>
       </c>
       <c r="G189" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6401,13 +6401,13 @@
         <v>452</v>
       </c>
       <c r="E190" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F190" t="s">
         <v>453</v>
       </c>
       <c r="G190" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6424,13 +6424,13 @@
         <v>452</v>
       </c>
       <c r="E191" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F191" t="s">
         <v>453</v>
       </c>
       <c r="G191" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6447,13 +6447,13 @@
         <v>452</v>
       </c>
       <c r="E192" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F192" t="s">
         <v>453</v>
       </c>
       <c r="G192" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6470,13 +6470,13 @@
         <v>452</v>
       </c>
       <c r="E193" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F193" t="s">
         <v>453</v>
       </c>
       <c r="G193" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6493,13 +6493,13 @@
         <v>452</v>
       </c>
       <c r="E194" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F194" t="s">
         <v>453</v>
       </c>
       <c r="G194" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6516,13 +6516,13 @@
         <v>466</v>
       </c>
       <c r="E195" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F195" t="s">
         <v>467</v>
       </c>
       <c r="G195" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6539,13 +6539,13 @@
         <v>470</v>
       </c>
       <c r="E196" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F196" t="s">
         <v>471</v>
       </c>
       <c r="G196" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6562,13 +6562,13 @@
         <v>470</v>
       </c>
       <c r="E197" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F197" t="s">
         <v>471</v>
       </c>
       <c r="G197" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6585,13 +6585,13 @@
         <v>470</v>
       </c>
       <c r="E198" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F198" t="s">
         <v>471</v>
       </c>
       <c r="G198" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6608,13 +6608,13 @@
         <v>470</v>
       </c>
       <c r="E199" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F199" t="s">
         <v>471</v>
       </c>
       <c r="G199" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6631,13 +6631,13 @@
         <v>470</v>
       </c>
       <c r="E200" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F200" t="s">
         <v>471</v>
       </c>
       <c r="G200" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6654,13 +6654,13 @@
         <v>470</v>
       </c>
       <c r="E201" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F201" t="s">
         <v>471</v>
       </c>
       <c r="G201" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6677,13 +6677,13 @@
         <v>484</v>
       </c>
       <c r="E202" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F202" t="s">
         <v>485</v>
       </c>
       <c r="G202" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6700,13 +6700,13 @@
         <v>484</v>
       </c>
       <c r="E203" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F203" t="s">
         <v>485</v>
       </c>
       <c r="G203" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6723,13 +6723,13 @@
         <v>484</v>
       </c>
       <c r="E204" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F204" t="s">
         <v>485</v>
       </c>
       <c r="G204" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6746,13 +6746,13 @@
         <v>484</v>
       </c>
       <c r="E205" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F205" t="s">
         <v>485</v>
       </c>
       <c r="G205" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6769,13 +6769,13 @@
         <v>484</v>
       </c>
       <c r="E206" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F206" t="s">
         <v>485</v>
       </c>
       <c r="G206" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6792,13 +6792,13 @@
         <v>484</v>
       </c>
       <c r="E207" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F207" t="s">
         <v>485</v>
       </c>
       <c r="G207" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6815,13 +6815,13 @@
         <v>484</v>
       </c>
       <c r="E208" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F208" t="s">
         <v>485</v>
       </c>
       <c r="G208" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6838,13 +6838,13 @@
         <v>484</v>
       </c>
       <c r="E209" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F209" t="s">
         <v>485</v>
       </c>
       <c r="G209" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6861,13 +6861,13 @@
         <v>484</v>
       </c>
       <c r="E210" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F210" t="s">
         <v>485</v>
       </c>
       <c r="G210" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6884,13 +6884,13 @@
         <v>484</v>
       </c>
       <c r="E211" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F211" t="s">
         <v>485</v>
       </c>
       <c r="G211" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6907,13 +6907,13 @@
         <v>506</v>
       </c>
       <c r="E212" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="F212" t="s">
         <v>507</v>
       </c>
       <c r="G212" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6930,13 +6930,13 @@
         <v>510</v>
       </c>
       <c r="E213" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F213" t="s">
         <v>511</v>
       </c>
       <c r="G213" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6953,13 +6953,13 @@
         <v>514</v>
       </c>
       <c r="E214" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F214" t="s">
         <v>515</v>
       </c>
       <c r="G214" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6976,13 +6976,13 @@
         <v>514</v>
       </c>
       <c r="E215" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F215" t="s">
         <v>515</v>
       </c>
       <c r="G215" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6999,13 +6999,13 @@
         <v>520</v>
       </c>
       <c r="E216" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F216" t="s">
         <v>521</v>
       </c>
       <c r="G216" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -7022,13 +7022,13 @@
         <v>520</v>
       </c>
       <c r="E217" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F217" t="s">
         <v>521</v>
       </c>
       <c r="G217" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -7045,13 +7045,13 @@
         <v>520</v>
       </c>
       <c r="E218" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F218" t="s">
         <v>521</v>
       </c>
       <c r="G218" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -7068,13 +7068,13 @@
         <v>520</v>
       </c>
       <c r="E219" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F219" t="s">
         <v>521</v>
       </c>
       <c r="G219" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -7091,13 +7091,13 @@
         <v>520</v>
       </c>
       <c r="E220" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F220" t="s">
         <v>521</v>
       </c>
       <c r="G220" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -7114,13 +7114,13 @@
         <v>520</v>
       </c>
       <c r="E221" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F221" t="s">
         <v>521</v>
       </c>
       <c r="G221" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -7137,13 +7137,13 @@
         <v>520</v>
       </c>
       <c r="E222" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F222" t="s">
         <v>521</v>
       </c>
       <c r="G222" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -7160,13 +7160,13 @@
         <v>536</v>
       </c>
       <c r="E223" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F223" t="s">
         <v>537</v>
       </c>
       <c r="G223" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -7183,13 +7183,13 @@
         <v>536</v>
       </c>
       <c r="E224" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F224" t="s">
         <v>537</v>
       </c>
       <c r="G224" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -7206,13 +7206,13 @@
         <v>536</v>
       </c>
       <c r="E225" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F225" t="s">
         <v>537</v>
       </c>
       <c r="G225" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -7229,13 +7229,13 @@
         <v>544</v>
       </c>
       <c r="E226" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F226" t="s">
         <v>545</v>
       </c>
       <c r="G226" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -7252,13 +7252,13 @@
         <v>548</v>
       </c>
       <c r="E227" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="F227" t="s">
         <v>549</v>
       </c>
       <c r="G227" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -7275,13 +7275,13 @@
         <v>552</v>
       </c>
       <c r="E228" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="F228" t="s">
         <v>553</v>
       </c>
       <c r="G228" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -7298,13 +7298,13 @@
         <v>556</v>
       </c>
       <c r="E229" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="F229" t="s">
         <v>557</v>
       </c>
       <c r="G229" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -7321,13 +7321,13 @@
         <v>560</v>
       </c>
       <c r="E230" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="F230" t="s">
         <v>561</v>
       </c>
       <c r="G230" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -7344,13 +7344,13 @@
         <v>560</v>
       </c>
       <c r="E231" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="F231" t="s">
         <v>561</v>
       </c>
       <c r="G231" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/en/SectorGroup.xlsx
+++ b/api/xlsx/en/SectorGroup.xlsx
@@ -25,15 +25,15 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
     <t>codeforiati:group-name</t>
   </si>
   <si>
     <t>codeforiati:category-name</t>
   </si>
   <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
@@ -46,15 +46,15 @@
     <t>active</t>
   </si>
   <si>
+    <t>110</t>
+  </si>
+  <si>
     <t>Education</t>
   </si>
   <si>
     <t>Education, Level Unspecified</t>
   </si>
   <si>
-    <t>110</t>
-  </si>
-  <si>
     <t>111</t>
   </si>
   <si>
@@ -148,15 +148,15 @@
     <t>Health policy and administrative management</t>
   </si>
   <si>
+    <t>120</t>
+  </si>
+  <si>
     <t>Health</t>
   </si>
   <si>
     <t>Health, General</t>
   </si>
   <si>
-    <t>120</t>
-  </si>
-  <si>
     <t>121</t>
   </si>
   <si>
@@ -280,12 +280,12 @@
     <t>Population policy and administrative management</t>
   </si>
   <si>
+    <t>130</t>
+  </si>
+  <si>
     <t>Population Policies/Programmes &amp; Reproductive Health</t>
   </si>
   <si>
-    <t>130</t>
-  </si>
-  <si>
     <t>13020</t>
   </si>
   <si>
@@ -316,12 +316,12 @@
     <t>Water sector policy and administrative management</t>
   </si>
   <si>
+    <t>140</t>
+  </si>
+  <si>
     <t>Water Supply &amp; Sanitation</t>
   </si>
   <si>
-    <t>140</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -388,15 +388,15 @@
     <t>Public sector policy and administrative management</t>
   </si>
   <si>
+    <t>150</t>
+  </si>
+  <si>
     <t>Government &amp; Civil Society</t>
   </si>
   <si>
     <t>Government &amp; Civil Society-general</t>
   </si>
   <si>
-    <t>150</t>
-  </si>
-  <si>
     <t>151</t>
   </si>
   <si>
@@ -538,12 +538,12 @@
     <t>Social Protection</t>
   </si>
   <si>
+    <t>160</t>
+  </si>
+  <si>
     <t>Other Social Infrastructure &amp; Services</t>
   </si>
   <si>
-    <t>160</t>
-  </si>
-  <si>
     <t>16020</t>
   </si>
   <si>
@@ -610,12 +610,12 @@
     <t>Transport policy and administrative management</t>
   </si>
   <si>
+    <t>210</t>
+  </si>
+  <si>
     <t>Transport &amp; Storage</t>
   </si>
   <si>
-    <t>210</t>
-  </si>
-  <si>
     <t>21020</t>
   </si>
   <si>
@@ -658,12 +658,12 @@
     <t>Communications policy and administrative management</t>
   </si>
   <si>
+    <t>220</t>
+  </si>
+  <si>
     <t>Communications</t>
   </si>
   <si>
-    <t>220</t>
-  </si>
-  <si>
     <t>22020</t>
   </si>
   <si>
@@ -688,15 +688,15 @@
     <t>Energy policy and administrative management</t>
   </si>
   <si>
+    <t>230</t>
+  </si>
+  <si>
     <t>Energy</t>
   </si>
   <si>
     <t>Energy Policy</t>
   </si>
   <si>
-    <t>230</t>
-  </si>
-  <si>
     <t>231</t>
   </si>
   <si>
@@ -898,12 +898,12 @@
     <t>Financial policy and administrative management</t>
   </si>
   <si>
+    <t>240</t>
+  </si>
+  <si>
     <t>Banking &amp; Financial Services</t>
   </si>
   <si>
-    <t>240</t>
-  </si>
-  <si>
     <t>24020</t>
   </si>
   <si>
@@ -940,12 +940,12 @@
     <t>Business policy and administration</t>
   </si>
   <si>
+    <t>250</t>
+  </si>
+  <si>
     <t>Business &amp; Other Services</t>
   </si>
   <si>
-    <t>250</t>
-  </si>
-  <si>
     <t>25020</t>
   </si>
   <si>
@@ -970,15 +970,15 @@
     <t>Agricultural policy and administrative management</t>
   </si>
   <si>
+    <t>310</t>
+  </si>
+  <si>
     <t>Agriculture, Forestry, Fishing</t>
   </si>
   <si>
     <t>Agriculture</t>
   </si>
   <si>
-    <t>310</t>
-  </si>
-  <si>
     <t>311</t>
   </si>
   <si>
@@ -1168,15 +1168,15 @@
     <t>Industrial policy and administrative management</t>
   </si>
   <si>
+    <t>320</t>
+  </si>
+  <si>
     <t>Industry, Mining, Construction</t>
   </si>
   <si>
     <t>Industry</t>
   </si>
   <si>
-    <t>320</t>
-  </si>
-  <si>
     <t>321</t>
   </si>
   <si>
@@ -1372,12 +1372,12 @@
     <t>Trade policy and administrative management</t>
   </si>
   <si>
+    <t>331</t>
+  </si>
+  <si>
     <t>Trade Policies &amp; Regulations</t>
   </si>
   <si>
-    <t>331</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1414,24 +1414,24 @@
     <t>Tourism policy and administrative management</t>
   </si>
   <si>
+    <t>332</t>
+  </si>
+  <si>
     <t>Tourism</t>
   </si>
   <si>
-    <t>332</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
     <t>Environmental policy and administrative management</t>
   </si>
   <si>
+    <t>410</t>
+  </si>
+  <si>
     <t>General Environment Protection</t>
   </si>
   <si>
-    <t>410</t>
-  </si>
-  <si>
     <t>41020</t>
   </si>
   <si>
@@ -1468,12 +1468,12 @@
     <t>Multisector aid</t>
   </si>
   <si>
+    <t>430</t>
+  </si>
+  <si>
     <t>Other Multisector</t>
   </si>
   <si>
-    <t>430</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -1534,36 +1534,36 @@
     <t>General budget support-related aid</t>
   </si>
   <si>
+    <t>510</t>
+  </si>
+  <si>
     <t>General Budget Support</t>
   </si>
   <si>
-    <t>510</t>
-  </si>
-  <si>
     <t>52010</t>
   </si>
   <si>
     <t>Food assistance</t>
   </si>
   <si>
+    <t>520</t>
+  </si>
+  <si>
     <t>Development Food Assistance</t>
   </si>
   <si>
-    <t>520</t>
-  </si>
-  <si>
     <t>53030</t>
   </si>
   <si>
     <t>Import support (capital goods)</t>
   </si>
   <si>
+    <t>530</t>
+  </si>
+  <si>
     <t>Other Commodity Assistance</t>
   </si>
   <si>
-    <t>530</t>
-  </si>
-  <si>
     <t>53040</t>
   </si>
   <si>
@@ -1576,12 +1576,12 @@
     <t>Action relating to debt</t>
   </si>
   <si>
+    <t>600</t>
+  </si>
+  <si>
     <t>Action Relating to Debt</t>
   </si>
   <si>
-    <t>600</t>
-  </si>
-  <si>
     <t>60020</t>
   </si>
   <si>
@@ -1624,12 +1624,12 @@
     <t>Material relief assistance and services</t>
   </si>
   <si>
+    <t>720</t>
+  </si>
+  <si>
     <t>Emergency Response</t>
   </si>
   <si>
-    <t>720</t>
-  </si>
-  <si>
     <t>72040</t>
   </si>
   <si>
@@ -1648,58 +1648,58 @@
     <t>Immediate post-emergency reconstruction and rehabilitation</t>
   </si>
   <si>
+    <t>730</t>
+  </si>
+  <si>
     <t>Reconstruction Relief &amp; Rehabilitation</t>
   </si>
   <si>
-    <t>730</t>
-  </si>
-  <si>
     <t>74020</t>
   </si>
   <si>
     <t>Multi-hazard response preparedness</t>
   </si>
   <si>
+    <t>740</t>
+  </si>
+  <si>
     <t>Disaster Prevention &amp; Preparedness</t>
   </si>
   <si>
-    <t>740</t>
-  </si>
-  <si>
     <t>91010</t>
   </si>
   <si>
     <t>Administrative costs (non-sector allocable)</t>
   </si>
   <si>
+    <t>910</t>
+  </si>
+  <si>
     <t>Administrative Costs of Donors</t>
   </si>
   <si>
-    <t>910</t>
-  </si>
-  <si>
     <t>93010</t>
   </si>
   <si>
     <t>Refugees/asylum seekers in donor countries (non-sector allocable)</t>
   </si>
   <si>
+    <t>930</t>
+  </si>
+  <si>
     <t>Refugees in Donor Countries</t>
   </si>
   <si>
-    <t>930</t>
-  </si>
-  <si>
     <t>99810</t>
   </si>
   <si>
     <t>Sectors not specified</t>
   </si>
   <si>
+    <t>998</t>
+  </si>
+  <si>
     <t>Unallocated / Unspecified</t>
-  </si>
-  <si>
-    <t>998</t>
   </si>
   <si>
     <t>99820</t>
@@ -2169,10 +2169,10 @@
         <v>10</v>
       </c>
       <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" t="s">
         <v>22</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
       </c>
       <c r="G6" t="s">
         <v>23</v>
@@ -2192,10 +2192,10 @@
         <v>10</v>
       </c>
       <c r="E7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" t="s">
         <v>22</v>
-      </c>
-      <c r="F7" t="s">
-        <v>12</v>
       </c>
       <c r="G7" t="s">
         <v>23</v>
@@ -2215,10 +2215,10 @@
         <v>10</v>
       </c>
       <c r="E8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" t="s">
         <v>22</v>
-      </c>
-      <c r="F8" t="s">
-        <v>12</v>
       </c>
       <c r="G8" t="s">
         <v>23</v>
@@ -2238,10 +2238,10 @@
         <v>10</v>
       </c>
       <c r="E9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" t="s">
         <v>22</v>
-      </c>
-      <c r="F9" t="s">
-        <v>12</v>
       </c>
       <c r="G9" t="s">
         <v>23</v>
@@ -2261,10 +2261,10 @@
         <v>10</v>
       </c>
       <c r="E10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" t="s">
         <v>32</v>
-      </c>
-      <c r="F10" t="s">
-        <v>12</v>
       </c>
       <c r="G10" t="s">
         <v>33</v>
@@ -2284,10 +2284,10 @@
         <v>10</v>
       </c>
       <c r="E11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" t="s">
         <v>32</v>
-      </c>
-      <c r="F11" t="s">
-        <v>12</v>
       </c>
       <c r="G11" t="s">
         <v>33</v>
@@ -2307,10 +2307,10 @@
         <v>10</v>
       </c>
       <c r="E12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" t="s">
         <v>38</v>
-      </c>
-      <c r="F12" t="s">
-        <v>12</v>
       </c>
       <c r="G12" t="s">
         <v>39</v>
@@ -2330,10 +2330,10 @@
         <v>10</v>
       </c>
       <c r="E13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" t="s">
         <v>38</v>
-      </c>
-      <c r="F13" t="s">
-        <v>12</v>
       </c>
       <c r="G13" t="s">
         <v>39</v>
@@ -2445,10 +2445,10 @@
         <v>44</v>
       </c>
       <c r="E18" t="s">
+        <v>45</v>
+      </c>
+      <c r="F18" t="s">
         <v>56</v>
-      </c>
-      <c r="F18" t="s">
-        <v>46</v>
       </c>
       <c r="G18" t="s">
         <v>57</v>
@@ -2468,10 +2468,10 @@
         <v>44</v>
       </c>
       <c r="E19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F19" t="s">
         <v>56</v>
-      </c>
-      <c r="F19" t="s">
-        <v>46</v>
       </c>
       <c r="G19" t="s">
         <v>57</v>
@@ -2491,10 +2491,10 @@
         <v>44</v>
       </c>
       <c r="E20" t="s">
+        <v>45</v>
+      </c>
+      <c r="F20" t="s">
         <v>56</v>
-      </c>
-      <c r="F20" t="s">
-        <v>46</v>
       </c>
       <c r="G20" t="s">
         <v>57</v>
@@ -2514,10 +2514,10 @@
         <v>44</v>
       </c>
       <c r="E21" t="s">
+        <v>45</v>
+      </c>
+      <c r="F21" t="s">
         <v>56</v>
-      </c>
-      <c r="F21" t="s">
-        <v>46</v>
       </c>
       <c r="G21" t="s">
         <v>57</v>
@@ -2537,10 +2537,10 @@
         <v>44</v>
       </c>
       <c r="E22" t="s">
+        <v>45</v>
+      </c>
+      <c r="F22" t="s">
         <v>56</v>
-      </c>
-      <c r="F22" t="s">
-        <v>46</v>
       </c>
       <c r="G22" t="s">
         <v>57</v>
@@ -2560,10 +2560,10 @@
         <v>44</v>
       </c>
       <c r="E23" t="s">
+        <v>45</v>
+      </c>
+      <c r="F23" t="s">
         <v>56</v>
-      </c>
-      <c r="F23" t="s">
-        <v>46</v>
       </c>
       <c r="G23" t="s">
         <v>57</v>
@@ -2583,10 +2583,10 @@
         <v>44</v>
       </c>
       <c r="E24" t="s">
+        <v>45</v>
+      </c>
+      <c r="F24" t="s">
         <v>56</v>
-      </c>
-      <c r="F24" t="s">
-        <v>46</v>
       </c>
       <c r="G24" t="s">
         <v>57</v>
@@ -2606,10 +2606,10 @@
         <v>44</v>
       </c>
       <c r="E25" t="s">
+        <v>45</v>
+      </c>
+      <c r="F25" t="s">
         <v>56</v>
-      </c>
-      <c r="F25" t="s">
-        <v>46</v>
       </c>
       <c r="G25" t="s">
         <v>57</v>
@@ -2629,10 +2629,10 @@
         <v>44</v>
       </c>
       <c r="E26" t="s">
+        <v>45</v>
+      </c>
+      <c r="F26" t="s">
         <v>74</v>
-      </c>
-      <c r="F26" t="s">
-        <v>46</v>
       </c>
       <c r="G26" t="s">
         <v>75</v>
@@ -2652,10 +2652,10 @@
         <v>44</v>
       </c>
       <c r="E27" t="s">
+        <v>45</v>
+      </c>
+      <c r="F27" t="s">
         <v>74</v>
-      </c>
-      <c r="F27" t="s">
-        <v>46</v>
       </c>
       <c r="G27" t="s">
         <v>75</v>
@@ -2675,10 +2675,10 @@
         <v>44</v>
       </c>
       <c r="E28" t="s">
+        <v>45</v>
+      </c>
+      <c r="F28" t="s">
         <v>74</v>
-      </c>
-      <c r="F28" t="s">
-        <v>46</v>
       </c>
       <c r="G28" t="s">
         <v>75</v>
@@ -2698,10 +2698,10 @@
         <v>44</v>
       </c>
       <c r="E29" t="s">
+        <v>45</v>
+      </c>
+      <c r="F29" t="s">
         <v>74</v>
-      </c>
-      <c r="F29" t="s">
-        <v>46</v>
       </c>
       <c r="G29" t="s">
         <v>75</v>
@@ -2721,10 +2721,10 @@
         <v>44</v>
       </c>
       <c r="E30" t="s">
+        <v>45</v>
+      </c>
+      <c r="F30" t="s">
         <v>74</v>
-      </c>
-      <c r="F30" t="s">
-        <v>46</v>
       </c>
       <c r="G30" t="s">
         <v>75</v>
@@ -2744,10 +2744,10 @@
         <v>44</v>
       </c>
       <c r="E31" t="s">
+        <v>45</v>
+      </c>
+      <c r="F31" t="s">
         <v>74</v>
-      </c>
-      <c r="F31" t="s">
-        <v>46</v>
       </c>
       <c r="G31" t="s">
         <v>75</v>
@@ -2767,13 +2767,13 @@
         <v>88</v>
       </c>
       <c r="E32" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F32" t="s">
         <v>89</v>
       </c>
       <c r="G32" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2790,13 +2790,13 @@
         <v>88</v>
       </c>
       <c r="E33" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F33" t="s">
         <v>89</v>
       </c>
       <c r="G33" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2813,13 +2813,13 @@
         <v>88</v>
       </c>
       <c r="E34" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F34" t="s">
         <v>89</v>
       </c>
       <c r="G34" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2836,13 +2836,13 @@
         <v>88</v>
       </c>
       <c r="E35" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F35" t="s">
         <v>89</v>
       </c>
       <c r="G35" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2859,13 +2859,13 @@
         <v>88</v>
       </c>
       <c r="E36" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F36" t="s">
         <v>89</v>
       </c>
       <c r="G36" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2882,13 +2882,13 @@
         <v>100</v>
       </c>
       <c r="E37" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F37" t="s">
         <v>101</v>
       </c>
       <c r="G37" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2905,13 +2905,13 @@
         <v>100</v>
       </c>
       <c r="E38" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F38" t="s">
         <v>101</v>
       </c>
       <c r="G38" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2928,13 +2928,13 @@
         <v>100</v>
       </c>
       <c r="E39" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F39" t="s">
         <v>101</v>
       </c>
       <c r="G39" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2951,13 +2951,13 @@
         <v>100</v>
       </c>
       <c r="E40" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F40" t="s">
         <v>101</v>
       </c>
       <c r="G40" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2974,13 +2974,13 @@
         <v>100</v>
       </c>
       <c r="E41" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F41" t="s">
         <v>101</v>
       </c>
       <c r="G41" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2997,13 +2997,13 @@
         <v>100</v>
       </c>
       <c r="E42" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F42" t="s">
         <v>101</v>
       </c>
       <c r="G42" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3020,13 +3020,13 @@
         <v>100</v>
       </c>
       <c r="E43" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F43" t="s">
         <v>101</v>
       </c>
       <c r="G43" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3043,13 +3043,13 @@
         <v>100</v>
       </c>
       <c r="E44" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F44" t="s">
         <v>101</v>
       </c>
       <c r="G44" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3066,13 +3066,13 @@
         <v>100</v>
       </c>
       <c r="E45" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F45" t="s">
         <v>101</v>
       </c>
       <c r="G45" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3089,13 +3089,13 @@
         <v>100</v>
       </c>
       <c r="E46" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F46" t="s">
         <v>101</v>
       </c>
       <c r="G46" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3112,13 +3112,13 @@
         <v>100</v>
       </c>
       <c r="E47" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F47" t="s">
         <v>101</v>
       </c>
       <c r="G47" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3503,10 +3503,10 @@
         <v>124</v>
       </c>
       <c r="E64" t="s">
+        <v>125</v>
+      </c>
+      <c r="F64" t="s">
         <v>160</v>
-      </c>
-      <c r="F64" t="s">
-        <v>126</v>
       </c>
       <c r="G64" t="s">
         <v>161</v>
@@ -3526,10 +3526,10 @@
         <v>124</v>
       </c>
       <c r="E65" t="s">
+        <v>125</v>
+      </c>
+      <c r="F65" t="s">
         <v>160</v>
-      </c>
-      <c r="F65" t="s">
-        <v>126</v>
       </c>
       <c r="G65" t="s">
         <v>161</v>
@@ -3549,10 +3549,10 @@
         <v>124</v>
       </c>
       <c r="E66" t="s">
+        <v>125</v>
+      </c>
+      <c r="F66" t="s">
         <v>160</v>
-      </c>
-      <c r="F66" t="s">
-        <v>126</v>
       </c>
       <c r="G66" t="s">
         <v>161</v>
@@ -3572,10 +3572,10 @@
         <v>124</v>
       </c>
       <c r="E67" t="s">
+        <v>125</v>
+      </c>
+      <c r="F67" t="s">
         <v>160</v>
-      </c>
-      <c r="F67" t="s">
-        <v>126</v>
       </c>
       <c r="G67" t="s">
         <v>161</v>
@@ -3595,10 +3595,10 @@
         <v>124</v>
       </c>
       <c r="E68" t="s">
+        <v>125</v>
+      </c>
+      <c r="F68" t="s">
         <v>160</v>
-      </c>
-      <c r="F68" t="s">
-        <v>126</v>
       </c>
       <c r="G68" t="s">
         <v>161</v>
@@ -3618,10 +3618,10 @@
         <v>124</v>
       </c>
       <c r="E69" t="s">
+        <v>125</v>
+      </c>
+      <c r="F69" t="s">
         <v>160</v>
-      </c>
-      <c r="F69" t="s">
-        <v>126</v>
       </c>
       <c r="G69" t="s">
         <v>161</v>
@@ -3641,13 +3641,13 @@
         <v>174</v>
       </c>
       <c r="E70" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F70" t="s">
         <v>175</v>
       </c>
       <c r="G70" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3664,13 +3664,13 @@
         <v>174</v>
       </c>
       <c r="E71" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F71" t="s">
         <v>175</v>
       </c>
       <c r="G71" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3687,13 +3687,13 @@
         <v>174</v>
       </c>
       <c r="E72" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F72" t="s">
         <v>175</v>
       </c>
       <c r="G72" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3710,13 +3710,13 @@
         <v>174</v>
       </c>
       <c r="E73" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F73" t="s">
         <v>175</v>
       </c>
       <c r="G73" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3733,13 +3733,13 @@
         <v>174</v>
       </c>
       <c r="E74" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F74" t="s">
         <v>175</v>
       </c>
       <c r="G74" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3756,13 +3756,13 @@
         <v>174</v>
       </c>
       <c r="E75" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F75" t="s">
         <v>175</v>
       </c>
       <c r="G75" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3779,13 +3779,13 @@
         <v>174</v>
       </c>
       <c r="E76" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F76" t="s">
         <v>175</v>
       </c>
       <c r="G76" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3802,13 +3802,13 @@
         <v>174</v>
       </c>
       <c r="E77" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F77" t="s">
         <v>175</v>
       </c>
       <c r="G77" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3825,13 +3825,13 @@
         <v>174</v>
       </c>
       <c r="E78" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F78" t="s">
         <v>175</v>
       </c>
       <c r="G78" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3848,13 +3848,13 @@
         <v>174</v>
       </c>
       <c r="E79" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F79" t="s">
         <v>175</v>
       </c>
       <c r="G79" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3871,13 +3871,13 @@
         <v>174</v>
       </c>
       <c r="E80" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F80" t="s">
         <v>175</v>
       </c>
       <c r="G80" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3894,13 +3894,13 @@
         <v>198</v>
       </c>
       <c r="E81" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F81" t="s">
         <v>199</v>
       </c>
       <c r="G81" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3917,13 +3917,13 @@
         <v>198</v>
       </c>
       <c r="E82" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F82" t="s">
         <v>199</v>
       </c>
       <c r="G82" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3940,13 +3940,13 @@
         <v>198</v>
       </c>
       <c r="E83" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F83" t="s">
         <v>199</v>
       </c>
       <c r="G83" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3963,13 +3963,13 @@
         <v>198</v>
       </c>
       <c r="E84" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F84" t="s">
         <v>199</v>
       </c>
       <c r="G84" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3986,13 +3986,13 @@
         <v>198</v>
       </c>
       <c r="E85" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F85" t="s">
         <v>199</v>
       </c>
       <c r="G85" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4009,13 +4009,13 @@
         <v>198</v>
       </c>
       <c r="E86" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F86" t="s">
         <v>199</v>
       </c>
       <c r="G86" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4032,13 +4032,13 @@
         <v>198</v>
       </c>
       <c r="E87" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F87" t="s">
         <v>199</v>
       </c>
       <c r="G87" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4055,13 +4055,13 @@
         <v>214</v>
       </c>
       <c r="E88" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F88" t="s">
         <v>215</v>
       </c>
       <c r="G88" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4078,13 +4078,13 @@
         <v>214</v>
       </c>
       <c r="E89" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F89" t="s">
         <v>215</v>
       </c>
       <c r="G89" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4101,13 +4101,13 @@
         <v>214</v>
       </c>
       <c r="E90" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F90" t="s">
         <v>215</v>
       </c>
       <c r="G90" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4124,13 +4124,13 @@
         <v>214</v>
       </c>
       <c r="E91" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F91" t="s">
         <v>215</v>
       </c>
       <c r="G91" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4239,10 +4239,10 @@
         <v>224</v>
       </c>
       <c r="E96" t="s">
+        <v>225</v>
+      </c>
+      <c r="F96" t="s">
         <v>236</v>
-      </c>
-      <c r="F96" t="s">
-        <v>226</v>
       </c>
       <c r="G96" t="s">
         <v>237</v>
@@ -4262,10 +4262,10 @@
         <v>224</v>
       </c>
       <c r="E97" t="s">
+        <v>225</v>
+      </c>
+      <c r="F97" t="s">
         <v>236</v>
-      </c>
-      <c r="F97" t="s">
-        <v>226</v>
       </c>
       <c r="G97" t="s">
         <v>237</v>
@@ -4285,10 +4285,10 @@
         <v>224</v>
       </c>
       <c r="E98" t="s">
+        <v>225</v>
+      </c>
+      <c r="F98" t="s">
         <v>236</v>
-      </c>
-      <c r="F98" t="s">
-        <v>226</v>
       </c>
       <c r="G98" t="s">
         <v>237</v>
@@ -4308,10 +4308,10 @@
         <v>224</v>
       </c>
       <c r="E99" t="s">
+        <v>225</v>
+      </c>
+      <c r="F99" t="s">
         <v>236</v>
-      </c>
-      <c r="F99" t="s">
-        <v>226</v>
       </c>
       <c r="G99" t="s">
         <v>237</v>
@@ -4331,10 +4331,10 @@
         <v>224</v>
       </c>
       <c r="E100" t="s">
+        <v>225</v>
+      </c>
+      <c r="F100" t="s">
         <v>236</v>
-      </c>
-      <c r="F100" t="s">
-        <v>226</v>
       </c>
       <c r="G100" t="s">
         <v>237</v>
@@ -4354,10 +4354,10 @@
         <v>224</v>
       </c>
       <c r="E101" t="s">
+        <v>225</v>
+      </c>
+      <c r="F101" t="s">
         <v>236</v>
-      </c>
-      <c r="F101" t="s">
-        <v>226</v>
       </c>
       <c r="G101" t="s">
         <v>237</v>
@@ -4377,10 +4377,10 @@
         <v>224</v>
       </c>
       <c r="E102" t="s">
+        <v>225</v>
+      </c>
+      <c r="F102" t="s">
         <v>236</v>
-      </c>
-      <c r="F102" t="s">
-        <v>226</v>
       </c>
       <c r="G102" t="s">
         <v>237</v>
@@ -4400,10 +4400,10 @@
         <v>224</v>
       </c>
       <c r="E103" t="s">
+        <v>225</v>
+      </c>
+      <c r="F103" t="s">
         <v>236</v>
-      </c>
-      <c r="F103" t="s">
-        <v>226</v>
       </c>
       <c r="G103" t="s">
         <v>237</v>
@@ -4423,10 +4423,10 @@
         <v>224</v>
       </c>
       <c r="E104" t="s">
+        <v>225</v>
+      </c>
+      <c r="F104" t="s">
         <v>236</v>
-      </c>
-      <c r="F104" t="s">
-        <v>226</v>
       </c>
       <c r="G104" t="s">
         <v>237</v>
@@ -4446,10 +4446,10 @@
         <v>224</v>
       </c>
       <c r="E105" t="s">
+        <v>225</v>
+      </c>
+      <c r="F105" t="s">
         <v>256</v>
-      </c>
-      <c r="F105" t="s">
-        <v>226</v>
       </c>
       <c r="G105" t="s">
         <v>257</v>
@@ -4469,10 +4469,10 @@
         <v>224</v>
       </c>
       <c r="E106" t="s">
+        <v>225</v>
+      </c>
+      <c r="F106" t="s">
         <v>256</v>
-      </c>
-      <c r="F106" t="s">
-        <v>226</v>
       </c>
       <c r="G106" t="s">
         <v>257</v>
@@ -4492,10 +4492,10 @@
         <v>224</v>
       </c>
       <c r="E107" t="s">
+        <v>225</v>
+      </c>
+      <c r="F107" t="s">
         <v>256</v>
-      </c>
-      <c r="F107" t="s">
-        <v>226</v>
       </c>
       <c r="G107" t="s">
         <v>257</v>
@@ -4515,10 +4515,10 @@
         <v>224</v>
       </c>
       <c r="E108" t="s">
+        <v>225</v>
+      </c>
+      <c r="F108" t="s">
         <v>256</v>
-      </c>
-      <c r="F108" t="s">
-        <v>226</v>
       </c>
       <c r="G108" t="s">
         <v>257</v>
@@ -4538,10 +4538,10 @@
         <v>224</v>
       </c>
       <c r="E109" t="s">
+        <v>225</v>
+      </c>
+      <c r="F109" t="s">
         <v>256</v>
-      </c>
-      <c r="F109" t="s">
-        <v>226</v>
       </c>
       <c r="G109" t="s">
         <v>257</v>
@@ -4561,10 +4561,10 @@
         <v>224</v>
       </c>
       <c r="E110" t="s">
+        <v>225</v>
+      </c>
+      <c r="F110" t="s">
         <v>256</v>
-      </c>
-      <c r="F110" t="s">
-        <v>226</v>
       </c>
       <c r="G110" t="s">
         <v>257</v>
@@ -4584,10 +4584,10 @@
         <v>224</v>
       </c>
       <c r="E111" t="s">
+        <v>225</v>
+      </c>
+      <c r="F111" t="s">
         <v>270</v>
-      </c>
-      <c r="F111" t="s">
-        <v>226</v>
       </c>
       <c r="G111" t="s">
         <v>271</v>
@@ -4607,10 +4607,10 @@
         <v>224</v>
       </c>
       <c r="E112" t="s">
+        <v>225</v>
+      </c>
+      <c r="F112" t="s">
         <v>274</v>
-      </c>
-      <c r="F112" t="s">
-        <v>226</v>
       </c>
       <c r="G112" t="s">
         <v>275</v>
@@ -4630,10 +4630,10 @@
         <v>224</v>
       </c>
       <c r="E113" t="s">
+        <v>225</v>
+      </c>
+      <c r="F113" t="s">
         <v>278</v>
-      </c>
-      <c r="F113" t="s">
-        <v>226</v>
       </c>
       <c r="G113" t="s">
         <v>279</v>
@@ -4653,10 +4653,10 @@
         <v>224</v>
       </c>
       <c r="E114" t="s">
+        <v>225</v>
+      </c>
+      <c r="F114" t="s">
         <v>278</v>
-      </c>
-      <c r="F114" t="s">
-        <v>226</v>
       </c>
       <c r="G114" t="s">
         <v>279</v>
@@ -4676,10 +4676,10 @@
         <v>224</v>
       </c>
       <c r="E115" t="s">
+        <v>225</v>
+      </c>
+      <c r="F115" t="s">
         <v>278</v>
-      </c>
-      <c r="F115" t="s">
-        <v>226</v>
       </c>
       <c r="G115" t="s">
         <v>279</v>
@@ -4699,10 +4699,10 @@
         <v>224</v>
       </c>
       <c r="E116" t="s">
+        <v>225</v>
+      </c>
+      <c r="F116" t="s">
         <v>278</v>
-      </c>
-      <c r="F116" t="s">
-        <v>226</v>
       </c>
       <c r="G116" t="s">
         <v>279</v>
@@ -4722,10 +4722,10 @@
         <v>224</v>
       </c>
       <c r="E117" t="s">
+        <v>225</v>
+      </c>
+      <c r="F117" t="s">
         <v>278</v>
-      </c>
-      <c r="F117" t="s">
-        <v>226</v>
       </c>
       <c r="G117" t="s">
         <v>279</v>
@@ -4745,10 +4745,10 @@
         <v>224</v>
       </c>
       <c r="E118" t="s">
+        <v>225</v>
+      </c>
+      <c r="F118" t="s">
         <v>278</v>
-      </c>
-      <c r="F118" t="s">
-        <v>226</v>
       </c>
       <c r="G118" t="s">
         <v>279</v>
@@ -4768,10 +4768,10 @@
         <v>224</v>
       </c>
       <c r="E119" t="s">
+        <v>225</v>
+      </c>
+      <c r="F119" t="s">
         <v>278</v>
-      </c>
-      <c r="F119" t="s">
-        <v>226</v>
       </c>
       <c r="G119" t="s">
         <v>279</v>
@@ -4791,13 +4791,13 @@
         <v>294</v>
       </c>
       <c r="E120" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F120" t="s">
         <v>295</v>
       </c>
       <c r="G120" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4814,13 +4814,13 @@
         <v>294</v>
       </c>
       <c r="E121" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F121" t="s">
         <v>295</v>
       </c>
       <c r="G121" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4837,13 +4837,13 @@
         <v>294</v>
       </c>
       <c r="E122" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F122" t="s">
         <v>295</v>
       </c>
       <c r="G122" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4860,13 +4860,13 @@
         <v>294</v>
       </c>
       <c r="E123" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F123" t="s">
         <v>295</v>
       </c>
       <c r="G123" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4883,13 +4883,13 @@
         <v>294</v>
       </c>
       <c r="E124" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F124" t="s">
         <v>295</v>
       </c>
       <c r="G124" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4906,13 +4906,13 @@
         <v>294</v>
       </c>
       <c r="E125" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F125" t="s">
         <v>295</v>
       </c>
       <c r="G125" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4929,13 +4929,13 @@
         <v>308</v>
       </c>
       <c r="E126" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F126" t="s">
         <v>309</v>
       </c>
       <c r="G126" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4952,13 +4952,13 @@
         <v>308</v>
       </c>
       <c r="E127" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F127" t="s">
         <v>309</v>
       </c>
       <c r="G127" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4975,13 +4975,13 @@
         <v>308</v>
       </c>
       <c r="E128" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F128" t="s">
         <v>309</v>
       </c>
       <c r="G128" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4998,13 +4998,13 @@
         <v>308</v>
       </c>
       <c r="E129" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F129" t="s">
         <v>309</v>
       </c>
       <c r="G129" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -5435,10 +5435,10 @@
         <v>318</v>
       </c>
       <c r="E148" t="s">
+        <v>319</v>
+      </c>
+      <c r="F148" t="s">
         <v>358</v>
-      </c>
-      <c r="F148" t="s">
-        <v>320</v>
       </c>
       <c r="G148" t="s">
         <v>359</v>
@@ -5458,10 +5458,10 @@
         <v>318</v>
       </c>
       <c r="E149" t="s">
+        <v>319</v>
+      </c>
+      <c r="F149" t="s">
         <v>358</v>
-      </c>
-      <c r="F149" t="s">
-        <v>320</v>
       </c>
       <c r="G149" t="s">
         <v>359</v>
@@ -5481,10 +5481,10 @@
         <v>318</v>
       </c>
       <c r="E150" t="s">
+        <v>319</v>
+      </c>
+      <c r="F150" t="s">
         <v>358</v>
-      </c>
-      <c r="F150" t="s">
-        <v>320</v>
       </c>
       <c r="G150" t="s">
         <v>359</v>
@@ -5504,10 +5504,10 @@
         <v>318</v>
       </c>
       <c r="E151" t="s">
+        <v>319</v>
+      </c>
+      <c r="F151" t="s">
         <v>358</v>
-      </c>
-      <c r="F151" t="s">
-        <v>320</v>
       </c>
       <c r="G151" t="s">
         <v>359</v>
@@ -5527,10 +5527,10 @@
         <v>318</v>
       </c>
       <c r="E152" t="s">
+        <v>319</v>
+      </c>
+      <c r="F152" t="s">
         <v>358</v>
-      </c>
-      <c r="F152" t="s">
-        <v>320</v>
       </c>
       <c r="G152" t="s">
         <v>359</v>
@@ -5550,10 +5550,10 @@
         <v>318</v>
       </c>
       <c r="E153" t="s">
+        <v>319</v>
+      </c>
+      <c r="F153" t="s">
         <v>358</v>
-      </c>
-      <c r="F153" t="s">
-        <v>320</v>
       </c>
       <c r="G153" t="s">
         <v>359</v>
@@ -5573,10 +5573,10 @@
         <v>318</v>
       </c>
       <c r="E154" t="s">
+        <v>319</v>
+      </c>
+      <c r="F154" t="s">
         <v>372</v>
-      </c>
-      <c r="F154" t="s">
-        <v>320</v>
       </c>
       <c r="G154" t="s">
         <v>373</v>
@@ -5596,10 +5596,10 @@
         <v>318</v>
       </c>
       <c r="E155" t="s">
+        <v>319</v>
+      </c>
+      <c r="F155" t="s">
         <v>372</v>
-      </c>
-      <c r="F155" t="s">
-        <v>320</v>
       </c>
       <c r="G155" t="s">
         <v>373</v>
@@ -5619,10 +5619,10 @@
         <v>318</v>
       </c>
       <c r="E156" t="s">
+        <v>319</v>
+      </c>
+      <c r="F156" t="s">
         <v>372</v>
-      </c>
-      <c r="F156" t="s">
-        <v>320</v>
       </c>
       <c r="G156" t="s">
         <v>373</v>
@@ -5642,10 +5642,10 @@
         <v>318</v>
       </c>
       <c r="E157" t="s">
+        <v>319</v>
+      </c>
+      <c r="F157" t="s">
         <v>372</v>
-      </c>
-      <c r="F157" t="s">
-        <v>320</v>
       </c>
       <c r="G157" t="s">
         <v>373</v>
@@ -5665,10 +5665,10 @@
         <v>318</v>
       </c>
       <c r="E158" t="s">
+        <v>319</v>
+      </c>
+      <c r="F158" t="s">
         <v>372</v>
-      </c>
-      <c r="F158" t="s">
-        <v>320</v>
       </c>
       <c r="G158" t="s">
         <v>373</v>
@@ -6125,10 +6125,10 @@
         <v>384</v>
       </c>
       <c r="E178" t="s">
+        <v>385</v>
+      </c>
+      <c r="F178" t="s">
         <v>426</v>
-      </c>
-      <c r="F178" t="s">
-        <v>386</v>
       </c>
       <c r="G178" t="s">
         <v>427</v>
@@ -6148,10 +6148,10 @@
         <v>384</v>
       </c>
       <c r="E179" t="s">
+        <v>385</v>
+      </c>
+      <c r="F179" t="s">
         <v>426</v>
-      </c>
-      <c r="F179" t="s">
-        <v>386</v>
       </c>
       <c r="G179" t="s">
         <v>427</v>
@@ -6171,10 +6171,10 @@
         <v>384</v>
       </c>
       <c r="E180" t="s">
+        <v>385</v>
+      </c>
+      <c r="F180" t="s">
         <v>426</v>
-      </c>
-      <c r="F180" t="s">
-        <v>386</v>
       </c>
       <c r="G180" t="s">
         <v>427</v>
@@ -6194,10 +6194,10 @@
         <v>384</v>
       </c>
       <c r="E181" t="s">
+        <v>385</v>
+      </c>
+      <c r="F181" t="s">
         <v>426</v>
-      </c>
-      <c r="F181" t="s">
-        <v>386</v>
       </c>
       <c r="G181" t="s">
         <v>427</v>
@@ -6217,10 +6217,10 @@
         <v>384</v>
       </c>
       <c r="E182" t="s">
+        <v>385</v>
+      </c>
+      <c r="F182" t="s">
         <v>426</v>
-      </c>
-      <c r="F182" t="s">
-        <v>386</v>
       </c>
       <c r="G182" t="s">
         <v>427</v>
@@ -6240,10 +6240,10 @@
         <v>384</v>
       </c>
       <c r="E183" t="s">
+        <v>385</v>
+      </c>
+      <c r="F183" t="s">
         <v>426</v>
-      </c>
-      <c r="F183" t="s">
-        <v>386</v>
       </c>
       <c r="G183" t="s">
         <v>427</v>
@@ -6263,10 +6263,10 @@
         <v>384</v>
       </c>
       <c r="E184" t="s">
+        <v>385</v>
+      </c>
+      <c r="F184" t="s">
         <v>426</v>
-      </c>
-      <c r="F184" t="s">
-        <v>386</v>
       </c>
       <c r="G184" t="s">
         <v>427</v>
@@ -6286,10 +6286,10 @@
         <v>384</v>
       </c>
       <c r="E185" t="s">
+        <v>385</v>
+      </c>
+      <c r="F185" t="s">
         <v>426</v>
-      </c>
-      <c r="F185" t="s">
-        <v>386</v>
       </c>
       <c r="G185" t="s">
         <v>427</v>
@@ -6309,10 +6309,10 @@
         <v>384</v>
       </c>
       <c r="E186" t="s">
+        <v>385</v>
+      </c>
+      <c r="F186" t="s">
         <v>426</v>
-      </c>
-      <c r="F186" t="s">
-        <v>386</v>
       </c>
       <c r="G186" t="s">
         <v>427</v>
@@ -6332,10 +6332,10 @@
         <v>384</v>
       </c>
       <c r="E187" t="s">
+        <v>385</v>
+      </c>
+      <c r="F187" t="s">
         <v>426</v>
-      </c>
-      <c r="F187" t="s">
-        <v>386</v>
       </c>
       <c r="G187" t="s">
         <v>427</v>
@@ -6355,10 +6355,10 @@
         <v>384</v>
       </c>
       <c r="E188" t="s">
+        <v>385</v>
+      </c>
+      <c r="F188" t="s">
         <v>448</v>
-      </c>
-      <c r="F188" t="s">
-        <v>386</v>
       </c>
       <c r="G188" t="s">
         <v>449</v>
@@ -6378,13 +6378,13 @@
         <v>452</v>
       </c>
       <c r="E189" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F189" t="s">
         <v>453</v>
       </c>
       <c r="G189" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6401,13 +6401,13 @@
         <v>452</v>
       </c>
       <c r="E190" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F190" t="s">
         <v>453</v>
       </c>
       <c r="G190" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6424,13 +6424,13 @@
         <v>452</v>
       </c>
       <c r="E191" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F191" t="s">
         <v>453</v>
       </c>
       <c r="G191" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6447,13 +6447,13 @@
         <v>452</v>
       </c>
       <c r="E192" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F192" t="s">
         <v>453</v>
       </c>
       <c r="G192" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6470,13 +6470,13 @@
         <v>452</v>
       </c>
       <c r="E193" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F193" t="s">
         <v>453</v>
       </c>
       <c r="G193" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6493,13 +6493,13 @@
         <v>452</v>
       </c>
       <c r="E194" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F194" t="s">
         <v>453</v>
       </c>
       <c r="G194" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6516,13 +6516,13 @@
         <v>466</v>
       </c>
       <c r="E195" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="F195" t="s">
         <v>467</v>
       </c>
       <c r="G195" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6539,13 +6539,13 @@
         <v>470</v>
       </c>
       <c r="E196" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F196" t="s">
         <v>471</v>
       </c>
       <c r="G196" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6562,13 +6562,13 @@
         <v>470</v>
       </c>
       <c r="E197" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F197" t="s">
         <v>471</v>
       </c>
       <c r="G197" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6585,13 +6585,13 @@
         <v>470</v>
       </c>
       <c r="E198" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F198" t="s">
         <v>471</v>
       </c>
       <c r="G198" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6608,13 +6608,13 @@
         <v>470</v>
       </c>
       <c r="E199" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F199" t="s">
         <v>471</v>
       </c>
       <c r="G199" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6631,13 +6631,13 @@
         <v>470</v>
       </c>
       <c r="E200" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F200" t="s">
         <v>471</v>
       </c>
       <c r="G200" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6654,13 +6654,13 @@
         <v>470</v>
       </c>
       <c r="E201" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F201" t="s">
         <v>471</v>
       </c>
       <c r="G201" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6677,13 +6677,13 @@
         <v>484</v>
       </c>
       <c r="E202" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F202" t="s">
         <v>485</v>
       </c>
       <c r="G202" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6700,13 +6700,13 @@
         <v>484</v>
       </c>
       <c r="E203" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F203" t="s">
         <v>485</v>
       </c>
       <c r="G203" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6723,13 +6723,13 @@
         <v>484</v>
       </c>
       <c r="E204" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F204" t="s">
         <v>485</v>
       </c>
       <c r="G204" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6746,13 +6746,13 @@
         <v>484</v>
       </c>
       <c r="E205" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F205" t="s">
         <v>485</v>
       </c>
       <c r="G205" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6769,13 +6769,13 @@
         <v>484</v>
       </c>
       <c r="E206" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F206" t="s">
         <v>485</v>
       </c>
       <c r="G206" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6792,13 +6792,13 @@
         <v>484</v>
       </c>
       <c r="E207" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F207" t="s">
         <v>485</v>
       </c>
       <c r="G207" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6815,13 +6815,13 @@
         <v>484</v>
       </c>
       <c r="E208" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F208" t="s">
         <v>485</v>
       </c>
       <c r="G208" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6838,13 +6838,13 @@
         <v>484</v>
       </c>
       <c r="E209" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F209" t="s">
         <v>485</v>
       </c>
       <c r="G209" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6861,13 +6861,13 @@
         <v>484</v>
       </c>
       <c r="E210" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F210" t="s">
         <v>485</v>
       </c>
       <c r="G210" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6884,13 +6884,13 @@
         <v>484</v>
       </c>
       <c r="E211" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F211" t="s">
         <v>485</v>
       </c>
       <c r="G211" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6907,13 +6907,13 @@
         <v>506</v>
       </c>
       <c r="E212" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F212" t="s">
         <v>507</v>
       </c>
       <c r="G212" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6930,13 +6930,13 @@
         <v>510</v>
       </c>
       <c r="E213" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F213" t="s">
         <v>511</v>
       </c>
       <c r="G213" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6953,13 +6953,13 @@
         <v>514</v>
       </c>
       <c r="E214" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="F214" t="s">
         <v>515</v>
       </c>
       <c r="G214" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6976,13 +6976,13 @@
         <v>514</v>
       </c>
       <c r="E215" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="F215" t="s">
         <v>515</v>
       </c>
       <c r="G215" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6999,13 +6999,13 @@
         <v>520</v>
       </c>
       <c r="E216" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F216" t="s">
         <v>521</v>
       </c>
       <c r="G216" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -7022,13 +7022,13 @@
         <v>520</v>
       </c>
       <c r="E217" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F217" t="s">
         <v>521</v>
       </c>
       <c r="G217" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -7045,13 +7045,13 @@
         <v>520</v>
       </c>
       <c r="E218" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F218" t="s">
         <v>521</v>
       </c>
       <c r="G218" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -7068,13 +7068,13 @@
         <v>520</v>
       </c>
       <c r="E219" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F219" t="s">
         <v>521</v>
       </c>
       <c r="G219" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -7091,13 +7091,13 @@
         <v>520</v>
       </c>
       <c r="E220" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F220" t="s">
         <v>521</v>
       </c>
       <c r="G220" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -7114,13 +7114,13 @@
         <v>520</v>
       </c>
       <c r="E221" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F221" t="s">
         <v>521</v>
       </c>
       <c r="G221" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -7137,13 +7137,13 @@
         <v>520</v>
       </c>
       <c r="E222" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F222" t="s">
         <v>521</v>
       </c>
       <c r="G222" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -7160,13 +7160,13 @@
         <v>536</v>
       </c>
       <c r="E223" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F223" t="s">
         <v>537</v>
       </c>
       <c r="G223" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -7183,13 +7183,13 @@
         <v>536</v>
       </c>
       <c r="E224" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F224" t="s">
         <v>537</v>
       </c>
       <c r="G224" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -7206,13 +7206,13 @@
         <v>536</v>
       </c>
       <c r="E225" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F225" t="s">
         <v>537</v>
       </c>
       <c r="G225" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -7229,13 +7229,13 @@
         <v>544</v>
       </c>
       <c r="E226" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="F226" t="s">
         <v>545</v>
       </c>
       <c r="G226" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -7252,13 +7252,13 @@
         <v>548</v>
       </c>
       <c r="E227" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="F227" t="s">
         <v>549</v>
       </c>
       <c r="G227" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -7275,13 +7275,13 @@
         <v>552</v>
       </c>
       <c r="E228" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="F228" t="s">
         <v>553</v>
       </c>
       <c r="G228" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -7298,13 +7298,13 @@
         <v>556</v>
       </c>
       <c r="E229" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="F229" t="s">
         <v>557</v>
       </c>
       <c r="G229" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -7321,13 +7321,13 @@
         <v>560</v>
       </c>
       <c r="E230" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F230" t="s">
         <v>561</v>
       </c>
       <c r="G230" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -7344,13 +7344,13 @@
         <v>560</v>
       </c>
       <c r="E231" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F231" t="s">
         <v>561</v>
       </c>
       <c r="G231" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/en/SectorGroup.xlsx
+++ b/api/xlsx/en/SectorGroup.xlsx
@@ -31,12 +31,12 @@
     <t>codeforiati:group-name</t>
   </si>
   <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
     <t>codeforiati:category-name</t>
   </si>
   <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -52,12 +52,12 @@
     <t>Education</t>
   </si>
   <si>
+    <t>111</t>
+  </si>
+  <si>
     <t>Education, Level Unspecified</t>
   </si>
   <si>
-    <t>111</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -82,12 +82,12 @@
     <t>Primary education</t>
   </si>
   <si>
+    <t>112</t>
+  </si>
+  <si>
     <t>Basic Education</t>
   </si>
   <si>
-    <t>112</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -112,12 +112,12 @@
     <t>Secondary education</t>
   </si>
   <si>
+    <t>113</t>
+  </si>
+  <si>
     <t>Secondary Education</t>
   </si>
   <si>
-    <t>113</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
@@ -130,12 +130,12 @@
     <t>Higher education</t>
   </si>
   <si>
+    <t>114</t>
+  </si>
+  <si>
     <t>Post-Secondary Education</t>
   </si>
   <si>
-    <t>114</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -154,12 +154,12 @@
     <t>Health</t>
   </si>
   <si>
+    <t>121</t>
+  </si>
+  <si>
     <t>Health, General</t>
   </si>
   <si>
-    <t>121</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -184,12 +184,12 @@
     <t>Basic health care</t>
   </si>
   <si>
+    <t>122</t>
+  </si>
+  <si>
     <t>Basic Health</t>
   </si>
   <si>
-    <t>122</t>
-  </si>
-  <si>
     <t>12230</t>
   </si>
   <si>
@@ -238,12 +238,12 @@
     <t>NCDs control, general</t>
   </si>
   <si>
+    <t>123</t>
+  </si>
+  <si>
     <t>Non-communicable diseases (NCDs)</t>
   </si>
   <si>
-    <t>123</t>
-  </si>
-  <si>
     <t>12320</t>
   </si>
   <si>
@@ -394,12 +394,12 @@
     <t>Government &amp; Civil Society</t>
   </si>
   <si>
+    <t>151</t>
+  </si>
+  <si>
     <t>Government &amp; Civil Society-general</t>
   </si>
   <si>
-    <t>151</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -496,12 +496,12 @@
     <t>Security system management and reform</t>
   </si>
   <si>
+    <t>152</t>
+  </si>
+  <si>
     <t>Conflict, Peace &amp; Security</t>
   </si>
   <si>
-    <t>152</t>
-  </si>
-  <si>
     <t>15220</t>
   </si>
   <si>
@@ -694,12 +694,12 @@
     <t>Energy</t>
   </si>
   <si>
+    <t>231</t>
+  </si>
+  <si>
     <t>Energy Policy</t>
   </si>
   <si>
-    <t>231</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -724,12 +724,12 @@
     <t>Energy generation, renewable sources - multiple technologies</t>
   </si>
   <si>
+    <t>232</t>
+  </si>
+  <si>
     <t>Energy generation, renewable sources</t>
   </si>
   <si>
-    <t>232</t>
-  </si>
-  <si>
     <t>23220</t>
   </si>
   <si>
@@ -784,12 +784,12 @@
     <t>Energy generation, non-renewable sources, unspecified</t>
   </si>
   <si>
+    <t>233</t>
+  </si>
+  <si>
     <t>Energy generation, non-renewable sources</t>
   </si>
   <si>
-    <t>233</t>
-  </si>
-  <si>
     <t>23320</t>
   </si>
   <si>
@@ -826,36 +826,36 @@
     <t>Hybrid energy electric power plants</t>
   </si>
   <si>
+    <t>234</t>
+  </si>
+  <si>
     <t>Hybrid energy plants</t>
   </si>
   <si>
-    <t>234</t>
-  </si>
-  <si>
     <t>23510</t>
   </si>
   <si>
     <t>Nuclear energy electric power plants and nuclear safety</t>
   </si>
   <si>
+    <t>235</t>
+  </si>
+  <si>
     <t>Nuclear energy plants</t>
   </si>
   <si>
-    <t>235</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
     <t>Heat plants</t>
   </si>
   <si>
+    <t>236</t>
+  </si>
+  <si>
     <t>Energy distribution</t>
   </si>
   <si>
-    <t>236</t>
-  </si>
-  <si>
     <t>23620</t>
   </si>
   <si>
@@ -976,12 +976,12 @@
     <t>Agriculture, Forestry, Fishing</t>
   </si>
   <si>
+    <t>311</t>
+  </si>
+  <si>
     <t>Agriculture</t>
   </si>
   <si>
-    <t>311</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1090,12 +1090,12 @@
     <t>Forestry policy and administrative management</t>
   </si>
   <si>
+    <t>312</t>
+  </si>
+  <si>
     <t>Forestry</t>
   </si>
   <si>
-    <t>312</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -1132,12 +1132,12 @@
     <t>Fishing policy and administrative management</t>
   </si>
   <si>
+    <t>313</t>
+  </si>
+  <si>
     <t>Fishing</t>
   </si>
   <si>
-    <t>313</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -1174,12 +1174,12 @@
     <t>Industry, Mining, Construction</t>
   </si>
   <si>
+    <t>321</t>
+  </si>
+  <si>
     <t>Industry</t>
   </si>
   <si>
-    <t>321</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1294,12 +1294,12 @@
     <t>Mineral/mining policy and administrative management</t>
   </si>
   <si>
+    <t>322</t>
+  </si>
+  <si>
     <t>Mineral Resources &amp; Mining</t>
   </si>
   <si>
-    <t>322</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -1360,10 +1360,10 @@
     <t>Construction policy and administrative management</t>
   </si>
   <si>
+    <t>323</t>
+  </si>
+  <si>
     <t>Construction</t>
-  </si>
-  <si>
-    <t>323</t>
   </si>
   <si>
     <t>33110</t>
@@ -2770,10 +2770,10 @@
         <v>89</v>
       </c>
       <c r="F32" t="s">
+        <v>88</v>
+      </c>
+      <c r="G32" t="s">
         <v>89</v>
-      </c>
-      <c r="G32" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2793,10 +2793,10 @@
         <v>89</v>
       </c>
       <c r="F33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G33" t="s">
         <v>89</v>
-      </c>
-      <c r="G33" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2816,10 +2816,10 @@
         <v>89</v>
       </c>
       <c r="F34" t="s">
+        <v>88</v>
+      </c>
+      <c r="G34" t="s">
         <v>89</v>
-      </c>
-      <c r="G34" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2839,10 +2839,10 @@
         <v>89</v>
       </c>
       <c r="F35" t="s">
+        <v>88</v>
+      </c>
+      <c r="G35" t="s">
         <v>89</v>
-      </c>
-      <c r="G35" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2862,10 +2862,10 @@
         <v>89</v>
       </c>
       <c r="F36" t="s">
+        <v>88</v>
+      </c>
+      <c r="G36" t="s">
         <v>89</v>
-      </c>
-      <c r="G36" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2885,10 +2885,10 @@
         <v>101</v>
       </c>
       <c r="F37" t="s">
+        <v>100</v>
+      </c>
+      <c r="G37" t="s">
         <v>101</v>
-      </c>
-      <c r="G37" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2908,10 +2908,10 @@
         <v>101</v>
       </c>
       <c r="F38" t="s">
+        <v>100</v>
+      </c>
+      <c r="G38" t="s">
         <v>101</v>
-      </c>
-      <c r="G38" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2931,10 +2931,10 @@
         <v>101</v>
       </c>
       <c r="F39" t="s">
+        <v>100</v>
+      </c>
+      <c r="G39" t="s">
         <v>101</v>
-      </c>
-      <c r="G39" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2954,10 +2954,10 @@
         <v>101</v>
       </c>
       <c r="F40" t="s">
+        <v>100</v>
+      </c>
+      <c r="G40" t="s">
         <v>101</v>
-      </c>
-      <c r="G40" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2977,10 +2977,10 @@
         <v>101</v>
       </c>
       <c r="F41" t="s">
+        <v>100</v>
+      </c>
+      <c r="G41" t="s">
         <v>101</v>
-      </c>
-      <c r="G41" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -3000,10 +3000,10 @@
         <v>101</v>
       </c>
       <c r="F42" t="s">
+        <v>100</v>
+      </c>
+      <c r="G42" t="s">
         <v>101</v>
-      </c>
-      <c r="G42" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3023,10 +3023,10 @@
         <v>101</v>
       </c>
       <c r="F43" t="s">
+        <v>100</v>
+      </c>
+      <c r="G43" t="s">
         <v>101</v>
-      </c>
-      <c r="G43" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3046,10 +3046,10 @@
         <v>101</v>
       </c>
       <c r="F44" t="s">
+        <v>100</v>
+      </c>
+      <c r="G44" t="s">
         <v>101</v>
-      </c>
-      <c r="G44" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3069,10 +3069,10 @@
         <v>101</v>
       </c>
       <c r="F45" t="s">
+        <v>100</v>
+      </c>
+      <c r="G45" t="s">
         <v>101</v>
-      </c>
-      <c r="G45" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3092,10 +3092,10 @@
         <v>101</v>
       </c>
       <c r="F46" t="s">
+        <v>100</v>
+      </c>
+      <c r="G46" t="s">
         <v>101</v>
-      </c>
-      <c r="G46" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3115,10 +3115,10 @@
         <v>101</v>
       </c>
       <c r="F47" t="s">
+        <v>100</v>
+      </c>
+      <c r="G47" t="s">
         <v>101</v>
-      </c>
-      <c r="G47" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3644,10 +3644,10 @@
         <v>175</v>
       </c>
       <c r="F70" t="s">
+        <v>174</v>
+      </c>
+      <c r="G70" t="s">
         <v>175</v>
-      </c>
-      <c r="G70" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3667,10 +3667,10 @@
         <v>175</v>
       </c>
       <c r="F71" t="s">
+        <v>174</v>
+      </c>
+      <c r="G71" t="s">
         <v>175</v>
-      </c>
-      <c r="G71" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3690,10 +3690,10 @@
         <v>175</v>
       </c>
       <c r="F72" t="s">
+        <v>174</v>
+      </c>
+      <c r="G72" t="s">
         <v>175</v>
-      </c>
-      <c r="G72" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3713,10 +3713,10 @@
         <v>175</v>
       </c>
       <c r="F73" t="s">
+        <v>174</v>
+      </c>
+      <c r="G73" t="s">
         <v>175</v>
-      </c>
-      <c r="G73" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3736,10 +3736,10 @@
         <v>175</v>
       </c>
       <c r="F74" t="s">
+        <v>174</v>
+      </c>
+      <c r="G74" t="s">
         <v>175</v>
-      </c>
-      <c r="G74" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3759,10 +3759,10 @@
         <v>175</v>
       </c>
       <c r="F75" t="s">
+        <v>174</v>
+      </c>
+      <c r="G75" t="s">
         <v>175</v>
-      </c>
-      <c r="G75" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3782,10 +3782,10 @@
         <v>175</v>
       </c>
       <c r="F76" t="s">
+        <v>174</v>
+      </c>
+      <c r="G76" t="s">
         <v>175</v>
-      </c>
-      <c r="G76" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3805,10 +3805,10 @@
         <v>175</v>
       </c>
       <c r="F77" t="s">
+        <v>174</v>
+      </c>
+      <c r="G77" t="s">
         <v>175</v>
-      </c>
-      <c r="G77" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3828,10 +3828,10 @@
         <v>175</v>
       </c>
       <c r="F78" t="s">
+        <v>174</v>
+      </c>
+      <c r="G78" t="s">
         <v>175</v>
-      </c>
-      <c r="G78" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3851,10 +3851,10 @@
         <v>175</v>
       </c>
       <c r="F79" t="s">
+        <v>174</v>
+      </c>
+      <c r="G79" t="s">
         <v>175</v>
-      </c>
-      <c r="G79" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3874,10 +3874,10 @@
         <v>175</v>
       </c>
       <c r="F80" t="s">
+        <v>174</v>
+      </c>
+      <c r="G80" t="s">
         <v>175</v>
-      </c>
-      <c r="G80" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3897,10 +3897,10 @@
         <v>199</v>
       </c>
       <c r="F81" t="s">
+        <v>198</v>
+      </c>
+      <c r="G81" t="s">
         <v>199</v>
-      </c>
-      <c r="G81" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3920,10 +3920,10 @@
         <v>199</v>
       </c>
       <c r="F82" t="s">
+        <v>198</v>
+      </c>
+      <c r="G82" t="s">
         <v>199</v>
-      </c>
-      <c r="G82" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3943,10 +3943,10 @@
         <v>199</v>
       </c>
       <c r="F83" t="s">
+        <v>198</v>
+      </c>
+      <c r="G83" t="s">
         <v>199</v>
-      </c>
-      <c r="G83" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3966,10 +3966,10 @@
         <v>199</v>
       </c>
       <c r="F84" t="s">
+        <v>198</v>
+      </c>
+      <c r="G84" t="s">
         <v>199</v>
-      </c>
-      <c r="G84" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3989,10 +3989,10 @@
         <v>199</v>
       </c>
       <c r="F85" t="s">
+        <v>198</v>
+      </c>
+      <c r="G85" t="s">
         <v>199</v>
-      </c>
-      <c r="G85" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4012,10 +4012,10 @@
         <v>199</v>
       </c>
       <c r="F86" t="s">
+        <v>198</v>
+      </c>
+      <c r="G86" t="s">
         <v>199</v>
-      </c>
-      <c r="G86" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4035,10 +4035,10 @@
         <v>199</v>
       </c>
       <c r="F87" t="s">
+        <v>198</v>
+      </c>
+      <c r="G87" t="s">
         <v>199</v>
-      </c>
-      <c r="G87" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4058,10 +4058,10 @@
         <v>215</v>
       </c>
       <c r="F88" t="s">
+        <v>214</v>
+      </c>
+      <c r="G88" t="s">
         <v>215</v>
-      </c>
-      <c r="G88" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4081,10 +4081,10 @@
         <v>215</v>
       </c>
       <c r="F89" t="s">
+        <v>214</v>
+      </c>
+      <c r="G89" t="s">
         <v>215</v>
-      </c>
-      <c r="G89" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4104,10 +4104,10 @@
         <v>215</v>
       </c>
       <c r="F90" t="s">
+        <v>214</v>
+      </c>
+      <c r="G90" t="s">
         <v>215</v>
-      </c>
-      <c r="G90" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4127,10 +4127,10 @@
         <v>215</v>
       </c>
       <c r="F91" t="s">
+        <v>214</v>
+      </c>
+      <c r="G91" t="s">
         <v>215</v>
-      </c>
-      <c r="G91" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4794,10 +4794,10 @@
         <v>295</v>
       </c>
       <c r="F120" t="s">
+        <v>294</v>
+      </c>
+      <c r="G120" t="s">
         <v>295</v>
-      </c>
-      <c r="G120" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4817,10 +4817,10 @@
         <v>295</v>
       </c>
       <c r="F121" t="s">
+        <v>294</v>
+      </c>
+      <c r="G121" t="s">
         <v>295</v>
-      </c>
-      <c r="G121" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4840,10 +4840,10 @@
         <v>295</v>
       </c>
       <c r="F122" t="s">
+        <v>294</v>
+      </c>
+      <c r="G122" t="s">
         <v>295</v>
-      </c>
-      <c r="G122" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4863,10 +4863,10 @@
         <v>295</v>
       </c>
       <c r="F123" t="s">
+        <v>294</v>
+      </c>
+      <c r="G123" t="s">
         <v>295</v>
-      </c>
-      <c r="G123" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4886,10 +4886,10 @@
         <v>295</v>
       </c>
       <c r="F124" t="s">
+        <v>294</v>
+      </c>
+      <c r="G124" t="s">
         <v>295</v>
-      </c>
-      <c r="G124" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4909,10 +4909,10 @@
         <v>295</v>
       </c>
       <c r="F125" t="s">
+        <v>294</v>
+      </c>
+      <c r="G125" t="s">
         <v>295</v>
-      </c>
-      <c r="G125" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4932,10 +4932,10 @@
         <v>309</v>
       </c>
       <c r="F126" t="s">
+        <v>308</v>
+      </c>
+      <c r="G126" t="s">
         <v>309</v>
-      </c>
-      <c r="G126" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4955,10 +4955,10 @@
         <v>309</v>
       </c>
       <c r="F127" t="s">
+        <v>308</v>
+      </c>
+      <c r="G127" t="s">
         <v>309</v>
-      </c>
-      <c r="G127" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4978,10 +4978,10 @@
         <v>309</v>
       </c>
       <c r="F128" t="s">
+        <v>308</v>
+      </c>
+      <c r="G128" t="s">
         <v>309</v>
-      </c>
-      <c r="G128" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -5001,10 +5001,10 @@
         <v>309</v>
       </c>
       <c r="F129" t="s">
+        <v>308</v>
+      </c>
+      <c r="G129" t="s">
         <v>309</v>
-      </c>
-      <c r="G129" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -6381,10 +6381,10 @@
         <v>453</v>
       </c>
       <c r="F189" t="s">
+        <v>452</v>
+      </c>
+      <c r="G189" t="s">
         <v>453</v>
-      </c>
-      <c r="G189" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6404,10 +6404,10 @@
         <v>453</v>
       </c>
       <c r="F190" t="s">
+        <v>452</v>
+      </c>
+      <c r="G190" t="s">
         <v>453</v>
-      </c>
-      <c r="G190" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6427,10 +6427,10 @@
         <v>453</v>
       </c>
       <c r="F191" t="s">
+        <v>452</v>
+      </c>
+      <c r="G191" t="s">
         <v>453</v>
-      </c>
-      <c r="G191" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6450,10 +6450,10 @@
         <v>453</v>
       </c>
       <c r="F192" t="s">
+        <v>452</v>
+      </c>
+      <c r="G192" t="s">
         <v>453</v>
-      </c>
-      <c r="G192" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6473,10 +6473,10 @@
         <v>453</v>
       </c>
       <c r="F193" t="s">
+        <v>452</v>
+      </c>
+      <c r="G193" t="s">
         <v>453</v>
-      </c>
-      <c r="G193" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6496,10 +6496,10 @@
         <v>453</v>
       </c>
       <c r="F194" t="s">
+        <v>452</v>
+      </c>
+      <c r="G194" t="s">
         <v>453</v>
-      </c>
-      <c r="G194" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6519,10 +6519,10 @@
         <v>467</v>
       </c>
       <c r="F195" t="s">
+        <v>466</v>
+      </c>
+      <c r="G195" t="s">
         <v>467</v>
-      </c>
-      <c r="G195" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6542,10 +6542,10 @@
         <v>471</v>
       </c>
       <c r="F196" t="s">
+        <v>470</v>
+      </c>
+      <c r="G196" t="s">
         <v>471</v>
-      </c>
-      <c r="G196" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6565,10 +6565,10 @@
         <v>471</v>
       </c>
       <c r="F197" t="s">
+        <v>470</v>
+      </c>
+      <c r="G197" t="s">
         <v>471</v>
-      </c>
-      <c r="G197" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6588,10 +6588,10 @@
         <v>471</v>
       </c>
       <c r="F198" t="s">
+        <v>470</v>
+      </c>
+      <c r="G198" t="s">
         <v>471</v>
-      </c>
-      <c r="G198" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6611,10 +6611,10 @@
         <v>471</v>
       </c>
       <c r="F199" t="s">
+        <v>470</v>
+      </c>
+      <c r="G199" t="s">
         <v>471</v>
-      </c>
-      <c r="G199" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6634,10 +6634,10 @@
         <v>471</v>
       </c>
       <c r="F200" t="s">
+        <v>470</v>
+      </c>
+      <c r="G200" t="s">
         <v>471</v>
-      </c>
-      <c r="G200" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6657,10 +6657,10 @@
         <v>471</v>
       </c>
       <c r="F201" t="s">
+        <v>470</v>
+      </c>
+      <c r="G201" t="s">
         <v>471</v>
-      </c>
-      <c r="G201" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6680,10 +6680,10 @@
         <v>485</v>
       </c>
       <c r="F202" t="s">
+        <v>484</v>
+      </c>
+      <c r="G202" t="s">
         <v>485</v>
-      </c>
-      <c r="G202" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6703,10 +6703,10 @@
         <v>485</v>
       </c>
       <c r="F203" t="s">
+        <v>484</v>
+      </c>
+      <c r="G203" t="s">
         <v>485</v>
-      </c>
-      <c r="G203" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6726,10 +6726,10 @@
         <v>485</v>
       </c>
       <c r="F204" t="s">
+        <v>484</v>
+      </c>
+      <c r="G204" t="s">
         <v>485</v>
-      </c>
-      <c r="G204" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6749,10 +6749,10 @@
         <v>485</v>
       </c>
       <c r="F205" t="s">
+        <v>484</v>
+      </c>
+      <c r="G205" t="s">
         <v>485</v>
-      </c>
-      <c r="G205" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6772,10 +6772,10 @@
         <v>485</v>
       </c>
       <c r="F206" t="s">
+        <v>484</v>
+      </c>
+      <c r="G206" t="s">
         <v>485</v>
-      </c>
-      <c r="G206" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6795,10 +6795,10 @@
         <v>485</v>
       </c>
       <c r="F207" t="s">
+        <v>484</v>
+      </c>
+      <c r="G207" t="s">
         <v>485</v>
-      </c>
-      <c r="G207" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6818,10 +6818,10 @@
         <v>485</v>
       </c>
       <c r="F208" t="s">
+        <v>484</v>
+      </c>
+      <c r="G208" t="s">
         <v>485</v>
-      </c>
-      <c r="G208" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6841,10 +6841,10 @@
         <v>485</v>
       </c>
       <c r="F209" t="s">
+        <v>484</v>
+      </c>
+      <c r="G209" t="s">
         <v>485</v>
-      </c>
-      <c r="G209" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6864,10 +6864,10 @@
         <v>485</v>
       </c>
       <c r="F210" t="s">
+        <v>484</v>
+      </c>
+      <c r="G210" t="s">
         <v>485</v>
-      </c>
-      <c r="G210" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6887,10 +6887,10 @@
         <v>485</v>
       </c>
       <c r="F211" t="s">
+        <v>484</v>
+      </c>
+      <c r="G211" t="s">
         <v>485</v>
-      </c>
-      <c r="G211" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6910,10 +6910,10 @@
         <v>507</v>
       </c>
       <c r="F212" t="s">
+        <v>506</v>
+      </c>
+      <c r="G212" t="s">
         <v>507</v>
-      </c>
-      <c r="G212" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6933,10 +6933,10 @@
         <v>511</v>
       </c>
       <c r="F213" t="s">
+        <v>510</v>
+      </c>
+      <c r="G213" t="s">
         <v>511</v>
-      </c>
-      <c r="G213" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6956,10 +6956,10 @@
         <v>515</v>
       </c>
       <c r="F214" t="s">
+        <v>514</v>
+      </c>
+      <c r="G214" t="s">
         <v>515</v>
-      </c>
-      <c r="G214" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6979,10 +6979,10 @@
         <v>515</v>
       </c>
       <c r="F215" t="s">
+        <v>514</v>
+      </c>
+      <c r="G215" t="s">
         <v>515</v>
-      </c>
-      <c r="G215" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -7002,10 +7002,10 @@
         <v>521</v>
       </c>
       <c r="F216" t="s">
+        <v>520</v>
+      </c>
+      <c r="G216" t="s">
         <v>521</v>
-      </c>
-      <c r="G216" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -7025,10 +7025,10 @@
         <v>521</v>
       </c>
       <c r="F217" t="s">
+        <v>520</v>
+      </c>
+      <c r="G217" t="s">
         <v>521</v>
-      </c>
-      <c r="G217" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -7048,10 +7048,10 @@
         <v>521</v>
       </c>
       <c r="F218" t="s">
+        <v>520</v>
+      </c>
+      <c r="G218" t="s">
         <v>521</v>
-      </c>
-      <c r="G218" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -7071,10 +7071,10 @@
         <v>521</v>
       </c>
       <c r="F219" t="s">
+        <v>520</v>
+      </c>
+      <c r="G219" t="s">
         <v>521</v>
-      </c>
-      <c r="G219" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -7094,10 +7094,10 @@
         <v>521</v>
       </c>
       <c r="F220" t="s">
+        <v>520</v>
+      </c>
+      <c r="G220" t="s">
         <v>521</v>
-      </c>
-      <c r="G220" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -7117,10 +7117,10 @@
         <v>521</v>
       </c>
       <c r="F221" t="s">
+        <v>520</v>
+      </c>
+      <c r="G221" t="s">
         <v>521</v>
-      </c>
-      <c r="G221" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -7140,10 +7140,10 @@
         <v>521</v>
       </c>
       <c r="F222" t="s">
+        <v>520</v>
+      </c>
+      <c r="G222" t="s">
         <v>521</v>
-      </c>
-      <c r="G222" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -7163,10 +7163,10 @@
         <v>537</v>
       </c>
       <c r="F223" t="s">
+        <v>536</v>
+      </c>
+      <c r="G223" t="s">
         <v>537</v>
-      </c>
-      <c r="G223" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -7186,10 +7186,10 @@
         <v>537</v>
       </c>
       <c r="F224" t="s">
+        <v>536</v>
+      </c>
+      <c r="G224" t="s">
         <v>537</v>
-      </c>
-      <c r="G224" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -7209,10 +7209,10 @@
         <v>537</v>
       </c>
       <c r="F225" t="s">
+        <v>536</v>
+      </c>
+      <c r="G225" t="s">
         <v>537</v>
-      </c>
-      <c r="G225" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -7232,10 +7232,10 @@
         <v>545</v>
       </c>
       <c r="F226" t="s">
+        <v>544</v>
+      </c>
+      <c r="G226" t="s">
         <v>545</v>
-      </c>
-      <c r="G226" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -7255,10 +7255,10 @@
         <v>549</v>
       </c>
       <c r="F227" t="s">
+        <v>548</v>
+      </c>
+      <c r="G227" t="s">
         <v>549</v>
-      </c>
-      <c r="G227" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -7278,10 +7278,10 @@
         <v>553</v>
       </c>
       <c r="F228" t="s">
+        <v>552</v>
+      </c>
+      <c r="G228" t="s">
         <v>553</v>
-      </c>
-      <c r="G228" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -7301,10 +7301,10 @@
         <v>557</v>
       </c>
       <c r="F229" t="s">
+        <v>556</v>
+      </c>
+      <c r="G229" t="s">
         <v>557</v>
-      </c>
-      <c r="G229" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -7324,10 +7324,10 @@
         <v>561</v>
       </c>
       <c r="F230" t="s">
+        <v>560</v>
+      </c>
+      <c r="G230" t="s">
         <v>561</v>
-      </c>
-      <c r="G230" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -7347,10 +7347,10 @@
         <v>561</v>
       </c>
       <c r="F231" t="s">
+        <v>560</v>
+      </c>
+      <c r="G231" t="s">
         <v>561</v>
-      </c>
-      <c r="G231" t="s">
-        <v>560</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/en/SectorGroup.xlsx
+++ b/api/xlsx/en/SectorGroup.xlsx
@@ -25,18 +25,18 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:category-name</t>
+  </si>
+  <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
     <t>codeforiati:group-name</t>
   </si>
   <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
-    <t>codeforiati:category-name</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -46,18 +46,18 @@
     <t>active</t>
   </si>
   <si>
+    <t>Education, Level Unspecified</t>
+  </si>
+  <si>
     <t>110</t>
   </si>
   <si>
+    <t>111</t>
+  </si>
+  <si>
     <t>Education</t>
   </si>
   <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>Education, Level Unspecified</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -82,12 +82,12 @@
     <t>Primary education</t>
   </si>
   <si>
+    <t>Basic Education</t>
+  </si>
+  <si>
     <t>112</t>
   </si>
   <si>
-    <t>Basic Education</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -112,12 +112,12 @@
     <t>Secondary education</t>
   </si>
   <si>
+    <t>Secondary Education</t>
+  </si>
+  <si>
     <t>113</t>
   </si>
   <si>
-    <t>Secondary Education</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
@@ -130,12 +130,12 @@
     <t>Higher education</t>
   </si>
   <si>
+    <t>Post-Secondary Education</t>
+  </si>
+  <si>
     <t>114</t>
   </si>
   <si>
-    <t>Post-Secondary Education</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -148,18 +148,18 @@
     <t>Health policy and administrative management</t>
   </si>
   <si>
+    <t>Health, General</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
+    <t>121</t>
+  </si>
+  <si>
     <t>Health</t>
   </si>
   <si>
-    <t>121</t>
-  </si>
-  <si>
-    <t>Health, General</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -184,12 +184,12 @@
     <t>Basic health care</t>
   </si>
   <si>
+    <t>Basic Health</t>
+  </si>
+  <si>
     <t>122</t>
   </si>
   <si>
-    <t>Basic Health</t>
-  </si>
-  <si>
     <t>12230</t>
   </si>
   <si>
@@ -238,12 +238,12 @@
     <t>NCDs control, general</t>
   </si>
   <si>
+    <t>Non-communicable diseases (NCDs)</t>
+  </si>
+  <si>
     <t>123</t>
   </si>
   <si>
-    <t>Non-communicable diseases (NCDs)</t>
-  </si>
-  <si>
     <t>12320</t>
   </si>
   <si>
@@ -280,12 +280,12 @@
     <t>Population policy and administrative management</t>
   </si>
   <si>
+    <t>Population Policies/Programmes &amp; Reproductive Health</t>
+  </si>
+  <si>
     <t>130</t>
   </si>
   <si>
-    <t>Population Policies/Programmes &amp; Reproductive Health</t>
-  </si>
-  <si>
     <t>13020</t>
   </si>
   <si>
@@ -316,12 +316,12 @@
     <t>Water sector policy and administrative management</t>
   </si>
   <si>
+    <t>Water Supply &amp; Sanitation</t>
+  </si>
+  <si>
     <t>140</t>
   </si>
   <si>
-    <t>Water Supply &amp; Sanitation</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -388,18 +388,18 @@
     <t>Public sector policy and administrative management</t>
   </si>
   <si>
+    <t>Government &amp; Civil Society-general</t>
+  </si>
+  <si>
     <t>150</t>
   </si>
   <si>
+    <t>151</t>
+  </si>
+  <si>
     <t>Government &amp; Civil Society</t>
   </si>
   <si>
-    <t>151</t>
-  </si>
-  <si>
-    <t>Government &amp; Civil Society-general</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -496,12 +496,12 @@
     <t>Security system management and reform</t>
   </si>
   <si>
+    <t>Conflict, Peace &amp; Security</t>
+  </si>
+  <si>
     <t>152</t>
   </si>
   <si>
-    <t>Conflict, Peace &amp; Security</t>
-  </si>
-  <si>
     <t>15220</t>
   </si>
   <si>
@@ -538,12 +538,12 @@
     <t>Social Protection</t>
   </si>
   <si>
+    <t>Other Social Infrastructure &amp; Services</t>
+  </si>
+  <si>
     <t>160</t>
   </si>
   <si>
-    <t>Other Social Infrastructure &amp; Services</t>
-  </si>
-  <si>
     <t>16020</t>
   </si>
   <si>
@@ -610,12 +610,12 @@
     <t>Transport policy and administrative management</t>
   </si>
   <si>
+    <t>Transport &amp; Storage</t>
+  </si>
+  <si>
     <t>210</t>
   </si>
   <si>
-    <t>Transport &amp; Storage</t>
-  </si>
-  <si>
     <t>21020</t>
   </si>
   <si>
@@ -658,12 +658,12 @@
     <t>Communications policy and administrative management</t>
   </si>
   <si>
+    <t>Communications</t>
+  </si>
+  <si>
     <t>220</t>
   </si>
   <si>
-    <t>Communications</t>
-  </si>
-  <si>
     <t>22020</t>
   </si>
   <si>
@@ -688,18 +688,18 @@
     <t>Energy policy and administrative management</t>
   </si>
   <si>
+    <t>Energy Policy</t>
+  </si>
+  <si>
     <t>230</t>
   </si>
   <si>
+    <t>231</t>
+  </si>
+  <si>
     <t>Energy</t>
   </si>
   <si>
-    <t>231</t>
-  </si>
-  <si>
-    <t>Energy Policy</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -724,12 +724,12 @@
     <t>Energy generation, renewable sources - multiple technologies</t>
   </si>
   <si>
+    <t>Energy generation, renewable sources</t>
+  </si>
+  <si>
     <t>232</t>
   </si>
   <si>
-    <t>Energy generation, renewable sources</t>
-  </si>
-  <si>
     <t>23220</t>
   </si>
   <si>
@@ -784,12 +784,12 @@
     <t>Energy generation, non-renewable sources, unspecified</t>
   </si>
   <si>
+    <t>Energy generation, non-renewable sources</t>
+  </si>
+  <si>
     <t>233</t>
   </si>
   <si>
-    <t>Energy generation, non-renewable sources</t>
-  </si>
-  <si>
     <t>23320</t>
   </si>
   <si>
@@ -826,36 +826,36 @@
     <t>Hybrid energy electric power plants</t>
   </si>
   <si>
+    <t>Hybrid energy plants</t>
+  </si>
+  <si>
     <t>234</t>
   </si>
   <si>
-    <t>Hybrid energy plants</t>
-  </si>
-  <si>
     <t>23510</t>
   </si>
   <si>
     <t>Nuclear energy electric power plants and nuclear safety</t>
   </si>
   <si>
+    <t>Nuclear energy plants</t>
+  </si>
+  <si>
     <t>235</t>
   </si>
   <si>
-    <t>Nuclear energy plants</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
     <t>Heat plants</t>
   </si>
   <si>
+    <t>Energy distribution</t>
+  </si>
+  <si>
     <t>236</t>
   </si>
   <si>
-    <t>Energy distribution</t>
-  </si>
-  <si>
     <t>23620</t>
   </si>
   <si>
@@ -898,12 +898,12 @@
     <t>Financial policy and administrative management</t>
   </si>
   <si>
+    <t>Banking &amp; Financial Services</t>
+  </si>
+  <si>
     <t>240</t>
   </si>
   <si>
-    <t>Banking &amp; Financial Services</t>
-  </si>
-  <si>
     <t>24020</t>
   </si>
   <si>
@@ -940,12 +940,12 @@
     <t>Business policy and administration</t>
   </si>
   <si>
+    <t>Business &amp; Other Services</t>
+  </si>
+  <si>
     <t>250</t>
   </si>
   <si>
-    <t>Business &amp; Other Services</t>
-  </si>
-  <si>
     <t>25020</t>
   </si>
   <si>
@@ -970,18 +970,18 @@
     <t>Agricultural policy and administrative management</t>
   </si>
   <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
     <t>310</t>
   </si>
   <si>
+    <t>311</t>
+  </si>
+  <si>
     <t>Agriculture, Forestry, Fishing</t>
   </si>
   <si>
-    <t>311</t>
-  </si>
-  <si>
-    <t>Agriculture</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1090,12 +1090,12 @@
     <t>Forestry policy and administrative management</t>
   </si>
   <si>
+    <t>Forestry</t>
+  </si>
+  <si>
     <t>312</t>
   </si>
   <si>
-    <t>Forestry</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -1132,12 +1132,12 @@
     <t>Fishing policy and administrative management</t>
   </si>
   <si>
+    <t>Fishing</t>
+  </si>
+  <si>
     <t>313</t>
   </si>
   <si>
-    <t>Fishing</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -1168,18 +1168,18 @@
     <t>Industrial policy and administrative management</t>
   </si>
   <si>
+    <t>Industry</t>
+  </si>
+  <si>
     <t>320</t>
   </si>
   <si>
+    <t>321</t>
+  </si>
+  <si>
     <t>Industry, Mining, Construction</t>
   </si>
   <si>
-    <t>321</t>
-  </si>
-  <si>
-    <t>Industry</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1294,12 +1294,12 @@
     <t>Mineral/mining policy and administrative management</t>
   </si>
   <si>
+    <t>Mineral Resources &amp; Mining</t>
+  </si>
+  <si>
     <t>322</t>
   </si>
   <si>
-    <t>Mineral Resources &amp; Mining</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -1360,24 +1360,24 @@
     <t>Construction policy and administrative management</t>
   </si>
   <si>
+    <t>Construction</t>
+  </si>
+  <si>
     <t>323</t>
   </si>
   <si>
-    <t>Construction</t>
-  </si>
-  <si>
     <t>33110</t>
   </si>
   <si>
     <t>Trade policy and administrative management</t>
   </si>
   <si>
+    <t>Trade Policies &amp; Regulations</t>
+  </si>
+  <si>
     <t>331</t>
   </si>
   <si>
-    <t>Trade Policies &amp; Regulations</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1414,24 +1414,24 @@
     <t>Tourism policy and administrative management</t>
   </si>
   <si>
+    <t>Tourism</t>
+  </si>
+  <si>
     <t>332</t>
   </si>
   <si>
-    <t>Tourism</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
     <t>Environmental policy and administrative management</t>
   </si>
   <si>
+    <t>General Environment Protection</t>
+  </si>
+  <si>
     <t>410</t>
   </si>
   <si>
-    <t>General Environment Protection</t>
-  </si>
-  <si>
     <t>41020</t>
   </si>
   <si>
@@ -1468,12 +1468,12 @@
     <t>Multisector aid</t>
   </si>
   <si>
+    <t>Other Multisector</t>
+  </si>
+  <si>
     <t>430</t>
   </si>
   <si>
-    <t>Other Multisector</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -1534,36 +1534,36 @@
     <t>General budget support-related aid</t>
   </si>
   <si>
+    <t>General Budget Support</t>
+  </si>
+  <si>
     <t>510</t>
   </si>
   <si>
-    <t>General Budget Support</t>
-  </si>
-  <si>
     <t>52010</t>
   </si>
   <si>
     <t>Food assistance</t>
   </si>
   <si>
+    <t>Development Food Assistance</t>
+  </si>
+  <si>
     <t>520</t>
   </si>
   <si>
-    <t>Development Food Assistance</t>
-  </si>
-  <si>
     <t>53030</t>
   </si>
   <si>
     <t>Import support (capital goods)</t>
   </si>
   <si>
+    <t>Other Commodity Assistance</t>
+  </si>
+  <si>
     <t>530</t>
   </si>
   <si>
-    <t>Other Commodity Assistance</t>
-  </si>
-  <si>
     <t>53040</t>
   </si>
   <si>
@@ -1576,12 +1576,12 @@
     <t>Action relating to debt</t>
   </si>
   <si>
+    <t>Action Relating to Debt</t>
+  </si>
+  <si>
     <t>600</t>
   </si>
   <si>
-    <t>Action Relating to Debt</t>
-  </si>
-  <si>
     <t>60020</t>
   </si>
   <si>
@@ -1624,12 +1624,12 @@
     <t>Material relief assistance and services</t>
   </si>
   <si>
+    <t>Emergency Response</t>
+  </si>
+  <si>
     <t>720</t>
   </si>
   <si>
-    <t>Emergency Response</t>
-  </si>
-  <si>
     <t>72040</t>
   </si>
   <si>
@@ -1648,58 +1648,58 @@
     <t>Immediate post-emergency reconstruction and rehabilitation</t>
   </si>
   <si>
+    <t>Reconstruction Relief &amp; Rehabilitation</t>
+  </si>
+  <si>
     <t>730</t>
   </si>
   <si>
-    <t>Reconstruction Relief &amp; Rehabilitation</t>
-  </si>
-  <si>
     <t>74020</t>
   </si>
   <si>
     <t>Multi-hazard response preparedness</t>
   </si>
   <si>
+    <t>Disaster Prevention &amp; Preparedness</t>
+  </si>
+  <si>
     <t>740</t>
   </si>
   <si>
-    <t>Disaster Prevention &amp; Preparedness</t>
-  </si>
-  <si>
     <t>91010</t>
   </si>
   <si>
     <t>Administrative costs (non-sector allocable)</t>
   </si>
   <si>
+    <t>Administrative Costs of Donors</t>
+  </si>
+  <si>
     <t>910</t>
   </si>
   <si>
-    <t>Administrative Costs of Donors</t>
-  </si>
-  <si>
     <t>93010</t>
   </si>
   <si>
     <t>Refugees/asylum seekers in donor countries (non-sector allocable)</t>
   </si>
   <si>
+    <t>Refugees in Donor Countries</t>
+  </si>
+  <si>
     <t>930</t>
   </si>
   <si>
-    <t>Refugees in Donor Countries</t>
-  </si>
-  <si>
     <t>99810</t>
   </si>
   <si>
     <t>Sectors not specified</t>
   </si>
   <si>
+    <t>Unallocated / Unspecified</t>
+  </si>
+  <si>
     <t>998</t>
-  </si>
-  <si>
-    <t>Unallocated / Unspecified</t>
   </si>
   <si>
     <t>99820</t>
@@ -2166,16 +2166,16 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
         <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2189,16 +2189,16 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G7" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2212,16 +2212,16 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E8" t="s">
         <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G8" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2235,16 +2235,16 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G9" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2258,16 +2258,16 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E10" t="s">
         <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G10" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2281,16 +2281,16 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
         <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G11" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2304,16 +2304,16 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E12" t="s">
         <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G12" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2327,16 +2327,16 @@
         <v>9</v>
       </c>
       <c r="D13" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E13" t="s">
         <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G13" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2442,16 +2442,16 @@
         <v>9</v>
       </c>
       <c r="D18" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E18" t="s">
         <v>45</v>
       </c>
       <c r="F18" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G18" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2465,16 +2465,16 @@
         <v>9</v>
       </c>
       <c r="D19" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E19" t="s">
         <v>45</v>
       </c>
       <c r="F19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G19" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2488,16 +2488,16 @@
         <v>9</v>
       </c>
       <c r="D20" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E20" t="s">
         <v>45</v>
       </c>
       <c r="F20" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G20" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2511,16 +2511,16 @@
         <v>9</v>
       </c>
       <c r="D21" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E21" t="s">
         <v>45</v>
       </c>
       <c r="F21" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G21" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2534,16 +2534,16 @@
         <v>9</v>
       </c>
       <c r="D22" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E22" t="s">
         <v>45</v>
       </c>
       <c r="F22" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G22" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2557,16 +2557,16 @@
         <v>9</v>
       </c>
       <c r="D23" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E23" t="s">
         <v>45</v>
       </c>
       <c r="F23" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G23" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2580,16 +2580,16 @@
         <v>9</v>
       </c>
       <c r="D24" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E24" t="s">
         <v>45</v>
       </c>
       <c r="F24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G24" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2603,16 +2603,16 @@
         <v>9</v>
       </c>
       <c r="D25" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E25" t="s">
         <v>45</v>
       </c>
       <c r="F25" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G25" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2626,16 +2626,16 @@
         <v>9</v>
       </c>
       <c r="D26" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E26" t="s">
         <v>45</v>
       </c>
       <c r="F26" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G26" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2649,16 +2649,16 @@
         <v>9</v>
       </c>
       <c r="D27" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E27" t="s">
         <v>45</v>
       </c>
       <c r="F27" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G27" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2672,16 +2672,16 @@
         <v>9</v>
       </c>
       <c r="D28" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E28" t="s">
         <v>45</v>
       </c>
       <c r="F28" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G28" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2695,16 +2695,16 @@
         <v>9</v>
       </c>
       <c r="D29" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E29" t="s">
         <v>45</v>
       </c>
       <c r="F29" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G29" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2718,16 +2718,16 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E30" t="s">
         <v>45</v>
       </c>
       <c r="F30" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G30" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2741,16 +2741,16 @@
         <v>9</v>
       </c>
       <c r="D31" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E31" t="s">
         <v>45</v>
       </c>
       <c r="F31" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G31" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2770,10 +2770,10 @@
         <v>89</v>
       </c>
       <c r="F32" t="s">
+        <v>89</v>
+      </c>
+      <c r="G32" t="s">
         <v>88</v>
-      </c>
-      <c r="G32" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2793,10 +2793,10 @@
         <v>89</v>
       </c>
       <c r="F33" t="s">
+        <v>89</v>
+      </c>
+      <c r="G33" t="s">
         <v>88</v>
-      </c>
-      <c r="G33" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2816,10 +2816,10 @@
         <v>89</v>
       </c>
       <c r="F34" t="s">
+        <v>89</v>
+      </c>
+      <c r="G34" t="s">
         <v>88</v>
-      </c>
-      <c r="G34" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2839,10 +2839,10 @@
         <v>89</v>
       </c>
       <c r="F35" t="s">
+        <v>89</v>
+      </c>
+      <c r="G35" t="s">
         <v>88</v>
-      </c>
-      <c r="G35" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2862,10 +2862,10 @@
         <v>89</v>
       </c>
       <c r="F36" t="s">
+        <v>89</v>
+      </c>
+      <c r="G36" t="s">
         <v>88</v>
-      </c>
-      <c r="G36" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2885,10 +2885,10 @@
         <v>101</v>
       </c>
       <c r="F37" t="s">
+        <v>101</v>
+      </c>
+      <c r="G37" t="s">
         <v>100</v>
-      </c>
-      <c r="G37" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2908,10 +2908,10 @@
         <v>101</v>
       </c>
       <c r="F38" t="s">
+        <v>101</v>
+      </c>
+      <c r="G38" t="s">
         <v>100</v>
-      </c>
-      <c r="G38" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2931,10 +2931,10 @@
         <v>101</v>
       </c>
       <c r="F39" t="s">
+        <v>101</v>
+      </c>
+      <c r="G39" t="s">
         <v>100</v>
-      </c>
-      <c r="G39" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2954,10 +2954,10 @@
         <v>101</v>
       </c>
       <c r="F40" t="s">
+        <v>101</v>
+      </c>
+      <c r="G40" t="s">
         <v>100</v>
-      </c>
-      <c r="G40" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2977,10 +2977,10 @@
         <v>101</v>
       </c>
       <c r="F41" t="s">
+        <v>101</v>
+      </c>
+      <c r="G41" t="s">
         <v>100</v>
-      </c>
-      <c r="G41" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -3000,10 +3000,10 @@
         <v>101</v>
       </c>
       <c r="F42" t="s">
+        <v>101</v>
+      </c>
+      <c r="G42" t="s">
         <v>100</v>
-      </c>
-      <c r="G42" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3023,10 +3023,10 @@
         <v>101</v>
       </c>
       <c r="F43" t="s">
+        <v>101</v>
+      </c>
+      <c r="G43" t="s">
         <v>100</v>
-      </c>
-      <c r="G43" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3046,10 +3046,10 @@
         <v>101</v>
       </c>
       <c r="F44" t="s">
+        <v>101</v>
+      </c>
+      <c r="G44" t="s">
         <v>100</v>
-      </c>
-      <c r="G44" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3069,10 +3069,10 @@
         <v>101</v>
       </c>
       <c r="F45" t="s">
+        <v>101</v>
+      </c>
+      <c r="G45" t="s">
         <v>100</v>
-      </c>
-      <c r="G45" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3092,10 +3092,10 @@
         <v>101</v>
       </c>
       <c r="F46" t="s">
+        <v>101</v>
+      </c>
+      <c r="G46" t="s">
         <v>100</v>
-      </c>
-      <c r="G46" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3115,10 +3115,10 @@
         <v>101</v>
       </c>
       <c r="F47" t="s">
+        <v>101</v>
+      </c>
+      <c r="G47" t="s">
         <v>100</v>
-      </c>
-      <c r="G47" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3500,16 +3500,16 @@
         <v>9</v>
       </c>
       <c r="D64" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E64" t="s">
         <v>125</v>
       </c>
       <c r="F64" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G64" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3523,16 +3523,16 @@
         <v>9</v>
       </c>
       <c r="D65" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E65" t="s">
         <v>125</v>
       </c>
       <c r="F65" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G65" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3546,16 +3546,16 @@
         <v>9</v>
       </c>
       <c r="D66" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E66" t="s">
         <v>125</v>
       </c>
       <c r="F66" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G66" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3569,16 +3569,16 @@
         <v>9</v>
       </c>
       <c r="D67" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E67" t="s">
         <v>125</v>
       </c>
       <c r="F67" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G67" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3592,16 +3592,16 @@
         <v>9</v>
       </c>
       <c r="D68" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E68" t="s">
         <v>125</v>
       </c>
       <c r="F68" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G68" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3615,16 +3615,16 @@
         <v>9</v>
       </c>
       <c r="D69" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E69" t="s">
         <v>125</v>
       </c>
       <c r="F69" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G69" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3644,10 +3644,10 @@
         <v>175</v>
       </c>
       <c r="F70" t="s">
+        <v>175</v>
+      </c>
+      <c r="G70" t="s">
         <v>174</v>
-      </c>
-      <c r="G70" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3667,10 +3667,10 @@
         <v>175</v>
       </c>
       <c r="F71" t="s">
+        <v>175</v>
+      </c>
+      <c r="G71" t="s">
         <v>174</v>
-      </c>
-      <c r="G71" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3690,10 +3690,10 @@
         <v>175</v>
       </c>
       <c r="F72" t="s">
+        <v>175</v>
+      </c>
+      <c r="G72" t="s">
         <v>174</v>
-      </c>
-      <c r="G72" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3713,10 +3713,10 @@
         <v>175</v>
       </c>
       <c r="F73" t="s">
+        <v>175</v>
+      </c>
+      <c r="G73" t="s">
         <v>174</v>
-      </c>
-      <c r="G73" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3736,10 +3736,10 @@
         <v>175</v>
       </c>
       <c r="F74" t="s">
+        <v>175</v>
+      </c>
+      <c r="G74" t="s">
         <v>174</v>
-      </c>
-      <c r="G74" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3759,10 +3759,10 @@
         <v>175</v>
       </c>
       <c r="F75" t="s">
+        <v>175</v>
+      </c>
+      <c r="G75" t="s">
         <v>174</v>
-      </c>
-      <c r="G75" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3782,10 +3782,10 @@
         <v>175</v>
       </c>
       <c r="F76" t="s">
+        <v>175</v>
+      </c>
+      <c r="G76" t="s">
         <v>174</v>
-      </c>
-      <c r="G76" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3805,10 +3805,10 @@
         <v>175</v>
       </c>
       <c r="F77" t="s">
+        <v>175</v>
+      </c>
+      <c r="G77" t="s">
         <v>174</v>
-      </c>
-      <c r="G77" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3828,10 +3828,10 @@
         <v>175</v>
       </c>
       <c r="F78" t="s">
+        <v>175</v>
+      </c>
+      <c r="G78" t="s">
         <v>174</v>
-      </c>
-      <c r="G78" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3851,10 +3851,10 @@
         <v>175</v>
       </c>
       <c r="F79" t="s">
+        <v>175</v>
+      </c>
+      <c r="G79" t="s">
         <v>174</v>
-      </c>
-      <c r="G79" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3874,10 +3874,10 @@
         <v>175</v>
       </c>
       <c r="F80" t="s">
+        <v>175</v>
+      </c>
+      <c r="G80" t="s">
         <v>174</v>
-      </c>
-      <c r="G80" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3897,10 +3897,10 @@
         <v>199</v>
       </c>
       <c r="F81" t="s">
+        <v>199</v>
+      </c>
+      <c r="G81" t="s">
         <v>198</v>
-      </c>
-      <c r="G81" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3920,10 +3920,10 @@
         <v>199</v>
       </c>
       <c r="F82" t="s">
+        <v>199</v>
+      </c>
+      <c r="G82" t="s">
         <v>198</v>
-      </c>
-      <c r="G82" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3943,10 +3943,10 @@
         <v>199</v>
       </c>
       <c r="F83" t="s">
+        <v>199</v>
+      </c>
+      <c r="G83" t="s">
         <v>198</v>
-      </c>
-      <c r="G83" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3966,10 +3966,10 @@
         <v>199</v>
       </c>
       <c r="F84" t="s">
+        <v>199</v>
+      </c>
+      <c r="G84" t="s">
         <v>198</v>
-      </c>
-      <c r="G84" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3989,10 +3989,10 @@
         <v>199</v>
       </c>
       <c r="F85" t="s">
+        <v>199</v>
+      </c>
+      <c r="G85" t="s">
         <v>198</v>
-      </c>
-      <c r="G85" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4012,10 +4012,10 @@
         <v>199</v>
       </c>
       <c r="F86" t="s">
+        <v>199</v>
+      </c>
+      <c r="G86" t="s">
         <v>198</v>
-      </c>
-      <c r="G86" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4035,10 +4035,10 @@
         <v>199</v>
       </c>
       <c r="F87" t="s">
+        <v>199</v>
+      </c>
+      <c r="G87" t="s">
         <v>198</v>
-      </c>
-      <c r="G87" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4058,10 +4058,10 @@
         <v>215</v>
       </c>
       <c r="F88" t="s">
+        <v>215</v>
+      </c>
+      <c r="G88" t="s">
         <v>214</v>
-      </c>
-      <c r="G88" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4081,10 +4081,10 @@
         <v>215</v>
       </c>
       <c r="F89" t="s">
+        <v>215</v>
+      </c>
+      <c r="G89" t="s">
         <v>214</v>
-      </c>
-      <c r="G89" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4104,10 +4104,10 @@
         <v>215</v>
       </c>
       <c r="F90" t="s">
+        <v>215</v>
+      </c>
+      <c r="G90" t="s">
         <v>214</v>
-      </c>
-      <c r="G90" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4127,10 +4127,10 @@
         <v>215</v>
       </c>
       <c r="F91" t="s">
+        <v>215</v>
+      </c>
+      <c r="G91" t="s">
         <v>214</v>
-      </c>
-      <c r="G91" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4236,16 +4236,16 @@
         <v>9</v>
       </c>
       <c r="D96" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E96" t="s">
         <v>225</v>
       </c>
       <c r="F96" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G96" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -4259,16 +4259,16 @@
         <v>9</v>
       </c>
       <c r="D97" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E97" t="s">
         <v>225</v>
       </c>
       <c r="F97" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G97" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4282,16 +4282,16 @@
         <v>9</v>
       </c>
       <c r="D98" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E98" t="s">
         <v>225</v>
       </c>
       <c r="F98" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G98" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4305,16 +4305,16 @@
         <v>9</v>
       </c>
       <c r="D99" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E99" t="s">
         <v>225</v>
       </c>
       <c r="F99" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G99" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4328,16 +4328,16 @@
         <v>9</v>
       </c>
       <c r="D100" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E100" t="s">
         <v>225</v>
       </c>
       <c r="F100" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G100" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4351,16 +4351,16 @@
         <v>9</v>
       </c>
       <c r="D101" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E101" t="s">
         <v>225</v>
       </c>
       <c r="F101" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G101" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4374,16 +4374,16 @@
         <v>9</v>
       </c>
       <c r="D102" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E102" t="s">
         <v>225</v>
       </c>
       <c r="F102" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G102" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4397,16 +4397,16 @@
         <v>9</v>
       </c>
       <c r="D103" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E103" t="s">
         <v>225</v>
       </c>
       <c r="F103" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G103" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4420,16 +4420,16 @@
         <v>9</v>
       </c>
       <c r="D104" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E104" t="s">
         <v>225</v>
       </c>
       <c r="F104" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G104" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4443,16 +4443,16 @@
         <v>9</v>
       </c>
       <c r="D105" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E105" t="s">
         <v>225</v>
       </c>
       <c r="F105" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G105" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4466,16 +4466,16 @@
         <v>9</v>
       </c>
       <c r="D106" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E106" t="s">
         <v>225</v>
       </c>
       <c r="F106" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G106" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4489,16 +4489,16 @@
         <v>9</v>
       </c>
       <c r="D107" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E107" t="s">
         <v>225</v>
       </c>
       <c r="F107" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G107" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4512,16 +4512,16 @@
         <v>9</v>
       </c>
       <c r="D108" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E108" t="s">
         <v>225</v>
       </c>
       <c r="F108" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G108" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4535,16 +4535,16 @@
         <v>9</v>
       </c>
       <c r="D109" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E109" t="s">
         <v>225</v>
       </c>
       <c r="F109" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G109" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4558,16 +4558,16 @@
         <v>9</v>
       </c>
       <c r="D110" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E110" t="s">
         <v>225</v>
       </c>
       <c r="F110" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G110" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4581,16 +4581,16 @@
         <v>9</v>
       </c>
       <c r="D111" t="s">
-        <v>224</v>
+        <v>270</v>
       </c>
       <c r="E111" t="s">
         <v>225</v>
       </c>
       <c r="F111" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="G111" t="s">
-        <v>271</v>
+        <v>227</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4604,16 +4604,16 @@
         <v>9</v>
       </c>
       <c r="D112" t="s">
-        <v>224</v>
+        <v>274</v>
       </c>
       <c r="E112" t="s">
         <v>225</v>
       </c>
       <c r="F112" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G112" t="s">
-        <v>275</v>
+        <v>227</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4627,16 +4627,16 @@
         <v>9</v>
       </c>
       <c r="D113" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E113" t="s">
         <v>225</v>
       </c>
       <c r="F113" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G113" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4650,16 +4650,16 @@
         <v>9</v>
       </c>
       <c r="D114" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E114" t="s">
         <v>225</v>
       </c>
       <c r="F114" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G114" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4673,16 +4673,16 @@
         <v>9</v>
       </c>
       <c r="D115" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E115" t="s">
         <v>225</v>
       </c>
       <c r="F115" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G115" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4696,16 +4696,16 @@
         <v>9</v>
       </c>
       <c r="D116" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E116" t="s">
         <v>225</v>
       </c>
       <c r="F116" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G116" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4719,16 +4719,16 @@
         <v>9</v>
       </c>
       <c r="D117" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E117" t="s">
         <v>225</v>
       </c>
       <c r="F117" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G117" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4742,16 +4742,16 @@
         <v>9</v>
       </c>
       <c r="D118" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E118" t="s">
         <v>225</v>
       </c>
       <c r="F118" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G118" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4765,16 +4765,16 @@
         <v>9</v>
       </c>
       <c r="D119" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E119" t="s">
         <v>225</v>
       </c>
       <c r="F119" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G119" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4794,10 +4794,10 @@
         <v>295</v>
       </c>
       <c r="F120" t="s">
+        <v>295</v>
+      </c>
+      <c r="G120" t="s">
         <v>294</v>
-      </c>
-      <c r="G120" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4817,10 +4817,10 @@
         <v>295</v>
       </c>
       <c r="F121" t="s">
+        <v>295</v>
+      </c>
+      <c r="G121" t="s">
         <v>294</v>
-      </c>
-      <c r="G121" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4840,10 +4840,10 @@
         <v>295</v>
       </c>
       <c r="F122" t="s">
+        <v>295</v>
+      </c>
+      <c r="G122" t="s">
         <v>294</v>
-      </c>
-      <c r="G122" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4863,10 +4863,10 @@
         <v>295</v>
       </c>
       <c r="F123" t="s">
+        <v>295</v>
+      </c>
+      <c r="G123" t="s">
         <v>294</v>
-      </c>
-      <c r="G123" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4886,10 +4886,10 @@
         <v>295</v>
       </c>
       <c r="F124" t="s">
+        <v>295</v>
+      </c>
+      <c r="G124" t="s">
         <v>294</v>
-      </c>
-      <c r="G124" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4909,10 +4909,10 @@
         <v>295</v>
       </c>
       <c r="F125" t="s">
+        <v>295</v>
+      </c>
+      <c r="G125" t="s">
         <v>294</v>
-      </c>
-      <c r="G125" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4932,10 +4932,10 @@
         <v>309</v>
       </c>
       <c r="F126" t="s">
+        <v>309</v>
+      </c>
+      <c r="G126" t="s">
         <v>308</v>
-      </c>
-      <c r="G126" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4955,10 +4955,10 @@
         <v>309</v>
       </c>
       <c r="F127" t="s">
+        <v>309</v>
+      </c>
+      <c r="G127" t="s">
         <v>308</v>
-      </c>
-      <c r="G127" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4978,10 +4978,10 @@
         <v>309</v>
       </c>
       <c r="F128" t="s">
+        <v>309</v>
+      </c>
+      <c r="G128" t="s">
         <v>308</v>
-      </c>
-      <c r="G128" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -5001,10 +5001,10 @@
         <v>309</v>
       </c>
       <c r="F129" t="s">
+        <v>309</v>
+      </c>
+      <c r="G129" t="s">
         <v>308</v>
-      </c>
-      <c r="G129" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -5432,16 +5432,16 @@
         <v>9</v>
       </c>
       <c r="D148" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E148" t="s">
         <v>319</v>
       </c>
       <c r="F148" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="G148" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5455,16 +5455,16 @@
         <v>9</v>
       </c>
       <c r="D149" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E149" t="s">
         <v>319</v>
       </c>
       <c r="F149" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="G149" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5478,16 +5478,16 @@
         <v>9</v>
       </c>
       <c r="D150" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E150" t="s">
         <v>319</v>
       </c>
       <c r="F150" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="G150" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5501,16 +5501,16 @@
         <v>9</v>
       </c>
       <c r="D151" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E151" t="s">
         <v>319</v>
       </c>
       <c r="F151" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="G151" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5524,16 +5524,16 @@
         <v>9</v>
       </c>
       <c r="D152" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E152" t="s">
         <v>319</v>
       </c>
       <c r="F152" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="G152" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5547,16 +5547,16 @@
         <v>9</v>
       </c>
       <c r="D153" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E153" t="s">
         <v>319</v>
       </c>
       <c r="F153" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="G153" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5570,16 +5570,16 @@
         <v>9</v>
       </c>
       <c r="D154" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="E154" t="s">
         <v>319</v>
       </c>
       <c r="F154" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G154" t="s">
-        <v>373</v>
+        <v>321</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5593,16 +5593,16 @@
         <v>9</v>
       </c>
       <c r="D155" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="E155" t="s">
         <v>319</v>
       </c>
       <c r="F155" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G155" t="s">
-        <v>373</v>
+        <v>321</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5616,16 +5616,16 @@
         <v>9</v>
       </c>
       <c r="D156" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="E156" t="s">
         <v>319</v>
       </c>
       <c r="F156" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G156" t="s">
-        <v>373</v>
+        <v>321</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5639,16 +5639,16 @@
         <v>9</v>
       </c>
       <c r="D157" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="E157" t="s">
         <v>319</v>
       </c>
       <c r="F157" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G157" t="s">
-        <v>373</v>
+        <v>321</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5662,16 +5662,16 @@
         <v>9</v>
       </c>
       <c r="D158" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="E158" t="s">
         <v>319</v>
       </c>
       <c r="F158" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G158" t="s">
-        <v>373</v>
+        <v>321</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -6122,16 +6122,16 @@
         <v>9</v>
       </c>
       <c r="D178" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E178" t="s">
         <v>385</v>
       </c>
       <c r="F178" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="G178" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -6145,16 +6145,16 @@
         <v>9</v>
       </c>
       <c r="D179" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E179" t="s">
         <v>385</v>
       </c>
       <c r="F179" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="G179" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -6168,16 +6168,16 @@
         <v>9</v>
       </c>
       <c r="D180" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E180" t="s">
         <v>385</v>
       </c>
       <c r="F180" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="G180" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -6191,16 +6191,16 @@
         <v>9</v>
       </c>
       <c r="D181" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E181" t="s">
         <v>385</v>
       </c>
       <c r="F181" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="G181" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -6214,16 +6214,16 @@
         <v>9</v>
       </c>
       <c r="D182" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E182" t="s">
         <v>385</v>
       </c>
       <c r="F182" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="G182" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -6237,16 +6237,16 @@
         <v>9</v>
       </c>
       <c r="D183" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E183" t="s">
         <v>385</v>
       </c>
       <c r="F183" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="G183" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -6260,16 +6260,16 @@
         <v>9</v>
       </c>
       <c r="D184" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E184" t="s">
         <v>385</v>
       </c>
       <c r="F184" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="G184" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -6283,16 +6283,16 @@
         <v>9</v>
       </c>
       <c r="D185" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E185" t="s">
         <v>385</v>
       </c>
       <c r="F185" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="G185" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -6306,16 +6306,16 @@
         <v>9</v>
       </c>
       <c r="D186" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E186" t="s">
         <v>385</v>
       </c>
       <c r="F186" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="G186" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -6329,16 +6329,16 @@
         <v>9</v>
       </c>
       <c r="D187" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E187" t="s">
         <v>385</v>
       </c>
       <c r="F187" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="G187" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -6352,16 +6352,16 @@
         <v>9</v>
       </c>
       <c r="D188" t="s">
-        <v>384</v>
+        <v>448</v>
       </c>
       <c r="E188" t="s">
         <v>385</v>
       </c>
       <c r="F188" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G188" t="s">
-        <v>449</v>
+        <v>387</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -6381,10 +6381,10 @@
         <v>453</v>
       </c>
       <c r="F189" t="s">
+        <v>453</v>
+      </c>
+      <c r="G189" t="s">
         <v>452</v>
-      </c>
-      <c r="G189" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6404,10 +6404,10 @@
         <v>453</v>
       </c>
       <c r="F190" t="s">
+        <v>453</v>
+      </c>
+      <c r="G190" t="s">
         <v>452</v>
-      </c>
-      <c r="G190" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6427,10 +6427,10 @@
         <v>453</v>
       </c>
       <c r="F191" t="s">
+        <v>453</v>
+      </c>
+      <c r="G191" t="s">
         <v>452</v>
-      </c>
-      <c r="G191" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6450,10 +6450,10 @@
         <v>453</v>
       </c>
       <c r="F192" t="s">
+        <v>453</v>
+      </c>
+      <c r="G192" t="s">
         <v>452</v>
-      </c>
-      <c r="G192" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6473,10 +6473,10 @@
         <v>453</v>
       </c>
       <c r="F193" t="s">
+        <v>453</v>
+      </c>
+      <c r="G193" t="s">
         <v>452</v>
-      </c>
-      <c r="G193" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6496,10 +6496,10 @@
         <v>453</v>
       </c>
       <c r="F194" t="s">
+        <v>453</v>
+      </c>
+      <c r="G194" t="s">
         <v>452</v>
-      </c>
-      <c r="G194" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6519,10 +6519,10 @@
         <v>467</v>
       </c>
       <c r="F195" t="s">
+        <v>467</v>
+      </c>
+      <c r="G195" t="s">
         <v>466</v>
-      </c>
-      <c r="G195" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6542,10 +6542,10 @@
         <v>471</v>
       </c>
       <c r="F196" t="s">
+        <v>471</v>
+      </c>
+      <c r="G196" t="s">
         <v>470</v>
-      </c>
-      <c r="G196" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6565,10 +6565,10 @@
         <v>471</v>
       </c>
       <c r="F197" t="s">
+        <v>471</v>
+      </c>
+      <c r="G197" t="s">
         <v>470</v>
-      </c>
-      <c r="G197" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6588,10 +6588,10 @@
         <v>471</v>
       </c>
       <c r="F198" t="s">
+        <v>471</v>
+      </c>
+      <c r="G198" t="s">
         <v>470</v>
-      </c>
-      <c r="G198" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6611,10 +6611,10 @@
         <v>471</v>
       </c>
       <c r="F199" t="s">
+        <v>471</v>
+      </c>
+      <c r="G199" t="s">
         <v>470</v>
-      </c>
-      <c r="G199" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6634,10 +6634,10 @@
         <v>471</v>
       </c>
       <c r="F200" t="s">
+        <v>471</v>
+      </c>
+      <c r="G200" t="s">
         <v>470</v>
-      </c>
-      <c r="G200" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6657,10 +6657,10 @@
         <v>471</v>
       </c>
       <c r="F201" t="s">
+        <v>471</v>
+      </c>
+      <c r="G201" t="s">
         <v>470</v>
-      </c>
-      <c r="G201" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6680,10 +6680,10 @@
         <v>485</v>
       </c>
       <c r="F202" t="s">
+        <v>485</v>
+      </c>
+      <c r="G202" t="s">
         <v>484</v>
-      </c>
-      <c r="G202" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6703,10 +6703,10 @@
         <v>485</v>
       </c>
       <c r="F203" t="s">
+        <v>485</v>
+      </c>
+      <c r="G203" t="s">
         <v>484</v>
-      </c>
-      <c r="G203" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6726,10 +6726,10 @@
         <v>485</v>
       </c>
       <c r="F204" t="s">
+        <v>485</v>
+      </c>
+      <c r="G204" t="s">
         <v>484</v>
-      </c>
-      <c r="G204" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6749,10 +6749,10 @@
         <v>485</v>
       </c>
       <c r="F205" t="s">
+        <v>485</v>
+      </c>
+      <c r="G205" t="s">
         <v>484</v>
-      </c>
-      <c r="G205" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6772,10 +6772,10 @@
         <v>485</v>
       </c>
       <c r="F206" t="s">
+        <v>485</v>
+      </c>
+      <c r="G206" t="s">
         <v>484</v>
-      </c>
-      <c r="G206" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6795,10 +6795,10 @@
         <v>485</v>
       </c>
       <c r="F207" t="s">
+        <v>485</v>
+      </c>
+      <c r="G207" t="s">
         <v>484</v>
-      </c>
-      <c r="G207" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6818,10 +6818,10 @@
         <v>485</v>
       </c>
       <c r="F208" t="s">
+        <v>485</v>
+      </c>
+      <c r="G208" t="s">
         <v>484</v>
-      </c>
-      <c r="G208" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6841,10 +6841,10 @@
         <v>485</v>
       </c>
       <c r="F209" t="s">
+        <v>485</v>
+      </c>
+      <c r="G209" t="s">
         <v>484</v>
-      </c>
-      <c r="G209" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6864,10 +6864,10 @@
         <v>485</v>
       </c>
       <c r="F210" t="s">
+        <v>485</v>
+      </c>
+      <c r="G210" t="s">
         <v>484</v>
-      </c>
-      <c r="G210" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6887,10 +6887,10 @@
         <v>485</v>
       </c>
       <c r="F211" t="s">
+        <v>485</v>
+      </c>
+      <c r="G211" t="s">
         <v>484</v>
-      </c>
-      <c r="G211" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6910,10 +6910,10 @@
         <v>507</v>
       </c>
       <c r="F212" t="s">
+        <v>507</v>
+      </c>
+      <c r="G212" t="s">
         <v>506</v>
-      </c>
-      <c r="G212" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6933,10 +6933,10 @@
         <v>511</v>
       </c>
       <c r="F213" t="s">
+        <v>511</v>
+      </c>
+      <c r="G213" t="s">
         <v>510</v>
-      </c>
-      <c r="G213" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6956,10 +6956,10 @@
         <v>515</v>
       </c>
       <c r="F214" t="s">
+        <v>515</v>
+      </c>
+      <c r="G214" t="s">
         <v>514</v>
-      </c>
-      <c r="G214" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6979,10 +6979,10 @@
         <v>515</v>
       </c>
       <c r="F215" t="s">
+        <v>515</v>
+      </c>
+      <c r="G215" t="s">
         <v>514</v>
-      </c>
-      <c r="G215" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -7002,10 +7002,10 @@
         <v>521</v>
       </c>
       <c r="F216" t="s">
+        <v>521</v>
+      </c>
+      <c r="G216" t="s">
         <v>520</v>
-      </c>
-      <c r="G216" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -7025,10 +7025,10 @@
         <v>521</v>
       </c>
       <c r="F217" t="s">
+        <v>521</v>
+      </c>
+      <c r="G217" t="s">
         <v>520</v>
-      </c>
-      <c r="G217" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -7048,10 +7048,10 @@
         <v>521</v>
       </c>
       <c r="F218" t="s">
+        <v>521</v>
+      </c>
+      <c r="G218" t="s">
         <v>520</v>
-      </c>
-      <c r="G218" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -7071,10 +7071,10 @@
         <v>521</v>
       </c>
       <c r="F219" t="s">
+        <v>521</v>
+      </c>
+      <c r="G219" t="s">
         <v>520</v>
-      </c>
-      <c r="G219" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -7094,10 +7094,10 @@
         <v>521</v>
       </c>
       <c r="F220" t="s">
+        <v>521</v>
+      </c>
+      <c r="G220" t="s">
         <v>520</v>
-      </c>
-      <c r="G220" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -7117,10 +7117,10 @@
         <v>521</v>
       </c>
       <c r="F221" t="s">
+        <v>521</v>
+      </c>
+      <c r="G221" t="s">
         <v>520</v>
-      </c>
-      <c r="G221" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -7140,10 +7140,10 @@
         <v>521</v>
       </c>
       <c r="F222" t="s">
+        <v>521</v>
+      </c>
+      <c r="G222" t="s">
         <v>520</v>
-      </c>
-      <c r="G222" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -7163,10 +7163,10 @@
         <v>537</v>
       </c>
       <c r="F223" t="s">
+        <v>537</v>
+      </c>
+      <c r="G223" t="s">
         <v>536</v>
-      </c>
-      <c r="G223" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -7186,10 +7186,10 @@
         <v>537</v>
       </c>
       <c r="F224" t="s">
+        <v>537</v>
+      </c>
+      <c r="G224" t="s">
         <v>536</v>
-      </c>
-      <c r="G224" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -7209,10 +7209,10 @@
         <v>537</v>
       </c>
       <c r="F225" t="s">
+        <v>537</v>
+      </c>
+      <c r="G225" t="s">
         <v>536</v>
-      </c>
-      <c r="G225" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -7232,10 +7232,10 @@
         <v>545</v>
       </c>
       <c r="F226" t="s">
+        <v>545</v>
+      </c>
+      <c r="G226" t="s">
         <v>544</v>
-      </c>
-      <c r="G226" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -7255,10 +7255,10 @@
         <v>549</v>
       </c>
       <c r="F227" t="s">
+        <v>549</v>
+      </c>
+      <c r="G227" t="s">
         <v>548</v>
-      </c>
-      <c r="G227" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -7278,10 +7278,10 @@
         <v>553</v>
       </c>
       <c r="F228" t="s">
+        <v>553</v>
+      </c>
+      <c r="G228" t="s">
         <v>552</v>
-      </c>
-      <c r="G228" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -7301,10 +7301,10 @@
         <v>557</v>
       </c>
       <c r="F229" t="s">
+        <v>557</v>
+      </c>
+      <c r="G229" t="s">
         <v>556</v>
-      </c>
-      <c r="G229" t="s">
-        <v>557</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -7324,10 +7324,10 @@
         <v>561</v>
       </c>
       <c r="F230" t="s">
+        <v>561</v>
+      </c>
+      <c r="G230" t="s">
         <v>560</v>
-      </c>
-      <c r="G230" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -7347,10 +7347,10 @@
         <v>561</v>
       </c>
       <c r="F231" t="s">
+        <v>561</v>
+      </c>
+      <c r="G231" t="s">
         <v>560</v>
-      </c>
-      <c r="G231" t="s">
-        <v>561</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/en/SectorGroup.xlsx
+++ b/api/xlsx/en/SectorGroup.xlsx
@@ -25,12 +25,12 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
     <t>codeforiati:category-name</t>
   </si>
   <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
@@ -46,12 +46,12 @@
     <t>active</t>
   </si>
   <si>
+    <t>110</t>
+  </si>
+  <si>
     <t>Education, Level Unspecified</t>
   </si>
   <si>
-    <t>110</t>
-  </si>
-  <si>
     <t>111</t>
   </si>
   <si>
@@ -148,12 +148,12 @@
     <t>Health policy and administrative management</t>
   </si>
   <si>
+    <t>120</t>
+  </si>
+  <si>
     <t>Health, General</t>
   </si>
   <si>
-    <t>120</t>
-  </si>
-  <si>
     <t>121</t>
   </si>
   <si>
@@ -280,12 +280,12 @@
     <t>Population policy and administrative management</t>
   </si>
   <si>
+    <t>130</t>
+  </si>
+  <si>
     <t>Population Policies/Programmes &amp; Reproductive Health</t>
   </si>
   <si>
-    <t>130</t>
-  </si>
-  <si>
     <t>13020</t>
   </si>
   <si>
@@ -316,12 +316,12 @@
     <t>Water sector policy and administrative management</t>
   </si>
   <si>
+    <t>140</t>
+  </si>
+  <si>
     <t>Water Supply &amp; Sanitation</t>
   </si>
   <si>
-    <t>140</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -388,12 +388,12 @@
     <t>Public sector policy and administrative management</t>
   </si>
   <si>
+    <t>150</t>
+  </si>
+  <si>
     <t>Government &amp; Civil Society-general</t>
   </si>
   <si>
-    <t>150</t>
-  </si>
-  <si>
     <t>151</t>
   </si>
   <si>
@@ -538,12 +538,12 @@
     <t>Social Protection</t>
   </si>
   <si>
+    <t>160</t>
+  </si>
+  <si>
     <t>Other Social Infrastructure &amp; Services</t>
   </si>
   <si>
-    <t>160</t>
-  </si>
-  <si>
     <t>16020</t>
   </si>
   <si>
@@ -610,12 +610,12 @@
     <t>Transport policy and administrative management</t>
   </si>
   <si>
+    <t>210</t>
+  </si>
+  <si>
     <t>Transport &amp; Storage</t>
   </si>
   <si>
-    <t>210</t>
-  </si>
-  <si>
     <t>21020</t>
   </si>
   <si>
@@ -658,12 +658,12 @@
     <t>Communications policy and administrative management</t>
   </si>
   <si>
+    <t>220</t>
+  </si>
+  <si>
     <t>Communications</t>
   </si>
   <si>
-    <t>220</t>
-  </si>
-  <si>
     <t>22020</t>
   </si>
   <si>
@@ -688,12 +688,12 @@
     <t>Energy policy and administrative management</t>
   </si>
   <si>
+    <t>230</t>
+  </si>
+  <si>
     <t>Energy Policy</t>
   </si>
   <si>
-    <t>230</t>
-  </si>
-  <si>
     <t>231</t>
   </si>
   <si>
@@ -898,12 +898,12 @@
     <t>Financial policy and administrative management</t>
   </si>
   <si>
+    <t>240</t>
+  </si>
+  <si>
     <t>Banking &amp; Financial Services</t>
   </si>
   <si>
-    <t>240</t>
-  </si>
-  <si>
     <t>24020</t>
   </si>
   <si>
@@ -940,12 +940,12 @@
     <t>Business policy and administration</t>
   </si>
   <si>
+    <t>250</t>
+  </si>
+  <si>
     <t>Business &amp; Other Services</t>
   </si>
   <si>
-    <t>250</t>
-  </si>
-  <si>
     <t>25020</t>
   </si>
   <si>
@@ -970,12 +970,12 @@
     <t>Agricultural policy and administrative management</t>
   </si>
   <si>
+    <t>310</t>
+  </si>
+  <si>
     <t>Agriculture</t>
   </si>
   <si>
-    <t>310</t>
-  </si>
-  <si>
     <t>311</t>
   </si>
   <si>
@@ -1168,12 +1168,12 @@
     <t>Industrial policy and administrative management</t>
   </si>
   <si>
+    <t>320</t>
+  </si>
+  <si>
     <t>Industry</t>
   </si>
   <si>
-    <t>320</t>
-  </si>
-  <si>
     <t>321</t>
   </si>
   <si>
@@ -1372,12 +1372,12 @@
     <t>Trade policy and administrative management</t>
   </si>
   <si>
+    <t>331</t>
+  </si>
+  <si>
     <t>Trade Policies &amp; Regulations</t>
   </si>
   <si>
-    <t>331</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1414,24 +1414,24 @@
     <t>Tourism policy and administrative management</t>
   </si>
   <si>
+    <t>332</t>
+  </si>
+  <si>
     <t>Tourism</t>
   </si>
   <si>
-    <t>332</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
     <t>Environmental policy and administrative management</t>
   </si>
   <si>
+    <t>410</t>
+  </si>
+  <si>
     <t>General Environment Protection</t>
   </si>
   <si>
-    <t>410</t>
-  </si>
-  <si>
     <t>41020</t>
   </si>
   <si>
@@ -1468,12 +1468,12 @@
     <t>Multisector aid</t>
   </si>
   <si>
+    <t>430</t>
+  </si>
+  <si>
     <t>Other Multisector</t>
   </si>
   <si>
-    <t>430</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -1534,36 +1534,36 @@
     <t>General budget support-related aid</t>
   </si>
   <si>
+    <t>510</t>
+  </si>
+  <si>
     <t>General Budget Support</t>
   </si>
   <si>
-    <t>510</t>
-  </si>
-  <si>
     <t>52010</t>
   </si>
   <si>
     <t>Food assistance</t>
   </si>
   <si>
+    <t>520</t>
+  </si>
+  <si>
     <t>Development Food Assistance</t>
   </si>
   <si>
-    <t>520</t>
-  </si>
-  <si>
     <t>53030</t>
   </si>
   <si>
     <t>Import support (capital goods)</t>
   </si>
   <si>
+    <t>530</t>
+  </si>
+  <si>
     <t>Other Commodity Assistance</t>
   </si>
   <si>
-    <t>530</t>
-  </si>
-  <si>
     <t>53040</t>
   </si>
   <si>
@@ -1576,12 +1576,12 @@
     <t>Action relating to debt</t>
   </si>
   <si>
+    <t>600</t>
+  </si>
+  <si>
     <t>Action Relating to Debt</t>
   </si>
   <si>
-    <t>600</t>
-  </si>
-  <si>
     <t>60020</t>
   </si>
   <si>
@@ -1624,12 +1624,12 @@
     <t>Material relief assistance and services</t>
   </si>
   <si>
+    <t>720</t>
+  </si>
+  <si>
     <t>Emergency Response</t>
   </si>
   <si>
-    <t>720</t>
-  </si>
-  <si>
     <t>72040</t>
   </si>
   <si>
@@ -1648,58 +1648,58 @@
     <t>Immediate post-emergency reconstruction and rehabilitation</t>
   </si>
   <si>
+    <t>730</t>
+  </si>
+  <si>
     <t>Reconstruction Relief &amp; Rehabilitation</t>
   </si>
   <si>
-    <t>730</t>
-  </si>
-  <si>
     <t>74020</t>
   </si>
   <si>
     <t>Multi-hazard response preparedness</t>
   </si>
   <si>
+    <t>740</t>
+  </si>
+  <si>
     <t>Disaster Prevention &amp; Preparedness</t>
   </si>
   <si>
-    <t>740</t>
-  </si>
-  <si>
     <t>91010</t>
   </si>
   <si>
     <t>Administrative costs (non-sector allocable)</t>
   </si>
   <si>
+    <t>910</t>
+  </si>
+  <si>
     <t>Administrative Costs of Donors</t>
   </si>
   <si>
-    <t>910</t>
-  </si>
-  <si>
     <t>93010</t>
   </si>
   <si>
     <t>Refugees/asylum seekers in donor countries (non-sector allocable)</t>
   </si>
   <si>
+    <t>930</t>
+  </si>
+  <si>
     <t>Refugees in Donor Countries</t>
   </si>
   <si>
-    <t>930</t>
-  </si>
-  <si>
     <t>99810</t>
   </si>
   <si>
     <t>Sectors not specified</t>
   </si>
   <si>
+    <t>998</t>
+  </si>
+  <si>
     <t>Unallocated / Unspecified</t>
-  </si>
-  <si>
-    <t>998</t>
   </si>
   <si>
     <t>99820</t>
@@ -2166,10 +2166,10 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
         <v>22</v>
-      </c>
-      <c r="E6" t="s">
-        <v>11</v>
       </c>
       <c r="F6" t="s">
         <v>23</v>
@@ -2189,10 +2189,10 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" t="s">
         <v>22</v>
-      </c>
-      <c r="E7" t="s">
-        <v>11</v>
       </c>
       <c r="F7" t="s">
         <v>23</v>
@@ -2212,10 +2212,10 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" t="s">
         <v>22</v>
-      </c>
-      <c r="E8" t="s">
-        <v>11</v>
       </c>
       <c r="F8" t="s">
         <v>23</v>
@@ -2235,10 +2235,10 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" t="s">
         <v>22</v>
-      </c>
-      <c r="E9" t="s">
-        <v>11</v>
       </c>
       <c r="F9" t="s">
         <v>23</v>
@@ -2258,10 +2258,10 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" t="s">
         <v>32</v>
-      </c>
-      <c r="E10" t="s">
-        <v>11</v>
       </c>
       <c r="F10" t="s">
         <v>33</v>
@@ -2281,10 +2281,10 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" t="s">
         <v>32</v>
-      </c>
-      <c r="E11" t="s">
-        <v>11</v>
       </c>
       <c r="F11" t="s">
         <v>33</v>
@@ -2304,10 +2304,10 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" t="s">
         <v>38</v>
-      </c>
-      <c r="E12" t="s">
-        <v>11</v>
       </c>
       <c r="F12" t="s">
         <v>39</v>
@@ -2327,10 +2327,10 @@
         <v>9</v>
       </c>
       <c r="D13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" t="s">
         <v>38</v>
-      </c>
-      <c r="E13" t="s">
-        <v>11</v>
       </c>
       <c r="F13" t="s">
         <v>39</v>
@@ -2442,10 +2442,10 @@
         <v>9</v>
       </c>
       <c r="D18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18" t="s">
         <v>56</v>
-      </c>
-      <c r="E18" t="s">
-        <v>45</v>
       </c>
       <c r="F18" t="s">
         <v>57</v>
@@ -2465,10 +2465,10 @@
         <v>9</v>
       </c>
       <c r="D19" t="s">
+        <v>44</v>
+      </c>
+      <c r="E19" t="s">
         <v>56</v>
-      </c>
-      <c r="E19" t="s">
-        <v>45</v>
       </c>
       <c r="F19" t="s">
         <v>57</v>
@@ -2488,10 +2488,10 @@
         <v>9</v>
       </c>
       <c r="D20" t="s">
+        <v>44</v>
+      </c>
+      <c r="E20" t="s">
         <v>56</v>
-      </c>
-      <c r="E20" t="s">
-        <v>45</v>
       </c>
       <c r="F20" t="s">
         <v>57</v>
@@ -2511,10 +2511,10 @@
         <v>9</v>
       </c>
       <c r="D21" t="s">
+        <v>44</v>
+      </c>
+      <c r="E21" t="s">
         <v>56</v>
-      </c>
-      <c r="E21" t="s">
-        <v>45</v>
       </c>
       <c r="F21" t="s">
         <v>57</v>
@@ -2534,10 +2534,10 @@
         <v>9</v>
       </c>
       <c r="D22" t="s">
+        <v>44</v>
+      </c>
+      <c r="E22" t="s">
         <v>56</v>
-      </c>
-      <c r="E22" t="s">
-        <v>45</v>
       </c>
       <c r="F22" t="s">
         <v>57</v>
@@ -2557,10 +2557,10 @@
         <v>9</v>
       </c>
       <c r="D23" t="s">
+        <v>44</v>
+      </c>
+      <c r="E23" t="s">
         <v>56</v>
-      </c>
-      <c r="E23" t="s">
-        <v>45</v>
       </c>
       <c r="F23" t="s">
         <v>57</v>
@@ -2580,10 +2580,10 @@
         <v>9</v>
       </c>
       <c r="D24" t="s">
+        <v>44</v>
+      </c>
+      <c r="E24" t="s">
         <v>56</v>
-      </c>
-      <c r="E24" t="s">
-        <v>45</v>
       </c>
       <c r="F24" t="s">
         <v>57</v>
@@ -2603,10 +2603,10 @@
         <v>9</v>
       </c>
       <c r="D25" t="s">
+        <v>44</v>
+      </c>
+      <c r="E25" t="s">
         <v>56</v>
-      </c>
-      <c r="E25" t="s">
-        <v>45</v>
       </c>
       <c r="F25" t="s">
         <v>57</v>
@@ -2626,10 +2626,10 @@
         <v>9</v>
       </c>
       <c r="D26" t="s">
+        <v>44</v>
+      </c>
+      <c r="E26" t="s">
         <v>74</v>
-      </c>
-      <c r="E26" t="s">
-        <v>45</v>
       </c>
       <c r="F26" t="s">
         <v>75</v>
@@ -2649,10 +2649,10 @@
         <v>9</v>
       </c>
       <c r="D27" t="s">
+        <v>44</v>
+      </c>
+      <c r="E27" t="s">
         <v>74</v>
-      </c>
-      <c r="E27" t="s">
-        <v>45</v>
       </c>
       <c r="F27" t="s">
         <v>75</v>
@@ -2672,10 +2672,10 @@
         <v>9</v>
       </c>
       <c r="D28" t="s">
+        <v>44</v>
+      </c>
+      <c r="E28" t="s">
         <v>74</v>
-      </c>
-      <c r="E28" t="s">
-        <v>45</v>
       </c>
       <c r="F28" t="s">
         <v>75</v>
@@ -2695,10 +2695,10 @@
         <v>9</v>
       </c>
       <c r="D29" t="s">
+        <v>44</v>
+      </c>
+      <c r="E29" t="s">
         <v>74</v>
-      </c>
-      <c r="E29" t="s">
-        <v>45</v>
       </c>
       <c r="F29" t="s">
         <v>75</v>
@@ -2718,10 +2718,10 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
+        <v>44</v>
+      </c>
+      <c r="E30" t="s">
         <v>74</v>
-      </c>
-      <c r="E30" t="s">
-        <v>45</v>
       </c>
       <c r="F30" t="s">
         <v>75</v>
@@ -2741,10 +2741,10 @@
         <v>9</v>
       </c>
       <c r="D31" t="s">
+        <v>44</v>
+      </c>
+      <c r="E31" t="s">
         <v>74</v>
-      </c>
-      <c r="E31" t="s">
-        <v>45</v>
       </c>
       <c r="F31" t="s">
         <v>75</v>
@@ -2770,10 +2770,10 @@
         <v>89</v>
       </c>
       <c r="F32" t="s">
+        <v>88</v>
+      </c>
+      <c r="G32" t="s">
         <v>89</v>
-      </c>
-      <c r="G32" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2793,10 +2793,10 @@
         <v>89</v>
       </c>
       <c r="F33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G33" t="s">
         <v>89</v>
-      </c>
-      <c r="G33" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2816,10 +2816,10 @@
         <v>89</v>
       </c>
       <c r="F34" t="s">
+        <v>88</v>
+      </c>
+      <c r="G34" t="s">
         <v>89</v>
-      </c>
-      <c r="G34" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2839,10 +2839,10 @@
         <v>89</v>
       </c>
       <c r="F35" t="s">
+        <v>88</v>
+      </c>
+      <c r="G35" t="s">
         <v>89</v>
-      </c>
-      <c r="G35" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2862,10 +2862,10 @@
         <v>89</v>
       </c>
       <c r="F36" t="s">
+        <v>88</v>
+      </c>
+      <c r="G36" t="s">
         <v>89</v>
-      </c>
-      <c r="G36" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2885,10 +2885,10 @@
         <v>101</v>
       </c>
       <c r="F37" t="s">
+        <v>100</v>
+      </c>
+      <c r="G37" t="s">
         <v>101</v>
-      </c>
-      <c r="G37" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2908,10 +2908,10 @@
         <v>101</v>
       </c>
       <c r="F38" t="s">
+        <v>100</v>
+      </c>
+      <c r="G38" t="s">
         <v>101</v>
-      </c>
-      <c r="G38" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2931,10 +2931,10 @@
         <v>101</v>
       </c>
       <c r="F39" t="s">
+        <v>100</v>
+      </c>
+      <c r="G39" t="s">
         <v>101</v>
-      </c>
-      <c r="G39" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2954,10 +2954,10 @@
         <v>101</v>
       </c>
       <c r="F40" t="s">
+        <v>100</v>
+      </c>
+      <c r="G40" t="s">
         <v>101</v>
-      </c>
-      <c r="G40" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2977,10 +2977,10 @@
         <v>101</v>
       </c>
       <c r="F41" t="s">
+        <v>100</v>
+      </c>
+      <c r="G41" t="s">
         <v>101</v>
-      </c>
-      <c r="G41" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -3000,10 +3000,10 @@
         <v>101</v>
       </c>
       <c r="F42" t="s">
+        <v>100</v>
+      </c>
+      <c r="G42" t="s">
         <v>101</v>
-      </c>
-      <c r="G42" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3023,10 +3023,10 @@
         <v>101</v>
       </c>
       <c r="F43" t="s">
+        <v>100</v>
+      </c>
+      <c r="G43" t="s">
         <v>101</v>
-      </c>
-      <c r="G43" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3046,10 +3046,10 @@
         <v>101</v>
       </c>
       <c r="F44" t="s">
+        <v>100</v>
+      </c>
+      <c r="G44" t="s">
         <v>101</v>
-      </c>
-      <c r="G44" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3069,10 +3069,10 @@
         <v>101</v>
       </c>
       <c r="F45" t="s">
+        <v>100</v>
+      </c>
+      <c r="G45" t="s">
         <v>101</v>
-      </c>
-      <c r="G45" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3092,10 +3092,10 @@
         <v>101</v>
       </c>
       <c r="F46" t="s">
+        <v>100</v>
+      </c>
+      <c r="G46" t="s">
         <v>101</v>
-      </c>
-      <c r="G46" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3115,10 +3115,10 @@
         <v>101</v>
       </c>
       <c r="F47" t="s">
+        <v>100</v>
+      </c>
+      <c r="G47" t="s">
         <v>101</v>
-      </c>
-      <c r="G47" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3500,10 +3500,10 @@
         <v>9</v>
       </c>
       <c r="D64" t="s">
+        <v>124</v>
+      </c>
+      <c r="E64" t="s">
         <v>160</v>
-      </c>
-      <c r="E64" t="s">
-        <v>125</v>
       </c>
       <c r="F64" t="s">
         <v>161</v>
@@ -3523,10 +3523,10 @@
         <v>9</v>
       </c>
       <c r="D65" t="s">
+        <v>124</v>
+      </c>
+      <c r="E65" t="s">
         <v>160</v>
-      </c>
-      <c r="E65" t="s">
-        <v>125</v>
       </c>
       <c r="F65" t="s">
         <v>161</v>
@@ -3546,10 +3546,10 @@
         <v>9</v>
       </c>
       <c r="D66" t="s">
+        <v>124</v>
+      </c>
+      <c r="E66" t="s">
         <v>160</v>
-      </c>
-      <c r="E66" t="s">
-        <v>125</v>
       </c>
       <c r="F66" t="s">
         <v>161</v>
@@ -3569,10 +3569,10 @@
         <v>9</v>
       </c>
       <c r="D67" t="s">
+        <v>124</v>
+      </c>
+      <c r="E67" t="s">
         <v>160</v>
-      </c>
-      <c r="E67" t="s">
-        <v>125</v>
       </c>
       <c r="F67" t="s">
         <v>161</v>
@@ -3592,10 +3592,10 @@
         <v>9</v>
       </c>
       <c r="D68" t="s">
+        <v>124</v>
+      </c>
+      <c r="E68" t="s">
         <v>160</v>
-      </c>
-      <c r="E68" t="s">
-        <v>125</v>
       </c>
       <c r="F68" t="s">
         <v>161</v>
@@ -3615,10 +3615,10 @@
         <v>9</v>
       </c>
       <c r="D69" t="s">
+        <v>124</v>
+      </c>
+      <c r="E69" t="s">
         <v>160</v>
-      </c>
-      <c r="E69" t="s">
-        <v>125</v>
       </c>
       <c r="F69" t="s">
         <v>161</v>
@@ -3644,10 +3644,10 @@
         <v>175</v>
       </c>
       <c r="F70" t="s">
+        <v>174</v>
+      </c>
+      <c r="G70" t="s">
         <v>175</v>
-      </c>
-      <c r="G70" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3667,10 +3667,10 @@
         <v>175</v>
       </c>
       <c r="F71" t="s">
+        <v>174</v>
+      </c>
+      <c r="G71" t="s">
         <v>175</v>
-      </c>
-      <c r="G71" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3690,10 +3690,10 @@
         <v>175</v>
       </c>
       <c r="F72" t="s">
+        <v>174</v>
+      </c>
+      <c r="G72" t="s">
         <v>175</v>
-      </c>
-      <c r="G72" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3713,10 +3713,10 @@
         <v>175</v>
       </c>
       <c r="F73" t="s">
+        <v>174</v>
+      </c>
+      <c r="G73" t="s">
         <v>175</v>
-      </c>
-      <c r="G73" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3736,10 +3736,10 @@
         <v>175</v>
       </c>
       <c r="F74" t="s">
+        <v>174</v>
+      </c>
+      <c r="G74" t="s">
         <v>175</v>
-      </c>
-      <c r="G74" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3759,10 +3759,10 @@
         <v>175</v>
       </c>
       <c r="F75" t="s">
+        <v>174</v>
+      </c>
+      <c r="G75" t="s">
         <v>175</v>
-      </c>
-      <c r="G75" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3782,10 +3782,10 @@
         <v>175</v>
       </c>
       <c r="F76" t="s">
+        <v>174</v>
+      </c>
+      <c r="G76" t="s">
         <v>175</v>
-      </c>
-      <c r="G76" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3805,10 +3805,10 @@
         <v>175</v>
       </c>
       <c r="F77" t="s">
+        <v>174</v>
+      </c>
+      <c r="G77" t="s">
         <v>175</v>
-      </c>
-      <c r="G77" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3828,10 +3828,10 @@
         <v>175</v>
       </c>
       <c r="F78" t="s">
+        <v>174</v>
+      </c>
+      <c r="G78" t="s">
         <v>175</v>
-      </c>
-      <c r="G78" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3851,10 +3851,10 @@
         <v>175</v>
       </c>
       <c r="F79" t="s">
+        <v>174</v>
+      </c>
+      <c r="G79" t="s">
         <v>175</v>
-      </c>
-      <c r="G79" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3874,10 +3874,10 @@
         <v>175</v>
       </c>
       <c r="F80" t="s">
+        <v>174</v>
+      </c>
+      <c r="G80" t="s">
         <v>175</v>
-      </c>
-      <c r="G80" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3897,10 +3897,10 @@
         <v>199</v>
       </c>
       <c r="F81" t="s">
+        <v>198</v>
+      </c>
+      <c r="G81" t="s">
         <v>199</v>
-      </c>
-      <c r="G81" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3920,10 +3920,10 @@
         <v>199</v>
       </c>
       <c r="F82" t="s">
+        <v>198</v>
+      </c>
+      <c r="G82" t="s">
         <v>199</v>
-      </c>
-      <c r="G82" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3943,10 +3943,10 @@
         <v>199</v>
       </c>
       <c r="F83" t="s">
+        <v>198</v>
+      </c>
+      <c r="G83" t="s">
         <v>199</v>
-      </c>
-      <c r="G83" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3966,10 +3966,10 @@
         <v>199</v>
       </c>
       <c r="F84" t="s">
+        <v>198</v>
+      </c>
+      <c r="G84" t="s">
         <v>199</v>
-      </c>
-      <c r="G84" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3989,10 +3989,10 @@
         <v>199</v>
       </c>
       <c r="F85" t="s">
+        <v>198</v>
+      </c>
+      <c r="G85" t="s">
         <v>199</v>
-      </c>
-      <c r="G85" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4012,10 +4012,10 @@
         <v>199</v>
       </c>
       <c r="F86" t="s">
+        <v>198</v>
+      </c>
+      <c r="G86" t="s">
         <v>199</v>
-      </c>
-      <c r="G86" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4035,10 +4035,10 @@
         <v>199</v>
       </c>
       <c r="F87" t="s">
+        <v>198</v>
+      </c>
+      <c r="G87" t="s">
         <v>199</v>
-      </c>
-      <c r="G87" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4058,10 +4058,10 @@
         <v>215</v>
       </c>
       <c r="F88" t="s">
+        <v>214</v>
+      </c>
+      <c r="G88" t="s">
         <v>215</v>
-      </c>
-      <c r="G88" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4081,10 +4081,10 @@
         <v>215</v>
       </c>
       <c r="F89" t="s">
+        <v>214</v>
+      </c>
+      <c r="G89" t="s">
         <v>215</v>
-      </c>
-      <c r="G89" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4104,10 +4104,10 @@
         <v>215</v>
       </c>
       <c r="F90" t="s">
+        <v>214</v>
+      </c>
+      <c r="G90" t="s">
         <v>215</v>
-      </c>
-      <c r="G90" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4127,10 +4127,10 @@
         <v>215</v>
       </c>
       <c r="F91" t="s">
+        <v>214</v>
+      </c>
+      <c r="G91" t="s">
         <v>215</v>
-      </c>
-      <c r="G91" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4236,10 +4236,10 @@
         <v>9</v>
       </c>
       <c r="D96" t="s">
+        <v>224</v>
+      </c>
+      <c r="E96" t="s">
         <v>236</v>
-      </c>
-      <c r="E96" t="s">
-        <v>225</v>
       </c>
       <c r="F96" t="s">
         <v>237</v>
@@ -4259,10 +4259,10 @@
         <v>9</v>
       </c>
       <c r="D97" t="s">
+        <v>224</v>
+      </c>
+      <c r="E97" t="s">
         <v>236</v>
-      </c>
-      <c r="E97" t="s">
-        <v>225</v>
       </c>
       <c r="F97" t="s">
         <v>237</v>
@@ -4282,10 +4282,10 @@
         <v>9</v>
       </c>
       <c r="D98" t="s">
+        <v>224</v>
+      </c>
+      <c r="E98" t="s">
         <v>236</v>
-      </c>
-      <c r="E98" t="s">
-        <v>225</v>
       </c>
       <c r="F98" t="s">
         <v>237</v>
@@ -4305,10 +4305,10 @@
         <v>9</v>
       </c>
       <c r="D99" t="s">
+        <v>224</v>
+      </c>
+      <c r="E99" t="s">
         <v>236</v>
-      </c>
-      <c r="E99" t="s">
-        <v>225</v>
       </c>
       <c r="F99" t="s">
         <v>237</v>
@@ -4328,10 +4328,10 @@
         <v>9</v>
       </c>
       <c r="D100" t="s">
+        <v>224</v>
+      </c>
+      <c r="E100" t="s">
         <v>236</v>
-      </c>
-      <c r="E100" t="s">
-        <v>225</v>
       </c>
       <c r="F100" t="s">
         <v>237</v>
@@ -4351,10 +4351,10 @@
         <v>9</v>
       </c>
       <c r="D101" t="s">
+        <v>224</v>
+      </c>
+      <c r="E101" t="s">
         <v>236</v>
-      </c>
-      <c r="E101" t="s">
-        <v>225</v>
       </c>
       <c r="F101" t="s">
         <v>237</v>
@@ -4374,10 +4374,10 @@
         <v>9</v>
       </c>
       <c r="D102" t="s">
+        <v>224</v>
+      </c>
+      <c r="E102" t="s">
         <v>236</v>
-      </c>
-      <c r="E102" t="s">
-        <v>225</v>
       </c>
       <c r="F102" t="s">
         <v>237</v>
@@ -4397,10 +4397,10 @@
         <v>9</v>
       </c>
       <c r="D103" t="s">
+        <v>224</v>
+      </c>
+      <c r="E103" t="s">
         <v>236</v>
-      </c>
-      <c r="E103" t="s">
-        <v>225</v>
       </c>
       <c r="F103" t="s">
         <v>237</v>
@@ -4420,10 +4420,10 @@
         <v>9</v>
       </c>
       <c r="D104" t="s">
+        <v>224</v>
+      </c>
+      <c r="E104" t="s">
         <v>236</v>
-      </c>
-      <c r="E104" t="s">
-        <v>225</v>
       </c>
       <c r="F104" t="s">
         <v>237</v>
@@ -4443,10 +4443,10 @@
         <v>9</v>
       </c>
       <c r="D105" t="s">
+        <v>224</v>
+      </c>
+      <c r="E105" t="s">
         <v>256</v>
-      </c>
-      <c r="E105" t="s">
-        <v>225</v>
       </c>
       <c r="F105" t="s">
         <v>257</v>
@@ -4466,10 +4466,10 @@
         <v>9</v>
       </c>
       <c r="D106" t="s">
+        <v>224</v>
+      </c>
+      <c r="E106" t="s">
         <v>256</v>
-      </c>
-      <c r="E106" t="s">
-        <v>225</v>
       </c>
       <c r="F106" t="s">
         <v>257</v>
@@ -4489,10 +4489,10 @@
         <v>9</v>
       </c>
       <c r="D107" t="s">
+        <v>224</v>
+      </c>
+      <c r="E107" t="s">
         <v>256</v>
-      </c>
-      <c r="E107" t="s">
-        <v>225</v>
       </c>
       <c r="F107" t="s">
         <v>257</v>
@@ -4512,10 +4512,10 @@
         <v>9</v>
       </c>
       <c r="D108" t="s">
+        <v>224</v>
+      </c>
+      <c r="E108" t="s">
         <v>256</v>
-      </c>
-      <c r="E108" t="s">
-        <v>225</v>
       </c>
       <c r="F108" t="s">
         <v>257</v>
@@ -4535,10 +4535,10 @@
         <v>9</v>
       </c>
       <c r="D109" t="s">
+        <v>224</v>
+      </c>
+      <c r="E109" t="s">
         <v>256</v>
-      </c>
-      <c r="E109" t="s">
-        <v>225</v>
       </c>
       <c r="F109" t="s">
         <v>257</v>
@@ -4558,10 +4558,10 @@
         <v>9</v>
       </c>
       <c r="D110" t="s">
+        <v>224</v>
+      </c>
+      <c r="E110" t="s">
         <v>256</v>
-      </c>
-      <c r="E110" t="s">
-        <v>225</v>
       </c>
       <c r="F110" t="s">
         <v>257</v>
@@ -4581,10 +4581,10 @@
         <v>9</v>
       </c>
       <c r="D111" t="s">
+        <v>224</v>
+      </c>
+      <c r="E111" t="s">
         <v>270</v>
-      </c>
-      <c r="E111" t="s">
-        <v>225</v>
       </c>
       <c r="F111" t="s">
         <v>271</v>
@@ -4604,10 +4604,10 @@
         <v>9</v>
       </c>
       <c r="D112" t="s">
+        <v>224</v>
+      </c>
+      <c r="E112" t="s">
         <v>274</v>
-      </c>
-      <c r="E112" t="s">
-        <v>225</v>
       </c>
       <c r="F112" t="s">
         <v>275</v>
@@ -4627,10 +4627,10 @@
         <v>9</v>
       </c>
       <c r="D113" t="s">
+        <v>224</v>
+      </c>
+      <c r="E113" t="s">
         <v>278</v>
-      </c>
-      <c r="E113" t="s">
-        <v>225</v>
       </c>
       <c r="F113" t="s">
         <v>279</v>
@@ -4650,10 +4650,10 @@
         <v>9</v>
       </c>
       <c r="D114" t="s">
+        <v>224</v>
+      </c>
+      <c r="E114" t="s">
         <v>278</v>
-      </c>
-      <c r="E114" t="s">
-        <v>225</v>
       </c>
       <c r="F114" t="s">
         <v>279</v>
@@ -4673,10 +4673,10 @@
         <v>9</v>
       </c>
       <c r="D115" t="s">
+        <v>224</v>
+      </c>
+      <c r="E115" t="s">
         <v>278</v>
-      </c>
-      <c r="E115" t="s">
-        <v>225</v>
       </c>
       <c r="F115" t="s">
         <v>279</v>
@@ -4696,10 +4696,10 @@
         <v>9</v>
       </c>
       <c r="D116" t="s">
+        <v>224</v>
+      </c>
+      <c r="E116" t="s">
         <v>278</v>
-      </c>
-      <c r="E116" t="s">
-        <v>225</v>
       </c>
       <c r="F116" t="s">
         <v>279</v>
@@ -4719,10 +4719,10 @@
         <v>9</v>
       </c>
       <c r="D117" t="s">
+        <v>224</v>
+      </c>
+      <c r="E117" t="s">
         <v>278</v>
-      </c>
-      <c r="E117" t="s">
-        <v>225</v>
       </c>
       <c r="F117" t="s">
         <v>279</v>
@@ -4742,10 +4742,10 @@
         <v>9</v>
       </c>
       <c r="D118" t="s">
+        <v>224</v>
+      </c>
+      <c r="E118" t="s">
         <v>278</v>
-      </c>
-      <c r="E118" t="s">
-        <v>225</v>
       </c>
       <c r="F118" t="s">
         <v>279</v>
@@ -4765,10 +4765,10 @@
         <v>9</v>
       </c>
       <c r="D119" t="s">
+        <v>224</v>
+      </c>
+      <c r="E119" t="s">
         <v>278</v>
-      </c>
-      <c r="E119" t="s">
-        <v>225</v>
       </c>
       <c r="F119" t="s">
         <v>279</v>
@@ -4794,10 +4794,10 @@
         <v>295</v>
       </c>
       <c r="F120" t="s">
+        <v>294</v>
+      </c>
+      <c r="G120" t="s">
         <v>295</v>
-      </c>
-      <c r="G120" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4817,10 +4817,10 @@
         <v>295</v>
       </c>
       <c r="F121" t="s">
+        <v>294</v>
+      </c>
+      <c r="G121" t="s">
         <v>295</v>
-      </c>
-      <c r="G121" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4840,10 +4840,10 @@
         <v>295</v>
       </c>
       <c r="F122" t="s">
+        <v>294</v>
+      </c>
+      <c r="G122" t="s">
         <v>295</v>
-      </c>
-      <c r="G122" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4863,10 +4863,10 @@
         <v>295</v>
       </c>
       <c r="F123" t="s">
+        <v>294</v>
+      </c>
+      <c r="G123" t="s">
         <v>295</v>
-      </c>
-      <c r="G123" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4886,10 +4886,10 @@
         <v>295</v>
       </c>
       <c r="F124" t="s">
+        <v>294</v>
+      </c>
+      <c r="G124" t="s">
         <v>295</v>
-      </c>
-      <c r="G124" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4909,10 +4909,10 @@
         <v>295</v>
       </c>
       <c r="F125" t="s">
+        <v>294</v>
+      </c>
+      <c r="G125" t="s">
         <v>295</v>
-      </c>
-      <c r="G125" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4932,10 +4932,10 @@
         <v>309</v>
       </c>
       <c r="F126" t="s">
+        <v>308</v>
+      </c>
+      <c r="G126" t="s">
         <v>309</v>
-      </c>
-      <c r="G126" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4955,10 +4955,10 @@
         <v>309</v>
       </c>
       <c r="F127" t="s">
+        <v>308</v>
+      </c>
+      <c r="G127" t="s">
         <v>309</v>
-      </c>
-      <c r="G127" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4978,10 +4978,10 @@
         <v>309</v>
       </c>
       <c r="F128" t="s">
+        <v>308</v>
+      </c>
+      <c r="G128" t="s">
         <v>309</v>
-      </c>
-      <c r="G128" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -5001,10 +5001,10 @@
         <v>309</v>
       </c>
       <c r="F129" t="s">
+        <v>308</v>
+      </c>
+      <c r="G129" t="s">
         <v>309</v>
-      </c>
-      <c r="G129" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -5432,10 +5432,10 @@
         <v>9</v>
       </c>
       <c r="D148" t="s">
+        <v>318</v>
+      </c>
+      <c r="E148" t="s">
         <v>358</v>
-      </c>
-      <c r="E148" t="s">
-        <v>319</v>
       </c>
       <c r="F148" t="s">
         <v>359</v>
@@ -5455,10 +5455,10 @@
         <v>9</v>
       </c>
       <c r="D149" t="s">
+        <v>318</v>
+      </c>
+      <c r="E149" t="s">
         <v>358</v>
-      </c>
-      <c r="E149" t="s">
-        <v>319</v>
       </c>
       <c r="F149" t="s">
         <v>359</v>
@@ -5478,10 +5478,10 @@
         <v>9</v>
       </c>
       <c r="D150" t="s">
+        <v>318</v>
+      </c>
+      <c r="E150" t="s">
         <v>358</v>
-      </c>
-      <c r="E150" t="s">
-        <v>319</v>
       </c>
       <c r="F150" t="s">
         <v>359</v>
@@ -5501,10 +5501,10 @@
         <v>9</v>
       </c>
       <c r="D151" t="s">
+        <v>318</v>
+      </c>
+      <c r="E151" t="s">
         <v>358</v>
-      </c>
-      <c r="E151" t="s">
-        <v>319</v>
       </c>
       <c r="F151" t="s">
         <v>359</v>
@@ -5524,10 +5524,10 @@
         <v>9</v>
       </c>
       <c r="D152" t="s">
+        <v>318</v>
+      </c>
+      <c r="E152" t="s">
         <v>358</v>
-      </c>
-      <c r="E152" t="s">
-        <v>319</v>
       </c>
       <c r="F152" t="s">
         <v>359</v>
@@ -5547,10 +5547,10 @@
         <v>9</v>
       </c>
       <c r="D153" t="s">
+        <v>318</v>
+      </c>
+      <c r="E153" t="s">
         <v>358</v>
-      </c>
-      <c r="E153" t="s">
-        <v>319</v>
       </c>
       <c r="F153" t="s">
         <v>359</v>
@@ -5570,10 +5570,10 @@
         <v>9</v>
       </c>
       <c r="D154" t="s">
+        <v>318</v>
+      </c>
+      <c r="E154" t="s">
         <v>372</v>
-      </c>
-      <c r="E154" t="s">
-        <v>319</v>
       </c>
       <c r="F154" t="s">
         <v>373</v>
@@ -5593,10 +5593,10 @@
         <v>9</v>
       </c>
       <c r="D155" t="s">
+        <v>318</v>
+      </c>
+      <c r="E155" t="s">
         <v>372</v>
-      </c>
-      <c r="E155" t="s">
-        <v>319</v>
       </c>
       <c r="F155" t="s">
         <v>373</v>
@@ -5616,10 +5616,10 @@
         <v>9</v>
       </c>
       <c r="D156" t="s">
+        <v>318</v>
+      </c>
+      <c r="E156" t="s">
         <v>372</v>
-      </c>
-      <c r="E156" t="s">
-        <v>319</v>
       </c>
       <c r="F156" t="s">
         <v>373</v>
@@ -5639,10 +5639,10 @@
         <v>9</v>
       </c>
       <c r="D157" t="s">
+        <v>318</v>
+      </c>
+      <c r="E157" t="s">
         <v>372</v>
-      </c>
-      <c r="E157" t="s">
-        <v>319</v>
       </c>
       <c r="F157" t="s">
         <v>373</v>
@@ -5662,10 +5662,10 @@
         <v>9</v>
       </c>
       <c r="D158" t="s">
+        <v>318</v>
+      </c>
+      <c r="E158" t="s">
         <v>372</v>
-      </c>
-      <c r="E158" t="s">
-        <v>319</v>
       </c>
       <c r="F158" t="s">
         <v>373</v>
@@ -6122,10 +6122,10 @@
         <v>9</v>
       </c>
       <c r="D178" t="s">
+        <v>384</v>
+      </c>
+      <c r="E178" t="s">
         <v>426</v>
-      </c>
-      <c r="E178" t="s">
-        <v>385</v>
       </c>
       <c r="F178" t="s">
         <v>427</v>
@@ -6145,10 +6145,10 @@
         <v>9</v>
       </c>
       <c r="D179" t="s">
+        <v>384</v>
+      </c>
+      <c r="E179" t="s">
         <v>426</v>
-      </c>
-      <c r="E179" t="s">
-        <v>385</v>
       </c>
       <c r="F179" t="s">
         <v>427</v>
@@ -6168,10 +6168,10 @@
         <v>9</v>
       </c>
       <c r="D180" t="s">
+        <v>384</v>
+      </c>
+      <c r="E180" t="s">
         <v>426</v>
-      </c>
-      <c r="E180" t="s">
-        <v>385</v>
       </c>
       <c r="F180" t="s">
         <v>427</v>
@@ -6191,10 +6191,10 @@
         <v>9</v>
       </c>
       <c r="D181" t="s">
+        <v>384</v>
+      </c>
+      <c r="E181" t="s">
         <v>426</v>
-      </c>
-      <c r="E181" t="s">
-        <v>385</v>
       </c>
       <c r="F181" t="s">
         <v>427</v>
@@ -6214,10 +6214,10 @@
         <v>9</v>
       </c>
       <c r="D182" t="s">
+        <v>384</v>
+      </c>
+      <c r="E182" t="s">
         <v>426</v>
-      </c>
-      <c r="E182" t="s">
-        <v>385</v>
       </c>
       <c r="F182" t="s">
         <v>427</v>
@@ -6237,10 +6237,10 @@
         <v>9</v>
       </c>
       <c r="D183" t="s">
+        <v>384</v>
+      </c>
+      <c r="E183" t="s">
         <v>426</v>
-      </c>
-      <c r="E183" t="s">
-        <v>385</v>
       </c>
       <c r="F183" t="s">
         <v>427</v>
@@ -6260,10 +6260,10 @@
         <v>9</v>
       </c>
       <c r="D184" t="s">
+        <v>384</v>
+      </c>
+      <c r="E184" t="s">
         <v>426</v>
-      </c>
-      <c r="E184" t="s">
-        <v>385</v>
       </c>
       <c r="F184" t="s">
         <v>427</v>
@@ -6283,10 +6283,10 @@
         <v>9</v>
       </c>
       <c r="D185" t="s">
+        <v>384</v>
+      </c>
+      <c r="E185" t="s">
         <v>426</v>
-      </c>
-      <c r="E185" t="s">
-        <v>385</v>
       </c>
       <c r="F185" t="s">
         <v>427</v>
@@ -6306,10 +6306,10 @@
         <v>9</v>
       </c>
       <c r="D186" t="s">
+        <v>384</v>
+      </c>
+      <c r="E186" t="s">
         <v>426</v>
-      </c>
-      <c r="E186" t="s">
-        <v>385</v>
       </c>
       <c r="F186" t="s">
         <v>427</v>
@@ -6329,10 +6329,10 @@
         <v>9</v>
       </c>
       <c r="D187" t="s">
+        <v>384</v>
+      </c>
+      <c r="E187" t="s">
         <v>426</v>
-      </c>
-      <c r="E187" t="s">
-        <v>385</v>
       </c>
       <c r="F187" t="s">
         <v>427</v>
@@ -6352,10 +6352,10 @@
         <v>9</v>
       </c>
       <c r="D188" t="s">
+        <v>384</v>
+      </c>
+      <c r="E188" t="s">
         <v>448</v>
-      </c>
-      <c r="E188" t="s">
-        <v>385</v>
       </c>
       <c r="F188" t="s">
         <v>449</v>
@@ -6381,10 +6381,10 @@
         <v>453</v>
       </c>
       <c r="F189" t="s">
+        <v>452</v>
+      </c>
+      <c r="G189" t="s">
         <v>453</v>
-      </c>
-      <c r="G189" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6404,10 +6404,10 @@
         <v>453</v>
       </c>
       <c r="F190" t="s">
+        <v>452</v>
+      </c>
+      <c r="G190" t="s">
         <v>453</v>
-      </c>
-      <c r="G190" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6427,10 +6427,10 @@
         <v>453</v>
       </c>
       <c r="F191" t="s">
+        <v>452</v>
+      </c>
+      <c r="G191" t="s">
         <v>453</v>
-      </c>
-      <c r="G191" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6450,10 +6450,10 @@
         <v>453</v>
       </c>
       <c r="F192" t="s">
+        <v>452</v>
+      </c>
+      <c r="G192" t="s">
         <v>453</v>
-      </c>
-      <c r="G192" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6473,10 +6473,10 @@
         <v>453</v>
       </c>
       <c r="F193" t="s">
+        <v>452</v>
+      </c>
+      <c r="G193" t="s">
         <v>453</v>
-      </c>
-      <c r="G193" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6496,10 +6496,10 @@
         <v>453</v>
       </c>
       <c r="F194" t="s">
+        <v>452</v>
+      </c>
+      <c r="G194" t="s">
         <v>453</v>
-      </c>
-      <c r="G194" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6519,10 +6519,10 @@
         <v>467</v>
       </c>
       <c r="F195" t="s">
+        <v>466</v>
+      </c>
+      <c r="G195" t="s">
         <v>467</v>
-      </c>
-      <c r="G195" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6542,10 +6542,10 @@
         <v>471</v>
       </c>
       <c r="F196" t="s">
+        <v>470</v>
+      </c>
+      <c r="G196" t="s">
         <v>471</v>
-      </c>
-      <c r="G196" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6565,10 +6565,10 @@
         <v>471</v>
       </c>
       <c r="F197" t="s">
+        <v>470</v>
+      </c>
+      <c r="G197" t="s">
         <v>471</v>
-      </c>
-      <c r="G197" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6588,10 +6588,10 @@
         <v>471</v>
       </c>
       <c r="F198" t="s">
+        <v>470</v>
+      </c>
+      <c r="G198" t="s">
         <v>471</v>
-      </c>
-      <c r="G198" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6611,10 +6611,10 @@
         <v>471</v>
       </c>
       <c r="F199" t="s">
+        <v>470</v>
+      </c>
+      <c r="G199" t="s">
         <v>471</v>
-      </c>
-      <c r="G199" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6634,10 +6634,10 @@
         <v>471</v>
       </c>
       <c r="F200" t="s">
+        <v>470</v>
+      </c>
+      <c r="G200" t="s">
         <v>471</v>
-      </c>
-      <c r="G200" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6657,10 +6657,10 @@
         <v>471</v>
       </c>
       <c r="F201" t="s">
+        <v>470</v>
+      </c>
+      <c r="G201" t="s">
         <v>471</v>
-      </c>
-      <c r="G201" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6680,10 +6680,10 @@
         <v>485</v>
       </c>
       <c r="F202" t="s">
+        <v>484</v>
+      </c>
+      <c r="G202" t="s">
         <v>485</v>
-      </c>
-      <c r="G202" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6703,10 +6703,10 @@
         <v>485</v>
       </c>
       <c r="F203" t="s">
+        <v>484</v>
+      </c>
+      <c r="G203" t="s">
         <v>485</v>
-      </c>
-      <c r="G203" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6726,10 +6726,10 @@
         <v>485</v>
       </c>
       <c r="F204" t="s">
+        <v>484</v>
+      </c>
+      <c r="G204" t="s">
         <v>485</v>
-      </c>
-      <c r="G204" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6749,10 +6749,10 @@
         <v>485</v>
       </c>
       <c r="F205" t="s">
+        <v>484</v>
+      </c>
+      <c r="G205" t="s">
         <v>485</v>
-      </c>
-      <c r="G205" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6772,10 +6772,10 @@
         <v>485</v>
       </c>
       <c r="F206" t="s">
+        <v>484</v>
+      </c>
+      <c r="G206" t="s">
         <v>485</v>
-      </c>
-      <c r="G206" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6795,10 +6795,10 @@
         <v>485</v>
       </c>
       <c r="F207" t="s">
+        <v>484</v>
+      </c>
+      <c r="G207" t="s">
         <v>485</v>
-      </c>
-      <c r="G207" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6818,10 +6818,10 @@
         <v>485</v>
       </c>
       <c r="F208" t="s">
+        <v>484</v>
+      </c>
+      <c r="G208" t="s">
         <v>485</v>
-      </c>
-      <c r="G208" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6841,10 +6841,10 @@
         <v>485</v>
       </c>
       <c r="F209" t="s">
+        <v>484</v>
+      </c>
+      <c r="G209" t="s">
         <v>485</v>
-      </c>
-      <c r="G209" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6864,10 +6864,10 @@
         <v>485</v>
       </c>
       <c r="F210" t="s">
+        <v>484</v>
+      </c>
+      <c r="G210" t="s">
         <v>485</v>
-      </c>
-      <c r="G210" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6887,10 +6887,10 @@
         <v>485</v>
       </c>
       <c r="F211" t="s">
+        <v>484</v>
+      </c>
+      <c r="G211" t="s">
         <v>485</v>
-      </c>
-      <c r="G211" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6910,10 +6910,10 @@
         <v>507</v>
       </c>
       <c r="F212" t="s">
+        <v>506</v>
+      </c>
+      <c r="G212" t="s">
         <v>507</v>
-      </c>
-      <c r="G212" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6933,10 +6933,10 @@
         <v>511</v>
       </c>
       <c r="F213" t="s">
+        <v>510</v>
+      </c>
+      <c r="G213" t="s">
         <v>511</v>
-      </c>
-      <c r="G213" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6956,10 +6956,10 @@
         <v>515</v>
       </c>
       <c r="F214" t="s">
+        <v>514</v>
+      </c>
+      <c r="G214" t="s">
         <v>515</v>
-      </c>
-      <c r="G214" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6979,10 +6979,10 @@
         <v>515</v>
       </c>
       <c r="F215" t="s">
+        <v>514</v>
+      </c>
+      <c r="G215" t="s">
         <v>515</v>
-      </c>
-      <c r="G215" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -7002,10 +7002,10 @@
         <v>521</v>
       </c>
       <c r="F216" t="s">
+        <v>520</v>
+      </c>
+      <c r="G216" t="s">
         <v>521</v>
-      </c>
-      <c r="G216" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -7025,10 +7025,10 @@
         <v>521</v>
       </c>
       <c r="F217" t="s">
+        <v>520</v>
+      </c>
+      <c r="G217" t="s">
         <v>521</v>
-      </c>
-      <c r="G217" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -7048,10 +7048,10 @@
         <v>521</v>
       </c>
       <c r="F218" t="s">
+        <v>520</v>
+      </c>
+      <c r="G218" t="s">
         <v>521</v>
-      </c>
-      <c r="G218" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -7071,10 +7071,10 @@
         <v>521</v>
       </c>
       <c r="F219" t="s">
+        <v>520</v>
+      </c>
+      <c r="G219" t="s">
         <v>521</v>
-      </c>
-      <c r="G219" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -7094,10 +7094,10 @@
         <v>521</v>
       </c>
       <c r="F220" t="s">
+        <v>520</v>
+      </c>
+      <c r="G220" t="s">
         <v>521</v>
-      </c>
-      <c r="G220" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -7117,10 +7117,10 @@
         <v>521</v>
       </c>
       <c r="F221" t="s">
+        <v>520</v>
+      </c>
+      <c r="G221" t="s">
         <v>521</v>
-      </c>
-      <c r="G221" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -7140,10 +7140,10 @@
         <v>521</v>
       </c>
       <c r="F222" t="s">
+        <v>520</v>
+      </c>
+      <c r="G222" t="s">
         <v>521</v>
-      </c>
-      <c r="G222" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -7163,10 +7163,10 @@
         <v>537</v>
       </c>
       <c r="F223" t="s">
+        <v>536</v>
+      </c>
+      <c r="G223" t="s">
         <v>537</v>
-      </c>
-      <c r="G223" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -7186,10 +7186,10 @@
         <v>537</v>
       </c>
       <c r="F224" t="s">
+        <v>536</v>
+      </c>
+      <c r="G224" t="s">
         <v>537</v>
-      </c>
-      <c r="G224" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -7209,10 +7209,10 @@
         <v>537</v>
       </c>
       <c r="F225" t="s">
+        <v>536</v>
+      </c>
+      <c r="G225" t="s">
         <v>537</v>
-      </c>
-      <c r="G225" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -7232,10 +7232,10 @@
         <v>545</v>
       </c>
       <c r="F226" t="s">
+        <v>544</v>
+      </c>
+      <c r="G226" t="s">
         <v>545</v>
-      </c>
-      <c r="G226" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -7255,10 +7255,10 @@
         <v>549</v>
       </c>
       <c r="F227" t="s">
+        <v>548</v>
+      </c>
+      <c r="G227" t="s">
         <v>549</v>
-      </c>
-      <c r="G227" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -7278,10 +7278,10 @@
         <v>553</v>
       </c>
       <c r="F228" t="s">
+        <v>552</v>
+      </c>
+      <c r="G228" t="s">
         <v>553</v>
-      </c>
-      <c r="G228" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -7301,10 +7301,10 @@
         <v>557</v>
       </c>
       <c r="F229" t="s">
+        <v>556</v>
+      </c>
+      <c r="G229" t="s">
         <v>557</v>
-      </c>
-      <c r="G229" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -7324,10 +7324,10 @@
         <v>561</v>
       </c>
       <c r="F230" t="s">
+        <v>560</v>
+      </c>
+      <c r="G230" t="s">
         <v>561</v>
-      </c>
-      <c r="G230" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -7347,10 +7347,10 @@
         <v>561</v>
       </c>
       <c r="F231" t="s">
+        <v>560</v>
+      </c>
+      <c r="G231" t="s">
         <v>561</v>
-      </c>
-      <c r="G231" t="s">
-        <v>560</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/en/SectorGroup.xlsx
+++ b/api/xlsx/en/SectorGroup.xlsx
@@ -25,18 +25,18 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
+    <t>codeforiati:category-name</t>
+  </si>
+  <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
-    <t>codeforiati:category-name</t>
-  </si>
-  <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -46,18 +46,18 @@
     <t>active</t>
   </si>
   <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>Education, Level Unspecified</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
     <t>110</t>
   </si>
   <si>
-    <t>Education, Level Unspecified</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>Education</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -148,18 +148,18 @@
     <t>Health policy and administrative management</t>
   </si>
   <si>
+    <t>Health</t>
+  </si>
+  <si>
+    <t>Health, General</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
-    <t>Health, General</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
-    <t>Health</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -280,12 +280,12 @@
     <t>Population policy and administrative management</t>
   </si>
   <si>
+    <t>Population Policies/Programmes &amp; Reproductive Health</t>
+  </si>
+  <si>
     <t>130</t>
   </si>
   <si>
-    <t>Population Policies/Programmes &amp; Reproductive Health</t>
-  </si>
-  <si>
     <t>13020</t>
   </si>
   <si>
@@ -316,12 +316,12 @@
     <t>Water sector policy and administrative management</t>
   </si>
   <si>
+    <t>Water Supply &amp; Sanitation</t>
+  </si>
+  <si>
     <t>140</t>
   </si>
   <si>
-    <t>Water Supply &amp; Sanitation</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -388,18 +388,18 @@
     <t>Public sector policy and administrative management</t>
   </si>
   <si>
+    <t>Government &amp; Civil Society</t>
+  </si>
+  <si>
+    <t>Government &amp; Civil Society-general</t>
+  </si>
+  <si>
+    <t>151</t>
+  </si>
+  <si>
     <t>150</t>
   </si>
   <si>
-    <t>Government &amp; Civil Society-general</t>
-  </si>
-  <si>
-    <t>151</t>
-  </si>
-  <si>
-    <t>Government &amp; Civil Society</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -538,12 +538,12 @@
     <t>Social Protection</t>
   </si>
   <si>
+    <t>Other Social Infrastructure &amp; Services</t>
+  </si>
+  <si>
     <t>160</t>
   </si>
   <si>
-    <t>Other Social Infrastructure &amp; Services</t>
-  </si>
-  <si>
     <t>16020</t>
   </si>
   <si>
@@ -610,12 +610,12 @@
     <t>Transport policy and administrative management</t>
   </si>
   <si>
+    <t>Transport &amp; Storage</t>
+  </si>
+  <si>
     <t>210</t>
   </si>
   <si>
-    <t>Transport &amp; Storage</t>
-  </si>
-  <si>
     <t>21020</t>
   </si>
   <si>
@@ -658,12 +658,12 @@
     <t>Communications policy and administrative management</t>
   </si>
   <si>
+    <t>Communications</t>
+  </si>
+  <si>
     <t>220</t>
   </si>
   <si>
-    <t>Communications</t>
-  </si>
-  <si>
     <t>22020</t>
   </si>
   <si>
@@ -688,18 +688,18 @@
     <t>Energy policy and administrative management</t>
   </si>
   <si>
+    <t>Energy</t>
+  </si>
+  <si>
+    <t>Energy Policy</t>
+  </si>
+  <si>
+    <t>231</t>
+  </si>
+  <si>
     <t>230</t>
   </si>
   <si>
-    <t>Energy Policy</t>
-  </si>
-  <si>
-    <t>231</t>
-  </si>
-  <si>
-    <t>Energy</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -898,12 +898,12 @@
     <t>Financial policy and administrative management</t>
   </si>
   <si>
+    <t>Banking &amp; Financial Services</t>
+  </si>
+  <si>
     <t>240</t>
   </si>
   <si>
-    <t>Banking &amp; Financial Services</t>
-  </si>
-  <si>
     <t>24020</t>
   </si>
   <si>
@@ -940,12 +940,12 @@
     <t>Business policy and administration</t>
   </si>
   <si>
+    <t>Business &amp; Other Services</t>
+  </si>
+  <si>
     <t>250</t>
   </si>
   <si>
-    <t>Business &amp; Other Services</t>
-  </si>
-  <si>
     <t>25020</t>
   </si>
   <si>
@@ -970,18 +970,18 @@
     <t>Agricultural policy and administrative management</t>
   </si>
   <si>
+    <t>Agriculture, Forestry, Fishing</t>
+  </si>
+  <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
+    <t>311</t>
+  </si>
+  <si>
     <t>310</t>
   </si>
   <si>
-    <t>Agriculture</t>
-  </si>
-  <si>
-    <t>311</t>
-  </si>
-  <si>
-    <t>Agriculture, Forestry, Fishing</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1168,18 +1168,18 @@
     <t>Industrial policy and administrative management</t>
   </si>
   <si>
+    <t>Industry, Mining, Construction</t>
+  </si>
+  <si>
+    <t>Industry</t>
+  </si>
+  <si>
+    <t>321</t>
+  </si>
+  <si>
     <t>320</t>
   </si>
   <si>
-    <t>Industry</t>
-  </si>
-  <si>
-    <t>321</t>
-  </si>
-  <si>
-    <t>Industry, Mining, Construction</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1372,12 +1372,12 @@
     <t>Trade policy and administrative management</t>
   </si>
   <si>
+    <t>Trade Policies &amp; Regulations</t>
+  </si>
+  <si>
     <t>331</t>
   </si>
   <si>
-    <t>Trade Policies &amp; Regulations</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1414,24 +1414,24 @@
     <t>Tourism policy and administrative management</t>
   </si>
   <si>
+    <t>Tourism</t>
+  </si>
+  <si>
     <t>332</t>
   </si>
   <si>
-    <t>Tourism</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
     <t>Environmental policy and administrative management</t>
   </si>
   <si>
+    <t>General Environment Protection</t>
+  </si>
+  <si>
     <t>410</t>
   </si>
   <si>
-    <t>General Environment Protection</t>
-  </si>
-  <si>
     <t>41020</t>
   </si>
   <si>
@@ -1468,12 +1468,12 @@
     <t>Multisector aid</t>
   </si>
   <si>
+    <t>Other Multisector</t>
+  </si>
+  <si>
     <t>430</t>
   </si>
   <si>
-    <t>Other Multisector</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -1534,36 +1534,36 @@
     <t>General budget support-related aid</t>
   </si>
   <si>
+    <t>General Budget Support</t>
+  </si>
+  <si>
     <t>510</t>
   </si>
   <si>
-    <t>General Budget Support</t>
-  </si>
-  <si>
     <t>52010</t>
   </si>
   <si>
     <t>Food assistance</t>
   </si>
   <si>
+    <t>Development Food Assistance</t>
+  </si>
+  <si>
     <t>520</t>
   </si>
   <si>
-    <t>Development Food Assistance</t>
-  </si>
-  <si>
     <t>53030</t>
   </si>
   <si>
     <t>Import support (capital goods)</t>
   </si>
   <si>
+    <t>Other Commodity Assistance</t>
+  </si>
+  <si>
     <t>530</t>
   </si>
   <si>
-    <t>Other Commodity Assistance</t>
-  </si>
-  <si>
     <t>53040</t>
   </si>
   <si>
@@ -1576,12 +1576,12 @@
     <t>Action relating to debt</t>
   </si>
   <si>
+    <t>Action Relating to Debt</t>
+  </si>
+  <si>
     <t>600</t>
   </si>
   <si>
-    <t>Action Relating to Debt</t>
-  </si>
-  <si>
     <t>60020</t>
   </si>
   <si>
@@ -1624,12 +1624,12 @@
     <t>Material relief assistance and services</t>
   </si>
   <si>
+    <t>Emergency Response</t>
+  </si>
+  <si>
     <t>720</t>
   </si>
   <si>
-    <t>Emergency Response</t>
-  </si>
-  <si>
     <t>72040</t>
   </si>
   <si>
@@ -1648,58 +1648,58 @@
     <t>Immediate post-emergency reconstruction and rehabilitation</t>
   </si>
   <si>
+    <t>Reconstruction Relief &amp; Rehabilitation</t>
+  </si>
+  <si>
     <t>730</t>
   </si>
   <si>
-    <t>Reconstruction Relief &amp; Rehabilitation</t>
-  </si>
-  <si>
     <t>74020</t>
   </si>
   <si>
     <t>Multi-hazard response preparedness</t>
   </si>
   <si>
+    <t>Disaster Prevention &amp; Preparedness</t>
+  </si>
+  <si>
     <t>740</t>
   </si>
   <si>
-    <t>Disaster Prevention &amp; Preparedness</t>
-  </si>
-  <si>
     <t>91010</t>
   </si>
   <si>
     <t>Administrative costs (non-sector allocable)</t>
   </si>
   <si>
+    <t>Administrative Costs of Donors</t>
+  </si>
+  <si>
     <t>910</t>
   </si>
   <si>
-    <t>Administrative Costs of Donors</t>
-  </si>
-  <si>
     <t>93010</t>
   </si>
   <si>
     <t>Refugees/asylum seekers in donor countries (non-sector allocable)</t>
   </si>
   <si>
+    <t>Refugees in Donor Countries</t>
+  </si>
+  <si>
     <t>930</t>
   </si>
   <si>
-    <t>Refugees in Donor Countries</t>
-  </si>
-  <si>
     <t>99810</t>
   </si>
   <si>
     <t>Sectors not specified</t>
   </si>
   <si>
+    <t>Unallocated / Unspecified</t>
+  </si>
+  <si>
     <t>998</t>
-  </si>
-  <si>
-    <t>Unallocated / Unspecified</t>
   </si>
   <si>
     <t>99820</t>
@@ -2767,10 +2767,10 @@
         <v>88</v>
       </c>
       <c r="E32" t="s">
+        <v>88</v>
+      </c>
+      <c r="F32" t="s">
         <v>89</v>
-      </c>
-      <c r="F32" t="s">
-        <v>88</v>
       </c>
       <c r="G32" t="s">
         <v>89</v>
@@ -2790,10 +2790,10 @@
         <v>88</v>
       </c>
       <c r="E33" t="s">
+        <v>88</v>
+      </c>
+      <c r="F33" t="s">
         <v>89</v>
-      </c>
-      <c r="F33" t="s">
-        <v>88</v>
       </c>
       <c r="G33" t="s">
         <v>89</v>
@@ -2813,10 +2813,10 @@
         <v>88</v>
       </c>
       <c r="E34" t="s">
+        <v>88</v>
+      </c>
+      <c r="F34" t="s">
         <v>89</v>
-      </c>
-      <c r="F34" t="s">
-        <v>88</v>
       </c>
       <c r="G34" t="s">
         <v>89</v>
@@ -2836,10 +2836,10 @@
         <v>88</v>
       </c>
       <c r="E35" t="s">
+        <v>88</v>
+      </c>
+      <c r="F35" t="s">
         <v>89</v>
-      </c>
-      <c r="F35" t="s">
-        <v>88</v>
       </c>
       <c r="G35" t="s">
         <v>89</v>
@@ -2859,10 +2859,10 @@
         <v>88</v>
       </c>
       <c r="E36" t="s">
+        <v>88</v>
+      </c>
+      <c r="F36" t="s">
         <v>89</v>
-      </c>
-      <c r="F36" t="s">
-        <v>88</v>
       </c>
       <c r="G36" t="s">
         <v>89</v>
@@ -2882,10 +2882,10 @@
         <v>100</v>
       </c>
       <c r="E37" t="s">
+        <v>100</v>
+      </c>
+      <c r="F37" t="s">
         <v>101</v>
-      </c>
-      <c r="F37" t="s">
-        <v>100</v>
       </c>
       <c r="G37" t="s">
         <v>101</v>
@@ -2905,10 +2905,10 @@
         <v>100</v>
       </c>
       <c r="E38" t="s">
+        <v>100</v>
+      </c>
+      <c r="F38" t="s">
         <v>101</v>
-      </c>
-      <c r="F38" t="s">
-        <v>100</v>
       </c>
       <c r="G38" t="s">
         <v>101</v>
@@ -2928,10 +2928,10 @@
         <v>100</v>
       </c>
       <c r="E39" t="s">
+        <v>100</v>
+      </c>
+      <c r="F39" t="s">
         <v>101</v>
-      </c>
-      <c r="F39" t="s">
-        <v>100</v>
       </c>
       <c r="G39" t="s">
         <v>101</v>
@@ -2951,10 +2951,10 @@
         <v>100</v>
       </c>
       <c r="E40" t="s">
+        <v>100</v>
+      </c>
+      <c r="F40" t="s">
         <v>101</v>
-      </c>
-      <c r="F40" t="s">
-        <v>100</v>
       </c>
       <c r="G40" t="s">
         <v>101</v>
@@ -2974,10 +2974,10 @@
         <v>100</v>
       </c>
       <c r="E41" t="s">
+        <v>100</v>
+      </c>
+      <c r="F41" t="s">
         <v>101</v>
-      </c>
-      <c r="F41" t="s">
-        <v>100</v>
       </c>
       <c r="G41" t="s">
         <v>101</v>
@@ -2997,10 +2997,10 @@
         <v>100</v>
       </c>
       <c r="E42" t="s">
+        <v>100</v>
+      </c>
+      <c r="F42" t="s">
         <v>101</v>
-      </c>
-      <c r="F42" t="s">
-        <v>100</v>
       </c>
       <c r="G42" t="s">
         <v>101</v>
@@ -3020,10 +3020,10 @@
         <v>100</v>
       </c>
       <c r="E43" t="s">
+        <v>100</v>
+      </c>
+      <c r="F43" t="s">
         <v>101</v>
-      </c>
-      <c r="F43" t="s">
-        <v>100</v>
       </c>
       <c r="G43" t="s">
         <v>101</v>
@@ -3043,10 +3043,10 @@
         <v>100</v>
       </c>
       <c r="E44" t="s">
+        <v>100</v>
+      </c>
+      <c r="F44" t="s">
         <v>101</v>
-      </c>
-      <c r="F44" t="s">
-        <v>100</v>
       </c>
       <c r="G44" t="s">
         <v>101</v>
@@ -3066,10 +3066,10 @@
         <v>100</v>
       </c>
       <c r="E45" t="s">
+        <v>100</v>
+      </c>
+      <c r="F45" t="s">
         <v>101</v>
-      </c>
-      <c r="F45" t="s">
-        <v>100</v>
       </c>
       <c r="G45" t="s">
         <v>101</v>
@@ -3089,10 +3089,10 @@
         <v>100</v>
       </c>
       <c r="E46" t="s">
+        <v>100</v>
+      </c>
+      <c r="F46" t="s">
         <v>101</v>
-      </c>
-      <c r="F46" t="s">
-        <v>100</v>
       </c>
       <c r="G46" t="s">
         <v>101</v>
@@ -3112,10 +3112,10 @@
         <v>100</v>
       </c>
       <c r="E47" t="s">
+        <v>100</v>
+      </c>
+      <c r="F47" t="s">
         <v>101</v>
-      </c>
-      <c r="F47" t="s">
-        <v>100</v>
       </c>
       <c r="G47" t="s">
         <v>101</v>
@@ -3641,10 +3641,10 @@
         <v>174</v>
       </c>
       <c r="E70" t="s">
+        <v>174</v>
+      </c>
+      <c r="F70" t="s">
         <v>175</v>
-      </c>
-      <c r="F70" t="s">
-        <v>174</v>
       </c>
       <c r="G70" t="s">
         <v>175</v>
@@ -3664,10 +3664,10 @@
         <v>174</v>
       </c>
       <c r="E71" t="s">
+        <v>174</v>
+      </c>
+      <c r="F71" t="s">
         <v>175</v>
-      </c>
-      <c r="F71" t="s">
-        <v>174</v>
       </c>
       <c r="G71" t="s">
         <v>175</v>
@@ -3687,10 +3687,10 @@
         <v>174</v>
       </c>
       <c r="E72" t="s">
+        <v>174</v>
+      </c>
+      <c r="F72" t="s">
         <v>175</v>
-      </c>
-      <c r="F72" t="s">
-        <v>174</v>
       </c>
       <c r="G72" t="s">
         <v>175</v>
@@ -3710,10 +3710,10 @@
         <v>174</v>
       </c>
       <c r="E73" t="s">
+        <v>174</v>
+      </c>
+      <c r="F73" t="s">
         <v>175</v>
-      </c>
-      <c r="F73" t="s">
-        <v>174</v>
       </c>
       <c r="G73" t="s">
         <v>175</v>
@@ -3733,10 +3733,10 @@
         <v>174</v>
       </c>
       <c r="E74" t="s">
+        <v>174</v>
+      </c>
+      <c r="F74" t="s">
         <v>175</v>
-      </c>
-      <c r="F74" t="s">
-        <v>174</v>
       </c>
       <c r="G74" t="s">
         <v>175</v>
@@ -3756,10 +3756,10 @@
         <v>174</v>
       </c>
       <c r="E75" t="s">
+        <v>174</v>
+      </c>
+      <c r="F75" t="s">
         <v>175</v>
-      </c>
-      <c r="F75" t="s">
-        <v>174</v>
       </c>
       <c r="G75" t="s">
         <v>175</v>
@@ -3779,10 +3779,10 @@
         <v>174</v>
       </c>
       <c r="E76" t="s">
+        <v>174</v>
+      </c>
+      <c r="F76" t="s">
         <v>175</v>
-      </c>
-      <c r="F76" t="s">
-        <v>174</v>
       </c>
       <c r="G76" t="s">
         <v>175</v>
@@ -3802,10 +3802,10 @@
         <v>174</v>
       </c>
       <c r="E77" t="s">
+        <v>174</v>
+      </c>
+      <c r="F77" t="s">
         <v>175</v>
-      </c>
-      <c r="F77" t="s">
-        <v>174</v>
       </c>
       <c r="G77" t="s">
         <v>175</v>
@@ -3825,10 +3825,10 @@
         <v>174</v>
       </c>
       <c r="E78" t="s">
+        <v>174</v>
+      </c>
+      <c r="F78" t="s">
         <v>175</v>
-      </c>
-      <c r="F78" t="s">
-        <v>174</v>
       </c>
       <c r="G78" t="s">
         <v>175</v>
@@ -3848,10 +3848,10 @@
         <v>174</v>
       </c>
       <c r="E79" t="s">
+        <v>174</v>
+      </c>
+      <c r="F79" t="s">
         <v>175</v>
-      </c>
-      <c r="F79" t="s">
-        <v>174</v>
       </c>
       <c r="G79" t="s">
         <v>175</v>
@@ -3871,10 +3871,10 @@
         <v>174</v>
       </c>
       <c r="E80" t="s">
+        <v>174</v>
+      </c>
+      <c r="F80" t="s">
         <v>175</v>
-      </c>
-      <c r="F80" t="s">
-        <v>174</v>
       </c>
       <c r="G80" t="s">
         <v>175</v>
@@ -3894,10 +3894,10 @@
         <v>198</v>
       </c>
       <c r="E81" t="s">
+        <v>198</v>
+      </c>
+      <c r="F81" t="s">
         <v>199</v>
-      </c>
-      <c r="F81" t="s">
-        <v>198</v>
       </c>
       <c r="G81" t="s">
         <v>199</v>
@@ -3917,10 +3917,10 @@
         <v>198</v>
       </c>
       <c r="E82" t="s">
+        <v>198</v>
+      </c>
+      <c r="F82" t="s">
         <v>199</v>
-      </c>
-      <c r="F82" t="s">
-        <v>198</v>
       </c>
       <c r="G82" t="s">
         <v>199</v>
@@ -3940,10 +3940,10 @@
         <v>198</v>
       </c>
       <c r="E83" t="s">
+        <v>198</v>
+      </c>
+      <c r="F83" t="s">
         <v>199</v>
-      </c>
-      <c r="F83" t="s">
-        <v>198</v>
       </c>
       <c r="G83" t="s">
         <v>199</v>
@@ -3963,10 +3963,10 @@
         <v>198</v>
       </c>
       <c r="E84" t="s">
+        <v>198</v>
+      </c>
+      <c r="F84" t="s">
         <v>199</v>
-      </c>
-      <c r="F84" t="s">
-        <v>198</v>
       </c>
       <c r="G84" t="s">
         <v>199</v>
@@ -3986,10 +3986,10 @@
         <v>198</v>
       </c>
       <c r="E85" t="s">
+        <v>198</v>
+      </c>
+      <c r="F85" t="s">
         <v>199</v>
-      </c>
-      <c r="F85" t="s">
-        <v>198</v>
       </c>
       <c r="G85" t="s">
         <v>199</v>
@@ -4009,10 +4009,10 @@
         <v>198</v>
       </c>
       <c r="E86" t="s">
+        <v>198</v>
+      </c>
+      <c r="F86" t="s">
         <v>199</v>
-      </c>
-      <c r="F86" t="s">
-        <v>198</v>
       </c>
       <c r="G86" t="s">
         <v>199</v>
@@ -4032,10 +4032,10 @@
         <v>198</v>
       </c>
       <c r="E87" t="s">
+        <v>198</v>
+      </c>
+      <c r="F87" t="s">
         <v>199</v>
-      </c>
-      <c r="F87" t="s">
-        <v>198</v>
       </c>
       <c r="G87" t="s">
         <v>199</v>
@@ -4055,10 +4055,10 @@
         <v>214</v>
       </c>
       <c r="E88" t="s">
+        <v>214</v>
+      </c>
+      <c r="F88" t="s">
         <v>215</v>
-      </c>
-      <c r="F88" t="s">
-        <v>214</v>
       </c>
       <c r="G88" t="s">
         <v>215</v>
@@ -4078,10 +4078,10 @@
         <v>214</v>
       </c>
       <c r="E89" t="s">
+        <v>214</v>
+      </c>
+      <c r="F89" t="s">
         <v>215</v>
-      </c>
-      <c r="F89" t="s">
-        <v>214</v>
       </c>
       <c r="G89" t="s">
         <v>215</v>
@@ -4101,10 +4101,10 @@
         <v>214</v>
       </c>
       <c r="E90" t="s">
+        <v>214</v>
+      </c>
+      <c r="F90" t="s">
         <v>215</v>
-      </c>
-      <c r="F90" t="s">
-        <v>214</v>
       </c>
       <c r="G90" t="s">
         <v>215</v>
@@ -4124,10 +4124,10 @@
         <v>214</v>
       </c>
       <c r="E91" t="s">
+        <v>214</v>
+      </c>
+      <c r="F91" t="s">
         <v>215</v>
-      </c>
-      <c r="F91" t="s">
-        <v>214</v>
       </c>
       <c r="G91" t="s">
         <v>215</v>
@@ -4791,10 +4791,10 @@
         <v>294</v>
       </c>
       <c r="E120" t="s">
+        <v>294</v>
+      </c>
+      <c r="F120" t="s">
         <v>295</v>
-      </c>
-      <c r="F120" t="s">
-        <v>294</v>
       </c>
       <c r="G120" t="s">
         <v>295</v>
@@ -4814,10 +4814,10 @@
         <v>294</v>
       </c>
       <c r="E121" t="s">
+        <v>294</v>
+      </c>
+      <c r="F121" t="s">
         <v>295</v>
-      </c>
-      <c r="F121" t="s">
-        <v>294</v>
       </c>
       <c r="G121" t="s">
         <v>295</v>
@@ -4837,10 +4837,10 @@
         <v>294</v>
       </c>
       <c r="E122" t="s">
+        <v>294</v>
+      </c>
+      <c r="F122" t="s">
         <v>295</v>
-      </c>
-      <c r="F122" t="s">
-        <v>294</v>
       </c>
       <c r="G122" t="s">
         <v>295</v>
@@ -4860,10 +4860,10 @@
         <v>294</v>
       </c>
       <c r="E123" t="s">
+        <v>294</v>
+      </c>
+      <c r="F123" t="s">
         <v>295</v>
-      </c>
-      <c r="F123" t="s">
-        <v>294</v>
       </c>
       <c r="G123" t="s">
         <v>295</v>
@@ -4883,10 +4883,10 @@
         <v>294</v>
       </c>
       <c r="E124" t="s">
+        <v>294</v>
+      </c>
+      <c r="F124" t="s">
         <v>295</v>
-      </c>
-      <c r="F124" t="s">
-        <v>294</v>
       </c>
       <c r="G124" t="s">
         <v>295</v>
@@ -4906,10 +4906,10 @@
         <v>294</v>
       </c>
       <c r="E125" t="s">
+        <v>294</v>
+      </c>
+      <c r="F125" t="s">
         <v>295</v>
-      </c>
-      <c r="F125" t="s">
-        <v>294</v>
       </c>
       <c r="G125" t="s">
         <v>295</v>
@@ -4929,10 +4929,10 @@
         <v>308</v>
       </c>
       <c r="E126" t="s">
+        <v>308</v>
+      </c>
+      <c r="F126" t="s">
         <v>309</v>
-      </c>
-      <c r="F126" t="s">
-        <v>308</v>
       </c>
       <c r="G126" t="s">
         <v>309</v>
@@ -4952,10 +4952,10 @@
         <v>308</v>
       </c>
       <c r="E127" t="s">
+        <v>308</v>
+      </c>
+      <c r="F127" t="s">
         <v>309</v>
-      </c>
-      <c r="F127" t="s">
-        <v>308</v>
       </c>
       <c r="G127" t="s">
         <v>309</v>
@@ -4975,10 +4975,10 @@
         <v>308</v>
       </c>
       <c r="E128" t="s">
+        <v>308</v>
+      </c>
+      <c r="F128" t="s">
         <v>309</v>
-      </c>
-      <c r="F128" t="s">
-        <v>308</v>
       </c>
       <c r="G128" t="s">
         <v>309</v>
@@ -4998,10 +4998,10 @@
         <v>308</v>
       </c>
       <c r="E129" t="s">
+        <v>308</v>
+      </c>
+      <c r="F129" t="s">
         <v>309</v>
-      </c>
-      <c r="F129" t="s">
-        <v>308</v>
       </c>
       <c r="G129" t="s">
         <v>309</v>
@@ -6378,10 +6378,10 @@
         <v>452</v>
       </c>
       <c r="E189" t="s">
+        <v>452</v>
+      </c>
+      <c r="F189" t="s">
         <v>453</v>
-      </c>
-      <c r="F189" t="s">
-        <v>452</v>
       </c>
       <c r="G189" t="s">
         <v>453</v>
@@ -6401,10 +6401,10 @@
         <v>452</v>
       </c>
       <c r="E190" t="s">
+        <v>452</v>
+      </c>
+      <c r="F190" t="s">
         <v>453</v>
-      </c>
-      <c r="F190" t="s">
-        <v>452</v>
       </c>
       <c r="G190" t="s">
         <v>453</v>
@@ -6424,10 +6424,10 @@
         <v>452</v>
       </c>
       <c r="E191" t="s">
+        <v>452</v>
+      </c>
+      <c r="F191" t="s">
         <v>453</v>
-      </c>
-      <c r="F191" t="s">
-        <v>452</v>
       </c>
       <c r="G191" t="s">
         <v>453</v>
@@ -6447,10 +6447,10 @@
         <v>452</v>
       </c>
       <c r="E192" t="s">
+        <v>452</v>
+      </c>
+      <c r="F192" t="s">
         <v>453</v>
-      </c>
-      <c r="F192" t="s">
-        <v>452</v>
       </c>
       <c r="G192" t="s">
         <v>453</v>
@@ -6470,10 +6470,10 @@
         <v>452</v>
       </c>
       <c r="E193" t="s">
+        <v>452</v>
+      </c>
+      <c r="F193" t="s">
         <v>453</v>
-      </c>
-      <c r="F193" t="s">
-        <v>452</v>
       </c>
       <c r="G193" t="s">
         <v>453</v>
@@ -6493,10 +6493,10 @@
         <v>452</v>
       </c>
       <c r="E194" t="s">
+        <v>452</v>
+      </c>
+      <c r="F194" t="s">
         <v>453</v>
-      </c>
-      <c r="F194" t="s">
-        <v>452</v>
       </c>
       <c r="G194" t="s">
         <v>453</v>
@@ -6516,10 +6516,10 @@
         <v>466</v>
       </c>
       <c r="E195" t="s">
+        <v>466</v>
+      </c>
+      <c r="F195" t="s">
         <v>467</v>
-      </c>
-      <c r="F195" t="s">
-        <v>466</v>
       </c>
       <c r="G195" t="s">
         <v>467</v>
@@ -6539,10 +6539,10 @@
         <v>470</v>
       </c>
       <c r="E196" t="s">
+        <v>470</v>
+      </c>
+      <c r="F196" t="s">
         <v>471</v>
-      </c>
-      <c r="F196" t="s">
-        <v>470</v>
       </c>
       <c r="G196" t="s">
         <v>471</v>
@@ -6562,10 +6562,10 @@
         <v>470</v>
       </c>
       <c r="E197" t="s">
+        <v>470</v>
+      </c>
+      <c r="F197" t="s">
         <v>471</v>
-      </c>
-      <c r="F197" t="s">
-        <v>470</v>
       </c>
       <c r="G197" t="s">
         <v>471</v>
@@ -6585,10 +6585,10 @@
         <v>470</v>
       </c>
       <c r="E198" t="s">
+        <v>470</v>
+      </c>
+      <c r="F198" t="s">
         <v>471</v>
-      </c>
-      <c r="F198" t="s">
-        <v>470</v>
       </c>
       <c r="G198" t="s">
         <v>471</v>
@@ -6608,10 +6608,10 @@
         <v>470</v>
       </c>
       <c r="E199" t="s">
+        <v>470</v>
+      </c>
+      <c r="F199" t="s">
         <v>471</v>
-      </c>
-      <c r="F199" t="s">
-        <v>470</v>
       </c>
       <c r="G199" t="s">
         <v>471</v>
@@ -6631,10 +6631,10 @@
         <v>470</v>
       </c>
       <c r="E200" t="s">
+        <v>470</v>
+      </c>
+      <c r="F200" t="s">
         <v>471</v>
-      </c>
-      <c r="F200" t="s">
-        <v>470</v>
       </c>
       <c r="G200" t="s">
         <v>471</v>
@@ -6654,10 +6654,10 @@
         <v>470</v>
       </c>
       <c r="E201" t="s">
+        <v>470</v>
+      </c>
+      <c r="F201" t="s">
         <v>471</v>
-      </c>
-      <c r="F201" t="s">
-        <v>470</v>
       </c>
       <c r="G201" t="s">
         <v>471</v>
@@ -6677,10 +6677,10 @@
         <v>484</v>
       </c>
       <c r="E202" t="s">
+        <v>484</v>
+      </c>
+      <c r="F202" t="s">
         <v>485</v>
-      </c>
-      <c r="F202" t="s">
-        <v>484</v>
       </c>
       <c r="G202" t="s">
         <v>485</v>
@@ -6700,10 +6700,10 @@
         <v>484</v>
       </c>
       <c r="E203" t="s">
+        <v>484</v>
+      </c>
+      <c r="F203" t="s">
         <v>485</v>
-      </c>
-      <c r="F203" t="s">
-        <v>484</v>
       </c>
       <c r="G203" t="s">
         <v>485</v>
@@ -6723,10 +6723,10 @@
         <v>484</v>
       </c>
       <c r="E204" t="s">
+        <v>484</v>
+      </c>
+      <c r="F204" t="s">
         <v>485</v>
-      </c>
-      <c r="F204" t="s">
-        <v>484</v>
       </c>
       <c r="G204" t="s">
         <v>485</v>
@@ -6746,10 +6746,10 @@
         <v>484</v>
       </c>
       <c r="E205" t="s">
+        <v>484</v>
+      </c>
+      <c r="F205" t="s">
         <v>485</v>
-      </c>
-      <c r="F205" t="s">
-        <v>484</v>
       </c>
       <c r="G205" t="s">
         <v>485</v>
@@ -6769,10 +6769,10 @@
         <v>484</v>
       </c>
       <c r="E206" t="s">
+        <v>484</v>
+      </c>
+      <c r="F206" t="s">
         <v>485</v>
-      </c>
-      <c r="F206" t="s">
-        <v>484</v>
       </c>
       <c r="G206" t="s">
         <v>485</v>
@@ -6792,10 +6792,10 @@
         <v>484</v>
       </c>
       <c r="E207" t="s">
+        <v>484</v>
+      </c>
+      <c r="F207" t="s">
         <v>485</v>
-      </c>
-      <c r="F207" t="s">
-        <v>484</v>
       </c>
       <c r="G207" t="s">
         <v>485</v>
@@ -6815,10 +6815,10 @@
         <v>484</v>
       </c>
       <c r="E208" t="s">
+        <v>484</v>
+      </c>
+      <c r="F208" t="s">
         <v>485</v>
-      </c>
-      <c r="F208" t="s">
-        <v>484</v>
       </c>
       <c r="G208" t="s">
         <v>485</v>
@@ -6838,10 +6838,10 @@
         <v>484</v>
       </c>
       <c r="E209" t="s">
+        <v>484</v>
+      </c>
+      <c r="F209" t="s">
         <v>485</v>
-      </c>
-      <c r="F209" t="s">
-        <v>484</v>
       </c>
       <c r="G209" t="s">
         <v>485</v>
@@ -6861,10 +6861,10 @@
         <v>484</v>
       </c>
       <c r="E210" t="s">
+        <v>484</v>
+      </c>
+      <c r="F210" t="s">
         <v>485</v>
-      </c>
-      <c r="F210" t="s">
-        <v>484</v>
       </c>
       <c r="G210" t="s">
         <v>485</v>
@@ -6884,10 +6884,10 @@
         <v>484</v>
       </c>
       <c r="E211" t="s">
+        <v>484</v>
+      </c>
+      <c r="F211" t="s">
         <v>485</v>
-      </c>
-      <c r="F211" t="s">
-        <v>484</v>
       </c>
       <c r="G211" t="s">
         <v>485</v>
@@ -6907,10 +6907,10 @@
         <v>506</v>
       </c>
       <c r="E212" t="s">
+        <v>506</v>
+      </c>
+      <c r="F212" t="s">
         <v>507</v>
-      </c>
-      <c r="F212" t="s">
-        <v>506</v>
       </c>
       <c r="G212" t="s">
         <v>507</v>
@@ -6930,10 +6930,10 @@
         <v>510</v>
       </c>
       <c r="E213" t="s">
+        <v>510</v>
+      </c>
+      <c r="F213" t="s">
         <v>511</v>
-      </c>
-      <c r="F213" t="s">
-        <v>510</v>
       </c>
       <c r="G213" t="s">
         <v>511</v>
@@ -6953,10 +6953,10 @@
         <v>514</v>
       </c>
       <c r="E214" t="s">
+        <v>514</v>
+      </c>
+      <c r="F214" t="s">
         <v>515</v>
-      </c>
-      <c r="F214" t="s">
-        <v>514</v>
       </c>
       <c r="G214" t="s">
         <v>515</v>
@@ -6976,10 +6976,10 @@
         <v>514</v>
       </c>
       <c r="E215" t="s">
+        <v>514</v>
+      </c>
+      <c r="F215" t="s">
         <v>515</v>
-      </c>
-      <c r="F215" t="s">
-        <v>514</v>
       </c>
       <c r="G215" t="s">
         <v>515</v>
@@ -6999,10 +6999,10 @@
         <v>520</v>
       </c>
       <c r="E216" t="s">
+        <v>520</v>
+      </c>
+      <c r="F216" t="s">
         <v>521</v>
-      </c>
-      <c r="F216" t="s">
-        <v>520</v>
       </c>
       <c r="G216" t="s">
         <v>521</v>
@@ -7022,10 +7022,10 @@
         <v>520</v>
       </c>
       <c r="E217" t="s">
+        <v>520</v>
+      </c>
+      <c r="F217" t="s">
         <v>521</v>
-      </c>
-      <c r="F217" t="s">
-        <v>520</v>
       </c>
       <c r="G217" t="s">
         <v>521</v>
@@ -7045,10 +7045,10 @@
         <v>520</v>
       </c>
       <c r="E218" t="s">
+        <v>520</v>
+      </c>
+      <c r="F218" t="s">
         <v>521</v>
-      </c>
-      <c r="F218" t="s">
-        <v>520</v>
       </c>
       <c r="G218" t="s">
         <v>521</v>
@@ -7068,10 +7068,10 @@
         <v>520</v>
       </c>
       <c r="E219" t="s">
+        <v>520</v>
+      </c>
+      <c r="F219" t="s">
         <v>521</v>
-      </c>
-      <c r="F219" t="s">
-        <v>520</v>
       </c>
       <c r="G219" t="s">
         <v>521</v>
@@ -7091,10 +7091,10 @@
         <v>520</v>
       </c>
       <c r="E220" t="s">
+        <v>520</v>
+      </c>
+      <c r="F220" t="s">
         <v>521</v>
-      </c>
-      <c r="F220" t="s">
-        <v>520</v>
       </c>
       <c r="G220" t="s">
         <v>521</v>
@@ -7114,10 +7114,10 @@
         <v>520</v>
       </c>
       <c r="E221" t="s">
+        <v>520</v>
+      </c>
+      <c r="F221" t="s">
         <v>521</v>
-      </c>
-      <c r="F221" t="s">
-        <v>520</v>
       </c>
       <c r="G221" t="s">
         <v>521</v>
@@ -7137,10 +7137,10 @@
         <v>520</v>
       </c>
       <c r="E222" t="s">
+        <v>520</v>
+      </c>
+      <c r="F222" t="s">
         <v>521</v>
-      </c>
-      <c r="F222" t="s">
-        <v>520</v>
       </c>
       <c r="G222" t="s">
         <v>521</v>
@@ -7160,10 +7160,10 @@
         <v>536</v>
       </c>
       <c r="E223" t="s">
+        <v>536</v>
+      </c>
+      <c r="F223" t="s">
         <v>537</v>
-      </c>
-      <c r="F223" t="s">
-        <v>536</v>
       </c>
       <c r="G223" t="s">
         <v>537</v>
@@ -7183,10 +7183,10 @@
         <v>536</v>
       </c>
       <c r="E224" t="s">
+        <v>536</v>
+      </c>
+      <c r="F224" t="s">
         <v>537</v>
-      </c>
-      <c r="F224" t="s">
-        <v>536</v>
       </c>
       <c r="G224" t="s">
         <v>537</v>
@@ -7206,10 +7206,10 @@
         <v>536</v>
       </c>
       <c r="E225" t="s">
+        <v>536</v>
+      </c>
+      <c r="F225" t="s">
         <v>537</v>
-      </c>
-      <c r="F225" t="s">
-        <v>536</v>
       </c>
       <c r="G225" t="s">
         <v>537</v>
@@ -7229,10 +7229,10 @@
         <v>544</v>
       </c>
       <c r="E226" t="s">
+        <v>544</v>
+      </c>
+      <c r="F226" t="s">
         <v>545</v>
-      </c>
-      <c r="F226" t="s">
-        <v>544</v>
       </c>
       <c r="G226" t="s">
         <v>545</v>
@@ -7252,10 +7252,10 @@
         <v>548</v>
       </c>
       <c r="E227" t="s">
+        <v>548</v>
+      </c>
+      <c r="F227" t="s">
         <v>549</v>
-      </c>
-      <c r="F227" t="s">
-        <v>548</v>
       </c>
       <c r="G227" t="s">
         <v>549</v>
@@ -7275,10 +7275,10 @@
         <v>552</v>
       </c>
       <c r="E228" t="s">
+        <v>552</v>
+      </c>
+      <c r="F228" t="s">
         <v>553</v>
-      </c>
-      <c r="F228" t="s">
-        <v>552</v>
       </c>
       <c r="G228" t="s">
         <v>553</v>
@@ -7298,10 +7298,10 @@
         <v>556</v>
       </c>
       <c r="E229" t="s">
+        <v>556</v>
+      </c>
+      <c r="F229" t="s">
         <v>557</v>
-      </c>
-      <c r="F229" t="s">
-        <v>556</v>
       </c>
       <c r="G229" t="s">
         <v>557</v>
@@ -7321,10 +7321,10 @@
         <v>560</v>
       </c>
       <c r="E230" t="s">
+        <v>560</v>
+      </c>
+      <c r="F230" t="s">
         <v>561</v>
-      </c>
-      <c r="F230" t="s">
-        <v>560</v>
       </c>
       <c r="G230" t="s">
         <v>561</v>
@@ -7344,10 +7344,10 @@
         <v>560</v>
       </c>
       <c r="E231" t="s">
+        <v>560</v>
+      </c>
+      <c r="F231" t="s">
         <v>561</v>
-      </c>
-      <c r="F231" t="s">
-        <v>560</v>
       </c>
       <c r="G231" t="s">
         <v>561</v>

--- a/api/xlsx/en/SectorGroup.xlsx
+++ b/api/xlsx/en/SectorGroup.xlsx
@@ -25,18 +25,18 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:category-name</t>
+  </si>
+  <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
     <t>codeforiati:group-name</t>
   </si>
   <si>
-    <t>codeforiati:category-name</t>
-  </si>
-  <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -46,18 +46,18 @@
     <t>active</t>
   </si>
   <si>
+    <t>Education, Level Unspecified</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
     <t>Education</t>
   </si>
   <si>
-    <t>Education, Level Unspecified</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -148,18 +148,18 @@
     <t>Health policy and administrative management</t>
   </si>
   <si>
+    <t>Health, General</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
     <t>Health</t>
   </si>
   <si>
-    <t>Health, General</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -388,18 +388,18 @@
     <t>Public sector policy and administrative management</t>
   </si>
   <si>
+    <t>Government &amp; Civil Society-general</t>
+  </si>
+  <si>
+    <t>151</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
     <t>Government &amp; Civil Society</t>
   </si>
   <si>
-    <t>Government &amp; Civil Society-general</t>
-  </si>
-  <si>
-    <t>151</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -688,18 +688,18 @@
     <t>Energy policy and administrative management</t>
   </si>
   <si>
+    <t>Energy Policy</t>
+  </si>
+  <si>
+    <t>231</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
     <t>Energy</t>
   </si>
   <si>
-    <t>Energy Policy</t>
-  </si>
-  <si>
-    <t>231</t>
-  </si>
-  <si>
-    <t>230</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -970,18 +970,18 @@
     <t>Agricultural policy and administrative management</t>
   </si>
   <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
+    <t>311</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
     <t>Agriculture, Forestry, Fishing</t>
   </si>
   <si>
-    <t>Agriculture</t>
-  </si>
-  <si>
-    <t>311</t>
-  </si>
-  <si>
-    <t>310</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1168,16 +1168,16 @@
     <t>Industrial policy and administrative management</t>
   </si>
   <si>
+    <t>Industry</t>
+  </si>
+  <si>
+    <t>321</t>
+  </si>
+  <si>
+    <t>320</t>
+  </si>
+  <si>
     <t>Industry, Mining, Construction</t>
-  </si>
-  <si>
-    <t>Industry</t>
-  </si>
-  <si>
-    <t>321</t>
-  </si>
-  <si>
-    <t>320</t>
   </si>
   <si>
     <t>32120</t>
@@ -2166,13 +2166,13 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F6" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G6" t="s">
         <v>13</v>
@@ -2189,13 +2189,13 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F7" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G7" t="s">
         <v>13</v>
@@ -2212,13 +2212,13 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F8" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G8" t="s">
         <v>13</v>
@@ -2235,13 +2235,13 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F9" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G9" t="s">
         <v>13</v>
@@ -2258,13 +2258,13 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F10" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="G10" t="s">
         <v>13</v>
@@ -2281,13 +2281,13 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F11" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="G11" t="s">
         <v>13</v>
@@ -2304,13 +2304,13 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F12" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="G12" t="s">
         <v>13</v>
@@ -2327,13 +2327,13 @@
         <v>9</v>
       </c>
       <c r="D13" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F13" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="G13" t="s">
         <v>13</v>
@@ -2442,13 +2442,13 @@
         <v>9</v>
       </c>
       <c r="D18" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E18" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F18" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G18" t="s">
         <v>47</v>
@@ -2465,13 +2465,13 @@
         <v>9</v>
       </c>
       <c r="D19" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F19" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G19" t="s">
         <v>47</v>
@@ -2488,13 +2488,13 @@
         <v>9</v>
       </c>
       <c r="D20" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E20" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F20" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G20" t="s">
         <v>47</v>
@@ -2511,13 +2511,13 @@
         <v>9</v>
       </c>
       <c r="D21" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E21" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F21" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G21" t="s">
         <v>47</v>
@@ -2534,13 +2534,13 @@
         <v>9</v>
       </c>
       <c r="D22" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E22" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F22" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G22" t="s">
         <v>47</v>
@@ -2557,13 +2557,13 @@
         <v>9</v>
       </c>
       <c r="D23" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E23" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F23" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G23" t="s">
         <v>47</v>
@@ -2580,13 +2580,13 @@
         <v>9</v>
       </c>
       <c r="D24" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F24" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G24" t="s">
         <v>47</v>
@@ -2603,13 +2603,13 @@
         <v>9</v>
       </c>
       <c r="D25" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E25" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F25" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G25" t="s">
         <v>47</v>
@@ -2626,13 +2626,13 @@
         <v>9</v>
       </c>
       <c r="D26" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E26" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F26" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="G26" t="s">
         <v>47</v>
@@ -2649,13 +2649,13 @@
         <v>9</v>
       </c>
       <c r="D27" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E27" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F27" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="G27" t="s">
         <v>47</v>
@@ -2672,13 +2672,13 @@
         <v>9</v>
       </c>
       <c r="D28" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E28" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F28" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="G28" t="s">
         <v>47</v>
@@ -2695,13 +2695,13 @@
         <v>9</v>
       </c>
       <c r="D29" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E29" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F29" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="G29" t="s">
         <v>47</v>
@@ -2718,13 +2718,13 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E30" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F30" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="G30" t="s">
         <v>47</v>
@@ -2741,13 +2741,13 @@
         <v>9</v>
       </c>
       <c r="D31" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E31" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F31" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="G31" t="s">
         <v>47</v>
@@ -2767,13 +2767,13 @@
         <v>88</v>
       </c>
       <c r="E32" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F32" t="s">
         <v>89</v>
       </c>
       <c r="G32" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2790,13 +2790,13 @@
         <v>88</v>
       </c>
       <c r="E33" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F33" t="s">
         <v>89</v>
       </c>
       <c r="G33" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2813,13 +2813,13 @@
         <v>88</v>
       </c>
       <c r="E34" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F34" t="s">
         <v>89</v>
       </c>
       <c r="G34" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2836,13 +2836,13 @@
         <v>88</v>
       </c>
       <c r="E35" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F35" t="s">
         <v>89</v>
       </c>
       <c r="G35" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2859,13 +2859,13 @@
         <v>88</v>
       </c>
       <c r="E36" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F36" t="s">
         <v>89</v>
       </c>
       <c r="G36" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2882,13 +2882,13 @@
         <v>100</v>
       </c>
       <c r="E37" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F37" t="s">
         <v>101</v>
       </c>
       <c r="G37" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2905,13 +2905,13 @@
         <v>100</v>
       </c>
       <c r="E38" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F38" t="s">
         <v>101</v>
       </c>
       <c r="G38" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2928,13 +2928,13 @@
         <v>100</v>
       </c>
       <c r="E39" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F39" t="s">
         <v>101</v>
       </c>
       <c r="G39" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2951,13 +2951,13 @@
         <v>100</v>
       </c>
       <c r="E40" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F40" t="s">
         <v>101</v>
       </c>
       <c r="G40" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2974,13 +2974,13 @@
         <v>100</v>
       </c>
       <c r="E41" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F41" t="s">
         <v>101</v>
       </c>
       <c r="G41" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2997,13 +2997,13 @@
         <v>100</v>
       </c>
       <c r="E42" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F42" t="s">
         <v>101</v>
       </c>
       <c r="G42" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3020,13 +3020,13 @@
         <v>100</v>
       </c>
       <c r="E43" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F43" t="s">
         <v>101</v>
       </c>
       <c r="G43" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3043,13 +3043,13 @@
         <v>100</v>
       </c>
       <c r="E44" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F44" t="s">
         <v>101</v>
       </c>
       <c r="G44" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3066,13 +3066,13 @@
         <v>100</v>
       </c>
       <c r="E45" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F45" t="s">
         <v>101</v>
       </c>
       <c r="G45" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3089,13 +3089,13 @@
         <v>100</v>
       </c>
       <c r="E46" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F46" t="s">
         <v>101</v>
       </c>
       <c r="G46" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3112,13 +3112,13 @@
         <v>100</v>
       </c>
       <c r="E47" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F47" t="s">
         <v>101</v>
       </c>
       <c r="G47" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3500,13 +3500,13 @@
         <v>9</v>
       </c>
       <c r="D64" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E64" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F64" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="G64" t="s">
         <v>127</v>
@@ -3523,13 +3523,13 @@
         <v>9</v>
       </c>
       <c r="D65" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E65" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F65" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="G65" t="s">
         <v>127</v>
@@ -3546,13 +3546,13 @@
         <v>9</v>
       </c>
       <c r="D66" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E66" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F66" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="G66" t="s">
         <v>127</v>
@@ -3569,13 +3569,13 @@
         <v>9</v>
       </c>
       <c r="D67" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E67" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F67" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="G67" t="s">
         <v>127</v>
@@ -3592,13 +3592,13 @@
         <v>9</v>
       </c>
       <c r="D68" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E68" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F68" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="G68" t="s">
         <v>127</v>
@@ -3615,13 +3615,13 @@
         <v>9</v>
       </c>
       <c r="D69" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E69" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F69" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="G69" t="s">
         <v>127</v>
@@ -3641,13 +3641,13 @@
         <v>174</v>
       </c>
       <c r="E70" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F70" t="s">
         <v>175</v>
       </c>
       <c r="G70" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3664,13 +3664,13 @@
         <v>174</v>
       </c>
       <c r="E71" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F71" t="s">
         <v>175</v>
       </c>
       <c r="G71" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3687,13 +3687,13 @@
         <v>174</v>
       </c>
       <c r="E72" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F72" t="s">
         <v>175</v>
       </c>
       <c r="G72" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3710,13 +3710,13 @@
         <v>174</v>
       </c>
       <c r="E73" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F73" t="s">
         <v>175</v>
       </c>
       <c r="G73" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3733,13 +3733,13 @@
         <v>174</v>
       </c>
       <c r="E74" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F74" t="s">
         <v>175</v>
       </c>
       <c r="G74" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3756,13 +3756,13 @@
         <v>174</v>
       </c>
       <c r="E75" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F75" t="s">
         <v>175</v>
       </c>
       <c r="G75" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3779,13 +3779,13 @@
         <v>174</v>
       </c>
       <c r="E76" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F76" t="s">
         <v>175</v>
       </c>
       <c r="G76" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3802,13 +3802,13 @@
         <v>174</v>
       </c>
       <c r="E77" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F77" t="s">
         <v>175</v>
       </c>
       <c r="G77" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3825,13 +3825,13 @@
         <v>174</v>
       </c>
       <c r="E78" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F78" t="s">
         <v>175</v>
       </c>
       <c r="G78" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3848,13 +3848,13 @@
         <v>174</v>
       </c>
       <c r="E79" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F79" t="s">
         <v>175</v>
       </c>
       <c r="G79" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3871,13 +3871,13 @@
         <v>174</v>
       </c>
       <c r="E80" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F80" t="s">
         <v>175</v>
       </c>
       <c r="G80" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3894,13 +3894,13 @@
         <v>198</v>
       </c>
       <c r="E81" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F81" t="s">
         <v>199</v>
       </c>
       <c r="G81" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3917,13 +3917,13 @@
         <v>198</v>
       </c>
       <c r="E82" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F82" t="s">
         <v>199</v>
       </c>
       <c r="G82" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3940,13 +3940,13 @@
         <v>198</v>
       </c>
       <c r="E83" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F83" t="s">
         <v>199</v>
       </c>
       <c r="G83" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3963,13 +3963,13 @@
         <v>198</v>
       </c>
       <c r="E84" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F84" t="s">
         <v>199</v>
       </c>
       <c r="G84" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3986,13 +3986,13 @@
         <v>198</v>
       </c>
       <c r="E85" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F85" t="s">
         <v>199</v>
       </c>
       <c r="G85" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4009,13 +4009,13 @@
         <v>198</v>
       </c>
       <c r="E86" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F86" t="s">
         <v>199</v>
       </c>
       <c r="G86" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4032,13 +4032,13 @@
         <v>198</v>
       </c>
       <c r="E87" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F87" t="s">
         <v>199</v>
       </c>
       <c r="G87" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4055,13 +4055,13 @@
         <v>214</v>
       </c>
       <c r="E88" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F88" t="s">
         <v>215</v>
       </c>
       <c r="G88" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4078,13 +4078,13 @@
         <v>214</v>
       </c>
       <c r="E89" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F89" t="s">
         <v>215</v>
       </c>
       <c r="G89" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4101,13 +4101,13 @@
         <v>214</v>
       </c>
       <c r="E90" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F90" t="s">
         <v>215</v>
       </c>
       <c r="G90" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4124,13 +4124,13 @@
         <v>214</v>
       </c>
       <c r="E91" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F91" t="s">
         <v>215</v>
       </c>
       <c r="G91" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4236,13 +4236,13 @@
         <v>9</v>
       </c>
       <c r="D96" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E96" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F96" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G96" t="s">
         <v>227</v>
@@ -4259,13 +4259,13 @@
         <v>9</v>
       </c>
       <c r="D97" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E97" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F97" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G97" t="s">
         <v>227</v>
@@ -4282,13 +4282,13 @@
         <v>9</v>
       </c>
       <c r="D98" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E98" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F98" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G98" t="s">
         <v>227</v>
@@ -4305,13 +4305,13 @@
         <v>9</v>
       </c>
       <c r="D99" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E99" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F99" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G99" t="s">
         <v>227</v>
@@ -4328,13 +4328,13 @@
         <v>9</v>
       </c>
       <c r="D100" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E100" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F100" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G100" t="s">
         <v>227</v>
@@ -4351,13 +4351,13 @@
         <v>9</v>
       </c>
       <c r="D101" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E101" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F101" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G101" t="s">
         <v>227</v>
@@ -4374,13 +4374,13 @@
         <v>9</v>
       </c>
       <c r="D102" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E102" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F102" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G102" t="s">
         <v>227</v>
@@ -4397,13 +4397,13 @@
         <v>9</v>
       </c>
       <c r="D103" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E103" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F103" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G103" t="s">
         <v>227</v>
@@ -4420,13 +4420,13 @@
         <v>9</v>
       </c>
       <c r="D104" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E104" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F104" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G104" t="s">
         <v>227</v>
@@ -4443,13 +4443,13 @@
         <v>9</v>
       </c>
       <c r="D105" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E105" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F105" t="s">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="G105" t="s">
         <v>227</v>
@@ -4466,13 +4466,13 @@
         <v>9</v>
       </c>
       <c r="D106" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E106" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F106" t="s">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="G106" t="s">
         <v>227</v>
@@ -4489,13 +4489,13 @@
         <v>9</v>
       </c>
       <c r="D107" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E107" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F107" t="s">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="G107" t="s">
         <v>227</v>
@@ -4512,13 +4512,13 @@
         <v>9</v>
       </c>
       <c r="D108" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E108" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F108" t="s">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="G108" t="s">
         <v>227</v>
@@ -4535,13 +4535,13 @@
         <v>9</v>
       </c>
       <c r="D109" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E109" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F109" t="s">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="G109" t="s">
         <v>227</v>
@@ -4558,13 +4558,13 @@
         <v>9</v>
       </c>
       <c r="D110" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E110" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F110" t="s">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="G110" t="s">
         <v>227</v>
@@ -4581,13 +4581,13 @@
         <v>9</v>
       </c>
       <c r="D111" t="s">
-        <v>224</v>
+        <v>270</v>
       </c>
       <c r="E111" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F111" t="s">
-        <v>271</v>
+        <v>226</v>
       </c>
       <c r="G111" t="s">
         <v>227</v>
@@ -4604,13 +4604,13 @@
         <v>9</v>
       </c>
       <c r="D112" t="s">
-        <v>224</v>
+        <v>274</v>
       </c>
       <c r="E112" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F112" t="s">
-        <v>275</v>
+        <v>226</v>
       </c>
       <c r="G112" t="s">
         <v>227</v>
@@ -4627,13 +4627,13 @@
         <v>9</v>
       </c>
       <c r="D113" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E113" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F113" t="s">
-        <v>279</v>
+        <v>226</v>
       </c>
       <c r="G113" t="s">
         <v>227</v>
@@ -4650,13 +4650,13 @@
         <v>9</v>
       </c>
       <c r="D114" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E114" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F114" t="s">
-        <v>279</v>
+        <v>226</v>
       </c>
       <c r="G114" t="s">
         <v>227</v>
@@ -4673,13 +4673,13 @@
         <v>9</v>
       </c>
       <c r="D115" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E115" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F115" t="s">
-        <v>279</v>
+        <v>226</v>
       </c>
       <c r="G115" t="s">
         <v>227</v>
@@ -4696,13 +4696,13 @@
         <v>9</v>
       </c>
       <c r="D116" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E116" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F116" t="s">
-        <v>279</v>
+        <v>226</v>
       </c>
       <c r="G116" t="s">
         <v>227</v>
@@ -4719,13 +4719,13 @@
         <v>9</v>
       </c>
       <c r="D117" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E117" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F117" t="s">
-        <v>279</v>
+        <v>226</v>
       </c>
       <c r="G117" t="s">
         <v>227</v>
@@ -4742,13 +4742,13 @@
         <v>9</v>
       </c>
       <c r="D118" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E118" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F118" t="s">
-        <v>279</v>
+        <v>226</v>
       </c>
       <c r="G118" t="s">
         <v>227</v>
@@ -4765,13 +4765,13 @@
         <v>9</v>
       </c>
       <c r="D119" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E119" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F119" t="s">
-        <v>279</v>
+        <v>226</v>
       </c>
       <c r="G119" t="s">
         <v>227</v>
@@ -4791,13 +4791,13 @@
         <v>294</v>
       </c>
       <c r="E120" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F120" t="s">
         <v>295</v>
       </c>
       <c r="G120" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4814,13 +4814,13 @@
         <v>294</v>
       </c>
       <c r="E121" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F121" t="s">
         <v>295</v>
       </c>
       <c r="G121" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4837,13 +4837,13 @@
         <v>294</v>
       </c>
       <c r="E122" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F122" t="s">
         <v>295</v>
       </c>
       <c r="G122" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4860,13 +4860,13 @@
         <v>294</v>
       </c>
       <c r="E123" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F123" t="s">
         <v>295</v>
       </c>
       <c r="G123" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4883,13 +4883,13 @@
         <v>294</v>
       </c>
       <c r="E124" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F124" t="s">
         <v>295</v>
       </c>
       <c r="G124" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4906,13 +4906,13 @@
         <v>294</v>
       </c>
       <c r="E125" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F125" t="s">
         <v>295</v>
       </c>
       <c r="G125" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4929,13 +4929,13 @@
         <v>308</v>
       </c>
       <c r="E126" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F126" t="s">
         <v>309</v>
       </c>
       <c r="G126" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4952,13 +4952,13 @@
         <v>308</v>
       </c>
       <c r="E127" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F127" t="s">
         <v>309</v>
       </c>
       <c r="G127" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4975,13 +4975,13 @@
         <v>308</v>
       </c>
       <c r="E128" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F128" t="s">
         <v>309</v>
       </c>
       <c r="G128" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4998,13 +4998,13 @@
         <v>308</v>
       </c>
       <c r="E129" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F129" t="s">
         <v>309</v>
       </c>
       <c r="G129" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -5432,13 +5432,13 @@
         <v>9</v>
       </c>
       <c r="D148" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E148" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F148" t="s">
-        <v>359</v>
+        <v>320</v>
       </c>
       <c r="G148" t="s">
         <v>321</v>
@@ -5455,13 +5455,13 @@
         <v>9</v>
       </c>
       <c r="D149" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E149" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F149" t="s">
-        <v>359</v>
+        <v>320</v>
       </c>
       <c r="G149" t="s">
         <v>321</v>
@@ -5478,13 +5478,13 @@
         <v>9</v>
       </c>
       <c r="D150" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E150" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F150" t="s">
-        <v>359</v>
+        <v>320</v>
       </c>
       <c r="G150" t="s">
         <v>321</v>
@@ -5501,13 +5501,13 @@
         <v>9</v>
       </c>
       <c r="D151" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E151" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F151" t="s">
-        <v>359</v>
+        <v>320</v>
       </c>
       <c r="G151" t="s">
         <v>321</v>
@@ -5524,13 +5524,13 @@
         <v>9</v>
       </c>
       <c r="D152" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E152" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F152" t="s">
-        <v>359</v>
+        <v>320</v>
       </c>
       <c r="G152" t="s">
         <v>321</v>
@@ -5547,13 +5547,13 @@
         <v>9</v>
       </c>
       <c r="D153" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E153" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F153" t="s">
-        <v>359</v>
+        <v>320</v>
       </c>
       <c r="G153" t="s">
         <v>321</v>
@@ -5570,13 +5570,13 @@
         <v>9</v>
       </c>
       <c r="D154" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="E154" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F154" t="s">
-        <v>373</v>
+        <v>320</v>
       </c>
       <c r="G154" t="s">
         <v>321</v>
@@ -5593,13 +5593,13 @@
         <v>9</v>
       </c>
       <c r="D155" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="E155" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F155" t="s">
-        <v>373</v>
+        <v>320</v>
       </c>
       <c r="G155" t="s">
         <v>321</v>
@@ -5616,13 +5616,13 @@
         <v>9</v>
       </c>
       <c r="D156" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="E156" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F156" t="s">
-        <v>373</v>
+        <v>320</v>
       </c>
       <c r="G156" t="s">
         <v>321</v>
@@ -5639,13 +5639,13 @@
         <v>9</v>
       </c>
       <c r="D157" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="E157" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F157" t="s">
-        <v>373</v>
+        <v>320</v>
       </c>
       <c r="G157" t="s">
         <v>321</v>
@@ -5662,13 +5662,13 @@
         <v>9</v>
       </c>
       <c r="D158" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="E158" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F158" t="s">
-        <v>373</v>
+        <v>320</v>
       </c>
       <c r="G158" t="s">
         <v>321</v>
@@ -6122,13 +6122,13 @@
         <v>9</v>
       </c>
       <c r="D178" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E178" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F178" t="s">
-        <v>427</v>
+        <v>386</v>
       </c>
       <c r="G178" t="s">
         <v>387</v>
@@ -6145,13 +6145,13 @@
         <v>9</v>
       </c>
       <c r="D179" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E179" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F179" t="s">
-        <v>427</v>
+        <v>386</v>
       </c>
       <c r="G179" t="s">
         <v>387</v>
@@ -6168,13 +6168,13 @@
         <v>9</v>
       </c>
       <c r="D180" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E180" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F180" t="s">
-        <v>427</v>
+        <v>386</v>
       </c>
       <c r="G180" t="s">
         <v>387</v>
@@ -6191,13 +6191,13 @@
         <v>9</v>
       </c>
       <c r="D181" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E181" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F181" t="s">
-        <v>427</v>
+        <v>386</v>
       </c>
       <c r="G181" t="s">
         <v>387</v>
@@ -6214,13 +6214,13 @@
         <v>9</v>
       </c>
       <c r="D182" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E182" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F182" t="s">
-        <v>427</v>
+        <v>386</v>
       </c>
       <c r="G182" t="s">
         <v>387</v>
@@ -6237,13 +6237,13 @@
         <v>9</v>
       </c>
       <c r="D183" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E183" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F183" t="s">
-        <v>427</v>
+        <v>386</v>
       </c>
       <c r="G183" t="s">
         <v>387</v>
@@ -6260,13 +6260,13 @@
         <v>9</v>
       </c>
       <c r="D184" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E184" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F184" t="s">
-        <v>427</v>
+        <v>386</v>
       </c>
       <c r="G184" t="s">
         <v>387</v>
@@ -6283,13 +6283,13 @@
         <v>9</v>
       </c>
       <c r="D185" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E185" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F185" t="s">
-        <v>427</v>
+        <v>386</v>
       </c>
       <c r="G185" t="s">
         <v>387</v>
@@ -6306,13 +6306,13 @@
         <v>9</v>
       </c>
       <c r="D186" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E186" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F186" t="s">
-        <v>427</v>
+        <v>386</v>
       </c>
       <c r="G186" t="s">
         <v>387</v>
@@ -6329,13 +6329,13 @@
         <v>9</v>
       </c>
       <c r="D187" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E187" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F187" t="s">
-        <v>427</v>
+        <v>386</v>
       </c>
       <c r="G187" t="s">
         <v>387</v>
@@ -6352,13 +6352,13 @@
         <v>9</v>
       </c>
       <c r="D188" t="s">
-        <v>384</v>
+        <v>448</v>
       </c>
       <c r="E188" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F188" t="s">
-        <v>449</v>
+        <v>386</v>
       </c>
       <c r="G188" t="s">
         <v>387</v>
@@ -6378,13 +6378,13 @@
         <v>452</v>
       </c>
       <c r="E189" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F189" t="s">
         <v>453</v>
       </c>
       <c r="G189" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6401,13 +6401,13 @@
         <v>452</v>
       </c>
       <c r="E190" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F190" t="s">
         <v>453</v>
       </c>
       <c r="G190" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6424,13 +6424,13 @@
         <v>452</v>
       </c>
       <c r="E191" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F191" t="s">
         <v>453</v>
       </c>
       <c r="G191" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6447,13 +6447,13 @@
         <v>452</v>
       </c>
       <c r="E192" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F192" t="s">
         <v>453</v>
       </c>
       <c r="G192" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6470,13 +6470,13 @@
         <v>452</v>
       </c>
       <c r="E193" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F193" t="s">
         <v>453</v>
       </c>
       <c r="G193" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6493,13 +6493,13 @@
         <v>452</v>
       </c>
       <c r="E194" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F194" t="s">
         <v>453</v>
       </c>
       <c r="G194" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6516,13 +6516,13 @@
         <v>466</v>
       </c>
       <c r="E195" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="F195" t="s">
         <v>467</v>
       </c>
       <c r="G195" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6539,13 +6539,13 @@
         <v>470</v>
       </c>
       <c r="E196" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F196" t="s">
         <v>471</v>
       </c>
       <c r="G196" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6562,13 +6562,13 @@
         <v>470</v>
       </c>
       <c r="E197" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F197" t="s">
         <v>471</v>
       </c>
       <c r="G197" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6585,13 +6585,13 @@
         <v>470</v>
       </c>
       <c r="E198" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F198" t="s">
         <v>471</v>
       </c>
       <c r="G198" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6608,13 +6608,13 @@
         <v>470</v>
       </c>
       <c r="E199" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F199" t="s">
         <v>471</v>
       </c>
       <c r="G199" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6631,13 +6631,13 @@
         <v>470</v>
       </c>
       <c r="E200" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F200" t="s">
         <v>471</v>
       </c>
       <c r="G200" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6654,13 +6654,13 @@
         <v>470</v>
       </c>
       <c r="E201" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F201" t="s">
         <v>471</v>
       </c>
       <c r="G201" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6677,13 +6677,13 @@
         <v>484</v>
       </c>
       <c r="E202" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F202" t="s">
         <v>485</v>
       </c>
       <c r="G202" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6700,13 +6700,13 @@
         <v>484</v>
       </c>
       <c r="E203" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F203" t="s">
         <v>485</v>
       </c>
       <c r="G203" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6723,13 +6723,13 @@
         <v>484</v>
       </c>
       <c r="E204" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F204" t="s">
         <v>485</v>
       </c>
       <c r="G204" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6746,13 +6746,13 @@
         <v>484</v>
       </c>
       <c r="E205" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F205" t="s">
         <v>485</v>
       </c>
       <c r="G205" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6769,13 +6769,13 @@
         <v>484</v>
       </c>
       <c r="E206" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F206" t="s">
         <v>485</v>
       </c>
       <c r="G206" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6792,13 +6792,13 @@
         <v>484</v>
       </c>
       <c r="E207" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F207" t="s">
         <v>485</v>
       </c>
       <c r="G207" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6815,13 +6815,13 @@
         <v>484</v>
       </c>
       <c r="E208" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F208" t="s">
         <v>485</v>
       </c>
       <c r="G208" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6838,13 +6838,13 @@
         <v>484</v>
       </c>
       <c r="E209" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F209" t="s">
         <v>485</v>
       </c>
       <c r="G209" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6861,13 +6861,13 @@
         <v>484</v>
       </c>
       <c r="E210" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F210" t="s">
         <v>485</v>
       </c>
       <c r="G210" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6884,13 +6884,13 @@
         <v>484</v>
       </c>
       <c r="E211" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F211" t="s">
         <v>485</v>
       </c>
       <c r="G211" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6907,13 +6907,13 @@
         <v>506</v>
       </c>
       <c r="E212" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F212" t="s">
         <v>507</v>
       </c>
       <c r="G212" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6930,13 +6930,13 @@
         <v>510</v>
       </c>
       <c r="E213" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F213" t="s">
         <v>511</v>
       </c>
       <c r="G213" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6953,13 +6953,13 @@
         <v>514</v>
       </c>
       <c r="E214" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="F214" t="s">
         <v>515</v>
       </c>
       <c r="G214" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6976,13 +6976,13 @@
         <v>514</v>
       </c>
       <c r="E215" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="F215" t="s">
         <v>515</v>
       </c>
       <c r="G215" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6999,13 +6999,13 @@
         <v>520</v>
       </c>
       <c r="E216" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F216" t="s">
         <v>521</v>
       </c>
       <c r="G216" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -7022,13 +7022,13 @@
         <v>520</v>
       </c>
       <c r="E217" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F217" t="s">
         <v>521</v>
       </c>
       <c r="G217" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -7045,13 +7045,13 @@
         <v>520</v>
       </c>
       <c r="E218" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F218" t="s">
         <v>521</v>
       </c>
       <c r="G218" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -7068,13 +7068,13 @@
         <v>520</v>
       </c>
       <c r="E219" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F219" t="s">
         <v>521</v>
       </c>
       <c r="G219" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -7091,13 +7091,13 @@
         <v>520</v>
       </c>
       <c r="E220" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F220" t="s">
         <v>521</v>
       </c>
       <c r="G220" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -7114,13 +7114,13 @@
         <v>520</v>
       </c>
       <c r="E221" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F221" t="s">
         <v>521</v>
       </c>
       <c r="G221" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -7137,13 +7137,13 @@
         <v>520</v>
       </c>
       <c r="E222" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F222" t="s">
         <v>521</v>
       </c>
       <c r="G222" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -7160,13 +7160,13 @@
         <v>536</v>
       </c>
       <c r="E223" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F223" t="s">
         <v>537</v>
       </c>
       <c r="G223" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -7183,13 +7183,13 @@
         <v>536</v>
       </c>
       <c r="E224" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F224" t="s">
         <v>537</v>
       </c>
       <c r="G224" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -7206,13 +7206,13 @@
         <v>536</v>
       </c>
       <c r="E225" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F225" t="s">
         <v>537</v>
       </c>
       <c r="G225" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -7229,13 +7229,13 @@
         <v>544</v>
       </c>
       <c r="E226" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="F226" t="s">
         <v>545</v>
       </c>
       <c r="G226" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -7252,13 +7252,13 @@
         <v>548</v>
       </c>
       <c r="E227" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="F227" t="s">
         <v>549</v>
       </c>
       <c r="G227" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -7275,13 +7275,13 @@
         <v>552</v>
       </c>
       <c r="E228" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="F228" t="s">
         <v>553</v>
       </c>
       <c r="G228" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -7298,13 +7298,13 @@
         <v>556</v>
       </c>
       <c r="E229" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="F229" t="s">
         <v>557</v>
       </c>
       <c r="G229" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -7321,13 +7321,13 @@
         <v>560</v>
       </c>
       <c r="E230" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F230" t="s">
         <v>561</v>
       </c>
       <c r="G230" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -7344,13 +7344,13 @@
         <v>560</v>
       </c>
       <c r="E231" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F231" t="s">
         <v>561</v>
       </c>
       <c r="G231" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/en/SectorGroup.xlsx
+++ b/api/xlsx/en/SectorGroup.xlsx
@@ -25,18 +25,18 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
     <t>codeforiati:category-name</t>
   </si>
   <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -46,18 +46,18 @@
     <t>active</t>
   </si>
   <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
     <t>Education, Level Unspecified</t>
   </si>
   <si>
     <t>111</t>
   </si>
   <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>Education</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -148,18 +148,18 @@
     <t>Health policy and administrative management</t>
   </si>
   <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>Health</t>
+  </si>
+  <si>
     <t>Health, General</t>
   </si>
   <si>
     <t>121</t>
   </si>
   <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>Health</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -280,12 +280,12 @@
     <t>Population policy and administrative management</t>
   </si>
   <si>
+    <t>130</t>
+  </si>
+  <si>
     <t>Population Policies/Programmes &amp; Reproductive Health</t>
   </si>
   <si>
-    <t>130</t>
-  </si>
-  <si>
     <t>13020</t>
   </si>
   <si>
@@ -316,12 +316,12 @@
     <t>Water sector policy and administrative management</t>
   </si>
   <si>
+    <t>140</t>
+  </si>
+  <si>
     <t>Water Supply &amp; Sanitation</t>
   </si>
   <si>
-    <t>140</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -388,18 +388,18 @@
     <t>Public sector policy and administrative management</t>
   </si>
   <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>Government &amp; Civil Society</t>
+  </si>
+  <si>
     <t>Government &amp; Civil Society-general</t>
   </si>
   <si>
     <t>151</t>
   </si>
   <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>Government &amp; Civil Society</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -538,12 +538,12 @@
     <t>Social Protection</t>
   </si>
   <si>
+    <t>160</t>
+  </si>
+  <si>
     <t>Other Social Infrastructure &amp; Services</t>
   </si>
   <si>
-    <t>160</t>
-  </si>
-  <si>
     <t>16020</t>
   </si>
   <si>
@@ -610,12 +610,12 @@
     <t>Transport policy and administrative management</t>
   </si>
   <si>
+    <t>210</t>
+  </si>
+  <si>
     <t>Transport &amp; Storage</t>
   </si>
   <si>
-    <t>210</t>
-  </si>
-  <si>
     <t>21020</t>
   </si>
   <si>
@@ -658,12 +658,12 @@
     <t>Communications policy and administrative management</t>
   </si>
   <si>
+    <t>220</t>
+  </si>
+  <si>
     <t>Communications</t>
   </si>
   <si>
-    <t>220</t>
-  </si>
-  <si>
     <t>22020</t>
   </si>
   <si>
@@ -688,18 +688,18 @@
     <t>Energy policy and administrative management</t>
   </si>
   <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>Energy</t>
+  </si>
+  <si>
     <t>Energy Policy</t>
   </si>
   <si>
     <t>231</t>
   </si>
   <si>
-    <t>230</t>
-  </si>
-  <si>
-    <t>Energy</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -898,12 +898,12 @@
     <t>Financial policy and administrative management</t>
   </si>
   <si>
+    <t>240</t>
+  </si>
+  <si>
     <t>Banking &amp; Financial Services</t>
   </si>
   <si>
-    <t>240</t>
-  </si>
-  <si>
     <t>24020</t>
   </si>
   <si>
@@ -940,12 +940,12 @@
     <t>Business policy and administration</t>
   </si>
   <si>
+    <t>250</t>
+  </si>
+  <si>
     <t>Business &amp; Other Services</t>
   </si>
   <si>
-    <t>250</t>
-  </si>
-  <si>
     <t>25020</t>
   </si>
   <si>
@@ -970,18 +970,18 @@
     <t>Agricultural policy and administrative management</t>
   </si>
   <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>Agriculture, Forestry, Fishing</t>
+  </si>
+  <si>
     <t>Agriculture</t>
   </si>
   <si>
     <t>311</t>
   </si>
   <si>
-    <t>310</t>
-  </si>
-  <si>
-    <t>Agriculture, Forestry, Fishing</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1168,18 +1168,18 @@
     <t>Industrial policy and administrative management</t>
   </si>
   <si>
+    <t>320</t>
+  </si>
+  <si>
+    <t>Industry, Mining, Construction</t>
+  </si>
+  <si>
     <t>Industry</t>
   </si>
   <si>
     <t>321</t>
   </si>
   <si>
-    <t>320</t>
-  </si>
-  <si>
-    <t>Industry, Mining, Construction</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1372,12 +1372,12 @@
     <t>Trade policy and administrative management</t>
   </si>
   <si>
+    <t>331</t>
+  </si>
+  <si>
     <t>Trade Policies &amp; Regulations</t>
   </si>
   <si>
-    <t>331</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1414,24 +1414,24 @@
     <t>Tourism policy and administrative management</t>
   </si>
   <si>
+    <t>332</t>
+  </si>
+  <si>
     <t>Tourism</t>
   </si>
   <si>
-    <t>332</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
     <t>Environmental policy and administrative management</t>
   </si>
   <si>
+    <t>410</t>
+  </si>
+  <si>
     <t>General Environment Protection</t>
   </si>
   <si>
-    <t>410</t>
-  </si>
-  <si>
     <t>41020</t>
   </si>
   <si>
@@ -1468,12 +1468,12 @@
     <t>Multisector aid</t>
   </si>
   <si>
+    <t>430</t>
+  </si>
+  <si>
     <t>Other Multisector</t>
   </si>
   <si>
-    <t>430</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -1534,36 +1534,36 @@
     <t>General budget support-related aid</t>
   </si>
   <si>
+    <t>510</t>
+  </si>
+  <si>
     <t>General Budget Support</t>
   </si>
   <si>
-    <t>510</t>
-  </si>
-  <si>
     <t>52010</t>
   </si>
   <si>
     <t>Food assistance</t>
   </si>
   <si>
+    <t>520</t>
+  </si>
+  <si>
     <t>Development Food Assistance</t>
   </si>
   <si>
-    <t>520</t>
-  </si>
-  <si>
     <t>53030</t>
   </si>
   <si>
     <t>Import support (capital goods)</t>
   </si>
   <si>
+    <t>530</t>
+  </si>
+  <si>
     <t>Other Commodity Assistance</t>
   </si>
   <si>
-    <t>530</t>
-  </si>
-  <si>
     <t>53040</t>
   </si>
   <si>
@@ -1576,12 +1576,12 @@
     <t>Action relating to debt</t>
   </si>
   <si>
+    <t>600</t>
+  </si>
+  <si>
     <t>Action Relating to Debt</t>
   </si>
   <si>
-    <t>600</t>
-  </si>
-  <si>
     <t>60020</t>
   </si>
   <si>
@@ -1624,12 +1624,12 @@
     <t>Material relief assistance and services</t>
   </si>
   <si>
+    <t>720</t>
+  </si>
+  <si>
     <t>Emergency Response</t>
   </si>
   <si>
-    <t>720</t>
-  </si>
-  <si>
     <t>72040</t>
   </si>
   <si>
@@ -1648,58 +1648,58 @@
     <t>Immediate post-emergency reconstruction and rehabilitation</t>
   </si>
   <si>
+    <t>730</t>
+  </si>
+  <si>
     <t>Reconstruction Relief &amp; Rehabilitation</t>
   </si>
   <si>
-    <t>730</t>
-  </si>
-  <si>
     <t>74020</t>
   </si>
   <si>
     <t>Multi-hazard response preparedness</t>
   </si>
   <si>
+    <t>740</t>
+  </si>
+  <si>
     <t>Disaster Prevention &amp; Preparedness</t>
   </si>
   <si>
-    <t>740</t>
-  </si>
-  <si>
     <t>91010</t>
   </si>
   <si>
     <t>Administrative costs (non-sector allocable)</t>
   </si>
   <si>
+    <t>910</t>
+  </si>
+  <si>
     <t>Administrative Costs of Donors</t>
   </si>
   <si>
-    <t>910</t>
-  </si>
-  <si>
     <t>93010</t>
   </si>
   <si>
     <t>Refugees/asylum seekers in donor countries (non-sector allocable)</t>
   </si>
   <si>
+    <t>930</t>
+  </si>
+  <si>
     <t>Refugees in Donor Countries</t>
   </si>
   <si>
-    <t>930</t>
-  </si>
-  <si>
     <t>99810</t>
   </si>
   <si>
     <t>Sectors not specified</t>
   </si>
   <si>
+    <t>998</t>
+  </si>
+  <si>
     <t>Unallocated / Unspecified</t>
-  </si>
-  <si>
-    <t>998</t>
   </si>
   <si>
     <t>99820</t>
@@ -2166,16 +2166,16 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" t="s">
         <v>22</v>
       </c>
-      <c r="E6" t="s">
+      <c r="G6" t="s">
         <v>23</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2189,16 +2189,16 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" t="s">
         <v>22</v>
       </c>
-      <c r="E7" t="s">
+      <c r="G7" t="s">
         <v>23</v>
-      </c>
-      <c r="F7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2212,16 +2212,16 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" t="s">
         <v>22</v>
       </c>
-      <c r="E8" t="s">
+      <c r="G8" t="s">
         <v>23</v>
-      </c>
-      <c r="F8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2235,16 +2235,16 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" t="s">
         <v>22</v>
       </c>
-      <c r="E9" t="s">
+      <c r="G9" t="s">
         <v>23</v>
-      </c>
-      <c r="F9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2258,16 +2258,16 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" t="s">
         <v>32</v>
       </c>
-      <c r="E10" t="s">
+      <c r="G10" t="s">
         <v>33</v>
-      </c>
-      <c r="F10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2281,16 +2281,16 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" t="s">
         <v>32</v>
       </c>
-      <c r="E11" t="s">
+      <c r="G11" t="s">
         <v>33</v>
-      </c>
-      <c r="F11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2304,16 +2304,16 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" t="s">
         <v>38</v>
       </c>
-      <c r="E12" t="s">
+      <c r="G12" t="s">
         <v>39</v>
-      </c>
-      <c r="F12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2327,16 +2327,16 @@
         <v>9</v>
       </c>
       <c r="D13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" t="s">
         <v>38</v>
       </c>
-      <c r="E13" t="s">
+      <c r="G13" t="s">
         <v>39</v>
-      </c>
-      <c r="F13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2442,16 +2442,16 @@
         <v>9</v>
       </c>
       <c r="D18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18" t="s">
+        <v>45</v>
+      </c>
+      <c r="F18" t="s">
         <v>56</v>
       </c>
-      <c r="E18" t="s">
+      <c r="G18" t="s">
         <v>57</v>
-      </c>
-      <c r="F18" t="s">
-        <v>46</v>
-      </c>
-      <c r="G18" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2465,16 +2465,16 @@
         <v>9</v>
       </c>
       <c r="D19" t="s">
+        <v>44</v>
+      </c>
+      <c r="E19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F19" t="s">
         <v>56</v>
       </c>
-      <c r="E19" t="s">
+      <c r="G19" t="s">
         <v>57</v>
-      </c>
-      <c r="F19" t="s">
-        <v>46</v>
-      </c>
-      <c r="G19" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2488,16 +2488,16 @@
         <v>9</v>
       </c>
       <c r="D20" t="s">
+        <v>44</v>
+      </c>
+      <c r="E20" t="s">
+        <v>45</v>
+      </c>
+      <c r="F20" t="s">
         <v>56</v>
       </c>
-      <c r="E20" t="s">
+      <c r="G20" t="s">
         <v>57</v>
-      </c>
-      <c r="F20" t="s">
-        <v>46</v>
-      </c>
-      <c r="G20" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2511,16 +2511,16 @@
         <v>9</v>
       </c>
       <c r="D21" t="s">
+        <v>44</v>
+      </c>
+      <c r="E21" t="s">
+        <v>45</v>
+      </c>
+      <c r="F21" t="s">
         <v>56</v>
       </c>
-      <c r="E21" t="s">
+      <c r="G21" t="s">
         <v>57</v>
-      </c>
-      <c r="F21" t="s">
-        <v>46</v>
-      </c>
-      <c r="G21" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2534,16 +2534,16 @@
         <v>9</v>
       </c>
       <c r="D22" t="s">
+        <v>44</v>
+      </c>
+      <c r="E22" t="s">
+        <v>45</v>
+      </c>
+      <c r="F22" t="s">
         <v>56</v>
       </c>
-      <c r="E22" t="s">
+      <c r="G22" t="s">
         <v>57</v>
-      </c>
-      <c r="F22" t="s">
-        <v>46</v>
-      </c>
-      <c r="G22" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2557,16 +2557,16 @@
         <v>9</v>
       </c>
       <c r="D23" t="s">
+        <v>44</v>
+      </c>
+      <c r="E23" t="s">
+        <v>45</v>
+      </c>
+      <c r="F23" t="s">
         <v>56</v>
       </c>
-      <c r="E23" t="s">
+      <c r="G23" t="s">
         <v>57</v>
-      </c>
-      <c r="F23" t="s">
-        <v>46</v>
-      </c>
-      <c r="G23" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2580,16 +2580,16 @@
         <v>9</v>
       </c>
       <c r="D24" t="s">
+        <v>44</v>
+      </c>
+      <c r="E24" t="s">
+        <v>45</v>
+      </c>
+      <c r="F24" t="s">
         <v>56</v>
       </c>
-      <c r="E24" t="s">
+      <c r="G24" t="s">
         <v>57</v>
-      </c>
-      <c r="F24" t="s">
-        <v>46</v>
-      </c>
-      <c r="G24" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2603,16 +2603,16 @@
         <v>9</v>
       </c>
       <c r="D25" t="s">
+        <v>44</v>
+      </c>
+      <c r="E25" t="s">
+        <v>45</v>
+      </c>
+      <c r="F25" t="s">
         <v>56</v>
       </c>
-      <c r="E25" t="s">
+      <c r="G25" t="s">
         <v>57</v>
-      </c>
-      <c r="F25" t="s">
-        <v>46</v>
-      </c>
-      <c r="G25" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2626,16 +2626,16 @@
         <v>9</v>
       </c>
       <c r="D26" t="s">
+        <v>44</v>
+      </c>
+      <c r="E26" t="s">
+        <v>45</v>
+      </c>
+      <c r="F26" t="s">
         <v>74</v>
       </c>
-      <c r="E26" t="s">
+      <c r="G26" t="s">
         <v>75</v>
-      </c>
-      <c r="F26" t="s">
-        <v>46</v>
-      </c>
-      <c r="G26" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2649,16 +2649,16 @@
         <v>9</v>
       </c>
       <c r="D27" t="s">
+        <v>44</v>
+      </c>
+      <c r="E27" t="s">
+        <v>45</v>
+      </c>
+      <c r="F27" t="s">
         <v>74</v>
       </c>
-      <c r="E27" t="s">
+      <c r="G27" t="s">
         <v>75</v>
-      </c>
-      <c r="F27" t="s">
-        <v>46</v>
-      </c>
-      <c r="G27" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2672,16 +2672,16 @@
         <v>9</v>
       </c>
       <c r="D28" t="s">
+        <v>44</v>
+      </c>
+      <c r="E28" t="s">
+        <v>45</v>
+      </c>
+      <c r="F28" t="s">
         <v>74</v>
       </c>
-      <c r="E28" t="s">
+      <c r="G28" t="s">
         <v>75</v>
-      </c>
-      <c r="F28" t="s">
-        <v>46</v>
-      </c>
-      <c r="G28" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2695,16 +2695,16 @@
         <v>9</v>
       </c>
       <c r="D29" t="s">
+        <v>44</v>
+      </c>
+      <c r="E29" t="s">
+        <v>45</v>
+      </c>
+      <c r="F29" t="s">
         <v>74</v>
       </c>
-      <c r="E29" t="s">
+      <c r="G29" t="s">
         <v>75</v>
-      </c>
-      <c r="F29" t="s">
-        <v>46</v>
-      </c>
-      <c r="G29" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2718,16 +2718,16 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
+        <v>44</v>
+      </c>
+      <c r="E30" t="s">
+        <v>45</v>
+      </c>
+      <c r="F30" t="s">
         <v>74</v>
       </c>
-      <c r="E30" t="s">
+      <c r="G30" t="s">
         <v>75</v>
-      </c>
-      <c r="F30" t="s">
-        <v>46</v>
-      </c>
-      <c r="G30" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2741,16 +2741,16 @@
         <v>9</v>
       </c>
       <c r="D31" t="s">
+        <v>44</v>
+      </c>
+      <c r="E31" t="s">
+        <v>45</v>
+      </c>
+      <c r="F31" t="s">
         <v>74</v>
       </c>
-      <c r="E31" t="s">
+      <c r="G31" t="s">
         <v>75</v>
-      </c>
-      <c r="F31" t="s">
-        <v>46</v>
-      </c>
-      <c r="G31" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -3500,16 +3500,16 @@
         <v>9</v>
       </c>
       <c r="D64" t="s">
+        <v>124</v>
+      </c>
+      <c r="E64" t="s">
+        <v>125</v>
+      </c>
+      <c r="F64" t="s">
         <v>160</v>
       </c>
-      <c r="E64" t="s">
+      <c r="G64" t="s">
         <v>161</v>
-      </c>
-      <c r="F64" t="s">
-        <v>126</v>
-      </c>
-      <c r="G64" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3523,16 +3523,16 @@
         <v>9</v>
       </c>
       <c r="D65" t="s">
+        <v>124</v>
+      </c>
+      <c r="E65" t="s">
+        <v>125</v>
+      </c>
+      <c r="F65" t="s">
         <v>160</v>
       </c>
-      <c r="E65" t="s">
+      <c r="G65" t="s">
         <v>161</v>
-      </c>
-      <c r="F65" t="s">
-        <v>126</v>
-      </c>
-      <c r="G65" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3546,16 +3546,16 @@
         <v>9</v>
       </c>
       <c r="D66" t="s">
+        <v>124</v>
+      </c>
+      <c r="E66" t="s">
+        <v>125</v>
+      </c>
+      <c r="F66" t="s">
         <v>160</v>
       </c>
-      <c r="E66" t="s">
+      <c r="G66" t="s">
         <v>161</v>
-      </c>
-      <c r="F66" t="s">
-        <v>126</v>
-      </c>
-      <c r="G66" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3569,16 +3569,16 @@
         <v>9</v>
       </c>
       <c r="D67" t="s">
+        <v>124</v>
+      </c>
+      <c r="E67" t="s">
+        <v>125</v>
+      </c>
+      <c r="F67" t="s">
         <v>160</v>
       </c>
-      <c r="E67" t="s">
+      <c r="G67" t="s">
         <v>161</v>
-      </c>
-      <c r="F67" t="s">
-        <v>126</v>
-      </c>
-      <c r="G67" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3592,16 +3592,16 @@
         <v>9</v>
       </c>
       <c r="D68" t="s">
+        <v>124</v>
+      </c>
+      <c r="E68" t="s">
+        <v>125</v>
+      </c>
+      <c r="F68" t="s">
         <v>160</v>
       </c>
-      <c r="E68" t="s">
+      <c r="G68" t="s">
         <v>161</v>
-      </c>
-      <c r="F68" t="s">
-        <v>126</v>
-      </c>
-      <c r="G68" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3615,16 +3615,16 @@
         <v>9</v>
       </c>
       <c r="D69" t="s">
+        <v>124</v>
+      </c>
+      <c r="E69" t="s">
+        <v>125</v>
+      </c>
+      <c r="F69" t="s">
         <v>160</v>
       </c>
-      <c r="E69" t="s">
+      <c r="G69" t="s">
         <v>161</v>
-      </c>
-      <c r="F69" t="s">
-        <v>126</v>
-      </c>
-      <c r="G69" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -4236,16 +4236,16 @@
         <v>9</v>
       </c>
       <c r="D96" t="s">
+        <v>224</v>
+      </c>
+      <c r="E96" t="s">
+        <v>225</v>
+      </c>
+      <c r="F96" t="s">
         <v>236</v>
       </c>
-      <c r="E96" t="s">
+      <c r="G96" t="s">
         <v>237</v>
-      </c>
-      <c r="F96" t="s">
-        <v>226</v>
-      </c>
-      <c r="G96" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -4259,16 +4259,16 @@
         <v>9</v>
       </c>
       <c r="D97" t="s">
+        <v>224</v>
+      </c>
+      <c r="E97" t="s">
+        <v>225</v>
+      </c>
+      <c r="F97" t="s">
         <v>236</v>
       </c>
-      <c r="E97" t="s">
+      <c r="G97" t="s">
         <v>237</v>
-      </c>
-      <c r="F97" t="s">
-        <v>226</v>
-      </c>
-      <c r="G97" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4282,16 +4282,16 @@
         <v>9</v>
       </c>
       <c r="D98" t="s">
+        <v>224</v>
+      </c>
+      <c r="E98" t="s">
+        <v>225</v>
+      </c>
+      <c r="F98" t="s">
         <v>236</v>
       </c>
-      <c r="E98" t="s">
+      <c r="G98" t="s">
         <v>237</v>
-      </c>
-      <c r="F98" t="s">
-        <v>226</v>
-      </c>
-      <c r="G98" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4305,16 +4305,16 @@
         <v>9</v>
       </c>
       <c r="D99" t="s">
+        <v>224</v>
+      </c>
+      <c r="E99" t="s">
+        <v>225</v>
+      </c>
+      <c r="F99" t="s">
         <v>236</v>
       </c>
-      <c r="E99" t="s">
+      <c r="G99" t="s">
         <v>237</v>
-      </c>
-      <c r="F99" t="s">
-        <v>226</v>
-      </c>
-      <c r="G99" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4328,16 +4328,16 @@
         <v>9</v>
       </c>
       <c r="D100" t="s">
+        <v>224</v>
+      </c>
+      <c r="E100" t="s">
+        <v>225</v>
+      </c>
+      <c r="F100" t="s">
         <v>236</v>
       </c>
-      <c r="E100" t="s">
+      <c r="G100" t="s">
         <v>237</v>
-      </c>
-      <c r="F100" t="s">
-        <v>226</v>
-      </c>
-      <c r="G100" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4351,16 +4351,16 @@
         <v>9</v>
       </c>
       <c r="D101" t="s">
+        <v>224</v>
+      </c>
+      <c r="E101" t="s">
+        <v>225</v>
+      </c>
+      <c r="F101" t="s">
         <v>236</v>
       </c>
-      <c r="E101" t="s">
+      <c r="G101" t="s">
         <v>237</v>
-      </c>
-      <c r="F101" t="s">
-        <v>226</v>
-      </c>
-      <c r="G101" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4374,16 +4374,16 @@
         <v>9</v>
       </c>
       <c r="D102" t="s">
+        <v>224</v>
+      </c>
+      <c r="E102" t="s">
+        <v>225</v>
+      </c>
+      <c r="F102" t="s">
         <v>236</v>
       </c>
-      <c r="E102" t="s">
+      <c r="G102" t="s">
         <v>237</v>
-      </c>
-      <c r="F102" t="s">
-        <v>226</v>
-      </c>
-      <c r="G102" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4397,16 +4397,16 @@
         <v>9</v>
       </c>
       <c r="D103" t="s">
+        <v>224</v>
+      </c>
+      <c r="E103" t="s">
+        <v>225</v>
+      </c>
+      <c r="F103" t="s">
         <v>236</v>
       </c>
-      <c r="E103" t="s">
+      <c r="G103" t="s">
         <v>237</v>
-      </c>
-      <c r="F103" t="s">
-        <v>226</v>
-      </c>
-      <c r="G103" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4420,16 +4420,16 @@
         <v>9</v>
       </c>
       <c r="D104" t="s">
+        <v>224</v>
+      </c>
+      <c r="E104" t="s">
+        <v>225</v>
+      </c>
+      <c r="F104" t="s">
         <v>236</v>
       </c>
-      <c r="E104" t="s">
+      <c r="G104" t="s">
         <v>237</v>
-      </c>
-      <c r="F104" t="s">
-        <v>226</v>
-      </c>
-      <c r="G104" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4443,16 +4443,16 @@
         <v>9</v>
       </c>
       <c r="D105" t="s">
+        <v>224</v>
+      </c>
+      <c r="E105" t="s">
+        <v>225</v>
+      </c>
+      <c r="F105" t="s">
         <v>256</v>
       </c>
-      <c r="E105" t="s">
+      <c r="G105" t="s">
         <v>257</v>
-      </c>
-      <c r="F105" t="s">
-        <v>226</v>
-      </c>
-      <c r="G105" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4466,16 +4466,16 @@
         <v>9</v>
       </c>
       <c r="D106" t="s">
+        <v>224</v>
+      </c>
+      <c r="E106" t="s">
+        <v>225</v>
+      </c>
+      <c r="F106" t="s">
         <v>256</v>
       </c>
-      <c r="E106" t="s">
+      <c r="G106" t="s">
         <v>257</v>
-      </c>
-      <c r="F106" t="s">
-        <v>226</v>
-      </c>
-      <c r="G106" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4489,16 +4489,16 @@
         <v>9</v>
       </c>
       <c r="D107" t="s">
+        <v>224</v>
+      </c>
+      <c r="E107" t="s">
+        <v>225</v>
+      </c>
+      <c r="F107" t="s">
         <v>256</v>
       </c>
-      <c r="E107" t="s">
+      <c r="G107" t="s">
         <v>257</v>
-      </c>
-      <c r="F107" t="s">
-        <v>226</v>
-      </c>
-      <c r="G107" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4512,16 +4512,16 @@
         <v>9</v>
       </c>
       <c r="D108" t="s">
+        <v>224</v>
+      </c>
+      <c r="E108" t="s">
+        <v>225</v>
+      </c>
+      <c r="F108" t="s">
         <v>256</v>
       </c>
-      <c r="E108" t="s">
+      <c r="G108" t="s">
         <v>257</v>
-      </c>
-      <c r="F108" t="s">
-        <v>226</v>
-      </c>
-      <c r="G108" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4535,16 +4535,16 @@
         <v>9</v>
       </c>
       <c r="D109" t="s">
+        <v>224</v>
+      </c>
+      <c r="E109" t="s">
+        <v>225</v>
+      </c>
+      <c r="F109" t="s">
         <v>256</v>
       </c>
-      <c r="E109" t="s">
+      <c r="G109" t="s">
         <v>257</v>
-      </c>
-      <c r="F109" t="s">
-        <v>226</v>
-      </c>
-      <c r="G109" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4558,16 +4558,16 @@
         <v>9</v>
       </c>
       <c r="D110" t="s">
+        <v>224</v>
+      </c>
+      <c r="E110" t="s">
+        <v>225</v>
+      </c>
+      <c r="F110" t="s">
         <v>256</v>
       </c>
-      <c r="E110" t="s">
+      <c r="G110" t="s">
         <v>257</v>
-      </c>
-      <c r="F110" t="s">
-        <v>226</v>
-      </c>
-      <c r="G110" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4581,16 +4581,16 @@
         <v>9</v>
       </c>
       <c r="D111" t="s">
+        <v>224</v>
+      </c>
+      <c r="E111" t="s">
+        <v>225</v>
+      </c>
+      <c r="F111" t="s">
         <v>270</v>
       </c>
-      <c r="E111" t="s">
+      <c r="G111" t="s">
         <v>271</v>
-      </c>
-      <c r="F111" t="s">
-        <v>226</v>
-      </c>
-      <c r="G111" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4604,16 +4604,16 @@
         <v>9</v>
       </c>
       <c r="D112" t="s">
+        <v>224</v>
+      </c>
+      <c r="E112" t="s">
+        <v>225</v>
+      </c>
+      <c r="F112" t="s">
         <v>274</v>
       </c>
-      <c r="E112" t="s">
+      <c r="G112" t="s">
         <v>275</v>
-      </c>
-      <c r="F112" t="s">
-        <v>226</v>
-      </c>
-      <c r="G112" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4627,16 +4627,16 @@
         <v>9</v>
       </c>
       <c r="D113" t="s">
+        <v>224</v>
+      </c>
+      <c r="E113" t="s">
+        <v>225</v>
+      </c>
+      <c r="F113" t="s">
         <v>278</v>
       </c>
-      <c r="E113" t="s">
+      <c r="G113" t="s">
         <v>279</v>
-      </c>
-      <c r="F113" t="s">
-        <v>226</v>
-      </c>
-      <c r="G113" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4650,16 +4650,16 @@
         <v>9</v>
       </c>
       <c r="D114" t="s">
+        <v>224</v>
+      </c>
+      <c r="E114" t="s">
+        <v>225</v>
+      </c>
+      <c r="F114" t="s">
         <v>278</v>
       </c>
-      <c r="E114" t="s">
+      <c r="G114" t="s">
         <v>279</v>
-      </c>
-      <c r="F114" t="s">
-        <v>226</v>
-      </c>
-      <c r="G114" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4673,16 +4673,16 @@
         <v>9</v>
       </c>
       <c r="D115" t="s">
+        <v>224</v>
+      </c>
+      <c r="E115" t="s">
+        <v>225</v>
+      </c>
+      <c r="F115" t="s">
         <v>278</v>
       </c>
-      <c r="E115" t="s">
+      <c r="G115" t="s">
         <v>279</v>
-      </c>
-      <c r="F115" t="s">
-        <v>226</v>
-      </c>
-      <c r="G115" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4696,16 +4696,16 @@
         <v>9</v>
       </c>
       <c r="D116" t="s">
+        <v>224</v>
+      </c>
+      <c r="E116" t="s">
+        <v>225</v>
+      </c>
+      <c r="F116" t="s">
         <v>278</v>
       </c>
-      <c r="E116" t="s">
+      <c r="G116" t="s">
         <v>279</v>
-      </c>
-      <c r="F116" t="s">
-        <v>226</v>
-      </c>
-      <c r="G116" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4719,16 +4719,16 @@
         <v>9</v>
       </c>
       <c r="D117" t="s">
+        <v>224</v>
+      </c>
+      <c r="E117" t="s">
+        <v>225</v>
+      </c>
+      <c r="F117" t="s">
         <v>278</v>
       </c>
-      <c r="E117" t="s">
+      <c r="G117" t="s">
         <v>279</v>
-      </c>
-      <c r="F117" t="s">
-        <v>226</v>
-      </c>
-      <c r="G117" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4742,16 +4742,16 @@
         <v>9</v>
       </c>
       <c r="D118" t="s">
+        <v>224</v>
+      </c>
+      <c r="E118" t="s">
+        <v>225</v>
+      </c>
+      <c r="F118" t="s">
         <v>278</v>
       </c>
-      <c r="E118" t="s">
+      <c r="G118" t="s">
         <v>279</v>
-      </c>
-      <c r="F118" t="s">
-        <v>226</v>
-      </c>
-      <c r="G118" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4765,16 +4765,16 @@
         <v>9</v>
       </c>
       <c r="D119" t="s">
+        <v>224</v>
+      </c>
+      <c r="E119" t="s">
+        <v>225</v>
+      </c>
+      <c r="F119" t="s">
         <v>278</v>
       </c>
-      <c r="E119" t="s">
+      <c r="G119" t="s">
         <v>279</v>
-      </c>
-      <c r="F119" t="s">
-        <v>226</v>
-      </c>
-      <c r="G119" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -5432,16 +5432,16 @@
         <v>9</v>
       </c>
       <c r="D148" t="s">
+        <v>318</v>
+      </c>
+      <c r="E148" t="s">
+        <v>319</v>
+      </c>
+      <c r="F148" t="s">
         <v>358</v>
       </c>
-      <c r="E148" t="s">
+      <c r="G148" t="s">
         <v>359</v>
-      </c>
-      <c r="F148" t="s">
-        <v>320</v>
-      </c>
-      <c r="G148" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5455,16 +5455,16 @@
         <v>9</v>
       </c>
       <c r="D149" t="s">
+        <v>318</v>
+      </c>
+      <c r="E149" t="s">
+        <v>319</v>
+      </c>
+      <c r="F149" t="s">
         <v>358</v>
       </c>
-      <c r="E149" t="s">
+      <c r="G149" t="s">
         <v>359</v>
-      </c>
-      <c r="F149" t="s">
-        <v>320</v>
-      </c>
-      <c r="G149" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5478,16 +5478,16 @@
         <v>9</v>
       </c>
       <c r="D150" t="s">
+        <v>318</v>
+      </c>
+      <c r="E150" t="s">
+        <v>319</v>
+      </c>
+      <c r="F150" t="s">
         <v>358</v>
       </c>
-      <c r="E150" t="s">
+      <c r="G150" t="s">
         <v>359</v>
-      </c>
-      <c r="F150" t="s">
-        <v>320</v>
-      </c>
-      <c r="G150" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5501,16 +5501,16 @@
         <v>9</v>
       </c>
       <c r="D151" t="s">
+        <v>318</v>
+      </c>
+      <c r="E151" t="s">
+        <v>319</v>
+      </c>
+      <c r="F151" t="s">
         <v>358</v>
       </c>
-      <c r="E151" t="s">
+      <c r="G151" t="s">
         <v>359</v>
-      </c>
-      <c r="F151" t="s">
-        <v>320</v>
-      </c>
-      <c r="G151" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5524,16 +5524,16 @@
         <v>9</v>
       </c>
       <c r="D152" t="s">
+        <v>318</v>
+      </c>
+      <c r="E152" t="s">
+        <v>319</v>
+      </c>
+      <c r="F152" t="s">
         <v>358</v>
       </c>
-      <c r="E152" t="s">
+      <c r="G152" t="s">
         <v>359</v>
-      </c>
-      <c r="F152" t="s">
-        <v>320</v>
-      </c>
-      <c r="G152" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5547,16 +5547,16 @@
         <v>9</v>
       </c>
       <c r="D153" t="s">
+        <v>318</v>
+      </c>
+      <c r="E153" t="s">
+        <v>319</v>
+      </c>
+      <c r="F153" t="s">
         <v>358</v>
       </c>
-      <c r="E153" t="s">
+      <c r="G153" t="s">
         <v>359</v>
-      </c>
-      <c r="F153" t="s">
-        <v>320</v>
-      </c>
-      <c r="G153" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5570,16 +5570,16 @@
         <v>9</v>
       </c>
       <c r="D154" t="s">
+        <v>318</v>
+      </c>
+      <c r="E154" t="s">
+        <v>319</v>
+      </c>
+      <c r="F154" t="s">
         <v>372</v>
       </c>
-      <c r="E154" t="s">
+      <c r="G154" t="s">
         <v>373</v>
-      </c>
-      <c r="F154" t="s">
-        <v>320</v>
-      </c>
-      <c r="G154" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5593,16 +5593,16 @@
         <v>9</v>
       </c>
       <c r="D155" t="s">
+        <v>318</v>
+      </c>
+      <c r="E155" t="s">
+        <v>319</v>
+      </c>
+      <c r="F155" t="s">
         <v>372</v>
       </c>
-      <c r="E155" t="s">
+      <c r="G155" t="s">
         <v>373</v>
-      </c>
-      <c r="F155" t="s">
-        <v>320</v>
-      </c>
-      <c r="G155" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5616,16 +5616,16 @@
         <v>9</v>
       </c>
       <c r="D156" t="s">
+        <v>318</v>
+      </c>
+      <c r="E156" t="s">
+        <v>319</v>
+      </c>
+      <c r="F156" t="s">
         <v>372</v>
       </c>
-      <c r="E156" t="s">
+      <c r="G156" t="s">
         <v>373</v>
-      </c>
-      <c r="F156" t="s">
-        <v>320</v>
-      </c>
-      <c r="G156" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5639,16 +5639,16 @@
         <v>9</v>
       </c>
       <c r="D157" t="s">
+        <v>318</v>
+      </c>
+      <c r="E157" t="s">
+        <v>319</v>
+      </c>
+      <c r="F157" t="s">
         <v>372</v>
       </c>
-      <c r="E157" t="s">
+      <c r="G157" t="s">
         <v>373</v>
-      </c>
-      <c r="F157" t="s">
-        <v>320</v>
-      </c>
-      <c r="G157" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5662,16 +5662,16 @@
         <v>9</v>
       </c>
       <c r="D158" t="s">
+        <v>318</v>
+      </c>
+      <c r="E158" t="s">
+        <v>319</v>
+      </c>
+      <c r="F158" t="s">
         <v>372</v>
       </c>
-      <c r="E158" t="s">
+      <c r="G158" t="s">
         <v>373</v>
-      </c>
-      <c r="F158" t="s">
-        <v>320</v>
-      </c>
-      <c r="G158" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -6122,16 +6122,16 @@
         <v>9</v>
       </c>
       <c r="D178" t="s">
+        <v>384</v>
+      </c>
+      <c r="E178" t="s">
+        <v>385</v>
+      </c>
+      <c r="F178" t="s">
         <v>426</v>
       </c>
-      <c r="E178" t="s">
+      <c r="G178" t="s">
         <v>427</v>
-      </c>
-      <c r="F178" t="s">
-        <v>386</v>
-      </c>
-      <c r="G178" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -6145,16 +6145,16 @@
         <v>9</v>
       </c>
       <c r="D179" t="s">
+        <v>384</v>
+      </c>
+      <c r="E179" t="s">
+        <v>385</v>
+      </c>
+      <c r="F179" t="s">
         <v>426</v>
       </c>
-      <c r="E179" t="s">
+      <c r="G179" t="s">
         <v>427</v>
-      </c>
-      <c r="F179" t="s">
-        <v>386</v>
-      </c>
-      <c r="G179" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -6168,16 +6168,16 @@
         <v>9</v>
       </c>
       <c r="D180" t="s">
+        <v>384</v>
+      </c>
+      <c r="E180" t="s">
+        <v>385</v>
+      </c>
+      <c r="F180" t="s">
         <v>426</v>
       </c>
-      <c r="E180" t="s">
+      <c r="G180" t="s">
         <v>427</v>
-      </c>
-      <c r="F180" t="s">
-        <v>386</v>
-      </c>
-      <c r="G180" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -6191,16 +6191,16 @@
         <v>9</v>
       </c>
       <c r="D181" t="s">
+        <v>384</v>
+      </c>
+      <c r="E181" t="s">
+        <v>385</v>
+      </c>
+      <c r="F181" t="s">
         <v>426</v>
       </c>
-      <c r="E181" t="s">
+      <c r="G181" t="s">
         <v>427</v>
-      </c>
-      <c r="F181" t="s">
-        <v>386</v>
-      </c>
-      <c r="G181" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -6214,16 +6214,16 @@
         <v>9</v>
       </c>
       <c r="D182" t="s">
+        <v>384</v>
+      </c>
+      <c r="E182" t="s">
+        <v>385</v>
+      </c>
+      <c r="F182" t="s">
         <v>426</v>
       </c>
-      <c r="E182" t="s">
+      <c r="G182" t="s">
         <v>427</v>
-      </c>
-      <c r="F182" t="s">
-        <v>386</v>
-      </c>
-      <c r="G182" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -6237,16 +6237,16 @@
         <v>9</v>
       </c>
       <c r="D183" t="s">
+        <v>384</v>
+      </c>
+      <c r="E183" t="s">
+        <v>385</v>
+      </c>
+      <c r="F183" t="s">
         <v>426</v>
       </c>
-      <c r="E183" t="s">
+      <c r="G183" t="s">
         <v>427</v>
-      </c>
-      <c r="F183" t="s">
-        <v>386</v>
-      </c>
-      <c r="G183" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -6260,16 +6260,16 @@
         <v>9</v>
       </c>
       <c r="D184" t="s">
+        <v>384</v>
+      </c>
+      <c r="E184" t="s">
+        <v>385</v>
+      </c>
+      <c r="F184" t="s">
         <v>426</v>
       </c>
-      <c r="E184" t="s">
+      <c r="G184" t="s">
         <v>427</v>
-      </c>
-      <c r="F184" t="s">
-        <v>386</v>
-      </c>
-      <c r="G184" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -6283,16 +6283,16 @@
         <v>9</v>
       </c>
       <c r="D185" t="s">
+        <v>384</v>
+      </c>
+      <c r="E185" t="s">
+        <v>385</v>
+      </c>
+      <c r="F185" t="s">
         <v>426</v>
       </c>
-      <c r="E185" t="s">
+      <c r="G185" t="s">
         <v>427</v>
-      </c>
-      <c r="F185" t="s">
-        <v>386</v>
-      </c>
-      <c r="G185" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -6306,16 +6306,16 @@
         <v>9</v>
       </c>
       <c r="D186" t="s">
+        <v>384</v>
+      </c>
+      <c r="E186" t="s">
+        <v>385</v>
+      </c>
+      <c r="F186" t="s">
         <v>426</v>
       </c>
-      <c r="E186" t="s">
+      <c r="G186" t="s">
         <v>427</v>
-      </c>
-      <c r="F186" t="s">
-        <v>386</v>
-      </c>
-      <c r="G186" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -6329,16 +6329,16 @@
         <v>9</v>
       </c>
       <c r="D187" t="s">
+        <v>384</v>
+      </c>
+      <c r="E187" t="s">
+        <v>385</v>
+      </c>
+      <c r="F187" t="s">
         <v>426</v>
       </c>
-      <c r="E187" t="s">
+      <c r="G187" t="s">
         <v>427</v>
-      </c>
-      <c r="F187" t="s">
-        <v>386</v>
-      </c>
-      <c r="G187" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -6352,16 +6352,16 @@
         <v>9</v>
       </c>
       <c r="D188" t="s">
+        <v>384</v>
+      </c>
+      <c r="E188" t="s">
+        <v>385</v>
+      </c>
+      <c r="F188" t="s">
         <v>448</v>
       </c>
-      <c r="E188" t="s">
+      <c r="G188" t="s">
         <v>449</v>
-      </c>
-      <c r="F188" t="s">
-        <v>386</v>
-      </c>
-      <c r="G188" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="189" spans="1:7">

--- a/api/xlsx/en/SectorGroup.xlsx
+++ b/api/xlsx/en/SectorGroup.xlsx
@@ -25,18 +25,18 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
+    <t>codeforiati:category-name</t>
+  </si>
+  <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
-    <t>codeforiati:category-name</t>
-  </si>
-  <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -46,18 +46,18 @@
     <t>active</t>
   </si>
   <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>Education, Level Unspecified</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
     <t>110</t>
   </si>
   <si>
-    <t>Education</t>
-  </si>
-  <si>
-    <t>Education, Level Unspecified</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -82,12 +82,12 @@
     <t>Primary education</t>
   </si>
   <si>
+    <t>112</t>
+  </si>
+  <si>
     <t>Basic Education</t>
   </si>
   <si>
-    <t>112</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -112,12 +112,12 @@
     <t>Secondary education</t>
   </si>
   <si>
+    <t>113</t>
+  </si>
+  <si>
     <t>Secondary Education</t>
   </si>
   <si>
-    <t>113</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
@@ -130,12 +130,12 @@
     <t>Higher education</t>
   </si>
   <si>
+    <t>114</t>
+  </si>
+  <si>
     <t>Post-Secondary Education</t>
   </si>
   <si>
-    <t>114</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -148,18 +148,18 @@
     <t>Health policy and administrative management</t>
   </si>
   <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>Health, General</t>
+  </si>
+  <si>
+    <t>Health</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
-    <t>Health</t>
-  </si>
-  <si>
-    <t>Health, General</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -184,12 +184,12 @@
     <t>Basic health care</t>
   </si>
   <si>
+    <t>122</t>
+  </si>
+  <si>
     <t>Basic Health</t>
   </si>
   <si>
-    <t>122</t>
-  </si>
-  <si>
     <t>12230</t>
   </si>
   <si>
@@ -238,12 +238,12 @@
     <t>NCDs control, general</t>
   </si>
   <si>
+    <t>123</t>
+  </si>
+  <si>
     <t>Non-communicable diseases (NCDs)</t>
   </si>
   <si>
-    <t>123</t>
-  </si>
-  <si>
     <t>12320</t>
   </si>
   <si>
@@ -388,18 +388,18 @@
     <t>Public sector policy and administrative management</t>
   </si>
   <si>
+    <t>151</t>
+  </si>
+  <si>
+    <t>Government &amp; Civil Society-general</t>
+  </si>
+  <si>
+    <t>Government &amp; Civil Society</t>
+  </si>
+  <si>
     <t>150</t>
   </si>
   <si>
-    <t>Government &amp; Civil Society</t>
-  </si>
-  <si>
-    <t>Government &amp; Civil Society-general</t>
-  </si>
-  <si>
-    <t>151</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -496,12 +496,12 @@
     <t>Security system management and reform</t>
   </si>
   <si>
+    <t>152</t>
+  </si>
+  <si>
     <t>Conflict, Peace &amp; Security</t>
   </si>
   <si>
-    <t>152</t>
-  </si>
-  <si>
     <t>15220</t>
   </si>
   <si>
@@ -688,18 +688,18 @@
     <t>Energy policy and administrative management</t>
   </si>
   <si>
+    <t>231</t>
+  </si>
+  <si>
+    <t>Energy Policy</t>
+  </si>
+  <si>
+    <t>Energy</t>
+  </si>
+  <si>
     <t>230</t>
   </si>
   <si>
-    <t>Energy</t>
-  </si>
-  <si>
-    <t>Energy Policy</t>
-  </si>
-  <si>
-    <t>231</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -724,12 +724,12 @@
     <t>Energy generation, renewable sources - multiple technologies</t>
   </si>
   <si>
+    <t>232</t>
+  </si>
+  <si>
     <t>Energy generation, renewable sources</t>
   </si>
   <si>
-    <t>232</t>
-  </si>
-  <si>
     <t>23220</t>
   </si>
   <si>
@@ -784,12 +784,12 @@
     <t>Energy generation, non-renewable sources, unspecified</t>
   </si>
   <si>
+    <t>233</t>
+  </si>
+  <si>
     <t>Energy generation, non-renewable sources</t>
   </si>
   <si>
-    <t>233</t>
-  </si>
-  <si>
     <t>23320</t>
   </si>
   <si>
@@ -826,36 +826,36 @@
     <t>Hybrid energy electric power plants</t>
   </si>
   <si>
+    <t>234</t>
+  </si>
+  <si>
     <t>Hybrid energy plants</t>
   </si>
   <si>
-    <t>234</t>
-  </si>
-  <si>
     <t>23510</t>
   </si>
   <si>
     <t>Nuclear energy electric power plants and nuclear safety</t>
   </si>
   <si>
+    <t>235</t>
+  </si>
+  <si>
     <t>Nuclear energy plants</t>
   </si>
   <si>
-    <t>235</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
     <t>Heat plants</t>
   </si>
   <si>
+    <t>236</t>
+  </si>
+  <si>
     <t>Energy distribution</t>
   </si>
   <si>
-    <t>236</t>
-  </si>
-  <si>
     <t>23620</t>
   </si>
   <si>
@@ -970,18 +970,18 @@
     <t>Agricultural policy and administrative management</t>
   </si>
   <si>
+    <t>311</t>
+  </si>
+  <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
+    <t>Agriculture, Forestry, Fishing</t>
+  </si>
+  <si>
     <t>310</t>
   </si>
   <si>
-    <t>Agriculture, Forestry, Fishing</t>
-  </si>
-  <si>
-    <t>Agriculture</t>
-  </si>
-  <si>
-    <t>311</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1090,12 +1090,12 @@
     <t>Forestry policy and administrative management</t>
   </si>
   <si>
+    <t>312</t>
+  </si>
+  <si>
     <t>Forestry</t>
   </si>
   <si>
-    <t>312</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -1132,12 +1132,12 @@
     <t>Fishing policy and administrative management</t>
   </si>
   <si>
+    <t>313</t>
+  </si>
+  <si>
     <t>Fishing</t>
   </si>
   <si>
-    <t>313</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -1168,18 +1168,18 @@
     <t>Industrial policy and administrative management</t>
   </si>
   <si>
+    <t>321</t>
+  </si>
+  <si>
+    <t>Industry</t>
+  </si>
+  <si>
+    <t>Industry, Mining, Construction</t>
+  </si>
+  <si>
     <t>320</t>
   </si>
   <si>
-    <t>Industry, Mining, Construction</t>
-  </si>
-  <si>
-    <t>Industry</t>
-  </si>
-  <si>
-    <t>321</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1294,12 +1294,12 @@
     <t>Mineral/mining policy and administrative management</t>
   </si>
   <si>
+    <t>322</t>
+  </si>
+  <si>
     <t>Mineral Resources &amp; Mining</t>
   </si>
   <si>
-    <t>322</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -1360,10 +1360,10 @@
     <t>Construction policy and administrative management</t>
   </si>
   <si>
+    <t>323</t>
+  </si>
+  <si>
     <t>Construction</t>
-  </si>
-  <si>
-    <t>323</t>
   </si>
   <si>
     <t>33110</t>
@@ -2166,16 +2166,16 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F6" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2189,16 +2189,16 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F7" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G7" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2212,16 +2212,16 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F8" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G8" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2235,16 +2235,16 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F9" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G9" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2258,16 +2258,16 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="F10" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="G10" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2281,16 +2281,16 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="F11" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="G11" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2304,16 +2304,16 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E12" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="F12" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="G12" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2327,16 +2327,16 @@
         <v>9</v>
       </c>
       <c r="D13" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E13" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="F13" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="G13" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2442,16 +2442,16 @@
         <v>9</v>
       </c>
       <c r="D18" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E18" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F18" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G18" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2465,16 +2465,16 @@
         <v>9</v>
       </c>
       <c r="D19" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E19" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F19" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G19" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2488,16 +2488,16 @@
         <v>9</v>
       </c>
       <c r="D20" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E20" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F20" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G20" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2511,16 +2511,16 @@
         <v>9</v>
       </c>
       <c r="D21" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E21" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F21" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G21" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2534,16 +2534,16 @@
         <v>9</v>
       </c>
       <c r="D22" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E22" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F22" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G22" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2557,16 +2557,16 @@
         <v>9</v>
       </c>
       <c r="D23" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E23" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F23" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G23" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2580,16 +2580,16 @@
         <v>9</v>
       </c>
       <c r="D24" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E24" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F24" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G24" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2603,16 +2603,16 @@
         <v>9</v>
       </c>
       <c r="D25" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E25" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F25" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G25" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2626,16 +2626,16 @@
         <v>9</v>
       </c>
       <c r="D26" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E26" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="F26" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G26" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2649,16 +2649,16 @@
         <v>9</v>
       </c>
       <c r="D27" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E27" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="F27" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G27" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2672,16 +2672,16 @@
         <v>9</v>
       </c>
       <c r="D28" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E28" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="F28" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G28" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2695,16 +2695,16 @@
         <v>9</v>
       </c>
       <c r="D29" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E29" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="F29" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G29" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2718,16 +2718,16 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E30" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="F30" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G30" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2741,16 +2741,16 @@
         <v>9</v>
       </c>
       <c r="D31" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E31" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="F31" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G31" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -3500,16 +3500,16 @@
         <v>9</v>
       </c>
       <c r="D64" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E64" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="F64" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="G64" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3523,16 +3523,16 @@
         <v>9</v>
       </c>
       <c r="D65" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E65" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="F65" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="G65" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3546,16 +3546,16 @@
         <v>9</v>
       </c>
       <c r="D66" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E66" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="F66" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="G66" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3569,16 +3569,16 @@
         <v>9</v>
       </c>
       <c r="D67" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E67" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="F67" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="G67" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3592,16 +3592,16 @@
         <v>9</v>
       </c>
       <c r="D68" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E68" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="F68" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="G68" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3615,16 +3615,16 @@
         <v>9</v>
       </c>
       <c r="D69" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E69" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="F69" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="G69" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -4236,16 +4236,16 @@
         <v>9</v>
       </c>
       <c r="D96" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E96" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F96" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G96" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -4259,16 +4259,16 @@
         <v>9</v>
       </c>
       <c r="D97" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E97" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F97" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G97" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4282,16 +4282,16 @@
         <v>9</v>
       </c>
       <c r="D98" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E98" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F98" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G98" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4305,16 +4305,16 @@
         <v>9</v>
       </c>
       <c r="D99" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E99" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F99" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G99" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4328,16 +4328,16 @@
         <v>9</v>
       </c>
       <c r="D100" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E100" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F100" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G100" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4351,16 +4351,16 @@
         <v>9</v>
       </c>
       <c r="D101" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E101" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F101" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G101" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4374,16 +4374,16 @@
         <v>9</v>
       </c>
       <c r="D102" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E102" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F102" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G102" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4397,16 +4397,16 @@
         <v>9</v>
       </c>
       <c r="D103" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E103" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F103" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G103" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4420,16 +4420,16 @@
         <v>9</v>
       </c>
       <c r="D104" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E104" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F104" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G104" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4443,16 +4443,16 @@
         <v>9</v>
       </c>
       <c r="D105" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E105" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="F105" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="G105" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4466,16 +4466,16 @@
         <v>9</v>
       </c>
       <c r="D106" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E106" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="F106" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="G106" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4489,16 +4489,16 @@
         <v>9</v>
       </c>
       <c r="D107" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E107" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="F107" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="G107" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4512,16 +4512,16 @@
         <v>9</v>
       </c>
       <c r="D108" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E108" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="F108" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="G108" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4535,16 +4535,16 @@
         <v>9</v>
       </c>
       <c r="D109" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E109" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="F109" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="G109" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4558,16 +4558,16 @@
         <v>9</v>
       </c>
       <c r="D110" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E110" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="F110" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="G110" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4581,16 +4581,16 @@
         <v>9</v>
       </c>
       <c r="D111" t="s">
-        <v>224</v>
+        <v>270</v>
       </c>
       <c r="E111" t="s">
-        <v>225</v>
+        <v>271</v>
       </c>
       <c r="F111" t="s">
-        <v>270</v>
+        <v>226</v>
       </c>
       <c r="G111" t="s">
-        <v>271</v>
+        <v>227</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4604,16 +4604,16 @@
         <v>9</v>
       </c>
       <c r="D112" t="s">
-        <v>224</v>
+        <v>274</v>
       </c>
       <c r="E112" t="s">
-        <v>225</v>
+        <v>275</v>
       </c>
       <c r="F112" t="s">
-        <v>274</v>
+        <v>226</v>
       </c>
       <c r="G112" t="s">
-        <v>275</v>
+        <v>227</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4627,16 +4627,16 @@
         <v>9</v>
       </c>
       <c r="D113" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E113" t="s">
-        <v>225</v>
+        <v>279</v>
       </c>
       <c r="F113" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="G113" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4650,16 +4650,16 @@
         <v>9</v>
       </c>
       <c r="D114" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E114" t="s">
-        <v>225</v>
+        <v>279</v>
       </c>
       <c r="F114" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="G114" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4673,16 +4673,16 @@
         <v>9</v>
       </c>
       <c r="D115" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E115" t="s">
-        <v>225</v>
+        <v>279</v>
       </c>
       <c r="F115" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="G115" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4696,16 +4696,16 @@
         <v>9</v>
       </c>
       <c r="D116" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E116" t="s">
-        <v>225</v>
+        <v>279</v>
       </c>
       <c r="F116" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="G116" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4719,16 +4719,16 @@
         <v>9</v>
       </c>
       <c r="D117" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E117" t="s">
-        <v>225</v>
+        <v>279</v>
       </c>
       <c r="F117" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="G117" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4742,16 +4742,16 @@
         <v>9</v>
       </c>
       <c r="D118" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E118" t="s">
-        <v>225</v>
+        <v>279</v>
       </c>
       <c r="F118" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="G118" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4765,16 +4765,16 @@
         <v>9</v>
       </c>
       <c r="D119" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E119" t="s">
-        <v>225</v>
+        <v>279</v>
       </c>
       <c r="F119" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="G119" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -5432,16 +5432,16 @@
         <v>9</v>
       </c>
       <c r="D148" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E148" t="s">
-        <v>319</v>
+        <v>359</v>
       </c>
       <c r="F148" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
       <c r="G148" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5455,16 +5455,16 @@
         <v>9</v>
       </c>
       <c r="D149" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E149" t="s">
-        <v>319</v>
+        <v>359</v>
       </c>
       <c r="F149" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
       <c r="G149" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5478,16 +5478,16 @@
         <v>9</v>
       </c>
       <c r="D150" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E150" t="s">
-        <v>319</v>
+        <v>359</v>
       </c>
       <c r="F150" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
       <c r="G150" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5501,16 +5501,16 @@
         <v>9</v>
       </c>
       <c r="D151" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E151" t="s">
-        <v>319</v>
+        <v>359</v>
       </c>
       <c r="F151" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
       <c r="G151" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5524,16 +5524,16 @@
         <v>9</v>
       </c>
       <c r="D152" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E152" t="s">
-        <v>319</v>
+        <v>359</v>
       </c>
       <c r="F152" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
       <c r="G152" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5547,16 +5547,16 @@
         <v>9</v>
       </c>
       <c r="D153" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E153" t="s">
-        <v>319</v>
+        <v>359</v>
       </c>
       <c r="F153" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
       <c r="G153" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5570,16 +5570,16 @@
         <v>9</v>
       </c>
       <c r="D154" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="E154" t="s">
-        <v>319</v>
+        <v>373</v>
       </c>
       <c r="F154" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
       <c r="G154" t="s">
-        <v>373</v>
+        <v>321</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5593,16 +5593,16 @@
         <v>9</v>
       </c>
       <c r="D155" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="E155" t="s">
-        <v>319</v>
+        <v>373</v>
       </c>
       <c r="F155" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
       <c r="G155" t="s">
-        <v>373</v>
+        <v>321</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5616,16 +5616,16 @@
         <v>9</v>
       </c>
       <c r="D156" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="E156" t="s">
-        <v>319</v>
+        <v>373</v>
       </c>
       <c r="F156" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
       <c r="G156" t="s">
-        <v>373</v>
+        <v>321</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5639,16 +5639,16 @@
         <v>9</v>
       </c>
       <c r="D157" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="E157" t="s">
-        <v>319</v>
+        <v>373</v>
       </c>
       <c r="F157" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
       <c r="G157" t="s">
-        <v>373</v>
+        <v>321</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5662,16 +5662,16 @@
         <v>9</v>
       </c>
       <c r="D158" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="E158" t="s">
-        <v>319</v>
+        <v>373</v>
       </c>
       <c r="F158" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
       <c r="G158" t="s">
-        <v>373</v>
+        <v>321</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -6122,16 +6122,16 @@
         <v>9</v>
       </c>
       <c r="D178" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E178" t="s">
-        <v>385</v>
+        <v>427</v>
       </c>
       <c r="F178" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
       <c r="G178" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -6145,16 +6145,16 @@
         <v>9</v>
       </c>
       <c r="D179" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E179" t="s">
-        <v>385</v>
+        <v>427</v>
       </c>
       <c r="F179" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
       <c r="G179" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -6168,16 +6168,16 @@
         <v>9</v>
       </c>
       <c r="D180" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E180" t="s">
-        <v>385</v>
+        <v>427</v>
       </c>
       <c r="F180" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
       <c r="G180" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -6191,16 +6191,16 @@
         <v>9</v>
       </c>
       <c r="D181" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E181" t="s">
-        <v>385</v>
+        <v>427</v>
       </c>
       <c r="F181" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
       <c r="G181" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -6214,16 +6214,16 @@
         <v>9</v>
       </c>
       <c r="D182" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E182" t="s">
-        <v>385</v>
+        <v>427</v>
       </c>
       <c r="F182" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
       <c r="G182" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -6237,16 +6237,16 @@
         <v>9</v>
       </c>
       <c r="D183" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E183" t="s">
-        <v>385</v>
+        <v>427</v>
       </c>
       <c r="F183" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
       <c r="G183" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -6260,16 +6260,16 @@
         <v>9</v>
       </c>
       <c r="D184" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E184" t="s">
-        <v>385</v>
+        <v>427</v>
       </c>
       <c r="F184" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
       <c r="G184" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -6283,16 +6283,16 @@
         <v>9</v>
       </c>
       <c r="D185" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E185" t="s">
-        <v>385</v>
+        <v>427</v>
       </c>
       <c r="F185" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
       <c r="G185" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -6306,16 +6306,16 @@
         <v>9</v>
       </c>
       <c r="D186" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E186" t="s">
-        <v>385</v>
+        <v>427</v>
       </c>
       <c r="F186" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
       <c r="G186" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -6329,16 +6329,16 @@
         <v>9</v>
       </c>
       <c r="D187" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E187" t="s">
-        <v>385</v>
+        <v>427</v>
       </c>
       <c r="F187" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
       <c r="G187" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -6352,16 +6352,16 @@
         <v>9</v>
       </c>
       <c r="D188" t="s">
-        <v>384</v>
+        <v>448</v>
       </c>
       <c r="E188" t="s">
-        <v>385</v>
+        <v>449</v>
       </c>
       <c r="F188" t="s">
-        <v>448</v>
+        <v>386</v>
       </c>
       <c r="G188" t="s">
-        <v>449</v>
+        <v>387</v>
       </c>
     </row>
     <row r="189" spans="1:7">

--- a/api/xlsx/en/SectorGroup.xlsx
+++ b/api/xlsx/en/SectorGroup.xlsx
@@ -28,15 +28,15 @@
     <t>codeforiati:category-code</t>
   </si>
   <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
     <t>codeforiati:category-name</t>
   </si>
   <si>
     <t>codeforiati:group-name</t>
   </si>
   <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -49,15 +49,15 @@
     <t>111</t>
   </si>
   <si>
+    <t>110</t>
+  </si>
+  <si>
     <t>Education, Level Unspecified</t>
   </si>
   <si>
     <t>Education</t>
   </si>
   <si>
-    <t>110</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -151,15 +151,15 @@
     <t>121</t>
   </si>
   <si>
+    <t>120</t>
+  </si>
+  <si>
     <t>Health, General</t>
   </si>
   <si>
     <t>Health</t>
   </si>
   <si>
-    <t>120</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -391,15 +391,15 @@
     <t>151</t>
   </si>
   <si>
+    <t>150</t>
+  </si>
+  <si>
     <t>Government &amp; Civil Society-general</t>
   </si>
   <si>
     <t>Government &amp; Civil Society</t>
   </si>
   <si>
-    <t>150</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -691,15 +691,15 @@
     <t>231</t>
   </si>
   <si>
+    <t>230</t>
+  </si>
+  <si>
     <t>Energy Policy</t>
   </si>
   <si>
     <t>Energy</t>
   </si>
   <si>
-    <t>230</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -973,15 +973,15 @@
     <t>311</t>
   </si>
   <si>
+    <t>310</t>
+  </si>
+  <si>
     <t>Agriculture</t>
   </si>
   <si>
     <t>Agriculture, Forestry, Fishing</t>
   </si>
   <si>
-    <t>310</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1171,13 +1171,13 @@
     <t>321</t>
   </si>
   <si>
+    <t>320</t>
+  </si>
+  <si>
     <t>Industry</t>
   </si>
   <si>
     <t>Industry, Mining, Construction</t>
-  </si>
-  <si>
-    <t>320</t>
   </si>
   <si>
     <t>32120</t>
@@ -2169,10 +2169,10 @@
         <v>22</v>
       </c>
       <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" t="s">
         <v>23</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
       </c>
       <c r="G6" t="s">
         <v>13</v>
@@ -2192,10 +2192,10 @@
         <v>22</v>
       </c>
       <c r="E7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" t="s">
         <v>23</v>
-      </c>
-      <c r="F7" t="s">
-        <v>12</v>
       </c>
       <c r="G7" t="s">
         <v>13</v>
@@ -2215,10 +2215,10 @@
         <v>22</v>
       </c>
       <c r="E8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" t="s">
         <v>23</v>
-      </c>
-      <c r="F8" t="s">
-        <v>12</v>
       </c>
       <c r="G8" t="s">
         <v>13</v>
@@ -2238,10 +2238,10 @@
         <v>22</v>
       </c>
       <c r="E9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" t="s">
         <v>23</v>
-      </c>
-      <c r="F9" t="s">
-        <v>12</v>
       </c>
       <c r="G9" t="s">
         <v>13</v>
@@ -2261,10 +2261,10 @@
         <v>32</v>
       </c>
       <c r="E10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" t="s">
         <v>33</v>
-      </c>
-      <c r="F10" t="s">
-        <v>12</v>
       </c>
       <c r="G10" t="s">
         <v>13</v>
@@ -2284,10 +2284,10 @@
         <v>32</v>
       </c>
       <c r="E11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" t="s">
         <v>33</v>
-      </c>
-      <c r="F11" t="s">
-        <v>12</v>
       </c>
       <c r="G11" t="s">
         <v>13</v>
@@ -2307,10 +2307,10 @@
         <v>38</v>
       </c>
       <c r="E12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" t="s">
         <v>39</v>
-      </c>
-      <c r="F12" t="s">
-        <v>12</v>
       </c>
       <c r="G12" t="s">
         <v>13</v>
@@ -2330,10 +2330,10 @@
         <v>38</v>
       </c>
       <c r="E13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" t="s">
         <v>39</v>
-      </c>
-      <c r="F13" t="s">
-        <v>12</v>
       </c>
       <c r="G13" t="s">
         <v>13</v>
@@ -2445,10 +2445,10 @@
         <v>56</v>
       </c>
       <c r="E18" t="s">
+        <v>45</v>
+      </c>
+      <c r="F18" t="s">
         <v>57</v>
-      </c>
-      <c r="F18" t="s">
-        <v>46</v>
       </c>
       <c r="G18" t="s">
         <v>47</v>
@@ -2468,10 +2468,10 @@
         <v>56</v>
       </c>
       <c r="E19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F19" t="s">
         <v>57</v>
-      </c>
-      <c r="F19" t="s">
-        <v>46</v>
       </c>
       <c r="G19" t="s">
         <v>47</v>
@@ -2491,10 +2491,10 @@
         <v>56</v>
       </c>
       <c r="E20" t="s">
+        <v>45</v>
+      </c>
+      <c r="F20" t="s">
         <v>57</v>
-      </c>
-      <c r="F20" t="s">
-        <v>46</v>
       </c>
       <c r="G20" t="s">
         <v>47</v>
@@ -2514,10 +2514,10 @@
         <v>56</v>
       </c>
       <c r="E21" t="s">
+        <v>45</v>
+      </c>
+      <c r="F21" t="s">
         <v>57</v>
-      </c>
-      <c r="F21" t="s">
-        <v>46</v>
       </c>
       <c r="G21" t="s">
         <v>47</v>
@@ -2537,10 +2537,10 @@
         <v>56</v>
       </c>
       <c r="E22" t="s">
+        <v>45</v>
+      </c>
+      <c r="F22" t="s">
         <v>57</v>
-      </c>
-      <c r="F22" t="s">
-        <v>46</v>
       </c>
       <c r="G22" t="s">
         <v>47</v>
@@ -2560,10 +2560,10 @@
         <v>56</v>
       </c>
       <c r="E23" t="s">
+        <v>45</v>
+      </c>
+      <c r="F23" t="s">
         <v>57</v>
-      </c>
-      <c r="F23" t="s">
-        <v>46</v>
       </c>
       <c r="G23" t="s">
         <v>47</v>
@@ -2583,10 +2583,10 @@
         <v>56</v>
       </c>
       <c r="E24" t="s">
+        <v>45</v>
+      </c>
+      <c r="F24" t="s">
         <v>57</v>
-      </c>
-      <c r="F24" t="s">
-        <v>46</v>
       </c>
       <c r="G24" t="s">
         <v>47</v>
@@ -2606,10 +2606,10 @@
         <v>56</v>
       </c>
       <c r="E25" t="s">
+        <v>45</v>
+      </c>
+      <c r="F25" t="s">
         <v>57</v>
-      </c>
-      <c r="F25" t="s">
-        <v>46</v>
       </c>
       <c r="G25" t="s">
         <v>47</v>
@@ -2629,10 +2629,10 @@
         <v>74</v>
       </c>
       <c r="E26" t="s">
+        <v>45</v>
+      </c>
+      <c r="F26" t="s">
         <v>75</v>
-      </c>
-      <c r="F26" t="s">
-        <v>46</v>
       </c>
       <c r="G26" t="s">
         <v>47</v>
@@ -2652,10 +2652,10 @@
         <v>74</v>
       </c>
       <c r="E27" t="s">
+        <v>45</v>
+      </c>
+      <c r="F27" t="s">
         <v>75</v>
-      </c>
-      <c r="F27" t="s">
-        <v>46</v>
       </c>
       <c r="G27" t="s">
         <v>47</v>
@@ -2675,10 +2675,10 @@
         <v>74</v>
       </c>
       <c r="E28" t="s">
+        <v>45</v>
+      </c>
+      <c r="F28" t="s">
         <v>75</v>
-      </c>
-      <c r="F28" t="s">
-        <v>46</v>
       </c>
       <c r="G28" t="s">
         <v>47</v>
@@ -2698,10 +2698,10 @@
         <v>74</v>
       </c>
       <c r="E29" t="s">
+        <v>45</v>
+      </c>
+      <c r="F29" t="s">
         <v>75</v>
-      </c>
-      <c r="F29" t="s">
-        <v>46</v>
       </c>
       <c r="G29" t="s">
         <v>47</v>
@@ -2721,10 +2721,10 @@
         <v>74</v>
       </c>
       <c r="E30" t="s">
+        <v>45</v>
+      </c>
+      <c r="F30" t="s">
         <v>75</v>
-      </c>
-      <c r="F30" t="s">
-        <v>46</v>
       </c>
       <c r="G30" t="s">
         <v>47</v>
@@ -2744,10 +2744,10 @@
         <v>74</v>
       </c>
       <c r="E31" t="s">
+        <v>45</v>
+      </c>
+      <c r="F31" t="s">
         <v>75</v>
-      </c>
-      <c r="F31" t="s">
-        <v>46</v>
       </c>
       <c r="G31" t="s">
         <v>47</v>
@@ -2767,13 +2767,13 @@
         <v>88</v>
       </c>
       <c r="E32" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F32" t="s">
         <v>89</v>
       </c>
       <c r="G32" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2790,13 +2790,13 @@
         <v>88</v>
       </c>
       <c r="E33" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F33" t="s">
         <v>89</v>
       </c>
       <c r="G33" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2813,13 +2813,13 @@
         <v>88</v>
       </c>
       <c r="E34" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F34" t="s">
         <v>89</v>
       </c>
       <c r="G34" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2836,13 +2836,13 @@
         <v>88</v>
       </c>
       <c r="E35" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F35" t="s">
         <v>89</v>
       </c>
       <c r="G35" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2859,13 +2859,13 @@
         <v>88</v>
       </c>
       <c r="E36" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F36" t="s">
         <v>89</v>
       </c>
       <c r="G36" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2882,13 +2882,13 @@
         <v>100</v>
       </c>
       <c r="E37" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F37" t="s">
         <v>101</v>
       </c>
       <c r="G37" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2905,13 +2905,13 @@
         <v>100</v>
       </c>
       <c r="E38" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F38" t="s">
         <v>101</v>
       </c>
       <c r="G38" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2928,13 +2928,13 @@
         <v>100</v>
       </c>
       <c r="E39" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F39" t="s">
         <v>101</v>
       </c>
       <c r="G39" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2951,13 +2951,13 @@
         <v>100</v>
       </c>
       <c r="E40" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F40" t="s">
         <v>101</v>
       </c>
       <c r="G40" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2974,13 +2974,13 @@
         <v>100</v>
       </c>
       <c r="E41" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F41" t="s">
         <v>101</v>
       </c>
       <c r="G41" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2997,13 +2997,13 @@
         <v>100</v>
       </c>
       <c r="E42" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F42" t="s">
         <v>101</v>
       </c>
       <c r="G42" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3020,13 +3020,13 @@
         <v>100</v>
       </c>
       <c r="E43" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F43" t="s">
         <v>101</v>
       </c>
       <c r="G43" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3043,13 +3043,13 @@
         <v>100</v>
       </c>
       <c r="E44" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F44" t="s">
         <v>101</v>
       </c>
       <c r="G44" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3066,13 +3066,13 @@
         <v>100</v>
       </c>
       <c r="E45" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F45" t="s">
         <v>101</v>
       </c>
       <c r="G45" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3089,13 +3089,13 @@
         <v>100</v>
       </c>
       <c r="E46" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F46" t="s">
         <v>101</v>
       </c>
       <c r="G46" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3112,13 +3112,13 @@
         <v>100</v>
       </c>
       <c r="E47" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F47" t="s">
         <v>101</v>
       </c>
       <c r="G47" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3503,10 +3503,10 @@
         <v>160</v>
       </c>
       <c r="E64" t="s">
+        <v>125</v>
+      </c>
+      <c r="F64" t="s">
         <v>161</v>
-      </c>
-      <c r="F64" t="s">
-        <v>126</v>
       </c>
       <c r="G64" t="s">
         <v>127</v>
@@ -3526,10 +3526,10 @@
         <v>160</v>
       </c>
       <c r="E65" t="s">
+        <v>125</v>
+      </c>
+      <c r="F65" t="s">
         <v>161</v>
-      </c>
-      <c r="F65" t="s">
-        <v>126</v>
       </c>
       <c r="G65" t="s">
         <v>127</v>
@@ -3549,10 +3549,10 @@
         <v>160</v>
       </c>
       <c r="E66" t="s">
+        <v>125</v>
+      </c>
+      <c r="F66" t="s">
         <v>161</v>
-      </c>
-      <c r="F66" t="s">
-        <v>126</v>
       </c>
       <c r="G66" t="s">
         <v>127</v>
@@ -3572,10 +3572,10 @@
         <v>160</v>
       </c>
       <c r="E67" t="s">
+        <v>125</v>
+      </c>
+      <c r="F67" t="s">
         <v>161</v>
-      </c>
-      <c r="F67" t="s">
-        <v>126</v>
       </c>
       <c r="G67" t="s">
         <v>127</v>
@@ -3595,10 +3595,10 @@
         <v>160</v>
       </c>
       <c r="E68" t="s">
+        <v>125</v>
+      </c>
+      <c r="F68" t="s">
         <v>161</v>
-      </c>
-      <c r="F68" t="s">
-        <v>126</v>
       </c>
       <c r="G68" t="s">
         <v>127</v>
@@ -3618,10 +3618,10 @@
         <v>160</v>
       </c>
       <c r="E69" t="s">
+        <v>125</v>
+      </c>
+      <c r="F69" t="s">
         <v>161</v>
-      </c>
-      <c r="F69" t="s">
-        <v>126</v>
       </c>
       <c r="G69" t="s">
         <v>127</v>
@@ -3641,13 +3641,13 @@
         <v>174</v>
       </c>
       <c r="E70" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F70" t="s">
         <v>175</v>
       </c>
       <c r="G70" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3664,13 +3664,13 @@
         <v>174</v>
       </c>
       <c r="E71" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F71" t="s">
         <v>175</v>
       </c>
       <c r="G71" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3687,13 +3687,13 @@
         <v>174</v>
       </c>
       <c r="E72" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F72" t="s">
         <v>175</v>
       </c>
       <c r="G72" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3710,13 +3710,13 @@
         <v>174</v>
       </c>
       <c r="E73" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F73" t="s">
         <v>175</v>
       </c>
       <c r="G73" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3733,13 +3733,13 @@
         <v>174</v>
       </c>
       <c r="E74" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F74" t="s">
         <v>175</v>
       </c>
       <c r="G74" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3756,13 +3756,13 @@
         <v>174</v>
       </c>
       <c r="E75" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F75" t="s">
         <v>175</v>
       </c>
       <c r="G75" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3779,13 +3779,13 @@
         <v>174</v>
       </c>
       <c r="E76" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F76" t="s">
         <v>175</v>
       </c>
       <c r="G76" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3802,13 +3802,13 @@
         <v>174</v>
       </c>
       <c r="E77" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F77" t="s">
         <v>175</v>
       </c>
       <c r="G77" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3825,13 +3825,13 @@
         <v>174</v>
       </c>
       <c r="E78" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F78" t="s">
         <v>175</v>
       </c>
       <c r="G78" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3848,13 +3848,13 @@
         <v>174</v>
       </c>
       <c r="E79" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F79" t="s">
         <v>175</v>
       </c>
       <c r="G79" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3871,13 +3871,13 @@
         <v>174</v>
       </c>
       <c r="E80" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F80" t="s">
         <v>175</v>
       </c>
       <c r="G80" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3894,13 +3894,13 @@
         <v>198</v>
       </c>
       <c r="E81" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F81" t="s">
         <v>199</v>
       </c>
       <c r="G81" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3917,13 +3917,13 @@
         <v>198</v>
       </c>
       <c r="E82" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F82" t="s">
         <v>199</v>
       </c>
       <c r="G82" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3940,13 +3940,13 @@
         <v>198</v>
       </c>
       <c r="E83" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F83" t="s">
         <v>199</v>
       </c>
       <c r="G83" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3963,13 +3963,13 @@
         <v>198</v>
       </c>
       <c r="E84" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F84" t="s">
         <v>199</v>
       </c>
       <c r="G84" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3986,13 +3986,13 @@
         <v>198</v>
       </c>
       <c r="E85" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F85" t="s">
         <v>199</v>
       </c>
       <c r="G85" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4009,13 +4009,13 @@
         <v>198</v>
       </c>
       <c r="E86" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F86" t="s">
         <v>199</v>
       </c>
       <c r="G86" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4032,13 +4032,13 @@
         <v>198</v>
       </c>
       <c r="E87" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F87" t="s">
         <v>199</v>
       </c>
       <c r="G87" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4055,13 +4055,13 @@
         <v>214</v>
       </c>
       <c r="E88" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F88" t="s">
         <v>215</v>
       </c>
       <c r="G88" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4078,13 +4078,13 @@
         <v>214</v>
       </c>
       <c r="E89" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F89" t="s">
         <v>215</v>
       </c>
       <c r="G89" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4101,13 +4101,13 @@
         <v>214</v>
       </c>
       <c r="E90" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F90" t="s">
         <v>215</v>
       </c>
       <c r="G90" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4124,13 +4124,13 @@
         <v>214</v>
       </c>
       <c r="E91" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F91" t="s">
         <v>215</v>
       </c>
       <c r="G91" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4239,10 +4239,10 @@
         <v>236</v>
       </c>
       <c r="E96" t="s">
+        <v>225</v>
+      </c>
+      <c r="F96" t="s">
         <v>237</v>
-      </c>
-      <c r="F96" t="s">
-        <v>226</v>
       </c>
       <c r="G96" t="s">
         <v>227</v>
@@ -4262,10 +4262,10 @@
         <v>236</v>
       </c>
       <c r="E97" t="s">
+        <v>225</v>
+      </c>
+      <c r="F97" t="s">
         <v>237</v>
-      </c>
-      <c r="F97" t="s">
-        <v>226</v>
       </c>
       <c r="G97" t="s">
         <v>227</v>
@@ -4285,10 +4285,10 @@
         <v>236</v>
       </c>
       <c r="E98" t="s">
+        <v>225</v>
+      </c>
+      <c r="F98" t="s">
         <v>237</v>
-      </c>
-      <c r="F98" t="s">
-        <v>226</v>
       </c>
       <c r="G98" t="s">
         <v>227</v>
@@ -4308,10 +4308,10 @@
         <v>236</v>
       </c>
       <c r="E99" t="s">
+        <v>225</v>
+      </c>
+      <c r="F99" t="s">
         <v>237</v>
-      </c>
-      <c r="F99" t="s">
-        <v>226</v>
       </c>
       <c r="G99" t="s">
         <v>227</v>
@@ -4331,10 +4331,10 @@
         <v>236</v>
       </c>
       <c r="E100" t="s">
+        <v>225</v>
+      </c>
+      <c r="F100" t="s">
         <v>237</v>
-      </c>
-      <c r="F100" t="s">
-        <v>226</v>
       </c>
       <c r="G100" t="s">
         <v>227</v>
@@ -4354,10 +4354,10 @@
         <v>236</v>
       </c>
       <c r="E101" t="s">
+        <v>225</v>
+      </c>
+      <c r="F101" t="s">
         <v>237</v>
-      </c>
-      <c r="F101" t="s">
-        <v>226</v>
       </c>
       <c r="G101" t="s">
         <v>227</v>
@@ -4377,10 +4377,10 @@
         <v>236</v>
       </c>
       <c r="E102" t="s">
+        <v>225</v>
+      </c>
+      <c r="F102" t="s">
         <v>237</v>
-      </c>
-      <c r="F102" t="s">
-        <v>226</v>
       </c>
       <c r="G102" t="s">
         <v>227</v>
@@ -4400,10 +4400,10 @@
         <v>236</v>
       </c>
       <c r="E103" t="s">
+        <v>225</v>
+      </c>
+      <c r="F103" t="s">
         <v>237</v>
-      </c>
-      <c r="F103" t="s">
-        <v>226</v>
       </c>
       <c r="G103" t="s">
         <v>227</v>
@@ -4423,10 +4423,10 @@
         <v>236</v>
       </c>
       <c r="E104" t="s">
+        <v>225</v>
+      </c>
+      <c r="F104" t="s">
         <v>237</v>
-      </c>
-      <c r="F104" t="s">
-        <v>226</v>
       </c>
       <c r="G104" t="s">
         <v>227</v>
@@ -4446,10 +4446,10 @@
         <v>256</v>
       </c>
       <c r="E105" t="s">
+        <v>225</v>
+      </c>
+      <c r="F105" t="s">
         <v>257</v>
-      </c>
-      <c r="F105" t="s">
-        <v>226</v>
       </c>
       <c r="G105" t="s">
         <v>227</v>
@@ -4469,10 +4469,10 @@
         <v>256</v>
       </c>
       <c r="E106" t="s">
+        <v>225</v>
+      </c>
+      <c r="F106" t="s">
         <v>257</v>
-      </c>
-      <c r="F106" t="s">
-        <v>226</v>
       </c>
       <c r="G106" t="s">
         <v>227</v>
@@ -4492,10 +4492,10 @@
         <v>256</v>
       </c>
       <c r="E107" t="s">
+        <v>225</v>
+      </c>
+      <c r="F107" t="s">
         <v>257</v>
-      </c>
-      <c r="F107" t="s">
-        <v>226</v>
       </c>
       <c r="G107" t="s">
         <v>227</v>
@@ -4515,10 +4515,10 @@
         <v>256</v>
       </c>
       <c r="E108" t="s">
+        <v>225</v>
+      </c>
+      <c r="F108" t="s">
         <v>257</v>
-      </c>
-      <c r="F108" t="s">
-        <v>226</v>
       </c>
       <c r="G108" t="s">
         <v>227</v>
@@ -4538,10 +4538,10 @@
         <v>256</v>
       </c>
       <c r="E109" t="s">
+        <v>225</v>
+      </c>
+      <c r="F109" t="s">
         <v>257</v>
-      </c>
-      <c r="F109" t="s">
-        <v>226</v>
       </c>
       <c r="G109" t="s">
         <v>227</v>
@@ -4561,10 +4561,10 @@
         <v>256</v>
       </c>
       <c r="E110" t="s">
+        <v>225</v>
+      </c>
+      <c r="F110" t="s">
         <v>257</v>
-      </c>
-      <c r="F110" t="s">
-        <v>226</v>
       </c>
       <c r="G110" t="s">
         <v>227</v>
@@ -4584,10 +4584,10 @@
         <v>270</v>
       </c>
       <c r="E111" t="s">
+        <v>225</v>
+      </c>
+      <c r="F111" t="s">
         <v>271</v>
-      </c>
-      <c r="F111" t="s">
-        <v>226</v>
       </c>
       <c r="G111" t="s">
         <v>227</v>
@@ -4607,10 +4607,10 @@
         <v>274</v>
       </c>
       <c r="E112" t="s">
+        <v>225</v>
+      </c>
+      <c r="F112" t="s">
         <v>275</v>
-      </c>
-      <c r="F112" t="s">
-        <v>226</v>
       </c>
       <c r="G112" t="s">
         <v>227</v>
@@ -4630,10 +4630,10 @@
         <v>278</v>
       </c>
       <c r="E113" t="s">
+        <v>225</v>
+      </c>
+      <c r="F113" t="s">
         <v>279</v>
-      </c>
-      <c r="F113" t="s">
-        <v>226</v>
       </c>
       <c r="G113" t="s">
         <v>227</v>
@@ -4653,10 +4653,10 @@
         <v>278</v>
       </c>
       <c r="E114" t="s">
+        <v>225</v>
+      </c>
+      <c r="F114" t="s">
         <v>279</v>
-      </c>
-      <c r="F114" t="s">
-        <v>226</v>
       </c>
       <c r="G114" t="s">
         <v>227</v>
@@ -4676,10 +4676,10 @@
         <v>278</v>
       </c>
       <c r="E115" t="s">
+        <v>225</v>
+      </c>
+      <c r="F115" t="s">
         <v>279</v>
-      </c>
-      <c r="F115" t="s">
-        <v>226</v>
       </c>
       <c r="G115" t="s">
         <v>227</v>
@@ -4699,10 +4699,10 @@
         <v>278</v>
       </c>
       <c r="E116" t="s">
+        <v>225</v>
+      </c>
+      <c r="F116" t="s">
         <v>279</v>
-      </c>
-      <c r="F116" t="s">
-        <v>226</v>
       </c>
       <c r="G116" t="s">
         <v>227</v>
@@ -4722,10 +4722,10 @@
         <v>278</v>
       </c>
       <c r="E117" t="s">
+        <v>225</v>
+      </c>
+      <c r="F117" t="s">
         <v>279</v>
-      </c>
-      <c r="F117" t="s">
-        <v>226</v>
       </c>
       <c r="G117" t="s">
         <v>227</v>
@@ -4745,10 +4745,10 @@
         <v>278</v>
       </c>
       <c r="E118" t="s">
+        <v>225</v>
+      </c>
+      <c r="F118" t="s">
         <v>279</v>
-      </c>
-      <c r="F118" t="s">
-        <v>226</v>
       </c>
       <c r="G118" t="s">
         <v>227</v>
@@ -4768,10 +4768,10 @@
         <v>278</v>
       </c>
       <c r="E119" t="s">
+        <v>225</v>
+      </c>
+      <c r="F119" t="s">
         <v>279</v>
-      </c>
-      <c r="F119" t="s">
-        <v>226</v>
       </c>
       <c r="G119" t="s">
         <v>227</v>
@@ -4791,13 +4791,13 @@
         <v>294</v>
       </c>
       <c r="E120" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F120" t="s">
         <v>295</v>
       </c>
       <c r="G120" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4814,13 +4814,13 @@
         <v>294</v>
       </c>
       <c r="E121" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F121" t="s">
         <v>295</v>
       </c>
       <c r="G121" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4837,13 +4837,13 @@
         <v>294</v>
       </c>
       <c r="E122" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F122" t="s">
         <v>295</v>
       </c>
       <c r="G122" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4860,13 +4860,13 @@
         <v>294</v>
       </c>
       <c r="E123" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F123" t="s">
         <v>295</v>
       </c>
       <c r="G123" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4883,13 +4883,13 @@
         <v>294</v>
       </c>
       <c r="E124" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F124" t="s">
         <v>295</v>
       </c>
       <c r="G124" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4906,13 +4906,13 @@
         <v>294</v>
       </c>
       <c r="E125" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F125" t="s">
         <v>295</v>
       </c>
       <c r="G125" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4929,13 +4929,13 @@
         <v>308</v>
       </c>
       <c r="E126" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F126" t="s">
         <v>309</v>
       </c>
       <c r="G126" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4952,13 +4952,13 @@
         <v>308</v>
       </c>
       <c r="E127" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F127" t="s">
         <v>309</v>
       </c>
       <c r="G127" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4975,13 +4975,13 @@
         <v>308</v>
       </c>
       <c r="E128" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F128" t="s">
         <v>309</v>
       </c>
       <c r="G128" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4998,13 +4998,13 @@
         <v>308</v>
       </c>
       <c r="E129" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F129" t="s">
         <v>309</v>
       </c>
       <c r="G129" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -5435,10 +5435,10 @@
         <v>358</v>
       </c>
       <c r="E148" t="s">
+        <v>319</v>
+      </c>
+      <c r="F148" t="s">
         <v>359</v>
-      </c>
-      <c r="F148" t="s">
-        <v>320</v>
       </c>
       <c r="G148" t="s">
         <v>321</v>
@@ -5458,10 +5458,10 @@
         <v>358</v>
       </c>
       <c r="E149" t="s">
+        <v>319</v>
+      </c>
+      <c r="F149" t="s">
         <v>359</v>
-      </c>
-      <c r="F149" t="s">
-        <v>320</v>
       </c>
       <c r="G149" t="s">
         <v>321</v>
@@ -5481,10 +5481,10 @@
         <v>358</v>
       </c>
       <c r="E150" t="s">
+        <v>319</v>
+      </c>
+      <c r="F150" t="s">
         <v>359</v>
-      </c>
-      <c r="F150" t="s">
-        <v>320</v>
       </c>
       <c r="G150" t="s">
         <v>321</v>
@@ -5504,10 +5504,10 @@
         <v>358</v>
       </c>
       <c r="E151" t="s">
+        <v>319</v>
+      </c>
+      <c r="F151" t="s">
         <v>359</v>
-      </c>
-      <c r="F151" t="s">
-        <v>320</v>
       </c>
       <c r="G151" t="s">
         <v>321</v>
@@ -5527,10 +5527,10 @@
         <v>358</v>
       </c>
       <c r="E152" t="s">
+        <v>319</v>
+      </c>
+      <c r="F152" t="s">
         <v>359</v>
-      </c>
-      <c r="F152" t="s">
-        <v>320</v>
       </c>
       <c r="G152" t="s">
         <v>321</v>
@@ -5550,10 +5550,10 @@
         <v>358</v>
       </c>
       <c r="E153" t="s">
+        <v>319</v>
+      </c>
+      <c r="F153" t="s">
         <v>359</v>
-      </c>
-      <c r="F153" t="s">
-        <v>320</v>
       </c>
       <c r="G153" t="s">
         <v>321</v>
@@ -5573,10 +5573,10 @@
         <v>372</v>
       </c>
       <c r="E154" t="s">
+        <v>319</v>
+      </c>
+      <c r="F154" t="s">
         <v>373</v>
-      </c>
-      <c r="F154" t="s">
-        <v>320</v>
       </c>
       <c r="G154" t="s">
         <v>321</v>
@@ -5596,10 +5596,10 @@
         <v>372</v>
       </c>
       <c r="E155" t="s">
+        <v>319</v>
+      </c>
+      <c r="F155" t="s">
         <v>373</v>
-      </c>
-      <c r="F155" t="s">
-        <v>320</v>
       </c>
       <c r="G155" t="s">
         <v>321</v>
@@ -5619,10 +5619,10 @@
         <v>372</v>
       </c>
       <c r="E156" t="s">
+        <v>319</v>
+      </c>
+      <c r="F156" t="s">
         <v>373</v>
-      </c>
-      <c r="F156" t="s">
-        <v>320</v>
       </c>
       <c r="G156" t="s">
         <v>321</v>
@@ -5642,10 +5642,10 @@
         <v>372</v>
       </c>
       <c r="E157" t="s">
+        <v>319</v>
+      </c>
+      <c r="F157" t="s">
         <v>373</v>
-      </c>
-      <c r="F157" t="s">
-        <v>320</v>
       </c>
       <c r="G157" t="s">
         <v>321</v>
@@ -5665,10 +5665,10 @@
         <v>372</v>
       </c>
       <c r="E158" t="s">
+        <v>319</v>
+      </c>
+      <c r="F158" t="s">
         <v>373</v>
-      </c>
-      <c r="F158" t="s">
-        <v>320</v>
       </c>
       <c r="G158" t="s">
         <v>321</v>
@@ -6125,10 +6125,10 @@
         <v>426</v>
       </c>
       <c r="E178" t="s">
+        <v>385</v>
+      </c>
+      <c r="F178" t="s">
         <v>427</v>
-      </c>
-      <c r="F178" t="s">
-        <v>386</v>
       </c>
       <c r="G178" t="s">
         <v>387</v>
@@ -6148,10 +6148,10 @@
         <v>426</v>
       </c>
       <c r="E179" t="s">
+        <v>385</v>
+      </c>
+      <c r="F179" t="s">
         <v>427</v>
-      </c>
-      <c r="F179" t="s">
-        <v>386</v>
       </c>
       <c r="G179" t="s">
         <v>387</v>
@@ -6171,10 +6171,10 @@
         <v>426</v>
       </c>
       <c r="E180" t="s">
+        <v>385</v>
+      </c>
+      <c r="F180" t="s">
         <v>427</v>
-      </c>
-      <c r="F180" t="s">
-        <v>386</v>
       </c>
       <c r="G180" t="s">
         <v>387</v>
@@ -6194,10 +6194,10 @@
         <v>426</v>
       </c>
       <c r="E181" t="s">
+        <v>385</v>
+      </c>
+      <c r="F181" t="s">
         <v>427</v>
-      </c>
-      <c r="F181" t="s">
-        <v>386</v>
       </c>
       <c r="G181" t="s">
         <v>387</v>
@@ -6217,10 +6217,10 @@
         <v>426</v>
       </c>
       <c r="E182" t="s">
+        <v>385</v>
+      </c>
+      <c r="F182" t="s">
         <v>427</v>
-      </c>
-      <c r="F182" t="s">
-        <v>386</v>
       </c>
       <c r="G182" t="s">
         <v>387</v>
@@ -6240,10 +6240,10 @@
         <v>426</v>
       </c>
       <c r="E183" t="s">
+        <v>385</v>
+      </c>
+      <c r="F183" t="s">
         <v>427</v>
-      </c>
-      <c r="F183" t="s">
-        <v>386</v>
       </c>
       <c r="G183" t="s">
         <v>387</v>
@@ -6263,10 +6263,10 @@
         <v>426</v>
       </c>
       <c r="E184" t="s">
+        <v>385</v>
+      </c>
+      <c r="F184" t="s">
         <v>427</v>
-      </c>
-      <c r="F184" t="s">
-        <v>386</v>
       </c>
       <c r="G184" t="s">
         <v>387</v>
@@ -6286,10 +6286,10 @@
         <v>426</v>
       </c>
       <c r="E185" t="s">
+        <v>385</v>
+      </c>
+      <c r="F185" t="s">
         <v>427</v>
-      </c>
-      <c r="F185" t="s">
-        <v>386</v>
       </c>
       <c r="G185" t="s">
         <v>387</v>
@@ -6309,10 +6309,10 @@
         <v>426</v>
       </c>
       <c r="E186" t="s">
+        <v>385</v>
+      </c>
+      <c r="F186" t="s">
         <v>427</v>
-      </c>
-      <c r="F186" t="s">
-        <v>386</v>
       </c>
       <c r="G186" t="s">
         <v>387</v>
@@ -6332,10 +6332,10 @@
         <v>426</v>
       </c>
       <c r="E187" t="s">
+        <v>385</v>
+      </c>
+      <c r="F187" t="s">
         <v>427</v>
-      </c>
-      <c r="F187" t="s">
-        <v>386</v>
       </c>
       <c r="G187" t="s">
         <v>387</v>
@@ -6355,10 +6355,10 @@
         <v>448</v>
       </c>
       <c r="E188" t="s">
+        <v>385</v>
+      </c>
+      <c r="F188" t="s">
         <v>449</v>
-      </c>
-      <c r="F188" t="s">
-        <v>386</v>
       </c>
       <c r="G188" t="s">
         <v>387</v>
@@ -6378,13 +6378,13 @@
         <v>452</v>
       </c>
       <c r="E189" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F189" t="s">
         <v>453</v>
       </c>
       <c r="G189" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6401,13 +6401,13 @@
         <v>452</v>
       </c>
       <c r="E190" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F190" t="s">
         <v>453</v>
       </c>
       <c r="G190" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6424,13 +6424,13 @@
         <v>452</v>
       </c>
       <c r="E191" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F191" t="s">
         <v>453</v>
       </c>
       <c r="G191" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6447,13 +6447,13 @@
         <v>452</v>
       </c>
       <c r="E192" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F192" t="s">
         <v>453</v>
       </c>
       <c r="G192" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6470,13 +6470,13 @@
         <v>452</v>
       </c>
       <c r="E193" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F193" t="s">
         <v>453</v>
       </c>
       <c r="G193" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6493,13 +6493,13 @@
         <v>452</v>
       </c>
       <c r="E194" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F194" t="s">
         <v>453</v>
       </c>
       <c r="G194" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6516,13 +6516,13 @@
         <v>466</v>
       </c>
       <c r="E195" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F195" t="s">
         <v>467</v>
       </c>
       <c r="G195" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6539,13 +6539,13 @@
         <v>470</v>
       </c>
       <c r="E196" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F196" t="s">
         <v>471</v>
       </c>
       <c r="G196" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6562,13 +6562,13 @@
         <v>470</v>
       </c>
       <c r="E197" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F197" t="s">
         <v>471</v>
       </c>
       <c r="G197" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6585,13 +6585,13 @@
         <v>470</v>
       </c>
       <c r="E198" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F198" t="s">
         <v>471</v>
       </c>
       <c r="G198" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6608,13 +6608,13 @@
         <v>470</v>
       </c>
       <c r="E199" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F199" t="s">
         <v>471</v>
       </c>
       <c r="G199" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6631,13 +6631,13 @@
         <v>470</v>
       </c>
       <c r="E200" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F200" t="s">
         <v>471</v>
       </c>
       <c r="G200" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6654,13 +6654,13 @@
         <v>470</v>
       </c>
       <c r="E201" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F201" t="s">
         <v>471</v>
       </c>
       <c r="G201" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6677,13 +6677,13 @@
         <v>484</v>
       </c>
       <c r="E202" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F202" t="s">
         <v>485</v>
       </c>
       <c r="G202" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6700,13 +6700,13 @@
         <v>484</v>
       </c>
       <c r="E203" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F203" t="s">
         <v>485</v>
       </c>
       <c r="G203" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6723,13 +6723,13 @@
         <v>484</v>
       </c>
       <c r="E204" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F204" t="s">
         <v>485</v>
       </c>
       <c r="G204" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6746,13 +6746,13 @@
         <v>484</v>
       </c>
       <c r="E205" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F205" t="s">
         <v>485</v>
       </c>
       <c r="G205" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6769,13 +6769,13 @@
         <v>484</v>
       </c>
       <c r="E206" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F206" t="s">
         <v>485</v>
       </c>
       <c r="G206" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6792,13 +6792,13 @@
         <v>484</v>
       </c>
       <c r="E207" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F207" t="s">
         <v>485</v>
       </c>
       <c r="G207" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6815,13 +6815,13 @@
         <v>484</v>
       </c>
       <c r="E208" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F208" t="s">
         <v>485</v>
       </c>
       <c r="G208" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6838,13 +6838,13 @@
         <v>484</v>
       </c>
       <c r="E209" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F209" t="s">
         <v>485</v>
       </c>
       <c r="G209" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6861,13 +6861,13 @@
         <v>484</v>
       </c>
       <c r="E210" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F210" t="s">
         <v>485</v>
       </c>
       <c r="G210" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6884,13 +6884,13 @@
         <v>484</v>
       </c>
       <c r="E211" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F211" t="s">
         <v>485</v>
       </c>
       <c r="G211" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6907,13 +6907,13 @@
         <v>506</v>
       </c>
       <c r="E212" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="F212" t="s">
         <v>507</v>
       </c>
       <c r="G212" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6930,13 +6930,13 @@
         <v>510</v>
       </c>
       <c r="E213" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F213" t="s">
         <v>511</v>
       </c>
       <c r="G213" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6953,13 +6953,13 @@
         <v>514</v>
       </c>
       <c r="E214" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F214" t="s">
         <v>515</v>
       </c>
       <c r="G214" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6976,13 +6976,13 @@
         <v>514</v>
       </c>
       <c r="E215" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F215" t="s">
         <v>515</v>
       </c>
       <c r="G215" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6999,13 +6999,13 @@
         <v>520</v>
       </c>
       <c r="E216" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F216" t="s">
         <v>521</v>
       </c>
       <c r="G216" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -7022,13 +7022,13 @@
         <v>520</v>
       </c>
       <c r="E217" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F217" t="s">
         <v>521</v>
       </c>
       <c r="G217" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -7045,13 +7045,13 @@
         <v>520</v>
       </c>
       <c r="E218" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F218" t="s">
         <v>521</v>
       </c>
       <c r="G218" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -7068,13 +7068,13 @@
         <v>520</v>
       </c>
       <c r="E219" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F219" t="s">
         <v>521</v>
       </c>
       <c r="G219" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -7091,13 +7091,13 @@
         <v>520</v>
       </c>
       <c r="E220" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F220" t="s">
         <v>521</v>
       </c>
       <c r="G220" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -7114,13 +7114,13 @@
         <v>520</v>
       </c>
       <c r="E221" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F221" t="s">
         <v>521</v>
       </c>
       <c r="G221" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -7137,13 +7137,13 @@
         <v>520</v>
       </c>
       <c r="E222" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F222" t="s">
         <v>521</v>
       </c>
       <c r="G222" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -7160,13 +7160,13 @@
         <v>536</v>
       </c>
       <c r="E223" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F223" t="s">
         <v>537</v>
       </c>
       <c r="G223" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -7183,13 +7183,13 @@
         <v>536</v>
       </c>
       <c r="E224" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F224" t="s">
         <v>537</v>
       </c>
       <c r="G224" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -7206,13 +7206,13 @@
         <v>536</v>
       </c>
       <c r="E225" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F225" t="s">
         <v>537</v>
       </c>
       <c r="G225" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -7229,13 +7229,13 @@
         <v>544</v>
       </c>
       <c r="E226" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F226" t="s">
         <v>545</v>
       </c>
       <c r="G226" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -7252,13 +7252,13 @@
         <v>548</v>
       </c>
       <c r="E227" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="F227" t="s">
         <v>549</v>
       </c>
       <c r="G227" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -7275,13 +7275,13 @@
         <v>552</v>
       </c>
       <c r="E228" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="F228" t="s">
         <v>553</v>
       </c>
       <c r="G228" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -7298,13 +7298,13 @@
         <v>556</v>
       </c>
       <c r="E229" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="F229" t="s">
         <v>557</v>
       </c>
       <c r="G229" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -7321,13 +7321,13 @@
         <v>560</v>
       </c>
       <c r="E230" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="F230" t="s">
         <v>561</v>
       </c>
       <c r="G230" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -7344,13 +7344,13 @@
         <v>560</v>
       </c>
       <c r="E231" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="F231" t="s">
         <v>561</v>
       </c>
       <c r="G231" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/en/SectorGroup.xlsx
+++ b/api/xlsx/en/SectorGroup.xlsx
@@ -28,15 +28,15 @@
     <t>codeforiati:category-code</t>
   </si>
   <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
     <t>codeforiati:category-name</t>
   </si>
   <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -49,15 +49,15 @@
     <t>111</t>
   </si>
   <si>
+    <t>Education</t>
+  </si>
+  <si>
     <t>110</t>
   </si>
   <si>
     <t>Education, Level Unspecified</t>
   </si>
   <si>
-    <t>Education</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -151,15 +151,15 @@
     <t>121</t>
   </si>
   <si>
+    <t>Health</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
     <t>Health, General</t>
   </si>
   <si>
-    <t>Health</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -391,15 +391,15 @@
     <t>151</t>
   </si>
   <si>
+    <t>Government &amp; Civil Society</t>
+  </si>
+  <si>
     <t>150</t>
   </si>
   <si>
     <t>Government &amp; Civil Society-general</t>
   </si>
   <si>
-    <t>Government &amp; Civil Society</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -691,15 +691,15 @@
     <t>231</t>
   </si>
   <si>
+    <t>Energy</t>
+  </si>
+  <si>
     <t>230</t>
   </si>
   <si>
     <t>Energy Policy</t>
   </si>
   <si>
-    <t>Energy</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -973,15 +973,15 @@
     <t>311</t>
   </si>
   <si>
+    <t>Agriculture, Forestry, Fishing</t>
+  </si>
+  <si>
     <t>310</t>
   </si>
   <si>
     <t>Agriculture</t>
   </si>
   <si>
-    <t>Agriculture, Forestry, Fishing</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1171,13 +1171,13 @@
     <t>321</t>
   </si>
   <si>
+    <t>Industry, Mining, Construction</t>
+  </si>
+  <si>
     <t>320</t>
   </si>
   <si>
     <t>Industry</t>
-  </si>
-  <si>
-    <t>Industry, Mining, Construction</t>
   </si>
   <si>
     <t>32120</t>
@@ -2172,10 +2172,10 @@
         <v>11</v>
       </c>
       <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" t="s">
         <v>23</v>
-      </c>
-      <c r="G6" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2195,10 +2195,10 @@
         <v>11</v>
       </c>
       <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" t="s">
         <v>23</v>
-      </c>
-      <c r="G7" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2218,10 +2218,10 @@
         <v>11</v>
       </c>
       <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" t="s">
         <v>23</v>
-      </c>
-      <c r="G8" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2241,10 +2241,10 @@
         <v>11</v>
       </c>
       <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" t="s">
         <v>23</v>
-      </c>
-      <c r="G9" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2264,10 +2264,10 @@
         <v>11</v>
       </c>
       <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" t="s">
         <v>33</v>
-      </c>
-      <c r="G10" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2287,10 +2287,10 @@
         <v>11</v>
       </c>
       <c r="F11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" t="s">
         <v>33</v>
-      </c>
-      <c r="G11" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2310,10 +2310,10 @@
         <v>11</v>
       </c>
       <c r="F12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" t="s">
         <v>39</v>
-      </c>
-      <c r="G12" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2333,10 +2333,10 @@
         <v>11</v>
       </c>
       <c r="F13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" t="s">
         <v>39</v>
-      </c>
-      <c r="G13" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2448,10 +2448,10 @@
         <v>45</v>
       </c>
       <c r="F18" t="s">
+        <v>46</v>
+      </c>
+      <c r="G18" t="s">
         <v>57</v>
-      </c>
-      <c r="G18" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2471,10 +2471,10 @@
         <v>45</v>
       </c>
       <c r="F19" t="s">
+        <v>46</v>
+      </c>
+      <c r="G19" t="s">
         <v>57</v>
-      </c>
-      <c r="G19" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2494,10 +2494,10 @@
         <v>45</v>
       </c>
       <c r="F20" t="s">
+        <v>46</v>
+      </c>
+      <c r="G20" t="s">
         <v>57</v>
-      </c>
-      <c r="G20" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2517,10 +2517,10 @@
         <v>45</v>
       </c>
       <c r="F21" t="s">
+        <v>46</v>
+      </c>
+      <c r="G21" t="s">
         <v>57</v>
-      </c>
-      <c r="G21" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2540,10 +2540,10 @@
         <v>45</v>
       </c>
       <c r="F22" t="s">
+        <v>46</v>
+      </c>
+      <c r="G22" t="s">
         <v>57</v>
-      </c>
-      <c r="G22" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2563,10 +2563,10 @@
         <v>45</v>
       </c>
       <c r="F23" t="s">
+        <v>46</v>
+      </c>
+      <c r="G23" t="s">
         <v>57</v>
-      </c>
-      <c r="G23" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2586,10 +2586,10 @@
         <v>45</v>
       </c>
       <c r="F24" t="s">
+        <v>46</v>
+      </c>
+      <c r="G24" t="s">
         <v>57</v>
-      </c>
-      <c r="G24" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2609,10 +2609,10 @@
         <v>45</v>
       </c>
       <c r="F25" t="s">
+        <v>46</v>
+      </c>
+      <c r="G25" t="s">
         <v>57</v>
-      </c>
-      <c r="G25" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2632,10 +2632,10 @@
         <v>45</v>
       </c>
       <c r="F26" t="s">
+        <v>46</v>
+      </c>
+      <c r="G26" t="s">
         <v>75</v>
-      </c>
-      <c r="G26" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2655,10 +2655,10 @@
         <v>45</v>
       </c>
       <c r="F27" t="s">
+        <v>46</v>
+      </c>
+      <c r="G27" t="s">
         <v>75</v>
-      </c>
-      <c r="G27" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2678,10 +2678,10 @@
         <v>45</v>
       </c>
       <c r="F28" t="s">
+        <v>46</v>
+      </c>
+      <c r="G28" t="s">
         <v>75</v>
-      </c>
-      <c r="G28" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2701,10 +2701,10 @@
         <v>45</v>
       </c>
       <c r="F29" t="s">
+        <v>46</v>
+      </c>
+      <c r="G29" t="s">
         <v>75</v>
-      </c>
-      <c r="G29" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2724,10 +2724,10 @@
         <v>45</v>
       </c>
       <c r="F30" t="s">
+        <v>46</v>
+      </c>
+      <c r="G30" t="s">
         <v>75</v>
-      </c>
-      <c r="G30" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2747,10 +2747,10 @@
         <v>45</v>
       </c>
       <c r="F31" t="s">
+        <v>46</v>
+      </c>
+      <c r="G31" t="s">
         <v>75</v>
-      </c>
-      <c r="G31" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2767,10 +2767,10 @@
         <v>88</v>
       </c>
       <c r="E32" t="s">
+        <v>89</v>
+      </c>
+      <c r="F32" t="s">
         <v>88</v>
-      </c>
-      <c r="F32" t="s">
-        <v>89</v>
       </c>
       <c r="G32" t="s">
         <v>89</v>
@@ -2790,10 +2790,10 @@
         <v>88</v>
       </c>
       <c r="E33" t="s">
+        <v>89</v>
+      </c>
+      <c r="F33" t="s">
         <v>88</v>
-      </c>
-      <c r="F33" t="s">
-        <v>89</v>
       </c>
       <c r="G33" t="s">
         <v>89</v>
@@ -2813,10 +2813,10 @@
         <v>88</v>
       </c>
       <c r="E34" t="s">
+        <v>89</v>
+      </c>
+      <c r="F34" t="s">
         <v>88</v>
-      </c>
-      <c r="F34" t="s">
-        <v>89</v>
       </c>
       <c r="G34" t="s">
         <v>89</v>
@@ -2836,10 +2836,10 @@
         <v>88</v>
       </c>
       <c r="E35" t="s">
+        <v>89</v>
+      </c>
+      <c r="F35" t="s">
         <v>88</v>
-      </c>
-      <c r="F35" t="s">
-        <v>89</v>
       </c>
       <c r="G35" t="s">
         <v>89</v>
@@ -2859,10 +2859,10 @@
         <v>88</v>
       </c>
       <c r="E36" t="s">
+        <v>89</v>
+      </c>
+      <c r="F36" t="s">
         <v>88</v>
-      </c>
-      <c r="F36" t="s">
-        <v>89</v>
       </c>
       <c r="G36" t="s">
         <v>89</v>
@@ -2882,10 +2882,10 @@
         <v>100</v>
       </c>
       <c r="E37" t="s">
+        <v>101</v>
+      </c>
+      <c r="F37" t="s">
         <v>100</v>
-      </c>
-      <c r="F37" t="s">
-        <v>101</v>
       </c>
       <c r="G37" t="s">
         <v>101</v>
@@ -2905,10 +2905,10 @@
         <v>100</v>
       </c>
       <c r="E38" t="s">
+        <v>101</v>
+      </c>
+      <c r="F38" t="s">
         <v>100</v>
-      </c>
-      <c r="F38" t="s">
-        <v>101</v>
       </c>
       <c r="G38" t="s">
         <v>101</v>
@@ -2928,10 +2928,10 @@
         <v>100</v>
       </c>
       <c r="E39" t="s">
+        <v>101</v>
+      </c>
+      <c r="F39" t="s">
         <v>100</v>
-      </c>
-      <c r="F39" t="s">
-        <v>101</v>
       </c>
       <c r="G39" t="s">
         <v>101</v>
@@ -2951,10 +2951,10 @@
         <v>100</v>
       </c>
       <c r="E40" t="s">
+        <v>101</v>
+      </c>
+      <c r="F40" t="s">
         <v>100</v>
-      </c>
-      <c r="F40" t="s">
-        <v>101</v>
       </c>
       <c r="G40" t="s">
         <v>101</v>
@@ -2974,10 +2974,10 @@
         <v>100</v>
       </c>
       <c r="E41" t="s">
+        <v>101</v>
+      </c>
+      <c r="F41" t="s">
         <v>100</v>
-      </c>
-      <c r="F41" t="s">
-        <v>101</v>
       </c>
       <c r="G41" t="s">
         <v>101</v>
@@ -2997,10 +2997,10 @@
         <v>100</v>
       </c>
       <c r="E42" t="s">
+        <v>101</v>
+      </c>
+      <c r="F42" t="s">
         <v>100</v>
-      </c>
-      <c r="F42" t="s">
-        <v>101</v>
       </c>
       <c r="G42" t="s">
         <v>101</v>
@@ -3020,10 +3020,10 @@
         <v>100</v>
       </c>
       <c r="E43" t="s">
+        <v>101</v>
+      </c>
+      <c r="F43" t="s">
         <v>100</v>
-      </c>
-      <c r="F43" t="s">
-        <v>101</v>
       </c>
       <c r="G43" t="s">
         <v>101</v>
@@ -3043,10 +3043,10 @@
         <v>100</v>
       </c>
       <c r="E44" t="s">
+        <v>101</v>
+      </c>
+      <c r="F44" t="s">
         <v>100</v>
-      </c>
-      <c r="F44" t="s">
-        <v>101</v>
       </c>
       <c r="G44" t="s">
         <v>101</v>
@@ -3066,10 +3066,10 @@
         <v>100</v>
       </c>
       <c r="E45" t="s">
+        <v>101</v>
+      </c>
+      <c r="F45" t="s">
         <v>100</v>
-      </c>
-      <c r="F45" t="s">
-        <v>101</v>
       </c>
       <c r="G45" t="s">
         <v>101</v>
@@ -3089,10 +3089,10 @@
         <v>100</v>
       </c>
       <c r="E46" t="s">
+        <v>101</v>
+      </c>
+      <c r="F46" t="s">
         <v>100</v>
-      </c>
-      <c r="F46" t="s">
-        <v>101</v>
       </c>
       <c r="G46" t="s">
         <v>101</v>
@@ -3112,10 +3112,10 @@
         <v>100</v>
       </c>
       <c r="E47" t="s">
+        <v>101</v>
+      </c>
+      <c r="F47" t="s">
         <v>100</v>
-      </c>
-      <c r="F47" t="s">
-        <v>101</v>
       </c>
       <c r="G47" t="s">
         <v>101</v>
@@ -3506,10 +3506,10 @@
         <v>125</v>
       </c>
       <c r="F64" t="s">
+        <v>126</v>
+      </c>
+      <c r="G64" t="s">
         <v>161</v>
-      </c>
-      <c r="G64" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3529,10 +3529,10 @@
         <v>125</v>
       </c>
       <c r="F65" t="s">
+        <v>126</v>
+      </c>
+      <c r="G65" t="s">
         <v>161</v>
-      </c>
-      <c r="G65" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3552,10 +3552,10 @@
         <v>125</v>
       </c>
       <c r="F66" t="s">
+        <v>126</v>
+      </c>
+      <c r="G66" t="s">
         <v>161</v>
-      </c>
-      <c r="G66" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3575,10 +3575,10 @@
         <v>125</v>
       </c>
       <c r="F67" t="s">
+        <v>126</v>
+      </c>
+      <c r="G67" t="s">
         <v>161</v>
-      </c>
-      <c r="G67" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3598,10 +3598,10 @@
         <v>125</v>
       </c>
       <c r="F68" t="s">
+        <v>126</v>
+      </c>
+      <c r="G68" t="s">
         <v>161</v>
-      </c>
-      <c r="G68" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3621,10 +3621,10 @@
         <v>125</v>
       </c>
       <c r="F69" t="s">
+        <v>126</v>
+      </c>
+      <c r="G69" t="s">
         <v>161</v>
-      </c>
-      <c r="G69" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3641,10 +3641,10 @@
         <v>174</v>
       </c>
       <c r="E70" t="s">
+        <v>175</v>
+      </c>
+      <c r="F70" t="s">
         <v>174</v>
-      </c>
-      <c r="F70" t="s">
-        <v>175</v>
       </c>
       <c r="G70" t="s">
         <v>175</v>
@@ -3664,10 +3664,10 @@
         <v>174</v>
       </c>
       <c r="E71" t="s">
+        <v>175</v>
+      </c>
+      <c r="F71" t="s">
         <v>174</v>
-      </c>
-      <c r="F71" t="s">
-        <v>175</v>
       </c>
       <c r="G71" t="s">
         <v>175</v>
@@ -3687,10 +3687,10 @@
         <v>174</v>
       </c>
       <c r="E72" t="s">
+        <v>175</v>
+      </c>
+      <c r="F72" t="s">
         <v>174</v>
-      </c>
-      <c r="F72" t="s">
-        <v>175</v>
       </c>
       <c r="G72" t="s">
         <v>175</v>
@@ -3710,10 +3710,10 @@
         <v>174</v>
       </c>
       <c r="E73" t="s">
+        <v>175</v>
+      </c>
+      <c r="F73" t="s">
         <v>174</v>
-      </c>
-      <c r="F73" t="s">
-        <v>175</v>
       </c>
       <c r="G73" t="s">
         <v>175</v>
@@ -3733,10 +3733,10 @@
         <v>174</v>
       </c>
       <c r="E74" t="s">
+        <v>175</v>
+      </c>
+      <c r="F74" t="s">
         <v>174</v>
-      </c>
-      <c r="F74" t="s">
-        <v>175</v>
       </c>
       <c r="G74" t="s">
         <v>175</v>
@@ -3756,10 +3756,10 @@
         <v>174</v>
       </c>
       <c r="E75" t="s">
+        <v>175</v>
+      </c>
+      <c r="F75" t="s">
         <v>174</v>
-      </c>
-      <c r="F75" t="s">
-        <v>175</v>
       </c>
       <c r="G75" t="s">
         <v>175</v>
@@ -3779,10 +3779,10 @@
         <v>174</v>
       </c>
       <c r="E76" t="s">
+        <v>175</v>
+      </c>
+      <c r="F76" t="s">
         <v>174</v>
-      </c>
-      <c r="F76" t="s">
-        <v>175</v>
       </c>
       <c r="G76" t="s">
         <v>175</v>
@@ -3802,10 +3802,10 @@
         <v>174</v>
       </c>
       <c r="E77" t="s">
+        <v>175</v>
+      </c>
+      <c r="F77" t="s">
         <v>174</v>
-      </c>
-      <c r="F77" t="s">
-        <v>175</v>
       </c>
       <c r="G77" t="s">
         <v>175</v>
@@ -3825,10 +3825,10 @@
         <v>174</v>
       </c>
       <c r="E78" t="s">
+        <v>175</v>
+      </c>
+      <c r="F78" t="s">
         <v>174</v>
-      </c>
-      <c r="F78" t="s">
-        <v>175</v>
       </c>
       <c r="G78" t="s">
         <v>175</v>
@@ -3848,10 +3848,10 @@
         <v>174</v>
       </c>
       <c r="E79" t="s">
+        <v>175</v>
+      </c>
+      <c r="F79" t="s">
         <v>174</v>
-      </c>
-      <c r="F79" t="s">
-        <v>175</v>
       </c>
       <c r="G79" t="s">
         <v>175</v>
@@ -3871,10 +3871,10 @@
         <v>174</v>
       </c>
       <c r="E80" t="s">
+        <v>175</v>
+      </c>
+      <c r="F80" t="s">
         <v>174</v>
-      </c>
-      <c r="F80" t="s">
-        <v>175</v>
       </c>
       <c r="G80" t="s">
         <v>175</v>
@@ -3894,10 +3894,10 @@
         <v>198</v>
       </c>
       <c r="E81" t="s">
+        <v>199</v>
+      </c>
+      <c r="F81" t="s">
         <v>198</v>
-      </c>
-      <c r="F81" t="s">
-        <v>199</v>
       </c>
       <c r="G81" t="s">
         <v>199</v>
@@ -3917,10 +3917,10 @@
         <v>198</v>
       </c>
       <c r="E82" t="s">
+        <v>199</v>
+      </c>
+      <c r="F82" t="s">
         <v>198</v>
-      </c>
-      <c r="F82" t="s">
-        <v>199</v>
       </c>
       <c r="G82" t="s">
         <v>199</v>
@@ -3940,10 +3940,10 @@
         <v>198</v>
       </c>
       <c r="E83" t="s">
+        <v>199</v>
+      </c>
+      <c r="F83" t="s">
         <v>198</v>
-      </c>
-      <c r="F83" t="s">
-        <v>199</v>
       </c>
       <c r="G83" t="s">
         <v>199</v>
@@ -3963,10 +3963,10 @@
         <v>198</v>
       </c>
       <c r="E84" t="s">
+        <v>199</v>
+      </c>
+      <c r="F84" t="s">
         <v>198</v>
-      </c>
-      <c r="F84" t="s">
-        <v>199</v>
       </c>
       <c r="G84" t="s">
         <v>199</v>
@@ -3986,10 +3986,10 @@
         <v>198</v>
       </c>
       <c r="E85" t="s">
+        <v>199</v>
+      </c>
+      <c r="F85" t="s">
         <v>198</v>
-      </c>
-      <c r="F85" t="s">
-        <v>199</v>
       </c>
       <c r="G85" t="s">
         <v>199</v>
@@ -4009,10 +4009,10 @@
         <v>198</v>
       </c>
       <c r="E86" t="s">
+        <v>199</v>
+      </c>
+      <c r="F86" t="s">
         <v>198</v>
-      </c>
-      <c r="F86" t="s">
-        <v>199</v>
       </c>
       <c r="G86" t="s">
         <v>199</v>
@@ -4032,10 +4032,10 @@
         <v>198</v>
       </c>
       <c r="E87" t="s">
+        <v>199</v>
+      </c>
+      <c r="F87" t="s">
         <v>198</v>
-      </c>
-      <c r="F87" t="s">
-        <v>199</v>
       </c>
       <c r="G87" t="s">
         <v>199</v>
@@ -4055,10 +4055,10 @@
         <v>214</v>
       </c>
       <c r="E88" t="s">
+        <v>215</v>
+      </c>
+      <c r="F88" t="s">
         <v>214</v>
-      </c>
-      <c r="F88" t="s">
-        <v>215</v>
       </c>
       <c r="G88" t="s">
         <v>215</v>
@@ -4078,10 +4078,10 @@
         <v>214</v>
       </c>
       <c r="E89" t="s">
+        <v>215</v>
+      </c>
+      <c r="F89" t="s">
         <v>214</v>
-      </c>
-      <c r="F89" t="s">
-        <v>215</v>
       </c>
       <c r="G89" t="s">
         <v>215</v>
@@ -4101,10 +4101,10 @@
         <v>214</v>
       </c>
       <c r="E90" t="s">
+        <v>215</v>
+      </c>
+      <c r="F90" t="s">
         <v>214</v>
-      </c>
-      <c r="F90" t="s">
-        <v>215</v>
       </c>
       <c r="G90" t="s">
         <v>215</v>
@@ -4124,10 +4124,10 @@
         <v>214</v>
       </c>
       <c r="E91" t="s">
+        <v>215</v>
+      </c>
+      <c r="F91" t="s">
         <v>214</v>
-      </c>
-      <c r="F91" t="s">
-        <v>215</v>
       </c>
       <c r="G91" t="s">
         <v>215</v>
@@ -4242,10 +4242,10 @@
         <v>225</v>
       </c>
       <c r="F96" t="s">
+        <v>226</v>
+      </c>
+      <c r="G96" t="s">
         <v>237</v>
-      </c>
-      <c r="G96" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -4265,10 +4265,10 @@
         <v>225</v>
       </c>
       <c r="F97" t="s">
+        <v>226</v>
+      </c>
+      <c r="G97" t="s">
         <v>237</v>
-      </c>
-      <c r="G97" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4288,10 +4288,10 @@
         <v>225</v>
       </c>
       <c r="F98" t="s">
+        <v>226</v>
+      </c>
+      <c r="G98" t="s">
         <v>237</v>
-      </c>
-      <c r="G98" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4311,10 +4311,10 @@
         <v>225</v>
       </c>
       <c r="F99" t="s">
+        <v>226</v>
+      </c>
+      <c r="G99" t="s">
         <v>237</v>
-      </c>
-      <c r="G99" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4334,10 +4334,10 @@
         <v>225</v>
       </c>
       <c r="F100" t="s">
+        <v>226</v>
+      </c>
+      <c r="G100" t="s">
         <v>237</v>
-      </c>
-      <c r="G100" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4357,10 +4357,10 @@
         <v>225</v>
       </c>
       <c r="F101" t="s">
+        <v>226</v>
+      </c>
+      <c r="G101" t="s">
         <v>237</v>
-      </c>
-      <c r="G101" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4380,10 +4380,10 @@
         <v>225</v>
       </c>
       <c r="F102" t="s">
+        <v>226</v>
+      </c>
+      <c r="G102" t="s">
         <v>237</v>
-      </c>
-      <c r="G102" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4403,10 +4403,10 @@
         <v>225</v>
       </c>
       <c r="F103" t="s">
+        <v>226</v>
+      </c>
+      <c r="G103" t="s">
         <v>237</v>
-      </c>
-      <c r="G103" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4426,10 +4426,10 @@
         <v>225</v>
       </c>
       <c r="F104" t="s">
+        <v>226</v>
+      </c>
+      <c r="G104" t="s">
         <v>237</v>
-      </c>
-      <c r="G104" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4449,10 +4449,10 @@
         <v>225</v>
       </c>
       <c r="F105" t="s">
+        <v>226</v>
+      </c>
+      <c r="G105" t="s">
         <v>257</v>
-      </c>
-      <c r="G105" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4472,10 +4472,10 @@
         <v>225</v>
       </c>
       <c r="F106" t="s">
+        <v>226</v>
+      </c>
+      <c r="G106" t="s">
         <v>257</v>
-      </c>
-      <c r="G106" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4495,10 +4495,10 @@
         <v>225</v>
       </c>
       <c r="F107" t="s">
+        <v>226</v>
+      </c>
+      <c r="G107" t="s">
         <v>257</v>
-      </c>
-      <c r="G107" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4518,10 +4518,10 @@
         <v>225</v>
       </c>
       <c r="F108" t="s">
+        <v>226</v>
+      </c>
+      <c r="G108" t="s">
         <v>257</v>
-      </c>
-      <c r="G108" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4541,10 +4541,10 @@
         <v>225</v>
       </c>
       <c r="F109" t="s">
+        <v>226</v>
+      </c>
+      <c r="G109" t="s">
         <v>257</v>
-      </c>
-      <c r="G109" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4564,10 +4564,10 @@
         <v>225</v>
       </c>
       <c r="F110" t="s">
+        <v>226</v>
+      </c>
+      <c r="G110" t="s">
         <v>257</v>
-      </c>
-      <c r="G110" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4587,10 +4587,10 @@
         <v>225</v>
       </c>
       <c r="F111" t="s">
+        <v>226</v>
+      </c>
+      <c r="G111" t="s">
         <v>271</v>
-      </c>
-      <c r="G111" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4610,10 +4610,10 @@
         <v>225</v>
       </c>
       <c r="F112" t="s">
+        <v>226</v>
+      </c>
+      <c r="G112" t="s">
         <v>275</v>
-      </c>
-      <c r="G112" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4633,10 +4633,10 @@
         <v>225</v>
       </c>
       <c r="F113" t="s">
+        <v>226</v>
+      </c>
+      <c r="G113" t="s">
         <v>279</v>
-      </c>
-      <c r="G113" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4656,10 +4656,10 @@
         <v>225</v>
       </c>
       <c r="F114" t="s">
+        <v>226</v>
+      </c>
+      <c r="G114" t="s">
         <v>279</v>
-      </c>
-      <c r="G114" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4679,10 +4679,10 @@
         <v>225</v>
       </c>
       <c r="F115" t="s">
+        <v>226</v>
+      </c>
+      <c r="G115" t="s">
         <v>279</v>
-      </c>
-      <c r="G115" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4702,10 +4702,10 @@
         <v>225</v>
       </c>
       <c r="F116" t="s">
+        <v>226</v>
+      </c>
+      <c r="G116" t="s">
         <v>279</v>
-      </c>
-      <c r="G116" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4725,10 +4725,10 @@
         <v>225</v>
       </c>
       <c r="F117" t="s">
+        <v>226</v>
+      </c>
+      <c r="G117" t="s">
         <v>279</v>
-      </c>
-      <c r="G117" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4748,10 +4748,10 @@
         <v>225</v>
       </c>
       <c r="F118" t="s">
+        <v>226</v>
+      </c>
+      <c r="G118" t="s">
         <v>279</v>
-      </c>
-      <c r="G118" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4771,10 +4771,10 @@
         <v>225</v>
       </c>
       <c r="F119" t="s">
+        <v>226</v>
+      </c>
+      <c r="G119" t="s">
         <v>279</v>
-      </c>
-      <c r="G119" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4791,10 +4791,10 @@
         <v>294</v>
       </c>
       <c r="E120" t="s">
+        <v>295</v>
+      </c>
+      <c r="F120" t="s">
         <v>294</v>
-      </c>
-      <c r="F120" t="s">
-        <v>295</v>
       </c>
       <c r="G120" t="s">
         <v>295</v>
@@ -4814,10 +4814,10 @@
         <v>294</v>
       </c>
       <c r="E121" t="s">
+        <v>295</v>
+      </c>
+      <c r="F121" t="s">
         <v>294</v>
-      </c>
-      <c r="F121" t="s">
-        <v>295</v>
       </c>
       <c r="G121" t="s">
         <v>295</v>
@@ -4837,10 +4837,10 @@
         <v>294</v>
       </c>
       <c r="E122" t="s">
+        <v>295</v>
+      </c>
+      <c r="F122" t="s">
         <v>294</v>
-      </c>
-      <c r="F122" t="s">
-        <v>295</v>
       </c>
       <c r="G122" t="s">
         <v>295</v>
@@ -4860,10 +4860,10 @@
         <v>294</v>
       </c>
       <c r="E123" t="s">
+        <v>295</v>
+      </c>
+      <c r="F123" t="s">
         <v>294</v>
-      </c>
-      <c r="F123" t="s">
-        <v>295</v>
       </c>
       <c r="G123" t="s">
         <v>295</v>
@@ -4883,10 +4883,10 @@
         <v>294</v>
       </c>
       <c r="E124" t="s">
+        <v>295</v>
+      </c>
+      <c r="F124" t="s">
         <v>294</v>
-      </c>
-      <c r="F124" t="s">
-        <v>295</v>
       </c>
       <c r="G124" t="s">
         <v>295</v>
@@ -4906,10 +4906,10 @@
         <v>294</v>
       </c>
       <c r="E125" t="s">
+        <v>295</v>
+      </c>
+      <c r="F125" t="s">
         <v>294</v>
-      </c>
-      <c r="F125" t="s">
-        <v>295</v>
       </c>
       <c r="G125" t="s">
         <v>295</v>
@@ -4929,10 +4929,10 @@
         <v>308</v>
       </c>
       <c r="E126" t="s">
+        <v>309</v>
+      </c>
+      <c r="F126" t="s">
         <v>308</v>
-      </c>
-      <c r="F126" t="s">
-        <v>309</v>
       </c>
       <c r="G126" t="s">
         <v>309</v>
@@ -4952,10 +4952,10 @@
         <v>308</v>
       </c>
       <c r="E127" t="s">
+        <v>309</v>
+      </c>
+      <c r="F127" t="s">
         <v>308</v>
-      </c>
-      <c r="F127" t="s">
-        <v>309</v>
       </c>
       <c r="G127" t="s">
         <v>309</v>
@@ -4975,10 +4975,10 @@
         <v>308</v>
       </c>
       <c r="E128" t="s">
+        <v>309</v>
+      </c>
+      <c r="F128" t="s">
         <v>308</v>
-      </c>
-      <c r="F128" t="s">
-        <v>309</v>
       </c>
       <c r="G128" t="s">
         <v>309</v>
@@ -4998,10 +4998,10 @@
         <v>308</v>
       </c>
       <c r="E129" t="s">
+        <v>309</v>
+      </c>
+      <c r="F129" t="s">
         <v>308</v>
-      </c>
-      <c r="F129" t="s">
-        <v>309</v>
       </c>
       <c r="G129" t="s">
         <v>309</v>
@@ -5438,10 +5438,10 @@
         <v>319</v>
       </c>
       <c r="F148" t="s">
+        <v>320</v>
+      </c>
+      <c r="G148" t="s">
         <v>359</v>
-      </c>
-      <c r="G148" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5461,10 +5461,10 @@
         <v>319</v>
       </c>
       <c r="F149" t="s">
+        <v>320</v>
+      </c>
+      <c r="G149" t="s">
         <v>359</v>
-      </c>
-      <c r="G149" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5484,10 +5484,10 @@
         <v>319</v>
       </c>
       <c r="F150" t="s">
+        <v>320</v>
+      </c>
+      <c r="G150" t="s">
         <v>359</v>
-      </c>
-      <c r="G150" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5507,10 +5507,10 @@
         <v>319</v>
       </c>
       <c r="F151" t="s">
+        <v>320</v>
+      </c>
+      <c r="G151" t="s">
         <v>359</v>
-      </c>
-      <c r="G151" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5530,10 +5530,10 @@
         <v>319</v>
       </c>
       <c r="F152" t="s">
+        <v>320</v>
+      </c>
+      <c r="G152" t="s">
         <v>359</v>
-      </c>
-      <c r="G152" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5553,10 +5553,10 @@
         <v>319</v>
       </c>
       <c r="F153" t="s">
+        <v>320</v>
+      </c>
+      <c r="G153" t="s">
         <v>359</v>
-      </c>
-      <c r="G153" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5576,10 +5576,10 @@
         <v>319</v>
       </c>
       <c r="F154" t="s">
+        <v>320</v>
+      </c>
+      <c r="G154" t="s">
         <v>373</v>
-      </c>
-      <c r="G154" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5599,10 +5599,10 @@
         <v>319</v>
       </c>
       <c r="F155" t="s">
+        <v>320</v>
+      </c>
+      <c r="G155" t="s">
         <v>373</v>
-      </c>
-      <c r="G155" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5622,10 +5622,10 @@
         <v>319</v>
       </c>
       <c r="F156" t="s">
+        <v>320</v>
+      </c>
+      <c r="G156" t="s">
         <v>373</v>
-      </c>
-      <c r="G156" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5645,10 +5645,10 @@
         <v>319</v>
       </c>
       <c r="F157" t="s">
+        <v>320</v>
+      </c>
+      <c r="G157" t="s">
         <v>373</v>
-      </c>
-      <c r="G157" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5668,10 +5668,10 @@
         <v>319</v>
       </c>
       <c r="F158" t="s">
+        <v>320</v>
+      </c>
+      <c r="G158" t="s">
         <v>373</v>
-      </c>
-      <c r="G158" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -6128,10 +6128,10 @@
         <v>385</v>
       </c>
       <c r="F178" t="s">
+        <v>386</v>
+      </c>
+      <c r="G178" t="s">
         <v>427</v>
-      </c>
-      <c r="G178" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -6151,10 +6151,10 @@
         <v>385</v>
       </c>
       <c r="F179" t="s">
+        <v>386</v>
+      </c>
+      <c r="G179" t="s">
         <v>427</v>
-      </c>
-      <c r="G179" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -6174,10 +6174,10 @@
         <v>385</v>
       </c>
       <c r="F180" t="s">
+        <v>386</v>
+      </c>
+      <c r="G180" t="s">
         <v>427</v>
-      </c>
-      <c r="G180" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -6197,10 +6197,10 @@
         <v>385</v>
       </c>
       <c r="F181" t="s">
+        <v>386</v>
+      </c>
+      <c r="G181" t="s">
         <v>427</v>
-      </c>
-      <c r="G181" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -6220,10 +6220,10 @@
         <v>385</v>
       </c>
       <c r="F182" t="s">
+        <v>386</v>
+      </c>
+      <c r="G182" t="s">
         <v>427</v>
-      </c>
-      <c r="G182" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -6243,10 +6243,10 @@
         <v>385</v>
       </c>
       <c r="F183" t="s">
+        <v>386</v>
+      </c>
+      <c r="G183" t="s">
         <v>427</v>
-      </c>
-      <c r="G183" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -6266,10 +6266,10 @@
         <v>385</v>
       </c>
       <c r="F184" t="s">
+        <v>386</v>
+      </c>
+      <c r="G184" t="s">
         <v>427</v>
-      </c>
-      <c r="G184" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -6289,10 +6289,10 @@
         <v>385</v>
       </c>
       <c r="F185" t="s">
+        <v>386</v>
+      </c>
+      <c r="G185" t="s">
         <v>427</v>
-      </c>
-      <c r="G185" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -6312,10 +6312,10 @@
         <v>385</v>
       </c>
       <c r="F186" t="s">
+        <v>386</v>
+      </c>
+      <c r="G186" t="s">
         <v>427</v>
-      </c>
-      <c r="G186" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -6335,10 +6335,10 @@
         <v>385</v>
       </c>
       <c r="F187" t="s">
+        <v>386</v>
+      </c>
+      <c r="G187" t="s">
         <v>427</v>
-      </c>
-      <c r="G187" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -6358,10 +6358,10 @@
         <v>385</v>
       </c>
       <c r="F188" t="s">
+        <v>386</v>
+      </c>
+      <c r="G188" t="s">
         <v>449</v>
-      </c>
-      <c r="G188" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -6378,10 +6378,10 @@
         <v>452</v>
       </c>
       <c r="E189" t="s">
+        <v>453</v>
+      </c>
+      <c r="F189" t="s">
         <v>452</v>
-      </c>
-      <c r="F189" t="s">
-        <v>453</v>
       </c>
       <c r="G189" t="s">
         <v>453</v>
@@ -6401,10 +6401,10 @@
         <v>452</v>
       </c>
       <c r="E190" t="s">
+        <v>453</v>
+      </c>
+      <c r="F190" t="s">
         <v>452</v>
-      </c>
-      <c r="F190" t="s">
-        <v>453</v>
       </c>
       <c r="G190" t="s">
         <v>453</v>
@@ -6424,10 +6424,10 @@
         <v>452</v>
       </c>
       <c r="E191" t="s">
+        <v>453</v>
+      </c>
+      <c r="F191" t="s">
         <v>452</v>
-      </c>
-      <c r="F191" t="s">
-        <v>453</v>
       </c>
       <c r="G191" t="s">
         <v>453</v>
@@ -6447,10 +6447,10 @@
         <v>452</v>
       </c>
       <c r="E192" t="s">
+        <v>453</v>
+      </c>
+      <c r="F192" t="s">
         <v>452</v>
-      </c>
-      <c r="F192" t="s">
-        <v>453</v>
       </c>
       <c r="G192" t="s">
         <v>453</v>
@@ -6470,10 +6470,10 @@
         <v>452</v>
       </c>
       <c r="E193" t="s">
+        <v>453</v>
+      </c>
+      <c r="F193" t="s">
         <v>452</v>
-      </c>
-      <c r="F193" t="s">
-        <v>453</v>
       </c>
       <c r="G193" t="s">
         <v>453</v>
@@ -6493,10 +6493,10 @@
         <v>452</v>
       </c>
       <c r="E194" t="s">
+        <v>453</v>
+      </c>
+      <c r="F194" t="s">
         <v>452</v>
-      </c>
-      <c r="F194" t="s">
-        <v>453</v>
       </c>
       <c r="G194" t="s">
         <v>453</v>
@@ -6516,10 +6516,10 @@
         <v>466</v>
       </c>
       <c r="E195" t="s">
+        <v>467</v>
+      </c>
+      <c r="F195" t="s">
         <v>466</v>
-      </c>
-      <c r="F195" t="s">
-        <v>467</v>
       </c>
       <c r="G195" t="s">
         <v>467</v>
@@ -6539,10 +6539,10 @@
         <v>470</v>
       </c>
       <c r="E196" t="s">
+        <v>471</v>
+      </c>
+      <c r="F196" t="s">
         <v>470</v>
-      </c>
-      <c r="F196" t="s">
-        <v>471</v>
       </c>
       <c r="G196" t="s">
         <v>471</v>
@@ -6562,10 +6562,10 @@
         <v>470</v>
       </c>
       <c r="E197" t="s">
+        <v>471</v>
+      </c>
+      <c r="F197" t="s">
         <v>470</v>
-      </c>
-      <c r="F197" t="s">
-        <v>471</v>
       </c>
       <c r="G197" t="s">
         <v>471</v>
@@ -6585,10 +6585,10 @@
         <v>470</v>
       </c>
       <c r="E198" t="s">
+        <v>471</v>
+      </c>
+      <c r="F198" t="s">
         <v>470</v>
-      </c>
-      <c r="F198" t="s">
-        <v>471</v>
       </c>
       <c r="G198" t="s">
         <v>471</v>
@@ -6608,10 +6608,10 @@
         <v>470</v>
       </c>
       <c r="E199" t="s">
+        <v>471</v>
+      </c>
+      <c r="F199" t="s">
         <v>470</v>
-      </c>
-      <c r="F199" t="s">
-        <v>471</v>
       </c>
       <c r="G199" t="s">
         <v>471</v>
@@ -6631,10 +6631,10 @@
         <v>470</v>
       </c>
       <c r="E200" t="s">
+        <v>471</v>
+      </c>
+      <c r="F200" t="s">
         <v>470</v>
-      </c>
-      <c r="F200" t="s">
-        <v>471</v>
       </c>
       <c r="G200" t="s">
         <v>471</v>
@@ -6654,10 +6654,10 @@
         <v>470</v>
       </c>
       <c r="E201" t="s">
+        <v>471</v>
+      </c>
+      <c r="F201" t="s">
         <v>470</v>
-      </c>
-      <c r="F201" t="s">
-        <v>471</v>
       </c>
       <c r="G201" t="s">
         <v>471</v>
@@ -6677,10 +6677,10 @@
         <v>484</v>
       </c>
       <c r="E202" t="s">
+        <v>485</v>
+      </c>
+      <c r="F202" t="s">
         <v>484</v>
-      </c>
-      <c r="F202" t="s">
-        <v>485</v>
       </c>
       <c r="G202" t="s">
         <v>485</v>
@@ -6700,10 +6700,10 @@
         <v>484</v>
       </c>
       <c r="E203" t="s">
+        <v>485</v>
+      </c>
+      <c r="F203" t="s">
         <v>484</v>
-      </c>
-      <c r="F203" t="s">
-        <v>485</v>
       </c>
       <c r="G203" t="s">
         <v>485</v>
@@ -6723,10 +6723,10 @@
         <v>484</v>
       </c>
       <c r="E204" t="s">
+        <v>485</v>
+      </c>
+      <c r="F204" t="s">
         <v>484</v>
-      </c>
-      <c r="F204" t="s">
-        <v>485</v>
       </c>
       <c r="G204" t="s">
         <v>485</v>
@@ -6746,10 +6746,10 @@
         <v>484</v>
       </c>
       <c r="E205" t="s">
+        <v>485</v>
+      </c>
+      <c r="F205" t="s">
         <v>484</v>
-      </c>
-      <c r="F205" t="s">
-        <v>485</v>
       </c>
       <c r="G205" t="s">
         <v>485</v>
@@ -6769,10 +6769,10 @@
         <v>484</v>
       </c>
       <c r="E206" t="s">
+        <v>485</v>
+      </c>
+      <c r="F206" t="s">
         <v>484</v>
-      </c>
-      <c r="F206" t="s">
-        <v>485</v>
       </c>
       <c r="G206" t="s">
         <v>485</v>
@@ -6792,10 +6792,10 @@
         <v>484</v>
       </c>
       <c r="E207" t="s">
+        <v>485</v>
+      </c>
+      <c r="F207" t="s">
         <v>484</v>
-      </c>
-      <c r="F207" t="s">
-        <v>485</v>
       </c>
       <c r="G207" t="s">
         <v>485</v>
@@ -6815,10 +6815,10 @@
         <v>484</v>
       </c>
       <c r="E208" t="s">
+        <v>485</v>
+      </c>
+      <c r="F208" t="s">
         <v>484</v>
-      </c>
-      <c r="F208" t="s">
-        <v>485</v>
       </c>
       <c r="G208" t="s">
         <v>485</v>
@@ -6838,10 +6838,10 @@
         <v>484</v>
       </c>
       <c r="E209" t="s">
+        <v>485</v>
+      </c>
+      <c r="F209" t="s">
         <v>484</v>
-      </c>
-      <c r="F209" t="s">
-        <v>485</v>
       </c>
       <c r="G209" t="s">
         <v>485</v>
@@ -6861,10 +6861,10 @@
         <v>484</v>
       </c>
       <c r="E210" t="s">
+        <v>485</v>
+      </c>
+      <c r="F210" t="s">
         <v>484</v>
-      </c>
-      <c r="F210" t="s">
-        <v>485</v>
       </c>
       <c r="G210" t="s">
         <v>485</v>
@@ -6884,10 +6884,10 @@
         <v>484</v>
       </c>
       <c r="E211" t="s">
+        <v>485</v>
+      </c>
+      <c r="F211" t="s">
         <v>484</v>
-      </c>
-      <c r="F211" t="s">
-        <v>485</v>
       </c>
       <c r="G211" t="s">
         <v>485</v>
@@ -6907,10 +6907,10 @@
         <v>506</v>
       </c>
       <c r="E212" t="s">
+        <v>507</v>
+      </c>
+      <c r="F212" t="s">
         <v>506</v>
-      </c>
-      <c r="F212" t="s">
-        <v>507</v>
       </c>
       <c r="G212" t="s">
         <v>507</v>
@@ -6930,10 +6930,10 @@
         <v>510</v>
       </c>
       <c r="E213" t="s">
+        <v>511</v>
+      </c>
+      <c r="F213" t="s">
         <v>510</v>
-      </c>
-      <c r="F213" t="s">
-        <v>511</v>
       </c>
       <c r="G213" t="s">
         <v>511</v>
@@ -6953,10 +6953,10 @@
         <v>514</v>
       </c>
       <c r="E214" t="s">
+        <v>515</v>
+      </c>
+      <c r="F214" t="s">
         <v>514</v>
-      </c>
-      <c r="F214" t="s">
-        <v>515</v>
       </c>
       <c r="G214" t="s">
         <v>515</v>
@@ -6976,10 +6976,10 @@
         <v>514</v>
       </c>
       <c r="E215" t="s">
+        <v>515</v>
+      </c>
+      <c r="F215" t="s">
         <v>514</v>
-      </c>
-      <c r="F215" t="s">
-        <v>515</v>
       </c>
       <c r="G215" t="s">
         <v>515</v>
@@ -6999,10 +6999,10 @@
         <v>520</v>
       </c>
       <c r="E216" t="s">
+        <v>521</v>
+      </c>
+      <c r="F216" t="s">
         <v>520</v>
-      </c>
-      <c r="F216" t="s">
-        <v>521</v>
       </c>
       <c r="G216" t="s">
         <v>521</v>
@@ -7022,10 +7022,10 @@
         <v>520</v>
       </c>
       <c r="E217" t="s">
+        <v>521</v>
+      </c>
+      <c r="F217" t="s">
         <v>520</v>
-      </c>
-      <c r="F217" t="s">
-        <v>521</v>
       </c>
       <c r="G217" t="s">
         <v>521</v>
@@ -7045,10 +7045,10 @@
         <v>520</v>
       </c>
       <c r="E218" t="s">
+        <v>521</v>
+      </c>
+      <c r="F218" t="s">
         <v>520</v>
-      </c>
-      <c r="F218" t="s">
-        <v>521</v>
       </c>
       <c r="G218" t="s">
         <v>521</v>
@@ -7068,10 +7068,10 @@
         <v>520</v>
       </c>
       <c r="E219" t="s">
+        <v>521</v>
+      </c>
+      <c r="F219" t="s">
         <v>520</v>
-      </c>
-      <c r="F219" t="s">
-        <v>521</v>
       </c>
       <c r="G219" t="s">
         <v>521</v>
@@ -7091,10 +7091,10 @@
         <v>520</v>
       </c>
       <c r="E220" t="s">
+        <v>521</v>
+      </c>
+      <c r="F220" t="s">
         <v>520</v>
-      </c>
-      <c r="F220" t="s">
-        <v>521</v>
       </c>
       <c r="G220" t="s">
         <v>521</v>
@@ -7114,10 +7114,10 @@
         <v>520</v>
       </c>
       <c r="E221" t="s">
+        <v>521</v>
+      </c>
+      <c r="F221" t="s">
         <v>520</v>
-      </c>
-      <c r="F221" t="s">
-        <v>521</v>
       </c>
       <c r="G221" t="s">
         <v>521</v>
@@ -7137,10 +7137,10 @@
         <v>520</v>
       </c>
       <c r="E222" t="s">
+        <v>521</v>
+      </c>
+      <c r="F222" t="s">
         <v>520</v>
-      </c>
-      <c r="F222" t="s">
-        <v>521</v>
       </c>
       <c r="G222" t="s">
         <v>521</v>
@@ -7160,10 +7160,10 @@
         <v>536</v>
       </c>
       <c r="E223" t="s">
+        <v>537</v>
+      </c>
+      <c r="F223" t="s">
         <v>536</v>
-      </c>
-      <c r="F223" t="s">
-        <v>537</v>
       </c>
       <c r="G223" t="s">
         <v>537</v>
@@ -7183,10 +7183,10 @@
         <v>536</v>
       </c>
       <c r="E224" t="s">
+        <v>537</v>
+      </c>
+      <c r="F224" t="s">
         <v>536</v>
-      </c>
-      <c r="F224" t="s">
-        <v>537</v>
       </c>
       <c r="G224" t="s">
         <v>537</v>
@@ -7206,10 +7206,10 @@
         <v>536</v>
       </c>
       <c r="E225" t="s">
+        <v>537</v>
+      </c>
+      <c r="F225" t="s">
         <v>536</v>
-      </c>
-      <c r="F225" t="s">
-        <v>537</v>
       </c>
       <c r="G225" t="s">
         <v>537</v>
@@ -7229,10 +7229,10 @@
         <v>544</v>
       </c>
       <c r="E226" t="s">
+        <v>545</v>
+      </c>
+      <c r="F226" t="s">
         <v>544</v>
-      </c>
-      <c r="F226" t="s">
-        <v>545</v>
       </c>
       <c r="G226" t="s">
         <v>545</v>
@@ -7252,10 +7252,10 @@
         <v>548</v>
       </c>
       <c r="E227" t="s">
+        <v>549</v>
+      </c>
+      <c r="F227" t="s">
         <v>548</v>
-      </c>
-      <c r="F227" t="s">
-        <v>549</v>
       </c>
       <c r="G227" t="s">
         <v>549</v>
@@ -7275,10 +7275,10 @@
         <v>552</v>
       </c>
       <c r="E228" t="s">
+        <v>553</v>
+      </c>
+      <c r="F228" t="s">
         <v>552</v>
-      </c>
-      <c r="F228" t="s">
-        <v>553</v>
       </c>
       <c r="G228" t="s">
         <v>553</v>
@@ -7298,10 +7298,10 @@
         <v>556</v>
       </c>
       <c r="E229" t="s">
+        <v>557</v>
+      </c>
+      <c r="F229" t="s">
         <v>556</v>
-      </c>
-      <c r="F229" t="s">
-        <v>557</v>
       </c>
       <c r="G229" t="s">
         <v>557</v>
@@ -7321,10 +7321,10 @@
         <v>560</v>
       </c>
       <c r="E230" t="s">
+        <v>561</v>
+      </c>
+      <c r="F230" t="s">
         <v>560</v>
-      </c>
-      <c r="F230" t="s">
-        <v>561</v>
       </c>
       <c r="G230" t="s">
         <v>561</v>
@@ -7344,10 +7344,10 @@
         <v>560</v>
       </c>
       <c r="E231" t="s">
+        <v>561</v>
+      </c>
+      <c r="F231" t="s">
         <v>560</v>
-      </c>
-      <c r="F231" t="s">
-        <v>561</v>
       </c>
       <c r="G231" t="s">
         <v>561</v>

--- a/api/xlsx/en/SectorGroup.xlsx
+++ b/api/xlsx/en/SectorGroup.xlsx
@@ -25,18 +25,18 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
-    <t>codeforiati:group-name</t>
+    <t>codeforiati:category-name</t>
   </si>
   <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
-    <t>codeforiati:category-name</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -46,18 +46,18 @@
     <t>active</t>
   </si>
   <si>
+    <t>Education</t>
+  </si>
+  <si>
     <t>111</t>
   </si>
   <si>
-    <t>Education</t>
+    <t>Education, Level Unspecified</t>
   </si>
   <si>
     <t>110</t>
   </si>
   <si>
-    <t>Education, Level Unspecified</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -148,18 +148,18 @@
     <t>Health policy and administrative management</t>
   </si>
   <si>
+    <t>Health</t>
+  </si>
+  <si>
     <t>121</t>
   </si>
   <si>
-    <t>Health</t>
+    <t>Health, General</t>
   </si>
   <si>
     <t>120</t>
   </si>
   <si>
-    <t>Health, General</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -280,12 +280,12 @@
     <t>Population policy and administrative management</t>
   </si>
   <si>
+    <t>Population Policies/Programmes &amp; Reproductive Health</t>
+  </si>
+  <si>
     <t>130</t>
   </si>
   <si>
-    <t>Population Policies/Programmes &amp; Reproductive Health</t>
-  </si>
-  <si>
     <t>13020</t>
   </si>
   <si>
@@ -316,12 +316,12 @@
     <t>Water sector policy and administrative management</t>
   </si>
   <si>
+    <t>Water Supply &amp; Sanitation</t>
+  </si>
+  <si>
     <t>140</t>
   </si>
   <si>
-    <t>Water Supply &amp; Sanitation</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -388,18 +388,18 @@
     <t>Public sector policy and administrative management</t>
   </si>
   <si>
+    <t>Government &amp; Civil Society</t>
+  </si>
+  <si>
     <t>151</t>
   </si>
   <si>
-    <t>Government &amp; Civil Society</t>
+    <t>Government &amp; Civil Society-general</t>
   </si>
   <si>
     <t>150</t>
   </si>
   <si>
-    <t>Government &amp; Civil Society-general</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -538,12 +538,12 @@
     <t>Social Protection</t>
   </si>
   <si>
+    <t>Other Social Infrastructure &amp; Services</t>
+  </si>
+  <si>
     <t>160</t>
   </si>
   <si>
-    <t>Other Social Infrastructure &amp; Services</t>
-  </si>
-  <si>
     <t>16020</t>
   </si>
   <si>
@@ -610,12 +610,12 @@
     <t>Transport policy and administrative management</t>
   </si>
   <si>
+    <t>Transport &amp; Storage</t>
+  </si>
+  <si>
     <t>210</t>
   </si>
   <si>
-    <t>Transport &amp; Storage</t>
-  </si>
-  <si>
     <t>21020</t>
   </si>
   <si>
@@ -658,12 +658,12 @@
     <t>Communications policy and administrative management</t>
   </si>
   <si>
+    <t>Communications</t>
+  </si>
+  <si>
     <t>220</t>
   </si>
   <si>
-    <t>Communications</t>
-  </si>
-  <si>
     <t>22020</t>
   </si>
   <si>
@@ -688,18 +688,18 @@
     <t>Energy policy and administrative management</t>
   </si>
   <si>
+    <t>Energy</t>
+  </si>
+  <si>
     <t>231</t>
   </si>
   <si>
-    <t>Energy</t>
+    <t>Energy Policy</t>
   </si>
   <si>
     <t>230</t>
   </si>
   <si>
-    <t>Energy Policy</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -898,12 +898,12 @@
     <t>Financial policy and administrative management</t>
   </si>
   <si>
+    <t>Banking &amp; Financial Services</t>
+  </si>
+  <si>
     <t>240</t>
   </si>
   <si>
-    <t>Banking &amp; Financial Services</t>
-  </si>
-  <si>
     <t>24020</t>
   </si>
   <si>
@@ -940,12 +940,12 @@
     <t>Business policy and administration</t>
   </si>
   <si>
+    <t>Business &amp; Other Services</t>
+  </si>
+  <si>
     <t>250</t>
   </si>
   <si>
-    <t>Business &amp; Other Services</t>
-  </si>
-  <si>
     <t>25020</t>
   </si>
   <si>
@@ -970,18 +970,18 @@
     <t>Agricultural policy and administrative management</t>
   </si>
   <si>
+    <t>Agriculture, Forestry, Fishing</t>
+  </si>
+  <si>
     <t>311</t>
   </si>
   <si>
-    <t>Agriculture, Forestry, Fishing</t>
+    <t>Agriculture</t>
   </si>
   <si>
     <t>310</t>
   </si>
   <si>
-    <t>Agriculture</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1168,18 +1168,18 @@
     <t>Industrial policy and administrative management</t>
   </si>
   <si>
+    <t>Industry, Mining, Construction</t>
+  </si>
+  <si>
     <t>321</t>
   </si>
   <si>
-    <t>Industry, Mining, Construction</t>
+    <t>Industry</t>
   </si>
   <si>
     <t>320</t>
   </si>
   <si>
-    <t>Industry</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1372,12 +1372,12 @@
     <t>Trade policy and administrative management</t>
   </si>
   <si>
+    <t>Trade Policies &amp; Regulations</t>
+  </si>
+  <si>
     <t>331</t>
   </si>
   <si>
-    <t>Trade Policies &amp; Regulations</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1414,24 +1414,24 @@
     <t>Tourism policy and administrative management</t>
   </si>
   <si>
+    <t>Tourism</t>
+  </si>
+  <si>
     <t>332</t>
   </si>
   <si>
-    <t>Tourism</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
     <t>Environmental policy and administrative management</t>
   </si>
   <si>
+    <t>General Environment Protection</t>
+  </si>
+  <si>
     <t>410</t>
   </si>
   <si>
-    <t>General Environment Protection</t>
-  </si>
-  <si>
     <t>41020</t>
   </si>
   <si>
@@ -1468,12 +1468,12 @@
     <t>Multisector aid</t>
   </si>
   <si>
+    <t>Other Multisector</t>
+  </si>
+  <si>
     <t>430</t>
   </si>
   <si>
-    <t>Other Multisector</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -1534,36 +1534,36 @@
     <t>General budget support-related aid</t>
   </si>
   <si>
+    <t>General Budget Support</t>
+  </si>
+  <si>
     <t>510</t>
   </si>
   <si>
-    <t>General Budget Support</t>
-  </si>
-  <si>
     <t>52010</t>
   </si>
   <si>
     <t>Food assistance</t>
   </si>
   <si>
+    <t>Development Food Assistance</t>
+  </si>
+  <si>
     <t>520</t>
   </si>
   <si>
-    <t>Development Food Assistance</t>
-  </si>
-  <si>
     <t>53030</t>
   </si>
   <si>
     <t>Import support (capital goods)</t>
   </si>
   <si>
+    <t>Other Commodity Assistance</t>
+  </si>
+  <si>
     <t>530</t>
   </si>
   <si>
-    <t>Other Commodity Assistance</t>
-  </si>
-  <si>
     <t>53040</t>
   </si>
   <si>
@@ -1576,12 +1576,12 @@
     <t>Action relating to debt</t>
   </si>
   <si>
+    <t>Action Relating to Debt</t>
+  </si>
+  <si>
     <t>600</t>
   </si>
   <si>
-    <t>Action Relating to Debt</t>
-  </si>
-  <si>
     <t>60020</t>
   </si>
   <si>
@@ -1624,12 +1624,12 @@
     <t>Material relief assistance and services</t>
   </si>
   <si>
+    <t>Emergency Response</t>
+  </si>
+  <si>
     <t>720</t>
   </si>
   <si>
-    <t>Emergency Response</t>
-  </si>
-  <si>
     <t>72040</t>
   </si>
   <si>
@@ -1648,58 +1648,58 @@
     <t>Immediate post-emergency reconstruction and rehabilitation</t>
   </si>
   <si>
+    <t>Reconstruction Relief &amp; Rehabilitation</t>
+  </si>
+  <si>
     <t>730</t>
   </si>
   <si>
-    <t>Reconstruction Relief &amp; Rehabilitation</t>
-  </si>
-  <si>
     <t>74020</t>
   </si>
   <si>
     <t>Multi-hazard response preparedness</t>
   </si>
   <si>
+    <t>Disaster Prevention &amp; Preparedness</t>
+  </si>
+  <si>
     <t>740</t>
   </si>
   <si>
-    <t>Disaster Prevention &amp; Preparedness</t>
-  </si>
-  <si>
     <t>91010</t>
   </si>
   <si>
     <t>Administrative costs (non-sector allocable)</t>
   </si>
   <si>
+    <t>Administrative Costs of Donors</t>
+  </si>
+  <si>
     <t>910</t>
   </si>
   <si>
-    <t>Administrative Costs of Donors</t>
-  </si>
-  <si>
     <t>93010</t>
   </si>
   <si>
     <t>Refugees/asylum seekers in donor countries (non-sector allocable)</t>
   </si>
   <si>
+    <t>Refugees in Donor Countries</t>
+  </si>
+  <si>
     <t>930</t>
   </si>
   <si>
-    <t>Refugees in Donor Countries</t>
-  </si>
-  <si>
     <t>99810</t>
   </si>
   <si>
     <t>Sectors not specified</t>
   </si>
   <si>
+    <t>Unallocated / Unspecified</t>
+  </si>
+  <si>
     <t>998</t>
-  </si>
-  <si>
-    <t>Unallocated / Unspecified</t>
   </si>
   <si>
     <t>99820</t>
@@ -2166,16 +2166,16 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
         <v>22</v>
       </c>
-      <c r="E6" t="s">
-        <v>11</v>
-      </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2189,16 +2189,16 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" t="s">
         <v>22</v>
       </c>
-      <c r="E7" t="s">
-        <v>11</v>
-      </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G7" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2212,16 +2212,16 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" t="s">
         <v>22</v>
       </c>
-      <c r="E8" t="s">
-        <v>11</v>
-      </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G8" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2235,16 +2235,16 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" t="s">
         <v>22</v>
       </c>
-      <c r="E9" t="s">
-        <v>11</v>
-      </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G9" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2258,16 +2258,16 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" t="s">
         <v>32</v>
       </c>
-      <c r="E10" t="s">
-        <v>11</v>
-      </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="G10" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2281,16 +2281,16 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" t="s">
         <v>32</v>
       </c>
-      <c r="E11" t="s">
-        <v>11</v>
-      </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="G11" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2304,16 +2304,16 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" t="s">
         <v>38</v>
       </c>
-      <c r="E12" t="s">
-        <v>11</v>
-      </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="G12" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2327,16 +2327,16 @@
         <v>9</v>
       </c>
       <c r="D13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" t="s">
         <v>38</v>
       </c>
-      <c r="E13" t="s">
-        <v>11</v>
-      </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="G13" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2442,16 +2442,16 @@
         <v>9</v>
       </c>
       <c r="D18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18" t="s">
         <v>56</v>
       </c>
-      <c r="E18" t="s">
-        <v>45</v>
-      </c>
       <c r="F18" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G18" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2465,16 +2465,16 @@
         <v>9</v>
       </c>
       <c r="D19" t="s">
+        <v>44</v>
+      </c>
+      <c r="E19" t="s">
         <v>56</v>
       </c>
-      <c r="E19" t="s">
-        <v>45</v>
-      </c>
       <c r="F19" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G19" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2488,16 +2488,16 @@
         <v>9</v>
       </c>
       <c r="D20" t="s">
+        <v>44</v>
+      </c>
+      <c r="E20" t="s">
         <v>56</v>
       </c>
-      <c r="E20" t="s">
-        <v>45</v>
-      </c>
       <c r="F20" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G20" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2511,16 +2511,16 @@
         <v>9</v>
       </c>
       <c r="D21" t="s">
+        <v>44</v>
+      </c>
+      <c r="E21" t="s">
         <v>56</v>
       </c>
-      <c r="E21" t="s">
-        <v>45</v>
-      </c>
       <c r="F21" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G21" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2534,16 +2534,16 @@
         <v>9</v>
       </c>
       <c r="D22" t="s">
+        <v>44</v>
+      </c>
+      <c r="E22" t="s">
         <v>56</v>
       </c>
-      <c r="E22" t="s">
-        <v>45</v>
-      </c>
       <c r="F22" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G22" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2557,16 +2557,16 @@
         <v>9</v>
       </c>
       <c r="D23" t="s">
+        <v>44</v>
+      </c>
+      <c r="E23" t="s">
         <v>56</v>
       </c>
-      <c r="E23" t="s">
-        <v>45</v>
-      </c>
       <c r="F23" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G23" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2580,16 +2580,16 @@
         <v>9</v>
       </c>
       <c r="D24" t="s">
+        <v>44</v>
+      </c>
+      <c r="E24" t="s">
         <v>56</v>
       </c>
-      <c r="E24" t="s">
-        <v>45</v>
-      </c>
       <c r="F24" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G24" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2603,16 +2603,16 @@
         <v>9</v>
       </c>
       <c r="D25" t="s">
+        <v>44</v>
+      </c>
+      <c r="E25" t="s">
         <v>56</v>
       </c>
-      <c r="E25" t="s">
-        <v>45</v>
-      </c>
       <c r="F25" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G25" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2626,16 +2626,16 @@
         <v>9</v>
       </c>
       <c r="D26" t="s">
+        <v>44</v>
+      </c>
+      <c r="E26" t="s">
         <v>74</v>
       </c>
-      <c r="E26" t="s">
-        <v>45</v>
-      </c>
       <c r="F26" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G26" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2649,16 +2649,16 @@
         <v>9</v>
       </c>
       <c r="D27" t="s">
+        <v>44</v>
+      </c>
+      <c r="E27" t="s">
         <v>74</v>
       </c>
-      <c r="E27" t="s">
-        <v>45</v>
-      </c>
       <c r="F27" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G27" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2672,16 +2672,16 @@
         <v>9</v>
       </c>
       <c r="D28" t="s">
+        <v>44</v>
+      </c>
+      <c r="E28" t="s">
         <v>74</v>
       </c>
-      <c r="E28" t="s">
-        <v>45</v>
-      </c>
       <c r="F28" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G28" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2695,16 +2695,16 @@
         <v>9</v>
       </c>
       <c r="D29" t="s">
+        <v>44</v>
+      </c>
+      <c r="E29" t="s">
         <v>74</v>
       </c>
-      <c r="E29" t="s">
-        <v>45</v>
-      </c>
       <c r="F29" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G29" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2718,16 +2718,16 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
+        <v>44</v>
+      </c>
+      <c r="E30" t="s">
         <v>74</v>
       </c>
-      <c r="E30" t="s">
-        <v>45</v>
-      </c>
       <c r="F30" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G30" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2741,16 +2741,16 @@
         <v>9</v>
       </c>
       <c r="D31" t="s">
+        <v>44</v>
+      </c>
+      <c r="E31" t="s">
         <v>74</v>
       </c>
-      <c r="E31" t="s">
-        <v>45</v>
-      </c>
       <c r="F31" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G31" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -3500,16 +3500,16 @@
         <v>9</v>
       </c>
       <c r="D64" t="s">
+        <v>124</v>
+      </c>
+      <c r="E64" t="s">
         <v>160</v>
       </c>
-      <c r="E64" t="s">
-        <v>125</v>
-      </c>
       <c r="F64" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G64" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3523,16 +3523,16 @@
         <v>9</v>
       </c>
       <c r="D65" t="s">
+        <v>124</v>
+      </c>
+      <c r="E65" t="s">
         <v>160</v>
       </c>
-      <c r="E65" t="s">
-        <v>125</v>
-      </c>
       <c r="F65" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G65" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3546,16 +3546,16 @@
         <v>9</v>
       </c>
       <c r="D66" t="s">
+        <v>124</v>
+      </c>
+      <c r="E66" t="s">
         <v>160</v>
       </c>
-      <c r="E66" t="s">
-        <v>125</v>
-      </c>
       <c r="F66" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G66" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3569,16 +3569,16 @@
         <v>9</v>
       </c>
       <c r="D67" t="s">
+        <v>124</v>
+      </c>
+      <c r="E67" t="s">
         <v>160</v>
       </c>
-      <c r="E67" t="s">
-        <v>125</v>
-      </c>
       <c r="F67" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G67" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3592,16 +3592,16 @@
         <v>9</v>
       </c>
       <c r="D68" t="s">
+        <v>124</v>
+      </c>
+      <c r="E68" t="s">
         <v>160</v>
       </c>
-      <c r="E68" t="s">
-        <v>125</v>
-      </c>
       <c r="F68" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G68" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3615,16 +3615,16 @@
         <v>9</v>
       </c>
       <c r="D69" t="s">
+        <v>124</v>
+      </c>
+      <c r="E69" t="s">
         <v>160</v>
       </c>
-      <c r="E69" t="s">
-        <v>125</v>
-      </c>
       <c r="F69" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G69" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -4236,16 +4236,16 @@
         <v>9</v>
       </c>
       <c r="D96" t="s">
+        <v>224</v>
+      </c>
+      <c r="E96" t="s">
         <v>236</v>
       </c>
-      <c r="E96" t="s">
-        <v>225</v>
-      </c>
       <c r="F96" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G96" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -4259,16 +4259,16 @@
         <v>9</v>
       </c>
       <c r="D97" t="s">
+        <v>224</v>
+      </c>
+      <c r="E97" t="s">
         <v>236</v>
       </c>
-      <c r="E97" t="s">
-        <v>225</v>
-      </c>
       <c r="F97" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G97" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4282,16 +4282,16 @@
         <v>9</v>
       </c>
       <c r="D98" t="s">
+        <v>224</v>
+      </c>
+      <c r="E98" t="s">
         <v>236</v>
       </c>
-      <c r="E98" t="s">
-        <v>225</v>
-      </c>
       <c r="F98" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G98" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4305,16 +4305,16 @@
         <v>9</v>
       </c>
       <c r="D99" t="s">
+        <v>224</v>
+      </c>
+      <c r="E99" t="s">
         <v>236</v>
       </c>
-      <c r="E99" t="s">
-        <v>225</v>
-      </c>
       <c r="F99" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G99" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4328,16 +4328,16 @@
         <v>9</v>
       </c>
       <c r="D100" t="s">
+        <v>224</v>
+      </c>
+      <c r="E100" t="s">
         <v>236</v>
       </c>
-      <c r="E100" t="s">
-        <v>225</v>
-      </c>
       <c r="F100" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G100" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4351,16 +4351,16 @@
         <v>9</v>
       </c>
       <c r="D101" t="s">
+        <v>224</v>
+      </c>
+      <c r="E101" t="s">
         <v>236</v>
       </c>
-      <c r="E101" t="s">
-        <v>225</v>
-      </c>
       <c r="F101" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G101" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4374,16 +4374,16 @@
         <v>9</v>
       </c>
       <c r="D102" t="s">
+        <v>224</v>
+      </c>
+      <c r="E102" t="s">
         <v>236</v>
       </c>
-      <c r="E102" t="s">
-        <v>225</v>
-      </c>
       <c r="F102" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G102" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4397,16 +4397,16 @@
         <v>9</v>
       </c>
       <c r="D103" t="s">
+        <v>224</v>
+      </c>
+      <c r="E103" t="s">
         <v>236</v>
       </c>
-      <c r="E103" t="s">
-        <v>225</v>
-      </c>
       <c r="F103" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G103" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4420,16 +4420,16 @@
         <v>9</v>
       </c>
       <c r="D104" t="s">
+        <v>224</v>
+      </c>
+      <c r="E104" t="s">
         <v>236</v>
       </c>
-      <c r="E104" t="s">
-        <v>225</v>
-      </c>
       <c r="F104" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G104" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4443,16 +4443,16 @@
         <v>9</v>
       </c>
       <c r="D105" t="s">
+        <v>224</v>
+      </c>
+      <c r="E105" t="s">
         <v>256</v>
       </c>
-      <c r="E105" t="s">
-        <v>225</v>
-      </c>
       <c r="F105" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G105" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4466,16 +4466,16 @@
         <v>9</v>
       </c>
       <c r="D106" t="s">
+        <v>224</v>
+      </c>
+      <c r="E106" t="s">
         <v>256</v>
       </c>
-      <c r="E106" t="s">
-        <v>225</v>
-      </c>
       <c r="F106" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G106" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4489,16 +4489,16 @@
         <v>9</v>
       </c>
       <c r="D107" t="s">
+        <v>224</v>
+      </c>
+      <c r="E107" t="s">
         <v>256</v>
       </c>
-      <c r="E107" t="s">
-        <v>225</v>
-      </c>
       <c r="F107" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G107" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4512,16 +4512,16 @@
         <v>9</v>
       </c>
       <c r="D108" t="s">
+        <v>224</v>
+      </c>
+      <c r="E108" t="s">
         <v>256</v>
       </c>
-      <c r="E108" t="s">
-        <v>225</v>
-      </c>
       <c r="F108" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G108" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4535,16 +4535,16 @@
         <v>9</v>
       </c>
       <c r="D109" t="s">
+        <v>224</v>
+      </c>
+      <c r="E109" t="s">
         <v>256</v>
       </c>
-      <c r="E109" t="s">
-        <v>225</v>
-      </c>
       <c r="F109" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G109" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4558,16 +4558,16 @@
         <v>9</v>
       </c>
       <c r="D110" t="s">
+        <v>224</v>
+      </c>
+      <c r="E110" t="s">
         <v>256</v>
       </c>
-      <c r="E110" t="s">
-        <v>225</v>
-      </c>
       <c r="F110" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G110" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4581,16 +4581,16 @@
         <v>9</v>
       </c>
       <c r="D111" t="s">
+        <v>224</v>
+      </c>
+      <c r="E111" t="s">
         <v>270</v>
       </c>
-      <c r="E111" t="s">
-        <v>225</v>
-      </c>
       <c r="F111" t="s">
-        <v>226</v>
+        <v>271</v>
       </c>
       <c r="G111" t="s">
-        <v>271</v>
+        <v>227</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4604,16 +4604,16 @@
         <v>9</v>
       </c>
       <c r="D112" t="s">
+        <v>224</v>
+      </c>
+      <c r="E112" t="s">
         <v>274</v>
       </c>
-      <c r="E112" t="s">
-        <v>225</v>
-      </c>
       <c r="F112" t="s">
-        <v>226</v>
+        <v>275</v>
       </c>
       <c r="G112" t="s">
-        <v>275</v>
+        <v>227</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4627,16 +4627,16 @@
         <v>9</v>
       </c>
       <c r="D113" t="s">
+        <v>224</v>
+      </c>
+      <c r="E113" t="s">
         <v>278</v>
       </c>
-      <c r="E113" t="s">
-        <v>225</v>
-      </c>
       <c r="F113" t="s">
-        <v>226</v>
+        <v>279</v>
       </c>
       <c r="G113" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4650,16 +4650,16 @@
         <v>9</v>
       </c>
       <c r="D114" t="s">
+        <v>224</v>
+      </c>
+      <c r="E114" t="s">
         <v>278</v>
       </c>
-      <c r="E114" t="s">
-        <v>225</v>
-      </c>
       <c r="F114" t="s">
-        <v>226</v>
+        <v>279</v>
       </c>
       <c r="G114" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4673,16 +4673,16 @@
         <v>9</v>
       </c>
       <c r="D115" t="s">
+        <v>224</v>
+      </c>
+      <c r="E115" t="s">
         <v>278</v>
       </c>
-      <c r="E115" t="s">
-        <v>225</v>
-      </c>
       <c r="F115" t="s">
-        <v>226</v>
+        <v>279</v>
       </c>
       <c r="G115" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4696,16 +4696,16 @@
         <v>9</v>
       </c>
       <c r="D116" t="s">
+        <v>224</v>
+      </c>
+      <c r="E116" t="s">
         <v>278</v>
       </c>
-      <c r="E116" t="s">
-        <v>225</v>
-      </c>
       <c r="F116" t="s">
-        <v>226</v>
+        <v>279</v>
       </c>
       <c r="G116" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4719,16 +4719,16 @@
         <v>9</v>
       </c>
       <c r="D117" t="s">
+        <v>224</v>
+      </c>
+      <c r="E117" t="s">
         <v>278</v>
       </c>
-      <c r="E117" t="s">
-        <v>225</v>
-      </c>
       <c r="F117" t="s">
-        <v>226</v>
+        <v>279</v>
       </c>
       <c r="G117" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4742,16 +4742,16 @@
         <v>9</v>
       </c>
       <c r="D118" t="s">
+        <v>224</v>
+      </c>
+      <c r="E118" t="s">
         <v>278</v>
       </c>
-      <c r="E118" t="s">
-        <v>225</v>
-      </c>
       <c r="F118" t="s">
-        <v>226</v>
+        <v>279</v>
       </c>
       <c r="G118" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4765,16 +4765,16 @@
         <v>9</v>
       </c>
       <c r="D119" t="s">
+        <v>224</v>
+      </c>
+      <c r="E119" t="s">
         <v>278</v>
       </c>
-      <c r="E119" t="s">
-        <v>225</v>
-      </c>
       <c r="F119" t="s">
-        <v>226</v>
+        <v>279</v>
       </c>
       <c r="G119" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -5432,16 +5432,16 @@
         <v>9</v>
       </c>
       <c r="D148" t="s">
+        <v>318</v>
+      </c>
+      <c r="E148" t="s">
         <v>358</v>
       </c>
-      <c r="E148" t="s">
-        <v>319</v>
-      </c>
       <c r="F148" t="s">
-        <v>320</v>
+        <v>359</v>
       </c>
       <c r="G148" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5455,16 +5455,16 @@
         <v>9</v>
       </c>
       <c r="D149" t="s">
+        <v>318</v>
+      </c>
+      <c r="E149" t="s">
         <v>358</v>
       </c>
-      <c r="E149" t="s">
-        <v>319</v>
-      </c>
       <c r="F149" t="s">
-        <v>320</v>
+        <v>359</v>
       </c>
       <c r="G149" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5478,16 +5478,16 @@
         <v>9</v>
       </c>
       <c r="D150" t="s">
+        <v>318</v>
+      </c>
+      <c r="E150" t="s">
         <v>358</v>
       </c>
-      <c r="E150" t="s">
-        <v>319</v>
-      </c>
       <c r="F150" t="s">
-        <v>320</v>
+        <v>359</v>
       </c>
       <c r="G150" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5501,16 +5501,16 @@
         <v>9</v>
       </c>
       <c r="D151" t="s">
+        <v>318</v>
+      </c>
+      <c r="E151" t="s">
         <v>358</v>
       </c>
-      <c r="E151" t="s">
-        <v>319</v>
-      </c>
       <c r="F151" t="s">
-        <v>320</v>
+        <v>359</v>
       </c>
       <c r="G151" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5524,16 +5524,16 @@
         <v>9</v>
       </c>
       <c r="D152" t="s">
+        <v>318</v>
+      </c>
+      <c r="E152" t="s">
         <v>358</v>
       </c>
-      <c r="E152" t="s">
-        <v>319</v>
-      </c>
       <c r="F152" t="s">
-        <v>320</v>
+        <v>359</v>
       </c>
       <c r="G152" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5547,16 +5547,16 @@
         <v>9</v>
       </c>
       <c r="D153" t="s">
+        <v>318</v>
+      </c>
+      <c r="E153" t="s">
         <v>358</v>
       </c>
-      <c r="E153" t="s">
-        <v>319</v>
-      </c>
       <c r="F153" t="s">
-        <v>320</v>
+        <v>359</v>
       </c>
       <c r="G153" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5570,16 +5570,16 @@
         <v>9</v>
       </c>
       <c r="D154" t="s">
+        <v>318</v>
+      </c>
+      <c r="E154" t="s">
         <v>372</v>
       </c>
-      <c r="E154" t="s">
-        <v>319</v>
-      </c>
       <c r="F154" t="s">
-        <v>320</v>
+        <v>373</v>
       </c>
       <c r="G154" t="s">
-        <v>373</v>
+        <v>321</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5593,16 +5593,16 @@
         <v>9</v>
       </c>
       <c r="D155" t="s">
+        <v>318</v>
+      </c>
+      <c r="E155" t="s">
         <v>372</v>
       </c>
-      <c r="E155" t="s">
-        <v>319</v>
-      </c>
       <c r="F155" t="s">
-        <v>320</v>
+        <v>373</v>
       </c>
       <c r="G155" t="s">
-        <v>373</v>
+        <v>321</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5616,16 +5616,16 @@
         <v>9</v>
       </c>
       <c r="D156" t="s">
+        <v>318</v>
+      </c>
+      <c r="E156" t="s">
         <v>372</v>
       </c>
-      <c r="E156" t="s">
-        <v>319</v>
-      </c>
       <c r="F156" t="s">
-        <v>320</v>
+        <v>373</v>
       </c>
       <c r="G156" t="s">
-        <v>373</v>
+        <v>321</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5639,16 +5639,16 @@
         <v>9</v>
       </c>
       <c r="D157" t="s">
+        <v>318</v>
+      </c>
+      <c r="E157" t="s">
         <v>372</v>
       </c>
-      <c r="E157" t="s">
-        <v>319</v>
-      </c>
       <c r="F157" t="s">
-        <v>320</v>
+        <v>373</v>
       </c>
       <c r="G157" t="s">
-        <v>373</v>
+        <v>321</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5662,16 +5662,16 @@
         <v>9</v>
       </c>
       <c r="D158" t="s">
+        <v>318</v>
+      </c>
+      <c r="E158" t="s">
         <v>372</v>
       </c>
-      <c r="E158" t="s">
-        <v>319</v>
-      </c>
       <c r="F158" t="s">
-        <v>320</v>
+        <v>373</v>
       </c>
       <c r="G158" t="s">
-        <v>373</v>
+        <v>321</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -6122,16 +6122,16 @@
         <v>9</v>
       </c>
       <c r="D178" t="s">
+        <v>384</v>
+      </c>
+      <c r="E178" t="s">
         <v>426</v>
       </c>
-      <c r="E178" t="s">
-        <v>385</v>
-      </c>
       <c r="F178" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G178" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -6145,16 +6145,16 @@
         <v>9</v>
       </c>
       <c r="D179" t="s">
+        <v>384</v>
+      </c>
+      <c r="E179" t="s">
         <v>426</v>
       </c>
-      <c r="E179" t="s">
-        <v>385</v>
-      </c>
       <c r="F179" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G179" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -6168,16 +6168,16 @@
         <v>9</v>
       </c>
       <c r="D180" t="s">
+        <v>384</v>
+      </c>
+      <c r="E180" t="s">
         <v>426</v>
       </c>
-      <c r="E180" t="s">
-        <v>385</v>
-      </c>
       <c r="F180" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G180" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -6191,16 +6191,16 @@
         <v>9</v>
       </c>
       <c r="D181" t="s">
+        <v>384</v>
+      </c>
+      <c r="E181" t="s">
         <v>426</v>
       </c>
-      <c r="E181" t="s">
-        <v>385</v>
-      </c>
       <c r="F181" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G181" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -6214,16 +6214,16 @@
         <v>9</v>
       </c>
       <c r="D182" t="s">
+        <v>384</v>
+      </c>
+      <c r="E182" t="s">
         <v>426</v>
       </c>
-      <c r="E182" t="s">
-        <v>385</v>
-      </c>
       <c r="F182" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G182" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -6237,16 +6237,16 @@
         <v>9</v>
       </c>
       <c r="D183" t="s">
+        <v>384</v>
+      </c>
+      <c r="E183" t="s">
         <v>426</v>
       </c>
-      <c r="E183" t="s">
-        <v>385</v>
-      </c>
       <c r="F183" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G183" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -6260,16 +6260,16 @@
         <v>9</v>
       </c>
       <c r="D184" t="s">
+        <v>384</v>
+      </c>
+      <c r="E184" t="s">
         <v>426</v>
       </c>
-      <c r="E184" t="s">
-        <v>385</v>
-      </c>
       <c r="F184" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G184" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -6283,16 +6283,16 @@
         <v>9</v>
       </c>
       <c r="D185" t="s">
+        <v>384</v>
+      </c>
+      <c r="E185" t="s">
         <v>426</v>
       </c>
-      <c r="E185" t="s">
-        <v>385</v>
-      </c>
       <c r="F185" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G185" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -6306,16 +6306,16 @@
         <v>9</v>
       </c>
       <c r="D186" t="s">
+        <v>384</v>
+      </c>
+      <c r="E186" t="s">
         <v>426</v>
       </c>
-      <c r="E186" t="s">
-        <v>385</v>
-      </c>
       <c r="F186" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G186" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -6329,16 +6329,16 @@
         <v>9</v>
       </c>
       <c r="D187" t="s">
+        <v>384</v>
+      </c>
+      <c r="E187" t="s">
         <v>426</v>
       </c>
-      <c r="E187" t="s">
-        <v>385</v>
-      </c>
       <c r="F187" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G187" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -6352,16 +6352,16 @@
         <v>9</v>
       </c>
       <c r="D188" t="s">
+        <v>384</v>
+      </c>
+      <c r="E188" t="s">
         <v>448</v>
       </c>
-      <c r="E188" t="s">
-        <v>385</v>
-      </c>
       <c r="F188" t="s">
-        <v>386</v>
+        <v>449</v>
       </c>
       <c r="G188" t="s">
-        <v>449</v>
+        <v>387</v>
       </c>
     </row>
     <row r="189" spans="1:7">

--- a/api/xlsx/en/SectorGroup.xlsx
+++ b/api/xlsx/en/SectorGroup.xlsx
@@ -31,12 +31,12 @@
     <t>codeforiati:category-code</t>
   </si>
   <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
     <t>codeforiati:category-name</t>
   </si>
   <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -52,12 +52,12 @@
     <t>111</t>
   </si>
   <si>
+    <t>110</t>
+  </si>
+  <si>
     <t>Education, Level Unspecified</t>
   </si>
   <si>
-    <t>110</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -154,12 +154,12 @@
     <t>121</t>
   </si>
   <si>
+    <t>120</t>
+  </si>
+  <si>
     <t>Health, General</t>
   </si>
   <si>
-    <t>120</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -394,12 +394,12 @@
     <t>151</t>
   </si>
   <si>
+    <t>150</t>
+  </si>
+  <si>
     <t>Government &amp; Civil Society-general</t>
   </si>
   <si>
-    <t>150</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -694,12 +694,12 @@
     <t>231</t>
   </si>
   <si>
+    <t>230</t>
+  </si>
+  <si>
     <t>Energy Policy</t>
   </si>
   <si>
-    <t>230</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -976,12 +976,12 @@
     <t>311</t>
   </si>
   <si>
+    <t>310</t>
+  </si>
+  <si>
     <t>Agriculture</t>
   </si>
   <si>
-    <t>310</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1174,10 +1174,10 @@
     <t>321</t>
   </si>
   <si>
+    <t>320</t>
+  </si>
+  <si>
     <t>Industry</t>
-  </si>
-  <si>
-    <t>320</t>
   </si>
   <si>
     <t>32120</t>
@@ -2172,10 +2172,10 @@
         <v>22</v>
       </c>
       <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" t="s">
         <v>23</v>
-      </c>
-      <c r="G6" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2195,10 +2195,10 @@
         <v>22</v>
       </c>
       <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" t="s">
         <v>23</v>
-      </c>
-      <c r="G7" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2218,10 +2218,10 @@
         <v>22</v>
       </c>
       <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" t="s">
         <v>23</v>
-      </c>
-      <c r="G8" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2241,10 +2241,10 @@
         <v>22</v>
       </c>
       <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" t="s">
         <v>23</v>
-      </c>
-      <c r="G9" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2264,10 +2264,10 @@
         <v>32</v>
       </c>
       <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" t="s">
         <v>33</v>
-      </c>
-      <c r="G10" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2287,10 +2287,10 @@
         <v>32</v>
       </c>
       <c r="F11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" t="s">
         <v>33</v>
-      </c>
-      <c r="G11" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2310,10 +2310,10 @@
         <v>38</v>
       </c>
       <c r="F12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" t="s">
         <v>39</v>
-      </c>
-      <c r="G12" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2333,10 +2333,10 @@
         <v>38</v>
       </c>
       <c r="F13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" t="s">
         <v>39</v>
-      </c>
-      <c r="G13" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2448,10 +2448,10 @@
         <v>56</v>
       </c>
       <c r="F18" t="s">
+        <v>46</v>
+      </c>
+      <c r="G18" t="s">
         <v>57</v>
-      </c>
-      <c r="G18" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2471,10 +2471,10 @@
         <v>56</v>
       </c>
       <c r="F19" t="s">
+        <v>46</v>
+      </c>
+      <c r="G19" t="s">
         <v>57</v>
-      </c>
-      <c r="G19" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2494,10 +2494,10 @@
         <v>56</v>
       </c>
       <c r="F20" t="s">
+        <v>46</v>
+      </c>
+      <c r="G20" t="s">
         <v>57</v>
-      </c>
-      <c r="G20" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2517,10 +2517,10 @@
         <v>56</v>
       </c>
       <c r="F21" t="s">
+        <v>46</v>
+      </c>
+      <c r="G21" t="s">
         <v>57</v>
-      </c>
-      <c r="G21" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2540,10 +2540,10 @@
         <v>56</v>
       </c>
       <c r="F22" t="s">
+        <v>46</v>
+      </c>
+      <c r="G22" t="s">
         <v>57</v>
-      </c>
-      <c r="G22" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2563,10 +2563,10 @@
         <v>56</v>
       </c>
       <c r="F23" t="s">
+        <v>46</v>
+      </c>
+      <c r="G23" t="s">
         <v>57</v>
-      </c>
-      <c r="G23" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2586,10 +2586,10 @@
         <v>56</v>
       </c>
       <c r="F24" t="s">
+        <v>46</v>
+      </c>
+      <c r="G24" t="s">
         <v>57</v>
-      </c>
-      <c r="G24" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2609,10 +2609,10 @@
         <v>56</v>
       </c>
       <c r="F25" t="s">
+        <v>46</v>
+      </c>
+      <c r="G25" t="s">
         <v>57</v>
-      </c>
-      <c r="G25" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2632,10 +2632,10 @@
         <v>74</v>
       </c>
       <c r="F26" t="s">
+        <v>46</v>
+      </c>
+      <c r="G26" t="s">
         <v>75</v>
-      </c>
-      <c r="G26" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2655,10 +2655,10 @@
         <v>74</v>
       </c>
       <c r="F27" t="s">
+        <v>46</v>
+      </c>
+      <c r="G27" t="s">
         <v>75</v>
-      </c>
-      <c r="G27" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2678,10 +2678,10 @@
         <v>74</v>
       </c>
       <c r="F28" t="s">
+        <v>46</v>
+      </c>
+      <c r="G28" t="s">
         <v>75</v>
-      </c>
-      <c r="G28" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2701,10 +2701,10 @@
         <v>74</v>
       </c>
       <c r="F29" t="s">
+        <v>46</v>
+      </c>
+      <c r="G29" t="s">
         <v>75</v>
-      </c>
-      <c r="G29" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2724,10 +2724,10 @@
         <v>74</v>
       </c>
       <c r="F30" t="s">
+        <v>46</v>
+      </c>
+      <c r="G30" t="s">
         <v>75</v>
-      </c>
-      <c r="G30" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2747,10 +2747,10 @@
         <v>74</v>
       </c>
       <c r="F31" t="s">
+        <v>46</v>
+      </c>
+      <c r="G31" t="s">
         <v>75</v>
-      </c>
-      <c r="G31" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2770,10 +2770,10 @@
         <v>89</v>
       </c>
       <c r="F32" t="s">
+        <v>89</v>
+      </c>
+      <c r="G32" t="s">
         <v>88</v>
-      </c>
-      <c r="G32" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2793,10 +2793,10 @@
         <v>89</v>
       </c>
       <c r="F33" t="s">
+        <v>89</v>
+      </c>
+      <c r="G33" t="s">
         <v>88</v>
-      </c>
-      <c r="G33" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2816,10 +2816,10 @@
         <v>89</v>
       </c>
       <c r="F34" t="s">
+        <v>89</v>
+      </c>
+      <c r="G34" t="s">
         <v>88</v>
-      </c>
-      <c r="G34" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2839,10 +2839,10 @@
         <v>89</v>
       </c>
       <c r="F35" t="s">
+        <v>89</v>
+      </c>
+      <c r="G35" t="s">
         <v>88</v>
-      </c>
-      <c r="G35" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2862,10 +2862,10 @@
         <v>89</v>
       </c>
       <c r="F36" t="s">
+        <v>89</v>
+      </c>
+      <c r="G36" t="s">
         <v>88</v>
-      </c>
-      <c r="G36" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2885,10 +2885,10 @@
         <v>101</v>
       </c>
       <c r="F37" t="s">
+        <v>101</v>
+      </c>
+      <c r="G37" t="s">
         <v>100</v>
-      </c>
-      <c r="G37" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2908,10 +2908,10 @@
         <v>101</v>
       </c>
       <c r="F38" t="s">
+        <v>101</v>
+      </c>
+      <c r="G38" t="s">
         <v>100</v>
-      </c>
-      <c r="G38" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2931,10 +2931,10 @@
         <v>101</v>
       </c>
       <c r="F39" t="s">
+        <v>101</v>
+      </c>
+      <c r="G39" t="s">
         <v>100</v>
-      </c>
-      <c r="G39" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2954,10 +2954,10 @@
         <v>101</v>
       </c>
       <c r="F40" t="s">
+        <v>101</v>
+      </c>
+      <c r="G40" t="s">
         <v>100</v>
-      </c>
-      <c r="G40" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2977,10 +2977,10 @@
         <v>101</v>
       </c>
       <c r="F41" t="s">
+        <v>101</v>
+      </c>
+      <c r="G41" t="s">
         <v>100</v>
-      </c>
-      <c r="G41" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -3000,10 +3000,10 @@
         <v>101</v>
       </c>
       <c r="F42" t="s">
+        <v>101</v>
+      </c>
+      <c r="G42" t="s">
         <v>100</v>
-      </c>
-      <c r="G42" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3023,10 +3023,10 @@
         <v>101</v>
       </c>
       <c r="F43" t="s">
+        <v>101</v>
+      </c>
+      <c r="G43" t="s">
         <v>100</v>
-      </c>
-      <c r="G43" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3046,10 +3046,10 @@
         <v>101</v>
       </c>
       <c r="F44" t="s">
+        <v>101</v>
+      </c>
+      <c r="G44" t="s">
         <v>100</v>
-      </c>
-      <c r="G44" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3069,10 +3069,10 @@
         <v>101</v>
       </c>
       <c r="F45" t="s">
+        <v>101</v>
+      </c>
+      <c r="G45" t="s">
         <v>100</v>
-      </c>
-      <c r="G45" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3092,10 +3092,10 @@
         <v>101</v>
       </c>
       <c r="F46" t="s">
+        <v>101</v>
+      </c>
+      <c r="G46" t="s">
         <v>100</v>
-      </c>
-      <c r="G46" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3115,10 +3115,10 @@
         <v>101</v>
       </c>
       <c r="F47" t="s">
+        <v>101</v>
+      </c>
+      <c r="G47" t="s">
         <v>100</v>
-      </c>
-      <c r="G47" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3506,10 +3506,10 @@
         <v>160</v>
       </c>
       <c r="F64" t="s">
+        <v>126</v>
+      </c>
+      <c r="G64" t="s">
         <v>161</v>
-      </c>
-      <c r="G64" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3529,10 +3529,10 @@
         <v>160</v>
       </c>
       <c r="F65" t="s">
+        <v>126</v>
+      </c>
+      <c r="G65" t="s">
         <v>161</v>
-      </c>
-      <c r="G65" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3552,10 +3552,10 @@
         <v>160</v>
       </c>
       <c r="F66" t="s">
+        <v>126</v>
+      </c>
+      <c r="G66" t="s">
         <v>161</v>
-      </c>
-      <c r="G66" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3575,10 +3575,10 @@
         <v>160</v>
       </c>
       <c r="F67" t="s">
+        <v>126</v>
+      </c>
+      <c r="G67" t="s">
         <v>161</v>
-      </c>
-      <c r="G67" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3598,10 +3598,10 @@
         <v>160</v>
       </c>
       <c r="F68" t="s">
+        <v>126</v>
+      </c>
+      <c r="G68" t="s">
         <v>161</v>
-      </c>
-      <c r="G68" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3621,10 +3621,10 @@
         <v>160</v>
       </c>
       <c r="F69" t="s">
+        <v>126</v>
+      </c>
+      <c r="G69" t="s">
         <v>161</v>
-      </c>
-      <c r="G69" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3644,10 +3644,10 @@
         <v>175</v>
       </c>
       <c r="F70" t="s">
+        <v>175</v>
+      </c>
+      <c r="G70" t="s">
         <v>174</v>
-      </c>
-      <c r="G70" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3667,10 +3667,10 @@
         <v>175</v>
       </c>
       <c r="F71" t="s">
+        <v>175</v>
+      </c>
+      <c r="G71" t="s">
         <v>174</v>
-      </c>
-      <c r="G71" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3690,10 +3690,10 @@
         <v>175</v>
       </c>
       <c r="F72" t="s">
+        <v>175</v>
+      </c>
+      <c r="G72" t="s">
         <v>174</v>
-      </c>
-      <c r="G72" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3713,10 +3713,10 @@
         <v>175</v>
       </c>
       <c r="F73" t="s">
+        <v>175</v>
+      </c>
+      <c r="G73" t="s">
         <v>174</v>
-      </c>
-      <c r="G73" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3736,10 +3736,10 @@
         <v>175</v>
       </c>
       <c r="F74" t="s">
+        <v>175</v>
+      </c>
+      <c r="G74" t="s">
         <v>174</v>
-      </c>
-      <c r="G74" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3759,10 +3759,10 @@
         <v>175</v>
       </c>
       <c r="F75" t="s">
+        <v>175</v>
+      </c>
+      <c r="G75" t="s">
         <v>174</v>
-      </c>
-      <c r="G75" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3782,10 +3782,10 @@
         <v>175</v>
       </c>
       <c r="F76" t="s">
+        <v>175</v>
+      </c>
+      <c r="G76" t="s">
         <v>174</v>
-      </c>
-      <c r="G76" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3805,10 +3805,10 @@
         <v>175</v>
       </c>
       <c r="F77" t="s">
+        <v>175</v>
+      </c>
+      <c r="G77" t="s">
         <v>174</v>
-      </c>
-      <c r="G77" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3828,10 +3828,10 @@
         <v>175</v>
       </c>
       <c r="F78" t="s">
+        <v>175</v>
+      </c>
+      <c r="G78" t="s">
         <v>174</v>
-      </c>
-      <c r="G78" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3851,10 +3851,10 @@
         <v>175</v>
       </c>
       <c r="F79" t="s">
+        <v>175</v>
+      </c>
+      <c r="G79" t="s">
         <v>174</v>
-      </c>
-      <c r="G79" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3874,10 +3874,10 @@
         <v>175</v>
       </c>
       <c r="F80" t="s">
+        <v>175</v>
+      </c>
+      <c r="G80" t="s">
         <v>174</v>
-      </c>
-      <c r="G80" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3897,10 +3897,10 @@
         <v>199</v>
       </c>
       <c r="F81" t="s">
+        <v>199</v>
+      </c>
+      <c r="G81" t="s">
         <v>198</v>
-      </c>
-      <c r="G81" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3920,10 +3920,10 @@
         <v>199</v>
       </c>
       <c r="F82" t="s">
+        <v>199</v>
+      </c>
+      <c r="G82" t="s">
         <v>198</v>
-      </c>
-      <c r="G82" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3943,10 +3943,10 @@
         <v>199</v>
       </c>
       <c r="F83" t="s">
+        <v>199</v>
+      </c>
+      <c r="G83" t="s">
         <v>198</v>
-      </c>
-      <c r="G83" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3966,10 +3966,10 @@
         <v>199</v>
       </c>
       <c r="F84" t="s">
+        <v>199</v>
+      </c>
+      <c r="G84" t="s">
         <v>198</v>
-      </c>
-      <c r="G84" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3989,10 +3989,10 @@
         <v>199</v>
       </c>
       <c r="F85" t="s">
+        <v>199</v>
+      </c>
+      <c r="G85" t="s">
         <v>198</v>
-      </c>
-      <c r="G85" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4012,10 +4012,10 @@
         <v>199</v>
       </c>
       <c r="F86" t="s">
+        <v>199</v>
+      </c>
+      <c r="G86" t="s">
         <v>198</v>
-      </c>
-      <c r="G86" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4035,10 +4035,10 @@
         <v>199</v>
       </c>
       <c r="F87" t="s">
+        <v>199</v>
+      </c>
+      <c r="G87" t="s">
         <v>198</v>
-      </c>
-      <c r="G87" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4058,10 +4058,10 @@
         <v>215</v>
       </c>
       <c r="F88" t="s">
+        <v>215</v>
+      </c>
+      <c r="G88" t="s">
         <v>214</v>
-      </c>
-      <c r="G88" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4081,10 +4081,10 @@
         <v>215</v>
       </c>
       <c r="F89" t="s">
+        <v>215</v>
+      </c>
+      <c r="G89" t="s">
         <v>214</v>
-      </c>
-      <c r="G89" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4104,10 +4104,10 @@
         <v>215</v>
       </c>
       <c r="F90" t="s">
+        <v>215</v>
+      </c>
+      <c r="G90" t="s">
         <v>214</v>
-      </c>
-      <c r="G90" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4127,10 +4127,10 @@
         <v>215</v>
       </c>
       <c r="F91" t="s">
+        <v>215</v>
+      </c>
+      <c r="G91" t="s">
         <v>214</v>
-      </c>
-      <c r="G91" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4242,10 +4242,10 @@
         <v>236</v>
       </c>
       <c r="F96" t="s">
+        <v>226</v>
+      </c>
+      <c r="G96" t="s">
         <v>237</v>
-      </c>
-      <c r="G96" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -4265,10 +4265,10 @@
         <v>236</v>
       </c>
       <c r="F97" t="s">
+        <v>226</v>
+      </c>
+      <c r="G97" t="s">
         <v>237</v>
-      </c>
-      <c r="G97" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4288,10 +4288,10 @@
         <v>236</v>
       </c>
       <c r="F98" t="s">
+        <v>226</v>
+      </c>
+      <c r="G98" t="s">
         <v>237</v>
-      </c>
-      <c r="G98" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4311,10 +4311,10 @@
         <v>236</v>
       </c>
       <c r="F99" t="s">
+        <v>226</v>
+      </c>
+      <c r="G99" t="s">
         <v>237</v>
-      </c>
-      <c r="G99" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4334,10 +4334,10 @@
         <v>236</v>
       </c>
       <c r="F100" t="s">
+        <v>226</v>
+      </c>
+      <c r="G100" t="s">
         <v>237</v>
-      </c>
-      <c r="G100" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4357,10 +4357,10 @@
         <v>236</v>
       </c>
       <c r="F101" t="s">
+        <v>226</v>
+      </c>
+      <c r="G101" t="s">
         <v>237</v>
-      </c>
-      <c r="G101" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4380,10 +4380,10 @@
         <v>236</v>
       </c>
       <c r="F102" t="s">
+        <v>226</v>
+      </c>
+      <c r="G102" t="s">
         <v>237</v>
-      </c>
-      <c r="G102" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4403,10 +4403,10 @@
         <v>236</v>
       </c>
       <c r="F103" t="s">
+        <v>226</v>
+      </c>
+      <c r="G103" t="s">
         <v>237</v>
-      </c>
-      <c r="G103" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4426,10 +4426,10 @@
         <v>236</v>
       </c>
       <c r="F104" t="s">
+        <v>226</v>
+      </c>
+      <c r="G104" t="s">
         <v>237</v>
-      </c>
-      <c r="G104" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4449,10 +4449,10 @@
         <v>256</v>
       </c>
       <c r="F105" t="s">
+        <v>226</v>
+      </c>
+      <c r="G105" t="s">
         <v>257</v>
-      </c>
-      <c r="G105" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4472,10 +4472,10 @@
         <v>256</v>
       </c>
       <c r="F106" t="s">
+        <v>226</v>
+      </c>
+      <c r="G106" t="s">
         <v>257</v>
-      </c>
-      <c r="G106" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4495,10 +4495,10 @@
         <v>256</v>
       </c>
       <c r="F107" t="s">
+        <v>226</v>
+      </c>
+      <c r="G107" t="s">
         <v>257</v>
-      </c>
-      <c r="G107" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4518,10 +4518,10 @@
         <v>256</v>
       </c>
       <c r="F108" t="s">
+        <v>226</v>
+      </c>
+      <c r="G108" t="s">
         <v>257</v>
-      </c>
-      <c r="G108" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4541,10 +4541,10 @@
         <v>256</v>
       </c>
       <c r="F109" t="s">
+        <v>226</v>
+      </c>
+      <c r="G109" t="s">
         <v>257</v>
-      </c>
-      <c r="G109" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4564,10 +4564,10 @@
         <v>256</v>
       </c>
       <c r="F110" t="s">
+        <v>226</v>
+      </c>
+      <c r="G110" t="s">
         <v>257</v>
-      </c>
-      <c r="G110" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4587,10 +4587,10 @@
         <v>270</v>
       </c>
       <c r="F111" t="s">
+        <v>226</v>
+      </c>
+      <c r="G111" t="s">
         <v>271</v>
-      </c>
-      <c r="G111" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4610,10 +4610,10 @@
         <v>274</v>
       </c>
       <c r="F112" t="s">
+        <v>226</v>
+      </c>
+      <c r="G112" t="s">
         <v>275</v>
-      </c>
-      <c r="G112" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4633,10 +4633,10 @@
         <v>278</v>
       </c>
       <c r="F113" t="s">
+        <v>226</v>
+      </c>
+      <c r="G113" t="s">
         <v>279</v>
-      </c>
-      <c r="G113" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4656,10 +4656,10 @@
         <v>278</v>
       </c>
       <c r="F114" t="s">
+        <v>226</v>
+      </c>
+      <c r="G114" t="s">
         <v>279</v>
-      </c>
-      <c r="G114" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4679,10 +4679,10 @@
         <v>278</v>
       </c>
       <c r="F115" t="s">
+        <v>226</v>
+      </c>
+      <c r="G115" t="s">
         <v>279</v>
-      </c>
-      <c r="G115" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4702,10 +4702,10 @@
         <v>278</v>
       </c>
       <c r="F116" t="s">
+        <v>226</v>
+      </c>
+      <c r="G116" t="s">
         <v>279</v>
-      </c>
-      <c r="G116" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4725,10 +4725,10 @@
         <v>278</v>
       </c>
       <c r="F117" t="s">
+        <v>226</v>
+      </c>
+      <c r="G117" t="s">
         <v>279</v>
-      </c>
-      <c r="G117" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4748,10 +4748,10 @@
         <v>278</v>
       </c>
       <c r="F118" t="s">
+        <v>226</v>
+      </c>
+      <c r="G118" t="s">
         <v>279</v>
-      </c>
-      <c r="G118" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4771,10 +4771,10 @@
         <v>278</v>
       </c>
       <c r="F119" t="s">
+        <v>226</v>
+      </c>
+      <c r="G119" t="s">
         <v>279</v>
-      </c>
-      <c r="G119" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4794,10 +4794,10 @@
         <v>295</v>
       </c>
       <c r="F120" t="s">
+        <v>295</v>
+      </c>
+      <c r="G120" t="s">
         <v>294</v>
-      </c>
-      <c r="G120" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4817,10 +4817,10 @@
         <v>295</v>
       </c>
       <c r="F121" t="s">
+        <v>295</v>
+      </c>
+      <c r="G121" t="s">
         <v>294</v>
-      </c>
-      <c r="G121" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4840,10 +4840,10 @@
         <v>295</v>
       </c>
       <c r="F122" t="s">
+        <v>295</v>
+      </c>
+      <c r="G122" t="s">
         <v>294</v>
-      </c>
-      <c r="G122" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4863,10 +4863,10 @@
         <v>295</v>
       </c>
       <c r="F123" t="s">
+        <v>295</v>
+      </c>
+      <c r="G123" t="s">
         <v>294</v>
-      </c>
-      <c r="G123" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4886,10 +4886,10 @@
         <v>295</v>
       </c>
       <c r="F124" t="s">
+        <v>295</v>
+      </c>
+      <c r="G124" t="s">
         <v>294</v>
-      </c>
-      <c r="G124" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4909,10 +4909,10 @@
         <v>295</v>
       </c>
       <c r="F125" t="s">
+        <v>295</v>
+      </c>
+      <c r="G125" t="s">
         <v>294</v>
-      </c>
-      <c r="G125" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4932,10 +4932,10 @@
         <v>309</v>
       </c>
       <c r="F126" t="s">
+        <v>309</v>
+      </c>
+      <c r="G126" t="s">
         <v>308</v>
-      </c>
-      <c r="G126" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4955,10 +4955,10 @@
         <v>309</v>
       </c>
       <c r="F127" t="s">
+        <v>309</v>
+      </c>
+      <c r="G127" t="s">
         <v>308</v>
-      </c>
-      <c r="G127" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4978,10 +4978,10 @@
         <v>309</v>
       </c>
       <c r="F128" t="s">
+        <v>309</v>
+      </c>
+      <c r="G128" t="s">
         <v>308</v>
-      </c>
-      <c r="G128" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -5001,10 +5001,10 @@
         <v>309</v>
       </c>
       <c r="F129" t="s">
+        <v>309</v>
+      </c>
+      <c r="G129" t="s">
         <v>308</v>
-      </c>
-      <c r="G129" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -5438,10 +5438,10 @@
         <v>358</v>
       </c>
       <c r="F148" t="s">
+        <v>320</v>
+      </c>
+      <c r="G148" t="s">
         <v>359</v>
-      </c>
-      <c r="G148" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5461,10 +5461,10 @@
         <v>358</v>
       </c>
       <c r="F149" t="s">
+        <v>320</v>
+      </c>
+      <c r="G149" t="s">
         <v>359</v>
-      </c>
-      <c r="G149" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5484,10 +5484,10 @@
         <v>358</v>
       </c>
       <c r="F150" t="s">
+        <v>320</v>
+      </c>
+      <c r="G150" t="s">
         <v>359</v>
-      </c>
-      <c r="G150" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5507,10 +5507,10 @@
         <v>358</v>
       </c>
       <c r="F151" t="s">
+        <v>320</v>
+      </c>
+      <c r="G151" t="s">
         <v>359</v>
-      </c>
-      <c r="G151" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5530,10 +5530,10 @@
         <v>358</v>
       </c>
       <c r="F152" t="s">
+        <v>320</v>
+      </c>
+      <c r="G152" t="s">
         <v>359</v>
-      </c>
-      <c r="G152" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5553,10 +5553,10 @@
         <v>358</v>
       </c>
       <c r="F153" t="s">
+        <v>320</v>
+      </c>
+      <c r="G153" t="s">
         <v>359</v>
-      </c>
-      <c r="G153" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5576,10 +5576,10 @@
         <v>372</v>
       </c>
       <c r="F154" t="s">
+        <v>320</v>
+      </c>
+      <c r="G154" t="s">
         <v>373</v>
-      </c>
-      <c r="G154" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5599,10 +5599,10 @@
         <v>372</v>
       </c>
       <c r="F155" t="s">
+        <v>320</v>
+      </c>
+      <c r="G155" t="s">
         <v>373</v>
-      </c>
-      <c r="G155" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5622,10 +5622,10 @@
         <v>372</v>
       </c>
       <c r="F156" t="s">
+        <v>320</v>
+      </c>
+      <c r="G156" t="s">
         <v>373</v>
-      </c>
-      <c r="G156" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5645,10 +5645,10 @@
         <v>372</v>
       </c>
       <c r="F157" t="s">
+        <v>320</v>
+      </c>
+      <c r="G157" t="s">
         <v>373</v>
-      </c>
-      <c r="G157" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5668,10 +5668,10 @@
         <v>372</v>
       </c>
       <c r="F158" t="s">
+        <v>320</v>
+      </c>
+      <c r="G158" t="s">
         <v>373</v>
-      </c>
-      <c r="G158" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -6128,10 +6128,10 @@
         <v>426</v>
       </c>
       <c r="F178" t="s">
+        <v>386</v>
+      </c>
+      <c r="G178" t="s">
         <v>427</v>
-      </c>
-      <c r="G178" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -6151,10 +6151,10 @@
         <v>426</v>
       </c>
       <c r="F179" t="s">
+        <v>386</v>
+      </c>
+      <c r="G179" t="s">
         <v>427</v>
-      </c>
-      <c r="G179" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -6174,10 +6174,10 @@
         <v>426</v>
       </c>
       <c r="F180" t="s">
+        <v>386</v>
+      </c>
+      <c r="G180" t="s">
         <v>427</v>
-      </c>
-      <c r="G180" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -6197,10 +6197,10 @@
         <v>426</v>
       </c>
       <c r="F181" t="s">
+        <v>386</v>
+      </c>
+      <c r="G181" t="s">
         <v>427</v>
-      </c>
-      <c r="G181" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -6220,10 +6220,10 @@
         <v>426</v>
       </c>
       <c r="F182" t="s">
+        <v>386</v>
+      </c>
+      <c r="G182" t="s">
         <v>427</v>
-      </c>
-      <c r="G182" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -6243,10 +6243,10 @@
         <v>426</v>
       </c>
       <c r="F183" t="s">
+        <v>386</v>
+      </c>
+      <c r="G183" t="s">
         <v>427</v>
-      </c>
-      <c r="G183" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -6266,10 +6266,10 @@
         <v>426</v>
       </c>
       <c r="F184" t="s">
+        <v>386</v>
+      </c>
+      <c r="G184" t="s">
         <v>427</v>
-      </c>
-      <c r="G184" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -6289,10 +6289,10 @@
         <v>426</v>
       </c>
       <c r="F185" t="s">
+        <v>386</v>
+      </c>
+      <c r="G185" t="s">
         <v>427</v>
-      </c>
-      <c r="G185" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -6312,10 +6312,10 @@
         <v>426</v>
       </c>
       <c r="F186" t="s">
+        <v>386</v>
+      </c>
+      <c r="G186" t="s">
         <v>427</v>
-      </c>
-      <c r="G186" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -6335,10 +6335,10 @@
         <v>426</v>
       </c>
       <c r="F187" t="s">
+        <v>386</v>
+      </c>
+      <c r="G187" t="s">
         <v>427</v>
-      </c>
-      <c r="G187" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -6358,10 +6358,10 @@
         <v>448</v>
       </c>
       <c r="F188" t="s">
+        <v>386</v>
+      </c>
+      <c r="G188" t="s">
         <v>449</v>
-      </c>
-      <c r="G188" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -6381,10 +6381,10 @@
         <v>453</v>
       </c>
       <c r="F189" t="s">
+        <v>453</v>
+      </c>
+      <c r="G189" t="s">
         <v>452</v>
-      </c>
-      <c r="G189" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6404,10 +6404,10 @@
         <v>453</v>
       </c>
       <c r="F190" t="s">
+        <v>453</v>
+      </c>
+      <c r="G190" t="s">
         <v>452</v>
-      </c>
-      <c r="G190" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6427,10 +6427,10 @@
         <v>453</v>
       </c>
       <c r="F191" t="s">
+        <v>453</v>
+      </c>
+      <c r="G191" t="s">
         <v>452</v>
-      </c>
-      <c r="G191" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6450,10 +6450,10 @@
         <v>453</v>
       </c>
       <c r="F192" t="s">
+        <v>453</v>
+      </c>
+      <c r="G192" t="s">
         <v>452</v>
-      </c>
-      <c r="G192" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6473,10 +6473,10 @@
         <v>453</v>
       </c>
       <c r="F193" t="s">
+        <v>453</v>
+      </c>
+      <c r="G193" t="s">
         <v>452</v>
-      </c>
-      <c r="G193" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6496,10 +6496,10 @@
         <v>453</v>
       </c>
       <c r="F194" t="s">
+        <v>453</v>
+      </c>
+      <c r="G194" t="s">
         <v>452</v>
-      </c>
-      <c r="G194" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6519,10 +6519,10 @@
         <v>467</v>
       </c>
       <c r="F195" t="s">
+        <v>467</v>
+      </c>
+      <c r="G195" t="s">
         <v>466</v>
-      </c>
-      <c r="G195" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6542,10 +6542,10 @@
         <v>471</v>
       </c>
       <c r="F196" t="s">
+        <v>471</v>
+      </c>
+      <c r="G196" t="s">
         <v>470</v>
-      </c>
-      <c r="G196" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6565,10 +6565,10 @@
         <v>471</v>
       </c>
       <c r="F197" t="s">
+        <v>471</v>
+      </c>
+      <c r="G197" t="s">
         <v>470</v>
-      </c>
-      <c r="G197" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6588,10 +6588,10 @@
         <v>471</v>
       </c>
       <c r="F198" t="s">
+        <v>471</v>
+      </c>
+      <c r="G198" t="s">
         <v>470</v>
-      </c>
-      <c r="G198" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6611,10 +6611,10 @@
         <v>471</v>
       </c>
       <c r="F199" t="s">
+        <v>471</v>
+      </c>
+      <c r="G199" t="s">
         <v>470</v>
-      </c>
-      <c r="G199" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6634,10 +6634,10 @@
         <v>471</v>
       </c>
       <c r="F200" t="s">
+        <v>471</v>
+      </c>
+      <c r="G200" t="s">
         <v>470</v>
-      </c>
-      <c r="G200" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6657,10 +6657,10 @@
         <v>471</v>
       </c>
       <c r="F201" t="s">
+        <v>471</v>
+      </c>
+      <c r="G201" t="s">
         <v>470</v>
-      </c>
-      <c r="G201" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6680,10 +6680,10 @@
         <v>485</v>
       </c>
       <c r="F202" t="s">
+        <v>485</v>
+      </c>
+      <c r="G202" t="s">
         <v>484</v>
-      </c>
-      <c r="G202" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6703,10 +6703,10 @@
         <v>485</v>
       </c>
       <c r="F203" t="s">
+        <v>485</v>
+      </c>
+      <c r="G203" t="s">
         <v>484</v>
-      </c>
-      <c r="G203" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6726,10 +6726,10 @@
         <v>485</v>
       </c>
       <c r="F204" t="s">
+        <v>485</v>
+      </c>
+      <c r="G204" t="s">
         <v>484</v>
-      </c>
-      <c r="G204" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6749,10 +6749,10 @@
         <v>485</v>
       </c>
       <c r="F205" t="s">
+        <v>485</v>
+      </c>
+      <c r="G205" t="s">
         <v>484</v>
-      </c>
-      <c r="G205" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6772,10 +6772,10 @@
         <v>485</v>
       </c>
       <c r="F206" t="s">
+        <v>485</v>
+      </c>
+      <c r="G206" t="s">
         <v>484</v>
-      </c>
-      <c r="G206" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6795,10 +6795,10 @@
         <v>485</v>
       </c>
       <c r="F207" t="s">
+        <v>485</v>
+      </c>
+      <c r="G207" t="s">
         <v>484</v>
-      </c>
-      <c r="G207" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6818,10 +6818,10 @@
         <v>485</v>
       </c>
       <c r="F208" t="s">
+        <v>485</v>
+      </c>
+      <c r="G208" t="s">
         <v>484</v>
-      </c>
-      <c r="G208" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6841,10 +6841,10 @@
         <v>485</v>
       </c>
       <c r="F209" t="s">
+        <v>485</v>
+      </c>
+      <c r="G209" t="s">
         <v>484</v>
-      </c>
-      <c r="G209" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6864,10 +6864,10 @@
         <v>485</v>
       </c>
       <c r="F210" t="s">
+        <v>485</v>
+      </c>
+      <c r="G210" t="s">
         <v>484</v>
-      </c>
-      <c r="G210" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6887,10 +6887,10 @@
         <v>485</v>
       </c>
       <c r="F211" t="s">
+        <v>485</v>
+      </c>
+      <c r="G211" t="s">
         <v>484</v>
-      </c>
-      <c r="G211" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6910,10 +6910,10 @@
         <v>507</v>
       </c>
       <c r="F212" t="s">
+        <v>507</v>
+      </c>
+      <c r="G212" t="s">
         <v>506</v>
-      </c>
-      <c r="G212" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6933,10 +6933,10 @@
         <v>511</v>
       </c>
       <c r="F213" t="s">
+        <v>511</v>
+      </c>
+      <c r="G213" t="s">
         <v>510</v>
-      </c>
-      <c r="G213" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6956,10 +6956,10 @@
         <v>515</v>
       </c>
       <c r="F214" t="s">
+        <v>515</v>
+      </c>
+      <c r="G214" t="s">
         <v>514</v>
-      </c>
-      <c r="G214" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6979,10 +6979,10 @@
         <v>515</v>
       </c>
       <c r="F215" t="s">
+        <v>515</v>
+      </c>
+      <c r="G215" t="s">
         <v>514</v>
-      </c>
-      <c r="G215" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -7002,10 +7002,10 @@
         <v>521</v>
       </c>
       <c r="F216" t="s">
+        <v>521</v>
+      </c>
+      <c r="G216" t="s">
         <v>520</v>
-      </c>
-      <c r="G216" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -7025,10 +7025,10 @@
         <v>521</v>
       </c>
       <c r="F217" t="s">
+        <v>521</v>
+      </c>
+      <c r="G217" t="s">
         <v>520</v>
-      </c>
-      <c r="G217" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -7048,10 +7048,10 @@
         <v>521</v>
       </c>
       <c r="F218" t="s">
+        <v>521</v>
+      </c>
+      <c r="G218" t="s">
         <v>520</v>
-      </c>
-      <c r="G218" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -7071,10 +7071,10 @@
         <v>521</v>
       </c>
       <c r="F219" t="s">
+        <v>521</v>
+      </c>
+      <c r="G219" t="s">
         <v>520</v>
-      </c>
-      <c r="G219" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -7094,10 +7094,10 @@
         <v>521</v>
       </c>
       <c r="F220" t="s">
+        <v>521</v>
+      </c>
+      <c r="G220" t="s">
         <v>520</v>
-      </c>
-      <c r="G220" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -7117,10 +7117,10 @@
         <v>521</v>
       </c>
       <c r="F221" t="s">
+        <v>521</v>
+      </c>
+      <c r="G221" t="s">
         <v>520</v>
-      </c>
-      <c r="G221" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -7140,10 +7140,10 @@
         <v>521</v>
       </c>
       <c r="F222" t="s">
+        <v>521</v>
+      </c>
+      <c r="G222" t="s">
         <v>520</v>
-      </c>
-      <c r="G222" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -7163,10 +7163,10 @@
         <v>537</v>
       </c>
       <c r="F223" t="s">
+        <v>537</v>
+      </c>
+      <c r="G223" t="s">
         <v>536</v>
-      </c>
-      <c r="G223" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -7186,10 +7186,10 @@
         <v>537</v>
       </c>
       <c r="F224" t="s">
+        <v>537</v>
+      </c>
+      <c r="G224" t="s">
         <v>536</v>
-      </c>
-      <c r="G224" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -7209,10 +7209,10 @@
         <v>537</v>
       </c>
       <c r="F225" t="s">
+        <v>537</v>
+      </c>
+      <c r="G225" t="s">
         <v>536</v>
-      </c>
-      <c r="G225" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -7232,10 +7232,10 @@
         <v>545</v>
       </c>
       <c r="F226" t="s">
+        <v>545</v>
+      </c>
+      <c r="G226" t="s">
         <v>544</v>
-      </c>
-      <c r="G226" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -7255,10 +7255,10 @@
         <v>549</v>
       </c>
       <c r="F227" t="s">
+        <v>549</v>
+      </c>
+      <c r="G227" t="s">
         <v>548</v>
-      </c>
-      <c r="G227" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -7278,10 +7278,10 @@
         <v>553</v>
       </c>
       <c r="F228" t="s">
+        <v>553</v>
+      </c>
+      <c r="G228" t="s">
         <v>552</v>
-      </c>
-      <c r="G228" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -7301,10 +7301,10 @@
         <v>557</v>
       </c>
       <c r="F229" t="s">
+        <v>557</v>
+      </c>
+      <c r="G229" t="s">
         <v>556</v>
-      </c>
-      <c r="G229" t="s">
-        <v>557</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -7324,10 +7324,10 @@
         <v>561</v>
       </c>
       <c r="F230" t="s">
+        <v>561</v>
+      </c>
+      <c r="G230" t="s">
         <v>560</v>
-      </c>
-      <c r="G230" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -7347,10 +7347,10 @@
         <v>561</v>
       </c>
       <c r="F231" t="s">
+        <v>561</v>
+      </c>
+      <c r="G231" t="s">
         <v>560</v>
-      </c>
-      <c r="G231" t="s">
-        <v>561</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/en/SectorGroup.xlsx
+++ b/api/xlsx/en/SectorGroup.xlsx
@@ -31,12 +31,12 @@
     <t>codeforiati:category-code</t>
   </si>
   <si>
+    <t>codeforiati:category-name</t>
+  </si>
+  <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
-    <t>codeforiati:category-name</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -52,12 +52,12 @@
     <t>111</t>
   </si>
   <si>
+    <t>Education, Level Unspecified</t>
+  </si>
+  <si>
     <t>110</t>
   </si>
   <si>
-    <t>Education, Level Unspecified</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -154,12 +154,12 @@
     <t>121</t>
   </si>
   <si>
+    <t>Health, General</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
-    <t>Health, General</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -394,12 +394,12 @@
     <t>151</t>
   </si>
   <si>
+    <t>Government &amp; Civil Society-general</t>
+  </si>
+  <si>
     <t>150</t>
   </si>
   <si>
-    <t>Government &amp; Civil Society-general</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -694,12 +694,12 @@
     <t>231</t>
   </si>
   <si>
+    <t>Energy Policy</t>
+  </si>
+  <si>
     <t>230</t>
   </si>
   <si>
-    <t>Energy Policy</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -976,12 +976,12 @@
     <t>311</t>
   </si>
   <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
     <t>310</t>
   </si>
   <si>
-    <t>Agriculture</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1174,10 +1174,10 @@
     <t>321</t>
   </si>
   <si>
+    <t>Industry</t>
+  </si>
+  <si>
     <t>320</t>
-  </si>
-  <si>
-    <t>Industry</t>
   </si>
   <si>
     <t>32120</t>
@@ -2172,10 +2172,10 @@
         <v>22</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2195,10 +2195,10 @@
         <v>22</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G7" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2218,10 +2218,10 @@
         <v>22</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G8" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2241,10 +2241,10 @@
         <v>22</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G9" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2264,10 +2264,10 @@
         <v>32</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="G10" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2287,10 +2287,10 @@
         <v>32</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="G11" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2310,10 +2310,10 @@
         <v>38</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="G12" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2333,10 +2333,10 @@
         <v>38</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="G13" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2448,10 +2448,10 @@
         <v>56</v>
       </c>
       <c r="F18" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G18" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2471,10 +2471,10 @@
         <v>56</v>
       </c>
       <c r="F19" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G19" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2494,10 +2494,10 @@
         <v>56</v>
       </c>
       <c r="F20" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G20" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2517,10 +2517,10 @@
         <v>56</v>
       </c>
       <c r="F21" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G21" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2540,10 +2540,10 @@
         <v>56</v>
       </c>
       <c r="F22" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G22" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2563,10 +2563,10 @@
         <v>56</v>
       </c>
       <c r="F23" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G23" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2586,10 +2586,10 @@
         <v>56</v>
       </c>
       <c r="F24" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G24" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2609,10 +2609,10 @@
         <v>56</v>
       </c>
       <c r="F25" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G25" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2632,10 +2632,10 @@
         <v>74</v>
       </c>
       <c r="F26" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G26" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2655,10 +2655,10 @@
         <v>74</v>
       </c>
       <c r="F27" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G27" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2678,10 +2678,10 @@
         <v>74</v>
       </c>
       <c r="F28" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G28" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2701,10 +2701,10 @@
         <v>74</v>
       </c>
       <c r="F29" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G29" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2724,10 +2724,10 @@
         <v>74</v>
       </c>
       <c r="F30" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G30" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2747,10 +2747,10 @@
         <v>74</v>
       </c>
       <c r="F31" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G31" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2770,10 +2770,10 @@
         <v>89</v>
       </c>
       <c r="F32" t="s">
+        <v>88</v>
+      </c>
+      <c r="G32" t="s">
         <v>89</v>
-      </c>
-      <c r="G32" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2793,10 +2793,10 @@
         <v>89</v>
       </c>
       <c r="F33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G33" t="s">
         <v>89</v>
-      </c>
-      <c r="G33" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2816,10 +2816,10 @@
         <v>89</v>
       </c>
       <c r="F34" t="s">
+        <v>88</v>
+      </c>
+      <c r="G34" t="s">
         <v>89</v>
-      </c>
-      <c r="G34" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2839,10 +2839,10 @@
         <v>89</v>
       </c>
       <c r="F35" t="s">
+        <v>88</v>
+      </c>
+      <c r="G35" t="s">
         <v>89</v>
-      </c>
-      <c r="G35" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2862,10 +2862,10 @@
         <v>89</v>
       </c>
       <c r="F36" t="s">
+        <v>88</v>
+      </c>
+      <c r="G36" t="s">
         <v>89</v>
-      </c>
-      <c r="G36" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2885,10 +2885,10 @@
         <v>101</v>
       </c>
       <c r="F37" t="s">
+        <v>100</v>
+      </c>
+      <c r="G37" t="s">
         <v>101</v>
-      </c>
-      <c r="G37" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2908,10 +2908,10 @@
         <v>101</v>
       </c>
       <c r="F38" t="s">
+        <v>100</v>
+      </c>
+      <c r="G38" t="s">
         <v>101</v>
-      </c>
-      <c r="G38" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2931,10 +2931,10 @@
         <v>101</v>
       </c>
       <c r="F39" t="s">
+        <v>100</v>
+      </c>
+      <c r="G39" t="s">
         <v>101</v>
-      </c>
-      <c r="G39" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2954,10 +2954,10 @@
         <v>101</v>
       </c>
       <c r="F40" t="s">
+        <v>100</v>
+      </c>
+      <c r="G40" t="s">
         <v>101</v>
-      </c>
-      <c r="G40" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2977,10 +2977,10 @@
         <v>101</v>
       </c>
       <c r="F41" t="s">
+        <v>100</v>
+      </c>
+      <c r="G41" t="s">
         <v>101</v>
-      </c>
-      <c r="G41" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -3000,10 +3000,10 @@
         <v>101</v>
       </c>
       <c r="F42" t="s">
+        <v>100</v>
+      </c>
+      <c r="G42" t="s">
         <v>101</v>
-      </c>
-      <c r="G42" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3023,10 +3023,10 @@
         <v>101</v>
       </c>
       <c r="F43" t="s">
+        <v>100</v>
+      </c>
+      <c r="G43" t="s">
         <v>101</v>
-      </c>
-      <c r="G43" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3046,10 +3046,10 @@
         <v>101</v>
       </c>
       <c r="F44" t="s">
+        <v>100</v>
+      </c>
+      <c r="G44" t="s">
         <v>101</v>
-      </c>
-      <c r="G44" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3069,10 +3069,10 @@
         <v>101</v>
       </c>
       <c r="F45" t="s">
+        <v>100</v>
+      </c>
+      <c r="G45" t="s">
         <v>101</v>
-      </c>
-      <c r="G45" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3092,10 +3092,10 @@
         <v>101</v>
       </c>
       <c r="F46" t="s">
+        <v>100</v>
+      </c>
+      <c r="G46" t="s">
         <v>101</v>
-      </c>
-      <c r="G46" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3115,10 +3115,10 @@
         <v>101</v>
       </c>
       <c r="F47" t="s">
+        <v>100</v>
+      </c>
+      <c r="G47" t="s">
         <v>101</v>
-      </c>
-      <c r="G47" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3506,10 +3506,10 @@
         <v>160</v>
       </c>
       <c r="F64" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G64" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3529,10 +3529,10 @@
         <v>160</v>
       </c>
       <c r="F65" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G65" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3552,10 +3552,10 @@
         <v>160</v>
       </c>
       <c r="F66" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G66" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3575,10 +3575,10 @@
         <v>160</v>
       </c>
       <c r="F67" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G67" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3598,10 +3598,10 @@
         <v>160</v>
       </c>
       <c r="F68" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G68" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3621,10 +3621,10 @@
         <v>160</v>
       </c>
       <c r="F69" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G69" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3644,10 +3644,10 @@
         <v>175</v>
       </c>
       <c r="F70" t="s">
+        <v>174</v>
+      </c>
+      <c r="G70" t="s">
         <v>175</v>
-      </c>
-      <c r="G70" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3667,10 +3667,10 @@
         <v>175</v>
       </c>
       <c r="F71" t="s">
+        <v>174</v>
+      </c>
+      <c r="G71" t="s">
         <v>175</v>
-      </c>
-      <c r="G71" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3690,10 +3690,10 @@
         <v>175</v>
       </c>
       <c r="F72" t="s">
+        <v>174</v>
+      </c>
+      <c r="G72" t="s">
         <v>175</v>
-      </c>
-      <c r="G72" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3713,10 +3713,10 @@
         <v>175</v>
       </c>
       <c r="F73" t="s">
+        <v>174</v>
+      </c>
+      <c r="G73" t="s">
         <v>175</v>
-      </c>
-      <c r="G73" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3736,10 +3736,10 @@
         <v>175</v>
       </c>
       <c r="F74" t="s">
+        <v>174</v>
+      </c>
+      <c r="G74" t="s">
         <v>175</v>
-      </c>
-      <c r="G74" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3759,10 +3759,10 @@
         <v>175</v>
       </c>
       <c r="F75" t="s">
+        <v>174</v>
+      </c>
+      <c r="G75" t="s">
         <v>175</v>
-      </c>
-      <c r="G75" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3782,10 +3782,10 @@
         <v>175</v>
       </c>
       <c r="F76" t="s">
+        <v>174</v>
+      </c>
+      <c r="G76" t="s">
         <v>175</v>
-      </c>
-      <c r="G76" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3805,10 +3805,10 @@
         <v>175</v>
       </c>
       <c r="F77" t="s">
+        <v>174</v>
+      </c>
+      <c r="G77" t="s">
         <v>175</v>
-      </c>
-      <c r="G77" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3828,10 +3828,10 @@
         <v>175</v>
       </c>
       <c r="F78" t="s">
+        <v>174</v>
+      </c>
+      <c r="G78" t="s">
         <v>175</v>
-      </c>
-      <c r="G78" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3851,10 +3851,10 @@
         <v>175</v>
       </c>
       <c r="F79" t="s">
+        <v>174</v>
+      </c>
+      <c r="G79" t="s">
         <v>175</v>
-      </c>
-      <c r="G79" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3874,10 +3874,10 @@
         <v>175</v>
       </c>
       <c r="F80" t="s">
+        <v>174</v>
+      </c>
+      <c r="G80" t="s">
         <v>175</v>
-      </c>
-      <c r="G80" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3897,10 +3897,10 @@
         <v>199</v>
       </c>
       <c r="F81" t="s">
+        <v>198</v>
+      </c>
+      <c r="G81" t="s">
         <v>199</v>
-      </c>
-      <c r="G81" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3920,10 +3920,10 @@
         <v>199</v>
       </c>
       <c r="F82" t="s">
+        <v>198</v>
+      </c>
+      <c r="G82" t="s">
         <v>199</v>
-      </c>
-      <c r="G82" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3943,10 +3943,10 @@
         <v>199</v>
       </c>
       <c r="F83" t="s">
+        <v>198</v>
+      </c>
+      <c r="G83" t="s">
         <v>199</v>
-      </c>
-      <c r="G83" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3966,10 +3966,10 @@
         <v>199</v>
       </c>
       <c r="F84" t="s">
+        <v>198</v>
+      </c>
+      <c r="G84" t="s">
         <v>199</v>
-      </c>
-      <c r="G84" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3989,10 +3989,10 @@
         <v>199</v>
       </c>
       <c r="F85" t="s">
+        <v>198</v>
+      </c>
+      <c r="G85" t="s">
         <v>199</v>
-      </c>
-      <c r="G85" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4012,10 +4012,10 @@
         <v>199</v>
       </c>
       <c r="F86" t="s">
+        <v>198</v>
+      </c>
+      <c r="G86" t="s">
         <v>199</v>
-      </c>
-      <c r="G86" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4035,10 +4035,10 @@
         <v>199</v>
       </c>
       <c r="F87" t="s">
+        <v>198</v>
+      </c>
+      <c r="G87" t="s">
         <v>199</v>
-      </c>
-      <c r="G87" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4058,10 +4058,10 @@
         <v>215</v>
       </c>
       <c r="F88" t="s">
+        <v>214</v>
+      </c>
+      <c r="G88" t="s">
         <v>215</v>
-      </c>
-      <c r="G88" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4081,10 +4081,10 @@
         <v>215</v>
       </c>
       <c r="F89" t="s">
+        <v>214</v>
+      </c>
+      <c r="G89" t="s">
         <v>215</v>
-      </c>
-      <c r="G89" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4104,10 +4104,10 @@
         <v>215</v>
       </c>
       <c r="F90" t="s">
+        <v>214</v>
+      </c>
+      <c r="G90" t="s">
         <v>215</v>
-      </c>
-      <c r="G90" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4127,10 +4127,10 @@
         <v>215</v>
       </c>
       <c r="F91" t="s">
+        <v>214</v>
+      </c>
+      <c r="G91" t="s">
         <v>215</v>
-      </c>
-      <c r="G91" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4242,10 +4242,10 @@
         <v>236</v>
       </c>
       <c r="F96" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G96" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -4265,10 +4265,10 @@
         <v>236</v>
       </c>
       <c r="F97" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G97" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4288,10 +4288,10 @@
         <v>236</v>
       </c>
       <c r="F98" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G98" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4311,10 +4311,10 @@
         <v>236</v>
       </c>
       <c r="F99" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G99" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4334,10 +4334,10 @@
         <v>236</v>
       </c>
       <c r="F100" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G100" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4357,10 +4357,10 @@
         <v>236</v>
       </c>
       <c r="F101" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G101" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4380,10 +4380,10 @@
         <v>236</v>
       </c>
       <c r="F102" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G102" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4403,10 +4403,10 @@
         <v>236</v>
       </c>
       <c r="F103" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G103" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4426,10 +4426,10 @@
         <v>236</v>
       </c>
       <c r="F104" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G104" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4449,10 +4449,10 @@
         <v>256</v>
       </c>
       <c r="F105" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G105" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4472,10 +4472,10 @@
         <v>256</v>
       </c>
       <c r="F106" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G106" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4495,10 +4495,10 @@
         <v>256</v>
       </c>
       <c r="F107" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G107" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4518,10 +4518,10 @@
         <v>256</v>
       </c>
       <c r="F108" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G108" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4541,10 +4541,10 @@
         <v>256</v>
       </c>
       <c r="F109" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G109" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4564,10 +4564,10 @@
         <v>256</v>
       </c>
       <c r="F110" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G110" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4587,10 +4587,10 @@
         <v>270</v>
       </c>
       <c r="F111" t="s">
-        <v>226</v>
+        <v>271</v>
       </c>
       <c r="G111" t="s">
-        <v>271</v>
+        <v>227</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4610,10 +4610,10 @@
         <v>274</v>
       </c>
       <c r="F112" t="s">
-        <v>226</v>
+        <v>275</v>
       </c>
       <c r="G112" t="s">
-        <v>275</v>
+        <v>227</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4633,10 +4633,10 @@
         <v>278</v>
       </c>
       <c r="F113" t="s">
-        <v>226</v>
+        <v>279</v>
       </c>
       <c r="G113" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4656,10 +4656,10 @@
         <v>278</v>
       </c>
       <c r="F114" t="s">
-        <v>226</v>
+        <v>279</v>
       </c>
       <c r="G114" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4679,10 +4679,10 @@
         <v>278</v>
       </c>
       <c r="F115" t="s">
-        <v>226</v>
+        <v>279</v>
       </c>
       <c r="G115" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4702,10 +4702,10 @@
         <v>278</v>
       </c>
       <c r="F116" t="s">
-        <v>226</v>
+        <v>279</v>
       </c>
       <c r="G116" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4725,10 +4725,10 @@
         <v>278</v>
       </c>
       <c r="F117" t="s">
-        <v>226</v>
+        <v>279</v>
       </c>
       <c r="G117" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4748,10 +4748,10 @@
         <v>278</v>
       </c>
       <c r="F118" t="s">
-        <v>226</v>
+        <v>279</v>
       </c>
       <c r="G118" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4771,10 +4771,10 @@
         <v>278</v>
       </c>
       <c r="F119" t="s">
-        <v>226</v>
+        <v>279</v>
       </c>
       <c r="G119" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4794,10 +4794,10 @@
         <v>295</v>
       </c>
       <c r="F120" t="s">
+        <v>294</v>
+      </c>
+      <c r="G120" t="s">
         <v>295</v>
-      </c>
-      <c r="G120" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4817,10 +4817,10 @@
         <v>295</v>
       </c>
       <c r="F121" t="s">
+        <v>294</v>
+      </c>
+      <c r="G121" t="s">
         <v>295</v>
-      </c>
-      <c r="G121" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4840,10 +4840,10 @@
         <v>295</v>
       </c>
       <c r="F122" t="s">
+        <v>294</v>
+      </c>
+      <c r="G122" t="s">
         <v>295</v>
-      </c>
-      <c r="G122" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4863,10 +4863,10 @@
         <v>295</v>
       </c>
       <c r="F123" t="s">
+        <v>294</v>
+      </c>
+      <c r="G123" t="s">
         <v>295</v>
-      </c>
-      <c r="G123" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4886,10 +4886,10 @@
         <v>295</v>
       </c>
       <c r="F124" t="s">
+        <v>294</v>
+      </c>
+      <c r="G124" t="s">
         <v>295</v>
-      </c>
-      <c r="G124" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4909,10 +4909,10 @@
         <v>295</v>
       </c>
       <c r="F125" t="s">
+        <v>294</v>
+      </c>
+      <c r="G125" t="s">
         <v>295</v>
-      </c>
-      <c r="G125" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4932,10 +4932,10 @@
         <v>309</v>
       </c>
       <c r="F126" t="s">
+        <v>308</v>
+      </c>
+      <c r="G126" t="s">
         <v>309</v>
-      </c>
-      <c r="G126" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4955,10 +4955,10 @@
         <v>309</v>
       </c>
       <c r="F127" t="s">
+        <v>308</v>
+      </c>
+      <c r="G127" t="s">
         <v>309</v>
-      </c>
-      <c r="G127" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4978,10 +4978,10 @@
         <v>309</v>
       </c>
       <c r="F128" t="s">
+        <v>308</v>
+      </c>
+      <c r="G128" t="s">
         <v>309</v>
-      </c>
-      <c r="G128" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -5001,10 +5001,10 @@
         <v>309</v>
       </c>
       <c r="F129" t="s">
+        <v>308</v>
+      </c>
+      <c r="G129" t="s">
         <v>309</v>
-      </c>
-      <c r="G129" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -5438,10 +5438,10 @@
         <v>358</v>
       </c>
       <c r="F148" t="s">
-        <v>320</v>
+        <v>359</v>
       </c>
       <c r="G148" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5461,10 +5461,10 @@
         <v>358</v>
       </c>
       <c r="F149" t="s">
-        <v>320</v>
+        <v>359</v>
       </c>
       <c r="G149" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5484,10 +5484,10 @@
         <v>358</v>
       </c>
       <c r="F150" t="s">
-        <v>320</v>
+        <v>359</v>
       </c>
       <c r="G150" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5507,10 +5507,10 @@
         <v>358</v>
       </c>
       <c r="F151" t="s">
-        <v>320</v>
+        <v>359</v>
       </c>
       <c r="G151" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5530,10 +5530,10 @@
         <v>358</v>
       </c>
       <c r="F152" t="s">
-        <v>320</v>
+        <v>359</v>
       </c>
       <c r="G152" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5553,10 +5553,10 @@
         <v>358</v>
       </c>
       <c r="F153" t="s">
-        <v>320</v>
+        <v>359</v>
       </c>
       <c r="G153" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5576,10 +5576,10 @@
         <v>372</v>
       </c>
       <c r="F154" t="s">
-        <v>320</v>
+        <v>373</v>
       </c>
       <c r="G154" t="s">
-        <v>373</v>
+        <v>321</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5599,10 +5599,10 @@
         <v>372</v>
       </c>
       <c r="F155" t="s">
-        <v>320</v>
+        <v>373</v>
       </c>
       <c r="G155" t="s">
-        <v>373</v>
+        <v>321</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5622,10 +5622,10 @@
         <v>372</v>
       </c>
       <c r="F156" t="s">
-        <v>320</v>
+        <v>373</v>
       </c>
       <c r="G156" t="s">
-        <v>373</v>
+        <v>321</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5645,10 +5645,10 @@
         <v>372</v>
       </c>
       <c r="F157" t="s">
-        <v>320</v>
+        <v>373</v>
       </c>
       <c r="G157" t="s">
-        <v>373</v>
+        <v>321</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5668,10 +5668,10 @@
         <v>372</v>
       </c>
       <c r="F158" t="s">
-        <v>320</v>
+        <v>373</v>
       </c>
       <c r="G158" t="s">
-        <v>373</v>
+        <v>321</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -6128,10 +6128,10 @@
         <v>426</v>
       </c>
       <c r="F178" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G178" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -6151,10 +6151,10 @@
         <v>426</v>
       </c>
       <c r="F179" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G179" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -6174,10 +6174,10 @@
         <v>426</v>
       </c>
       <c r="F180" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G180" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -6197,10 +6197,10 @@
         <v>426</v>
       </c>
       <c r="F181" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G181" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -6220,10 +6220,10 @@
         <v>426</v>
       </c>
       <c r="F182" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G182" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -6243,10 +6243,10 @@
         <v>426</v>
       </c>
       <c r="F183" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G183" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -6266,10 +6266,10 @@
         <v>426</v>
       </c>
       <c r="F184" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G184" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -6289,10 +6289,10 @@
         <v>426</v>
       </c>
       <c r="F185" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G185" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -6312,10 +6312,10 @@
         <v>426</v>
       </c>
       <c r="F186" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G186" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -6335,10 +6335,10 @@
         <v>426</v>
       </c>
       <c r="F187" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G187" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -6358,10 +6358,10 @@
         <v>448</v>
       </c>
       <c r="F188" t="s">
-        <v>386</v>
+        <v>449</v>
       </c>
       <c r="G188" t="s">
-        <v>449</v>
+        <v>387</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -6381,10 +6381,10 @@
         <v>453</v>
       </c>
       <c r="F189" t="s">
+        <v>452</v>
+      </c>
+      <c r="G189" t="s">
         <v>453</v>
-      </c>
-      <c r="G189" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6404,10 +6404,10 @@
         <v>453</v>
       </c>
       <c r="F190" t="s">
+        <v>452</v>
+      </c>
+      <c r="G190" t="s">
         <v>453</v>
-      </c>
-      <c r="G190" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6427,10 +6427,10 @@
         <v>453</v>
       </c>
       <c r="F191" t="s">
+        <v>452</v>
+      </c>
+      <c r="G191" t="s">
         <v>453</v>
-      </c>
-      <c r="G191" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6450,10 +6450,10 @@
         <v>453</v>
       </c>
       <c r="F192" t="s">
+        <v>452</v>
+      </c>
+      <c r="G192" t="s">
         <v>453</v>
-      </c>
-      <c r="G192" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6473,10 +6473,10 @@
         <v>453</v>
       </c>
       <c r="F193" t="s">
+        <v>452</v>
+      </c>
+      <c r="G193" t="s">
         <v>453</v>
-      </c>
-      <c r="G193" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6496,10 +6496,10 @@
         <v>453</v>
       </c>
       <c r="F194" t="s">
+        <v>452</v>
+      </c>
+      <c r="G194" t="s">
         <v>453</v>
-      </c>
-      <c r="G194" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6519,10 +6519,10 @@
         <v>467</v>
       </c>
       <c r="F195" t="s">
+        <v>466</v>
+      </c>
+      <c r="G195" t="s">
         <v>467</v>
-      </c>
-      <c r="G195" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6542,10 +6542,10 @@
         <v>471</v>
       </c>
       <c r="F196" t="s">
+        <v>470</v>
+      </c>
+      <c r="G196" t="s">
         <v>471</v>
-      </c>
-      <c r="G196" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6565,10 +6565,10 @@
         <v>471</v>
       </c>
       <c r="F197" t="s">
+        <v>470</v>
+      </c>
+      <c r="G197" t="s">
         <v>471</v>
-      </c>
-      <c r="G197" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6588,10 +6588,10 @@
         <v>471</v>
       </c>
       <c r="F198" t="s">
+        <v>470</v>
+      </c>
+      <c r="G198" t="s">
         <v>471</v>
-      </c>
-      <c r="G198" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6611,10 +6611,10 @@
         <v>471</v>
       </c>
       <c r="F199" t="s">
+        <v>470</v>
+      </c>
+      <c r="G199" t="s">
         <v>471</v>
-      </c>
-      <c r="G199" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6634,10 +6634,10 @@
         <v>471</v>
       </c>
       <c r="F200" t="s">
+        <v>470</v>
+      </c>
+      <c r="G200" t="s">
         <v>471</v>
-      </c>
-      <c r="G200" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6657,10 +6657,10 @@
         <v>471</v>
       </c>
       <c r="F201" t="s">
+        <v>470</v>
+      </c>
+      <c r="G201" t="s">
         <v>471</v>
-      </c>
-      <c r="G201" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6680,10 +6680,10 @@
         <v>485</v>
       </c>
       <c r="F202" t="s">
+        <v>484</v>
+      </c>
+      <c r="G202" t="s">
         <v>485</v>
-      </c>
-      <c r="G202" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6703,10 +6703,10 @@
         <v>485</v>
       </c>
       <c r="F203" t="s">
+        <v>484</v>
+      </c>
+      <c r="G203" t="s">
         <v>485</v>
-      </c>
-      <c r="G203" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6726,10 +6726,10 @@
         <v>485</v>
       </c>
       <c r="F204" t="s">
+        <v>484</v>
+      </c>
+      <c r="G204" t="s">
         <v>485</v>
-      </c>
-      <c r="G204" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6749,10 +6749,10 @@
         <v>485</v>
       </c>
       <c r="F205" t="s">
+        <v>484</v>
+      </c>
+      <c r="G205" t="s">
         <v>485</v>
-      </c>
-      <c r="G205" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6772,10 +6772,10 @@
         <v>485</v>
       </c>
       <c r="F206" t="s">
+        <v>484</v>
+      </c>
+      <c r="G206" t="s">
         <v>485</v>
-      </c>
-      <c r="G206" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6795,10 +6795,10 @@
         <v>485</v>
       </c>
       <c r="F207" t="s">
+        <v>484</v>
+      </c>
+      <c r="G207" t="s">
         <v>485</v>
-      </c>
-      <c r="G207" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6818,10 +6818,10 @@
         <v>485</v>
       </c>
       <c r="F208" t="s">
+        <v>484</v>
+      </c>
+      <c r="G208" t="s">
         <v>485</v>
-      </c>
-      <c r="G208" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6841,10 +6841,10 @@
         <v>485</v>
       </c>
       <c r="F209" t="s">
+        <v>484</v>
+      </c>
+      <c r="G209" t="s">
         <v>485</v>
-      </c>
-      <c r="G209" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6864,10 +6864,10 @@
         <v>485</v>
       </c>
       <c r="F210" t="s">
+        <v>484</v>
+      </c>
+      <c r="G210" t="s">
         <v>485</v>
-      </c>
-      <c r="G210" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6887,10 +6887,10 @@
         <v>485</v>
       </c>
       <c r="F211" t="s">
+        <v>484</v>
+      </c>
+      <c r="G211" t="s">
         <v>485</v>
-      </c>
-      <c r="G211" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6910,10 +6910,10 @@
         <v>507</v>
       </c>
       <c r="F212" t="s">
+        <v>506</v>
+      </c>
+      <c r="G212" t="s">
         <v>507</v>
-      </c>
-      <c r="G212" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6933,10 +6933,10 @@
         <v>511</v>
       </c>
       <c r="F213" t="s">
+        <v>510</v>
+      </c>
+      <c r="G213" t="s">
         <v>511</v>
-      </c>
-      <c r="G213" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6956,10 +6956,10 @@
         <v>515</v>
       </c>
       <c r="F214" t="s">
+        <v>514</v>
+      </c>
+      <c r="G214" t="s">
         <v>515</v>
-      </c>
-      <c r="G214" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6979,10 +6979,10 @@
         <v>515</v>
       </c>
       <c r="F215" t="s">
+        <v>514</v>
+      </c>
+      <c r="G215" t="s">
         <v>515</v>
-      </c>
-      <c r="G215" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -7002,10 +7002,10 @@
         <v>521</v>
       </c>
       <c r="F216" t="s">
+        <v>520</v>
+      </c>
+      <c r="G216" t="s">
         <v>521</v>
-      </c>
-      <c r="G216" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -7025,10 +7025,10 @@
         <v>521</v>
       </c>
       <c r="F217" t="s">
+        <v>520</v>
+      </c>
+      <c r="G217" t="s">
         <v>521</v>
-      </c>
-      <c r="G217" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -7048,10 +7048,10 @@
         <v>521</v>
       </c>
       <c r="F218" t="s">
+        <v>520</v>
+      </c>
+      <c r="G218" t="s">
         <v>521</v>
-      </c>
-      <c r="G218" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -7071,10 +7071,10 @@
         <v>521</v>
       </c>
       <c r="F219" t="s">
+        <v>520</v>
+      </c>
+      <c r="G219" t="s">
         <v>521</v>
-      </c>
-      <c r="G219" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -7094,10 +7094,10 @@
         <v>521</v>
       </c>
       <c r="F220" t="s">
+        <v>520</v>
+      </c>
+      <c r="G220" t="s">
         <v>521</v>
-      </c>
-      <c r="G220" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -7117,10 +7117,10 @@
         <v>521</v>
       </c>
       <c r="F221" t="s">
+        <v>520</v>
+      </c>
+      <c r="G221" t="s">
         <v>521</v>
-      </c>
-      <c r="G221" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -7140,10 +7140,10 @@
         <v>521</v>
       </c>
       <c r="F222" t="s">
+        <v>520</v>
+      </c>
+      <c r="G222" t="s">
         <v>521</v>
-      </c>
-      <c r="G222" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -7163,10 +7163,10 @@
         <v>537</v>
       </c>
       <c r="F223" t="s">
+        <v>536</v>
+      </c>
+      <c r="G223" t="s">
         <v>537</v>
-      </c>
-      <c r="G223" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -7186,10 +7186,10 @@
         <v>537</v>
       </c>
       <c r="F224" t="s">
+        <v>536</v>
+      </c>
+      <c r="G224" t="s">
         <v>537</v>
-      </c>
-      <c r="G224" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -7209,10 +7209,10 @@
         <v>537</v>
       </c>
       <c r="F225" t="s">
+        <v>536</v>
+      </c>
+      <c r="G225" t="s">
         <v>537</v>
-      </c>
-      <c r="G225" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -7232,10 +7232,10 @@
         <v>545</v>
       </c>
       <c r="F226" t="s">
+        <v>544</v>
+      </c>
+      <c r="G226" t="s">
         <v>545</v>
-      </c>
-      <c r="G226" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -7255,10 +7255,10 @@
         <v>549</v>
       </c>
       <c r="F227" t="s">
+        <v>548</v>
+      </c>
+      <c r="G227" t="s">
         <v>549</v>
-      </c>
-      <c r="G227" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -7278,10 +7278,10 @@
         <v>553</v>
       </c>
       <c r="F228" t="s">
+        <v>552</v>
+      </c>
+      <c r="G228" t="s">
         <v>553</v>
-      </c>
-      <c r="G228" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -7301,10 +7301,10 @@
         <v>557</v>
       </c>
       <c r="F229" t="s">
+        <v>556</v>
+      </c>
+      <c r="G229" t="s">
         <v>557</v>
-      </c>
-      <c r="G229" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -7324,10 +7324,10 @@
         <v>561</v>
       </c>
       <c r="F230" t="s">
+        <v>560</v>
+      </c>
+      <c r="G230" t="s">
         <v>561</v>
-      </c>
-      <c r="G230" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -7347,10 +7347,10 @@
         <v>561</v>
       </c>
       <c r="F231" t="s">
+        <v>560</v>
+      </c>
+      <c r="G231" t="s">
         <v>561</v>
-      </c>
-      <c r="G231" t="s">
-        <v>560</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/en/SectorGroup.xlsx
+++ b/api/xlsx/en/SectorGroup.xlsx
@@ -25,18 +25,18 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
+    <t>codeforiati:category-name</t>
+  </si>
+  <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
     <t>codeforiati:group-name</t>
   </si>
   <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
-    <t>codeforiati:category-name</t>
-  </si>
-  <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -46,18 +46,18 @@
     <t>active</t>
   </si>
   <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>Education, Level Unspecified</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
     <t>Education</t>
   </si>
   <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>Education, Level Unspecified</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -148,18 +148,18 @@
     <t>Health policy and administrative management</t>
   </si>
   <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>Health, General</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
     <t>Health</t>
   </si>
   <si>
-    <t>121</t>
-  </si>
-  <si>
-    <t>Health, General</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -280,12 +280,12 @@
     <t>Population policy and administrative management</t>
   </si>
   <si>
+    <t>130</t>
+  </si>
+  <si>
     <t>Population Policies/Programmes &amp; Reproductive Health</t>
   </si>
   <si>
-    <t>130</t>
-  </si>
-  <si>
     <t>13020</t>
   </si>
   <si>
@@ -316,12 +316,12 @@
     <t>Water sector policy and administrative management</t>
   </si>
   <si>
+    <t>140</t>
+  </si>
+  <si>
     <t>Water Supply &amp; Sanitation</t>
   </si>
   <si>
-    <t>140</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -388,18 +388,18 @@
     <t>Public sector policy and administrative management</t>
   </si>
   <si>
+    <t>151</t>
+  </si>
+  <si>
+    <t>Government &amp; Civil Society-general</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
     <t>Government &amp; Civil Society</t>
   </si>
   <si>
-    <t>151</t>
-  </si>
-  <si>
-    <t>Government &amp; Civil Society-general</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -538,12 +538,12 @@
     <t>Social Protection</t>
   </si>
   <si>
+    <t>160</t>
+  </si>
+  <si>
     <t>Other Social Infrastructure &amp; Services</t>
   </si>
   <si>
-    <t>160</t>
-  </si>
-  <si>
     <t>16020</t>
   </si>
   <si>
@@ -610,12 +610,12 @@
     <t>Transport policy and administrative management</t>
   </si>
   <si>
+    <t>210</t>
+  </si>
+  <si>
     <t>Transport &amp; Storage</t>
   </si>
   <si>
-    <t>210</t>
-  </si>
-  <si>
     <t>21020</t>
   </si>
   <si>
@@ -658,12 +658,12 @@
     <t>Communications policy and administrative management</t>
   </si>
   <si>
+    <t>220</t>
+  </si>
+  <si>
     <t>Communications</t>
   </si>
   <si>
-    <t>220</t>
-  </si>
-  <si>
     <t>22020</t>
   </si>
   <si>
@@ -688,18 +688,18 @@
     <t>Energy policy and administrative management</t>
   </si>
   <si>
+    <t>231</t>
+  </si>
+  <si>
+    <t>Energy Policy</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
     <t>Energy</t>
   </si>
   <si>
-    <t>231</t>
-  </si>
-  <si>
-    <t>Energy Policy</t>
-  </si>
-  <si>
-    <t>230</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -898,12 +898,12 @@
     <t>Financial policy and administrative management</t>
   </si>
   <si>
+    <t>240</t>
+  </si>
+  <si>
     <t>Banking &amp; Financial Services</t>
   </si>
   <si>
-    <t>240</t>
-  </si>
-  <si>
     <t>24020</t>
   </si>
   <si>
@@ -940,12 +940,12 @@
     <t>Business policy and administration</t>
   </si>
   <si>
+    <t>250</t>
+  </si>
+  <si>
     <t>Business &amp; Other Services</t>
   </si>
   <si>
-    <t>250</t>
-  </si>
-  <si>
     <t>25020</t>
   </si>
   <si>
@@ -970,18 +970,18 @@
     <t>Agricultural policy and administrative management</t>
   </si>
   <si>
+    <t>311</t>
+  </si>
+  <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
     <t>Agriculture, Forestry, Fishing</t>
   </si>
   <si>
-    <t>311</t>
-  </si>
-  <si>
-    <t>Agriculture</t>
-  </si>
-  <si>
-    <t>310</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1168,18 +1168,18 @@
     <t>Industrial policy and administrative management</t>
   </si>
   <si>
+    <t>321</t>
+  </si>
+  <si>
+    <t>Industry</t>
+  </si>
+  <si>
+    <t>320</t>
+  </si>
+  <si>
     <t>Industry, Mining, Construction</t>
   </si>
   <si>
-    <t>321</t>
-  </si>
-  <si>
-    <t>Industry</t>
-  </si>
-  <si>
-    <t>320</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1372,12 +1372,12 @@
     <t>Trade policy and administrative management</t>
   </si>
   <si>
+    <t>331</t>
+  </si>
+  <si>
     <t>Trade Policies &amp; Regulations</t>
   </si>
   <si>
-    <t>331</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1414,24 +1414,24 @@
     <t>Tourism policy and administrative management</t>
   </si>
   <si>
+    <t>332</t>
+  </si>
+  <si>
     <t>Tourism</t>
   </si>
   <si>
-    <t>332</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
     <t>Environmental policy and administrative management</t>
   </si>
   <si>
+    <t>410</t>
+  </si>
+  <si>
     <t>General Environment Protection</t>
   </si>
   <si>
-    <t>410</t>
-  </si>
-  <si>
     <t>41020</t>
   </si>
   <si>
@@ -1468,12 +1468,12 @@
     <t>Multisector aid</t>
   </si>
   <si>
+    <t>430</t>
+  </si>
+  <si>
     <t>Other Multisector</t>
   </si>
   <si>
-    <t>430</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -1534,36 +1534,36 @@
     <t>General budget support-related aid</t>
   </si>
   <si>
+    <t>510</t>
+  </si>
+  <si>
     <t>General Budget Support</t>
   </si>
   <si>
-    <t>510</t>
-  </si>
-  <si>
     <t>52010</t>
   </si>
   <si>
     <t>Food assistance</t>
   </si>
   <si>
+    <t>520</t>
+  </si>
+  <si>
     <t>Development Food Assistance</t>
   </si>
   <si>
-    <t>520</t>
-  </si>
-  <si>
     <t>53030</t>
   </si>
   <si>
     <t>Import support (capital goods)</t>
   </si>
   <si>
+    <t>530</t>
+  </si>
+  <si>
     <t>Other Commodity Assistance</t>
   </si>
   <si>
-    <t>530</t>
-  </si>
-  <si>
     <t>53040</t>
   </si>
   <si>
@@ -1576,12 +1576,12 @@
     <t>Action relating to debt</t>
   </si>
   <si>
+    <t>600</t>
+  </si>
+  <si>
     <t>Action Relating to Debt</t>
   </si>
   <si>
-    <t>600</t>
-  </si>
-  <si>
     <t>60020</t>
   </si>
   <si>
@@ -1624,12 +1624,12 @@
     <t>Material relief assistance and services</t>
   </si>
   <si>
+    <t>720</t>
+  </si>
+  <si>
     <t>Emergency Response</t>
   </si>
   <si>
-    <t>720</t>
-  </si>
-  <si>
     <t>72040</t>
   </si>
   <si>
@@ -1648,58 +1648,58 @@
     <t>Immediate post-emergency reconstruction and rehabilitation</t>
   </si>
   <si>
+    <t>730</t>
+  </si>
+  <si>
     <t>Reconstruction Relief &amp; Rehabilitation</t>
   </si>
   <si>
-    <t>730</t>
-  </si>
-  <si>
     <t>74020</t>
   </si>
   <si>
     <t>Multi-hazard response preparedness</t>
   </si>
   <si>
+    <t>740</t>
+  </si>
+  <si>
     <t>Disaster Prevention &amp; Preparedness</t>
   </si>
   <si>
-    <t>740</t>
-  </si>
-  <si>
     <t>91010</t>
   </si>
   <si>
     <t>Administrative costs (non-sector allocable)</t>
   </si>
   <si>
+    <t>910</t>
+  </si>
+  <si>
     <t>Administrative Costs of Donors</t>
   </si>
   <si>
-    <t>910</t>
-  </si>
-  <si>
     <t>93010</t>
   </si>
   <si>
     <t>Refugees/asylum seekers in donor countries (non-sector allocable)</t>
   </si>
   <si>
+    <t>930</t>
+  </si>
+  <si>
     <t>Refugees in Donor Countries</t>
   </si>
   <si>
-    <t>930</t>
-  </si>
-  <si>
     <t>99810</t>
   </si>
   <si>
     <t>Sectors not specified</t>
   </si>
   <si>
+    <t>998</t>
+  </si>
+  <si>
     <t>Unallocated / Unspecified</t>
-  </si>
-  <si>
-    <t>998</t>
   </si>
   <si>
     <t>99820</t>
@@ -2166,13 +2166,13 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F6" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G6" t="s">
         <v>13</v>
@@ -2189,13 +2189,13 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F7" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G7" t="s">
         <v>13</v>
@@ -2212,13 +2212,13 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F8" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G8" t="s">
         <v>13</v>
@@ -2235,13 +2235,13 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F9" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G9" t="s">
         <v>13</v>
@@ -2258,13 +2258,13 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F10" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="G10" t="s">
         <v>13</v>
@@ -2281,13 +2281,13 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F11" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="G11" t="s">
         <v>13</v>
@@ -2304,13 +2304,13 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F12" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="G12" t="s">
         <v>13</v>
@@ -2327,13 +2327,13 @@
         <v>9</v>
       </c>
       <c r="D13" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F13" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="G13" t="s">
         <v>13</v>
@@ -2442,13 +2442,13 @@
         <v>9</v>
       </c>
       <c r="D18" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E18" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F18" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G18" t="s">
         <v>47</v>
@@ -2465,13 +2465,13 @@
         <v>9</v>
       </c>
       <c r="D19" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F19" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G19" t="s">
         <v>47</v>
@@ -2488,13 +2488,13 @@
         <v>9</v>
       </c>
       <c r="D20" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E20" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F20" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G20" t="s">
         <v>47</v>
@@ -2511,13 +2511,13 @@
         <v>9</v>
       </c>
       <c r="D21" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E21" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F21" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G21" t="s">
         <v>47</v>
@@ -2534,13 +2534,13 @@
         <v>9</v>
       </c>
       <c r="D22" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E22" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F22" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G22" t="s">
         <v>47</v>
@@ -2557,13 +2557,13 @@
         <v>9</v>
       </c>
       <c r="D23" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E23" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F23" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G23" t="s">
         <v>47</v>
@@ -2580,13 +2580,13 @@
         <v>9</v>
       </c>
       <c r="D24" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F24" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G24" t="s">
         <v>47</v>
@@ -2603,13 +2603,13 @@
         <v>9</v>
       </c>
       <c r="D25" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E25" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F25" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G25" t="s">
         <v>47</v>
@@ -2626,13 +2626,13 @@
         <v>9</v>
       </c>
       <c r="D26" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E26" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F26" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="G26" t="s">
         <v>47</v>
@@ -2649,13 +2649,13 @@
         <v>9</v>
       </c>
       <c r="D27" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E27" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F27" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="G27" t="s">
         <v>47</v>
@@ -2672,13 +2672,13 @@
         <v>9</v>
       </c>
       <c r="D28" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E28" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F28" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="G28" t="s">
         <v>47</v>
@@ -2695,13 +2695,13 @@
         <v>9</v>
       </c>
       <c r="D29" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E29" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F29" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="G29" t="s">
         <v>47</v>
@@ -2718,13 +2718,13 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E30" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F30" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="G30" t="s">
         <v>47</v>
@@ -2741,13 +2741,13 @@
         <v>9</v>
       </c>
       <c r="D31" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E31" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F31" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="G31" t="s">
         <v>47</v>
@@ -3500,13 +3500,13 @@
         <v>9</v>
       </c>
       <c r="D64" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E64" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F64" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="G64" t="s">
         <v>127</v>
@@ -3523,13 +3523,13 @@
         <v>9</v>
       </c>
       <c r="D65" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E65" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F65" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="G65" t="s">
         <v>127</v>
@@ -3546,13 +3546,13 @@
         <v>9</v>
       </c>
       <c r="D66" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E66" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F66" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="G66" t="s">
         <v>127</v>
@@ -3569,13 +3569,13 @@
         <v>9</v>
       </c>
       <c r="D67" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E67" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F67" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="G67" t="s">
         <v>127</v>
@@ -3592,13 +3592,13 @@
         <v>9</v>
       </c>
       <c r="D68" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E68" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F68" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="G68" t="s">
         <v>127</v>
@@ -3615,13 +3615,13 @@
         <v>9</v>
       </c>
       <c r="D69" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E69" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F69" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="G69" t="s">
         <v>127</v>
@@ -4236,13 +4236,13 @@
         <v>9</v>
       </c>
       <c r="D96" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E96" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F96" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G96" t="s">
         <v>227</v>
@@ -4259,13 +4259,13 @@
         <v>9</v>
       </c>
       <c r="D97" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E97" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F97" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G97" t="s">
         <v>227</v>
@@ -4282,13 +4282,13 @@
         <v>9</v>
       </c>
       <c r="D98" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E98" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F98" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G98" t="s">
         <v>227</v>
@@ -4305,13 +4305,13 @@
         <v>9</v>
       </c>
       <c r="D99" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E99" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F99" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G99" t="s">
         <v>227</v>
@@ -4328,13 +4328,13 @@
         <v>9</v>
       </c>
       <c r="D100" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E100" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F100" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G100" t="s">
         <v>227</v>
@@ -4351,13 +4351,13 @@
         <v>9</v>
       </c>
       <c r="D101" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E101" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F101" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G101" t="s">
         <v>227</v>
@@ -4374,13 +4374,13 @@
         <v>9</v>
       </c>
       <c r="D102" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E102" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F102" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G102" t="s">
         <v>227</v>
@@ -4397,13 +4397,13 @@
         <v>9</v>
       </c>
       <c r="D103" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E103" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F103" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G103" t="s">
         <v>227</v>
@@ -4420,13 +4420,13 @@
         <v>9</v>
       </c>
       <c r="D104" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E104" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F104" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G104" t="s">
         <v>227</v>
@@ -4443,13 +4443,13 @@
         <v>9</v>
       </c>
       <c r="D105" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E105" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F105" t="s">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="G105" t="s">
         <v>227</v>
@@ -4466,13 +4466,13 @@
         <v>9</v>
       </c>
       <c r="D106" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E106" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F106" t="s">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="G106" t="s">
         <v>227</v>
@@ -4489,13 +4489,13 @@
         <v>9</v>
       </c>
       <c r="D107" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E107" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F107" t="s">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="G107" t="s">
         <v>227</v>
@@ -4512,13 +4512,13 @@
         <v>9</v>
       </c>
       <c r="D108" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E108" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F108" t="s">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="G108" t="s">
         <v>227</v>
@@ -4535,13 +4535,13 @@
         <v>9</v>
       </c>
       <c r="D109" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E109" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F109" t="s">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="G109" t="s">
         <v>227</v>
@@ -4558,13 +4558,13 @@
         <v>9</v>
       </c>
       <c r="D110" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E110" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F110" t="s">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="G110" t="s">
         <v>227</v>
@@ -4581,13 +4581,13 @@
         <v>9</v>
       </c>
       <c r="D111" t="s">
-        <v>224</v>
+        <v>270</v>
       </c>
       <c r="E111" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F111" t="s">
-        <v>271</v>
+        <v>226</v>
       </c>
       <c r="G111" t="s">
         <v>227</v>
@@ -4604,13 +4604,13 @@
         <v>9</v>
       </c>
       <c r="D112" t="s">
-        <v>224</v>
+        <v>274</v>
       </c>
       <c r="E112" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F112" t="s">
-        <v>275</v>
+        <v>226</v>
       </c>
       <c r="G112" t="s">
         <v>227</v>
@@ -4627,13 +4627,13 @@
         <v>9</v>
       </c>
       <c r="D113" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E113" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F113" t="s">
-        <v>279</v>
+        <v>226</v>
       </c>
       <c r="G113" t="s">
         <v>227</v>
@@ -4650,13 +4650,13 @@
         <v>9</v>
       </c>
       <c r="D114" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E114" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F114" t="s">
-        <v>279</v>
+        <v>226</v>
       </c>
       <c r="G114" t="s">
         <v>227</v>
@@ -4673,13 +4673,13 @@
         <v>9</v>
       </c>
       <c r="D115" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E115" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F115" t="s">
-        <v>279</v>
+        <v>226</v>
       </c>
       <c r="G115" t="s">
         <v>227</v>
@@ -4696,13 +4696,13 @@
         <v>9</v>
       </c>
       <c r="D116" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E116" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F116" t="s">
-        <v>279</v>
+        <v>226</v>
       </c>
       <c r="G116" t="s">
         <v>227</v>
@@ -4719,13 +4719,13 @@
         <v>9</v>
       </c>
       <c r="D117" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E117" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F117" t="s">
-        <v>279</v>
+        <v>226</v>
       </c>
       <c r="G117" t="s">
         <v>227</v>
@@ -4742,13 +4742,13 @@
         <v>9</v>
       </c>
       <c r="D118" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E118" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F118" t="s">
-        <v>279</v>
+        <v>226</v>
       </c>
       <c r="G118" t="s">
         <v>227</v>
@@ -4765,13 +4765,13 @@
         <v>9</v>
       </c>
       <c r="D119" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E119" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F119" t="s">
-        <v>279</v>
+        <v>226</v>
       </c>
       <c r="G119" t="s">
         <v>227</v>
@@ -5432,13 +5432,13 @@
         <v>9</v>
       </c>
       <c r="D148" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E148" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F148" t="s">
-        <v>359</v>
+        <v>320</v>
       </c>
       <c r="G148" t="s">
         <v>321</v>
@@ -5455,13 +5455,13 @@
         <v>9</v>
       </c>
       <c r="D149" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E149" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F149" t="s">
-        <v>359</v>
+        <v>320</v>
       </c>
       <c r="G149" t="s">
         <v>321</v>
@@ -5478,13 +5478,13 @@
         <v>9</v>
       </c>
       <c r="D150" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E150" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F150" t="s">
-        <v>359</v>
+        <v>320</v>
       </c>
       <c r="G150" t="s">
         <v>321</v>
@@ -5501,13 +5501,13 @@
         <v>9</v>
       </c>
       <c r="D151" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E151" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F151" t="s">
-        <v>359</v>
+        <v>320</v>
       </c>
       <c r="G151" t="s">
         <v>321</v>
@@ -5524,13 +5524,13 @@
         <v>9</v>
       </c>
       <c r="D152" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E152" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F152" t="s">
-        <v>359</v>
+        <v>320</v>
       </c>
       <c r="G152" t="s">
         <v>321</v>
@@ -5547,13 +5547,13 @@
         <v>9</v>
       </c>
       <c r="D153" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E153" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F153" t="s">
-        <v>359</v>
+        <v>320</v>
       </c>
       <c r="G153" t="s">
         <v>321</v>
@@ -5570,13 +5570,13 @@
         <v>9</v>
       </c>
       <c r="D154" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="E154" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F154" t="s">
-        <v>373</v>
+        <v>320</v>
       </c>
       <c r="G154" t="s">
         <v>321</v>
@@ -5593,13 +5593,13 @@
         <v>9</v>
       </c>
       <c r="D155" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="E155" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F155" t="s">
-        <v>373</v>
+        <v>320</v>
       </c>
       <c r="G155" t="s">
         <v>321</v>
@@ -5616,13 +5616,13 @@
         <v>9</v>
       </c>
       <c r="D156" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="E156" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F156" t="s">
-        <v>373</v>
+        <v>320</v>
       </c>
       <c r="G156" t="s">
         <v>321</v>
@@ -5639,13 +5639,13 @@
         <v>9</v>
       </c>
       <c r="D157" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="E157" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F157" t="s">
-        <v>373</v>
+        <v>320</v>
       </c>
       <c r="G157" t="s">
         <v>321</v>
@@ -5662,13 +5662,13 @@
         <v>9</v>
       </c>
       <c r="D158" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="E158" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F158" t="s">
-        <v>373</v>
+        <v>320</v>
       </c>
       <c r="G158" t="s">
         <v>321</v>
@@ -6122,13 +6122,13 @@
         <v>9</v>
       </c>
       <c r="D178" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E178" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F178" t="s">
-        <v>427</v>
+        <v>386</v>
       </c>
       <c r="G178" t="s">
         <v>387</v>
@@ -6145,13 +6145,13 @@
         <v>9</v>
       </c>
       <c r="D179" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E179" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F179" t="s">
-        <v>427</v>
+        <v>386</v>
       </c>
       <c r="G179" t="s">
         <v>387</v>
@@ -6168,13 +6168,13 @@
         <v>9</v>
       </c>
       <c r="D180" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E180" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F180" t="s">
-        <v>427</v>
+        <v>386</v>
       </c>
       <c r="G180" t="s">
         <v>387</v>
@@ -6191,13 +6191,13 @@
         <v>9</v>
       </c>
       <c r="D181" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E181" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F181" t="s">
-        <v>427</v>
+        <v>386</v>
       </c>
       <c r="G181" t="s">
         <v>387</v>
@@ -6214,13 +6214,13 @@
         <v>9</v>
       </c>
       <c r="D182" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E182" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F182" t="s">
-        <v>427</v>
+        <v>386</v>
       </c>
       <c r="G182" t="s">
         <v>387</v>
@@ -6237,13 +6237,13 @@
         <v>9</v>
       </c>
       <c r="D183" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E183" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F183" t="s">
-        <v>427</v>
+        <v>386</v>
       </c>
       <c r="G183" t="s">
         <v>387</v>
@@ -6260,13 +6260,13 @@
         <v>9</v>
       </c>
       <c r="D184" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E184" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F184" t="s">
-        <v>427</v>
+        <v>386</v>
       </c>
       <c r="G184" t="s">
         <v>387</v>
@@ -6283,13 +6283,13 @@
         <v>9</v>
       </c>
       <c r="D185" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E185" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F185" t="s">
-        <v>427</v>
+        <v>386</v>
       </c>
       <c r="G185" t="s">
         <v>387</v>
@@ -6306,13 +6306,13 @@
         <v>9</v>
       </c>
       <c r="D186" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E186" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F186" t="s">
-        <v>427</v>
+        <v>386</v>
       </c>
       <c r="G186" t="s">
         <v>387</v>
@@ -6329,13 +6329,13 @@
         <v>9</v>
       </c>
       <c r="D187" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E187" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F187" t="s">
-        <v>427</v>
+        <v>386</v>
       </c>
       <c r="G187" t="s">
         <v>387</v>
@@ -6352,13 +6352,13 @@
         <v>9</v>
       </c>
       <c r="D188" t="s">
-        <v>384</v>
+        <v>448</v>
       </c>
       <c r="E188" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F188" t="s">
-        <v>449</v>
+        <v>386</v>
       </c>
       <c r="G188" t="s">
         <v>387</v>

--- a/api/xlsx/en/SectorGroup.xlsx
+++ b/api/xlsx/en/SectorGroup.xlsx
@@ -28,15 +28,15 @@
     <t>codeforiati:category-code</t>
   </si>
   <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
     <t>codeforiati:category-name</t>
   </si>
   <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -49,15 +49,15 @@
     <t>111</t>
   </si>
   <si>
+    <t>Education</t>
+  </si>
+  <si>
     <t>Education, Level Unspecified</t>
   </si>
   <si>
     <t>110</t>
   </si>
   <si>
-    <t>Education</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -151,15 +151,15 @@
     <t>121</t>
   </si>
   <si>
+    <t>Health</t>
+  </si>
+  <si>
     <t>Health, General</t>
   </si>
   <si>
     <t>120</t>
   </si>
   <si>
-    <t>Health</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -391,15 +391,15 @@
     <t>151</t>
   </si>
   <si>
+    <t>Government &amp; Civil Society</t>
+  </si>
+  <si>
     <t>Government &amp; Civil Society-general</t>
   </si>
   <si>
     <t>150</t>
   </si>
   <si>
-    <t>Government &amp; Civil Society</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -691,15 +691,15 @@
     <t>231</t>
   </si>
   <si>
+    <t>Energy</t>
+  </si>
+  <si>
     <t>Energy Policy</t>
   </si>
   <si>
     <t>230</t>
   </si>
   <si>
-    <t>Energy</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -973,15 +973,15 @@
     <t>311</t>
   </si>
   <si>
+    <t>Agriculture, Forestry, Fishing</t>
+  </si>
+  <si>
     <t>Agriculture</t>
   </si>
   <si>
     <t>310</t>
   </si>
   <si>
-    <t>Agriculture, Forestry, Fishing</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1171,13 +1171,13 @@
     <t>321</t>
   </si>
   <si>
+    <t>Industry, Mining, Construction</t>
+  </si>
+  <si>
     <t>Industry</t>
   </si>
   <si>
     <t>320</t>
-  </si>
-  <si>
-    <t>Industry, Mining, Construction</t>
   </si>
   <si>
     <t>32120</t>
@@ -2169,10 +2169,10 @@
         <v>22</v>
       </c>
       <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" t="s">
         <v>23</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
       </c>
       <c r="G6" t="s">
         <v>13</v>
@@ -2192,10 +2192,10 @@
         <v>22</v>
       </c>
       <c r="E7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" t="s">
         <v>23</v>
-      </c>
-      <c r="F7" t="s">
-        <v>12</v>
       </c>
       <c r="G7" t="s">
         <v>13</v>
@@ -2215,10 +2215,10 @@
         <v>22</v>
       </c>
       <c r="E8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" t="s">
         <v>23</v>
-      </c>
-      <c r="F8" t="s">
-        <v>12</v>
       </c>
       <c r="G8" t="s">
         <v>13</v>
@@ -2238,10 +2238,10 @@
         <v>22</v>
       </c>
       <c r="E9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" t="s">
         <v>23</v>
-      </c>
-      <c r="F9" t="s">
-        <v>12</v>
       </c>
       <c r="G9" t="s">
         <v>13</v>
@@ -2261,10 +2261,10 @@
         <v>32</v>
       </c>
       <c r="E10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" t="s">
         <v>33</v>
-      </c>
-      <c r="F10" t="s">
-        <v>12</v>
       </c>
       <c r="G10" t="s">
         <v>13</v>
@@ -2284,10 +2284,10 @@
         <v>32</v>
       </c>
       <c r="E11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" t="s">
         <v>33</v>
-      </c>
-      <c r="F11" t="s">
-        <v>12</v>
       </c>
       <c r="G11" t="s">
         <v>13</v>
@@ -2307,10 +2307,10 @@
         <v>38</v>
       </c>
       <c r="E12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" t="s">
         <v>39</v>
-      </c>
-      <c r="F12" t="s">
-        <v>12</v>
       </c>
       <c r="G12" t="s">
         <v>13</v>
@@ -2330,10 +2330,10 @@
         <v>38</v>
       </c>
       <c r="E13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" t="s">
         <v>39</v>
-      </c>
-      <c r="F13" t="s">
-        <v>12</v>
       </c>
       <c r="G13" t="s">
         <v>13</v>
@@ -2445,10 +2445,10 @@
         <v>56</v>
       </c>
       <c r="E18" t="s">
+        <v>45</v>
+      </c>
+      <c r="F18" t="s">
         <v>57</v>
-      </c>
-      <c r="F18" t="s">
-        <v>46</v>
       </c>
       <c r="G18" t="s">
         <v>47</v>
@@ -2468,10 +2468,10 @@
         <v>56</v>
       </c>
       <c r="E19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F19" t="s">
         <v>57</v>
-      </c>
-      <c r="F19" t="s">
-        <v>46</v>
       </c>
       <c r="G19" t="s">
         <v>47</v>
@@ -2491,10 +2491,10 @@
         <v>56</v>
       </c>
       <c r="E20" t="s">
+        <v>45</v>
+      </c>
+      <c r="F20" t="s">
         <v>57</v>
-      </c>
-      <c r="F20" t="s">
-        <v>46</v>
       </c>
       <c r="G20" t="s">
         <v>47</v>
@@ -2514,10 +2514,10 @@
         <v>56</v>
       </c>
       <c r="E21" t="s">
+        <v>45</v>
+      </c>
+      <c r="F21" t="s">
         <v>57</v>
-      </c>
-      <c r="F21" t="s">
-        <v>46</v>
       </c>
       <c r="G21" t="s">
         <v>47</v>
@@ -2537,10 +2537,10 @@
         <v>56</v>
       </c>
       <c r="E22" t="s">
+        <v>45</v>
+      </c>
+      <c r="F22" t="s">
         <v>57</v>
-      </c>
-      <c r="F22" t="s">
-        <v>46</v>
       </c>
       <c r="G22" t="s">
         <v>47</v>
@@ -2560,10 +2560,10 @@
         <v>56</v>
       </c>
       <c r="E23" t="s">
+        <v>45</v>
+      </c>
+      <c r="F23" t="s">
         <v>57</v>
-      </c>
-      <c r="F23" t="s">
-        <v>46</v>
       </c>
       <c r="G23" t="s">
         <v>47</v>
@@ -2583,10 +2583,10 @@
         <v>56</v>
       </c>
       <c r="E24" t="s">
+        <v>45</v>
+      </c>
+      <c r="F24" t="s">
         <v>57</v>
-      </c>
-      <c r="F24" t="s">
-        <v>46</v>
       </c>
       <c r="G24" t="s">
         <v>47</v>
@@ -2606,10 +2606,10 @@
         <v>56</v>
       </c>
       <c r="E25" t="s">
+        <v>45</v>
+      </c>
+      <c r="F25" t="s">
         <v>57</v>
-      </c>
-      <c r="F25" t="s">
-        <v>46</v>
       </c>
       <c r="G25" t="s">
         <v>47</v>
@@ -2629,10 +2629,10 @@
         <v>74</v>
       </c>
       <c r="E26" t="s">
+        <v>45</v>
+      </c>
+      <c r="F26" t="s">
         <v>75</v>
-      </c>
-      <c r="F26" t="s">
-        <v>46</v>
       </c>
       <c r="G26" t="s">
         <v>47</v>
@@ -2652,10 +2652,10 @@
         <v>74</v>
       </c>
       <c r="E27" t="s">
+        <v>45</v>
+      </c>
+      <c r="F27" t="s">
         <v>75</v>
-      </c>
-      <c r="F27" t="s">
-        <v>46</v>
       </c>
       <c r="G27" t="s">
         <v>47</v>
@@ -2675,10 +2675,10 @@
         <v>74</v>
       </c>
       <c r="E28" t="s">
+        <v>45</v>
+      </c>
+      <c r="F28" t="s">
         <v>75</v>
-      </c>
-      <c r="F28" t="s">
-        <v>46</v>
       </c>
       <c r="G28" t="s">
         <v>47</v>
@@ -2698,10 +2698,10 @@
         <v>74</v>
       </c>
       <c r="E29" t="s">
+        <v>45</v>
+      </c>
+      <c r="F29" t="s">
         <v>75</v>
-      </c>
-      <c r="F29" t="s">
-        <v>46</v>
       </c>
       <c r="G29" t="s">
         <v>47</v>
@@ -2721,10 +2721,10 @@
         <v>74</v>
       </c>
       <c r="E30" t="s">
+        <v>45</v>
+      </c>
+      <c r="F30" t="s">
         <v>75</v>
-      </c>
-      <c r="F30" t="s">
-        <v>46</v>
       </c>
       <c r="G30" t="s">
         <v>47</v>
@@ -2744,10 +2744,10 @@
         <v>74</v>
       </c>
       <c r="E31" t="s">
+        <v>45</v>
+      </c>
+      <c r="F31" t="s">
         <v>75</v>
-      </c>
-      <c r="F31" t="s">
-        <v>46</v>
       </c>
       <c r="G31" t="s">
         <v>47</v>
@@ -2770,10 +2770,10 @@
         <v>89</v>
       </c>
       <c r="F32" t="s">
+        <v>89</v>
+      </c>
+      <c r="G32" t="s">
         <v>88</v>
-      </c>
-      <c r="G32" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2793,10 +2793,10 @@
         <v>89</v>
       </c>
       <c r="F33" t="s">
+        <v>89</v>
+      </c>
+      <c r="G33" t="s">
         <v>88</v>
-      </c>
-      <c r="G33" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2816,10 +2816,10 @@
         <v>89</v>
       </c>
       <c r="F34" t="s">
+        <v>89</v>
+      </c>
+      <c r="G34" t="s">
         <v>88</v>
-      </c>
-      <c r="G34" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2839,10 +2839,10 @@
         <v>89</v>
       </c>
       <c r="F35" t="s">
+        <v>89</v>
+      </c>
+      <c r="G35" t="s">
         <v>88</v>
-      </c>
-      <c r="G35" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2862,10 +2862,10 @@
         <v>89</v>
       </c>
       <c r="F36" t="s">
+        <v>89</v>
+      </c>
+      <c r="G36" t="s">
         <v>88</v>
-      </c>
-      <c r="G36" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2885,10 +2885,10 @@
         <v>101</v>
       </c>
       <c r="F37" t="s">
+        <v>101</v>
+      </c>
+      <c r="G37" t="s">
         <v>100</v>
-      </c>
-      <c r="G37" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2908,10 +2908,10 @@
         <v>101</v>
       </c>
       <c r="F38" t="s">
+        <v>101</v>
+      </c>
+      <c r="G38" t="s">
         <v>100</v>
-      </c>
-      <c r="G38" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2931,10 +2931,10 @@
         <v>101</v>
       </c>
       <c r="F39" t="s">
+        <v>101</v>
+      </c>
+      <c r="G39" t="s">
         <v>100</v>
-      </c>
-      <c r="G39" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2954,10 +2954,10 @@
         <v>101</v>
       </c>
       <c r="F40" t="s">
+        <v>101</v>
+      </c>
+      <c r="G40" t="s">
         <v>100</v>
-      </c>
-      <c r="G40" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2977,10 +2977,10 @@
         <v>101</v>
       </c>
       <c r="F41" t="s">
+        <v>101</v>
+      </c>
+      <c r="G41" t="s">
         <v>100</v>
-      </c>
-      <c r="G41" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -3000,10 +3000,10 @@
         <v>101</v>
       </c>
       <c r="F42" t="s">
+        <v>101</v>
+      </c>
+      <c r="G42" t="s">
         <v>100</v>
-      </c>
-      <c r="G42" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3023,10 +3023,10 @@
         <v>101</v>
       </c>
       <c r="F43" t="s">
+        <v>101</v>
+      </c>
+      <c r="G43" t="s">
         <v>100</v>
-      </c>
-      <c r="G43" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3046,10 +3046,10 @@
         <v>101</v>
       </c>
       <c r="F44" t="s">
+        <v>101</v>
+      </c>
+      <c r="G44" t="s">
         <v>100</v>
-      </c>
-      <c r="G44" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3069,10 +3069,10 @@
         <v>101</v>
       </c>
       <c r="F45" t="s">
+        <v>101</v>
+      </c>
+      <c r="G45" t="s">
         <v>100</v>
-      </c>
-      <c r="G45" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3092,10 +3092,10 @@
         <v>101</v>
       </c>
       <c r="F46" t="s">
+        <v>101</v>
+      </c>
+      <c r="G46" t="s">
         <v>100</v>
-      </c>
-      <c r="G46" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3115,10 +3115,10 @@
         <v>101</v>
       </c>
       <c r="F47" t="s">
+        <v>101</v>
+      </c>
+      <c r="G47" t="s">
         <v>100</v>
-      </c>
-      <c r="G47" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3503,10 +3503,10 @@
         <v>160</v>
       </c>
       <c r="E64" t="s">
+        <v>125</v>
+      </c>
+      <c r="F64" t="s">
         <v>161</v>
-      </c>
-      <c r="F64" t="s">
-        <v>126</v>
       </c>
       <c r="G64" t="s">
         <v>127</v>
@@ -3526,10 +3526,10 @@
         <v>160</v>
       </c>
       <c r="E65" t="s">
+        <v>125</v>
+      </c>
+      <c r="F65" t="s">
         <v>161</v>
-      </c>
-      <c r="F65" t="s">
-        <v>126</v>
       </c>
       <c r="G65" t="s">
         <v>127</v>
@@ -3549,10 +3549,10 @@
         <v>160</v>
       </c>
       <c r="E66" t="s">
+        <v>125</v>
+      </c>
+      <c r="F66" t="s">
         <v>161</v>
-      </c>
-      <c r="F66" t="s">
-        <v>126</v>
       </c>
       <c r="G66" t="s">
         <v>127</v>
@@ -3572,10 +3572,10 @@
         <v>160</v>
       </c>
       <c r="E67" t="s">
+        <v>125</v>
+      </c>
+      <c r="F67" t="s">
         <v>161</v>
-      </c>
-      <c r="F67" t="s">
-        <v>126</v>
       </c>
       <c r="G67" t="s">
         <v>127</v>
@@ -3595,10 +3595,10 @@
         <v>160</v>
       </c>
       <c r="E68" t="s">
+        <v>125</v>
+      </c>
+      <c r="F68" t="s">
         <v>161</v>
-      </c>
-      <c r="F68" t="s">
-        <v>126</v>
       </c>
       <c r="G68" t="s">
         <v>127</v>
@@ -3618,10 +3618,10 @@
         <v>160</v>
       </c>
       <c r="E69" t="s">
+        <v>125</v>
+      </c>
+      <c r="F69" t="s">
         <v>161</v>
-      </c>
-      <c r="F69" t="s">
-        <v>126</v>
       </c>
       <c r="G69" t="s">
         <v>127</v>
@@ -3644,10 +3644,10 @@
         <v>175</v>
       </c>
       <c r="F70" t="s">
+        <v>175</v>
+      </c>
+      <c r="G70" t="s">
         <v>174</v>
-      </c>
-      <c r="G70" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3667,10 +3667,10 @@
         <v>175</v>
       </c>
       <c r="F71" t="s">
+        <v>175</v>
+      </c>
+      <c r="G71" t="s">
         <v>174</v>
-      </c>
-      <c r="G71" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3690,10 +3690,10 @@
         <v>175</v>
       </c>
       <c r="F72" t="s">
+        <v>175</v>
+      </c>
+      <c r="G72" t="s">
         <v>174</v>
-      </c>
-      <c r="G72" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3713,10 +3713,10 @@
         <v>175</v>
       </c>
       <c r="F73" t="s">
+        <v>175</v>
+      </c>
+      <c r="G73" t="s">
         <v>174</v>
-      </c>
-      <c r="G73" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3736,10 +3736,10 @@
         <v>175</v>
       </c>
       <c r="F74" t="s">
+        <v>175</v>
+      </c>
+      <c r="G74" t="s">
         <v>174</v>
-      </c>
-      <c r="G74" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3759,10 +3759,10 @@
         <v>175</v>
       </c>
       <c r="F75" t="s">
+        <v>175</v>
+      </c>
+      <c r="G75" t="s">
         <v>174</v>
-      </c>
-      <c r="G75" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3782,10 +3782,10 @@
         <v>175</v>
       </c>
       <c r="F76" t="s">
+        <v>175</v>
+      </c>
+      <c r="G76" t="s">
         <v>174</v>
-      </c>
-      <c r="G76" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3805,10 +3805,10 @@
         <v>175</v>
       </c>
       <c r="F77" t="s">
+        <v>175</v>
+      </c>
+      <c r="G77" t="s">
         <v>174</v>
-      </c>
-      <c r="G77" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3828,10 +3828,10 @@
         <v>175</v>
       </c>
       <c r="F78" t="s">
+        <v>175</v>
+      </c>
+      <c r="G78" t="s">
         <v>174</v>
-      </c>
-      <c r="G78" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3851,10 +3851,10 @@
         <v>175</v>
       </c>
       <c r="F79" t="s">
+        <v>175</v>
+      </c>
+      <c r="G79" t="s">
         <v>174</v>
-      </c>
-      <c r="G79" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3874,10 +3874,10 @@
         <v>175</v>
       </c>
       <c r="F80" t="s">
+        <v>175</v>
+      </c>
+      <c r="G80" t="s">
         <v>174</v>
-      </c>
-      <c r="G80" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3897,10 +3897,10 @@
         <v>199</v>
       </c>
       <c r="F81" t="s">
+        <v>199</v>
+      </c>
+      <c r="G81" t="s">
         <v>198</v>
-      </c>
-      <c r="G81" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3920,10 +3920,10 @@
         <v>199</v>
       </c>
       <c r="F82" t="s">
+        <v>199</v>
+      </c>
+      <c r="G82" t="s">
         <v>198</v>
-      </c>
-      <c r="G82" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3943,10 +3943,10 @@
         <v>199</v>
       </c>
       <c r="F83" t="s">
+        <v>199</v>
+      </c>
+      <c r="G83" t="s">
         <v>198</v>
-      </c>
-      <c r="G83" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3966,10 +3966,10 @@
         <v>199</v>
       </c>
       <c r="F84" t="s">
+        <v>199</v>
+      </c>
+      <c r="G84" t="s">
         <v>198</v>
-      </c>
-      <c r="G84" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3989,10 +3989,10 @@
         <v>199</v>
       </c>
       <c r="F85" t="s">
+        <v>199</v>
+      </c>
+      <c r="G85" t="s">
         <v>198</v>
-      </c>
-      <c r="G85" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4012,10 +4012,10 @@
         <v>199</v>
       </c>
       <c r="F86" t="s">
+        <v>199</v>
+      </c>
+      <c r="G86" t="s">
         <v>198</v>
-      </c>
-      <c r="G86" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4035,10 +4035,10 @@
         <v>199</v>
       </c>
       <c r="F87" t="s">
+        <v>199</v>
+      </c>
+      <c r="G87" t="s">
         <v>198</v>
-      </c>
-      <c r="G87" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4058,10 +4058,10 @@
         <v>215</v>
       </c>
       <c r="F88" t="s">
+        <v>215</v>
+      </c>
+      <c r="G88" t="s">
         <v>214</v>
-      </c>
-      <c r="G88" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4081,10 +4081,10 @@
         <v>215</v>
       </c>
       <c r="F89" t="s">
+        <v>215</v>
+      </c>
+      <c r="G89" t="s">
         <v>214</v>
-      </c>
-      <c r="G89" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4104,10 +4104,10 @@
         <v>215</v>
       </c>
       <c r="F90" t="s">
+        <v>215</v>
+      </c>
+      <c r="G90" t="s">
         <v>214</v>
-      </c>
-      <c r="G90" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4127,10 +4127,10 @@
         <v>215</v>
       </c>
       <c r="F91" t="s">
+        <v>215</v>
+      </c>
+      <c r="G91" t="s">
         <v>214</v>
-      </c>
-      <c r="G91" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4239,10 +4239,10 @@
         <v>236</v>
       </c>
       <c r="E96" t="s">
+        <v>225</v>
+      </c>
+      <c r="F96" t="s">
         <v>237</v>
-      </c>
-      <c r="F96" t="s">
-        <v>226</v>
       </c>
       <c r="G96" t="s">
         <v>227</v>
@@ -4262,10 +4262,10 @@
         <v>236</v>
       </c>
       <c r="E97" t="s">
+        <v>225</v>
+      </c>
+      <c r="F97" t="s">
         <v>237</v>
-      </c>
-      <c r="F97" t="s">
-        <v>226</v>
       </c>
       <c r="G97" t="s">
         <v>227</v>
@@ -4285,10 +4285,10 @@
         <v>236</v>
       </c>
       <c r="E98" t="s">
+        <v>225</v>
+      </c>
+      <c r="F98" t="s">
         <v>237</v>
-      </c>
-      <c r="F98" t="s">
-        <v>226</v>
       </c>
       <c r="G98" t="s">
         <v>227</v>
@@ -4308,10 +4308,10 @@
         <v>236</v>
       </c>
       <c r="E99" t="s">
+        <v>225</v>
+      </c>
+      <c r="F99" t="s">
         <v>237</v>
-      </c>
-      <c r="F99" t="s">
-        <v>226</v>
       </c>
       <c r="G99" t="s">
         <v>227</v>
@@ -4331,10 +4331,10 @@
         <v>236</v>
       </c>
       <c r="E100" t="s">
+        <v>225</v>
+      </c>
+      <c r="F100" t="s">
         <v>237</v>
-      </c>
-      <c r="F100" t="s">
-        <v>226</v>
       </c>
       <c r="G100" t="s">
         <v>227</v>
@@ -4354,10 +4354,10 @@
         <v>236</v>
       </c>
       <c r="E101" t="s">
+        <v>225</v>
+      </c>
+      <c r="F101" t="s">
         <v>237</v>
-      </c>
-      <c r="F101" t="s">
-        <v>226</v>
       </c>
       <c r="G101" t="s">
         <v>227</v>
@@ -4377,10 +4377,10 @@
         <v>236</v>
       </c>
       <c r="E102" t="s">
+        <v>225</v>
+      </c>
+      <c r="F102" t="s">
         <v>237</v>
-      </c>
-      <c r="F102" t="s">
-        <v>226</v>
       </c>
       <c r="G102" t="s">
         <v>227</v>
@@ -4400,10 +4400,10 @@
         <v>236</v>
       </c>
       <c r="E103" t="s">
+        <v>225</v>
+      </c>
+      <c r="F103" t="s">
         <v>237</v>
-      </c>
-      <c r="F103" t="s">
-        <v>226</v>
       </c>
       <c r="G103" t="s">
         <v>227</v>
@@ -4423,10 +4423,10 @@
         <v>236</v>
       </c>
       <c r="E104" t="s">
+        <v>225</v>
+      </c>
+      <c r="F104" t="s">
         <v>237</v>
-      </c>
-      <c r="F104" t="s">
-        <v>226</v>
       </c>
       <c r="G104" t="s">
         <v>227</v>
@@ -4446,10 +4446,10 @@
         <v>256</v>
       </c>
       <c r="E105" t="s">
+        <v>225</v>
+      </c>
+      <c r="F105" t="s">
         <v>257</v>
-      </c>
-      <c r="F105" t="s">
-        <v>226</v>
       </c>
       <c r="G105" t="s">
         <v>227</v>
@@ -4469,10 +4469,10 @@
         <v>256</v>
       </c>
       <c r="E106" t="s">
+        <v>225</v>
+      </c>
+      <c r="F106" t="s">
         <v>257</v>
-      </c>
-      <c r="F106" t="s">
-        <v>226</v>
       </c>
       <c r="G106" t="s">
         <v>227</v>
@@ -4492,10 +4492,10 @@
         <v>256</v>
       </c>
       <c r="E107" t="s">
+        <v>225</v>
+      </c>
+      <c r="F107" t="s">
         <v>257</v>
-      </c>
-      <c r="F107" t="s">
-        <v>226</v>
       </c>
       <c r="G107" t="s">
         <v>227</v>
@@ -4515,10 +4515,10 @@
         <v>256</v>
       </c>
       <c r="E108" t="s">
+        <v>225</v>
+      </c>
+      <c r="F108" t="s">
         <v>257</v>
-      </c>
-      <c r="F108" t="s">
-        <v>226</v>
       </c>
       <c r="G108" t="s">
         <v>227</v>
@@ -4538,10 +4538,10 @@
         <v>256</v>
       </c>
       <c r="E109" t="s">
+        <v>225</v>
+      </c>
+      <c r="F109" t="s">
         <v>257</v>
-      </c>
-      <c r="F109" t="s">
-        <v>226</v>
       </c>
       <c r="G109" t="s">
         <v>227</v>
@@ -4561,10 +4561,10 @@
         <v>256</v>
       </c>
       <c r="E110" t="s">
+        <v>225</v>
+      </c>
+      <c r="F110" t="s">
         <v>257</v>
-      </c>
-      <c r="F110" t="s">
-        <v>226</v>
       </c>
       <c r="G110" t="s">
         <v>227</v>
@@ -4584,10 +4584,10 @@
         <v>270</v>
       </c>
       <c r="E111" t="s">
+        <v>225</v>
+      </c>
+      <c r="F111" t="s">
         <v>271</v>
-      </c>
-      <c r="F111" t="s">
-        <v>226</v>
       </c>
       <c r="G111" t="s">
         <v>227</v>
@@ -4607,10 +4607,10 @@
         <v>274</v>
       </c>
       <c r="E112" t="s">
+        <v>225</v>
+      </c>
+      <c r="F112" t="s">
         <v>275</v>
-      </c>
-      <c r="F112" t="s">
-        <v>226</v>
       </c>
       <c r="G112" t="s">
         <v>227</v>
@@ -4630,10 +4630,10 @@
         <v>278</v>
       </c>
       <c r="E113" t="s">
+        <v>225</v>
+      </c>
+      <c r="F113" t="s">
         <v>279</v>
-      </c>
-      <c r="F113" t="s">
-        <v>226</v>
       </c>
       <c r="G113" t="s">
         <v>227</v>
@@ -4653,10 +4653,10 @@
         <v>278</v>
       </c>
       <c r="E114" t="s">
+        <v>225</v>
+      </c>
+      <c r="F114" t="s">
         <v>279</v>
-      </c>
-      <c r="F114" t="s">
-        <v>226</v>
       </c>
       <c r="G114" t="s">
         <v>227</v>
@@ -4676,10 +4676,10 @@
         <v>278</v>
       </c>
       <c r="E115" t="s">
+        <v>225</v>
+      </c>
+      <c r="F115" t="s">
         <v>279</v>
-      </c>
-      <c r="F115" t="s">
-        <v>226</v>
       </c>
       <c r="G115" t="s">
         <v>227</v>
@@ -4699,10 +4699,10 @@
         <v>278</v>
       </c>
       <c r="E116" t="s">
+        <v>225</v>
+      </c>
+      <c r="F116" t="s">
         <v>279</v>
-      </c>
-      <c r="F116" t="s">
-        <v>226</v>
       </c>
       <c r="G116" t="s">
         <v>227</v>
@@ -4722,10 +4722,10 @@
         <v>278</v>
       </c>
       <c r="E117" t="s">
+        <v>225</v>
+      </c>
+      <c r="F117" t="s">
         <v>279</v>
-      </c>
-      <c r="F117" t="s">
-        <v>226</v>
       </c>
       <c r="G117" t="s">
         <v>227</v>
@@ -4745,10 +4745,10 @@
         <v>278</v>
       </c>
       <c r="E118" t="s">
+        <v>225</v>
+      </c>
+      <c r="F118" t="s">
         <v>279</v>
-      </c>
-      <c r="F118" t="s">
-        <v>226</v>
       </c>
       <c r="G118" t="s">
         <v>227</v>
@@ -4768,10 +4768,10 @@
         <v>278</v>
       </c>
       <c r="E119" t="s">
+        <v>225</v>
+      </c>
+      <c r="F119" t="s">
         <v>279</v>
-      </c>
-      <c r="F119" t="s">
-        <v>226</v>
       </c>
       <c r="G119" t="s">
         <v>227</v>
@@ -4794,10 +4794,10 @@
         <v>295</v>
       </c>
       <c r="F120" t="s">
+        <v>295</v>
+      </c>
+      <c r="G120" t="s">
         <v>294</v>
-      </c>
-      <c r="G120" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4817,10 +4817,10 @@
         <v>295</v>
       </c>
       <c r="F121" t="s">
+        <v>295</v>
+      </c>
+      <c r="G121" t="s">
         <v>294</v>
-      </c>
-      <c r="G121" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4840,10 +4840,10 @@
         <v>295</v>
       </c>
       <c r="F122" t="s">
+        <v>295</v>
+      </c>
+      <c r="G122" t="s">
         <v>294</v>
-      </c>
-      <c r="G122" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4863,10 +4863,10 @@
         <v>295</v>
       </c>
       <c r="F123" t="s">
+        <v>295</v>
+      </c>
+      <c r="G123" t="s">
         <v>294</v>
-      </c>
-      <c r="G123" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4886,10 +4886,10 @@
         <v>295</v>
       </c>
       <c r="F124" t="s">
+        <v>295</v>
+      </c>
+      <c r="G124" t="s">
         <v>294</v>
-      </c>
-      <c r="G124" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4909,10 +4909,10 @@
         <v>295</v>
       </c>
       <c r="F125" t="s">
+        <v>295</v>
+      </c>
+      <c r="G125" t="s">
         <v>294</v>
-      </c>
-      <c r="G125" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4932,10 +4932,10 @@
         <v>309</v>
       </c>
       <c r="F126" t="s">
+        <v>309</v>
+      </c>
+      <c r="G126" t="s">
         <v>308</v>
-      </c>
-      <c r="G126" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4955,10 +4955,10 @@
         <v>309</v>
       </c>
       <c r="F127" t="s">
+        <v>309</v>
+      </c>
+      <c r="G127" t="s">
         <v>308</v>
-      </c>
-      <c r="G127" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4978,10 +4978,10 @@
         <v>309</v>
       </c>
       <c r="F128" t="s">
+        <v>309</v>
+      </c>
+      <c r="G128" t="s">
         <v>308</v>
-      </c>
-      <c r="G128" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -5001,10 +5001,10 @@
         <v>309</v>
       </c>
       <c r="F129" t="s">
+        <v>309</v>
+      </c>
+      <c r="G129" t="s">
         <v>308</v>
-      </c>
-      <c r="G129" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -5435,10 +5435,10 @@
         <v>358</v>
       </c>
       <c r="E148" t="s">
+        <v>319</v>
+      </c>
+      <c r="F148" t="s">
         <v>359</v>
-      </c>
-      <c r="F148" t="s">
-        <v>320</v>
       </c>
       <c r="G148" t="s">
         <v>321</v>
@@ -5458,10 +5458,10 @@
         <v>358</v>
       </c>
       <c r="E149" t="s">
+        <v>319</v>
+      </c>
+      <c r="F149" t="s">
         <v>359</v>
-      </c>
-      <c r="F149" t="s">
-        <v>320</v>
       </c>
       <c r="G149" t="s">
         <v>321</v>
@@ -5481,10 +5481,10 @@
         <v>358</v>
       </c>
       <c r="E150" t="s">
+        <v>319</v>
+      </c>
+      <c r="F150" t="s">
         <v>359</v>
-      </c>
-      <c r="F150" t="s">
-        <v>320</v>
       </c>
       <c r="G150" t="s">
         <v>321</v>
@@ -5504,10 +5504,10 @@
         <v>358</v>
       </c>
       <c r="E151" t="s">
+        <v>319</v>
+      </c>
+      <c r="F151" t="s">
         <v>359</v>
-      </c>
-      <c r="F151" t="s">
-        <v>320</v>
       </c>
       <c r="G151" t="s">
         <v>321</v>
@@ -5527,10 +5527,10 @@
         <v>358</v>
       </c>
       <c r="E152" t="s">
+        <v>319</v>
+      </c>
+      <c r="F152" t="s">
         <v>359</v>
-      </c>
-      <c r="F152" t="s">
-        <v>320</v>
       </c>
       <c r="G152" t="s">
         <v>321</v>
@@ -5550,10 +5550,10 @@
         <v>358</v>
       </c>
       <c r="E153" t="s">
+        <v>319</v>
+      </c>
+      <c r="F153" t="s">
         <v>359</v>
-      </c>
-      <c r="F153" t="s">
-        <v>320</v>
       </c>
       <c r="G153" t="s">
         <v>321</v>
@@ -5573,10 +5573,10 @@
         <v>372</v>
       </c>
       <c r="E154" t="s">
+        <v>319</v>
+      </c>
+      <c r="F154" t="s">
         <v>373</v>
-      </c>
-      <c r="F154" t="s">
-        <v>320</v>
       </c>
       <c r="G154" t="s">
         <v>321</v>
@@ -5596,10 +5596,10 @@
         <v>372</v>
       </c>
       <c r="E155" t="s">
+        <v>319</v>
+      </c>
+      <c r="F155" t="s">
         <v>373</v>
-      </c>
-      <c r="F155" t="s">
-        <v>320</v>
       </c>
       <c r="G155" t="s">
         <v>321</v>
@@ -5619,10 +5619,10 @@
         <v>372</v>
       </c>
       <c r="E156" t="s">
+        <v>319</v>
+      </c>
+      <c r="F156" t="s">
         <v>373</v>
-      </c>
-      <c r="F156" t="s">
-        <v>320</v>
       </c>
       <c r="G156" t="s">
         <v>321</v>
@@ -5642,10 +5642,10 @@
         <v>372</v>
       </c>
       <c r="E157" t="s">
+        <v>319</v>
+      </c>
+      <c r="F157" t="s">
         <v>373</v>
-      </c>
-      <c r="F157" t="s">
-        <v>320</v>
       </c>
       <c r="G157" t="s">
         <v>321</v>
@@ -5665,10 +5665,10 @@
         <v>372</v>
       </c>
       <c r="E158" t="s">
+        <v>319</v>
+      </c>
+      <c r="F158" t="s">
         <v>373</v>
-      </c>
-      <c r="F158" t="s">
-        <v>320</v>
       </c>
       <c r="G158" t="s">
         <v>321</v>
@@ -6125,10 +6125,10 @@
         <v>426</v>
       </c>
       <c r="E178" t="s">
+        <v>385</v>
+      </c>
+      <c r="F178" t="s">
         <v>427</v>
-      </c>
-      <c r="F178" t="s">
-        <v>386</v>
       </c>
       <c r="G178" t="s">
         <v>387</v>
@@ -6148,10 +6148,10 @@
         <v>426</v>
       </c>
       <c r="E179" t="s">
+        <v>385</v>
+      </c>
+      <c r="F179" t="s">
         <v>427</v>
-      </c>
-      <c r="F179" t="s">
-        <v>386</v>
       </c>
       <c r="G179" t="s">
         <v>387</v>
@@ -6171,10 +6171,10 @@
         <v>426</v>
       </c>
       <c r="E180" t="s">
+        <v>385</v>
+      </c>
+      <c r="F180" t="s">
         <v>427</v>
-      </c>
-      <c r="F180" t="s">
-        <v>386</v>
       </c>
       <c r="G180" t="s">
         <v>387</v>
@@ -6194,10 +6194,10 @@
         <v>426</v>
       </c>
       <c r="E181" t="s">
+        <v>385</v>
+      </c>
+      <c r="F181" t="s">
         <v>427</v>
-      </c>
-      <c r="F181" t="s">
-        <v>386</v>
       </c>
       <c r="G181" t="s">
         <v>387</v>
@@ -6217,10 +6217,10 @@
         <v>426</v>
       </c>
       <c r="E182" t="s">
+        <v>385</v>
+      </c>
+      <c r="F182" t="s">
         <v>427</v>
-      </c>
-      <c r="F182" t="s">
-        <v>386</v>
       </c>
       <c r="G182" t="s">
         <v>387</v>
@@ -6240,10 +6240,10 @@
         <v>426</v>
       </c>
       <c r="E183" t="s">
+        <v>385</v>
+      </c>
+      <c r="F183" t="s">
         <v>427</v>
-      </c>
-      <c r="F183" t="s">
-        <v>386</v>
       </c>
       <c r="G183" t="s">
         <v>387</v>
@@ -6263,10 +6263,10 @@
         <v>426</v>
       </c>
       <c r="E184" t="s">
+        <v>385</v>
+      </c>
+      <c r="F184" t="s">
         <v>427</v>
-      </c>
-      <c r="F184" t="s">
-        <v>386</v>
       </c>
       <c r="G184" t="s">
         <v>387</v>
@@ -6286,10 +6286,10 @@
         <v>426</v>
       </c>
       <c r="E185" t="s">
+        <v>385</v>
+      </c>
+      <c r="F185" t="s">
         <v>427</v>
-      </c>
-      <c r="F185" t="s">
-        <v>386</v>
       </c>
       <c r="G185" t="s">
         <v>387</v>
@@ -6309,10 +6309,10 @@
         <v>426</v>
       </c>
       <c r="E186" t="s">
+        <v>385</v>
+      </c>
+      <c r="F186" t="s">
         <v>427</v>
-      </c>
-      <c r="F186" t="s">
-        <v>386</v>
       </c>
       <c r="G186" t="s">
         <v>387</v>
@@ -6332,10 +6332,10 @@
         <v>426</v>
       </c>
       <c r="E187" t="s">
+        <v>385</v>
+      </c>
+      <c r="F187" t="s">
         <v>427</v>
-      </c>
-      <c r="F187" t="s">
-        <v>386</v>
       </c>
       <c r="G187" t="s">
         <v>387</v>
@@ -6355,10 +6355,10 @@
         <v>448</v>
       </c>
       <c r="E188" t="s">
+        <v>385</v>
+      </c>
+      <c r="F188" t="s">
         <v>449</v>
-      </c>
-      <c r="F188" t="s">
-        <v>386</v>
       </c>
       <c r="G188" t="s">
         <v>387</v>
@@ -6381,10 +6381,10 @@
         <v>453</v>
       </c>
       <c r="F189" t="s">
+        <v>453</v>
+      </c>
+      <c r="G189" t="s">
         <v>452</v>
-      </c>
-      <c r="G189" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6404,10 +6404,10 @@
         <v>453</v>
       </c>
       <c r="F190" t="s">
+        <v>453</v>
+      </c>
+      <c r="G190" t="s">
         <v>452</v>
-      </c>
-      <c r="G190" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6427,10 +6427,10 @@
         <v>453</v>
       </c>
       <c r="F191" t="s">
+        <v>453</v>
+      </c>
+      <c r="G191" t="s">
         <v>452</v>
-      </c>
-      <c r="G191" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6450,10 +6450,10 @@
         <v>453</v>
       </c>
       <c r="F192" t="s">
+        <v>453</v>
+      </c>
+      <c r="G192" t="s">
         <v>452</v>
-      </c>
-      <c r="G192" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6473,10 +6473,10 @@
         <v>453</v>
       </c>
       <c r="F193" t="s">
+        <v>453</v>
+      </c>
+      <c r="G193" t="s">
         <v>452</v>
-      </c>
-      <c r="G193" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6496,10 +6496,10 @@
         <v>453</v>
       </c>
       <c r="F194" t="s">
+        <v>453</v>
+      </c>
+      <c r="G194" t="s">
         <v>452</v>
-      </c>
-      <c r="G194" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6519,10 +6519,10 @@
         <v>467</v>
       </c>
       <c r="F195" t="s">
+        <v>467</v>
+      </c>
+      <c r="G195" t="s">
         <v>466</v>
-      </c>
-      <c r="G195" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6542,10 +6542,10 @@
         <v>471</v>
       </c>
       <c r="F196" t="s">
+        <v>471</v>
+      </c>
+      <c r="G196" t="s">
         <v>470</v>
-      </c>
-      <c r="G196" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6565,10 +6565,10 @@
         <v>471</v>
       </c>
       <c r="F197" t="s">
+        <v>471</v>
+      </c>
+      <c r="G197" t="s">
         <v>470</v>
-      </c>
-      <c r="G197" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6588,10 +6588,10 @@
         <v>471</v>
       </c>
       <c r="F198" t="s">
+        <v>471</v>
+      </c>
+      <c r="G198" t="s">
         <v>470</v>
-      </c>
-      <c r="G198" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6611,10 +6611,10 @@
         <v>471</v>
       </c>
       <c r="F199" t="s">
+        <v>471</v>
+      </c>
+      <c r="G199" t="s">
         <v>470</v>
-      </c>
-      <c r="G199" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6634,10 +6634,10 @@
         <v>471</v>
       </c>
       <c r="F200" t="s">
+        <v>471</v>
+      </c>
+      <c r="G200" t="s">
         <v>470</v>
-      </c>
-      <c r="G200" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6657,10 +6657,10 @@
         <v>471</v>
       </c>
       <c r="F201" t="s">
+        <v>471</v>
+      </c>
+      <c r="G201" t="s">
         <v>470</v>
-      </c>
-      <c r="G201" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6680,10 +6680,10 @@
         <v>485</v>
       </c>
       <c r="F202" t="s">
+        <v>485</v>
+      </c>
+      <c r="G202" t="s">
         <v>484</v>
-      </c>
-      <c r="G202" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6703,10 +6703,10 @@
         <v>485</v>
       </c>
       <c r="F203" t="s">
+        <v>485</v>
+      </c>
+      <c r="G203" t="s">
         <v>484</v>
-      </c>
-      <c r="G203" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6726,10 +6726,10 @@
         <v>485</v>
       </c>
       <c r="F204" t="s">
+        <v>485</v>
+      </c>
+      <c r="G204" t="s">
         <v>484</v>
-      </c>
-      <c r="G204" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6749,10 +6749,10 @@
         <v>485</v>
       </c>
       <c r="F205" t="s">
+        <v>485</v>
+      </c>
+      <c r="G205" t="s">
         <v>484</v>
-      </c>
-      <c r="G205" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6772,10 +6772,10 @@
         <v>485</v>
       </c>
       <c r="F206" t="s">
+        <v>485</v>
+      </c>
+      <c r="G206" t="s">
         <v>484</v>
-      </c>
-      <c r="G206" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6795,10 +6795,10 @@
         <v>485</v>
       </c>
       <c r="F207" t="s">
+        <v>485</v>
+      </c>
+      <c r="G207" t="s">
         <v>484</v>
-      </c>
-      <c r="G207" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6818,10 +6818,10 @@
         <v>485</v>
       </c>
       <c r="F208" t="s">
+        <v>485</v>
+      </c>
+      <c r="G208" t="s">
         <v>484</v>
-      </c>
-      <c r="G208" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6841,10 +6841,10 @@
         <v>485</v>
       </c>
       <c r="F209" t="s">
+        <v>485</v>
+      </c>
+      <c r="G209" t="s">
         <v>484</v>
-      </c>
-      <c r="G209" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6864,10 +6864,10 @@
         <v>485</v>
       </c>
       <c r="F210" t="s">
+        <v>485</v>
+      </c>
+      <c r="G210" t="s">
         <v>484</v>
-      </c>
-      <c r="G210" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6887,10 +6887,10 @@
         <v>485</v>
       </c>
       <c r="F211" t="s">
+        <v>485</v>
+      </c>
+      <c r="G211" t="s">
         <v>484</v>
-      </c>
-      <c r="G211" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6910,10 +6910,10 @@
         <v>507</v>
       </c>
       <c r="F212" t="s">
+        <v>507</v>
+      </c>
+      <c r="G212" t="s">
         <v>506</v>
-      </c>
-      <c r="G212" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6933,10 +6933,10 @@
         <v>511</v>
       </c>
       <c r="F213" t="s">
+        <v>511</v>
+      </c>
+      <c r="G213" t="s">
         <v>510</v>
-      </c>
-      <c r="G213" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6956,10 +6956,10 @@
         <v>515</v>
       </c>
       <c r="F214" t="s">
+        <v>515</v>
+      </c>
+      <c r="G214" t="s">
         <v>514</v>
-      </c>
-      <c r="G214" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6979,10 +6979,10 @@
         <v>515</v>
       </c>
       <c r="F215" t="s">
+        <v>515</v>
+      </c>
+      <c r="G215" t="s">
         <v>514</v>
-      </c>
-      <c r="G215" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -7002,10 +7002,10 @@
         <v>521</v>
       </c>
       <c r="F216" t="s">
+        <v>521</v>
+      </c>
+      <c r="G216" t="s">
         <v>520</v>
-      </c>
-      <c r="G216" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -7025,10 +7025,10 @@
         <v>521</v>
       </c>
       <c r="F217" t="s">
+        <v>521</v>
+      </c>
+      <c r="G217" t="s">
         <v>520</v>
-      </c>
-      <c r="G217" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -7048,10 +7048,10 @@
         <v>521</v>
       </c>
       <c r="F218" t="s">
+        <v>521</v>
+      </c>
+      <c r="G218" t="s">
         <v>520</v>
-      </c>
-      <c r="G218" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -7071,10 +7071,10 @@
         <v>521</v>
       </c>
       <c r="F219" t="s">
+        <v>521</v>
+      </c>
+      <c r="G219" t="s">
         <v>520</v>
-      </c>
-      <c r="G219" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -7094,10 +7094,10 @@
         <v>521</v>
       </c>
       <c r="F220" t="s">
+        <v>521</v>
+      </c>
+      <c r="G220" t="s">
         <v>520</v>
-      </c>
-      <c r="G220" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -7117,10 +7117,10 @@
         <v>521</v>
       </c>
       <c r="F221" t="s">
+        <v>521</v>
+      </c>
+      <c r="G221" t="s">
         <v>520</v>
-      </c>
-      <c r="G221" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -7140,10 +7140,10 @@
         <v>521</v>
       </c>
       <c r="F222" t="s">
+        <v>521</v>
+      </c>
+      <c r="G222" t="s">
         <v>520</v>
-      </c>
-      <c r="G222" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -7163,10 +7163,10 @@
         <v>537</v>
       </c>
       <c r="F223" t="s">
+        <v>537</v>
+      </c>
+      <c r="G223" t="s">
         <v>536</v>
-      </c>
-      <c r="G223" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -7186,10 +7186,10 @@
         <v>537</v>
       </c>
       <c r="F224" t="s">
+        <v>537</v>
+      </c>
+      <c r="G224" t="s">
         <v>536</v>
-      </c>
-      <c r="G224" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -7209,10 +7209,10 @@
         <v>537</v>
       </c>
       <c r="F225" t="s">
+        <v>537</v>
+      </c>
+      <c r="G225" t="s">
         <v>536</v>
-      </c>
-      <c r="G225" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -7232,10 +7232,10 @@
         <v>545</v>
       </c>
       <c r="F226" t="s">
+        <v>545</v>
+      </c>
+      <c r="G226" t="s">
         <v>544</v>
-      </c>
-      <c r="G226" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -7255,10 +7255,10 @@
         <v>549</v>
       </c>
       <c r="F227" t="s">
+        <v>549</v>
+      </c>
+      <c r="G227" t="s">
         <v>548</v>
-      </c>
-      <c r="G227" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -7278,10 +7278,10 @@
         <v>553</v>
       </c>
       <c r="F228" t="s">
+        <v>553</v>
+      </c>
+      <c r="G228" t="s">
         <v>552</v>
-      </c>
-      <c r="G228" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -7301,10 +7301,10 @@
         <v>557</v>
       </c>
       <c r="F229" t="s">
+        <v>557</v>
+      </c>
+      <c r="G229" t="s">
         <v>556</v>
-      </c>
-      <c r="G229" t="s">
-        <v>557</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -7324,10 +7324,10 @@
         <v>561</v>
       </c>
       <c r="F230" t="s">
+        <v>561</v>
+      </c>
+      <c r="G230" t="s">
         <v>560</v>
-      </c>
-      <c r="G230" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -7347,10 +7347,10 @@
         <v>561</v>
       </c>
       <c r="F231" t="s">
+        <v>561</v>
+      </c>
+      <c r="G231" t="s">
         <v>560</v>
-      </c>
-      <c r="G231" t="s">
-        <v>561</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/en/SectorGroup.xlsx
+++ b/api/xlsx/en/SectorGroup.xlsx
@@ -25,12 +25,12 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
     <t>codeforiati:category-name</t>
   </si>
   <si>
@@ -46,12 +46,12 @@
     <t>active</t>
   </si>
   <si>
+    <t>Education</t>
+  </si>
+  <si>
     <t>111</t>
   </si>
   <si>
-    <t>Education</t>
-  </si>
-  <si>
     <t>Education, Level Unspecified</t>
   </si>
   <si>
@@ -148,12 +148,12 @@
     <t>Health policy and administrative management</t>
   </si>
   <si>
+    <t>Health</t>
+  </si>
+  <si>
     <t>121</t>
   </si>
   <si>
-    <t>Health</t>
-  </si>
-  <si>
     <t>Health, General</t>
   </si>
   <si>
@@ -280,12 +280,12 @@
     <t>Population policy and administrative management</t>
   </si>
   <si>
+    <t>Population Policies/Programmes &amp; Reproductive Health</t>
+  </si>
+  <si>
     <t>130</t>
   </si>
   <si>
-    <t>Population Policies/Programmes &amp; Reproductive Health</t>
-  </si>
-  <si>
     <t>13020</t>
   </si>
   <si>
@@ -316,12 +316,12 @@
     <t>Water sector policy and administrative management</t>
   </si>
   <si>
+    <t>Water Supply &amp; Sanitation</t>
+  </si>
+  <si>
     <t>140</t>
   </si>
   <si>
-    <t>Water Supply &amp; Sanitation</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -388,12 +388,12 @@
     <t>Public sector policy and administrative management</t>
   </si>
   <si>
+    <t>Government &amp; Civil Society</t>
+  </si>
+  <si>
     <t>151</t>
   </si>
   <si>
-    <t>Government &amp; Civil Society</t>
-  </si>
-  <si>
     <t>Government &amp; Civil Society-general</t>
   </si>
   <si>
@@ -538,12 +538,12 @@
     <t>Social Protection</t>
   </si>
   <si>
+    <t>Other Social Infrastructure &amp; Services</t>
+  </si>
+  <si>
     <t>160</t>
   </si>
   <si>
-    <t>Other Social Infrastructure &amp; Services</t>
-  </si>
-  <si>
     <t>16020</t>
   </si>
   <si>
@@ -610,12 +610,12 @@
     <t>Transport policy and administrative management</t>
   </si>
   <si>
+    <t>Transport &amp; Storage</t>
+  </si>
+  <si>
     <t>210</t>
   </si>
   <si>
-    <t>Transport &amp; Storage</t>
-  </si>
-  <si>
     <t>21020</t>
   </si>
   <si>
@@ -658,12 +658,12 @@
     <t>Communications policy and administrative management</t>
   </si>
   <si>
+    <t>Communications</t>
+  </si>
+  <si>
     <t>220</t>
   </si>
   <si>
-    <t>Communications</t>
-  </si>
-  <si>
     <t>22020</t>
   </si>
   <si>
@@ -688,12 +688,12 @@
     <t>Energy policy and administrative management</t>
   </si>
   <si>
+    <t>Energy</t>
+  </si>
+  <si>
     <t>231</t>
   </si>
   <si>
-    <t>Energy</t>
-  </si>
-  <si>
     <t>Energy Policy</t>
   </si>
   <si>
@@ -898,12 +898,12 @@
     <t>Financial policy and administrative management</t>
   </si>
   <si>
+    <t>Banking &amp; Financial Services</t>
+  </si>
+  <si>
     <t>240</t>
   </si>
   <si>
-    <t>Banking &amp; Financial Services</t>
-  </si>
-  <si>
     <t>24020</t>
   </si>
   <si>
@@ -940,12 +940,12 @@
     <t>Business policy and administration</t>
   </si>
   <si>
+    <t>Business &amp; Other Services</t>
+  </si>
+  <si>
     <t>250</t>
   </si>
   <si>
-    <t>Business &amp; Other Services</t>
-  </si>
-  <si>
     <t>25020</t>
   </si>
   <si>
@@ -970,12 +970,12 @@
     <t>Agricultural policy and administrative management</t>
   </si>
   <si>
+    <t>Agriculture, Forestry, Fishing</t>
+  </si>
+  <si>
     <t>311</t>
   </si>
   <si>
-    <t>Agriculture, Forestry, Fishing</t>
-  </si>
-  <si>
     <t>Agriculture</t>
   </si>
   <si>
@@ -1168,12 +1168,12 @@
     <t>Industrial policy and administrative management</t>
   </si>
   <si>
+    <t>Industry, Mining, Construction</t>
+  </si>
+  <si>
     <t>321</t>
   </si>
   <si>
-    <t>Industry, Mining, Construction</t>
-  </si>
-  <si>
     <t>Industry</t>
   </si>
   <si>
@@ -1372,12 +1372,12 @@
     <t>Trade policy and administrative management</t>
   </si>
   <si>
+    <t>Trade Policies &amp; Regulations</t>
+  </si>
+  <si>
     <t>331</t>
   </si>
   <si>
-    <t>Trade Policies &amp; Regulations</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1414,24 +1414,24 @@
     <t>Tourism policy and administrative management</t>
   </si>
   <si>
+    <t>Tourism</t>
+  </si>
+  <si>
     <t>332</t>
   </si>
   <si>
-    <t>Tourism</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
     <t>Environmental policy and administrative management</t>
   </si>
   <si>
+    <t>General Environment Protection</t>
+  </si>
+  <si>
     <t>410</t>
   </si>
   <si>
-    <t>General Environment Protection</t>
-  </si>
-  <si>
     <t>41020</t>
   </si>
   <si>
@@ -1468,12 +1468,12 @@
     <t>Multisector aid</t>
   </si>
   <si>
+    <t>Other Multisector</t>
+  </si>
+  <si>
     <t>430</t>
   </si>
   <si>
-    <t>Other Multisector</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -1534,36 +1534,36 @@
     <t>General budget support-related aid</t>
   </si>
   <si>
+    <t>General Budget Support</t>
+  </si>
+  <si>
     <t>510</t>
   </si>
   <si>
-    <t>General Budget Support</t>
-  </si>
-  <si>
     <t>52010</t>
   </si>
   <si>
     <t>Food assistance</t>
   </si>
   <si>
+    <t>Development Food Assistance</t>
+  </si>
+  <si>
     <t>520</t>
   </si>
   <si>
-    <t>Development Food Assistance</t>
-  </si>
-  <si>
     <t>53030</t>
   </si>
   <si>
     <t>Import support (capital goods)</t>
   </si>
   <si>
+    <t>Other Commodity Assistance</t>
+  </si>
+  <si>
     <t>530</t>
   </si>
   <si>
-    <t>Other Commodity Assistance</t>
-  </si>
-  <si>
     <t>53040</t>
   </si>
   <si>
@@ -1576,12 +1576,12 @@
     <t>Action relating to debt</t>
   </si>
   <si>
+    <t>Action Relating to Debt</t>
+  </si>
+  <si>
     <t>600</t>
   </si>
   <si>
-    <t>Action Relating to Debt</t>
-  </si>
-  <si>
     <t>60020</t>
   </si>
   <si>
@@ -1624,12 +1624,12 @@
     <t>Material relief assistance and services</t>
   </si>
   <si>
+    <t>Emergency Response</t>
+  </si>
+  <si>
     <t>720</t>
   </si>
   <si>
-    <t>Emergency Response</t>
-  </si>
-  <si>
     <t>72040</t>
   </si>
   <si>
@@ -1648,58 +1648,58 @@
     <t>Immediate post-emergency reconstruction and rehabilitation</t>
   </si>
   <si>
+    <t>Reconstruction Relief &amp; Rehabilitation</t>
+  </si>
+  <si>
     <t>730</t>
   </si>
   <si>
-    <t>Reconstruction Relief &amp; Rehabilitation</t>
-  </si>
-  <si>
     <t>74020</t>
   </si>
   <si>
     <t>Multi-hazard response preparedness</t>
   </si>
   <si>
+    <t>Disaster Prevention &amp; Preparedness</t>
+  </si>
+  <si>
     <t>740</t>
   </si>
   <si>
-    <t>Disaster Prevention &amp; Preparedness</t>
-  </si>
-  <si>
     <t>91010</t>
   </si>
   <si>
     <t>Administrative costs (non-sector allocable)</t>
   </si>
   <si>
+    <t>Administrative Costs of Donors</t>
+  </si>
+  <si>
     <t>910</t>
   </si>
   <si>
-    <t>Administrative Costs of Donors</t>
-  </si>
-  <si>
     <t>93010</t>
   </si>
   <si>
     <t>Refugees/asylum seekers in donor countries (non-sector allocable)</t>
   </si>
   <si>
+    <t>Refugees in Donor Countries</t>
+  </si>
+  <si>
     <t>930</t>
   </si>
   <si>
-    <t>Refugees in Donor Countries</t>
-  </si>
-  <si>
     <t>99810</t>
   </si>
   <si>
     <t>Sectors not specified</t>
   </si>
   <si>
+    <t>Unallocated / Unspecified</t>
+  </si>
+  <si>
     <t>998</t>
-  </si>
-  <si>
-    <t>Unallocated / Unspecified</t>
   </si>
   <si>
     <t>99820</t>
@@ -2166,10 +2166,10 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
         <v>22</v>
-      </c>
-      <c r="E6" t="s">
-        <v>11</v>
       </c>
       <c r="F6" t="s">
         <v>23</v>
@@ -2189,10 +2189,10 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" t="s">
         <v>22</v>
-      </c>
-      <c r="E7" t="s">
-        <v>11</v>
       </c>
       <c r="F7" t="s">
         <v>23</v>
@@ -2212,10 +2212,10 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" t="s">
         <v>22</v>
-      </c>
-      <c r="E8" t="s">
-        <v>11</v>
       </c>
       <c r="F8" t="s">
         <v>23</v>
@@ -2235,10 +2235,10 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" t="s">
         <v>22</v>
-      </c>
-      <c r="E9" t="s">
-        <v>11</v>
       </c>
       <c r="F9" t="s">
         <v>23</v>
@@ -2258,10 +2258,10 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" t="s">
         <v>32</v>
-      </c>
-      <c r="E10" t="s">
-        <v>11</v>
       </c>
       <c r="F10" t="s">
         <v>33</v>
@@ -2281,10 +2281,10 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" t="s">
         <v>32</v>
-      </c>
-      <c r="E11" t="s">
-        <v>11</v>
       </c>
       <c r="F11" t="s">
         <v>33</v>
@@ -2304,10 +2304,10 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" t="s">
         <v>38</v>
-      </c>
-      <c r="E12" t="s">
-        <v>11</v>
       </c>
       <c r="F12" t="s">
         <v>39</v>
@@ -2327,10 +2327,10 @@
         <v>9</v>
       </c>
       <c r="D13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" t="s">
         <v>38</v>
-      </c>
-      <c r="E13" t="s">
-        <v>11</v>
       </c>
       <c r="F13" t="s">
         <v>39</v>
@@ -2442,10 +2442,10 @@
         <v>9</v>
       </c>
       <c r="D18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18" t="s">
         <v>56</v>
-      </c>
-      <c r="E18" t="s">
-        <v>45</v>
       </c>
       <c r="F18" t="s">
         <v>57</v>
@@ -2465,10 +2465,10 @@
         <v>9</v>
       </c>
       <c r="D19" t="s">
+        <v>44</v>
+      </c>
+      <c r="E19" t="s">
         <v>56</v>
-      </c>
-      <c r="E19" t="s">
-        <v>45</v>
       </c>
       <c r="F19" t="s">
         <v>57</v>
@@ -2488,10 +2488,10 @@
         <v>9</v>
       </c>
       <c r="D20" t="s">
+        <v>44</v>
+      </c>
+      <c r="E20" t="s">
         <v>56</v>
-      </c>
-      <c r="E20" t="s">
-        <v>45</v>
       </c>
       <c r="F20" t="s">
         <v>57</v>
@@ -2511,10 +2511,10 @@
         <v>9</v>
       </c>
       <c r="D21" t="s">
+        <v>44</v>
+      </c>
+      <c r="E21" t="s">
         <v>56</v>
-      </c>
-      <c r="E21" t="s">
-        <v>45</v>
       </c>
       <c r="F21" t="s">
         <v>57</v>
@@ -2534,10 +2534,10 @@
         <v>9</v>
       </c>
       <c r="D22" t="s">
+        <v>44</v>
+      </c>
+      <c r="E22" t="s">
         <v>56</v>
-      </c>
-      <c r="E22" t="s">
-        <v>45</v>
       </c>
       <c r="F22" t="s">
         <v>57</v>
@@ -2557,10 +2557,10 @@
         <v>9</v>
       </c>
       <c r="D23" t="s">
+        <v>44</v>
+      </c>
+      <c r="E23" t="s">
         <v>56</v>
-      </c>
-      <c r="E23" t="s">
-        <v>45</v>
       </c>
       <c r="F23" t="s">
         <v>57</v>
@@ -2580,10 +2580,10 @@
         <v>9</v>
       </c>
       <c r="D24" t="s">
+        <v>44</v>
+      </c>
+      <c r="E24" t="s">
         <v>56</v>
-      </c>
-      <c r="E24" t="s">
-        <v>45</v>
       </c>
       <c r="F24" t="s">
         <v>57</v>
@@ -2603,10 +2603,10 @@
         <v>9</v>
       </c>
       <c r="D25" t="s">
+        <v>44</v>
+      </c>
+      <c r="E25" t="s">
         <v>56</v>
-      </c>
-      <c r="E25" t="s">
-        <v>45</v>
       </c>
       <c r="F25" t="s">
         <v>57</v>
@@ -2626,10 +2626,10 @@
         <v>9</v>
       </c>
       <c r="D26" t="s">
+        <v>44</v>
+      </c>
+      <c r="E26" t="s">
         <v>74</v>
-      </c>
-      <c r="E26" t="s">
-        <v>45</v>
       </c>
       <c r="F26" t="s">
         <v>75</v>
@@ -2649,10 +2649,10 @@
         <v>9</v>
       </c>
       <c r="D27" t="s">
+        <v>44</v>
+      </c>
+      <c r="E27" t="s">
         <v>74</v>
-      </c>
-      <c r="E27" t="s">
-        <v>45</v>
       </c>
       <c r="F27" t="s">
         <v>75</v>
@@ -2672,10 +2672,10 @@
         <v>9</v>
       </c>
       <c r="D28" t="s">
+        <v>44</v>
+      </c>
+      <c r="E28" t="s">
         <v>74</v>
-      </c>
-      <c r="E28" t="s">
-        <v>45</v>
       </c>
       <c r="F28" t="s">
         <v>75</v>
@@ -2695,10 +2695,10 @@
         <v>9</v>
       </c>
       <c r="D29" t="s">
+        <v>44</v>
+      </c>
+      <c r="E29" t="s">
         <v>74</v>
-      </c>
-      <c r="E29" t="s">
-        <v>45</v>
       </c>
       <c r="F29" t="s">
         <v>75</v>
@@ -2718,10 +2718,10 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
+        <v>44</v>
+      </c>
+      <c r="E30" t="s">
         <v>74</v>
-      </c>
-      <c r="E30" t="s">
-        <v>45</v>
       </c>
       <c r="F30" t="s">
         <v>75</v>
@@ -2741,10 +2741,10 @@
         <v>9</v>
       </c>
       <c r="D31" t="s">
+        <v>44</v>
+      </c>
+      <c r="E31" t="s">
         <v>74</v>
-      </c>
-      <c r="E31" t="s">
-        <v>45</v>
       </c>
       <c r="F31" t="s">
         <v>75</v>
@@ -2770,10 +2770,10 @@
         <v>89</v>
       </c>
       <c r="F32" t="s">
+        <v>88</v>
+      </c>
+      <c r="G32" t="s">
         <v>89</v>
-      </c>
-      <c r="G32" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2793,10 +2793,10 @@
         <v>89</v>
       </c>
       <c r="F33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G33" t="s">
         <v>89</v>
-      </c>
-      <c r="G33" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2816,10 +2816,10 @@
         <v>89</v>
       </c>
       <c r="F34" t="s">
+        <v>88</v>
+      </c>
+      <c r="G34" t="s">
         <v>89</v>
-      </c>
-      <c r="G34" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2839,10 +2839,10 @@
         <v>89</v>
       </c>
       <c r="F35" t="s">
+        <v>88</v>
+      </c>
+      <c r="G35" t="s">
         <v>89</v>
-      </c>
-      <c r="G35" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2862,10 +2862,10 @@
         <v>89</v>
       </c>
       <c r="F36" t="s">
+        <v>88</v>
+      </c>
+      <c r="G36" t="s">
         <v>89</v>
-      </c>
-      <c r="G36" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2885,10 +2885,10 @@
         <v>101</v>
       </c>
       <c r="F37" t="s">
+        <v>100</v>
+      </c>
+      <c r="G37" t="s">
         <v>101</v>
-      </c>
-      <c r="G37" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2908,10 +2908,10 @@
         <v>101</v>
       </c>
       <c r="F38" t="s">
+        <v>100</v>
+      </c>
+      <c r="G38" t="s">
         <v>101</v>
-      </c>
-      <c r="G38" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2931,10 +2931,10 @@
         <v>101</v>
       </c>
       <c r="F39" t="s">
+        <v>100</v>
+      </c>
+      <c r="G39" t="s">
         <v>101</v>
-      </c>
-      <c r="G39" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2954,10 +2954,10 @@
         <v>101</v>
       </c>
       <c r="F40" t="s">
+        <v>100</v>
+      </c>
+      <c r="G40" t="s">
         <v>101</v>
-      </c>
-      <c r="G40" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2977,10 +2977,10 @@
         <v>101</v>
       </c>
       <c r="F41" t="s">
+        <v>100</v>
+      </c>
+      <c r="G41" t="s">
         <v>101</v>
-      </c>
-      <c r="G41" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -3000,10 +3000,10 @@
         <v>101</v>
       </c>
       <c r="F42" t="s">
+        <v>100</v>
+      </c>
+      <c r="G42" t="s">
         <v>101</v>
-      </c>
-      <c r="G42" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3023,10 +3023,10 @@
         <v>101</v>
       </c>
       <c r="F43" t="s">
+        <v>100</v>
+      </c>
+      <c r="G43" t="s">
         <v>101</v>
-      </c>
-      <c r="G43" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3046,10 +3046,10 @@
         <v>101</v>
       </c>
       <c r="F44" t="s">
+        <v>100</v>
+      </c>
+      <c r="G44" t="s">
         <v>101</v>
-      </c>
-      <c r="G44" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3069,10 +3069,10 @@
         <v>101</v>
       </c>
       <c r="F45" t="s">
+        <v>100</v>
+      </c>
+      <c r="G45" t="s">
         <v>101</v>
-      </c>
-      <c r="G45" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3092,10 +3092,10 @@
         <v>101</v>
       </c>
       <c r="F46" t="s">
+        <v>100</v>
+      </c>
+      <c r="G46" t="s">
         <v>101</v>
-      </c>
-      <c r="G46" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3115,10 +3115,10 @@
         <v>101</v>
       </c>
       <c r="F47" t="s">
+        <v>100</v>
+      </c>
+      <c r="G47" t="s">
         <v>101</v>
-      </c>
-      <c r="G47" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3500,10 +3500,10 @@
         <v>9</v>
       </c>
       <c r="D64" t="s">
+        <v>124</v>
+      </c>
+      <c r="E64" t="s">
         <v>160</v>
-      </c>
-      <c r="E64" t="s">
-        <v>125</v>
       </c>
       <c r="F64" t="s">
         <v>161</v>
@@ -3523,10 +3523,10 @@
         <v>9</v>
       </c>
       <c r="D65" t="s">
+        <v>124</v>
+      </c>
+      <c r="E65" t="s">
         <v>160</v>
-      </c>
-      <c r="E65" t="s">
-        <v>125</v>
       </c>
       <c r="F65" t="s">
         <v>161</v>
@@ -3546,10 +3546,10 @@
         <v>9</v>
       </c>
       <c r="D66" t="s">
+        <v>124</v>
+      </c>
+      <c r="E66" t="s">
         <v>160</v>
-      </c>
-      <c r="E66" t="s">
-        <v>125</v>
       </c>
       <c r="F66" t="s">
         <v>161</v>
@@ -3569,10 +3569,10 @@
         <v>9</v>
       </c>
       <c r="D67" t="s">
+        <v>124</v>
+      </c>
+      <c r="E67" t="s">
         <v>160</v>
-      </c>
-      <c r="E67" t="s">
-        <v>125</v>
       </c>
       <c r="F67" t="s">
         <v>161</v>
@@ -3592,10 +3592,10 @@
         <v>9</v>
       </c>
       <c r="D68" t="s">
+        <v>124</v>
+      </c>
+      <c r="E68" t="s">
         <v>160</v>
-      </c>
-      <c r="E68" t="s">
-        <v>125</v>
       </c>
       <c r="F68" t="s">
         <v>161</v>
@@ -3615,10 +3615,10 @@
         <v>9</v>
       </c>
       <c r="D69" t="s">
+        <v>124</v>
+      </c>
+      <c r="E69" t="s">
         <v>160</v>
-      </c>
-      <c r="E69" t="s">
-        <v>125</v>
       </c>
       <c r="F69" t="s">
         <v>161</v>
@@ -3644,10 +3644,10 @@
         <v>175</v>
       </c>
       <c r="F70" t="s">
+        <v>174</v>
+      </c>
+      <c r="G70" t="s">
         <v>175</v>
-      </c>
-      <c r="G70" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3667,10 +3667,10 @@
         <v>175</v>
       </c>
       <c r="F71" t="s">
+        <v>174</v>
+      </c>
+      <c r="G71" t="s">
         <v>175</v>
-      </c>
-      <c r="G71" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3690,10 +3690,10 @@
         <v>175</v>
       </c>
       <c r="F72" t="s">
+        <v>174</v>
+      </c>
+      <c r="G72" t="s">
         <v>175</v>
-      </c>
-      <c r="G72" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3713,10 +3713,10 @@
         <v>175</v>
       </c>
       <c r="F73" t="s">
+        <v>174</v>
+      </c>
+      <c r="G73" t="s">
         <v>175</v>
-      </c>
-      <c r="G73" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3736,10 +3736,10 @@
         <v>175</v>
       </c>
       <c r="F74" t="s">
+        <v>174</v>
+      </c>
+      <c r="G74" t="s">
         <v>175</v>
-      </c>
-      <c r="G74" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3759,10 +3759,10 @@
         <v>175</v>
       </c>
       <c r="F75" t="s">
+        <v>174</v>
+      </c>
+      <c r="G75" t="s">
         <v>175</v>
-      </c>
-      <c r="G75" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3782,10 +3782,10 @@
         <v>175</v>
       </c>
       <c r="F76" t="s">
+        <v>174</v>
+      </c>
+      <c r="G76" t="s">
         <v>175</v>
-      </c>
-      <c r="G76" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3805,10 +3805,10 @@
         <v>175</v>
       </c>
       <c r="F77" t="s">
+        <v>174</v>
+      </c>
+      <c r="G77" t="s">
         <v>175</v>
-      </c>
-      <c r="G77" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3828,10 +3828,10 @@
         <v>175</v>
       </c>
       <c r="F78" t="s">
+        <v>174</v>
+      </c>
+      <c r="G78" t="s">
         <v>175</v>
-      </c>
-      <c r="G78" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3851,10 +3851,10 @@
         <v>175</v>
       </c>
       <c r="F79" t="s">
+        <v>174</v>
+      </c>
+      <c r="G79" t="s">
         <v>175</v>
-      </c>
-      <c r="G79" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3874,10 +3874,10 @@
         <v>175</v>
       </c>
       <c r="F80" t="s">
+        <v>174</v>
+      </c>
+      <c r="G80" t="s">
         <v>175</v>
-      </c>
-      <c r="G80" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3897,10 +3897,10 @@
         <v>199</v>
       </c>
       <c r="F81" t="s">
+        <v>198</v>
+      </c>
+      <c r="G81" t="s">
         <v>199</v>
-      </c>
-      <c r="G81" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3920,10 +3920,10 @@
         <v>199</v>
       </c>
       <c r="F82" t="s">
+        <v>198</v>
+      </c>
+      <c r="G82" t="s">
         <v>199</v>
-      </c>
-      <c r="G82" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3943,10 +3943,10 @@
         <v>199</v>
       </c>
       <c r="F83" t="s">
+        <v>198</v>
+      </c>
+      <c r="G83" t="s">
         <v>199</v>
-      </c>
-      <c r="G83" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3966,10 +3966,10 @@
         <v>199</v>
       </c>
       <c r="F84" t="s">
+        <v>198</v>
+      </c>
+      <c r="G84" t="s">
         <v>199</v>
-      </c>
-      <c r="G84" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3989,10 +3989,10 @@
         <v>199</v>
       </c>
       <c r="F85" t="s">
+        <v>198</v>
+      </c>
+      <c r="G85" t="s">
         <v>199</v>
-      </c>
-      <c r="G85" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4012,10 +4012,10 @@
         <v>199</v>
       </c>
       <c r="F86" t="s">
+        <v>198</v>
+      </c>
+      <c r="G86" t="s">
         <v>199</v>
-      </c>
-      <c r="G86" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4035,10 +4035,10 @@
         <v>199</v>
       </c>
       <c r="F87" t="s">
+        <v>198</v>
+      </c>
+      <c r="G87" t="s">
         <v>199</v>
-      </c>
-      <c r="G87" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4058,10 +4058,10 @@
         <v>215</v>
       </c>
       <c r="F88" t="s">
+        <v>214</v>
+      </c>
+      <c r="G88" t="s">
         <v>215</v>
-      </c>
-      <c r="G88" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4081,10 +4081,10 @@
         <v>215</v>
       </c>
       <c r="F89" t="s">
+        <v>214</v>
+      </c>
+      <c r="G89" t="s">
         <v>215</v>
-      </c>
-      <c r="G89" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4104,10 +4104,10 @@
         <v>215</v>
       </c>
       <c r="F90" t="s">
+        <v>214</v>
+      </c>
+      <c r="G90" t="s">
         <v>215</v>
-      </c>
-      <c r="G90" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4127,10 +4127,10 @@
         <v>215</v>
       </c>
       <c r="F91" t="s">
+        <v>214</v>
+      </c>
+      <c r="G91" t="s">
         <v>215</v>
-      </c>
-      <c r="G91" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4236,10 +4236,10 @@
         <v>9</v>
       </c>
       <c r="D96" t="s">
+        <v>224</v>
+      </c>
+      <c r="E96" t="s">
         <v>236</v>
-      </c>
-      <c r="E96" t="s">
-        <v>225</v>
       </c>
       <c r="F96" t="s">
         <v>237</v>
@@ -4259,10 +4259,10 @@
         <v>9</v>
       </c>
       <c r="D97" t="s">
+        <v>224</v>
+      </c>
+      <c r="E97" t="s">
         <v>236</v>
-      </c>
-      <c r="E97" t="s">
-        <v>225</v>
       </c>
       <c r="F97" t="s">
         <v>237</v>
@@ -4282,10 +4282,10 @@
         <v>9</v>
       </c>
       <c r="D98" t="s">
+        <v>224</v>
+      </c>
+      <c r="E98" t="s">
         <v>236</v>
-      </c>
-      <c r="E98" t="s">
-        <v>225</v>
       </c>
       <c r="F98" t="s">
         <v>237</v>
@@ -4305,10 +4305,10 @@
         <v>9</v>
       </c>
       <c r="D99" t="s">
+        <v>224</v>
+      </c>
+      <c r="E99" t="s">
         <v>236</v>
-      </c>
-      <c r="E99" t="s">
-        <v>225</v>
       </c>
       <c r="F99" t="s">
         <v>237</v>
@@ -4328,10 +4328,10 @@
         <v>9</v>
       </c>
       <c r="D100" t="s">
+        <v>224</v>
+      </c>
+      <c r="E100" t="s">
         <v>236</v>
-      </c>
-      <c r="E100" t="s">
-        <v>225</v>
       </c>
       <c r="F100" t="s">
         <v>237</v>
@@ -4351,10 +4351,10 @@
         <v>9</v>
       </c>
       <c r="D101" t="s">
+        <v>224</v>
+      </c>
+      <c r="E101" t="s">
         <v>236</v>
-      </c>
-      <c r="E101" t="s">
-        <v>225</v>
       </c>
       <c r="F101" t="s">
         <v>237</v>
@@ -4374,10 +4374,10 @@
         <v>9</v>
       </c>
       <c r="D102" t="s">
+        <v>224</v>
+      </c>
+      <c r="E102" t="s">
         <v>236</v>
-      </c>
-      <c r="E102" t="s">
-        <v>225</v>
       </c>
       <c r="F102" t="s">
         <v>237</v>
@@ -4397,10 +4397,10 @@
         <v>9</v>
       </c>
       <c r="D103" t="s">
+        <v>224</v>
+      </c>
+      <c r="E103" t="s">
         <v>236</v>
-      </c>
-      <c r="E103" t="s">
-        <v>225</v>
       </c>
       <c r="F103" t="s">
         <v>237</v>
@@ -4420,10 +4420,10 @@
         <v>9</v>
       </c>
       <c r="D104" t="s">
+        <v>224</v>
+      </c>
+      <c r="E104" t="s">
         <v>236</v>
-      </c>
-      <c r="E104" t="s">
-        <v>225</v>
       </c>
       <c r="F104" t="s">
         <v>237</v>
@@ -4443,10 +4443,10 @@
         <v>9</v>
       </c>
       <c r="D105" t="s">
+        <v>224</v>
+      </c>
+      <c r="E105" t="s">
         <v>256</v>
-      </c>
-      <c r="E105" t="s">
-        <v>225</v>
       </c>
       <c r="F105" t="s">
         <v>257</v>
@@ -4466,10 +4466,10 @@
         <v>9</v>
       </c>
       <c r="D106" t="s">
+        <v>224</v>
+      </c>
+      <c r="E106" t="s">
         <v>256</v>
-      </c>
-      <c r="E106" t="s">
-        <v>225</v>
       </c>
       <c r="F106" t="s">
         <v>257</v>
@@ -4489,10 +4489,10 @@
         <v>9</v>
       </c>
       <c r="D107" t="s">
+        <v>224</v>
+      </c>
+      <c r="E107" t="s">
         <v>256</v>
-      </c>
-      <c r="E107" t="s">
-        <v>225</v>
       </c>
       <c r="F107" t="s">
         <v>257</v>
@@ -4512,10 +4512,10 @@
         <v>9</v>
       </c>
       <c r="D108" t="s">
+        <v>224</v>
+      </c>
+      <c r="E108" t="s">
         <v>256</v>
-      </c>
-      <c r="E108" t="s">
-        <v>225</v>
       </c>
       <c r="F108" t="s">
         <v>257</v>
@@ -4535,10 +4535,10 @@
         <v>9</v>
       </c>
       <c r="D109" t="s">
+        <v>224</v>
+      </c>
+      <c r="E109" t="s">
         <v>256</v>
-      </c>
-      <c r="E109" t="s">
-        <v>225</v>
       </c>
       <c r="F109" t="s">
         <v>257</v>
@@ -4558,10 +4558,10 @@
         <v>9</v>
       </c>
       <c r="D110" t="s">
+        <v>224</v>
+      </c>
+      <c r="E110" t="s">
         <v>256</v>
-      </c>
-      <c r="E110" t="s">
-        <v>225</v>
       </c>
       <c r="F110" t="s">
         <v>257</v>
@@ -4581,10 +4581,10 @@
         <v>9</v>
       </c>
       <c r="D111" t="s">
+        <v>224</v>
+      </c>
+      <c r="E111" t="s">
         <v>270</v>
-      </c>
-      <c r="E111" t="s">
-        <v>225</v>
       </c>
       <c r="F111" t="s">
         <v>271</v>
@@ -4604,10 +4604,10 @@
         <v>9</v>
       </c>
       <c r="D112" t="s">
+        <v>224</v>
+      </c>
+      <c r="E112" t="s">
         <v>274</v>
-      </c>
-      <c r="E112" t="s">
-        <v>225</v>
       </c>
       <c r="F112" t="s">
         <v>275</v>
@@ -4627,10 +4627,10 @@
         <v>9</v>
       </c>
       <c r="D113" t="s">
+        <v>224</v>
+      </c>
+      <c r="E113" t="s">
         <v>278</v>
-      </c>
-      <c r="E113" t="s">
-        <v>225</v>
       </c>
       <c r="F113" t="s">
         <v>279</v>
@@ -4650,10 +4650,10 @@
         <v>9</v>
       </c>
       <c r="D114" t="s">
+        <v>224</v>
+      </c>
+      <c r="E114" t="s">
         <v>278</v>
-      </c>
-      <c r="E114" t="s">
-        <v>225</v>
       </c>
       <c r="F114" t="s">
         <v>279</v>
@@ -4673,10 +4673,10 @@
         <v>9</v>
       </c>
       <c r="D115" t="s">
+        <v>224</v>
+      </c>
+      <c r="E115" t="s">
         <v>278</v>
-      </c>
-      <c r="E115" t="s">
-        <v>225</v>
       </c>
       <c r="F115" t="s">
         <v>279</v>
@@ -4696,10 +4696,10 @@
         <v>9</v>
       </c>
       <c r="D116" t="s">
+        <v>224</v>
+      </c>
+      <c r="E116" t="s">
         <v>278</v>
-      </c>
-      <c r="E116" t="s">
-        <v>225</v>
       </c>
       <c r="F116" t="s">
         <v>279</v>
@@ -4719,10 +4719,10 @@
         <v>9</v>
       </c>
       <c r="D117" t="s">
+        <v>224</v>
+      </c>
+      <c r="E117" t="s">
         <v>278</v>
-      </c>
-      <c r="E117" t="s">
-        <v>225</v>
       </c>
       <c r="F117" t="s">
         <v>279</v>
@@ -4742,10 +4742,10 @@
         <v>9</v>
       </c>
       <c r="D118" t="s">
+        <v>224</v>
+      </c>
+      <c r="E118" t="s">
         <v>278</v>
-      </c>
-      <c r="E118" t="s">
-        <v>225</v>
       </c>
       <c r="F118" t="s">
         <v>279</v>
@@ -4765,10 +4765,10 @@
         <v>9</v>
       </c>
       <c r="D119" t="s">
+        <v>224</v>
+      </c>
+      <c r="E119" t="s">
         <v>278</v>
-      </c>
-      <c r="E119" t="s">
-        <v>225</v>
       </c>
       <c r="F119" t="s">
         <v>279</v>
@@ -4794,10 +4794,10 @@
         <v>295</v>
       </c>
       <c r="F120" t="s">
+        <v>294</v>
+      </c>
+      <c r="G120" t="s">
         <v>295</v>
-      </c>
-      <c r="G120" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4817,10 +4817,10 @@
         <v>295</v>
       </c>
       <c r="F121" t="s">
+        <v>294</v>
+      </c>
+      <c r="G121" t="s">
         <v>295</v>
-      </c>
-      <c r="G121" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4840,10 +4840,10 @@
         <v>295</v>
       </c>
       <c r="F122" t="s">
+        <v>294</v>
+      </c>
+      <c r="G122" t="s">
         <v>295</v>
-      </c>
-      <c r="G122" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4863,10 +4863,10 @@
         <v>295</v>
       </c>
       <c r="F123" t="s">
+        <v>294</v>
+      </c>
+      <c r="G123" t="s">
         <v>295</v>
-      </c>
-      <c r="G123" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4886,10 +4886,10 @@
         <v>295</v>
       </c>
       <c r="F124" t="s">
+        <v>294</v>
+      </c>
+      <c r="G124" t="s">
         <v>295</v>
-      </c>
-      <c r="G124" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4909,10 +4909,10 @@
         <v>295</v>
       </c>
       <c r="F125" t="s">
+        <v>294</v>
+      </c>
+      <c r="G125" t="s">
         <v>295</v>
-      </c>
-      <c r="G125" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4932,10 +4932,10 @@
         <v>309</v>
       </c>
       <c r="F126" t="s">
+        <v>308</v>
+      </c>
+      <c r="G126" t="s">
         <v>309</v>
-      </c>
-      <c r="G126" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4955,10 +4955,10 @@
         <v>309</v>
       </c>
       <c r="F127" t="s">
+        <v>308</v>
+      </c>
+      <c r="G127" t="s">
         <v>309</v>
-      </c>
-      <c r="G127" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4978,10 +4978,10 @@
         <v>309</v>
       </c>
       <c r="F128" t="s">
+        <v>308</v>
+      </c>
+      <c r="G128" t="s">
         <v>309</v>
-      </c>
-      <c r="G128" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -5001,10 +5001,10 @@
         <v>309</v>
       </c>
       <c r="F129" t="s">
+        <v>308</v>
+      </c>
+      <c r="G129" t="s">
         <v>309</v>
-      </c>
-      <c r="G129" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -5432,10 +5432,10 @@
         <v>9</v>
       </c>
       <c r="D148" t="s">
+        <v>318</v>
+      </c>
+      <c r="E148" t="s">
         <v>358</v>
-      </c>
-      <c r="E148" t="s">
-        <v>319</v>
       </c>
       <c r="F148" t="s">
         <v>359</v>
@@ -5455,10 +5455,10 @@
         <v>9</v>
       </c>
       <c r="D149" t="s">
+        <v>318</v>
+      </c>
+      <c r="E149" t="s">
         <v>358</v>
-      </c>
-      <c r="E149" t="s">
-        <v>319</v>
       </c>
       <c r="F149" t="s">
         <v>359</v>
@@ -5478,10 +5478,10 @@
         <v>9</v>
       </c>
       <c r="D150" t="s">
+        <v>318</v>
+      </c>
+      <c r="E150" t="s">
         <v>358</v>
-      </c>
-      <c r="E150" t="s">
-        <v>319</v>
       </c>
       <c r="F150" t="s">
         <v>359</v>
@@ -5501,10 +5501,10 @@
         <v>9</v>
       </c>
       <c r="D151" t="s">
+        <v>318</v>
+      </c>
+      <c r="E151" t="s">
         <v>358</v>
-      </c>
-      <c r="E151" t="s">
-        <v>319</v>
       </c>
       <c r="F151" t="s">
         <v>359</v>
@@ -5524,10 +5524,10 @@
         <v>9</v>
       </c>
       <c r="D152" t="s">
+        <v>318</v>
+      </c>
+      <c r="E152" t="s">
         <v>358</v>
-      </c>
-      <c r="E152" t="s">
-        <v>319</v>
       </c>
       <c r="F152" t="s">
         <v>359</v>
@@ -5547,10 +5547,10 @@
         <v>9</v>
       </c>
       <c r="D153" t="s">
+        <v>318</v>
+      </c>
+      <c r="E153" t="s">
         <v>358</v>
-      </c>
-      <c r="E153" t="s">
-        <v>319</v>
       </c>
       <c r="F153" t="s">
         <v>359</v>
@@ -5570,10 +5570,10 @@
         <v>9</v>
       </c>
       <c r="D154" t="s">
+        <v>318</v>
+      </c>
+      <c r="E154" t="s">
         <v>372</v>
-      </c>
-      <c r="E154" t="s">
-        <v>319</v>
       </c>
       <c r="F154" t="s">
         <v>373</v>
@@ -5593,10 +5593,10 @@
         <v>9</v>
       </c>
       <c r="D155" t="s">
+        <v>318</v>
+      </c>
+      <c r="E155" t="s">
         <v>372</v>
-      </c>
-      <c r="E155" t="s">
-        <v>319</v>
       </c>
       <c r="F155" t="s">
         <v>373</v>
@@ -5616,10 +5616,10 @@
         <v>9</v>
       </c>
       <c r="D156" t="s">
+        <v>318</v>
+      </c>
+      <c r="E156" t="s">
         <v>372</v>
-      </c>
-      <c r="E156" t="s">
-        <v>319</v>
       </c>
       <c r="F156" t="s">
         <v>373</v>
@@ -5639,10 +5639,10 @@
         <v>9</v>
       </c>
       <c r="D157" t="s">
+        <v>318</v>
+      </c>
+      <c r="E157" t="s">
         <v>372</v>
-      </c>
-      <c r="E157" t="s">
-        <v>319</v>
       </c>
       <c r="F157" t="s">
         <v>373</v>
@@ -5662,10 +5662,10 @@
         <v>9</v>
       </c>
       <c r="D158" t="s">
+        <v>318</v>
+      </c>
+      <c r="E158" t="s">
         <v>372</v>
-      </c>
-      <c r="E158" t="s">
-        <v>319</v>
       </c>
       <c r="F158" t="s">
         <v>373</v>
@@ -6122,10 +6122,10 @@
         <v>9</v>
       </c>
       <c r="D178" t="s">
+        <v>384</v>
+      </c>
+      <c r="E178" t="s">
         <v>426</v>
-      </c>
-      <c r="E178" t="s">
-        <v>385</v>
       </c>
       <c r="F178" t="s">
         <v>427</v>
@@ -6145,10 +6145,10 @@
         <v>9</v>
       </c>
       <c r="D179" t="s">
+        <v>384</v>
+      </c>
+      <c r="E179" t="s">
         <v>426</v>
-      </c>
-      <c r="E179" t="s">
-        <v>385</v>
       </c>
       <c r="F179" t="s">
         <v>427</v>
@@ -6168,10 +6168,10 @@
         <v>9</v>
       </c>
       <c r="D180" t="s">
+        <v>384</v>
+      </c>
+      <c r="E180" t="s">
         <v>426</v>
-      </c>
-      <c r="E180" t="s">
-        <v>385</v>
       </c>
       <c r="F180" t="s">
         <v>427</v>
@@ -6191,10 +6191,10 @@
         <v>9</v>
       </c>
       <c r="D181" t="s">
+        <v>384</v>
+      </c>
+      <c r="E181" t="s">
         <v>426</v>
-      </c>
-      <c r="E181" t="s">
-        <v>385</v>
       </c>
       <c r="F181" t="s">
         <v>427</v>
@@ -6214,10 +6214,10 @@
         <v>9</v>
       </c>
       <c r="D182" t="s">
+        <v>384</v>
+      </c>
+      <c r="E182" t="s">
         <v>426</v>
-      </c>
-      <c r="E182" t="s">
-        <v>385</v>
       </c>
       <c r="F182" t="s">
         <v>427</v>
@@ -6237,10 +6237,10 @@
         <v>9</v>
       </c>
       <c r="D183" t="s">
+        <v>384</v>
+      </c>
+      <c r="E183" t="s">
         <v>426</v>
-      </c>
-      <c r="E183" t="s">
-        <v>385</v>
       </c>
       <c r="F183" t="s">
         <v>427</v>
@@ -6260,10 +6260,10 @@
         <v>9</v>
       </c>
       <c r="D184" t="s">
+        <v>384</v>
+      </c>
+      <c r="E184" t="s">
         <v>426</v>
-      </c>
-      <c r="E184" t="s">
-        <v>385</v>
       </c>
       <c r="F184" t="s">
         <v>427</v>
@@ -6283,10 +6283,10 @@
         <v>9</v>
       </c>
       <c r="D185" t="s">
+        <v>384</v>
+      </c>
+      <c r="E185" t="s">
         <v>426</v>
-      </c>
-      <c r="E185" t="s">
-        <v>385</v>
       </c>
       <c r="F185" t="s">
         <v>427</v>
@@ -6306,10 +6306,10 @@
         <v>9</v>
       </c>
       <c r="D186" t="s">
+        <v>384</v>
+      </c>
+      <c r="E186" t="s">
         <v>426</v>
-      </c>
-      <c r="E186" t="s">
-        <v>385</v>
       </c>
       <c r="F186" t="s">
         <v>427</v>
@@ -6329,10 +6329,10 @@
         <v>9</v>
       </c>
       <c r="D187" t="s">
+        <v>384</v>
+      </c>
+      <c r="E187" t="s">
         <v>426</v>
-      </c>
-      <c r="E187" t="s">
-        <v>385</v>
       </c>
       <c r="F187" t="s">
         <v>427</v>
@@ -6352,10 +6352,10 @@
         <v>9</v>
       </c>
       <c r="D188" t="s">
+        <v>384</v>
+      </c>
+      <c r="E188" t="s">
         <v>448</v>
-      </c>
-      <c r="E188" t="s">
-        <v>385</v>
       </c>
       <c r="F188" t="s">
         <v>449</v>
@@ -6381,10 +6381,10 @@
         <v>453</v>
       </c>
       <c r="F189" t="s">
+        <v>452</v>
+      </c>
+      <c r="G189" t="s">
         <v>453</v>
-      </c>
-      <c r="G189" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6404,10 +6404,10 @@
         <v>453</v>
       </c>
       <c r="F190" t="s">
+        <v>452</v>
+      </c>
+      <c r="G190" t="s">
         <v>453</v>
-      </c>
-      <c r="G190" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6427,10 +6427,10 @@
         <v>453</v>
       </c>
       <c r="F191" t="s">
+        <v>452</v>
+      </c>
+      <c r="G191" t="s">
         <v>453</v>
-      </c>
-      <c r="G191" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6450,10 +6450,10 @@
         <v>453</v>
       </c>
       <c r="F192" t="s">
+        <v>452</v>
+      </c>
+      <c r="G192" t="s">
         <v>453</v>
-      </c>
-      <c r="G192" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6473,10 +6473,10 @@
         <v>453</v>
       </c>
       <c r="F193" t="s">
+        <v>452</v>
+      </c>
+      <c r="G193" t="s">
         <v>453</v>
-      </c>
-      <c r="G193" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6496,10 +6496,10 @@
         <v>453</v>
       </c>
       <c r="F194" t="s">
+        <v>452</v>
+      </c>
+      <c r="G194" t="s">
         <v>453</v>
-      </c>
-      <c r="G194" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6519,10 +6519,10 @@
         <v>467</v>
       </c>
       <c r="F195" t="s">
+        <v>466</v>
+      </c>
+      <c r="G195" t="s">
         <v>467</v>
-      </c>
-      <c r="G195" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6542,10 +6542,10 @@
         <v>471</v>
       </c>
       <c r="F196" t="s">
+        <v>470</v>
+      </c>
+      <c r="G196" t="s">
         <v>471</v>
-      </c>
-      <c r="G196" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6565,10 +6565,10 @@
         <v>471</v>
       </c>
       <c r="F197" t="s">
+        <v>470</v>
+      </c>
+      <c r="G197" t="s">
         <v>471</v>
-      </c>
-      <c r="G197" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6588,10 +6588,10 @@
         <v>471</v>
       </c>
       <c r="F198" t="s">
+        <v>470</v>
+      </c>
+      <c r="G198" t="s">
         <v>471</v>
-      </c>
-      <c r="G198" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6611,10 +6611,10 @@
         <v>471</v>
       </c>
       <c r="F199" t="s">
+        <v>470</v>
+      </c>
+      <c r="G199" t="s">
         <v>471</v>
-      </c>
-      <c r="G199" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6634,10 +6634,10 @@
         <v>471</v>
       </c>
       <c r="F200" t="s">
+        <v>470</v>
+      </c>
+      <c r="G200" t="s">
         <v>471</v>
-      </c>
-      <c r="G200" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6657,10 +6657,10 @@
         <v>471</v>
       </c>
       <c r="F201" t="s">
+        <v>470</v>
+      </c>
+      <c r="G201" t="s">
         <v>471</v>
-      </c>
-      <c r="G201" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6680,10 +6680,10 @@
         <v>485</v>
       </c>
       <c r="F202" t="s">
+        <v>484</v>
+      </c>
+      <c r="G202" t="s">
         <v>485</v>
-      </c>
-      <c r="G202" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6703,10 +6703,10 @@
         <v>485</v>
       </c>
       <c r="F203" t="s">
+        <v>484</v>
+      </c>
+      <c r="G203" t="s">
         <v>485</v>
-      </c>
-      <c r="G203" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6726,10 +6726,10 @@
         <v>485</v>
       </c>
       <c r="F204" t="s">
+        <v>484</v>
+      </c>
+      <c r="G204" t="s">
         <v>485</v>
-      </c>
-      <c r="G204" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6749,10 +6749,10 @@
         <v>485</v>
       </c>
       <c r="F205" t="s">
+        <v>484</v>
+      </c>
+      <c r="G205" t="s">
         <v>485</v>
-      </c>
-      <c r="G205" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6772,10 +6772,10 @@
         <v>485</v>
       </c>
       <c r="F206" t="s">
+        <v>484</v>
+      </c>
+      <c r="G206" t="s">
         <v>485</v>
-      </c>
-      <c r="G206" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6795,10 +6795,10 @@
         <v>485</v>
       </c>
       <c r="F207" t="s">
+        <v>484</v>
+      </c>
+      <c r="G207" t="s">
         <v>485</v>
-      </c>
-      <c r="G207" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6818,10 +6818,10 @@
         <v>485</v>
       </c>
       <c r="F208" t="s">
+        <v>484</v>
+      </c>
+      <c r="G208" t="s">
         <v>485</v>
-      </c>
-      <c r="G208" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6841,10 +6841,10 @@
         <v>485</v>
       </c>
       <c r="F209" t="s">
+        <v>484</v>
+      </c>
+      <c r="G209" t="s">
         <v>485</v>
-      </c>
-      <c r="G209" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6864,10 +6864,10 @@
         <v>485</v>
       </c>
       <c r="F210" t="s">
+        <v>484</v>
+      </c>
+      <c r="G210" t="s">
         <v>485</v>
-      </c>
-      <c r="G210" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6887,10 +6887,10 @@
         <v>485</v>
       </c>
       <c r="F211" t="s">
+        <v>484</v>
+      </c>
+      <c r="G211" t="s">
         <v>485</v>
-      </c>
-      <c r="G211" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6910,10 +6910,10 @@
         <v>507</v>
       </c>
       <c r="F212" t="s">
+        <v>506</v>
+      </c>
+      <c r="G212" t="s">
         <v>507</v>
-      </c>
-      <c r="G212" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6933,10 +6933,10 @@
         <v>511</v>
       </c>
       <c r="F213" t="s">
+        <v>510</v>
+      </c>
+      <c r="G213" t="s">
         <v>511</v>
-      </c>
-      <c r="G213" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6956,10 +6956,10 @@
         <v>515</v>
       </c>
       <c r="F214" t="s">
+        <v>514</v>
+      </c>
+      <c r="G214" t="s">
         <v>515</v>
-      </c>
-      <c r="G214" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6979,10 +6979,10 @@
         <v>515</v>
       </c>
       <c r="F215" t="s">
+        <v>514</v>
+      </c>
+      <c r="G215" t="s">
         <v>515</v>
-      </c>
-      <c r="G215" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -7002,10 +7002,10 @@
         <v>521</v>
       </c>
       <c r="F216" t="s">
+        <v>520</v>
+      </c>
+      <c r="G216" t="s">
         <v>521</v>
-      </c>
-      <c r="G216" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -7025,10 +7025,10 @@
         <v>521</v>
       </c>
       <c r="F217" t="s">
+        <v>520</v>
+      </c>
+      <c r="G217" t="s">
         <v>521</v>
-      </c>
-      <c r="G217" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -7048,10 +7048,10 @@
         <v>521</v>
       </c>
       <c r="F218" t="s">
+        <v>520</v>
+      </c>
+      <c r="G218" t="s">
         <v>521</v>
-      </c>
-      <c r="G218" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -7071,10 +7071,10 @@
         <v>521</v>
       </c>
       <c r="F219" t="s">
+        <v>520</v>
+      </c>
+      <c r="G219" t="s">
         <v>521</v>
-      </c>
-      <c r="G219" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -7094,10 +7094,10 @@
         <v>521</v>
       </c>
       <c r="F220" t="s">
+        <v>520</v>
+      </c>
+      <c r="G220" t="s">
         <v>521</v>
-      </c>
-      <c r="G220" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -7117,10 +7117,10 @@
         <v>521</v>
       </c>
       <c r="F221" t="s">
+        <v>520</v>
+      </c>
+      <c r="G221" t="s">
         <v>521</v>
-      </c>
-      <c r="G221" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -7140,10 +7140,10 @@
         <v>521</v>
       </c>
       <c r="F222" t="s">
+        <v>520</v>
+      </c>
+      <c r="G222" t="s">
         <v>521</v>
-      </c>
-      <c r="G222" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -7163,10 +7163,10 @@
         <v>537</v>
       </c>
       <c r="F223" t="s">
+        <v>536</v>
+      </c>
+      <c r="G223" t="s">
         <v>537</v>
-      </c>
-      <c r="G223" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -7186,10 +7186,10 @@
         <v>537</v>
       </c>
       <c r="F224" t="s">
+        <v>536</v>
+      </c>
+      <c r="G224" t="s">
         <v>537</v>
-      </c>
-      <c r="G224" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -7209,10 +7209,10 @@
         <v>537</v>
       </c>
       <c r="F225" t="s">
+        <v>536</v>
+      </c>
+      <c r="G225" t="s">
         <v>537</v>
-      </c>
-      <c r="G225" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -7232,10 +7232,10 @@
         <v>545</v>
       </c>
       <c r="F226" t="s">
+        <v>544</v>
+      </c>
+      <c r="G226" t="s">
         <v>545</v>
-      </c>
-      <c r="G226" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -7255,10 +7255,10 @@
         <v>549</v>
       </c>
       <c r="F227" t="s">
+        <v>548</v>
+      </c>
+      <c r="G227" t="s">
         <v>549</v>
-      </c>
-      <c r="G227" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -7278,10 +7278,10 @@
         <v>553</v>
       </c>
       <c r="F228" t="s">
+        <v>552</v>
+      </c>
+      <c r="G228" t="s">
         <v>553</v>
-      </c>
-      <c r="G228" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -7301,10 +7301,10 @@
         <v>557</v>
       </c>
       <c r="F229" t="s">
+        <v>556</v>
+      </c>
+      <c r="G229" t="s">
         <v>557</v>
-      </c>
-      <c r="G229" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -7324,10 +7324,10 @@
         <v>561</v>
       </c>
       <c r="F230" t="s">
+        <v>560</v>
+      </c>
+      <c r="G230" t="s">
         <v>561</v>
-      </c>
-      <c r="G230" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -7347,10 +7347,10 @@
         <v>561</v>
       </c>
       <c r="F231" t="s">
+        <v>560</v>
+      </c>
+      <c r="G231" t="s">
         <v>561</v>
-      </c>
-      <c r="G231" t="s">
-        <v>560</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/en/SectorGroup.xlsx
+++ b/api/xlsx/en/SectorGroup.xlsx
@@ -25,15 +25,15 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
+    <t>codeforiati:category-name</t>
+  </si>
+  <si>
     <t>codeforiati:group-name</t>
   </si>
   <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
-    <t>codeforiati:category-name</t>
-  </si>
-  <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
@@ -46,15 +46,15 @@
     <t>active</t>
   </si>
   <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>Education, Level Unspecified</t>
+  </si>
+  <si>
     <t>Education</t>
   </si>
   <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>Education, Level Unspecified</t>
-  </si>
-  <si>
     <t>110</t>
   </si>
   <si>
@@ -148,15 +148,15 @@
     <t>Health policy and administrative management</t>
   </si>
   <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>Health, General</t>
+  </si>
+  <si>
     <t>Health</t>
   </si>
   <si>
-    <t>121</t>
-  </si>
-  <si>
-    <t>Health, General</t>
-  </si>
-  <si>
     <t>120</t>
   </si>
   <si>
@@ -280,12 +280,12 @@
     <t>Population policy and administrative management</t>
   </si>
   <si>
+    <t>130</t>
+  </si>
+  <si>
     <t>Population Policies/Programmes &amp; Reproductive Health</t>
   </si>
   <si>
-    <t>130</t>
-  </si>
-  <si>
     <t>13020</t>
   </si>
   <si>
@@ -316,12 +316,12 @@
     <t>Water sector policy and administrative management</t>
   </si>
   <si>
+    <t>140</t>
+  </si>
+  <si>
     <t>Water Supply &amp; Sanitation</t>
   </si>
   <si>
-    <t>140</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -388,15 +388,15 @@
     <t>Public sector policy and administrative management</t>
   </si>
   <si>
+    <t>151</t>
+  </si>
+  <si>
+    <t>Government &amp; Civil Society-general</t>
+  </si>
+  <si>
     <t>Government &amp; Civil Society</t>
   </si>
   <si>
-    <t>151</t>
-  </si>
-  <si>
-    <t>Government &amp; Civil Society-general</t>
-  </si>
-  <si>
     <t>150</t>
   </si>
   <si>
@@ -538,12 +538,12 @@
     <t>Social Protection</t>
   </si>
   <si>
+    <t>160</t>
+  </si>
+  <si>
     <t>Other Social Infrastructure &amp; Services</t>
   </si>
   <si>
-    <t>160</t>
-  </si>
-  <si>
     <t>16020</t>
   </si>
   <si>
@@ -610,12 +610,12 @@
     <t>Transport policy and administrative management</t>
   </si>
   <si>
+    <t>210</t>
+  </si>
+  <si>
     <t>Transport &amp; Storage</t>
   </si>
   <si>
-    <t>210</t>
-  </si>
-  <si>
     <t>21020</t>
   </si>
   <si>
@@ -658,12 +658,12 @@
     <t>Communications policy and administrative management</t>
   </si>
   <si>
+    <t>220</t>
+  </si>
+  <si>
     <t>Communications</t>
   </si>
   <si>
-    <t>220</t>
-  </si>
-  <si>
     <t>22020</t>
   </si>
   <si>
@@ -688,15 +688,15 @@
     <t>Energy policy and administrative management</t>
   </si>
   <si>
+    <t>231</t>
+  </si>
+  <si>
+    <t>Energy Policy</t>
+  </si>
+  <si>
     <t>Energy</t>
   </si>
   <si>
-    <t>231</t>
-  </si>
-  <si>
-    <t>Energy Policy</t>
-  </si>
-  <si>
     <t>230</t>
   </si>
   <si>
@@ -898,12 +898,12 @@
     <t>Financial policy and administrative management</t>
   </si>
   <si>
+    <t>240</t>
+  </si>
+  <si>
     <t>Banking &amp; Financial Services</t>
   </si>
   <si>
-    <t>240</t>
-  </si>
-  <si>
     <t>24020</t>
   </si>
   <si>
@@ -940,12 +940,12 @@
     <t>Business policy and administration</t>
   </si>
   <si>
+    <t>250</t>
+  </si>
+  <si>
     <t>Business &amp; Other Services</t>
   </si>
   <si>
-    <t>250</t>
-  </si>
-  <si>
     <t>25020</t>
   </si>
   <si>
@@ -970,15 +970,15 @@
     <t>Agricultural policy and administrative management</t>
   </si>
   <si>
+    <t>311</t>
+  </si>
+  <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
     <t>Agriculture, Forestry, Fishing</t>
   </si>
   <si>
-    <t>311</t>
-  </si>
-  <si>
-    <t>Agriculture</t>
-  </si>
-  <si>
     <t>310</t>
   </si>
   <si>
@@ -1168,15 +1168,15 @@
     <t>Industrial policy and administrative management</t>
   </si>
   <si>
+    <t>321</t>
+  </si>
+  <si>
+    <t>Industry</t>
+  </si>
+  <si>
     <t>Industry, Mining, Construction</t>
   </si>
   <si>
-    <t>321</t>
-  </si>
-  <si>
-    <t>Industry</t>
-  </si>
-  <si>
     <t>320</t>
   </si>
   <si>
@@ -1372,12 +1372,12 @@
     <t>Trade policy and administrative management</t>
   </si>
   <si>
+    <t>331</t>
+  </si>
+  <si>
     <t>Trade Policies &amp; Regulations</t>
   </si>
   <si>
-    <t>331</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1414,24 +1414,24 @@
     <t>Tourism policy and administrative management</t>
   </si>
   <si>
+    <t>332</t>
+  </si>
+  <si>
     <t>Tourism</t>
   </si>
   <si>
-    <t>332</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
     <t>Environmental policy and administrative management</t>
   </si>
   <si>
+    <t>410</t>
+  </si>
+  <si>
     <t>General Environment Protection</t>
   </si>
   <si>
-    <t>410</t>
-  </si>
-  <si>
     <t>41020</t>
   </si>
   <si>
@@ -1468,12 +1468,12 @@
     <t>Multisector aid</t>
   </si>
   <si>
+    <t>430</t>
+  </si>
+  <si>
     <t>Other Multisector</t>
   </si>
   <si>
-    <t>430</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -1534,36 +1534,36 @@
     <t>General budget support-related aid</t>
   </si>
   <si>
+    <t>510</t>
+  </si>
+  <si>
     <t>General Budget Support</t>
   </si>
   <si>
-    <t>510</t>
-  </si>
-  <si>
     <t>52010</t>
   </si>
   <si>
     <t>Food assistance</t>
   </si>
   <si>
+    <t>520</t>
+  </si>
+  <si>
     <t>Development Food Assistance</t>
   </si>
   <si>
-    <t>520</t>
-  </si>
-  <si>
     <t>53030</t>
   </si>
   <si>
     <t>Import support (capital goods)</t>
   </si>
   <si>
+    <t>530</t>
+  </si>
+  <si>
     <t>Other Commodity Assistance</t>
   </si>
   <si>
-    <t>530</t>
-  </si>
-  <si>
     <t>53040</t>
   </si>
   <si>
@@ -1576,12 +1576,12 @@
     <t>Action relating to debt</t>
   </si>
   <si>
+    <t>600</t>
+  </si>
+  <si>
     <t>Action Relating to Debt</t>
   </si>
   <si>
-    <t>600</t>
-  </si>
-  <si>
     <t>60020</t>
   </si>
   <si>
@@ -1624,12 +1624,12 @@
     <t>Material relief assistance and services</t>
   </si>
   <si>
+    <t>720</t>
+  </si>
+  <si>
     <t>Emergency Response</t>
   </si>
   <si>
-    <t>720</t>
-  </si>
-  <si>
     <t>72040</t>
   </si>
   <si>
@@ -1648,58 +1648,58 @@
     <t>Immediate post-emergency reconstruction and rehabilitation</t>
   </si>
   <si>
+    <t>730</t>
+  </si>
+  <si>
     <t>Reconstruction Relief &amp; Rehabilitation</t>
   </si>
   <si>
-    <t>730</t>
-  </si>
-  <si>
     <t>74020</t>
   </si>
   <si>
     <t>Multi-hazard response preparedness</t>
   </si>
   <si>
+    <t>740</t>
+  </si>
+  <si>
     <t>Disaster Prevention &amp; Preparedness</t>
   </si>
   <si>
-    <t>740</t>
-  </si>
-  <si>
     <t>91010</t>
   </si>
   <si>
     <t>Administrative costs (non-sector allocable)</t>
   </si>
   <si>
+    <t>910</t>
+  </si>
+  <si>
     <t>Administrative Costs of Donors</t>
   </si>
   <si>
-    <t>910</t>
-  </si>
-  <si>
     <t>93010</t>
   </si>
   <si>
     <t>Refugees/asylum seekers in donor countries (non-sector allocable)</t>
   </si>
   <si>
+    <t>930</t>
+  </si>
+  <si>
     <t>Refugees in Donor Countries</t>
   </si>
   <si>
-    <t>930</t>
-  </si>
-  <si>
     <t>99810</t>
   </si>
   <si>
     <t>Sectors not specified</t>
   </si>
   <si>
+    <t>998</t>
+  </si>
+  <si>
     <t>Unallocated / Unspecified</t>
-  </si>
-  <si>
-    <t>998</t>
   </si>
   <si>
     <t>99820</t>
@@ -2166,13 +2166,13 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F6" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G6" t="s">
         <v>13</v>
@@ -2189,13 +2189,13 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F7" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G7" t="s">
         <v>13</v>
@@ -2212,13 +2212,13 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F8" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G8" t="s">
         <v>13</v>
@@ -2235,13 +2235,13 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F9" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G9" t="s">
         <v>13</v>
@@ -2258,13 +2258,13 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F10" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="G10" t="s">
         <v>13</v>
@@ -2281,13 +2281,13 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F11" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="G11" t="s">
         <v>13</v>
@@ -2304,13 +2304,13 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F12" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="G12" t="s">
         <v>13</v>
@@ -2327,13 +2327,13 @@
         <v>9</v>
       </c>
       <c r="D13" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F13" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="G13" t="s">
         <v>13</v>
@@ -2442,13 +2442,13 @@
         <v>9</v>
       </c>
       <c r="D18" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E18" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F18" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G18" t="s">
         <v>47</v>
@@ -2465,13 +2465,13 @@
         <v>9</v>
       </c>
       <c r="D19" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F19" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G19" t="s">
         <v>47</v>
@@ -2488,13 +2488,13 @@
         <v>9</v>
       </c>
       <c r="D20" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E20" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F20" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G20" t="s">
         <v>47</v>
@@ -2511,13 +2511,13 @@
         <v>9</v>
       </c>
       <c r="D21" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E21" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F21" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G21" t="s">
         <v>47</v>
@@ -2534,13 +2534,13 @@
         <v>9</v>
       </c>
       <c r="D22" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E22" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F22" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G22" t="s">
         <v>47</v>
@@ -2557,13 +2557,13 @@
         <v>9</v>
       </c>
       <c r="D23" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E23" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F23" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G23" t="s">
         <v>47</v>
@@ -2580,13 +2580,13 @@
         <v>9</v>
       </c>
       <c r="D24" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F24" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G24" t="s">
         <v>47</v>
@@ -2603,13 +2603,13 @@
         <v>9</v>
       </c>
       <c r="D25" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E25" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F25" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G25" t="s">
         <v>47</v>
@@ -2626,13 +2626,13 @@
         <v>9</v>
       </c>
       <c r="D26" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E26" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F26" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="G26" t="s">
         <v>47</v>
@@ -2649,13 +2649,13 @@
         <v>9</v>
       </c>
       <c r="D27" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E27" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F27" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="G27" t="s">
         <v>47</v>
@@ -2672,13 +2672,13 @@
         <v>9</v>
       </c>
       <c r="D28" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E28" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F28" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="G28" t="s">
         <v>47</v>
@@ -2695,13 +2695,13 @@
         <v>9</v>
       </c>
       <c r="D29" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E29" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F29" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="G29" t="s">
         <v>47</v>
@@ -2718,13 +2718,13 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E30" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F30" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="G30" t="s">
         <v>47</v>
@@ -2741,13 +2741,13 @@
         <v>9</v>
       </c>
       <c r="D31" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E31" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F31" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="G31" t="s">
         <v>47</v>
@@ -2770,10 +2770,10 @@
         <v>89</v>
       </c>
       <c r="F32" t="s">
+        <v>89</v>
+      </c>
+      <c r="G32" t="s">
         <v>88</v>
-      </c>
-      <c r="G32" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2793,10 +2793,10 @@
         <v>89</v>
       </c>
       <c r="F33" t="s">
+        <v>89</v>
+      </c>
+      <c r="G33" t="s">
         <v>88</v>
-      </c>
-      <c r="G33" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2816,10 +2816,10 @@
         <v>89</v>
       </c>
       <c r="F34" t="s">
+        <v>89</v>
+      </c>
+      <c r="G34" t="s">
         <v>88</v>
-      </c>
-      <c r="G34" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2839,10 +2839,10 @@
         <v>89</v>
       </c>
       <c r="F35" t="s">
+        <v>89</v>
+      </c>
+      <c r="G35" t="s">
         <v>88</v>
-      </c>
-      <c r="G35" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2862,10 +2862,10 @@
         <v>89</v>
       </c>
       <c r="F36" t="s">
+        <v>89</v>
+      </c>
+      <c r="G36" t="s">
         <v>88</v>
-      </c>
-      <c r="G36" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2885,10 +2885,10 @@
         <v>101</v>
       </c>
       <c r="F37" t="s">
+        <v>101</v>
+      </c>
+      <c r="G37" t="s">
         <v>100</v>
-      </c>
-      <c r="G37" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2908,10 +2908,10 @@
         <v>101</v>
       </c>
       <c r="F38" t="s">
+        <v>101</v>
+      </c>
+      <c r="G38" t="s">
         <v>100</v>
-      </c>
-      <c r="G38" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2931,10 +2931,10 @@
         <v>101</v>
       </c>
       <c r="F39" t="s">
+        <v>101</v>
+      </c>
+      <c r="G39" t="s">
         <v>100</v>
-      </c>
-      <c r="G39" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2954,10 +2954,10 @@
         <v>101</v>
       </c>
       <c r="F40" t="s">
+        <v>101</v>
+      </c>
+      <c r="G40" t="s">
         <v>100</v>
-      </c>
-      <c r="G40" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2977,10 +2977,10 @@
         <v>101</v>
       </c>
       <c r="F41" t="s">
+        <v>101</v>
+      </c>
+      <c r="G41" t="s">
         <v>100</v>
-      </c>
-      <c r="G41" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -3000,10 +3000,10 @@
         <v>101</v>
       </c>
       <c r="F42" t="s">
+        <v>101</v>
+      </c>
+      <c r="G42" t="s">
         <v>100</v>
-      </c>
-      <c r="G42" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3023,10 +3023,10 @@
         <v>101</v>
       </c>
       <c r="F43" t="s">
+        <v>101</v>
+      </c>
+      <c r="G43" t="s">
         <v>100</v>
-      </c>
-      <c r="G43" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3046,10 +3046,10 @@
         <v>101</v>
       </c>
       <c r="F44" t="s">
+        <v>101</v>
+      </c>
+      <c r="G44" t="s">
         <v>100</v>
-      </c>
-      <c r="G44" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3069,10 +3069,10 @@
         <v>101</v>
       </c>
       <c r="F45" t="s">
+        <v>101</v>
+      </c>
+      <c r="G45" t="s">
         <v>100</v>
-      </c>
-      <c r="G45" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3092,10 +3092,10 @@
         <v>101</v>
       </c>
       <c r="F46" t="s">
+        <v>101</v>
+      </c>
+      <c r="G46" t="s">
         <v>100</v>
-      </c>
-      <c r="G46" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3115,10 +3115,10 @@
         <v>101</v>
       </c>
       <c r="F47" t="s">
+        <v>101</v>
+      </c>
+      <c r="G47" t="s">
         <v>100</v>
-      </c>
-      <c r="G47" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3500,13 +3500,13 @@
         <v>9</v>
       </c>
       <c r="D64" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E64" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F64" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="G64" t="s">
         <v>127</v>
@@ -3523,13 +3523,13 @@
         <v>9</v>
       </c>
       <c r="D65" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E65" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F65" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="G65" t="s">
         <v>127</v>
@@ -3546,13 +3546,13 @@
         <v>9</v>
       </c>
       <c r="D66" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E66" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F66" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="G66" t="s">
         <v>127</v>
@@ -3569,13 +3569,13 @@
         <v>9</v>
       </c>
       <c r="D67" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E67" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F67" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="G67" t="s">
         <v>127</v>
@@ -3592,13 +3592,13 @@
         <v>9</v>
       </c>
       <c r="D68" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E68" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F68" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="G68" t="s">
         <v>127</v>
@@ -3615,13 +3615,13 @@
         <v>9</v>
       </c>
       <c r="D69" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E69" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F69" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="G69" t="s">
         <v>127</v>
@@ -3644,10 +3644,10 @@
         <v>175</v>
       </c>
       <c r="F70" t="s">
+        <v>175</v>
+      </c>
+      <c r="G70" t="s">
         <v>174</v>
-      </c>
-      <c r="G70" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3667,10 +3667,10 @@
         <v>175</v>
       </c>
       <c r="F71" t="s">
+        <v>175</v>
+      </c>
+      <c r="G71" t="s">
         <v>174</v>
-      </c>
-      <c r="G71" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3690,10 +3690,10 @@
         <v>175</v>
       </c>
       <c r="F72" t="s">
+        <v>175</v>
+      </c>
+      <c r="G72" t="s">
         <v>174</v>
-      </c>
-      <c r="G72" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3713,10 +3713,10 @@
         <v>175</v>
       </c>
       <c r="F73" t="s">
+        <v>175</v>
+      </c>
+      <c r="G73" t="s">
         <v>174</v>
-      </c>
-      <c r="G73" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3736,10 +3736,10 @@
         <v>175</v>
       </c>
       <c r="F74" t="s">
+        <v>175</v>
+      </c>
+      <c r="G74" t="s">
         <v>174</v>
-      </c>
-      <c r="G74" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3759,10 +3759,10 @@
         <v>175</v>
       </c>
       <c r="F75" t="s">
+        <v>175</v>
+      </c>
+      <c r="G75" t="s">
         <v>174</v>
-      </c>
-      <c r="G75" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3782,10 +3782,10 @@
         <v>175</v>
       </c>
       <c r="F76" t="s">
+        <v>175</v>
+      </c>
+      <c r="G76" t="s">
         <v>174</v>
-      </c>
-      <c r="G76" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3805,10 +3805,10 @@
         <v>175</v>
       </c>
       <c r="F77" t="s">
+        <v>175</v>
+      </c>
+      <c r="G77" t="s">
         <v>174</v>
-      </c>
-      <c r="G77" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3828,10 +3828,10 @@
         <v>175</v>
       </c>
       <c r="F78" t="s">
+        <v>175</v>
+      </c>
+      <c r="G78" t="s">
         <v>174</v>
-      </c>
-      <c r="G78" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3851,10 +3851,10 @@
         <v>175</v>
       </c>
       <c r="F79" t="s">
+        <v>175</v>
+      </c>
+      <c r="G79" t="s">
         <v>174</v>
-      </c>
-      <c r="G79" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3874,10 +3874,10 @@
         <v>175</v>
       </c>
       <c r="F80" t="s">
+        <v>175</v>
+      </c>
+      <c r="G80" t="s">
         <v>174</v>
-      </c>
-      <c r="G80" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3897,10 +3897,10 @@
         <v>199</v>
       </c>
       <c r="F81" t="s">
+        <v>199</v>
+      </c>
+      <c r="G81" t="s">
         <v>198</v>
-      </c>
-      <c r="G81" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3920,10 +3920,10 @@
         <v>199</v>
       </c>
       <c r="F82" t="s">
+        <v>199</v>
+      </c>
+      <c r="G82" t="s">
         <v>198</v>
-      </c>
-      <c r="G82" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3943,10 +3943,10 @@
         <v>199</v>
       </c>
       <c r="F83" t="s">
+        <v>199</v>
+      </c>
+      <c r="G83" t="s">
         <v>198</v>
-      </c>
-      <c r="G83" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3966,10 +3966,10 @@
         <v>199</v>
       </c>
       <c r="F84" t="s">
+        <v>199</v>
+      </c>
+      <c r="G84" t="s">
         <v>198</v>
-      </c>
-      <c r="G84" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3989,10 +3989,10 @@
         <v>199</v>
       </c>
       <c r="F85" t="s">
+        <v>199</v>
+      </c>
+      <c r="G85" t="s">
         <v>198</v>
-      </c>
-      <c r="G85" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4012,10 +4012,10 @@
         <v>199</v>
       </c>
       <c r="F86" t="s">
+        <v>199</v>
+      </c>
+      <c r="G86" t="s">
         <v>198</v>
-      </c>
-      <c r="G86" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4035,10 +4035,10 @@
         <v>199</v>
       </c>
       <c r="F87" t="s">
+        <v>199</v>
+      </c>
+      <c r="G87" t="s">
         <v>198</v>
-      </c>
-      <c r="G87" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4058,10 +4058,10 @@
         <v>215</v>
       </c>
       <c r="F88" t="s">
+        <v>215</v>
+      </c>
+      <c r="G88" t="s">
         <v>214</v>
-      </c>
-      <c r="G88" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4081,10 +4081,10 @@
         <v>215</v>
       </c>
       <c r="F89" t="s">
+        <v>215</v>
+      </c>
+      <c r="G89" t="s">
         <v>214</v>
-      </c>
-      <c r="G89" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4104,10 +4104,10 @@
         <v>215</v>
       </c>
       <c r="F90" t="s">
+        <v>215</v>
+      </c>
+      <c r="G90" t="s">
         <v>214</v>
-      </c>
-      <c r="G90" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4127,10 +4127,10 @@
         <v>215</v>
       </c>
       <c r="F91" t="s">
+        <v>215</v>
+      </c>
+      <c r="G91" t="s">
         <v>214</v>
-      </c>
-      <c r="G91" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4236,13 +4236,13 @@
         <v>9</v>
       </c>
       <c r="D96" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E96" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F96" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G96" t="s">
         <v>227</v>
@@ -4259,13 +4259,13 @@
         <v>9</v>
       </c>
       <c r="D97" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E97" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F97" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G97" t="s">
         <v>227</v>
@@ -4282,13 +4282,13 @@
         <v>9</v>
       </c>
       <c r="D98" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E98" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F98" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G98" t="s">
         <v>227</v>
@@ -4305,13 +4305,13 @@
         <v>9</v>
       </c>
       <c r="D99" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E99" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F99" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G99" t="s">
         <v>227</v>
@@ -4328,13 +4328,13 @@
         <v>9</v>
       </c>
       <c r="D100" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E100" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F100" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G100" t="s">
         <v>227</v>
@@ -4351,13 +4351,13 @@
         <v>9</v>
       </c>
       <c r="D101" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E101" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F101" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G101" t="s">
         <v>227</v>
@@ -4374,13 +4374,13 @@
         <v>9</v>
       </c>
       <c r="D102" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E102" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F102" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G102" t="s">
         <v>227</v>
@@ -4397,13 +4397,13 @@
         <v>9</v>
       </c>
       <c r="D103" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E103" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F103" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G103" t="s">
         <v>227</v>
@@ -4420,13 +4420,13 @@
         <v>9</v>
       </c>
       <c r="D104" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E104" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F104" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G104" t="s">
         <v>227</v>
@@ -4443,13 +4443,13 @@
         <v>9</v>
       </c>
       <c r="D105" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E105" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F105" t="s">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="G105" t="s">
         <v>227</v>
@@ -4466,13 +4466,13 @@
         <v>9</v>
       </c>
       <c r="D106" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E106" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F106" t="s">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="G106" t="s">
         <v>227</v>
@@ -4489,13 +4489,13 @@
         <v>9</v>
       </c>
       <c r="D107" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E107" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F107" t="s">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="G107" t="s">
         <v>227</v>
@@ -4512,13 +4512,13 @@
         <v>9</v>
       </c>
       <c r="D108" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E108" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F108" t="s">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="G108" t="s">
         <v>227</v>
@@ -4535,13 +4535,13 @@
         <v>9</v>
       </c>
       <c r="D109" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E109" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F109" t="s">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="G109" t="s">
         <v>227</v>
@@ -4558,13 +4558,13 @@
         <v>9</v>
       </c>
       <c r="D110" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E110" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F110" t="s">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="G110" t="s">
         <v>227</v>
@@ -4581,13 +4581,13 @@
         <v>9</v>
       </c>
       <c r="D111" t="s">
-        <v>224</v>
+        <v>270</v>
       </c>
       <c r="E111" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F111" t="s">
-        <v>271</v>
+        <v>226</v>
       </c>
       <c r="G111" t="s">
         <v>227</v>
@@ -4604,13 +4604,13 @@
         <v>9</v>
       </c>
       <c r="D112" t="s">
-        <v>224</v>
+        <v>274</v>
       </c>
       <c r="E112" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F112" t="s">
-        <v>275</v>
+        <v>226</v>
       </c>
       <c r="G112" t="s">
         <v>227</v>
@@ -4627,13 +4627,13 @@
         <v>9</v>
       </c>
       <c r="D113" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E113" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F113" t="s">
-        <v>279</v>
+        <v>226</v>
       </c>
       <c r="G113" t="s">
         <v>227</v>
@@ -4650,13 +4650,13 @@
         <v>9</v>
       </c>
       <c r="D114" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E114" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F114" t="s">
-        <v>279</v>
+        <v>226</v>
       </c>
       <c r="G114" t="s">
         <v>227</v>
@@ -4673,13 +4673,13 @@
         <v>9</v>
       </c>
       <c r="D115" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E115" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F115" t="s">
-        <v>279</v>
+        <v>226</v>
       </c>
       <c r="G115" t="s">
         <v>227</v>
@@ -4696,13 +4696,13 @@
         <v>9</v>
       </c>
       <c r="D116" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E116" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F116" t="s">
-        <v>279</v>
+        <v>226</v>
       </c>
       <c r="G116" t="s">
         <v>227</v>
@@ -4719,13 +4719,13 @@
         <v>9</v>
       </c>
       <c r="D117" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E117" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F117" t="s">
-        <v>279</v>
+        <v>226</v>
       </c>
       <c r="G117" t="s">
         <v>227</v>
@@ -4742,13 +4742,13 @@
         <v>9</v>
       </c>
       <c r="D118" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E118" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F118" t="s">
-        <v>279</v>
+        <v>226</v>
       </c>
       <c r="G118" t="s">
         <v>227</v>
@@ -4765,13 +4765,13 @@
         <v>9</v>
       </c>
       <c r="D119" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E119" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F119" t="s">
-        <v>279</v>
+        <v>226</v>
       </c>
       <c r="G119" t="s">
         <v>227</v>
@@ -4794,10 +4794,10 @@
         <v>295</v>
       </c>
       <c r="F120" t="s">
+        <v>295</v>
+      </c>
+      <c r="G120" t="s">
         <v>294</v>
-      </c>
-      <c r="G120" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4817,10 +4817,10 @@
         <v>295</v>
       </c>
       <c r="F121" t="s">
+        <v>295</v>
+      </c>
+      <c r="G121" t="s">
         <v>294</v>
-      </c>
-      <c r="G121" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4840,10 +4840,10 @@
         <v>295</v>
       </c>
       <c r="F122" t="s">
+        <v>295</v>
+      </c>
+      <c r="G122" t="s">
         <v>294</v>
-      </c>
-      <c r="G122" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4863,10 +4863,10 @@
         <v>295</v>
       </c>
       <c r="F123" t="s">
+        <v>295</v>
+      </c>
+      <c r="G123" t="s">
         <v>294</v>
-      </c>
-      <c r="G123" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4886,10 +4886,10 @@
         <v>295</v>
       </c>
       <c r="F124" t="s">
+        <v>295</v>
+      </c>
+      <c r="G124" t="s">
         <v>294</v>
-      </c>
-      <c r="G124" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4909,10 +4909,10 @@
         <v>295</v>
       </c>
       <c r="F125" t="s">
+        <v>295</v>
+      </c>
+      <c r="G125" t="s">
         <v>294</v>
-      </c>
-      <c r="G125" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4932,10 +4932,10 @@
         <v>309</v>
       </c>
       <c r="F126" t="s">
+        <v>309</v>
+      </c>
+      <c r="G126" t="s">
         <v>308</v>
-      </c>
-      <c r="G126" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4955,10 +4955,10 @@
         <v>309</v>
       </c>
       <c r="F127" t="s">
+        <v>309</v>
+      </c>
+      <c r="G127" t="s">
         <v>308</v>
-      </c>
-      <c r="G127" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4978,10 +4978,10 @@
         <v>309</v>
       </c>
       <c r="F128" t="s">
+        <v>309</v>
+      </c>
+      <c r="G128" t="s">
         <v>308</v>
-      </c>
-      <c r="G128" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -5001,10 +5001,10 @@
         <v>309</v>
       </c>
       <c r="F129" t="s">
+        <v>309</v>
+      </c>
+      <c r="G129" t="s">
         <v>308</v>
-      </c>
-      <c r="G129" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -5432,13 +5432,13 @@
         <v>9</v>
       </c>
       <c r="D148" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E148" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F148" t="s">
-        <v>359</v>
+        <v>320</v>
       </c>
       <c r="G148" t="s">
         <v>321</v>
@@ -5455,13 +5455,13 @@
         <v>9</v>
       </c>
       <c r="D149" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E149" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F149" t="s">
-        <v>359</v>
+        <v>320</v>
       </c>
       <c r="G149" t="s">
         <v>321</v>
@@ -5478,13 +5478,13 @@
         <v>9</v>
       </c>
       <c r="D150" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E150" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F150" t="s">
-        <v>359</v>
+        <v>320</v>
       </c>
       <c r="G150" t="s">
         <v>321</v>
@@ -5501,13 +5501,13 @@
         <v>9</v>
       </c>
       <c r="D151" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E151" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F151" t="s">
-        <v>359</v>
+        <v>320</v>
       </c>
       <c r="G151" t="s">
         <v>321</v>
@@ -5524,13 +5524,13 @@
         <v>9</v>
       </c>
       <c r="D152" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E152" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F152" t="s">
-        <v>359</v>
+        <v>320</v>
       </c>
       <c r="G152" t="s">
         <v>321</v>
@@ -5547,13 +5547,13 @@
         <v>9</v>
       </c>
       <c r="D153" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E153" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F153" t="s">
-        <v>359</v>
+        <v>320</v>
       </c>
       <c r="G153" t="s">
         <v>321</v>
@@ -5570,13 +5570,13 @@
         <v>9</v>
       </c>
       <c r="D154" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="E154" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F154" t="s">
-        <v>373</v>
+        <v>320</v>
       </c>
       <c r="G154" t="s">
         <v>321</v>
@@ -5593,13 +5593,13 @@
         <v>9</v>
       </c>
       <c r="D155" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="E155" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F155" t="s">
-        <v>373</v>
+        <v>320</v>
       </c>
       <c r="G155" t="s">
         <v>321</v>
@@ -5616,13 +5616,13 @@
         <v>9</v>
       </c>
       <c r="D156" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="E156" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F156" t="s">
-        <v>373</v>
+        <v>320</v>
       </c>
       <c r="G156" t="s">
         <v>321</v>
@@ -5639,13 +5639,13 @@
         <v>9</v>
       </c>
       <c r="D157" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="E157" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F157" t="s">
-        <v>373</v>
+        <v>320</v>
       </c>
       <c r="G157" t="s">
         <v>321</v>
@@ -5662,13 +5662,13 @@
         <v>9</v>
       </c>
       <c r="D158" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="E158" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F158" t="s">
-        <v>373</v>
+        <v>320</v>
       </c>
       <c r="G158" t="s">
         <v>321</v>
@@ -6122,13 +6122,13 @@
         <v>9</v>
       </c>
       <c r="D178" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E178" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F178" t="s">
-        <v>427</v>
+        <v>386</v>
       </c>
       <c r="G178" t="s">
         <v>387</v>
@@ -6145,13 +6145,13 @@
         <v>9</v>
       </c>
       <c r="D179" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E179" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F179" t="s">
-        <v>427</v>
+        <v>386</v>
       </c>
       <c r="G179" t="s">
         <v>387</v>
@@ -6168,13 +6168,13 @@
         <v>9</v>
       </c>
       <c r="D180" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E180" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F180" t="s">
-        <v>427</v>
+        <v>386</v>
       </c>
       <c r="G180" t="s">
         <v>387</v>
@@ -6191,13 +6191,13 @@
         <v>9</v>
       </c>
       <c r="D181" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E181" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F181" t="s">
-        <v>427</v>
+        <v>386</v>
       </c>
       <c r="G181" t="s">
         <v>387</v>
@@ -6214,13 +6214,13 @@
         <v>9</v>
       </c>
       <c r="D182" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E182" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F182" t="s">
-        <v>427</v>
+        <v>386</v>
       </c>
       <c r="G182" t="s">
         <v>387</v>
@@ -6237,13 +6237,13 @@
         <v>9</v>
       </c>
       <c r="D183" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E183" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F183" t="s">
-        <v>427</v>
+        <v>386</v>
       </c>
       <c r="G183" t="s">
         <v>387</v>
@@ -6260,13 +6260,13 @@
         <v>9</v>
       </c>
       <c r="D184" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E184" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F184" t="s">
-        <v>427</v>
+        <v>386</v>
       </c>
       <c r="G184" t="s">
         <v>387</v>
@@ -6283,13 +6283,13 @@
         <v>9</v>
       </c>
       <c r="D185" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E185" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F185" t="s">
-        <v>427</v>
+        <v>386</v>
       </c>
       <c r="G185" t="s">
         <v>387</v>
@@ -6306,13 +6306,13 @@
         <v>9</v>
       </c>
       <c r="D186" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E186" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F186" t="s">
-        <v>427</v>
+        <v>386</v>
       </c>
       <c r="G186" t="s">
         <v>387</v>
@@ -6329,13 +6329,13 @@
         <v>9</v>
       </c>
       <c r="D187" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E187" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F187" t="s">
-        <v>427</v>
+        <v>386</v>
       </c>
       <c r="G187" t="s">
         <v>387</v>
@@ -6352,13 +6352,13 @@
         <v>9</v>
       </c>
       <c r="D188" t="s">
-        <v>384</v>
+        <v>448</v>
       </c>
       <c r="E188" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F188" t="s">
-        <v>449</v>
+        <v>386</v>
       </c>
       <c r="G188" t="s">
         <v>387</v>
@@ -6381,10 +6381,10 @@
         <v>453</v>
       </c>
       <c r="F189" t="s">
+        <v>453</v>
+      </c>
+      <c r="G189" t="s">
         <v>452</v>
-      </c>
-      <c r="G189" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6404,10 +6404,10 @@
         <v>453</v>
       </c>
       <c r="F190" t="s">
+        <v>453</v>
+      </c>
+      <c r="G190" t="s">
         <v>452</v>
-      </c>
-      <c r="G190" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6427,10 +6427,10 @@
         <v>453</v>
       </c>
       <c r="F191" t="s">
+        <v>453</v>
+      </c>
+      <c r="G191" t="s">
         <v>452</v>
-      </c>
-      <c r="G191" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6450,10 +6450,10 @@
         <v>453</v>
       </c>
       <c r="F192" t="s">
+        <v>453</v>
+      </c>
+      <c r="G192" t="s">
         <v>452</v>
-      </c>
-      <c r="G192" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6473,10 +6473,10 @@
         <v>453</v>
       </c>
       <c r="F193" t="s">
+        <v>453</v>
+      </c>
+      <c r="G193" t="s">
         <v>452</v>
-      </c>
-      <c r="G193" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6496,10 +6496,10 @@
         <v>453</v>
       </c>
       <c r="F194" t="s">
+        <v>453</v>
+      </c>
+      <c r="G194" t="s">
         <v>452</v>
-      </c>
-      <c r="G194" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6519,10 +6519,10 @@
         <v>467</v>
       </c>
       <c r="F195" t="s">
+        <v>467</v>
+      </c>
+      <c r="G195" t="s">
         <v>466</v>
-      </c>
-      <c r="G195" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6542,10 +6542,10 @@
         <v>471</v>
       </c>
       <c r="F196" t="s">
+        <v>471</v>
+      </c>
+      <c r="G196" t="s">
         <v>470</v>
-      </c>
-      <c r="G196" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6565,10 +6565,10 @@
         <v>471</v>
       </c>
       <c r="F197" t="s">
+        <v>471</v>
+      </c>
+      <c r="G197" t="s">
         <v>470</v>
-      </c>
-      <c r="G197" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6588,10 +6588,10 @@
         <v>471</v>
       </c>
       <c r="F198" t="s">
+        <v>471</v>
+      </c>
+      <c r="G198" t="s">
         <v>470</v>
-      </c>
-      <c r="G198" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6611,10 +6611,10 @@
         <v>471</v>
       </c>
       <c r="F199" t="s">
+        <v>471</v>
+      </c>
+      <c r="G199" t="s">
         <v>470</v>
-      </c>
-      <c r="G199" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6634,10 +6634,10 @@
         <v>471</v>
       </c>
       <c r="F200" t="s">
+        <v>471</v>
+      </c>
+      <c r="G200" t="s">
         <v>470</v>
-      </c>
-      <c r="G200" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6657,10 +6657,10 @@
         <v>471</v>
       </c>
       <c r="F201" t="s">
+        <v>471</v>
+      </c>
+      <c r="G201" t="s">
         <v>470</v>
-      </c>
-      <c r="G201" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6680,10 +6680,10 @@
         <v>485</v>
       </c>
       <c r="F202" t="s">
+        <v>485</v>
+      </c>
+      <c r="G202" t="s">
         <v>484</v>
-      </c>
-      <c r="G202" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6703,10 +6703,10 @@
         <v>485</v>
       </c>
       <c r="F203" t="s">
+        <v>485</v>
+      </c>
+      <c r="G203" t="s">
         <v>484</v>
-      </c>
-      <c r="G203" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6726,10 +6726,10 @@
         <v>485</v>
       </c>
       <c r="F204" t="s">
+        <v>485</v>
+      </c>
+      <c r="G204" t="s">
         <v>484</v>
-      </c>
-      <c r="G204" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6749,10 +6749,10 @@
         <v>485</v>
       </c>
       <c r="F205" t="s">
+        <v>485</v>
+      </c>
+      <c r="G205" t="s">
         <v>484</v>
-      </c>
-      <c r="G205" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6772,10 +6772,10 @@
         <v>485</v>
       </c>
       <c r="F206" t="s">
+        <v>485</v>
+      </c>
+      <c r="G206" t="s">
         <v>484</v>
-      </c>
-      <c r="G206" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6795,10 +6795,10 @@
         <v>485</v>
       </c>
       <c r="F207" t="s">
+        <v>485</v>
+      </c>
+      <c r="G207" t="s">
         <v>484</v>
-      </c>
-      <c r="G207" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6818,10 +6818,10 @@
         <v>485</v>
       </c>
       <c r="F208" t="s">
+        <v>485</v>
+      </c>
+      <c r="G208" t="s">
         <v>484</v>
-      </c>
-      <c r="G208" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6841,10 +6841,10 @@
         <v>485</v>
       </c>
       <c r="F209" t="s">
+        <v>485</v>
+      </c>
+      <c r="G209" t="s">
         <v>484</v>
-      </c>
-      <c r="G209" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6864,10 +6864,10 @@
         <v>485</v>
       </c>
       <c r="F210" t="s">
+        <v>485</v>
+      </c>
+      <c r="G210" t="s">
         <v>484</v>
-      </c>
-      <c r="G210" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6887,10 +6887,10 @@
         <v>485</v>
       </c>
       <c r="F211" t="s">
+        <v>485</v>
+      </c>
+      <c r="G211" t="s">
         <v>484</v>
-      </c>
-      <c r="G211" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6910,10 +6910,10 @@
         <v>507</v>
       </c>
       <c r="F212" t="s">
+        <v>507</v>
+      </c>
+      <c r="G212" t="s">
         <v>506</v>
-      </c>
-      <c r="G212" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6933,10 +6933,10 @@
         <v>511</v>
       </c>
       <c r="F213" t="s">
+        <v>511</v>
+      </c>
+      <c r="G213" t="s">
         <v>510</v>
-      </c>
-      <c r="G213" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6956,10 +6956,10 @@
         <v>515</v>
       </c>
       <c r="F214" t="s">
+        <v>515</v>
+      </c>
+      <c r="G214" t="s">
         <v>514</v>
-      </c>
-      <c r="G214" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6979,10 +6979,10 @@
         <v>515</v>
       </c>
       <c r="F215" t="s">
+        <v>515</v>
+      </c>
+      <c r="G215" t="s">
         <v>514</v>
-      </c>
-      <c r="G215" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -7002,10 +7002,10 @@
         <v>521</v>
       </c>
       <c r="F216" t="s">
+        <v>521</v>
+      </c>
+      <c r="G216" t="s">
         <v>520</v>
-      </c>
-      <c r="G216" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -7025,10 +7025,10 @@
         <v>521</v>
       </c>
       <c r="F217" t="s">
+        <v>521</v>
+      </c>
+      <c r="G217" t="s">
         <v>520</v>
-      </c>
-      <c r="G217" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -7048,10 +7048,10 @@
         <v>521</v>
       </c>
       <c r="F218" t="s">
+        <v>521</v>
+      </c>
+      <c r="G218" t="s">
         <v>520</v>
-      </c>
-      <c r="G218" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -7071,10 +7071,10 @@
         <v>521</v>
       </c>
       <c r="F219" t="s">
+        <v>521</v>
+      </c>
+      <c r="G219" t="s">
         <v>520</v>
-      </c>
-      <c r="G219" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -7094,10 +7094,10 @@
         <v>521</v>
       </c>
       <c r="F220" t="s">
+        <v>521</v>
+      </c>
+      <c r="G220" t="s">
         <v>520</v>
-      </c>
-      <c r="G220" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -7117,10 +7117,10 @@
         <v>521</v>
       </c>
       <c r="F221" t="s">
+        <v>521</v>
+      </c>
+      <c r="G221" t="s">
         <v>520</v>
-      </c>
-      <c r="G221" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -7140,10 +7140,10 @@
         <v>521</v>
       </c>
       <c r="F222" t="s">
+        <v>521</v>
+      </c>
+      <c r="G222" t="s">
         <v>520</v>
-      </c>
-      <c r="G222" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -7163,10 +7163,10 @@
         <v>537</v>
       </c>
       <c r="F223" t="s">
+        <v>537</v>
+      </c>
+      <c r="G223" t="s">
         <v>536</v>
-      </c>
-      <c r="G223" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -7186,10 +7186,10 @@
         <v>537</v>
       </c>
       <c r="F224" t="s">
+        <v>537</v>
+      </c>
+      <c r="G224" t="s">
         <v>536</v>
-      </c>
-      <c r="G224" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -7209,10 +7209,10 @@
         <v>537</v>
       </c>
       <c r="F225" t="s">
+        <v>537</v>
+      </c>
+      <c r="G225" t="s">
         <v>536</v>
-      </c>
-      <c r="G225" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -7232,10 +7232,10 @@
         <v>545</v>
       </c>
       <c r="F226" t="s">
+        <v>545</v>
+      </c>
+      <c r="G226" t="s">
         <v>544</v>
-      </c>
-      <c r="G226" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -7255,10 +7255,10 @@
         <v>549</v>
       </c>
       <c r="F227" t="s">
+        <v>549</v>
+      </c>
+      <c r="G227" t="s">
         <v>548</v>
-      </c>
-      <c r="G227" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -7278,10 +7278,10 @@
         <v>553</v>
       </c>
       <c r="F228" t="s">
+        <v>553</v>
+      </c>
+      <c r="G228" t="s">
         <v>552</v>
-      </c>
-      <c r="G228" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -7301,10 +7301,10 @@
         <v>557</v>
       </c>
       <c r="F229" t="s">
+        <v>557</v>
+      </c>
+      <c r="G229" t="s">
         <v>556</v>
-      </c>
-      <c r="G229" t="s">
-        <v>557</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -7324,10 +7324,10 @@
         <v>561</v>
       </c>
       <c r="F230" t="s">
+        <v>561</v>
+      </c>
+      <c r="G230" t="s">
         <v>560</v>
-      </c>
-      <c r="G230" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -7347,10 +7347,10 @@
         <v>561</v>
       </c>
       <c r="F231" t="s">
+        <v>561</v>
+      </c>
+      <c r="G231" t="s">
         <v>560</v>
-      </c>
-      <c r="G231" t="s">
-        <v>561</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/en/SectorGroup.xlsx
+++ b/api/xlsx/en/SectorGroup.xlsx
@@ -28,15 +28,15 @@
     <t>codeforiati:category-code</t>
   </si>
   <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
     <t>codeforiati:category-name</t>
   </si>
   <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -49,15 +49,15 @@
     <t>111</t>
   </si>
   <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
     <t>Education, Level Unspecified</t>
   </si>
   <si>
-    <t>Education</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -151,15 +151,15 @@
     <t>121</t>
   </si>
   <si>
+    <t>Health</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
     <t>Health, General</t>
   </si>
   <si>
-    <t>Health</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -391,15 +391,15 @@
     <t>151</t>
   </si>
   <si>
+    <t>Government &amp; Civil Society</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
     <t>Government &amp; Civil Society-general</t>
   </si>
   <si>
-    <t>Government &amp; Civil Society</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -691,15 +691,15 @@
     <t>231</t>
   </si>
   <si>
+    <t>Energy</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
     <t>Energy Policy</t>
   </si>
   <si>
-    <t>Energy</t>
-  </si>
-  <si>
-    <t>230</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -973,15 +973,15 @@
     <t>311</t>
   </si>
   <si>
+    <t>Agriculture, Forestry, Fishing</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
     <t>Agriculture</t>
   </si>
   <si>
-    <t>Agriculture, Forestry, Fishing</t>
-  </si>
-  <si>
-    <t>310</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1171,13 +1171,13 @@
     <t>321</t>
   </si>
   <si>
+    <t>Industry, Mining, Construction</t>
+  </si>
+  <si>
+    <t>320</t>
+  </si>
+  <si>
     <t>Industry</t>
-  </si>
-  <si>
-    <t>Industry, Mining, Construction</t>
-  </si>
-  <si>
-    <t>320</t>
   </si>
   <si>
     <t>32120</t>
@@ -2169,13 +2169,13 @@
         <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
         <v>12</v>
       </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2192,13 +2192,13 @@
         <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
         <v>12</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2215,13 +2215,13 @@
         <v>22</v>
       </c>
       <c r="E8" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s">
         <v>12</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2238,13 +2238,13 @@
         <v>22</v>
       </c>
       <c r="E9" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
         <v>12</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2261,13 +2261,13 @@
         <v>32</v>
       </c>
       <c r="E10" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="F10" t="s">
         <v>12</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2284,13 +2284,13 @@
         <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="F11" t="s">
         <v>12</v>
       </c>
       <c r="G11" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2307,13 +2307,13 @@
         <v>38</v>
       </c>
       <c r="E12" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="F12" t="s">
         <v>12</v>
       </c>
       <c r="G12" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2330,13 +2330,13 @@
         <v>38</v>
       </c>
       <c r="E13" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="F13" t="s">
         <v>12</v>
       </c>
       <c r="G13" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2445,13 +2445,13 @@
         <v>56</v>
       </c>
       <c r="E18" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="F18" t="s">
         <v>46</v>
       </c>
       <c r="G18" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2468,13 +2468,13 @@
         <v>56</v>
       </c>
       <c r="E19" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="F19" t="s">
         <v>46</v>
       </c>
       <c r="G19" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2491,13 +2491,13 @@
         <v>56</v>
       </c>
       <c r="E20" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="F20" t="s">
         <v>46</v>
       </c>
       <c r="G20" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2514,13 +2514,13 @@
         <v>56</v>
       </c>
       <c r="E21" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="F21" t="s">
         <v>46</v>
       </c>
       <c r="G21" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2537,13 +2537,13 @@
         <v>56</v>
       </c>
       <c r="E22" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="F22" t="s">
         <v>46</v>
       </c>
       <c r="G22" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2560,13 +2560,13 @@
         <v>56</v>
       </c>
       <c r="E23" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="F23" t="s">
         <v>46</v>
       </c>
       <c r="G23" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2583,13 +2583,13 @@
         <v>56</v>
       </c>
       <c r="E24" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="F24" t="s">
         <v>46</v>
       </c>
       <c r="G24" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2606,13 +2606,13 @@
         <v>56</v>
       </c>
       <c r="E25" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="F25" t="s">
         <v>46</v>
       </c>
       <c r="G25" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2629,13 +2629,13 @@
         <v>74</v>
       </c>
       <c r="E26" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="F26" t="s">
         <v>46</v>
       </c>
       <c r="G26" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2652,13 +2652,13 @@
         <v>74</v>
       </c>
       <c r="E27" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="F27" t="s">
         <v>46</v>
       </c>
       <c r="G27" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2675,13 +2675,13 @@
         <v>74</v>
       </c>
       <c r="E28" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="F28" t="s">
         <v>46</v>
       </c>
       <c r="G28" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2698,13 +2698,13 @@
         <v>74</v>
       </c>
       <c r="E29" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="F29" t="s">
         <v>46</v>
       </c>
       <c r="G29" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2721,13 +2721,13 @@
         <v>74</v>
       </c>
       <c r="E30" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="F30" t="s">
         <v>46</v>
       </c>
       <c r="G30" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2744,13 +2744,13 @@
         <v>74</v>
       </c>
       <c r="E31" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="F31" t="s">
         <v>46</v>
       </c>
       <c r="G31" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2770,10 +2770,10 @@
         <v>89</v>
       </c>
       <c r="F32" t="s">
+        <v>88</v>
+      </c>
+      <c r="G32" t="s">
         <v>89</v>
-      </c>
-      <c r="G32" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2793,10 +2793,10 @@
         <v>89</v>
       </c>
       <c r="F33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G33" t="s">
         <v>89</v>
-      </c>
-      <c r="G33" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2816,10 +2816,10 @@
         <v>89</v>
       </c>
       <c r="F34" t="s">
+        <v>88</v>
+      </c>
+      <c r="G34" t="s">
         <v>89</v>
-      </c>
-      <c r="G34" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2839,10 +2839,10 @@
         <v>89</v>
       </c>
       <c r="F35" t="s">
+        <v>88</v>
+      </c>
+      <c r="G35" t="s">
         <v>89</v>
-      </c>
-      <c r="G35" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2862,10 +2862,10 @@
         <v>89</v>
       </c>
       <c r="F36" t="s">
+        <v>88</v>
+      </c>
+      <c r="G36" t="s">
         <v>89</v>
-      </c>
-      <c r="G36" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2885,10 +2885,10 @@
         <v>101</v>
       </c>
       <c r="F37" t="s">
+        <v>100</v>
+      </c>
+      <c r="G37" t="s">
         <v>101</v>
-      </c>
-      <c r="G37" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2908,10 +2908,10 @@
         <v>101</v>
       </c>
       <c r="F38" t="s">
+        <v>100</v>
+      </c>
+      <c r="G38" t="s">
         <v>101</v>
-      </c>
-      <c r="G38" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2931,10 +2931,10 @@
         <v>101</v>
       </c>
       <c r="F39" t="s">
+        <v>100</v>
+      </c>
+      <c r="G39" t="s">
         <v>101</v>
-      </c>
-      <c r="G39" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2954,10 +2954,10 @@
         <v>101</v>
       </c>
       <c r="F40" t="s">
+        <v>100</v>
+      </c>
+      <c r="G40" t="s">
         <v>101</v>
-      </c>
-      <c r="G40" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2977,10 +2977,10 @@
         <v>101</v>
       </c>
       <c r="F41" t="s">
+        <v>100</v>
+      </c>
+      <c r="G41" t="s">
         <v>101</v>
-      </c>
-      <c r="G41" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -3000,10 +3000,10 @@
         <v>101</v>
       </c>
       <c r="F42" t="s">
+        <v>100</v>
+      </c>
+      <c r="G42" t="s">
         <v>101</v>
-      </c>
-      <c r="G42" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3023,10 +3023,10 @@
         <v>101</v>
       </c>
       <c r="F43" t="s">
+        <v>100</v>
+      </c>
+      <c r="G43" t="s">
         <v>101</v>
-      </c>
-      <c r="G43" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3046,10 +3046,10 @@
         <v>101</v>
       </c>
       <c r="F44" t="s">
+        <v>100</v>
+      </c>
+      <c r="G44" t="s">
         <v>101</v>
-      </c>
-      <c r="G44" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3069,10 +3069,10 @@
         <v>101</v>
       </c>
       <c r="F45" t="s">
+        <v>100</v>
+      </c>
+      <c r="G45" t="s">
         <v>101</v>
-      </c>
-      <c r="G45" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3092,10 +3092,10 @@
         <v>101</v>
       </c>
       <c r="F46" t="s">
+        <v>100</v>
+      </c>
+      <c r="G46" t="s">
         <v>101</v>
-      </c>
-      <c r="G46" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3115,10 +3115,10 @@
         <v>101</v>
       </c>
       <c r="F47" t="s">
+        <v>100</v>
+      </c>
+      <c r="G47" t="s">
         <v>101</v>
-      </c>
-      <c r="G47" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3503,13 +3503,13 @@
         <v>160</v>
       </c>
       <c r="E64" t="s">
-        <v>161</v>
+        <v>125</v>
       </c>
       <c r="F64" t="s">
         <v>126</v>
       </c>
       <c r="G64" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3526,13 +3526,13 @@
         <v>160</v>
       </c>
       <c r="E65" t="s">
-        <v>161</v>
+        <v>125</v>
       </c>
       <c r="F65" t="s">
         <v>126</v>
       </c>
       <c r="G65" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3549,13 +3549,13 @@
         <v>160</v>
       </c>
       <c r="E66" t="s">
-        <v>161</v>
+        <v>125</v>
       </c>
       <c r="F66" t="s">
         <v>126</v>
       </c>
       <c r="G66" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3572,13 +3572,13 @@
         <v>160</v>
       </c>
       <c r="E67" t="s">
-        <v>161</v>
+        <v>125</v>
       </c>
       <c r="F67" t="s">
         <v>126</v>
       </c>
       <c r="G67" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3595,13 +3595,13 @@
         <v>160</v>
       </c>
       <c r="E68" t="s">
-        <v>161</v>
+        <v>125</v>
       </c>
       <c r="F68" t="s">
         <v>126</v>
       </c>
       <c r="G68" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3618,13 +3618,13 @@
         <v>160</v>
       </c>
       <c r="E69" t="s">
-        <v>161</v>
+        <v>125</v>
       </c>
       <c r="F69" t="s">
         <v>126</v>
       </c>
       <c r="G69" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3644,10 +3644,10 @@
         <v>175</v>
       </c>
       <c r="F70" t="s">
+        <v>174</v>
+      </c>
+      <c r="G70" t="s">
         <v>175</v>
-      </c>
-      <c r="G70" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3667,10 +3667,10 @@
         <v>175</v>
       </c>
       <c r="F71" t="s">
+        <v>174</v>
+      </c>
+      <c r="G71" t="s">
         <v>175</v>
-      </c>
-      <c r="G71" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3690,10 +3690,10 @@
         <v>175</v>
       </c>
       <c r="F72" t="s">
+        <v>174</v>
+      </c>
+      <c r="G72" t="s">
         <v>175</v>
-      </c>
-      <c r="G72" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3713,10 +3713,10 @@
         <v>175</v>
       </c>
       <c r="F73" t="s">
+        <v>174</v>
+      </c>
+      <c r="G73" t="s">
         <v>175</v>
-      </c>
-      <c r="G73" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3736,10 +3736,10 @@
         <v>175</v>
       </c>
       <c r="F74" t="s">
+        <v>174</v>
+      </c>
+      <c r="G74" t="s">
         <v>175</v>
-      </c>
-      <c r="G74" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3759,10 +3759,10 @@
         <v>175</v>
       </c>
       <c r="F75" t="s">
+        <v>174</v>
+      </c>
+      <c r="G75" t="s">
         <v>175</v>
-      </c>
-      <c r="G75" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3782,10 +3782,10 @@
         <v>175</v>
       </c>
       <c r="F76" t="s">
+        <v>174</v>
+      </c>
+      <c r="G76" t="s">
         <v>175</v>
-      </c>
-      <c r="G76" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3805,10 +3805,10 @@
         <v>175</v>
       </c>
       <c r="F77" t="s">
+        <v>174</v>
+      </c>
+      <c r="G77" t="s">
         <v>175</v>
-      </c>
-      <c r="G77" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3828,10 +3828,10 @@
         <v>175</v>
       </c>
       <c r="F78" t="s">
+        <v>174</v>
+      </c>
+      <c r="G78" t="s">
         <v>175</v>
-      </c>
-      <c r="G78" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3851,10 +3851,10 @@
         <v>175</v>
       </c>
       <c r="F79" t="s">
+        <v>174</v>
+      </c>
+      <c r="G79" t="s">
         <v>175</v>
-      </c>
-      <c r="G79" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3874,10 +3874,10 @@
         <v>175</v>
       </c>
       <c r="F80" t="s">
+        <v>174</v>
+      </c>
+      <c r="G80" t="s">
         <v>175</v>
-      </c>
-      <c r="G80" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3897,10 +3897,10 @@
         <v>199</v>
       </c>
       <c r="F81" t="s">
+        <v>198</v>
+      </c>
+      <c r="G81" t="s">
         <v>199</v>
-      </c>
-      <c r="G81" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3920,10 +3920,10 @@
         <v>199</v>
       </c>
       <c r="F82" t="s">
+        <v>198</v>
+      </c>
+      <c r="G82" t="s">
         <v>199</v>
-      </c>
-      <c r="G82" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3943,10 +3943,10 @@
         <v>199</v>
       </c>
       <c r="F83" t="s">
+        <v>198</v>
+      </c>
+      <c r="G83" t="s">
         <v>199</v>
-      </c>
-      <c r="G83" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3966,10 +3966,10 @@
         <v>199</v>
       </c>
       <c r="F84" t="s">
+        <v>198</v>
+      </c>
+      <c r="G84" t="s">
         <v>199</v>
-      </c>
-      <c r="G84" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3989,10 +3989,10 @@
         <v>199</v>
       </c>
       <c r="F85" t="s">
+        <v>198</v>
+      </c>
+      <c r="G85" t="s">
         <v>199</v>
-      </c>
-      <c r="G85" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4012,10 +4012,10 @@
         <v>199</v>
       </c>
       <c r="F86" t="s">
+        <v>198</v>
+      </c>
+      <c r="G86" t="s">
         <v>199</v>
-      </c>
-      <c r="G86" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4035,10 +4035,10 @@
         <v>199</v>
       </c>
       <c r="F87" t="s">
+        <v>198</v>
+      </c>
+      <c r="G87" t="s">
         <v>199</v>
-      </c>
-      <c r="G87" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4058,10 +4058,10 @@
         <v>215</v>
       </c>
       <c r="F88" t="s">
+        <v>214</v>
+      </c>
+      <c r="G88" t="s">
         <v>215</v>
-      </c>
-      <c r="G88" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4081,10 +4081,10 @@
         <v>215</v>
       </c>
       <c r="F89" t="s">
+        <v>214</v>
+      </c>
+      <c r="G89" t="s">
         <v>215</v>
-      </c>
-      <c r="G89" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4104,10 +4104,10 @@
         <v>215</v>
       </c>
       <c r="F90" t="s">
+        <v>214</v>
+      </c>
+      <c r="G90" t="s">
         <v>215</v>
-      </c>
-      <c r="G90" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4127,10 +4127,10 @@
         <v>215</v>
       </c>
       <c r="F91" t="s">
+        <v>214</v>
+      </c>
+      <c r="G91" t="s">
         <v>215</v>
-      </c>
-      <c r="G91" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4239,13 +4239,13 @@
         <v>236</v>
       </c>
       <c r="E96" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F96" t="s">
         <v>226</v>
       </c>
       <c r="G96" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -4262,13 +4262,13 @@
         <v>236</v>
       </c>
       <c r="E97" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F97" t="s">
         <v>226</v>
       </c>
       <c r="G97" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4285,13 +4285,13 @@
         <v>236</v>
       </c>
       <c r="E98" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F98" t="s">
         <v>226</v>
       </c>
       <c r="G98" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4308,13 +4308,13 @@
         <v>236</v>
       </c>
       <c r="E99" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F99" t="s">
         <v>226</v>
       </c>
       <c r="G99" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4331,13 +4331,13 @@
         <v>236</v>
       </c>
       <c r="E100" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F100" t="s">
         <v>226</v>
       </c>
       <c r="G100" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4354,13 +4354,13 @@
         <v>236</v>
       </c>
       <c r="E101" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F101" t="s">
         <v>226</v>
       </c>
       <c r="G101" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4377,13 +4377,13 @@
         <v>236</v>
       </c>
       <c r="E102" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F102" t="s">
         <v>226</v>
       </c>
       <c r="G102" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4400,13 +4400,13 @@
         <v>236</v>
       </c>
       <c r="E103" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F103" t="s">
         <v>226</v>
       </c>
       <c r="G103" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4423,13 +4423,13 @@
         <v>236</v>
       </c>
       <c r="E104" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F104" t="s">
         <v>226</v>
       </c>
       <c r="G104" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4446,13 +4446,13 @@
         <v>256</v>
       </c>
       <c r="E105" t="s">
-        <v>257</v>
+        <v>225</v>
       </c>
       <c r="F105" t="s">
         <v>226</v>
       </c>
       <c r="G105" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4469,13 +4469,13 @@
         <v>256</v>
       </c>
       <c r="E106" t="s">
-        <v>257</v>
+        <v>225</v>
       </c>
       <c r="F106" t="s">
         <v>226</v>
       </c>
       <c r="G106" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4492,13 +4492,13 @@
         <v>256</v>
       </c>
       <c r="E107" t="s">
-        <v>257</v>
+        <v>225</v>
       </c>
       <c r="F107" t="s">
         <v>226</v>
       </c>
       <c r="G107" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4515,13 +4515,13 @@
         <v>256</v>
       </c>
       <c r="E108" t="s">
-        <v>257</v>
+        <v>225</v>
       </c>
       <c r="F108" t="s">
         <v>226</v>
       </c>
       <c r="G108" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4538,13 +4538,13 @@
         <v>256</v>
       </c>
       <c r="E109" t="s">
-        <v>257</v>
+        <v>225</v>
       </c>
       <c r="F109" t="s">
         <v>226</v>
       </c>
       <c r="G109" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4561,13 +4561,13 @@
         <v>256</v>
       </c>
       <c r="E110" t="s">
-        <v>257</v>
+        <v>225</v>
       </c>
       <c r="F110" t="s">
         <v>226</v>
       </c>
       <c r="G110" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4584,13 +4584,13 @@
         <v>270</v>
       </c>
       <c r="E111" t="s">
-        <v>271</v>
+        <v>225</v>
       </c>
       <c r="F111" t="s">
         <v>226</v>
       </c>
       <c r="G111" t="s">
-        <v>227</v>
+        <v>271</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4607,13 +4607,13 @@
         <v>274</v>
       </c>
       <c r="E112" t="s">
-        <v>275</v>
+        <v>225</v>
       </c>
       <c r="F112" t="s">
         <v>226</v>
       </c>
       <c r="G112" t="s">
-        <v>227</v>
+        <v>275</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4630,13 +4630,13 @@
         <v>278</v>
       </c>
       <c r="E113" t="s">
-        <v>279</v>
+        <v>225</v>
       </c>
       <c r="F113" t="s">
         <v>226</v>
       </c>
       <c r="G113" t="s">
-        <v>227</v>
+        <v>279</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4653,13 +4653,13 @@
         <v>278</v>
       </c>
       <c r="E114" t="s">
-        <v>279</v>
+        <v>225</v>
       </c>
       <c r="F114" t="s">
         <v>226</v>
       </c>
       <c r="G114" t="s">
-        <v>227</v>
+        <v>279</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4676,13 +4676,13 @@
         <v>278</v>
       </c>
       <c r="E115" t="s">
-        <v>279</v>
+        <v>225</v>
       </c>
       <c r="F115" t="s">
         <v>226</v>
       </c>
       <c r="G115" t="s">
-        <v>227</v>
+        <v>279</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4699,13 +4699,13 @@
         <v>278</v>
       </c>
       <c r="E116" t="s">
-        <v>279</v>
+        <v>225</v>
       </c>
       <c r="F116" t="s">
         <v>226</v>
       </c>
       <c r="G116" t="s">
-        <v>227</v>
+        <v>279</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4722,13 +4722,13 @@
         <v>278</v>
       </c>
       <c r="E117" t="s">
-        <v>279</v>
+        <v>225</v>
       </c>
       <c r="F117" t="s">
         <v>226</v>
       </c>
       <c r="G117" t="s">
-        <v>227</v>
+        <v>279</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4745,13 +4745,13 @@
         <v>278</v>
       </c>
       <c r="E118" t="s">
-        <v>279</v>
+        <v>225</v>
       </c>
       <c r="F118" t="s">
         <v>226</v>
       </c>
       <c r="G118" t="s">
-        <v>227</v>
+        <v>279</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4768,13 +4768,13 @@
         <v>278</v>
       </c>
       <c r="E119" t="s">
-        <v>279</v>
+        <v>225</v>
       </c>
       <c r="F119" t="s">
         <v>226</v>
       </c>
       <c r="G119" t="s">
-        <v>227</v>
+        <v>279</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4794,10 +4794,10 @@
         <v>295</v>
       </c>
       <c r="F120" t="s">
+        <v>294</v>
+      </c>
+      <c r="G120" t="s">
         <v>295</v>
-      </c>
-      <c r="G120" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4817,10 +4817,10 @@
         <v>295</v>
       </c>
       <c r="F121" t="s">
+        <v>294</v>
+      </c>
+      <c r="G121" t="s">
         <v>295</v>
-      </c>
-      <c r="G121" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4840,10 +4840,10 @@
         <v>295</v>
       </c>
       <c r="F122" t="s">
+        <v>294</v>
+      </c>
+      <c r="G122" t="s">
         <v>295</v>
-      </c>
-      <c r="G122" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4863,10 +4863,10 @@
         <v>295</v>
       </c>
       <c r="F123" t="s">
+        <v>294</v>
+      </c>
+      <c r="G123" t="s">
         <v>295</v>
-      </c>
-      <c r="G123" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4886,10 +4886,10 @@
         <v>295</v>
       </c>
       <c r="F124" t="s">
+        <v>294</v>
+      </c>
+      <c r="G124" t="s">
         <v>295</v>
-      </c>
-      <c r="G124" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4909,10 +4909,10 @@
         <v>295</v>
       </c>
       <c r="F125" t="s">
+        <v>294</v>
+      </c>
+      <c r="G125" t="s">
         <v>295</v>
-      </c>
-      <c r="G125" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4932,10 +4932,10 @@
         <v>309</v>
       </c>
       <c r="F126" t="s">
+        <v>308</v>
+      </c>
+      <c r="G126" t="s">
         <v>309</v>
-      </c>
-      <c r="G126" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4955,10 +4955,10 @@
         <v>309</v>
       </c>
       <c r="F127" t="s">
+        <v>308</v>
+      </c>
+      <c r="G127" t="s">
         <v>309</v>
-      </c>
-      <c r="G127" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4978,10 +4978,10 @@
         <v>309</v>
       </c>
       <c r="F128" t="s">
+        <v>308</v>
+      </c>
+      <c r="G128" t="s">
         <v>309</v>
-      </c>
-      <c r="G128" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -5001,10 +5001,10 @@
         <v>309</v>
       </c>
       <c r="F129" t="s">
+        <v>308</v>
+      </c>
+      <c r="G129" t="s">
         <v>309</v>
-      </c>
-      <c r="G129" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -5435,13 +5435,13 @@
         <v>358</v>
       </c>
       <c r="E148" t="s">
-        <v>359</v>
+        <v>319</v>
       </c>
       <c r="F148" t="s">
         <v>320</v>
       </c>
       <c r="G148" t="s">
-        <v>321</v>
+        <v>359</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5458,13 +5458,13 @@
         <v>358</v>
       </c>
       <c r="E149" t="s">
-        <v>359</v>
+        <v>319</v>
       </c>
       <c r="F149" t="s">
         <v>320</v>
       </c>
       <c r="G149" t="s">
-        <v>321</v>
+        <v>359</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5481,13 +5481,13 @@
         <v>358</v>
       </c>
       <c r="E150" t="s">
-        <v>359</v>
+        <v>319</v>
       </c>
       <c r="F150" t="s">
         <v>320</v>
       </c>
       <c r="G150" t="s">
-        <v>321</v>
+        <v>359</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5504,13 +5504,13 @@
         <v>358</v>
       </c>
       <c r="E151" t="s">
-        <v>359</v>
+        <v>319</v>
       </c>
       <c r="F151" t="s">
         <v>320</v>
       </c>
       <c r="G151" t="s">
-        <v>321</v>
+        <v>359</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5527,13 +5527,13 @@
         <v>358</v>
       </c>
       <c r="E152" t="s">
-        <v>359</v>
+        <v>319</v>
       </c>
       <c r="F152" t="s">
         <v>320</v>
       </c>
       <c r="G152" t="s">
-        <v>321</v>
+        <v>359</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5550,13 +5550,13 @@
         <v>358</v>
       </c>
       <c r="E153" t="s">
-        <v>359</v>
+        <v>319</v>
       </c>
       <c r="F153" t="s">
         <v>320</v>
       </c>
       <c r="G153" t="s">
-        <v>321</v>
+        <v>359</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5573,13 +5573,13 @@
         <v>372</v>
       </c>
       <c r="E154" t="s">
-        <v>373</v>
+        <v>319</v>
       </c>
       <c r="F154" t="s">
         <v>320</v>
       </c>
       <c r="G154" t="s">
-        <v>321</v>
+        <v>373</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5596,13 +5596,13 @@
         <v>372</v>
       </c>
       <c r="E155" t="s">
-        <v>373</v>
+        <v>319</v>
       </c>
       <c r="F155" t="s">
         <v>320</v>
       </c>
       <c r="G155" t="s">
-        <v>321</v>
+        <v>373</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5619,13 +5619,13 @@
         <v>372</v>
       </c>
       <c r="E156" t="s">
-        <v>373</v>
+        <v>319</v>
       </c>
       <c r="F156" t="s">
         <v>320</v>
       </c>
       <c r="G156" t="s">
-        <v>321</v>
+        <v>373</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5642,13 +5642,13 @@
         <v>372</v>
       </c>
       <c r="E157" t="s">
-        <v>373</v>
+        <v>319</v>
       </c>
       <c r="F157" t="s">
         <v>320</v>
       </c>
       <c r="G157" t="s">
-        <v>321</v>
+        <v>373</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5665,13 +5665,13 @@
         <v>372</v>
       </c>
       <c r="E158" t="s">
-        <v>373</v>
+        <v>319</v>
       </c>
       <c r="F158" t="s">
         <v>320</v>
       </c>
       <c r="G158" t="s">
-        <v>321</v>
+        <v>373</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -6125,13 +6125,13 @@
         <v>426</v>
       </c>
       <c r="E178" t="s">
-        <v>427</v>
+        <v>385</v>
       </c>
       <c r="F178" t="s">
         <v>386</v>
       </c>
       <c r="G178" t="s">
-        <v>387</v>
+        <v>427</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -6148,13 +6148,13 @@
         <v>426</v>
       </c>
       <c r="E179" t="s">
-        <v>427</v>
+        <v>385</v>
       </c>
       <c r="F179" t="s">
         <v>386</v>
       </c>
       <c r="G179" t="s">
-        <v>387</v>
+        <v>427</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -6171,13 +6171,13 @@
         <v>426</v>
       </c>
       <c r="E180" t="s">
-        <v>427</v>
+        <v>385</v>
       </c>
       <c r="F180" t="s">
         <v>386</v>
       </c>
       <c r="G180" t="s">
-        <v>387</v>
+        <v>427</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -6194,13 +6194,13 @@
         <v>426</v>
       </c>
       <c r="E181" t="s">
-        <v>427</v>
+        <v>385</v>
       </c>
       <c r="F181" t="s">
         <v>386</v>
       </c>
       <c r="G181" t="s">
-        <v>387</v>
+        <v>427</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -6217,13 +6217,13 @@
         <v>426</v>
       </c>
       <c r="E182" t="s">
-        <v>427</v>
+        <v>385</v>
       </c>
       <c r="F182" t="s">
         <v>386</v>
       </c>
       <c r="G182" t="s">
-        <v>387</v>
+        <v>427</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -6240,13 +6240,13 @@
         <v>426</v>
       </c>
       <c r="E183" t="s">
-        <v>427</v>
+        <v>385</v>
       </c>
       <c r="F183" t="s">
         <v>386</v>
       </c>
       <c r="G183" t="s">
-        <v>387</v>
+        <v>427</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -6263,13 +6263,13 @@
         <v>426</v>
       </c>
       <c r="E184" t="s">
-        <v>427</v>
+        <v>385</v>
       </c>
       <c r="F184" t="s">
         <v>386</v>
       </c>
       <c r="G184" t="s">
-        <v>387</v>
+        <v>427</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -6286,13 +6286,13 @@
         <v>426</v>
       </c>
       <c r="E185" t="s">
-        <v>427</v>
+        <v>385</v>
       </c>
       <c r="F185" t="s">
         <v>386</v>
       </c>
       <c r="G185" t="s">
-        <v>387</v>
+        <v>427</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -6309,13 +6309,13 @@
         <v>426</v>
       </c>
       <c r="E186" t="s">
-        <v>427</v>
+        <v>385</v>
       </c>
       <c r="F186" t="s">
         <v>386</v>
       </c>
       <c r="G186" t="s">
-        <v>387</v>
+        <v>427</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -6332,13 +6332,13 @@
         <v>426</v>
       </c>
       <c r="E187" t="s">
-        <v>427</v>
+        <v>385</v>
       </c>
       <c r="F187" t="s">
         <v>386</v>
       </c>
       <c r="G187" t="s">
-        <v>387</v>
+        <v>427</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -6355,13 +6355,13 @@
         <v>448</v>
       </c>
       <c r="E188" t="s">
-        <v>449</v>
+        <v>385</v>
       </c>
       <c r="F188" t="s">
         <v>386</v>
       </c>
       <c r="G188" t="s">
-        <v>387</v>
+        <v>449</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -6381,10 +6381,10 @@
         <v>453</v>
       </c>
       <c r="F189" t="s">
+        <v>452</v>
+      </c>
+      <c r="G189" t="s">
         <v>453</v>
-      </c>
-      <c r="G189" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6404,10 +6404,10 @@
         <v>453</v>
       </c>
       <c r="F190" t="s">
+        <v>452</v>
+      </c>
+      <c r="G190" t="s">
         <v>453</v>
-      </c>
-      <c r="G190" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6427,10 +6427,10 @@
         <v>453</v>
       </c>
       <c r="F191" t="s">
+        <v>452</v>
+      </c>
+      <c r="G191" t="s">
         <v>453</v>
-      </c>
-      <c r="G191" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6450,10 +6450,10 @@
         <v>453</v>
       </c>
       <c r="F192" t="s">
+        <v>452</v>
+      </c>
+      <c r="G192" t="s">
         <v>453</v>
-      </c>
-      <c r="G192" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6473,10 +6473,10 @@
         <v>453</v>
       </c>
       <c r="F193" t="s">
+        <v>452</v>
+      </c>
+      <c r="G193" t="s">
         <v>453</v>
-      </c>
-      <c r="G193" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6496,10 +6496,10 @@
         <v>453</v>
       </c>
       <c r="F194" t="s">
+        <v>452</v>
+      </c>
+      <c r="G194" t="s">
         <v>453</v>
-      </c>
-      <c r="G194" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6519,10 +6519,10 @@
         <v>467</v>
       </c>
       <c r="F195" t="s">
+        <v>466</v>
+      </c>
+      <c r="G195" t="s">
         <v>467</v>
-      </c>
-      <c r="G195" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6542,10 +6542,10 @@
         <v>471</v>
       </c>
       <c r="F196" t="s">
+        <v>470</v>
+      </c>
+      <c r="G196" t="s">
         <v>471</v>
-      </c>
-      <c r="G196" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6565,10 +6565,10 @@
         <v>471</v>
       </c>
       <c r="F197" t="s">
+        <v>470</v>
+      </c>
+      <c r="G197" t="s">
         <v>471</v>
-      </c>
-      <c r="G197" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6588,10 +6588,10 @@
         <v>471</v>
       </c>
       <c r="F198" t="s">
+        <v>470</v>
+      </c>
+      <c r="G198" t="s">
         <v>471</v>
-      </c>
-      <c r="G198" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6611,10 +6611,10 @@
         <v>471</v>
       </c>
       <c r="F199" t="s">
+        <v>470</v>
+      </c>
+      <c r="G199" t="s">
         <v>471</v>
-      </c>
-      <c r="G199" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6634,10 +6634,10 @@
         <v>471</v>
       </c>
       <c r="F200" t="s">
+        <v>470</v>
+      </c>
+      <c r="G200" t="s">
         <v>471</v>
-      </c>
-      <c r="G200" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6657,10 +6657,10 @@
         <v>471</v>
       </c>
       <c r="F201" t="s">
+        <v>470</v>
+      </c>
+      <c r="G201" t="s">
         <v>471</v>
-      </c>
-      <c r="G201" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6680,10 +6680,10 @@
         <v>485</v>
       </c>
       <c r="F202" t="s">
+        <v>484</v>
+      </c>
+      <c r="G202" t="s">
         <v>485</v>
-      </c>
-      <c r="G202" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6703,10 +6703,10 @@
         <v>485</v>
       </c>
       <c r="F203" t="s">
+        <v>484</v>
+      </c>
+      <c r="G203" t="s">
         <v>485</v>
-      </c>
-      <c r="G203" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6726,10 +6726,10 @@
         <v>485</v>
       </c>
       <c r="F204" t="s">
+        <v>484</v>
+      </c>
+      <c r="G204" t="s">
         <v>485</v>
-      </c>
-      <c r="G204" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6749,10 +6749,10 @@
         <v>485</v>
       </c>
       <c r="F205" t="s">
+        <v>484</v>
+      </c>
+      <c r="G205" t="s">
         <v>485</v>
-      </c>
-      <c r="G205" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6772,10 +6772,10 @@
         <v>485</v>
       </c>
       <c r="F206" t="s">
+        <v>484</v>
+      </c>
+      <c r="G206" t="s">
         <v>485</v>
-      </c>
-      <c r="G206" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6795,10 +6795,10 @@
         <v>485</v>
       </c>
       <c r="F207" t="s">
+        <v>484</v>
+      </c>
+      <c r="G207" t="s">
         <v>485</v>
-      </c>
-      <c r="G207" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6818,10 +6818,10 @@
         <v>485</v>
       </c>
       <c r="F208" t="s">
+        <v>484</v>
+      </c>
+      <c r="G208" t="s">
         <v>485</v>
-      </c>
-      <c r="G208" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6841,10 +6841,10 @@
         <v>485</v>
       </c>
       <c r="F209" t="s">
+        <v>484</v>
+      </c>
+      <c r="G209" t="s">
         <v>485</v>
-      </c>
-      <c r="G209" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6864,10 +6864,10 @@
         <v>485</v>
       </c>
       <c r="F210" t="s">
+        <v>484</v>
+      </c>
+      <c r="G210" t="s">
         <v>485</v>
-      </c>
-      <c r="G210" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6887,10 +6887,10 @@
         <v>485</v>
       </c>
       <c r="F211" t="s">
+        <v>484</v>
+      </c>
+      <c r="G211" t="s">
         <v>485</v>
-      </c>
-      <c r="G211" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6910,10 +6910,10 @@
         <v>507</v>
       </c>
       <c r="F212" t="s">
+        <v>506</v>
+      </c>
+      <c r="G212" t="s">
         <v>507</v>
-      </c>
-      <c r="G212" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6933,10 +6933,10 @@
         <v>511</v>
       </c>
       <c r="F213" t="s">
+        <v>510</v>
+      </c>
+      <c r="G213" t="s">
         <v>511</v>
-      </c>
-      <c r="G213" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6956,10 +6956,10 @@
         <v>515</v>
       </c>
       <c r="F214" t="s">
+        <v>514</v>
+      </c>
+      <c r="G214" t="s">
         <v>515</v>
-      </c>
-      <c r="G214" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6979,10 +6979,10 @@
         <v>515</v>
       </c>
       <c r="F215" t="s">
+        <v>514</v>
+      </c>
+      <c r="G215" t="s">
         <v>515</v>
-      </c>
-      <c r="G215" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -7002,10 +7002,10 @@
         <v>521</v>
       </c>
       <c r="F216" t="s">
+        <v>520</v>
+      </c>
+      <c r="G216" t="s">
         <v>521</v>
-      </c>
-      <c r="G216" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -7025,10 +7025,10 @@
         <v>521</v>
       </c>
       <c r="F217" t="s">
+        <v>520</v>
+      </c>
+      <c r="G217" t="s">
         <v>521</v>
-      </c>
-      <c r="G217" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -7048,10 +7048,10 @@
         <v>521</v>
       </c>
       <c r="F218" t="s">
+        <v>520</v>
+      </c>
+      <c r="G218" t="s">
         <v>521</v>
-      </c>
-      <c r="G218" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -7071,10 +7071,10 @@
         <v>521</v>
       </c>
       <c r="F219" t="s">
+        <v>520</v>
+      </c>
+      <c r="G219" t="s">
         <v>521</v>
-      </c>
-      <c r="G219" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -7094,10 +7094,10 @@
         <v>521</v>
       </c>
       <c r="F220" t="s">
+        <v>520</v>
+      </c>
+      <c r="G220" t="s">
         <v>521</v>
-      </c>
-      <c r="G220" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -7117,10 +7117,10 @@
         <v>521</v>
       </c>
       <c r="F221" t="s">
+        <v>520</v>
+      </c>
+      <c r="G221" t="s">
         <v>521</v>
-      </c>
-      <c r="G221" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -7140,10 +7140,10 @@
         <v>521</v>
       </c>
       <c r="F222" t="s">
+        <v>520</v>
+      </c>
+      <c r="G222" t="s">
         <v>521</v>
-      </c>
-      <c r="G222" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -7163,10 +7163,10 @@
         <v>537</v>
       </c>
       <c r="F223" t="s">
+        <v>536</v>
+      </c>
+      <c r="G223" t="s">
         <v>537</v>
-      </c>
-      <c r="G223" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -7186,10 +7186,10 @@
         <v>537</v>
       </c>
       <c r="F224" t="s">
+        <v>536</v>
+      </c>
+      <c r="G224" t="s">
         <v>537</v>
-      </c>
-      <c r="G224" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -7209,10 +7209,10 @@
         <v>537</v>
       </c>
       <c r="F225" t="s">
+        <v>536</v>
+      </c>
+      <c r="G225" t="s">
         <v>537</v>
-      </c>
-      <c r="G225" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -7232,10 +7232,10 @@
         <v>545</v>
       </c>
       <c r="F226" t="s">
+        <v>544</v>
+      </c>
+      <c r="G226" t="s">
         <v>545</v>
-      </c>
-      <c r="G226" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -7255,10 +7255,10 @@
         <v>549</v>
       </c>
       <c r="F227" t="s">
+        <v>548</v>
+      </c>
+      <c r="G227" t="s">
         <v>549</v>
-      </c>
-      <c r="G227" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -7278,10 +7278,10 @@
         <v>553</v>
       </c>
       <c r="F228" t="s">
+        <v>552</v>
+      </c>
+      <c r="G228" t="s">
         <v>553</v>
-      </c>
-      <c r="G228" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -7301,10 +7301,10 @@
         <v>557</v>
       </c>
       <c r="F229" t="s">
+        <v>556</v>
+      </c>
+      <c r="G229" t="s">
         <v>557</v>
-      </c>
-      <c r="G229" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -7324,10 +7324,10 @@
         <v>561</v>
       </c>
       <c r="F230" t="s">
+        <v>560</v>
+      </c>
+      <c r="G230" t="s">
         <v>561</v>
-      </c>
-      <c r="G230" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -7347,10 +7347,10 @@
         <v>561</v>
       </c>
       <c r="F231" t="s">
+        <v>560</v>
+      </c>
+      <c r="G231" t="s">
         <v>561</v>
-      </c>
-      <c r="G231" t="s">
-        <v>560</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/en/SectorGroup.xlsx
+++ b/api/xlsx/en/SectorGroup.xlsx
@@ -31,12 +31,12 @@
     <t>codeforiati:group-name</t>
   </si>
   <si>
+    <t>codeforiati:category-name</t>
+  </si>
+  <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
-    <t>codeforiati:category-name</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -52,12 +52,12 @@
     <t>Education</t>
   </si>
   <si>
+    <t>Education, Level Unspecified</t>
+  </si>
+  <si>
     <t>110</t>
   </si>
   <si>
-    <t>Education, Level Unspecified</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -154,12 +154,12 @@
     <t>Health</t>
   </si>
   <si>
+    <t>Health, General</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
-    <t>Health, General</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -394,12 +394,12 @@
     <t>Government &amp; Civil Society</t>
   </si>
   <si>
+    <t>Government &amp; Civil Society-general</t>
+  </si>
+  <si>
     <t>150</t>
   </si>
   <si>
-    <t>Government &amp; Civil Society-general</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -694,12 +694,12 @@
     <t>Energy</t>
   </si>
   <si>
+    <t>Energy Policy</t>
+  </si>
+  <si>
     <t>230</t>
   </si>
   <si>
-    <t>Energy Policy</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -976,12 +976,12 @@
     <t>Agriculture, Forestry, Fishing</t>
   </si>
   <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
     <t>310</t>
   </si>
   <si>
-    <t>Agriculture</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1174,10 +1174,10 @@
     <t>Industry, Mining, Construction</t>
   </si>
   <si>
+    <t>Industry</t>
+  </si>
+  <si>
     <t>320</t>
-  </si>
-  <si>
-    <t>Industry</t>
   </si>
   <si>
     <t>32120</t>
@@ -2172,10 +2172,10 @@
         <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2195,10 +2195,10 @@
         <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G7" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2218,10 +2218,10 @@
         <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G8" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2241,10 +2241,10 @@
         <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G9" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2264,10 +2264,10 @@
         <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="G10" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2287,10 +2287,10 @@
         <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="G11" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2310,10 +2310,10 @@
         <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="G12" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2333,10 +2333,10 @@
         <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="G13" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2448,10 +2448,10 @@
         <v>45</v>
       </c>
       <c r="F18" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G18" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2471,10 +2471,10 @@
         <v>45</v>
       </c>
       <c r="F19" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G19" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2494,10 +2494,10 @@
         <v>45</v>
       </c>
       <c r="F20" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G20" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2517,10 +2517,10 @@
         <v>45</v>
       </c>
       <c r="F21" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G21" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2540,10 +2540,10 @@
         <v>45</v>
       </c>
       <c r="F22" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G22" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2563,10 +2563,10 @@
         <v>45</v>
       </c>
       <c r="F23" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G23" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2586,10 +2586,10 @@
         <v>45</v>
       </c>
       <c r="F24" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G24" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2609,10 +2609,10 @@
         <v>45</v>
       </c>
       <c r="F25" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G25" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2632,10 +2632,10 @@
         <v>45</v>
       </c>
       <c r="F26" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G26" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2655,10 +2655,10 @@
         <v>45</v>
       </c>
       <c r="F27" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G27" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2678,10 +2678,10 @@
         <v>45</v>
       </c>
       <c r="F28" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G28" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2701,10 +2701,10 @@
         <v>45</v>
       </c>
       <c r="F29" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G29" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2724,10 +2724,10 @@
         <v>45</v>
       </c>
       <c r="F30" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G30" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2747,10 +2747,10 @@
         <v>45</v>
       </c>
       <c r="F31" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G31" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2770,10 +2770,10 @@
         <v>89</v>
       </c>
       <c r="F32" t="s">
+        <v>89</v>
+      </c>
+      <c r="G32" t="s">
         <v>88</v>
-      </c>
-      <c r="G32" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2793,10 +2793,10 @@
         <v>89</v>
       </c>
       <c r="F33" t="s">
+        <v>89</v>
+      </c>
+      <c r="G33" t="s">
         <v>88</v>
-      </c>
-      <c r="G33" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2816,10 +2816,10 @@
         <v>89</v>
       </c>
       <c r="F34" t="s">
+        <v>89</v>
+      </c>
+      <c r="G34" t="s">
         <v>88</v>
-      </c>
-      <c r="G34" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2839,10 +2839,10 @@
         <v>89</v>
       </c>
       <c r="F35" t="s">
+        <v>89</v>
+      </c>
+      <c r="G35" t="s">
         <v>88</v>
-      </c>
-      <c r="G35" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2862,10 +2862,10 @@
         <v>89</v>
       </c>
       <c r="F36" t="s">
+        <v>89</v>
+      </c>
+      <c r="G36" t="s">
         <v>88</v>
-      </c>
-      <c r="G36" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2885,10 +2885,10 @@
         <v>101</v>
       </c>
       <c r="F37" t="s">
+        <v>101</v>
+      </c>
+      <c r="G37" t="s">
         <v>100</v>
-      </c>
-      <c r="G37" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2908,10 +2908,10 @@
         <v>101</v>
       </c>
       <c r="F38" t="s">
+        <v>101</v>
+      </c>
+      <c r="G38" t="s">
         <v>100</v>
-      </c>
-      <c r="G38" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2931,10 +2931,10 @@
         <v>101</v>
       </c>
       <c r="F39" t="s">
+        <v>101</v>
+      </c>
+      <c r="G39" t="s">
         <v>100</v>
-      </c>
-      <c r="G39" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2954,10 +2954,10 @@
         <v>101</v>
       </c>
       <c r="F40" t="s">
+        <v>101</v>
+      </c>
+      <c r="G40" t="s">
         <v>100</v>
-      </c>
-      <c r="G40" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2977,10 +2977,10 @@
         <v>101</v>
       </c>
       <c r="F41" t="s">
+        <v>101</v>
+      </c>
+      <c r="G41" t="s">
         <v>100</v>
-      </c>
-      <c r="G41" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -3000,10 +3000,10 @@
         <v>101</v>
       </c>
       <c r="F42" t="s">
+        <v>101</v>
+      </c>
+      <c r="G42" t="s">
         <v>100</v>
-      </c>
-      <c r="G42" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3023,10 +3023,10 @@
         <v>101</v>
       </c>
       <c r="F43" t="s">
+        <v>101</v>
+      </c>
+      <c r="G43" t="s">
         <v>100</v>
-      </c>
-      <c r="G43" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3046,10 +3046,10 @@
         <v>101</v>
       </c>
       <c r="F44" t="s">
+        <v>101</v>
+      </c>
+      <c r="G44" t="s">
         <v>100</v>
-      </c>
-      <c r="G44" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3069,10 +3069,10 @@
         <v>101</v>
       </c>
       <c r="F45" t="s">
+        <v>101</v>
+      </c>
+      <c r="G45" t="s">
         <v>100</v>
-      </c>
-      <c r="G45" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3092,10 +3092,10 @@
         <v>101</v>
       </c>
       <c r="F46" t="s">
+        <v>101</v>
+      </c>
+      <c r="G46" t="s">
         <v>100</v>
-      </c>
-      <c r="G46" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3115,10 +3115,10 @@
         <v>101</v>
       </c>
       <c r="F47" t="s">
+        <v>101</v>
+      </c>
+      <c r="G47" t="s">
         <v>100</v>
-      </c>
-      <c r="G47" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3506,10 +3506,10 @@
         <v>125</v>
       </c>
       <c r="F64" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G64" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3529,10 +3529,10 @@
         <v>125</v>
       </c>
       <c r="F65" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G65" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3552,10 +3552,10 @@
         <v>125</v>
       </c>
       <c r="F66" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G66" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3575,10 +3575,10 @@
         <v>125</v>
       </c>
       <c r="F67" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G67" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3598,10 +3598,10 @@
         <v>125</v>
       </c>
       <c r="F68" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G68" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3621,10 +3621,10 @@
         <v>125</v>
       </c>
       <c r="F69" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G69" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3644,10 +3644,10 @@
         <v>175</v>
       </c>
       <c r="F70" t="s">
+        <v>175</v>
+      </c>
+      <c r="G70" t="s">
         <v>174</v>
-      </c>
-      <c r="G70" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3667,10 +3667,10 @@
         <v>175</v>
       </c>
       <c r="F71" t="s">
+        <v>175</v>
+      </c>
+      <c r="G71" t="s">
         <v>174</v>
-      </c>
-      <c r="G71" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3690,10 +3690,10 @@
         <v>175</v>
       </c>
       <c r="F72" t="s">
+        <v>175</v>
+      </c>
+      <c r="G72" t="s">
         <v>174</v>
-      </c>
-      <c r="G72" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3713,10 +3713,10 @@
         <v>175</v>
       </c>
       <c r="F73" t="s">
+        <v>175</v>
+      </c>
+      <c r="G73" t="s">
         <v>174</v>
-      </c>
-      <c r="G73" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3736,10 +3736,10 @@
         <v>175</v>
       </c>
       <c r="F74" t="s">
+        <v>175</v>
+      </c>
+      <c r="G74" t="s">
         <v>174</v>
-      </c>
-      <c r="G74" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3759,10 +3759,10 @@
         <v>175</v>
       </c>
       <c r="F75" t="s">
+        <v>175</v>
+      </c>
+      <c r="G75" t="s">
         <v>174</v>
-      </c>
-      <c r="G75" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3782,10 +3782,10 @@
         <v>175</v>
       </c>
       <c r="F76" t="s">
+        <v>175</v>
+      </c>
+      <c r="G76" t="s">
         <v>174</v>
-      </c>
-      <c r="G76" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3805,10 +3805,10 @@
         <v>175</v>
       </c>
       <c r="F77" t="s">
+        <v>175</v>
+      </c>
+      <c r="G77" t="s">
         <v>174</v>
-      </c>
-      <c r="G77" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3828,10 +3828,10 @@
         <v>175</v>
       </c>
       <c r="F78" t="s">
+        <v>175</v>
+      </c>
+      <c r="G78" t="s">
         <v>174</v>
-      </c>
-      <c r="G78" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3851,10 +3851,10 @@
         <v>175</v>
       </c>
       <c r="F79" t="s">
+        <v>175</v>
+      </c>
+      <c r="G79" t="s">
         <v>174</v>
-      </c>
-      <c r="G79" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3874,10 +3874,10 @@
         <v>175</v>
       </c>
       <c r="F80" t="s">
+        <v>175</v>
+      </c>
+      <c r="G80" t="s">
         <v>174</v>
-      </c>
-      <c r="G80" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3897,10 +3897,10 @@
         <v>199</v>
       </c>
       <c r="F81" t="s">
+        <v>199</v>
+      </c>
+      <c r="G81" t="s">
         <v>198</v>
-      </c>
-      <c r="G81" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3920,10 +3920,10 @@
         <v>199</v>
       </c>
       <c r="F82" t="s">
+        <v>199</v>
+      </c>
+      <c r="G82" t="s">
         <v>198</v>
-      </c>
-      <c r="G82" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3943,10 +3943,10 @@
         <v>199</v>
       </c>
       <c r="F83" t="s">
+        <v>199</v>
+      </c>
+      <c r="G83" t="s">
         <v>198</v>
-      </c>
-      <c r="G83" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3966,10 +3966,10 @@
         <v>199</v>
       </c>
       <c r="F84" t="s">
+        <v>199</v>
+      </c>
+      <c r="G84" t="s">
         <v>198</v>
-      </c>
-      <c r="G84" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3989,10 +3989,10 @@
         <v>199</v>
       </c>
       <c r="F85" t="s">
+        <v>199</v>
+      </c>
+      <c r="G85" t="s">
         <v>198</v>
-      </c>
-      <c r="G85" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4012,10 +4012,10 @@
         <v>199</v>
       </c>
       <c r="F86" t="s">
+        <v>199</v>
+      </c>
+      <c r="G86" t="s">
         <v>198</v>
-      </c>
-      <c r="G86" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4035,10 +4035,10 @@
         <v>199</v>
       </c>
       <c r="F87" t="s">
+        <v>199</v>
+      </c>
+      <c r="G87" t="s">
         <v>198</v>
-      </c>
-      <c r="G87" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4058,10 +4058,10 @@
         <v>215</v>
       </c>
       <c r="F88" t="s">
+        <v>215</v>
+      </c>
+      <c r="G88" t="s">
         <v>214</v>
-      </c>
-      <c r="G88" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4081,10 +4081,10 @@
         <v>215</v>
       </c>
       <c r="F89" t="s">
+        <v>215</v>
+      </c>
+      <c r="G89" t="s">
         <v>214</v>
-      </c>
-      <c r="G89" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4104,10 +4104,10 @@
         <v>215</v>
       </c>
       <c r="F90" t="s">
+        <v>215</v>
+      </c>
+      <c r="G90" t="s">
         <v>214</v>
-      </c>
-      <c r="G90" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4127,10 +4127,10 @@
         <v>215</v>
       </c>
       <c r="F91" t="s">
+        <v>215</v>
+      </c>
+      <c r="G91" t="s">
         <v>214</v>
-      </c>
-      <c r="G91" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4242,10 +4242,10 @@
         <v>225</v>
       </c>
       <c r="F96" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G96" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -4265,10 +4265,10 @@
         <v>225</v>
       </c>
       <c r="F97" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G97" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4288,10 +4288,10 @@
         <v>225</v>
       </c>
       <c r="F98" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G98" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4311,10 +4311,10 @@
         <v>225</v>
       </c>
       <c r="F99" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G99" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4334,10 +4334,10 @@
         <v>225</v>
       </c>
       <c r="F100" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G100" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4357,10 +4357,10 @@
         <v>225</v>
       </c>
       <c r="F101" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G101" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4380,10 +4380,10 @@
         <v>225</v>
       </c>
       <c r="F102" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G102" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4403,10 +4403,10 @@
         <v>225</v>
       </c>
       <c r="F103" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G103" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4426,10 +4426,10 @@
         <v>225</v>
       </c>
       <c r="F104" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G104" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4449,10 +4449,10 @@
         <v>225</v>
       </c>
       <c r="F105" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G105" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4472,10 +4472,10 @@
         <v>225</v>
       </c>
       <c r="F106" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G106" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4495,10 +4495,10 @@
         <v>225</v>
       </c>
       <c r="F107" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G107" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4518,10 +4518,10 @@
         <v>225</v>
       </c>
       <c r="F108" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G108" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4541,10 +4541,10 @@
         <v>225</v>
       </c>
       <c r="F109" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G109" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4564,10 +4564,10 @@
         <v>225</v>
       </c>
       <c r="F110" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G110" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4587,10 +4587,10 @@
         <v>225</v>
       </c>
       <c r="F111" t="s">
-        <v>226</v>
+        <v>271</v>
       </c>
       <c r="G111" t="s">
-        <v>271</v>
+        <v>227</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4610,10 +4610,10 @@
         <v>225</v>
       </c>
       <c r="F112" t="s">
-        <v>226</v>
+        <v>275</v>
       </c>
       <c r="G112" t="s">
-        <v>275</v>
+        <v>227</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4633,10 +4633,10 @@
         <v>225</v>
       </c>
       <c r="F113" t="s">
-        <v>226</v>
+        <v>279</v>
       </c>
       <c r="G113" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4656,10 +4656,10 @@
         <v>225</v>
       </c>
       <c r="F114" t="s">
-        <v>226</v>
+        <v>279</v>
       </c>
       <c r="G114" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4679,10 +4679,10 @@
         <v>225</v>
       </c>
       <c r="F115" t="s">
-        <v>226</v>
+        <v>279</v>
       </c>
       <c r="G115" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4702,10 +4702,10 @@
         <v>225</v>
       </c>
       <c r="F116" t="s">
-        <v>226</v>
+        <v>279</v>
       </c>
       <c r="G116" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4725,10 +4725,10 @@
         <v>225</v>
       </c>
       <c r="F117" t="s">
-        <v>226</v>
+        <v>279</v>
       </c>
       <c r="G117" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4748,10 +4748,10 @@
         <v>225</v>
       </c>
       <c r="F118" t="s">
-        <v>226</v>
+        <v>279</v>
       </c>
       <c r="G118" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4771,10 +4771,10 @@
         <v>225</v>
       </c>
       <c r="F119" t="s">
-        <v>226</v>
+        <v>279</v>
       </c>
       <c r="G119" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4794,10 +4794,10 @@
         <v>295</v>
       </c>
       <c r="F120" t="s">
+        <v>295</v>
+      </c>
+      <c r="G120" t="s">
         <v>294</v>
-      </c>
-      <c r="G120" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4817,10 +4817,10 @@
         <v>295</v>
       </c>
       <c r="F121" t="s">
+        <v>295</v>
+      </c>
+      <c r="G121" t="s">
         <v>294</v>
-      </c>
-      <c r="G121" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4840,10 +4840,10 @@
         <v>295</v>
       </c>
       <c r="F122" t="s">
+        <v>295</v>
+      </c>
+      <c r="G122" t="s">
         <v>294</v>
-      </c>
-      <c r="G122" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4863,10 +4863,10 @@
         <v>295</v>
       </c>
       <c r="F123" t="s">
+        <v>295</v>
+      </c>
+      <c r="G123" t="s">
         <v>294</v>
-      </c>
-      <c r="G123" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4886,10 +4886,10 @@
         <v>295</v>
       </c>
       <c r="F124" t="s">
+        <v>295</v>
+      </c>
+      <c r="G124" t="s">
         <v>294</v>
-      </c>
-      <c r="G124" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4909,10 +4909,10 @@
         <v>295</v>
       </c>
       <c r="F125" t="s">
+        <v>295</v>
+      </c>
+      <c r="G125" t="s">
         <v>294</v>
-      </c>
-      <c r="G125" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4932,10 +4932,10 @@
         <v>309</v>
       </c>
       <c r="F126" t="s">
+        <v>309</v>
+      </c>
+      <c r="G126" t="s">
         <v>308</v>
-      </c>
-      <c r="G126" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4955,10 +4955,10 @@
         <v>309</v>
       </c>
       <c r="F127" t="s">
+        <v>309</v>
+      </c>
+      <c r="G127" t="s">
         <v>308</v>
-      </c>
-      <c r="G127" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4978,10 +4978,10 @@
         <v>309</v>
       </c>
       <c r="F128" t="s">
+        <v>309</v>
+      </c>
+      <c r="G128" t="s">
         <v>308</v>
-      </c>
-      <c r="G128" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -5001,10 +5001,10 @@
         <v>309</v>
       </c>
       <c r="F129" t="s">
+        <v>309</v>
+      </c>
+      <c r="G129" t="s">
         <v>308</v>
-      </c>
-      <c r="G129" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -5438,10 +5438,10 @@
         <v>319</v>
       </c>
       <c r="F148" t="s">
-        <v>320</v>
+        <v>359</v>
       </c>
       <c r="G148" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5461,10 +5461,10 @@
         <v>319</v>
       </c>
       <c r="F149" t="s">
-        <v>320</v>
+        <v>359</v>
       </c>
       <c r="G149" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5484,10 +5484,10 @@
         <v>319</v>
       </c>
       <c r="F150" t="s">
-        <v>320</v>
+        <v>359</v>
       </c>
       <c r="G150" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5507,10 +5507,10 @@
         <v>319</v>
       </c>
       <c r="F151" t="s">
-        <v>320</v>
+        <v>359</v>
       </c>
       <c r="G151" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5530,10 +5530,10 @@
         <v>319</v>
       </c>
       <c r="F152" t="s">
-        <v>320</v>
+        <v>359</v>
       </c>
       <c r="G152" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5553,10 +5553,10 @@
         <v>319</v>
       </c>
       <c r="F153" t="s">
-        <v>320</v>
+        <v>359</v>
       </c>
       <c r="G153" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5576,10 +5576,10 @@
         <v>319</v>
       </c>
       <c r="F154" t="s">
-        <v>320</v>
+        <v>373</v>
       </c>
       <c r="G154" t="s">
-        <v>373</v>
+        <v>321</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5599,10 +5599,10 @@
         <v>319</v>
       </c>
       <c r="F155" t="s">
-        <v>320</v>
+        <v>373</v>
       </c>
       <c r="G155" t="s">
-        <v>373</v>
+        <v>321</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5622,10 +5622,10 @@
         <v>319</v>
       </c>
       <c r="F156" t="s">
-        <v>320</v>
+        <v>373</v>
       </c>
       <c r="G156" t="s">
-        <v>373</v>
+        <v>321</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5645,10 +5645,10 @@
         <v>319</v>
       </c>
       <c r="F157" t="s">
-        <v>320</v>
+        <v>373</v>
       </c>
       <c r="G157" t="s">
-        <v>373</v>
+        <v>321</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5668,10 +5668,10 @@
         <v>319</v>
       </c>
       <c r="F158" t="s">
-        <v>320</v>
+        <v>373</v>
       </c>
       <c r="G158" t="s">
-        <v>373</v>
+        <v>321</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -6128,10 +6128,10 @@
         <v>385</v>
       </c>
       <c r="F178" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G178" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -6151,10 +6151,10 @@
         <v>385</v>
       </c>
       <c r="F179" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G179" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -6174,10 +6174,10 @@
         <v>385</v>
       </c>
       <c r="F180" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G180" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -6197,10 +6197,10 @@
         <v>385</v>
       </c>
       <c r="F181" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G181" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -6220,10 +6220,10 @@
         <v>385</v>
       </c>
       <c r="F182" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G182" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -6243,10 +6243,10 @@
         <v>385</v>
       </c>
       <c r="F183" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G183" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -6266,10 +6266,10 @@
         <v>385</v>
       </c>
       <c r="F184" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G184" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -6289,10 +6289,10 @@
         <v>385</v>
       </c>
       <c r="F185" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G185" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -6312,10 +6312,10 @@
         <v>385</v>
       </c>
       <c r="F186" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G186" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -6335,10 +6335,10 @@
         <v>385</v>
       </c>
       <c r="F187" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G187" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -6358,10 +6358,10 @@
         <v>385</v>
       </c>
       <c r="F188" t="s">
-        <v>386</v>
+        <v>449</v>
       </c>
       <c r="G188" t="s">
-        <v>449</v>
+        <v>387</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -6381,10 +6381,10 @@
         <v>453</v>
       </c>
       <c r="F189" t="s">
+        <v>453</v>
+      </c>
+      <c r="G189" t="s">
         <v>452</v>
-      </c>
-      <c r="G189" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6404,10 +6404,10 @@
         <v>453</v>
       </c>
       <c r="F190" t="s">
+        <v>453</v>
+      </c>
+      <c r="G190" t="s">
         <v>452</v>
-      </c>
-      <c r="G190" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6427,10 +6427,10 @@
         <v>453</v>
       </c>
       <c r="F191" t="s">
+        <v>453</v>
+      </c>
+      <c r="G191" t="s">
         <v>452</v>
-      </c>
-      <c r="G191" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6450,10 +6450,10 @@
         <v>453</v>
       </c>
       <c r="F192" t="s">
+        <v>453</v>
+      </c>
+      <c r="G192" t="s">
         <v>452</v>
-      </c>
-      <c r="G192" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6473,10 +6473,10 @@
         <v>453</v>
       </c>
       <c r="F193" t="s">
+        <v>453</v>
+      </c>
+      <c r="G193" t="s">
         <v>452</v>
-      </c>
-      <c r="G193" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6496,10 +6496,10 @@
         <v>453</v>
       </c>
       <c r="F194" t="s">
+        <v>453</v>
+      </c>
+      <c r="G194" t="s">
         <v>452</v>
-      </c>
-      <c r="G194" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6519,10 +6519,10 @@
         <v>467</v>
       </c>
       <c r="F195" t="s">
+        <v>467</v>
+      </c>
+      <c r="G195" t="s">
         <v>466</v>
-      </c>
-      <c r="G195" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6542,10 +6542,10 @@
         <v>471</v>
       </c>
       <c r="F196" t="s">
+        <v>471</v>
+      </c>
+      <c r="G196" t="s">
         <v>470</v>
-      </c>
-      <c r="G196" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6565,10 +6565,10 @@
         <v>471</v>
       </c>
       <c r="F197" t="s">
+        <v>471</v>
+      </c>
+      <c r="G197" t="s">
         <v>470</v>
-      </c>
-      <c r="G197" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6588,10 +6588,10 @@
         <v>471</v>
       </c>
       <c r="F198" t="s">
+        <v>471</v>
+      </c>
+      <c r="G198" t="s">
         <v>470</v>
-      </c>
-      <c r="G198" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6611,10 +6611,10 @@
         <v>471</v>
       </c>
       <c r="F199" t="s">
+        <v>471</v>
+      </c>
+      <c r="G199" t="s">
         <v>470</v>
-      </c>
-      <c r="G199" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6634,10 +6634,10 @@
         <v>471</v>
       </c>
       <c r="F200" t="s">
+        <v>471</v>
+      </c>
+      <c r="G200" t="s">
         <v>470</v>
-      </c>
-      <c r="G200" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6657,10 +6657,10 @@
         <v>471</v>
       </c>
       <c r="F201" t="s">
+        <v>471</v>
+      </c>
+      <c r="G201" t="s">
         <v>470</v>
-      </c>
-      <c r="G201" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6680,10 +6680,10 @@
         <v>485</v>
       </c>
       <c r="F202" t="s">
+        <v>485</v>
+      </c>
+      <c r="G202" t="s">
         <v>484</v>
-      </c>
-      <c r="G202" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6703,10 +6703,10 @@
         <v>485</v>
       </c>
       <c r="F203" t="s">
+        <v>485</v>
+      </c>
+      <c r="G203" t="s">
         <v>484</v>
-      </c>
-      <c r="G203" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6726,10 +6726,10 @@
         <v>485</v>
       </c>
       <c r="F204" t="s">
+        <v>485</v>
+      </c>
+      <c r="G204" t="s">
         <v>484</v>
-      </c>
-      <c r="G204" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6749,10 +6749,10 @@
         <v>485</v>
       </c>
       <c r="F205" t="s">
+        <v>485</v>
+      </c>
+      <c r="G205" t="s">
         <v>484</v>
-      </c>
-      <c r="G205" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6772,10 +6772,10 @@
         <v>485</v>
       </c>
       <c r="F206" t="s">
+        <v>485</v>
+      </c>
+      <c r="G206" t="s">
         <v>484</v>
-      </c>
-      <c r="G206" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6795,10 +6795,10 @@
         <v>485</v>
       </c>
       <c r="F207" t="s">
+        <v>485</v>
+      </c>
+      <c r="G207" t="s">
         <v>484</v>
-      </c>
-      <c r="G207" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6818,10 +6818,10 @@
         <v>485</v>
       </c>
       <c r="F208" t="s">
+        <v>485</v>
+      </c>
+      <c r="G208" t="s">
         <v>484</v>
-      </c>
-      <c r="G208" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6841,10 +6841,10 @@
         <v>485</v>
       </c>
       <c r="F209" t="s">
+        <v>485</v>
+      </c>
+      <c r="G209" t="s">
         <v>484</v>
-      </c>
-      <c r="G209" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6864,10 +6864,10 @@
         <v>485</v>
       </c>
       <c r="F210" t="s">
+        <v>485</v>
+      </c>
+      <c r="G210" t="s">
         <v>484</v>
-      </c>
-      <c r="G210" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6887,10 +6887,10 @@
         <v>485</v>
       </c>
       <c r="F211" t="s">
+        <v>485</v>
+      </c>
+      <c r="G211" t="s">
         <v>484</v>
-      </c>
-      <c r="G211" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6910,10 +6910,10 @@
         <v>507</v>
       </c>
       <c r="F212" t="s">
+        <v>507</v>
+      </c>
+      <c r="G212" t="s">
         <v>506</v>
-      </c>
-      <c r="G212" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6933,10 +6933,10 @@
         <v>511</v>
       </c>
       <c r="F213" t="s">
+        <v>511</v>
+      </c>
+      <c r="G213" t="s">
         <v>510</v>
-      </c>
-      <c r="G213" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6956,10 +6956,10 @@
         <v>515</v>
       </c>
       <c r="F214" t="s">
+        <v>515</v>
+      </c>
+      <c r="G214" t="s">
         <v>514</v>
-      </c>
-      <c r="G214" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6979,10 +6979,10 @@
         <v>515</v>
       </c>
       <c r="F215" t="s">
+        <v>515</v>
+      </c>
+      <c r="G215" t="s">
         <v>514</v>
-      </c>
-      <c r="G215" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -7002,10 +7002,10 @@
         <v>521</v>
       </c>
       <c r="F216" t="s">
+        <v>521</v>
+      </c>
+      <c r="G216" t="s">
         <v>520</v>
-      </c>
-      <c r="G216" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -7025,10 +7025,10 @@
         <v>521</v>
       </c>
       <c r="F217" t="s">
+        <v>521</v>
+      </c>
+      <c r="G217" t="s">
         <v>520</v>
-      </c>
-      <c r="G217" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -7048,10 +7048,10 @@
         <v>521</v>
       </c>
       <c r="F218" t="s">
+        <v>521</v>
+      </c>
+      <c r="G218" t="s">
         <v>520</v>
-      </c>
-      <c r="G218" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -7071,10 +7071,10 @@
         <v>521</v>
       </c>
       <c r="F219" t="s">
+        <v>521</v>
+      </c>
+      <c r="G219" t="s">
         <v>520</v>
-      </c>
-      <c r="G219" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -7094,10 +7094,10 @@
         <v>521</v>
       </c>
       <c r="F220" t="s">
+        <v>521</v>
+      </c>
+      <c r="G220" t="s">
         <v>520</v>
-      </c>
-      <c r="G220" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -7117,10 +7117,10 @@
         <v>521</v>
       </c>
       <c r="F221" t="s">
+        <v>521</v>
+      </c>
+      <c r="G221" t="s">
         <v>520</v>
-      </c>
-      <c r="G221" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -7140,10 +7140,10 @@
         <v>521</v>
       </c>
       <c r="F222" t="s">
+        <v>521</v>
+      </c>
+      <c r="G222" t="s">
         <v>520</v>
-      </c>
-      <c r="G222" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -7163,10 +7163,10 @@
         <v>537</v>
       </c>
       <c r="F223" t="s">
+        <v>537</v>
+      </c>
+      <c r="G223" t="s">
         <v>536</v>
-      </c>
-      <c r="G223" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -7186,10 +7186,10 @@
         <v>537</v>
       </c>
       <c r="F224" t="s">
+        <v>537</v>
+      </c>
+      <c r="G224" t="s">
         <v>536</v>
-      </c>
-      <c r="G224" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -7209,10 +7209,10 @@
         <v>537</v>
       </c>
       <c r="F225" t="s">
+        <v>537</v>
+      </c>
+      <c r="G225" t="s">
         <v>536</v>
-      </c>
-      <c r="G225" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -7232,10 +7232,10 @@
         <v>545</v>
       </c>
       <c r="F226" t="s">
+        <v>545</v>
+      </c>
+      <c r="G226" t="s">
         <v>544</v>
-      </c>
-      <c r="G226" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -7255,10 +7255,10 @@
         <v>549</v>
       </c>
       <c r="F227" t="s">
+        <v>549</v>
+      </c>
+      <c r="G227" t="s">
         <v>548</v>
-      </c>
-      <c r="G227" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -7278,10 +7278,10 @@
         <v>553</v>
       </c>
       <c r="F228" t="s">
+        <v>553</v>
+      </c>
+      <c r="G228" t="s">
         <v>552</v>
-      </c>
-      <c r="G228" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -7301,10 +7301,10 @@
         <v>557</v>
       </c>
       <c r="F229" t="s">
+        <v>557</v>
+      </c>
+      <c r="G229" t="s">
         <v>556</v>
-      </c>
-      <c r="G229" t="s">
-        <v>557</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -7324,10 +7324,10 @@
         <v>561</v>
       </c>
       <c r="F230" t="s">
+        <v>561</v>
+      </c>
+      <c r="G230" t="s">
         <v>560</v>
-      </c>
-      <c r="G230" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -7347,10 +7347,10 @@
         <v>561</v>
       </c>
       <c r="F231" t="s">
+        <v>561</v>
+      </c>
+      <c r="G231" t="s">
         <v>560</v>
-      </c>
-      <c r="G231" t="s">
-        <v>561</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/en/SectorGroup.xlsx
+++ b/api/xlsx/en/SectorGroup.xlsx
@@ -25,18 +25,18 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
+    <t>codeforiati:category-name</t>
+  </si>
+  <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
-    <t>codeforiati:category-name</t>
-  </si>
-  <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -46,18 +46,18 @@
     <t>active</t>
   </si>
   <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>Education, Level Unspecified</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
     <t>111</t>
   </si>
   <si>
-    <t>Education</t>
-  </si>
-  <si>
-    <t>Education, Level Unspecified</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -82,12 +82,12 @@
     <t>Primary education</t>
   </si>
   <si>
+    <t>Basic Education</t>
+  </si>
+  <si>
     <t>112</t>
   </si>
   <si>
-    <t>Basic Education</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -112,12 +112,12 @@
     <t>Secondary education</t>
   </si>
   <si>
+    <t>Secondary Education</t>
+  </si>
+  <si>
     <t>113</t>
   </si>
   <si>
-    <t>Secondary Education</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
@@ -130,12 +130,12 @@
     <t>Higher education</t>
   </si>
   <si>
+    <t>Post-Secondary Education</t>
+  </si>
+  <si>
     <t>114</t>
   </si>
   <si>
-    <t>Post-Secondary Education</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -148,18 +148,18 @@
     <t>Health policy and administrative management</t>
   </si>
   <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>Health, General</t>
+  </si>
+  <si>
+    <t>Health</t>
+  </si>
+  <si>
     <t>121</t>
   </si>
   <si>
-    <t>Health</t>
-  </si>
-  <si>
-    <t>Health, General</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -184,12 +184,12 @@
     <t>Basic health care</t>
   </si>
   <si>
+    <t>Basic Health</t>
+  </si>
+  <si>
     <t>122</t>
   </si>
   <si>
-    <t>Basic Health</t>
-  </si>
-  <si>
     <t>12230</t>
   </si>
   <si>
@@ -238,12 +238,12 @@
     <t>NCDs control, general</t>
   </si>
   <si>
+    <t>Non-communicable diseases (NCDs)</t>
+  </si>
+  <si>
     <t>123</t>
   </si>
   <si>
-    <t>Non-communicable diseases (NCDs)</t>
-  </si>
-  <si>
     <t>12320</t>
   </si>
   <si>
@@ -388,18 +388,18 @@
     <t>Public sector policy and administrative management</t>
   </si>
   <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>Government &amp; Civil Society-general</t>
+  </si>
+  <si>
+    <t>Government &amp; Civil Society</t>
+  </si>
+  <si>
     <t>151</t>
   </si>
   <si>
-    <t>Government &amp; Civil Society</t>
-  </si>
-  <si>
-    <t>Government &amp; Civil Society-general</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -496,12 +496,12 @@
     <t>Security system management and reform</t>
   </si>
   <si>
+    <t>Conflict, Peace &amp; Security</t>
+  </si>
+  <si>
     <t>152</t>
   </si>
   <si>
-    <t>Conflict, Peace &amp; Security</t>
-  </si>
-  <si>
     <t>15220</t>
   </si>
   <si>
@@ -688,18 +688,18 @@
     <t>Energy policy and administrative management</t>
   </si>
   <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>Energy Policy</t>
+  </si>
+  <si>
+    <t>Energy</t>
+  </si>
+  <si>
     <t>231</t>
   </si>
   <si>
-    <t>Energy</t>
-  </si>
-  <si>
-    <t>Energy Policy</t>
-  </si>
-  <si>
-    <t>230</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -724,12 +724,12 @@
     <t>Energy generation, renewable sources - multiple technologies</t>
   </si>
   <si>
+    <t>Energy generation, renewable sources</t>
+  </si>
+  <si>
     <t>232</t>
   </si>
   <si>
-    <t>Energy generation, renewable sources</t>
-  </si>
-  <si>
     <t>23220</t>
   </si>
   <si>
@@ -784,12 +784,12 @@
     <t>Energy generation, non-renewable sources, unspecified</t>
   </si>
   <si>
+    <t>Energy generation, non-renewable sources</t>
+  </si>
+  <si>
     <t>233</t>
   </si>
   <si>
-    <t>Energy generation, non-renewable sources</t>
-  </si>
-  <si>
     <t>23320</t>
   </si>
   <si>
@@ -826,36 +826,36 @@
     <t>Hybrid energy electric power plants</t>
   </si>
   <si>
+    <t>Hybrid energy plants</t>
+  </si>
+  <si>
     <t>234</t>
   </si>
   <si>
-    <t>Hybrid energy plants</t>
-  </si>
-  <si>
     <t>23510</t>
   </si>
   <si>
     <t>Nuclear energy electric power plants and nuclear safety</t>
   </si>
   <si>
+    <t>Nuclear energy plants</t>
+  </si>
+  <si>
     <t>235</t>
   </si>
   <si>
-    <t>Nuclear energy plants</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
     <t>Heat plants</t>
   </si>
   <si>
+    <t>Energy distribution</t>
+  </si>
+  <si>
     <t>236</t>
   </si>
   <si>
-    <t>Energy distribution</t>
-  </si>
-  <si>
     <t>23620</t>
   </si>
   <si>
@@ -970,18 +970,18 @@
     <t>Agricultural policy and administrative management</t>
   </si>
   <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
+    <t>Agriculture, Forestry, Fishing</t>
+  </si>
+  <si>
     <t>311</t>
   </si>
   <si>
-    <t>Agriculture, Forestry, Fishing</t>
-  </si>
-  <si>
-    <t>Agriculture</t>
-  </si>
-  <si>
-    <t>310</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1090,12 +1090,12 @@
     <t>Forestry policy and administrative management</t>
   </si>
   <si>
+    <t>Forestry</t>
+  </si>
+  <si>
     <t>312</t>
   </si>
   <si>
-    <t>Forestry</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -1132,12 +1132,12 @@
     <t>Fishing policy and administrative management</t>
   </si>
   <si>
+    <t>Fishing</t>
+  </si>
+  <si>
     <t>313</t>
   </si>
   <si>
-    <t>Fishing</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -1168,18 +1168,18 @@
     <t>Industrial policy and administrative management</t>
   </si>
   <si>
+    <t>320</t>
+  </si>
+  <si>
+    <t>Industry</t>
+  </si>
+  <si>
+    <t>Industry, Mining, Construction</t>
+  </si>
+  <si>
     <t>321</t>
   </si>
   <si>
-    <t>Industry, Mining, Construction</t>
-  </si>
-  <si>
-    <t>Industry</t>
-  </si>
-  <si>
-    <t>320</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1294,12 +1294,12 @@
     <t>Mineral/mining policy and administrative management</t>
   </si>
   <si>
+    <t>Mineral Resources &amp; Mining</t>
+  </si>
+  <si>
     <t>322</t>
   </si>
   <si>
-    <t>Mineral Resources &amp; Mining</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -1360,10 +1360,10 @@
     <t>Construction policy and administrative management</t>
   </si>
   <si>
+    <t>Construction</t>
+  </si>
+  <si>
     <t>323</t>
-  </si>
-  <si>
-    <t>Construction</t>
   </si>
   <si>
     <t>33110</t>
@@ -2166,16 +2166,16 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
         <v>22</v>
       </c>
-      <c r="E6" t="s">
-        <v>11</v>
-      </c>
       <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" t="s">
         <v>23</v>
-      </c>
-      <c r="G6" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2189,16 +2189,16 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" t="s">
         <v>22</v>
       </c>
-      <c r="E7" t="s">
-        <v>11</v>
-      </c>
       <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" t="s">
         <v>23</v>
-      </c>
-      <c r="G7" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2212,16 +2212,16 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" t="s">
         <v>22</v>
       </c>
-      <c r="E8" t="s">
-        <v>11</v>
-      </c>
       <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" t="s">
         <v>23</v>
-      </c>
-      <c r="G8" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2235,16 +2235,16 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" t="s">
         <v>22</v>
       </c>
-      <c r="E9" t="s">
-        <v>11</v>
-      </c>
       <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" t="s">
         <v>23</v>
-      </c>
-      <c r="G9" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2258,16 +2258,16 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" t="s">
         <v>32</v>
       </c>
-      <c r="E10" t="s">
-        <v>11</v>
-      </c>
       <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" t="s">
         <v>33</v>
-      </c>
-      <c r="G10" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2281,16 +2281,16 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" t="s">
         <v>32</v>
       </c>
-      <c r="E11" t="s">
-        <v>11</v>
-      </c>
       <c r="F11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" t="s">
         <v>33</v>
-      </c>
-      <c r="G11" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2304,16 +2304,16 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" t="s">
         <v>38</v>
       </c>
-      <c r="E12" t="s">
-        <v>11</v>
-      </c>
       <c r="F12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" t="s">
         <v>39</v>
-      </c>
-      <c r="G12" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2327,16 +2327,16 @@
         <v>9</v>
       </c>
       <c r="D13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" t="s">
         <v>38</v>
       </c>
-      <c r="E13" t="s">
-        <v>11</v>
-      </c>
       <c r="F13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" t="s">
         <v>39</v>
-      </c>
-      <c r="G13" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2442,16 +2442,16 @@
         <v>9</v>
       </c>
       <c r="D18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18" t="s">
         <v>56</v>
       </c>
-      <c r="E18" t="s">
-        <v>45</v>
-      </c>
       <c r="F18" t="s">
+        <v>46</v>
+      </c>
+      <c r="G18" t="s">
         <v>57</v>
-      </c>
-      <c r="G18" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2465,16 +2465,16 @@
         <v>9</v>
       </c>
       <c r="D19" t="s">
+        <v>44</v>
+      </c>
+      <c r="E19" t="s">
         <v>56</v>
       </c>
-      <c r="E19" t="s">
-        <v>45</v>
-      </c>
       <c r="F19" t="s">
+        <v>46</v>
+      </c>
+      <c r="G19" t="s">
         <v>57</v>
-      </c>
-      <c r="G19" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2488,16 +2488,16 @@
         <v>9</v>
       </c>
       <c r="D20" t="s">
+        <v>44</v>
+      </c>
+      <c r="E20" t="s">
         <v>56</v>
       </c>
-      <c r="E20" t="s">
-        <v>45</v>
-      </c>
       <c r="F20" t="s">
+        <v>46</v>
+      </c>
+      <c r="G20" t="s">
         <v>57</v>
-      </c>
-      <c r="G20" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2511,16 +2511,16 @@
         <v>9</v>
       </c>
       <c r="D21" t="s">
+        <v>44</v>
+      </c>
+      <c r="E21" t="s">
         <v>56</v>
       </c>
-      <c r="E21" t="s">
-        <v>45</v>
-      </c>
       <c r="F21" t="s">
+        <v>46</v>
+      </c>
+      <c r="G21" t="s">
         <v>57</v>
-      </c>
-      <c r="G21" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2534,16 +2534,16 @@
         <v>9</v>
       </c>
       <c r="D22" t="s">
+        <v>44</v>
+      </c>
+      <c r="E22" t="s">
         <v>56</v>
       </c>
-      <c r="E22" t="s">
-        <v>45</v>
-      </c>
       <c r="F22" t="s">
+        <v>46</v>
+      </c>
+      <c r="G22" t="s">
         <v>57</v>
-      </c>
-      <c r="G22" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2557,16 +2557,16 @@
         <v>9</v>
       </c>
       <c r="D23" t="s">
+        <v>44</v>
+      </c>
+      <c r="E23" t="s">
         <v>56</v>
       </c>
-      <c r="E23" t="s">
-        <v>45</v>
-      </c>
       <c r="F23" t="s">
+        <v>46</v>
+      </c>
+      <c r="G23" t="s">
         <v>57</v>
-      </c>
-      <c r="G23" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2580,16 +2580,16 @@
         <v>9</v>
       </c>
       <c r="D24" t="s">
+        <v>44</v>
+      </c>
+      <c r="E24" t="s">
         <v>56</v>
       </c>
-      <c r="E24" t="s">
-        <v>45</v>
-      </c>
       <c r="F24" t="s">
+        <v>46</v>
+      </c>
+      <c r="G24" t="s">
         <v>57</v>
-      </c>
-      <c r="G24" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2603,16 +2603,16 @@
         <v>9</v>
       </c>
       <c r="D25" t="s">
+        <v>44</v>
+      </c>
+      <c r="E25" t="s">
         <v>56</v>
       </c>
-      <c r="E25" t="s">
-        <v>45</v>
-      </c>
       <c r="F25" t="s">
+        <v>46</v>
+      </c>
+      <c r="G25" t="s">
         <v>57</v>
-      </c>
-      <c r="G25" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2626,16 +2626,16 @@
         <v>9</v>
       </c>
       <c r="D26" t="s">
+        <v>44</v>
+      </c>
+      <c r="E26" t="s">
         <v>74</v>
       </c>
-      <c r="E26" t="s">
-        <v>45</v>
-      </c>
       <c r="F26" t="s">
+        <v>46</v>
+      </c>
+      <c r="G26" t="s">
         <v>75</v>
-      </c>
-      <c r="G26" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2649,16 +2649,16 @@
         <v>9</v>
       </c>
       <c r="D27" t="s">
+        <v>44</v>
+      </c>
+      <c r="E27" t="s">
         <v>74</v>
       </c>
-      <c r="E27" t="s">
-        <v>45</v>
-      </c>
       <c r="F27" t="s">
+        <v>46</v>
+      </c>
+      <c r="G27" t="s">
         <v>75</v>
-      </c>
-      <c r="G27" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2672,16 +2672,16 @@
         <v>9</v>
       </c>
       <c r="D28" t="s">
+        <v>44</v>
+      </c>
+      <c r="E28" t="s">
         <v>74</v>
       </c>
-      <c r="E28" t="s">
-        <v>45</v>
-      </c>
       <c r="F28" t="s">
+        <v>46</v>
+      </c>
+      <c r="G28" t="s">
         <v>75</v>
-      </c>
-      <c r="G28" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2695,16 +2695,16 @@
         <v>9</v>
       </c>
       <c r="D29" t="s">
+        <v>44</v>
+      </c>
+      <c r="E29" t="s">
         <v>74</v>
       </c>
-      <c r="E29" t="s">
-        <v>45</v>
-      </c>
       <c r="F29" t="s">
+        <v>46</v>
+      </c>
+      <c r="G29" t="s">
         <v>75</v>
-      </c>
-      <c r="G29" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2718,16 +2718,16 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
+        <v>44</v>
+      </c>
+      <c r="E30" t="s">
         <v>74</v>
       </c>
-      <c r="E30" t="s">
-        <v>45</v>
-      </c>
       <c r="F30" t="s">
+        <v>46</v>
+      </c>
+      <c r="G30" t="s">
         <v>75</v>
-      </c>
-      <c r="G30" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2741,16 +2741,16 @@
         <v>9</v>
       </c>
       <c r="D31" t="s">
+        <v>44</v>
+      </c>
+      <c r="E31" t="s">
         <v>74</v>
       </c>
-      <c r="E31" t="s">
-        <v>45</v>
-      </c>
       <c r="F31" t="s">
+        <v>46</v>
+      </c>
+      <c r="G31" t="s">
         <v>75</v>
-      </c>
-      <c r="G31" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -3500,16 +3500,16 @@
         <v>9</v>
       </c>
       <c r="D64" t="s">
+        <v>124</v>
+      </c>
+      <c r="E64" t="s">
         <v>160</v>
       </c>
-      <c r="E64" t="s">
-        <v>125</v>
-      </c>
       <c r="F64" t="s">
+        <v>126</v>
+      </c>
+      <c r="G64" t="s">
         <v>161</v>
-      </c>
-      <c r="G64" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3523,16 +3523,16 @@
         <v>9</v>
       </c>
       <c r="D65" t="s">
+        <v>124</v>
+      </c>
+      <c r="E65" t="s">
         <v>160</v>
       </c>
-      <c r="E65" t="s">
-        <v>125</v>
-      </c>
       <c r="F65" t="s">
+        <v>126</v>
+      </c>
+      <c r="G65" t="s">
         <v>161</v>
-      </c>
-      <c r="G65" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3546,16 +3546,16 @@
         <v>9</v>
       </c>
       <c r="D66" t="s">
+        <v>124</v>
+      </c>
+      <c r="E66" t="s">
         <v>160</v>
       </c>
-      <c r="E66" t="s">
-        <v>125</v>
-      </c>
       <c r="F66" t="s">
+        <v>126</v>
+      </c>
+      <c r="G66" t="s">
         <v>161</v>
-      </c>
-      <c r="G66" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3569,16 +3569,16 @@
         <v>9</v>
       </c>
       <c r="D67" t="s">
+        <v>124</v>
+      </c>
+      <c r="E67" t="s">
         <v>160</v>
       </c>
-      <c r="E67" t="s">
-        <v>125</v>
-      </c>
       <c r="F67" t="s">
+        <v>126</v>
+      </c>
+      <c r="G67" t="s">
         <v>161</v>
-      </c>
-      <c r="G67" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3592,16 +3592,16 @@
         <v>9</v>
       </c>
       <c r="D68" t="s">
+        <v>124</v>
+      </c>
+      <c r="E68" t="s">
         <v>160</v>
       </c>
-      <c r="E68" t="s">
-        <v>125</v>
-      </c>
       <c r="F68" t="s">
+        <v>126</v>
+      </c>
+      <c r="G68" t="s">
         <v>161</v>
-      </c>
-      <c r="G68" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3615,16 +3615,16 @@
         <v>9</v>
       </c>
       <c r="D69" t="s">
+        <v>124</v>
+      </c>
+      <c r="E69" t="s">
         <v>160</v>
       </c>
-      <c r="E69" t="s">
-        <v>125</v>
-      </c>
       <c r="F69" t="s">
+        <v>126</v>
+      </c>
+      <c r="G69" t="s">
         <v>161</v>
-      </c>
-      <c r="G69" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -4236,16 +4236,16 @@
         <v>9</v>
       </c>
       <c r="D96" t="s">
+        <v>224</v>
+      </c>
+      <c r="E96" t="s">
         <v>236</v>
       </c>
-      <c r="E96" t="s">
-        <v>225</v>
-      </c>
       <c r="F96" t="s">
+        <v>226</v>
+      </c>
+      <c r="G96" t="s">
         <v>237</v>
-      </c>
-      <c r="G96" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -4259,16 +4259,16 @@
         <v>9</v>
       </c>
       <c r="D97" t="s">
+        <v>224</v>
+      </c>
+      <c r="E97" t="s">
         <v>236</v>
       </c>
-      <c r="E97" t="s">
-        <v>225</v>
-      </c>
       <c r="F97" t="s">
+        <v>226</v>
+      </c>
+      <c r="G97" t="s">
         <v>237</v>
-      </c>
-      <c r="G97" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4282,16 +4282,16 @@
         <v>9</v>
       </c>
       <c r="D98" t="s">
+        <v>224</v>
+      </c>
+      <c r="E98" t="s">
         <v>236</v>
       </c>
-      <c r="E98" t="s">
-        <v>225</v>
-      </c>
       <c r="F98" t="s">
+        <v>226</v>
+      </c>
+      <c r="G98" t="s">
         <v>237</v>
-      </c>
-      <c r="G98" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4305,16 +4305,16 @@
         <v>9</v>
       </c>
       <c r="D99" t="s">
+        <v>224</v>
+      </c>
+      <c r="E99" t="s">
         <v>236</v>
       </c>
-      <c r="E99" t="s">
-        <v>225</v>
-      </c>
       <c r="F99" t="s">
+        <v>226</v>
+      </c>
+      <c r="G99" t="s">
         <v>237</v>
-      </c>
-      <c r="G99" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4328,16 +4328,16 @@
         <v>9</v>
       </c>
       <c r="D100" t="s">
+        <v>224</v>
+      </c>
+      <c r="E100" t="s">
         <v>236</v>
       </c>
-      <c r="E100" t="s">
-        <v>225</v>
-      </c>
       <c r="F100" t="s">
+        <v>226</v>
+      </c>
+      <c r="G100" t="s">
         <v>237</v>
-      </c>
-      <c r="G100" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4351,16 +4351,16 @@
         <v>9</v>
       </c>
       <c r="D101" t="s">
+        <v>224</v>
+      </c>
+      <c r="E101" t="s">
         <v>236</v>
       </c>
-      <c r="E101" t="s">
-        <v>225</v>
-      </c>
       <c r="F101" t="s">
+        <v>226</v>
+      </c>
+      <c r="G101" t="s">
         <v>237</v>
-      </c>
-      <c r="G101" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4374,16 +4374,16 @@
         <v>9</v>
       </c>
       <c r="D102" t="s">
+        <v>224</v>
+      </c>
+      <c r="E102" t="s">
         <v>236</v>
       </c>
-      <c r="E102" t="s">
-        <v>225</v>
-      </c>
       <c r="F102" t="s">
+        <v>226</v>
+      </c>
+      <c r="G102" t="s">
         <v>237</v>
-      </c>
-      <c r="G102" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4397,16 +4397,16 @@
         <v>9</v>
       </c>
       <c r="D103" t="s">
+        <v>224</v>
+      </c>
+      <c r="E103" t="s">
         <v>236</v>
       </c>
-      <c r="E103" t="s">
-        <v>225</v>
-      </c>
       <c r="F103" t="s">
+        <v>226</v>
+      </c>
+      <c r="G103" t="s">
         <v>237</v>
-      </c>
-      <c r="G103" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4420,16 +4420,16 @@
         <v>9</v>
       </c>
       <c r="D104" t="s">
+        <v>224</v>
+      </c>
+      <c r="E104" t="s">
         <v>236</v>
       </c>
-      <c r="E104" t="s">
-        <v>225</v>
-      </c>
       <c r="F104" t="s">
+        <v>226</v>
+      </c>
+      <c r="G104" t="s">
         <v>237</v>
-      </c>
-      <c r="G104" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4443,16 +4443,16 @@
         <v>9</v>
       </c>
       <c r="D105" t="s">
+        <v>224</v>
+      </c>
+      <c r="E105" t="s">
         <v>256</v>
       </c>
-      <c r="E105" t="s">
-        <v>225</v>
-      </c>
       <c r="F105" t="s">
+        <v>226</v>
+      </c>
+      <c r="G105" t="s">
         <v>257</v>
-      </c>
-      <c r="G105" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4466,16 +4466,16 @@
         <v>9</v>
       </c>
       <c r="D106" t="s">
+        <v>224</v>
+      </c>
+      <c r="E106" t="s">
         <v>256</v>
       </c>
-      <c r="E106" t="s">
-        <v>225</v>
-      </c>
       <c r="F106" t="s">
+        <v>226</v>
+      </c>
+      <c r="G106" t="s">
         <v>257</v>
-      </c>
-      <c r="G106" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4489,16 +4489,16 @@
         <v>9</v>
       </c>
       <c r="D107" t="s">
+        <v>224</v>
+      </c>
+      <c r="E107" t="s">
         <v>256</v>
       </c>
-      <c r="E107" t="s">
-        <v>225</v>
-      </c>
       <c r="F107" t="s">
+        <v>226</v>
+      </c>
+      <c r="G107" t="s">
         <v>257</v>
-      </c>
-      <c r="G107" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4512,16 +4512,16 @@
         <v>9</v>
       </c>
       <c r="D108" t="s">
+        <v>224</v>
+      </c>
+      <c r="E108" t="s">
         <v>256</v>
       </c>
-      <c r="E108" t="s">
-        <v>225</v>
-      </c>
       <c r="F108" t="s">
+        <v>226</v>
+      </c>
+      <c r="G108" t="s">
         <v>257</v>
-      </c>
-      <c r="G108" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4535,16 +4535,16 @@
         <v>9</v>
       </c>
       <c r="D109" t="s">
+        <v>224</v>
+      </c>
+      <c r="E109" t="s">
         <v>256</v>
       </c>
-      <c r="E109" t="s">
-        <v>225</v>
-      </c>
       <c r="F109" t="s">
+        <v>226</v>
+      </c>
+      <c r="G109" t="s">
         <v>257</v>
-      </c>
-      <c r="G109" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4558,16 +4558,16 @@
         <v>9</v>
       </c>
       <c r="D110" t="s">
+        <v>224</v>
+      </c>
+      <c r="E110" t="s">
         <v>256</v>
       </c>
-      <c r="E110" t="s">
-        <v>225</v>
-      </c>
       <c r="F110" t="s">
+        <v>226</v>
+      </c>
+      <c r="G110" t="s">
         <v>257</v>
-      </c>
-      <c r="G110" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4581,16 +4581,16 @@
         <v>9</v>
       </c>
       <c r="D111" t="s">
+        <v>224</v>
+      </c>
+      <c r="E111" t="s">
         <v>270</v>
       </c>
-      <c r="E111" t="s">
-        <v>225</v>
-      </c>
       <c r="F111" t="s">
+        <v>226</v>
+      </c>
+      <c r="G111" t="s">
         <v>271</v>
-      </c>
-      <c r="G111" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4604,16 +4604,16 @@
         <v>9</v>
       </c>
       <c r="D112" t="s">
+        <v>224</v>
+      </c>
+      <c r="E112" t="s">
         <v>274</v>
       </c>
-      <c r="E112" t="s">
-        <v>225</v>
-      </c>
       <c r="F112" t="s">
+        <v>226</v>
+      </c>
+      <c r="G112" t="s">
         <v>275</v>
-      </c>
-      <c r="G112" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4627,16 +4627,16 @@
         <v>9</v>
       </c>
       <c r="D113" t="s">
+        <v>224</v>
+      </c>
+      <c r="E113" t="s">
         <v>278</v>
       </c>
-      <c r="E113" t="s">
-        <v>225</v>
-      </c>
       <c r="F113" t="s">
+        <v>226</v>
+      </c>
+      <c r="G113" t="s">
         <v>279</v>
-      </c>
-      <c r="G113" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4650,16 +4650,16 @@
         <v>9</v>
       </c>
       <c r="D114" t="s">
+        <v>224</v>
+      </c>
+      <c r="E114" t="s">
         <v>278</v>
       </c>
-      <c r="E114" t="s">
-        <v>225</v>
-      </c>
       <c r="F114" t="s">
+        <v>226</v>
+      </c>
+      <c r="G114" t="s">
         <v>279</v>
-      </c>
-      <c r="G114" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4673,16 +4673,16 @@
         <v>9</v>
       </c>
       <c r="D115" t="s">
+        <v>224</v>
+      </c>
+      <c r="E115" t="s">
         <v>278</v>
       </c>
-      <c r="E115" t="s">
-        <v>225</v>
-      </c>
       <c r="F115" t="s">
+        <v>226</v>
+      </c>
+      <c r="G115" t="s">
         <v>279</v>
-      </c>
-      <c r="G115" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4696,16 +4696,16 @@
         <v>9</v>
       </c>
       <c r="D116" t="s">
+        <v>224</v>
+      </c>
+      <c r="E116" t="s">
         <v>278</v>
       </c>
-      <c r="E116" t="s">
-        <v>225</v>
-      </c>
       <c r="F116" t="s">
+        <v>226</v>
+      </c>
+      <c r="G116" t="s">
         <v>279</v>
-      </c>
-      <c r="G116" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4719,16 +4719,16 @@
         <v>9</v>
       </c>
       <c r="D117" t="s">
+        <v>224</v>
+      </c>
+      <c r="E117" t="s">
         <v>278</v>
       </c>
-      <c r="E117" t="s">
-        <v>225</v>
-      </c>
       <c r="F117" t="s">
+        <v>226</v>
+      </c>
+      <c r="G117" t="s">
         <v>279</v>
-      </c>
-      <c r="G117" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4742,16 +4742,16 @@
         <v>9</v>
       </c>
       <c r="D118" t="s">
+        <v>224</v>
+      </c>
+      <c r="E118" t="s">
         <v>278</v>
       </c>
-      <c r="E118" t="s">
-        <v>225</v>
-      </c>
       <c r="F118" t="s">
+        <v>226</v>
+      </c>
+      <c r="G118" t="s">
         <v>279</v>
-      </c>
-      <c r="G118" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4765,16 +4765,16 @@
         <v>9</v>
       </c>
       <c r="D119" t="s">
+        <v>224</v>
+      </c>
+      <c r="E119" t="s">
         <v>278</v>
       </c>
-      <c r="E119" t="s">
-        <v>225</v>
-      </c>
       <c r="F119" t="s">
+        <v>226</v>
+      </c>
+      <c r="G119" t="s">
         <v>279</v>
-      </c>
-      <c r="G119" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -5432,16 +5432,16 @@
         <v>9</v>
       </c>
       <c r="D148" t="s">
+        <v>318</v>
+      </c>
+      <c r="E148" t="s">
         <v>358</v>
       </c>
-      <c r="E148" t="s">
-        <v>319</v>
-      </c>
       <c r="F148" t="s">
+        <v>320</v>
+      </c>
+      <c r="G148" t="s">
         <v>359</v>
-      </c>
-      <c r="G148" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5455,16 +5455,16 @@
         <v>9</v>
       </c>
       <c r="D149" t="s">
+        <v>318</v>
+      </c>
+      <c r="E149" t="s">
         <v>358</v>
       </c>
-      <c r="E149" t="s">
-        <v>319</v>
-      </c>
       <c r="F149" t="s">
+        <v>320</v>
+      </c>
+      <c r="G149" t="s">
         <v>359</v>
-      </c>
-      <c r="G149" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5478,16 +5478,16 @@
         <v>9</v>
       </c>
       <c r="D150" t="s">
+        <v>318</v>
+      </c>
+      <c r="E150" t="s">
         <v>358</v>
       </c>
-      <c r="E150" t="s">
-        <v>319</v>
-      </c>
       <c r="F150" t="s">
+        <v>320</v>
+      </c>
+      <c r="G150" t="s">
         <v>359</v>
-      </c>
-      <c r="G150" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5501,16 +5501,16 @@
         <v>9</v>
       </c>
       <c r="D151" t="s">
+        <v>318</v>
+      </c>
+      <c r="E151" t="s">
         <v>358</v>
       </c>
-      <c r="E151" t="s">
-        <v>319</v>
-      </c>
       <c r="F151" t="s">
+        <v>320</v>
+      </c>
+      <c r="G151" t="s">
         <v>359</v>
-      </c>
-      <c r="G151" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5524,16 +5524,16 @@
         <v>9</v>
       </c>
       <c r="D152" t="s">
+        <v>318</v>
+      </c>
+      <c r="E152" t="s">
         <v>358</v>
       </c>
-      <c r="E152" t="s">
-        <v>319</v>
-      </c>
       <c r="F152" t="s">
+        <v>320</v>
+      </c>
+      <c r="G152" t="s">
         <v>359</v>
-      </c>
-      <c r="G152" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5547,16 +5547,16 @@
         <v>9</v>
       </c>
       <c r="D153" t="s">
+        <v>318</v>
+      </c>
+      <c r="E153" t="s">
         <v>358</v>
       </c>
-      <c r="E153" t="s">
-        <v>319</v>
-      </c>
       <c r="F153" t="s">
+        <v>320</v>
+      </c>
+      <c r="G153" t="s">
         <v>359</v>
-      </c>
-      <c r="G153" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5570,16 +5570,16 @@
         <v>9</v>
       </c>
       <c r="D154" t="s">
+        <v>318</v>
+      </c>
+      <c r="E154" t="s">
         <v>372</v>
       </c>
-      <c r="E154" t="s">
-        <v>319</v>
-      </c>
       <c r="F154" t="s">
+        <v>320</v>
+      </c>
+      <c r="G154" t="s">
         <v>373</v>
-      </c>
-      <c r="G154" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5593,16 +5593,16 @@
         <v>9</v>
       </c>
       <c r="D155" t="s">
+        <v>318</v>
+      </c>
+      <c r="E155" t="s">
         <v>372</v>
       </c>
-      <c r="E155" t="s">
-        <v>319</v>
-      </c>
       <c r="F155" t="s">
+        <v>320</v>
+      </c>
+      <c r="G155" t="s">
         <v>373</v>
-      </c>
-      <c r="G155" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5616,16 +5616,16 @@
         <v>9</v>
       </c>
       <c r="D156" t="s">
+        <v>318</v>
+      </c>
+      <c r="E156" t="s">
         <v>372</v>
       </c>
-      <c r="E156" t="s">
-        <v>319</v>
-      </c>
       <c r="F156" t="s">
+        <v>320</v>
+      </c>
+      <c r="G156" t="s">
         <v>373</v>
-      </c>
-      <c r="G156" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5639,16 +5639,16 @@
         <v>9</v>
       </c>
       <c r="D157" t="s">
+        <v>318</v>
+      </c>
+      <c r="E157" t="s">
         <v>372</v>
       </c>
-      <c r="E157" t="s">
-        <v>319</v>
-      </c>
       <c r="F157" t="s">
+        <v>320</v>
+      </c>
+      <c r="G157" t="s">
         <v>373</v>
-      </c>
-      <c r="G157" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5662,16 +5662,16 @@
         <v>9</v>
       </c>
       <c r="D158" t="s">
+        <v>318</v>
+      </c>
+      <c r="E158" t="s">
         <v>372</v>
       </c>
-      <c r="E158" t="s">
-        <v>319</v>
-      </c>
       <c r="F158" t="s">
+        <v>320</v>
+      </c>
+      <c r="G158" t="s">
         <v>373</v>
-      </c>
-      <c r="G158" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -6122,16 +6122,16 @@
         <v>9</v>
       </c>
       <c r="D178" t="s">
+        <v>384</v>
+      </c>
+      <c r="E178" t="s">
         <v>426</v>
       </c>
-      <c r="E178" t="s">
-        <v>385</v>
-      </c>
       <c r="F178" t="s">
+        <v>386</v>
+      </c>
+      <c r="G178" t="s">
         <v>427</v>
-      </c>
-      <c r="G178" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -6145,16 +6145,16 @@
         <v>9</v>
       </c>
       <c r="D179" t="s">
+        <v>384</v>
+      </c>
+      <c r="E179" t="s">
         <v>426</v>
       </c>
-      <c r="E179" t="s">
-        <v>385</v>
-      </c>
       <c r="F179" t="s">
+        <v>386</v>
+      </c>
+      <c r="G179" t="s">
         <v>427</v>
-      </c>
-      <c r="G179" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -6168,16 +6168,16 @@
         <v>9</v>
       </c>
       <c r="D180" t="s">
+        <v>384</v>
+      </c>
+      <c r="E180" t="s">
         <v>426</v>
       </c>
-      <c r="E180" t="s">
-        <v>385</v>
-      </c>
       <c r="F180" t="s">
+        <v>386</v>
+      </c>
+      <c r="G180" t="s">
         <v>427</v>
-      </c>
-      <c r="G180" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -6191,16 +6191,16 @@
         <v>9</v>
       </c>
       <c r="D181" t="s">
+        <v>384</v>
+      </c>
+      <c r="E181" t="s">
         <v>426</v>
       </c>
-      <c r="E181" t="s">
-        <v>385</v>
-      </c>
       <c r="F181" t="s">
+        <v>386</v>
+      </c>
+      <c r="G181" t="s">
         <v>427</v>
-      </c>
-      <c r="G181" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -6214,16 +6214,16 @@
         <v>9</v>
       </c>
       <c r="D182" t="s">
+        <v>384</v>
+      </c>
+      <c r="E182" t="s">
         <v>426</v>
       </c>
-      <c r="E182" t="s">
-        <v>385</v>
-      </c>
       <c r="F182" t="s">
+        <v>386</v>
+      </c>
+      <c r="G182" t="s">
         <v>427</v>
-      </c>
-      <c r="G182" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -6237,16 +6237,16 @@
         <v>9</v>
       </c>
       <c r="D183" t="s">
+        <v>384</v>
+      </c>
+      <c r="E183" t="s">
         <v>426</v>
       </c>
-      <c r="E183" t="s">
-        <v>385</v>
-      </c>
       <c r="F183" t="s">
+        <v>386</v>
+      </c>
+      <c r="G183" t="s">
         <v>427</v>
-      </c>
-      <c r="G183" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -6260,16 +6260,16 @@
         <v>9</v>
       </c>
       <c r="D184" t="s">
+        <v>384</v>
+      </c>
+      <c r="E184" t="s">
         <v>426</v>
       </c>
-      <c r="E184" t="s">
-        <v>385</v>
-      </c>
       <c r="F184" t="s">
+        <v>386</v>
+      </c>
+      <c r="G184" t="s">
         <v>427</v>
-      </c>
-      <c r="G184" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -6283,16 +6283,16 @@
         <v>9</v>
       </c>
       <c r="D185" t="s">
+        <v>384</v>
+      </c>
+      <c r="E185" t="s">
         <v>426</v>
       </c>
-      <c r="E185" t="s">
-        <v>385</v>
-      </c>
       <c r="F185" t="s">
+        <v>386</v>
+      </c>
+      <c r="G185" t="s">
         <v>427</v>
-      </c>
-      <c r="G185" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -6306,16 +6306,16 @@
         <v>9</v>
       </c>
       <c r="D186" t="s">
+        <v>384</v>
+      </c>
+      <c r="E186" t="s">
         <v>426</v>
       </c>
-      <c r="E186" t="s">
-        <v>385</v>
-      </c>
       <c r="F186" t="s">
+        <v>386</v>
+      </c>
+      <c r="G186" t="s">
         <v>427</v>
-      </c>
-      <c r="G186" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -6329,16 +6329,16 @@
         <v>9</v>
       </c>
       <c r="D187" t="s">
+        <v>384</v>
+      </c>
+      <c r="E187" t="s">
         <v>426</v>
       </c>
-      <c r="E187" t="s">
-        <v>385</v>
-      </c>
       <c r="F187" t="s">
+        <v>386</v>
+      </c>
+      <c r="G187" t="s">
         <v>427</v>
-      </c>
-      <c r="G187" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -6352,16 +6352,16 @@
         <v>9</v>
       </c>
       <c r="D188" t="s">
+        <v>384</v>
+      </c>
+      <c r="E188" t="s">
         <v>448</v>
       </c>
-      <c r="E188" t="s">
-        <v>385</v>
-      </c>
       <c r="F188" t="s">
+        <v>386</v>
+      </c>
+      <c r="G188" t="s">
         <v>449</v>
-      </c>
-      <c r="G188" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="189" spans="1:7">

--- a/api/xlsx/en/SectorGroup.xlsx
+++ b/api/xlsx/en/SectorGroup.xlsx
@@ -25,6 +25,9 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
@@ -34,9 +37,6 @@
     <t>codeforiati:group-name</t>
   </si>
   <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -46,6 +46,9 @@
     <t>active</t>
   </si>
   <si>
+    <t>111</t>
+  </si>
+  <si>
     <t>110</t>
   </si>
   <si>
@@ -55,9 +58,6 @@
     <t>Education</t>
   </si>
   <si>
-    <t>111</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -82,12 +82,12 @@
     <t>Primary education</t>
   </si>
   <si>
+    <t>112</t>
+  </si>
+  <si>
     <t>Basic Education</t>
   </si>
   <si>
-    <t>112</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -112,12 +112,12 @@
     <t>Secondary education</t>
   </si>
   <si>
+    <t>113</t>
+  </si>
+  <si>
     <t>Secondary Education</t>
   </si>
   <si>
-    <t>113</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
@@ -130,12 +130,12 @@
     <t>Higher education</t>
   </si>
   <si>
+    <t>114</t>
+  </si>
+  <si>
     <t>Post-Secondary Education</t>
   </si>
   <si>
-    <t>114</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -148,6 +148,9 @@
     <t>Health policy and administrative management</t>
   </si>
   <si>
+    <t>121</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
@@ -157,9 +160,6 @@
     <t>Health</t>
   </si>
   <si>
-    <t>121</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -184,12 +184,12 @@
     <t>Basic health care</t>
   </si>
   <si>
+    <t>122</t>
+  </si>
+  <si>
     <t>Basic Health</t>
   </si>
   <si>
-    <t>122</t>
-  </si>
-  <si>
     <t>12230</t>
   </si>
   <si>
@@ -238,12 +238,12 @@
     <t>NCDs control, general</t>
   </si>
   <si>
+    <t>123</t>
+  </si>
+  <si>
     <t>Non-communicable diseases (NCDs)</t>
   </si>
   <si>
-    <t>123</t>
-  </si>
-  <si>
     <t>12320</t>
   </si>
   <si>
@@ -388,6 +388,9 @@
     <t>Public sector policy and administrative management</t>
   </si>
   <si>
+    <t>151</t>
+  </si>
+  <si>
     <t>150</t>
   </si>
   <si>
@@ -397,9 +400,6 @@
     <t>Government &amp; Civil Society</t>
   </si>
   <si>
-    <t>151</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -496,12 +496,12 @@
     <t>Security system management and reform</t>
   </si>
   <si>
+    <t>152</t>
+  </si>
+  <si>
     <t>Conflict, Peace &amp; Security</t>
   </si>
   <si>
-    <t>152</t>
-  </si>
-  <si>
     <t>15220</t>
   </si>
   <si>
@@ -688,6 +688,9 @@
     <t>Energy policy and administrative management</t>
   </si>
   <si>
+    <t>231</t>
+  </si>
+  <si>
     <t>230</t>
   </si>
   <si>
@@ -697,9 +700,6 @@
     <t>Energy</t>
   </si>
   <si>
-    <t>231</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -724,12 +724,12 @@
     <t>Energy generation, renewable sources - multiple technologies</t>
   </si>
   <si>
+    <t>232</t>
+  </si>
+  <si>
     <t>Energy generation, renewable sources</t>
   </si>
   <si>
-    <t>232</t>
-  </si>
-  <si>
     <t>23220</t>
   </si>
   <si>
@@ -784,12 +784,12 @@
     <t>Energy generation, non-renewable sources, unspecified</t>
   </si>
   <si>
+    <t>233</t>
+  </si>
+  <si>
     <t>Energy generation, non-renewable sources</t>
   </si>
   <si>
-    <t>233</t>
-  </si>
-  <si>
     <t>23320</t>
   </si>
   <si>
@@ -826,36 +826,36 @@
     <t>Hybrid energy electric power plants</t>
   </si>
   <si>
+    <t>234</t>
+  </si>
+  <si>
     <t>Hybrid energy plants</t>
   </si>
   <si>
-    <t>234</t>
-  </si>
-  <si>
     <t>23510</t>
   </si>
   <si>
     <t>Nuclear energy electric power plants and nuclear safety</t>
   </si>
   <si>
+    <t>235</t>
+  </si>
+  <si>
     <t>Nuclear energy plants</t>
   </si>
   <si>
-    <t>235</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
     <t>Heat plants</t>
   </si>
   <si>
+    <t>236</t>
+  </si>
+  <si>
     <t>Energy distribution</t>
   </si>
   <si>
-    <t>236</t>
-  </si>
-  <si>
     <t>23620</t>
   </si>
   <si>
@@ -970,6 +970,9 @@
     <t>Agricultural policy and administrative management</t>
   </si>
   <si>
+    <t>311</t>
+  </si>
+  <si>
     <t>310</t>
   </si>
   <si>
@@ -979,9 +982,6 @@
     <t>Agriculture, Forestry, Fishing</t>
   </si>
   <si>
-    <t>311</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1090,12 +1090,12 @@
     <t>Forestry policy and administrative management</t>
   </si>
   <si>
+    <t>312</t>
+  </si>
+  <si>
     <t>Forestry</t>
   </si>
   <si>
-    <t>312</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -1132,12 +1132,12 @@
     <t>Fishing policy and administrative management</t>
   </si>
   <si>
+    <t>313</t>
+  </si>
+  <si>
     <t>Fishing</t>
   </si>
   <si>
-    <t>313</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -1168,6 +1168,9 @@
     <t>Industrial policy and administrative management</t>
   </si>
   <si>
+    <t>321</t>
+  </si>
+  <si>
     <t>320</t>
   </si>
   <si>
@@ -1177,9 +1180,6 @@
     <t>Industry, Mining, Construction</t>
   </si>
   <si>
-    <t>321</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1294,12 +1294,12 @@
     <t>Mineral/mining policy and administrative management</t>
   </si>
   <si>
+    <t>322</t>
+  </si>
+  <si>
     <t>Mineral Resources &amp; Mining</t>
   </si>
   <si>
-    <t>322</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -1360,10 +1360,10 @@
     <t>Construction policy and administrative management</t>
   </si>
   <si>
+    <t>323</t>
+  </si>
+  <si>
     <t>Construction</t>
-  </si>
-  <si>
-    <t>323</t>
   </si>
   <si>
     <t>33110</t>
@@ -2166,16 +2166,16 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2189,16 +2189,16 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G7" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2212,16 +2212,16 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G8" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2235,16 +2235,16 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E9" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G9" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2258,16 +2258,16 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E10" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="G10" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2281,16 +2281,16 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="G11" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2304,16 +2304,16 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="G12" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2327,16 +2327,16 @@
         <v>9</v>
       </c>
       <c r="D13" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E13" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="G13" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2442,16 +2442,16 @@
         <v>9</v>
       </c>
       <c r="D18" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E18" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F18" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G18" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2465,16 +2465,16 @@
         <v>9</v>
       </c>
       <c r="D19" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E19" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F19" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G19" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2488,16 +2488,16 @@
         <v>9</v>
       </c>
       <c r="D20" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E20" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F20" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G20" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2511,16 +2511,16 @@
         <v>9</v>
       </c>
       <c r="D21" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E21" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F21" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G21" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2534,16 +2534,16 @@
         <v>9</v>
       </c>
       <c r="D22" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E22" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F22" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G22" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2557,16 +2557,16 @@
         <v>9</v>
       </c>
       <c r="D23" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E23" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F23" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G23" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2580,16 +2580,16 @@
         <v>9</v>
       </c>
       <c r="D24" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E24" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F24" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G24" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2603,16 +2603,16 @@
         <v>9</v>
       </c>
       <c r="D25" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E25" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F25" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G25" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2626,16 +2626,16 @@
         <v>9</v>
       </c>
       <c r="D26" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E26" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="F26" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G26" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2649,16 +2649,16 @@
         <v>9</v>
       </c>
       <c r="D27" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E27" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="F27" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G27" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2672,16 +2672,16 @@
         <v>9</v>
       </c>
       <c r="D28" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E28" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="F28" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G28" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2695,16 +2695,16 @@
         <v>9</v>
       </c>
       <c r="D29" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E29" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="F29" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G29" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2718,16 +2718,16 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E30" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="F30" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G30" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2741,16 +2741,16 @@
         <v>9</v>
       </c>
       <c r="D31" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E31" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="F31" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G31" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2767,13 +2767,13 @@
         <v>88</v>
       </c>
       <c r="E32" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F32" t="s">
         <v>89</v>
       </c>
       <c r="G32" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2790,13 +2790,13 @@
         <v>88</v>
       </c>
       <c r="E33" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F33" t="s">
         <v>89</v>
       </c>
       <c r="G33" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2813,13 +2813,13 @@
         <v>88</v>
       </c>
       <c r="E34" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F34" t="s">
         <v>89</v>
       </c>
       <c r="G34" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2836,13 +2836,13 @@
         <v>88</v>
       </c>
       <c r="E35" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F35" t="s">
         <v>89</v>
       </c>
       <c r="G35" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2859,13 +2859,13 @@
         <v>88</v>
       </c>
       <c r="E36" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F36" t="s">
         <v>89</v>
       </c>
       <c r="G36" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2882,13 +2882,13 @@
         <v>100</v>
       </c>
       <c r="E37" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F37" t="s">
         <v>101</v>
       </c>
       <c r="G37" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2905,13 +2905,13 @@
         <v>100</v>
       </c>
       <c r="E38" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F38" t="s">
         <v>101</v>
       </c>
       <c r="G38" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2928,13 +2928,13 @@
         <v>100</v>
       </c>
       <c r="E39" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F39" t="s">
         <v>101</v>
       </c>
       <c r="G39" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2951,13 +2951,13 @@
         <v>100</v>
       </c>
       <c r="E40" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F40" t="s">
         <v>101</v>
       </c>
       <c r="G40" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2974,13 +2974,13 @@
         <v>100</v>
       </c>
       <c r="E41" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F41" t="s">
         <v>101</v>
       </c>
       <c r="G41" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2997,13 +2997,13 @@
         <v>100</v>
       </c>
       <c r="E42" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F42" t="s">
         <v>101</v>
       </c>
       <c r="G42" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3020,13 +3020,13 @@
         <v>100</v>
       </c>
       <c r="E43" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F43" t="s">
         <v>101</v>
       </c>
       <c r="G43" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3043,13 +3043,13 @@
         <v>100</v>
       </c>
       <c r="E44" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F44" t="s">
         <v>101</v>
       </c>
       <c r="G44" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3066,13 +3066,13 @@
         <v>100</v>
       </c>
       <c r="E45" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F45" t="s">
         <v>101</v>
       </c>
       <c r="G45" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3089,13 +3089,13 @@
         <v>100</v>
       </c>
       <c r="E46" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F46" t="s">
         <v>101</v>
       </c>
       <c r="G46" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3112,13 +3112,13 @@
         <v>100</v>
       </c>
       <c r="E47" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F47" t="s">
         <v>101</v>
       </c>
       <c r="G47" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3500,16 +3500,16 @@
         <v>9</v>
       </c>
       <c r="D64" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E64" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="F64" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G64" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3523,16 +3523,16 @@
         <v>9</v>
       </c>
       <c r="D65" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E65" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="F65" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G65" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3546,16 +3546,16 @@
         <v>9</v>
       </c>
       <c r="D66" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E66" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="F66" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G66" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3569,16 +3569,16 @@
         <v>9</v>
       </c>
       <c r="D67" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E67" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="F67" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G67" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3592,16 +3592,16 @@
         <v>9</v>
       </c>
       <c r="D68" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E68" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="F68" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G68" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3615,16 +3615,16 @@
         <v>9</v>
       </c>
       <c r="D69" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E69" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="F69" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G69" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3641,13 +3641,13 @@
         <v>174</v>
       </c>
       <c r="E70" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F70" t="s">
         <v>175</v>
       </c>
       <c r="G70" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3664,13 +3664,13 @@
         <v>174</v>
       </c>
       <c r="E71" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F71" t="s">
         <v>175</v>
       </c>
       <c r="G71" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3687,13 +3687,13 @@
         <v>174</v>
       </c>
       <c r="E72" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F72" t="s">
         <v>175</v>
       </c>
       <c r="G72" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3710,13 +3710,13 @@
         <v>174</v>
       </c>
       <c r="E73" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F73" t="s">
         <v>175</v>
       </c>
       <c r="G73" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3733,13 +3733,13 @@
         <v>174</v>
       </c>
       <c r="E74" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F74" t="s">
         <v>175</v>
       </c>
       <c r="G74" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3756,13 +3756,13 @@
         <v>174</v>
       </c>
       <c r="E75" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F75" t="s">
         <v>175</v>
       </c>
       <c r="G75" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3779,13 +3779,13 @@
         <v>174</v>
       </c>
       <c r="E76" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F76" t="s">
         <v>175</v>
       </c>
       <c r="G76" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3802,13 +3802,13 @@
         <v>174</v>
       </c>
       <c r="E77" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F77" t="s">
         <v>175</v>
       </c>
       <c r="G77" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3825,13 +3825,13 @@
         <v>174</v>
       </c>
       <c r="E78" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F78" t="s">
         <v>175</v>
       </c>
       <c r="G78" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3848,13 +3848,13 @@
         <v>174</v>
       </c>
       <c r="E79" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F79" t="s">
         <v>175</v>
       </c>
       <c r="G79" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3871,13 +3871,13 @@
         <v>174</v>
       </c>
       <c r="E80" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F80" t="s">
         <v>175</v>
       </c>
       <c r="G80" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3894,13 +3894,13 @@
         <v>198</v>
       </c>
       <c r="E81" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F81" t="s">
         <v>199</v>
       </c>
       <c r="G81" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3917,13 +3917,13 @@
         <v>198</v>
       </c>
       <c r="E82" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F82" t="s">
         <v>199</v>
       </c>
       <c r="G82" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3940,13 +3940,13 @@
         <v>198</v>
       </c>
       <c r="E83" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F83" t="s">
         <v>199</v>
       </c>
       <c r="G83" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3963,13 +3963,13 @@
         <v>198</v>
       </c>
       <c r="E84" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F84" t="s">
         <v>199</v>
       </c>
       <c r="G84" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3986,13 +3986,13 @@
         <v>198</v>
       </c>
       <c r="E85" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F85" t="s">
         <v>199</v>
       </c>
       <c r="G85" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4009,13 +4009,13 @@
         <v>198</v>
       </c>
       <c r="E86" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F86" t="s">
         <v>199</v>
       </c>
       <c r="G86" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4032,13 +4032,13 @@
         <v>198</v>
       </c>
       <c r="E87" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F87" t="s">
         <v>199</v>
       </c>
       <c r="G87" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4055,13 +4055,13 @@
         <v>214</v>
       </c>
       <c r="E88" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F88" t="s">
         <v>215</v>
       </c>
       <c r="G88" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4078,13 +4078,13 @@
         <v>214</v>
       </c>
       <c r="E89" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F89" t="s">
         <v>215</v>
       </c>
       <c r="G89" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4101,13 +4101,13 @@
         <v>214</v>
       </c>
       <c r="E90" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F90" t="s">
         <v>215</v>
       </c>
       <c r="G90" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4124,13 +4124,13 @@
         <v>214</v>
       </c>
       <c r="E91" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F91" t="s">
         <v>215</v>
       </c>
       <c r="G91" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4236,16 +4236,16 @@
         <v>9</v>
       </c>
       <c r="D96" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E96" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F96" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G96" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -4259,16 +4259,16 @@
         <v>9</v>
       </c>
       <c r="D97" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E97" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F97" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G97" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4282,16 +4282,16 @@
         <v>9</v>
       </c>
       <c r="D98" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E98" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F98" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G98" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4305,16 +4305,16 @@
         <v>9</v>
       </c>
       <c r="D99" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E99" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F99" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G99" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4328,16 +4328,16 @@
         <v>9</v>
       </c>
       <c r="D100" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E100" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F100" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G100" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4351,16 +4351,16 @@
         <v>9</v>
       </c>
       <c r="D101" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E101" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F101" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G101" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4374,16 +4374,16 @@
         <v>9</v>
       </c>
       <c r="D102" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E102" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F102" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G102" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4397,16 +4397,16 @@
         <v>9</v>
       </c>
       <c r="D103" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E103" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F103" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G103" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4420,16 +4420,16 @@
         <v>9</v>
       </c>
       <c r="D104" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E104" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F104" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G104" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4443,16 +4443,16 @@
         <v>9</v>
       </c>
       <c r="D105" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E105" t="s">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="F105" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G105" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4466,16 +4466,16 @@
         <v>9</v>
       </c>
       <c r="D106" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E106" t="s">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="F106" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G106" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4489,16 +4489,16 @@
         <v>9</v>
       </c>
       <c r="D107" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E107" t="s">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="F107" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G107" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4512,16 +4512,16 @@
         <v>9</v>
       </c>
       <c r="D108" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E108" t="s">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="F108" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G108" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4535,16 +4535,16 @@
         <v>9</v>
       </c>
       <c r="D109" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E109" t="s">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="F109" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G109" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4558,16 +4558,16 @@
         <v>9</v>
       </c>
       <c r="D110" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E110" t="s">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="F110" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G110" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4581,16 +4581,16 @@
         <v>9</v>
       </c>
       <c r="D111" t="s">
-        <v>224</v>
+        <v>270</v>
       </c>
       <c r="E111" t="s">
-        <v>270</v>
+        <v>225</v>
       </c>
       <c r="F111" t="s">
-        <v>226</v>
+        <v>271</v>
       </c>
       <c r="G111" t="s">
-        <v>271</v>
+        <v>227</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4604,16 +4604,16 @@
         <v>9</v>
       </c>
       <c r="D112" t="s">
-        <v>224</v>
+        <v>274</v>
       </c>
       <c r="E112" t="s">
-        <v>274</v>
+        <v>225</v>
       </c>
       <c r="F112" t="s">
-        <v>226</v>
+        <v>275</v>
       </c>
       <c r="G112" t="s">
-        <v>275</v>
+        <v>227</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4627,16 +4627,16 @@
         <v>9</v>
       </c>
       <c r="D113" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E113" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="F113" t="s">
-        <v>226</v>
+        <v>279</v>
       </c>
       <c r="G113" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4650,16 +4650,16 @@
         <v>9</v>
       </c>
       <c r="D114" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E114" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="F114" t="s">
-        <v>226</v>
+        <v>279</v>
       </c>
       <c r="G114" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4673,16 +4673,16 @@
         <v>9</v>
       </c>
       <c r="D115" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E115" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="F115" t="s">
-        <v>226</v>
+        <v>279</v>
       </c>
       <c r="G115" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4696,16 +4696,16 @@
         <v>9</v>
       </c>
       <c r="D116" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E116" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="F116" t="s">
-        <v>226</v>
+        <v>279</v>
       </c>
       <c r="G116" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4719,16 +4719,16 @@
         <v>9</v>
       </c>
       <c r="D117" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E117" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="F117" t="s">
-        <v>226</v>
+        <v>279</v>
       </c>
       <c r="G117" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4742,16 +4742,16 @@
         <v>9</v>
       </c>
       <c r="D118" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E118" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="F118" t="s">
-        <v>226</v>
+        <v>279</v>
       </c>
       <c r="G118" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4765,16 +4765,16 @@
         <v>9</v>
       </c>
       <c r="D119" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E119" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="F119" t="s">
-        <v>226</v>
+        <v>279</v>
       </c>
       <c r="G119" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4791,13 +4791,13 @@
         <v>294</v>
       </c>
       <c r="E120" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F120" t="s">
         <v>295</v>
       </c>
       <c r="G120" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4814,13 +4814,13 @@
         <v>294</v>
       </c>
       <c r="E121" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F121" t="s">
         <v>295</v>
       </c>
       <c r="G121" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4837,13 +4837,13 @@
         <v>294</v>
       </c>
       <c r="E122" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F122" t="s">
         <v>295</v>
       </c>
       <c r="G122" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4860,13 +4860,13 @@
         <v>294</v>
       </c>
       <c r="E123" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F123" t="s">
         <v>295</v>
       </c>
       <c r="G123" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4883,13 +4883,13 @@
         <v>294</v>
       </c>
       <c r="E124" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F124" t="s">
         <v>295</v>
       </c>
       <c r="G124" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4906,13 +4906,13 @@
         <v>294</v>
       </c>
       <c r="E125" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F125" t="s">
         <v>295</v>
       </c>
       <c r="G125" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4929,13 +4929,13 @@
         <v>308</v>
       </c>
       <c r="E126" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F126" t="s">
         <v>309</v>
       </c>
       <c r="G126" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4952,13 +4952,13 @@
         <v>308</v>
       </c>
       <c r="E127" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F127" t="s">
         <v>309</v>
       </c>
       <c r="G127" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4975,13 +4975,13 @@
         <v>308</v>
       </c>
       <c r="E128" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F128" t="s">
         <v>309</v>
       </c>
       <c r="G128" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4998,13 +4998,13 @@
         <v>308</v>
       </c>
       <c r="E129" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F129" t="s">
         <v>309</v>
       </c>
       <c r="G129" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -5432,16 +5432,16 @@
         <v>9</v>
       </c>
       <c r="D148" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E148" t="s">
-        <v>358</v>
+        <v>319</v>
       </c>
       <c r="F148" t="s">
-        <v>320</v>
+        <v>359</v>
       </c>
       <c r="G148" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5455,16 +5455,16 @@
         <v>9</v>
       </c>
       <c r="D149" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E149" t="s">
-        <v>358</v>
+        <v>319</v>
       </c>
       <c r="F149" t="s">
-        <v>320</v>
+        <v>359</v>
       </c>
       <c r="G149" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5478,16 +5478,16 @@
         <v>9</v>
       </c>
       <c r="D150" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E150" t="s">
-        <v>358</v>
+        <v>319</v>
       </c>
       <c r="F150" t="s">
-        <v>320</v>
+        <v>359</v>
       </c>
       <c r="G150" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5501,16 +5501,16 @@
         <v>9</v>
       </c>
       <c r="D151" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E151" t="s">
-        <v>358</v>
+        <v>319</v>
       </c>
       <c r="F151" t="s">
-        <v>320</v>
+        <v>359</v>
       </c>
       <c r="G151" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5524,16 +5524,16 @@
         <v>9</v>
       </c>
       <c r="D152" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E152" t="s">
-        <v>358</v>
+        <v>319</v>
       </c>
       <c r="F152" t="s">
-        <v>320</v>
+        <v>359</v>
       </c>
       <c r="G152" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5547,16 +5547,16 @@
         <v>9</v>
       </c>
       <c r="D153" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E153" t="s">
-        <v>358</v>
+        <v>319</v>
       </c>
       <c r="F153" t="s">
-        <v>320</v>
+        <v>359</v>
       </c>
       <c r="G153" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5570,16 +5570,16 @@
         <v>9</v>
       </c>
       <c r="D154" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="E154" t="s">
-        <v>372</v>
+        <v>319</v>
       </c>
       <c r="F154" t="s">
-        <v>320</v>
+        <v>373</v>
       </c>
       <c r="G154" t="s">
-        <v>373</v>
+        <v>321</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5593,16 +5593,16 @@
         <v>9</v>
       </c>
       <c r="D155" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="E155" t="s">
-        <v>372</v>
+        <v>319</v>
       </c>
       <c r="F155" t="s">
-        <v>320</v>
+        <v>373</v>
       </c>
       <c r="G155" t="s">
-        <v>373</v>
+        <v>321</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5616,16 +5616,16 @@
         <v>9</v>
       </c>
       <c r="D156" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="E156" t="s">
-        <v>372</v>
+        <v>319</v>
       </c>
       <c r="F156" t="s">
-        <v>320</v>
+        <v>373</v>
       </c>
       <c r="G156" t="s">
-        <v>373</v>
+        <v>321</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5639,16 +5639,16 @@
         <v>9</v>
       </c>
       <c r="D157" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="E157" t="s">
-        <v>372</v>
+        <v>319</v>
       </c>
       <c r="F157" t="s">
-        <v>320</v>
+        <v>373</v>
       </c>
       <c r="G157" t="s">
-        <v>373</v>
+        <v>321</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5662,16 +5662,16 @@
         <v>9</v>
       </c>
       <c r="D158" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="E158" t="s">
-        <v>372</v>
+        <v>319</v>
       </c>
       <c r="F158" t="s">
-        <v>320</v>
+        <v>373</v>
       </c>
       <c r="G158" t="s">
-        <v>373</v>
+        <v>321</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -6122,16 +6122,16 @@
         <v>9</v>
       </c>
       <c r="D178" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E178" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="F178" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G178" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -6145,16 +6145,16 @@
         <v>9</v>
       </c>
       <c r="D179" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E179" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="F179" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G179" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -6168,16 +6168,16 @@
         <v>9</v>
       </c>
       <c r="D180" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E180" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="F180" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G180" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -6191,16 +6191,16 @@
         <v>9</v>
       </c>
       <c r="D181" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E181" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="F181" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G181" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -6214,16 +6214,16 @@
         <v>9</v>
       </c>
       <c r="D182" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E182" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="F182" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G182" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -6237,16 +6237,16 @@
         <v>9</v>
       </c>
       <c r="D183" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E183" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="F183" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G183" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -6260,16 +6260,16 @@
         <v>9</v>
       </c>
       <c r="D184" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E184" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="F184" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G184" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -6283,16 +6283,16 @@
         <v>9</v>
       </c>
       <c r="D185" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E185" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="F185" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G185" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -6306,16 +6306,16 @@
         <v>9</v>
       </c>
       <c r="D186" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E186" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="F186" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G186" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -6329,16 +6329,16 @@
         <v>9</v>
       </c>
       <c r="D187" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E187" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="F187" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G187" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -6352,16 +6352,16 @@
         <v>9</v>
       </c>
       <c r="D188" t="s">
-        <v>384</v>
+        <v>448</v>
       </c>
       <c r="E188" t="s">
-        <v>448</v>
+        <v>385</v>
       </c>
       <c r="F188" t="s">
-        <v>386</v>
+        <v>449</v>
       </c>
       <c r="G188" t="s">
-        <v>449</v>
+        <v>387</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -6378,13 +6378,13 @@
         <v>452</v>
       </c>
       <c r="E189" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F189" t="s">
         <v>453</v>
       </c>
       <c r="G189" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6401,13 +6401,13 @@
         <v>452</v>
       </c>
       <c r="E190" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F190" t="s">
         <v>453</v>
       </c>
       <c r="G190" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6424,13 +6424,13 @@
         <v>452</v>
       </c>
       <c r="E191" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F191" t="s">
         <v>453</v>
       </c>
       <c r="G191" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6447,13 +6447,13 @@
         <v>452</v>
       </c>
       <c r="E192" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F192" t="s">
         <v>453</v>
       </c>
       <c r="G192" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6470,13 +6470,13 @@
         <v>452</v>
       </c>
       <c r="E193" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F193" t="s">
         <v>453</v>
       </c>
       <c r="G193" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6493,13 +6493,13 @@
         <v>452</v>
       </c>
       <c r="E194" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F194" t="s">
         <v>453</v>
       </c>
       <c r="G194" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6516,13 +6516,13 @@
         <v>466</v>
       </c>
       <c r="E195" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F195" t="s">
         <v>467</v>
       </c>
       <c r="G195" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6539,13 +6539,13 @@
         <v>470</v>
       </c>
       <c r="E196" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F196" t="s">
         <v>471</v>
       </c>
       <c r="G196" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6562,13 +6562,13 @@
         <v>470</v>
       </c>
       <c r="E197" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F197" t="s">
         <v>471</v>
       </c>
       <c r="G197" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6585,13 +6585,13 @@
         <v>470</v>
       </c>
       <c r="E198" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F198" t="s">
         <v>471</v>
       </c>
       <c r="G198" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6608,13 +6608,13 @@
         <v>470</v>
       </c>
       <c r="E199" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F199" t="s">
         <v>471</v>
       </c>
       <c r="G199" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6631,13 +6631,13 @@
         <v>470</v>
       </c>
       <c r="E200" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F200" t="s">
         <v>471</v>
       </c>
       <c r="G200" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6654,13 +6654,13 @@
         <v>470</v>
       </c>
       <c r="E201" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F201" t="s">
         <v>471</v>
       </c>
       <c r="G201" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6677,13 +6677,13 @@
         <v>484</v>
       </c>
       <c r="E202" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F202" t="s">
         <v>485</v>
       </c>
       <c r="G202" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6700,13 +6700,13 @@
         <v>484</v>
       </c>
       <c r="E203" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F203" t="s">
         <v>485</v>
       </c>
       <c r="G203" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6723,13 +6723,13 @@
         <v>484</v>
       </c>
       <c r="E204" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F204" t="s">
         <v>485</v>
       </c>
       <c r="G204" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6746,13 +6746,13 @@
         <v>484</v>
       </c>
       <c r="E205" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F205" t="s">
         <v>485</v>
       </c>
       <c r="G205" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6769,13 +6769,13 @@
         <v>484</v>
       </c>
       <c r="E206" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F206" t="s">
         <v>485</v>
       </c>
       <c r="G206" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6792,13 +6792,13 @@
         <v>484</v>
       </c>
       <c r="E207" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F207" t="s">
         <v>485</v>
       </c>
       <c r="G207" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6815,13 +6815,13 @@
         <v>484</v>
       </c>
       <c r="E208" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F208" t="s">
         <v>485</v>
       </c>
       <c r="G208" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6838,13 +6838,13 @@
         <v>484</v>
       </c>
       <c r="E209" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F209" t="s">
         <v>485</v>
       </c>
       <c r="G209" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6861,13 +6861,13 @@
         <v>484</v>
       </c>
       <c r="E210" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F210" t="s">
         <v>485</v>
       </c>
       <c r="G210" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6884,13 +6884,13 @@
         <v>484</v>
       </c>
       <c r="E211" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F211" t="s">
         <v>485</v>
       </c>
       <c r="G211" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6907,13 +6907,13 @@
         <v>506</v>
       </c>
       <c r="E212" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="F212" t="s">
         <v>507</v>
       </c>
       <c r="G212" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6930,13 +6930,13 @@
         <v>510</v>
       </c>
       <c r="E213" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F213" t="s">
         <v>511</v>
       </c>
       <c r="G213" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6953,13 +6953,13 @@
         <v>514</v>
       </c>
       <c r="E214" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F214" t="s">
         <v>515</v>
       </c>
       <c r="G214" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6976,13 +6976,13 @@
         <v>514</v>
       </c>
       <c r="E215" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F215" t="s">
         <v>515</v>
       </c>
       <c r="G215" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6999,13 +6999,13 @@
         <v>520</v>
       </c>
       <c r="E216" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F216" t="s">
         <v>521</v>
       </c>
       <c r="G216" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -7022,13 +7022,13 @@
         <v>520</v>
       </c>
       <c r="E217" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F217" t="s">
         <v>521</v>
       </c>
       <c r="G217" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -7045,13 +7045,13 @@
         <v>520</v>
       </c>
       <c r="E218" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F218" t="s">
         <v>521</v>
       </c>
       <c r="G218" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -7068,13 +7068,13 @@
         <v>520</v>
       </c>
       <c r="E219" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F219" t="s">
         <v>521</v>
       </c>
       <c r="G219" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -7091,13 +7091,13 @@
         <v>520</v>
       </c>
       <c r="E220" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F220" t="s">
         <v>521</v>
       </c>
       <c r="G220" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -7114,13 +7114,13 @@
         <v>520</v>
       </c>
       <c r="E221" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F221" t="s">
         <v>521</v>
       </c>
       <c r="G221" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -7137,13 +7137,13 @@
         <v>520</v>
       </c>
       <c r="E222" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F222" t="s">
         <v>521</v>
       </c>
       <c r="G222" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -7160,13 +7160,13 @@
         <v>536</v>
       </c>
       <c r="E223" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F223" t="s">
         <v>537</v>
       </c>
       <c r="G223" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -7183,13 +7183,13 @@
         <v>536</v>
       </c>
       <c r="E224" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F224" t="s">
         <v>537</v>
       </c>
       <c r="G224" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -7206,13 +7206,13 @@
         <v>536</v>
       </c>
       <c r="E225" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F225" t="s">
         <v>537</v>
       </c>
       <c r="G225" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -7229,13 +7229,13 @@
         <v>544</v>
       </c>
       <c r="E226" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F226" t="s">
         <v>545</v>
       </c>
       <c r="G226" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -7252,13 +7252,13 @@
         <v>548</v>
       </c>
       <c r="E227" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="F227" t="s">
         <v>549</v>
       </c>
       <c r="G227" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -7275,13 +7275,13 @@
         <v>552</v>
       </c>
       <c r="E228" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="F228" t="s">
         <v>553</v>
       </c>
       <c r="G228" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -7298,13 +7298,13 @@
         <v>556</v>
       </c>
       <c r="E229" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="F229" t="s">
         <v>557</v>
       </c>
       <c r="G229" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -7321,13 +7321,13 @@
         <v>560</v>
       </c>
       <c r="E230" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="F230" t="s">
         <v>561</v>
       </c>
       <c r="G230" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -7344,13 +7344,13 @@
         <v>560</v>
       </c>
       <c r="E231" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="F231" t="s">
         <v>561</v>
       </c>
       <c r="G231" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/en/SectorGroup.xlsx
+++ b/api/xlsx/en/SectorGroup.xlsx
@@ -25,18 +25,18 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:category-name</t>
+  </si>
+  <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
-    <t>codeforiati:category-name</t>
-  </si>
-  <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -46,18 +46,18 @@
     <t>active</t>
   </si>
   <si>
+    <t>Education, Level Unspecified</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
     <t>111</t>
   </si>
   <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>Education, Level Unspecified</t>
-  </si>
-  <si>
-    <t>Education</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -82,12 +82,12 @@
     <t>Primary education</t>
   </si>
   <si>
+    <t>Basic Education</t>
+  </si>
+  <si>
     <t>112</t>
   </si>
   <si>
-    <t>Basic Education</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -112,12 +112,12 @@
     <t>Secondary education</t>
   </si>
   <si>
+    <t>Secondary Education</t>
+  </si>
+  <si>
     <t>113</t>
   </si>
   <si>
-    <t>Secondary Education</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
@@ -130,12 +130,12 @@
     <t>Higher education</t>
   </si>
   <si>
+    <t>Post-Secondary Education</t>
+  </si>
+  <si>
     <t>114</t>
   </si>
   <si>
-    <t>Post-Secondary Education</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -148,18 +148,18 @@
     <t>Health policy and administrative management</t>
   </si>
   <si>
+    <t>Health, General</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>Health</t>
+  </si>
+  <si>
     <t>121</t>
   </si>
   <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>Health, General</t>
-  </si>
-  <si>
-    <t>Health</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -184,12 +184,12 @@
     <t>Basic health care</t>
   </si>
   <si>
+    <t>Basic Health</t>
+  </si>
+  <si>
     <t>122</t>
   </si>
   <si>
-    <t>Basic Health</t>
-  </si>
-  <si>
     <t>12230</t>
   </si>
   <si>
@@ -238,12 +238,12 @@
     <t>NCDs control, general</t>
   </si>
   <si>
+    <t>Non-communicable diseases (NCDs)</t>
+  </si>
+  <si>
     <t>123</t>
   </si>
   <si>
-    <t>Non-communicable diseases (NCDs)</t>
-  </si>
-  <si>
     <t>12320</t>
   </si>
   <si>
@@ -280,12 +280,12 @@
     <t>Population policy and administrative management</t>
   </si>
   <si>
+    <t>Population Policies/Programmes &amp; Reproductive Health</t>
+  </si>
+  <si>
     <t>130</t>
   </si>
   <si>
-    <t>Population Policies/Programmes &amp; Reproductive Health</t>
-  </si>
-  <si>
     <t>13020</t>
   </si>
   <si>
@@ -316,12 +316,12 @@
     <t>Water sector policy and administrative management</t>
   </si>
   <si>
+    <t>Water Supply &amp; Sanitation</t>
+  </si>
+  <si>
     <t>140</t>
   </si>
   <si>
-    <t>Water Supply &amp; Sanitation</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -388,18 +388,18 @@
     <t>Public sector policy and administrative management</t>
   </si>
   <si>
+    <t>Government &amp; Civil Society-general</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>Government &amp; Civil Society</t>
+  </si>
+  <si>
     <t>151</t>
   </si>
   <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>Government &amp; Civil Society-general</t>
-  </si>
-  <si>
-    <t>Government &amp; Civil Society</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -496,12 +496,12 @@
     <t>Security system management and reform</t>
   </si>
   <si>
+    <t>Conflict, Peace &amp; Security</t>
+  </si>
+  <si>
     <t>152</t>
   </si>
   <si>
-    <t>Conflict, Peace &amp; Security</t>
-  </si>
-  <si>
     <t>15220</t>
   </si>
   <si>
@@ -538,12 +538,12 @@
     <t>Social Protection</t>
   </si>
   <si>
+    <t>Other Social Infrastructure &amp; Services</t>
+  </si>
+  <si>
     <t>160</t>
   </si>
   <si>
-    <t>Other Social Infrastructure &amp; Services</t>
-  </si>
-  <si>
     <t>16020</t>
   </si>
   <si>
@@ -610,12 +610,12 @@
     <t>Transport policy and administrative management</t>
   </si>
   <si>
+    <t>Transport &amp; Storage</t>
+  </si>
+  <si>
     <t>210</t>
   </si>
   <si>
-    <t>Transport &amp; Storage</t>
-  </si>
-  <si>
     <t>21020</t>
   </si>
   <si>
@@ -658,12 +658,12 @@
     <t>Communications policy and administrative management</t>
   </si>
   <si>
+    <t>Communications</t>
+  </si>
+  <si>
     <t>220</t>
   </si>
   <si>
-    <t>Communications</t>
-  </si>
-  <si>
     <t>22020</t>
   </si>
   <si>
@@ -688,18 +688,18 @@
     <t>Energy policy and administrative management</t>
   </si>
   <si>
+    <t>Energy Policy</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>Energy</t>
+  </si>
+  <si>
     <t>231</t>
   </si>
   <si>
-    <t>230</t>
-  </si>
-  <si>
-    <t>Energy Policy</t>
-  </si>
-  <si>
-    <t>Energy</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -724,12 +724,12 @@
     <t>Energy generation, renewable sources - multiple technologies</t>
   </si>
   <si>
+    <t>Energy generation, renewable sources</t>
+  </si>
+  <si>
     <t>232</t>
   </si>
   <si>
-    <t>Energy generation, renewable sources</t>
-  </si>
-  <si>
     <t>23220</t>
   </si>
   <si>
@@ -784,12 +784,12 @@
     <t>Energy generation, non-renewable sources, unspecified</t>
   </si>
   <si>
+    <t>Energy generation, non-renewable sources</t>
+  </si>
+  <si>
     <t>233</t>
   </si>
   <si>
-    <t>Energy generation, non-renewable sources</t>
-  </si>
-  <si>
     <t>23320</t>
   </si>
   <si>
@@ -826,36 +826,36 @@
     <t>Hybrid energy electric power plants</t>
   </si>
   <si>
+    <t>Hybrid energy plants</t>
+  </si>
+  <si>
     <t>234</t>
   </si>
   <si>
-    <t>Hybrid energy plants</t>
-  </si>
-  <si>
     <t>23510</t>
   </si>
   <si>
     <t>Nuclear energy electric power plants and nuclear safety</t>
   </si>
   <si>
+    <t>Nuclear energy plants</t>
+  </si>
+  <si>
     <t>235</t>
   </si>
   <si>
-    <t>Nuclear energy plants</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
     <t>Heat plants</t>
   </si>
   <si>
+    <t>Energy distribution</t>
+  </si>
+  <si>
     <t>236</t>
   </si>
   <si>
-    <t>Energy distribution</t>
-  </si>
-  <si>
     <t>23620</t>
   </si>
   <si>
@@ -898,12 +898,12 @@
     <t>Financial policy and administrative management</t>
   </si>
   <si>
+    <t>Banking &amp; Financial Services</t>
+  </si>
+  <si>
     <t>240</t>
   </si>
   <si>
-    <t>Banking &amp; Financial Services</t>
-  </si>
-  <si>
     <t>24020</t>
   </si>
   <si>
@@ -940,12 +940,12 @@
     <t>Business policy and administration</t>
   </si>
   <si>
+    <t>Business &amp; Other Services</t>
+  </si>
+  <si>
     <t>250</t>
   </si>
   <si>
-    <t>Business &amp; Other Services</t>
-  </si>
-  <si>
     <t>25020</t>
   </si>
   <si>
@@ -970,18 +970,18 @@
     <t>Agricultural policy and administrative management</t>
   </si>
   <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>Agriculture, Forestry, Fishing</t>
+  </si>
+  <si>
     <t>311</t>
   </si>
   <si>
-    <t>310</t>
-  </si>
-  <si>
-    <t>Agriculture</t>
-  </si>
-  <si>
-    <t>Agriculture, Forestry, Fishing</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1090,12 +1090,12 @@
     <t>Forestry policy and administrative management</t>
   </si>
   <si>
+    <t>Forestry</t>
+  </si>
+  <si>
     <t>312</t>
   </si>
   <si>
-    <t>Forestry</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -1132,12 +1132,12 @@
     <t>Fishing policy and administrative management</t>
   </si>
   <si>
+    <t>Fishing</t>
+  </si>
+  <si>
     <t>313</t>
   </si>
   <si>
-    <t>Fishing</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -1168,18 +1168,18 @@
     <t>Industrial policy and administrative management</t>
   </si>
   <si>
+    <t>Industry</t>
+  </si>
+  <si>
+    <t>320</t>
+  </si>
+  <si>
+    <t>Industry, Mining, Construction</t>
+  </si>
+  <si>
     <t>321</t>
   </si>
   <si>
-    <t>320</t>
-  </si>
-  <si>
-    <t>Industry</t>
-  </si>
-  <si>
-    <t>Industry, Mining, Construction</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1294,12 +1294,12 @@
     <t>Mineral/mining policy and administrative management</t>
   </si>
   <si>
+    <t>Mineral Resources &amp; Mining</t>
+  </si>
+  <si>
     <t>322</t>
   </si>
   <si>
-    <t>Mineral Resources &amp; Mining</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -1360,24 +1360,24 @@
     <t>Construction policy and administrative management</t>
   </si>
   <si>
+    <t>Construction</t>
+  </si>
+  <si>
     <t>323</t>
   </si>
   <si>
-    <t>Construction</t>
-  </si>
-  <si>
     <t>33110</t>
   </si>
   <si>
     <t>Trade policy and administrative management</t>
   </si>
   <si>
+    <t>Trade Policies &amp; Regulations</t>
+  </si>
+  <si>
     <t>331</t>
   </si>
   <si>
-    <t>Trade Policies &amp; Regulations</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1414,24 +1414,24 @@
     <t>Tourism policy and administrative management</t>
   </si>
   <si>
+    <t>Tourism</t>
+  </si>
+  <si>
     <t>332</t>
   </si>
   <si>
-    <t>Tourism</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
     <t>Environmental policy and administrative management</t>
   </si>
   <si>
+    <t>General Environment Protection</t>
+  </si>
+  <si>
     <t>410</t>
   </si>
   <si>
-    <t>General Environment Protection</t>
-  </si>
-  <si>
     <t>41020</t>
   </si>
   <si>
@@ -1468,12 +1468,12 @@
     <t>Multisector aid</t>
   </si>
   <si>
+    <t>Other Multisector</t>
+  </si>
+  <si>
     <t>430</t>
   </si>
   <si>
-    <t>Other Multisector</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -1534,36 +1534,36 @@
     <t>General budget support-related aid</t>
   </si>
   <si>
+    <t>General Budget Support</t>
+  </si>
+  <si>
     <t>510</t>
   </si>
   <si>
-    <t>General Budget Support</t>
-  </si>
-  <si>
     <t>52010</t>
   </si>
   <si>
     <t>Food assistance</t>
   </si>
   <si>
+    <t>Development Food Assistance</t>
+  </si>
+  <si>
     <t>520</t>
   </si>
   <si>
-    <t>Development Food Assistance</t>
-  </si>
-  <si>
     <t>53030</t>
   </si>
   <si>
     <t>Import support (capital goods)</t>
   </si>
   <si>
+    <t>Other Commodity Assistance</t>
+  </si>
+  <si>
     <t>530</t>
   </si>
   <si>
-    <t>Other Commodity Assistance</t>
-  </si>
-  <si>
     <t>53040</t>
   </si>
   <si>
@@ -1576,12 +1576,12 @@
     <t>Action relating to debt</t>
   </si>
   <si>
+    <t>Action Relating to Debt</t>
+  </si>
+  <si>
     <t>600</t>
   </si>
   <si>
-    <t>Action Relating to Debt</t>
-  </si>
-  <si>
     <t>60020</t>
   </si>
   <si>
@@ -1624,12 +1624,12 @@
     <t>Material relief assistance and services</t>
   </si>
   <si>
+    <t>Emergency Response</t>
+  </si>
+  <si>
     <t>720</t>
   </si>
   <si>
-    <t>Emergency Response</t>
-  </si>
-  <si>
     <t>72040</t>
   </si>
   <si>
@@ -1648,58 +1648,58 @@
     <t>Immediate post-emergency reconstruction and rehabilitation</t>
   </si>
   <si>
+    <t>Reconstruction Relief &amp; Rehabilitation</t>
+  </si>
+  <si>
     <t>730</t>
   </si>
   <si>
-    <t>Reconstruction Relief &amp; Rehabilitation</t>
-  </si>
-  <si>
     <t>74020</t>
   </si>
   <si>
     <t>Multi-hazard response preparedness</t>
   </si>
   <si>
+    <t>Disaster Prevention &amp; Preparedness</t>
+  </si>
+  <si>
     <t>740</t>
   </si>
   <si>
-    <t>Disaster Prevention &amp; Preparedness</t>
-  </si>
-  <si>
     <t>91010</t>
   </si>
   <si>
     <t>Administrative costs (non-sector allocable)</t>
   </si>
   <si>
+    <t>Administrative Costs of Donors</t>
+  </si>
+  <si>
     <t>910</t>
   </si>
   <si>
-    <t>Administrative Costs of Donors</t>
-  </si>
-  <si>
     <t>93010</t>
   </si>
   <si>
     <t>Refugees/asylum seekers in donor countries (non-sector allocable)</t>
   </si>
   <si>
+    <t>Refugees in Donor Countries</t>
+  </si>
+  <si>
     <t>930</t>
   </si>
   <si>
-    <t>Refugees in Donor Countries</t>
-  </si>
-  <si>
     <t>99810</t>
   </si>
   <si>
     <t>Sectors not specified</t>
   </si>
   <si>
+    <t>Unallocated / Unspecified</t>
+  </si>
+  <si>
     <t>998</t>
-  </si>
-  <si>
-    <t>Unallocated / Unspecified</t>
   </si>
   <si>
     <t>99820</t>
@@ -2172,10 +2172,10 @@
         <v>11</v>
       </c>
       <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" t="s">
         <v>23</v>
-      </c>
-      <c r="G6" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2195,10 +2195,10 @@
         <v>11</v>
       </c>
       <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" t="s">
         <v>23</v>
-      </c>
-      <c r="G7" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2218,10 +2218,10 @@
         <v>11</v>
       </c>
       <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" t="s">
         <v>23</v>
-      </c>
-      <c r="G8" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2241,10 +2241,10 @@
         <v>11</v>
       </c>
       <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" t="s">
         <v>23</v>
-      </c>
-      <c r="G9" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2264,10 +2264,10 @@
         <v>11</v>
       </c>
       <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" t="s">
         <v>33</v>
-      </c>
-      <c r="G10" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2287,10 +2287,10 @@
         <v>11</v>
       </c>
       <c r="F11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" t="s">
         <v>33</v>
-      </c>
-      <c r="G11" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2310,10 +2310,10 @@
         <v>11</v>
       </c>
       <c r="F12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" t="s">
         <v>39</v>
-      </c>
-      <c r="G12" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2333,10 +2333,10 @@
         <v>11</v>
       </c>
       <c r="F13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" t="s">
         <v>39</v>
-      </c>
-      <c r="G13" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2448,10 +2448,10 @@
         <v>45</v>
       </c>
       <c r="F18" t="s">
+        <v>46</v>
+      </c>
+      <c r="G18" t="s">
         <v>57</v>
-      </c>
-      <c r="G18" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2471,10 +2471,10 @@
         <v>45</v>
       </c>
       <c r="F19" t="s">
+        <v>46</v>
+      </c>
+      <c r="G19" t="s">
         <v>57</v>
-      </c>
-      <c r="G19" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2494,10 +2494,10 @@
         <v>45</v>
       </c>
       <c r="F20" t="s">
+        <v>46</v>
+      </c>
+      <c r="G20" t="s">
         <v>57</v>
-      </c>
-      <c r="G20" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2517,10 +2517,10 @@
         <v>45</v>
       </c>
       <c r="F21" t="s">
+        <v>46</v>
+      </c>
+      <c r="G21" t="s">
         <v>57</v>
-      </c>
-      <c r="G21" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2540,10 +2540,10 @@
         <v>45</v>
       </c>
       <c r="F22" t="s">
+        <v>46</v>
+      </c>
+      <c r="G22" t="s">
         <v>57</v>
-      </c>
-      <c r="G22" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2563,10 +2563,10 @@
         <v>45</v>
       </c>
       <c r="F23" t="s">
+        <v>46</v>
+      </c>
+      <c r="G23" t="s">
         <v>57</v>
-      </c>
-      <c r="G23" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2586,10 +2586,10 @@
         <v>45</v>
       </c>
       <c r="F24" t="s">
+        <v>46</v>
+      </c>
+      <c r="G24" t="s">
         <v>57</v>
-      </c>
-      <c r="G24" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2609,10 +2609,10 @@
         <v>45</v>
       </c>
       <c r="F25" t="s">
+        <v>46</v>
+      </c>
+      <c r="G25" t="s">
         <v>57</v>
-      </c>
-      <c r="G25" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2632,10 +2632,10 @@
         <v>45</v>
       </c>
       <c r="F26" t="s">
+        <v>46</v>
+      </c>
+      <c r="G26" t="s">
         <v>75</v>
-      </c>
-      <c r="G26" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2655,10 +2655,10 @@
         <v>45</v>
       </c>
       <c r="F27" t="s">
+        <v>46</v>
+      </c>
+      <c r="G27" t="s">
         <v>75</v>
-      </c>
-      <c r="G27" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2678,10 +2678,10 @@
         <v>45</v>
       </c>
       <c r="F28" t="s">
+        <v>46</v>
+      </c>
+      <c r="G28" t="s">
         <v>75</v>
-      </c>
-      <c r="G28" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2701,10 +2701,10 @@
         <v>45</v>
       </c>
       <c r="F29" t="s">
+        <v>46</v>
+      </c>
+      <c r="G29" t="s">
         <v>75</v>
-      </c>
-      <c r="G29" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2724,10 +2724,10 @@
         <v>45</v>
       </c>
       <c r="F30" t="s">
+        <v>46</v>
+      </c>
+      <c r="G30" t="s">
         <v>75</v>
-      </c>
-      <c r="G30" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2747,10 +2747,10 @@
         <v>45</v>
       </c>
       <c r="F31" t="s">
+        <v>46</v>
+      </c>
+      <c r="G31" t="s">
         <v>75</v>
-      </c>
-      <c r="G31" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2767,10 +2767,10 @@
         <v>88</v>
       </c>
       <c r="E32" t="s">
+        <v>89</v>
+      </c>
+      <c r="F32" t="s">
         <v>88</v>
-      </c>
-      <c r="F32" t="s">
-        <v>89</v>
       </c>
       <c r="G32" t="s">
         <v>89</v>
@@ -2790,10 +2790,10 @@
         <v>88</v>
       </c>
       <c r="E33" t="s">
+        <v>89</v>
+      </c>
+      <c r="F33" t="s">
         <v>88</v>
-      </c>
-      <c r="F33" t="s">
-        <v>89</v>
       </c>
       <c r="G33" t="s">
         <v>89</v>
@@ -2813,10 +2813,10 @@
         <v>88</v>
       </c>
       <c r="E34" t="s">
+        <v>89</v>
+      </c>
+      <c r="F34" t="s">
         <v>88</v>
-      </c>
-      <c r="F34" t="s">
-        <v>89</v>
       </c>
       <c r="G34" t="s">
         <v>89</v>
@@ -2836,10 +2836,10 @@
         <v>88</v>
       </c>
       <c r="E35" t="s">
+        <v>89</v>
+      </c>
+      <c r="F35" t="s">
         <v>88</v>
-      </c>
-      <c r="F35" t="s">
-        <v>89</v>
       </c>
       <c r="G35" t="s">
         <v>89</v>
@@ -2859,10 +2859,10 @@
         <v>88</v>
       </c>
       <c r="E36" t="s">
+        <v>89</v>
+      </c>
+      <c r="F36" t="s">
         <v>88</v>
-      </c>
-      <c r="F36" t="s">
-        <v>89</v>
       </c>
       <c r="G36" t="s">
         <v>89</v>
@@ -2882,10 +2882,10 @@
         <v>100</v>
       </c>
       <c r="E37" t="s">
+        <v>101</v>
+      </c>
+      <c r="F37" t="s">
         <v>100</v>
-      </c>
-      <c r="F37" t="s">
-        <v>101</v>
       </c>
       <c r="G37" t="s">
         <v>101</v>
@@ -2905,10 +2905,10 @@
         <v>100</v>
       </c>
       <c r="E38" t="s">
+        <v>101</v>
+      </c>
+      <c r="F38" t="s">
         <v>100</v>
-      </c>
-      <c r="F38" t="s">
-        <v>101</v>
       </c>
       <c r="G38" t="s">
         <v>101</v>
@@ -2928,10 +2928,10 @@
         <v>100</v>
       </c>
       <c r="E39" t="s">
+        <v>101</v>
+      </c>
+      <c r="F39" t="s">
         <v>100</v>
-      </c>
-      <c r="F39" t="s">
-        <v>101</v>
       </c>
       <c r="G39" t="s">
         <v>101</v>
@@ -2951,10 +2951,10 @@
         <v>100</v>
       </c>
       <c r="E40" t="s">
+        <v>101</v>
+      </c>
+      <c r="F40" t="s">
         <v>100</v>
-      </c>
-      <c r="F40" t="s">
-        <v>101</v>
       </c>
       <c r="G40" t="s">
         <v>101</v>
@@ -2974,10 +2974,10 @@
         <v>100</v>
       </c>
       <c r="E41" t="s">
+        <v>101</v>
+      </c>
+      <c r="F41" t="s">
         <v>100</v>
-      </c>
-      <c r="F41" t="s">
-        <v>101</v>
       </c>
       <c r="G41" t="s">
         <v>101</v>
@@ -2997,10 +2997,10 @@
         <v>100</v>
       </c>
       <c r="E42" t="s">
+        <v>101</v>
+      </c>
+      <c r="F42" t="s">
         <v>100</v>
-      </c>
-      <c r="F42" t="s">
-        <v>101</v>
       </c>
       <c r="G42" t="s">
         <v>101</v>
@@ -3020,10 +3020,10 @@
         <v>100</v>
       </c>
       <c r="E43" t="s">
+        <v>101</v>
+      </c>
+      <c r="F43" t="s">
         <v>100</v>
-      </c>
-      <c r="F43" t="s">
-        <v>101</v>
       </c>
       <c r="G43" t="s">
         <v>101</v>
@@ -3043,10 +3043,10 @@
         <v>100</v>
       </c>
       <c r="E44" t="s">
+        <v>101</v>
+      </c>
+      <c r="F44" t="s">
         <v>100</v>
-      </c>
-      <c r="F44" t="s">
-        <v>101</v>
       </c>
       <c r="G44" t="s">
         <v>101</v>
@@ -3066,10 +3066,10 @@
         <v>100</v>
       </c>
       <c r="E45" t="s">
+        <v>101</v>
+      </c>
+      <c r="F45" t="s">
         <v>100</v>
-      </c>
-      <c r="F45" t="s">
-        <v>101</v>
       </c>
       <c r="G45" t="s">
         <v>101</v>
@@ -3089,10 +3089,10 @@
         <v>100</v>
       </c>
       <c r="E46" t="s">
+        <v>101</v>
+      </c>
+      <c r="F46" t="s">
         <v>100</v>
-      </c>
-      <c r="F46" t="s">
-        <v>101</v>
       </c>
       <c r="G46" t="s">
         <v>101</v>
@@ -3112,10 +3112,10 @@
         <v>100</v>
       </c>
       <c r="E47" t="s">
+        <v>101</v>
+      </c>
+      <c r="F47" t="s">
         <v>100</v>
-      </c>
-      <c r="F47" t="s">
-        <v>101</v>
       </c>
       <c r="G47" t="s">
         <v>101</v>
@@ -3506,10 +3506,10 @@
         <v>125</v>
       </c>
       <c r="F64" t="s">
+        <v>126</v>
+      </c>
+      <c r="G64" t="s">
         <v>161</v>
-      </c>
-      <c r="G64" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3529,10 +3529,10 @@
         <v>125</v>
       </c>
       <c r="F65" t="s">
+        <v>126</v>
+      </c>
+      <c r="G65" t="s">
         <v>161</v>
-      </c>
-      <c r="G65" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3552,10 +3552,10 @@
         <v>125</v>
       </c>
       <c r="F66" t="s">
+        <v>126</v>
+      </c>
+      <c r="G66" t="s">
         <v>161</v>
-      </c>
-      <c r="G66" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3575,10 +3575,10 @@
         <v>125</v>
       </c>
       <c r="F67" t="s">
+        <v>126</v>
+      </c>
+      <c r="G67" t="s">
         <v>161</v>
-      </c>
-      <c r="G67" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3598,10 +3598,10 @@
         <v>125</v>
       </c>
       <c r="F68" t="s">
+        <v>126</v>
+      </c>
+      <c r="G68" t="s">
         <v>161</v>
-      </c>
-      <c r="G68" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3621,10 +3621,10 @@
         <v>125</v>
       </c>
       <c r="F69" t="s">
+        <v>126</v>
+      </c>
+      <c r="G69" t="s">
         <v>161</v>
-      </c>
-      <c r="G69" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3641,10 +3641,10 @@
         <v>174</v>
       </c>
       <c r="E70" t="s">
+        <v>175</v>
+      </c>
+      <c r="F70" t="s">
         <v>174</v>
-      </c>
-      <c r="F70" t="s">
-        <v>175</v>
       </c>
       <c r="G70" t="s">
         <v>175</v>
@@ -3664,10 +3664,10 @@
         <v>174</v>
       </c>
       <c r="E71" t="s">
+        <v>175</v>
+      </c>
+      <c r="F71" t="s">
         <v>174</v>
-      </c>
-      <c r="F71" t="s">
-        <v>175</v>
       </c>
       <c r="G71" t="s">
         <v>175</v>
@@ -3687,10 +3687,10 @@
         <v>174</v>
       </c>
       <c r="E72" t="s">
+        <v>175</v>
+      </c>
+      <c r="F72" t="s">
         <v>174</v>
-      </c>
-      <c r="F72" t="s">
-        <v>175</v>
       </c>
       <c r="G72" t="s">
         <v>175</v>
@@ -3710,10 +3710,10 @@
         <v>174</v>
       </c>
       <c r="E73" t="s">
+        <v>175</v>
+      </c>
+      <c r="F73" t="s">
         <v>174</v>
-      </c>
-      <c r="F73" t="s">
-        <v>175</v>
       </c>
       <c r="G73" t="s">
         <v>175</v>
@@ -3733,10 +3733,10 @@
         <v>174</v>
       </c>
       <c r="E74" t="s">
+        <v>175</v>
+      </c>
+      <c r="F74" t="s">
         <v>174</v>
-      </c>
-      <c r="F74" t="s">
-        <v>175</v>
       </c>
       <c r="G74" t="s">
         <v>175</v>
@@ -3756,10 +3756,10 @@
         <v>174</v>
       </c>
       <c r="E75" t="s">
+        <v>175</v>
+      </c>
+      <c r="F75" t="s">
         <v>174</v>
-      </c>
-      <c r="F75" t="s">
-        <v>175</v>
       </c>
       <c r="G75" t="s">
         <v>175</v>
@@ -3779,10 +3779,10 @@
         <v>174</v>
       </c>
       <c r="E76" t="s">
+        <v>175</v>
+      </c>
+      <c r="F76" t="s">
         <v>174</v>
-      </c>
-      <c r="F76" t="s">
-        <v>175</v>
       </c>
       <c r="G76" t="s">
         <v>175</v>
@@ -3802,10 +3802,10 @@
         <v>174</v>
       </c>
       <c r="E77" t="s">
+        <v>175</v>
+      </c>
+      <c r="F77" t="s">
         <v>174</v>
-      </c>
-      <c r="F77" t="s">
-        <v>175</v>
       </c>
       <c r="G77" t="s">
         <v>175</v>
@@ -3825,10 +3825,10 @@
         <v>174</v>
       </c>
       <c r="E78" t="s">
+        <v>175</v>
+      </c>
+      <c r="F78" t="s">
         <v>174</v>
-      </c>
-      <c r="F78" t="s">
-        <v>175</v>
       </c>
       <c r="G78" t="s">
         <v>175</v>
@@ -3848,10 +3848,10 @@
         <v>174</v>
       </c>
       <c r="E79" t="s">
+        <v>175</v>
+      </c>
+      <c r="F79" t="s">
         <v>174</v>
-      </c>
-      <c r="F79" t="s">
-        <v>175</v>
       </c>
       <c r="G79" t="s">
         <v>175</v>
@@ -3871,10 +3871,10 @@
         <v>174</v>
       </c>
       <c r="E80" t="s">
+        <v>175</v>
+      </c>
+      <c r="F80" t="s">
         <v>174</v>
-      </c>
-      <c r="F80" t="s">
-        <v>175</v>
       </c>
       <c r="G80" t="s">
         <v>175</v>
@@ -3894,10 +3894,10 @@
         <v>198</v>
       </c>
       <c r="E81" t="s">
+        <v>199</v>
+      </c>
+      <c r="F81" t="s">
         <v>198</v>
-      </c>
-      <c r="F81" t="s">
-        <v>199</v>
       </c>
       <c r="G81" t="s">
         <v>199</v>
@@ -3917,10 +3917,10 @@
         <v>198</v>
       </c>
       <c r="E82" t="s">
+        <v>199</v>
+      </c>
+      <c r="F82" t="s">
         <v>198</v>
-      </c>
-      <c r="F82" t="s">
-        <v>199</v>
       </c>
       <c r="G82" t="s">
         <v>199</v>
@@ -3940,10 +3940,10 @@
         <v>198</v>
       </c>
       <c r="E83" t="s">
+        <v>199</v>
+      </c>
+      <c r="F83" t="s">
         <v>198</v>
-      </c>
-      <c r="F83" t="s">
-        <v>199</v>
       </c>
       <c r="G83" t="s">
         <v>199</v>
@@ -3963,10 +3963,10 @@
         <v>198</v>
       </c>
       <c r="E84" t="s">
+        <v>199</v>
+      </c>
+      <c r="F84" t="s">
         <v>198</v>
-      </c>
-      <c r="F84" t="s">
-        <v>199</v>
       </c>
       <c r="G84" t="s">
         <v>199</v>
@@ -3986,10 +3986,10 @@
         <v>198</v>
       </c>
       <c r="E85" t="s">
+        <v>199</v>
+      </c>
+      <c r="F85" t="s">
         <v>198</v>
-      </c>
-      <c r="F85" t="s">
-        <v>199</v>
       </c>
       <c r="G85" t="s">
         <v>199</v>
@@ -4009,10 +4009,10 @@
         <v>198</v>
       </c>
       <c r="E86" t="s">
+        <v>199</v>
+      </c>
+      <c r="F86" t="s">
         <v>198</v>
-      </c>
-      <c r="F86" t="s">
-        <v>199</v>
       </c>
       <c r="G86" t="s">
         <v>199</v>
@@ -4032,10 +4032,10 @@
         <v>198</v>
       </c>
       <c r="E87" t="s">
+        <v>199</v>
+      </c>
+      <c r="F87" t="s">
         <v>198</v>
-      </c>
-      <c r="F87" t="s">
-        <v>199</v>
       </c>
       <c r="G87" t="s">
         <v>199</v>
@@ -4055,10 +4055,10 @@
         <v>214</v>
       </c>
       <c r="E88" t="s">
+        <v>215</v>
+      </c>
+      <c r="F88" t="s">
         <v>214</v>
-      </c>
-      <c r="F88" t="s">
-        <v>215</v>
       </c>
       <c r="G88" t="s">
         <v>215</v>
@@ -4078,10 +4078,10 @@
         <v>214</v>
       </c>
       <c r="E89" t="s">
+        <v>215</v>
+      </c>
+      <c r="F89" t="s">
         <v>214</v>
-      </c>
-      <c r="F89" t="s">
-        <v>215</v>
       </c>
       <c r="G89" t="s">
         <v>215</v>
@@ -4101,10 +4101,10 @@
         <v>214</v>
       </c>
       <c r="E90" t="s">
+        <v>215</v>
+      </c>
+      <c r="F90" t="s">
         <v>214</v>
-      </c>
-      <c r="F90" t="s">
-        <v>215</v>
       </c>
       <c r="G90" t="s">
         <v>215</v>
@@ -4124,10 +4124,10 @@
         <v>214</v>
       </c>
       <c r="E91" t="s">
+        <v>215</v>
+      </c>
+      <c r="F91" t="s">
         <v>214</v>
-      </c>
-      <c r="F91" t="s">
-        <v>215</v>
       </c>
       <c r="G91" t="s">
         <v>215</v>
@@ -4242,10 +4242,10 @@
         <v>225</v>
       </c>
       <c r="F96" t="s">
+        <v>226</v>
+      </c>
+      <c r="G96" t="s">
         <v>237</v>
-      </c>
-      <c r="G96" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -4265,10 +4265,10 @@
         <v>225</v>
       </c>
       <c r="F97" t="s">
+        <v>226</v>
+      </c>
+      <c r="G97" t="s">
         <v>237</v>
-      </c>
-      <c r="G97" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4288,10 +4288,10 @@
         <v>225</v>
       </c>
       <c r="F98" t="s">
+        <v>226</v>
+      </c>
+      <c r="G98" t="s">
         <v>237</v>
-      </c>
-      <c r="G98" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4311,10 +4311,10 @@
         <v>225</v>
       </c>
       <c r="F99" t="s">
+        <v>226</v>
+      </c>
+      <c r="G99" t="s">
         <v>237</v>
-      </c>
-      <c r="G99" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4334,10 +4334,10 @@
         <v>225</v>
       </c>
       <c r="F100" t="s">
+        <v>226</v>
+      </c>
+      <c r="G100" t="s">
         <v>237</v>
-      </c>
-      <c r="G100" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4357,10 +4357,10 @@
         <v>225</v>
       </c>
       <c r="F101" t="s">
+        <v>226</v>
+      </c>
+      <c r="G101" t="s">
         <v>237</v>
-      </c>
-      <c r="G101" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4380,10 +4380,10 @@
         <v>225</v>
       </c>
       <c r="F102" t="s">
+        <v>226</v>
+      </c>
+      <c r="G102" t="s">
         <v>237</v>
-      </c>
-      <c r="G102" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4403,10 +4403,10 @@
         <v>225</v>
       </c>
       <c r="F103" t="s">
+        <v>226</v>
+      </c>
+      <c r="G103" t="s">
         <v>237</v>
-      </c>
-      <c r="G103" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4426,10 +4426,10 @@
         <v>225</v>
       </c>
       <c r="F104" t="s">
+        <v>226</v>
+      </c>
+      <c r="G104" t="s">
         <v>237</v>
-      </c>
-      <c r="G104" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4449,10 +4449,10 @@
         <v>225</v>
       </c>
       <c r="F105" t="s">
+        <v>226</v>
+      </c>
+      <c r="G105" t="s">
         <v>257</v>
-      </c>
-      <c r="G105" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4472,10 +4472,10 @@
         <v>225</v>
       </c>
       <c r="F106" t="s">
+        <v>226</v>
+      </c>
+      <c r="G106" t="s">
         <v>257</v>
-      </c>
-      <c r="G106" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4495,10 +4495,10 @@
         <v>225</v>
       </c>
       <c r="F107" t="s">
+        <v>226</v>
+      </c>
+      <c r="G107" t="s">
         <v>257</v>
-      </c>
-      <c r="G107" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4518,10 +4518,10 @@
         <v>225</v>
       </c>
       <c r="F108" t="s">
+        <v>226</v>
+      </c>
+      <c r="G108" t="s">
         <v>257</v>
-      </c>
-      <c r="G108" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4541,10 +4541,10 @@
         <v>225</v>
       </c>
       <c r="F109" t="s">
+        <v>226</v>
+      </c>
+      <c r="G109" t="s">
         <v>257</v>
-      </c>
-      <c r="G109" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4564,10 +4564,10 @@
         <v>225</v>
       </c>
       <c r="F110" t="s">
+        <v>226</v>
+      </c>
+      <c r="G110" t="s">
         <v>257</v>
-      </c>
-      <c r="G110" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4587,10 +4587,10 @@
         <v>225</v>
       </c>
       <c r="F111" t="s">
+        <v>226</v>
+      </c>
+      <c r="G111" t="s">
         <v>271</v>
-      </c>
-      <c r="G111" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4610,10 +4610,10 @@
         <v>225</v>
       </c>
       <c r="F112" t="s">
+        <v>226</v>
+      </c>
+      <c r="G112" t="s">
         <v>275</v>
-      </c>
-      <c r="G112" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4633,10 +4633,10 @@
         <v>225</v>
       </c>
       <c r="F113" t="s">
+        <v>226</v>
+      </c>
+      <c r="G113" t="s">
         <v>279</v>
-      </c>
-      <c r="G113" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4656,10 +4656,10 @@
         <v>225</v>
       </c>
       <c r="F114" t="s">
+        <v>226</v>
+      </c>
+      <c r="G114" t="s">
         <v>279</v>
-      </c>
-      <c r="G114" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4679,10 +4679,10 @@
         <v>225</v>
       </c>
       <c r="F115" t="s">
+        <v>226</v>
+      </c>
+      <c r="G115" t="s">
         <v>279</v>
-      </c>
-      <c r="G115" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4702,10 +4702,10 @@
         <v>225</v>
       </c>
       <c r="F116" t="s">
+        <v>226</v>
+      </c>
+      <c r="G116" t="s">
         <v>279</v>
-      </c>
-      <c r="G116" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4725,10 +4725,10 @@
         <v>225</v>
       </c>
       <c r="F117" t="s">
+        <v>226</v>
+      </c>
+      <c r="G117" t="s">
         <v>279</v>
-      </c>
-      <c r="G117" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4748,10 +4748,10 @@
         <v>225</v>
       </c>
       <c r="F118" t="s">
+        <v>226</v>
+      </c>
+      <c r="G118" t="s">
         <v>279</v>
-      </c>
-      <c r="G118" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4771,10 +4771,10 @@
         <v>225</v>
       </c>
       <c r="F119" t="s">
+        <v>226</v>
+      </c>
+      <c r="G119" t="s">
         <v>279</v>
-      </c>
-      <c r="G119" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4791,10 +4791,10 @@
         <v>294</v>
       </c>
       <c r="E120" t="s">
+        <v>295</v>
+      </c>
+      <c r="F120" t="s">
         <v>294</v>
-      </c>
-      <c r="F120" t="s">
-        <v>295</v>
       </c>
       <c r="G120" t="s">
         <v>295</v>
@@ -4814,10 +4814,10 @@
         <v>294</v>
       </c>
       <c r="E121" t="s">
+        <v>295</v>
+      </c>
+      <c r="F121" t="s">
         <v>294</v>
-      </c>
-      <c r="F121" t="s">
-        <v>295</v>
       </c>
       <c r="G121" t="s">
         <v>295</v>
@@ -4837,10 +4837,10 @@
         <v>294</v>
       </c>
       <c r="E122" t="s">
+        <v>295</v>
+      </c>
+      <c r="F122" t="s">
         <v>294</v>
-      </c>
-      <c r="F122" t="s">
-        <v>295</v>
       </c>
       <c r="G122" t="s">
         <v>295</v>
@@ -4860,10 +4860,10 @@
         <v>294</v>
       </c>
       <c r="E123" t="s">
+        <v>295</v>
+      </c>
+      <c r="F123" t="s">
         <v>294</v>
-      </c>
-      <c r="F123" t="s">
-        <v>295</v>
       </c>
       <c r="G123" t="s">
         <v>295</v>
@@ -4883,10 +4883,10 @@
         <v>294</v>
       </c>
       <c r="E124" t="s">
+        <v>295</v>
+      </c>
+      <c r="F124" t="s">
         <v>294</v>
-      </c>
-      <c r="F124" t="s">
-        <v>295</v>
       </c>
       <c r="G124" t="s">
         <v>295</v>
@@ -4906,10 +4906,10 @@
         <v>294</v>
       </c>
       <c r="E125" t="s">
+        <v>295</v>
+      </c>
+      <c r="F125" t="s">
         <v>294</v>
-      </c>
-      <c r="F125" t="s">
-        <v>295</v>
       </c>
       <c r="G125" t="s">
         <v>295</v>
@@ -4929,10 +4929,10 @@
         <v>308</v>
       </c>
       <c r="E126" t="s">
+        <v>309</v>
+      </c>
+      <c r="F126" t="s">
         <v>308</v>
-      </c>
-      <c r="F126" t="s">
-        <v>309</v>
       </c>
       <c r="G126" t="s">
         <v>309</v>
@@ -4952,10 +4952,10 @@
         <v>308</v>
       </c>
       <c r="E127" t="s">
+        <v>309</v>
+      </c>
+      <c r="F127" t="s">
         <v>308</v>
-      </c>
-      <c r="F127" t="s">
-        <v>309</v>
       </c>
       <c r="G127" t="s">
         <v>309</v>
@@ -4975,10 +4975,10 @@
         <v>308</v>
       </c>
       <c r="E128" t="s">
+        <v>309</v>
+      </c>
+      <c r="F128" t="s">
         <v>308</v>
-      </c>
-      <c r="F128" t="s">
-        <v>309</v>
       </c>
       <c r="G128" t="s">
         <v>309</v>
@@ -4998,10 +4998,10 @@
         <v>308</v>
       </c>
       <c r="E129" t="s">
+        <v>309</v>
+      </c>
+      <c r="F129" t="s">
         <v>308</v>
-      </c>
-      <c r="F129" t="s">
-        <v>309</v>
       </c>
       <c r="G129" t="s">
         <v>309</v>
@@ -5438,10 +5438,10 @@
         <v>319</v>
       </c>
       <c r="F148" t="s">
+        <v>320</v>
+      </c>
+      <c r="G148" t="s">
         <v>359</v>
-      </c>
-      <c r="G148" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5461,10 +5461,10 @@
         <v>319</v>
       </c>
       <c r="F149" t="s">
+        <v>320</v>
+      </c>
+      <c r="G149" t="s">
         <v>359</v>
-      </c>
-      <c r="G149" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5484,10 +5484,10 @@
         <v>319</v>
       </c>
       <c r="F150" t="s">
+        <v>320</v>
+      </c>
+      <c r="G150" t="s">
         <v>359</v>
-      </c>
-      <c r="G150" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5507,10 +5507,10 @@
         <v>319</v>
       </c>
       <c r="F151" t="s">
+        <v>320</v>
+      </c>
+      <c r="G151" t="s">
         <v>359</v>
-      </c>
-      <c r="G151" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5530,10 +5530,10 @@
         <v>319</v>
       </c>
       <c r="F152" t="s">
+        <v>320</v>
+      </c>
+      <c r="G152" t="s">
         <v>359</v>
-      </c>
-      <c r="G152" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5553,10 +5553,10 @@
         <v>319</v>
       </c>
       <c r="F153" t="s">
+        <v>320</v>
+      </c>
+      <c r="G153" t="s">
         <v>359</v>
-      </c>
-      <c r="G153" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5576,10 +5576,10 @@
         <v>319</v>
       </c>
       <c r="F154" t="s">
+        <v>320</v>
+      </c>
+      <c r="G154" t="s">
         <v>373</v>
-      </c>
-      <c r="G154" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5599,10 +5599,10 @@
         <v>319</v>
       </c>
       <c r="F155" t="s">
+        <v>320</v>
+      </c>
+      <c r="G155" t="s">
         <v>373</v>
-      </c>
-      <c r="G155" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5622,10 +5622,10 @@
         <v>319</v>
       </c>
       <c r="F156" t="s">
+        <v>320</v>
+      </c>
+      <c r="G156" t="s">
         <v>373</v>
-      </c>
-      <c r="G156" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5645,10 +5645,10 @@
         <v>319</v>
       </c>
       <c r="F157" t="s">
+        <v>320</v>
+      </c>
+      <c r="G157" t="s">
         <v>373</v>
-      </c>
-      <c r="G157" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5668,10 +5668,10 @@
         <v>319</v>
       </c>
       <c r="F158" t="s">
+        <v>320</v>
+      </c>
+      <c r="G158" t="s">
         <v>373</v>
-      </c>
-      <c r="G158" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -6128,10 +6128,10 @@
         <v>385</v>
       </c>
       <c r="F178" t="s">
+        <v>386</v>
+      </c>
+      <c r="G178" t="s">
         <v>427</v>
-      </c>
-      <c r="G178" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -6151,10 +6151,10 @@
         <v>385</v>
       </c>
       <c r="F179" t="s">
+        <v>386</v>
+      </c>
+      <c r="G179" t="s">
         <v>427</v>
-      </c>
-      <c r="G179" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -6174,10 +6174,10 @@
         <v>385</v>
       </c>
       <c r="F180" t="s">
+        <v>386</v>
+      </c>
+      <c r="G180" t="s">
         <v>427</v>
-      </c>
-      <c r="G180" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -6197,10 +6197,10 @@
         <v>385</v>
       </c>
       <c r="F181" t="s">
+        <v>386</v>
+      </c>
+      <c r="G181" t="s">
         <v>427</v>
-      </c>
-      <c r="G181" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -6220,10 +6220,10 @@
         <v>385</v>
       </c>
       <c r="F182" t="s">
+        <v>386</v>
+      </c>
+      <c r="G182" t="s">
         <v>427</v>
-      </c>
-      <c r="G182" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -6243,10 +6243,10 @@
         <v>385</v>
       </c>
       <c r="F183" t="s">
+        <v>386</v>
+      </c>
+      <c r="G183" t="s">
         <v>427</v>
-      </c>
-      <c r="G183" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -6266,10 +6266,10 @@
         <v>385</v>
       </c>
       <c r="F184" t="s">
+        <v>386</v>
+      </c>
+      <c r="G184" t="s">
         <v>427</v>
-      </c>
-      <c r="G184" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -6289,10 +6289,10 @@
         <v>385</v>
       </c>
       <c r="F185" t="s">
+        <v>386</v>
+      </c>
+      <c r="G185" t="s">
         <v>427</v>
-      </c>
-      <c r="G185" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -6312,10 +6312,10 @@
         <v>385</v>
       </c>
       <c r="F186" t="s">
+        <v>386</v>
+      </c>
+      <c r="G186" t="s">
         <v>427</v>
-      </c>
-      <c r="G186" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -6335,10 +6335,10 @@
         <v>385</v>
       </c>
       <c r="F187" t="s">
+        <v>386</v>
+      </c>
+      <c r="G187" t="s">
         <v>427</v>
-      </c>
-      <c r="G187" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -6358,10 +6358,10 @@
         <v>385</v>
       </c>
       <c r="F188" t="s">
+        <v>386</v>
+      </c>
+      <c r="G188" t="s">
         <v>449</v>
-      </c>
-      <c r="G188" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -6378,10 +6378,10 @@
         <v>452</v>
       </c>
       <c r="E189" t="s">
+        <v>453</v>
+      </c>
+      <c r="F189" t="s">
         <v>452</v>
-      </c>
-      <c r="F189" t="s">
-        <v>453</v>
       </c>
       <c r="G189" t="s">
         <v>453</v>
@@ -6401,10 +6401,10 @@
         <v>452</v>
       </c>
       <c r="E190" t="s">
+        <v>453</v>
+      </c>
+      <c r="F190" t="s">
         <v>452</v>
-      </c>
-      <c r="F190" t="s">
-        <v>453</v>
       </c>
       <c r="G190" t="s">
         <v>453</v>
@@ -6424,10 +6424,10 @@
         <v>452</v>
       </c>
       <c r="E191" t="s">
+        <v>453</v>
+      </c>
+      <c r="F191" t="s">
         <v>452</v>
-      </c>
-      <c r="F191" t="s">
-        <v>453</v>
       </c>
       <c r="G191" t="s">
         <v>453</v>
@@ -6447,10 +6447,10 @@
         <v>452</v>
       </c>
       <c r="E192" t="s">
+        <v>453</v>
+      </c>
+      <c r="F192" t="s">
         <v>452</v>
-      </c>
-      <c r="F192" t="s">
-        <v>453</v>
       </c>
       <c r="G192" t="s">
         <v>453</v>
@@ -6470,10 +6470,10 @@
         <v>452</v>
       </c>
       <c r="E193" t="s">
+        <v>453</v>
+      </c>
+      <c r="F193" t="s">
         <v>452</v>
-      </c>
-      <c r="F193" t="s">
-        <v>453</v>
       </c>
       <c r="G193" t="s">
         <v>453</v>
@@ -6493,10 +6493,10 @@
         <v>452</v>
       </c>
       <c r="E194" t="s">
+        <v>453</v>
+      </c>
+      <c r="F194" t="s">
         <v>452</v>
-      </c>
-      <c r="F194" t="s">
-        <v>453</v>
       </c>
       <c r="G194" t="s">
         <v>453</v>
@@ -6516,10 +6516,10 @@
         <v>466</v>
       </c>
       <c r="E195" t="s">
+        <v>467</v>
+      </c>
+      <c r="F195" t="s">
         <v>466</v>
-      </c>
-      <c r="F195" t="s">
-        <v>467</v>
       </c>
       <c r="G195" t="s">
         <v>467</v>
@@ -6539,10 +6539,10 @@
         <v>470</v>
       </c>
       <c r="E196" t="s">
+        <v>471</v>
+      </c>
+      <c r="F196" t="s">
         <v>470</v>
-      </c>
-      <c r="F196" t="s">
-        <v>471</v>
       </c>
       <c r="G196" t="s">
         <v>471</v>
@@ -6562,10 +6562,10 @@
         <v>470</v>
       </c>
       <c r="E197" t="s">
+        <v>471</v>
+      </c>
+      <c r="F197" t="s">
         <v>470</v>
-      </c>
-      <c r="F197" t="s">
-        <v>471</v>
       </c>
       <c r="G197" t="s">
         <v>471</v>
@@ -6585,10 +6585,10 @@
         <v>470</v>
       </c>
       <c r="E198" t="s">
+        <v>471</v>
+      </c>
+      <c r="F198" t="s">
         <v>470</v>
-      </c>
-      <c r="F198" t="s">
-        <v>471</v>
       </c>
       <c r="G198" t="s">
         <v>471</v>
@@ -6608,10 +6608,10 @@
         <v>470</v>
       </c>
       <c r="E199" t="s">
+        <v>471</v>
+      </c>
+      <c r="F199" t="s">
         <v>470</v>
-      </c>
-      <c r="F199" t="s">
-        <v>471</v>
       </c>
       <c r="G199" t="s">
         <v>471</v>
@@ -6631,10 +6631,10 @@
         <v>470</v>
       </c>
       <c r="E200" t="s">
+        <v>471</v>
+      </c>
+      <c r="F200" t="s">
         <v>470</v>
-      </c>
-      <c r="F200" t="s">
-        <v>471</v>
       </c>
       <c r="G200" t="s">
         <v>471</v>
@@ -6654,10 +6654,10 @@
         <v>470</v>
       </c>
       <c r="E201" t="s">
+        <v>471</v>
+      </c>
+      <c r="F201" t="s">
         <v>470</v>
-      </c>
-      <c r="F201" t="s">
-        <v>471</v>
       </c>
       <c r="G201" t="s">
         <v>471</v>
@@ -6677,10 +6677,10 @@
         <v>484</v>
       </c>
       <c r="E202" t="s">
+        <v>485</v>
+      </c>
+      <c r="F202" t="s">
         <v>484</v>
-      </c>
-      <c r="F202" t="s">
-        <v>485</v>
       </c>
       <c r="G202" t="s">
         <v>485</v>
@@ -6700,10 +6700,10 @@
         <v>484</v>
       </c>
       <c r="E203" t="s">
+        <v>485</v>
+      </c>
+      <c r="F203" t="s">
         <v>484</v>
-      </c>
-      <c r="F203" t="s">
-        <v>485</v>
       </c>
       <c r="G203" t="s">
         <v>485</v>
@@ -6723,10 +6723,10 @@
         <v>484</v>
       </c>
       <c r="E204" t="s">
+        <v>485</v>
+      </c>
+      <c r="F204" t="s">
         <v>484</v>
-      </c>
-      <c r="F204" t="s">
-        <v>485</v>
       </c>
       <c r="G204" t="s">
         <v>485</v>
@@ -6746,10 +6746,10 @@
         <v>484</v>
       </c>
       <c r="E205" t="s">
+        <v>485</v>
+      </c>
+      <c r="F205" t="s">
         <v>484</v>
-      </c>
-      <c r="F205" t="s">
-        <v>485</v>
       </c>
       <c r="G205" t="s">
         <v>485</v>
@@ -6769,10 +6769,10 @@
         <v>484</v>
       </c>
       <c r="E206" t="s">
+        <v>485</v>
+      </c>
+      <c r="F206" t="s">
         <v>484</v>
-      </c>
-      <c r="F206" t="s">
-        <v>485</v>
       </c>
       <c r="G206" t="s">
         <v>485</v>
@@ -6792,10 +6792,10 @@
         <v>484</v>
       </c>
       <c r="E207" t="s">
+        <v>485</v>
+      </c>
+      <c r="F207" t="s">
         <v>484</v>
-      </c>
-      <c r="F207" t="s">
-        <v>485</v>
       </c>
       <c r="G207" t="s">
         <v>485</v>
@@ -6815,10 +6815,10 @@
         <v>484</v>
       </c>
       <c r="E208" t="s">
+        <v>485</v>
+      </c>
+      <c r="F208" t="s">
         <v>484</v>
-      </c>
-      <c r="F208" t="s">
-        <v>485</v>
       </c>
       <c r="G208" t="s">
         <v>485</v>
@@ -6838,10 +6838,10 @@
         <v>484</v>
       </c>
       <c r="E209" t="s">
+        <v>485</v>
+      </c>
+      <c r="F209" t="s">
         <v>484</v>
-      </c>
-      <c r="F209" t="s">
-        <v>485</v>
       </c>
       <c r="G209" t="s">
         <v>485</v>
@@ -6861,10 +6861,10 @@
         <v>484</v>
       </c>
       <c r="E210" t="s">
+        <v>485</v>
+      </c>
+      <c r="F210" t="s">
         <v>484</v>
-      </c>
-      <c r="F210" t="s">
-        <v>485</v>
       </c>
       <c r="G210" t="s">
         <v>485</v>
@@ -6884,10 +6884,10 @@
         <v>484</v>
       </c>
       <c r="E211" t="s">
+        <v>485</v>
+      </c>
+      <c r="F211" t="s">
         <v>484</v>
-      </c>
-      <c r="F211" t="s">
-        <v>485</v>
       </c>
       <c r="G211" t="s">
         <v>485</v>
@@ -6907,10 +6907,10 @@
         <v>506</v>
       </c>
       <c r="E212" t="s">
+        <v>507</v>
+      </c>
+      <c r="F212" t="s">
         <v>506</v>
-      </c>
-      <c r="F212" t="s">
-        <v>507</v>
       </c>
       <c r="G212" t="s">
         <v>507</v>
@@ -6930,10 +6930,10 @@
         <v>510</v>
       </c>
       <c r="E213" t="s">
+        <v>511</v>
+      </c>
+      <c r="F213" t="s">
         <v>510</v>
-      </c>
-      <c r="F213" t="s">
-        <v>511</v>
       </c>
       <c r="G213" t="s">
         <v>511</v>
@@ -6953,10 +6953,10 @@
         <v>514</v>
       </c>
       <c r="E214" t="s">
+        <v>515</v>
+      </c>
+      <c r="F214" t="s">
         <v>514</v>
-      </c>
-      <c r="F214" t="s">
-        <v>515</v>
       </c>
       <c r="G214" t="s">
         <v>515</v>
@@ -6976,10 +6976,10 @@
         <v>514</v>
       </c>
       <c r="E215" t="s">
+        <v>515</v>
+      </c>
+      <c r="F215" t="s">
         <v>514</v>
-      </c>
-      <c r="F215" t="s">
-        <v>515</v>
       </c>
       <c r="G215" t="s">
         <v>515</v>
@@ -6999,10 +6999,10 @@
         <v>520</v>
       </c>
       <c r="E216" t="s">
+        <v>521</v>
+      </c>
+      <c r="F216" t="s">
         <v>520</v>
-      </c>
-      <c r="F216" t="s">
-        <v>521</v>
       </c>
       <c r="G216" t="s">
         <v>521</v>
@@ -7022,10 +7022,10 @@
         <v>520</v>
       </c>
       <c r="E217" t="s">
+        <v>521</v>
+      </c>
+      <c r="F217" t="s">
         <v>520</v>
-      </c>
-      <c r="F217" t="s">
-        <v>521</v>
       </c>
       <c r="G217" t="s">
         <v>521</v>
@@ -7045,10 +7045,10 @@
         <v>520</v>
       </c>
       <c r="E218" t="s">
+        <v>521</v>
+      </c>
+      <c r="F218" t="s">
         <v>520</v>
-      </c>
-      <c r="F218" t="s">
-        <v>521</v>
       </c>
       <c r="G218" t="s">
         <v>521</v>
@@ -7068,10 +7068,10 @@
         <v>520</v>
       </c>
       <c r="E219" t="s">
+        <v>521</v>
+      </c>
+      <c r="F219" t="s">
         <v>520</v>
-      </c>
-      <c r="F219" t="s">
-        <v>521</v>
       </c>
       <c r="G219" t="s">
         <v>521</v>
@@ -7091,10 +7091,10 @@
         <v>520</v>
       </c>
       <c r="E220" t="s">
+        <v>521</v>
+      </c>
+      <c r="F220" t="s">
         <v>520</v>
-      </c>
-      <c r="F220" t="s">
-        <v>521</v>
       </c>
       <c r="G220" t="s">
         <v>521</v>
@@ -7114,10 +7114,10 @@
         <v>520</v>
       </c>
       <c r="E221" t="s">
+        <v>521</v>
+      </c>
+      <c r="F221" t="s">
         <v>520</v>
-      </c>
-      <c r="F221" t="s">
-        <v>521</v>
       </c>
       <c r="G221" t="s">
         <v>521</v>
@@ -7137,10 +7137,10 @@
         <v>520</v>
       </c>
       <c r="E222" t="s">
+        <v>521</v>
+      </c>
+      <c r="F222" t="s">
         <v>520</v>
-      </c>
-      <c r="F222" t="s">
-        <v>521</v>
       </c>
       <c r="G222" t="s">
         <v>521</v>
@@ -7160,10 +7160,10 @@
         <v>536</v>
       </c>
       <c r="E223" t="s">
+        <v>537</v>
+      </c>
+      <c r="F223" t="s">
         <v>536</v>
-      </c>
-      <c r="F223" t="s">
-        <v>537</v>
       </c>
       <c r="G223" t="s">
         <v>537</v>
@@ -7183,10 +7183,10 @@
         <v>536</v>
       </c>
       <c r="E224" t="s">
+        <v>537</v>
+      </c>
+      <c r="F224" t="s">
         <v>536</v>
-      </c>
-      <c r="F224" t="s">
-        <v>537</v>
       </c>
       <c r="G224" t="s">
         <v>537</v>
@@ -7206,10 +7206,10 @@
         <v>536</v>
       </c>
       <c r="E225" t="s">
+        <v>537</v>
+      </c>
+      <c r="F225" t="s">
         <v>536</v>
-      </c>
-      <c r="F225" t="s">
-        <v>537</v>
       </c>
       <c r="G225" t="s">
         <v>537</v>
@@ -7229,10 +7229,10 @@
         <v>544</v>
       </c>
       <c r="E226" t="s">
+        <v>545</v>
+      </c>
+      <c r="F226" t="s">
         <v>544</v>
-      </c>
-      <c r="F226" t="s">
-        <v>545</v>
       </c>
       <c r="G226" t="s">
         <v>545</v>
@@ -7252,10 +7252,10 @@
         <v>548</v>
       </c>
       <c r="E227" t="s">
+        <v>549</v>
+      </c>
+      <c r="F227" t="s">
         <v>548</v>
-      </c>
-      <c r="F227" t="s">
-        <v>549</v>
       </c>
       <c r="G227" t="s">
         <v>549</v>
@@ -7275,10 +7275,10 @@
         <v>552</v>
       </c>
       <c r="E228" t="s">
+        <v>553</v>
+      </c>
+      <c r="F228" t="s">
         <v>552</v>
-      </c>
-      <c r="F228" t="s">
-        <v>553</v>
       </c>
       <c r="G228" t="s">
         <v>553</v>
@@ -7298,10 +7298,10 @@
         <v>556</v>
       </c>
       <c r="E229" t="s">
+        <v>557</v>
+      </c>
+      <c r="F229" t="s">
         <v>556</v>
-      </c>
-      <c r="F229" t="s">
-        <v>557</v>
       </c>
       <c r="G229" t="s">
         <v>557</v>
@@ -7321,10 +7321,10 @@
         <v>560</v>
       </c>
       <c r="E230" t="s">
+        <v>561</v>
+      </c>
+      <c r="F230" t="s">
         <v>560</v>
-      </c>
-      <c r="F230" t="s">
-        <v>561</v>
       </c>
       <c r="G230" t="s">
         <v>561</v>
@@ -7344,10 +7344,10 @@
         <v>560</v>
       </c>
       <c r="E231" t="s">
+        <v>561</v>
+      </c>
+      <c r="F231" t="s">
         <v>560</v>
-      </c>
-      <c r="F231" t="s">
-        <v>561</v>
       </c>
       <c r="G231" t="s">
         <v>561</v>

--- a/api/xlsx/en/SectorGroup.xlsx
+++ b/api/xlsx/en/SectorGroup.xlsx
@@ -28,15 +28,15 @@
     <t>codeforiati:category-name</t>
   </si>
   <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
     <t>codeforiati:group-name</t>
   </si>
   <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -49,15 +49,15 @@
     <t>Education, Level Unspecified</t>
   </si>
   <si>
+    <t>111</t>
+  </si>
+  <si>
     <t>110</t>
   </si>
   <si>
     <t>Education</t>
   </si>
   <si>
-    <t>111</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -151,15 +151,15 @@
     <t>Health, General</t>
   </si>
   <si>
+    <t>121</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
     <t>Health</t>
   </si>
   <si>
-    <t>121</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -391,15 +391,15 @@
     <t>Government &amp; Civil Society-general</t>
   </si>
   <si>
+    <t>151</t>
+  </si>
+  <si>
     <t>150</t>
   </si>
   <si>
     <t>Government &amp; Civil Society</t>
   </si>
   <si>
-    <t>151</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -691,15 +691,15 @@
     <t>Energy Policy</t>
   </si>
   <si>
+    <t>231</t>
+  </si>
+  <si>
     <t>230</t>
   </si>
   <si>
     <t>Energy</t>
   </si>
   <si>
-    <t>231</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -973,15 +973,15 @@
     <t>Agriculture</t>
   </si>
   <si>
+    <t>311</t>
+  </si>
+  <si>
     <t>310</t>
   </si>
   <si>
     <t>Agriculture, Forestry, Fishing</t>
   </si>
   <si>
-    <t>311</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1171,13 +1171,13 @@
     <t>Industry</t>
   </si>
   <si>
+    <t>321</t>
+  </si>
+  <si>
     <t>320</t>
   </si>
   <si>
     <t>Industry, Mining, Construction</t>
-  </si>
-  <si>
-    <t>321</t>
   </si>
   <si>
     <t>32120</t>
@@ -2169,13 +2169,13 @@
         <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F6" t="s">
         <v>12</v>
       </c>
       <c r="G6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2192,13 +2192,13 @@
         <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F7" t="s">
         <v>12</v>
       </c>
       <c r="G7" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2215,13 +2215,13 @@
         <v>22</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F8" t="s">
         <v>12</v>
       </c>
       <c r="G8" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2238,13 +2238,13 @@
         <v>22</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F9" t="s">
         <v>12</v>
       </c>
       <c r="G9" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2261,13 +2261,13 @@
         <v>32</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="F10" t="s">
         <v>12</v>
       </c>
       <c r="G10" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2284,13 +2284,13 @@
         <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="F11" t="s">
         <v>12</v>
       </c>
       <c r="G11" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2307,13 +2307,13 @@
         <v>38</v>
       </c>
       <c r="E12" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="F12" t="s">
         <v>12</v>
       </c>
       <c r="G12" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2330,13 +2330,13 @@
         <v>38</v>
       </c>
       <c r="E13" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="F13" t="s">
         <v>12</v>
       </c>
       <c r="G13" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2445,13 +2445,13 @@
         <v>56</v>
       </c>
       <c r="E18" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F18" t="s">
         <v>46</v>
       </c>
       <c r="G18" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2468,13 +2468,13 @@
         <v>56</v>
       </c>
       <c r="E19" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F19" t="s">
         <v>46</v>
       </c>
       <c r="G19" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2491,13 +2491,13 @@
         <v>56</v>
       </c>
       <c r="E20" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F20" t="s">
         <v>46</v>
       </c>
       <c r="G20" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2514,13 +2514,13 @@
         <v>56</v>
       </c>
       <c r="E21" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F21" t="s">
         <v>46</v>
       </c>
       <c r="G21" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2537,13 +2537,13 @@
         <v>56</v>
       </c>
       <c r="E22" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F22" t="s">
         <v>46</v>
       </c>
       <c r="G22" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2560,13 +2560,13 @@
         <v>56</v>
       </c>
       <c r="E23" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F23" t="s">
         <v>46</v>
       </c>
       <c r="G23" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2583,13 +2583,13 @@
         <v>56</v>
       </c>
       <c r="E24" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F24" t="s">
         <v>46</v>
       </c>
       <c r="G24" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2606,13 +2606,13 @@
         <v>56</v>
       </c>
       <c r="E25" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F25" t="s">
         <v>46</v>
       </c>
       <c r="G25" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2629,13 +2629,13 @@
         <v>74</v>
       </c>
       <c r="E26" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="F26" t="s">
         <v>46</v>
       </c>
       <c r="G26" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2652,13 +2652,13 @@
         <v>74</v>
       </c>
       <c r="E27" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="F27" t="s">
         <v>46</v>
       </c>
       <c r="G27" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2675,13 +2675,13 @@
         <v>74</v>
       </c>
       <c r="E28" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="F28" t="s">
         <v>46</v>
       </c>
       <c r="G28" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2698,13 +2698,13 @@
         <v>74</v>
       </c>
       <c r="E29" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="F29" t="s">
         <v>46</v>
       </c>
       <c r="G29" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2721,13 +2721,13 @@
         <v>74</v>
       </c>
       <c r="E30" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="F30" t="s">
         <v>46</v>
       </c>
       <c r="G30" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2744,13 +2744,13 @@
         <v>74</v>
       </c>
       <c r="E31" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="F31" t="s">
         <v>46</v>
       </c>
       <c r="G31" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2770,10 +2770,10 @@
         <v>89</v>
       </c>
       <c r="F32" t="s">
+        <v>89</v>
+      </c>
+      <c r="G32" t="s">
         <v>88</v>
-      </c>
-      <c r="G32" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2793,10 +2793,10 @@
         <v>89</v>
       </c>
       <c r="F33" t="s">
+        <v>89</v>
+      </c>
+      <c r="G33" t="s">
         <v>88</v>
-      </c>
-      <c r="G33" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2816,10 +2816,10 @@
         <v>89</v>
       </c>
       <c r="F34" t="s">
+        <v>89</v>
+      </c>
+      <c r="G34" t="s">
         <v>88</v>
-      </c>
-      <c r="G34" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2839,10 +2839,10 @@
         <v>89</v>
       </c>
       <c r="F35" t="s">
+        <v>89</v>
+      </c>
+      <c r="G35" t="s">
         <v>88</v>
-      </c>
-      <c r="G35" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2862,10 +2862,10 @@
         <v>89</v>
       </c>
       <c r="F36" t="s">
+        <v>89</v>
+      </c>
+      <c r="G36" t="s">
         <v>88</v>
-      </c>
-      <c r="G36" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2885,10 +2885,10 @@
         <v>101</v>
       </c>
       <c r="F37" t="s">
+        <v>101</v>
+      </c>
+      <c r="G37" t="s">
         <v>100</v>
-      </c>
-      <c r="G37" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2908,10 +2908,10 @@
         <v>101</v>
       </c>
       <c r="F38" t="s">
+        <v>101</v>
+      </c>
+      <c r="G38" t="s">
         <v>100</v>
-      </c>
-      <c r="G38" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2931,10 +2931,10 @@
         <v>101</v>
       </c>
       <c r="F39" t="s">
+        <v>101</v>
+      </c>
+      <c r="G39" t="s">
         <v>100</v>
-      </c>
-      <c r="G39" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2954,10 +2954,10 @@
         <v>101</v>
       </c>
       <c r="F40" t="s">
+        <v>101</v>
+      </c>
+      <c r="G40" t="s">
         <v>100</v>
-      </c>
-      <c r="G40" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2977,10 +2977,10 @@
         <v>101</v>
       </c>
       <c r="F41" t="s">
+        <v>101</v>
+      </c>
+      <c r="G41" t="s">
         <v>100</v>
-      </c>
-      <c r="G41" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -3000,10 +3000,10 @@
         <v>101</v>
       </c>
       <c r="F42" t="s">
+        <v>101</v>
+      </c>
+      <c r="G42" t="s">
         <v>100</v>
-      </c>
-      <c r="G42" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3023,10 +3023,10 @@
         <v>101</v>
       </c>
       <c r="F43" t="s">
+        <v>101</v>
+      </c>
+      <c r="G43" t="s">
         <v>100</v>
-      </c>
-      <c r="G43" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3046,10 +3046,10 @@
         <v>101</v>
       </c>
       <c r="F44" t="s">
+        <v>101</v>
+      </c>
+      <c r="G44" t="s">
         <v>100</v>
-      </c>
-      <c r="G44" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3069,10 +3069,10 @@
         <v>101</v>
       </c>
       <c r="F45" t="s">
+        <v>101</v>
+      </c>
+      <c r="G45" t="s">
         <v>100</v>
-      </c>
-      <c r="G45" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3092,10 +3092,10 @@
         <v>101</v>
       </c>
       <c r="F46" t="s">
+        <v>101</v>
+      </c>
+      <c r="G46" t="s">
         <v>100</v>
-      </c>
-      <c r="G46" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3115,10 +3115,10 @@
         <v>101</v>
       </c>
       <c r="F47" t="s">
+        <v>101</v>
+      </c>
+      <c r="G47" t="s">
         <v>100</v>
-      </c>
-      <c r="G47" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3503,13 +3503,13 @@
         <v>160</v>
       </c>
       <c r="E64" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="F64" t="s">
         <v>126</v>
       </c>
       <c r="G64" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3526,13 +3526,13 @@
         <v>160</v>
       </c>
       <c r="E65" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="F65" t="s">
         <v>126</v>
       </c>
       <c r="G65" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3549,13 +3549,13 @@
         <v>160</v>
       </c>
       <c r="E66" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="F66" t="s">
         <v>126</v>
       </c>
       <c r="G66" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3572,13 +3572,13 @@
         <v>160</v>
       </c>
       <c r="E67" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="F67" t="s">
         <v>126</v>
       </c>
       <c r="G67" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3595,13 +3595,13 @@
         <v>160</v>
       </c>
       <c r="E68" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="F68" t="s">
         <v>126</v>
       </c>
       <c r="G68" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3618,13 +3618,13 @@
         <v>160</v>
       </c>
       <c r="E69" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="F69" t="s">
         <v>126</v>
       </c>
       <c r="G69" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3644,10 +3644,10 @@
         <v>175</v>
       </c>
       <c r="F70" t="s">
+        <v>175</v>
+      </c>
+      <c r="G70" t="s">
         <v>174</v>
-      </c>
-      <c r="G70" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3667,10 +3667,10 @@
         <v>175</v>
       </c>
       <c r="F71" t="s">
+        <v>175</v>
+      </c>
+      <c r="G71" t="s">
         <v>174</v>
-      </c>
-      <c r="G71" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3690,10 +3690,10 @@
         <v>175</v>
       </c>
       <c r="F72" t="s">
+        <v>175</v>
+      </c>
+      <c r="G72" t="s">
         <v>174</v>
-      </c>
-      <c r="G72" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3713,10 +3713,10 @@
         <v>175</v>
       </c>
       <c r="F73" t="s">
+        <v>175</v>
+      </c>
+      <c r="G73" t="s">
         <v>174</v>
-      </c>
-      <c r="G73" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3736,10 +3736,10 @@
         <v>175</v>
       </c>
       <c r="F74" t="s">
+        <v>175</v>
+      </c>
+      <c r="G74" t="s">
         <v>174</v>
-      </c>
-      <c r="G74" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3759,10 +3759,10 @@
         <v>175</v>
       </c>
       <c r="F75" t="s">
+        <v>175</v>
+      </c>
+      <c r="G75" t="s">
         <v>174</v>
-      </c>
-      <c r="G75" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3782,10 +3782,10 @@
         <v>175</v>
       </c>
       <c r="F76" t="s">
+        <v>175</v>
+      </c>
+      <c r="G76" t="s">
         <v>174</v>
-      </c>
-      <c r="G76" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3805,10 +3805,10 @@
         <v>175</v>
       </c>
       <c r="F77" t="s">
+        <v>175</v>
+      </c>
+      <c r="G77" t="s">
         <v>174</v>
-      </c>
-      <c r="G77" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3828,10 +3828,10 @@
         <v>175</v>
       </c>
       <c r="F78" t="s">
+        <v>175</v>
+      </c>
+      <c r="G78" t="s">
         <v>174</v>
-      </c>
-      <c r="G78" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3851,10 +3851,10 @@
         <v>175</v>
       </c>
       <c r="F79" t="s">
+        <v>175</v>
+      </c>
+      <c r="G79" t="s">
         <v>174</v>
-      </c>
-      <c r="G79" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3874,10 +3874,10 @@
         <v>175</v>
       </c>
       <c r="F80" t="s">
+        <v>175</v>
+      </c>
+      <c r="G80" t="s">
         <v>174</v>
-      </c>
-      <c r="G80" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3897,10 +3897,10 @@
         <v>199</v>
       </c>
       <c r="F81" t="s">
+        <v>199</v>
+      </c>
+      <c r="G81" t="s">
         <v>198</v>
-      </c>
-      <c r="G81" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3920,10 +3920,10 @@
         <v>199</v>
       </c>
       <c r="F82" t="s">
+        <v>199</v>
+      </c>
+      <c r="G82" t="s">
         <v>198</v>
-      </c>
-      <c r="G82" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3943,10 +3943,10 @@
         <v>199</v>
       </c>
       <c r="F83" t="s">
+        <v>199</v>
+      </c>
+      <c r="G83" t="s">
         <v>198</v>
-      </c>
-      <c r="G83" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3966,10 +3966,10 @@
         <v>199</v>
       </c>
       <c r="F84" t="s">
+        <v>199</v>
+      </c>
+      <c r="G84" t="s">
         <v>198</v>
-      </c>
-      <c r="G84" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3989,10 +3989,10 @@
         <v>199</v>
       </c>
       <c r="F85" t="s">
+        <v>199</v>
+      </c>
+      <c r="G85" t="s">
         <v>198</v>
-      </c>
-      <c r="G85" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4012,10 +4012,10 @@
         <v>199</v>
       </c>
       <c r="F86" t="s">
+        <v>199</v>
+      </c>
+      <c r="G86" t="s">
         <v>198</v>
-      </c>
-      <c r="G86" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4035,10 +4035,10 @@
         <v>199</v>
       </c>
       <c r="F87" t="s">
+        <v>199</v>
+      </c>
+      <c r="G87" t="s">
         <v>198</v>
-      </c>
-      <c r="G87" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4058,10 +4058,10 @@
         <v>215</v>
       </c>
       <c r="F88" t="s">
+        <v>215</v>
+      </c>
+      <c r="G88" t="s">
         <v>214</v>
-      </c>
-      <c r="G88" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4081,10 +4081,10 @@
         <v>215</v>
       </c>
       <c r="F89" t="s">
+        <v>215</v>
+      </c>
+      <c r="G89" t="s">
         <v>214</v>
-      </c>
-      <c r="G89" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4104,10 +4104,10 @@
         <v>215</v>
       </c>
       <c r="F90" t="s">
+        <v>215</v>
+      </c>
+      <c r="G90" t="s">
         <v>214</v>
-      </c>
-      <c r="G90" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4127,10 +4127,10 @@
         <v>215</v>
       </c>
       <c r="F91" t="s">
+        <v>215</v>
+      </c>
+      <c r="G91" t="s">
         <v>214</v>
-      </c>
-      <c r="G91" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4239,13 +4239,13 @@
         <v>236</v>
       </c>
       <c r="E96" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F96" t="s">
         <v>226</v>
       </c>
       <c r="G96" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -4262,13 +4262,13 @@
         <v>236</v>
       </c>
       <c r="E97" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F97" t="s">
         <v>226</v>
       </c>
       <c r="G97" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4285,13 +4285,13 @@
         <v>236</v>
       </c>
       <c r="E98" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F98" t="s">
         <v>226</v>
       </c>
       <c r="G98" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4308,13 +4308,13 @@
         <v>236</v>
       </c>
       <c r="E99" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F99" t="s">
         <v>226</v>
       </c>
       <c r="G99" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4331,13 +4331,13 @@
         <v>236</v>
       </c>
       <c r="E100" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F100" t="s">
         <v>226</v>
       </c>
       <c r="G100" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4354,13 +4354,13 @@
         <v>236</v>
       </c>
       <c r="E101" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F101" t="s">
         <v>226</v>
       </c>
       <c r="G101" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4377,13 +4377,13 @@
         <v>236</v>
       </c>
       <c r="E102" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F102" t="s">
         <v>226</v>
       </c>
       <c r="G102" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4400,13 +4400,13 @@
         <v>236</v>
       </c>
       <c r="E103" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F103" t="s">
         <v>226</v>
       </c>
       <c r="G103" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4423,13 +4423,13 @@
         <v>236</v>
       </c>
       <c r="E104" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F104" t="s">
         <v>226</v>
       </c>
       <c r="G104" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4446,13 +4446,13 @@
         <v>256</v>
       </c>
       <c r="E105" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="F105" t="s">
         <v>226</v>
       </c>
       <c r="G105" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4469,13 +4469,13 @@
         <v>256</v>
       </c>
       <c r="E106" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="F106" t="s">
         <v>226</v>
       </c>
       <c r="G106" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4492,13 +4492,13 @@
         <v>256</v>
       </c>
       <c r="E107" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="F107" t="s">
         <v>226</v>
       </c>
       <c r="G107" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4515,13 +4515,13 @@
         <v>256</v>
       </c>
       <c r="E108" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="F108" t="s">
         <v>226</v>
       </c>
       <c r="G108" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4538,13 +4538,13 @@
         <v>256</v>
       </c>
       <c r="E109" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="F109" t="s">
         <v>226</v>
       </c>
       <c r="G109" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4561,13 +4561,13 @@
         <v>256</v>
       </c>
       <c r="E110" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="F110" t="s">
         <v>226</v>
       </c>
       <c r="G110" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4584,13 +4584,13 @@
         <v>270</v>
       </c>
       <c r="E111" t="s">
-        <v>225</v>
+        <v>271</v>
       </c>
       <c r="F111" t="s">
         <v>226</v>
       </c>
       <c r="G111" t="s">
-        <v>271</v>
+        <v>227</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4607,13 +4607,13 @@
         <v>274</v>
       </c>
       <c r="E112" t="s">
-        <v>225</v>
+        <v>275</v>
       </c>
       <c r="F112" t="s">
         <v>226</v>
       </c>
       <c r="G112" t="s">
-        <v>275</v>
+        <v>227</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4630,13 +4630,13 @@
         <v>278</v>
       </c>
       <c r="E113" t="s">
-        <v>225</v>
+        <v>279</v>
       </c>
       <c r="F113" t="s">
         <v>226</v>
       </c>
       <c r="G113" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4653,13 +4653,13 @@
         <v>278</v>
       </c>
       <c r="E114" t="s">
-        <v>225</v>
+        <v>279</v>
       </c>
       <c r="F114" t="s">
         <v>226</v>
       </c>
       <c r="G114" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4676,13 +4676,13 @@
         <v>278</v>
       </c>
       <c r="E115" t="s">
-        <v>225</v>
+        <v>279</v>
       </c>
       <c r="F115" t="s">
         <v>226</v>
       </c>
       <c r="G115" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4699,13 +4699,13 @@
         <v>278</v>
       </c>
       <c r="E116" t="s">
-        <v>225</v>
+        <v>279</v>
       </c>
       <c r="F116" t="s">
         <v>226</v>
       </c>
       <c r="G116" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4722,13 +4722,13 @@
         <v>278</v>
       </c>
       <c r="E117" t="s">
-        <v>225</v>
+        <v>279</v>
       </c>
       <c r="F117" t="s">
         <v>226</v>
       </c>
       <c r="G117" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4745,13 +4745,13 @@
         <v>278</v>
       </c>
       <c r="E118" t="s">
-        <v>225</v>
+        <v>279</v>
       </c>
       <c r="F118" t="s">
         <v>226</v>
       </c>
       <c r="G118" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4768,13 +4768,13 @@
         <v>278</v>
       </c>
       <c r="E119" t="s">
-        <v>225</v>
+        <v>279</v>
       </c>
       <c r="F119" t="s">
         <v>226</v>
       </c>
       <c r="G119" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4794,10 +4794,10 @@
         <v>295</v>
       </c>
       <c r="F120" t="s">
+        <v>295</v>
+      </c>
+      <c r="G120" t="s">
         <v>294</v>
-      </c>
-      <c r="G120" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4817,10 +4817,10 @@
         <v>295</v>
       </c>
       <c r="F121" t="s">
+        <v>295</v>
+      </c>
+      <c r="G121" t="s">
         <v>294</v>
-      </c>
-      <c r="G121" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4840,10 +4840,10 @@
         <v>295</v>
       </c>
       <c r="F122" t="s">
+        <v>295</v>
+      </c>
+      <c r="G122" t="s">
         <v>294</v>
-      </c>
-      <c r="G122" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4863,10 +4863,10 @@
         <v>295</v>
       </c>
       <c r="F123" t="s">
+        <v>295</v>
+      </c>
+      <c r="G123" t="s">
         <v>294</v>
-      </c>
-      <c r="G123" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4886,10 +4886,10 @@
         <v>295</v>
       </c>
       <c r="F124" t="s">
+        <v>295</v>
+      </c>
+      <c r="G124" t="s">
         <v>294</v>
-      </c>
-      <c r="G124" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4909,10 +4909,10 @@
         <v>295</v>
       </c>
       <c r="F125" t="s">
+        <v>295</v>
+      </c>
+      <c r="G125" t="s">
         <v>294</v>
-      </c>
-      <c r="G125" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4932,10 +4932,10 @@
         <v>309</v>
       </c>
       <c r="F126" t="s">
+        <v>309</v>
+      </c>
+      <c r="G126" t="s">
         <v>308</v>
-      </c>
-      <c r="G126" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4955,10 +4955,10 @@
         <v>309</v>
       </c>
       <c r="F127" t="s">
+        <v>309</v>
+      </c>
+      <c r="G127" t="s">
         <v>308</v>
-      </c>
-      <c r="G127" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4978,10 +4978,10 @@
         <v>309</v>
       </c>
       <c r="F128" t="s">
+        <v>309</v>
+      </c>
+      <c r="G128" t="s">
         <v>308</v>
-      </c>
-      <c r="G128" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -5001,10 +5001,10 @@
         <v>309</v>
       </c>
       <c r="F129" t="s">
+        <v>309</v>
+      </c>
+      <c r="G129" t="s">
         <v>308</v>
-      </c>
-      <c r="G129" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -5435,13 +5435,13 @@
         <v>358</v>
       </c>
       <c r="E148" t="s">
-        <v>319</v>
+        <v>359</v>
       </c>
       <c r="F148" t="s">
         <v>320</v>
       </c>
       <c r="G148" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5458,13 +5458,13 @@
         <v>358</v>
       </c>
       <c r="E149" t="s">
-        <v>319</v>
+        <v>359</v>
       </c>
       <c r="F149" t="s">
         <v>320</v>
       </c>
       <c r="G149" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5481,13 +5481,13 @@
         <v>358</v>
       </c>
       <c r="E150" t="s">
-        <v>319</v>
+        <v>359</v>
       </c>
       <c r="F150" t="s">
         <v>320</v>
       </c>
       <c r="G150" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5504,13 +5504,13 @@
         <v>358</v>
       </c>
       <c r="E151" t="s">
-        <v>319</v>
+        <v>359</v>
       </c>
       <c r="F151" t="s">
         <v>320</v>
       </c>
       <c r="G151" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5527,13 +5527,13 @@
         <v>358</v>
       </c>
       <c r="E152" t="s">
-        <v>319</v>
+        <v>359</v>
       </c>
       <c r="F152" t="s">
         <v>320</v>
       </c>
       <c r="G152" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5550,13 +5550,13 @@
         <v>358</v>
       </c>
       <c r="E153" t="s">
-        <v>319</v>
+        <v>359</v>
       </c>
       <c r="F153" t="s">
         <v>320</v>
       </c>
       <c r="G153" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5573,13 +5573,13 @@
         <v>372</v>
       </c>
       <c r="E154" t="s">
-        <v>319</v>
+        <v>373</v>
       </c>
       <c r="F154" t="s">
         <v>320</v>
       </c>
       <c r="G154" t="s">
-        <v>373</v>
+        <v>321</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5596,13 +5596,13 @@
         <v>372</v>
       </c>
       <c r="E155" t="s">
-        <v>319</v>
+        <v>373</v>
       </c>
       <c r="F155" t="s">
         <v>320</v>
       </c>
       <c r="G155" t="s">
-        <v>373</v>
+        <v>321</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5619,13 +5619,13 @@
         <v>372</v>
       </c>
       <c r="E156" t="s">
-        <v>319</v>
+        <v>373</v>
       </c>
       <c r="F156" t="s">
         <v>320</v>
       </c>
       <c r="G156" t="s">
-        <v>373</v>
+        <v>321</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5642,13 +5642,13 @@
         <v>372</v>
       </c>
       <c r="E157" t="s">
-        <v>319</v>
+        <v>373</v>
       </c>
       <c r="F157" t="s">
         <v>320</v>
       </c>
       <c r="G157" t="s">
-        <v>373</v>
+        <v>321</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5665,13 +5665,13 @@
         <v>372</v>
       </c>
       <c r="E158" t="s">
-        <v>319</v>
+        <v>373</v>
       </c>
       <c r="F158" t="s">
         <v>320</v>
       </c>
       <c r="G158" t="s">
-        <v>373</v>
+        <v>321</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -6125,13 +6125,13 @@
         <v>426</v>
       </c>
       <c r="E178" t="s">
-        <v>385</v>
+        <v>427</v>
       </c>
       <c r="F178" t="s">
         <v>386</v>
       </c>
       <c r="G178" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -6148,13 +6148,13 @@
         <v>426</v>
       </c>
       <c r="E179" t="s">
-        <v>385</v>
+        <v>427</v>
       </c>
       <c r="F179" t="s">
         <v>386</v>
       </c>
       <c r="G179" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -6171,13 +6171,13 @@
         <v>426</v>
       </c>
       <c r="E180" t="s">
-        <v>385</v>
+        <v>427</v>
       </c>
       <c r="F180" t="s">
         <v>386</v>
       </c>
       <c r="G180" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -6194,13 +6194,13 @@
         <v>426</v>
       </c>
       <c r="E181" t="s">
-        <v>385</v>
+        <v>427</v>
       </c>
       <c r="F181" t="s">
         <v>386</v>
       </c>
       <c r="G181" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -6217,13 +6217,13 @@
         <v>426</v>
       </c>
       <c r="E182" t="s">
-        <v>385</v>
+        <v>427</v>
       </c>
       <c r="F182" t="s">
         <v>386</v>
       </c>
       <c r="G182" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -6240,13 +6240,13 @@
         <v>426</v>
       </c>
       <c r="E183" t="s">
-        <v>385</v>
+        <v>427</v>
       </c>
       <c r="F183" t="s">
         <v>386</v>
       </c>
       <c r="G183" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -6263,13 +6263,13 @@
         <v>426</v>
       </c>
       <c r="E184" t="s">
-        <v>385</v>
+        <v>427</v>
       </c>
       <c r="F184" t="s">
         <v>386</v>
       </c>
       <c r="G184" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -6286,13 +6286,13 @@
         <v>426</v>
       </c>
       <c r="E185" t="s">
-        <v>385</v>
+        <v>427</v>
       </c>
       <c r="F185" t="s">
         <v>386</v>
       </c>
       <c r="G185" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -6309,13 +6309,13 @@
         <v>426</v>
       </c>
       <c r="E186" t="s">
-        <v>385</v>
+        <v>427</v>
       </c>
       <c r="F186" t="s">
         <v>386</v>
       </c>
       <c r="G186" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -6332,13 +6332,13 @@
         <v>426</v>
       </c>
       <c r="E187" t="s">
-        <v>385</v>
+        <v>427</v>
       </c>
       <c r="F187" t="s">
         <v>386</v>
       </c>
       <c r="G187" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -6355,13 +6355,13 @@
         <v>448</v>
       </c>
       <c r="E188" t="s">
-        <v>385</v>
+        <v>449</v>
       </c>
       <c r="F188" t="s">
         <v>386</v>
       </c>
       <c r="G188" t="s">
-        <v>449</v>
+        <v>387</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -6381,10 +6381,10 @@
         <v>453</v>
       </c>
       <c r="F189" t="s">
+        <v>453</v>
+      </c>
+      <c r="G189" t="s">
         <v>452</v>
-      </c>
-      <c r="G189" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6404,10 +6404,10 @@
         <v>453</v>
       </c>
       <c r="F190" t="s">
+        <v>453</v>
+      </c>
+      <c r="G190" t="s">
         <v>452</v>
-      </c>
-      <c r="G190" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6427,10 +6427,10 @@
         <v>453</v>
       </c>
       <c r="F191" t="s">
+        <v>453</v>
+      </c>
+      <c r="G191" t="s">
         <v>452</v>
-      </c>
-      <c r="G191" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6450,10 +6450,10 @@
         <v>453</v>
       </c>
       <c r="F192" t="s">
+        <v>453</v>
+      </c>
+      <c r="G192" t="s">
         <v>452</v>
-      </c>
-      <c r="G192" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6473,10 +6473,10 @@
         <v>453</v>
       </c>
       <c r="F193" t="s">
+        <v>453</v>
+      </c>
+      <c r="G193" t="s">
         <v>452</v>
-      </c>
-      <c r="G193" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6496,10 +6496,10 @@
         <v>453</v>
       </c>
       <c r="F194" t="s">
+        <v>453</v>
+      </c>
+      <c r="G194" t="s">
         <v>452</v>
-      </c>
-      <c r="G194" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6519,10 +6519,10 @@
         <v>467</v>
       </c>
       <c r="F195" t="s">
+        <v>467</v>
+      </c>
+      <c r="G195" t="s">
         <v>466</v>
-      </c>
-      <c r="G195" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6542,10 +6542,10 @@
         <v>471</v>
       </c>
       <c r="F196" t="s">
+        <v>471</v>
+      </c>
+      <c r="G196" t="s">
         <v>470</v>
-      </c>
-      <c r="G196" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6565,10 +6565,10 @@
         <v>471</v>
       </c>
       <c r="F197" t="s">
+        <v>471</v>
+      </c>
+      <c r="G197" t="s">
         <v>470</v>
-      </c>
-      <c r="G197" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6588,10 +6588,10 @@
         <v>471</v>
       </c>
       <c r="F198" t="s">
+        <v>471</v>
+      </c>
+      <c r="G198" t="s">
         <v>470</v>
-      </c>
-      <c r="G198" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6611,10 +6611,10 @@
         <v>471</v>
       </c>
       <c r="F199" t="s">
+        <v>471</v>
+      </c>
+      <c r="G199" t="s">
         <v>470</v>
-      </c>
-      <c r="G199" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6634,10 +6634,10 @@
         <v>471</v>
       </c>
       <c r="F200" t="s">
+        <v>471</v>
+      </c>
+      <c r="G200" t="s">
         <v>470</v>
-      </c>
-      <c r="G200" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6657,10 +6657,10 @@
         <v>471</v>
       </c>
       <c r="F201" t="s">
+        <v>471</v>
+      </c>
+      <c r="G201" t="s">
         <v>470</v>
-      </c>
-      <c r="G201" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6680,10 +6680,10 @@
         <v>485</v>
       </c>
       <c r="F202" t="s">
+        <v>485</v>
+      </c>
+      <c r="G202" t="s">
         <v>484</v>
-      </c>
-      <c r="G202" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6703,10 +6703,10 @@
         <v>485</v>
       </c>
       <c r="F203" t="s">
+        <v>485</v>
+      </c>
+      <c r="G203" t="s">
         <v>484</v>
-      </c>
-      <c r="G203" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6726,10 +6726,10 @@
         <v>485</v>
       </c>
       <c r="F204" t="s">
+        <v>485</v>
+      </c>
+      <c r="G204" t="s">
         <v>484</v>
-      </c>
-      <c r="G204" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6749,10 +6749,10 @@
         <v>485</v>
       </c>
       <c r="F205" t="s">
+        <v>485</v>
+      </c>
+      <c r="G205" t="s">
         <v>484</v>
-      </c>
-      <c r="G205" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6772,10 +6772,10 @@
         <v>485</v>
       </c>
       <c r="F206" t="s">
+        <v>485</v>
+      </c>
+      <c r="G206" t="s">
         <v>484</v>
-      </c>
-      <c r="G206" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6795,10 +6795,10 @@
         <v>485</v>
       </c>
       <c r="F207" t="s">
+        <v>485</v>
+      </c>
+      <c r="G207" t="s">
         <v>484</v>
-      </c>
-      <c r="G207" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6818,10 +6818,10 @@
         <v>485</v>
       </c>
       <c r="F208" t="s">
+        <v>485</v>
+      </c>
+      <c r="G208" t="s">
         <v>484</v>
-      </c>
-      <c r="G208" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6841,10 +6841,10 @@
         <v>485</v>
       </c>
       <c r="F209" t="s">
+        <v>485</v>
+      </c>
+      <c r="G209" t="s">
         <v>484</v>
-      </c>
-      <c r="G209" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6864,10 +6864,10 @@
         <v>485</v>
       </c>
       <c r="F210" t="s">
+        <v>485</v>
+      </c>
+      <c r="G210" t="s">
         <v>484</v>
-      </c>
-      <c r="G210" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6887,10 +6887,10 @@
         <v>485</v>
       </c>
       <c r="F211" t="s">
+        <v>485</v>
+      </c>
+      <c r="G211" t="s">
         <v>484</v>
-      </c>
-      <c r="G211" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6910,10 +6910,10 @@
         <v>507</v>
       </c>
       <c r="F212" t="s">
+        <v>507</v>
+      </c>
+      <c r="G212" t="s">
         <v>506</v>
-      </c>
-      <c r="G212" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6933,10 +6933,10 @@
         <v>511</v>
       </c>
       <c r="F213" t="s">
+        <v>511</v>
+      </c>
+      <c r="G213" t="s">
         <v>510</v>
-      </c>
-      <c r="G213" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6956,10 +6956,10 @@
         <v>515</v>
       </c>
       <c r="F214" t="s">
+        <v>515</v>
+      </c>
+      <c r="G214" t="s">
         <v>514</v>
-      </c>
-      <c r="G214" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6979,10 +6979,10 @@
         <v>515</v>
       </c>
       <c r="F215" t="s">
+        <v>515</v>
+      </c>
+      <c r="G215" t="s">
         <v>514</v>
-      </c>
-      <c r="G215" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -7002,10 +7002,10 @@
         <v>521</v>
       </c>
       <c r="F216" t="s">
+        <v>521</v>
+      </c>
+      <c r="G216" t="s">
         <v>520</v>
-      </c>
-      <c r="G216" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -7025,10 +7025,10 @@
         <v>521</v>
       </c>
       <c r="F217" t="s">
+        <v>521</v>
+      </c>
+      <c r="G217" t="s">
         <v>520</v>
-      </c>
-      <c r="G217" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -7048,10 +7048,10 @@
         <v>521</v>
       </c>
       <c r="F218" t="s">
+        <v>521</v>
+      </c>
+      <c r="G218" t="s">
         <v>520</v>
-      </c>
-      <c r="G218" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -7071,10 +7071,10 @@
         <v>521</v>
       </c>
       <c r="F219" t="s">
+        <v>521</v>
+      </c>
+      <c r="G219" t="s">
         <v>520</v>
-      </c>
-      <c r="G219" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -7094,10 +7094,10 @@
         <v>521</v>
       </c>
       <c r="F220" t="s">
+        <v>521</v>
+      </c>
+      <c r="G220" t="s">
         <v>520</v>
-      </c>
-      <c r="G220" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -7117,10 +7117,10 @@
         <v>521</v>
       </c>
       <c r="F221" t="s">
+        <v>521</v>
+      </c>
+      <c r="G221" t="s">
         <v>520</v>
-      </c>
-      <c r="G221" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -7140,10 +7140,10 @@
         <v>521</v>
       </c>
       <c r="F222" t="s">
+        <v>521</v>
+      </c>
+      <c r="G222" t="s">
         <v>520</v>
-      </c>
-      <c r="G222" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -7163,10 +7163,10 @@
         <v>537</v>
       </c>
       <c r="F223" t="s">
+        <v>537</v>
+      </c>
+      <c r="G223" t="s">
         <v>536</v>
-      </c>
-      <c r="G223" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -7186,10 +7186,10 @@
         <v>537</v>
       </c>
       <c r="F224" t="s">
+        <v>537</v>
+      </c>
+      <c r="G224" t="s">
         <v>536</v>
-      </c>
-      <c r="G224" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -7209,10 +7209,10 @@
         <v>537</v>
       </c>
       <c r="F225" t="s">
+        <v>537</v>
+      </c>
+      <c r="G225" t="s">
         <v>536</v>
-      </c>
-      <c r="G225" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -7232,10 +7232,10 @@
         <v>545</v>
       </c>
       <c r="F226" t="s">
+        <v>545</v>
+      </c>
+      <c r="G226" t="s">
         <v>544</v>
-      </c>
-      <c r="G226" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -7255,10 +7255,10 @@
         <v>549</v>
       </c>
       <c r="F227" t="s">
+        <v>549</v>
+      </c>
+      <c r="G227" t="s">
         <v>548</v>
-      </c>
-      <c r="G227" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -7278,10 +7278,10 @@
         <v>553</v>
       </c>
       <c r="F228" t="s">
+        <v>553</v>
+      </c>
+      <c r="G228" t="s">
         <v>552</v>
-      </c>
-      <c r="G228" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -7301,10 +7301,10 @@
         <v>557</v>
       </c>
       <c r="F229" t="s">
+        <v>557</v>
+      </c>
+      <c r="G229" t="s">
         <v>556</v>
-      </c>
-      <c r="G229" t="s">
-        <v>557</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -7324,10 +7324,10 @@
         <v>561</v>
       </c>
       <c r="F230" t="s">
+        <v>561</v>
+      </c>
+      <c r="G230" t="s">
         <v>560</v>
-      </c>
-      <c r="G230" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -7347,10 +7347,10 @@
         <v>561</v>
       </c>
       <c r="F231" t="s">
+        <v>561</v>
+      </c>
+      <c r="G231" t="s">
         <v>560</v>
-      </c>
-      <c r="G231" t="s">
-        <v>561</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/en/SectorGroup.xlsx
+++ b/api/xlsx/en/SectorGroup.xlsx
@@ -25,18 +25,18 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
     <t>codeforiati:category-name</t>
   </si>
   <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -46,18 +46,18 @@
     <t>active</t>
   </si>
   <si>
+    <t>110</t>
+  </si>
+  <si>
     <t>Education, Level Unspecified</t>
   </si>
   <si>
+    <t>Education</t>
+  </si>
+  <si>
     <t>111</t>
   </si>
   <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>Education</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -148,18 +148,18 @@
     <t>Health policy and administrative management</t>
   </si>
   <si>
+    <t>120</t>
+  </si>
+  <si>
     <t>Health, General</t>
   </si>
   <si>
+    <t>Health</t>
+  </si>
+  <si>
     <t>121</t>
   </si>
   <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>Health</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -280,12 +280,12 @@
     <t>Population policy and administrative management</t>
   </si>
   <si>
+    <t>130</t>
+  </si>
+  <si>
     <t>Population Policies/Programmes &amp; Reproductive Health</t>
   </si>
   <si>
-    <t>130</t>
-  </si>
-  <si>
     <t>13020</t>
   </si>
   <si>
@@ -316,12 +316,12 @@
     <t>Water sector policy and administrative management</t>
   </si>
   <si>
+    <t>140</t>
+  </si>
+  <si>
     <t>Water Supply &amp; Sanitation</t>
   </si>
   <si>
-    <t>140</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -388,18 +388,18 @@
     <t>Public sector policy and administrative management</t>
   </si>
   <si>
+    <t>150</t>
+  </si>
+  <si>
     <t>Government &amp; Civil Society-general</t>
   </si>
   <si>
+    <t>Government &amp; Civil Society</t>
+  </si>
+  <si>
     <t>151</t>
   </si>
   <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>Government &amp; Civil Society</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -538,12 +538,12 @@
     <t>Social Protection</t>
   </si>
   <si>
+    <t>160</t>
+  </si>
+  <si>
     <t>Other Social Infrastructure &amp; Services</t>
   </si>
   <si>
-    <t>160</t>
-  </si>
-  <si>
     <t>16020</t>
   </si>
   <si>
@@ -610,12 +610,12 @@
     <t>Transport policy and administrative management</t>
   </si>
   <si>
+    <t>210</t>
+  </si>
+  <si>
     <t>Transport &amp; Storage</t>
   </si>
   <si>
-    <t>210</t>
-  </si>
-  <si>
     <t>21020</t>
   </si>
   <si>
@@ -658,12 +658,12 @@
     <t>Communications policy and administrative management</t>
   </si>
   <si>
+    <t>220</t>
+  </si>
+  <si>
     <t>Communications</t>
   </si>
   <si>
-    <t>220</t>
-  </si>
-  <si>
     <t>22020</t>
   </si>
   <si>
@@ -688,18 +688,18 @@
     <t>Energy policy and administrative management</t>
   </si>
   <si>
+    <t>230</t>
+  </si>
+  <si>
     <t>Energy Policy</t>
   </si>
   <si>
+    <t>Energy</t>
+  </si>
+  <si>
     <t>231</t>
   </si>
   <si>
-    <t>230</t>
-  </si>
-  <si>
-    <t>Energy</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -898,12 +898,12 @@
     <t>Financial policy and administrative management</t>
   </si>
   <si>
+    <t>240</t>
+  </si>
+  <si>
     <t>Banking &amp; Financial Services</t>
   </si>
   <si>
-    <t>240</t>
-  </si>
-  <si>
     <t>24020</t>
   </si>
   <si>
@@ -940,12 +940,12 @@
     <t>Business policy and administration</t>
   </si>
   <si>
+    <t>250</t>
+  </si>
+  <si>
     <t>Business &amp; Other Services</t>
   </si>
   <si>
-    <t>250</t>
-  </si>
-  <si>
     <t>25020</t>
   </si>
   <si>
@@ -970,18 +970,18 @@
     <t>Agricultural policy and administrative management</t>
   </si>
   <si>
+    <t>310</t>
+  </si>
+  <si>
     <t>Agriculture</t>
   </si>
   <si>
+    <t>Agriculture, Forestry, Fishing</t>
+  </si>
+  <si>
     <t>311</t>
   </si>
   <si>
-    <t>310</t>
-  </si>
-  <si>
-    <t>Agriculture, Forestry, Fishing</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1168,18 +1168,18 @@
     <t>Industrial policy and administrative management</t>
   </si>
   <si>
+    <t>320</t>
+  </si>
+  <si>
     <t>Industry</t>
   </si>
   <si>
+    <t>Industry, Mining, Construction</t>
+  </si>
+  <si>
     <t>321</t>
   </si>
   <si>
-    <t>320</t>
-  </si>
-  <si>
-    <t>Industry, Mining, Construction</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1372,12 +1372,12 @@
     <t>Trade policy and administrative management</t>
   </si>
   <si>
+    <t>331</t>
+  </si>
+  <si>
     <t>Trade Policies &amp; Regulations</t>
   </si>
   <si>
-    <t>331</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1414,24 +1414,24 @@
     <t>Tourism policy and administrative management</t>
   </si>
   <si>
+    <t>332</t>
+  </si>
+  <si>
     <t>Tourism</t>
   </si>
   <si>
-    <t>332</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
     <t>Environmental policy and administrative management</t>
   </si>
   <si>
+    <t>410</t>
+  </si>
+  <si>
     <t>General Environment Protection</t>
   </si>
   <si>
-    <t>410</t>
-  </si>
-  <si>
     <t>41020</t>
   </si>
   <si>
@@ -1468,12 +1468,12 @@
     <t>Multisector aid</t>
   </si>
   <si>
+    <t>430</t>
+  </si>
+  <si>
     <t>Other Multisector</t>
   </si>
   <si>
-    <t>430</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -1534,36 +1534,36 @@
     <t>General budget support-related aid</t>
   </si>
   <si>
+    <t>510</t>
+  </si>
+  <si>
     <t>General Budget Support</t>
   </si>
   <si>
-    <t>510</t>
-  </si>
-  <si>
     <t>52010</t>
   </si>
   <si>
     <t>Food assistance</t>
   </si>
   <si>
+    <t>520</t>
+  </si>
+  <si>
     <t>Development Food Assistance</t>
   </si>
   <si>
-    <t>520</t>
-  </si>
-  <si>
     <t>53030</t>
   </si>
   <si>
     <t>Import support (capital goods)</t>
   </si>
   <si>
+    <t>530</t>
+  </si>
+  <si>
     <t>Other Commodity Assistance</t>
   </si>
   <si>
-    <t>530</t>
-  </si>
-  <si>
     <t>53040</t>
   </si>
   <si>
@@ -1576,12 +1576,12 @@
     <t>Action relating to debt</t>
   </si>
   <si>
+    <t>600</t>
+  </si>
+  <si>
     <t>Action Relating to Debt</t>
   </si>
   <si>
-    <t>600</t>
-  </si>
-  <si>
     <t>60020</t>
   </si>
   <si>
@@ -1624,12 +1624,12 @@
     <t>Material relief assistance and services</t>
   </si>
   <si>
+    <t>720</t>
+  </si>
+  <si>
     <t>Emergency Response</t>
   </si>
   <si>
-    <t>720</t>
-  </si>
-  <si>
     <t>72040</t>
   </si>
   <si>
@@ -1648,58 +1648,58 @@
     <t>Immediate post-emergency reconstruction and rehabilitation</t>
   </si>
   <si>
+    <t>730</t>
+  </si>
+  <si>
     <t>Reconstruction Relief &amp; Rehabilitation</t>
   </si>
   <si>
-    <t>730</t>
-  </si>
-  <si>
     <t>74020</t>
   </si>
   <si>
     <t>Multi-hazard response preparedness</t>
   </si>
   <si>
+    <t>740</t>
+  </si>
+  <si>
     <t>Disaster Prevention &amp; Preparedness</t>
   </si>
   <si>
-    <t>740</t>
-  </si>
-  <si>
     <t>91010</t>
   </si>
   <si>
     <t>Administrative costs (non-sector allocable)</t>
   </si>
   <si>
+    <t>910</t>
+  </si>
+  <si>
     <t>Administrative Costs of Donors</t>
   </si>
   <si>
-    <t>910</t>
-  </si>
-  <si>
     <t>93010</t>
   </si>
   <si>
     <t>Refugees/asylum seekers in donor countries (non-sector allocable)</t>
   </si>
   <si>
+    <t>930</t>
+  </si>
+  <si>
     <t>Refugees in Donor Countries</t>
   </si>
   <si>
-    <t>930</t>
-  </si>
-  <si>
     <t>99810</t>
   </si>
   <si>
     <t>Sectors not specified</t>
   </si>
   <si>
+    <t>998</t>
+  </si>
+  <si>
     <t>Unallocated / Unspecified</t>
-  </si>
-  <si>
-    <t>998</t>
   </si>
   <si>
     <t>99820</t>
@@ -2166,16 +2166,16 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
         <v>22</v>
-      </c>
-      <c r="E6" t="s">
-        <v>23</v>
       </c>
       <c r="F6" t="s">
         <v>12</v>
       </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2189,16 +2189,16 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" t="s">
         <v>22</v>
-      </c>
-      <c r="E7" t="s">
-        <v>23</v>
       </c>
       <c r="F7" t="s">
         <v>12</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2212,16 +2212,16 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" t="s">
         <v>22</v>
-      </c>
-      <c r="E8" t="s">
-        <v>23</v>
       </c>
       <c r="F8" t="s">
         <v>12</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2235,16 +2235,16 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" t="s">
         <v>22</v>
-      </c>
-      <c r="E9" t="s">
-        <v>23</v>
       </c>
       <c r="F9" t="s">
         <v>12</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2258,16 +2258,16 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" t="s">
         <v>32</v>
-      </c>
-      <c r="E10" t="s">
-        <v>33</v>
       </c>
       <c r="F10" t="s">
         <v>12</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2281,16 +2281,16 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" t="s">
         <v>32</v>
-      </c>
-      <c r="E11" t="s">
-        <v>33</v>
       </c>
       <c r="F11" t="s">
         <v>12</v>
       </c>
       <c r="G11" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2304,16 +2304,16 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" t="s">
         <v>38</v>
-      </c>
-      <c r="E12" t="s">
-        <v>39</v>
       </c>
       <c r="F12" t="s">
         <v>12</v>
       </c>
       <c r="G12" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2327,16 +2327,16 @@
         <v>9</v>
       </c>
       <c r="D13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" t="s">
         <v>38</v>
-      </c>
-      <c r="E13" t="s">
-        <v>39</v>
       </c>
       <c r="F13" t="s">
         <v>12</v>
       </c>
       <c r="G13" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2442,16 +2442,16 @@
         <v>9</v>
       </c>
       <c r="D18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18" t="s">
         <v>56</v>
-      </c>
-      <c r="E18" t="s">
-        <v>57</v>
       </c>
       <c r="F18" t="s">
         <v>46</v>
       </c>
       <c r="G18" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2465,16 +2465,16 @@
         <v>9</v>
       </c>
       <c r="D19" t="s">
+        <v>44</v>
+      </c>
+      <c r="E19" t="s">
         <v>56</v>
-      </c>
-      <c r="E19" t="s">
-        <v>57</v>
       </c>
       <c r="F19" t="s">
         <v>46</v>
       </c>
       <c r="G19" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2488,16 +2488,16 @@
         <v>9</v>
       </c>
       <c r="D20" t="s">
+        <v>44</v>
+      </c>
+      <c r="E20" t="s">
         <v>56</v>
-      </c>
-      <c r="E20" t="s">
-        <v>57</v>
       </c>
       <c r="F20" t="s">
         <v>46</v>
       </c>
       <c r="G20" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2511,16 +2511,16 @@
         <v>9</v>
       </c>
       <c r="D21" t="s">
+        <v>44</v>
+      </c>
+      <c r="E21" t="s">
         <v>56</v>
-      </c>
-      <c r="E21" t="s">
-        <v>57</v>
       </c>
       <c r="F21" t="s">
         <v>46</v>
       </c>
       <c r="G21" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2534,16 +2534,16 @@
         <v>9</v>
       </c>
       <c r="D22" t="s">
+        <v>44</v>
+      </c>
+      <c r="E22" t="s">
         <v>56</v>
-      </c>
-      <c r="E22" t="s">
-        <v>57</v>
       </c>
       <c r="F22" t="s">
         <v>46</v>
       </c>
       <c r="G22" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2557,16 +2557,16 @@
         <v>9</v>
       </c>
       <c r="D23" t="s">
+        <v>44</v>
+      </c>
+      <c r="E23" t="s">
         <v>56</v>
-      </c>
-      <c r="E23" t="s">
-        <v>57</v>
       </c>
       <c r="F23" t="s">
         <v>46</v>
       </c>
       <c r="G23" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2580,16 +2580,16 @@
         <v>9</v>
       </c>
       <c r="D24" t="s">
+        <v>44</v>
+      </c>
+      <c r="E24" t="s">
         <v>56</v>
-      </c>
-      <c r="E24" t="s">
-        <v>57</v>
       </c>
       <c r="F24" t="s">
         <v>46</v>
       </c>
       <c r="G24" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2603,16 +2603,16 @@
         <v>9</v>
       </c>
       <c r="D25" t="s">
+        <v>44</v>
+      </c>
+      <c r="E25" t="s">
         <v>56</v>
-      </c>
-      <c r="E25" t="s">
-        <v>57</v>
       </c>
       <c r="F25" t="s">
         <v>46</v>
       </c>
       <c r="G25" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2626,16 +2626,16 @@
         <v>9</v>
       </c>
       <c r="D26" t="s">
+        <v>44</v>
+      </c>
+      <c r="E26" t="s">
         <v>74</v>
-      </c>
-      <c r="E26" t="s">
-        <v>75</v>
       </c>
       <c r="F26" t="s">
         <v>46</v>
       </c>
       <c r="G26" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2649,16 +2649,16 @@
         <v>9</v>
       </c>
       <c r="D27" t="s">
+        <v>44</v>
+      </c>
+      <c r="E27" t="s">
         <v>74</v>
-      </c>
-      <c r="E27" t="s">
-        <v>75</v>
       </c>
       <c r="F27" t="s">
         <v>46</v>
       </c>
       <c r="G27" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2672,16 +2672,16 @@
         <v>9</v>
       </c>
       <c r="D28" t="s">
+        <v>44</v>
+      </c>
+      <c r="E28" t="s">
         <v>74</v>
-      </c>
-      <c r="E28" t="s">
-        <v>75</v>
       </c>
       <c r="F28" t="s">
         <v>46</v>
       </c>
       <c r="G28" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2695,16 +2695,16 @@
         <v>9</v>
       </c>
       <c r="D29" t="s">
+        <v>44</v>
+      </c>
+      <c r="E29" t="s">
         <v>74</v>
-      </c>
-      <c r="E29" t="s">
-        <v>75</v>
       </c>
       <c r="F29" t="s">
         <v>46</v>
       </c>
       <c r="G29" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2718,16 +2718,16 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
+        <v>44</v>
+      </c>
+      <c r="E30" t="s">
         <v>74</v>
-      </c>
-      <c r="E30" t="s">
-        <v>75</v>
       </c>
       <c r="F30" t="s">
         <v>46</v>
       </c>
       <c r="G30" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2741,16 +2741,16 @@
         <v>9</v>
       </c>
       <c r="D31" t="s">
+        <v>44</v>
+      </c>
+      <c r="E31" t="s">
         <v>74</v>
-      </c>
-      <c r="E31" t="s">
-        <v>75</v>
       </c>
       <c r="F31" t="s">
         <v>46</v>
       </c>
       <c r="G31" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -3500,16 +3500,16 @@
         <v>9</v>
       </c>
       <c r="D64" t="s">
+        <v>124</v>
+      </c>
+      <c r="E64" t="s">
         <v>160</v>
-      </c>
-      <c r="E64" t="s">
-        <v>161</v>
       </c>
       <c r="F64" t="s">
         <v>126</v>
       </c>
       <c r="G64" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3523,16 +3523,16 @@
         <v>9</v>
       </c>
       <c r="D65" t="s">
+        <v>124</v>
+      </c>
+      <c r="E65" t="s">
         <v>160</v>
-      </c>
-      <c r="E65" t="s">
-        <v>161</v>
       </c>
       <c r="F65" t="s">
         <v>126</v>
       </c>
       <c r="G65" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3546,16 +3546,16 @@
         <v>9</v>
       </c>
       <c r="D66" t="s">
+        <v>124</v>
+      </c>
+      <c r="E66" t="s">
         <v>160</v>
-      </c>
-      <c r="E66" t="s">
-        <v>161</v>
       </c>
       <c r="F66" t="s">
         <v>126</v>
       </c>
       <c r="G66" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3569,16 +3569,16 @@
         <v>9</v>
       </c>
       <c r="D67" t="s">
+        <v>124</v>
+      </c>
+      <c r="E67" t="s">
         <v>160</v>
-      </c>
-      <c r="E67" t="s">
-        <v>161</v>
       </c>
       <c r="F67" t="s">
         <v>126</v>
       </c>
       <c r="G67" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3592,16 +3592,16 @@
         <v>9</v>
       </c>
       <c r="D68" t="s">
+        <v>124</v>
+      </c>
+      <c r="E68" t="s">
         <v>160</v>
-      </c>
-      <c r="E68" t="s">
-        <v>161</v>
       </c>
       <c r="F68" t="s">
         <v>126</v>
       </c>
       <c r="G68" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3615,16 +3615,16 @@
         <v>9</v>
       </c>
       <c r="D69" t="s">
+        <v>124</v>
+      </c>
+      <c r="E69" t="s">
         <v>160</v>
-      </c>
-      <c r="E69" t="s">
-        <v>161</v>
       </c>
       <c r="F69" t="s">
         <v>126</v>
       </c>
       <c r="G69" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -4236,16 +4236,16 @@
         <v>9</v>
       </c>
       <c r="D96" t="s">
+        <v>224</v>
+      </c>
+      <c r="E96" t="s">
         <v>236</v>
-      </c>
-      <c r="E96" t="s">
-        <v>237</v>
       </c>
       <c r="F96" t="s">
         <v>226</v>
       </c>
       <c r="G96" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -4259,16 +4259,16 @@
         <v>9</v>
       </c>
       <c r="D97" t="s">
+        <v>224</v>
+      </c>
+      <c r="E97" t="s">
         <v>236</v>
-      </c>
-      <c r="E97" t="s">
-        <v>237</v>
       </c>
       <c r="F97" t="s">
         <v>226</v>
       </c>
       <c r="G97" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4282,16 +4282,16 @@
         <v>9</v>
       </c>
       <c r="D98" t="s">
+        <v>224</v>
+      </c>
+      <c r="E98" t="s">
         <v>236</v>
-      </c>
-      <c r="E98" t="s">
-        <v>237</v>
       </c>
       <c r="F98" t="s">
         <v>226</v>
       </c>
       <c r="G98" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4305,16 +4305,16 @@
         <v>9</v>
       </c>
       <c r="D99" t="s">
+        <v>224</v>
+      </c>
+      <c r="E99" t="s">
         <v>236</v>
-      </c>
-      <c r="E99" t="s">
-        <v>237</v>
       </c>
       <c r="F99" t="s">
         <v>226</v>
       </c>
       <c r="G99" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4328,16 +4328,16 @@
         <v>9</v>
       </c>
       <c r="D100" t="s">
+        <v>224</v>
+      </c>
+      <c r="E100" t="s">
         <v>236</v>
-      </c>
-      <c r="E100" t="s">
-        <v>237</v>
       </c>
       <c r="F100" t="s">
         <v>226</v>
       </c>
       <c r="G100" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4351,16 +4351,16 @@
         <v>9</v>
       </c>
       <c r="D101" t="s">
+        <v>224</v>
+      </c>
+      <c r="E101" t="s">
         <v>236</v>
-      </c>
-      <c r="E101" t="s">
-        <v>237</v>
       </c>
       <c r="F101" t="s">
         <v>226</v>
       </c>
       <c r="G101" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4374,16 +4374,16 @@
         <v>9</v>
       </c>
       <c r="D102" t="s">
+        <v>224</v>
+      </c>
+      <c r="E102" t="s">
         <v>236</v>
-      </c>
-      <c r="E102" t="s">
-        <v>237</v>
       </c>
       <c r="F102" t="s">
         <v>226</v>
       </c>
       <c r="G102" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4397,16 +4397,16 @@
         <v>9</v>
       </c>
       <c r="D103" t="s">
+        <v>224</v>
+      </c>
+      <c r="E103" t="s">
         <v>236</v>
-      </c>
-      <c r="E103" t="s">
-        <v>237</v>
       </c>
       <c r="F103" t="s">
         <v>226</v>
       </c>
       <c r="G103" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4420,16 +4420,16 @@
         <v>9</v>
       </c>
       <c r="D104" t="s">
+        <v>224</v>
+      </c>
+      <c r="E104" t="s">
         <v>236</v>
-      </c>
-      <c r="E104" t="s">
-        <v>237</v>
       </c>
       <c r="F104" t="s">
         <v>226</v>
       </c>
       <c r="G104" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4443,16 +4443,16 @@
         <v>9</v>
       </c>
       <c r="D105" t="s">
+        <v>224</v>
+      </c>
+      <c r="E105" t="s">
         <v>256</v>
-      </c>
-      <c r="E105" t="s">
-        <v>257</v>
       </c>
       <c r="F105" t="s">
         <v>226</v>
       </c>
       <c r="G105" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4466,16 +4466,16 @@
         <v>9</v>
       </c>
       <c r="D106" t="s">
+        <v>224</v>
+      </c>
+      <c r="E106" t="s">
         <v>256</v>
-      </c>
-      <c r="E106" t="s">
-        <v>257</v>
       </c>
       <c r="F106" t="s">
         <v>226</v>
       </c>
       <c r="G106" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4489,16 +4489,16 @@
         <v>9</v>
       </c>
       <c r="D107" t="s">
+        <v>224</v>
+      </c>
+      <c r="E107" t="s">
         <v>256</v>
-      </c>
-      <c r="E107" t="s">
-        <v>257</v>
       </c>
       <c r="F107" t="s">
         <v>226</v>
       </c>
       <c r="G107" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4512,16 +4512,16 @@
         <v>9</v>
       </c>
       <c r="D108" t="s">
+        <v>224</v>
+      </c>
+      <c r="E108" t="s">
         <v>256</v>
-      </c>
-      <c r="E108" t="s">
-        <v>257</v>
       </c>
       <c r="F108" t="s">
         <v>226</v>
       </c>
       <c r="G108" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4535,16 +4535,16 @@
         <v>9</v>
       </c>
       <c r="D109" t="s">
+        <v>224</v>
+      </c>
+      <c r="E109" t="s">
         <v>256</v>
-      </c>
-      <c r="E109" t="s">
-        <v>257</v>
       </c>
       <c r="F109" t="s">
         <v>226</v>
       </c>
       <c r="G109" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4558,16 +4558,16 @@
         <v>9</v>
       </c>
       <c r="D110" t="s">
+        <v>224</v>
+      </c>
+      <c r="E110" t="s">
         <v>256</v>
-      </c>
-      <c r="E110" t="s">
-        <v>257</v>
       </c>
       <c r="F110" t="s">
         <v>226</v>
       </c>
       <c r="G110" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4581,16 +4581,16 @@
         <v>9</v>
       </c>
       <c r="D111" t="s">
+        <v>224</v>
+      </c>
+      <c r="E111" t="s">
         <v>270</v>
-      </c>
-      <c r="E111" t="s">
-        <v>271</v>
       </c>
       <c r="F111" t="s">
         <v>226</v>
       </c>
       <c r="G111" t="s">
-        <v>227</v>
+        <v>271</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4604,16 +4604,16 @@
         <v>9</v>
       </c>
       <c r="D112" t="s">
+        <v>224</v>
+      </c>
+      <c r="E112" t="s">
         <v>274</v>
-      </c>
-      <c r="E112" t="s">
-        <v>275</v>
       </c>
       <c r="F112" t="s">
         <v>226</v>
       </c>
       <c r="G112" t="s">
-        <v>227</v>
+        <v>275</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4627,16 +4627,16 @@
         <v>9</v>
       </c>
       <c r="D113" t="s">
+        <v>224</v>
+      </c>
+      <c r="E113" t="s">
         <v>278</v>
-      </c>
-      <c r="E113" t="s">
-        <v>279</v>
       </c>
       <c r="F113" t="s">
         <v>226</v>
       </c>
       <c r="G113" t="s">
-        <v>227</v>
+        <v>279</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4650,16 +4650,16 @@
         <v>9</v>
       </c>
       <c r="D114" t="s">
+        <v>224</v>
+      </c>
+      <c r="E114" t="s">
         <v>278</v>
-      </c>
-      <c r="E114" t="s">
-        <v>279</v>
       </c>
       <c r="F114" t="s">
         <v>226</v>
       </c>
       <c r="G114" t="s">
-        <v>227</v>
+        <v>279</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4673,16 +4673,16 @@
         <v>9</v>
       </c>
       <c r="D115" t="s">
+        <v>224</v>
+      </c>
+      <c r="E115" t="s">
         <v>278</v>
-      </c>
-      <c r="E115" t="s">
-        <v>279</v>
       </c>
       <c r="F115" t="s">
         <v>226</v>
       </c>
       <c r="G115" t="s">
-        <v>227</v>
+        <v>279</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4696,16 +4696,16 @@
         <v>9</v>
       </c>
       <c r="D116" t="s">
+        <v>224</v>
+      </c>
+      <c r="E116" t="s">
         <v>278</v>
-      </c>
-      <c r="E116" t="s">
-        <v>279</v>
       </c>
       <c r="F116" t="s">
         <v>226</v>
       </c>
       <c r="G116" t="s">
-        <v>227</v>
+        <v>279</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4719,16 +4719,16 @@
         <v>9</v>
       </c>
       <c r="D117" t="s">
+        <v>224</v>
+      </c>
+      <c r="E117" t="s">
         <v>278</v>
-      </c>
-      <c r="E117" t="s">
-        <v>279</v>
       </c>
       <c r="F117" t="s">
         <v>226</v>
       </c>
       <c r="G117" t="s">
-        <v>227</v>
+        <v>279</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4742,16 +4742,16 @@
         <v>9</v>
       </c>
       <c r="D118" t="s">
+        <v>224</v>
+      </c>
+      <c r="E118" t="s">
         <v>278</v>
-      </c>
-      <c r="E118" t="s">
-        <v>279</v>
       </c>
       <c r="F118" t="s">
         <v>226</v>
       </c>
       <c r="G118" t="s">
-        <v>227</v>
+        <v>279</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4765,16 +4765,16 @@
         <v>9</v>
       </c>
       <c r="D119" t="s">
+        <v>224</v>
+      </c>
+      <c r="E119" t="s">
         <v>278</v>
-      </c>
-      <c r="E119" t="s">
-        <v>279</v>
       </c>
       <c r="F119" t="s">
         <v>226</v>
       </c>
       <c r="G119" t="s">
-        <v>227</v>
+        <v>279</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -5432,16 +5432,16 @@
         <v>9</v>
       </c>
       <c r="D148" t="s">
+        <v>318</v>
+      </c>
+      <c r="E148" t="s">
         <v>358</v>
-      </c>
-      <c r="E148" t="s">
-        <v>359</v>
       </c>
       <c r="F148" t="s">
         <v>320</v>
       </c>
       <c r="G148" t="s">
-        <v>321</v>
+        <v>359</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5455,16 +5455,16 @@
         <v>9</v>
       </c>
       <c r="D149" t="s">
+        <v>318</v>
+      </c>
+      <c r="E149" t="s">
         <v>358</v>
-      </c>
-      <c r="E149" t="s">
-        <v>359</v>
       </c>
       <c r="F149" t="s">
         <v>320</v>
       </c>
       <c r="G149" t="s">
-        <v>321</v>
+        <v>359</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5478,16 +5478,16 @@
         <v>9</v>
       </c>
       <c r="D150" t="s">
+        <v>318</v>
+      </c>
+      <c r="E150" t="s">
         <v>358</v>
-      </c>
-      <c r="E150" t="s">
-        <v>359</v>
       </c>
       <c r="F150" t="s">
         <v>320</v>
       </c>
       <c r="G150" t="s">
-        <v>321</v>
+        <v>359</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5501,16 +5501,16 @@
         <v>9</v>
       </c>
       <c r="D151" t="s">
+        <v>318</v>
+      </c>
+      <c r="E151" t="s">
         <v>358</v>
-      </c>
-      <c r="E151" t="s">
-        <v>359</v>
       </c>
       <c r="F151" t="s">
         <v>320</v>
       </c>
       <c r="G151" t="s">
-        <v>321</v>
+        <v>359</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5524,16 +5524,16 @@
         <v>9</v>
       </c>
       <c r="D152" t="s">
+        <v>318</v>
+      </c>
+      <c r="E152" t="s">
         <v>358</v>
-      </c>
-      <c r="E152" t="s">
-        <v>359</v>
       </c>
       <c r="F152" t="s">
         <v>320</v>
       </c>
       <c r="G152" t="s">
-        <v>321</v>
+        <v>359</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5547,16 +5547,16 @@
         <v>9</v>
       </c>
       <c r="D153" t="s">
+        <v>318</v>
+      </c>
+      <c r="E153" t="s">
         <v>358</v>
-      </c>
-      <c r="E153" t="s">
-        <v>359</v>
       </c>
       <c r="F153" t="s">
         <v>320</v>
       </c>
       <c r="G153" t="s">
-        <v>321</v>
+        <v>359</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5570,16 +5570,16 @@
         <v>9</v>
       </c>
       <c r="D154" t="s">
+        <v>318</v>
+      </c>
+      <c r="E154" t="s">
         <v>372</v>
-      </c>
-      <c r="E154" t="s">
-        <v>373</v>
       </c>
       <c r="F154" t="s">
         <v>320</v>
       </c>
       <c r="G154" t="s">
-        <v>321</v>
+        <v>373</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5593,16 +5593,16 @@
         <v>9</v>
       </c>
       <c r="D155" t="s">
+        <v>318</v>
+      </c>
+      <c r="E155" t="s">
         <v>372</v>
-      </c>
-      <c r="E155" t="s">
-        <v>373</v>
       </c>
       <c r="F155" t="s">
         <v>320</v>
       </c>
       <c r="G155" t="s">
-        <v>321</v>
+        <v>373</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5616,16 +5616,16 @@
         <v>9</v>
       </c>
       <c r="D156" t="s">
+        <v>318</v>
+      </c>
+      <c r="E156" t="s">
         <v>372</v>
-      </c>
-      <c r="E156" t="s">
-        <v>373</v>
       </c>
       <c r="F156" t="s">
         <v>320</v>
       </c>
       <c r="G156" t="s">
-        <v>321</v>
+        <v>373</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5639,16 +5639,16 @@
         <v>9</v>
       </c>
       <c r="D157" t="s">
+        <v>318</v>
+      </c>
+      <c r="E157" t="s">
         <v>372</v>
-      </c>
-      <c r="E157" t="s">
-        <v>373</v>
       </c>
       <c r="F157" t="s">
         <v>320</v>
       </c>
       <c r="G157" t="s">
-        <v>321</v>
+        <v>373</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5662,16 +5662,16 @@
         <v>9</v>
       </c>
       <c r="D158" t="s">
+        <v>318</v>
+      </c>
+      <c r="E158" t="s">
         <v>372</v>
-      </c>
-      <c r="E158" t="s">
-        <v>373</v>
       </c>
       <c r="F158" t="s">
         <v>320</v>
       </c>
       <c r="G158" t="s">
-        <v>321</v>
+        <v>373</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -6122,16 +6122,16 @@
         <v>9</v>
       </c>
       <c r="D178" t="s">
+        <v>384</v>
+      </c>
+      <c r="E178" t="s">
         <v>426</v>
-      </c>
-      <c r="E178" t="s">
-        <v>427</v>
       </c>
       <c r="F178" t="s">
         <v>386</v>
       </c>
       <c r="G178" t="s">
-        <v>387</v>
+        <v>427</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -6145,16 +6145,16 @@
         <v>9</v>
       </c>
       <c r="D179" t="s">
+        <v>384</v>
+      </c>
+      <c r="E179" t="s">
         <v>426</v>
-      </c>
-      <c r="E179" t="s">
-        <v>427</v>
       </c>
       <c r="F179" t="s">
         <v>386</v>
       </c>
       <c r="G179" t="s">
-        <v>387</v>
+        <v>427</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -6168,16 +6168,16 @@
         <v>9</v>
       </c>
       <c r="D180" t="s">
+        <v>384</v>
+      </c>
+      <c r="E180" t="s">
         <v>426</v>
-      </c>
-      <c r="E180" t="s">
-        <v>427</v>
       </c>
       <c r="F180" t="s">
         <v>386</v>
       </c>
       <c r="G180" t="s">
-        <v>387</v>
+        <v>427</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -6191,16 +6191,16 @@
         <v>9</v>
       </c>
       <c r="D181" t="s">
+        <v>384</v>
+      </c>
+      <c r="E181" t="s">
         <v>426</v>
-      </c>
-      <c r="E181" t="s">
-        <v>427</v>
       </c>
       <c r="F181" t="s">
         <v>386</v>
       </c>
       <c r="G181" t="s">
-        <v>387</v>
+        <v>427</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -6214,16 +6214,16 @@
         <v>9</v>
       </c>
       <c r="D182" t="s">
+        <v>384</v>
+      </c>
+      <c r="E182" t="s">
         <v>426</v>
-      </c>
-      <c r="E182" t="s">
-        <v>427</v>
       </c>
       <c r="F182" t="s">
         <v>386</v>
       </c>
       <c r="G182" t="s">
-        <v>387</v>
+        <v>427</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -6237,16 +6237,16 @@
         <v>9</v>
       </c>
       <c r="D183" t="s">
+        <v>384</v>
+      </c>
+      <c r="E183" t="s">
         <v>426</v>
-      </c>
-      <c r="E183" t="s">
-        <v>427</v>
       </c>
       <c r="F183" t="s">
         <v>386</v>
       </c>
       <c r="G183" t="s">
-        <v>387</v>
+        <v>427</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -6260,16 +6260,16 @@
         <v>9</v>
       </c>
       <c r="D184" t="s">
+        <v>384</v>
+      </c>
+      <c r="E184" t="s">
         <v>426</v>
-      </c>
-      <c r="E184" t="s">
-        <v>427</v>
       </c>
       <c r="F184" t="s">
         <v>386</v>
       </c>
       <c r="G184" t="s">
-        <v>387</v>
+        <v>427</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -6283,16 +6283,16 @@
         <v>9</v>
       </c>
       <c r="D185" t="s">
+        <v>384</v>
+      </c>
+      <c r="E185" t="s">
         <v>426</v>
-      </c>
-      <c r="E185" t="s">
-        <v>427</v>
       </c>
       <c r="F185" t="s">
         <v>386</v>
       </c>
       <c r="G185" t="s">
-        <v>387</v>
+        <v>427</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -6306,16 +6306,16 @@
         <v>9</v>
       </c>
       <c r="D186" t="s">
+        <v>384</v>
+      </c>
+      <c r="E186" t="s">
         <v>426</v>
-      </c>
-      <c r="E186" t="s">
-        <v>427</v>
       </c>
       <c r="F186" t="s">
         <v>386</v>
       </c>
       <c r="G186" t="s">
-        <v>387</v>
+        <v>427</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -6329,16 +6329,16 @@
         <v>9</v>
       </c>
       <c r="D187" t="s">
+        <v>384</v>
+      </c>
+      <c r="E187" t="s">
         <v>426</v>
-      </c>
-      <c r="E187" t="s">
-        <v>427</v>
       </c>
       <c r="F187" t="s">
         <v>386</v>
       </c>
       <c r="G187" t="s">
-        <v>387</v>
+        <v>427</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -6352,16 +6352,16 @@
         <v>9</v>
       </c>
       <c r="D188" t="s">
+        <v>384</v>
+      </c>
+      <c r="E188" t="s">
         <v>448</v>
-      </c>
-      <c r="E188" t="s">
-        <v>449</v>
       </c>
       <c r="F188" t="s">
         <v>386</v>
       </c>
       <c r="G188" t="s">
-        <v>387</v>
+        <v>449</v>
       </c>
     </row>
     <row r="189" spans="1:7">

--- a/api/xlsx/en/SectorGroup.xlsx
+++ b/api/xlsx/en/SectorGroup.xlsx
@@ -25,15 +25,15 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
+    <t>codeforiati:category-name</t>
+  </si>
+  <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
-    <t>codeforiati:category-name</t>
-  </si>
-  <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
@@ -46,15 +46,15 @@
     <t>active</t>
   </si>
   <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>Education, Level Unspecified</t>
+  </si>
+  <si>
     <t>110</t>
   </si>
   <si>
-    <t>Education, Level Unspecified</t>
-  </si>
-  <si>
-    <t>Education</t>
-  </si>
-  <si>
     <t>111</t>
   </si>
   <si>
@@ -148,15 +148,15 @@
     <t>Health policy and administrative management</t>
   </si>
   <si>
+    <t>Health</t>
+  </si>
+  <si>
+    <t>Health, General</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
-    <t>Health, General</t>
-  </si>
-  <si>
-    <t>Health</t>
-  </si>
-  <si>
     <t>121</t>
   </si>
   <si>
@@ -280,12 +280,12 @@
     <t>Population policy and administrative management</t>
   </si>
   <si>
+    <t>Population Policies/Programmes &amp; Reproductive Health</t>
+  </si>
+  <si>
     <t>130</t>
   </si>
   <si>
-    <t>Population Policies/Programmes &amp; Reproductive Health</t>
-  </si>
-  <si>
     <t>13020</t>
   </si>
   <si>
@@ -316,12 +316,12 @@
     <t>Water sector policy and administrative management</t>
   </si>
   <si>
+    <t>Water Supply &amp; Sanitation</t>
+  </si>
+  <si>
     <t>140</t>
   </si>
   <si>
-    <t>Water Supply &amp; Sanitation</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -388,15 +388,15 @@
     <t>Public sector policy and administrative management</t>
   </si>
   <si>
+    <t>Government &amp; Civil Society</t>
+  </si>
+  <si>
+    <t>Government &amp; Civil Society-general</t>
+  </si>
+  <si>
     <t>150</t>
   </si>
   <si>
-    <t>Government &amp; Civil Society-general</t>
-  </si>
-  <si>
-    <t>Government &amp; Civil Society</t>
-  </si>
-  <si>
     <t>151</t>
   </si>
   <si>
@@ -538,12 +538,12 @@
     <t>Social Protection</t>
   </si>
   <si>
+    <t>Other Social Infrastructure &amp; Services</t>
+  </si>
+  <si>
     <t>160</t>
   </si>
   <si>
-    <t>Other Social Infrastructure &amp; Services</t>
-  </si>
-  <si>
     <t>16020</t>
   </si>
   <si>
@@ -610,12 +610,12 @@
     <t>Transport policy and administrative management</t>
   </si>
   <si>
+    <t>Transport &amp; Storage</t>
+  </si>
+  <si>
     <t>210</t>
   </si>
   <si>
-    <t>Transport &amp; Storage</t>
-  </si>
-  <si>
     <t>21020</t>
   </si>
   <si>
@@ -658,12 +658,12 @@
     <t>Communications policy and administrative management</t>
   </si>
   <si>
+    <t>Communications</t>
+  </si>
+  <si>
     <t>220</t>
   </si>
   <si>
-    <t>Communications</t>
-  </si>
-  <si>
     <t>22020</t>
   </si>
   <si>
@@ -688,15 +688,15 @@
     <t>Energy policy and administrative management</t>
   </si>
   <si>
+    <t>Energy</t>
+  </si>
+  <si>
+    <t>Energy Policy</t>
+  </si>
+  <si>
     <t>230</t>
   </si>
   <si>
-    <t>Energy Policy</t>
-  </si>
-  <si>
-    <t>Energy</t>
-  </si>
-  <si>
     <t>231</t>
   </si>
   <si>
@@ -898,12 +898,12 @@
     <t>Financial policy and administrative management</t>
   </si>
   <si>
+    <t>Banking &amp; Financial Services</t>
+  </si>
+  <si>
     <t>240</t>
   </si>
   <si>
-    <t>Banking &amp; Financial Services</t>
-  </si>
-  <si>
     <t>24020</t>
   </si>
   <si>
@@ -940,12 +940,12 @@
     <t>Business policy and administration</t>
   </si>
   <si>
+    <t>Business &amp; Other Services</t>
+  </si>
+  <si>
     <t>250</t>
   </si>
   <si>
-    <t>Business &amp; Other Services</t>
-  </si>
-  <si>
     <t>25020</t>
   </si>
   <si>
@@ -970,15 +970,15 @@
     <t>Agricultural policy and administrative management</t>
   </si>
   <si>
+    <t>Agriculture, Forestry, Fishing</t>
+  </si>
+  <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
     <t>310</t>
   </si>
   <si>
-    <t>Agriculture</t>
-  </si>
-  <si>
-    <t>Agriculture, Forestry, Fishing</t>
-  </si>
-  <si>
     <t>311</t>
   </si>
   <si>
@@ -1168,15 +1168,15 @@
     <t>Industrial policy and administrative management</t>
   </si>
   <si>
+    <t>Industry, Mining, Construction</t>
+  </si>
+  <si>
+    <t>Industry</t>
+  </si>
+  <si>
     <t>320</t>
   </si>
   <si>
-    <t>Industry</t>
-  </si>
-  <si>
-    <t>Industry, Mining, Construction</t>
-  </si>
-  <si>
     <t>321</t>
   </si>
   <si>
@@ -1372,12 +1372,12 @@
     <t>Trade policy and administrative management</t>
   </si>
   <si>
+    <t>Trade Policies &amp; Regulations</t>
+  </si>
+  <si>
     <t>331</t>
   </si>
   <si>
-    <t>Trade Policies &amp; Regulations</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1414,24 +1414,24 @@
     <t>Tourism policy and administrative management</t>
   </si>
   <si>
+    <t>Tourism</t>
+  </si>
+  <si>
     <t>332</t>
   </si>
   <si>
-    <t>Tourism</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
     <t>Environmental policy and administrative management</t>
   </si>
   <si>
+    <t>General Environment Protection</t>
+  </si>
+  <si>
     <t>410</t>
   </si>
   <si>
-    <t>General Environment Protection</t>
-  </si>
-  <si>
     <t>41020</t>
   </si>
   <si>
@@ -1468,12 +1468,12 @@
     <t>Multisector aid</t>
   </si>
   <si>
+    <t>Other Multisector</t>
+  </si>
+  <si>
     <t>430</t>
   </si>
   <si>
-    <t>Other Multisector</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -1534,36 +1534,36 @@
     <t>General budget support-related aid</t>
   </si>
   <si>
+    <t>General Budget Support</t>
+  </si>
+  <si>
     <t>510</t>
   </si>
   <si>
-    <t>General Budget Support</t>
-  </si>
-  <si>
     <t>52010</t>
   </si>
   <si>
     <t>Food assistance</t>
   </si>
   <si>
+    <t>Development Food Assistance</t>
+  </si>
+  <si>
     <t>520</t>
   </si>
   <si>
-    <t>Development Food Assistance</t>
-  </si>
-  <si>
     <t>53030</t>
   </si>
   <si>
     <t>Import support (capital goods)</t>
   </si>
   <si>
+    <t>Other Commodity Assistance</t>
+  </si>
+  <si>
     <t>530</t>
   </si>
   <si>
-    <t>Other Commodity Assistance</t>
-  </si>
-  <si>
     <t>53040</t>
   </si>
   <si>
@@ -1576,12 +1576,12 @@
     <t>Action relating to debt</t>
   </si>
   <si>
+    <t>Action Relating to Debt</t>
+  </si>
+  <si>
     <t>600</t>
   </si>
   <si>
-    <t>Action Relating to Debt</t>
-  </si>
-  <si>
     <t>60020</t>
   </si>
   <si>
@@ -1624,12 +1624,12 @@
     <t>Material relief assistance and services</t>
   </si>
   <si>
+    <t>Emergency Response</t>
+  </si>
+  <si>
     <t>720</t>
   </si>
   <si>
-    <t>Emergency Response</t>
-  </si>
-  <si>
     <t>72040</t>
   </si>
   <si>
@@ -1648,58 +1648,58 @@
     <t>Immediate post-emergency reconstruction and rehabilitation</t>
   </si>
   <si>
+    <t>Reconstruction Relief &amp; Rehabilitation</t>
+  </si>
+  <si>
     <t>730</t>
   </si>
   <si>
-    <t>Reconstruction Relief &amp; Rehabilitation</t>
-  </si>
-  <si>
     <t>74020</t>
   </si>
   <si>
     <t>Multi-hazard response preparedness</t>
   </si>
   <si>
+    <t>Disaster Prevention &amp; Preparedness</t>
+  </si>
+  <si>
     <t>740</t>
   </si>
   <si>
-    <t>Disaster Prevention &amp; Preparedness</t>
-  </si>
-  <si>
     <t>91010</t>
   </si>
   <si>
     <t>Administrative costs (non-sector allocable)</t>
   </si>
   <si>
+    <t>Administrative Costs of Donors</t>
+  </si>
+  <si>
     <t>910</t>
   </si>
   <si>
-    <t>Administrative Costs of Donors</t>
-  </si>
-  <si>
     <t>93010</t>
   </si>
   <si>
     <t>Refugees/asylum seekers in donor countries (non-sector allocable)</t>
   </si>
   <si>
+    <t>Refugees in Donor Countries</t>
+  </si>
+  <si>
     <t>930</t>
   </si>
   <si>
-    <t>Refugees in Donor Countries</t>
-  </si>
-  <si>
     <t>99810</t>
   </si>
   <si>
     <t>Sectors not specified</t>
   </si>
   <si>
+    <t>Unallocated / Unspecified</t>
+  </si>
+  <si>
     <t>998</t>
-  </si>
-  <si>
-    <t>Unallocated / Unspecified</t>
   </si>
   <si>
     <t>99820</t>
@@ -2767,13 +2767,13 @@
         <v>88</v>
       </c>
       <c r="E32" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F32" t="s">
         <v>89</v>
       </c>
       <c r="G32" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2790,13 +2790,13 @@
         <v>88</v>
       </c>
       <c r="E33" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F33" t="s">
         <v>89</v>
       </c>
       <c r="G33" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2813,13 +2813,13 @@
         <v>88</v>
       </c>
       <c r="E34" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F34" t="s">
         <v>89</v>
       </c>
       <c r="G34" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2836,13 +2836,13 @@
         <v>88</v>
       </c>
       <c r="E35" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F35" t="s">
         <v>89</v>
       </c>
       <c r="G35" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2859,13 +2859,13 @@
         <v>88</v>
       </c>
       <c r="E36" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F36" t="s">
         <v>89</v>
       </c>
       <c r="G36" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2882,13 +2882,13 @@
         <v>100</v>
       </c>
       <c r="E37" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F37" t="s">
         <v>101</v>
       </c>
       <c r="G37" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2905,13 +2905,13 @@
         <v>100</v>
       </c>
       <c r="E38" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F38" t="s">
         <v>101</v>
       </c>
       <c r="G38" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2928,13 +2928,13 @@
         <v>100</v>
       </c>
       <c r="E39" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F39" t="s">
         <v>101</v>
       </c>
       <c r="G39" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2951,13 +2951,13 @@
         <v>100</v>
       </c>
       <c r="E40" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F40" t="s">
         <v>101</v>
       </c>
       <c r="G40" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2974,13 +2974,13 @@
         <v>100</v>
       </c>
       <c r="E41" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F41" t="s">
         <v>101</v>
       </c>
       <c r="G41" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2997,13 +2997,13 @@
         <v>100</v>
       </c>
       <c r="E42" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F42" t="s">
         <v>101</v>
       </c>
       <c r="G42" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3020,13 +3020,13 @@
         <v>100</v>
       </c>
       <c r="E43" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F43" t="s">
         <v>101</v>
       </c>
       <c r="G43" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3043,13 +3043,13 @@
         <v>100</v>
       </c>
       <c r="E44" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F44" t="s">
         <v>101</v>
       </c>
       <c r="G44" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3066,13 +3066,13 @@
         <v>100</v>
       </c>
       <c r="E45" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F45" t="s">
         <v>101</v>
       </c>
       <c r="G45" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3089,13 +3089,13 @@
         <v>100</v>
       </c>
       <c r="E46" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F46" t="s">
         <v>101</v>
       </c>
       <c r="G46" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3112,13 +3112,13 @@
         <v>100</v>
       </c>
       <c r="E47" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F47" t="s">
         <v>101</v>
       </c>
       <c r="G47" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3641,13 +3641,13 @@
         <v>174</v>
       </c>
       <c r="E70" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F70" t="s">
         <v>175</v>
       </c>
       <c r="G70" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3664,13 +3664,13 @@
         <v>174</v>
       </c>
       <c r="E71" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F71" t="s">
         <v>175</v>
       </c>
       <c r="G71" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3687,13 +3687,13 @@
         <v>174</v>
       </c>
       <c r="E72" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F72" t="s">
         <v>175</v>
       </c>
       <c r="G72" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3710,13 +3710,13 @@
         <v>174</v>
       </c>
       <c r="E73" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F73" t="s">
         <v>175</v>
       </c>
       <c r="G73" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3733,13 +3733,13 @@
         <v>174</v>
       </c>
       <c r="E74" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F74" t="s">
         <v>175</v>
       </c>
       <c r="G74" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3756,13 +3756,13 @@
         <v>174</v>
       </c>
       <c r="E75" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F75" t="s">
         <v>175</v>
       </c>
       <c r="G75" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3779,13 +3779,13 @@
         <v>174</v>
       </c>
       <c r="E76" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F76" t="s">
         <v>175</v>
       </c>
       <c r="G76" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3802,13 +3802,13 @@
         <v>174</v>
       </c>
       <c r="E77" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F77" t="s">
         <v>175</v>
       </c>
       <c r="G77" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3825,13 +3825,13 @@
         <v>174</v>
       </c>
       <c r="E78" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F78" t="s">
         <v>175</v>
       </c>
       <c r="G78" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3848,13 +3848,13 @@
         <v>174</v>
       </c>
       <c r="E79" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F79" t="s">
         <v>175</v>
       </c>
       <c r="G79" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3871,13 +3871,13 @@
         <v>174</v>
       </c>
       <c r="E80" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F80" t="s">
         <v>175</v>
       </c>
       <c r="G80" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3894,13 +3894,13 @@
         <v>198</v>
       </c>
       <c r="E81" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F81" t="s">
         <v>199</v>
       </c>
       <c r="G81" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3917,13 +3917,13 @@
         <v>198</v>
       </c>
       <c r="E82" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F82" t="s">
         <v>199</v>
       </c>
       <c r="G82" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3940,13 +3940,13 @@
         <v>198</v>
       </c>
       <c r="E83" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F83" t="s">
         <v>199</v>
       </c>
       <c r="G83" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3963,13 +3963,13 @@
         <v>198</v>
       </c>
       <c r="E84" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F84" t="s">
         <v>199</v>
       </c>
       <c r="G84" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3986,13 +3986,13 @@
         <v>198</v>
       </c>
       <c r="E85" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F85" t="s">
         <v>199</v>
       </c>
       <c r="G85" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4009,13 +4009,13 @@
         <v>198</v>
       </c>
       <c r="E86" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F86" t="s">
         <v>199</v>
       </c>
       <c r="G86" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4032,13 +4032,13 @@
         <v>198</v>
       </c>
       <c r="E87" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F87" t="s">
         <v>199</v>
       </c>
       <c r="G87" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4055,13 +4055,13 @@
         <v>214</v>
       </c>
       <c r="E88" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F88" t="s">
         <v>215</v>
       </c>
       <c r="G88" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4078,13 +4078,13 @@
         <v>214</v>
       </c>
       <c r="E89" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F89" t="s">
         <v>215</v>
       </c>
       <c r="G89" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4101,13 +4101,13 @@
         <v>214</v>
       </c>
       <c r="E90" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F90" t="s">
         <v>215</v>
       </c>
       <c r="G90" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4124,13 +4124,13 @@
         <v>214</v>
       </c>
       <c r="E91" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F91" t="s">
         <v>215</v>
       </c>
       <c r="G91" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4791,13 +4791,13 @@
         <v>294</v>
       </c>
       <c r="E120" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F120" t="s">
         <v>295</v>
       </c>
       <c r="G120" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4814,13 +4814,13 @@
         <v>294</v>
       </c>
       <c r="E121" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F121" t="s">
         <v>295</v>
       </c>
       <c r="G121" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4837,13 +4837,13 @@
         <v>294</v>
       </c>
       <c r="E122" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F122" t="s">
         <v>295</v>
       </c>
       <c r="G122" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4860,13 +4860,13 @@
         <v>294</v>
       </c>
       <c r="E123" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F123" t="s">
         <v>295</v>
       </c>
       <c r="G123" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4883,13 +4883,13 @@
         <v>294</v>
       </c>
       <c r="E124" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F124" t="s">
         <v>295</v>
       </c>
       <c r="G124" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4906,13 +4906,13 @@
         <v>294</v>
       </c>
       <c r="E125" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F125" t="s">
         <v>295</v>
       </c>
       <c r="G125" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4929,13 +4929,13 @@
         <v>308</v>
       </c>
       <c r="E126" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F126" t="s">
         <v>309</v>
       </c>
       <c r="G126" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4952,13 +4952,13 @@
         <v>308</v>
       </c>
       <c r="E127" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F127" t="s">
         <v>309</v>
       </c>
       <c r="G127" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4975,13 +4975,13 @@
         <v>308</v>
       </c>
       <c r="E128" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F128" t="s">
         <v>309</v>
       </c>
       <c r="G128" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4998,13 +4998,13 @@
         <v>308</v>
       </c>
       <c r="E129" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F129" t="s">
         <v>309</v>
       </c>
       <c r="G129" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -6378,13 +6378,13 @@
         <v>452</v>
       </c>
       <c r="E189" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F189" t="s">
         <v>453</v>
       </c>
       <c r="G189" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6401,13 +6401,13 @@
         <v>452</v>
       </c>
       <c r="E190" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F190" t="s">
         <v>453</v>
       </c>
       <c r="G190" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6424,13 +6424,13 @@
         <v>452</v>
       </c>
       <c r="E191" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F191" t="s">
         <v>453</v>
       </c>
       <c r="G191" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6447,13 +6447,13 @@
         <v>452</v>
       </c>
       <c r="E192" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F192" t="s">
         <v>453</v>
       </c>
       <c r="G192" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6470,13 +6470,13 @@
         <v>452</v>
       </c>
       <c r="E193" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F193" t="s">
         <v>453</v>
       </c>
       <c r="G193" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6493,13 +6493,13 @@
         <v>452</v>
       </c>
       <c r="E194" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F194" t="s">
         <v>453</v>
       </c>
       <c r="G194" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6516,13 +6516,13 @@
         <v>466</v>
       </c>
       <c r="E195" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F195" t="s">
         <v>467</v>
       </c>
       <c r="G195" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6539,13 +6539,13 @@
         <v>470</v>
       </c>
       <c r="E196" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F196" t="s">
         <v>471</v>
       </c>
       <c r="G196" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6562,13 +6562,13 @@
         <v>470</v>
       </c>
       <c r="E197" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F197" t="s">
         <v>471</v>
       </c>
       <c r="G197" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6585,13 +6585,13 @@
         <v>470</v>
       </c>
       <c r="E198" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F198" t="s">
         <v>471</v>
       </c>
       <c r="G198" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6608,13 +6608,13 @@
         <v>470</v>
       </c>
       <c r="E199" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F199" t="s">
         <v>471</v>
       </c>
       <c r="G199" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6631,13 +6631,13 @@
         <v>470</v>
       </c>
       <c r="E200" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F200" t="s">
         <v>471</v>
       </c>
       <c r="G200" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6654,13 +6654,13 @@
         <v>470</v>
       </c>
       <c r="E201" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F201" t="s">
         <v>471</v>
       </c>
       <c r="G201" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6677,13 +6677,13 @@
         <v>484</v>
       </c>
       <c r="E202" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F202" t="s">
         <v>485</v>
       </c>
       <c r="G202" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6700,13 +6700,13 @@
         <v>484</v>
       </c>
       <c r="E203" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F203" t="s">
         <v>485</v>
       </c>
       <c r="G203" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6723,13 +6723,13 @@
         <v>484</v>
       </c>
       <c r="E204" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F204" t="s">
         <v>485</v>
       </c>
       <c r="G204" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6746,13 +6746,13 @@
         <v>484</v>
       </c>
       <c r="E205" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F205" t="s">
         <v>485</v>
       </c>
       <c r="G205" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6769,13 +6769,13 @@
         <v>484</v>
       </c>
       <c r="E206" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F206" t="s">
         <v>485</v>
       </c>
       <c r="G206" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6792,13 +6792,13 @@
         <v>484</v>
       </c>
       <c r="E207" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F207" t="s">
         <v>485</v>
       </c>
       <c r="G207" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6815,13 +6815,13 @@
         <v>484</v>
       </c>
       <c r="E208" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F208" t="s">
         <v>485</v>
       </c>
       <c r="G208" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6838,13 +6838,13 @@
         <v>484</v>
       </c>
       <c r="E209" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F209" t="s">
         <v>485</v>
       </c>
       <c r="G209" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6861,13 +6861,13 @@
         <v>484</v>
       </c>
       <c r="E210" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F210" t="s">
         <v>485</v>
       </c>
       <c r="G210" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6884,13 +6884,13 @@
         <v>484</v>
       </c>
       <c r="E211" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F211" t="s">
         <v>485</v>
       </c>
       <c r="G211" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6907,13 +6907,13 @@
         <v>506</v>
       </c>
       <c r="E212" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="F212" t="s">
         <v>507</v>
       </c>
       <c r="G212" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6930,13 +6930,13 @@
         <v>510</v>
       </c>
       <c r="E213" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F213" t="s">
         <v>511</v>
       </c>
       <c r="G213" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6953,13 +6953,13 @@
         <v>514</v>
       </c>
       <c r="E214" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F214" t="s">
         <v>515</v>
       </c>
       <c r="G214" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6976,13 +6976,13 @@
         <v>514</v>
       </c>
       <c r="E215" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F215" t="s">
         <v>515</v>
       </c>
       <c r="G215" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6999,13 +6999,13 @@
         <v>520</v>
       </c>
       <c r="E216" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F216" t="s">
         <v>521</v>
       </c>
       <c r="G216" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -7022,13 +7022,13 @@
         <v>520</v>
       </c>
       <c r="E217" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F217" t="s">
         <v>521</v>
       </c>
       <c r="G217" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -7045,13 +7045,13 @@
         <v>520</v>
       </c>
       <c r="E218" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F218" t="s">
         <v>521</v>
       </c>
       <c r="G218" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -7068,13 +7068,13 @@
         <v>520</v>
       </c>
       <c r="E219" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F219" t="s">
         <v>521</v>
       </c>
       <c r="G219" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -7091,13 +7091,13 @@
         <v>520</v>
       </c>
       <c r="E220" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F220" t="s">
         <v>521</v>
       </c>
       <c r="G220" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -7114,13 +7114,13 @@
         <v>520</v>
       </c>
       <c r="E221" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F221" t="s">
         <v>521</v>
       </c>
       <c r="G221" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -7137,13 +7137,13 @@
         <v>520</v>
       </c>
       <c r="E222" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F222" t="s">
         <v>521</v>
       </c>
       <c r="G222" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -7160,13 +7160,13 @@
         <v>536</v>
       </c>
       <c r="E223" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F223" t="s">
         <v>537</v>
       </c>
       <c r="G223" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -7183,13 +7183,13 @@
         <v>536</v>
       </c>
       <c r="E224" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F224" t="s">
         <v>537</v>
       </c>
       <c r="G224" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -7206,13 +7206,13 @@
         <v>536</v>
       </c>
       <c r="E225" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F225" t="s">
         <v>537</v>
       </c>
       <c r="G225" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -7229,13 +7229,13 @@
         <v>544</v>
       </c>
       <c r="E226" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F226" t="s">
         <v>545</v>
       </c>
       <c r="G226" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -7252,13 +7252,13 @@
         <v>548</v>
       </c>
       <c r="E227" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="F227" t="s">
         <v>549</v>
       </c>
       <c r="G227" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -7275,13 +7275,13 @@
         <v>552</v>
       </c>
       <c r="E228" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="F228" t="s">
         <v>553</v>
       </c>
       <c r="G228" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -7298,13 +7298,13 @@
         <v>556</v>
       </c>
       <c r="E229" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="F229" t="s">
         <v>557</v>
       </c>
       <c r="G229" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -7321,13 +7321,13 @@
         <v>560</v>
       </c>
       <c r="E230" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="F230" t="s">
         <v>561</v>
       </c>
       <c r="G230" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -7344,13 +7344,13 @@
         <v>560</v>
       </c>
       <c r="E231" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="F231" t="s">
         <v>561</v>
       </c>
       <c r="G231" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/en/SectorGroup.xlsx
+++ b/api/xlsx/en/SectorGroup.xlsx
@@ -25,18 +25,18 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:category-name</t>
+  </si>
+  <si>
     <t>codeforiati:group-name</t>
   </si>
   <si>
-    <t>codeforiati:category-name</t>
+    <t>codeforiati:category-code</t>
   </si>
   <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -46,18 +46,18 @@
     <t>active</t>
   </si>
   <si>
+    <t>Education, Level Unspecified</t>
+  </si>
+  <si>
     <t>Education</t>
   </si>
   <si>
-    <t>Education, Level Unspecified</t>
+    <t>111</t>
   </si>
   <si>
     <t>110</t>
   </si>
   <si>
-    <t>111</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -148,18 +148,18 @@
     <t>Health policy and administrative management</t>
   </si>
   <si>
+    <t>Health, General</t>
+  </si>
+  <si>
     <t>Health</t>
   </si>
   <si>
-    <t>Health, General</t>
+    <t>121</t>
   </si>
   <si>
     <t>120</t>
   </si>
   <si>
-    <t>121</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -388,18 +388,18 @@
     <t>Public sector policy and administrative management</t>
   </si>
   <si>
+    <t>Government &amp; Civil Society-general</t>
+  </si>
+  <si>
     <t>Government &amp; Civil Society</t>
   </si>
   <si>
-    <t>Government &amp; Civil Society-general</t>
+    <t>151</t>
   </si>
   <si>
     <t>150</t>
   </si>
   <si>
-    <t>151</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -688,18 +688,18 @@
     <t>Energy policy and administrative management</t>
   </si>
   <si>
+    <t>Energy Policy</t>
+  </si>
+  <si>
     <t>Energy</t>
   </si>
   <si>
-    <t>Energy Policy</t>
+    <t>231</t>
   </si>
   <si>
     <t>230</t>
   </si>
   <si>
-    <t>231</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -970,18 +970,18 @@
     <t>Agricultural policy and administrative management</t>
   </si>
   <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
     <t>Agriculture, Forestry, Fishing</t>
   </si>
   <si>
-    <t>Agriculture</t>
+    <t>311</t>
   </si>
   <si>
     <t>310</t>
   </si>
   <si>
-    <t>311</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1168,16 +1168,16 @@
     <t>Industrial policy and administrative management</t>
   </si>
   <si>
+    <t>Industry</t>
+  </si>
+  <si>
     <t>Industry, Mining, Construction</t>
   </si>
   <si>
-    <t>Industry</t>
+    <t>321</t>
   </si>
   <si>
     <t>320</t>
-  </si>
-  <si>
-    <t>321</t>
   </si>
   <si>
     <t>32120</t>
@@ -2166,16 +2166,16 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2189,16 +2189,16 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G7" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2212,16 +2212,16 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G8" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2235,16 +2235,16 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E9" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G9" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2258,16 +2258,16 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E10" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="G10" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2281,16 +2281,16 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="G11" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2304,16 +2304,16 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="G12" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2327,16 +2327,16 @@
         <v>9</v>
       </c>
       <c r="D13" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E13" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="G13" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2442,16 +2442,16 @@
         <v>9</v>
       </c>
       <c r="D18" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E18" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F18" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G18" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2465,16 +2465,16 @@
         <v>9</v>
       </c>
       <c r="D19" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E19" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F19" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G19" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2488,16 +2488,16 @@
         <v>9</v>
       </c>
       <c r="D20" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E20" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F20" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G20" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2511,16 +2511,16 @@
         <v>9</v>
       </c>
       <c r="D21" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E21" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F21" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G21" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2534,16 +2534,16 @@
         <v>9</v>
       </c>
       <c r="D22" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E22" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F22" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G22" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2557,16 +2557,16 @@
         <v>9</v>
       </c>
       <c r="D23" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E23" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F23" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G23" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2580,16 +2580,16 @@
         <v>9</v>
       </c>
       <c r="D24" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E24" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F24" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G24" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2603,16 +2603,16 @@
         <v>9</v>
       </c>
       <c r="D25" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E25" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F25" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G25" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2626,16 +2626,16 @@
         <v>9</v>
       </c>
       <c r="D26" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E26" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="F26" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G26" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2649,16 +2649,16 @@
         <v>9</v>
       </c>
       <c r="D27" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E27" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="F27" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G27" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2672,16 +2672,16 @@
         <v>9</v>
       </c>
       <c r="D28" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E28" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="F28" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G28" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2695,16 +2695,16 @@
         <v>9</v>
       </c>
       <c r="D29" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E29" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="F29" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G29" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2718,16 +2718,16 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E30" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="F30" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G30" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2741,16 +2741,16 @@
         <v>9</v>
       </c>
       <c r="D31" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E31" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="F31" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G31" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -3500,16 +3500,16 @@
         <v>9</v>
       </c>
       <c r="D64" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E64" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="F64" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G64" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3523,16 +3523,16 @@
         <v>9</v>
       </c>
       <c r="D65" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E65" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="F65" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G65" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3546,16 +3546,16 @@
         <v>9</v>
       </c>
       <c r="D66" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E66" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="F66" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G66" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3569,16 +3569,16 @@
         <v>9</v>
       </c>
       <c r="D67" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E67" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="F67" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G67" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3592,16 +3592,16 @@
         <v>9</v>
       </c>
       <c r="D68" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E68" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="F68" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G68" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3615,16 +3615,16 @@
         <v>9</v>
       </c>
       <c r="D69" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E69" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="F69" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G69" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -4236,16 +4236,16 @@
         <v>9</v>
       </c>
       <c r="D96" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E96" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F96" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G96" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -4259,16 +4259,16 @@
         <v>9</v>
       </c>
       <c r="D97" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E97" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F97" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G97" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4282,16 +4282,16 @@
         <v>9</v>
       </c>
       <c r="D98" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E98" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F98" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G98" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4305,16 +4305,16 @@
         <v>9</v>
       </c>
       <c r="D99" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E99" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F99" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G99" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4328,16 +4328,16 @@
         <v>9</v>
       </c>
       <c r="D100" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E100" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F100" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G100" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4351,16 +4351,16 @@
         <v>9</v>
       </c>
       <c r="D101" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E101" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F101" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G101" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4374,16 +4374,16 @@
         <v>9</v>
       </c>
       <c r="D102" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E102" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F102" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G102" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4397,16 +4397,16 @@
         <v>9</v>
       </c>
       <c r="D103" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E103" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F103" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G103" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4420,16 +4420,16 @@
         <v>9</v>
       </c>
       <c r="D104" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E104" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F104" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G104" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4443,16 +4443,16 @@
         <v>9</v>
       </c>
       <c r="D105" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E105" t="s">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="F105" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G105" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4466,16 +4466,16 @@
         <v>9</v>
       </c>
       <c r="D106" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E106" t="s">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="F106" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G106" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4489,16 +4489,16 @@
         <v>9</v>
       </c>
       <c r="D107" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E107" t="s">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="F107" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G107" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4512,16 +4512,16 @@
         <v>9</v>
       </c>
       <c r="D108" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E108" t="s">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="F108" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G108" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4535,16 +4535,16 @@
         <v>9</v>
       </c>
       <c r="D109" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E109" t="s">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="F109" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G109" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4558,16 +4558,16 @@
         <v>9</v>
       </c>
       <c r="D110" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E110" t="s">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="F110" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G110" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4581,16 +4581,16 @@
         <v>9</v>
       </c>
       <c r="D111" t="s">
-        <v>224</v>
+        <v>270</v>
       </c>
       <c r="E111" t="s">
-        <v>270</v>
+        <v>225</v>
       </c>
       <c r="F111" t="s">
-        <v>226</v>
+        <v>271</v>
       </c>
       <c r="G111" t="s">
-        <v>271</v>
+        <v>227</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4604,16 +4604,16 @@
         <v>9</v>
       </c>
       <c r="D112" t="s">
-        <v>224</v>
+        <v>274</v>
       </c>
       <c r="E112" t="s">
-        <v>274</v>
+        <v>225</v>
       </c>
       <c r="F112" t="s">
-        <v>226</v>
+        <v>275</v>
       </c>
       <c r="G112" t="s">
-        <v>275</v>
+        <v>227</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4627,16 +4627,16 @@
         <v>9</v>
       </c>
       <c r="D113" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E113" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="F113" t="s">
-        <v>226</v>
+        <v>279</v>
       </c>
       <c r="G113" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4650,16 +4650,16 @@
         <v>9</v>
       </c>
       <c r="D114" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E114" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="F114" t="s">
-        <v>226</v>
+        <v>279</v>
       </c>
       <c r="G114" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4673,16 +4673,16 @@
         <v>9</v>
       </c>
       <c r="D115" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E115" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="F115" t="s">
-        <v>226</v>
+        <v>279</v>
       </c>
       <c r="G115" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4696,16 +4696,16 @@
         <v>9</v>
       </c>
       <c r="D116" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E116" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="F116" t="s">
-        <v>226</v>
+        <v>279</v>
       </c>
       <c r="G116" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4719,16 +4719,16 @@
         <v>9</v>
       </c>
       <c r="D117" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E117" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="F117" t="s">
-        <v>226</v>
+        <v>279</v>
       </c>
       <c r="G117" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4742,16 +4742,16 @@
         <v>9</v>
       </c>
       <c r="D118" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E118" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="F118" t="s">
-        <v>226</v>
+        <v>279</v>
       </c>
       <c r="G118" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4765,16 +4765,16 @@
         <v>9</v>
       </c>
       <c r="D119" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E119" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="F119" t="s">
-        <v>226</v>
+        <v>279</v>
       </c>
       <c r="G119" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -5432,16 +5432,16 @@
         <v>9</v>
       </c>
       <c r="D148" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E148" t="s">
-        <v>358</v>
+        <v>319</v>
       </c>
       <c r="F148" t="s">
-        <v>320</v>
+        <v>359</v>
       </c>
       <c r="G148" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5455,16 +5455,16 @@
         <v>9</v>
       </c>
       <c r="D149" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E149" t="s">
-        <v>358</v>
+        <v>319</v>
       </c>
       <c r="F149" t="s">
-        <v>320</v>
+        <v>359</v>
       </c>
       <c r="G149" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5478,16 +5478,16 @@
         <v>9</v>
       </c>
       <c r="D150" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E150" t="s">
-        <v>358</v>
+        <v>319</v>
       </c>
       <c r="F150" t="s">
-        <v>320</v>
+        <v>359</v>
       </c>
       <c r="G150" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5501,16 +5501,16 @@
         <v>9</v>
       </c>
       <c r="D151" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E151" t="s">
-        <v>358</v>
+        <v>319</v>
       </c>
       <c r="F151" t="s">
-        <v>320</v>
+        <v>359</v>
       </c>
       <c r="G151" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5524,16 +5524,16 @@
         <v>9</v>
       </c>
       <c r="D152" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E152" t="s">
-        <v>358</v>
+        <v>319</v>
       </c>
       <c r="F152" t="s">
-        <v>320</v>
+        <v>359</v>
       </c>
       <c r="G152" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5547,16 +5547,16 @@
         <v>9</v>
       </c>
       <c r="D153" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E153" t="s">
-        <v>358</v>
+        <v>319</v>
       </c>
       <c r="F153" t="s">
-        <v>320</v>
+        <v>359</v>
       </c>
       <c r="G153" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5570,16 +5570,16 @@
         <v>9</v>
       </c>
       <c r="D154" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="E154" t="s">
-        <v>372</v>
+        <v>319</v>
       </c>
       <c r="F154" t="s">
-        <v>320</v>
+        <v>373</v>
       </c>
       <c r="G154" t="s">
-        <v>373</v>
+        <v>321</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5593,16 +5593,16 @@
         <v>9</v>
       </c>
       <c r="D155" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="E155" t="s">
-        <v>372</v>
+        <v>319</v>
       </c>
       <c r="F155" t="s">
-        <v>320</v>
+        <v>373</v>
       </c>
       <c r="G155" t="s">
-        <v>373</v>
+        <v>321</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5616,16 +5616,16 @@
         <v>9</v>
       </c>
       <c r="D156" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="E156" t="s">
-        <v>372</v>
+        <v>319</v>
       </c>
       <c r="F156" t="s">
-        <v>320</v>
+        <v>373</v>
       </c>
       <c r="G156" t="s">
-        <v>373</v>
+        <v>321</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5639,16 +5639,16 @@
         <v>9</v>
       </c>
       <c r="D157" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="E157" t="s">
-        <v>372</v>
+        <v>319</v>
       </c>
       <c r="F157" t="s">
-        <v>320</v>
+        <v>373</v>
       </c>
       <c r="G157" t="s">
-        <v>373</v>
+        <v>321</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5662,16 +5662,16 @@
         <v>9</v>
       </c>
       <c r="D158" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="E158" t="s">
-        <v>372</v>
+        <v>319</v>
       </c>
       <c r="F158" t="s">
-        <v>320</v>
+        <v>373</v>
       </c>
       <c r="G158" t="s">
-        <v>373</v>
+        <v>321</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -6122,16 +6122,16 @@
         <v>9</v>
       </c>
       <c r="D178" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E178" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="F178" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G178" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -6145,16 +6145,16 @@
         <v>9</v>
       </c>
       <c r="D179" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E179" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="F179" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G179" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -6168,16 +6168,16 @@
         <v>9</v>
       </c>
       <c r="D180" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E180" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="F180" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G180" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -6191,16 +6191,16 @@
         <v>9</v>
       </c>
       <c r="D181" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E181" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="F181" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G181" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -6214,16 +6214,16 @@
         <v>9</v>
       </c>
       <c r="D182" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E182" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="F182" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G182" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -6237,16 +6237,16 @@
         <v>9</v>
       </c>
       <c r="D183" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E183" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="F183" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G183" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -6260,16 +6260,16 @@
         <v>9</v>
       </c>
       <c r="D184" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E184" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="F184" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G184" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -6283,16 +6283,16 @@
         <v>9</v>
       </c>
       <c r="D185" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E185" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="F185" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G185" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -6306,16 +6306,16 @@
         <v>9</v>
       </c>
       <c r="D186" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E186" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="F186" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G186" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -6329,16 +6329,16 @@
         <v>9</v>
       </c>
       <c r="D187" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E187" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="F187" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="G187" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -6352,16 +6352,16 @@
         <v>9</v>
       </c>
       <c r="D188" t="s">
-        <v>384</v>
+        <v>448</v>
       </c>
       <c r="E188" t="s">
-        <v>448</v>
+        <v>385</v>
       </c>
       <c r="F188" t="s">
-        <v>386</v>
+        <v>449</v>
       </c>
       <c r="G188" t="s">
-        <v>449</v>
+        <v>387</v>
       </c>
     </row>
     <row r="189" spans="1:7">

--- a/api/xlsx/en/SectorGroup.xlsx
+++ b/api/xlsx/en/SectorGroup.xlsx
@@ -25,18 +25,18 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
     <t>codeforiati:category-name</t>
   </si>
   <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -46,18 +46,18 @@
     <t>active</t>
   </si>
   <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
     <t>Education, Level Unspecified</t>
   </si>
   <si>
-    <t>Education</t>
-  </si>
-  <si>
     <t>111</t>
   </si>
   <si>
-    <t>110</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -148,18 +148,18 @@
     <t>Health policy and administrative management</t>
   </si>
   <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>Health</t>
+  </si>
+  <si>
     <t>Health, General</t>
   </si>
   <si>
-    <t>Health</t>
-  </si>
-  <si>
     <t>121</t>
   </si>
   <si>
-    <t>120</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -280,12 +280,12 @@
     <t>Population policy and administrative management</t>
   </si>
   <si>
+    <t>130</t>
+  </si>
+  <si>
     <t>Population Policies/Programmes &amp; Reproductive Health</t>
   </si>
   <si>
-    <t>130</t>
-  </si>
-  <si>
     <t>13020</t>
   </si>
   <si>
@@ -316,12 +316,12 @@
     <t>Water sector policy and administrative management</t>
   </si>
   <si>
+    <t>140</t>
+  </si>
+  <si>
     <t>Water Supply &amp; Sanitation</t>
   </si>
   <si>
-    <t>140</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -388,18 +388,18 @@
     <t>Public sector policy and administrative management</t>
   </si>
   <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>Government &amp; Civil Society</t>
+  </si>
+  <si>
     <t>Government &amp; Civil Society-general</t>
   </si>
   <si>
-    <t>Government &amp; Civil Society</t>
-  </si>
-  <si>
     <t>151</t>
   </si>
   <si>
-    <t>150</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -538,12 +538,12 @@
     <t>Social Protection</t>
   </si>
   <si>
+    <t>160</t>
+  </si>
+  <si>
     <t>Other Social Infrastructure &amp; Services</t>
   </si>
   <si>
-    <t>160</t>
-  </si>
-  <si>
     <t>16020</t>
   </si>
   <si>
@@ -610,12 +610,12 @@
     <t>Transport policy and administrative management</t>
   </si>
   <si>
+    <t>210</t>
+  </si>
+  <si>
     <t>Transport &amp; Storage</t>
   </si>
   <si>
-    <t>210</t>
-  </si>
-  <si>
     <t>21020</t>
   </si>
   <si>
@@ -658,12 +658,12 @@
     <t>Communications policy and administrative management</t>
   </si>
   <si>
+    <t>220</t>
+  </si>
+  <si>
     <t>Communications</t>
   </si>
   <si>
-    <t>220</t>
-  </si>
-  <si>
     <t>22020</t>
   </si>
   <si>
@@ -688,18 +688,18 @@
     <t>Energy policy and administrative management</t>
   </si>
   <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>Energy</t>
+  </si>
+  <si>
     <t>Energy Policy</t>
   </si>
   <si>
-    <t>Energy</t>
-  </si>
-  <si>
     <t>231</t>
   </si>
   <si>
-    <t>230</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -898,12 +898,12 @@
     <t>Financial policy and administrative management</t>
   </si>
   <si>
+    <t>240</t>
+  </si>
+  <si>
     <t>Banking &amp; Financial Services</t>
   </si>
   <si>
-    <t>240</t>
-  </si>
-  <si>
     <t>24020</t>
   </si>
   <si>
@@ -940,12 +940,12 @@
     <t>Business policy and administration</t>
   </si>
   <si>
+    <t>250</t>
+  </si>
+  <si>
     <t>Business &amp; Other Services</t>
   </si>
   <si>
-    <t>250</t>
-  </si>
-  <si>
     <t>25020</t>
   </si>
   <si>
@@ -970,18 +970,18 @@
     <t>Agricultural policy and administrative management</t>
   </si>
   <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>Agriculture, Forestry, Fishing</t>
+  </si>
+  <si>
     <t>Agriculture</t>
   </si>
   <si>
-    <t>Agriculture, Forestry, Fishing</t>
-  </si>
-  <si>
     <t>311</t>
   </si>
   <si>
-    <t>310</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1168,18 +1168,18 @@
     <t>Industrial policy and administrative management</t>
   </si>
   <si>
+    <t>320</t>
+  </si>
+  <si>
+    <t>Industry, Mining, Construction</t>
+  </si>
+  <si>
     <t>Industry</t>
   </si>
   <si>
-    <t>Industry, Mining, Construction</t>
-  </si>
-  <si>
     <t>321</t>
   </si>
   <si>
-    <t>320</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1372,12 +1372,12 @@
     <t>Trade policy and administrative management</t>
   </si>
   <si>
+    <t>331</t>
+  </si>
+  <si>
     <t>Trade Policies &amp; Regulations</t>
   </si>
   <si>
-    <t>331</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1414,24 +1414,24 @@
     <t>Tourism policy and administrative management</t>
   </si>
   <si>
+    <t>332</t>
+  </si>
+  <si>
     <t>Tourism</t>
   </si>
   <si>
-    <t>332</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
     <t>Environmental policy and administrative management</t>
   </si>
   <si>
+    <t>410</t>
+  </si>
+  <si>
     <t>General Environment Protection</t>
   </si>
   <si>
-    <t>410</t>
-  </si>
-  <si>
     <t>41020</t>
   </si>
   <si>
@@ -1468,12 +1468,12 @@
     <t>Multisector aid</t>
   </si>
   <si>
+    <t>430</t>
+  </si>
+  <si>
     <t>Other Multisector</t>
   </si>
   <si>
-    <t>430</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -1534,36 +1534,36 @@
     <t>General budget support-related aid</t>
   </si>
   <si>
+    <t>510</t>
+  </si>
+  <si>
     <t>General Budget Support</t>
   </si>
   <si>
-    <t>510</t>
-  </si>
-  <si>
     <t>52010</t>
   </si>
   <si>
     <t>Food assistance</t>
   </si>
   <si>
+    <t>520</t>
+  </si>
+  <si>
     <t>Development Food Assistance</t>
   </si>
   <si>
-    <t>520</t>
-  </si>
-  <si>
     <t>53030</t>
   </si>
   <si>
     <t>Import support (capital goods)</t>
   </si>
   <si>
+    <t>530</t>
+  </si>
+  <si>
     <t>Other Commodity Assistance</t>
   </si>
   <si>
-    <t>530</t>
-  </si>
-  <si>
     <t>53040</t>
   </si>
   <si>
@@ -1576,12 +1576,12 @@
     <t>Action relating to debt</t>
   </si>
   <si>
+    <t>600</t>
+  </si>
+  <si>
     <t>Action Relating to Debt</t>
   </si>
   <si>
-    <t>600</t>
-  </si>
-  <si>
     <t>60020</t>
   </si>
   <si>
@@ -1624,12 +1624,12 @@
     <t>Material relief assistance and services</t>
   </si>
   <si>
+    <t>720</t>
+  </si>
+  <si>
     <t>Emergency Response</t>
   </si>
   <si>
-    <t>720</t>
-  </si>
-  <si>
     <t>72040</t>
   </si>
   <si>
@@ -1648,58 +1648,58 @@
     <t>Immediate post-emergency reconstruction and rehabilitation</t>
   </si>
   <si>
+    <t>730</t>
+  </si>
+  <si>
     <t>Reconstruction Relief &amp; Rehabilitation</t>
   </si>
   <si>
-    <t>730</t>
-  </si>
-  <si>
     <t>74020</t>
   </si>
   <si>
     <t>Multi-hazard response preparedness</t>
   </si>
   <si>
+    <t>740</t>
+  </si>
+  <si>
     <t>Disaster Prevention &amp; Preparedness</t>
   </si>
   <si>
-    <t>740</t>
-  </si>
-  <si>
     <t>91010</t>
   </si>
   <si>
     <t>Administrative costs (non-sector allocable)</t>
   </si>
   <si>
+    <t>910</t>
+  </si>
+  <si>
     <t>Administrative Costs of Donors</t>
   </si>
   <si>
-    <t>910</t>
-  </si>
-  <si>
     <t>93010</t>
   </si>
   <si>
     <t>Refugees/asylum seekers in donor countries (non-sector allocable)</t>
   </si>
   <si>
+    <t>930</t>
+  </si>
+  <si>
     <t>Refugees in Donor Countries</t>
   </si>
   <si>
-    <t>930</t>
-  </si>
-  <si>
     <t>99810</t>
   </si>
   <si>
     <t>Sectors not specified</t>
   </si>
   <si>
+    <t>998</t>
+  </si>
+  <si>
     <t>Unallocated / Unspecified</t>
-  </si>
-  <si>
-    <t>998</t>
   </si>
   <si>
     <t>99820</t>
@@ -2166,16 +2166,16 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E6" t="s">
         <v>11</v>
       </c>
       <c r="F6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" t="s">
         <v>23</v>
-      </c>
-      <c r="G6" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2189,16 +2189,16 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
       </c>
       <c r="F7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" t="s">
         <v>23</v>
-      </c>
-      <c r="G7" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2212,16 +2212,16 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E8" t="s">
         <v>11</v>
       </c>
       <c r="F8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" t="s">
         <v>23</v>
-      </c>
-      <c r="G8" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2235,16 +2235,16 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
       </c>
       <c r="F9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" t="s">
         <v>23</v>
-      </c>
-      <c r="G9" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2258,16 +2258,16 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="E10" t="s">
         <v>11</v>
       </c>
       <c r="F10" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" t="s">
         <v>33</v>
-      </c>
-      <c r="G10" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2281,16 +2281,16 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="E11" t="s">
         <v>11</v>
       </c>
       <c r="F11" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" t="s">
         <v>33</v>
-      </c>
-      <c r="G11" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2304,16 +2304,16 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="E12" t="s">
         <v>11</v>
       </c>
       <c r="F12" t="s">
+        <v>38</v>
+      </c>
+      <c r="G12" t="s">
         <v>39</v>
-      </c>
-      <c r="G12" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2327,16 +2327,16 @@
         <v>9</v>
       </c>
       <c r="D13" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="E13" t="s">
         <v>11</v>
       </c>
       <c r="F13" t="s">
+        <v>38</v>
+      </c>
+      <c r="G13" t="s">
         <v>39</v>
-      </c>
-      <c r="G13" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2442,16 +2442,16 @@
         <v>9</v>
       </c>
       <c r="D18" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E18" t="s">
         <v>45</v>
       </c>
       <c r="F18" t="s">
+        <v>56</v>
+      </c>
+      <c r="G18" t="s">
         <v>57</v>
-      </c>
-      <c r="G18" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2465,16 +2465,16 @@
         <v>9</v>
       </c>
       <c r="D19" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E19" t="s">
         <v>45</v>
       </c>
       <c r="F19" t="s">
+        <v>56</v>
+      </c>
+      <c r="G19" t="s">
         <v>57</v>
-      </c>
-      <c r="G19" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2488,16 +2488,16 @@
         <v>9</v>
       </c>
       <c r="D20" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E20" t="s">
         <v>45</v>
       </c>
       <c r="F20" t="s">
+        <v>56</v>
+      </c>
+      <c r="G20" t="s">
         <v>57</v>
-      </c>
-      <c r="G20" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2511,16 +2511,16 @@
         <v>9</v>
       </c>
       <c r="D21" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E21" t="s">
         <v>45</v>
       </c>
       <c r="F21" t="s">
+        <v>56</v>
+      </c>
+      <c r="G21" t="s">
         <v>57</v>
-      </c>
-      <c r="G21" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2534,16 +2534,16 @@
         <v>9</v>
       </c>
       <c r="D22" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E22" t="s">
         <v>45</v>
       </c>
       <c r="F22" t="s">
+        <v>56</v>
+      </c>
+      <c r="G22" t="s">
         <v>57</v>
-      </c>
-      <c r="G22" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2557,16 +2557,16 @@
         <v>9</v>
       </c>
       <c r="D23" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E23" t="s">
         <v>45</v>
       </c>
       <c r="F23" t="s">
+        <v>56</v>
+      </c>
+      <c r="G23" t="s">
         <v>57</v>
-      </c>
-      <c r="G23" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2580,16 +2580,16 @@
         <v>9</v>
       </c>
       <c r="D24" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E24" t="s">
         <v>45</v>
       </c>
       <c r="F24" t="s">
+        <v>56</v>
+      </c>
+      <c r="G24" t="s">
         <v>57</v>
-      </c>
-      <c r="G24" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2603,16 +2603,16 @@
         <v>9</v>
       </c>
       <c r="D25" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E25" t="s">
         <v>45</v>
       </c>
       <c r="F25" t="s">
+        <v>56</v>
+      </c>
+      <c r="G25" t="s">
         <v>57</v>
-      </c>
-      <c r="G25" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2626,16 +2626,16 @@
         <v>9</v>
       </c>
       <c r="D26" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="E26" t="s">
         <v>45</v>
       </c>
       <c r="F26" t="s">
+        <v>74</v>
+      </c>
+      <c r="G26" t="s">
         <v>75</v>
-      </c>
-      <c r="G26" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2649,16 +2649,16 @@
         <v>9</v>
       </c>
       <c r="D27" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="E27" t="s">
         <v>45</v>
       </c>
       <c r="F27" t="s">
+        <v>74</v>
+      </c>
+      <c r="G27" t="s">
         <v>75</v>
-      </c>
-      <c r="G27" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2672,16 +2672,16 @@
         <v>9</v>
       </c>
       <c r="D28" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="E28" t="s">
         <v>45</v>
       </c>
       <c r="F28" t="s">
+        <v>74</v>
+      </c>
+      <c r="G28" t="s">
         <v>75</v>
-      </c>
-      <c r="G28" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2695,16 +2695,16 @@
         <v>9</v>
       </c>
       <c r="D29" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="E29" t="s">
         <v>45</v>
       </c>
       <c r="F29" t="s">
+        <v>74</v>
+      </c>
+      <c r="G29" t="s">
         <v>75</v>
-      </c>
-      <c r="G29" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2718,16 +2718,16 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="E30" t="s">
         <v>45</v>
       </c>
       <c r="F30" t="s">
+        <v>74</v>
+      </c>
+      <c r="G30" t="s">
         <v>75</v>
-      </c>
-      <c r="G30" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2741,16 +2741,16 @@
         <v>9</v>
       </c>
       <c r="D31" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="E31" t="s">
         <v>45</v>
       </c>
       <c r="F31" t="s">
+        <v>74</v>
+      </c>
+      <c r="G31" t="s">
         <v>75</v>
-      </c>
-      <c r="G31" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2767,13 +2767,13 @@
         <v>88</v>
       </c>
       <c r="E32" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F32" t="s">
         <v>89</v>
       </c>
       <c r="G32" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2790,13 +2790,13 @@
         <v>88</v>
       </c>
       <c r="E33" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F33" t="s">
         <v>89</v>
       </c>
       <c r="G33" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2813,13 +2813,13 @@
         <v>88</v>
       </c>
       <c r="E34" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F34" t="s">
         <v>89</v>
       </c>
       <c r="G34" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2836,13 +2836,13 @@
         <v>88</v>
       </c>
       <c r="E35" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F35" t="s">
         <v>89</v>
       </c>
       <c r="G35" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2859,13 +2859,13 @@
         <v>88</v>
       </c>
       <c r="E36" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F36" t="s">
         <v>89</v>
       </c>
       <c r="G36" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2882,13 +2882,13 @@
         <v>100</v>
       </c>
       <c r="E37" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F37" t="s">
         <v>101</v>
       </c>
       <c r="G37" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2905,13 +2905,13 @@
         <v>100</v>
       </c>
       <c r="E38" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F38" t="s">
         <v>101</v>
       </c>
       <c r="G38" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2928,13 +2928,13 @@
         <v>100</v>
       </c>
       <c r="E39" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F39" t="s">
         <v>101</v>
       </c>
       <c r="G39" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2951,13 +2951,13 @@
         <v>100</v>
       </c>
       <c r="E40" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F40" t="s">
         <v>101</v>
       </c>
       <c r="G40" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2974,13 +2974,13 @@
         <v>100</v>
       </c>
       <c r="E41" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F41" t="s">
         <v>101</v>
       </c>
       <c r="G41" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2997,13 +2997,13 @@
         <v>100</v>
       </c>
       <c r="E42" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F42" t="s">
         <v>101</v>
       </c>
       <c r="G42" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3020,13 +3020,13 @@
         <v>100</v>
       </c>
       <c r="E43" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F43" t="s">
         <v>101</v>
       </c>
       <c r="G43" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3043,13 +3043,13 @@
         <v>100</v>
       </c>
       <c r="E44" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F44" t="s">
         <v>101</v>
       </c>
       <c r="G44" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3066,13 +3066,13 @@
         <v>100</v>
       </c>
       <c r="E45" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F45" t="s">
         <v>101</v>
       </c>
       <c r="G45" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3089,13 +3089,13 @@
         <v>100</v>
       </c>
       <c r="E46" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F46" t="s">
         <v>101</v>
       </c>
       <c r="G46" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3112,13 +3112,13 @@
         <v>100</v>
       </c>
       <c r="E47" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F47" t="s">
         <v>101</v>
       </c>
       <c r="G47" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3500,16 +3500,16 @@
         <v>9</v>
       </c>
       <c r="D64" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="E64" t="s">
         <v>125</v>
       </c>
       <c r="F64" t="s">
+        <v>160</v>
+      </c>
+      <c r="G64" t="s">
         <v>161</v>
-      </c>
-      <c r="G64" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3523,16 +3523,16 @@
         <v>9</v>
       </c>
       <c r="D65" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="E65" t="s">
         <v>125</v>
       </c>
       <c r="F65" t="s">
+        <v>160</v>
+      </c>
+      <c r="G65" t="s">
         <v>161</v>
-      </c>
-      <c r="G65" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3546,16 +3546,16 @@
         <v>9</v>
       </c>
       <c r="D66" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="E66" t="s">
         <v>125</v>
       </c>
       <c r="F66" t="s">
+        <v>160</v>
+      </c>
+      <c r="G66" t="s">
         <v>161</v>
-      </c>
-      <c r="G66" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3569,16 +3569,16 @@
         <v>9</v>
       </c>
       <c r="D67" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="E67" t="s">
         <v>125</v>
       </c>
       <c r="F67" t="s">
+        <v>160</v>
+      </c>
+      <c r="G67" t="s">
         <v>161</v>
-      </c>
-      <c r="G67" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3592,16 +3592,16 @@
         <v>9</v>
       </c>
       <c r="D68" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="E68" t="s">
         <v>125</v>
       </c>
       <c r="F68" t="s">
+        <v>160</v>
+      </c>
+      <c r="G68" t="s">
         <v>161</v>
-      </c>
-      <c r="G68" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3615,16 +3615,16 @@
         <v>9</v>
       </c>
       <c r="D69" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="E69" t="s">
         <v>125</v>
       </c>
       <c r="F69" t="s">
+        <v>160</v>
+      </c>
+      <c r="G69" t="s">
         <v>161</v>
-      </c>
-      <c r="G69" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3641,13 +3641,13 @@
         <v>174</v>
       </c>
       <c r="E70" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F70" t="s">
         <v>175</v>
       </c>
       <c r="G70" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3664,13 +3664,13 @@
         <v>174</v>
       </c>
       <c r="E71" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F71" t="s">
         <v>175</v>
       </c>
       <c r="G71" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3687,13 +3687,13 @@
         <v>174</v>
       </c>
       <c r="E72" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F72" t="s">
         <v>175</v>
       </c>
       <c r="G72" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3710,13 +3710,13 @@
         <v>174</v>
       </c>
       <c r="E73" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F73" t="s">
         <v>175</v>
       </c>
       <c r="G73" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3733,13 +3733,13 @@
         <v>174</v>
       </c>
       <c r="E74" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F74" t="s">
         <v>175</v>
       </c>
       <c r="G74" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3756,13 +3756,13 @@
         <v>174</v>
       </c>
       <c r="E75" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F75" t="s">
         <v>175</v>
       </c>
       <c r="G75" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3779,13 +3779,13 @@
         <v>174</v>
       </c>
       <c r="E76" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F76" t="s">
         <v>175</v>
       </c>
       <c r="G76" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3802,13 +3802,13 @@
         <v>174</v>
       </c>
       <c r="E77" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F77" t="s">
         <v>175</v>
       </c>
       <c r="G77" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3825,13 +3825,13 @@
         <v>174</v>
       </c>
       <c r="E78" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F78" t="s">
         <v>175</v>
       </c>
       <c r="G78" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3848,13 +3848,13 @@
         <v>174</v>
       </c>
       <c r="E79" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F79" t="s">
         <v>175</v>
       </c>
       <c r="G79" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3871,13 +3871,13 @@
         <v>174</v>
       </c>
       <c r="E80" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F80" t="s">
         <v>175</v>
       </c>
       <c r="G80" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3894,13 +3894,13 @@
         <v>198</v>
       </c>
       <c r="E81" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F81" t="s">
         <v>199</v>
       </c>
       <c r="G81" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3917,13 +3917,13 @@
         <v>198</v>
       </c>
       <c r="E82" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F82" t="s">
         <v>199</v>
       </c>
       <c r="G82" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3940,13 +3940,13 @@
         <v>198</v>
       </c>
       <c r="E83" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F83" t="s">
         <v>199</v>
       </c>
       <c r="G83" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3963,13 +3963,13 @@
         <v>198</v>
       </c>
       <c r="E84" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F84" t="s">
         <v>199</v>
       </c>
       <c r="G84" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3986,13 +3986,13 @@
         <v>198</v>
       </c>
       <c r="E85" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F85" t="s">
         <v>199</v>
       </c>
       <c r="G85" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4009,13 +4009,13 @@
         <v>198</v>
       </c>
       <c r="E86" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F86" t="s">
         <v>199</v>
       </c>
       <c r="G86" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4032,13 +4032,13 @@
         <v>198</v>
       </c>
       <c r="E87" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F87" t="s">
         <v>199</v>
       </c>
       <c r="G87" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4055,13 +4055,13 @@
         <v>214</v>
       </c>
       <c r="E88" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F88" t="s">
         <v>215</v>
       </c>
       <c r="G88" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4078,13 +4078,13 @@
         <v>214</v>
       </c>
       <c r="E89" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F89" t="s">
         <v>215</v>
       </c>
       <c r="G89" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4101,13 +4101,13 @@
         <v>214</v>
       </c>
       <c r="E90" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F90" t="s">
         <v>215</v>
       </c>
       <c r="G90" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4124,13 +4124,13 @@
         <v>214</v>
       </c>
       <c r="E91" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F91" t="s">
         <v>215</v>
       </c>
       <c r="G91" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4236,16 +4236,16 @@
         <v>9</v>
       </c>
       <c r="D96" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E96" t="s">
         <v>225</v>
       </c>
       <c r="F96" t="s">
+        <v>236</v>
+      </c>
+      <c r="G96" t="s">
         <v>237</v>
-      </c>
-      <c r="G96" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -4259,16 +4259,16 @@
         <v>9</v>
       </c>
       <c r="D97" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E97" t="s">
         <v>225</v>
       </c>
       <c r="F97" t="s">
+        <v>236</v>
+      </c>
+      <c r="G97" t="s">
         <v>237</v>
-      </c>
-      <c r="G97" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4282,16 +4282,16 @@
         <v>9</v>
       </c>
       <c r="D98" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E98" t="s">
         <v>225</v>
       </c>
       <c r="F98" t="s">
+        <v>236</v>
+      </c>
+      <c r="G98" t="s">
         <v>237</v>
-      </c>
-      <c r="G98" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4305,16 +4305,16 @@
         <v>9</v>
       </c>
       <c r="D99" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E99" t="s">
         <v>225</v>
       </c>
       <c r="F99" t="s">
+        <v>236</v>
+      </c>
+      <c r="G99" t="s">
         <v>237</v>
-      </c>
-      <c r="G99" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4328,16 +4328,16 @@
         <v>9</v>
       </c>
       <c r="D100" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E100" t="s">
         <v>225</v>
       </c>
       <c r="F100" t="s">
+        <v>236</v>
+      </c>
+      <c r="G100" t="s">
         <v>237</v>
-      </c>
-      <c r="G100" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4351,16 +4351,16 @@
         <v>9</v>
       </c>
       <c r="D101" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E101" t="s">
         <v>225</v>
       </c>
       <c r="F101" t="s">
+        <v>236</v>
+      </c>
+      <c r="G101" t="s">
         <v>237</v>
-      </c>
-      <c r="G101" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4374,16 +4374,16 @@
         <v>9</v>
       </c>
       <c r="D102" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E102" t="s">
         <v>225</v>
       </c>
       <c r="F102" t="s">
+        <v>236</v>
+      </c>
+      <c r="G102" t="s">
         <v>237</v>
-      </c>
-      <c r="G102" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4397,16 +4397,16 @@
         <v>9</v>
       </c>
       <c r="D103" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E103" t="s">
         <v>225</v>
       </c>
       <c r="F103" t="s">
+        <v>236</v>
+      </c>
+      <c r="G103" t="s">
         <v>237</v>
-      </c>
-      <c r="G103" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4420,16 +4420,16 @@
         <v>9</v>
       </c>
       <c r="D104" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E104" t="s">
         <v>225</v>
       </c>
       <c r="F104" t="s">
+        <v>236</v>
+      </c>
+      <c r="G104" t="s">
         <v>237</v>
-      </c>
-      <c r="G104" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4443,16 +4443,16 @@
         <v>9</v>
       </c>
       <c r="D105" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="E105" t="s">
         <v>225</v>
       </c>
       <c r="F105" t="s">
+        <v>256</v>
+      </c>
+      <c r="G105" t="s">
         <v>257</v>
-      </c>
-      <c r="G105" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4466,16 +4466,16 @@
         <v>9</v>
       </c>
       <c r="D106" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="E106" t="s">
         <v>225</v>
       </c>
       <c r="F106" t="s">
+        <v>256</v>
+      </c>
+      <c r="G106" t="s">
         <v>257</v>
-      </c>
-      <c r="G106" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4489,16 +4489,16 @@
         <v>9</v>
       </c>
       <c r="D107" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="E107" t="s">
         <v>225</v>
       </c>
       <c r="F107" t="s">
+        <v>256</v>
+      </c>
+      <c r="G107" t="s">
         <v>257</v>
-      </c>
-      <c r="G107" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4512,16 +4512,16 @@
         <v>9</v>
       </c>
       <c r="D108" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="E108" t="s">
         <v>225</v>
       </c>
       <c r="F108" t="s">
+        <v>256</v>
+      </c>
+      <c r="G108" t="s">
         <v>257</v>
-      </c>
-      <c r="G108" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4535,16 +4535,16 @@
         <v>9</v>
       </c>
       <c r="D109" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="E109" t="s">
         <v>225</v>
       </c>
       <c r="F109" t="s">
+        <v>256</v>
+      </c>
+      <c r="G109" t="s">
         <v>257</v>
-      </c>
-      <c r="G109" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4558,16 +4558,16 @@
         <v>9</v>
       </c>
       <c r="D110" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="E110" t="s">
         <v>225</v>
       </c>
       <c r="F110" t="s">
+        <v>256</v>
+      </c>
+      <c r="G110" t="s">
         <v>257</v>
-      </c>
-      <c r="G110" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4581,16 +4581,16 @@
         <v>9</v>
       </c>
       <c r="D111" t="s">
-        <v>270</v>
+        <v>224</v>
       </c>
       <c r="E111" t="s">
         <v>225</v>
       </c>
       <c r="F111" t="s">
+        <v>270</v>
+      </c>
+      <c r="G111" t="s">
         <v>271</v>
-      </c>
-      <c r="G111" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4604,16 +4604,16 @@
         <v>9</v>
       </c>
       <c r="D112" t="s">
-        <v>274</v>
+        <v>224</v>
       </c>
       <c r="E112" t="s">
         <v>225</v>
       </c>
       <c r="F112" t="s">
+        <v>274</v>
+      </c>
+      <c r="G112" t="s">
         <v>275</v>
-      </c>
-      <c r="G112" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4627,16 +4627,16 @@
         <v>9</v>
       </c>
       <c r="D113" t="s">
-        <v>278</v>
+        <v>224</v>
       </c>
       <c r="E113" t="s">
         <v>225</v>
       </c>
       <c r="F113" t="s">
+        <v>278</v>
+      </c>
+      <c r="G113" t="s">
         <v>279</v>
-      </c>
-      <c r="G113" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4650,16 +4650,16 @@
         <v>9</v>
       </c>
       <c r="D114" t="s">
-        <v>278</v>
+        <v>224</v>
       </c>
       <c r="E114" t="s">
         <v>225</v>
       </c>
       <c r="F114" t="s">
+        <v>278</v>
+      </c>
+      <c r="G114" t="s">
         <v>279</v>
-      </c>
-      <c r="G114" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4673,16 +4673,16 @@
         <v>9</v>
       </c>
       <c r="D115" t="s">
-        <v>278</v>
+        <v>224</v>
       </c>
       <c r="E115" t="s">
         <v>225</v>
       </c>
       <c r="F115" t="s">
+        <v>278</v>
+      </c>
+      <c r="G115" t="s">
         <v>279</v>
-      </c>
-      <c r="G115" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4696,16 +4696,16 @@
         <v>9</v>
       </c>
       <c r="D116" t="s">
-        <v>278</v>
+        <v>224</v>
       </c>
       <c r="E116" t="s">
         <v>225</v>
       </c>
       <c r="F116" t="s">
+        <v>278</v>
+      </c>
+      <c r="G116" t="s">
         <v>279</v>
-      </c>
-      <c r="G116" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4719,16 +4719,16 @@
         <v>9</v>
       </c>
       <c r="D117" t="s">
-        <v>278</v>
+        <v>224</v>
       </c>
       <c r="E117" t="s">
         <v>225</v>
       </c>
       <c r="F117" t="s">
+        <v>278</v>
+      </c>
+      <c r="G117" t="s">
         <v>279</v>
-      </c>
-      <c r="G117" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4742,16 +4742,16 @@
         <v>9</v>
       </c>
       <c r="D118" t="s">
-        <v>278</v>
+        <v>224</v>
       </c>
       <c r="E118" t="s">
         <v>225</v>
       </c>
       <c r="F118" t="s">
+        <v>278</v>
+      </c>
+      <c r="G118" t="s">
         <v>279</v>
-      </c>
-      <c r="G118" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4765,16 +4765,16 @@
         <v>9</v>
       </c>
       <c r="D119" t="s">
-        <v>278</v>
+        <v>224</v>
       </c>
       <c r="E119" t="s">
         <v>225</v>
       </c>
       <c r="F119" t="s">
+        <v>278</v>
+      </c>
+      <c r="G119" t="s">
         <v>279</v>
-      </c>
-      <c r="G119" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4791,13 +4791,13 @@
         <v>294</v>
       </c>
       <c r="E120" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F120" t="s">
         <v>295</v>
       </c>
       <c r="G120" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4814,13 +4814,13 @@
         <v>294</v>
       </c>
       <c r="E121" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F121" t="s">
         <v>295</v>
       </c>
       <c r="G121" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4837,13 +4837,13 @@
         <v>294</v>
       </c>
       <c r="E122" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F122" t="s">
         <v>295</v>
       </c>
       <c r="G122" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4860,13 +4860,13 @@
         <v>294</v>
       </c>
       <c r="E123" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F123" t="s">
         <v>295</v>
       </c>
       <c r="G123" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4883,13 +4883,13 @@
         <v>294</v>
       </c>
       <c r="E124" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F124" t="s">
         <v>295</v>
       </c>
       <c r="G124" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4906,13 +4906,13 @@
         <v>294</v>
       </c>
       <c r="E125" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F125" t="s">
         <v>295</v>
       </c>
       <c r="G125" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4929,13 +4929,13 @@
         <v>308</v>
       </c>
       <c r="E126" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F126" t="s">
         <v>309</v>
       </c>
       <c r="G126" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4952,13 +4952,13 @@
         <v>308</v>
       </c>
       <c r="E127" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F127" t="s">
         <v>309</v>
       </c>
       <c r="G127" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4975,13 +4975,13 @@
         <v>308</v>
       </c>
       <c r="E128" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F128" t="s">
         <v>309</v>
       </c>
       <c r="G128" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4998,13 +4998,13 @@
         <v>308</v>
       </c>
       <c r="E129" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F129" t="s">
         <v>309</v>
       </c>
       <c r="G129" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -5432,16 +5432,16 @@
         <v>9</v>
       </c>
       <c r="D148" t="s">
-        <v>358</v>
+        <v>318</v>
       </c>
       <c r="E148" t="s">
         <v>319</v>
       </c>
       <c r="F148" t="s">
+        <v>358</v>
+      </c>
+      <c r="G148" t="s">
         <v>359</v>
-      </c>
-      <c r="G148" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5455,16 +5455,16 @@
         <v>9</v>
       </c>
       <c r="D149" t="s">
-        <v>358</v>
+        <v>318</v>
       </c>
       <c r="E149" t="s">
         <v>319</v>
       </c>
       <c r="F149" t="s">
+        <v>358</v>
+      </c>
+      <c r="G149" t="s">
         <v>359</v>
-      </c>
-      <c r="G149" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5478,16 +5478,16 @@
         <v>9</v>
       </c>
       <c r="D150" t="s">
-        <v>358</v>
+        <v>318</v>
       </c>
       <c r="E150" t="s">
         <v>319</v>
       </c>
       <c r="F150" t="s">
+        <v>358</v>
+      </c>
+      <c r="G150" t="s">
         <v>359</v>
-      </c>
-      <c r="G150" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5501,16 +5501,16 @@
         <v>9</v>
       </c>
       <c r="D151" t="s">
-        <v>358</v>
+        <v>318</v>
       </c>
       <c r="E151" t="s">
         <v>319</v>
       </c>
       <c r="F151" t="s">
+        <v>358</v>
+      </c>
+      <c r="G151" t="s">
         <v>359</v>
-      </c>
-      <c r="G151" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5524,16 +5524,16 @@
         <v>9</v>
       </c>
       <c r="D152" t="s">
-        <v>358</v>
+        <v>318</v>
       </c>
       <c r="E152" t="s">
         <v>319</v>
       </c>
       <c r="F152" t="s">
+        <v>358</v>
+      </c>
+      <c r="G152" t="s">
         <v>359</v>
-      </c>
-      <c r="G152" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5547,16 +5547,16 @@
         <v>9</v>
       </c>
       <c r="D153" t="s">
-        <v>358</v>
+        <v>318</v>
       </c>
       <c r="E153" t="s">
         <v>319</v>
       </c>
       <c r="F153" t="s">
+        <v>358</v>
+      </c>
+      <c r="G153" t="s">
         <v>359</v>
-      </c>
-      <c r="G153" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5570,16 +5570,16 @@
         <v>9</v>
       </c>
       <c r="D154" t="s">
-        <v>372</v>
+        <v>318</v>
       </c>
       <c r="E154" t="s">
         <v>319</v>
       </c>
       <c r="F154" t="s">
+        <v>372</v>
+      </c>
+      <c r="G154" t="s">
         <v>373</v>
-      </c>
-      <c r="G154" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5593,16 +5593,16 @@
         <v>9</v>
       </c>
       <c r="D155" t="s">
-        <v>372</v>
+        <v>318</v>
       </c>
       <c r="E155" t="s">
         <v>319</v>
       </c>
       <c r="F155" t="s">
+        <v>372</v>
+      </c>
+      <c r="G155" t="s">
         <v>373</v>
-      </c>
-      <c r="G155" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5616,16 +5616,16 @@
         <v>9</v>
       </c>
       <c r="D156" t="s">
-        <v>372</v>
+        <v>318</v>
       </c>
       <c r="E156" t="s">
         <v>319</v>
       </c>
       <c r="F156" t="s">
+        <v>372</v>
+      </c>
+      <c r="G156" t="s">
         <v>373</v>
-      </c>
-      <c r="G156" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5639,16 +5639,16 @@
         <v>9</v>
       </c>
       <c r="D157" t="s">
-        <v>372</v>
+        <v>318</v>
       </c>
       <c r="E157" t="s">
         <v>319</v>
       </c>
       <c r="F157" t="s">
+        <v>372</v>
+      </c>
+      <c r="G157" t="s">
         <v>373</v>
-      </c>
-      <c r="G157" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5662,16 +5662,16 @@
         <v>9</v>
       </c>
       <c r="D158" t="s">
-        <v>372</v>
+        <v>318</v>
       </c>
       <c r="E158" t="s">
         <v>319</v>
       </c>
       <c r="F158" t="s">
+        <v>372</v>
+      </c>
+      <c r="G158" t="s">
         <v>373</v>
-      </c>
-      <c r="G158" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -6122,16 +6122,16 @@
         <v>9</v>
       </c>
       <c r="D178" t="s">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="E178" t="s">
         <v>385</v>
       </c>
       <c r="F178" t="s">
+        <v>426</v>
+      </c>
+      <c r="G178" t="s">
         <v>427</v>
-      </c>
-      <c r="G178" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -6145,16 +6145,16 @@
         <v>9</v>
       </c>
       <c r="D179" t="s">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="E179" t="s">
         <v>385</v>
       </c>
       <c r="F179" t="s">
+        <v>426</v>
+      </c>
+      <c r="G179" t="s">
         <v>427</v>
-      </c>
-      <c r="G179" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -6168,16 +6168,16 @@
         <v>9</v>
       </c>
       <c r="D180" t="s">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="E180" t="s">
         <v>385</v>
       </c>
       <c r="F180" t="s">
+        <v>426</v>
+      </c>
+      <c r="G180" t="s">
         <v>427</v>
-      </c>
-      <c r="G180" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -6191,16 +6191,16 @@
         <v>9</v>
       </c>
       <c r="D181" t="s">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="E181" t="s">
         <v>385</v>
       </c>
       <c r="F181" t="s">
+        <v>426</v>
+      </c>
+      <c r="G181" t="s">
         <v>427</v>
-      </c>
-      <c r="G181" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -6214,16 +6214,16 @@
         <v>9</v>
       </c>
       <c r="D182" t="s">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="E182" t="s">
         <v>385</v>
       </c>
       <c r="F182" t="s">
+        <v>426</v>
+      </c>
+      <c r="G182" t="s">
         <v>427</v>
-      </c>
-      <c r="G182" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -6237,16 +6237,16 @@
         <v>9</v>
       </c>
       <c r="D183" t="s">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="E183" t="s">
         <v>385</v>
       </c>
       <c r="F183" t="s">
+        <v>426</v>
+      </c>
+      <c r="G183" t="s">
         <v>427</v>
-      </c>
-      <c r="G183" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -6260,16 +6260,16 @@
         <v>9</v>
       </c>
       <c r="D184" t="s">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="E184" t="s">
         <v>385</v>
       </c>
       <c r="F184" t="s">
+        <v>426</v>
+      </c>
+      <c r="G184" t="s">
         <v>427</v>
-      </c>
-      <c r="G184" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -6283,16 +6283,16 @@
         <v>9</v>
       </c>
       <c r="D185" t="s">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="E185" t="s">
         <v>385</v>
       </c>
       <c r="F185" t="s">
+        <v>426</v>
+      </c>
+      <c r="G185" t="s">
         <v>427</v>
-      </c>
-      <c r="G185" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -6306,16 +6306,16 @@
         <v>9</v>
       </c>
       <c r="D186" t="s">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="E186" t="s">
         <v>385</v>
       </c>
       <c r="F186" t="s">
+        <v>426</v>
+      </c>
+      <c r="G186" t="s">
         <v>427</v>
-      </c>
-      <c r="G186" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -6329,16 +6329,16 @@
         <v>9</v>
       </c>
       <c r="D187" t="s">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="E187" t="s">
         <v>385</v>
       </c>
       <c r="F187" t="s">
+        <v>426</v>
+      </c>
+      <c r="G187" t="s">
         <v>427</v>
-      </c>
-      <c r="G187" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -6352,16 +6352,16 @@
         <v>9</v>
       </c>
       <c r="D188" t="s">
-        <v>448</v>
+        <v>384</v>
       </c>
       <c r="E188" t="s">
         <v>385</v>
       </c>
       <c r="F188" t="s">
+        <v>448</v>
+      </c>
+      <c r="G188" t="s">
         <v>449</v>
-      </c>
-      <c r="G188" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -6378,13 +6378,13 @@
         <v>452</v>
       </c>
       <c r="E189" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F189" t="s">
         <v>453</v>
       </c>
       <c r="G189" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6401,13 +6401,13 @@
         <v>452</v>
       </c>
       <c r="E190" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F190" t="s">
         <v>453</v>
       </c>
       <c r="G190" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6424,13 +6424,13 @@
         <v>452</v>
       </c>
       <c r="E191" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F191" t="s">
         <v>453</v>
       </c>
       <c r="G191" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6447,13 +6447,13 @@
         <v>452</v>
       </c>
       <c r="E192" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F192" t="s">
         <v>453</v>
       </c>
       <c r="G192" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6470,13 +6470,13 @@
         <v>452</v>
       </c>
       <c r="E193" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F193" t="s">
         <v>453</v>
       </c>
       <c r="G193" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6493,13 +6493,13 @@
         <v>452</v>
       </c>
       <c r="E194" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F194" t="s">
         <v>453</v>
       </c>
       <c r="G194" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6516,13 +6516,13 @@
         <v>466</v>
       </c>
       <c r="E195" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="F195" t="s">
         <v>467</v>
       </c>
       <c r="G195" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6539,13 +6539,13 @@
         <v>470</v>
       </c>
       <c r="E196" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F196" t="s">
         <v>471</v>
       </c>
       <c r="G196" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6562,13 +6562,13 @@
         <v>470</v>
       </c>
       <c r="E197" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F197" t="s">
         <v>471</v>
       </c>
       <c r="G197" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6585,13 +6585,13 @@
         <v>470</v>
       </c>
       <c r="E198" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F198" t="s">
         <v>471</v>
       </c>
       <c r="G198" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6608,13 +6608,13 @@
         <v>470</v>
       </c>
       <c r="E199" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F199" t="s">
         <v>471</v>
       </c>
       <c r="G199" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6631,13 +6631,13 @@
         <v>470</v>
       </c>
       <c r="E200" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F200" t="s">
         <v>471</v>
       </c>
       <c r="G200" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6654,13 +6654,13 @@
         <v>470</v>
       </c>
       <c r="E201" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F201" t="s">
         <v>471</v>
       </c>
       <c r="G201" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6677,13 +6677,13 @@
         <v>484</v>
       </c>
       <c r="E202" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F202" t="s">
         <v>485</v>
       </c>
       <c r="G202" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6700,13 +6700,13 @@
         <v>484</v>
       </c>
       <c r="E203" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F203" t="s">
         <v>485</v>
       </c>
       <c r="G203" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6723,13 +6723,13 @@
         <v>484</v>
       </c>
       <c r="E204" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F204" t="s">
         <v>485</v>
       </c>
       <c r="G204" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6746,13 +6746,13 @@
         <v>484</v>
       </c>
       <c r="E205" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F205" t="s">
         <v>485</v>
       </c>
       <c r="G205" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6769,13 +6769,13 @@
         <v>484</v>
       </c>
       <c r="E206" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F206" t="s">
         <v>485</v>
       </c>
       <c r="G206" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6792,13 +6792,13 @@
         <v>484</v>
       </c>
       <c r="E207" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F207" t="s">
         <v>485</v>
       </c>
       <c r="G207" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6815,13 +6815,13 @@
         <v>484</v>
       </c>
       <c r="E208" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F208" t="s">
         <v>485</v>
       </c>
       <c r="G208" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6838,13 +6838,13 @@
         <v>484</v>
       </c>
       <c r="E209" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F209" t="s">
         <v>485</v>
       </c>
       <c r="G209" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6861,13 +6861,13 @@
         <v>484</v>
       </c>
       <c r="E210" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F210" t="s">
         <v>485</v>
       </c>
       <c r="G210" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6884,13 +6884,13 @@
         <v>484</v>
       </c>
       <c r="E211" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F211" t="s">
         <v>485</v>
       </c>
       <c r="G211" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6907,13 +6907,13 @@
         <v>506</v>
       </c>
       <c r="E212" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F212" t="s">
         <v>507</v>
       </c>
       <c r="G212" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6930,13 +6930,13 @@
         <v>510</v>
       </c>
       <c r="E213" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F213" t="s">
         <v>511</v>
       </c>
       <c r="G213" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6953,13 +6953,13 @@
         <v>514</v>
       </c>
       <c r="E214" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="F214" t="s">
         <v>515</v>
       </c>
       <c r="G214" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6976,13 +6976,13 @@
         <v>514</v>
       </c>
       <c r="E215" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="F215" t="s">
         <v>515</v>
       </c>
       <c r="G215" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6999,13 +6999,13 @@
         <v>520</v>
       </c>
       <c r="E216" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F216" t="s">
         <v>521</v>
       </c>
       <c r="G216" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -7022,13 +7022,13 @@
         <v>520</v>
       </c>
       <c r="E217" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F217" t="s">
         <v>521</v>
       </c>
       <c r="G217" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -7045,13 +7045,13 @@
         <v>520</v>
       </c>
       <c r="E218" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F218" t="s">
         <v>521</v>
       </c>
       <c r="G218" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -7068,13 +7068,13 @@
         <v>520</v>
       </c>
       <c r="E219" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F219" t="s">
         <v>521</v>
       </c>
       <c r="G219" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -7091,13 +7091,13 @@
         <v>520</v>
       </c>
       <c r="E220" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F220" t="s">
         <v>521</v>
       </c>
       <c r="G220" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -7114,13 +7114,13 @@
         <v>520</v>
       </c>
       <c r="E221" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F221" t="s">
         <v>521</v>
       </c>
       <c r="G221" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -7137,13 +7137,13 @@
         <v>520</v>
       </c>
       <c r="E222" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F222" t="s">
         <v>521</v>
       </c>
       <c r="G222" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -7160,13 +7160,13 @@
         <v>536</v>
       </c>
       <c r="E223" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F223" t="s">
         <v>537</v>
       </c>
       <c r="G223" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -7183,13 +7183,13 @@
         <v>536</v>
       </c>
       <c r="E224" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F224" t="s">
         <v>537</v>
       </c>
       <c r="G224" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -7206,13 +7206,13 @@
         <v>536</v>
       </c>
       <c r="E225" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F225" t="s">
         <v>537</v>
       </c>
       <c r="G225" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -7229,13 +7229,13 @@
         <v>544</v>
       </c>
       <c r="E226" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="F226" t="s">
         <v>545</v>
       </c>
       <c r="G226" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -7252,13 +7252,13 @@
         <v>548</v>
       </c>
       <c r="E227" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="F227" t="s">
         <v>549</v>
       </c>
       <c r="G227" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -7275,13 +7275,13 @@
         <v>552</v>
       </c>
       <c r="E228" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="F228" t="s">
         <v>553</v>
       </c>
       <c r="G228" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -7298,13 +7298,13 @@
         <v>556</v>
       </c>
       <c r="E229" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="F229" t="s">
         <v>557</v>
       </c>
       <c r="G229" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -7321,13 +7321,13 @@
         <v>560</v>
       </c>
       <c r="E230" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F230" t="s">
         <v>561</v>
       </c>
       <c r="G230" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -7344,13 +7344,13 @@
         <v>560</v>
       </c>
       <c r="E231" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F231" t="s">
         <v>561</v>
       </c>
       <c r="G231" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/en/SectorGroup.xlsx
+++ b/api/xlsx/en/SectorGroup.xlsx
@@ -25,18 +25,18 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
-    <t>codeforiati:group-name</t>
+    <t>codeforiati:category-code</t>
   </si>
   <si>
     <t>codeforiati:category-name</t>
   </si>
   <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -46,18 +46,18 @@
     <t>active</t>
   </si>
   <si>
+    <t>Education</t>
+  </si>
+  <si>
     <t>110</t>
   </si>
   <si>
-    <t>Education</t>
+    <t>111</t>
   </si>
   <si>
     <t>Education, Level Unspecified</t>
   </si>
   <si>
-    <t>111</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -82,12 +82,12 @@
     <t>Primary education</t>
   </si>
   <si>
+    <t>112</t>
+  </si>
+  <si>
     <t>Basic Education</t>
   </si>
   <si>
-    <t>112</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -112,12 +112,12 @@
     <t>Secondary education</t>
   </si>
   <si>
+    <t>113</t>
+  </si>
+  <si>
     <t>Secondary Education</t>
   </si>
   <si>
-    <t>113</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
@@ -130,12 +130,12 @@
     <t>Higher education</t>
   </si>
   <si>
+    <t>114</t>
+  </si>
+  <si>
     <t>Post-Secondary Education</t>
   </si>
   <si>
-    <t>114</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -148,18 +148,18 @@
     <t>Health policy and administrative management</t>
   </si>
   <si>
+    <t>Health</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
-    <t>Health</t>
+    <t>121</t>
   </si>
   <si>
     <t>Health, General</t>
   </si>
   <si>
-    <t>121</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -184,12 +184,12 @@
     <t>Basic health care</t>
   </si>
   <si>
+    <t>122</t>
+  </si>
+  <si>
     <t>Basic Health</t>
   </si>
   <si>
-    <t>122</t>
-  </si>
-  <si>
     <t>12230</t>
   </si>
   <si>
@@ -238,12 +238,12 @@
     <t>NCDs control, general</t>
   </si>
   <si>
+    <t>123</t>
+  </si>
+  <si>
     <t>Non-communicable diseases (NCDs)</t>
   </si>
   <si>
-    <t>123</t>
-  </si>
-  <si>
     <t>12320</t>
   </si>
   <si>
@@ -280,12 +280,12 @@
     <t>Population policy and administrative management</t>
   </si>
   <si>
+    <t>Population Policies/Programmes &amp; Reproductive Health</t>
+  </si>
+  <si>
     <t>130</t>
   </si>
   <si>
-    <t>Population Policies/Programmes &amp; Reproductive Health</t>
-  </si>
-  <si>
     <t>13020</t>
   </si>
   <si>
@@ -316,12 +316,12 @@
     <t>Water sector policy and administrative management</t>
   </si>
   <si>
+    <t>Water Supply &amp; Sanitation</t>
+  </si>
+  <si>
     <t>140</t>
   </si>
   <si>
-    <t>Water Supply &amp; Sanitation</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -388,18 +388,18 @@
     <t>Public sector policy and administrative management</t>
   </si>
   <si>
+    <t>Government &amp; Civil Society</t>
+  </si>
+  <si>
     <t>150</t>
   </si>
   <si>
-    <t>Government &amp; Civil Society</t>
+    <t>151</t>
   </si>
   <si>
     <t>Government &amp; Civil Society-general</t>
   </si>
   <si>
-    <t>151</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -496,12 +496,12 @@
     <t>Security system management and reform</t>
   </si>
   <si>
+    <t>152</t>
+  </si>
+  <si>
     <t>Conflict, Peace &amp; Security</t>
   </si>
   <si>
-    <t>152</t>
-  </si>
-  <si>
     <t>15220</t>
   </si>
   <si>
@@ -538,12 +538,12 @@
     <t>Social Protection</t>
   </si>
   <si>
+    <t>Other Social Infrastructure &amp; Services</t>
+  </si>
+  <si>
     <t>160</t>
   </si>
   <si>
-    <t>Other Social Infrastructure &amp; Services</t>
-  </si>
-  <si>
     <t>16020</t>
   </si>
   <si>
@@ -610,12 +610,12 @@
     <t>Transport policy and administrative management</t>
   </si>
   <si>
+    <t>Transport &amp; Storage</t>
+  </si>
+  <si>
     <t>210</t>
   </si>
   <si>
-    <t>Transport &amp; Storage</t>
-  </si>
-  <si>
     <t>21020</t>
   </si>
   <si>
@@ -658,12 +658,12 @@
     <t>Communications policy and administrative management</t>
   </si>
   <si>
+    <t>Communications</t>
+  </si>
+  <si>
     <t>220</t>
   </si>
   <si>
-    <t>Communications</t>
-  </si>
-  <si>
     <t>22020</t>
   </si>
   <si>
@@ -688,18 +688,18 @@
     <t>Energy policy and administrative management</t>
   </si>
   <si>
+    <t>Energy</t>
+  </si>
+  <si>
     <t>230</t>
   </si>
   <si>
-    <t>Energy</t>
+    <t>231</t>
   </si>
   <si>
     <t>Energy Policy</t>
   </si>
   <si>
-    <t>231</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -724,12 +724,12 @@
     <t>Energy generation, renewable sources - multiple technologies</t>
   </si>
   <si>
+    <t>232</t>
+  </si>
+  <si>
     <t>Energy generation, renewable sources</t>
   </si>
   <si>
-    <t>232</t>
-  </si>
-  <si>
     <t>23220</t>
   </si>
   <si>
@@ -784,12 +784,12 @@
     <t>Energy generation, non-renewable sources, unspecified</t>
   </si>
   <si>
+    <t>233</t>
+  </si>
+  <si>
     <t>Energy generation, non-renewable sources</t>
   </si>
   <si>
-    <t>233</t>
-  </si>
-  <si>
     <t>23320</t>
   </si>
   <si>
@@ -826,36 +826,36 @@
     <t>Hybrid energy electric power plants</t>
   </si>
   <si>
+    <t>234</t>
+  </si>
+  <si>
     <t>Hybrid energy plants</t>
   </si>
   <si>
-    <t>234</t>
-  </si>
-  <si>
     <t>23510</t>
   </si>
   <si>
     <t>Nuclear energy electric power plants and nuclear safety</t>
   </si>
   <si>
+    <t>235</t>
+  </si>
+  <si>
     <t>Nuclear energy plants</t>
   </si>
   <si>
-    <t>235</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
     <t>Heat plants</t>
   </si>
   <si>
+    <t>236</t>
+  </si>
+  <si>
     <t>Energy distribution</t>
   </si>
   <si>
-    <t>236</t>
-  </si>
-  <si>
     <t>23620</t>
   </si>
   <si>
@@ -898,12 +898,12 @@
     <t>Financial policy and administrative management</t>
   </si>
   <si>
+    <t>Banking &amp; Financial Services</t>
+  </si>
+  <si>
     <t>240</t>
   </si>
   <si>
-    <t>Banking &amp; Financial Services</t>
-  </si>
-  <si>
     <t>24020</t>
   </si>
   <si>
@@ -940,12 +940,12 @@
     <t>Business policy and administration</t>
   </si>
   <si>
+    <t>Business &amp; Other Services</t>
+  </si>
+  <si>
     <t>250</t>
   </si>
   <si>
-    <t>Business &amp; Other Services</t>
-  </si>
-  <si>
     <t>25020</t>
   </si>
   <si>
@@ -970,18 +970,18 @@
     <t>Agricultural policy and administrative management</t>
   </si>
   <si>
+    <t>Agriculture, Forestry, Fishing</t>
+  </si>
+  <si>
     <t>310</t>
   </si>
   <si>
-    <t>Agriculture, Forestry, Fishing</t>
+    <t>311</t>
   </si>
   <si>
     <t>Agriculture</t>
   </si>
   <si>
-    <t>311</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1090,12 +1090,12 @@
     <t>Forestry policy and administrative management</t>
   </si>
   <si>
+    <t>312</t>
+  </si>
+  <si>
     <t>Forestry</t>
   </si>
   <si>
-    <t>312</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -1132,12 +1132,12 @@
     <t>Fishing policy and administrative management</t>
   </si>
   <si>
+    <t>313</t>
+  </si>
+  <si>
     <t>Fishing</t>
   </si>
   <si>
-    <t>313</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -1168,18 +1168,18 @@
     <t>Industrial policy and administrative management</t>
   </si>
   <si>
+    <t>Industry, Mining, Construction</t>
+  </si>
+  <si>
     <t>320</t>
   </si>
   <si>
-    <t>Industry, Mining, Construction</t>
+    <t>321</t>
   </si>
   <si>
     <t>Industry</t>
   </si>
   <si>
-    <t>321</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1294,12 +1294,12 @@
     <t>Mineral/mining policy and administrative management</t>
   </si>
   <si>
+    <t>322</t>
+  </si>
+  <si>
     <t>Mineral Resources &amp; Mining</t>
   </si>
   <si>
-    <t>322</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -1360,24 +1360,24 @@
     <t>Construction policy and administrative management</t>
   </si>
   <si>
+    <t>323</t>
+  </si>
+  <si>
     <t>Construction</t>
   </si>
   <si>
-    <t>323</t>
-  </si>
-  <si>
     <t>33110</t>
   </si>
   <si>
     <t>Trade policy and administrative management</t>
   </si>
   <si>
+    <t>Trade Policies &amp; Regulations</t>
+  </si>
+  <si>
     <t>331</t>
   </si>
   <si>
-    <t>Trade Policies &amp; Regulations</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1414,24 +1414,24 @@
     <t>Tourism policy and administrative management</t>
   </si>
   <si>
+    <t>Tourism</t>
+  </si>
+  <si>
     <t>332</t>
   </si>
   <si>
-    <t>Tourism</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
     <t>Environmental policy and administrative management</t>
   </si>
   <si>
+    <t>General Environment Protection</t>
+  </si>
+  <si>
     <t>410</t>
   </si>
   <si>
-    <t>General Environment Protection</t>
-  </si>
-  <si>
     <t>41020</t>
   </si>
   <si>
@@ -1468,12 +1468,12 @@
     <t>Multisector aid</t>
   </si>
   <si>
+    <t>Other Multisector</t>
+  </si>
+  <si>
     <t>430</t>
   </si>
   <si>
-    <t>Other Multisector</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -1534,36 +1534,36 @@
     <t>General budget support-related aid</t>
   </si>
   <si>
+    <t>General Budget Support</t>
+  </si>
+  <si>
     <t>510</t>
   </si>
   <si>
-    <t>General Budget Support</t>
-  </si>
-  <si>
     <t>52010</t>
   </si>
   <si>
     <t>Food assistance</t>
   </si>
   <si>
+    <t>Development Food Assistance</t>
+  </si>
+  <si>
     <t>520</t>
   </si>
   <si>
-    <t>Development Food Assistance</t>
-  </si>
-  <si>
     <t>53030</t>
   </si>
   <si>
     <t>Import support (capital goods)</t>
   </si>
   <si>
+    <t>Other Commodity Assistance</t>
+  </si>
+  <si>
     <t>530</t>
   </si>
   <si>
-    <t>Other Commodity Assistance</t>
-  </si>
-  <si>
     <t>53040</t>
   </si>
   <si>
@@ -1576,12 +1576,12 @@
     <t>Action relating to debt</t>
   </si>
   <si>
+    <t>Action Relating to Debt</t>
+  </si>
+  <si>
     <t>600</t>
   </si>
   <si>
-    <t>Action Relating to Debt</t>
-  </si>
-  <si>
     <t>60020</t>
   </si>
   <si>
@@ -1624,12 +1624,12 @@
     <t>Material relief assistance and services</t>
   </si>
   <si>
+    <t>Emergency Response</t>
+  </si>
+  <si>
     <t>720</t>
   </si>
   <si>
-    <t>Emergency Response</t>
-  </si>
-  <si>
     <t>72040</t>
   </si>
   <si>
@@ -1648,58 +1648,58 @@
     <t>Immediate post-emergency reconstruction and rehabilitation</t>
   </si>
   <si>
+    <t>Reconstruction Relief &amp; Rehabilitation</t>
+  </si>
+  <si>
     <t>730</t>
   </si>
   <si>
-    <t>Reconstruction Relief &amp; Rehabilitation</t>
-  </si>
-  <si>
     <t>74020</t>
   </si>
   <si>
     <t>Multi-hazard response preparedness</t>
   </si>
   <si>
+    <t>Disaster Prevention &amp; Preparedness</t>
+  </si>
+  <si>
     <t>740</t>
   </si>
   <si>
-    <t>Disaster Prevention &amp; Preparedness</t>
-  </si>
-  <si>
     <t>91010</t>
   </si>
   <si>
     <t>Administrative costs (non-sector allocable)</t>
   </si>
   <si>
+    <t>Administrative Costs of Donors</t>
+  </si>
+  <si>
     <t>910</t>
   </si>
   <si>
-    <t>Administrative Costs of Donors</t>
-  </si>
-  <si>
     <t>93010</t>
   </si>
   <si>
     <t>Refugees/asylum seekers in donor countries (non-sector allocable)</t>
   </si>
   <si>
+    <t>Refugees in Donor Countries</t>
+  </si>
+  <si>
     <t>930</t>
   </si>
   <si>
-    <t>Refugees in Donor Countries</t>
-  </si>
-  <si>
     <t>99810</t>
   </si>
   <si>
     <t>Sectors not specified</t>
   </si>
   <si>
+    <t>Unallocated / Unspecified</t>
+  </si>
+  <si>
     <t>998</t>
-  </si>
-  <si>
-    <t>Unallocated / Unspecified</t>
   </si>
   <si>
     <t>99820</t>

--- a/api/xlsx/en/SectorGroup.xlsx
+++ b/api/xlsx/en/SectorGroup.xlsx
@@ -25,18 +25,18 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
+    <t>codeforiati:category-name</t>
+  </si>
+  <si>
     <t>codeforiati:group-name</t>
   </si>
   <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
-    <t>codeforiati:category-name</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -46,18 +46,18 @@
     <t>active</t>
   </si>
   <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>Education, Level Unspecified</t>
+  </si>
+  <si>
     <t>Education</t>
   </si>
   <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>Education, Level Unspecified</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -148,18 +148,18 @@
     <t>Health policy and administrative management</t>
   </si>
   <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>Health, General</t>
+  </si>
+  <si>
     <t>Health</t>
   </si>
   <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
-    <t>Health, General</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -280,12 +280,12 @@
     <t>Population policy and administrative management</t>
   </si>
   <si>
+    <t>130</t>
+  </si>
+  <si>
     <t>Population Policies/Programmes &amp; Reproductive Health</t>
   </si>
   <si>
-    <t>130</t>
-  </si>
-  <si>
     <t>13020</t>
   </si>
   <si>
@@ -316,12 +316,12 @@
     <t>Water sector policy and administrative management</t>
   </si>
   <si>
+    <t>140</t>
+  </si>
+  <si>
     <t>Water Supply &amp; Sanitation</t>
   </si>
   <si>
-    <t>140</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -388,18 +388,18 @@
     <t>Public sector policy and administrative management</t>
   </si>
   <si>
+    <t>151</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>Government &amp; Civil Society-general</t>
+  </si>
+  <si>
     <t>Government &amp; Civil Society</t>
   </si>
   <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>151</t>
-  </si>
-  <si>
-    <t>Government &amp; Civil Society-general</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -538,12 +538,12 @@
     <t>Social Protection</t>
   </si>
   <si>
+    <t>160</t>
+  </si>
+  <si>
     <t>Other Social Infrastructure &amp; Services</t>
   </si>
   <si>
-    <t>160</t>
-  </si>
-  <si>
     <t>16020</t>
   </si>
   <si>
@@ -610,12 +610,12 @@
     <t>Transport policy and administrative management</t>
   </si>
   <si>
+    <t>210</t>
+  </si>
+  <si>
     <t>Transport &amp; Storage</t>
   </si>
   <si>
-    <t>210</t>
-  </si>
-  <si>
     <t>21020</t>
   </si>
   <si>
@@ -658,12 +658,12 @@
     <t>Communications policy and administrative management</t>
   </si>
   <si>
+    <t>220</t>
+  </si>
+  <si>
     <t>Communications</t>
   </si>
   <si>
-    <t>220</t>
-  </si>
-  <si>
     <t>22020</t>
   </si>
   <si>
@@ -688,18 +688,18 @@
     <t>Energy policy and administrative management</t>
   </si>
   <si>
+    <t>231</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>Energy Policy</t>
+  </si>
+  <si>
     <t>Energy</t>
   </si>
   <si>
-    <t>230</t>
-  </si>
-  <si>
-    <t>231</t>
-  </si>
-  <si>
-    <t>Energy Policy</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -898,12 +898,12 @@
     <t>Financial policy and administrative management</t>
   </si>
   <si>
+    <t>240</t>
+  </si>
+  <si>
     <t>Banking &amp; Financial Services</t>
   </si>
   <si>
-    <t>240</t>
-  </si>
-  <si>
     <t>24020</t>
   </si>
   <si>
@@ -940,12 +940,12 @@
     <t>Business policy and administration</t>
   </si>
   <si>
+    <t>250</t>
+  </si>
+  <si>
     <t>Business &amp; Other Services</t>
   </si>
   <si>
-    <t>250</t>
-  </si>
-  <si>
     <t>25020</t>
   </si>
   <si>
@@ -970,18 +970,18 @@
     <t>Agricultural policy and administrative management</t>
   </si>
   <si>
+    <t>311</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
     <t>Agriculture, Forestry, Fishing</t>
   </si>
   <si>
-    <t>310</t>
-  </si>
-  <si>
-    <t>311</t>
-  </si>
-  <si>
-    <t>Agriculture</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1168,18 +1168,18 @@
     <t>Industrial policy and administrative management</t>
   </si>
   <si>
+    <t>321</t>
+  </si>
+  <si>
+    <t>320</t>
+  </si>
+  <si>
+    <t>Industry</t>
+  </si>
+  <si>
     <t>Industry, Mining, Construction</t>
   </si>
   <si>
-    <t>320</t>
-  </si>
-  <si>
-    <t>321</t>
-  </si>
-  <si>
-    <t>Industry</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1372,12 +1372,12 @@
     <t>Trade policy and administrative management</t>
   </si>
   <si>
+    <t>331</t>
+  </si>
+  <si>
     <t>Trade Policies &amp; Regulations</t>
   </si>
   <si>
-    <t>331</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1414,24 +1414,24 @@
     <t>Tourism policy and administrative management</t>
   </si>
   <si>
+    <t>332</t>
+  </si>
+  <si>
     <t>Tourism</t>
   </si>
   <si>
-    <t>332</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
     <t>Environmental policy and administrative management</t>
   </si>
   <si>
+    <t>410</t>
+  </si>
+  <si>
     <t>General Environment Protection</t>
   </si>
   <si>
-    <t>410</t>
-  </si>
-  <si>
     <t>41020</t>
   </si>
   <si>
@@ -1468,12 +1468,12 @@
     <t>Multisector aid</t>
   </si>
   <si>
+    <t>430</t>
+  </si>
+  <si>
     <t>Other Multisector</t>
   </si>
   <si>
-    <t>430</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -1534,36 +1534,36 @@
     <t>General budget support-related aid</t>
   </si>
   <si>
+    <t>510</t>
+  </si>
+  <si>
     <t>General Budget Support</t>
   </si>
   <si>
-    <t>510</t>
-  </si>
-  <si>
     <t>52010</t>
   </si>
   <si>
     <t>Food assistance</t>
   </si>
   <si>
+    <t>520</t>
+  </si>
+  <si>
     <t>Development Food Assistance</t>
   </si>
   <si>
-    <t>520</t>
-  </si>
-  <si>
     <t>53030</t>
   </si>
   <si>
     <t>Import support (capital goods)</t>
   </si>
   <si>
+    <t>530</t>
+  </si>
+  <si>
     <t>Other Commodity Assistance</t>
   </si>
   <si>
-    <t>530</t>
-  </si>
-  <si>
     <t>53040</t>
   </si>
   <si>
@@ -1576,12 +1576,12 @@
     <t>Action relating to debt</t>
   </si>
   <si>
+    <t>600</t>
+  </si>
+  <si>
     <t>Action Relating to Debt</t>
   </si>
   <si>
-    <t>600</t>
-  </si>
-  <si>
     <t>60020</t>
   </si>
   <si>
@@ -1624,12 +1624,12 @@
     <t>Material relief assistance and services</t>
   </si>
   <si>
+    <t>720</t>
+  </si>
+  <si>
     <t>Emergency Response</t>
   </si>
   <si>
-    <t>720</t>
-  </si>
-  <si>
     <t>72040</t>
   </si>
   <si>
@@ -1648,58 +1648,58 @@
     <t>Immediate post-emergency reconstruction and rehabilitation</t>
   </si>
   <si>
+    <t>730</t>
+  </si>
+  <si>
     <t>Reconstruction Relief &amp; Rehabilitation</t>
   </si>
   <si>
-    <t>730</t>
-  </si>
-  <si>
     <t>74020</t>
   </si>
   <si>
     <t>Multi-hazard response preparedness</t>
   </si>
   <si>
+    <t>740</t>
+  </si>
+  <si>
     <t>Disaster Prevention &amp; Preparedness</t>
   </si>
   <si>
-    <t>740</t>
-  </si>
-  <si>
     <t>91010</t>
   </si>
   <si>
     <t>Administrative costs (non-sector allocable)</t>
   </si>
   <si>
+    <t>910</t>
+  </si>
+  <si>
     <t>Administrative Costs of Donors</t>
   </si>
   <si>
-    <t>910</t>
-  </si>
-  <si>
     <t>93010</t>
   </si>
   <si>
     <t>Refugees/asylum seekers in donor countries (non-sector allocable)</t>
   </si>
   <si>
+    <t>930</t>
+  </si>
+  <si>
     <t>Refugees in Donor Countries</t>
   </si>
   <si>
-    <t>930</t>
-  </si>
-  <si>
     <t>99810</t>
   </si>
   <si>
     <t>Sectors not specified</t>
   </si>
   <si>
+    <t>998</t>
+  </si>
+  <si>
     <t>Unallocated / Unspecified</t>
-  </si>
-  <si>
-    <t>998</t>
   </si>
   <si>
     <t>99820</t>
@@ -2166,16 +2166,16 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
         <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2189,16 +2189,16 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G7" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2212,16 +2212,16 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E8" t="s">
         <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G8" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2235,16 +2235,16 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G9" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2258,16 +2258,16 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E10" t="s">
         <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G10" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2281,16 +2281,16 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
         <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G11" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2304,16 +2304,16 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E12" t="s">
         <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G12" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2327,16 +2327,16 @@
         <v>9</v>
       </c>
       <c r="D13" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E13" t="s">
         <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G13" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2442,16 +2442,16 @@
         <v>9</v>
       </c>
       <c r="D18" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E18" t="s">
         <v>45</v>
       </c>
       <c r="F18" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G18" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2465,16 +2465,16 @@
         <v>9</v>
       </c>
       <c r="D19" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E19" t="s">
         <v>45</v>
       </c>
       <c r="F19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G19" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2488,16 +2488,16 @@
         <v>9</v>
       </c>
       <c r="D20" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E20" t="s">
         <v>45</v>
       </c>
       <c r="F20" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G20" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2511,16 +2511,16 @@
         <v>9</v>
       </c>
       <c r="D21" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E21" t="s">
         <v>45</v>
       </c>
       <c r="F21" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G21" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2534,16 +2534,16 @@
         <v>9</v>
       </c>
       <c r="D22" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E22" t="s">
         <v>45</v>
       </c>
       <c r="F22" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G22" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2557,16 +2557,16 @@
         <v>9</v>
       </c>
       <c r="D23" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E23" t="s">
         <v>45</v>
       </c>
       <c r="F23" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G23" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2580,16 +2580,16 @@
         <v>9</v>
       </c>
       <c r="D24" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E24" t="s">
         <v>45</v>
       </c>
       <c r="F24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G24" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2603,16 +2603,16 @@
         <v>9</v>
       </c>
       <c r="D25" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E25" t="s">
         <v>45</v>
       </c>
       <c r="F25" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G25" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2626,16 +2626,16 @@
         <v>9</v>
       </c>
       <c r="D26" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E26" t="s">
         <v>45</v>
       </c>
       <c r="F26" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G26" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2649,16 +2649,16 @@
         <v>9</v>
       </c>
       <c r="D27" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E27" t="s">
         <v>45</v>
       </c>
       <c r="F27" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G27" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2672,16 +2672,16 @@
         <v>9</v>
       </c>
       <c r="D28" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E28" t="s">
         <v>45</v>
       </c>
       <c r="F28" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G28" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2695,16 +2695,16 @@
         <v>9</v>
       </c>
       <c r="D29" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E29" t="s">
         <v>45</v>
       </c>
       <c r="F29" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G29" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2718,16 +2718,16 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E30" t="s">
         <v>45</v>
       </c>
       <c r="F30" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G30" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2741,16 +2741,16 @@
         <v>9</v>
       </c>
       <c r="D31" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E31" t="s">
         <v>45</v>
       </c>
       <c r="F31" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G31" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2767,13 +2767,13 @@
         <v>88</v>
       </c>
       <c r="E32" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F32" t="s">
         <v>89</v>
       </c>
       <c r="G32" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2790,13 +2790,13 @@
         <v>88</v>
       </c>
       <c r="E33" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F33" t="s">
         <v>89</v>
       </c>
       <c r="G33" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2813,13 +2813,13 @@
         <v>88</v>
       </c>
       <c r="E34" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F34" t="s">
         <v>89</v>
       </c>
       <c r="G34" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2836,13 +2836,13 @@
         <v>88</v>
       </c>
       <c r="E35" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F35" t="s">
         <v>89</v>
       </c>
       <c r="G35" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2859,13 +2859,13 @@
         <v>88</v>
       </c>
       <c r="E36" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F36" t="s">
         <v>89</v>
       </c>
       <c r="G36" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2882,13 +2882,13 @@
         <v>100</v>
       </c>
       <c r="E37" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F37" t="s">
         <v>101</v>
       </c>
       <c r="G37" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2905,13 +2905,13 @@
         <v>100</v>
       </c>
       <c r="E38" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F38" t="s">
         <v>101</v>
       </c>
       <c r="G38" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2928,13 +2928,13 @@
         <v>100</v>
       </c>
       <c r="E39" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F39" t="s">
         <v>101</v>
       </c>
       <c r="G39" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2951,13 +2951,13 @@
         <v>100</v>
       </c>
       <c r="E40" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F40" t="s">
         <v>101</v>
       </c>
       <c r="G40" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2974,13 +2974,13 @@
         <v>100</v>
       </c>
       <c r="E41" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F41" t="s">
         <v>101</v>
       </c>
       <c r="G41" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2997,13 +2997,13 @@
         <v>100</v>
       </c>
       <c r="E42" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F42" t="s">
         <v>101</v>
       </c>
       <c r="G42" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3020,13 +3020,13 @@
         <v>100</v>
       </c>
       <c r="E43" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F43" t="s">
         <v>101</v>
       </c>
       <c r="G43" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3043,13 +3043,13 @@
         <v>100</v>
       </c>
       <c r="E44" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F44" t="s">
         <v>101</v>
       </c>
       <c r="G44" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3066,13 +3066,13 @@
         <v>100</v>
       </c>
       <c r="E45" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F45" t="s">
         <v>101</v>
       </c>
       <c r="G45" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3089,13 +3089,13 @@
         <v>100</v>
       </c>
       <c r="E46" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F46" t="s">
         <v>101</v>
       </c>
       <c r="G46" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3112,13 +3112,13 @@
         <v>100</v>
       </c>
       <c r="E47" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F47" t="s">
         <v>101</v>
       </c>
       <c r="G47" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3500,16 +3500,16 @@
         <v>9</v>
       </c>
       <c r="D64" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E64" t="s">
         <v>125</v>
       </c>
       <c r="F64" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G64" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3523,16 +3523,16 @@
         <v>9</v>
       </c>
       <c r="D65" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E65" t="s">
         <v>125</v>
       </c>
       <c r="F65" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G65" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3546,16 +3546,16 @@
         <v>9</v>
       </c>
       <c r="D66" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E66" t="s">
         <v>125</v>
       </c>
       <c r="F66" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G66" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3569,16 +3569,16 @@
         <v>9</v>
       </c>
       <c r="D67" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E67" t="s">
         <v>125</v>
       </c>
       <c r="F67" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G67" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3592,16 +3592,16 @@
         <v>9</v>
       </c>
       <c r="D68" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E68" t="s">
         <v>125</v>
       </c>
       <c r="F68" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G68" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3615,16 +3615,16 @@
         <v>9</v>
       </c>
       <c r="D69" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E69" t="s">
         <v>125</v>
       </c>
       <c r="F69" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G69" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3641,13 +3641,13 @@
         <v>174</v>
       </c>
       <c r="E70" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F70" t="s">
         <v>175</v>
       </c>
       <c r="G70" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3664,13 +3664,13 @@
         <v>174</v>
       </c>
       <c r="E71" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F71" t="s">
         <v>175</v>
       </c>
       <c r="G71" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3687,13 +3687,13 @@
         <v>174</v>
       </c>
       <c r="E72" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F72" t="s">
         <v>175</v>
       </c>
       <c r="G72" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3710,13 +3710,13 @@
         <v>174</v>
       </c>
       <c r="E73" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F73" t="s">
         <v>175</v>
       </c>
       <c r="G73" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3733,13 +3733,13 @@
         <v>174</v>
       </c>
       <c r="E74" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F74" t="s">
         <v>175</v>
       </c>
       <c r="G74" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3756,13 +3756,13 @@
         <v>174</v>
       </c>
       <c r="E75" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F75" t="s">
         <v>175</v>
       </c>
       <c r="G75" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3779,13 +3779,13 @@
         <v>174</v>
       </c>
       <c r="E76" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F76" t="s">
         <v>175</v>
       </c>
       <c r="G76" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3802,13 +3802,13 @@
         <v>174</v>
       </c>
       <c r="E77" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F77" t="s">
         <v>175</v>
       </c>
       <c r="G77" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3825,13 +3825,13 @@
         <v>174</v>
       </c>
       <c r="E78" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F78" t="s">
         <v>175</v>
       </c>
       <c r="G78" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3848,13 +3848,13 @@
         <v>174</v>
       </c>
       <c r="E79" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F79" t="s">
         <v>175</v>
       </c>
       <c r="G79" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3871,13 +3871,13 @@
         <v>174</v>
       </c>
       <c r="E80" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F80" t="s">
         <v>175</v>
       </c>
       <c r="G80" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3894,13 +3894,13 @@
         <v>198</v>
       </c>
       <c r="E81" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F81" t="s">
         <v>199</v>
       </c>
       <c r="G81" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3917,13 +3917,13 @@
         <v>198</v>
       </c>
       <c r="E82" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F82" t="s">
         <v>199</v>
       </c>
       <c r="G82" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3940,13 +3940,13 @@
         <v>198</v>
       </c>
       <c r="E83" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F83" t="s">
         <v>199</v>
       </c>
       <c r="G83" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3963,13 +3963,13 @@
         <v>198</v>
       </c>
       <c r="E84" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F84" t="s">
         <v>199</v>
       </c>
       <c r="G84" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3986,13 +3986,13 @@
         <v>198</v>
       </c>
       <c r="E85" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F85" t="s">
         <v>199</v>
       </c>
       <c r="G85" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4009,13 +4009,13 @@
         <v>198</v>
       </c>
       <c r="E86" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F86" t="s">
         <v>199</v>
       </c>
       <c r="G86" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4032,13 +4032,13 @@
         <v>198</v>
       </c>
       <c r="E87" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F87" t="s">
         <v>199</v>
       </c>
       <c r="G87" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4055,13 +4055,13 @@
         <v>214</v>
       </c>
       <c r="E88" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F88" t="s">
         <v>215</v>
       </c>
       <c r="G88" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4078,13 +4078,13 @@
         <v>214</v>
       </c>
       <c r="E89" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F89" t="s">
         <v>215</v>
       </c>
       <c r="G89" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4101,13 +4101,13 @@
         <v>214</v>
       </c>
       <c r="E90" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F90" t="s">
         <v>215</v>
       </c>
       <c r="G90" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4124,13 +4124,13 @@
         <v>214</v>
       </c>
       <c r="E91" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F91" t="s">
         <v>215</v>
       </c>
       <c r="G91" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4236,16 +4236,16 @@
         <v>9</v>
       </c>
       <c r="D96" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E96" t="s">
         <v>225</v>
       </c>
       <c r="F96" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G96" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -4259,16 +4259,16 @@
         <v>9</v>
       </c>
       <c r="D97" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E97" t="s">
         <v>225</v>
       </c>
       <c r="F97" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G97" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4282,16 +4282,16 @@
         <v>9</v>
       </c>
       <c r="D98" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E98" t="s">
         <v>225</v>
       </c>
       <c r="F98" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G98" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4305,16 +4305,16 @@
         <v>9</v>
       </c>
       <c r="D99" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E99" t="s">
         <v>225</v>
       </c>
       <c r="F99" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G99" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4328,16 +4328,16 @@
         <v>9</v>
       </c>
       <c r="D100" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E100" t="s">
         <v>225</v>
       </c>
       <c r="F100" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G100" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4351,16 +4351,16 @@
         <v>9</v>
       </c>
       <c r="D101" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E101" t="s">
         <v>225</v>
       </c>
       <c r="F101" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G101" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4374,16 +4374,16 @@
         <v>9</v>
       </c>
       <c r="D102" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E102" t="s">
         <v>225</v>
       </c>
       <c r="F102" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G102" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4397,16 +4397,16 @@
         <v>9</v>
       </c>
       <c r="D103" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E103" t="s">
         <v>225</v>
       </c>
       <c r="F103" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G103" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4420,16 +4420,16 @@
         <v>9</v>
       </c>
       <c r="D104" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E104" t="s">
         <v>225</v>
       </c>
       <c r="F104" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G104" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4443,16 +4443,16 @@
         <v>9</v>
       </c>
       <c r="D105" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E105" t="s">
         <v>225</v>
       </c>
       <c r="F105" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G105" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4466,16 +4466,16 @@
         <v>9</v>
       </c>
       <c r="D106" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E106" t="s">
         <v>225</v>
       </c>
       <c r="F106" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G106" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4489,16 +4489,16 @@
         <v>9</v>
       </c>
       <c r="D107" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E107" t="s">
         <v>225</v>
       </c>
       <c r="F107" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G107" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4512,16 +4512,16 @@
         <v>9</v>
       </c>
       <c r="D108" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E108" t="s">
         <v>225</v>
       </c>
       <c r="F108" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G108" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4535,16 +4535,16 @@
         <v>9</v>
       </c>
       <c r="D109" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E109" t="s">
         <v>225</v>
       </c>
       <c r="F109" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G109" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4558,16 +4558,16 @@
         <v>9</v>
       </c>
       <c r="D110" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E110" t="s">
         <v>225</v>
       </c>
       <c r="F110" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G110" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4581,16 +4581,16 @@
         <v>9</v>
       </c>
       <c r="D111" t="s">
-        <v>224</v>
+        <v>270</v>
       </c>
       <c r="E111" t="s">
         <v>225</v>
       </c>
       <c r="F111" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="G111" t="s">
-        <v>271</v>
+        <v>227</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4604,16 +4604,16 @@
         <v>9</v>
       </c>
       <c r="D112" t="s">
-        <v>224</v>
+        <v>274</v>
       </c>
       <c r="E112" t="s">
         <v>225</v>
       </c>
       <c r="F112" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G112" t="s">
-        <v>275</v>
+        <v>227</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4627,16 +4627,16 @@
         <v>9</v>
       </c>
       <c r="D113" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E113" t="s">
         <v>225</v>
       </c>
       <c r="F113" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G113" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4650,16 +4650,16 @@
         <v>9</v>
       </c>
       <c r="D114" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E114" t="s">
         <v>225</v>
       </c>
       <c r="F114" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G114" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4673,16 +4673,16 @@
         <v>9</v>
       </c>
       <c r="D115" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E115" t="s">
         <v>225</v>
       </c>
       <c r="F115" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G115" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4696,16 +4696,16 @@
         <v>9</v>
       </c>
       <c r="D116" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E116" t="s">
         <v>225</v>
       </c>
       <c r="F116" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G116" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4719,16 +4719,16 @@
         <v>9</v>
       </c>
       <c r="D117" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E117" t="s">
         <v>225</v>
       </c>
       <c r="F117" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G117" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4742,16 +4742,16 @@
         <v>9</v>
       </c>
       <c r="D118" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E118" t="s">
         <v>225</v>
       </c>
       <c r="F118" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G118" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4765,16 +4765,16 @@
         <v>9</v>
       </c>
       <c r="D119" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="E119" t="s">
         <v>225</v>
       </c>
       <c r="F119" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G119" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4791,13 +4791,13 @@
         <v>294</v>
       </c>
       <c r="E120" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F120" t="s">
         <v>295</v>
       </c>
       <c r="G120" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4814,13 +4814,13 @@
         <v>294</v>
       </c>
       <c r="E121" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F121" t="s">
         <v>295</v>
       </c>
       <c r="G121" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4837,13 +4837,13 @@
         <v>294</v>
       </c>
       <c r="E122" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F122" t="s">
         <v>295</v>
       </c>
       <c r="G122" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4860,13 +4860,13 @@
         <v>294</v>
       </c>
       <c r="E123" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F123" t="s">
         <v>295</v>
       </c>
       <c r="G123" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4883,13 +4883,13 @@
         <v>294</v>
       </c>
       <c r="E124" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F124" t="s">
         <v>295</v>
       </c>
       <c r="G124" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4906,13 +4906,13 @@
         <v>294</v>
       </c>
       <c r="E125" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F125" t="s">
         <v>295</v>
       </c>
       <c r="G125" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4929,13 +4929,13 @@
         <v>308</v>
       </c>
       <c r="E126" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F126" t="s">
         <v>309</v>
       </c>
       <c r="G126" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4952,13 +4952,13 @@
         <v>308</v>
       </c>
       <c r="E127" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F127" t="s">
         <v>309</v>
       </c>
       <c r="G127" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4975,13 +4975,13 @@
         <v>308</v>
       </c>
       <c r="E128" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F128" t="s">
         <v>309</v>
       </c>
       <c r="G128" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4998,13 +4998,13 @@
         <v>308</v>
       </c>
       <c r="E129" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F129" t="s">
         <v>309</v>
       </c>
       <c r="G129" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -5432,16 +5432,16 @@
         <v>9</v>
       </c>
       <c r="D148" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E148" t="s">
         <v>319</v>
       </c>
       <c r="F148" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="G148" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5455,16 +5455,16 @@
         <v>9</v>
       </c>
       <c r="D149" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E149" t="s">
         <v>319</v>
       </c>
       <c r="F149" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="G149" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5478,16 +5478,16 @@
         <v>9</v>
       </c>
       <c r="D150" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E150" t="s">
         <v>319</v>
       </c>
       <c r="F150" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="G150" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5501,16 +5501,16 @@
         <v>9</v>
       </c>
       <c r="D151" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E151" t="s">
         <v>319</v>
       </c>
       <c r="F151" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="G151" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5524,16 +5524,16 @@
         <v>9</v>
       </c>
       <c r="D152" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E152" t="s">
         <v>319</v>
       </c>
       <c r="F152" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="G152" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5547,16 +5547,16 @@
         <v>9</v>
       </c>
       <c r="D153" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="E153" t="s">
         <v>319</v>
       </c>
       <c r="F153" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="G153" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5570,16 +5570,16 @@
         <v>9</v>
       </c>
       <c r="D154" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="E154" t="s">
         <v>319</v>
       </c>
       <c r="F154" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G154" t="s">
-        <v>373</v>
+        <v>321</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5593,16 +5593,16 @@
         <v>9</v>
       </c>
       <c r="D155" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="E155" t="s">
         <v>319</v>
       </c>
       <c r="F155" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G155" t="s">
-        <v>373</v>
+        <v>321</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5616,16 +5616,16 @@
         <v>9</v>
       </c>
       <c r="D156" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="E156" t="s">
         <v>319</v>
       </c>
       <c r="F156" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G156" t="s">
-        <v>373</v>
+        <v>321</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5639,16 +5639,16 @@
         <v>9</v>
       </c>
       <c r="D157" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="E157" t="s">
         <v>319</v>
       </c>
       <c r="F157" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G157" t="s">
-        <v>373</v>
+        <v>321</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5662,16 +5662,16 @@
         <v>9</v>
       </c>
       <c r="D158" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="E158" t="s">
         <v>319</v>
       </c>
       <c r="F158" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G158" t="s">
-        <v>373</v>
+        <v>321</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -6122,16 +6122,16 @@
         <v>9</v>
       </c>
       <c r="D178" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E178" t="s">
         <v>385</v>
       </c>
       <c r="F178" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="G178" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -6145,16 +6145,16 @@
         <v>9</v>
       </c>
       <c r="D179" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E179" t="s">
         <v>385</v>
       </c>
       <c r="F179" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="G179" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -6168,16 +6168,16 @@
         <v>9</v>
       </c>
       <c r="D180" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E180" t="s">
         <v>385</v>
       </c>
       <c r="F180" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="G180" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -6191,16 +6191,16 @@
         <v>9</v>
       </c>
       <c r="D181" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E181" t="s">
         <v>385</v>
       </c>
       <c r="F181" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="G181" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -6214,16 +6214,16 @@
         <v>9</v>
       </c>
       <c r="D182" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E182" t="s">
         <v>385</v>
       </c>
       <c r="F182" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="G182" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -6237,16 +6237,16 @@
         <v>9</v>
       </c>
       <c r="D183" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E183" t="s">
         <v>385</v>
       </c>
       <c r="F183" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="G183" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -6260,16 +6260,16 @@
         <v>9</v>
       </c>
       <c r="D184" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E184" t="s">
         <v>385</v>
       </c>
       <c r="F184" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="G184" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -6283,16 +6283,16 @@
         <v>9</v>
       </c>
       <c r="D185" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E185" t="s">
         <v>385</v>
       </c>
       <c r="F185" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="G185" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -6306,16 +6306,16 @@
         <v>9</v>
       </c>
       <c r="D186" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E186" t="s">
         <v>385</v>
       </c>
       <c r="F186" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="G186" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -6329,16 +6329,16 @@
         <v>9</v>
       </c>
       <c r="D187" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E187" t="s">
         <v>385</v>
       </c>
       <c r="F187" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="G187" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -6352,16 +6352,16 @@
         <v>9</v>
       </c>
       <c r="D188" t="s">
-        <v>384</v>
+        <v>448</v>
       </c>
       <c r="E188" t="s">
         <v>385</v>
       </c>
       <c r="F188" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G188" t="s">
-        <v>449</v>
+        <v>387</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -6378,13 +6378,13 @@
         <v>452</v>
       </c>
       <c r="E189" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F189" t="s">
         <v>453</v>
       </c>
       <c r="G189" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6401,13 +6401,13 @@
         <v>452</v>
       </c>
       <c r="E190" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F190" t="s">
         <v>453</v>
       </c>
       <c r="G190" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6424,13 +6424,13 @@
         <v>452</v>
       </c>
       <c r="E191" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F191" t="s">
         <v>453</v>
       </c>
       <c r="G191" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6447,13 +6447,13 @@
         <v>452</v>
       </c>
       <c r="E192" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F192" t="s">
         <v>453</v>
       </c>
       <c r="G192" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6470,13 +6470,13 @@
         <v>452</v>
       </c>
       <c r="E193" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F193" t="s">
         <v>453</v>
       </c>
       <c r="G193" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6493,13 +6493,13 @@
         <v>452</v>
       </c>
       <c r="E194" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F194" t="s">
         <v>453</v>
       </c>
       <c r="G194" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6516,13 +6516,13 @@
         <v>466</v>
       </c>
       <c r="E195" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F195" t="s">
         <v>467</v>
       </c>
       <c r="G195" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6539,13 +6539,13 @@
         <v>470</v>
       </c>
       <c r="E196" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F196" t="s">
         <v>471</v>
       </c>
       <c r="G196" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6562,13 +6562,13 @@
         <v>470</v>
       </c>
       <c r="E197" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F197" t="s">
         <v>471</v>
       </c>
       <c r="G197" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6585,13 +6585,13 @@
         <v>470</v>
       </c>
       <c r="E198" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F198" t="s">
         <v>471</v>
       </c>
       <c r="G198" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6608,13 +6608,13 @@
         <v>470</v>
       </c>
       <c r="E199" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F199" t="s">
         <v>471</v>
       </c>
       <c r="G199" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6631,13 +6631,13 @@
         <v>470</v>
       </c>
       <c r="E200" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F200" t="s">
         <v>471</v>
       </c>
       <c r="G200" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6654,13 +6654,13 @@
         <v>470</v>
       </c>
       <c r="E201" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F201" t="s">
         <v>471</v>
       </c>
       <c r="G201" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6677,13 +6677,13 @@
         <v>484</v>
       </c>
       <c r="E202" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F202" t="s">
         <v>485</v>
       </c>
       <c r="G202" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6700,13 +6700,13 @@
         <v>484</v>
       </c>
       <c r="E203" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F203" t="s">
         <v>485</v>
       </c>
       <c r="G203" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6723,13 +6723,13 @@
         <v>484</v>
       </c>
       <c r="E204" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F204" t="s">
         <v>485</v>
       </c>
       <c r="G204" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6746,13 +6746,13 @@
         <v>484</v>
       </c>
       <c r="E205" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F205" t="s">
         <v>485</v>
       </c>
       <c r="G205" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6769,13 +6769,13 @@
         <v>484</v>
       </c>
       <c r="E206" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F206" t="s">
         <v>485</v>
       </c>
       <c r="G206" 